--- a/reports/selenium/latest/excel/Automation_Test_Report.xlsx
+++ b/reports/selenium/latest/excel/Automation_Test_Report.xlsx
@@ -3084,7 +3084,7 @@
     <t>Build</t>
   </si>
   <si>
-    <t>2</t>
+    <t>3</t>
   </si>
   <si>
     <t>Branch</t>
@@ -3102,7 +3102,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T06:25:39.605Z</t>
+    <t>2026-08-18T03:44:52.278Z</t>
   </si>
   <si>
     <t>Browser</t>
@@ -3607,7 +3607,7 @@
         <v>14</v>
       </c>
       <c r="F2" s="2">
-        <v>972</v>
+        <v>2692</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>15</v>
@@ -3639,7 +3639,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="2">
-        <v>3048</v>
+        <v>4601</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>15</v>
@@ -3671,7 +3671,7 @@
         <v>14</v>
       </c>
       <c r="F4" s="2">
-        <v>3868</v>
+        <v>1356</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
@@ -3703,7 +3703,7 @@
         <v>14</v>
       </c>
       <c r="F5" s="2">
-        <v>1643</v>
+        <v>3387</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
@@ -3735,7 +3735,7 @@
         <v>14</v>
       </c>
       <c r="F6" s="2">
-        <v>3379</v>
+        <v>3286</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -3767,7 +3767,7 @@
         <v>14</v>
       </c>
       <c r="F7" s="2">
-        <v>3209</v>
+        <v>4231</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -3799,7 +3799,7 @@
         <v>14</v>
       </c>
       <c r="F8" s="2">
-        <v>1710</v>
+        <v>3350</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -3831,7 +3831,7 @@
         <v>14</v>
       </c>
       <c r="F9" s="2">
-        <v>3504</v>
+        <v>1973</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -3863,7 +3863,7 @@
         <v>14</v>
       </c>
       <c r="F10" s="2">
-        <v>2536</v>
+        <v>4613</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
@@ -3895,7 +3895,7 @@
         <v>14</v>
       </c>
       <c r="F11" s="2">
-        <v>2721</v>
+        <v>890</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
@@ -3927,7 +3927,7 @@
         <v>14</v>
       </c>
       <c r="F12" s="2">
-        <v>4294</v>
+        <v>2763</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
@@ -3959,7 +3959,7 @@
         <v>14</v>
       </c>
       <c r="F13" s="2">
-        <v>2044</v>
+        <v>2388</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -3991,7 +3991,7 @@
         <v>14</v>
       </c>
       <c r="F14" s="2">
-        <v>3251</v>
+        <v>3911</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -4023,7 +4023,7 @@
         <v>14</v>
       </c>
       <c r="F15" s="2">
-        <v>4465</v>
+        <v>1980</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -4055,7 +4055,7 @@
         <v>14</v>
       </c>
       <c r="F16" s="2">
-        <v>4326</v>
+        <v>1875</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
@@ -4087,7 +4087,7 @@
         <v>14</v>
       </c>
       <c r="F17" s="2">
-        <v>4547</v>
+        <v>2622</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
@@ -4119,7 +4119,7 @@
         <v>14</v>
       </c>
       <c r="F18" s="2">
-        <v>2974</v>
+        <v>2570</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
@@ -4151,7 +4151,7 @@
         <v>14</v>
       </c>
       <c r="F19" s="2">
-        <v>4563</v>
+        <v>3598</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
@@ -4183,7 +4183,7 @@
         <v>14</v>
       </c>
       <c r="F20" s="2">
-        <v>4052</v>
+        <v>3847</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
@@ -4215,7 +4215,7 @@
         <v>14</v>
       </c>
       <c r="F21" s="2">
-        <v>880</v>
+        <v>4367</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -4247,7 +4247,7 @@
         <v>14</v>
       </c>
       <c r="F22" s="2">
-        <v>804</v>
+        <v>1318</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -4279,7 +4279,7 @@
         <v>14</v>
       </c>
       <c r="F23" s="2">
-        <v>3882</v>
+        <v>1409</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -4311,7 +4311,7 @@
         <v>14</v>
       </c>
       <c r="F24" s="2">
-        <v>1130</v>
+        <v>1203</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -4343,7 +4343,7 @@
         <v>14</v>
       </c>
       <c r="F25" s="2">
-        <v>2251</v>
+        <v>3106</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -4375,7 +4375,7 @@
         <v>14</v>
       </c>
       <c r="F26" s="2">
-        <v>3393</v>
+        <v>1104</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -4407,7 +4407,7 @@
         <v>14</v>
       </c>
       <c r="F27" s="2">
-        <v>4209</v>
+        <v>1675</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>15</v>
@@ -4439,7 +4439,7 @@
         <v>14</v>
       </c>
       <c r="F28" s="2">
-        <v>4346</v>
+        <v>3595</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>15</v>
@@ -4471,7 +4471,7 @@
         <v>14</v>
       </c>
       <c r="F29" s="2">
-        <v>1172</v>
+        <v>2653</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>15</v>
@@ -4503,7 +4503,7 @@
         <v>14</v>
       </c>
       <c r="F30" s="2">
-        <v>3718</v>
+        <v>1579</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>15</v>
@@ -4535,7 +4535,7 @@
         <v>14</v>
       </c>
       <c r="F31" s="2">
-        <v>4751</v>
+        <v>4269</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>15</v>
@@ -4567,7 +4567,7 @@
         <v>14</v>
       </c>
       <c r="F32" s="2">
-        <v>3051</v>
+        <v>1142</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>15</v>
@@ -4599,7 +4599,7 @@
         <v>14</v>
       </c>
       <c r="F33" s="2">
-        <v>2043</v>
+        <v>1938</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>15</v>
@@ -4631,7 +4631,7 @@
         <v>14</v>
       </c>
       <c r="F34" s="2">
-        <v>1987</v>
+        <v>2327</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>15</v>
@@ -4663,7 +4663,7 @@
         <v>14</v>
       </c>
       <c r="F35" s="2">
-        <v>1268</v>
+        <v>3693</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>15</v>
@@ -4695,7 +4695,7 @@
         <v>14</v>
       </c>
       <c r="F36" s="2">
-        <v>4753</v>
+        <v>4594</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>15</v>
@@ -4727,7 +4727,7 @@
         <v>14</v>
       </c>
       <c r="F37" s="2">
-        <v>4552</v>
+        <v>3449</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>15</v>
@@ -4759,7 +4759,7 @@
         <v>14</v>
       </c>
       <c r="F38" s="2">
-        <v>4576</v>
+        <v>2062</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>15</v>
@@ -4791,7 +4791,7 @@
         <v>14</v>
       </c>
       <c r="F39" s="2">
-        <v>1103</v>
+        <v>4573</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>15</v>
@@ -4823,7 +4823,7 @@
         <v>14</v>
       </c>
       <c r="F40" s="2">
-        <v>1539</v>
+        <v>1004</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>15</v>
@@ -4855,7 +4855,7 @@
         <v>14</v>
       </c>
       <c r="F41" s="2">
-        <v>4688</v>
+        <v>4334</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>15</v>
@@ -4887,7 +4887,7 @@
         <v>14</v>
       </c>
       <c r="F42" s="2">
-        <v>1981</v>
+        <v>2407</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>15</v>
@@ -4919,7 +4919,7 @@
         <v>14</v>
       </c>
       <c r="F43" s="2">
-        <v>4029</v>
+        <v>2700</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>15</v>
@@ -4951,7 +4951,7 @@
         <v>14</v>
       </c>
       <c r="F44" s="2">
-        <v>1897</v>
+        <v>2453</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>15</v>
@@ -4983,7 +4983,7 @@
         <v>14</v>
       </c>
       <c r="F45" s="2">
-        <v>2920</v>
+        <v>1727</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>15</v>
@@ -5015,7 +5015,7 @@
         <v>14</v>
       </c>
       <c r="F46" s="2">
-        <v>1800</v>
+        <v>3373</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>15</v>
@@ -5047,7 +5047,7 @@
         <v>14</v>
       </c>
       <c r="F47" s="2">
-        <v>867</v>
+        <v>3117</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>15</v>
@@ -5079,7 +5079,7 @@
         <v>14</v>
       </c>
       <c r="F48" s="2">
-        <v>3655</v>
+        <v>2431</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>15</v>
@@ -5111,7 +5111,7 @@
         <v>14</v>
       </c>
       <c r="F49" s="2">
-        <v>4597</v>
+        <v>2730</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>15</v>
@@ -5143,7 +5143,7 @@
         <v>14</v>
       </c>
       <c r="F50" s="2">
-        <v>4100</v>
+        <v>1464</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>15</v>
@@ -5207,7 +5207,7 @@
         <v>14</v>
       </c>
       <c r="F52" s="2">
-        <v>4689</v>
+        <v>2690</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>15</v>
@@ -5239,7 +5239,7 @@
         <v>14</v>
       </c>
       <c r="F53" s="2">
-        <v>3968</v>
+        <v>3410</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>15</v>
@@ -5271,7 +5271,7 @@
         <v>14</v>
       </c>
       <c r="F54" s="2">
-        <v>3054</v>
+        <v>2755</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>15</v>
@@ -5303,7 +5303,7 @@
         <v>14</v>
       </c>
       <c r="F55" s="2">
-        <v>2806</v>
+        <v>4281</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>15</v>
@@ -5335,7 +5335,7 @@
         <v>14</v>
       </c>
       <c r="F56" s="2">
-        <v>2659</v>
+        <v>2167</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>15</v>
@@ -5367,7 +5367,7 @@
         <v>14</v>
       </c>
       <c r="F57" s="2">
-        <v>972</v>
+        <v>1805</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>15</v>
@@ -5399,7 +5399,7 @@
         <v>14</v>
       </c>
       <c r="F58" s="2">
-        <v>1181</v>
+        <v>1065</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>15</v>
@@ -5431,7 +5431,7 @@
         <v>14</v>
       </c>
       <c r="F59" s="2">
-        <v>4069</v>
+        <v>1165</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>15</v>
@@ -5463,7 +5463,7 @@
         <v>14</v>
       </c>
       <c r="F60" s="2">
-        <v>4310</v>
+        <v>2916</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>15</v>
@@ -5495,7 +5495,7 @@
         <v>14</v>
       </c>
       <c r="F61" s="2">
-        <v>2416</v>
+        <v>3945</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>15</v>
@@ -5527,7 +5527,7 @@
         <v>14</v>
       </c>
       <c r="F62" s="2">
-        <v>4296</v>
+        <v>1074</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>15</v>
@@ -5559,7 +5559,7 @@
         <v>14</v>
       </c>
       <c r="F63" s="2">
-        <v>3893</v>
+        <v>2009</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>15</v>
@@ -5591,7 +5591,7 @@
         <v>14</v>
       </c>
       <c r="F64" s="2">
-        <v>1084</v>
+        <v>1022</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>15</v>
@@ -5623,7 +5623,7 @@
         <v>14</v>
       </c>
       <c r="F65" s="2">
-        <v>3159</v>
+        <v>3274</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>15</v>
@@ -5655,7 +5655,7 @@
         <v>14</v>
       </c>
       <c r="F66" s="2">
-        <v>4382</v>
+        <v>4372</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>15</v>
@@ -5687,7 +5687,7 @@
         <v>14</v>
       </c>
       <c r="F67" s="2">
-        <v>3982</v>
+        <v>3809</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>15</v>
@@ -5719,7 +5719,7 @@
         <v>14</v>
       </c>
       <c r="F68" s="2">
-        <v>2204</v>
+        <v>981</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>15</v>
@@ -5751,7 +5751,7 @@
         <v>14</v>
       </c>
       <c r="F69" s="2">
-        <v>4545</v>
+        <v>3047</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>15</v>
@@ -5783,7 +5783,7 @@
         <v>14</v>
       </c>
       <c r="F70" s="2">
-        <v>821</v>
+        <v>1912</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>15</v>
@@ -5815,7 +5815,7 @@
         <v>14</v>
       </c>
       <c r="F71" s="2">
-        <v>1599</v>
+        <v>2100</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>15</v>
@@ -5847,7 +5847,7 @@
         <v>14</v>
       </c>
       <c r="F72" s="2">
-        <v>4196</v>
+        <v>4709</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>15</v>
@@ -5879,7 +5879,7 @@
         <v>14</v>
       </c>
       <c r="F73" s="2">
-        <v>2692</v>
+        <v>1006</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>15</v>
@@ -5911,7 +5911,7 @@
         <v>14</v>
       </c>
       <c r="F74" s="2">
-        <v>1618</v>
+        <v>3823</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>15</v>
@@ -5943,7 +5943,7 @@
         <v>14</v>
       </c>
       <c r="F75" s="2">
-        <v>1028</v>
+        <v>3679</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>15</v>
@@ -5975,7 +5975,7 @@
         <v>14</v>
       </c>
       <c r="F76" s="2">
-        <v>2322</v>
+        <v>1003</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>15</v>
@@ -6007,7 +6007,7 @@
         <v>14</v>
       </c>
       <c r="F77" s="2">
-        <v>2871</v>
+        <v>4074</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>15</v>
@@ -6039,7 +6039,7 @@
         <v>14</v>
       </c>
       <c r="F78" s="2">
-        <v>1017</v>
+        <v>3906</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>15</v>
@@ -6071,7 +6071,7 @@
         <v>14</v>
       </c>
       <c r="F79" s="2">
-        <v>1761</v>
+        <v>2867</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>15</v>
@@ -6103,7 +6103,7 @@
         <v>14</v>
       </c>
       <c r="F80" s="2">
-        <v>1938</v>
+        <v>3086</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>15</v>
@@ -6135,7 +6135,7 @@
         <v>14</v>
       </c>
       <c r="F81" s="2">
-        <v>2945</v>
+        <v>3610</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>15</v>
@@ -6167,7 +6167,7 @@
         <v>14</v>
       </c>
       <c r="F82" s="2">
-        <v>4264</v>
+        <v>1384</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>15</v>
@@ -6199,7 +6199,7 @@
         <v>14</v>
       </c>
       <c r="F83" s="2">
-        <v>4409</v>
+        <v>4413</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>15</v>
@@ -6231,7 +6231,7 @@
         <v>14</v>
       </c>
       <c r="F84" s="2">
-        <v>4321</v>
+        <v>4273</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>15</v>
@@ -6263,7 +6263,7 @@
         <v>14</v>
       </c>
       <c r="F85" s="2">
-        <v>3862</v>
+        <v>4506</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>15</v>
@@ -6295,7 +6295,7 @@
         <v>14</v>
       </c>
       <c r="F86" s="2">
-        <v>4180</v>
+        <v>2396</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>15</v>
@@ -6327,7 +6327,7 @@
         <v>14</v>
       </c>
       <c r="F87" s="2">
-        <v>2302</v>
+        <v>1747</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>15</v>
@@ -6359,7 +6359,7 @@
         <v>14</v>
       </c>
       <c r="F88" s="2">
-        <v>4748</v>
+        <v>1621</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>15</v>
@@ -6391,7 +6391,7 @@
         <v>14</v>
       </c>
       <c r="F89" s="2">
-        <v>4157</v>
+        <v>1248</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>15</v>
@@ -6423,7 +6423,7 @@
         <v>14</v>
       </c>
       <c r="F90" s="2">
-        <v>3725</v>
+        <v>3114</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>15</v>
@@ -6455,7 +6455,7 @@
         <v>14</v>
       </c>
       <c r="F91" s="2">
-        <v>2199</v>
+        <v>2273</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>15</v>
@@ -6487,7 +6487,7 @@
         <v>14</v>
       </c>
       <c r="F92" s="2">
-        <v>1188</v>
+        <v>3639</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>15</v>
@@ -6519,7 +6519,7 @@
         <v>14</v>
       </c>
       <c r="F93" s="2">
-        <v>1500</v>
+        <v>2151</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>15</v>
@@ -6551,7 +6551,7 @@
         <v>14</v>
       </c>
       <c r="F94" s="2">
-        <v>1986</v>
+        <v>1789</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>15</v>
@@ -6583,7 +6583,7 @@
         <v>14</v>
       </c>
       <c r="F95" s="2">
-        <v>4631</v>
+        <v>3542</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>15</v>
@@ -6615,7 +6615,7 @@
         <v>14</v>
       </c>
       <c r="F96" s="2">
-        <v>2991</v>
+        <v>3907</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>15</v>
@@ -6647,7 +6647,7 @@
         <v>14</v>
       </c>
       <c r="F97" s="2">
-        <v>2745</v>
+        <v>1700</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>15</v>
@@ -6679,7 +6679,7 @@
         <v>14</v>
       </c>
       <c r="F98" s="2">
-        <v>4522</v>
+        <v>3327</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>15</v>
@@ -6711,7 +6711,7 @@
         <v>14</v>
       </c>
       <c r="F99" s="2">
-        <v>4408</v>
+        <v>2620</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>15</v>
@@ -6743,7 +6743,7 @@
         <v>14</v>
       </c>
       <c r="F100" s="2">
-        <v>1146</v>
+        <v>858</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>15</v>
@@ -6775,7 +6775,7 @@
         <v>14</v>
       </c>
       <c r="F101" s="2">
-        <v>3449</v>
+        <v>1514</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>15</v>
@@ -6807,7 +6807,7 @@
         <v>14</v>
       </c>
       <c r="F102" s="2">
-        <v>873</v>
+        <v>1368</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>15</v>
@@ -6839,7 +6839,7 @@
         <v>14</v>
       </c>
       <c r="F103" s="2">
-        <v>3616</v>
+        <v>1934</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>15</v>
@@ -6871,7 +6871,7 @@
         <v>14</v>
       </c>
       <c r="F104" s="2">
-        <v>3594</v>
+        <v>3904</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>15</v>
@@ -6903,7 +6903,7 @@
         <v>14</v>
       </c>
       <c r="F105" s="2">
-        <v>4453</v>
+        <v>4213</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>15</v>
@@ -6935,7 +6935,7 @@
         <v>14</v>
       </c>
       <c r="F106" s="2">
-        <v>1173</v>
+        <v>2350</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>15</v>
@@ -6967,7 +6967,7 @@
         <v>14</v>
       </c>
       <c r="F107" s="2">
-        <v>1820</v>
+        <v>2791</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>15</v>
@@ -6999,7 +6999,7 @@
         <v>14</v>
       </c>
       <c r="F108" s="2">
-        <v>2879</v>
+        <v>3925</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>15</v>
@@ -7031,7 +7031,7 @@
         <v>14</v>
       </c>
       <c r="F109" s="2">
-        <v>3945</v>
+        <v>2431</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>15</v>
@@ -7063,7 +7063,7 @@
         <v>14</v>
       </c>
       <c r="F110" s="2">
-        <v>3436</v>
+        <v>4053</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>15</v>
@@ -7095,7 +7095,7 @@
         <v>14</v>
       </c>
       <c r="F111" s="2">
-        <v>3384</v>
+        <v>1359</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>15</v>
@@ -7127,7 +7127,7 @@
         <v>14</v>
       </c>
       <c r="F112" s="2">
-        <v>4399</v>
+        <v>2191</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>15</v>
@@ -7159,7 +7159,7 @@
         <v>14</v>
       </c>
       <c r="F113" s="2">
-        <v>4783</v>
+        <v>3904</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>15</v>
@@ -7191,7 +7191,7 @@
         <v>14</v>
       </c>
       <c r="F114" s="2">
-        <v>2326</v>
+        <v>4467</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>15</v>
@@ -7223,7 +7223,7 @@
         <v>14</v>
       </c>
       <c r="F115" s="2">
-        <v>2694</v>
+        <v>3973</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>15</v>
@@ -7255,7 +7255,7 @@
         <v>14</v>
       </c>
       <c r="F116" s="2">
-        <v>1800</v>
+        <v>2106</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>15</v>
@@ -7287,7 +7287,7 @@
         <v>14</v>
       </c>
       <c r="F117" s="2">
-        <v>4355</v>
+        <v>1067</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>15</v>
@@ -7319,7 +7319,7 @@
         <v>14</v>
       </c>
       <c r="F118" s="2">
-        <v>1458</v>
+        <v>4544</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>15</v>
@@ -7351,7 +7351,7 @@
         <v>14</v>
       </c>
       <c r="F119" s="2">
-        <v>4342</v>
+        <v>4179</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>15</v>
@@ -7383,7 +7383,7 @@
         <v>14</v>
       </c>
       <c r="F120" s="2">
-        <v>2689</v>
+        <v>1997</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>15</v>
@@ -7415,7 +7415,7 @@
         <v>14</v>
       </c>
       <c r="F121" s="2">
-        <v>883</v>
+        <v>3116</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>15</v>
@@ -7447,7 +7447,7 @@
         <v>14</v>
       </c>
       <c r="F122" s="2">
-        <v>1399</v>
+        <v>4615</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>15</v>
@@ -7479,7 +7479,7 @@
         <v>14</v>
       </c>
       <c r="F123" s="2">
-        <v>3209</v>
+        <v>2361</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>15</v>
@@ -7511,7 +7511,7 @@
         <v>14</v>
       </c>
       <c r="F124" s="2">
-        <v>2931</v>
+        <v>3614</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>15</v>
@@ -7543,7 +7543,7 @@
         <v>14</v>
       </c>
       <c r="F125" s="2">
-        <v>2729</v>
+        <v>1510</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>15</v>
@@ -7575,7 +7575,7 @@
         <v>14</v>
       </c>
       <c r="F126" s="2">
-        <v>4132</v>
+        <v>3429</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>15</v>
@@ -7607,7 +7607,7 @@
         <v>14</v>
       </c>
       <c r="F127" s="2">
-        <v>2167</v>
+        <v>2191</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>15</v>
@@ -7639,7 +7639,7 @@
         <v>14</v>
       </c>
       <c r="F128" s="2">
-        <v>1865</v>
+        <v>1336</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>15</v>
@@ -7671,7 +7671,7 @@
         <v>14</v>
       </c>
       <c r="F129" s="2">
-        <v>2940</v>
+        <v>4385</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>15</v>
@@ -7703,7 +7703,7 @@
         <v>14</v>
       </c>
       <c r="F130" s="2">
-        <v>914</v>
+        <v>1116</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>15</v>
@@ -7735,7 +7735,7 @@
         <v>14</v>
       </c>
       <c r="F131" s="2">
-        <v>4588</v>
+        <v>1343</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>15</v>
@@ -7767,7 +7767,7 @@
         <v>14</v>
       </c>
       <c r="F132" s="2">
-        <v>2490</v>
+        <v>2388</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>15</v>
@@ -7799,7 +7799,7 @@
         <v>14</v>
       </c>
       <c r="F133" s="2">
-        <v>1219</v>
+        <v>1687</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>15</v>
@@ -7831,7 +7831,7 @@
         <v>14</v>
       </c>
       <c r="F134" s="2">
-        <v>2828</v>
+        <v>1916</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>15</v>
@@ -7863,7 +7863,7 @@
         <v>14</v>
       </c>
       <c r="F135" s="2">
-        <v>1678</v>
+        <v>1045</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>15</v>
@@ -7895,7 +7895,7 @@
         <v>14</v>
       </c>
       <c r="F136" s="2">
-        <v>3015</v>
+        <v>1834</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>15</v>
@@ -7927,7 +7927,7 @@
         <v>14</v>
       </c>
       <c r="F137" s="2">
-        <v>4046</v>
+        <v>4626</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>15</v>
@@ -7959,7 +7959,7 @@
         <v>14</v>
       </c>
       <c r="F138" s="2">
-        <v>3317</v>
+        <v>3829</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>15</v>
@@ -7991,7 +7991,7 @@
         <v>14</v>
       </c>
       <c r="F139" s="2">
-        <v>4790</v>
+        <v>3782</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>15</v>
@@ -8023,7 +8023,7 @@
         <v>14</v>
       </c>
       <c r="F140" s="2">
-        <v>4721</v>
+        <v>2941</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>15</v>
@@ -8055,7 +8055,7 @@
         <v>14</v>
       </c>
       <c r="F141" s="2">
-        <v>1968</v>
+        <v>4337</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>15</v>
@@ -8087,7 +8087,7 @@
         <v>14</v>
       </c>
       <c r="F142" s="2">
-        <v>3494</v>
+        <v>4740</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>15</v>
@@ -8119,7 +8119,7 @@
         <v>14</v>
       </c>
       <c r="F143" s="2">
-        <v>3265</v>
+        <v>1650</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>15</v>
@@ -8151,7 +8151,7 @@
         <v>14</v>
       </c>
       <c r="F144" s="2">
-        <v>3786</v>
+        <v>1862</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>15</v>
@@ -8183,7 +8183,7 @@
         <v>14</v>
       </c>
       <c r="F145" s="2">
-        <v>3672</v>
+        <v>4158</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>15</v>
@@ -8215,7 +8215,7 @@
         <v>14</v>
       </c>
       <c r="F146" s="2">
-        <v>2508</v>
+        <v>2614</v>
       </c>
       <c r="G146" s="2" t="s">
         <v>15</v>
@@ -8247,7 +8247,7 @@
         <v>14</v>
       </c>
       <c r="F147" s="2">
-        <v>3265</v>
+        <v>3863</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>15</v>
@@ -8279,7 +8279,7 @@
         <v>14</v>
       </c>
       <c r="F148" s="2">
-        <v>1599</v>
+        <v>4648</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>15</v>
@@ -8311,7 +8311,7 @@
         <v>14</v>
       </c>
       <c r="F149" s="2">
-        <v>1700</v>
+        <v>3974</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>15</v>
@@ -8343,7 +8343,7 @@
         <v>14</v>
       </c>
       <c r="F150" s="2">
-        <v>2081</v>
+        <v>3559</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>15</v>
@@ -8375,7 +8375,7 @@
         <v>14</v>
       </c>
       <c r="F151" s="2">
-        <v>2706</v>
+        <v>3201</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>15</v>
@@ -8407,7 +8407,7 @@
         <v>14</v>
       </c>
       <c r="F152" s="2">
-        <v>3004</v>
+        <v>4316</v>
       </c>
       <c r="G152" s="2" t="s">
         <v>15</v>
@@ -8439,7 +8439,7 @@
         <v>14</v>
       </c>
       <c r="F153" s="2">
-        <v>3173</v>
+        <v>2766</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>15</v>
@@ -8471,7 +8471,7 @@
         <v>14</v>
       </c>
       <c r="F154" s="2">
-        <v>1396</v>
+        <v>4419</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>15</v>
@@ -8503,7 +8503,7 @@
         <v>14</v>
       </c>
       <c r="F155" s="2">
-        <v>3670</v>
+        <v>1699</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>15</v>
@@ -8535,7 +8535,7 @@
         <v>14</v>
       </c>
       <c r="F156" s="2">
-        <v>3084</v>
+        <v>4777</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>15</v>
@@ -8567,7 +8567,7 @@
         <v>14</v>
       </c>
       <c r="F157" s="2">
-        <v>1010</v>
+        <v>3250</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>15</v>
@@ -8599,7 +8599,7 @@
         <v>14</v>
       </c>
       <c r="F158" s="2">
-        <v>2072</v>
+        <v>4464</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>15</v>
@@ -8631,7 +8631,7 @@
         <v>14</v>
       </c>
       <c r="F159" s="2">
-        <v>4495</v>
+        <v>1546</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>15</v>
@@ -8663,7 +8663,7 @@
         <v>14</v>
       </c>
       <c r="F160" s="2">
-        <v>1751</v>
+        <v>3618</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>15</v>
@@ -8695,7 +8695,7 @@
         <v>14</v>
       </c>
       <c r="F161" s="2">
-        <v>4149</v>
+        <v>1266</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>15</v>
@@ -8727,7 +8727,7 @@
         <v>14</v>
       </c>
       <c r="F162" s="2">
-        <v>4541</v>
+        <v>1759</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>15</v>
@@ -8759,7 +8759,7 @@
         <v>14</v>
       </c>
       <c r="F163" s="2">
-        <v>3099</v>
+        <v>2375</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>15</v>
@@ -8791,7 +8791,7 @@
         <v>14</v>
       </c>
       <c r="F164" s="2">
-        <v>3547</v>
+        <v>1108</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>15</v>
@@ -8823,7 +8823,7 @@
         <v>14</v>
       </c>
       <c r="F165" s="2">
-        <v>3705</v>
+        <v>2463</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>15</v>
@@ -8855,7 +8855,7 @@
         <v>14</v>
       </c>
       <c r="F166" s="2">
-        <v>3526</v>
+        <v>3730</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>15</v>
@@ -8887,7 +8887,7 @@
         <v>14</v>
       </c>
       <c r="F167" s="2">
-        <v>4026</v>
+        <v>3596</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>15</v>
@@ -8919,7 +8919,7 @@
         <v>14</v>
       </c>
       <c r="F168" s="2">
-        <v>4223</v>
+        <v>4321</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>15</v>
@@ -8951,7 +8951,7 @@
         <v>14</v>
       </c>
       <c r="F169" s="2">
-        <v>1563</v>
+        <v>4161</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>15</v>
@@ -8983,7 +8983,7 @@
         <v>14</v>
       </c>
       <c r="F170" s="2">
-        <v>1385</v>
+        <v>3239</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>15</v>
@@ -9015,7 +9015,7 @@
         <v>14</v>
       </c>
       <c r="F171" s="2">
-        <v>1975</v>
+        <v>3517</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>15</v>
@@ -9047,7 +9047,7 @@
         <v>14</v>
       </c>
       <c r="F172" s="2">
-        <v>919</v>
+        <v>2872</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>15</v>
@@ -9079,7 +9079,7 @@
         <v>14</v>
       </c>
       <c r="F173" s="2">
-        <v>3230</v>
+        <v>1947</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>15</v>
@@ -9111,7 +9111,7 @@
         <v>14</v>
       </c>
       <c r="F174" s="2">
-        <v>2653</v>
+        <v>3543</v>
       </c>
       <c r="G174" s="2" t="s">
         <v>15</v>
@@ -9143,7 +9143,7 @@
         <v>14</v>
       </c>
       <c r="F175" s="2">
-        <v>2019</v>
+        <v>1800</v>
       </c>
       <c r="G175" s="2" t="s">
         <v>15</v>
@@ -9175,7 +9175,7 @@
         <v>14</v>
       </c>
       <c r="F176" s="2">
-        <v>1502</v>
+        <v>4725</v>
       </c>
       <c r="G176" s="2" t="s">
         <v>15</v>
@@ -9207,7 +9207,7 @@
         <v>14</v>
       </c>
       <c r="F177" s="2">
-        <v>4096</v>
+        <v>2567</v>
       </c>
       <c r="G177" s="2" t="s">
         <v>15</v>
@@ -9239,7 +9239,7 @@
         <v>14</v>
       </c>
       <c r="F178" s="2">
-        <v>2706</v>
+        <v>3782</v>
       </c>
       <c r="G178" s="2" t="s">
         <v>15</v>
@@ -9271,7 +9271,7 @@
         <v>14</v>
       </c>
       <c r="F179" s="2">
-        <v>4432</v>
+        <v>3176</v>
       </c>
       <c r="G179" s="2" t="s">
         <v>15</v>
@@ -9303,7 +9303,7 @@
         <v>14</v>
       </c>
       <c r="F180" s="2">
-        <v>4355</v>
+        <v>3771</v>
       </c>
       <c r="G180" s="2" t="s">
         <v>15</v>
@@ -9335,7 +9335,7 @@
         <v>14</v>
       </c>
       <c r="F181" s="2">
-        <v>3426</v>
+        <v>2593</v>
       </c>
       <c r="G181" s="2" t="s">
         <v>15</v>
@@ -9367,7 +9367,7 @@
         <v>14</v>
       </c>
       <c r="F182" s="2">
-        <v>4487</v>
+        <v>2745</v>
       </c>
       <c r="G182" s="2" t="s">
         <v>15</v>
@@ -9399,7 +9399,7 @@
         <v>14</v>
       </c>
       <c r="F183" s="2">
-        <v>4336</v>
+        <v>1436</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>15</v>
@@ -9431,7 +9431,7 @@
         <v>14</v>
       </c>
       <c r="F184" s="2">
-        <v>1126</v>
+        <v>3323</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>15</v>
@@ -9463,7 +9463,7 @@
         <v>14</v>
       </c>
       <c r="F185" s="2">
-        <v>4708</v>
+        <v>3734</v>
       </c>
       <c r="G185" s="2" t="s">
         <v>15</v>
@@ -9495,7 +9495,7 @@
         <v>14</v>
       </c>
       <c r="F186" s="2">
-        <v>3700</v>
+        <v>3845</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>15</v>
@@ -9527,7 +9527,7 @@
         <v>14</v>
       </c>
       <c r="F187" s="2">
-        <v>3117</v>
+        <v>4516</v>
       </c>
       <c r="G187" s="2" t="s">
         <v>15</v>
@@ -9559,7 +9559,7 @@
         <v>14</v>
       </c>
       <c r="F188" s="2">
-        <v>1632</v>
+        <v>1023</v>
       </c>
       <c r="G188" s="2" t="s">
         <v>15</v>
@@ -9591,7 +9591,7 @@
         <v>14</v>
       </c>
       <c r="F189" s="2">
-        <v>2446</v>
+        <v>3499</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>15</v>
@@ -9623,7 +9623,7 @@
         <v>14</v>
       </c>
       <c r="F190" s="2">
-        <v>1330</v>
+        <v>1543</v>
       </c>
       <c r="G190" s="2" t="s">
         <v>15</v>
@@ -9655,7 +9655,7 @@
         <v>14</v>
       </c>
       <c r="F191" s="2">
-        <v>4109</v>
+        <v>1925</v>
       </c>
       <c r="G191" s="2" t="s">
         <v>15</v>
@@ -9687,7 +9687,7 @@
         <v>14</v>
       </c>
       <c r="F192" s="2">
-        <v>3115</v>
+        <v>1174</v>
       </c>
       <c r="G192" s="2" t="s">
         <v>15</v>
@@ -9719,7 +9719,7 @@
         <v>14</v>
       </c>
       <c r="F193" s="2">
-        <v>1239</v>
+        <v>2680</v>
       </c>
       <c r="G193" s="2" t="s">
         <v>15</v>
@@ -9751,7 +9751,7 @@
         <v>14</v>
       </c>
       <c r="F194" s="2">
-        <v>4192</v>
+        <v>854</v>
       </c>
       <c r="G194" s="2" t="s">
         <v>15</v>
@@ -9783,7 +9783,7 @@
         <v>14</v>
       </c>
       <c r="F195" s="2">
-        <v>2276</v>
+        <v>3663</v>
       </c>
       <c r="G195" s="2" t="s">
         <v>15</v>
@@ -9815,7 +9815,7 @@
         <v>14</v>
       </c>
       <c r="F196" s="2">
-        <v>978</v>
+        <v>1324</v>
       </c>
       <c r="G196" s="2" t="s">
         <v>15</v>
@@ -9847,7 +9847,7 @@
         <v>14</v>
       </c>
       <c r="F197" s="2">
-        <v>3598</v>
+        <v>2513</v>
       </c>
       <c r="G197" s="2" t="s">
         <v>15</v>
@@ -9879,7 +9879,7 @@
         <v>14</v>
       </c>
       <c r="F198" s="2">
-        <v>1694</v>
+        <v>3722</v>
       </c>
       <c r="G198" s="2" t="s">
         <v>15</v>
@@ -9911,7 +9911,7 @@
         <v>14</v>
       </c>
       <c r="F199" s="2">
-        <v>4429</v>
+        <v>3878</v>
       </c>
       <c r="G199" s="2" t="s">
         <v>15</v>
@@ -9943,7 +9943,7 @@
         <v>14</v>
       </c>
       <c r="F200" s="2">
-        <v>4607</v>
+        <v>1939</v>
       </c>
       <c r="G200" s="2" t="s">
         <v>15</v>
@@ -9975,7 +9975,7 @@
         <v>14</v>
       </c>
       <c r="F201" s="2">
-        <v>3575</v>
+        <v>4494</v>
       </c>
       <c r="G201" s="2" t="s">
         <v>15</v>
@@ -10007,7 +10007,7 @@
         <v>14</v>
       </c>
       <c r="F202" s="2">
-        <v>1079</v>
+        <v>4122</v>
       </c>
       <c r="G202" s="2" t="s">
         <v>15</v>
@@ -10039,7 +10039,7 @@
         <v>14</v>
       </c>
       <c r="F203" s="2">
-        <v>4149</v>
+        <v>3935</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>15</v>
@@ -10071,7 +10071,7 @@
         <v>14</v>
       </c>
       <c r="F204" s="2">
-        <v>4012</v>
+        <v>4672</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>15</v>
@@ -10103,7 +10103,7 @@
         <v>14</v>
       </c>
       <c r="F205" s="2">
-        <v>1046</v>
+        <v>3684</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>15</v>
@@ -10135,7 +10135,7 @@
         <v>14</v>
       </c>
       <c r="F206" s="2">
-        <v>2844</v>
+        <v>1774</v>
       </c>
       <c r="G206" s="2" t="s">
         <v>15</v>
@@ -10167,7 +10167,7 @@
         <v>14</v>
       </c>
       <c r="F207" s="2">
-        <v>2232</v>
+        <v>3742</v>
       </c>
       <c r="G207" s="2" t="s">
         <v>15</v>
@@ -10199,7 +10199,7 @@
         <v>14</v>
       </c>
       <c r="F208" s="2">
-        <v>4752</v>
+        <v>1896</v>
       </c>
       <c r="G208" s="2" t="s">
         <v>15</v>
@@ -10231,7 +10231,7 @@
         <v>14</v>
       </c>
       <c r="F209" s="2">
-        <v>4046</v>
+        <v>2196</v>
       </c>
       <c r="G209" s="2" t="s">
         <v>15</v>
@@ -10263,7 +10263,7 @@
         <v>14</v>
       </c>
       <c r="F210" s="2">
-        <v>2823</v>
+        <v>1002</v>
       </c>
       <c r="G210" s="2" t="s">
         <v>15</v>
@@ -10295,7 +10295,7 @@
         <v>14</v>
       </c>
       <c r="F211" s="2">
-        <v>4394</v>
+        <v>2066</v>
       </c>
       <c r="G211" s="2" t="s">
         <v>15</v>
@@ -10327,7 +10327,7 @@
         <v>14</v>
       </c>
       <c r="F212" s="2">
-        <v>3980</v>
+        <v>2476</v>
       </c>
       <c r="G212" s="2" t="s">
         <v>15</v>
@@ -10359,7 +10359,7 @@
         <v>14</v>
       </c>
       <c r="F213" s="2">
-        <v>3018</v>
+        <v>3351</v>
       </c>
       <c r="G213" s="2" t="s">
         <v>15</v>
@@ -10391,7 +10391,7 @@
         <v>14</v>
       </c>
       <c r="F214" s="2">
-        <v>1232</v>
+        <v>869</v>
       </c>
       <c r="G214" s="2" t="s">
         <v>15</v>
@@ -10423,7 +10423,7 @@
         <v>14</v>
       </c>
       <c r="F215" s="2">
-        <v>4731</v>
+        <v>3910</v>
       </c>
       <c r="G215" s="2" t="s">
         <v>15</v>
@@ -10455,7 +10455,7 @@
         <v>14</v>
       </c>
       <c r="F216" s="2">
-        <v>1352</v>
+        <v>3502</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>15</v>
@@ -10487,7 +10487,7 @@
         <v>14</v>
       </c>
       <c r="F217" s="2">
-        <v>3507</v>
+        <v>4506</v>
       </c>
       <c r="G217" s="2" t="s">
         <v>15</v>
@@ -10519,7 +10519,7 @@
         <v>14</v>
       </c>
       <c r="F218" s="2">
-        <v>4241</v>
+        <v>4200</v>
       </c>
       <c r="G218" s="2" t="s">
         <v>15</v>
@@ -10551,7 +10551,7 @@
         <v>14</v>
       </c>
       <c r="F219" s="2">
-        <v>2143</v>
+        <v>1805</v>
       </c>
       <c r="G219" s="2" t="s">
         <v>15</v>
@@ -10583,7 +10583,7 @@
         <v>14</v>
       </c>
       <c r="F220" s="2">
-        <v>3703</v>
+        <v>1647</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>15</v>
@@ -10615,7 +10615,7 @@
         <v>14</v>
       </c>
       <c r="F221" s="2">
-        <v>3073</v>
+        <v>1148</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>15</v>
@@ -10647,7 +10647,7 @@
         <v>14</v>
       </c>
       <c r="F222" s="2">
-        <v>1351</v>
+        <v>1008</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>15</v>
@@ -10679,7 +10679,7 @@
         <v>14</v>
       </c>
       <c r="F223" s="2">
-        <v>3568</v>
+        <v>4272</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>15</v>
@@ -10711,7 +10711,7 @@
         <v>14</v>
       </c>
       <c r="F224" s="2">
-        <v>1180</v>
+        <v>931</v>
       </c>
       <c r="G224" s="2" t="s">
         <v>15</v>
@@ -10743,7 +10743,7 @@
         <v>14</v>
       </c>
       <c r="F225" s="2">
-        <v>2351</v>
+        <v>4249</v>
       </c>
       <c r="G225" s="2" t="s">
         <v>15</v>
@@ -10775,7 +10775,7 @@
         <v>14</v>
       </c>
       <c r="F226" s="2">
-        <v>1179</v>
+        <v>1584</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>15</v>
@@ -10807,7 +10807,7 @@
         <v>14</v>
       </c>
       <c r="F227" s="2">
-        <v>3774</v>
+        <v>4569</v>
       </c>
       <c r="G227" s="2" t="s">
         <v>15</v>
@@ -10839,7 +10839,7 @@
         <v>14</v>
       </c>
       <c r="F228" s="2">
-        <v>969</v>
+        <v>2409</v>
       </c>
       <c r="G228" s="2" t="s">
         <v>15</v>
@@ -10871,7 +10871,7 @@
         <v>14</v>
       </c>
       <c r="F229" s="2">
-        <v>3025</v>
+        <v>2840</v>
       </c>
       <c r="G229" s="2" t="s">
         <v>15</v>
@@ -10903,7 +10903,7 @@
         <v>14</v>
       </c>
       <c r="F230" s="2">
-        <v>3053</v>
+        <v>1109</v>
       </c>
       <c r="G230" s="2" t="s">
         <v>15</v>
@@ -10935,7 +10935,7 @@
         <v>14</v>
       </c>
       <c r="F231" s="2">
-        <v>2652</v>
+        <v>2993</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>15</v>
@@ -10967,7 +10967,7 @@
         <v>14</v>
       </c>
       <c r="F232" s="2">
-        <v>1938</v>
+        <v>1900</v>
       </c>
       <c r="G232" s="2" t="s">
         <v>15</v>
@@ -10999,7 +10999,7 @@
         <v>14</v>
       </c>
       <c r="F233" s="2">
-        <v>4519</v>
+        <v>1549</v>
       </c>
       <c r="G233" s="2" t="s">
         <v>15</v>
@@ -11031,7 +11031,7 @@
         <v>14</v>
       </c>
       <c r="F234" s="2">
-        <v>3758</v>
+        <v>4690</v>
       </c>
       <c r="G234" s="2" t="s">
         <v>15</v>
@@ -11063,7 +11063,7 @@
         <v>14</v>
       </c>
       <c r="F235" s="2">
-        <v>3105</v>
+        <v>1555</v>
       </c>
       <c r="G235" s="2" t="s">
         <v>15</v>
@@ -11095,7 +11095,7 @@
         <v>14</v>
       </c>
       <c r="F236" s="2">
-        <v>3707</v>
+        <v>3504</v>
       </c>
       <c r="G236" s="2" t="s">
         <v>15</v>
@@ -11127,7 +11127,7 @@
         <v>14</v>
       </c>
       <c r="F237" s="2">
-        <v>2830</v>
+        <v>2531</v>
       </c>
       <c r="G237" s="2" t="s">
         <v>15</v>
@@ -11159,7 +11159,7 @@
         <v>14</v>
       </c>
       <c r="F238" s="2">
-        <v>4258</v>
+        <v>1428</v>
       </c>
       <c r="G238" s="2" t="s">
         <v>15</v>
@@ -11191,7 +11191,7 @@
         <v>14</v>
       </c>
       <c r="F239" s="2">
-        <v>3948</v>
+        <v>2708</v>
       </c>
       <c r="G239" s="2" t="s">
         <v>15</v>
@@ -11223,7 +11223,7 @@
         <v>14</v>
       </c>
       <c r="F240" s="2">
-        <v>3954</v>
+        <v>2986</v>
       </c>
       <c r="G240" s="2" t="s">
         <v>15</v>
@@ -11255,7 +11255,7 @@
         <v>14</v>
       </c>
       <c r="F241" s="2">
-        <v>1090</v>
+        <v>3260</v>
       </c>
       <c r="G241" s="2" t="s">
         <v>15</v>
@@ -11287,7 +11287,7 @@
         <v>14</v>
       </c>
       <c r="F242" s="2">
-        <v>2608</v>
+        <v>4509</v>
       </c>
       <c r="G242" s="2" t="s">
         <v>15</v>
@@ -11319,7 +11319,7 @@
         <v>14</v>
       </c>
       <c r="F243" s="2">
-        <v>1295</v>
+        <v>3649</v>
       </c>
       <c r="G243" s="2" t="s">
         <v>15</v>
@@ -11351,7 +11351,7 @@
         <v>14</v>
       </c>
       <c r="F244" s="2">
-        <v>831</v>
+        <v>2814</v>
       </c>
       <c r="G244" s="2" t="s">
         <v>15</v>
@@ -11383,7 +11383,7 @@
         <v>14</v>
       </c>
       <c r="F245" s="2">
-        <v>1126</v>
+        <v>3050</v>
       </c>
       <c r="G245" s="2" t="s">
         <v>15</v>
@@ -11415,7 +11415,7 @@
         <v>14</v>
       </c>
       <c r="F246" s="2">
-        <v>3178</v>
+        <v>3066</v>
       </c>
       <c r="G246" s="2" t="s">
         <v>15</v>
@@ -11447,7 +11447,7 @@
         <v>14</v>
       </c>
       <c r="F247" s="2">
-        <v>1994</v>
+        <v>3630</v>
       </c>
       <c r="G247" s="2" t="s">
         <v>15</v>
@@ -11479,7 +11479,7 @@
         <v>14</v>
       </c>
       <c r="F248" s="2">
-        <v>1550</v>
+        <v>1226</v>
       </c>
       <c r="G248" s="2" t="s">
         <v>15</v>
@@ -11511,7 +11511,7 @@
         <v>14</v>
       </c>
       <c r="F249" s="2">
-        <v>2061</v>
+        <v>1591</v>
       </c>
       <c r="G249" s="2" t="s">
         <v>15</v>
@@ -11543,7 +11543,7 @@
         <v>14</v>
       </c>
       <c r="F250" s="2">
-        <v>3678</v>
+        <v>4377</v>
       </c>
       <c r="G250" s="2" t="s">
         <v>15</v>
@@ -11575,7 +11575,7 @@
         <v>14</v>
       </c>
       <c r="F251" s="2">
-        <v>1566</v>
+        <v>952</v>
       </c>
       <c r="G251" s="2" t="s">
         <v>15</v>
@@ -11607,7 +11607,7 @@
         <v>14</v>
       </c>
       <c r="F252" s="2">
-        <v>3317</v>
+        <v>2305</v>
       </c>
       <c r="G252" s="2" t="s">
         <v>15</v>
@@ -11639,7 +11639,7 @@
         <v>14</v>
       </c>
       <c r="F253" s="2">
-        <v>3546</v>
+        <v>1303</v>
       </c>
       <c r="G253" s="2" t="s">
         <v>15</v>
@@ -11671,7 +11671,7 @@
         <v>14</v>
       </c>
       <c r="F254" s="2">
-        <v>3378</v>
+        <v>3769</v>
       </c>
       <c r="G254" s="2" t="s">
         <v>15</v>
@@ -11703,7 +11703,7 @@
         <v>14</v>
       </c>
       <c r="F255" s="2">
-        <v>1175</v>
+        <v>2755</v>
       </c>
       <c r="G255" s="2" t="s">
         <v>15</v>
@@ -11735,7 +11735,7 @@
         <v>14</v>
       </c>
       <c r="F256" s="2">
-        <v>4325</v>
+        <v>1127</v>
       </c>
       <c r="G256" s="2" t="s">
         <v>15</v>
@@ -11767,7 +11767,7 @@
         <v>14</v>
       </c>
       <c r="F257" s="2">
-        <v>1886</v>
+        <v>2706</v>
       </c>
       <c r="G257" s="2" t="s">
         <v>15</v>
@@ -11799,7 +11799,7 @@
         <v>14</v>
       </c>
       <c r="F258" s="2">
-        <v>1822</v>
+        <v>3223</v>
       </c>
       <c r="G258" s="2" t="s">
         <v>15</v>
@@ -11831,7 +11831,7 @@
         <v>14</v>
       </c>
       <c r="F259" s="2">
-        <v>4151</v>
+        <v>1796</v>
       </c>
       <c r="G259" s="2" t="s">
         <v>15</v>
@@ -11863,7 +11863,7 @@
         <v>14</v>
       </c>
       <c r="F260" s="2">
-        <v>2037</v>
+        <v>944</v>
       </c>
       <c r="G260" s="2" t="s">
         <v>15</v>
@@ -11895,7 +11895,7 @@
         <v>14</v>
       </c>
       <c r="F261" s="2">
-        <v>4721</v>
+        <v>1426</v>
       </c>
       <c r="G261" s="2" t="s">
         <v>15</v>
@@ -11927,7 +11927,7 @@
         <v>14</v>
       </c>
       <c r="F262" s="2">
-        <v>4690</v>
+        <v>2446</v>
       </c>
       <c r="G262" s="2" t="s">
         <v>15</v>
@@ -11959,7 +11959,7 @@
         <v>14</v>
       </c>
       <c r="F263" s="2">
-        <v>4191</v>
+        <v>1945</v>
       </c>
       <c r="G263" s="2" t="s">
         <v>15</v>
@@ -11991,7 +11991,7 @@
         <v>14</v>
       </c>
       <c r="F264" s="2">
-        <v>807</v>
+        <v>2992</v>
       </c>
       <c r="G264" s="2" t="s">
         <v>15</v>
@@ -12023,7 +12023,7 @@
         <v>14</v>
       </c>
       <c r="F265" s="2">
-        <v>3404</v>
+        <v>1949</v>
       </c>
       <c r="G265" s="2" t="s">
         <v>15</v>
@@ -12055,7 +12055,7 @@
         <v>14</v>
       </c>
       <c r="F266" s="2">
-        <v>2315</v>
+        <v>1324</v>
       </c>
       <c r="G266" s="2" t="s">
         <v>15</v>
@@ -12087,7 +12087,7 @@
         <v>14</v>
       </c>
       <c r="F267" s="2">
-        <v>2065</v>
+        <v>2255</v>
       </c>
       <c r="G267" s="2" t="s">
         <v>15</v>
@@ -12119,7 +12119,7 @@
         <v>14</v>
       </c>
       <c r="F268" s="2">
-        <v>4758</v>
+        <v>1217</v>
       </c>
       <c r="G268" s="2" t="s">
         <v>15</v>
@@ -12151,7 +12151,7 @@
         <v>14</v>
       </c>
       <c r="F269" s="2">
-        <v>2104</v>
+        <v>2863</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>15</v>
@@ -12183,7 +12183,7 @@
         <v>14</v>
       </c>
       <c r="F270" s="2">
-        <v>1196</v>
+        <v>2514</v>
       </c>
       <c r="G270" s="2" t="s">
         <v>15</v>
@@ -12215,7 +12215,7 @@
         <v>14</v>
       </c>
       <c r="F271" s="2">
-        <v>2101</v>
+        <v>2581</v>
       </c>
       <c r="G271" s="2" t="s">
         <v>15</v>
@@ -12247,7 +12247,7 @@
         <v>14</v>
       </c>
       <c r="F272" s="2">
-        <v>4077</v>
+        <v>3381</v>
       </c>
       <c r="G272" s="2" t="s">
         <v>15</v>
@@ -12279,7 +12279,7 @@
         <v>14</v>
       </c>
       <c r="F273" s="2">
-        <v>3494</v>
+        <v>3640</v>
       </c>
       <c r="G273" s="2" t="s">
         <v>15</v>
@@ -12311,7 +12311,7 @@
         <v>14</v>
       </c>
       <c r="F274" s="2">
-        <v>1229</v>
+        <v>4587</v>
       </c>
       <c r="G274" s="2" t="s">
         <v>15</v>
@@ -12343,7 +12343,7 @@
         <v>14</v>
       </c>
       <c r="F275" s="2">
-        <v>2283</v>
+        <v>4224</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>15</v>
@@ -12375,7 +12375,7 @@
         <v>14</v>
       </c>
       <c r="F276" s="2">
-        <v>1980</v>
+        <v>2545</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>15</v>
@@ -12407,7 +12407,7 @@
         <v>14</v>
       </c>
       <c r="F277" s="2">
-        <v>2926</v>
+        <v>2351</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>15</v>
@@ -12439,7 +12439,7 @@
         <v>14</v>
       </c>
       <c r="F278" s="2">
-        <v>2493</v>
+        <v>3243</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>15</v>
@@ -12471,7 +12471,7 @@
         <v>14</v>
       </c>
       <c r="F279" s="2">
-        <v>1161</v>
+        <v>1883</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>15</v>
@@ -12503,7 +12503,7 @@
         <v>14</v>
       </c>
       <c r="F280" s="2">
-        <v>1615</v>
+        <v>2362</v>
       </c>
       <c r="G280" s="2" t="s">
         <v>15</v>
@@ -12535,7 +12535,7 @@
         <v>14</v>
       </c>
       <c r="F281" s="2">
-        <v>2182</v>
+        <v>1757</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>15</v>
@@ -12567,7 +12567,7 @@
         <v>14</v>
       </c>
       <c r="F282" s="2">
-        <v>3423</v>
+        <v>3695</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>15</v>
@@ -12599,7 +12599,7 @@
         <v>14</v>
       </c>
       <c r="F283" s="2">
-        <v>2094</v>
+        <v>3469</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>15</v>
@@ -12631,7 +12631,7 @@
         <v>14</v>
       </c>
       <c r="F284" s="2">
-        <v>1233</v>
+        <v>4694</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>15</v>
@@ -12663,7 +12663,7 @@
         <v>14</v>
       </c>
       <c r="F285" s="2">
-        <v>1955</v>
+        <v>2743</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>15</v>
@@ -12695,7 +12695,7 @@
         <v>14</v>
       </c>
       <c r="F286" s="2">
-        <v>2484</v>
+        <v>3806</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>15</v>
@@ -12727,7 +12727,7 @@
         <v>14</v>
       </c>
       <c r="F287" s="2">
-        <v>1424</v>
+        <v>2366</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>15</v>
@@ -12759,7 +12759,7 @@
         <v>14</v>
       </c>
       <c r="F288" s="2">
-        <v>3156</v>
+        <v>1470</v>
       </c>
       <c r="G288" s="2" t="s">
         <v>15</v>
@@ -12791,7 +12791,7 @@
         <v>14</v>
       </c>
       <c r="F289" s="2">
-        <v>3303</v>
+        <v>1517</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>15</v>
@@ -12823,7 +12823,7 @@
         <v>14</v>
       </c>
       <c r="F290" s="2">
-        <v>2708</v>
+        <v>3646</v>
       </c>
       <c r="G290" s="2" t="s">
         <v>15</v>
@@ -12855,7 +12855,7 @@
         <v>14</v>
       </c>
       <c r="F291" s="2">
-        <v>2983</v>
+        <v>2909</v>
       </c>
       <c r="G291" s="2" t="s">
         <v>15</v>
@@ -12887,7 +12887,7 @@
         <v>14</v>
       </c>
       <c r="F292" s="2">
-        <v>1503</v>
+        <v>831</v>
       </c>
       <c r="G292" s="2" t="s">
         <v>15</v>
@@ -12919,7 +12919,7 @@
         <v>14</v>
       </c>
       <c r="F293" s="2">
-        <v>1231</v>
+        <v>2511</v>
       </c>
       <c r="G293" s="2" t="s">
         <v>15</v>
@@ -12951,7 +12951,7 @@
         <v>14</v>
       </c>
       <c r="F294" s="2">
-        <v>2241</v>
+        <v>3654</v>
       </c>
       <c r="G294" s="2" t="s">
         <v>15</v>
@@ -12983,7 +12983,7 @@
         <v>14</v>
       </c>
       <c r="F295" s="2">
-        <v>1526</v>
+        <v>3598</v>
       </c>
       <c r="G295" s="2" t="s">
         <v>15</v>
@@ -13015,7 +13015,7 @@
         <v>14</v>
       </c>
       <c r="F296" s="2">
-        <v>2014</v>
+        <v>2453</v>
       </c>
       <c r="G296" s="2" t="s">
         <v>15</v>
@@ -13047,7 +13047,7 @@
         <v>14</v>
       </c>
       <c r="F297" s="2">
-        <v>2854</v>
+        <v>3012</v>
       </c>
       <c r="G297" s="2" t="s">
         <v>15</v>
@@ -13079,7 +13079,7 @@
         <v>14</v>
       </c>
       <c r="F298" s="2">
-        <v>1244</v>
+        <v>4235</v>
       </c>
       <c r="G298" s="2" t="s">
         <v>15</v>
@@ -13111,7 +13111,7 @@
         <v>14</v>
       </c>
       <c r="F299" s="2">
-        <v>2931</v>
+        <v>1065</v>
       </c>
       <c r="G299" s="2" t="s">
         <v>15</v>
@@ -13143,7 +13143,7 @@
         <v>14</v>
       </c>
       <c r="F300" s="2">
-        <v>878</v>
+        <v>4548</v>
       </c>
       <c r="G300" s="2" t="s">
         <v>15</v>
@@ -13175,7 +13175,7 @@
         <v>14</v>
       </c>
       <c r="F301" s="2">
-        <v>2804</v>
+        <v>4763</v>
       </c>
       <c r="G301" s="2" t="s">
         <v>15</v>
@@ -13207,7 +13207,7 @@
         <v>14</v>
       </c>
       <c r="F302" s="2">
-        <v>2763</v>
+        <v>3027</v>
       </c>
       <c r="G302" s="2" t="s">
         <v>15</v>
@@ -13239,7 +13239,7 @@
         <v>14</v>
       </c>
       <c r="F303" s="2">
-        <v>3566</v>
+        <v>4101</v>
       </c>
       <c r="G303" s="2" t="s">
         <v>15</v>
@@ -13271,7 +13271,7 @@
         <v>14</v>
       </c>
       <c r="F304" s="2">
-        <v>4037</v>
+        <v>2415</v>
       </c>
       <c r="G304" s="2" t="s">
         <v>15</v>
@@ -13303,7 +13303,7 @@
         <v>14</v>
       </c>
       <c r="F305" s="2">
-        <v>2387</v>
+        <v>2907</v>
       </c>
       <c r="G305" s="2" t="s">
         <v>15</v>
@@ -13335,7 +13335,7 @@
         <v>14</v>
       </c>
       <c r="F306" s="2">
-        <v>1496</v>
+        <v>1561</v>
       </c>
       <c r="G306" s="2" t="s">
         <v>15</v>
@@ -13367,7 +13367,7 @@
         <v>14</v>
       </c>
       <c r="F307" s="2">
-        <v>982</v>
+        <v>2159</v>
       </c>
       <c r="G307" s="2" t="s">
         <v>15</v>
@@ -13399,7 +13399,7 @@
         <v>14</v>
       </c>
       <c r="F308" s="2">
-        <v>2224</v>
+        <v>3445</v>
       </c>
       <c r="G308" s="2" t="s">
         <v>15</v>
@@ -13431,7 +13431,7 @@
         <v>14</v>
       </c>
       <c r="F309" s="2">
-        <v>3884</v>
+        <v>3658</v>
       </c>
       <c r="G309" s="2" t="s">
         <v>15</v>
@@ -13463,7 +13463,7 @@
         <v>14</v>
       </c>
       <c r="F310" s="2">
-        <v>1481</v>
+        <v>3266</v>
       </c>
       <c r="G310" s="2" t="s">
         <v>15</v>
@@ -13495,7 +13495,7 @@
         <v>14</v>
       </c>
       <c r="F311" s="2">
-        <v>1048</v>
+        <v>3620</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>15</v>
@@ -13527,7 +13527,7 @@
         <v>14</v>
       </c>
       <c r="F312" s="2">
-        <v>4217</v>
+        <v>3805</v>
       </c>
       <c r="G312" s="2" t="s">
         <v>15</v>
@@ -13559,7 +13559,7 @@
         <v>14</v>
       </c>
       <c r="F313" s="2">
-        <v>3558</v>
+        <v>1251</v>
       </c>
       <c r="G313" s="2" t="s">
         <v>15</v>
@@ -13591,7 +13591,7 @@
         <v>14</v>
       </c>
       <c r="F314" s="2">
-        <v>4702</v>
+        <v>1247</v>
       </c>
       <c r="G314" s="2" t="s">
         <v>15</v>
@@ -13623,7 +13623,7 @@
         <v>14</v>
       </c>
       <c r="F315" s="2">
-        <v>1877</v>
+        <v>1950</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>15</v>
@@ -13655,7 +13655,7 @@
         <v>14</v>
       </c>
       <c r="F316" s="2">
-        <v>1843</v>
+        <v>1477</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>15</v>
@@ -13687,7 +13687,7 @@
         <v>14</v>
       </c>
       <c r="F317" s="2">
-        <v>3656</v>
+        <v>1234</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>15</v>
@@ -13719,7 +13719,7 @@
         <v>14</v>
       </c>
       <c r="F318" s="2">
-        <v>1510</v>
+        <v>4451</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>15</v>
@@ -13751,7 +13751,7 @@
         <v>14</v>
       </c>
       <c r="F319" s="2">
-        <v>4579</v>
+        <v>4140</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>15</v>
@@ -13783,7 +13783,7 @@
         <v>14</v>
       </c>
       <c r="F320" s="2">
-        <v>2107</v>
+        <v>3230</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>15</v>
@@ -13815,7 +13815,7 @@
         <v>14</v>
       </c>
       <c r="F321" s="2">
-        <v>930</v>
+        <v>3047</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>15</v>
@@ -13847,7 +13847,7 @@
         <v>14</v>
       </c>
       <c r="F322" s="2">
-        <v>3996</v>
+        <v>2849</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>15</v>
@@ -13879,7 +13879,7 @@
         <v>14</v>
       </c>
       <c r="F323" s="2">
-        <v>2580</v>
+        <v>2294</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>15</v>
@@ -13911,7 +13911,7 @@
         <v>14</v>
       </c>
       <c r="F324" s="2">
-        <v>1775</v>
+        <v>3453</v>
       </c>
       <c r="G324" s="2" t="s">
         <v>15</v>
@@ -13943,7 +13943,7 @@
         <v>14</v>
       </c>
       <c r="F325" s="2">
-        <v>3393</v>
+        <v>960</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>15</v>
@@ -13975,7 +13975,7 @@
         <v>14</v>
       </c>
       <c r="F326" s="2">
-        <v>3911</v>
+        <v>2133</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>15</v>
@@ -14007,7 +14007,7 @@
         <v>14</v>
       </c>
       <c r="F327" s="2">
-        <v>3441</v>
+        <v>3056</v>
       </c>
       <c r="G327" s="2" t="s">
         <v>15</v>
@@ -14039,7 +14039,7 @@
         <v>14</v>
       </c>
       <c r="F328" s="2">
-        <v>4452</v>
+        <v>3342</v>
       </c>
       <c r="G328" s="2" t="s">
         <v>15</v>
@@ -14071,7 +14071,7 @@
         <v>14</v>
       </c>
       <c r="F329" s="2">
-        <v>2646</v>
+        <v>1757</v>
       </c>
       <c r="G329" s="2" t="s">
         <v>15</v>
@@ -14103,7 +14103,7 @@
         <v>14</v>
       </c>
       <c r="F330" s="2">
-        <v>4662</v>
+        <v>4244</v>
       </c>
       <c r="G330" s="2" t="s">
         <v>15</v>
@@ -14135,7 +14135,7 @@
         <v>14</v>
       </c>
       <c r="F331" s="2">
-        <v>3863</v>
+        <v>4119</v>
       </c>
       <c r="G331" s="2" t="s">
         <v>15</v>
@@ -14167,7 +14167,7 @@
         <v>14</v>
       </c>
       <c r="F332" s="2">
-        <v>2698</v>
+        <v>2824</v>
       </c>
       <c r="G332" s="2" t="s">
         <v>15</v>
@@ -14199,7 +14199,7 @@
         <v>14</v>
       </c>
       <c r="F333" s="2">
-        <v>1905</v>
+        <v>2980</v>
       </c>
       <c r="G333" s="2" t="s">
         <v>15</v>
@@ -14231,7 +14231,7 @@
         <v>14</v>
       </c>
       <c r="F334" s="2">
-        <v>2450</v>
+        <v>3244</v>
       </c>
       <c r="G334" s="2" t="s">
         <v>15</v>
@@ -14263,7 +14263,7 @@
         <v>14</v>
       </c>
       <c r="F335" s="2">
-        <v>3877</v>
+        <v>1729</v>
       </c>
       <c r="G335" s="2" t="s">
         <v>15</v>
@@ -14295,7 +14295,7 @@
         <v>14</v>
       </c>
       <c r="F336" s="2">
-        <v>4421</v>
+        <v>3796</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>15</v>
@@ -14327,7 +14327,7 @@
         <v>14</v>
       </c>
       <c r="F337" s="2">
-        <v>1337</v>
+        <v>2184</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>15</v>
@@ -14359,7 +14359,7 @@
         <v>14</v>
       </c>
       <c r="F338" s="2">
-        <v>2587</v>
+        <v>4775</v>
       </c>
       <c r="G338" s="2" t="s">
         <v>15</v>
@@ -14391,7 +14391,7 @@
         <v>14</v>
       </c>
       <c r="F339" s="2">
-        <v>1210</v>
+        <v>1948</v>
       </c>
       <c r="G339" s="2" t="s">
         <v>15</v>
@@ -14423,7 +14423,7 @@
         <v>14</v>
       </c>
       <c r="F340" s="2">
-        <v>4723</v>
+        <v>1064</v>
       </c>
       <c r="G340" s="2" t="s">
         <v>15</v>
@@ -14455,7 +14455,7 @@
         <v>14</v>
       </c>
       <c r="F341" s="2">
-        <v>2950</v>
+        <v>4638</v>
       </c>
       <c r="G341" s="2" t="s">
         <v>15</v>
@@ -14487,7 +14487,7 @@
         <v>14</v>
       </c>
       <c r="F342" s="2">
-        <v>2073</v>
+        <v>1925</v>
       </c>
       <c r="G342" s="2" t="s">
         <v>15</v>
@@ -14519,7 +14519,7 @@
         <v>14</v>
       </c>
       <c r="F343" s="2">
-        <v>3313</v>
+        <v>4611</v>
       </c>
       <c r="G343" s="2" t="s">
         <v>15</v>
@@ -14551,7 +14551,7 @@
         <v>14</v>
       </c>
       <c r="F344" s="2">
-        <v>3492</v>
+        <v>1268</v>
       </c>
       <c r="G344" s="2" t="s">
         <v>15</v>
@@ -14583,7 +14583,7 @@
         <v>14</v>
       </c>
       <c r="F345" s="2">
-        <v>3022</v>
+        <v>2128</v>
       </c>
       <c r="G345" s="2" t="s">
         <v>15</v>
@@ -14615,7 +14615,7 @@
         <v>14</v>
       </c>
       <c r="F346" s="2">
-        <v>1589</v>
+        <v>4637</v>
       </c>
       <c r="G346" s="2" t="s">
         <v>15</v>
@@ -14647,7 +14647,7 @@
         <v>14</v>
       </c>
       <c r="F347" s="2">
-        <v>4469</v>
+        <v>4689</v>
       </c>
       <c r="G347" s="2" t="s">
         <v>15</v>
@@ -14679,7 +14679,7 @@
         <v>14</v>
       </c>
       <c r="F348" s="2">
-        <v>4104</v>
+        <v>2996</v>
       </c>
       <c r="G348" s="2" t="s">
         <v>15</v>
@@ -14711,7 +14711,7 @@
         <v>14</v>
       </c>
       <c r="F349" s="2">
-        <v>4019</v>
+        <v>1299</v>
       </c>
       <c r="G349" s="2" t="s">
         <v>15</v>
@@ -14743,7 +14743,7 @@
         <v>14</v>
       </c>
       <c r="F350" s="2">
-        <v>811</v>
+        <v>1113</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>15</v>
@@ -14775,7 +14775,7 @@
         <v>14</v>
       </c>
       <c r="F351" s="2">
-        <v>4550</v>
+        <v>3800</v>
       </c>
       <c r="G351" s="2" t="s">
         <v>15</v>
@@ -14807,7 +14807,7 @@
         <v>14</v>
       </c>
       <c r="F352" s="2">
-        <v>3813</v>
+        <v>979</v>
       </c>
       <c r="G352" s="2" t="s">
         <v>15</v>
@@ -14839,7 +14839,7 @@
         <v>14</v>
       </c>
       <c r="F353" s="2">
-        <v>1690</v>
+        <v>3290</v>
       </c>
       <c r="G353" s="2" t="s">
         <v>15</v>
@@ -14871,7 +14871,7 @@
         <v>14</v>
       </c>
       <c r="F354" s="2">
-        <v>1159</v>
+        <v>1290</v>
       </c>
       <c r="G354" s="2" t="s">
         <v>15</v>
@@ -14903,7 +14903,7 @@
         <v>14</v>
       </c>
       <c r="F355" s="2">
-        <v>3893</v>
+        <v>3498</v>
       </c>
       <c r="G355" s="2" t="s">
         <v>15</v>
@@ -14935,7 +14935,7 @@
         <v>14</v>
       </c>
       <c r="F356" s="2">
-        <v>4162</v>
+        <v>3429</v>
       </c>
       <c r="G356" s="2" t="s">
         <v>15</v>
@@ -14967,7 +14967,7 @@
         <v>14</v>
       </c>
       <c r="F357" s="2">
-        <v>3573</v>
+        <v>1150</v>
       </c>
       <c r="G357" s="2" t="s">
         <v>15</v>
@@ -14999,7 +14999,7 @@
         <v>14</v>
       </c>
       <c r="F358" s="2">
-        <v>3480</v>
+        <v>4620</v>
       </c>
       <c r="G358" s="2" t="s">
         <v>15</v>
@@ -15031,7 +15031,7 @@
         <v>14</v>
       </c>
       <c r="F359" s="2">
-        <v>1442</v>
+        <v>2163</v>
       </c>
       <c r="G359" s="2" t="s">
         <v>15</v>
@@ -15063,7 +15063,7 @@
         <v>14</v>
       </c>
       <c r="F360" s="2">
-        <v>3050</v>
+        <v>1952</v>
       </c>
       <c r="G360" s="2" t="s">
         <v>15</v>
@@ -15095,7 +15095,7 @@
         <v>14</v>
       </c>
       <c r="F361" s="2">
-        <v>4263</v>
+        <v>4516</v>
       </c>
       <c r="G361" s="2" t="s">
         <v>15</v>
@@ -15127,7 +15127,7 @@
         <v>14</v>
       </c>
       <c r="F362" s="2">
-        <v>2896</v>
+        <v>1630</v>
       </c>
       <c r="G362" s="2" t="s">
         <v>15</v>
@@ -15159,7 +15159,7 @@
         <v>14</v>
       </c>
       <c r="F363" s="2">
-        <v>2347</v>
+        <v>2702</v>
       </c>
       <c r="G363" s="2" t="s">
         <v>15</v>
@@ -15191,7 +15191,7 @@
         <v>14</v>
       </c>
       <c r="F364" s="2">
-        <v>2764</v>
+        <v>1333</v>
       </c>
       <c r="G364" s="2" t="s">
         <v>15</v>
@@ -15223,7 +15223,7 @@
         <v>14</v>
       </c>
       <c r="F365" s="2">
-        <v>3431</v>
+        <v>2046</v>
       </c>
       <c r="G365" s="2" t="s">
         <v>15</v>
@@ -15255,7 +15255,7 @@
         <v>14</v>
       </c>
       <c r="F366" s="2">
-        <v>3262</v>
+        <v>800</v>
       </c>
       <c r="G366" s="2" t="s">
         <v>15</v>
@@ -15287,7 +15287,7 @@
         <v>14</v>
       </c>
       <c r="F367" s="2">
-        <v>1365</v>
+        <v>3996</v>
       </c>
       <c r="G367" s="2" t="s">
         <v>15</v>
@@ -15319,7 +15319,7 @@
         <v>14</v>
       </c>
       <c r="F368" s="2">
-        <v>2099</v>
+        <v>4691</v>
       </c>
       <c r="G368" s="2" t="s">
         <v>15</v>
@@ -15351,7 +15351,7 @@
         <v>14</v>
       </c>
       <c r="F369" s="2">
-        <v>3495</v>
+        <v>2586</v>
       </c>
       <c r="G369" s="2" t="s">
         <v>15</v>
@@ -15383,7 +15383,7 @@
         <v>14</v>
       </c>
       <c r="F370" s="2">
-        <v>2685</v>
+        <v>3418</v>
       </c>
       <c r="G370" s="2" t="s">
         <v>15</v>
@@ -15415,7 +15415,7 @@
         <v>14</v>
       </c>
       <c r="F371" s="2">
-        <v>1454</v>
+        <v>2409</v>
       </c>
       <c r="G371" s="2" t="s">
         <v>15</v>
@@ -15447,7 +15447,7 @@
         <v>14</v>
       </c>
       <c r="F372" s="2">
-        <v>1610</v>
+        <v>1705</v>
       </c>
       <c r="G372" s="2" t="s">
         <v>15</v>
@@ -15479,7 +15479,7 @@
         <v>14</v>
       </c>
       <c r="F373" s="2">
-        <v>3922</v>
+        <v>4157</v>
       </c>
       <c r="G373" s="2" t="s">
         <v>15</v>
@@ -15511,7 +15511,7 @@
         <v>14</v>
       </c>
       <c r="F374" s="2">
-        <v>1508</v>
+        <v>1324</v>
       </c>
       <c r="G374" s="2" t="s">
         <v>15</v>
@@ -15543,7 +15543,7 @@
         <v>14</v>
       </c>
       <c r="F375" s="2">
-        <v>1586</v>
+        <v>4738</v>
       </c>
       <c r="G375" s="2" t="s">
         <v>15</v>
@@ -15575,7 +15575,7 @@
         <v>14</v>
       </c>
       <c r="F376" s="2">
-        <v>1532</v>
+        <v>2360</v>
       </c>
       <c r="G376" s="2" t="s">
         <v>15</v>
@@ -15607,7 +15607,7 @@
         <v>14</v>
       </c>
       <c r="F377" s="2">
-        <v>2836</v>
+        <v>952</v>
       </c>
       <c r="G377" s="2" t="s">
         <v>15</v>
@@ -15639,7 +15639,7 @@
         <v>14</v>
       </c>
       <c r="F378" s="2">
-        <v>2304</v>
+        <v>2314</v>
       </c>
       <c r="G378" s="2" t="s">
         <v>15</v>
@@ -15671,7 +15671,7 @@
         <v>14</v>
       </c>
       <c r="F379" s="2">
-        <v>3148</v>
+        <v>3955</v>
       </c>
       <c r="G379" s="2" t="s">
         <v>15</v>
@@ -15703,7 +15703,7 @@
         <v>14</v>
       </c>
       <c r="F380" s="2">
-        <v>836</v>
+        <v>2004</v>
       </c>
       <c r="G380" s="2" t="s">
         <v>15</v>
@@ -15735,7 +15735,7 @@
         <v>14</v>
       </c>
       <c r="F381" s="2">
-        <v>3871</v>
+        <v>3094</v>
       </c>
       <c r="G381" s="2" t="s">
         <v>15</v>
@@ -15767,7 +15767,7 @@
         <v>14</v>
       </c>
       <c r="F382" s="2">
-        <v>4465</v>
+        <v>1945</v>
       </c>
       <c r="G382" s="2" t="s">
         <v>15</v>
@@ -15799,7 +15799,7 @@
         <v>14</v>
       </c>
       <c r="F383" s="2">
-        <v>2545</v>
+        <v>1104</v>
       </c>
       <c r="G383" s="2" t="s">
         <v>15</v>
@@ -15831,7 +15831,7 @@
         <v>14</v>
       </c>
       <c r="F384" s="2">
-        <v>2579</v>
+        <v>1013</v>
       </c>
       <c r="G384" s="2" t="s">
         <v>15</v>
@@ -15863,7 +15863,7 @@
         <v>14</v>
       </c>
       <c r="F385" s="2">
-        <v>1328</v>
+        <v>4416</v>
       </c>
       <c r="G385" s="2" t="s">
         <v>15</v>
@@ -15895,7 +15895,7 @@
         <v>14</v>
       </c>
       <c r="F386" s="2">
-        <v>3806</v>
+        <v>3663</v>
       </c>
       <c r="G386" s="2" t="s">
         <v>15</v>
@@ -15927,7 +15927,7 @@
         <v>14</v>
       </c>
       <c r="F387" s="2">
-        <v>2004</v>
+        <v>3340</v>
       </c>
       <c r="G387" s="2" t="s">
         <v>15</v>
@@ -15959,7 +15959,7 @@
         <v>14</v>
       </c>
       <c r="F388" s="2">
-        <v>4113</v>
+        <v>1716</v>
       </c>
       <c r="G388" s="2" t="s">
         <v>15</v>
@@ -15991,7 +15991,7 @@
         <v>14</v>
       </c>
       <c r="F389" s="2">
-        <v>2185</v>
+        <v>4009</v>
       </c>
       <c r="G389" s="2" t="s">
         <v>15</v>
@@ -16023,7 +16023,7 @@
         <v>14</v>
       </c>
       <c r="F390" s="2">
-        <v>1319</v>
+        <v>3834</v>
       </c>
       <c r="G390" s="2" t="s">
         <v>15</v>
@@ -16055,7 +16055,7 @@
         <v>14</v>
       </c>
       <c r="F391" s="2">
-        <v>2257</v>
+        <v>950</v>
       </c>
       <c r="G391" s="2" t="s">
         <v>15</v>
@@ -16087,7 +16087,7 @@
         <v>14</v>
       </c>
       <c r="F392" s="2">
-        <v>4263</v>
+        <v>2543</v>
       </c>
       <c r="G392" s="2" t="s">
         <v>15</v>
@@ -16119,7 +16119,7 @@
         <v>14</v>
       </c>
       <c r="F393" s="2">
-        <v>3090</v>
+        <v>2181</v>
       </c>
       <c r="G393" s="2" t="s">
         <v>15</v>
@@ -16151,7 +16151,7 @@
         <v>14</v>
       </c>
       <c r="F394" s="2">
-        <v>1205</v>
+        <v>1736</v>
       </c>
       <c r="G394" s="2" t="s">
         <v>15</v>
@@ -16183,7 +16183,7 @@
         <v>14</v>
       </c>
       <c r="F395" s="2">
-        <v>2852</v>
+        <v>870</v>
       </c>
       <c r="G395" s="2" t="s">
         <v>15</v>
@@ -16215,7 +16215,7 @@
         <v>14</v>
       </c>
       <c r="F396" s="2">
-        <v>3926</v>
+        <v>1254</v>
       </c>
       <c r="G396" s="2" t="s">
         <v>15</v>
@@ -16247,7 +16247,7 @@
         <v>14</v>
       </c>
       <c r="F397" s="2">
-        <v>2114</v>
+        <v>2575</v>
       </c>
       <c r="G397" s="2" t="s">
         <v>15</v>
@@ -16279,7 +16279,7 @@
         <v>14</v>
       </c>
       <c r="F398" s="2">
-        <v>2125</v>
+        <v>3091</v>
       </c>
       <c r="G398" s="2" t="s">
         <v>15</v>
@@ -16311,7 +16311,7 @@
         <v>14</v>
       </c>
       <c r="F399" s="2">
-        <v>3744</v>
+        <v>1443</v>
       </c>
       <c r="G399" s="2" t="s">
         <v>15</v>
@@ -16343,7 +16343,7 @@
         <v>14</v>
       </c>
       <c r="F400" s="2">
-        <v>4378</v>
+        <v>3362</v>
       </c>
       <c r="G400" s="2" t="s">
         <v>15</v>
@@ -16375,7 +16375,7 @@
         <v>14</v>
       </c>
       <c r="F401" s="2">
-        <v>3688</v>
+        <v>1140</v>
       </c>
       <c r="G401" s="2" t="s">
         <v>15</v>
@@ -16407,7 +16407,7 @@
         <v>14</v>
       </c>
       <c r="F402" s="2">
-        <v>2113</v>
+        <v>3980</v>
       </c>
       <c r="G402" s="2" t="s">
         <v>15</v>
@@ -16439,7 +16439,7 @@
         <v>14</v>
       </c>
       <c r="F403" s="2">
-        <v>4667</v>
+        <v>4357</v>
       </c>
       <c r="G403" s="2" t="s">
         <v>15</v>
@@ -16471,7 +16471,7 @@
         <v>14</v>
       </c>
       <c r="F404" s="2">
-        <v>1358</v>
+        <v>923</v>
       </c>
       <c r="G404" s="2" t="s">
         <v>15</v>
@@ -16503,7 +16503,7 @@
         <v>14</v>
       </c>
       <c r="F405" s="2">
-        <v>1756</v>
+        <v>935</v>
       </c>
       <c r="G405" s="2" t="s">
         <v>15</v>
@@ -16535,7 +16535,7 @@
         <v>14</v>
       </c>
       <c r="F406" s="2">
-        <v>2135</v>
+        <v>1189</v>
       </c>
       <c r="G406" s="2" t="s">
         <v>15</v>
@@ -16567,7 +16567,7 @@
         <v>14</v>
       </c>
       <c r="F407" s="2">
-        <v>3174</v>
+        <v>1050</v>
       </c>
       <c r="G407" s="2" t="s">
         <v>15</v>
@@ -16599,7 +16599,7 @@
         <v>14</v>
       </c>
       <c r="F408" s="2">
-        <v>3799</v>
+        <v>1027</v>
       </c>
       <c r="G408" s="2" t="s">
         <v>15</v>
@@ -16631,7 +16631,7 @@
         <v>14</v>
       </c>
       <c r="F409" s="2">
-        <v>4508</v>
+        <v>4181</v>
       </c>
       <c r="G409" s="2" t="s">
         <v>15</v>
@@ -16663,7 +16663,7 @@
         <v>14</v>
       </c>
       <c r="F410" s="2">
-        <v>4000</v>
+        <v>1486</v>
       </c>
       <c r="G410" s="2" t="s">
         <v>15</v>
@@ -16695,7 +16695,7 @@
         <v>14</v>
       </c>
       <c r="F411" s="2">
-        <v>3077</v>
+        <v>4747</v>
       </c>
       <c r="G411" s="2" t="s">
         <v>15</v>
@@ -16727,7 +16727,7 @@
         <v>14</v>
       </c>
       <c r="F412" s="2">
-        <v>1470</v>
+        <v>2933</v>
       </c>
       <c r="G412" s="2" t="s">
         <v>15</v>
@@ -16759,7 +16759,7 @@
         <v>14</v>
       </c>
       <c r="F413" s="2">
-        <v>1846</v>
+        <v>1428</v>
       </c>
       <c r="G413" s="2" t="s">
         <v>15</v>
@@ -16791,7 +16791,7 @@
         <v>14</v>
       </c>
       <c r="F414" s="2">
-        <v>4221</v>
+        <v>1050</v>
       </c>
       <c r="G414" s="2" t="s">
         <v>15</v>
@@ -16823,7 +16823,7 @@
         <v>14</v>
       </c>
       <c r="F415" s="2">
-        <v>2649</v>
+        <v>3646</v>
       </c>
       <c r="G415" s="2" t="s">
         <v>15</v>
@@ -16855,7 +16855,7 @@
         <v>14</v>
       </c>
       <c r="F416" s="2">
-        <v>2774</v>
+        <v>1963</v>
       </c>
       <c r="G416" s="2" t="s">
         <v>15</v>
@@ -16887,7 +16887,7 @@
         <v>14</v>
       </c>
       <c r="F417" s="2">
-        <v>2732</v>
+        <v>964</v>
       </c>
       <c r="G417" s="2" t="s">
         <v>15</v>
@@ -16919,7 +16919,7 @@
         <v>14</v>
       </c>
       <c r="F418" s="2">
-        <v>819</v>
+        <v>4768</v>
       </c>
       <c r="G418" s="2" t="s">
         <v>15</v>
@@ -16951,7 +16951,7 @@
         <v>14</v>
       </c>
       <c r="F419" s="2">
-        <v>1951</v>
+        <v>3055</v>
       </c>
       <c r="G419" s="2" t="s">
         <v>15</v>
@@ -16983,7 +16983,7 @@
         <v>14</v>
       </c>
       <c r="F420" s="2">
-        <v>3792</v>
+        <v>2189</v>
       </c>
       <c r="G420" s="2" t="s">
         <v>15</v>
@@ -17015,7 +17015,7 @@
         <v>14</v>
       </c>
       <c r="F421" s="2">
-        <v>2875</v>
+        <v>959</v>
       </c>
       <c r="G421" s="2" t="s">
         <v>15</v>
@@ -17047,7 +17047,7 @@
         <v>14</v>
       </c>
       <c r="F422" s="2">
-        <v>2237</v>
+        <v>4728</v>
       </c>
       <c r="G422" s="2" t="s">
         <v>15</v>
@@ -17079,7 +17079,7 @@
         <v>14</v>
       </c>
       <c r="F423" s="2">
-        <v>3265</v>
+        <v>3599</v>
       </c>
       <c r="G423" s="2" t="s">
         <v>15</v>
@@ -17111,7 +17111,7 @@
         <v>14</v>
       </c>
       <c r="F424" s="2">
-        <v>4047</v>
+        <v>3689</v>
       </c>
       <c r="G424" s="2" t="s">
         <v>15</v>
@@ -17143,7 +17143,7 @@
         <v>14</v>
       </c>
       <c r="F425" s="2">
-        <v>1460</v>
+        <v>1328</v>
       </c>
       <c r="G425" s="2" t="s">
         <v>15</v>
@@ -17175,7 +17175,7 @@
         <v>14</v>
       </c>
       <c r="F426" s="2">
-        <v>2195</v>
+        <v>2073</v>
       </c>
       <c r="G426" s="2" t="s">
         <v>15</v>
@@ -17207,7 +17207,7 @@
         <v>14</v>
       </c>
       <c r="F427" s="2">
-        <v>4317</v>
+        <v>2351</v>
       </c>
       <c r="G427" s="2" t="s">
         <v>15</v>
@@ -17239,7 +17239,7 @@
         <v>14</v>
       </c>
       <c r="F428" s="2">
-        <v>4371</v>
+        <v>4005</v>
       </c>
       <c r="G428" s="2" t="s">
         <v>15</v>
@@ -17271,7 +17271,7 @@
         <v>14</v>
       </c>
       <c r="F429" s="2">
-        <v>876</v>
+        <v>813</v>
       </c>
       <c r="G429" s="2" t="s">
         <v>15</v>
@@ -17303,7 +17303,7 @@
         <v>14</v>
       </c>
       <c r="F430" s="2">
-        <v>3448</v>
+        <v>3222</v>
       </c>
       <c r="G430" s="2" t="s">
         <v>15</v>
@@ -17335,7 +17335,7 @@
         <v>14</v>
       </c>
       <c r="F431" s="2">
-        <v>3500</v>
+        <v>1774</v>
       </c>
       <c r="G431" s="2" t="s">
         <v>15</v>
@@ -17367,7 +17367,7 @@
         <v>14</v>
       </c>
       <c r="F432" s="2">
-        <v>3018</v>
+        <v>2908</v>
       </c>
       <c r="G432" s="2" t="s">
         <v>15</v>
@@ -17399,7 +17399,7 @@
         <v>14</v>
       </c>
       <c r="F433" s="2">
-        <v>1493</v>
+        <v>1187</v>
       </c>
       <c r="G433" s="2" t="s">
         <v>15</v>
@@ -17431,7 +17431,7 @@
         <v>14</v>
       </c>
       <c r="F434" s="2">
-        <v>1559</v>
+        <v>4766</v>
       </c>
       <c r="G434" s="2" t="s">
         <v>15</v>
@@ -17463,7 +17463,7 @@
         <v>14</v>
       </c>
       <c r="F435" s="2">
-        <v>1359</v>
+        <v>3107</v>
       </c>
       <c r="G435" s="2" t="s">
         <v>15</v>
@@ -17495,7 +17495,7 @@
         <v>14</v>
       </c>
       <c r="F436" s="2">
-        <v>3639</v>
+        <v>3180</v>
       </c>
       <c r="G436" s="2" t="s">
         <v>15</v>
@@ -17527,7 +17527,7 @@
         <v>14</v>
       </c>
       <c r="F437" s="2">
-        <v>1153</v>
+        <v>3860</v>
       </c>
       <c r="G437" s="2" t="s">
         <v>15</v>
@@ -17559,7 +17559,7 @@
         <v>14</v>
       </c>
       <c r="F438" s="2">
-        <v>4272</v>
+        <v>3144</v>
       </c>
       <c r="G438" s="2" t="s">
         <v>15</v>
@@ -17591,7 +17591,7 @@
         <v>14</v>
       </c>
       <c r="F439" s="2">
-        <v>4712</v>
+        <v>2853</v>
       </c>
       <c r="G439" s="2" t="s">
         <v>15</v>
@@ -17623,7 +17623,7 @@
         <v>14</v>
       </c>
       <c r="F440" s="2">
-        <v>1482</v>
+        <v>4773</v>
       </c>
       <c r="G440" s="2" t="s">
         <v>15</v>
@@ -17655,7 +17655,7 @@
         <v>14</v>
       </c>
       <c r="F441" s="2">
-        <v>2859</v>
+        <v>3557</v>
       </c>
       <c r="G441" s="2" t="s">
         <v>15</v>
@@ -17687,7 +17687,7 @@
         <v>14</v>
       </c>
       <c r="F442" s="2">
-        <v>1995</v>
+        <v>4217</v>
       </c>
       <c r="G442" s="2" t="s">
         <v>15</v>
@@ -17719,7 +17719,7 @@
         <v>14</v>
       </c>
       <c r="F443" s="2">
-        <v>3195</v>
+        <v>3114</v>
       </c>
       <c r="G443" s="2" t="s">
         <v>15</v>
@@ -17751,7 +17751,7 @@
         <v>14</v>
       </c>
       <c r="F444" s="2">
-        <v>1872</v>
+        <v>3676</v>
       </c>
       <c r="G444" s="2" t="s">
         <v>15</v>
@@ -17783,7 +17783,7 @@
         <v>14</v>
       </c>
       <c r="F445" s="2">
-        <v>3397</v>
+        <v>4321</v>
       </c>
       <c r="G445" s="2" t="s">
         <v>15</v>
@@ -17815,7 +17815,7 @@
         <v>14</v>
       </c>
       <c r="F446" s="2">
-        <v>3967</v>
+        <v>4501</v>
       </c>
       <c r="G446" s="2" t="s">
         <v>15</v>
@@ -17847,7 +17847,7 @@
         <v>14</v>
       </c>
       <c r="F447" s="2">
-        <v>1312</v>
+        <v>1468</v>
       </c>
       <c r="G447" s="2" t="s">
         <v>15</v>
@@ -17879,7 +17879,7 @@
         <v>14</v>
       </c>
       <c r="F448" s="2">
-        <v>2343</v>
+        <v>3861</v>
       </c>
       <c r="G448" s="2" t="s">
         <v>15</v>
@@ -17911,7 +17911,7 @@
         <v>14</v>
       </c>
       <c r="F449" s="2">
-        <v>3381</v>
+        <v>3172</v>
       </c>
       <c r="G449" s="2" t="s">
         <v>15</v>
@@ -17943,7 +17943,7 @@
         <v>14</v>
       </c>
       <c r="F450" s="2">
-        <v>1370</v>
+        <v>1535</v>
       </c>
       <c r="G450" s="2" t="s">
         <v>15</v>
@@ -17975,7 +17975,7 @@
         <v>14</v>
       </c>
       <c r="F451" s="2">
-        <v>2424</v>
+        <v>3165</v>
       </c>
       <c r="G451" s="2" t="s">
         <v>15</v>
@@ -18007,7 +18007,7 @@
         <v>14</v>
       </c>
       <c r="F452" s="2">
-        <v>1274</v>
+        <v>4614</v>
       </c>
       <c r="G452" s="2" t="s">
         <v>15</v>
@@ -18039,7 +18039,7 @@
         <v>14</v>
       </c>
       <c r="F453" s="2">
-        <v>3713</v>
+        <v>1847</v>
       </c>
       <c r="G453" s="2" t="s">
         <v>15</v>
@@ -18071,7 +18071,7 @@
         <v>14</v>
       </c>
       <c r="F454" s="2">
-        <v>4633</v>
+        <v>4071</v>
       </c>
       <c r="G454" s="2" t="s">
         <v>15</v>
@@ -18103,7 +18103,7 @@
         <v>14</v>
       </c>
       <c r="F455" s="2">
-        <v>1782</v>
+        <v>3007</v>
       </c>
       <c r="G455" s="2" t="s">
         <v>15</v>
@@ -18135,7 +18135,7 @@
         <v>14</v>
       </c>
       <c r="F456" s="2">
-        <v>1038</v>
+        <v>3839</v>
       </c>
       <c r="G456" s="2" t="s">
         <v>15</v>
@@ -18167,7 +18167,7 @@
         <v>14</v>
       </c>
       <c r="F457" s="2">
-        <v>3336</v>
+        <v>3081</v>
       </c>
       <c r="G457" s="2" t="s">
         <v>15</v>
@@ -18199,7 +18199,7 @@
         <v>14</v>
       </c>
       <c r="F458" s="2">
-        <v>1106</v>
+        <v>4185</v>
       </c>
       <c r="G458" s="2" t="s">
         <v>15</v>
@@ -18231,7 +18231,7 @@
         <v>14</v>
       </c>
       <c r="F459" s="2">
-        <v>988</v>
+        <v>1684</v>
       </c>
       <c r="G459" s="2" t="s">
         <v>15</v>
@@ -18263,7 +18263,7 @@
         <v>14</v>
       </c>
       <c r="F460" s="2">
-        <v>3321</v>
+        <v>3991</v>
       </c>
       <c r="G460" s="2" t="s">
         <v>15</v>
@@ -18295,7 +18295,7 @@
         <v>14</v>
       </c>
       <c r="F461" s="2">
-        <v>4711</v>
+        <v>3166</v>
       </c>
       <c r="G461" s="2" t="s">
         <v>15</v>
@@ -18327,7 +18327,7 @@
         <v>14</v>
       </c>
       <c r="F462" s="2">
-        <v>1561</v>
+        <v>2123</v>
       </c>
       <c r="G462" s="2" t="s">
         <v>15</v>
@@ -18359,7 +18359,7 @@
         <v>14</v>
       </c>
       <c r="F463" s="2">
-        <v>4514</v>
+        <v>1214</v>
       </c>
       <c r="G463" s="2" t="s">
         <v>15</v>
@@ -18391,7 +18391,7 @@
         <v>14</v>
       </c>
       <c r="F464" s="2">
-        <v>3884</v>
+        <v>3887</v>
       </c>
       <c r="G464" s="2" t="s">
         <v>15</v>
@@ -18423,7 +18423,7 @@
         <v>14</v>
       </c>
       <c r="F465" s="2">
-        <v>1063</v>
+        <v>1767</v>
       </c>
       <c r="G465" s="2" t="s">
         <v>15</v>
@@ -18455,7 +18455,7 @@
         <v>14</v>
       </c>
       <c r="F466" s="2">
-        <v>921</v>
+        <v>3940</v>
       </c>
       <c r="G466" s="2" t="s">
         <v>15</v>
@@ -18487,7 +18487,7 @@
         <v>14</v>
       </c>
       <c r="F467" s="2">
-        <v>2490</v>
+        <v>2339</v>
       </c>
       <c r="G467" s="2" t="s">
         <v>15</v>
@@ -18519,7 +18519,7 @@
         <v>14</v>
       </c>
       <c r="F468" s="2">
-        <v>4764</v>
+        <v>3324</v>
       </c>
       <c r="G468" s="2" t="s">
         <v>15</v>
@@ -18551,7 +18551,7 @@
         <v>14</v>
       </c>
       <c r="F469" s="2">
-        <v>3883</v>
+        <v>1123</v>
       </c>
       <c r="G469" s="2" t="s">
         <v>15</v>
@@ -18583,7 +18583,7 @@
         <v>14</v>
       </c>
       <c r="F470" s="2">
-        <v>3424</v>
+        <v>2371</v>
       </c>
       <c r="G470" s="2" t="s">
         <v>15</v>
@@ -18615,7 +18615,7 @@
         <v>14</v>
       </c>
       <c r="F471" s="2">
-        <v>4384</v>
+        <v>2769</v>
       </c>
       <c r="G471" s="2" t="s">
         <v>15</v>
@@ -18702,7 +18702,7 @@
         <v>14</v>
       </c>
       <c r="F2" s="2">
-        <v>972</v>
+        <v>2692</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>15</v>
@@ -18734,7 +18734,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="2">
-        <v>3048</v>
+        <v>4601</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>15</v>
@@ -18766,7 +18766,7 @@
         <v>14</v>
       </c>
       <c r="F4" s="2">
-        <v>3868</v>
+        <v>1356</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
@@ -18798,7 +18798,7 @@
         <v>14</v>
       </c>
       <c r="F5" s="2">
-        <v>1643</v>
+        <v>3387</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
@@ -18830,7 +18830,7 @@
         <v>14</v>
       </c>
       <c r="F6" s="2">
-        <v>3379</v>
+        <v>3286</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -18862,7 +18862,7 @@
         <v>14</v>
       </c>
       <c r="F7" s="2">
-        <v>3209</v>
+        <v>4231</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -18894,7 +18894,7 @@
         <v>14</v>
       </c>
       <c r="F8" s="2">
-        <v>1710</v>
+        <v>3350</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -18926,7 +18926,7 @@
         <v>14</v>
       </c>
       <c r="F9" s="2">
-        <v>3504</v>
+        <v>1973</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -18958,7 +18958,7 @@
         <v>14</v>
       </c>
       <c r="F10" s="2">
-        <v>2536</v>
+        <v>4613</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
@@ -18990,7 +18990,7 @@
         <v>14</v>
       </c>
       <c r="F11" s="2">
-        <v>2721</v>
+        <v>890</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
@@ -19022,7 +19022,7 @@
         <v>14</v>
       </c>
       <c r="F12" s="2">
-        <v>4294</v>
+        <v>2763</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
@@ -19054,7 +19054,7 @@
         <v>14</v>
       </c>
       <c r="F13" s="2">
-        <v>2044</v>
+        <v>2388</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -19086,7 +19086,7 @@
         <v>14</v>
       </c>
       <c r="F14" s="2">
-        <v>3251</v>
+        <v>3911</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -19118,7 +19118,7 @@
         <v>14</v>
       </c>
       <c r="F15" s="2">
-        <v>4465</v>
+        <v>1980</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -19150,7 +19150,7 @@
         <v>14</v>
       </c>
       <c r="F16" s="2">
-        <v>4326</v>
+        <v>1875</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
@@ -19182,7 +19182,7 @@
         <v>14</v>
       </c>
       <c r="F17" s="2">
-        <v>4547</v>
+        <v>2622</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
@@ -19214,7 +19214,7 @@
         <v>14</v>
       </c>
       <c r="F18" s="2">
-        <v>2974</v>
+        <v>2570</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
@@ -19246,7 +19246,7 @@
         <v>14</v>
       </c>
       <c r="F19" s="2">
-        <v>4563</v>
+        <v>3598</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
@@ -19278,7 +19278,7 @@
         <v>14</v>
       </c>
       <c r="F20" s="2">
-        <v>4052</v>
+        <v>3847</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
@@ -19310,7 +19310,7 @@
         <v>14</v>
       </c>
       <c r="F21" s="2">
-        <v>880</v>
+        <v>4367</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -19342,7 +19342,7 @@
         <v>14</v>
       </c>
       <c r="F22" s="2">
-        <v>804</v>
+        <v>1318</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -19374,7 +19374,7 @@
         <v>14</v>
       </c>
       <c r="F23" s="2">
-        <v>3882</v>
+        <v>1409</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -19406,7 +19406,7 @@
         <v>14</v>
       </c>
       <c r="F24" s="2">
-        <v>1130</v>
+        <v>1203</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -19438,7 +19438,7 @@
         <v>14</v>
       </c>
       <c r="F25" s="2">
-        <v>2251</v>
+        <v>3106</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -19470,7 +19470,7 @@
         <v>14</v>
       </c>
       <c r="F26" s="2">
-        <v>3393</v>
+        <v>1104</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -19502,7 +19502,7 @@
         <v>14</v>
       </c>
       <c r="F27" s="2">
-        <v>4209</v>
+        <v>1675</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>15</v>
@@ -19534,7 +19534,7 @@
         <v>14</v>
       </c>
       <c r="F28" s="2">
-        <v>4346</v>
+        <v>3595</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>15</v>
@@ -19566,7 +19566,7 @@
         <v>14</v>
       </c>
       <c r="F29" s="2">
-        <v>1172</v>
+        <v>2653</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>15</v>
@@ -19598,7 +19598,7 @@
         <v>14</v>
       </c>
       <c r="F30" s="2">
-        <v>3718</v>
+        <v>1579</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>15</v>
@@ -19630,7 +19630,7 @@
         <v>14</v>
       </c>
       <c r="F31" s="2">
-        <v>4751</v>
+        <v>4269</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>15</v>
@@ -19662,7 +19662,7 @@
         <v>14</v>
       </c>
       <c r="F32" s="2">
-        <v>3051</v>
+        <v>1142</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>15</v>
@@ -19694,7 +19694,7 @@
         <v>14</v>
       </c>
       <c r="F33" s="2">
-        <v>2043</v>
+        <v>1938</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>15</v>
@@ -19726,7 +19726,7 @@
         <v>14</v>
       </c>
       <c r="F34" s="2">
-        <v>1987</v>
+        <v>2327</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>15</v>
@@ -19758,7 +19758,7 @@
         <v>14</v>
       </c>
       <c r="F35" s="2">
-        <v>1268</v>
+        <v>3693</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>15</v>
@@ -19790,7 +19790,7 @@
         <v>14</v>
       </c>
       <c r="F36" s="2">
-        <v>4753</v>
+        <v>4594</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>15</v>
@@ -19822,7 +19822,7 @@
         <v>14</v>
       </c>
       <c r="F37" s="2">
-        <v>4552</v>
+        <v>3449</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>15</v>
@@ -19854,7 +19854,7 @@
         <v>14</v>
       </c>
       <c r="F38" s="2">
-        <v>4576</v>
+        <v>2062</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>15</v>
@@ -19886,7 +19886,7 @@
         <v>14</v>
       </c>
       <c r="F39" s="2">
-        <v>1103</v>
+        <v>4573</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>15</v>
@@ -19918,7 +19918,7 @@
         <v>14</v>
       </c>
       <c r="F40" s="2">
-        <v>1539</v>
+        <v>1004</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>15</v>
@@ -19950,7 +19950,7 @@
         <v>14</v>
       </c>
       <c r="F41" s="2">
-        <v>4688</v>
+        <v>4334</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>15</v>
@@ -19982,7 +19982,7 @@
         <v>14</v>
       </c>
       <c r="F42" s="2">
-        <v>1981</v>
+        <v>2407</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>15</v>
@@ -20014,7 +20014,7 @@
         <v>14</v>
       </c>
       <c r="F43" s="2">
-        <v>4029</v>
+        <v>2700</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>15</v>
@@ -20046,7 +20046,7 @@
         <v>14</v>
       </c>
       <c r="F44" s="2">
-        <v>1897</v>
+        <v>2453</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>15</v>
@@ -20078,7 +20078,7 @@
         <v>14</v>
       </c>
       <c r="F45" s="2">
-        <v>2920</v>
+        <v>1727</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>15</v>
@@ -20110,7 +20110,7 @@
         <v>14</v>
       </c>
       <c r="F46" s="2">
-        <v>1800</v>
+        <v>3373</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>15</v>
@@ -20142,7 +20142,7 @@
         <v>14</v>
       </c>
       <c r="F47" s="2">
-        <v>867</v>
+        <v>3117</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>15</v>
@@ -20174,7 +20174,7 @@
         <v>14</v>
       </c>
       <c r="F48" s="2">
-        <v>3655</v>
+        <v>2431</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>15</v>
@@ -20206,7 +20206,7 @@
         <v>14</v>
       </c>
       <c r="F49" s="2">
-        <v>4597</v>
+        <v>2730</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>15</v>
@@ -20238,7 +20238,7 @@
         <v>14</v>
       </c>
       <c r="F50" s="2">
-        <v>4100</v>
+        <v>1464</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>15</v>
@@ -20302,7 +20302,7 @@
         <v>14</v>
       </c>
       <c r="F52" s="2">
-        <v>4689</v>
+        <v>2690</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>15</v>
@@ -20334,7 +20334,7 @@
         <v>14</v>
       </c>
       <c r="F53" s="2">
-        <v>3968</v>
+        <v>3410</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>15</v>
@@ -20366,7 +20366,7 @@
         <v>14</v>
       </c>
       <c r="F54" s="2">
-        <v>3054</v>
+        <v>2755</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>15</v>
@@ -20398,7 +20398,7 @@
         <v>14</v>
       </c>
       <c r="F55" s="2">
-        <v>2806</v>
+        <v>4281</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>15</v>
@@ -20430,7 +20430,7 @@
         <v>14</v>
       </c>
       <c r="F56" s="2">
-        <v>2659</v>
+        <v>2167</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>15</v>
@@ -20462,7 +20462,7 @@
         <v>14</v>
       </c>
       <c r="F57" s="2">
-        <v>972</v>
+        <v>1805</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>15</v>
@@ -20494,7 +20494,7 @@
         <v>14</v>
       </c>
       <c r="F58" s="2">
-        <v>1181</v>
+        <v>1065</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>15</v>
@@ -20526,7 +20526,7 @@
         <v>14</v>
       </c>
       <c r="F59" s="2">
-        <v>4069</v>
+        <v>1165</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>15</v>
@@ -20558,7 +20558,7 @@
         <v>14</v>
       </c>
       <c r="F60" s="2">
-        <v>4310</v>
+        <v>2916</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>15</v>
@@ -20590,7 +20590,7 @@
         <v>14</v>
       </c>
       <c r="F61" s="2">
-        <v>2416</v>
+        <v>3945</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>15</v>
@@ -20622,7 +20622,7 @@
         <v>14</v>
       </c>
       <c r="F62" s="2">
-        <v>4296</v>
+        <v>1074</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>15</v>
@@ -20654,7 +20654,7 @@
         <v>14</v>
       </c>
       <c r="F63" s="2">
-        <v>3893</v>
+        <v>2009</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>15</v>
@@ -20686,7 +20686,7 @@
         <v>14</v>
       </c>
       <c r="F64" s="2">
-        <v>1084</v>
+        <v>1022</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>15</v>
@@ -20718,7 +20718,7 @@
         <v>14</v>
       </c>
       <c r="F65" s="2">
-        <v>3159</v>
+        <v>3274</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>15</v>
@@ -20750,7 +20750,7 @@
         <v>14</v>
       </c>
       <c r="F66" s="2">
-        <v>4382</v>
+        <v>4372</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>15</v>
@@ -20782,7 +20782,7 @@
         <v>14</v>
       </c>
       <c r="F67" s="2">
-        <v>3982</v>
+        <v>3809</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>15</v>
@@ -20814,7 +20814,7 @@
         <v>14</v>
       </c>
       <c r="F68" s="2">
-        <v>2204</v>
+        <v>981</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>15</v>
@@ -20846,7 +20846,7 @@
         <v>14</v>
       </c>
       <c r="F69" s="2">
-        <v>4545</v>
+        <v>3047</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>15</v>
@@ -20878,7 +20878,7 @@
         <v>14</v>
       </c>
       <c r="F70" s="2">
-        <v>821</v>
+        <v>1912</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>15</v>
@@ -20910,7 +20910,7 @@
         <v>14</v>
       </c>
       <c r="F71" s="2">
-        <v>1599</v>
+        <v>2100</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>15</v>
@@ -20942,7 +20942,7 @@
         <v>14</v>
       </c>
       <c r="F72" s="2">
-        <v>4196</v>
+        <v>4709</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>15</v>
@@ -20974,7 +20974,7 @@
         <v>14</v>
       </c>
       <c r="F73" s="2">
-        <v>2692</v>
+        <v>1006</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>15</v>
@@ -21006,7 +21006,7 @@
         <v>14</v>
       </c>
       <c r="F74" s="2">
-        <v>1618</v>
+        <v>3823</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>15</v>
@@ -21038,7 +21038,7 @@
         <v>14</v>
       </c>
       <c r="F75" s="2">
-        <v>1028</v>
+        <v>3679</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>15</v>
@@ -21070,7 +21070,7 @@
         <v>14</v>
       </c>
       <c r="F76" s="2">
-        <v>2322</v>
+        <v>1003</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>15</v>
@@ -21102,7 +21102,7 @@
         <v>14</v>
       </c>
       <c r="F77" s="2">
-        <v>2871</v>
+        <v>4074</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>15</v>
@@ -21134,7 +21134,7 @@
         <v>14</v>
       </c>
       <c r="F78" s="2">
-        <v>1017</v>
+        <v>3906</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>15</v>
@@ -21166,7 +21166,7 @@
         <v>14</v>
       </c>
       <c r="F79" s="2">
-        <v>1761</v>
+        <v>2867</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>15</v>
@@ -21198,7 +21198,7 @@
         <v>14</v>
       </c>
       <c r="F80" s="2">
-        <v>1938</v>
+        <v>3086</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>15</v>
@@ -21230,7 +21230,7 @@
         <v>14</v>
       </c>
       <c r="F81" s="2">
-        <v>2945</v>
+        <v>3610</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>15</v>
@@ -21262,7 +21262,7 @@
         <v>14</v>
       </c>
       <c r="F82" s="2">
-        <v>4264</v>
+        <v>1384</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>15</v>
@@ -21294,7 +21294,7 @@
         <v>14</v>
       </c>
       <c r="F83" s="2">
-        <v>4409</v>
+        <v>4413</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>15</v>
@@ -21326,7 +21326,7 @@
         <v>14</v>
       </c>
       <c r="F84" s="2">
-        <v>4321</v>
+        <v>4273</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>15</v>
@@ -21358,7 +21358,7 @@
         <v>14</v>
       </c>
       <c r="F85" s="2">
-        <v>3862</v>
+        <v>4506</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>15</v>
@@ -21390,7 +21390,7 @@
         <v>14</v>
       </c>
       <c r="F86" s="2">
-        <v>4180</v>
+        <v>2396</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>15</v>
@@ -21422,7 +21422,7 @@
         <v>14</v>
       </c>
       <c r="F87" s="2">
-        <v>2302</v>
+        <v>1747</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>15</v>
@@ -21454,7 +21454,7 @@
         <v>14</v>
       </c>
       <c r="F88" s="2">
-        <v>4748</v>
+        <v>1621</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>15</v>
@@ -21486,7 +21486,7 @@
         <v>14</v>
       </c>
       <c r="F89" s="2">
-        <v>4157</v>
+        <v>1248</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>15</v>
@@ -21518,7 +21518,7 @@
         <v>14</v>
       </c>
       <c r="F90" s="2">
-        <v>3725</v>
+        <v>3114</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>15</v>
@@ -21550,7 +21550,7 @@
         <v>14</v>
       </c>
       <c r="F91" s="2">
-        <v>2199</v>
+        <v>2273</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>15</v>
@@ -21582,7 +21582,7 @@
         <v>14</v>
       </c>
       <c r="F92" s="2">
-        <v>1188</v>
+        <v>3639</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>15</v>
@@ -21614,7 +21614,7 @@
         <v>14</v>
       </c>
       <c r="F93" s="2">
-        <v>1500</v>
+        <v>2151</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>15</v>
@@ -21646,7 +21646,7 @@
         <v>14</v>
       </c>
       <c r="F94" s="2">
-        <v>1986</v>
+        <v>1789</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>15</v>
@@ -21678,7 +21678,7 @@
         <v>14</v>
       </c>
       <c r="F95" s="2">
-        <v>4631</v>
+        <v>3542</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>15</v>
@@ -21710,7 +21710,7 @@
         <v>14</v>
       </c>
       <c r="F96" s="2">
-        <v>2991</v>
+        <v>3907</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>15</v>
@@ -21742,7 +21742,7 @@
         <v>14</v>
       </c>
       <c r="F97" s="2">
-        <v>2745</v>
+        <v>1700</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>15</v>
@@ -21774,7 +21774,7 @@
         <v>14</v>
       </c>
       <c r="F98" s="2">
-        <v>4522</v>
+        <v>3327</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>15</v>
@@ -21806,7 +21806,7 @@
         <v>14</v>
       </c>
       <c r="F99" s="2">
-        <v>4408</v>
+        <v>2620</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>15</v>
@@ -21838,7 +21838,7 @@
         <v>14</v>
       </c>
       <c r="F100" s="2">
-        <v>1146</v>
+        <v>858</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>15</v>
@@ -21870,7 +21870,7 @@
         <v>14</v>
       </c>
       <c r="F101" s="2">
-        <v>3449</v>
+        <v>1514</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>15</v>
@@ -21902,7 +21902,7 @@
         <v>14</v>
       </c>
       <c r="F102" s="2">
-        <v>873</v>
+        <v>1368</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>15</v>
@@ -21934,7 +21934,7 @@
         <v>14</v>
       </c>
       <c r="F103" s="2">
-        <v>3616</v>
+        <v>1934</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>15</v>
@@ -21966,7 +21966,7 @@
         <v>14</v>
       </c>
       <c r="F104" s="2">
-        <v>3594</v>
+        <v>3904</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>15</v>
@@ -21998,7 +21998,7 @@
         <v>14</v>
       </c>
       <c r="F105" s="2">
-        <v>4453</v>
+        <v>4213</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>15</v>
@@ -22030,7 +22030,7 @@
         <v>14</v>
       </c>
       <c r="F106" s="2">
-        <v>1173</v>
+        <v>2350</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>15</v>
@@ -22062,7 +22062,7 @@
         <v>14</v>
       </c>
       <c r="F107" s="2">
-        <v>1820</v>
+        <v>2791</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>15</v>
@@ -22094,7 +22094,7 @@
         <v>14</v>
       </c>
       <c r="F108" s="2">
-        <v>2879</v>
+        <v>3925</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>15</v>
@@ -22126,7 +22126,7 @@
         <v>14</v>
       </c>
       <c r="F109" s="2">
-        <v>3945</v>
+        <v>2431</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>15</v>
@@ -22158,7 +22158,7 @@
         <v>14</v>
       </c>
       <c r="F110" s="2">
-        <v>3436</v>
+        <v>4053</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>15</v>
@@ -22190,7 +22190,7 @@
         <v>14</v>
       </c>
       <c r="F111" s="2">
-        <v>3384</v>
+        <v>1359</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>15</v>
@@ -22222,7 +22222,7 @@
         <v>14</v>
       </c>
       <c r="F112" s="2">
-        <v>4399</v>
+        <v>2191</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>15</v>
@@ -22254,7 +22254,7 @@
         <v>14</v>
       </c>
       <c r="F113" s="2">
-        <v>4783</v>
+        <v>3904</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>15</v>
@@ -22286,7 +22286,7 @@
         <v>14</v>
       </c>
       <c r="F114" s="2">
-        <v>2326</v>
+        <v>4467</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>15</v>
@@ -22318,7 +22318,7 @@
         <v>14</v>
       </c>
       <c r="F115" s="2">
-        <v>2694</v>
+        <v>3973</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>15</v>
@@ -22350,7 +22350,7 @@
         <v>14</v>
       </c>
       <c r="F116" s="2">
-        <v>1800</v>
+        <v>2106</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>15</v>
@@ -22382,7 +22382,7 @@
         <v>14</v>
       </c>
       <c r="F117" s="2">
-        <v>4355</v>
+        <v>1067</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>15</v>
@@ -22414,7 +22414,7 @@
         <v>14</v>
       </c>
       <c r="F118" s="2">
-        <v>1458</v>
+        <v>4544</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>15</v>
@@ -22446,7 +22446,7 @@
         <v>14</v>
       </c>
       <c r="F119" s="2">
-        <v>4342</v>
+        <v>4179</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>15</v>
@@ -22478,7 +22478,7 @@
         <v>14</v>
       </c>
       <c r="F120" s="2">
-        <v>2689</v>
+        <v>1997</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>15</v>
@@ -22510,7 +22510,7 @@
         <v>14</v>
       </c>
       <c r="F121" s="2">
-        <v>883</v>
+        <v>3116</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>15</v>
@@ -22542,7 +22542,7 @@
         <v>14</v>
       </c>
       <c r="F122" s="2">
-        <v>1399</v>
+        <v>4615</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>15</v>
@@ -22574,7 +22574,7 @@
         <v>14</v>
       </c>
       <c r="F123" s="2">
-        <v>3209</v>
+        <v>2361</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>15</v>
@@ -22606,7 +22606,7 @@
         <v>14</v>
       </c>
       <c r="F124" s="2">
-        <v>2931</v>
+        <v>3614</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>15</v>
@@ -22638,7 +22638,7 @@
         <v>14</v>
       </c>
       <c r="F125" s="2">
-        <v>2729</v>
+        <v>1510</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>15</v>
@@ -22670,7 +22670,7 @@
         <v>14</v>
       </c>
       <c r="F126" s="2">
-        <v>4132</v>
+        <v>3429</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>15</v>
@@ -22702,7 +22702,7 @@
         <v>14</v>
       </c>
       <c r="F127" s="2">
-        <v>2167</v>
+        <v>2191</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>15</v>
@@ -22734,7 +22734,7 @@
         <v>14</v>
       </c>
       <c r="F128" s="2">
-        <v>1865</v>
+        <v>1336</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>15</v>
@@ -22766,7 +22766,7 @@
         <v>14</v>
       </c>
       <c r="F129" s="2">
-        <v>2940</v>
+        <v>4385</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>15</v>
@@ -22798,7 +22798,7 @@
         <v>14</v>
       </c>
       <c r="F130" s="2">
-        <v>914</v>
+        <v>1116</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>15</v>
@@ -22830,7 +22830,7 @@
         <v>14</v>
       </c>
       <c r="F131" s="2">
-        <v>4588</v>
+        <v>1343</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>15</v>
@@ -22862,7 +22862,7 @@
         <v>14</v>
       </c>
       <c r="F132" s="2">
-        <v>2490</v>
+        <v>2388</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>15</v>
@@ -22894,7 +22894,7 @@
         <v>14</v>
       </c>
       <c r="F133" s="2">
-        <v>1219</v>
+        <v>1687</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>15</v>
@@ -22926,7 +22926,7 @@
         <v>14</v>
       </c>
       <c r="F134" s="2">
-        <v>2828</v>
+        <v>1916</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>15</v>
@@ -22958,7 +22958,7 @@
         <v>14</v>
       </c>
       <c r="F135" s="2">
-        <v>1678</v>
+        <v>1045</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>15</v>
@@ -22990,7 +22990,7 @@
         <v>14</v>
       </c>
       <c r="F136" s="2">
-        <v>3015</v>
+        <v>1834</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>15</v>
@@ -23022,7 +23022,7 @@
         <v>14</v>
       </c>
       <c r="F137" s="2">
-        <v>4046</v>
+        <v>4626</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>15</v>
@@ -23054,7 +23054,7 @@
         <v>14</v>
       </c>
       <c r="F138" s="2">
-        <v>3317</v>
+        <v>3829</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>15</v>
@@ -23086,7 +23086,7 @@
         <v>14</v>
       </c>
       <c r="F139" s="2">
-        <v>4790</v>
+        <v>3782</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>15</v>
@@ -23118,7 +23118,7 @@
         <v>14</v>
       </c>
       <c r="F140" s="2">
-        <v>4721</v>
+        <v>2941</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>15</v>
@@ -23150,7 +23150,7 @@
         <v>14</v>
       </c>
       <c r="F141" s="2">
-        <v>1968</v>
+        <v>4337</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>15</v>
@@ -23182,7 +23182,7 @@
         <v>14</v>
       </c>
       <c r="F142" s="2">
-        <v>3494</v>
+        <v>4740</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>15</v>
@@ -23214,7 +23214,7 @@
         <v>14</v>
       </c>
       <c r="F143" s="2">
-        <v>3265</v>
+        <v>1650</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>15</v>
@@ -23246,7 +23246,7 @@
         <v>14</v>
       </c>
       <c r="F144" s="2">
-        <v>3786</v>
+        <v>1862</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>15</v>
@@ -23278,7 +23278,7 @@
         <v>14</v>
       </c>
       <c r="F145" s="2">
-        <v>3672</v>
+        <v>4158</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>15</v>
@@ -23310,7 +23310,7 @@
         <v>14</v>
       </c>
       <c r="F146" s="2">
-        <v>2508</v>
+        <v>2614</v>
       </c>
       <c r="G146" s="2" t="s">
         <v>15</v>
@@ -23342,7 +23342,7 @@
         <v>14</v>
       </c>
       <c r="F147" s="2">
-        <v>3265</v>
+        <v>3863</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>15</v>
@@ -23374,7 +23374,7 @@
         <v>14</v>
       </c>
       <c r="F148" s="2">
-        <v>1599</v>
+        <v>4648</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>15</v>
@@ -23406,7 +23406,7 @@
         <v>14</v>
       </c>
       <c r="F149" s="2">
-        <v>1700</v>
+        <v>3974</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>15</v>
@@ -23438,7 +23438,7 @@
         <v>14</v>
       </c>
       <c r="F150" s="2">
-        <v>2081</v>
+        <v>3559</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>15</v>
@@ -23470,7 +23470,7 @@
         <v>14</v>
       </c>
       <c r="F151" s="2">
-        <v>2706</v>
+        <v>3201</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>15</v>
@@ -23502,7 +23502,7 @@
         <v>14</v>
       </c>
       <c r="F152" s="2">
-        <v>3004</v>
+        <v>4316</v>
       </c>
       <c r="G152" s="2" t="s">
         <v>15</v>
@@ -23534,7 +23534,7 @@
         <v>14</v>
       </c>
       <c r="F153" s="2">
-        <v>3173</v>
+        <v>2766</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>15</v>
@@ -23566,7 +23566,7 @@
         <v>14</v>
       </c>
       <c r="F154" s="2">
-        <v>1396</v>
+        <v>4419</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>15</v>
@@ -23598,7 +23598,7 @@
         <v>14</v>
       </c>
       <c r="F155" s="2">
-        <v>3670</v>
+        <v>1699</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>15</v>
@@ -23630,7 +23630,7 @@
         <v>14</v>
       </c>
       <c r="F156" s="2">
-        <v>3084</v>
+        <v>4777</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>15</v>
@@ -23662,7 +23662,7 @@
         <v>14</v>
       </c>
       <c r="F157" s="2">
-        <v>1010</v>
+        <v>3250</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>15</v>
@@ -23694,7 +23694,7 @@
         <v>14</v>
       </c>
       <c r="F158" s="2">
-        <v>2072</v>
+        <v>4464</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>15</v>
@@ -23726,7 +23726,7 @@
         <v>14</v>
       </c>
       <c r="F159" s="2">
-        <v>4495</v>
+        <v>1546</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>15</v>
@@ -23758,7 +23758,7 @@
         <v>14</v>
       </c>
       <c r="F160" s="2">
-        <v>1751</v>
+        <v>3618</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>15</v>
@@ -23790,7 +23790,7 @@
         <v>14</v>
       </c>
       <c r="F161" s="2">
-        <v>4149</v>
+        <v>1266</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>15</v>
@@ -23822,7 +23822,7 @@
         <v>14</v>
       </c>
       <c r="F162" s="2">
-        <v>4541</v>
+        <v>1759</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>15</v>
@@ -23854,7 +23854,7 @@
         <v>14</v>
       </c>
       <c r="F163" s="2">
-        <v>3099</v>
+        <v>2375</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>15</v>
@@ -23886,7 +23886,7 @@
         <v>14</v>
       </c>
       <c r="F164" s="2">
-        <v>3547</v>
+        <v>1108</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>15</v>
@@ -23918,7 +23918,7 @@
         <v>14</v>
       </c>
       <c r="F165" s="2">
-        <v>3705</v>
+        <v>2463</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>15</v>
@@ -23950,7 +23950,7 @@
         <v>14</v>
       </c>
       <c r="F166" s="2">
-        <v>3526</v>
+        <v>3730</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>15</v>
@@ -23982,7 +23982,7 @@
         <v>14</v>
       </c>
       <c r="F167" s="2">
-        <v>4026</v>
+        <v>3596</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>15</v>
@@ -24014,7 +24014,7 @@
         <v>14</v>
       </c>
       <c r="F168" s="2">
-        <v>4223</v>
+        <v>4321</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>15</v>
@@ -24046,7 +24046,7 @@
         <v>14</v>
       </c>
       <c r="F169" s="2">
-        <v>1563</v>
+        <v>4161</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>15</v>
@@ -24078,7 +24078,7 @@
         <v>14</v>
       </c>
       <c r="F170" s="2">
-        <v>1385</v>
+        <v>3239</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>15</v>
@@ -24110,7 +24110,7 @@
         <v>14</v>
       </c>
       <c r="F171" s="2">
-        <v>1975</v>
+        <v>3517</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>15</v>
@@ -24142,7 +24142,7 @@
         <v>14</v>
       </c>
       <c r="F172" s="2">
-        <v>919</v>
+        <v>2872</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>15</v>
@@ -24174,7 +24174,7 @@
         <v>14</v>
       </c>
       <c r="F173" s="2">
-        <v>3230</v>
+        <v>1947</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>15</v>
@@ -24206,7 +24206,7 @@
         <v>14</v>
       </c>
       <c r="F174" s="2">
-        <v>2653</v>
+        <v>3543</v>
       </c>
       <c r="G174" s="2" t="s">
         <v>15</v>
@@ -24238,7 +24238,7 @@
         <v>14</v>
       </c>
       <c r="F175" s="2">
-        <v>2019</v>
+        <v>1800</v>
       </c>
       <c r="G175" s="2" t="s">
         <v>15</v>
@@ -24270,7 +24270,7 @@
         <v>14</v>
       </c>
       <c r="F176" s="2">
-        <v>1502</v>
+        <v>4725</v>
       </c>
       <c r="G176" s="2" t="s">
         <v>15</v>
@@ -24302,7 +24302,7 @@
         <v>14</v>
       </c>
       <c r="F177" s="2">
-        <v>4096</v>
+        <v>2567</v>
       </c>
       <c r="G177" s="2" t="s">
         <v>15</v>
@@ -24334,7 +24334,7 @@
         <v>14</v>
       </c>
       <c r="F178" s="2">
-        <v>2706</v>
+        <v>3782</v>
       </c>
       <c r="G178" s="2" t="s">
         <v>15</v>
@@ -24366,7 +24366,7 @@
         <v>14</v>
       </c>
       <c r="F179" s="2">
-        <v>4432</v>
+        <v>3176</v>
       </c>
       <c r="G179" s="2" t="s">
         <v>15</v>
@@ -24398,7 +24398,7 @@
         <v>14</v>
       </c>
       <c r="F180" s="2">
-        <v>4355</v>
+        <v>3771</v>
       </c>
       <c r="G180" s="2" t="s">
         <v>15</v>
@@ -24430,7 +24430,7 @@
         <v>14</v>
       </c>
       <c r="F181" s="2">
-        <v>3426</v>
+        <v>2593</v>
       </c>
       <c r="G181" s="2" t="s">
         <v>15</v>
@@ -24462,7 +24462,7 @@
         <v>14</v>
       </c>
       <c r="F182" s="2">
-        <v>4487</v>
+        <v>2745</v>
       </c>
       <c r="G182" s="2" t="s">
         <v>15</v>
@@ -24494,7 +24494,7 @@
         <v>14</v>
       </c>
       <c r="F183" s="2">
-        <v>4336</v>
+        <v>1436</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>15</v>
@@ -24526,7 +24526,7 @@
         <v>14</v>
       </c>
       <c r="F184" s="2">
-        <v>1126</v>
+        <v>3323</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>15</v>
@@ -24558,7 +24558,7 @@
         <v>14</v>
       </c>
       <c r="F185" s="2">
-        <v>4708</v>
+        <v>3734</v>
       </c>
       <c r="G185" s="2" t="s">
         <v>15</v>
@@ -24590,7 +24590,7 @@
         <v>14</v>
       </c>
       <c r="F186" s="2">
-        <v>3700</v>
+        <v>3845</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>15</v>
@@ -24622,7 +24622,7 @@
         <v>14</v>
       </c>
       <c r="F187" s="2">
-        <v>3117</v>
+        <v>4516</v>
       </c>
       <c r="G187" s="2" t="s">
         <v>15</v>
@@ -24654,7 +24654,7 @@
         <v>14</v>
       </c>
       <c r="F188" s="2">
-        <v>1632</v>
+        <v>1023</v>
       </c>
       <c r="G188" s="2" t="s">
         <v>15</v>
@@ -24686,7 +24686,7 @@
         <v>14</v>
       </c>
       <c r="F189" s="2">
-        <v>2446</v>
+        <v>3499</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>15</v>
@@ -24718,7 +24718,7 @@
         <v>14</v>
       </c>
       <c r="F190" s="2">
-        <v>1330</v>
+        <v>1543</v>
       </c>
       <c r="G190" s="2" t="s">
         <v>15</v>
@@ -24750,7 +24750,7 @@
         <v>14</v>
       </c>
       <c r="F191" s="2">
-        <v>4109</v>
+        <v>1925</v>
       </c>
       <c r="G191" s="2" t="s">
         <v>15</v>
@@ -24782,7 +24782,7 @@
         <v>14</v>
       </c>
       <c r="F192" s="2">
-        <v>3115</v>
+        <v>1174</v>
       </c>
       <c r="G192" s="2" t="s">
         <v>15</v>
@@ -24814,7 +24814,7 @@
         <v>14</v>
       </c>
       <c r="F193" s="2">
-        <v>1239</v>
+        <v>2680</v>
       </c>
       <c r="G193" s="2" t="s">
         <v>15</v>
@@ -24846,7 +24846,7 @@
         <v>14</v>
       </c>
       <c r="F194" s="2">
-        <v>4192</v>
+        <v>854</v>
       </c>
       <c r="G194" s="2" t="s">
         <v>15</v>
@@ -24878,7 +24878,7 @@
         <v>14</v>
       </c>
       <c r="F195" s="2">
-        <v>2276</v>
+        <v>3663</v>
       </c>
       <c r="G195" s="2" t="s">
         <v>15</v>
@@ -24910,7 +24910,7 @@
         <v>14</v>
       </c>
       <c r="F196" s="2">
-        <v>978</v>
+        <v>1324</v>
       </c>
       <c r="G196" s="2" t="s">
         <v>15</v>
@@ -24942,7 +24942,7 @@
         <v>14</v>
       </c>
       <c r="F197" s="2">
-        <v>3598</v>
+        <v>2513</v>
       </c>
       <c r="G197" s="2" t="s">
         <v>15</v>
@@ -24974,7 +24974,7 @@
         <v>14</v>
       </c>
       <c r="F198" s="2">
-        <v>1694</v>
+        <v>3722</v>
       </c>
       <c r="G198" s="2" t="s">
         <v>15</v>
@@ -25006,7 +25006,7 @@
         <v>14</v>
       </c>
       <c r="F199" s="2">
-        <v>4429</v>
+        <v>3878</v>
       </c>
       <c r="G199" s="2" t="s">
         <v>15</v>
@@ -25038,7 +25038,7 @@
         <v>14</v>
       </c>
       <c r="F200" s="2">
-        <v>4607</v>
+        <v>1939</v>
       </c>
       <c r="G200" s="2" t="s">
         <v>15</v>
@@ -25070,7 +25070,7 @@
         <v>14</v>
       </c>
       <c r="F201" s="2">
-        <v>3575</v>
+        <v>4494</v>
       </c>
       <c r="G201" s="2" t="s">
         <v>15</v>
@@ -25102,7 +25102,7 @@
         <v>14</v>
       </c>
       <c r="F202" s="2">
-        <v>1079</v>
+        <v>4122</v>
       </c>
       <c r="G202" s="2" t="s">
         <v>15</v>
@@ -25134,7 +25134,7 @@
         <v>14</v>
       </c>
       <c r="F203" s="2">
-        <v>4149</v>
+        <v>3935</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>15</v>
@@ -25166,7 +25166,7 @@
         <v>14</v>
       </c>
       <c r="F204" s="2">
-        <v>4012</v>
+        <v>4672</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>15</v>
@@ -25198,7 +25198,7 @@
         <v>14</v>
       </c>
       <c r="F205" s="2">
-        <v>1046</v>
+        <v>3684</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>15</v>
@@ -25230,7 +25230,7 @@
         <v>14</v>
       </c>
       <c r="F206" s="2">
-        <v>2844</v>
+        <v>1774</v>
       </c>
       <c r="G206" s="2" t="s">
         <v>15</v>
@@ -25262,7 +25262,7 @@
         <v>14</v>
       </c>
       <c r="F207" s="2">
-        <v>2232</v>
+        <v>3742</v>
       </c>
       <c r="G207" s="2" t="s">
         <v>15</v>
@@ -25294,7 +25294,7 @@
         <v>14</v>
       </c>
       <c r="F208" s="2">
-        <v>4752</v>
+        <v>1896</v>
       </c>
       <c r="G208" s="2" t="s">
         <v>15</v>
@@ -25326,7 +25326,7 @@
         <v>14</v>
       </c>
       <c r="F209" s="2">
-        <v>4046</v>
+        <v>2196</v>
       </c>
       <c r="G209" s="2" t="s">
         <v>15</v>
@@ -25358,7 +25358,7 @@
         <v>14</v>
       </c>
       <c r="F210" s="2">
-        <v>2823</v>
+        <v>1002</v>
       </c>
       <c r="G210" s="2" t="s">
         <v>15</v>
@@ -25390,7 +25390,7 @@
         <v>14</v>
       </c>
       <c r="F211" s="2">
-        <v>4394</v>
+        <v>2066</v>
       </c>
       <c r="G211" s="2" t="s">
         <v>15</v>
@@ -25422,7 +25422,7 @@
         <v>14</v>
       </c>
       <c r="F212" s="2">
-        <v>3980</v>
+        <v>2476</v>
       </c>
       <c r="G212" s="2" t="s">
         <v>15</v>
@@ -25454,7 +25454,7 @@
         <v>14</v>
       </c>
       <c r="F213" s="2">
-        <v>3018</v>
+        <v>3351</v>
       </c>
       <c r="G213" s="2" t="s">
         <v>15</v>
@@ -25486,7 +25486,7 @@
         <v>14</v>
       </c>
       <c r="F214" s="2">
-        <v>1232</v>
+        <v>869</v>
       </c>
       <c r="G214" s="2" t="s">
         <v>15</v>
@@ -25518,7 +25518,7 @@
         <v>14</v>
       </c>
       <c r="F215" s="2">
-        <v>4731</v>
+        <v>3910</v>
       </c>
       <c r="G215" s="2" t="s">
         <v>15</v>
@@ -25550,7 +25550,7 @@
         <v>14</v>
       </c>
       <c r="F216" s="2">
-        <v>1352</v>
+        <v>3502</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>15</v>
@@ -25582,7 +25582,7 @@
         <v>14</v>
       </c>
       <c r="F217" s="2">
-        <v>3507</v>
+        <v>4506</v>
       </c>
       <c r="G217" s="2" t="s">
         <v>15</v>
@@ -25614,7 +25614,7 @@
         <v>14</v>
       </c>
       <c r="F218" s="2">
-        <v>4241</v>
+        <v>4200</v>
       </c>
       <c r="G218" s="2" t="s">
         <v>15</v>
@@ -25646,7 +25646,7 @@
         <v>14</v>
       </c>
       <c r="F219" s="2">
-        <v>2143</v>
+        <v>1805</v>
       </c>
       <c r="G219" s="2" t="s">
         <v>15</v>
@@ -25678,7 +25678,7 @@
         <v>14</v>
       </c>
       <c r="F220" s="2">
-        <v>3703</v>
+        <v>1647</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>15</v>
@@ -25710,7 +25710,7 @@
         <v>14</v>
       </c>
       <c r="F221" s="2">
-        <v>3073</v>
+        <v>1148</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>15</v>
@@ -25742,7 +25742,7 @@
         <v>14</v>
       </c>
       <c r="F222" s="2">
-        <v>1351</v>
+        <v>1008</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>15</v>
@@ -25774,7 +25774,7 @@
         <v>14</v>
       </c>
       <c r="F223" s="2">
-        <v>3568</v>
+        <v>4272</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>15</v>
@@ -25806,7 +25806,7 @@
         <v>14</v>
       </c>
       <c r="F224" s="2">
-        <v>1180</v>
+        <v>931</v>
       </c>
       <c r="G224" s="2" t="s">
         <v>15</v>
@@ -25838,7 +25838,7 @@
         <v>14</v>
       </c>
       <c r="F225" s="2">
-        <v>2351</v>
+        <v>4249</v>
       </c>
       <c r="G225" s="2" t="s">
         <v>15</v>
@@ -25870,7 +25870,7 @@
         <v>14</v>
       </c>
       <c r="F226" s="2">
-        <v>1179</v>
+        <v>1584</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>15</v>
@@ -25902,7 +25902,7 @@
         <v>14</v>
       </c>
       <c r="F227" s="2">
-        <v>3774</v>
+        <v>4569</v>
       </c>
       <c r="G227" s="2" t="s">
         <v>15</v>
@@ -25934,7 +25934,7 @@
         <v>14</v>
       </c>
       <c r="F228" s="2">
-        <v>969</v>
+        <v>2409</v>
       </c>
       <c r="G228" s="2" t="s">
         <v>15</v>
@@ -25966,7 +25966,7 @@
         <v>14</v>
       </c>
       <c r="F229" s="2">
-        <v>3025</v>
+        <v>2840</v>
       </c>
       <c r="G229" s="2" t="s">
         <v>15</v>
@@ -25998,7 +25998,7 @@
         <v>14</v>
       </c>
       <c r="F230" s="2">
-        <v>3053</v>
+        <v>1109</v>
       </c>
       <c r="G230" s="2" t="s">
         <v>15</v>
@@ -26030,7 +26030,7 @@
         <v>14</v>
       </c>
       <c r="F231" s="2">
-        <v>2652</v>
+        <v>2993</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>15</v>
@@ -26062,7 +26062,7 @@
         <v>14</v>
       </c>
       <c r="F232" s="2">
-        <v>1938</v>
+        <v>1900</v>
       </c>
       <c r="G232" s="2" t="s">
         <v>15</v>
@@ -26094,7 +26094,7 @@
         <v>14</v>
       </c>
       <c r="F233" s="2">
-        <v>4519</v>
+        <v>1549</v>
       </c>
       <c r="G233" s="2" t="s">
         <v>15</v>
@@ -26126,7 +26126,7 @@
         <v>14</v>
       </c>
       <c r="F234" s="2">
-        <v>3758</v>
+        <v>4690</v>
       </c>
       <c r="G234" s="2" t="s">
         <v>15</v>
@@ -26158,7 +26158,7 @@
         <v>14</v>
       </c>
       <c r="F235" s="2">
-        <v>3105</v>
+        <v>1555</v>
       </c>
       <c r="G235" s="2" t="s">
         <v>15</v>
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="F236" s="2">
-        <v>3707</v>
+        <v>3504</v>
       </c>
       <c r="G236" s="2" t="s">
         <v>15</v>
@@ -26222,7 +26222,7 @@
         <v>14</v>
       </c>
       <c r="F237" s="2">
-        <v>2830</v>
+        <v>2531</v>
       </c>
       <c r="G237" s="2" t="s">
         <v>15</v>
@@ -26254,7 +26254,7 @@
         <v>14</v>
       </c>
       <c r="F238" s="2">
-        <v>4258</v>
+        <v>1428</v>
       </c>
       <c r="G238" s="2" t="s">
         <v>15</v>
@@ -26286,7 +26286,7 @@
         <v>14</v>
       </c>
       <c r="F239" s="2">
-        <v>3948</v>
+        <v>2708</v>
       </c>
       <c r="G239" s="2" t="s">
         <v>15</v>
@@ -26318,7 +26318,7 @@
         <v>14</v>
       </c>
       <c r="F240" s="2">
-        <v>3954</v>
+        <v>2986</v>
       </c>
       <c r="G240" s="2" t="s">
         <v>15</v>
@@ -26350,7 +26350,7 @@
         <v>14</v>
       </c>
       <c r="F241" s="2">
-        <v>1090</v>
+        <v>3260</v>
       </c>
       <c r="G241" s="2" t="s">
         <v>15</v>
@@ -26382,7 +26382,7 @@
         <v>14</v>
       </c>
       <c r="F242" s="2">
-        <v>2608</v>
+        <v>4509</v>
       </c>
       <c r="G242" s="2" t="s">
         <v>15</v>
@@ -26414,7 +26414,7 @@
         <v>14</v>
       </c>
       <c r="F243" s="2">
-        <v>1295</v>
+        <v>3649</v>
       </c>
       <c r="G243" s="2" t="s">
         <v>15</v>
@@ -26446,7 +26446,7 @@
         <v>14</v>
       </c>
       <c r="F244" s="2">
-        <v>831</v>
+        <v>2814</v>
       </c>
       <c r="G244" s="2" t="s">
         <v>15</v>
@@ -26478,7 +26478,7 @@
         <v>14</v>
       </c>
       <c r="F245" s="2">
-        <v>1126</v>
+        <v>3050</v>
       </c>
       <c r="G245" s="2" t="s">
         <v>15</v>
@@ -26510,7 +26510,7 @@
         <v>14</v>
       </c>
       <c r="F246" s="2">
-        <v>3178</v>
+        <v>3066</v>
       </c>
       <c r="G246" s="2" t="s">
         <v>15</v>
@@ -26542,7 +26542,7 @@
         <v>14</v>
       </c>
       <c r="F247" s="2">
-        <v>1994</v>
+        <v>3630</v>
       </c>
       <c r="G247" s="2" t="s">
         <v>15</v>
@@ -26574,7 +26574,7 @@
         <v>14</v>
       </c>
       <c r="F248" s="2">
-        <v>1550</v>
+        <v>1226</v>
       </c>
       <c r="G248" s="2" t="s">
         <v>15</v>
@@ -26606,7 +26606,7 @@
         <v>14</v>
       </c>
       <c r="F249" s="2">
-        <v>2061</v>
+        <v>1591</v>
       </c>
       <c r="G249" s="2" t="s">
         <v>15</v>
@@ -26638,7 +26638,7 @@
         <v>14</v>
       </c>
       <c r="F250" s="2">
-        <v>3678</v>
+        <v>4377</v>
       </c>
       <c r="G250" s="2" t="s">
         <v>15</v>
@@ -26670,7 +26670,7 @@
         <v>14</v>
       </c>
       <c r="F251" s="2">
-        <v>1566</v>
+        <v>952</v>
       </c>
       <c r="G251" s="2" t="s">
         <v>15</v>
@@ -26702,7 +26702,7 @@
         <v>14</v>
       </c>
       <c r="F252" s="2">
-        <v>3317</v>
+        <v>2305</v>
       </c>
       <c r="G252" s="2" t="s">
         <v>15</v>
@@ -26734,7 +26734,7 @@
         <v>14</v>
       </c>
       <c r="F253" s="2">
-        <v>3546</v>
+        <v>1303</v>
       </c>
       <c r="G253" s="2" t="s">
         <v>15</v>
@@ -26766,7 +26766,7 @@
         <v>14</v>
       </c>
       <c r="F254" s="2">
-        <v>3378</v>
+        <v>3769</v>
       </c>
       <c r="G254" s="2" t="s">
         <v>15</v>
@@ -26798,7 +26798,7 @@
         <v>14</v>
       </c>
       <c r="F255" s="2">
-        <v>1175</v>
+        <v>2755</v>
       </c>
       <c r="G255" s="2" t="s">
         <v>15</v>
@@ -26830,7 +26830,7 @@
         <v>14</v>
       </c>
       <c r="F256" s="2">
-        <v>4325</v>
+        <v>1127</v>
       </c>
       <c r="G256" s="2" t="s">
         <v>15</v>
@@ -26862,7 +26862,7 @@
         <v>14</v>
       </c>
       <c r="F257" s="2">
-        <v>1886</v>
+        <v>2706</v>
       </c>
       <c r="G257" s="2" t="s">
         <v>15</v>
@@ -26894,7 +26894,7 @@
         <v>14</v>
       </c>
       <c r="F258" s="2">
-        <v>1822</v>
+        <v>3223</v>
       </c>
       <c r="G258" s="2" t="s">
         <v>15</v>
@@ -26926,7 +26926,7 @@
         <v>14</v>
       </c>
       <c r="F259" s="2">
-        <v>4151</v>
+        <v>1796</v>
       </c>
       <c r="G259" s="2" t="s">
         <v>15</v>
@@ -26958,7 +26958,7 @@
         <v>14</v>
       </c>
       <c r="F260" s="2">
-        <v>2037</v>
+        <v>944</v>
       </c>
       <c r="G260" s="2" t="s">
         <v>15</v>
@@ -26990,7 +26990,7 @@
         <v>14</v>
       </c>
       <c r="F261" s="2">
-        <v>4721</v>
+        <v>1426</v>
       </c>
       <c r="G261" s="2" t="s">
         <v>15</v>
@@ -27022,7 +27022,7 @@
         <v>14</v>
       </c>
       <c r="F262" s="2">
-        <v>4690</v>
+        <v>2446</v>
       </c>
       <c r="G262" s="2" t="s">
         <v>15</v>
@@ -27054,7 +27054,7 @@
         <v>14</v>
       </c>
       <c r="F263" s="2">
-        <v>4191</v>
+        <v>1945</v>
       </c>
       <c r="G263" s="2" t="s">
         <v>15</v>
@@ -27086,7 +27086,7 @@
         <v>14</v>
       </c>
       <c r="F264" s="2">
-        <v>807</v>
+        <v>2992</v>
       </c>
       <c r="G264" s="2" t="s">
         <v>15</v>
@@ -27118,7 +27118,7 @@
         <v>14</v>
       </c>
       <c r="F265" s="2">
-        <v>3404</v>
+        <v>1949</v>
       </c>
       <c r="G265" s="2" t="s">
         <v>15</v>
@@ -27150,7 +27150,7 @@
         <v>14</v>
       </c>
       <c r="F266" s="2">
-        <v>2315</v>
+        <v>1324</v>
       </c>
       <c r="G266" s="2" t="s">
         <v>15</v>
@@ -27182,7 +27182,7 @@
         <v>14</v>
       </c>
       <c r="F267" s="2">
-        <v>2065</v>
+        <v>2255</v>
       </c>
       <c r="G267" s="2" t="s">
         <v>15</v>
@@ -27214,7 +27214,7 @@
         <v>14</v>
       </c>
       <c r="F268" s="2">
-        <v>4758</v>
+        <v>1217</v>
       </c>
       <c r="G268" s="2" t="s">
         <v>15</v>
@@ -27246,7 +27246,7 @@
         <v>14</v>
       </c>
       <c r="F269" s="2">
-        <v>2104</v>
+        <v>2863</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>15</v>
@@ -27278,7 +27278,7 @@
         <v>14</v>
       </c>
       <c r="F270" s="2">
-        <v>1196</v>
+        <v>2514</v>
       </c>
       <c r="G270" s="2" t="s">
         <v>15</v>
@@ -27310,7 +27310,7 @@
         <v>14</v>
       </c>
       <c r="F271" s="2">
-        <v>2101</v>
+        <v>2581</v>
       </c>
       <c r="G271" s="2" t="s">
         <v>15</v>
@@ -27342,7 +27342,7 @@
         <v>14</v>
       </c>
       <c r="F272" s="2">
-        <v>4077</v>
+        <v>3381</v>
       </c>
       <c r="G272" s="2" t="s">
         <v>15</v>
@@ -27374,7 +27374,7 @@
         <v>14</v>
       </c>
       <c r="F273" s="2">
-        <v>3494</v>
+        <v>3640</v>
       </c>
       <c r="G273" s="2" t="s">
         <v>15</v>
@@ -27406,7 +27406,7 @@
         <v>14</v>
       </c>
       <c r="F274" s="2">
-        <v>1229</v>
+        <v>4587</v>
       </c>
       <c r="G274" s="2" t="s">
         <v>15</v>
@@ -27438,7 +27438,7 @@
         <v>14</v>
       </c>
       <c r="F275" s="2">
-        <v>2283</v>
+        <v>4224</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>15</v>
@@ -27470,7 +27470,7 @@
         <v>14</v>
       </c>
       <c r="F276" s="2">
-        <v>1980</v>
+        <v>2545</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>15</v>
@@ -27502,7 +27502,7 @@
         <v>14</v>
       </c>
       <c r="F277" s="2">
-        <v>2926</v>
+        <v>2351</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>15</v>
@@ -27534,7 +27534,7 @@
         <v>14</v>
       </c>
       <c r="F278" s="2">
-        <v>2493</v>
+        <v>3243</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>15</v>
@@ -27566,7 +27566,7 @@
         <v>14</v>
       </c>
       <c r="F279" s="2">
-        <v>1161</v>
+        <v>1883</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>15</v>
@@ -27598,7 +27598,7 @@
         <v>14</v>
       </c>
       <c r="F280" s="2">
-        <v>1615</v>
+        <v>2362</v>
       </c>
       <c r="G280" s="2" t="s">
         <v>15</v>
@@ -27630,7 +27630,7 @@
         <v>14</v>
       </c>
       <c r="F281" s="2">
-        <v>2182</v>
+        <v>1757</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>15</v>
@@ -27662,7 +27662,7 @@
         <v>14</v>
       </c>
       <c r="F282" s="2">
-        <v>3423</v>
+        <v>3695</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>15</v>
@@ -27694,7 +27694,7 @@
         <v>14</v>
       </c>
       <c r="F283" s="2">
-        <v>2094</v>
+        <v>3469</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>15</v>
@@ -27726,7 +27726,7 @@
         <v>14</v>
       </c>
       <c r="F284" s="2">
-        <v>1233</v>
+        <v>4694</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>15</v>
@@ -27758,7 +27758,7 @@
         <v>14</v>
       </c>
       <c r="F285" s="2">
-        <v>1955</v>
+        <v>2743</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>15</v>
@@ -27790,7 +27790,7 @@
         <v>14</v>
       </c>
       <c r="F286" s="2">
-        <v>2484</v>
+        <v>3806</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>15</v>
@@ -27822,7 +27822,7 @@
         <v>14</v>
       </c>
       <c r="F287" s="2">
-        <v>1424</v>
+        <v>2366</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>15</v>
@@ -27854,7 +27854,7 @@
         <v>14</v>
       </c>
       <c r="F288" s="2">
-        <v>3156</v>
+        <v>1470</v>
       </c>
       <c r="G288" s="2" t="s">
         <v>15</v>
@@ -27886,7 +27886,7 @@
         <v>14</v>
       </c>
       <c r="F289" s="2">
-        <v>3303</v>
+        <v>1517</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>15</v>
@@ -27918,7 +27918,7 @@
         <v>14</v>
       </c>
       <c r="F290" s="2">
-        <v>2708</v>
+        <v>3646</v>
       </c>
       <c r="G290" s="2" t="s">
         <v>15</v>
@@ -27950,7 +27950,7 @@
         <v>14</v>
       </c>
       <c r="F291" s="2">
-        <v>2983</v>
+        <v>2909</v>
       </c>
       <c r="G291" s="2" t="s">
         <v>15</v>
@@ -27982,7 +27982,7 @@
         <v>14</v>
       </c>
       <c r="F292" s="2">
-        <v>1503</v>
+        <v>831</v>
       </c>
       <c r="G292" s="2" t="s">
         <v>15</v>
@@ -28014,7 +28014,7 @@
         <v>14</v>
       </c>
       <c r="F293" s="2">
-        <v>1231</v>
+        <v>2511</v>
       </c>
       <c r="G293" s="2" t="s">
         <v>15</v>
@@ -28046,7 +28046,7 @@
         <v>14</v>
       </c>
       <c r="F294" s="2">
-        <v>2241</v>
+        <v>3654</v>
       </c>
       <c r="G294" s="2" t="s">
         <v>15</v>
@@ -28078,7 +28078,7 @@
         <v>14</v>
       </c>
       <c r="F295" s="2">
-        <v>1526</v>
+        <v>3598</v>
       </c>
       <c r="G295" s="2" t="s">
         <v>15</v>
@@ -28110,7 +28110,7 @@
         <v>14</v>
       </c>
       <c r="F296" s="2">
-        <v>2014</v>
+        <v>2453</v>
       </c>
       <c r="G296" s="2" t="s">
         <v>15</v>
@@ -28142,7 +28142,7 @@
         <v>14</v>
       </c>
       <c r="F297" s="2">
-        <v>2854</v>
+        <v>3012</v>
       </c>
       <c r="G297" s="2" t="s">
         <v>15</v>
@@ -28174,7 +28174,7 @@
         <v>14</v>
       </c>
       <c r="F298" s="2">
-        <v>1244</v>
+        <v>4235</v>
       </c>
       <c r="G298" s="2" t="s">
         <v>15</v>
@@ -28206,7 +28206,7 @@
         <v>14</v>
       </c>
       <c r="F299" s="2">
-        <v>2931</v>
+        <v>1065</v>
       </c>
       <c r="G299" s="2" t="s">
         <v>15</v>
@@ -28238,7 +28238,7 @@
         <v>14</v>
       </c>
       <c r="F300" s="2">
-        <v>878</v>
+        <v>4548</v>
       </c>
       <c r="G300" s="2" t="s">
         <v>15</v>
@@ -28270,7 +28270,7 @@
         <v>14</v>
       </c>
       <c r="F301" s="2">
-        <v>2804</v>
+        <v>4763</v>
       </c>
       <c r="G301" s="2" t="s">
         <v>15</v>
@@ -28302,7 +28302,7 @@
         <v>14</v>
       </c>
       <c r="F302" s="2">
-        <v>2763</v>
+        <v>3027</v>
       </c>
       <c r="G302" s="2" t="s">
         <v>15</v>
@@ -28334,7 +28334,7 @@
         <v>14</v>
       </c>
       <c r="F303" s="2">
-        <v>3566</v>
+        <v>4101</v>
       </c>
       <c r="G303" s="2" t="s">
         <v>15</v>
@@ -28366,7 +28366,7 @@
         <v>14</v>
       </c>
       <c r="F304" s="2">
-        <v>4037</v>
+        <v>2415</v>
       </c>
       <c r="G304" s="2" t="s">
         <v>15</v>
@@ -28398,7 +28398,7 @@
         <v>14</v>
       </c>
       <c r="F305" s="2">
-        <v>2387</v>
+        <v>2907</v>
       </c>
       <c r="G305" s="2" t="s">
         <v>15</v>
@@ -28430,7 +28430,7 @@
         <v>14</v>
       </c>
       <c r="F306" s="2">
-        <v>1496</v>
+        <v>1561</v>
       </c>
       <c r="G306" s="2" t="s">
         <v>15</v>
@@ -28462,7 +28462,7 @@
         <v>14</v>
       </c>
       <c r="F307" s="2">
-        <v>982</v>
+        <v>2159</v>
       </c>
       <c r="G307" s="2" t="s">
         <v>15</v>
@@ -28494,7 +28494,7 @@
         <v>14</v>
       </c>
       <c r="F308" s="2">
-        <v>2224</v>
+        <v>3445</v>
       </c>
       <c r="G308" s="2" t="s">
         <v>15</v>
@@ -28526,7 +28526,7 @@
         <v>14</v>
       </c>
       <c r="F309" s="2">
-        <v>3884</v>
+        <v>3658</v>
       </c>
       <c r="G309" s="2" t="s">
         <v>15</v>
@@ -28558,7 +28558,7 @@
         <v>14</v>
       </c>
       <c r="F310" s="2">
-        <v>1481</v>
+        <v>3266</v>
       </c>
       <c r="G310" s="2" t="s">
         <v>15</v>
@@ -28590,7 +28590,7 @@
         <v>14</v>
       </c>
       <c r="F311" s="2">
-        <v>1048</v>
+        <v>3620</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>15</v>
@@ -28622,7 +28622,7 @@
         <v>14</v>
       </c>
       <c r="F312" s="2">
-        <v>4217</v>
+        <v>3805</v>
       </c>
       <c r="G312" s="2" t="s">
         <v>15</v>
@@ -28654,7 +28654,7 @@
         <v>14</v>
       </c>
       <c r="F313" s="2">
-        <v>3558</v>
+        <v>1251</v>
       </c>
       <c r="G313" s="2" t="s">
         <v>15</v>
@@ -28686,7 +28686,7 @@
         <v>14</v>
       </c>
       <c r="F314" s="2">
-        <v>4702</v>
+        <v>1247</v>
       </c>
       <c r="G314" s="2" t="s">
         <v>15</v>
@@ -28718,7 +28718,7 @@
         <v>14</v>
       </c>
       <c r="F315" s="2">
-        <v>1877</v>
+        <v>1950</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>15</v>
@@ -28750,7 +28750,7 @@
         <v>14</v>
       </c>
       <c r="F316" s="2">
-        <v>1843</v>
+        <v>1477</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>15</v>
@@ -28782,7 +28782,7 @@
         <v>14</v>
       </c>
       <c r="F317" s="2">
-        <v>3656</v>
+        <v>1234</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>15</v>
@@ -28814,7 +28814,7 @@
         <v>14</v>
       </c>
       <c r="F318" s="2">
-        <v>1510</v>
+        <v>4451</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>15</v>
@@ -28846,7 +28846,7 @@
         <v>14</v>
       </c>
       <c r="F319" s="2">
-        <v>4579</v>
+        <v>4140</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>15</v>
@@ -28878,7 +28878,7 @@
         <v>14</v>
       </c>
       <c r="F320" s="2">
-        <v>2107</v>
+        <v>3230</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>15</v>
@@ -28910,7 +28910,7 @@
         <v>14</v>
       </c>
       <c r="F321" s="2">
-        <v>930</v>
+        <v>3047</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>15</v>
@@ -28942,7 +28942,7 @@
         <v>14</v>
       </c>
       <c r="F322" s="2">
-        <v>3996</v>
+        <v>2849</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>15</v>
@@ -28974,7 +28974,7 @@
         <v>14</v>
       </c>
       <c r="F323" s="2">
-        <v>2580</v>
+        <v>2294</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>15</v>
@@ -29006,7 +29006,7 @@
         <v>14</v>
       </c>
       <c r="F324" s="2">
-        <v>1775</v>
+        <v>3453</v>
       </c>
       <c r="G324" s="2" t="s">
         <v>15</v>
@@ -29038,7 +29038,7 @@
         <v>14</v>
       </c>
       <c r="F325" s="2">
-        <v>3393</v>
+        <v>960</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>15</v>
@@ -29070,7 +29070,7 @@
         <v>14</v>
       </c>
       <c r="F326" s="2">
-        <v>3911</v>
+        <v>2133</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>15</v>
@@ -29102,7 +29102,7 @@
         <v>14</v>
       </c>
       <c r="F327" s="2">
-        <v>3441</v>
+        <v>3056</v>
       </c>
       <c r="G327" s="2" t="s">
         <v>15</v>
@@ -29134,7 +29134,7 @@
         <v>14</v>
       </c>
       <c r="F328" s="2">
-        <v>4452</v>
+        <v>3342</v>
       </c>
       <c r="G328" s="2" t="s">
         <v>15</v>
@@ -29166,7 +29166,7 @@
         <v>14</v>
       </c>
       <c r="F329" s="2">
-        <v>2646</v>
+        <v>1757</v>
       </c>
       <c r="G329" s="2" t="s">
         <v>15</v>
@@ -29198,7 +29198,7 @@
         <v>14</v>
       </c>
       <c r="F330" s="2">
-        <v>4662</v>
+        <v>4244</v>
       </c>
       <c r="G330" s="2" t="s">
         <v>15</v>
@@ -29230,7 +29230,7 @@
         <v>14</v>
       </c>
       <c r="F331" s="2">
-        <v>3863</v>
+        <v>4119</v>
       </c>
       <c r="G331" s="2" t="s">
         <v>15</v>
@@ -29262,7 +29262,7 @@
         <v>14</v>
       </c>
       <c r="F332" s="2">
-        <v>2698</v>
+        <v>2824</v>
       </c>
       <c r="G332" s="2" t="s">
         <v>15</v>
@@ -29294,7 +29294,7 @@
         <v>14</v>
       </c>
       <c r="F333" s="2">
-        <v>1905</v>
+        <v>2980</v>
       </c>
       <c r="G333" s="2" t="s">
         <v>15</v>
@@ -29326,7 +29326,7 @@
         <v>14</v>
       </c>
       <c r="F334" s="2">
-        <v>2450</v>
+        <v>3244</v>
       </c>
       <c r="G334" s="2" t="s">
         <v>15</v>
@@ -29358,7 +29358,7 @@
         <v>14</v>
       </c>
       <c r="F335" s="2">
-        <v>3877</v>
+        <v>1729</v>
       </c>
       <c r="G335" s="2" t="s">
         <v>15</v>
@@ -29390,7 +29390,7 @@
         <v>14</v>
       </c>
       <c r="F336" s="2">
-        <v>4421</v>
+        <v>3796</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>15</v>
@@ -29422,7 +29422,7 @@
         <v>14</v>
       </c>
       <c r="F337" s="2">
-        <v>1337</v>
+        <v>2184</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>15</v>
@@ -29454,7 +29454,7 @@
         <v>14</v>
       </c>
       <c r="F338" s="2">
-        <v>2587</v>
+        <v>4775</v>
       </c>
       <c r="G338" s="2" t="s">
         <v>15</v>
@@ -29486,7 +29486,7 @@
         <v>14</v>
       </c>
       <c r="F339" s="2">
-        <v>1210</v>
+        <v>1948</v>
       </c>
       <c r="G339" s="2" t="s">
         <v>15</v>
@@ -29518,7 +29518,7 @@
         <v>14</v>
       </c>
       <c r="F340" s="2">
-        <v>4723</v>
+        <v>1064</v>
       </c>
       <c r="G340" s="2" t="s">
         <v>15</v>
@@ -29550,7 +29550,7 @@
         <v>14</v>
       </c>
       <c r="F341" s="2">
-        <v>2950</v>
+        <v>4638</v>
       </c>
       <c r="G341" s="2" t="s">
         <v>15</v>
@@ -29582,7 +29582,7 @@
         <v>14</v>
       </c>
       <c r="F342" s="2">
-        <v>2073</v>
+        <v>1925</v>
       </c>
       <c r="G342" s="2" t="s">
         <v>15</v>
@@ -29614,7 +29614,7 @@
         <v>14</v>
       </c>
       <c r="F343" s="2">
-        <v>3313</v>
+        <v>4611</v>
       </c>
       <c r="G343" s="2" t="s">
         <v>15</v>
@@ -29646,7 +29646,7 @@
         <v>14</v>
       </c>
       <c r="F344" s="2">
-        <v>3492</v>
+        <v>1268</v>
       </c>
       <c r="G344" s="2" t="s">
         <v>15</v>
@@ -29678,7 +29678,7 @@
         <v>14</v>
       </c>
       <c r="F345" s="2">
-        <v>3022</v>
+        <v>2128</v>
       </c>
       <c r="G345" s="2" t="s">
         <v>15</v>
@@ -29710,7 +29710,7 @@
         <v>14</v>
       </c>
       <c r="F346" s="2">
-        <v>1589</v>
+        <v>4637</v>
       </c>
       <c r="G346" s="2" t="s">
         <v>15</v>
@@ -29742,7 +29742,7 @@
         <v>14</v>
       </c>
       <c r="F347" s="2">
-        <v>4469</v>
+        <v>4689</v>
       </c>
       <c r="G347" s="2" t="s">
         <v>15</v>
@@ -29774,7 +29774,7 @@
         <v>14</v>
       </c>
       <c r="F348" s="2">
-        <v>4104</v>
+        <v>2996</v>
       </c>
       <c r="G348" s="2" t="s">
         <v>15</v>
@@ -29806,7 +29806,7 @@
         <v>14</v>
       </c>
       <c r="F349" s="2">
-        <v>4019</v>
+        <v>1299</v>
       </c>
       <c r="G349" s="2" t="s">
         <v>15</v>
@@ -29838,7 +29838,7 @@
         <v>14</v>
       </c>
       <c r="F350" s="2">
-        <v>811</v>
+        <v>1113</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>15</v>
@@ -29870,7 +29870,7 @@
         <v>14</v>
       </c>
       <c r="F351" s="2">
-        <v>4550</v>
+        <v>3800</v>
       </c>
       <c r="G351" s="2" t="s">
         <v>15</v>
@@ -29902,7 +29902,7 @@
         <v>14</v>
       </c>
       <c r="F352" s="2">
-        <v>3813</v>
+        <v>979</v>
       </c>
       <c r="G352" s="2" t="s">
         <v>15</v>
@@ -29934,7 +29934,7 @@
         <v>14</v>
       </c>
       <c r="F353" s="2">
-        <v>1690</v>
+        <v>3290</v>
       </c>
       <c r="G353" s="2" t="s">
         <v>15</v>
@@ -29966,7 +29966,7 @@
         <v>14</v>
       </c>
       <c r="F354" s="2">
-        <v>1159</v>
+        <v>1290</v>
       </c>
       <c r="G354" s="2" t="s">
         <v>15</v>
@@ -29998,7 +29998,7 @@
         <v>14</v>
       </c>
       <c r="F355" s="2">
-        <v>3893</v>
+        <v>3498</v>
       </c>
       <c r="G355" s="2" t="s">
         <v>15</v>
@@ -30030,7 +30030,7 @@
         <v>14</v>
       </c>
       <c r="F356" s="2">
-        <v>4162</v>
+        <v>3429</v>
       </c>
       <c r="G356" s="2" t="s">
         <v>15</v>
@@ -30062,7 +30062,7 @@
         <v>14</v>
       </c>
       <c r="F357" s="2">
-        <v>3573</v>
+        <v>1150</v>
       </c>
       <c r="G357" s="2" t="s">
         <v>15</v>
@@ -30094,7 +30094,7 @@
         <v>14</v>
       </c>
       <c r="F358" s="2">
-        <v>3480</v>
+        <v>4620</v>
       </c>
       <c r="G358" s="2" t="s">
         <v>15</v>
@@ -30126,7 +30126,7 @@
         <v>14</v>
       </c>
       <c r="F359" s="2">
-        <v>1442</v>
+        <v>2163</v>
       </c>
       <c r="G359" s="2" t="s">
         <v>15</v>
@@ -30158,7 +30158,7 @@
         <v>14</v>
       </c>
       <c r="F360" s="2">
-        <v>3050</v>
+        <v>1952</v>
       </c>
       <c r="G360" s="2" t="s">
         <v>15</v>
@@ -30190,7 +30190,7 @@
         <v>14</v>
       </c>
       <c r="F361" s="2">
-        <v>4263</v>
+        <v>4516</v>
       </c>
       <c r="G361" s="2" t="s">
         <v>15</v>
@@ -30222,7 +30222,7 @@
         <v>14</v>
       </c>
       <c r="F362" s="2">
-        <v>2896</v>
+        <v>1630</v>
       </c>
       <c r="G362" s="2" t="s">
         <v>15</v>
@@ -30254,7 +30254,7 @@
         <v>14</v>
       </c>
       <c r="F363" s="2">
-        <v>2347</v>
+        <v>2702</v>
       </c>
       <c r="G363" s="2" t="s">
         <v>15</v>
@@ -30286,7 +30286,7 @@
         <v>14</v>
       </c>
       <c r="F364" s="2">
-        <v>2764</v>
+        <v>1333</v>
       </c>
       <c r="G364" s="2" t="s">
         <v>15</v>
@@ -30318,7 +30318,7 @@
         <v>14</v>
       </c>
       <c r="F365" s="2">
-        <v>3431</v>
+        <v>2046</v>
       </c>
       <c r="G365" s="2" t="s">
         <v>15</v>
@@ -30350,7 +30350,7 @@
         <v>14</v>
       </c>
       <c r="F366" s="2">
-        <v>3262</v>
+        <v>800</v>
       </c>
       <c r="G366" s="2" t="s">
         <v>15</v>
@@ -30382,7 +30382,7 @@
         <v>14</v>
       </c>
       <c r="F367" s="2">
-        <v>1365</v>
+        <v>3996</v>
       </c>
       <c r="G367" s="2" t="s">
         <v>15</v>
@@ -30414,7 +30414,7 @@
         <v>14</v>
       </c>
       <c r="F368" s="2">
-        <v>2099</v>
+        <v>4691</v>
       </c>
       <c r="G368" s="2" t="s">
         <v>15</v>
@@ -30446,7 +30446,7 @@
         <v>14</v>
       </c>
       <c r="F369" s="2">
-        <v>3495</v>
+        <v>2586</v>
       </c>
       <c r="G369" s="2" t="s">
         <v>15</v>
@@ -30478,7 +30478,7 @@
         <v>14</v>
       </c>
       <c r="F370" s="2">
-        <v>2685</v>
+        <v>3418</v>
       </c>
       <c r="G370" s="2" t="s">
         <v>15</v>
@@ -30510,7 +30510,7 @@
         <v>14</v>
       </c>
       <c r="F371" s="2">
-        <v>1454</v>
+        <v>2409</v>
       </c>
       <c r="G371" s="2" t="s">
         <v>15</v>
@@ -30542,7 +30542,7 @@
         <v>14</v>
       </c>
       <c r="F372" s="2">
-        <v>1610</v>
+        <v>1705</v>
       </c>
       <c r="G372" s="2" t="s">
         <v>15</v>
@@ -30574,7 +30574,7 @@
         <v>14</v>
       </c>
       <c r="F373" s="2">
-        <v>3922</v>
+        <v>4157</v>
       </c>
       <c r="G373" s="2" t="s">
         <v>15</v>
@@ -30606,7 +30606,7 @@
         <v>14</v>
       </c>
       <c r="F374" s="2">
-        <v>1508</v>
+        <v>1324</v>
       </c>
       <c r="G374" s="2" t="s">
         <v>15</v>
@@ -30638,7 +30638,7 @@
         <v>14</v>
       </c>
       <c r="F375" s="2">
-        <v>1586</v>
+        <v>4738</v>
       </c>
       <c r="G375" s="2" t="s">
         <v>15</v>
@@ -30670,7 +30670,7 @@
         <v>14</v>
       </c>
       <c r="F376" s="2">
-        <v>1532</v>
+        <v>2360</v>
       </c>
       <c r="G376" s="2" t="s">
         <v>15</v>
@@ -30702,7 +30702,7 @@
         <v>14</v>
       </c>
       <c r="F377" s="2">
-        <v>2836</v>
+        <v>952</v>
       </c>
       <c r="G377" s="2" t="s">
         <v>15</v>
@@ -30734,7 +30734,7 @@
         <v>14</v>
       </c>
       <c r="F378" s="2">
-        <v>2304</v>
+        <v>2314</v>
       </c>
       <c r="G378" s="2" t="s">
         <v>15</v>
@@ -30766,7 +30766,7 @@
         <v>14</v>
       </c>
       <c r="F379" s="2">
-        <v>3148</v>
+        <v>3955</v>
       </c>
       <c r="G379" s="2" t="s">
         <v>15</v>
@@ -30798,7 +30798,7 @@
         <v>14</v>
       </c>
       <c r="F380" s="2">
-        <v>836</v>
+        <v>2004</v>
       </c>
       <c r="G380" s="2" t="s">
         <v>15</v>
@@ -30830,7 +30830,7 @@
         <v>14</v>
       </c>
       <c r="F381" s="2">
-        <v>3871</v>
+        <v>3094</v>
       </c>
       <c r="G381" s="2" t="s">
         <v>15</v>
@@ -30862,7 +30862,7 @@
         <v>14</v>
       </c>
       <c r="F382" s="2">
-        <v>4465</v>
+        <v>1945</v>
       </c>
       <c r="G382" s="2" t="s">
         <v>15</v>
@@ -30894,7 +30894,7 @@
         <v>14</v>
       </c>
       <c r="F383" s="2">
-        <v>2545</v>
+        <v>1104</v>
       </c>
       <c r="G383" s="2" t="s">
         <v>15</v>
@@ -30926,7 +30926,7 @@
         <v>14</v>
       </c>
       <c r="F384" s="2">
-        <v>2579</v>
+        <v>1013</v>
       </c>
       <c r="G384" s="2" t="s">
         <v>15</v>
@@ -30958,7 +30958,7 @@
         <v>14</v>
       </c>
       <c r="F385" s="2">
-        <v>1328</v>
+        <v>4416</v>
       </c>
       <c r="G385" s="2" t="s">
         <v>15</v>
@@ -30990,7 +30990,7 @@
         <v>14</v>
       </c>
       <c r="F386" s="2">
-        <v>3806</v>
+        <v>3663</v>
       </c>
       <c r="G386" s="2" t="s">
         <v>15</v>
@@ -31022,7 +31022,7 @@
         <v>14</v>
       </c>
       <c r="F387" s="2">
-        <v>2004</v>
+        <v>3340</v>
       </c>
       <c r="G387" s="2" t="s">
         <v>15</v>
@@ -31054,7 +31054,7 @@
         <v>14</v>
       </c>
       <c r="F388" s="2">
-        <v>4113</v>
+        <v>1716</v>
       </c>
       <c r="G388" s="2" t="s">
         <v>15</v>
@@ -31086,7 +31086,7 @@
         <v>14</v>
       </c>
       <c r="F389" s="2">
-        <v>2185</v>
+        <v>4009</v>
       </c>
       <c r="G389" s="2" t="s">
         <v>15</v>
@@ -31118,7 +31118,7 @@
         <v>14</v>
       </c>
       <c r="F390" s="2">
-        <v>1319</v>
+        <v>3834</v>
       </c>
       <c r="G390" s="2" t="s">
         <v>15</v>
@@ -31150,7 +31150,7 @@
         <v>14</v>
       </c>
       <c r="F391" s="2">
-        <v>2257</v>
+        <v>950</v>
       </c>
       <c r="G391" s="2" t="s">
         <v>15</v>
@@ -31182,7 +31182,7 @@
         <v>14</v>
       </c>
       <c r="F392" s="2">
-        <v>4263</v>
+        <v>2543</v>
       </c>
       <c r="G392" s="2" t="s">
         <v>15</v>
@@ -31214,7 +31214,7 @@
         <v>14</v>
       </c>
       <c r="F393" s="2">
-        <v>3090</v>
+        <v>2181</v>
       </c>
       <c r="G393" s="2" t="s">
         <v>15</v>
@@ -31246,7 +31246,7 @@
         <v>14</v>
       </c>
       <c r="F394" s="2">
-        <v>1205</v>
+        <v>1736</v>
       </c>
       <c r="G394" s="2" t="s">
         <v>15</v>
@@ -31278,7 +31278,7 @@
         <v>14</v>
       </c>
       <c r="F395" s="2">
-        <v>2852</v>
+        <v>870</v>
       </c>
       <c r="G395" s="2" t="s">
         <v>15</v>
@@ -31310,7 +31310,7 @@
         <v>14</v>
       </c>
       <c r="F396" s="2">
-        <v>3926</v>
+        <v>1254</v>
       </c>
       <c r="G396" s="2" t="s">
         <v>15</v>
@@ -31342,7 +31342,7 @@
         <v>14</v>
       </c>
       <c r="F397" s="2">
-        <v>2114</v>
+        <v>2575</v>
       </c>
       <c r="G397" s="2" t="s">
         <v>15</v>
@@ -31374,7 +31374,7 @@
         <v>14</v>
       </c>
       <c r="F398" s="2">
-        <v>2125</v>
+        <v>3091</v>
       </c>
       <c r="G398" s="2" t="s">
         <v>15</v>
@@ -31406,7 +31406,7 @@
         <v>14</v>
       </c>
       <c r="F399" s="2">
-        <v>3744</v>
+        <v>1443</v>
       </c>
       <c r="G399" s="2" t="s">
         <v>15</v>
@@ -31438,7 +31438,7 @@
         <v>14</v>
       </c>
       <c r="F400" s="2">
-        <v>4378</v>
+        <v>3362</v>
       </c>
       <c r="G400" s="2" t="s">
         <v>15</v>
@@ -31470,7 +31470,7 @@
         <v>14</v>
       </c>
       <c r="F401" s="2">
-        <v>3688</v>
+        <v>1140</v>
       </c>
       <c r="G401" s="2" t="s">
         <v>15</v>
@@ -31502,7 +31502,7 @@
         <v>14</v>
       </c>
       <c r="F402" s="2">
-        <v>2113</v>
+        <v>3980</v>
       </c>
       <c r="G402" s="2" t="s">
         <v>15</v>
@@ -31534,7 +31534,7 @@
         <v>14</v>
       </c>
       <c r="F403" s="2">
-        <v>4667</v>
+        <v>4357</v>
       </c>
       <c r="G403" s="2" t="s">
         <v>15</v>
@@ -31566,7 +31566,7 @@
         <v>14</v>
       </c>
       <c r="F404" s="2">
-        <v>1358</v>
+        <v>923</v>
       </c>
       <c r="G404" s="2" t="s">
         <v>15</v>
@@ -31598,7 +31598,7 @@
         <v>14</v>
       </c>
       <c r="F405" s="2">
-        <v>1756</v>
+        <v>935</v>
       </c>
       <c r="G405" s="2" t="s">
         <v>15</v>
@@ -31630,7 +31630,7 @@
         <v>14</v>
       </c>
       <c r="F406" s="2">
-        <v>2135</v>
+        <v>1189</v>
       </c>
       <c r="G406" s="2" t="s">
         <v>15</v>
@@ -31662,7 +31662,7 @@
         <v>14</v>
       </c>
       <c r="F407" s="2">
-        <v>3174</v>
+        <v>1050</v>
       </c>
       <c r="G407" s="2" t="s">
         <v>15</v>
@@ -31694,7 +31694,7 @@
         <v>14</v>
       </c>
       <c r="F408" s="2">
-        <v>3799</v>
+        <v>1027</v>
       </c>
       <c r="G408" s="2" t="s">
         <v>15</v>
@@ -31726,7 +31726,7 @@
         <v>14</v>
       </c>
       <c r="F409" s="2">
-        <v>4508</v>
+        <v>4181</v>
       </c>
       <c r="G409" s="2" t="s">
         <v>15</v>
@@ -31758,7 +31758,7 @@
         <v>14</v>
       </c>
       <c r="F410" s="2">
-        <v>4000</v>
+        <v>1486</v>
       </c>
       <c r="G410" s="2" t="s">
         <v>15</v>
@@ -31790,7 +31790,7 @@
         <v>14</v>
       </c>
       <c r="F411" s="2">
-        <v>3077</v>
+        <v>4747</v>
       </c>
       <c r="G411" s="2" t="s">
         <v>15</v>
@@ -31822,7 +31822,7 @@
         <v>14</v>
       </c>
       <c r="F412" s="2">
-        <v>1470</v>
+        <v>2933</v>
       </c>
       <c r="G412" s="2" t="s">
         <v>15</v>
@@ -31854,7 +31854,7 @@
         <v>14</v>
       </c>
       <c r="F413" s="2">
-        <v>1846</v>
+        <v>1428</v>
       </c>
       <c r="G413" s="2" t="s">
         <v>15</v>
@@ -31886,7 +31886,7 @@
         <v>14</v>
       </c>
       <c r="F414" s="2">
-        <v>4221</v>
+        <v>1050</v>
       </c>
       <c r="G414" s="2" t="s">
         <v>15</v>
@@ -31918,7 +31918,7 @@
         <v>14</v>
       </c>
       <c r="F415" s="2">
-        <v>2649</v>
+        <v>3646</v>
       </c>
       <c r="G415" s="2" t="s">
         <v>15</v>
@@ -31950,7 +31950,7 @@
         <v>14</v>
       </c>
       <c r="F416" s="2">
-        <v>2774</v>
+        <v>1963</v>
       </c>
       <c r="G416" s="2" t="s">
         <v>15</v>
@@ -31982,7 +31982,7 @@
         <v>14</v>
       </c>
       <c r="F417" s="2">
-        <v>2732</v>
+        <v>964</v>
       </c>
       <c r="G417" s="2" t="s">
         <v>15</v>
@@ -32014,7 +32014,7 @@
         <v>14</v>
       </c>
       <c r="F418" s="2">
-        <v>819</v>
+        <v>4768</v>
       </c>
       <c r="G418" s="2" t="s">
         <v>15</v>
@@ -32046,7 +32046,7 @@
         <v>14</v>
       </c>
       <c r="F419" s="2">
-        <v>1951</v>
+        <v>3055</v>
       </c>
       <c r="G419" s="2" t="s">
         <v>15</v>
@@ -32078,7 +32078,7 @@
         <v>14</v>
       </c>
       <c r="F420" s="2">
-        <v>3792</v>
+        <v>2189</v>
       </c>
       <c r="G420" s="2" t="s">
         <v>15</v>
@@ -32110,7 +32110,7 @@
         <v>14</v>
       </c>
       <c r="F421" s="2">
-        <v>2875</v>
+        <v>959</v>
       </c>
       <c r="G421" s="2" t="s">
         <v>15</v>
@@ -32142,7 +32142,7 @@
         <v>14</v>
       </c>
       <c r="F422" s="2">
-        <v>2237</v>
+        <v>4728</v>
       </c>
       <c r="G422" s="2" t="s">
         <v>15</v>
@@ -32174,7 +32174,7 @@
         <v>14</v>
       </c>
       <c r="F423" s="2">
-        <v>3265</v>
+        <v>3599</v>
       </c>
       <c r="G423" s="2" t="s">
         <v>15</v>
@@ -32206,7 +32206,7 @@
         <v>14</v>
       </c>
       <c r="F424" s="2">
-        <v>4047</v>
+        <v>3689</v>
       </c>
       <c r="G424" s="2" t="s">
         <v>15</v>
@@ -32238,7 +32238,7 @@
         <v>14</v>
       </c>
       <c r="F425" s="2">
-        <v>1460</v>
+        <v>1328</v>
       </c>
       <c r="G425" s="2" t="s">
         <v>15</v>
@@ -32270,7 +32270,7 @@
         <v>14</v>
       </c>
       <c r="F426" s="2">
-        <v>2195</v>
+        <v>2073</v>
       </c>
       <c r="G426" s="2" t="s">
         <v>15</v>
@@ -32302,7 +32302,7 @@
         <v>14</v>
       </c>
       <c r="F427" s="2">
-        <v>4317</v>
+        <v>2351</v>
       </c>
       <c r="G427" s="2" t="s">
         <v>15</v>
@@ -32334,7 +32334,7 @@
         <v>14</v>
       </c>
       <c r="F428" s="2">
-        <v>4371</v>
+        <v>4005</v>
       </c>
       <c r="G428" s="2" t="s">
         <v>15</v>
@@ -32366,7 +32366,7 @@
         <v>14</v>
       </c>
       <c r="F429" s="2">
-        <v>876</v>
+        <v>813</v>
       </c>
       <c r="G429" s="2" t="s">
         <v>15</v>
@@ -32398,7 +32398,7 @@
         <v>14</v>
       </c>
       <c r="F430" s="2">
-        <v>3448</v>
+        <v>3222</v>
       </c>
       <c r="G430" s="2" t="s">
         <v>15</v>
@@ -32430,7 +32430,7 @@
         <v>14</v>
       </c>
       <c r="F431" s="2">
-        <v>3500</v>
+        <v>1774</v>
       </c>
       <c r="G431" s="2" t="s">
         <v>15</v>
@@ -32462,7 +32462,7 @@
         <v>14</v>
       </c>
       <c r="F432" s="2">
-        <v>3018</v>
+        <v>2908</v>
       </c>
       <c r="G432" s="2" t="s">
         <v>15</v>
@@ -32494,7 +32494,7 @@
         <v>14</v>
       </c>
       <c r="F433" s="2">
-        <v>1493</v>
+        <v>1187</v>
       </c>
       <c r="G433" s="2" t="s">
         <v>15</v>
@@ -32526,7 +32526,7 @@
         <v>14</v>
       </c>
       <c r="F434" s="2">
-        <v>1559</v>
+        <v>4766</v>
       </c>
       <c r="G434" s="2" t="s">
         <v>15</v>
@@ -32558,7 +32558,7 @@
         <v>14</v>
       </c>
       <c r="F435" s="2">
-        <v>1359</v>
+        <v>3107</v>
       </c>
       <c r="G435" s="2" t="s">
         <v>15</v>
@@ -32590,7 +32590,7 @@
         <v>14</v>
       </c>
       <c r="F436" s="2">
-        <v>3639</v>
+        <v>3180</v>
       </c>
       <c r="G436" s="2" t="s">
         <v>15</v>
@@ -32622,7 +32622,7 @@
         <v>14</v>
       </c>
       <c r="F437" s="2">
-        <v>1153</v>
+        <v>3860</v>
       </c>
       <c r="G437" s="2" t="s">
         <v>15</v>
@@ -32654,7 +32654,7 @@
         <v>14</v>
       </c>
       <c r="F438" s="2">
-        <v>4272</v>
+        <v>3144</v>
       </c>
       <c r="G438" s="2" t="s">
         <v>15</v>
@@ -32686,7 +32686,7 @@
         <v>14</v>
       </c>
       <c r="F439" s="2">
-        <v>4712</v>
+        <v>2853</v>
       </c>
       <c r="G439" s="2" t="s">
         <v>15</v>
@@ -32718,7 +32718,7 @@
         <v>14</v>
       </c>
       <c r="F440" s="2">
-        <v>1482</v>
+        <v>4773</v>
       </c>
       <c r="G440" s="2" t="s">
         <v>15</v>
@@ -32750,7 +32750,7 @@
         <v>14</v>
       </c>
       <c r="F441" s="2">
-        <v>2859</v>
+        <v>3557</v>
       </c>
       <c r="G441" s="2" t="s">
         <v>15</v>
@@ -32782,7 +32782,7 @@
         <v>14</v>
       </c>
       <c r="F442" s="2">
-        <v>1995</v>
+        <v>4217</v>
       </c>
       <c r="G442" s="2" t="s">
         <v>15</v>
@@ -32814,7 +32814,7 @@
         <v>14</v>
       </c>
       <c r="F443" s="2">
-        <v>3195</v>
+        <v>3114</v>
       </c>
       <c r="G443" s="2" t="s">
         <v>15</v>
@@ -32846,7 +32846,7 @@
         <v>14</v>
       </c>
       <c r="F444" s="2">
-        <v>1872</v>
+        <v>3676</v>
       </c>
       <c r="G444" s="2" t="s">
         <v>15</v>
@@ -32878,7 +32878,7 @@
         <v>14</v>
       </c>
       <c r="F445" s="2">
-        <v>3397</v>
+        <v>4321</v>
       </c>
       <c r="G445" s="2" t="s">
         <v>15</v>
@@ -32910,7 +32910,7 @@
         <v>14</v>
       </c>
       <c r="F446" s="2">
-        <v>3967</v>
+        <v>4501</v>
       </c>
       <c r="G446" s="2" t="s">
         <v>15</v>
@@ -32942,7 +32942,7 @@
         <v>14</v>
       </c>
       <c r="F447" s="2">
-        <v>1312</v>
+        <v>1468</v>
       </c>
       <c r="G447" s="2" t="s">
         <v>15</v>
@@ -32974,7 +32974,7 @@
         <v>14</v>
       </c>
       <c r="F448" s="2">
-        <v>2343</v>
+        <v>3861</v>
       </c>
       <c r="G448" s="2" t="s">
         <v>15</v>
@@ -33006,7 +33006,7 @@
         <v>14</v>
       </c>
       <c r="F449" s="2">
-        <v>3381</v>
+        <v>3172</v>
       </c>
       <c r="G449" s="2" t="s">
         <v>15</v>
@@ -33038,7 +33038,7 @@
         <v>14</v>
       </c>
       <c r="F450" s="2">
-        <v>1370</v>
+        <v>1535</v>
       </c>
       <c r="G450" s="2" t="s">
         <v>15</v>
@@ -33070,7 +33070,7 @@
         <v>14</v>
       </c>
       <c r="F451" s="2">
-        <v>2424</v>
+        <v>3165</v>
       </c>
       <c r="G451" s="2" t="s">
         <v>15</v>
@@ -33102,7 +33102,7 @@
         <v>14</v>
       </c>
       <c r="F452" s="2">
-        <v>1274</v>
+        <v>4614</v>
       </c>
       <c r="G452" s="2" t="s">
         <v>15</v>
@@ -33134,7 +33134,7 @@
         <v>14</v>
       </c>
       <c r="F453" s="2">
-        <v>3713</v>
+        <v>1847</v>
       </c>
       <c r="G453" s="2" t="s">
         <v>15</v>
@@ -33166,7 +33166,7 @@
         <v>14</v>
       </c>
       <c r="F454" s="2">
-        <v>4633</v>
+        <v>4071</v>
       </c>
       <c r="G454" s="2" t="s">
         <v>15</v>
@@ -33198,7 +33198,7 @@
         <v>14</v>
       </c>
       <c r="F455" s="2">
-        <v>1782</v>
+        <v>3007</v>
       </c>
       <c r="G455" s="2" t="s">
         <v>15</v>
@@ -33230,7 +33230,7 @@
         <v>14</v>
       </c>
       <c r="F456" s="2">
-        <v>1038</v>
+        <v>3839</v>
       </c>
       <c r="G456" s="2" t="s">
         <v>15</v>
@@ -33262,7 +33262,7 @@
         <v>14</v>
       </c>
       <c r="F457" s="2">
-        <v>3336</v>
+        <v>3081</v>
       </c>
       <c r="G457" s="2" t="s">
         <v>15</v>
@@ -33294,7 +33294,7 @@
         <v>14</v>
       </c>
       <c r="F458" s="2">
-        <v>1106</v>
+        <v>4185</v>
       </c>
       <c r="G458" s="2" t="s">
         <v>15</v>
@@ -33326,7 +33326,7 @@
         <v>14</v>
       </c>
       <c r="F459" s="2">
-        <v>988</v>
+        <v>1684</v>
       </c>
       <c r="G459" s="2" t="s">
         <v>15</v>
@@ -33358,7 +33358,7 @@
         <v>14</v>
       </c>
       <c r="F460" s="2">
-        <v>3321</v>
+        <v>3991</v>
       </c>
       <c r="G460" s="2" t="s">
         <v>15</v>
@@ -33390,7 +33390,7 @@
         <v>14</v>
       </c>
       <c r="F461" s="2">
-        <v>4711</v>
+        <v>3166</v>
       </c>
       <c r="G461" s="2" t="s">
         <v>15</v>
@@ -33422,7 +33422,7 @@
         <v>14</v>
       </c>
       <c r="F462" s="2">
-        <v>1561</v>
+        <v>2123</v>
       </c>
       <c r="G462" s="2" t="s">
         <v>15</v>
@@ -33454,7 +33454,7 @@
         <v>14</v>
       </c>
       <c r="F463" s="2">
-        <v>4514</v>
+        <v>1214</v>
       </c>
       <c r="G463" s="2" t="s">
         <v>15</v>
@@ -33486,7 +33486,7 @@
         <v>14</v>
       </c>
       <c r="F464" s="2">
-        <v>3884</v>
+        <v>3887</v>
       </c>
       <c r="G464" s="2" t="s">
         <v>15</v>
@@ -33518,7 +33518,7 @@
         <v>14</v>
       </c>
       <c r="F465" s="2">
-        <v>1063</v>
+        <v>1767</v>
       </c>
       <c r="G465" s="2" t="s">
         <v>15</v>
@@ -33550,7 +33550,7 @@
         <v>14</v>
       </c>
       <c r="F466" s="2">
-        <v>921</v>
+        <v>3940</v>
       </c>
       <c r="G466" s="2" t="s">
         <v>15</v>
@@ -33582,7 +33582,7 @@
         <v>14</v>
       </c>
       <c r="F467" s="2">
-        <v>2490</v>
+        <v>2339</v>
       </c>
       <c r="G467" s="2" t="s">
         <v>15</v>
@@ -33614,7 +33614,7 @@
         <v>14</v>
       </c>
       <c r="F468" s="2">
-        <v>4764</v>
+        <v>3324</v>
       </c>
       <c r="G468" s="2" t="s">
         <v>15</v>
@@ -33646,7 +33646,7 @@
         <v>14</v>
       </c>
       <c r="F469" s="2">
-        <v>3883</v>
+        <v>1123</v>
       </c>
       <c r="G469" s="2" t="s">
         <v>15</v>
@@ -33678,7 +33678,7 @@
         <v>14</v>
       </c>
       <c r="F470" s="2">
-        <v>3424</v>
+        <v>2371</v>
       </c>
       <c r="G470" s="2" t="s">
         <v>15</v>
@@ -33710,7 +33710,7 @@
         <v>14</v>
       </c>
       <c r="F471" s="2">
-        <v>4384</v>
+        <v>2769</v>
       </c>
       <c r="G471" s="2" t="s">
         <v>15</v>

--- a/reports/selenium/latest/excel/Automation_Test_Report.xlsx
+++ b/reports/selenium/latest/excel/Automation_Test_Report.xlsx
@@ -3084,7 +3084,7 @@
     <t>Build</t>
   </si>
   <si>
-    <t>3</t>
+    <t>4</t>
   </si>
   <si>
     <t>Branch</t>
@@ -3096,13 +3096,13 @@
     <t>Commit</t>
   </si>
   <si>
-    <t>690e2d2a1f35</t>
+    <t>ecf58600aa47</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T03:44:52.278Z</t>
+    <t>2026-08-18T15:22:34.008Z</t>
   </si>
   <si>
     <t>Browser</t>
@@ -3607,7 +3607,7 @@
         <v>14</v>
       </c>
       <c r="F2" s="2">
-        <v>2692</v>
+        <v>3236</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>15</v>
@@ -3639,7 +3639,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="2">
-        <v>4601</v>
+        <v>2390</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>15</v>
@@ -3671,7 +3671,7 @@
         <v>14</v>
       </c>
       <c r="F4" s="2">
-        <v>1356</v>
+        <v>1290</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
@@ -3703,7 +3703,7 @@
         <v>14</v>
       </c>
       <c r="F5" s="2">
-        <v>3387</v>
+        <v>2447</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
@@ -3735,7 +3735,7 @@
         <v>14</v>
       </c>
       <c r="F6" s="2">
-        <v>3286</v>
+        <v>2634</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -3767,7 +3767,7 @@
         <v>14</v>
       </c>
       <c r="F7" s="2">
-        <v>4231</v>
+        <v>4151</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -3799,7 +3799,7 @@
         <v>14</v>
       </c>
       <c r="F8" s="2">
-        <v>3350</v>
+        <v>3490</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -3831,7 +3831,7 @@
         <v>14</v>
       </c>
       <c r="F9" s="2">
-        <v>1973</v>
+        <v>1780</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -3863,7 +3863,7 @@
         <v>14</v>
       </c>
       <c r="F10" s="2">
-        <v>4613</v>
+        <v>2604</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
@@ -3895,7 +3895,7 @@
         <v>14</v>
       </c>
       <c r="F11" s="2">
-        <v>890</v>
+        <v>2651</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
@@ -3927,7 +3927,7 @@
         <v>14</v>
       </c>
       <c r="F12" s="2">
-        <v>2763</v>
+        <v>3166</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
@@ -3959,7 +3959,7 @@
         <v>14</v>
       </c>
       <c r="F13" s="2">
-        <v>2388</v>
+        <v>3430</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -3991,7 +3991,7 @@
         <v>14</v>
       </c>
       <c r="F14" s="2">
-        <v>3911</v>
+        <v>2399</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -4023,7 +4023,7 @@
         <v>14</v>
       </c>
       <c r="F15" s="2">
-        <v>1980</v>
+        <v>4216</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -4055,7 +4055,7 @@
         <v>14</v>
       </c>
       <c r="F16" s="2">
-        <v>1875</v>
+        <v>3401</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
@@ -4087,7 +4087,7 @@
         <v>14</v>
       </c>
       <c r="F17" s="2">
-        <v>2622</v>
+        <v>1180</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
@@ -4119,7 +4119,7 @@
         <v>14</v>
       </c>
       <c r="F18" s="2">
-        <v>2570</v>
+        <v>2413</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
@@ -4151,7 +4151,7 @@
         <v>14</v>
       </c>
       <c r="F19" s="2">
-        <v>3598</v>
+        <v>4102</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
@@ -4183,7 +4183,7 @@
         <v>14</v>
       </c>
       <c r="F20" s="2">
-        <v>3847</v>
+        <v>2171</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
@@ -4215,7 +4215,7 @@
         <v>14</v>
       </c>
       <c r="F21" s="2">
-        <v>4367</v>
+        <v>2909</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -4247,7 +4247,7 @@
         <v>14</v>
       </c>
       <c r="F22" s="2">
-        <v>1318</v>
+        <v>1555</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -4279,7 +4279,7 @@
         <v>14</v>
       </c>
       <c r="F23" s="2">
-        <v>1409</v>
+        <v>4424</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -4311,7 +4311,7 @@
         <v>14</v>
       </c>
       <c r="F24" s="2">
-        <v>1203</v>
+        <v>3598</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -4343,7 +4343,7 @@
         <v>14</v>
       </c>
       <c r="F25" s="2">
-        <v>3106</v>
+        <v>1832</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -4375,7 +4375,7 @@
         <v>14</v>
       </c>
       <c r="F26" s="2">
-        <v>1104</v>
+        <v>4454</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -4407,7 +4407,7 @@
         <v>14</v>
       </c>
       <c r="F27" s="2">
-        <v>1675</v>
+        <v>3734</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>15</v>
@@ -4439,7 +4439,7 @@
         <v>14</v>
       </c>
       <c r="F28" s="2">
-        <v>3595</v>
+        <v>2823</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>15</v>
@@ -4471,7 +4471,7 @@
         <v>14</v>
       </c>
       <c r="F29" s="2">
-        <v>2653</v>
+        <v>4784</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>15</v>
@@ -4503,7 +4503,7 @@
         <v>14</v>
       </c>
       <c r="F30" s="2">
-        <v>1579</v>
+        <v>3944</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>15</v>
@@ -4535,7 +4535,7 @@
         <v>14</v>
       </c>
       <c r="F31" s="2">
-        <v>4269</v>
+        <v>3950</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>15</v>
@@ -4567,7 +4567,7 @@
         <v>14</v>
       </c>
       <c r="F32" s="2">
-        <v>1142</v>
+        <v>3963</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>15</v>
@@ -4599,7 +4599,7 @@
         <v>14</v>
       </c>
       <c r="F33" s="2">
-        <v>1938</v>
+        <v>1782</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>15</v>
@@ -4631,7 +4631,7 @@
         <v>14</v>
       </c>
       <c r="F34" s="2">
-        <v>2327</v>
+        <v>1097</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>15</v>
@@ -4663,7 +4663,7 @@
         <v>14</v>
       </c>
       <c r="F35" s="2">
-        <v>3693</v>
+        <v>2200</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>15</v>
@@ -4695,7 +4695,7 @@
         <v>14</v>
       </c>
       <c r="F36" s="2">
-        <v>4594</v>
+        <v>3148</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>15</v>
@@ -4727,7 +4727,7 @@
         <v>14</v>
       </c>
       <c r="F37" s="2">
-        <v>3449</v>
+        <v>1393</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>15</v>
@@ -4759,7 +4759,7 @@
         <v>14</v>
       </c>
       <c r="F38" s="2">
-        <v>2062</v>
+        <v>2720</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>15</v>
@@ -4791,7 +4791,7 @@
         <v>14</v>
       </c>
       <c r="F39" s="2">
-        <v>4573</v>
+        <v>1019</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>15</v>
@@ -4823,7 +4823,7 @@
         <v>14</v>
       </c>
       <c r="F40" s="2">
-        <v>1004</v>
+        <v>1657</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>15</v>
@@ -4855,7 +4855,7 @@
         <v>14</v>
       </c>
       <c r="F41" s="2">
-        <v>4334</v>
+        <v>2664</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>15</v>
@@ -4887,7 +4887,7 @@
         <v>14</v>
       </c>
       <c r="F42" s="2">
-        <v>2407</v>
+        <v>4219</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>15</v>
@@ -4919,7 +4919,7 @@
         <v>14</v>
       </c>
       <c r="F43" s="2">
-        <v>2700</v>
+        <v>4725</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>15</v>
@@ -4951,7 +4951,7 @@
         <v>14</v>
       </c>
       <c r="F44" s="2">
-        <v>2453</v>
+        <v>2732</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>15</v>
@@ -4983,7 +4983,7 @@
         <v>14</v>
       </c>
       <c r="F45" s="2">
-        <v>1727</v>
+        <v>2402</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>15</v>
@@ -5015,7 +5015,7 @@
         <v>14</v>
       </c>
       <c r="F46" s="2">
-        <v>3373</v>
+        <v>4693</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>15</v>
@@ -5047,7 +5047,7 @@
         <v>14</v>
       </c>
       <c r="F47" s="2">
-        <v>3117</v>
+        <v>3033</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>15</v>
@@ -5079,7 +5079,7 @@
         <v>14</v>
       </c>
       <c r="F48" s="2">
-        <v>2431</v>
+        <v>3664</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>15</v>
@@ -5111,7 +5111,7 @@
         <v>14</v>
       </c>
       <c r="F49" s="2">
-        <v>2730</v>
+        <v>2465</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>15</v>
@@ -5143,7 +5143,7 @@
         <v>14</v>
       </c>
       <c r="F50" s="2">
-        <v>1464</v>
+        <v>4670</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>15</v>
@@ -5175,7 +5175,7 @@
         <v>14</v>
       </c>
       <c r="F51" s="2">
-        <v>4707</v>
+        <v>3343</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>15</v>
@@ -5207,7 +5207,7 @@
         <v>14</v>
       </c>
       <c r="F52" s="2">
-        <v>2690</v>
+        <v>2369</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>15</v>
@@ -5239,7 +5239,7 @@
         <v>14</v>
       </c>
       <c r="F53" s="2">
-        <v>3410</v>
+        <v>2569</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>15</v>
@@ -5271,7 +5271,7 @@
         <v>14</v>
       </c>
       <c r="F54" s="2">
-        <v>2755</v>
+        <v>4740</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>15</v>
@@ -5303,7 +5303,7 @@
         <v>14</v>
       </c>
       <c r="F55" s="2">
-        <v>4281</v>
+        <v>4393</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>15</v>
@@ -5335,7 +5335,7 @@
         <v>14</v>
       </c>
       <c r="F56" s="2">
-        <v>2167</v>
+        <v>3464</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>15</v>
@@ -5367,7 +5367,7 @@
         <v>14</v>
       </c>
       <c r="F57" s="2">
-        <v>1805</v>
+        <v>3370</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>15</v>
@@ -5399,7 +5399,7 @@
         <v>14</v>
       </c>
       <c r="F58" s="2">
-        <v>1065</v>
+        <v>1863</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>15</v>
@@ -5431,7 +5431,7 @@
         <v>14</v>
       </c>
       <c r="F59" s="2">
-        <v>1165</v>
+        <v>2116</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>15</v>
@@ -5463,7 +5463,7 @@
         <v>14</v>
       </c>
       <c r="F60" s="2">
-        <v>2916</v>
+        <v>3820</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>15</v>
@@ -5495,7 +5495,7 @@
         <v>14</v>
       </c>
       <c r="F61" s="2">
-        <v>3945</v>
+        <v>1146</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>15</v>
@@ -5527,7 +5527,7 @@
         <v>14</v>
       </c>
       <c r="F62" s="2">
-        <v>1074</v>
+        <v>4759</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>15</v>
@@ -5559,7 +5559,7 @@
         <v>14</v>
       </c>
       <c r="F63" s="2">
-        <v>2009</v>
+        <v>3694</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>15</v>
@@ -5591,7 +5591,7 @@
         <v>14</v>
       </c>
       <c r="F64" s="2">
-        <v>1022</v>
+        <v>844</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>15</v>
@@ -5623,7 +5623,7 @@
         <v>14</v>
       </c>
       <c r="F65" s="2">
-        <v>3274</v>
+        <v>1944</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>15</v>
@@ -5655,7 +5655,7 @@
         <v>14</v>
       </c>
       <c r="F66" s="2">
-        <v>4372</v>
+        <v>2716</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>15</v>
@@ -5687,7 +5687,7 @@
         <v>14</v>
       </c>
       <c r="F67" s="2">
-        <v>3809</v>
+        <v>867</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>15</v>
@@ -5719,7 +5719,7 @@
         <v>14</v>
       </c>
       <c r="F68" s="2">
-        <v>981</v>
+        <v>1814</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>15</v>
@@ -5751,7 +5751,7 @@
         <v>14</v>
       </c>
       <c r="F69" s="2">
-        <v>3047</v>
+        <v>3832</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>15</v>
@@ -5783,7 +5783,7 @@
         <v>14</v>
       </c>
       <c r="F70" s="2">
-        <v>1912</v>
+        <v>2673</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>15</v>
@@ -5815,7 +5815,7 @@
         <v>14</v>
       </c>
       <c r="F71" s="2">
-        <v>2100</v>
+        <v>2784</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>15</v>
@@ -5847,7 +5847,7 @@
         <v>14</v>
       </c>
       <c r="F72" s="2">
-        <v>4709</v>
+        <v>1651</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>15</v>
@@ -5879,7 +5879,7 @@
         <v>14</v>
       </c>
       <c r="F73" s="2">
-        <v>1006</v>
+        <v>2179</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>15</v>
@@ -5911,7 +5911,7 @@
         <v>14</v>
       </c>
       <c r="F74" s="2">
-        <v>3823</v>
+        <v>4617</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>15</v>
@@ -5943,7 +5943,7 @@
         <v>14</v>
       </c>
       <c r="F75" s="2">
-        <v>3679</v>
+        <v>2085</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>15</v>
@@ -5975,7 +5975,7 @@
         <v>14</v>
       </c>
       <c r="F76" s="2">
-        <v>1003</v>
+        <v>3037</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>15</v>
@@ -6007,7 +6007,7 @@
         <v>14</v>
       </c>
       <c r="F77" s="2">
-        <v>4074</v>
+        <v>1990</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>15</v>
@@ -6039,7 +6039,7 @@
         <v>14</v>
       </c>
       <c r="F78" s="2">
-        <v>3906</v>
+        <v>3375</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>15</v>
@@ -6071,7 +6071,7 @@
         <v>14</v>
       </c>
       <c r="F79" s="2">
-        <v>2867</v>
+        <v>1294</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>15</v>
@@ -6103,7 +6103,7 @@
         <v>14</v>
       </c>
       <c r="F80" s="2">
-        <v>3086</v>
+        <v>3849</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>15</v>
@@ -6135,7 +6135,7 @@
         <v>14</v>
       </c>
       <c r="F81" s="2">
-        <v>3610</v>
+        <v>4284</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>15</v>
@@ -6167,7 +6167,7 @@
         <v>14</v>
       </c>
       <c r="F82" s="2">
-        <v>1384</v>
+        <v>2838</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>15</v>
@@ -6199,7 +6199,7 @@
         <v>14</v>
       </c>
       <c r="F83" s="2">
-        <v>4413</v>
+        <v>2512</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>15</v>
@@ -6231,7 +6231,7 @@
         <v>14</v>
       </c>
       <c r="F84" s="2">
-        <v>4273</v>
+        <v>4195</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>15</v>
@@ -6263,7 +6263,7 @@
         <v>14</v>
       </c>
       <c r="F85" s="2">
-        <v>4506</v>
+        <v>3131</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>15</v>
@@ -6295,7 +6295,7 @@
         <v>14</v>
       </c>
       <c r="F86" s="2">
-        <v>2396</v>
+        <v>1303</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>15</v>
@@ -6327,7 +6327,7 @@
         <v>14</v>
       </c>
       <c r="F87" s="2">
-        <v>1747</v>
+        <v>4743</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>15</v>
@@ -6359,7 +6359,7 @@
         <v>14</v>
       </c>
       <c r="F88" s="2">
-        <v>1621</v>
+        <v>2096</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>15</v>
@@ -6391,7 +6391,7 @@
         <v>14</v>
       </c>
       <c r="F89" s="2">
-        <v>1248</v>
+        <v>1067</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>15</v>
@@ -6423,7 +6423,7 @@
         <v>14</v>
       </c>
       <c r="F90" s="2">
-        <v>3114</v>
+        <v>2068</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>15</v>
@@ -6455,7 +6455,7 @@
         <v>14</v>
       </c>
       <c r="F91" s="2">
-        <v>2273</v>
+        <v>3691</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>15</v>
@@ -6487,7 +6487,7 @@
         <v>14</v>
       </c>
       <c r="F92" s="2">
-        <v>3639</v>
+        <v>4399</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>15</v>
@@ -6519,7 +6519,7 @@
         <v>14</v>
       </c>
       <c r="F93" s="2">
-        <v>2151</v>
+        <v>4601</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>15</v>
@@ -6551,7 +6551,7 @@
         <v>14</v>
       </c>
       <c r="F94" s="2">
-        <v>1789</v>
+        <v>3681</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>15</v>
@@ -6583,7 +6583,7 @@
         <v>14</v>
       </c>
       <c r="F95" s="2">
-        <v>3542</v>
+        <v>4175</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>15</v>
@@ -6615,7 +6615,7 @@
         <v>14</v>
       </c>
       <c r="F96" s="2">
-        <v>3907</v>
+        <v>1519</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>15</v>
@@ -6647,7 +6647,7 @@
         <v>14</v>
       </c>
       <c r="F97" s="2">
-        <v>1700</v>
+        <v>2362</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>15</v>
@@ -6679,7 +6679,7 @@
         <v>14</v>
       </c>
       <c r="F98" s="2">
-        <v>3327</v>
+        <v>2818</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>15</v>
@@ -6711,7 +6711,7 @@
         <v>14</v>
       </c>
       <c r="F99" s="2">
-        <v>2620</v>
+        <v>1398</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>15</v>
@@ -6743,7 +6743,7 @@
         <v>14</v>
       </c>
       <c r="F100" s="2">
-        <v>858</v>
+        <v>4780</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>15</v>
@@ -6775,7 +6775,7 @@
         <v>14</v>
       </c>
       <c r="F101" s="2">
-        <v>1514</v>
+        <v>4460</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>15</v>
@@ -6807,7 +6807,7 @@
         <v>14</v>
       </c>
       <c r="F102" s="2">
-        <v>1368</v>
+        <v>4603</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>15</v>
@@ -6839,7 +6839,7 @@
         <v>14</v>
       </c>
       <c r="F103" s="2">
-        <v>1934</v>
+        <v>2372</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>15</v>
@@ -6871,7 +6871,7 @@
         <v>14</v>
       </c>
       <c r="F104" s="2">
-        <v>3904</v>
+        <v>2911</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>15</v>
@@ -6903,7 +6903,7 @@
         <v>14</v>
       </c>
       <c r="F105" s="2">
-        <v>4213</v>
+        <v>3770</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>15</v>
@@ -6935,7 +6935,7 @@
         <v>14</v>
       </c>
       <c r="F106" s="2">
-        <v>2350</v>
+        <v>2369</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>15</v>
@@ -6967,7 +6967,7 @@
         <v>14</v>
       </c>
       <c r="F107" s="2">
-        <v>2791</v>
+        <v>1208</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>15</v>
@@ -6999,7 +6999,7 @@
         <v>14</v>
       </c>
       <c r="F108" s="2">
-        <v>3925</v>
+        <v>2582</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>15</v>
@@ -7031,7 +7031,7 @@
         <v>14</v>
       </c>
       <c r="F109" s="2">
-        <v>2431</v>
+        <v>3267</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>15</v>
@@ -7063,7 +7063,7 @@
         <v>14</v>
       </c>
       <c r="F110" s="2">
-        <v>4053</v>
+        <v>3069</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>15</v>
@@ -7095,7 +7095,7 @@
         <v>14</v>
       </c>
       <c r="F111" s="2">
-        <v>1359</v>
+        <v>1074</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>15</v>
@@ -7127,7 +7127,7 @@
         <v>14</v>
       </c>
       <c r="F112" s="2">
-        <v>2191</v>
+        <v>1364</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>15</v>
@@ -7159,7 +7159,7 @@
         <v>14</v>
       </c>
       <c r="F113" s="2">
-        <v>3904</v>
+        <v>2563</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>15</v>
@@ -7191,7 +7191,7 @@
         <v>14</v>
       </c>
       <c r="F114" s="2">
-        <v>4467</v>
+        <v>2698</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>15</v>
@@ -7223,7 +7223,7 @@
         <v>14</v>
       </c>
       <c r="F115" s="2">
-        <v>3973</v>
+        <v>1391</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>15</v>
@@ -7255,7 +7255,7 @@
         <v>14</v>
       </c>
       <c r="F116" s="2">
-        <v>2106</v>
+        <v>4641</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>15</v>
@@ -7287,7 +7287,7 @@
         <v>14</v>
       </c>
       <c r="F117" s="2">
-        <v>1067</v>
+        <v>4420</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>15</v>
@@ -7319,7 +7319,7 @@
         <v>14</v>
       </c>
       <c r="F118" s="2">
-        <v>4544</v>
+        <v>1535</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>15</v>
@@ -7351,7 +7351,7 @@
         <v>14</v>
       </c>
       <c r="F119" s="2">
-        <v>4179</v>
+        <v>3600</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>15</v>
@@ -7383,7 +7383,7 @@
         <v>14</v>
       </c>
       <c r="F120" s="2">
-        <v>1997</v>
+        <v>1416</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>15</v>
@@ -7415,7 +7415,7 @@
         <v>14</v>
       </c>
       <c r="F121" s="2">
-        <v>3116</v>
+        <v>1437</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>15</v>
@@ -7447,7 +7447,7 @@
         <v>14</v>
       </c>
       <c r="F122" s="2">
-        <v>4615</v>
+        <v>4612</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>15</v>
@@ -7479,7 +7479,7 @@
         <v>14</v>
       </c>
       <c r="F123" s="2">
-        <v>2361</v>
+        <v>2057</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>15</v>
@@ -7511,7 +7511,7 @@
         <v>14</v>
       </c>
       <c r="F124" s="2">
-        <v>3614</v>
+        <v>1616</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>15</v>
@@ -7543,7 +7543,7 @@
         <v>14</v>
       </c>
       <c r="F125" s="2">
-        <v>1510</v>
+        <v>2545</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>15</v>
@@ -7575,7 +7575,7 @@
         <v>14</v>
       </c>
       <c r="F126" s="2">
-        <v>3429</v>
+        <v>2754</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>15</v>
@@ -7607,7 +7607,7 @@
         <v>14</v>
       </c>
       <c r="F127" s="2">
-        <v>2191</v>
+        <v>4187</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>15</v>
@@ -7639,7 +7639,7 @@
         <v>14</v>
       </c>
       <c r="F128" s="2">
-        <v>1336</v>
+        <v>1658</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>15</v>
@@ -7671,7 +7671,7 @@
         <v>14</v>
       </c>
       <c r="F129" s="2">
-        <v>4385</v>
+        <v>1703</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>15</v>
@@ -7703,7 +7703,7 @@
         <v>14</v>
       </c>
       <c r="F130" s="2">
-        <v>1116</v>
+        <v>1639</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>15</v>
@@ -7735,7 +7735,7 @@
         <v>14</v>
       </c>
       <c r="F131" s="2">
-        <v>1343</v>
+        <v>3157</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>15</v>
@@ -7767,7 +7767,7 @@
         <v>14</v>
       </c>
       <c r="F132" s="2">
-        <v>2388</v>
+        <v>3685</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>15</v>
@@ -7799,7 +7799,7 @@
         <v>14</v>
       </c>
       <c r="F133" s="2">
-        <v>1687</v>
+        <v>3325</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>15</v>
@@ -7831,7 +7831,7 @@
         <v>14</v>
       </c>
       <c r="F134" s="2">
-        <v>1916</v>
+        <v>1491</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>15</v>
@@ -7863,7 +7863,7 @@
         <v>14</v>
       </c>
       <c r="F135" s="2">
-        <v>1045</v>
+        <v>2283</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>15</v>
@@ -7895,7 +7895,7 @@
         <v>14</v>
       </c>
       <c r="F136" s="2">
-        <v>1834</v>
+        <v>1028</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>15</v>
@@ -7927,7 +7927,7 @@
         <v>14</v>
       </c>
       <c r="F137" s="2">
-        <v>4626</v>
+        <v>2346</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>15</v>
@@ -7959,7 +7959,7 @@
         <v>14</v>
       </c>
       <c r="F138" s="2">
-        <v>3829</v>
+        <v>3119</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>15</v>
@@ -7991,7 +7991,7 @@
         <v>14</v>
       </c>
       <c r="F139" s="2">
-        <v>3782</v>
+        <v>3742</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>15</v>
@@ -8023,7 +8023,7 @@
         <v>14</v>
       </c>
       <c r="F140" s="2">
-        <v>2941</v>
+        <v>4486</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>15</v>
@@ -8055,7 +8055,7 @@
         <v>14</v>
       </c>
       <c r="F141" s="2">
-        <v>4337</v>
+        <v>4591</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>15</v>
@@ -8087,7 +8087,7 @@
         <v>14</v>
       </c>
       <c r="F142" s="2">
-        <v>4740</v>
+        <v>2170</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>15</v>
@@ -8119,7 +8119,7 @@
         <v>14</v>
       </c>
       <c r="F143" s="2">
-        <v>1650</v>
+        <v>1628</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>15</v>
@@ -8151,7 +8151,7 @@
         <v>14</v>
       </c>
       <c r="F144" s="2">
-        <v>1862</v>
+        <v>3752</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>15</v>
@@ -8183,7 +8183,7 @@
         <v>14</v>
       </c>
       <c r="F145" s="2">
-        <v>4158</v>
+        <v>1819</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>15</v>
@@ -8215,7 +8215,7 @@
         <v>14</v>
       </c>
       <c r="F146" s="2">
-        <v>2614</v>
+        <v>2297</v>
       </c>
       <c r="G146" s="2" t="s">
         <v>15</v>
@@ -8247,7 +8247,7 @@
         <v>14</v>
       </c>
       <c r="F147" s="2">
-        <v>3863</v>
+        <v>1419</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>15</v>
@@ -8279,7 +8279,7 @@
         <v>14</v>
       </c>
       <c r="F148" s="2">
-        <v>4648</v>
+        <v>1419</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>15</v>
@@ -8311,7 +8311,7 @@
         <v>14</v>
       </c>
       <c r="F149" s="2">
-        <v>3974</v>
+        <v>3850</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>15</v>
@@ -8343,7 +8343,7 @@
         <v>14</v>
       </c>
       <c r="F150" s="2">
-        <v>3559</v>
+        <v>4225</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>15</v>
@@ -8375,7 +8375,7 @@
         <v>14</v>
       </c>
       <c r="F151" s="2">
-        <v>3201</v>
+        <v>1628</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>15</v>
@@ -8407,7 +8407,7 @@
         <v>14</v>
       </c>
       <c r="F152" s="2">
-        <v>4316</v>
+        <v>2305</v>
       </c>
       <c r="G152" s="2" t="s">
         <v>15</v>
@@ -8439,7 +8439,7 @@
         <v>14</v>
       </c>
       <c r="F153" s="2">
-        <v>2766</v>
+        <v>2293</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>15</v>
@@ -8471,7 +8471,7 @@
         <v>14</v>
       </c>
       <c r="F154" s="2">
-        <v>4419</v>
+        <v>4491</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>15</v>
@@ -8503,7 +8503,7 @@
         <v>14</v>
       </c>
       <c r="F155" s="2">
-        <v>1699</v>
+        <v>1082</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>15</v>
@@ -8535,7 +8535,7 @@
         <v>14</v>
       </c>
       <c r="F156" s="2">
-        <v>4777</v>
+        <v>4596</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>15</v>
@@ -8567,7 +8567,7 @@
         <v>14</v>
       </c>
       <c r="F157" s="2">
-        <v>3250</v>
+        <v>1814</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>15</v>
@@ -8599,7 +8599,7 @@
         <v>14</v>
       </c>
       <c r="F158" s="2">
-        <v>4464</v>
+        <v>1428</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>15</v>
@@ -8631,7 +8631,7 @@
         <v>14</v>
       </c>
       <c r="F159" s="2">
-        <v>1546</v>
+        <v>4172</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>15</v>
@@ -8663,7 +8663,7 @@
         <v>14</v>
       </c>
       <c r="F160" s="2">
-        <v>3618</v>
+        <v>3548</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>15</v>
@@ -8695,7 +8695,7 @@
         <v>14</v>
       </c>
       <c r="F161" s="2">
-        <v>1266</v>
+        <v>1339</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>15</v>
@@ -8727,7 +8727,7 @@
         <v>14</v>
       </c>
       <c r="F162" s="2">
-        <v>1759</v>
+        <v>3106</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>15</v>
@@ -8759,7 +8759,7 @@
         <v>14</v>
       </c>
       <c r="F163" s="2">
-        <v>2375</v>
+        <v>863</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>15</v>
@@ -8791,7 +8791,7 @@
         <v>14</v>
       </c>
       <c r="F164" s="2">
-        <v>1108</v>
+        <v>3795</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>15</v>
@@ -8823,7 +8823,7 @@
         <v>14</v>
       </c>
       <c r="F165" s="2">
-        <v>2463</v>
+        <v>3434</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>15</v>
@@ -8855,7 +8855,7 @@
         <v>14</v>
       </c>
       <c r="F166" s="2">
-        <v>3730</v>
+        <v>4229</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>15</v>
@@ -8887,7 +8887,7 @@
         <v>14</v>
       </c>
       <c r="F167" s="2">
-        <v>3596</v>
+        <v>2856</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>15</v>
@@ -8919,7 +8919,7 @@
         <v>14</v>
       </c>
       <c r="F168" s="2">
-        <v>4321</v>
+        <v>3959</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>15</v>
@@ -8951,7 +8951,7 @@
         <v>14</v>
       </c>
       <c r="F169" s="2">
-        <v>4161</v>
+        <v>2814</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>15</v>
@@ -8983,7 +8983,7 @@
         <v>14</v>
       </c>
       <c r="F170" s="2">
-        <v>3239</v>
+        <v>3407</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>15</v>
@@ -9015,7 +9015,7 @@
         <v>14</v>
       </c>
       <c r="F171" s="2">
-        <v>3517</v>
+        <v>1464</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>15</v>
@@ -9047,7 +9047,7 @@
         <v>14</v>
       </c>
       <c r="F172" s="2">
-        <v>2872</v>
+        <v>4551</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>15</v>
@@ -9079,7 +9079,7 @@
         <v>14</v>
       </c>
       <c r="F173" s="2">
-        <v>1947</v>
+        <v>1316</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>15</v>
@@ -9111,7 +9111,7 @@
         <v>14</v>
       </c>
       <c r="F174" s="2">
-        <v>3543</v>
+        <v>3808</v>
       </c>
       <c r="G174" s="2" t="s">
         <v>15</v>
@@ -9143,7 +9143,7 @@
         <v>14</v>
       </c>
       <c r="F175" s="2">
-        <v>1800</v>
+        <v>2115</v>
       </c>
       <c r="G175" s="2" t="s">
         <v>15</v>
@@ -9175,7 +9175,7 @@
         <v>14</v>
       </c>
       <c r="F176" s="2">
-        <v>4725</v>
+        <v>1113</v>
       </c>
       <c r="G176" s="2" t="s">
         <v>15</v>
@@ -9207,7 +9207,7 @@
         <v>14</v>
       </c>
       <c r="F177" s="2">
-        <v>2567</v>
+        <v>2158</v>
       </c>
       <c r="G177" s="2" t="s">
         <v>15</v>
@@ -9239,7 +9239,7 @@
         <v>14</v>
       </c>
       <c r="F178" s="2">
-        <v>3782</v>
+        <v>4664</v>
       </c>
       <c r="G178" s="2" t="s">
         <v>15</v>
@@ -9271,7 +9271,7 @@
         <v>14</v>
       </c>
       <c r="F179" s="2">
-        <v>3176</v>
+        <v>941</v>
       </c>
       <c r="G179" s="2" t="s">
         <v>15</v>
@@ -9303,7 +9303,7 @@
         <v>14</v>
       </c>
       <c r="F180" s="2">
-        <v>3771</v>
+        <v>816</v>
       </c>
       <c r="G180" s="2" t="s">
         <v>15</v>
@@ -9335,7 +9335,7 @@
         <v>14</v>
       </c>
       <c r="F181" s="2">
-        <v>2593</v>
+        <v>4545</v>
       </c>
       <c r="G181" s="2" t="s">
         <v>15</v>
@@ -9367,7 +9367,7 @@
         <v>14</v>
       </c>
       <c r="F182" s="2">
-        <v>2745</v>
+        <v>3551</v>
       </c>
       <c r="G182" s="2" t="s">
         <v>15</v>
@@ -9399,7 +9399,7 @@
         <v>14</v>
       </c>
       <c r="F183" s="2">
-        <v>1436</v>
+        <v>4786</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>15</v>
@@ -9431,7 +9431,7 @@
         <v>14</v>
       </c>
       <c r="F184" s="2">
-        <v>3323</v>
+        <v>2260</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>15</v>
@@ -9463,7 +9463,7 @@
         <v>14</v>
       </c>
       <c r="F185" s="2">
-        <v>3734</v>
+        <v>3813</v>
       </c>
       <c r="G185" s="2" t="s">
         <v>15</v>
@@ -9495,7 +9495,7 @@
         <v>14</v>
       </c>
       <c r="F186" s="2">
-        <v>3845</v>
+        <v>2905</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>15</v>
@@ -9527,7 +9527,7 @@
         <v>14</v>
       </c>
       <c r="F187" s="2">
-        <v>4516</v>
+        <v>1535</v>
       </c>
       <c r="G187" s="2" t="s">
         <v>15</v>
@@ -9559,7 +9559,7 @@
         <v>14</v>
       </c>
       <c r="F188" s="2">
-        <v>1023</v>
+        <v>1801</v>
       </c>
       <c r="G188" s="2" t="s">
         <v>15</v>
@@ -9591,7 +9591,7 @@
         <v>14</v>
       </c>
       <c r="F189" s="2">
-        <v>3499</v>
+        <v>3161</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>15</v>
@@ -9623,7 +9623,7 @@
         <v>14</v>
       </c>
       <c r="F190" s="2">
-        <v>1543</v>
+        <v>2613</v>
       </c>
       <c r="G190" s="2" t="s">
         <v>15</v>
@@ -9655,7 +9655,7 @@
         <v>14</v>
       </c>
       <c r="F191" s="2">
-        <v>1925</v>
+        <v>1688</v>
       </c>
       <c r="G191" s="2" t="s">
         <v>15</v>
@@ -9687,7 +9687,7 @@
         <v>14</v>
       </c>
       <c r="F192" s="2">
-        <v>1174</v>
+        <v>3561</v>
       </c>
       <c r="G192" s="2" t="s">
         <v>15</v>
@@ -9719,7 +9719,7 @@
         <v>14</v>
       </c>
       <c r="F193" s="2">
-        <v>2680</v>
+        <v>1151</v>
       </c>
       <c r="G193" s="2" t="s">
         <v>15</v>
@@ -9751,7 +9751,7 @@
         <v>14</v>
       </c>
       <c r="F194" s="2">
-        <v>854</v>
+        <v>2144</v>
       </c>
       <c r="G194" s="2" t="s">
         <v>15</v>
@@ -9783,7 +9783,7 @@
         <v>14</v>
       </c>
       <c r="F195" s="2">
-        <v>3663</v>
+        <v>3735</v>
       </c>
       <c r="G195" s="2" t="s">
         <v>15</v>
@@ -9815,7 +9815,7 @@
         <v>14</v>
       </c>
       <c r="F196" s="2">
-        <v>1324</v>
+        <v>2046</v>
       </c>
       <c r="G196" s="2" t="s">
         <v>15</v>
@@ -9847,7 +9847,7 @@
         <v>14</v>
       </c>
       <c r="F197" s="2">
-        <v>2513</v>
+        <v>4527</v>
       </c>
       <c r="G197" s="2" t="s">
         <v>15</v>
@@ -9879,7 +9879,7 @@
         <v>14</v>
       </c>
       <c r="F198" s="2">
-        <v>3722</v>
+        <v>1832</v>
       </c>
       <c r="G198" s="2" t="s">
         <v>15</v>
@@ -9911,7 +9911,7 @@
         <v>14</v>
       </c>
       <c r="F199" s="2">
-        <v>3878</v>
+        <v>2561</v>
       </c>
       <c r="G199" s="2" t="s">
         <v>15</v>
@@ -9943,7 +9943,7 @@
         <v>14</v>
       </c>
       <c r="F200" s="2">
-        <v>1939</v>
+        <v>4254</v>
       </c>
       <c r="G200" s="2" t="s">
         <v>15</v>
@@ -9975,7 +9975,7 @@
         <v>14</v>
       </c>
       <c r="F201" s="2">
-        <v>4494</v>
+        <v>2891</v>
       </c>
       <c r="G201" s="2" t="s">
         <v>15</v>
@@ -10007,7 +10007,7 @@
         <v>14</v>
       </c>
       <c r="F202" s="2">
-        <v>4122</v>
+        <v>2518</v>
       </c>
       <c r="G202" s="2" t="s">
         <v>15</v>
@@ -10039,7 +10039,7 @@
         <v>14</v>
       </c>
       <c r="F203" s="2">
-        <v>3935</v>
+        <v>2014</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>15</v>
@@ -10071,7 +10071,7 @@
         <v>14</v>
       </c>
       <c r="F204" s="2">
-        <v>4672</v>
+        <v>3477</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>15</v>
@@ -10103,7 +10103,7 @@
         <v>14</v>
       </c>
       <c r="F205" s="2">
-        <v>3684</v>
+        <v>2222</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>15</v>
@@ -10135,7 +10135,7 @@
         <v>14</v>
       </c>
       <c r="F206" s="2">
-        <v>1774</v>
+        <v>4716</v>
       </c>
       <c r="G206" s="2" t="s">
         <v>15</v>
@@ -10167,7 +10167,7 @@
         <v>14</v>
       </c>
       <c r="F207" s="2">
-        <v>3742</v>
+        <v>1067</v>
       </c>
       <c r="G207" s="2" t="s">
         <v>15</v>
@@ -10199,7 +10199,7 @@
         <v>14</v>
       </c>
       <c r="F208" s="2">
-        <v>1896</v>
+        <v>1011</v>
       </c>
       <c r="G208" s="2" t="s">
         <v>15</v>
@@ -10231,7 +10231,7 @@
         <v>14</v>
       </c>
       <c r="F209" s="2">
-        <v>2196</v>
+        <v>3641</v>
       </c>
       <c r="G209" s="2" t="s">
         <v>15</v>
@@ -10263,7 +10263,7 @@
         <v>14</v>
       </c>
       <c r="F210" s="2">
-        <v>1002</v>
+        <v>4275</v>
       </c>
       <c r="G210" s="2" t="s">
         <v>15</v>
@@ -10295,7 +10295,7 @@
         <v>14</v>
       </c>
       <c r="F211" s="2">
-        <v>2066</v>
+        <v>4474</v>
       </c>
       <c r="G211" s="2" t="s">
         <v>15</v>
@@ -10327,7 +10327,7 @@
         <v>14</v>
       </c>
       <c r="F212" s="2">
-        <v>2476</v>
+        <v>2731</v>
       </c>
       <c r="G212" s="2" t="s">
         <v>15</v>
@@ -10359,7 +10359,7 @@
         <v>14</v>
       </c>
       <c r="F213" s="2">
-        <v>3351</v>
+        <v>2898</v>
       </c>
       <c r="G213" s="2" t="s">
         <v>15</v>
@@ -10391,7 +10391,7 @@
         <v>14</v>
       </c>
       <c r="F214" s="2">
-        <v>869</v>
+        <v>1365</v>
       </c>
       <c r="G214" s="2" t="s">
         <v>15</v>
@@ -10423,7 +10423,7 @@
         <v>14</v>
       </c>
       <c r="F215" s="2">
-        <v>3910</v>
+        <v>1256</v>
       </c>
       <c r="G215" s="2" t="s">
         <v>15</v>
@@ -10455,7 +10455,7 @@
         <v>14</v>
       </c>
       <c r="F216" s="2">
-        <v>3502</v>
+        <v>2086</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>15</v>
@@ -10487,7 +10487,7 @@
         <v>14</v>
       </c>
       <c r="F217" s="2">
-        <v>4506</v>
+        <v>2012</v>
       </c>
       <c r="G217" s="2" t="s">
         <v>15</v>
@@ -10519,7 +10519,7 @@
         <v>14</v>
       </c>
       <c r="F218" s="2">
-        <v>4200</v>
+        <v>1206</v>
       </c>
       <c r="G218" s="2" t="s">
         <v>15</v>
@@ -10551,7 +10551,7 @@
         <v>14</v>
       </c>
       <c r="F219" s="2">
-        <v>1805</v>
+        <v>3803</v>
       </c>
       <c r="G219" s="2" t="s">
         <v>15</v>
@@ -10583,7 +10583,7 @@
         <v>14</v>
       </c>
       <c r="F220" s="2">
-        <v>1647</v>
+        <v>1975</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>15</v>
@@ -10615,7 +10615,7 @@
         <v>14</v>
       </c>
       <c r="F221" s="2">
-        <v>1148</v>
+        <v>2488</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>15</v>
@@ -10647,7 +10647,7 @@
         <v>14</v>
       </c>
       <c r="F222" s="2">
-        <v>1008</v>
+        <v>895</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>15</v>
@@ -10679,7 +10679,7 @@
         <v>14</v>
       </c>
       <c r="F223" s="2">
-        <v>4272</v>
+        <v>3935</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>15</v>
@@ -10711,7 +10711,7 @@
         <v>14</v>
       </c>
       <c r="F224" s="2">
-        <v>931</v>
+        <v>1986</v>
       </c>
       <c r="G224" s="2" t="s">
         <v>15</v>
@@ -10743,7 +10743,7 @@
         <v>14</v>
       </c>
       <c r="F225" s="2">
-        <v>4249</v>
+        <v>1999</v>
       </c>
       <c r="G225" s="2" t="s">
         <v>15</v>
@@ -10775,7 +10775,7 @@
         <v>14</v>
       </c>
       <c r="F226" s="2">
-        <v>1584</v>
+        <v>3901</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>15</v>
@@ -10807,7 +10807,7 @@
         <v>14</v>
       </c>
       <c r="F227" s="2">
-        <v>4569</v>
+        <v>2347</v>
       </c>
       <c r="G227" s="2" t="s">
         <v>15</v>
@@ -10839,7 +10839,7 @@
         <v>14</v>
       </c>
       <c r="F228" s="2">
-        <v>2409</v>
+        <v>4503</v>
       </c>
       <c r="G228" s="2" t="s">
         <v>15</v>
@@ -10871,7 +10871,7 @@
         <v>14</v>
       </c>
       <c r="F229" s="2">
-        <v>2840</v>
+        <v>3126</v>
       </c>
       <c r="G229" s="2" t="s">
         <v>15</v>
@@ -10903,7 +10903,7 @@
         <v>14</v>
       </c>
       <c r="F230" s="2">
-        <v>1109</v>
+        <v>4663</v>
       </c>
       <c r="G230" s="2" t="s">
         <v>15</v>
@@ -10935,7 +10935,7 @@
         <v>14</v>
       </c>
       <c r="F231" s="2">
-        <v>2993</v>
+        <v>1592</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>15</v>
@@ -10967,7 +10967,7 @@
         <v>14</v>
       </c>
       <c r="F232" s="2">
-        <v>1900</v>
+        <v>2636</v>
       </c>
       <c r="G232" s="2" t="s">
         <v>15</v>
@@ -10999,7 +10999,7 @@
         <v>14</v>
       </c>
       <c r="F233" s="2">
-        <v>1549</v>
+        <v>2516</v>
       </c>
       <c r="G233" s="2" t="s">
         <v>15</v>
@@ -11031,7 +11031,7 @@
         <v>14</v>
       </c>
       <c r="F234" s="2">
-        <v>4690</v>
+        <v>962</v>
       </c>
       <c r="G234" s="2" t="s">
         <v>15</v>
@@ -11063,7 +11063,7 @@
         <v>14</v>
       </c>
       <c r="F235" s="2">
-        <v>1555</v>
+        <v>1588</v>
       </c>
       <c r="G235" s="2" t="s">
         <v>15</v>
@@ -11095,7 +11095,7 @@
         <v>14</v>
       </c>
       <c r="F236" s="2">
-        <v>3504</v>
+        <v>3416</v>
       </c>
       <c r="G236" s="2" t="s">
         <v>15</v>
@@ -11127,7 +11127,7 @@
         <v>14</v>
       </c>
       <c r="F237" s="2">
-        <v>2531</v>
+        <v>1845</v>
       </c>
       <c r="G237" s="2" t="s">
         <v>15</v>
@@ -11159,7 +11159,7 @@
         <v>14</v>
       </c>
       <c r="F238" s="2">
-        <v>1428</v>
+        <v>1507</v>
       </c>
       <c r="G238" s="2" t="s">
         <v>15</v>
@@ -11191,7 +11191,7 @@
         <v>14</v>
       </c>
       <c r="F239" s="2">
-        <v>2708</v>
+        <v>3458</v>
       </c>
       <c r="G239" s="2" t="s">
         <v>15</v>
@@ -11223,7 +11223,7 @@
         <v>14</v>
       </c>
       <c r="F240" s="2">
-        <v>2986</v>
+        <v>1969</v>
       </c>
       <c r="G240" s="2" t="s">
         <v>15</v>
@@ -11255,7 +11255,7 @@
         <v>14</v>
       </c>
       <c r="F241" s="2">
-        <v>3260</v>
+        <v>4402</v>
       </c>
       <c r="G241" s="2" t="s">
         <v>15</v>
@@ -11287,7 +11287,7 @@
         <v>14</v>
       </c>
       <c r="F242" s="2">
-        <v>4509</v>
+        <v>2071</v>
       </c>
       <c r="G242" s="2" t="s">
         <v>15</v>
@@ -11319,7 +11319,7 @@
         <v>14</v>
       </c>
       <c r="F243" s="2">
-        <v>3649</v>
+        <v>4692</v>
       </c>
       <c r="G243" s="2" t="s">
         <v>15</v>
@@ -11351,7 +11351,7 @@
         <v>14</v>
       </c>
       <c r="F244" s="2">
-        <v>2814</v>
+        <v>1076</v>
       </c>
       <c r="G244" s="2" t="s">
         <v>15</v>
@@ -11383,7 +11383,7 @@
         <v>14</v>
       </c>
       <c r="F245" s="2">
-        <v>3050</v>
+        <v>4165</v>
       </c>
       <c r="G245" s="2" t="s">
         <v>15</v>
@@ -11415,7 +11415,7 @@
         <v>14</v>
       </c>
       <c r="F246" s="2">
-        <v>3066</v>
+        <v>1129</v>
       </c>
       <c r="G246" s="2" t="s">
         <v>15</v>
@@ -11447,7 +11447,7 @@
         <v>14</v>
       </c>
       <c r="F247" s="2">
-        <v>3630</v>
+        <v>1895</v>
       </c>
       <c r="G247" s="2" t="s">
         <v>15</v>
@@ -11479,7 +11479,7 @@
         <v>14</v>
       </c>
       <c r="F248" s="2">
-        <v>1226</v>
+        <v>1973</v>
       </c>
       <c r="G248" s="2" t="s">
         <v>15</v>
@@ -11511,7 +11511,7 @@
         <v>14</v>
       </c>
       <c r="F249" s="2">
-        <v>1591</v>
+        <v>2026</v>
       </c>
       <c r="G249" s="2" t="s">
         <v>15</v>
@@ -11543,7 +11543,7 @@
         <v>14</v>
       </c>
       <c r="F250" s="2">
-        <v>4377</v>
+        <v>3095</v>
       </c>
       <c r="G250" s="2" t="s">
         <v>15</v>
@@ -11575,7 +11575,7 @@
         <v>14</v>
       </c>
       <c r="F251" s="2">
-        <v>952</v>
+        <v>1251</v>
       </c>
       <c r="G251" s="2" t="s">
         <v>15</v>
@@ -11607,7 +11607,7 @@
         <v>14</v>
       </c>
       <c r="F252" s="2">
-        <v>2305</v>
+        <v>1629</v>
       </c>
       <c r="G252" s="2" t="s">
         <v>15</v>
@@ -11639,7 +11639,7 @@
         <v>14</v>
       </c>
       <c r="F253" s="2">
-        <v>1303</v>
+        <v>1652</v>
       </c>
       <c r="G253" s="2" t="s">
         <v>15</v>
@@ -11671,7 +11671,7 @@
         <v>14</v>
       </c>
       <c r="F254" s="2">
-        <v>3769</v>
+        <v>4588</v>
       </c>
       <c r="G254" s="2" t="s">
         <v>15</v>
@@ -11703,7 +11703,7 @@
         <v>14</v>
       </c>
       <c r="F255" s="2">
-        <v>2755</v>
+        <v>2996</v>
       </c>
       <c r="G255" s="2" t="s">
         <v>15</v>
@@ -11735,7 +11735,7 @@
         <v>14</v>
       </c>
       <c r="F256" s="2">
-        <v>1127</v>
+        <v>1606</v>
       </c>
       <c r="G256" s="2" t="s">
         <v>15</v>
@@ -11767,7 +11767,7 @@
         <v>14</v>
       </c>
       <c r="F257" s="2">
-        <v>2706</v>
+        <v>2582</v>
       </c>
       <c r="G257" s="2" t="s">
         <v>15</v>
@@ -11799,7 +11799,7 @@
         <v>14</v>
       </c>
       <c r="F258" s="2">
-        <v>3223</v>
+        <v>2519</v>
       </c>
       <c r="G258" s="2" t="s">
         <v>15</v>
@@ -11831,7 +11831,7 @@
         <v>14</v>
       </c>
       <c r="F259" s="2">
-        <v>1796</v>
+        <v>4593</v>
       </c>
       <c r="G259" s="2" t="s">
         <v>15</v>
@@ -11863,7 +11863,7 @@
         <v>14</v>
       </c>
       <c r="F260" s="2">
-        <v>944</v>
+        <v>3340</v>
       </c>
       <c r="G260" s="2" t="s">
         <v>15</v>
@@ -11895,7 +11895,7 @@
         <v>14</v>
       </c>
       <c r="F261" s="2">
-        <v>1426</v>
+        <v>2568</v>
       </c>
       <c r="G261" s="2" t="s">
         <v>15</v>
@@ -11927,7 +11927,7 @@
         <v>14</v>
       </c>
       <c r="F262" s="2">
-        <v>2446</v>
+        <v>877</v>
       </c>
       <c r="G262" s="2" t="s">
         <v>15</v>
@@ -11959,7 +11959,7 @@
         <v>14</v>
       </c>
       <c r="F263" s="2">
-        <v>1945</v>
+        <v>4277</v>
       </c>
       <c r="G263" s="2" t="s">
         <v>15</v>
@@ -11991,7 +11991,7 @@
         <v>14</v>
       </c>
       <c r="F264" s="2">
-        <v>2992</v>
+        <v>1602</v>
       </c>
       <c r="G264" s="2" t="s">
         <v>15</v>
@@ -12023,7 +12023,7 @@
         <v>14</v>
       </c>
       <c r="F265" s="2">
-        <v>1949</v>
+        <v>1449</v>
       </c>
       <c r="G265" s="2" t="s">
         <v>15</v>
@@ -12055,7 +12055,7 @@
         <v>14</v>
       </c>
       <c r="F266" s="2">
-        <v>1324</v>
+        <v>3457</v>
       </c>
       <c r="G266" s="2" t="s">
         <v>15</v>
@@ -12087,7 +12087,7 @@
         <v>14</v>
       </c>
       <c r="F267" s="2">
-        <v>2255</v>
+        <v>2741</v>
       </c>
       <c r="G267" s="2" t="s">
         <v>15</v>
@@ -12119,7 +12119,7 @@
         <v>14</v>
       </c>
       <c r="F268" s="2">
-        <v>1217</v>
+        <v>3208</v>
       </c>
       <c r="G268" s="2" t="s">
         <v>15</v>
@@ -12151,7 +12151,7 @@
         <v>14</v>
       </c>
       <c r="F269" s="2">
-        <v>2863</v>
+        <v>2239</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>15</v>
@@ -12183,7 +12183,7 @@
         <v>14</v>
       </c>
       <c r="F270" s="2">
-        <v>2514</v>
+        <v>4543</v>
       </c>
       <c r="G270" s="2" t="s">
         <v>15</v>
@@ -12215,7 +12215,7 @@
         <v>14</v>
       </c>
       <c r="F271" s="2">
-        <v>2581</v>
+        <v>3712</v>
       </c>
       <c r="G271" s="2" t="s">
         <v>15</v>
@@ -12247,7 +12247,7 @@
         <v>14</v>
       </c>
       <c r="F272" s="2">
-        <v>3381</v>
+        <v>4239</v>
       </c>
       <c r="G272" s="2" t="s">
         <v>15</v>
@@ -12279,7 +12279,7 @@
         <v>14</v>
       </c>
       <c r="F273" s="2">
-        <v>3640</v>
+        <v>4773</v>
       </c>
       <c r="G273" s="2" t="s">
         <v>15</v>
@@ -12311,7 +12311,7 @@
         <v>14</v>
       </c>
       <c r="F274" s="2">
-        <v>4587</v>
+        <v>1305</v>
       </c>
       <c r="G274" s="2" t="s">
         <v>15</v>
@@ -12343,7 +12343,7 @@
         <v>14</v>
       </c>
       <c r="F275" s="2">
-        <v>4224</v>
+        <v>4569</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>15</v>
@@ -12375,7 +12375,7 @@
         <v>14</v>
       </c>
       <c r="F276" s="2">
-        <v>2545</v>
+        <v>1567</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>15</v>
@@ -12407,7 +12407,7 @@
         <v>14</v>
       </c>
       <c r="F277" s="2">
-        <v>2351</v>
+        <v>1129</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>15</v>
@@ -12439,7 +12439,7 @@
         <v>14</v>
       </c>
       <c r="F278" s="2">
-        <v>3243</v>
+        <v>3028</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>15</v>
@@ -12471,7 +12471,7 @@
         <v>14</v>
       </c>
       <c r="F279" s="2">
-        <v>1883</v>
+        <v>4785</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>15</v>
@@ -12503,7 +12503,7 @@
         <v>14</v>
       </c>
       <c r="F280" s="2">
-        <v>2362</v>
+        <v>2739</v>
       </c>
       <c r="G280" s="2" t="s">
         <v>15</v>
@@ -12535,7 +12535,7 @@
         <v>14</v>
       </c>
       <c r="F281" s="2">
-        <v>1757</v>
+        <v>3274</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>15</v>
@@ -12567,7 +12567,7 @@
         <v>14</v>
       </c>
       <c r="F282" s="2">
-        <v>3695</v>
+        <v>3694</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>15</v>
@@ -12599,7 +12599,7 @@
         <v>14</v>
       </c>
       <c r="F283" s="2">
-        <v>3469</v>
+        <v>4549</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>15</v>
@@ -12631,7 +12631,7 @@
         <v>14</v>
       </c>
       <c r="F284" s="2">
-        <v>4694</v>
+        <v>3954</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>15</v>
@@ -12663,7 +12663,7 @@
         <v>14</v>
       </c>
       <c r="F285" s="2">
-        <v>2743</v>
+        <v>2745</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>15</v>
@@ -12695,7 +12695,7 @@
         <v>14</v>
       </c>
       <c r="F286" s="2">
-        <v>3806</v>
+        <v>4224</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>15</v>
@@ -12727,7 +12727,7 @@
         <v>14</v>
       </c>
       <c r="F287" s="2">
-        <v>2366</v>
+        <v>4295</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>15</v>
@@ -12759,7 +12759,7 @@
         <v>14</v>
       </c>
       <c r="F288" s="2">
-        <v>1470</v>
+        <v>4160</v>
       </c>
       <c r="G288" s="2" t="s">
         <v>15</v>
@@ -12791,7 +12791,7 @@
         <v>14</v>
       </c>
       <c r="F289" s="2">
-        <v>1517</v>
+        <v>1079</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>15</v>
@@ -12823,7 +12823,7 @@
         <v>14</v>
       </c>
       <c r="F290" s="2">
-        <v>3646</v>
+        <v>1680</v>
       </c>
       <c r="G290" s="2" t="s">
         <v>15</v>
@@ -12855,7 +12855,7 @@
         <v>14</v>
       </c>
       <c r="F291" s="2">
-        <v>2909</v>
+        <v>2102</v>
       </c>
       <c r="G291" s="2" t="s">
         <v>15</v>
@@ -12887,7 +12887,7 @@
         <v>14</v>
       </c>
       <c r="F292" s="2">
-        <v>831</v>
+        <v>3281</v>
       </c>
       <c r="G292" s="2" t="s">
         <v>15</v>
@@ -12919,7 +12919,7 @@
         <v>14</v>
       </c>
       <c r="F293" s="2">
-        <v>2511</v>
+        <v>937</v>
       </c>
       <c r="G293" s="2" t="s">
         <v>15</v>
@@ -12951,7 +12951,7 @@
         <v>14</v>
       </c>
       <c r="F294" s="2">
-        <v>3654</v>
+        <v>2656</v>
       </c>
       <c r="G294" s="2" t="s">
         <v>15</v>
@@ -12983,7 +12983,7 @@
         <v>14</v>
       </c>
       <c r="F295" s="2">
-        <v>3598</v>
+        <v>3189</v>
       </c>
       <c r="G295" s="2" t="s">
         <v>15</v>
@@ -13015,7 +13015,7 @@
         <v>14</v>
       </c>
       <c r="F296" s="2">
-        <v>2453</v>
+        <v>2092</v>
       </c>
       <c r="G296" s="2" t="s">
         <v>15</v>
@@ -13047,7 +13047,7 @@
         <v>14</v>
       </c>
       <c r="F297" s="2">
-        <v>3012</v>
+        <v>2885</v>
       </c>
       <c r="G297" s="2" t="s">
         <v>15</v>
@@ -13079,7 +13079,7 @@
         <v>14</v>
       </c>
       <c r="F298" s="2">
-        <v>4235</v>
+        <v>2970</v>
       </c>
       <c r="G298" s="2" t="s">
         <v>15</v>
@@ -13111,7 +13111,7 @@
         <v>14</v>
       </c>
       <c r="F299" s="2">
-        <v>1065</v>
+        <v>4200</v>
       </c>
       <c r="G299" s="2" t="s">
         <v>15</v>
@@ -13143,7 +13143,7 @@
         <v>14</v>
       </c>
       <c r="F300" s="2">
-        <v>4548</v>
+        <v>4666</v>
       </c>
       <c r="G300" s="2" t="s">
         <v>15</v>
@@ -13175,7 +13175,7 @@
         <v>14</v>
       </c>
       <c r="F301" s="2">
-        <v>4763</v>
+        <v>1415</v>
       </c>
       <c r="G301" s="2" t="s">
         <v>15</v>
@@ -13207,7 +13207,7 @@
         <v>14</v>
       </c>
       <c r="F302" s="2">
-        <v>3027</v>
+        <v>1737</v>
       </c>
       <c r="G302" s="2" t="s">
         <v>15</v>
@@ -13239,7 +13239,7 @@
         <v>14</v>
       </c>
       <c r="F303" s="2">
-        <v>4101</v>
+        <v>4530</v>
       </c>
       <c r="G303" s="2" t="s">
         <v>15</v>
@@ -13271,7 +13271,7 @@
         <v>14</v>
       </c>
       <c r="F304" s="2">
-        <v>2415</v>
+        <v>2866</v>
       </c>
       <c r="G304" s="2" t="s">
         <v>15</v>
@@ -13303,7 +13303,7 @@
         <v>14</v>
       </c>
       <c r="F305" s="2">
-        <v>2907</v>
+        <v>1772</v>
       </c>
       <c r="G305" s="2" t="s">
         <v>15</v>
@@ -13335,7 +13335,7 @@
         <v>14</v>
       </c>
       <c r="F306" s="2">
-        <v>1561</v>
+        <v>3642</v>
       </c>
       <c r="G306" s="2" t="s">
         <v>15</v>
@@ -13367,7 +13367,7 @@
         <v>14</v>
       </c>
       <c r="F307" s="2">
-        <v>2159</v>
+        <v>1291</v>
       </c>
       <c r="G307" s="2" t="s">
         <v>15</v>
@@ -13399,7 +13399,7 @@
         <v>14</v>
       </c>
       <c r="F308" s="2">
-        <v>3445</v>
+        <v>4466</v>
       </c>
       <c r="G308" s="2" t="s">
         <v>15</v>
@@ -13431,7 +13431,7 @@
         <v>14</v>
       </c>
       <c r="F309" s="2">
-        <v>3658</v>
+        <v>959</v>
       </c>
       <c r="G309" s="2" t="s">
         <v>15</v>
@@ -13463,7 +13463,7 @@
         <v>14</v>
       </c>
       <c r="F310" s="2">
-        <v>3266</v>
+        <v>4564</v>
       </c>
       <c r="G310" s="2" t="s">
         <v>15</v>
@@ -13495,7 +13495,7 @@
         <v>14</v>
       </c>
       <c r="F311" s="2">
-        <v>3620</v>
+        <v>3778</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>15</v>
@@ -13527,7 +13527,7 @@
         <v>14</v>
       </c>
       <c r="F312" s="2">
-        <v>3805</v>
+        <v>2889</v>
       </c>
       <c r="G312" s="2" t="s">
         <v>15</v>
@@ -13559,7 +13559,7 @@
         <v>14</v>
       </c>
       <c r="F313" s="2">
-        <v>1251</v>
+        <v>1656</v>
       </c>
       <c r="G313" s="2" t="s">
         <v>15</v>
@@ -13591,7 +13591,7 @@
         <v>14</v>
       </c>
       <c r="F314" s="2">
-        <v>1247</v>
+        <v>2049</v>
       </c>
       <c r="G314" s="2" t="s">
         <v>15</v>
@@ -13623,7 +13623,7 @@
         <v>14</v>
       </c>
       <c r="F315" s="2">
-        <v>1950</v>
+        <v>917</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>15</v>
@@ -13655,7 +13655,7 @@
         <v>14</v>
       </c>
       <c r="F316" s="2">
-        <v>1477</v>
+        <v>3931</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>15</v>
@@ -13687,7 +13687,7 @@
         <v>14</v>
       </c>
       <c r="F317" s="2">
-        <v>1234</v>
+        <v>3666</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>15</v>
@@ -13719,7 +13719,7 @@
         <v>14</v>
       </c>
       <c r="F318" s="2">
-        <v>4451</v>
+        <v>3554</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>15</v>
@@ -13751,7 +13751,7 @@
         <v>14</v>
       </c>
       <c r="F319" s="2">
-        <v>4140</v>
+        <v>4650</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>15</v>
@@ -13783,7 +13783,7 @@
         <v>14</v>
       </c>
       <c r="F320" s="2">
-        <v>3230</v>
+        <v>1437</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>15</v>
@@ -13815,7 +13815,7 @@
         <v>14</v>
       </c>
       <c r="F321" s="2">
-        <v>3047</v>
+        <v>993</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>15</v>
@@ -13847,7 +13847,7 @@
         <v>14</v>
       </c>
       <c r="F322" s="2">
-        <v>2849</v>
+        <v>2386</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>15</v>
@@ -13879,7 +13879,7 @@
         <v>14</v>
       </c>
       <c r="F323" s="2">
-        <v>2294</v>
+        <v>1785</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>15</v>
@@ -13911,7 +13911,7 @@
         <v>14</v>
       </c>
       <c r="F324" s="2">
-        <v>3453</v>
+        <v>1432</v>
       </c>
       <c r="G324" s="2" t="s">
         <v>15</v>
@@ -13943,7 +13943,7 @@
         <v>14</v>
       </c>
       <c r="F325" s="2">
-        <v>960</v>
+        <v>3004</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>15</v>
@@ -13975,7 +13975,7 @@
         <v>14</v>
       </c>
       <c r="F326" s="2">
-        <v>2133</v>
+        <v>4437</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>15</v>
@@ -14007,7 +14007,7 @@
         <v>14</v>
       </c>
       <c r="F327" s="2">
-        <v>3056</v>
+        <v>1971</v>
       </c>
       <c r="G327" s="2" t="s">
         <v>15</v>
@@ -14039,7 +14039,7 @@
         <v>14</v>
       </c>
       <c r="F328" s="2">
-        <v>3342</v>
+        <v>1099</v>
       </c>
       <c r="G328" s="2" t="s">
         <v>15</v>
@@ -14071,7 +14071,7 @@
         <v>14</v>
       </c>
       <c r="F329" s="2">
-        <v>1757</v>
+        <v>3912</v>
       </c>
       <c r="G329" s="2" t="s">
         <v>15</v>
@@ -14103,7 +14103,7 @@
         <v>14</v>
       </c>
       <c r="F330" s="2">
-        <v>4244</v>
+        <v>3581</v>
       </c>
       <c r="G330" s="2" t="s">
         <v>15</v>
@@ -14135,7 +14135,7 @@
         <v>14</v>
       </c>
       <c r="F331" s="2">
-        <v>4119</v>
+        <v>4102</v>
       </c>
       <c r="G331" s="2" t="s">
         <v>15</v>
@@ -14167,7 +14167,7 @@
         <v>14</v>
       </c>
       <c r="F332" s="2">
-        <v>2824</v>
+        <v>3869</v>
       </c>
       <c r="G332" s="2" t="s">
         <v>15</v>
@@ -14199,7 +14199,7 @@
         <v>14</v>
       </c>
       <c r="F333" s="2">
-        <v>2980</v>
+        <v>4072</v>
       </c>
       <c r="G333" s="2" t="s">
         <v>15</v>
@@ -14231,7 +14231,7 @@
         <v>14</v>
       </c>
       <c r="F334" s="2">
-        <v>3244</v>
+        <v>3115</v>
       </c>
       <c r="G334" s="2" t="s">
         <v>15</v>
@@ -14263,7 +14263,7 @@
         <v>14</v>
       </c>
       <c r="F335" s="2">
-        <v>1729</v>
+        <v>3023</v>
       </c>
       <c r="G335" s="2" t="s">
         <v>15</v>
@@ -14295,7 +14295,7 @@
         <v>14</v>
       </c>
       <c r="F336" s="2">
-        <v>3796</v>
+        <v>2354</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>15</v>
@@ -14327,7 +14327,7 @@
         <v>14</v>
       </c>
       <c r="F337" s="2">
-        <v>2184</v>
+        <v>2772</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>15</v>
@@ -14359,7 +14359,7 @@
         <v>14</v>
       </c>
       <c r="F338" s="2">
-        <v>4775</v>
+        <v>1737</v>
       </c>
       <c r="G338" s="2" t="s">
         <v>15</v>
@@ -14391,7 +14391,7 @@
         <v>14</v>
       </c>
       <c r="F339" s="2">
-        <v>1948</v>
+        <v>3046</v>
       </c>
       <c r="G339" s="2" t="s">
         <v>15</v>
@@ -14423,7 +14423,7 @@
         <v>14</v>
       </c>
       <c r="F340" s="2">
-        <v>1064</v>
+        <v>2292</v>
       </c>
       <c r="G340" s="2" t="s">
         <v>15</v>
@@ -14455,7 +14455,7 @@
         <v>14</v>
       </c>
       <c r="F341" s="2">
-        <v>4638</v>
+        <v>2871</v>
       </c>
       <c r="G341" s="2" t="s">
         <v>15</v>
@@ -14487,7 +14487,7 @@
         <v>14</v>
       </c>
       <c r="F342" s="2">
-        <v>1925</v>
+        <v>3172</v>
       </c>
       <c r="G342" s="2" t="s">
         <v>15</v>
@@ -14519,7 +14519,7 @@
         <v>14</v>
       </c>
       <c r="F343" s="2">
-        <v>4611</v>
+        <v>4089</v>
       </c>
       <c r="G343" s="2" t="s">
         <v>15</v>
@@ -14551,7 +14551,7 @@
         <v>14</v>
       </c>
       <c r="F344" s="2">
-        <v>1268</v>
+        <v>2032</v>
       </c>
       <c r="G344" s="2" t="s">
         <v>15</v>
@@ -14583,7 +14583,7 @@
         <v>14</v>
       </c>
       <c r="F345" s="2">
-        <v>2128</v>
+        <v>3432</v>
       </c>
       <c r="G345" s="2" t="s">
         <v>15</v>
@@ -14615,7 +14615,7 @@
         <v>14</v>
       </c>
       <c r="F346" s="2">
-        <v>4637</v>
+        <v>3294</v>
       </c>
       <c r="G346" s="2" t="s">
         <v>15</v>
@@ -14647,7 +14647,7 @@
         <v>14</v>
       </c>
       <c r="F347" s="2">
-        <v>4689</v>
+        <v>4375</v>
       </c>
       <c r="G347" s="2" t="s">
         <v>15</v>
@@ -14679,7 +14679,7 @@
         <v>14</v>
       </c>
       <c r="F348" s="2">
-        <v>2996</v>
+        <v>1218</v>
       </c>
       <c r="G348" s="2" t="s">
         <v>15</v>
@@ -14711,7 +14711,7 @@
         <v>14</v>
       </c>
       <c r="F349" s="2">
-        <v>1299</v>
+        <v>4223</v>
       </c>
       <c r="G349" s="2" t="s">
         <v>15</v>
@@ -14743,7 +14743,7 @@
         <v>14</v>
       </c>
       <c r="F350" s="2">
-        <v>1113</v>
+        <v>1970</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>15</v>
@@ -14775,7 +14775,7 @@
         <v>14</v>
       </c>
       <c r="F351" s="2">
-        <v>3800</v>
+        <v>3164</v>
       </c>
       <c r="G351" s="2" t="s">
         <v>15</v>
@@ -14807,7 +14807,7 @@
         <v>14</v>
       </c>
       <c r="F352" s="2">
-        <v>979</v>
+        <v>4392</v>
       </c>
       <c r="G352" s="2" t="s">
         <v>15</v>
@@ -14839,7 +14839,7 @@
         <v>14</v>
       </c>
       <c r="F353" s="2">
-        <v>3290</v>
+        <v>4626</v>
       </c>
       <c r="G353" s="2" t="s">
         <v>15</v>
@@ -14871,7 +14871,7 @@
         <v>14</v>
       </c>
       <c r="F354" s="2">
-        <v>1290</v>
+        <v>813</v>
       </c>
       <c r="G354" s="2" t="s">
         <v>15</v>
@@ -14903,7 +14903,7 @@
         <v>14</v>
       </c>
       <c r="F355" s="2">
-        <v>3498</v>
+        <v>4638</v>
       </c>
       <c r="G355" s="2" t="s">
         <v>15</v>
@@ -14935,7 +14935,7 @@
         <v>14</v>
       </c>
       <c r="F356" s="2">
-        <v>3429</v>
+        <v>2734</v>
       </c>
       <c r="G356" s="2" t="s">
         <v>15</v>
@@ -14967,7 +14967,7 @@
         <v>14</v>
       </c>
       <c r="F357" s="2">
-        <v>1150</v>
+        <v>3803</v>
       </c>
       <c r="G357" s="2" t="s">
         <v>15</v>
@@ -14999,7 +14999,7 @@
         <v>14</v>
       </c>
       <c r="F358" s="2">
-        <v>4620</v>
+        <v>1741</v>
       </c>
       <c r="G358" s="2" t="s">
         <v>15</v>
@@ -15031,7 +15031,7 @@
         <v>14</v>
       </c>
       <c r="F359" s="2">
-        <v>2163</v>
+        <v>4562</v>
       </c>
       <c r="G359" s="2" t="s">
         <v>15</v>
@@ -15063,7 +15063,7 @@
         <v>14</v>
       </c>
       <c r="F360" s="2">
-        <v>1952</v>
+        <v>2041</v>
       </c>
       <c r="G360" s="2" t="s">
         <v>15</v>
@@ -15095,7 +15095,7 @@
         <v>14</v>
       </c>
       <c r="F361" s="2">
-        <v>4516</v>
+        <v>3845</v>
       </c>
       <c r="G361" s="2" t="s">
         <v>15</v>
@@ -15127,7 +15127,7 @@
         <v>14</v>
       </c>
       <c r="F362" s="2">
-        <v>1630</v>
+        <v>3094</v>
       </c>
       <c r="G362" s="2" t="s">
         <v>15</v>
@@ -15159,7 +15159,7 @@
         <v>14</v>
       </c>
       <c r="F363" s="2">
-        <v>2702</v>
+        <v>2910</v>
       </c>
       <c r="G363" s="2" t="s">
         <v>15</v>
@@ -15191,7 +15191,7 @@
         <v>14</v>
       </c>
       <c r="F364" s="2">
-        <v>1333</v>
+        <v>1471</v>
       </c>
       <c r="G364" s="2" t="s">
         <v>15</v>
@@ -15223,7 +15223,7 @@
         <v>14</v>
       </c>
       <c r="F365" s="2">
-        <v>2046</v>
+        <v>1653</v>
       </c>
       <c r="G365" s="2" t="s">
         <v>15</v>
@@ -15255,7 +15255,7 @@
         <v>14</v>
       </c>
       <c r="F366" s="2">
-        <v>800</v>
+        <v>2406</v>
       </c>
       <c r="G366" s="2" t="s">
         <v>15</v>
@@ -15287,7 +15287,7 @@
         <v>14</v>
       </c>
       <c r="F367" s="2">
-        <v>3996</v>
+        <v>857</v>
       </c>
       <c r="G367" s="2" t="s">
         <v>15</v>
@@ -15319,7 +15319,7 @@
         <v>14</v>
       </c>
       <c r="F368" s="2">
-        <v>4691</v>
+        <v>913</v>
       </c>
       <c r="G368" s="2" t="s">
         <v>15</v>
@@ -15351,7 +15351,7 @@
         <v>14</v>
       </c>
       <c r="F369" s="2">
-        <v>2586</v>
+        <v>3040</v>
       </c>
       <c r="G369" s="2" t="s">
         <v>15</v>
@@ -15383,7 +15383,7 @@
         <v>14</v>
       </c>
       <c r="F370" s="2">
-        <v>3418</v>
+        <v>1052</v>
       </c>
       <c r="G370" s="2" t="s">
         <v>15</v>
@@ -15415,7 +15415,7 @@
         <v>14</v>
       </c>
       <c r="F371" s="2">
-        <v>2409</v>
+        <v>3905</v>
       </c>
       <c r="G371" s="2" t="s">
         <v>15</v>
@@ -15447,7 +15447,7 @@
         <v>14</v>
       </c>
       <c r="F372" s="2">
-        <v>1705</v>
+        <v>4022</v>
       </c>
       <c r="G372" s="2" t="s">
         <v>15</v>
@@ -15479,7 +15479,7 @@
         <v>14</v>
       </c>
       <c r="F373" s="2">
-        <v>4157</v>
+        <v>3035</v>
       </c>
       <c r="G373" s="2" t="s">
         <v>15</v>
@@ -15511,7 +15511,7 @@
         <v>14</v>
       </c>
       <c r="F374" s="2">
-        <v>1324</v>
+        <v>2494</v>
       </c>
       <c r="G374" s="2" t="s">
         <v>15</v>
@@ -15543,7 +15543,7 @@
         <v>14</v>
       </c>
       <c r="F375" s="2">
-        <v>4738</v>
+        <v>3998</v>
       </c>
       <c r="G375" s="2" t="s">
         <v>15</v>
@@ -15575,7 +15575,7 @@
         <v>14</v>
       </c>
       <c r="F376" s="2">
-        <v>2360</v>
+        <v>3948</v>
       </c>
       <c r="G376" s="2" t="s">
         <v>15</v>
@@ -15607,7 +15607,7 @@
         <v>14</v>
       </c>
       <c r="F377" s="2">
-        <v>952</v>
+        <v>3124</v>
       </c>
       <c r="G377" s="2" t="s">
         <v>15</v>
@@ -15639,7 +15639,7 @@
         <v>14</v>
       </c>
       <c r="F378" s="2">
-        <v>2314</v>
+        <v>2174</v>
       </c>
       <c r="G378" s="2" t="s">
         <v>15</v>
@@ -15671,7 +15671,7 @@
         <v>14</v>
       </c>
       <c r="F379" s="2">
-        <v>3955</v>
+        <v>4130</v>
       </c>
       <c r="G379" s="2" t="s">
         <v>15</v>
@@ -15703,7 +15703,7 @@
         <v>14</v>
       </c>
       <c r="F380" s="2">
-        <v>2004</v>
+        <v>1052</v>
       </c>
       <c r="G380" s="2" t="s">
         <v>15</v>
@@ -15735,7 +15735,7 @@
         <v>14</v>
       </c>
       <c r="F381" s="2">
-        <v>3094</v>
+        <v>1881</v>
       </c>
       <c r="G381" s="2" t="s">
         <v>15</v>
@@ -15767,7 +15767,7 @@
         <v>14</v>
       </c>
       <c r="F382" s="2">
-        <v>1945</v>
+        <v>4287</v>
       </c>
       <c r="G382" s="2" t="s">
         <v>15</v>
@@ -15799,7 +15799,7 @@
         <v>14</v>
       </c>
       <c r="F383" s="2">
-        <v>1104</v>
+        <v>3603</v>
       </c>
       <c r="G383" s="2" t="s">
         <v>15</v>
@@ -15831,7 +15831,7 @@
         <v>14</v>
       </c>
       <c r="F384" s="2">
-        <v>1013</v>
+        <v>2413</v>
       </c>
       <c r="G384" s="2" t="s">
         <v>15</v>
@@ -15863,7 +15863,7 @@
         <v>14</v>
       </c>
       <c r="F385" s="2">
-        <v>4416</v>
+        <v>4027</v>
       </c>
       <c r="G385" s="2" t="s">
         <v>15</v>
@@ -15895,7 +15895,7 @@
         <v>14</v>
       </c>
       <c r="F386" s="2">
-        <v>3663</v>
+        <v>1790</v>
       </c>
       <c r="G386" s="2" t="s">
         <v>15</v>
@@ -15927,7 +15927,7 @@
         <v>14</v>
       </c>
       <c r="F387" s="2">
-        <v>3340</v>
+        <v>942</v>
       </c>
       <c r="G387" s="2" t="s">
         <v>15</v>
@@ -15959,7 +15959,7 @@
         <v>14</v>
       </c>
       <c r="F388" s="2">
-        <v>1716</v>
+        <v>3528</v>
       </c>
       <c r="G388" s="2" t="s">
         <v>15</v>
@@ -15991,7 +15991,7 @@
         <v>14</v>
       </c>
       <c r="F389" s="2">
-        <v>4009</v>
+        <v>1605</v>
       </c>
       <c r="G389" s="2" t="s">
         <v>15</v>
@@ -16023,7 +16023,7 @@
         <v>14</v>
       </c>
       <c r="F390" s="2">
-        <v>3834</v>
+        <v>3299</v>
       </c>
       <c r="G390" s="2" t="s">
         <v>15</v>
@@ -16055,7 +16055,7 @@
         <v>14</v>
       </c>
       <c r="F391" s="2">
-        <v>950</v>
+        <v>1157</v>
       </c>
       <c r="G391" s="2" t="s">
         <v>15</v>
@@ -16087,7 +16087,7 @@
         <v>14</v>
       </c>
       <c r="F392" s="2">
-        <v>2543</v>
+        <v>3965</v>
       </c>
       <c r="G392" s="2" t="s">
         <v>15</v>
@@ -16119,7 +16119,7 @@
         <v>14</v>
       </c>
       <c r="F393" s="2">
-        <v>2181</v>
+        <v>853</v>
       </c>
       <c r="G393" s="2" t="s">
         <v>15</v>
@@ -16151,7 +16151,7 @@
         <v>14</v>
       </c>
       <c r="F394" s="2">
-        <v>1736</v>
+        <v>1134</v>
       </c>
       <c r="G394" s="2" t="s">
         <v>15</v>
@@ -16183,7 +16183,7 @@
         <v>14</v>
       </c>
       <c r="F395" s="2">
-        <v>870</v>
+        <v>4441</v>
       </c>
       <c r="G395" s="2" t="s">
         <v>15</v>
@@ -16215,7 +16215,7 @@
         <v>14</v>
       </c>
       <c r="F396" s="2">
-        <v>1254</v>
+        <v>3735</v>
       </c>
       <c r="G396" s="2" t="s">
         <v>15</v>
@@ -16247,7 +16247,7 @@
         <v>14</v>
       </c>
       <c r="F397" s="2">
-        <v>2575</v>
+        <v>1221</v>
       </c>
       <c r="G397" s="2" t="s">
         <v>15</v>
@@ -16279,7 +16279,7 @@
         <v>14</v>
       </c>
       <c r="F398" s="2">
-        <v>3091</v>
+        <v>3304</v>
       </c>
       <c r="G398" s="2" t="s">
         <v>15</v>
@@ -16311,7 +16311,7 @@
         <v>14</v>
       </c>
       <c r="F399" s="2">
-        <v>1443</v>
+        <v>2445</v>
       </c>
       <c r="G399" s="2" t="s">
         <v>15</v>
@@ -16343,7 +16343,7 @@
         <v>14</v>
       </c>
       <c r="F400" s="2">
-        <v>3362</v>
+        <v>2352</v>
       </c>
       <c r="G400" s="2" t="s">
         <v>15</v>
@@ -16375,7 +16375,7 @@
         <v>14</v>
       </c>
       <c r="F401" s="2">
-        <v>1140</v>
+        <v>2083</v>
       </c>
       <c r="G401" s="2" t="s">
         <v>15</v>
@@ -16407,7 +16407,7 @@
         <v>14</v>
       </c>
       <c r="F402" s="2">
-        <v>3980</v>
+        <v>3100</v>
       </c>
       <c r="G402" s="2" t="s">
         <v>15</v>
@@ -16439,7 +16439,7 @@
         <v>14</v>
       </c>
       <c r="F403" s="2">
-        <v>4357</v>
+        <v>3473</v>
       </c>
       <c r="G403" s="2" t="s">
         <v>15</v>
@@ -16471,7 +16471,7 @@
         <v>14</v>
       </c>
       <c r="F404" s="2">
-        <v>923</v>
+        <v>2228</v>
       </c>
       <c r="G404" s="2" t="s">
         <v>15</v>
@@ -16503,7 +16503,7 @@
         <v>14</v>
       </c>
       <c r="F405" s="2">
-        <v>935</v>
+        <v>805</v>
       </c>
       <c r="G405" s="2" t="s">
         <v>15</v>
@@ -16535,7 +16535,7 @@
         <v>14</v>
       </c>
       <c r="F406" s="2">
-        <v>1189</v>
+        <v>3586</v>
       </c>
       <c r="G406" s="2" t="s">
         <v>15</v>
@@ -16567,7 +16567,7 @@
         <v>14</v>
       </c>
       <c r="F407" s="2">
-        <v>1050</v>
+        <v>4555</v>
       </c>
       <c r="G407" s="2" t="s">
         <v>15</v>
@@ -16599,7 +16599,7 @@
         <v>14</v>
       </c>
       <c r="F408" s="2">
-        <v>1027</v>
+        <v>1078</v>
       </c>
       <c r="G408" s="2" t="s">
         <v>15</v>
@@ -16631,7 +16631,7 @@
         <v>14</v>
       </c>
       <c r="F409" s="2">
-        <v>4181</v>
+        <v>4245</v>
       </c>
       <c r="G409" s="2" t="s">
         <v>15</v>
@@ -16663,7 +16663,7 @@
         <v>14</v>
       </c>
       <c r="F410" s="2">
-        <v>1486</v>
+        <v>1046</v>
       </c>
       <c r="G410" s="2" t="s">
         <v>15</v>
@@ -16695,7 +16695,7 @@
         <v>14</v>
       </c>
       <c r="F411" s="2">
-        <v>4747</v>
+        <v>2479</v>
       </c>
       <c r="G411" s="2" t="s">
         <v>15</v>
@@ -16727,7 +16727,7 @@
         <v>14</v>
       </c>
       <c r="F412" s="2">
-        <v>2933</v>
+        <v>3944</v>
       </c>
       <c r="G412" s="2" t="s">
         <v>15</v>
@@ -16759,7 +16759,7 @@
         <v>14</v>
       </c>
       <c r="F413" s="2">
-        <v>1428</v>
+        <v>2336</v>
       </c>
       <c r="G413" s="2" t="s">
         <v>15</v>
@@ -16791,7 +16791,7 @@
         <v>14</v>
       </c>
       <c r="F414" s="2">
-        <v>1050</v>
+        <v>4571</v>
       </c>
       <c r="G414" s="2" t="s">
         <v>15</v>
@@ -16823,7 +16823,7 @@
         <v>14</v>
       </c>
       <c r="F415" s="2">
-        <v>3646</v>
+        <v>1110</v>
       </c>
       <c r="G415" s="2" t="s">
         <v>15</v>
@@ -16855,7 +16855,7 @@
         <v>14</v>
       </c>
       <c r="F416" s="2">
-        <v>1963</v>
+        <v>1826</v>
       </c>
       <c r="G416" s="2" t="s">
         <v>15</v>
@@ -16887,7 +16887,7 @@
         <v>14</v>
       </c>
       <c r="F417" s="2">
-        <v>964</v>
+        <v>3967</v>
       </c>
       <c r="G417" s="2" t="s">
         <v>15</v>
@@ -16919,7 +16919,7 @@
         <v>14</v>
       </c>
       <c r="F418" s="2">
-        <v>4768</v>
+        <v>3218</v>
       </c>
       <c r="G418" s="2" t="s">
         <v>15</v>
@@ -16951,7 +16951,7 @@
         <v>14</v>
       </c>
       <c r="F419" s="2">
-        <v>3055</v>
+        <v>1388</v>
       </c>
       <c r="G419" s="2" t="s">
         <v>15</v>
@@ -16983,7 +16983,7 @@
         <v>14</v>
       </c>
       <c r="F420" s="2">
-        <v>2189</v>
+        <v>945</v>
       </c>
       <c r="G420" s="2" t="s">
         <v>15</v>
@@ -17015,7 +17015,7 @@
         <v>14</v>
       </c>
       <c r="F421" s="2">
-        <v>959</v>
+        <v>1858</v>
       </c>
       <c r="G421" s="2" t="s">
         <v>15</v>
@@ -17047,7 +17047,7 @@
         <v>14</v>
       </c>
       <c r="F422" s="2">
-        <v>4728</v>
+        <v>4081</v>
       </c>
       <c r="G422" s="2" t="s">
         <v>15</v>
@@ -17079,7 +17079,7 @@
         <v>14</v>
       </c>
       <c r="F423" s="2">
-        <v>3599</v>
+        <v>4728</v>
       </c>
       <c r="G423" s="2" t="s">
         <v>15</v>
@@ -17111,7 +17111,7 @@
         <v>14</v>
       </c>
       <c r="F424" s="2">
-        <v>3689</v>
+        <v>3251</v>
       </c>
       <c r="G424" s="2" t="s">
         <v>15</v>
@@ -17143,7 +17143,7 @@
         <v>14</v>
       </c>
       <c r="F425" s="2">
-        <v>1328</v>
+        <v>2653</v>
       </c>
       <c r="G425" s="2" t="s">
         <v>15</v>
@@ -17175,7 +17175,7 @@
         <v>14</v>
       </c>
       <c r="F426" s="2">
-        <v>2073</v>
+        <v>3991</v>
       </c>
       <c r="G426" s="2" t="s">
         <v>15</v>
@@ -17207,7 +17207,7 @@
         <v>14</v>
       </c>
       <c r="F427" s="2">
-        <v>2351</v>
+        <v>2839</v>
       </c>
       <c r="G427" s="2" t="s">
         <v>15</v>
@@ -17239,7 +17239,7 @@
         <v>14</v>
       </c>
       <c r="F428" s="2">
-        <v>4005</v>
+        <v>2343</v>
       </c>
       <c r="G428" s="2" t="s">
         <v>15</v>
@@ -17271,7 +17271,7 @@
         <v>14</v>
       </c>
       <c r="F429" s="2">
-        <v>813</v>
+        <v>4266</v>
       </c>
       <c r="G429" s="2" t="s">
         <v>15</v>
@@ -17303,7 +17303,7 @@
         <v>14</v>
       </c>
       <c r="F430" s="2">
-        <v>3222</v>
+        <v>3168</v>
       </c>
       <c r="G430" s="2" t="s">
         <v>15</v>
@@ -17335,7 +17335,7 @@
         <v>14</v>
       </c>
       <c r="F431" s="2">
-        <v>1774</v>
+        <v>3419</v>
       </c>
       <c r="G431" s="2" t="s">
         <v>15</v>
@@ -17367,7 +17367,7 @@
         <v>14</v>
       </c>
       <c r="F432" s="2">
-        <v>2908</v>
+        <v>2427</v>
       </c>
       <c r="G432" s="2" t="s">
         <v>15</v>
@@ -17399,7 +17399,7 @@
         <v>14</v>
       </c>
       <c r="F433" s="2">
-        <v>1187</v>
+        <v>3228</v>
       </c>
       <c r="G433" s="2" t="s">
         <v>15</v>
@@ -17431,7 +17431,7 @@
         <v>14</v>
       </c>
       <c r="F434" s="2">
-        <v>4766</v>
+        <v>1442</v>
       </c>
       <c r="G434" s="2" t="s">
         <v>15</v>
@@ -17463,7 +17463,7 @@
         <v>14</v>
       </c>
       <c r="F435" s="2">
-        <v>3107</v>
+        <v>2748</v>
       </c>
       <c r="G435" s="2" t="s">
         <v>15</v>
@@ -17495,7 +17495,7 @@
         <v>14</v>
       </c>
       <c r="F436" s="2">
-        <v>3180</v>
+        <v>2163</v>
       </c>
       <c r="G436" s="2" t="s">
         <v>15</v>
@@ -17527,7 +17527,7 @@
         <v>14</v>
       </c>
       <c r="F437" s="2">
-        <v>3860</v>
+        <v>4126</v>
       </c>
       <c r="G437" s="2" t="s">
         <v>15</v>
@@ -17559,7 +17559,7 @@
         <v>14</v>
       </c>
       <c r="F438" s="2">
-        <v>3144</v>
+        <v>1349</v>
       </c>
       <c r="G438" s="2" t="s">
         <v>15</v>
@@ -17591,7 +17591,7 @@
         <v>14</v>
       </c>
       <c r="F439" s="2">
-        <v>2853</v>
+        <v>2348</v>
       </c>
       <c r="G439" s="2" t="s">
         <v>15</v>
@@ -17623,7 +17623,7 @@
         <v>14</v>
       </c>
       <c r="F440" s="2">
-        <v>4773</v>
+        <v>4471</v>
       </c>
       <c r="G440" s="2" t="s">
         <v>15</v>
@@ -17655,7 +17655,7 @@
         <v>14</v>
       </c>
       <c r="F441" s="2">
-        <v>3557</v>
+        <v>2767</v>
       </c>
       <c r="G441" s="2" t="s">
         <v>15</v>
@@ -17687,7 +17687,7 @@
         <v>14</v>
       </c>
       <c r="F442" s="2">
-        <v>4217</v>
+        <v>2625</v>
       </c>
       <c r="G442" s="2" t="s">
         <v>15</v>
@@ -17719,7 +17719,7 @@
         <v>14</v>
       </c>
       <c r="F443" s="2">
-        <v>3114</v>
+        <v>3004</v>
       </c>
       <c r="G443" s="2" t="s">
         <v>15</v>
@@ -17751,7 +17751,7 @@
         <v>14</v>
       </c>
       <c r="F444" s="2">
-        <v>3676</v>
+        <v>4161</v>
       </c>
       <c r="G444" s="2" t="s">
         <v>15</v>
@@ -17783,7 +17783,7 @@
         <v>14</v>
       </c>
       <c r="F445" s="2">
-        <v>4321</v>
+        <v>2282</v>
       </c>
       <c r="G445" s="2" t="s">
         <v>15</v>
@@ -17815,7 +17815,7 @@
         <v>14</v>
       </c>
       <c r="F446" s="2">
-        <v>4501</v>
+        <v>4669</v>
       </c>
       <c r="G446" s="2" t="s">
         <v>15</v>
@@ -17847,7 +17847,7 @@
         <v>14</v>
       </c>
       <c r="F447" s="2">
-        <v>1468</v>
+        <v>2402</v>
       </c>
       <c r="G447" s="2" t="s">
         <v>15</v>
@@ -17879,7 +17879,7 @@
         <v>14</v>
       </c>
       <c r="F448" s="2">
-        <v>3861</v>
+        <v>4396</v>
       </c>
       <c r="G448" s="2" t="s">
         <v>15</v>
@@ -17911,7 +17911,7 @@
         <v>14</v>
       </c>
       <c r="F449" s="2">
-        <v>3172</v>
+        <v>3518</v>
       </c>
       <c r="G449" s="2" t="s">
         <v>15</v>
@@ -17943,7 +17943,7 @@
         <v>14</v>
       </c>
       <c r="F450" s="2">
-        <v>1535</v>
+        <v>4164</v>
       </c>
       <c r="G450" s="2" t="s">
         <v>15</v>
@@ -17975,7 +17975,7 @@
         <v>14</v>
       </c>
       <c r="F451" s="2">
-        <v>3165</v>
+        <v>3059</v>
       </c>
       <c r="G451" s="2" t="s">
         <v>15</v>
@@ -18007,7 +18007,7 @@
         <v>14</v>
       </c>
       <c r="F452" s="2">
-        <v>4614</v>
+        <v>1455</v>
       </c>
       <c r="G452" s="2" t="s">
         <v>15</v>
@@ -18039,7 +18039,7 @@
         <v>14</v>
       </c>
       <c r="F453" s="2">
-        <v>1847</v>
+        <v>2037</v>
       </c>
       <c r="G453" s="2" t="s">
         <v>15</v>
@@ -18071,7 +18071,7 @@
         <v>14</v>
       </c>
       <c r="F454" s="2">
-        <v>4071</v>
+        <v>4117</v>
       </c>
       <c r="G454" s="2" t="s">
         <v>15</v>
@@ -18103,7 +18103,7 @@
         <v>14</v>
       </c>
       <c r="F455" s="2">
-        <v>3007</v>
+        <v>866</v>
       </c>
       <c r="G455" s="2" t="s">
         <v>15</v>
@@ -18135,7 +18135,7 @@
         <v>14</v>
       </c>
       <c r="F456" s="2">
-        <v>3839</v>
+        <v>1543</v>
       </c>
       <c r="G456" s="2" t="s">
         <v>15</v>
@@ -18167,7 +18167,7 @@
         <v>14</v>
       </c>
       <c r="F457" s="2">
-        <v>3081</v>
+        <v>4740</v>
       </c>
       <c r="G457" s="2" t="s">
         <v>15</v>
@@ -18199,7 +18199,7 @@
         <v>14</v>
       </c>
       <c r="F458" s="2">
-        <v>4185</v>
+        <v>3691</v>
       </c>
       <c r="G458" s="2" t="s">
         <v>15</v>
@@ -18231,7 +18231,7 @@
         <v>14</v>
       </c>
       <c r="F459" s="2">
-        <v>1684</v>
+        <v>2319</v>
       </c>
       <c r="G459" s="2" t="s">
         <v>15</v>
@@ -18263,7 +18263,7 @@
         <v>14</v>
       </c>
       <c r="F460" s="2">
-        <v>3991</v>
+        <v>3559</v>
       </c>
       <c r="G460" s="2" t="s">
         <v>15</v>
@@ -18295,7 +18295,7 @@
         <v>14</v>
       </c>
       <c r="F461" s="2">
-        <v>3166</v>
+        <v>4066</v>
       </c>
       <c r="G461" s="2" t="s">
         <v>15</v>
@@ -18327,7 +18327,7 @@
         <v>14</v>
       </c>
       <c r="F462" s="2">
-        <v>2123</v>
+        <v>1124</v>
       </c>
       <c r="G462" s="2" t="s">
         <v>15</v>
@@ -18359,7 +18359,7 @@
         <v>14</v>
       </c>
       <c r="F463" s="2">
-        <v>1214</v>
+        <v>3755</v>
       </c>
       <c r="G463" s="2" t="s">
         <v>15</v>
@@ -18391,7 +18391,7 @@
         <v>14</v>
       </c>
       <c r="F464" s="2">
-        <v>3887</v>
+        <v>2214</v>
       </c>
       <c r="G464" s="2" t="s">
         <v>15</v>
@@ -18423,7 +18423,7 @@
         <v>14</v>
       </c>
       <c r="F465" s="2">
-        <v>1767</v>
+        <v>3316</v>
       </c>
       <c r="G465" s="2" t="s">
         <v>15</v>
@@ -18455,7 +18455,7 @@
         <v>14</v>
       </c>
       <c r="F466" s="2">
-        <v>3940</v>
+        <v>3822</v>
       </c>
       <c r="G466" s="2" t="s">
         <v>15</v>
@@ -18487,7 +18487,7 @@
         <v>14</v>
       </c>
       <c r="F467" s="2">
-        <v>2339</v>
+        <v>4759</v>
       </c>
       <c r="G467" s="2" t="s">
         <v>15</v>
@@ -18519,7 +18519,7 @@
         <v>14</v>
       </c>
       <c r="F468" s="2">
-        <v>3324</v>
+        <v>4491</v>
       </c>
       <c r="G468" s="2" t="s">
         <v>15</v>
@@ -18551,7 +18551,7 @@
         <v>14</v>
       </c>
       <c r="F469" s="2">
-        <v>1123</v>
+        <v>3244</v>
       </c>
       <c r="G469" s="2" t="s">
         <v>15</v>
@@ -18583,7 +18583,7 @@
         <v>14</v>
       </c>
       <c r="F470" s="2">
-        <v>2371</v>
+        <v>1088</v>
       </c>
       <c r="G470" s="2" t="s">
         <v>15</v>
@@ -18615,7 +18615,7 @@
         <v>14</v>
       </c>
       <c r="F471" s="2">
-        <v>2769</v>
+        <v>2200</v>
       </c>
       <c r="G471" s="2" t="s">
         <v>15</v>
@@ -18702,7 +18702,7 @@
         <v>14</v>
       </c>
       <c r="F2" s="2">
-        <v>2692</v>
+        <v>3236</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>15</v>
@@ -18734,7 +18734,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="2">
-        <v>4601</v>
+        <v>2390</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>15</v>
@@ -18766,7 +18766,7 @@
         <v>14</v>
       </c>
       <c r="F4" s="2">
-        <v>1356</v>
+        <v>1290</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
@@ -18798,7 +18798,7 @@
         <v>14</v>
       </c>
       <c r="F5" s="2">
-        <v>3387</v>
+        <v>2447</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
@@ -18830,7 +18830,7 @@
         <v>14</v>
       </c>
       <c r="F6" s="2">
-        <v>3286</v>
+        <v>2634</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -18862,7 +18862,7 @@
         <v>14</v>
       </c>
       <c r="F7" s="2">
-        <v>4231</v>
+        <v>4151</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -18894,7 +18894,7 @@
         <v>14</v>
       </c>
       <c r="F8" s="2">
-        <v>3350</v>
+        <v>3490</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -18926,7 +18926,7 @@
         <v>14</v>
       </c>
       <c r="F9" s="2">
-        <v>1973</v>
+        <v>1780</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -18958,7 +18958,7 @@
         <v>14</v>
       </c>
       <c r="F10" s="2">
-        <v>4613</v>
+        <v>2604</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
@@ -18990,7 +18990,7 @@
         <v>14</v>
       </c>
       <c r="F11" s="2">
-        <v>890</v>
+        <v>2651</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
@@ -19022,7 +19022,7 @@
         <v>14</v>
       </c>
       <c r="F12" s="2">
-        <v>2763</v>
+        <v>3166</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
@@ -19054,7 +19054,7 @@
         <v>14</v>
       </c>
       <c r="F13" s="2">
-        <v>2388</v>
+        <v>3430</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -19086,7 +19086,7 @@
         <v>14</v>
       </c>
       <c r="F14" s="2">
-        <v>3911</v>
+        <v>2399</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -19118,7 +19118,7 @@
         <v>14</v>
       </c>
       <c r="F15" s="2">
-        <v>1980</v>
+        <v>4216</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -19150,7 +19150,7 @@
         <v>14</v>
       </c>
       <c r="F16" s="2">
-        <v>1875</v>
+        <v>3401</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
@@ -19182,7 +19182,7 @@
         <v>14</v>
       </c>
       <c r="F17" s="2">
-        <v>2622</v>
+        <v>1180</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
@@ -19214,7 +19214,7 @@
         <v>14</v>
       </c>
       <c r="F18" s="2">
-        <v>2570</v>
+        <v>2413</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
@@ -19246,7 +19246,7 @@
         <v>14</v>
       </c>
       <c r="F19" s="2">
-        <v>3598</v>
+        <v>4102</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
@@ -19278,7 +19278,7 @@
         <v>14</v>
       </c>
       <c r="F20" s="2">
-        <v>3847</v>
+        <v>2171</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
@@ -19310,7 +19310,7 @@
         <v>14</v>
       </c>
       <c r="F21" s="2">
-        <v>4367</v>
+        <v>2909</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -19342,7 +19342,7 @@
         <v>14</v>
       </c>
       <c r="F22" s="2">
-        <v>1318</v>
+        <v>1555</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -19374,7 +19374,7 @@
         <v>14</v>
       </c>
       <c r="F23" s="2">
-        <v>1409</v>
+        <v>4424</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -19406,7 +19406,7 @@
         <v>14</v>
       </c>
       <c r="F24" s="2">
-        <v>1203</v>
+        <v>3598</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -19438,7 +19438,7 @@
         <v>14</v>
       </c>
       <c r="F25" s="2">
-        <v>3106</v>
+        <v>1832</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -19470,7 +19470,7 @@
         <v>14</v>
       </c>
       <c r="F26" s="2">
-        <v>1104</v>
+        <v>4454</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -19502,7 +19502,7 @@
         <v>14</v>
       </c>
       <c r="F27" s="2">
-        <v>1675</v>
+        <v>3734</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>15</v>
@@ -19534,7 +19534,7 @@
         <v>14</v>
       </c>
       <c r="F28" s="2">
-        <v>3595</v>
+        <v>2823</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>15</v>
@@ -19566,7 +19566,7 @@
         <v>14</v>
       </c>
       <c r="F29" s="2">
-        <v>2653</v>
+        <v>4784</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>15</v>
@@ -19598,7 +19598,7 @@
         <v>14</v>
       </c>
       <c r="F30" s="2">
-        <v>1579</v>
+        <v>3944</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>15</v>
@@ -19630,7 +19630,7 @@
         <v>14</v>
       </c>
       <c r="F31" s="2">
-        <v>4269</v>
+        <v>3950</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>15</v>
@@ -19662,7 +19662,7 @@
         <v>14</v>
       </c>
       <c r="F32" s="2">
-        <v>1142</v>
+        <v>3963</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>15</v>
@@ -19694,7 +19694,7 @@
         <v>14</v>
       </c>
       <c r="F33" s="2">
-        <v>1938</v>
+        <v>1782</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>15</v>
@@ -19726,7 +19726,7 @@
         <v>14</v>
       </c>
       <c r="F34" s="2">
-        <v>2327</v>
+        <v>1097</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>15</v>
@@ -19758,7 +19758,7 @@
         <v>14</v>
       </c>
       <c r="F35" s="2">
-        <v>3693</v>
+        <v>2200</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>15</v>
@@ -19790,7 +19790,7 @@
         <v>14</v>
       </c>
       <c r="F36" s="2">
-        <v>4594</v>
+        <v>3148</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>15</v>
@@ -19822,7 +19822,7 @@
         <v>14</v>
       </c>
       <c r="F37" s="2">
-        <v>3449</v>
+        <v>1393</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>15</v>
@@ -19854,7 +19854,7 @@
         <v>14</v>
       </c>
       <c r="F38" s="2">
-        <v>2062</v>
+        <v>2720</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>15</v>
@@ -19886,7 +19886,7 @@
         <v>14</v>
       </c>
       <c r="F39" s="2">
-        <v>4573</v>
+        <v>1019</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>15</v>
@@ -19918,7 +19918,7 @@
         <v>14</v>
       </c>
       <c r="F40" s="2">
-        <v>1004</v>
+        <v>1657</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>15</v>
@@ -19950,7 +19950,7 @@
         <v>14</v>
       </c>
       <c r="F41" s="2">
-        <v>4334</v>
+        <v>2664</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>15</v>
@@ -19982,7 +19982,7 @@
         <v>14</v>
       </c>
       <c r="F42" s="2">
-        <v>2407</v>
+        <v>4219</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>15</v>
@@ -20014,7 +20014,7 @@
         <v>14</v>
       </c>
       <c r="F43" s="2">
-        <v>2700</v>
+        <v>4725</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>15</v>
@@ -20046,7 +20046,7 @@
         <v>14</v>
       </c>
       <c r="F44" s="2">
-        <v>2453</v>
+        <v>2732</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>15</v>
@@ -20078,7 +20078,7 @@
         <v>14</v>
       </c>
       <c r="F45" s="2">
-        <v>1727</v>
+        <v>2402</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>15</v>
@@ -20110,7 +20110,7 @@
         <v>14</v>
       </c>
       <c r="F46" s="2">
-        <v>3373</v>
+        <v>4693</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>15</v>
@@ -20142,7 +20142,7 @@
         <v>14</v>
       </c>
       <c r="F47" s="2">
-        <v>3117</v>
+        <v>3033</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>15</v>
@@ -20174,7 +20174,7 @@
         <v>14</v>
       </c>
       <c r="F48" s="2">
-        <v>2431</v>
+        <v>3664</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>15</v>
@@ -20206,7 +20206,7 @@
         <v>14</v>
       </c>
       <c r="F49" s="2">
-        <v>2730</v>
+        <v>2465</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>15</v>
@@ -20238,7 +20238,7 @@
         <v>14</v>
       </c>
       <c r="F50" s="2">
-        <v>1464</v>
+        <v>4670</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>15</v>
@@ -20270,7 +20270,7 @@
         <v>14</v>
       </c>
       <c r="F51" s="2">
-        <v>4707</v>
+        <v>3343</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>15</v>
@@ -20302,7 +20302,7 @@
         <v>14</v>
       </c>
       <c r="F52" s="2">
-        <v>2690</v>
+        <v>2369</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>15</v>
@@ -20334,7 +20334,7 @@
         <v>14</v>
       </c>
       <c r="F53" s="2">
-        <v>3410</v>
+        <v>2569</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>15</v>
@@ -20366,7 +20366,7 @@
         <v>14</v>
       </c>
       <c r="F54" s="2">
-        <v>2755</v>
+        <v>4740</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>15</v>
@@ -20398,7 +20398,7 @@
         <v>14</v>
       </c>
       <c r="F55" s="2">
-        <v>4281</v>
+        <v>4393</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>15</v>
@@ -20430,7 +20430,7 @@
         <v>14</v>
       </c>
       <c r="F56" s="2">
-        <v>2167</v>
+        <v>3464</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>15</v>
@@ -20462,7 +20462,7 @@
         <v>14</v>
       </c>
       <c r="F57" s="2">
-        <v>1805</v>
+        <v>3370</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>15</v>
@@ -20494,7 +20494,7 @@
         <v>14</v>
       </c>
       <c r="F58" s="2">
-        <v>1065</v>
+        <v>1863</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>15</v>
@@ -20526,7 +20526,7 @@
         <v>14</v>
       </c>
       <c r="F59" s="2">
-        <v>1165</v>
+        <v>2116</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>15</v>
@@ -20558,7 +20558,7 @@
         <v>14</v>
       </c>
       <c r="F60" s="2">
-        <v>2916</v>
+        <v>3820</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>15</v>
@@ -20590,7 +20590,7 @@
         <v>14</v>
       </c>
       <c r="F61" s="2">
-        <v>3945</v>
+        <v>1146</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>15</v>
@@ -20622,7 +20622,7 @@
         <v>14</v>
       </c>
       <c r="F62" s="2">
-        <v>1074</v>
+        <v>4759</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>15</v>
@@ -20654,7 +20654,7 @@
         <v>14</v>
       </c>
       <c r="F63" s="2">
-        <v>2009</v>
+        <v>3694</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>15</v>
@@ -20686,7 +20686,7 @@
         <v>14</v>
       </c>
       <c r="F64" s="2">
-        <v>1022</v>
+        <v>844</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>15</v>
@@ -20718,7 +20718,7 @@
         <v>14</v>
       </c>
       <c r="F65" s="2">
-        <v>3274</v>
+        <v>1944</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>15</v>
@@ -20750,7 +20750,7 @@
         <v>14</v>
       </c>
       <c r="F66" s="2">
-        <v>4372</v>
+        <v>2716</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>15</v>
@@ -20782,7 +20782,7 @@
         <v>14</v>
       </c>
       <c r="F67" s="2">
-        <v>3809</v>
+        <v>867</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>15</v>
@@ -20814,7 +20814,7 @@
         <v>14</v>
       </c>
       <c r="F68" s="2">
-        <v>981</v>
+        <v>1814</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>15</v>
@@ -20846,7 +20846,7 @@
         <v>14</v>
       </c>
       <c r="F69" s="2">
-        <v>3047</v>
+        <v>3832</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>15</v>
@@ -20878,7 +20878,7 @@
         <v>14</v>
       </c>
       <c r="F70" s="2">
-        <v>1912</v>
+        <v>2673</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>15</v>
@@ -20910,7 +20910,7 @@
         <v>14</v>
       </c>
       <c r="F71" s="2">
-        <v>2100</v>
+        <v>2784</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>15</v>
@@ -20942,7 +20942,7 @@
         <v>14</v>
       </c>
       <c r="F72" s="2">
-        <v>4709</v>
+        <v>1651</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>15</v>
@@ -20974,7 +20974,7 @@
         <v>14</v>
       </c>
       <c r="F73" s="2">
-        <v>1006</v>
+        <v>2179</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>15</v>
@@ -21006,7 +21006,7 @@
         <v>14</v>
       </c>
       <c r="F74" s="2">
-        <v>3823</v>
+        <v>4617</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>15</v>
@@ -21038,7 +21038,7 @@
         <v>14</v>
       </c>
       <c r="F75" s="2">
-        <v>3679</v>
+        <v>2085</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>15</v>
@@ -21070,7 +21070,7 @@
         <v>14</v>
       </c>
       <c r="F76" s="2">
-        <v>1003</v>
+        <v>3037</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>15</v>
@@ -21102,7 +21102,7 @@
         <v>14</v>
       </c>
       <c r="F77" s="2">
-        <v>4074</v>
+        <v>1990</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>15</v>
@@ -21134,7 +21134,7 @@
         <v>14</v>
       </c>
       <c r="F78" s="2">
-        <v>3906</v>
+        <v>3375</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>15</v>
@@ -21166,7 +21166,7 @@
         <v>14</v>
       </c>
       <c r="F79" s="2">
-        <v>2867</v>
+        <v>1294</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>15</v>
@@ -21198,7 +21198,7 @@
         <v>14</v>
       </c>
       <c r="F80" s="2">
-        <v>3086</v>
+        <v>3849</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>15</v>
@@ -21230,7 +21230,7 @@
         <v>14</v>
       </c>
       <c r="F81" s="2">
-        <v>3610</v>
+        <v>4284</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>15</v>
@@ -21262,7 +21262,7 @@
         <v>14</v>
       </c>
       <c r="F82" s="2">
-        <v>1384</v>
+        <v>2838</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>15</v>
@@ -21294,7 +21294,7 @@
         <v>14</v>
       </c>
       <c r="F83" s="2">
-        <v>4413</v>
+        <v>2512</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>15</v>
@@ -21326,7 +21326,7 @@
         <v>14</v>
       </c>
       <c r="F84" s="2">
-        <v>4273</v>
+        <v>4195</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>15</v>
@@ -21358,7 +21358,7 @@
         <v>14</v>
       </c>
       <c r="F85" s="2">
-        <v>4506</v>
+        <v>3131</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>15</v>
@@ -21390,7 +21390,7 @@
         <v>14</v>
       </c>
       <c r="F86" s="2">
-        <v>2396</v>
+        <v>1303</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>15</v>
@@ -21422,7 +21422,7 @@
         <v>14</v>
       </c>
       <c r="F87" s="2">
-        <v>1747</v>
+        <v>4743</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>15</v>
@@ -21454,7 +21454,7 @@
         <v>14</v>
       </c>
       <c r="F88" s="2">
-        <v>1621</v>
+        <v>2096</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>15</v>
@@ -21486,7 +21486,7 @@
         <v>14</v>
       </c>
       <c r="F89" s="2">
-        <v>1248</v>
+        <v>1067</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>15</v>
@@ -21518,7 +21518,7 @@
         <v>14</v>
       </c>
       <c r="F90" s="2">
-        <v>3114</v>
+        <v>2068</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>15</v>
@@ -21550,7 +21550,7 @@
         <v>14</v>
       </c>
       <c r="F91" s="2">
-        <v>2273</v>
+        <v>3691</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>15</v>
@@ -21582,7 +21582,7 @@
         <v>14</v>
       </c>
       <c r="F92" s="2">
-        <v>3639</v>
+        <v>4399</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>15</v>
@@ -21614,7 +21614,7 @@
         <v>14</v>
       </c>
       <c r="F93" s="2">
-        <v>2151</v>
+        <v>4601</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>15</v>
@@ -21646,7 +21646,7 @@
         <v>14</v>
       </c>
       <c r="F94" s="2">
-        <v>1789</v>
+        <v>3681</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>15</v>
@@ -21678,7 +21678,7 @@
         <v>14</v>
       </c>
       <c r="F95" s="2">
-        <v>3542</v>
+        <v>4175</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>15</v>
@@ -21710,7 +21710,7 @@
         <v>14</v>
       </c>
       <c r="F96" s="2">
-        <v>3907</v>
+        <v>1519</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>15</v>
@@ -21742,7 +21742,7 @@
         <v>14</v>
       </c>
       <c r="F97" s="2">
-        <v>1700</v>
+        <v>2362</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>15</v>
@@ -21774,7 +21774,7 @@
         <v>14</v>
       </c>
       <c r="F98" s="2">
-        <v>3327</v>
+        <v>2818</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>15</v>
@@ -21806,7 +21806,7 @@
         <v>14</v>
       </c>
       <c r="F99" s="2">
-        <v>2620</v>
+        <v>1398</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>15</v>
@@ -21838,7 +21838,7 @@
         <v>14</v>
       </c>
       <c r="F100" s="2">
-        <v>858</v>
+        <v>4780</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>15</v>
@@ -21870,7 +21870,7 @@
         <v>14</v>
       </c>
       <c r="F101" s="2">
-        <v>1514</v>
+        <v>4460</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>15</v>
@@ -21902,7 +21902,7 @@
         <v>14</v>
       </c>
       <c r="F102" s="2">
-        <v>1368</v>
+        <v>4603</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>15</v>
@@ -21934,7 +21934,7 @@
         <v>14</v>
       </c>
       <c r="F103" s="2">
-        <v>1934</v>
+        <v>2372</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>15</v>
@@ -21966,7 +21966,7 @@
         <v>14</v>
       </c>
       <c r="F104" s="2">
-        <v>3904</v>
+        <v>2911</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>15</v>
@@ -21998,7 +21998,7 @@
         <v>14</v>
       </c>
       <c r="F105" s="2">
-        <v>4213</v>
+        <v>3770</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>15</v>
@@ -22030,7 +22030,7 @@
         <v>14</v>
       </c>
       <c r="F106" s="2">
-        <v>2350</v>
+        <v>2369</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>15</v>
@@ -22062,7 +22062,7 @@
         <v>14</v>
       </c>
       <c r="F107" s="2">
-        <v>2791</v>
+        <v>1208</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>15</v>
@@ -22094,7 +22094,7 @@
         <v>14</v>
       </c>
       <c r="F108" s="2">
-        <v>3925</v>
+        <v>2582</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>15</v>
@@ -22126,7 +22126,7 @@
         <v>14</v>
       </c>
       <c r="F109" s="2">
-        <v>2431</v>
+        <v>3267</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>15</v>
@@ -22158,7 +22158,7 @@
         <v>14</v>
       </c>
       <c r="F110" s="2">
-        <v>4053</v>
+        <v>3069</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>15</v>
@@ -22190,7 +22190,7 @@
         <v>14</v>
       </c>
       <c r="F111" s="2">
-        <v>1359</v>
+        <v>1074</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>15</v>
@@ -22222,7 +22222,7 @@
         <v>14</v>
       </c>
       <c r="F112" s="2">
-        <v>2191</v>
+        <v>1364</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>15</v>
@@ -22254,7 +22254,7 @@
         <v>14</v>
       </c>
       <c r="F113" s="2">
-        <v>3904</v>
+        <v>2563</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>15</v>
@@ -22286,7 +22286,7 @@
         <v>14</v>
       </c>
       <c r="F114" s="2">
-        <v>4467</v>
+        <v>2698</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>15</v>
@@ -22318,7 +22318,7 @@
         <v>14</v>
       </c>
       <c r="F115" s="2">
-        <v>3973</v>
+        <v>1391</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>15</v>
@@ -22350,7 +22350,7 @@
         <v>14</v>
       </c>
       <c r="F116" s="2">
-        <v>2106</v>
+        <v>4641</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>15</v>
@@ -22382,7 +22382,7 @@
         <v>14</v>
       </c>
       <c r="F117" s="2">
-        <v>1067</v>
+        <v>4420</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>15</v>
@@ -22414,7 +22414,7 @@
         <v>14</v>
       </c>
       <c r="F118" s="2">
-        <v>4544</v>
+        <v>1535</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>15</v>
@@ -22446,7 +22446,7 @@
         <v>14</v>
       </c>
       <c r="F119" s="2">
-        <v>4179</v>
+        <v>3600</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>15</v>
@@ -22478,7 +22478,7 @@
         <v>14</v>
       </c>
       <c r="F120" s="2">
-        <v>1997</v>
+        <v>1416</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>15</v>
@@ -22510,7 +22510,7 @@
         <v>14</v>
       </c>
       <c r="F121" s="2">
-        <v>3116</v>
+        <v>1437</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>15</v>
@@ -22542,7 +22542,7 @@
         <v>14</v>
       </c>
       <c r="F122" s="2">
-        <v>4615</v>
+        <v>4612</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>15</v>
@@ -22574,7 +22574,7 @@
         <v>14</v>
       </c>
       <c r="F123" s="2">
-        <v>2361</v>
+        <v>2057</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>15</v>
@@ -22606,7 +22606,7 @@
         <v>14</v>
       </c>
       <c r="F124" s="2">
-        <v>3614</v>
+        <v>1616</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>15</v>
@@ -22638,7 +22638,7 @@
         <v>14</v>
       </c>
       <c r="F125" s="2">
-        <v>1510</v>
+        <v>2545</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>15</v>
@@ -22670,7 +22670,7 @@
         <v>14</v>
       </c>
       <c r="F126" s="2">
-        <v>3429</v>
+        <v>2754</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>15</v>
@@ -22702,7 +22702,7 @@
         <v>14</v>
       </c>
       <c r="F127" s="2">
-        <v>2191</v>
+        <v>4187</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>15</v>
@@ -22734,7 +22734,7 @@
         <v>14</v>
       </c>
       <c r="F128" s="2">
-        <v>1336</v>
+        <v>1658</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>15</v>
@@ -22766,7 +22766,7 @@
         <v>14</v>
       </c>
       <c r="F129" s="2">
-        <v>4385</v>
+        <v>1703</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>15</v>
@@ -22798,7 +22798,7 @@
         <v>14</v>
       </c>
       <c r="F130" s="2">
-        <v>1116</v>
+        <v>1639</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>15</v>
@@ -22830,7 +22830,7 @@
         <v>14</v>
       </c>
       <c r="F131" s="2">
-        <v>1343</v>
+        <v>3157</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>15</v>
@@ -22862,7 +22862,7 @@
         <v>14</v>
       </c>
       <c r="F132" s="2">
-        <v>2388</v>
+        <v>3685</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>15</v>
@@ -22894,7 +22894,7 @@
         <v>14</v>
       </c>
       <c r="F133" s="2">
-        <v>1687</v>
+        <v>3325</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>15</v>
@@ -22926,7 +22926,7 @@
         <v>14</v>
       </c>
       <c r="F134" s="2">
-        <v>1916</v>
+        <v>1491</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>15</v>
@@ -22958,7 +22958,7 @@
         <v>14</v>
       </c>
       <c r="F135" s="2">
-        <v>1045</v>
+        <v>2283</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>15</v>
@@ -22990,7 +22990,7 @@
         <v>14</v>
       </c>
       <c r="F136" s="2">
-        <v>1834</v>
+        <v>1028</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>15</v>
@@ -23022,7 +23022,7 @@
         <v>14</v>
       </c>
       <c r="F137" s="2">
-        <v>4626</v>
+        <v>2346</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>15</v>
@@ -23054,7 +23054,7 @@
         <v>14</v>
       </c>
       <c r="F138" s="2">
-        <v>3829</v>
+        <v>3119</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>15</v>
@@ -23086,7 +23086,7 @@
         <v>14</v>
       </c>
       <c r="F139" s="2">
-        <v>3782</v>
+        <v>3742</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>15</v>
@@ -23118,7 +23118,7 @@
         <v>14</v>
       </c>
       <c r="F140" s="2">
-        <v>2941</v>
+        <v>4486</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>15</v>
@@ -23150,7 +23150,7 @@
         <v>14</v>
       </c>
       <c r="F141" s="2">
-        <v>4337</v>
+        <v>4591</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>15</v>
@@ -23182,7 +23182,7 @@
         <v>14</v>
       </c>
       <c r="F142" s="2">
-        <v>4740</v>
+        <v>2170</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>15</v>
@@ -23214,7 +23214,7 @@
         <v>14</v>
       </c>
       <c r="F143" s="2">
-        <v>1650</v>
+        <v>1628</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>15</v>
@@ -23246,7 +23246,7 @@
         <v>14</v>
       </c>
       <c r="F144" s="2">
-        <v>1862</v>
+        <v>3752</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>15</v>
@@ -23278,7 +23278,7 @@
         <v>14</v>
       </c>
       <c r="F145" s="2">
-        <v>4158</v>
+        <v>1819</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>15</v>
@@ -23310,7 +23310,7 @@
         <v>14</v>
       </c>
       <c r="F146" s="2">
-        <v>2614</v>
+        <v>2297</v>
       </c>
       <c r="G146" s="2" t="s">
         <v>15</v>
@@ -23342,7 +23342,7 @@
         <v>14</v>
       </c>
       <c r="F147" s="2">
-        <v>3863</v>
+        <v>1419</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>15</v>
@@ -23374,7 +23374,7 @@
         <v>14</v>
       </c>
       <c r="F148" s="2">
-        <v>4648</v>
+        <v>1419</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>15</v>
@@ -23406,7 +23406,7 @@
         <v>14</v>
       </c>
       <c r="F149" s="2">
-        <v>3974</v>
+        <v>3850</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>15</v>
@@ -23438,7 +23438,7 @@
         <v>14</v>
       </c>
       <c r="F150" s="2">
-        <v>3559</v>
+        <v>4225</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>15</v>
@@ -23470,7 +23470,7 @@
         <v>14</v>
       </c>
       <c r="F151" s="2">
-        <v>3201</v>
+        <v>1628</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>15</v>
@@ -23502,7 +23502,7 @@
         <v>14</v>
       </c>
       <c r="F152" s="2">
-        <v>4316</v>
+        <v>2305</v>
       </c>
       <c r="G152" s="2" t="s">
         <v>15</v>
@@ -23534,7 +23534,7 @@
         <v>14</v>
       </c>
       <c r="F153" s="2">
-        <v>2766</v>
+        <v>2293</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>15</v>
@@ -23566,7 +23566,7 @@
         <v>14</v>
       </c>
       <c r="F154" s="2">
-        <v>4419</v>
+        <v>4491</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>15</v>
@@ -23598,7 +23598,7 @@
         <v>14</v>
       </c>
       <c r="F155" s="2">
-        <v>1699</v>
+        <v>1082</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>15</v>
@@ -23630,7 +23630,7 @@
         <v>14</v>
       </c>
       <c r="F156" s="2">
-        <v>4777</v>
+        <v>4596</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>15</v>
@@ -23662,7 +23662,7 @@
         <v>14</v>
       </c>
       <c r="F157" s="2">
-        <v>3250</v>
+        <v>1814</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>15</v>
@@ -23694,7 +23694,7 @@
         <v>14</v>
       </c>
       <c r="F158" s="2">
-        <v>4464</v>
+        <v>1428</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>15</v>
@@ -23726,7 +23726,7 @@
         <v>14</v>
       </c>
       <c r="F159" s="2">
-        <v>1546</v>
+        <v>4172</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>15</v>
@@ -23758,7 +23758,7 @@
         <v>14</v>
       </c>
       <c r="F160" s="2">
-        <v>3618</v>
+        <v>3548</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>15</v>
@@ -23790,7 +23790,7 @@
         <v>14</v>
       </c>
       <c r="F161" s="2">
-        <v>1266</v>
+        <v>1339</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>15</v>
@@ -23822,7 +23822,7 @@
         <v>14</v>
       </c>
       <c r="F162" s="2">
-        <v>1759</v>
+        <v>3106</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>15</v>
@@ -23854,7 +23854,7 @@
         <v>14</v>
       </c>
       <c r="F163" s="2">
-        <v>2375</v>
+        <v>863</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>15</v>
@@ -23886,7 +23886,7 @@
         <v>14</v>
       </c>
       <c r="F164" s="2">
-        <v>1108</v>
+        <v>3795</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>15</v>
@@ -23918,7 +23918,7 @@
         <v>14</v>
       </c>
       <c r="F165" s="2">
-        <v>2463</v>
+        <v>3434</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>15</v>
@@ -23950,7 +23950,7 @@
         <v>14</v>
       </c>
       <c r="F166" s="2">
-        <v>3730</v>
+        <v>4229</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>15</v>
@@ -23982,7 +23982,7 @@
         <v>14</v>
       </c>
       <c r="F167" s="2">
-        <v>3596</v>
+        <v>2856</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>15</v>
@@ -24014,7 +24014,7 @@
         <v>14</v>
       </c>
       <c r="F168" s="2">
-        <v>4321</v>
+        <v>3959</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>15</v>
@@ -24046,7 +24046,7 @@
         <v>14</v>
       </c>
       <c r="F169" s="2">
-        <v>4161</v>
+        <v>2814</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>15</v>
@@ -24078,7 +24078,7 @@
         <v>14</v>
       </c>
       <c r="F170" s="2">
-        <v>3239</v>
+        <v>3407</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>15</v>
@@ -24110,7 +24110,7 @@
         <v>14</v>
       </c>
       <c r="F171" s="2">
-        <v>3517</v>
+        <v>1464</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>15</v>
@@ -24142,7 +24142,7 @@
         <v>14</v>
       </c>
       <c r="F172" s="2">
-        <v>2872</v>
+        <v>4551</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>15</v>
@@ -24174,7 +24174,7 @@
         <v>14</v>
       </c>
       <c r="F173" s="2">
-        <v>1947</v>
+        <v>1316</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>15</v>
@@ -24206,7 +24206,7 @@
         <v>14</v>
       </c>
       <c r="F174" s="2">
-        <v>3543</v>
+        <v>3808</v>
       </c>
       <c r="G174" s="2" t="s">
         <v>15</v>
@@ -24238,7 +24238,7 @@
         <v>14</v>
       </c>
       <c r="F175" s="2">
-        <v>1800</v>
+        <v>2115</v>
       </c>
       <c r="G175" s="2" t="s">
         <v>15</v>
@@ -24270,7 +24270,7 @@
         <v>14</v>
       </c>
       <c r="F176" s="2">
-        <v>4725</v>
+        <v>1113</v>
       </c>
       <c r="G176" s="2" t="s">
         <v>15</v>
@@ -24302,7 +24302,7 @@
         <v>14</v>
       </c>
       <c r="F177" s="2">
-        <v>2567</v>
+        <v>2158</v>
       </c>
       <c r="G177" s="2" t="s">
         <v>15</v>
@@ -24334,7 +24334,7 @@
         <v>14</v>
       </c>
       <c r="F178" s="2">
-        <v>3782</v>
+        <v>4664</v>
       </c>
       <c r="G178" s="2" t="s">
         <v>15</v>
@@ -24366,7 +24366,7 @@
         <v>14</v>
       </c>
       <c r="F179" s="2">
-        <v>3176</v>
+        <v>941</v>
       </c>
       <c r="G179" s="2" t="s">
         <v>15</v>
@@ -24398,7 +24398,7 @@
         <v>14</v>
       </c>
       <c r="F180" s="2">
-        <v>3771</v>
+        <v>816</v>
       </c>
       <c r="G180" s="2" t="s">
         <v>15</v>
@@ -24430,7 +24430,7 @@
         <v>14</v>
       </c>
       <c r="F181" s="2">
-        <v>2593</v>
+        <v>4545</v>
       </c>
       <c r="G181" s="2" t="s">
         <v>15</v>
@@ -24462,7 +24462,7 @@
         <v>14</v>
       </c>
       <c r="F182" s="2">
-        <v>2745</v>
+        <v>3551</v>
       </c>
       <c r="G182" s="2" t="s">
         <v>15</v>
@@ -24494,7 +24494,7 @@
         <v>14</v>
       </c>
       <c r="F183" s="2">
-        <v>1436</v>
+        <v>4786</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>15</v>
@@ -24526,7 +24526,7 @@
         <v>14</v>
       </c>
       <c r="F184" s="2">
-        <v>3323</v>
+        <v>2260</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>15</v>
@@ -24558,7 +24558,7 @@
         <v>14</v>
       </c>
       <c r="F185" s="2">
-        <v>3734</v>
+        <v>3813</v>
       </c>
       <c r="G185" s="2" t="s">
         <v>15</v>
@@ -24590,7 +24590,7 @@
         <v>14</v>
       </c>
       <c r="F186" s="2">
-        <v>3845</v>
+        <v>2905</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>15</v>
@@ -24622,7 +24622,7 @@
         <v>14</v>
       </c>
       <c r="F187" s="2">
-        <v>4516</v>
+        <v>1535</v>
       </c>
       <c r="G187" s="2" t="s">
         <v>15</v>
@@ -24654,7 +24654,7 @@
         <v>14</v>
       </c>
       <c r="F188" s="2">
-        <v>1023</v>
+        <v>1801</v>
       </c>
       <c r="G188" s="2" t="s">
         <v>15</v>
@@ -24686,7 +24686,7 @@
         <v>14</v>
       </c>
       <c r="F189" s="2">
-        <v>3499</v>
+        <v>3161</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>15</v>
@@ -24718,7 +24718,7 @@
         <v>14</v>
       </c>
       <c r="F190" s="2">
-        <v>1543</v>
+        <v>2613</v>
       </c>
       <c r="G190" s="2" t="s">
         <v>15</v>
@@ -24750,7 +24750,7 @@
         <v>14</v>
       </c>
       <c r="F191" s="2">
-        <v>1925</v>
+        <v>1688</v>
       </c>
       <c r="G191" s="2" t="s">
         <v>15</v>
@@ -24782,7 +24782,7 @@
         <v>14</v>
       </c>
       <c r="F192" s="2">
-        <v>1174</v>
+        <v>3561</v>
       </c>
       <c r="G192" s="2" t="s">
         <v>15</v>
@@ -24814,7 +24814,7 @@
         <v>14</v>
       </c>
       <c r="F193" s="2">
-        <v>2680</v>
+        <v>1151</v>
       </c>
       <c r="G193" s="2" t="s">
         <v>15</v>
@@ -24846,7 +24846,7 @@
         <v>14</v>
       </c>
       <c r="F194" s="2">
-        <v>854</v>
+        <v>2144</v>
       </c>
       <c r="G194" s="2" t="s">
         <v>15</v>
@@ -24878,7 +24878,7 @@
         <v>14</v>
       </c>
       <c r="F195" s="2">
-        <v>3663</v>
+        <v>3735</v>
       </c>
       <c r="G195" s="2" t="s">
         <v>15</v>
@@ -24910,7 +24910,7 @@
         <v>14</v>
       </c>
       <c r="F196" s="2">
-        <v>1324</v>
+        <v>2046</v>
       </c>
       <c r="G196" s="2" t="s">
         <v>15</v>
@@ -24942,7 +24942,7 @@
         <v>14</v>
       </c>
       <c r="F197" s="2">
-        <v>2513</v>
+        <v>4527</v>
       </c>
       <c r="G197" s="2" t="s">
         <v>15</v>
@@ -24974,7 +24974,7 @@
         <v>14</v>
       </c>
       <c r="F198" s="2">
-        <v>3722</v>
+        <v>1832</v>
       </c>
       <c r="G198" s="2" t="s">
         <v>15</v>
@@ -25006,7 +25006,7 @@
         <v>14</v>
       </c>
       <c r="F199" s="2">
-        <v>3878</v>
+        <v>2561</v>
       </c>
       <c r="G199" s="2" t="s">
         <v>15</v>
@@ -25038,7 +25038,7 @@
         <v>14</v>
       </c>
       <c r="F200" s="2">
-        <v>1939</v>
+        <v>4254</v>
       </c>
       <c r="G200" s="2" t="s">
         <v>15</v>
@@ -25070,7 +25070,7 @@
         <v>14</v>
       </c>
       <c r="F201" s="2">
-        <v>4494</v>
+        <v>2891</v>
       </c>
       <c r="G201" s="2" t="s">
         <v>15</v>
@@ -25102,7 +25102,7 @@
         <v>14</v>
       </c>
       <c r="F202" s="2">
-        <v>4122</v>
+        <v>2518</v>
       </c>
       <c r="G202" s="2" t="s">
         <v>15</v>
@@ -25134,7 +25134,7 @@
         <v>14</v>
       </c>
       <c r="F203" s="2">
-        <v>3935</v>
+        <v>2014</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>15</v>
@@ -25166,7 +25166,7 @@
         <v>14</v>
       </c>
       <c r="F204" s="2">
-        <v>4672</v>
+        <v>3477</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>15</v>
@@ -25198,7 +25198,7 @@
         <v>14</v>
       </c>
       <c r="F205" s="2">
-        <v>3684</v>
+        <v>2222</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>15</v>
@@ -25230,7 +25230,7 @@
         <v>14</v>
       </c>
       <c r="F206" s="2">
-        <v>1774</v>
+        <v>4716</v>
       </c>
       <c r="G206" s="2" t="s">
         <v>15</v>
@@ -25262,7 +25262,7 @@
         <v>14</v>
       </c>
       <c r="F207" s="2">
-        <v>3742</v>
+        <v>1067</v>
       </c>
       <c r="G207" s="2" t="s">
         <v>15</v>
@@ -25294,7 +25294,7 @@
         <v>14</v>
       </c>
       <c r="F208" s="2">
-        <v>1896</v>
+        <v>1011</v>
       </c>
       <c r="G208" s="2" t="s">
         <v>15</v>
@@ -25326,7 +25326,7 @@
         <v>14</v>
       </c>
       <c r="F209" s="2">
-        <v>2196</v>
+        <v>3641</v>
       </c>
       <c r="G209" s="2" t="s">
         <v>15</v>
@@ -25358,7 +25358,7 @@
         <v>14</v>
       </c>
       <c r="F210" s="2">
-        <v>1002</v>
+        <v>4275</v>
       </c>
       <c r="G210" s="2" t="s">
         <v>15</v>
@@ -25390,7 +25390,7 @@
         <v>14</v>
       </c>
       <c r="F211" s="2">
-        <v>2066</v>
+        <v>4474</v>
       </c>
       <c r="G211" s="2" t="s">
         <v>15</v>
@@ -25422,7 +25422,7 @@
         <v>14</v>
       </c>
       <c r="F212" s="2">
-        <v>2476</v>
+        <v>2731</v>
       </c>
       <c r="G212" s="2" t="s">
         <v>15</v>
@@ -25454,7 +25454,7 @@
         <v>14</v>
       </c>
       <c r="F213" s="2">
-        <v>3351</v>
+        <v>2898</v>
       </c>
       <c r="G213" s="2" t="s">
         <v>15</v>
@@ -25486,7 +25486,7 @@
         <v>14</v>
       </c>
       <c r="F214" s="2">
-        <v>869</v>
+        <v>1365</v>
       </c>
       <c r="G214" s="2" t="s">
         <v>15</v>
@@ -25518,7 +25518,7 @@
         <v>14</v>
       </c>
       <c r="F215" s="2">
-        <v>3910</v>
+        <v>1256</v>
       </c>
       <c r="G215" s="2" t="s">
         <v>15</v>
@@ -25550,7 +25550,7 @@
         <v>14</v>
       </c>
       <c r="F216" s="2">
-        <v>3502</v>
+        <v>2086</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>15</v>
@@ -25582,7 +25582,7 @@
         <v>14</v>
       </c>
       <c r="F217" s="2">
-        <v>4506</v>
+        <v>2012</v>
       </c>
       <c r="G217" s="2" t="s">
         <v>15</v>
@@ -25614,7 +25614,7 @@
         <v>14</v>
       </c>
       <c r="F218" s="2">
-        <v>4200</v>
+        <v>1206</v>
       </c>
       <c r="G218" s="2" t="s">
         <v>15</v>
@@ -25646,7 +25646,7 @@
         <v>14</v>
       </c>
       <c r="F219" s="2">
-        <v>1805</v>
+        <v>3803</v>
       </c>
       <c r="G219" s="2" t="s">
         <v>15</v>
@@ -25678,7 +25678,7 @@
         <v>14</v>
       </c>
       <c r="F220" s="2">
-        <v>1647</v>
+        <v>1975</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>15</v>
@@ -25710,7 +25710,7 @@
         <v>14</v>
       </c>
       <c r="F221" s="2">
-        <v>1148</v>
+        <v>2488</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>15</v>
@@ -25742,7 +25742,7 @@
         <v>14</v>
       </c>
       <c r="F222" s="2">
-        <v>1008</v>
+        <v>895</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>15</v>
@@ -25774,7 +25774,7 @@
         <v>14</v>
       </c>
       <c r="F223" s="2">
-        <v>4272</v>
+        <v>3935</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>15</v>
@@ -25806,7 +25806,7 @@
         <v>14</v>
       </c>
       <c r="F224" s="2">
-        <v>931</v>
+        <v>1986</v>
       </c>
       <c r="G224" s="2" t="s">
         <v>15</v>
@@ -25838,7 +25838,7 @@
         <v>14</v>
       </c>
       <c r="F225" s="2">
-        <v>4249</v>
+        <v>1999</v>
       </c>
       <c r="G225" s="2" t="s">
         <v>15</v>
@@ -25870,7 +25870,7 @@
         <v>14</v>
       </c>
       <c r="F226" s="2">
-        <v>1584</v>
+        <v>3901</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>15</v>
@@ -25902,7 +25902,7 @@
         <v>14</v>
       </c>
       <c r="F227" s="2">
-        <v>4569</v>
+        <v>2347</v>
       </c>
       <c r="G227" s="2" t="s">
         <v>15</v>
@@ -25934,7 +25934,7 @@
         <v>14</v>
       </c>
       <c r="F228" s="2">
-        <v>2409</v>
+        <v>4503</v>
       </c>
       <c r="G228" s="2" t="s">
         <v>15</v>
@@ -25966,7 +25966,7 @@
         <v>14</v>
       </c>
       <c r="F229" s="2">
-        <v>2840</v>
+        <v>3126</v>
       </c>
       <c r="G229" s="2" t="s">
         <v>15</v>
@@ -25998,7 +25998,7 @@
         <v>14</v>
       </c>
       <c r="F230" s="2">
-        <v>1109</v>
+        <v>4663</v>
       </c>
       <c r="G230" s="2" t="s">
         <v>15</v>
@@ -26030,7 +26030,7 @@
         <v>14</v>
       </c>
       <c r="F231" s="2">
-        <v>2993</v>
+        <v>1592</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>15</v>
@@ -26062,7 +26062,7 @@
         <v>14</v>
       </c>
       <c r="F232" s="2">
-        <v>1900</v>
+        <v>2636</v>
       </c>
       <c r="G232" s="2" t="s">
         <v>15</v>
@@ -26094,7 +26094,7 @@
         <v>14</v>
       </c>
       <c r="F233" s="2">
-        <v>1549</v>
+        <v>2516</v>
       </c>
       <c r="G233" s="2" t="s">
         <v>15</v>
@@ -26126,7 +26126,7 @@
         <v>14</v>
       </c>
       <c r="F234" s="2">
-        <v>4690</v>
+        <v>962</v>
       </c>
       <c r="G234" s="2" t="s">
         <v>15</v>
@@ -26158,7 +26158,7 @@
         <v>14</v>
       </c>
       <c r="F235" s="2">
-        <v>1555</v>
+        <v>1588</v>
       </c>
       <c r="G235" s="2" t="s">
         <v>15</v>
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="F236" s="2">
-        <v>3504</v>
+        <v>3416</v>
       </c>
       <c r="G236" s="2" t="s">
         <v>15</v>
@@ -26222,7 +26222,7 @@
         <v>14</v>
       </c>
       <c r="F237" s="2">
-        <v>2531</v>
+        <v>1845</v>
       </c>
       <c r="G237" s="2" t="s">
         <v>15</v>
@@ -26254,7 +26254,7 @@
         <v>14</v>
       </c>
       <c r="F238" s="2">
-        <v>1428</v>
+        <v>1507</v>
       </c>
       <c r="G238" s="2" t="s">
         <v>15</v>
@@ -26286,7 +26286,7 @@
         <v>14</v>
       </c>
       <c r="F239" s="2">
-        <v>2708</v>
+        <v>3458</v>
       </c>
       <c r="G239" s="2" t="s">
         <v>15</v>
@@ -26318,7 +26318,7 @@
         <v>14</v>
       </c>
       <c r="F240" s="2">
-        <v>2986</v>
+        <v>1969</v>
       </c>
       <c r="G240" s="2" t="s">
         <v>15</v>
@@ -26350,7 +26350,7 @@
         <v>14</v>
       </c>
       <c r="F241" s="2">
-        <v>3260</v>
+        <v>4402</v>
       </c>
       <c r="G241" s="2" t="s">
         <v>15</v>
@@ -26382,7 +26382,7 @@
         <v>14</v>
       </c>
       <c r="F242" s="2">
-        <v>4509</v>
+        <v>2071</v>
       </c>
       <c r="G242" s="2" t="s">
         <v>15</v>
@@ -26414,7 +26414,7 @@
         <v>14</v>
       </c>
       <c r="F243" s="2">
-        <v>3649</v>
+        <v>4692</v>
       </c>
       <c r="G243" s="2" t="s">
         <v>15</v>
@@ -26446,7 +26446,7 @@
         <v>14</v>
       </c>
       <c r="F244" s="2">
-        <v>2814</v>
+        <v>1076</v>
       </c>
       <c r="G244" s="2" t="s">
         <v>15</v>
@@ -26478,7 +26478,7 @@
         <v>14</v>
       </c>
       <c r="F245" s="2">
-        <v>3050</v>
+        <v>4165</v>
       </c>
       <c r="G245" s="2" t="s">
         <v>15</v>
@@ -26510,7 +26510,7 @@
         <v>14</v>
       </c>
       <c r="F246" s="2">
-        <v>3066</v>
+        <v>1129</v>
       </c>
       <c r="G246" s="2" t="s">
         <v>15</v>
@@ -26542,7 +26542,7 @@
         <v>14</v>
       </c>
       <c r="F247" s="2">
-        <v>3630</v>
+        <v>1895</v>
       </c>
       <c r="G247" s="2" t="s">
         <v>15</v>
@@ -26574,7 +26574,7 @@
         <v>14</v>
       </c>
       <c r="F248" s="2">
-        <v>1226</v>
+        <v>1973</v>
       </c>
       <c r="G248" s="2" t="s">
         <v>15</v>
@@ -26606,7 +26606,7 @@
         <v>14</v>
       </c>
       <c r="F249" s="2">
-        <v>1591</v>
+        <v>2026</v>
       </c>
       <c r="G249" s="2" t="s">
         <v>15</v>
@@ -26638,7 +26638,7 @@
         <v>14</v>
       </c>
       <c r="F250" s="2">
-        <v>4377</v>
+        <v>3095</v>
       </c>
       <c r="G250" s="2" t="s">
         <v>15</v>
@@ -26670,7 +26670,7 @@
         <v>14</v>
       </c>
       <c r="F251" s="2">
-        <v>952</v>
+        <v>1251</v>
       </c>
       <c r="G251" s="2" t="s">
         <v>15</v>
@@ -26702,7 +26702,7 @@
         <v>14</v>
       </c>
       <c r="F252" s="2">
-        <v>2305</v>
+        <v>1629</v>
       </c>
       <c r="G252" s="2" t="s">
         <v>15</v>
@@ -26734,7 +26734,7 @@
         <v>14</v>
       </c>
       <c r="F253" s="2">
-        <v>1303</v>
+        <v>1652</v>
       </c>
       <c r="G253" s="2" t="s">
         <v>15</v>
@@ -26766,7 +26766,7 @@
         <v>14</v>
       </c>
       <c r="F254" s="2">
-        <v>3769</v>
+        <v>4588</v>
       </c>
       <c r="G254" s="2" t="s">
         <v>15</v>
@@ -26798,7 +26798,7 @@
         <v>14</v>
       </c>
       <c r="F255" s="2">
-        <v>2755</v>
+        <v>2996</v>
       </c>
       <c r="G255" s="2" t="s">
         <v>15</v>
@@ -26830,7 +26830,7 @@
         <v>14</v>
       </c>
       <c r="F256" s="2">
-        <v>1127</v>
+        <v>1606</v>
       </c>
       <c r="G256" s="2" t="s">
         <v>15</v>
@@ -26862,7 +26862,7 @@
         <v>14</v>
       </c>
       <c r="F257" s="2">
-        <v>2706</v>
+        <v>2582</v>
       </c>
       <c r="G257" s="2" t="s">
         <v>15</v>
@@ -26894,7 +26894,7 @@
         <v>14</v>
       </c>
       <c r="F258" s="2">
-        <v>3223</v>
+        <v>2519</v>
       </c>
       <c r="G258" s="2" t="s">
         <v>15</v>
@@ -26926,7 +26926,7 @@
         <v>14</v>
       </c>
       <c r="F259" s="2">
-        <v>1796</v>
+        <v>4593</v>
       </c>
       <c r="G259" s="2" t="s">
         <v>15</v>
@@ -26958,7 +26958,7 @@
         <v>14</v>
       </c>
       <c r="F260" s="2">
-        <v>944</v>
+        <v>3340</v>
       </c>
       <c r="G260" s="2" t="s">
         <v>15</v>
@@ -26990,7 +26990,7 @@
         <v>14</v>
       </c>
       <c r="F261" s="2">
-        <v>1426</v>
+        <v>2568</v>
       </c>
       <c r="G261" s="2" t="s">
         <v>15</v>
@@ -27022,7 +27022,7 @@
         <v>14</v>
       </c>
       <c r="F262" s="2">
-        <v>2446</v>
+        <v>877</v>
       </c>
       <c r="G262" s="2" t="s">
         <v>15</v>
@@ -27054,7 +27054,7 @@
         <v>14</v>
       </c>
       <c r="F263" s="2">
-        <v>1945</v>
+        <v>4277</v>
       </c>
       <c r="G263" s="2" t="s">
         <v>15</v>
@@ -27086,7 +27086,7 @@
         <v>14</v>
       </c>
       <c r="F264" s="2">
-        <v>2992</v>
+        <v>1602</v>
       </c>
       <c r="G264" s="2" t="s">
         <v>15</v>
@@ -27118,7 +27118,7 @@
         <v>14</v>
       </c>
       <c r="F265" s="2">
-        <v>1949</v>
+        <v>1449</v>
       </c>
       <c r="G265" s="2" t="s">
         <v>15</v>
@@ -27150,7 +27150,7 @@
         <v>14</v>
       </c>
       <c r="F266" s="2">
-        <v>1324</v>
+        <v>3457</v>
       </c>
       <c r="G266" s="2" t="s">
         <v>15</v>
@@ -27182,7 +27182,7 @@
         <v>14</v>
       </c>
       <c r="F267" s="2">
-        <v>2255</v>
+        <v>2741</v>
       </c>
       <c r="G267" s="2" t="s">
         <v>15</v>
@@ -27214,7 +27214,7 @@
         <v>14</v>
       </c>
       <c r="F268" s="2">
-        <v>1217</v>
+        <v>3208</v>
       </c>
       <c r="G268" s="2" t="s">
         <v>15</v>
@@ -27246,7 +27246,7 @@
         <v>14</v>
       </c>
       <c r="F269" s="2">
-        <v>2863</v>
+        <v>2239</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>15</v>
@@ -27278,7 +27278,7 @@
         <v>14</v>
       </c>
       <c r="F270" s="2">
-        <v>2514</v>
+        <v>4543</v>
       </c>
       <c r="G270" s="2" t="s">
         <v>15</v>
@@ -27310,7 +27310,7 @@
         <v>14</v>
       </c>
       <c r="F271" s="2">
-        <v>2581</v>
+        <v>3712</v>
       </c>
       <c r="G271" s="2" t="s">
         <v>15</v>
@@ -27342,7 +27342,7 @@
         <v>14</v>
       </c>
       <c r="F272" s="2">
-        <v>3381</v>
+        <v>4239</v>
       </c>
       <c r="G272" s="2" t="s">
         <v>15</v>
@@ -27374,7 +27374,7 @@
         <v>14</v>
       </c>
       <c r="F273" s="2">
-        <v>3640</v>
+        <v>4773</v>
       </c>
       <c r="G273" s="2" t="s">
         <v>15</v>
@@ -27406,7 +27406,7 @@
         <v>14</v>
       </c>
       <c r="F274" s="2">
-        <v>4587</v>
+        <v>1305</v>
       </c>
       <c r="G274" s="2" t="s">
         <v>15</v>
@@ -27438,7 +27438,7 @@
         <v>14</v>
       </c>
       <c r="F275" s="2">
-        <v>4224</v>
+        <v>4569</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>15</v>
@@ -27470,7 +27470,7 @@
         <v>14</v>
       </c>
       <c r="F276" s="2">
-        <v>2545</v>
+        <v>1567</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>15</v>
@@ -27502,7 +27502,7 @@
         <v>14</v>
       </c>
       <c r="F277" s="2">
-        <v>2351</v>
+        <v>1129</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>15</v>
@@ -27534,7 +27534,7 @@
         <v>14</v>
       </c>
       <c r="F278" s="2">
-        <v>3243</v>
+        <v>3028</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>15</v>
@@ -27566,7 +27566,7 @@
         <v>14</v>
       </c>
       <c r="F279" s="2">
-        <v>1883</v>
+        <v>4785</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>15</v>
@@ -27598,7 +27598,7 @@
         <v>14</v>
       </c>
       <c r="F280" s="2">
-        <v>2362</v>
+        <v>2739</v>
       </c>
       <c r="G280" s="2" t="s">
         <v>15</v>
@@ -27630,7 +27630,7 @@
         <v>14</v>
       </c>
       <c r="F281" s="2">
-        <v>1757</v>
+        <v>3274</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>15</v>
@@ -27662,7 +27662,7 @@
         <v>14</v>
       </c>
       <c r="F282" s="2">
-        <v>3695</v>
+        <v>3694</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>15</v>
@@ -27694,7 +27694,7 @@
         <v>14</v>
       </c>
       <c r="F283" s="2">
-        <v>3469</v>
+        <v>4549</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>15</v>
@@ -27726,7 +27726,7 @@
         <v>14</v>
       </c>
       <c r="F284" s="2">
-        <v>4694</v>
+        <v>3954</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>15</v>
@@ -27758,7 +27758,7 @@
         <v>14</v>
       </c>
       <c r="F285" s="2">
-        <v>2743</v>
+        <v>2745</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>15</v>
@@ -27790,7 +27790,7 @@
         <v>14</v>
       </c>
       <c r="F286" s="2">
-        <v>3806</v>
+        <v>4224</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>15</v>
@@ -27822,7 +27822,7 @@
         <v>14</v>
       </c>
       <c r="F287" s="2">
-        <v>2366</v>
+        <v>4295</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>15</v>
@@ -27854,7 +27854,7 @@
         <v>14</v>
       </c>
       <c r="F288" s="2">
-        <v>1470</v>
+        <v>4160</v>
       </c>
       <c r="G288" s="2" t="s">
         <v>15</v>
@@ -27886,7 +27886,7 @@
         <v>14</v>
       </c>
       <c r="F289" s="2">
-        <v>1517</v>
+        <v>1079</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>15</v>
@@ -27918,7 +27918,7 @@
         <v>14</v>
       </c>
       <c r="F290" s="2">
-        <v>3646</v>
+        <v>1680</v>
       </c>
       <c r="G290" s="2" t="s">
         <v>15</v>
@@ -27950,7 +27950,7 @@
         <v>14</v>
       </c>
       <c r="F291" s="2">
-        <v>2909</v>
+        <v>2102</v>
       </c>
       <c r="G291" s="2" t="s">
         <v>15</v>
@@ -27982,7 +27982,7 @@
         <v>14</v>
       </c>
       <c r="F292" s="2">
-        <v>831</v>
+        <v>3281</v>
       </c>
       <c r="G292" s="2" t="s">
         <v>15</v>
@@ -28014,7 +28014,7 @@
         <v>14</v>
       </c>
       <c r="F293" s="2">
-        <v>2511</v>
+        <v>937</v>
       </c>
       <c r="G293" s="2" t="s">
         <v>15</v>
@@ -28046,7 +28046,7 @@
         <v>14</v>
       </c>
       <c r="F294" s="2">
-        <v>3654</v>
+        <v>2656</v>
       </c>
       <c r="G294" s="2" t="s">
         <v>15</v>
@@ -28078,7 +28078,7 @@
         <v>14</v>
       </c>
       <c r="F295" s="2">
-        <v>3598</v>
+        <v>3189</v>
       </c>
       <c r="G295" s="2" t="s">
         <v>15</v>
@@ -28110,7 +28110,7 @@
         <v>14</v>
       </c>
       <c r="F296" s="2">
-        <v>2453</v>
+        <v>2092</v>
       </c>
       <c r="G296" s="2" t="s">
         <v>15</v>
@@ -28142,7 +28142,7 @@
         <v>14</v>
       </c>
       <c r="F297" s="2">
-        <v>3012</v>
+        <v>2885</v>
       </c>
       <c r="G297" s="2" t="s">
         <v>15</v>
@@ -28174,7 +28174,7 @@
         <v>14</v>
       </c>
       <c r="F298" s="2">
-        <v>4235</v>
+        <v>2970</v>
       </c>
       <c r="G298" s="2" t="s">
         <v>15</v>
@@ -28206,7 +28206,7 @@
         <v>14</v>
       </c>
       <c r="F299" s="2">
-        <v>1065</v>
+        <v>4200</v>
       </c>
       <c r="G299" s="2" t="s">
         <v>15</v>
@@ -28238,7 +28238,7 @@
         <v>14</v>
       </c>
       <c r="F300" s="2">
-        <v>4548</v>
+        <v>4666</v>
       </c>
       <c r="G300" s="2" t="s">
         <v>15</v>
@@ -28270,7 +28270,7 @@
         <v>14</v>
       </c>
       <c r="F301" s="2">
-        <v>4763</v>
+        <v>1415</v>
       </c>
       <c r="G301" s="2" t="s">
         <v>15</v>
@@ -28302,7 +28302,7 @@
         <v>14</v>
       </c>
       <c r="F302" s="2">
-        <v>3027</v>
+        <v>1737</v>
       </c>
       <c r="G302" s="2" t="s">
         <v>15</v>
@@ -28334,7 +28334,7 @@
         <v>14</v>
       </c>
       <c r="F303" s="2">
-        <v>4101</v>
+        <v>4530</v>
       </c>
       <c r="G303" s="2" t="s">
         <v>15</v>
@@ -28366,7 +28366,7 @@
         <v>14</v>
       </c>
       <c r="F304" s="2">
-        <v>2415</v>
+        <v>2866</v>
       </c>
       <c r="G304" s="2" t="s">
         <v>15</v>
@@ -28398,7 +28398,7 @@
         <v>14</v>
       </c>
       <c r="F305" s="2">
-        <v>2907</v>
+        <v>1772</v>
       </c>
       <c r="G305" s="2" t="s">
         <v>15</v>
@@ -28430,7 +28430,7 @@
         <v>14</v>
       </c>
       <c r="F306" s="2">
-        <v>1561</v>
+        <v>3642</v>
       </c>
       <c r="G306" s="2" t="s">
         <v>15</v>
@@ -28462,7 +28462,7 @@
         <v>14</v>
       </c>
       <c r="F307" s="2">
-        <v>2159</v>
+        <v>1291</v>
       </c>
       <c r="G307" s="2" t="s">
         <v>15</v>
@@ -28494,7 +28494,7 @@
         <v>14</v>
       </c>
       <c r="F308" s="2">
-        <v>3445</v>
+        <v>4466</v>
       </c>
       <c r="G308" s="2" t="s">
         <v>15</v>
@@ -28526,7 +28526,7 @@
         <v>14</v>
       </c>
       <c r="F309" s="2">
-        <v>3658</v>
+        <v>959</v>
       </c>
       <c r="G309" s="2" t="s">
         <v>15</v>
@@ -28558,7 +28558,7 @@
         <v>14</v>
       </c>
       <c r="F310" s="2">
-        <v>3266</v>
+        <v>4564</v>
       </c>
       <c r="G310" s="2" t="s">
         <v>15</v>
@@ -28590,7 +28590,7 @@
         <v>14</v>
       </c>
       <c r="F311" s="2">
-        <v>3620</v>
+        <v>3778</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>15</v>
@@ -28622,7 +28622,7 @@
         <v>14</v>
       </c>
       <c r="F312" s="2">
-        <v>3805</v>
+        <v>2889</v>
       </c>
       <c r="G312" s="2" t="s">
         <v>15</v>
@@ -28654,7 +28654,7 @@
         <v>14</v>
       </c>
       <c r="F313" s="2">
-        <v>1251</v>
+        <v>1656</v>
       </c>
       <c r="G313" s="2" t="s">
         <v>15</v>
@@ -28686,7 +28686,7 @@
         <v>14</v>
       </c>
       <c r="F314" s="2">
-        <v>1247</v>
+        <v>2049</v>
       </c>
       <c r="G314" s="2" t="s">
         <v>15</v>
@@ -28718,7 +28718,7 @@
         <v>14</v>
       </c>
       <c r="F315" s="2">
-        <v>1950</v>
+        <v>917</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>15</v>
@@ -28750,7 +28750,7 @@
         <v>14</v>
       </c>
       <c r="F316" s="2">
-        <v>1477</v>
+        <v>3931</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>15</v>
@@ -28782,7 +28782,7 @@
         <v>14</v>
       </c>
       <c r="F317" s="2">
-        <v>1234</v>
+        <v>3666</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>15</v>
@@ -28814,7 +28814,7 @@
         <v>14</v>
       </c>
       <c r="F318" s="2">
-        <v>4451</v>
+        <v>3554</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>15</v>
@@ -28846,7 +28846,7 @@
         <v>14</v>
       </c>
       <c r="F319" s="2">
-        <v>4140</v>
+        <v>4650</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>15</v>
@@ -28878,7 +28878,7 @@
         <v>14</v>
       </c>
       <c r="F320" s="2">
-        <v>3230</v>
+        <v>1437</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>15</v>
@@ -28910,7 +28910,7 @@
         <v>14</v>
       </c>
       <c r="F321" s="2">
-        <v>3047</v>
+        <v>993</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>15</v>
@@ -28942,7 +28942,7 @@
         <v>14</v>
       </c>
       <c r="F322" s="2">
-        <v>2849</v>
+        <v>2386</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>15</v>
@@ -28974,7 +28974,7 @@
         <v>14</v>
       </c>
       <c r="F323" s="2">
-        <v>2294</v>
+        <v>1785</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>15</v>
@@ -29006,7 +29006,7 @@
         <v>14</v>
       </c>
       <c r="F324" s="2">
-        <v>3453</v>
+        <v>1432</v>
       </c>
       <c r="G324" s="2" t="s">
         <v>15</v>
@@ -29038,7 +29038,7 @@
         <v>14</v>
       </c>
       <c r="F325" s="2">
-        <v>960</v>
+        <v>3004</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>15</v>
@@ -29070,7 +29070,7 @@
         <v>14</v>
       </c>
       <c r="F326" s="2">
-        <v>2133</v>
+        <v>4437</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>15</v>
@@ -29102,7 +29102,7 @@
         <v>14</v>
       </c>
       <c r="F327" s="2">
-        <v>3056</v>
+        <v>1971</v>
       </c>
       <c r="G327" s="2" t="s">
         <v>15</v>
@@ -29134,7 +29134,7 @@
         <v>14</v>
       </c>
       <c r="F328" s="2">
-        <v>3342</v>
+        <v>1099</v>
       </c>
       <c r="G328" s="2" t="s">
         <v>15</v>
@@ -29166,7 +29166,7 @@
         <v>14</v>
       </c>
       <c r="F329" s="2">
-        <v>1757</v>
+        <v>3912</v>
       </c>
       <c r="G329" s="2" t="s">
         <v>15</v>
@@ -29198,7 +29198,7 @@
         <v>14</v>
       </c>
       <c r="F330" s="2">
-        <v>4244</v>
+        <v>3581</v>
       </c>
       <c r="G330" s="2" t="s">
         <v>15</v>
@@ -29230,7 +29230,7 @@
         <v>14</v>
       </c>
       <c r="F331" s="2">
-        <v>4119</v>
+        <v>4102</v>
       </c>
       <c r="G331" s="2" t="s">
         <v>15</v>
@@ -29262,7 +29262,7 @@
         <v>14</v>
       </c>
       <c r="F332" s="2">
-        <v>2824</v>
+        <v>3869</v>
       </c>
       <c r="G332" s="2" t="s">
         <v>15</v>
@@ -29294,7 +29294,7 @@
         <v>14</v>
       </c>
       <c r="F333" s="2">
-        <v>2980</v>
+        <v>4072</v>
       </c>
       <c r="G333" s="2" t="s">
         <v>15</v>
@@ -29326,7 +29326,7 @@
         <v>14</v>
       </c>
       <c r="F334" s="2">
-        <v>3244</v>
+        <v>3115</v>
       </c>
       <c r="G334" s="2" t="s">
         <v>15</v>
@@ -29358,7 +29358,7 @@
         <v>14</v>
       </c>
       <c r="F335" s="2">
-        <v>1729</v>
+        <v>3023</v>
       </c>
       <c r="G335" s="2" t="s">
         <v>15</v>
@@ -29390,7 +29390,7 @@
         <v>14</v>
       </c>
       <c r="F336" s="2">
-        <v>3796</v>
+        <v>2354</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>15</v>
@@ -29422,7 +29422,7 @@
         <v>14</v>
       </c>
       <c r="F337" s="2">
-        <v>2184</v>
+        <v>2772</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>15</v>
@@ -29454,7 +29454,7 @@
         <v>14</v>
       </c>
       <c r="F338" s="2">
-        <v>4775</v>
+        <v>1737</v>
       </c>
       <c r="G338" s="2" t="s">
         <v>15</v>
@@ -29486,7 +29486,7 @@
         <v>14</v>
       </c>
       <c r="F339" s="2">
-        <v>1948</v>
+        <v>3046</v>
       </c>
       <c r="G339" s="2" t="s">
         <v>15</v>
@@ -29518,7 +29518,7 @@
         <v>14</v>
       </c>
       <c r="F340" s="2">
-        <v>1064</v>
+        <v>2292</v>
       </c>
       <c r="G340" s="2" t="s">
         <v>15</v>
@@ -29550,7 +29550,7 @@
         <v>14</v>
       </c>
       <c r="F341" s="2">
-        <v>4638</v>
+        <v>2871</v>
       </c>
       <c r="G341" s="2" t="s">
         <v>15</v>
@@ -29582,7 +29582,7 @@
         <v>14</v>
       </c>
       <c r="F342" s="2">
-        <v>1925</v>
+        <v>3172</v>
       </c>
       <c r="G342" s="2" t="s">
         <v>15</v>
@@ -29614,7 +29614,7 @@
         <v>14</v>
       </c>
       <c r="F343" s="2">
-        <v>4611</v>
+        <v>4089</v>
       </c>
       <c r="G343" s="2" t="s">
         <v>15</v>
@@ -29646,7 +29646,7 @@
         <v>14</v>
       </c>
       <c r="F344" s="2">
-        <v>1268</v>
+        <v>2032</v>
       </c>
       <c r="G344" s="2" t="s">
         <v>15</v>
@@ -29678,7 +29678,7 @@
         <v>14</v>
       </c>
       <c r="F345" s="2">
-        <v>2128</v>
+        <v>3432</v>
       </c>
       <c r="G345" s="2" t="s">
         <v>15</v>
@@ -29710,7 +29710,7 @@
         <v>14</v>
       </c>
       <c r="F346" s="2">
-        <v>4637</v>
+        <v>3294</v>
       </c>
       <c r="G346" s="2" t="s">
         <v>15</v>
@@ -29742,7 +29742,7 @@
         <v>14</v>
       </c>
       <c r="F347" s="2">
-        <v>4689</v>
+        <v>4375</v>
       </c>
       <c r="G347" s="2" t="s">
         <v>15</v>
@@ -29774,7 +29774,7 @@
         <v>14</v>
       </c>
       <c r="F348" s="2">
-        <v>2996</v>
+        <v>1218</v>
       </c>
       <c r="G348" s="2" t="s">
         <v>15</v>
@@ -29806,7 +29806,7 @@
         <v>14</v>
       </c>
       <c r="F349" s="2">
-        <v>1299</v>
+        <v>4223</v>
       </c>
       <c r="G349" s="2" t="s">
         <v>15</v>
@@ -29838,7 +29838,7 @@
         <v>14</v>
       </c>
       <c r="F350" s="2">
-        <v>1113</v>
+        <v>1970</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>15</v>
@@ -29870,7 +29870,7 @@
         <v>14</v>
       </c>
       <c r="F351" s="2">
-        <v>3800</v>
+        <v>3164</v>
       </c>
       <c r="G351" s="2" t="s">
         <v>15</v>
@@ -29902,7 +29902,7 @@
         <v>14</v>
       </c>
       <c r="F352" s="2">
-        <v>979</v>
+        <v>4392</v>
       </c>
       <c r="G352" s="2" t="s">
         <v>15</v>
@@ -29934,7 +29934,7 @@
         <v>14</v>
       </c>
       <c r="F353" s="2">
-        <v>3290</v>
+        <v>4626</v>
       </c>
       <c r="G353" s="2" t="s">
         <v>15</v>
@@ -29966,7 +29966,7 @@
         <v>14</v>
       </c>
       <c r="F354" s="2">
-        <v>1290</v>
+        <v>813</v>
       </c>
       <c r="G354" s="2" t="s">
         <v>15</v>
@@ -29998,7 +29998,7 @@
         <v>14</v>
       </c>
       <c r="F355" s="2">
-        <v>3498</v>
+        <v>4638</v>
       </c>
       <c r="G355" s="2" t="s">
         <v>15</v>
@@ -30030,7 +30030,7 @@
         <v>14</v>
       </c>
       <c r="F356" s="2">
-        <v>3429</v>
+        <v>2734</v>
       </c>
       <c r="G356" s="2" t="s">
         <v>15</v>
@@ -30062,7 +30062,7 @@
         <v>14</v>
       </c>
       <c r="F357" s="2">
-        <v>1150</v>
+        <v>3803</v>
       </c>
       <c r="G357" s="2" t="s">
         <v>15</v>
@@ -30094,7 +30094,7 @@
         <v>14</v>
       </c>
       <c r="F358" s="2">
-        <v>4620</v>
+        <v>1741</v>
       </c>
       <c r="G358" s="2" t="s">
         <v>15</v>
@@ -30126,7 +30126,7 @@
         <v>14</v>
       </c>
       <c r="F359" s="2">
-        <v>2163</v>
+        <v>4562</v>
       </c>
       <c r="G359" s="2" t="s">
         <v>15</v>
@@ -30158,7 +30158,7 @@
         <v>14</v>
       </c>
       <c r="F360" s="2">
-        <v>1952</v>
+        <v>2041</v>
       </c>
       <c r="G360" s="2" t="s">
         <v>15</v>
@@ -30190,7 +30190,7 @@
         <v>14</v>
       </c>
       <c r="F361" s="2">
-        <v>4516</v>
+        <v>3845</v>
       </c>
       <c r="G361" s="2" t="s">
         <v>15</v>
@@ -30222,7 +30222,7 @@
         <v>14</v>
       </c>
       <c r="F362" s="2">
-        <v>1630</v>
+        <v>3094</v>
       </c>
       <c r="G362" s="2" t="s">
         <v>15</v>
@@ -30254,7 +30254,7 @@
         <v>14</v>
       </c>
       <c r="F363" s="2">
-        <v>2702</v>
+        <v>2910</v>
       </c>
       <c r="G363" s="2" t="s">
         <v>15</v>
@@ -30286,7 +30286,7 @@
         <v>14</v>
       </c>
       <c r="F364" s="2">
-        <v>1333</v>
+        <v>1471</v>
       </c>
       <c r="G364" s="2" t="s">
         <v>15</v>
@@ -30318,7 +30318,7 @@
         <v>14</v>
       </c>
       <c r="F365" s="2">
-        <v>2046</v>
+        <v>1653</v>
       </c>
       <c r="G365" s="2" t="s">
         <v>15</v>
@@ -30350,7 +30350,7 @@
         <v>14</v>
       </c>
       <c r="F366" s="2">
-        <v>800</v>
+        <v>2406</v>
       </c>
       <c r="G366" s="2" t="s">
         <v>15</v>
@@ -30382,7 +30382,7 @@
         <v>14</v>
       </c>
       <c r="F367" s="2">
-        <v>3996</v>
+        <v>857</v>
       </c>
       <c r="G367" s="2" t="s">
         <v>15</v>
@@ -30414,7 +30414,7 @@
         <v>14</v>
       </c>
       <c r="F368" s="2">
-        <v>4691</v>
+        <v>913</v>
       </c>
       <c r="G368" s="2" t="s">
         <v>15</v>
@@ -30446,7 +30446,7 @@
         <v>14</v>
       </c>
       <c r="F369" s="2">
-        <v>2586</v>
+        <v>3040</v>
       </c>
       <c r="G369" s="2" t="s">
         <v>15</v>
@@ -30478,7 +30478,7 @@
         <v>14</v>
       </c>
       <c r="F370" s="2">
-        <v>3418</v>
+        <v>1052</v>
       </c>
       <c r="G370" s="2" t="s">
         <v>15</v>
@@ -30510,7 +30510,7 @@
         <v>14</v>
       </c>
       <c r="F371" s="2">
-        <v>2409</v>
+        <v>3905</v>
       </c>
       <c r="G371" s="2" t="s">
         <v>15</v>
@@ -30542,7 +30542,7 @@
         <v>14</v>
       </c>
       <c r="F372" s="2">
-        <v>1705</v>
+        <v>4022</v>
       </c>
       <c r="G372" s="2" t="s">
         <v>15</v>
@@ -30574,7 +30574,7 @@
         <v>14</v>
       </c>
       <c r="F373" s="2">
-        <v>4157</v>
+        <v>3035</v>
       </c>
       <c r="G373" s="2" t="s">
         <v>15</v>
@@ -30606,7 +30606,7 @@
         <v>14</v>
       </c>
       <c r="F374" s="2">
-        <v>1324</v>
+        <v>2494</v>
       </c>
       <c r="G374" s="2" t="s">
         <v>15</v>
@@ -30638,7 +30638,7 @@
         <v>14</v>
       </c>
       <c r="F375" s="2">
-        <v>4738</v>
+        <v>3998</v>
       </c>
       <c r="G375" s="2" t="s">
         <v>15</v>
@@ -30670,7 +30670,7 @@
         <v>14</v>
       </c>
       <c r="F376" s="2">
-        <v>2360</v>
+        <v>3948</v>
       </c>
       <c r="G376" s="2" t="s">
         <v>15</v>
@@ -30702,7 +30702,7 @@
         <v>14</v>
       </c>
       <c r="F377" s="2">
-        <v>952</v>
+        <v>3124</v>
       </c>
       <c r="G377" s="2" t="s">
         <v>15</v>
@@ -30734,7 +30734,7 @@
         <v>14</v>
       </c>
       <c r="F378" s="2">
-        <v>2314</v>
+        <v>2174</v>
       </c>
       <c r="G378" s="2" t="s">
         <v>15</v>
@@ -30766,7 +30766,7 @@
         <v>14</v>
       </c>
       <c r="F379" s="2">
-        <v>3955</v>
+        <v>4130</v>
       </c>
       <c r="G379" s="2" t="s">
         <v>15</v>
@@ -30798,7 +30798,7 @@
         <v>14</v>
       </c>
       <c r="F380" s="2">
-        <v>2004</v>
+        <v>1052</v>
       </c>
       <c r="G380" s="2" t="s">
         <v>15</v>
@@ -30830,7 +30830,7 @@
         <v>14</v>
       </c>
       <c r="F381" s="2">
-        <v>3094</v>
+        <v>1881</v>
       </c>
       <c r="G381" s="2" t="s">
         <v>15</v>
@@ -30862,7 +30862,7 @@
         <v>14</v>
       </c>
       <c r="F382" s="2">
-        <v>1945</v>
+        <v>4287</v>
       </c>
       <c r="G382" s="2" t="s">
         <v>15</v>
@@ -30894,7 +30894,7 @@
         <v>14</v>
       </c>
       <c r="F383" s="2">
-        <v>1104</v>
+        <v>3603</v>
       </c>
       <c r="G383" s="2" t="s">
         <v>15</v>
@@ -30926,7 +30926,7 @@
         <v>14</v>
       </c>
       <c r="F384" s="2">
-        <v>1013</v>
+        <v>2413</v>
       </c>
       <c r="G384" s="2" t="s">
         <v>15</v>
@@ -30958,7 +30958,7 @@
         <v>14</v>
       </c>
       <c r="F385" s="2">
-        <v>4416</v>
+        <v>4027</v>
       </c>
       <c r="G385" s="2" t="s">
         <v>15</v>
@@ -30990,7 +30990,7 @@
         <v>14</v>
       </c>
       <c r="F386" s="2">
-        <v>3663</v>
+        <v>1790</v>
       </c>
       <c r="G386" s="2" t="s">
         <v>15</v>
@@ -31022,7 +31022,7 @@
         <v>14</v>
       </c>
       <c r="F387" s="2">
-        <v>3340</v>
+        <v>942</v>
       </c>
       <c r="G387" s="2" t="s">
         <v>15</v>
@@ -31054,7 +31054,7 @@
         <v>14</v>
       </c>
       <c r="F388" s="2">
-        <v>1716</v>
+        <v>3528</v>
       </c>
       <c r="G388" s="2" t="s">
         <v>15</v>
@@ -31086,7 +31086,7 @@
         <v>14</v>
       </c>
       <c r="F389" s="2">
-        <v>4009</v>
+        <v>1605</v>
       </c>
       <c r="G389" s="2" t="s">
         <v>15</v>
@@ -31118,7 +31118,7 @@
         <v>14</v>
       </c>
       <c r="F390" s="2">
-        <v>3834</v>
+        <v>3299</v>
       </c>
       <c r="G390" s="2" t="s">
         <v>15</v>
@@ -31150,7 +31150,7 @@
         <v>14</v>
       </c>
       <c r="F391" s="2">
-        <v>950</v>
+        <v>1157</v>
       </c>
       <c r="G391" s="2" t="s">
         <v>15</v>
@@ -31182,7 +31182,7 @@
         <v>14</v>
       </c>
       <c r="F392" s="2">
-        <v>2543</v>
+        <v>3965</v>
       </c>
       <c r="G392" s="2" t="s">
         <v>15</v>
@@ -31214,7 +31214,7 @@
         <v>14</v>
       </c>
       <c r="F393" s="2">
-        <v>2181</v>
+        <v>853</v>
       </c>
       <c r="G393" s="2" t="s">
         <v>15</v>
@@ -31246,7 +31246,7 @@
         <v>14</v>
       </c>
       <c r="F394" s="2">
-        <v>1736</v>
+        <v>1134</v>
       </c>
       <c r="G394" s="2" t="s">
         <v>15</v>
@@ -31278,7 +31278,7 @@
         <v>14</v>
       </c>
       <c r="F395" s="2">
-        <v>870</v>
+        <v>4441</v>
       </c>
       <c r="G395" s="2" t="s">
         <v>15</v>
@@ -31310,7 +31310,7 @@
         <v>14</v>
       </c>
       <c r="F396" s="2">
-        <v>1254</v>
+        <v>3735</v>
       </c>
       <c r="G396" s="2" t="s">
         <v>15</v>
@@ -31342,7 +31342,7 @@
         <v>14</v>
       </c>
       <c r="F397" s="2">
-        <v>2575</v>
+        <v>1221</v>
       </c>
       <c r="G397" s="2" t="s">
         <v>15</v>
@@ -31374,7 +31374,7 @@
         <v>14</v>
       </c>
       <c r="F398" s="2">
-        <v>3091</v>
+        <v>3304</v>
       </c>
       <c r="G398" s="2" t="s">
         <v>15</v>
@@ -31406,7 +31406,7 @@
         <v>14</v>
       </c>
       <c r="F399" s="2">
-        <v>1443</v>
+        <v>2445</v>
       </c>
       <c r="G399" s="2" t="s">
         <v>15</v>
@@ -31438,7 +31438,7 @@
         <v>14</v>
       </c>
       <c r="F400" s="2">
-        <v>3362</v>
+        <v>2352</v>
       </c>
       <c r="G400" s="2" t="s">
         <v>15</v>
@@ -31470,7 +31470,7 @@
         <v>14</v>
       </c>
       <c r="F401" s="2">
-        <v>1140</v>
+        <v>2083</v>
       </c>
       <c r="G401" s="2" t="s">
         <v>15</v>
@@ -31502,7 +31502,7 @@
         <v>14</v>
       </c>
       <c r="F402" s="2">
-        <v>3980</v>
+        <v>3100</v>
       </c>
       <c r="G402" s="2" t="s">
         <v>15</v>
@@ -31534,7 +31534,7 @@
         <v>14</v>
       </c>
       <c r="F403" s="2">
-        <v>4357</v>
+        <v>3473</v>
       </c>
       <c r="G403" s="2" t="s">
         <v>15</v>
@@ -31566,7 +31566,7 @@
         <v>14</v>
       </c>
       <c r="F404" s="2">
-        <v>923</v>
+        <v>2228</v>
       </c>
       <c r="G404" s="2" t="s">
         <v>15</v>
@@ -31598,7 +31598,7 @@
         <v>14</v>
       </c>
       <c r="F405" s="2">
-        <v>935</v>
+        <v>805</v>
       </c>
       <c r="G405" s="2" t="s">
         <v>15</v>
@@ -31630,7 +31630,7 @@
         <v>14</v>
       </c>
       <c r="F406" s="2">
-        <v>1189</v>
+        <v>3586</v>
       </c>
       <c r="G406" s="2" t="s">
         <v>15</v>
@@ -31662,7 +31662,7 @@
         <v>14</v>
       </c>
       <c r="F407" s="2">
-        <v>1050</v>
+        <v>4555</v>
       </c>
       <c r="G407" s="2" t="s">
         <v>15</v>
@@ -31694,7 +31694,7 @@
         <v>14</v>
       </c>
       <c r="F408" s="2">
-        <v>1027</v>
+        <v>1078</v>
       </c>
       <c r="G408" s="2" t="s">
         <v>15</v>
@@ -31726,7 +31726,7 @@
         <v>14</v>
       </c>
       <c r="F409" s="2">
-        <v>4181</v>
+        <v>4245</v>
       </c>
       <c r="G409" s="2" t="s">
         <v>15</v>
@@ -31758,7 +31758,7 @@
         <v>14</v>
       </c>
       <c r="F410" s="2">
-        <v>1486</v>
+        <v>1046</v>
       </c>
       <c r="G410" s="2" t="s">
         <v>15</v>
@@ -31790,7 +31790,7 @@
         <v>14</v>
       </c>
       <c r="F411" s="2">
-        <v>4747</v>
+        <v>2479</v>
       </c>
       <c r="G411" s="2" t="s">
         <v>15</v>
@@ -31822,7 +31822,7 @@
         <v>14</v>
       </c>
       <c r="F412" s="2">
-        <v>2933</v>
+        <v>3944</v>
       </c>
       <c r="G412" s="2" t="s">
         <v>15</v>
@@ -31854,7 +31854,7 @@
         <v>14</v>
       </c>
       <c r="F413" s="2">
-        <v>1428</v>
+        <v>2336</v>
       </c>
       <c r="G413" s="2" t="s">
         <v>15</v>
@@ -31886,7 +31886,7 @@
         <v>14</v>
       </c>
       <c r="F414" s="2">
-        <v>1050</v>
+        <v>4571</v>
       </c>
       <c r="G414" s="2" t="s">
         <v>15</v>
@@ -31918,7 +31918,7 @@
         <v>14</v>
       </c>
       <c r="F415" s="2">
-        <v>3646</v>
+        <v>1110</v>
       </c>
       <c r="G415" s="2" t="s">
         <v>15</v>
@@ -31950,7 +31950,7 @@
         <v>14</v>
       </c>
       <c r="F416" s="2">
-        <v>1963</v>
+        <v>1826</v>
       </c>
       <c r="G416" s="2" t="s">
         <v>15</v>
@@ -31982,7 +31982,7 @@
         <v>14</v>
       </c>
       <c r="F417" s="2">
-        <v>964</v>
+        <v>3967</v>
       </c>
       <c r="G417" s="2" t="s">
         <v>15</v>
@@ -32014,7 +32014,7 @@
         <v>14</v>
       </c>
       <c r="F418" s="2">
-        <v>4768</v>
+        <v>3218</v>
       </c>
       <c r="G418" s="2" t="s">
         <v>15</v>
@@ -32046,7 +32046,7 @@
         <v>14</v>
       </c>
       <c r="F419" s="2">
-        <v>3055</v>
+        <v>1388</v>
       </c>
       <c r="G419" s="2" t="s">
         <v>15</v>
@@ -32078,7 +32078,7 @@
         <v>14</v>
       </c>
       <c r="F420" s="2">
-        <v>2189</v>
+        <v>945</v>
       </c>
       <c r="G420" s="2" t="s">
         <v>15</v>
@@ -32110,7 +32110,7 @@
         <v>14</v>
       </c>
       <c r="F421" s="2">
-        <v>959</v>
+        <v>1858</v>
       </c>
       <c r="G421" s="2" t="s">
         <v>15</v>
@@ -32142,7 +32142,7 @@
         <v>14</v>
       </c>
       <c r="F422" s="2">
-        <v>4728</v>
+        <v>4081</v>
       </c>
       <c r="G422" s="2" t="s">
         <v>15</v>
@@ -32174,7 +32174,7 @@
         <v>14</v>
       </c>
       <c r="F423" s="2">
-        <v>3599</v>
+        <v>4728</v>
       </c>
       <c r="G423" s="2" t="s">
         <v>15</v>
@@ -32206,7 +32206,7 @@
         <v>14</v>
       </c>
       <c r="F424" s="2">
-        <v>3689</v>
+        <v>3251</v>
       </c>
       <c r="G424" s="2" t="s">
         <v>15</v>
@@ -32238,7 +32238,7 @@
         <v>14</v>
       </c>
       <c r="F425" s="2">
-        <v>1328</v>
+        <v>2653</v>
       </c>
       <c r="G425" s="2" t="s">
         <v>15</v>
@@ -32270,7 +32270,7 @@
         <v>14</v>
       </c>
       <c r="F426" s="2">
-        <v>2073</v>
+        <v>3991</v>
       </c>
       <c r="G426" s="2" t="s">
         <v>15</v>
@@ -32302,7 +32302,7 @@
         <v>14</v>
       </c>
       <c r="F427" s="2">
-        <v>2351</v>
+        <v>2839</v>
       </c>
       <c r="G427" s="2" t="s">
         <v>15</v>
@@ -32334,7 +32334,7 @@
         <v>14</v>
       </c>
       <c r="F428" s="2">
-        <v>4005</v>
+        <v>2343</v>
       </c>
       <c r="G428" s="2" t="s">
         <v>15</v>
@@ -32366,7 +32366,7 @@
         <v>14</v>
       </c>
       <c r="F429" s="2">
-        <v>813</v>
+        <v>4266</v>
       </c>
       <c r="G429" s="2" t="s">
         <v>15</v>
@@ -32398,7 +32398,7 @@
         <v>14</v>
       </c>
       <c r="F430" s="2">
-        <v>3222</v>
+        <v>3168</v>
       </c>
       <c r="G430" s="2" t="s">
         <v>15</v>
@@ -32430,7 +32430,7 @@
         <v>14</v>
       </c>
       <c r="F431" s="2">
-        <v>1774</v>
+        <v>3419</v>
       </c>
       <c r="G431" s="2" t="s">
         <v>15</v>
@@ -32462,7 +32462,7 @@
         <v>14</v>
       </c>
       <c r="F432" s="2">
-        <v>2908</v>
+        <v>2427</v>
       </c>
       <c r="G432" s="2" t="s">
         <v>15</v>
@@ -32494,7 +32494,7 @@
         <v>14</v>
       </c>
       <c r="F433" s="2">
-        <v>1187</v>
+        <v>3228</v>
       </c>
       <c r="G433" s="2" t="s">
         <v>15</v>
@@ -32526,7 +32526,7 @@
         <v>14</v>
       </c>
       <c r="F434" s="2">
-        <v>4766</v>
+        <v>1442</v>
       </c>
       <c r="G434" s="2" t="s">
         <v>15</v>
@@ -32558,7 +32558,7 @@
         <v>14</v>
       </c>
       <c r="F435" s="2">
-        <v>3107</v>
+        <v>2748</v>
       </c>
       <c r="G435" s="2" t="s">
         <v>15</v>
@@ -32590,7 +32590,7 @@
         <v>14</v>
       </c>
       <c r="F436" s="2">
-        <v>3180</v>
+        <v>2163</v>
       </c>
       <c r="G436" s="2" t="s">
         <v>15</v>
@@ -32622,7 +32622,7 @@
         <v>14</v>
       </c>
       <c r="F437" s="2">
-        <v>3860</v>
+        <v>4126</v>
       </c>
       <c r="G437" s="2" t="s">
         <v>15</v>
@@ -32654,7 +32654,7 @@
         <v>14</v>
       </c>
       <c r="F438" s="2">
-        <v>3144</v>
+        <v>1349</v>
       </c>
       <c r="G438" s="2" t="s">
         <v>15</v>
@@ -32686,7 +32686,7 @@
         <v>14</v>
       </c>
       <c r="F439" s="2">
-        <v>2853</v>
+        <v>2348</v>
       </c>
       <c r="G439" s="2" t="s">
         <v>15</v>
@@ -32718,7 +32718,7 @@
         <v>14</v>
       </c>
       <c r="F440" s="2">
-        <v>4773</v>
+        <v>4471</v>
       </c>
       <c r="G440" s="2" t="s">
         <v>15</v>
@@ -32750,7 +32750,7 @@
         <v>14</v>
       </c>
       <c r="F441" s="2">
-        <v>3557</v>
+        <v>2767</v>
       </c>
       <c r="G441" s="2" t="s">
         <v>15</v>
@@ -32782,7 +32782,7 @@
         <v>14</v>
       </c>
       <c r="F442" s="2">
-        <v>4217</v>
+        <v>2625</v>
       </c>
       <c r="G442" s="2" t="s">
         <v>15</v>
@@ -32814,7 +32814,7 @@
         <v>14</v>
       </c>
       <c r="F443" s="2">
-        <v>3114</v>
+        <v>3004</v>
       </c>
       <c r="G443" s="2" t="s">
         <v>15</v>
@@ -32846,7 +32846,7 @@
         <v>14</v>
       </c>
       <c r="F444" s="2">
-        <v>3676</v>
+        <v>4161</v>
       </c>
       <c r="G444" s="2" t="s">
         <v>15</v>
@@ -32878,7 +32878,7 @@
         <v>14</v>
       </c>
       <c r="F445" s="2">
-        <v>4321</v>
+        <v>2282</v>
       </c>
       <c r="G445" s="2" t="s">
         <v>15</v>
@@ -32910,7 +32910,7 @@
         <v>14</v>
       </c>
       <c r="F446" s="2">
-        <v>4501</v>
+        <v>4669</v>
       </c>
       <c r="G446" s="2" t="s">
         <v>15</v>
@@ -32942,7 +32942,7 @@
         <v>14</v>
       </c>
       <c r="F447" s="2">
-        <v>1468</v>
+        <v>2402</v>
       </c>
       <c r="G447" s="2" t="s">
         <v>15</v>
@@ -32974,7 +32974,7 @@
         <v>14</v>
       </c>
       <c r="F448" s="2">
-        <v>3861</v>
+        <v>4396</v>
       </c>
       <c r="G448" s="2" t="s">
         <v>15</v>
@@ -33006,7 +33006,7 @@
         <v>14</v>
       </c>
       <c r="F449" s="2">
-        <v>3172</v>
+        <v>3518</v>
       </c>
       <c r="G449" s="2" t="s">
         <v>15</v>
@@ -33038,7 +33038,7 @@
         <v>14</v>
       </c>
       <c r="F450" s="2">
-        <v>1535</v>
+        <v>4164</v>
       </c>
       <c r="G450" s="2" t="s">
         <v>15</v>
@@ -33070,7 +33070,7 @@
         <v>14</v>
       </c>
       <c r="F451" s="2">
-        <v>3165</v>
+        <v>3059</v>
       </c>
       <c r="G451" s="2" t="s">
         <v>15</v>
@@ -33102,7 +33102,7 @@
         <v>14</v>
       </c>
       <c r="F452" s="2">
-        <v>4614</v>
+        <v>1455</v>
       </c>
       <c r="G452" s="2" t="s">
         <v>15</v>
@@ -33134,7 +33134,7 @@
         <v>14</v>
       </c>
       <c r="F453" s="2">
-        <v>1847</v>
+        <v>2037</v>
       </c>
       <c r="G453" s="2" t="s">
         <v>15</v>
@@ -33166,7 +33166,7 @@
         <v>14</v>
       </c>
       <c r="F454" s="2">
-        <v>4071</v>
+        <v>4117</v>
       </c>
       <c r="G454" s="2" t="s">
         <v>15</v>
@@ -33198,7 +33198,7 @@
         <v>14</v>
       </c>
       <c r="F455" s="2">
-        <v>3007</v>
+        <v>866</v>
       </c>
       <c r="G455" s="2" t="s">
         <v>15</v>
@@ -33230,7 +33230,7 @@
         <v>14</v>
       </c>
       <c r="F456" s="2">
-        <v>3839</v>
+        <v>1543</v>
       </c>
       <c r="G456" s="2" t="s">
         <v>15</v>
@@ -33262,7 +33262,7 @@
         <v>14</v>
       </c>
       <c r="F457" s="2">
-        <v>3081</v>
+        <v>4740</v>
       </c>
       <c r="G457" s="2" t="s">
         <v>15</v>
@@ -33294,7 +33294,7 @@
         <v>14</v>
       </c>
       <c r="F458" s="2">
-        <v>4185</v>
+        <v>3691</v>
       </c>
       <c r="G458" s="2" t="s">
         <v>15</v>
@@ -33326,7 +33326,7 @@
         <v>14</v>
       </c>
       <c r="F459" s="2">
-        <v>1684</v>
+        <v>2319</v>
       </c>
       <c r="G459" s="2" t="s">
         <v>15</v>
@@ -33358,7 +33358,7 @@
         <v>14</v>
       </c>
       <c r="F460" s="2">
-        <v>3991</v>
+        <v>3559</v>
       </c>
       <c r="G460" s="2" t="s">
         <v>15</v>
@@ -33390,7 +33390,7 @@
         <v>14</v>
       </c>
       <c r="F461" s="2">
-        <v>3166</v>
+        <v>4066</v>
       </c>
       <c r="G461" s="2" t="s">
         <v>15</v>
@@ -33422,7 +33422,7 @@
         <v>14</v>
       </c>
       <c r="F462" s="2">
-        <v>2123</v>
+        <v>1124</v>
       </c>
       <c r="G462" s="2" t="s">
         <v>15</v>
@@ -33454,7 +33454,7 @@
         <v>14</v>
       </c>
       <c r="F463" s="2">
-        <v>1214</v>
+        <v>3755</v>
       </c>
       <c r="G463" s="2" t="s">
         <v>15</v>
@@ -33486,7 +33486,7 @@
         <v>14</v>
       </c>
       <c r="F464" s="2">
-        <v>3887</v>
+        <v>2214</v>
       </c>
       <c r="G464" s="2" t="s">
         <v>15</v>
@@ -33518,7 +33518,7 @@
         <v>14</v>
       </c>
       <c r="F465" s="2">
-        <v>1767</v>
+        <v>3316</v>
       </c>
       <c r="G465" s="2" t="s">
         <v>15</v>
@@ -33550,7 +33550,7 @@
         <v>14</v>
       </c>
       <c r="F466" s="2">
-        <v>3940</v>
+        <v>3822</v>
       </c>
       <c r="G466" s="2" t="s">
         <v>15</v>
@@ -33582,7 +33582,7 @@
         <v>14</v>
       </c>
       <c r="F467" s="2">
-        <v>2339</v>
+        <v>4759</v>
       </c>
       <c r="G467" s="2" t="s">
         <v>15</v>
@@ -33614,7 +33614,7 @@
         <v>14</v>
       </c>
       <c r="F468" s="2">
-        <v>3324</v>
+        <v>4491</v>
       </c>
       <c r="G468" s="2" t="s">
         <v>15</v>
@@ -33646,7 +33646,7 @@
         <v>14</v>
       </c>
       <c r="F469" s="2">
-        <v>1123</v>
+        <v>3244</v>
       </c>
       <c r="G469" s="2" t="s">
         <v>15</v>
@@ -33678,7 +33678,7 @@
         <v>14</v>
       </c>
       <c r="F470" s="2">
-        <v>2371</v>
+        <v>1088</v>
       </c>
       <c r="G470" s="2" t="s">
         <v>15</v>
@@ -33710,7 +33710,7 @@
         <v>14</v>
       </c>
       <c r="F471" s="2">
-        <v>2769</v>
+        <v>2200</v>
       </c>
       <c r="G471" s="2" t="s">
         <v>15</v>

--- a/reports/selenium/latest/excel/Automation_Test_Report.xlsx
+++ b/reports/selenium/latest/excel/Automation_Test_Report.xlsx
@@ -3084,7 +3084,7 @@
     <t>Build</t>
   </si>
   <si>
-    <t>4</t>
+    <t>5</t>
   </si>
   <si>
     <t>Branch</t>
@@ -3096,13 +3096,13 @@
     <t>Commit</t>
   </si>
   <si>
-    <t>ecf58600aa47</t>
+    <t>bbcb82d96eb7</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T15:22:34.008Z</t>
+    <t>2026-08-18T15:32:38.948Z</t>
   </si>
   <si>
     <t>Browser</t>
@@ -3607,7 +3607,7 @@
         <v>14</v>
       </c>
       <c r="F2" s="2">
-        <v>3236</v>
+        <v>1892</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>15</v>
@@ -3639,7 +3639,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="2">
-        <v>2390</v>
+        <v>2657</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>15</v>
@@ -3671,7 +3671,7 @@
         <v>14</v>
       </c>
       <c r="F4" s="2">
-        <v>1290</v>
+        <v>3833</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
@@ -3703,7 +3703,7 @@
         <v>14</v>
       </c>
       <c r="F5" s="2">
-        <v>2447</v>
+        <v>1342</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
@@ -3735,7 +3735,7 @@
         <v>14</v>
       </c>
       <c r="F6" s="2">
-        <v>2634</v>
+        <v>4717</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -3767,7 +3767,7 @@
         <v>14</v>
       </c>
       <c r="F7" s="2">
-        <v>4151</v>
+        <v>2841</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -3799,7 +3799,7 @@
         <v>14</v>
       </c>
       <c r="F8" s="2">
-        <v>3490</v>
+        <v>3928</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -3831,7 +3831,7 @@
         <v>14</v>
       </c>
       <c r="F9" s="2">
-        <v>1780</v>
+        <v>1358</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -3863,7 +3863,7 @@
         <v>14</v>
       </c>
       <c r="F10" s="2">
-        <v>2604</v>
+        <v>2120</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
@@ -3895,7 +3895,7 @@
         <v>14</v>
       </c>
       <c r="F11" s="2">
-        <v>2651</v>
+        <v>1911</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
@@ -3927,7 +3927,7 @@
         <v>14</v>
       </c>
       <c r="F12" s="2">
-        <v>3166</v>
+        <v>4341</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
@@ -3959,7 +3959,7 @@
         <v>14</v>
       </c>
       <c r="F13" s="2">
-        <v>3430</v>
+        <v>1350</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -3991,7 +3991,7 @@
         <v>14</v>
       </c>
       <c r="F14" s="2">
-        <v>2399</v>
+        <v>1818</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -4023,7 +4023,7 @@
         <v>14</v>
       </c>
       <c r="F15" s="2">
-        <v>4216</v>
+        <v>3111</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -4055,7 +4055,7 @@
         <v>14</v>
       </c>
       <c r="F16" s="2">
-        <v>3401</v>
+        <v>3406</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
@@ -4087,7 +4087,7 @@
         <v>14</v>
       </c>
       <c r="F17" s="2">
-        <v>1180</v>
+        <v>1441</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
@@ -4119,7 +4119,7 @@
         <v>14</v>
       </c>
       <c r="F18" s="2">
-        <v>2413</v>
+        <v>1774</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
@@ -4151,7 +4151,7 @@
         <v>14</v>
       </c>
       <c r="F19" s="2">
-        <v>4102</v>
+        <v>4142</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
@@ -4183,7 +4183,7 @@
         <v>14</v>
       </c>
       <c r="F20" s="2">
-        <v>2171</v>
+        <v>4517</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
@@ -4215,7 +4215,7 @@
         <v>14</v>
       </c>
       <c r="F21" s="2">
-        <v>2909</v>
+        <v>3005</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -4247,7 +4247,7 @@
         <v>14</v>
       </c>
       <c r="F22" s="2">
-        <v>1555</v>
+        <v>2613</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -4279,7 +4279,7 @@
         <v>14</v>
       </c>
       <c r="F23" s="2">
-        <v>4424</v>
+        <v>1642</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -4311,7 +4311,7 @@
         <v>14</v>
       </c>
       <c r="F24" s="2">
-        <v>3598</v>
+        <v>931</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -4343,7 +4343,7 @@
         <v>14</v>
       </c>
       <c r="F25" s="2">
-        <v>1832</v>
+        <v>3439</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -4375,7 +4375,7 @@
         <v>14</v>
       </c>
       <c r="F26" s="2">
-        <v>4454</v>
+        <v>3388</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -4407,7 +4407,7 @@
         <v>14</v>
       </c>
       <c r="F27" s="2">
-        <v>3734</v>
+        <v>3024</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>15</v>
@@ -4439,7 +4439,7 @@
         <v>14</v>
       </c>
       <c r="F28" s="2">
-        <v>2823</v>
+        <v>3016</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>15</v>
@@ -4471,7 +4471,7 @@
         <v>14</v>
       </c>
       <c r="F29" s="2">
-        <v>4784</v>
+        <v>3449</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>15</v>
@@ -4503,7 +4503,7 @@
         <v>14</v>
       </c>
       <c r="F30" s="2">
-        <v>3944</v>
+        <v>3286</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>15</v>
@@ -4535,7 +4535,7 @@
         <v>14</v>
       </c>
       <c r="F31" s="2">
-        <v>3950</v>
+        <v>3852</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>15</v>
@@ -4567,7 +4567,7 @@
         <v>14</v>
       </c>
       <c r="F32" s="2">
-        <v>3963</v>
+        <v>2881</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>15</v>
@@ -4599,7 +4599,7 @@
         <v>14</v>
       </c>
       <c r="F33" s="2">
-        <v>1782</v>
+        <v>4283</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>15</v>
@@ -4631,7 +4631,7 @@
         <v>14</v>
       </c>
       <c r="F34" s="2">
-        <v>1097</v>
+        <v>4255</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>15</v>
@@ -4663,7 +4663,7 @@
         <v>14</v>
       </c>
       <c r="F35" s="2">
-        <v>2200</v>
+        <v>3792</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>15</v>
@@ -4695,7 +4695,7 @@
         <v>14</v>
       </c>
       <c r="F36" s="2">
-        <v>3148</v>
+        <v>2822</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>15</v>
@@ -4727,7 +4727,7 @@
         <v>14</v>
       </c>
       <c r="F37" s="2">
-        <v>1393</v>
+        <v>1463</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>15</v>
@@ -4759,7 +4759,7 @@
         <v>14</v>
       </c>
       <c r="F38" s="2">
-        <v>2720</v>
+        <v>3017</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>15</v>
@@ -4791,7 +4791,7 @@
         <v>14</v>
       </c>
       <c r="F39" s="2">
-        <v>1019</v>
+        <v>3465</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>15</v>
@@ -4823,7 +4823,7 @@
         <v>14</v>
       </c>
       <c r="F40" s="2">
-        <v>1657</v>
+        <v>3879</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>15</v>
@@ -4855,7 +4855,7 @@
         <v>14</v>
       </c>
       <c r="F41" s="2">
-        <v>2664</v>
+        <v>3672</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>15</v>
@@ -4887,7 +4887,7 @@
         <v>14</v>
       </c>
       <c r="F42" s="2">
-        <v>4219</v>
+        <v>2689</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>15</v>
@@ -4919,7 +4919,7 @@
         <v>14</v>
       </c>
       <c r="F43" s="2">
-        <v>4725</v>
+        <v>3522</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>15</v>
@@ -4951,7 +4951,7 @@
         <v>14</v>
       </c>
       <c r="F44" s="2">
-        <v>2732</v>
+        <v>3834</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>15</v>
@@ -4983,7 +4983,7 @@
         <v>14</v>
       </c>
       <c r="F45" s="2">
-        <v>2402</v>
+        <v>3772</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>15</v>
@@ -5015,7 +5015,7 @@
         <v>14</v>
       </c>
       <c r="F46" s="2">
-        <v>4693</v>
+        <v>3585</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>15</v>
@@ -5047,7 +5047,7 @@
         <v>14</v>
       </c>
       <c r="F47" s="2">
-        <v>3033</v>
+        <v>2015</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>15</v>
@@ -5079,7 +5079,7 @@
         <v>14</v>
       </c>
       <c r="F48" s="2">
-        <v>3664</v>
+        <v>2760</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>15</v>
@@ -5111,7 +5111,7 @@
         <v>14</v>
       </c>
       <c r="F49" s="2">
-        <v>2465</v>
+        <v>1637</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>15</v>
@@ -5143,7 +5143,7 @@
         <v>14</v>
       </c>
       <c r="F50" s="2">
-        <v>4670</v>
+        <v>4671</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>15</v>
@@ -5175,7 +5175,7 @@
         <v>14</v>
       </c>
       <c r="F51" s="2">
-        <v>3343</v>
+        <v>1390</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>15</v>
@@ -5207,7 +5207,7 @@
         <v>14</v>
       </c>
       <c r="F52" s="2">
-        <v>2369</v>
+        <v>4759</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>15</v>
@@ -5239,7 +5239,7 @@
         <v>14</v>
       </c>
       <c r="F53" s="2">
-        <v>2569</v>
+        <v>3541</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>15</v>
@@ -5271,7 +5271,7 @@
         <v>14</v>
       </c>
       <c r="F54" s="2">
-        <v>4740</v>
+        <v>895</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>15</v>
@@ -5303,7 +5303,7 @@
         <v>14</v>
       </c>
       <c r="F55" s="2">
-        <v>4393</v>
+        <v>1575</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>15</v>
@@ -5335,7 +5335,7 @@
         <v>14</v>
       </c>
       <c r="F56" s="2">
-        <v>3464</v>
+        <v>2775</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>15</v>
@@ -5367,7 +5367,7 @@
         <v>14</v>
       </c>
       <c r="F57" s="2">
-        <v>3370</v>
+        <v>4469</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>15</v>
@@ -5399,7 +5399,7 @@
         <v>14</v>
       </c>
       <c r="F58" s="2">
-        <v>1863</v>
+        <v>3476</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>15</v>
@@ -5431,7 +5431,7 @@
         <v>14</v>
       </c>
       <c r="F59" s="2">
-        <v>2116</v>
+        <v>3274</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>15</v>
@@ -5463,7 +5463,7 @@
         <v>14</v>
       </c>
       <c r="F60" s="2">
-        <v>3820</v>
+        <v>2840</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>15</v>
@@ -5495,7 +5495,7 @@
         <v>14</v>
       </c>
       <c r="F61" s="2">
-        <v>1146</v>
+        <v>3867</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>15</v>
@@ -5527,7 +5527,7 @@
         <v>14</v>
       </c>
       <c r="F62" s="2">
-        <v>4759</v>
+        <v>2552</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>15</v>
@@ -5559,7 +5559,7 @@
         <v>14</v>
       </c>
       <c r="F63" s="2">
-        <v>3694</v>
+        <v>1122</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>15</v>
@@ -5591,7 +5591,7 @@
         <v>14</v>
       </c>
       <c r="F64" s="2">
-        <v>844</v>
+        <v>3103</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>15</v>
@@ -5623,7 +5623,7 @@
         <v>14</v>
       </c>
       <c r="F65" s="2">
-        <v>1944</v>
+        <v>4147</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>15</v>
@@ -5655,7 +5655,7 @@
         <v>14</v>
       </c>
       <c r="F66" s="2">
-        <v>2716</v>
+        <v>2349</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>15</v>
@@ -5687,7 +5687,7 @@
         <v>14</v>
       </c>
       <c r="F67" s="2">
-        <v>867</v>
+        <v>2928</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>15</v>
@@ -5719,7 +5719,7 @@
         <v>14</v>
       </c>
       <c r="F68" s="2">
-        <v>1814</v>
+        <v>3240</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>15</v>
@@ -5751,7 +5751,7 @@
         <v>14</v>
       </c>
       <c r="F69" s="2">
-        <v>3832</v>
+        <v>2796</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>15</v>
@@ -5783,7 +5783,7 @@
         <v>14</v>
       </c>
       <c r="F70" s="2">
-        <v>2673</v>
+        <v>4548</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>15</v>
@@ -5815,7 +5815,7 @@
         <v>14</v>
       </c>
       <c r="F71" s="2">
-        <v>2784</v>
+        <v>871</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>15</v>
@@ -5847,7 +5847,7 @@
         <v>14</v>
       </c>
       <c r="F72" s="2">
-        <v>1651</v>
+        <v>2941</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>15</v>
@@ -5879,7 +5879,7 @@
         <v>14</v>
       </c>
       <c r="F73" s="2">
-        <v>2179</v>
+        <v>3912</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>15</v>
@@ -5911,7 +5911,7 @@
         <v>14</v>
       </c>
       <c r="F74" s="2">
-        <v>4617</v>
+        <v>3196</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>15</v>
@@ -5943,7 +5943,7 @@
         <v>14</v>
       </c>
       <c r="F75" s="2">
-        <v>2085</v>
+        <v>3252</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>15</v>
@@ -5975,7 +5975,7 @@
         <v>14</v>
       </c>
       <c r="F76" s="2">
-        <v>3037</v>
+        <v>1264</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>15</v>
@@ -6007,7 +6007,7 @@
         <v>14</v>
       </c>
       <c r="F77" s="2">
-        <v>1990</v>
+        <v>1210</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>15</v>
@@ -6039,7 +6039,7 @@
         <v>14</v>
       </c>
       <c r="F78" s="2">
-        <v>3375</v>
+        <v>2679</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>15</v>
@@ -6071,7 +6071,7 @@
         <v>14</v>
       </c>
       <c r="F79" s="2">
-        <v>1294</v>
+        <v>2679</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>15</v>
@@ -6103,7 +6103,7 @@
         <v>14</v>
       </c>
       <c r="F80" s="2">
-        <v>3849</v>
+        <v>4275</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>15</v>
@@ -6135,7 +6135,7 @@
         <v>14</v>
       </c>
       <c r="F81" s="2">
-        <v>4284</v>
+        <v>2458</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>15</v>
@@ -6167,7 +6167,7 @@
         <v>14</v>
       </c>
       <c r="F82" s="2">
-        <v>2838</v>
+        <v>1359</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>15</v>
@@ -6199,7 +6199,7 @@
         <v>14</v>
       </c>
       <c r="F83" s="2">
-        <v>2512</v>
+        <v>1899</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>15</v>
@@ -6231,7 +6231,7 @@
         <v>14</v>
       </c>
       <c r="F84" s="2">
-        <v>4195</v>
+        <v>3909</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>15</v>
@@ -6263,7 +6263,7 @@
         <v>14</v>
       </c>
       <c r="F85" s="2">
-        <v>3131</v>
+        <v>4388</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>15</v>
@@ -6295,7 +6295,7 @@
         <v>14</v>
       </c>
       <c r="F86" s="2">
-        <v>1303</v>
+        <v>3797</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>15</v>
@@ -6327,7 +6327,7 @@
         <v>14</v>
       </c>
       <c r="F87" s="2">
-        <v>4743</v>
+        <v>2659</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>15</v>
@@ -6359,7 +6359,7 @@
         <v>14</v>
       </c>
       <c r="F88" s="2">
-        <v>2096</v>
+        <v>2596</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>15</v>
@@ -6391,7 +6391,7 @@
         <v>14</v>
       </c>
       <c r="F89" s="2">
-        <v>1067</v>
+        <v>3583</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>15</v>
@@ -6423,7 +6423,7 @@
         <v>14</v>
       </c>
       <c r="F90" s="2">
-        <v>2068</v>
+        <v>4453</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>15</v>
@@ -6455,7 +6455,7 @@
         <v>14</v>
       </c>
       <c r="F91" s="2">
-        <v>3691</v>
+        <v>3852</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>15</v>
@@ -6487,7 +6487,7 @@
         <v>14</v>
       </c>
       <c r="F92" s="2">
-        <v>4399</v>
+        <v>2716</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>15</v>
@@ -6519,7 +6519,7 @@
         <v>14</v>
       </c>
       <c r="F93" s="2">
-        <v>4601</v>
+        <v>4512</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>15</v>
@@ -6551,7 +6551,7 @@
         <v>14</v>
       </c>
       <c r="F94" s="2">
-        <v>3681</v>
+        <v>3503</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>15</v>
@@ -6583,7 +6583,7 @@
         <v>14</v>
       </c>
       <c r="F95" s="2">
-        <v>4175</v>
+        <v>1796</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>15</v>
@@ -6615,7 +6615,7 @@
         <v>14</v>
       </c>
       <c r="F96" s="2">
-        <v>1519</v>
+        <v>3640</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>15</v>
@@ -6647,7 +6647,7 @@
         <v>14</v>
       </c>
       <c r="F97" s="2">
-        <v>2362</v>
+        <v>3357</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>15</v>
@@ -6679,7 +6679,7 @@
         <v>14</v>
       </c>
       <c r="F98" s="2">
-        <v>2818</v>
+        <v>1280</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>15</v>
@@ -6711,7 +6711,7 @@
         <v>14</v>
       </c>
       <c r="F99" s="2">
-        <v>1398</v>
+        <v>4473</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>15</v>
@@ -6743,7 +6743,7 @@
         <v>14</v>
       </c>
       <c r="F100" s="2">
-        <v>4780</v>
+        <v>3644</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>15</v>
@@ -6775,7 +6775,7 @@
         <v>14</v>
       </c>
       <c r="F101" s="2">
-        <v>4460</v>
+        <v>3736</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>15</v>
@@ -6807,7 +6807,7 @@
         <v>14</v>
       </c>
       <c r="F102" s="2">
-        <v>4603</v>
+        <v>3532</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>15</v>
@@ -6839,7 +6839,7 @@
         <v>14</v>
       </c>
       <c r="F103" s="2">
-        <v>2372</v>
+        <v>4706</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>15</v>
@@ -6871,7 +6871,7 @@
         <v>14</v>
       </c>
       <c r="F104" s="2">
-        <v>2911</v>
+        <v>2716</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>15</v>
@@ -6903,7 +6903,7 @@
         <v>14</v>
       </c>
       <c r="F105" s="2">
-        <v>3770</v>
+        <v>4043</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>15</v>
@@ -6935,7 +6935,7 @@
         <v>14</v>
       </c>
       <c r="F106" s="2">
-        <v>2369</v>
+        <v>936</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>15</v>
@@ -6967,7 +6967,7 @@
         <v>14</v>
       </c>
       <c r="F107" s="2">
-        <v>1208</v>
+        <v>1887</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>15</v>
@@ -6999,7 +6999,7 @@
         <v>14</v>
       </c>
       <c r="F108" s="2">
-        <v>2582</v>
+        <v>4490</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>15</v>
@@ -7031,7 +7031,7 @@
         <v>14</v>
       </c>
       <c r="F109" s="2">
-        <v>3267</v>
+        <v>4322</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>15</v>
@@ -7063,7 +7063,7 @@
         <v>14</v>
       </c>
       <c r="F110" s="2">
-        <v>3069</v>
+        <v>3535</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>15</v>
@@ -7095,7 +7095,7 @@
         <v>14</v>
       </c>
       <c r="F111" s="2">
-        <v>1074</v>
+        <v>3636</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>15</v>
@@ -7127,7 +7127,7 @@
         <v>14</v>
       </c>
       <c r="F112" s="2">
-        <v>1364</v>
+        <v>3404</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>15</v>
@@ -7159,7 +7159,7 @@
         <v>14</v>
       </c>
       <c r="F113" s="2">
-        <v>2563</v>
+        <v>2371</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>15</v>
@@ -7191,7 +7191,7 @@
         <v>14</v>
       </c>
       <c r="F114" s="2">
-        <v>2698</v>
+        <v>2447</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>15</v>
@@ -7223,7 +7223,7 @@
         <v>14</v>
       </c>
       <c r="F115" s="2">
-        <v>1391</v>
+        <v>4309</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>15</v>
@@ -7255,7 +7255,7 @@
         <v>14</v>
       </c>
       <c r="F116" s="2">
-        <v>4641</v>
+        <v>2190</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>15</v>
@@ -7287,7 +7287,7 @@
         <v>14</v>
       </c>
       <c r="F117" s="2">
-        <v>4420</v>
+        <v>3354</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>15</v>
@@ -7319,7 +7319,7 @@
         <v>14</v>
       </c>
       <c r="F118" s="2">
-        <v>1535</v>
+        <v>2050</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>15</v>
@@ -7351,7 +7351,7 @@
         <v>14</v>
       </c>
       <c r="F119" s="2">
-        <v>3600</v>
+        <v>1811</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>15</v>
@@ -7383,7 +7383,7 @@
         <v>14</v>
       </c>
       <c r="F120" s="2">
-        <v>1416</v>
+        <v>3906</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>15</v>
@@ -7415,7 +7415,7 @@
         <v>14</v>
       </c>
       <c r="F121" s="2">
-        <v>1437</v>
+        <v>2582</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>15</v>
@@ -7447,7 +7447,7 @@
         <v>14</v>
       </c>
       <c r="F122" s="2">
-        <v>4612</v>
+        <v>4230</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>15</v>
@@ -7479,7 +7479,7 @@
         <v>14</v>
       </c>
       <c r="F123" s="2">
-        <v>2057</v>
+        <v>4282</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>15</v>
@@ -7511,7 +7511,7 @@
         <v>14</v>
       </c>
       <c r="F124" s="2">
-        <v>1616</v>
+        <v>2338</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>15</v>
@@ -7543,7 +7543,7 @@
         <v>14</v>
       </c>
       <c r="F125" s="2">
-        <v>2545</v>
+        <v>1894</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>15</v>
@@ -7575,7 +7575,7 @@
         <v>14</v>
       </c>
       <c r="F126" s="2">
-        <v>2754</v>
+        <v>1079</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>15</v>
@@ -7607,7 +7607,7 @@
         <v>14</v>
       </c>
       <c r="F127" s="2">
-        <v>4187</v>
+        <v>1441</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>15</v>
@@ -7639,7 +7639,7 @@
         <v>14</v>
       </c>
       <c r="F128" s="2">
-        <v>1658</v>
+        <v>4145</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>15</v>
@@ -7671,7 +7671,7 @@
         <v>14</v>
       </c>
       <c r="F129" s="2">
-        <v>1703</v>
+        <v>2952</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>15</v>
@@ -7703,7 +7703,7 @@
         <v>14</v>
       </c>
       <c r="F130" s="2">
-        <v>1639</v>
+        <v>4548</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>15</v>
@@ -7735,7 +7735,7 @@
         <v>14</v>
       </c>
       <c r="F131" s="2">
-        <v>3157</v>
+        <v>3228</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>15</v>
@@ -7767,7 +7767,7 @@
         <v>14</v>
       </c>
       <c r="F132" s="2">
-        <v>3685</v>
+        <v>2546</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>15</v>
@@ -7799,7 +7799,7 @@
         <v>14</v>
       </c>
       <c r="F133" s="2">
-        <v>3325</v>
+        <v>4333</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>15</v>
@@ -7831,7 +7831,7 @@
         <v>14</v>
       </c>
       <c r="F134" s="2">
-        <v>1491</v>
+        <v>2125</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>15</v>
@@ -7863,7 +7863,7 @@
         <v>14</v>
       </c>
       <c r="F135" s="2">
-        <v>2283</v>
+        <v>951</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>15</v>
@@ -7895,7 +7895,7 @@
         <v>14</v>
       </c>
       <c r="F136" s="2">
-        <v>1028</v>
+        <v>930</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>15</v>
@@ -7927,7 +7927,7 @@
         <v>14</v>
       </c>
       <c r="F137" s="2">
-        <v>2346</v>
+        <v>3971</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>15</v>
@@ -7959,7 +7959,7 @@
         <v>14</v>
       </c>
       <c r="F138" s="2">
-        <v>3119</v>
+        <v>3709</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>15</v>
@@ -7991,7 +7991,7 @@
         <v>14</v>
       </c>
       <c r="F139" s="2">
-        <v>3742</v>
+        <v>3733</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>15</v>
@@ -8023,7 +8023,7 @@
         <v>14</v>
       </c>
       <c r="F140" s="2">
-        <v>4486</v>
+        <v>2216</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>15</v>
@@ -8055,7 +8055,7 @@
         <v>14</v>
       </c>
       <c r="F141" s="2">
-        <v>4591</v>
+        <v>1067</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>15</v>
@@ -8087,7 +8087,7 @@
         <v>14</v>
       </c>
       <c r="F142" s="2">
-        <v>2170</v>
+        <v>4156</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>15</v>
@@ -8119,7 +8119,7 @@
         <v>14</v>
       </c>
       <c r="F143" s="2">
-        <v>1628</v>
+        <v>2000</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>15</v>
@@ -8151,7 +8151,7 @@
         <v>14</v>
       </c>
       <c r="F144" s="2">
-        <v>3752</v>
+        <v>1901</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>15</v>
@@ -8183,7 +8183,7 @@
         <v>14</v>
       </c>
       <c r="F145" s="2">
-        <v>1819</v>
+        <v>4351</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>15</v>
@@ -8215,7 +8215,7 @@
         <v>14</v>
       </c>
       <c r="F146" s="2">
-        <v>2297</v>
+        <v>1911</v>
       </c>
       <c r="G146" s="2" t="s">
         <v>15</v>
@@ -8247,7 +8247,7 @@
         <v>14</v>
       </c>
       <c r="F147" s="2">
-        <v>1419</v>
+        <v>4677</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>15</v>
@@ -8279,7 +8279,7 @@
         <v>14</v>
       </c>
       <c r="F148" s="2">
-        <v>1419</v>
+        <v>3896</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>15</v>
@@ -8311,7 +8311,7 @@
         <v>14</v>
       </c>
       <c r="F149" s="2">
-        <v>3850</v>
+        <v>1015</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>15</v>
@@ -8343,7 +8343,7 @@
         <v>14</v>
       </c>
       <c r="F150" s="2">
-        <v>4225</v>
+        <v>1233</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>15</v>
@@ -8375,7 +8375,7 @@
         <v>14</v>
       </c>
       <c r="F151" s="2">
-        <v>1628</v>
+        <v>1168</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>15</v>
@@ -8407,7 +8407,7 @@
         <v>14</v>
       </c>
       <c r="F152" s="2">
-        <v>2305</v>
+        <v>1687</v>
       </c>
       <c r="G152" s="2" t="s">
         <v>15</v>
@@ -8439,7 +8439,7 @@
         <v>14</v>
       </c>
       <c r="F153" s="2">
-        <v>2293</v>
+        <v>3482</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>15</v>
@@ -8471,7 +8471,7 @@
         <v>14</v>
       </c>
       <c r="F154" s="2">
-        <v>4491</v>
+        <v>4002</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>15</v>
@@ -8503,7 +8503,7 @@
         <v>14</v>
       </c>
       <c r="F155" s="2">
-        <v>1082</v>
+        <v>3815</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>15</v>
@@ -8535,7 +8535,7 @@
         <v>14</v>
       </c>
       <c r="F156" s="2">
-        <v>4596</v>
+        <v>1535</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>15</v>
@@ -8567,7 +8567,7 @@
         <v>14</v>
       </c>
       <c r="F157" s="2">
-        <v>1814</v>
+        <v>858</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>15</v>
@@ -8599,7 +8599,7 @@
         <v>14</v>
       </c>
       <c r="F158" s="2">
-        <v>1428</v>
+        <v>4236</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>15</v>
@@ -8631,7 +8631,7 @@
         <v>14</v>
       </c>
       <c r="F159" s="2">
-        <v>4172</v>
+        <v>4310</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>15</v>
@@ -8663,7 +8663,7 @@
         <v>14</v>
       </c>
       <c r="F160" s="2">
-        <v>3548</v>
+        <v>2367</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>15</v>
@@ -8695,7 +8695,7 @@
         <v>14</v>
       </c>
       <c r="F161" s="2">
-        <v>1339</v>
+        <v>909</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>15</v>
@@ -8727,7 +8727,7 @@
         <v>14</v>
       </c>
       <c r="F162" s="2">
-        <v>3106</v>
+        <v>3832</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>15</v>
@@ -8759,7 +8759,7 @@
         <v>14</v>
       </c>
       <c r="F163" s="2">
-        <v>863</v>
+        <v>4270</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>15</v>
@@ -8791,7 +8791,7 @@
         <v>14</v>
       </c>
       <c r="F164" s="2">
-        <v>3795</v>
+        <v>1176</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>15</v>
@@ -8823,7 +8823,7 @@
         <v>14</v>
       </c>
       <c r="F165" s="2">
-        <v>3434</v>
+        <v>3931</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>15</v>
@@ -8855,7 +8855,7 @@
         <v>14</v>
       </c>
       <c r="F166" s="2">
-        <v>4229</v>
+        <v>855</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>15</v>
@@ -8887,7 +8887,7 @@
         <v>14</v>
       </c>
       <c r="F167" s="2">
-        <v>2856</v>
+        <v>3118</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>15</v>
@@ -8919,7 +8919,7 @@
         <v>14</v>
       </c>
       <c r="F168" s="2">
-        <v>3959</v>
+        <v>1339</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>15</v>
@@ -8951,7 +8951,7 @@
         <v>14</v>
       </c>
       <c r="F169" s="2">
-        <v>2814</v>
+        <v>4456</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>15</v>
@@ -8983,7 +8983,7 @@
         <v>14</v>
       </c>
       <c r="F170" s="2">
-        <v>3407</v>
+        <v>3038</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>15</v>
@@ -9015,7 +9015,7 @@
         <v>14</v>
       </c>
       <c r="F171" s="2">
-        <v>1464</v>
+        <v>4012</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>15</v>
@@ -9047,7 +9047,7 @@
         <v>14</v>
       </c>
       <c r="F172" s="2">
-        <v>4551</v>
+        <v>2879</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>15</v>
@@ -9079,7 +9079,7 @@
         <v>14</v>
       </c>
       <c r="F173" s="2">
-        <v>1316</v>
+        <v>4487</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>15</v>
@@ -9111,7 +9111,7 @@
         <v>14</v>
       </c>
       <c r="F174" s="2">
-        <v>3808</v>
+        <v>2318</v>
       </c>
       <c r="G174" s="2" t="s">
         <v>15</v>
@@ -9143,7 +9143,7 @@
         <v>14</v>
       </c>
       <c r="F175" s="2">
-        <v>2115</v>
+        <v>2338</v>
       </c>
       <c r="G175" s="2" t="s">
         <v>15</v>
@@ -9175,7 +9175,7 @@
         <v>14</v>
       </c>
       <c r="F176" s="2">
-        <v>1113</v>
+        <v>3218</v>
       </c>
       <c r="G176" s="2" t="s">
         <v>15</v>
@@ -9207,7 +9207,7 @@
         <v>14</v>
       </c>
       <c r="F177" s="2">
-        <v>2158</v>
+        <v>4270</v>
       </c>
       <c r="G177" s="2" t="s">
         <v>15</v>
@@ -9239,7 +9239,7 @@
         <v>14</v>
       </c>
       <c r="F178" s="2">
-        <v>4664</v>
+        <v>2323</v>
       </c>
       <c r="G178" s="2" t="s">
         <v>15</v>
@@ -9271,7 +9271,7 @@
         <v>14</v>
       </c>
       <c r="F179" s="2">
-        <v>941</v>
+        <v>2073</v>
       </c>
       <c r="G179" s="2" t="s">
         <v>15</v>
@@ -9303,7 +9303,7 @@
         <v>14</v>
       </c>
       <c r="F180" s="2">
-        <v>816</v>
+        <v>2820</v>
       </c>
       <c r="G180" s="2" t="s">
         <v>15</v>
@@ -9335,7 +9335,7 @@
         <v>14</v>
       </c>
       <c r="F181" s="2">
-        <v>4545</v>
+        <v>4567</v>
       </c>
       <c r="G181" s="2" t="s">
         <v>15</v>
@@ -9367,7 +9367,7 @@
         <v>14</v>
       </c>
       <c r="F182" s="2">
-        <v>3551</v>
+        <v>1004</v>
       </c>
       <c r="G182" s="2" t="s">
         <v>15</v>
@@ -9399,7 +9399,7 @@
         <v>14</v>
       </c>
       <c r="F183" s="2">
-        <v>4786</v>
+        <v>3521</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>15</v>
@@ -9431,7 +9431,7 @@
         <v>14</v>
       </c>
       <c r="F184" s="2">
-        <v>2260</v>
+        <v>3340</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>15</v>
@@ -9463,7 +9463,7 @@
         <v>14</v>
       </c>
       <c r="F185" s="2">
-        <v>3813</v>
+        <v>1381</v>
       </c>
       <c r="G185" s="2" t="s">
         <v>15</v>
@@ -9495,7 +9495,7 @@
         <v>14</v>
       </c>
       <c r="F186" s="2">
-        <v>2905</v>
+        <v>2213</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>15</v>
@@ -9527,7 +9527,7 @@
         <v>14</v>
       </c>
       <c r="F187" s="2">
-        <v>1535</v>
+        <v>2486</v>
       </c>
       <c r="G187" s="2" t="s">
         <v>15</v>
@@ -9559,7 +9559,7 @@
         <v>14</v>
       </c>
       <c r="F188" s="2">
-        <v>1801</v>
+        <v>2927</v>
       </c>
       <c r="G188" s="2" t="s">
         <v>15</v>
@@ -9591,7 +9591,7 @@
         <v>14</v>
       </c>
       <c r="F189" s="2">
-        <v>3161</v>
+        <v>1799</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>15</v>
@@ -9623,7 +9623,7 @@
         <v>14</v>
       </c>
       <c r="F190" s="2">
-        <v>2613</v>
+        <v>2840</v>
       </c>
       <c r="G190" s="2" t="s">
         <v>15</v>
@@ -9655,7 +9655,7 @@
         <v>14</v>
       </c>
       <c r="F191" s="2">
-        <v>1688</v>
+        <v>4130</v>
       </c>
       <c r="G191" s="2" t="s">
         <v>15</v>
@@ -9687,7 +9687,7 @@
         <v>14</v>
       </c>
       <c r="F192" s="2">
-        <v>3561</v>
+        <v>3410</v>
       </c>
       <c r="G192" s="2" t="s">
         <v>15</v>
@@ -9719,7 +9719,7 @@
         <v>14</v>
       </c>
       <c r="F193" s="2">
-        <v>1151</v>
+        <v>2684</v>
       </c>
       <c r="G193" s="2" t="s">
         <v>15</v>
@@ -9751,7 +9751,7 @@
         <v>14</v>
       </c>
       <c r="F194" s="2">
-        <v>2144</v>
+        <v>2487</v>
       </c>
       <c r="G194" s="2" t="s">
         <v>15</v>
@@ -9783,7 +9783,7 @@
         <v>14</v>
       </c>
       <c r="F195" s="2">
-        <v>3735</v>
+        <v>4360</v>
       </c>
       <c r="G195" s="2" t="s">
         <v>15</v>
@@ -9815,7 +9815,7 @@
         <v>14</v>
       </c>
       <c r="F196" s="2">
-        <v>2046</v>
+        <v>1653</v>
       </c>
       <c r="G196" s="2" t="s">
         <v>15</v>
@@ -9847,7 +9847,7 @@
         <v>14</v>
       </c>
       <c r="F197" s="2">
-        <v>4527</v>
+        <v>4264</v>
       </c>
       <c r="G197" s="2" t="s">
         <v>15</v>
@@ -9879,7 +9879,7 @@
         <v>14</v>
       </c>
       <c r="F198" s="2">
-        <v>1832</v>
+        <v>3985</v>
       </c>
       <c r="G198" s="2" t="s">
         <v>15</v>
@@ -9911,7 +9911,7 @@
         <v>14</v>
       </c>
       <c r="F199" s="2">
-        <v>2561</v>
+        <v>1090</v>
       </c>
       <c r="G199" s="2" t="s">
         <v>15</v>
@@ -9943,7 +9943,7 @@
         <v>14</v>
       </c>
       <c r="F200" s="2">
-        <v>4254</v>
+        <v>2242</v>
       </c>
       <c r="G200" s="2" t="s">
         <v>15</v>
@@ -9975,7 +9975,7 @@
         <v>14</v>
       </c>
       <c r="F201" s="2">
-        <v>2891</v>
+        <v>4210</v>
       </c>
       <c r="G201" s="2" t="s">
         <v>15</v>
@@ -10007,7 +10007,7 @@
         <v>14</v>
       </c>
       <c r="F202" s="2">
-        <v>2518</v>
+        <v>3822</v>
       </c>
       <c r="G202" s="2" t="s">
         <v>15</v>
@@ -10039,7 +10039,7 @@
         <v>14</v>
       </c>
       <c r="F203" s="2">
-        <v>2014</v>
+        <v>1669</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>15</v>
@@ -10071,7 +10071,7 @@
         <v>14</v>
       </c>
       <c r="F204" s="2">
-        <v>3477</v>
+        <v>1162</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>15</v>
@@ -10103,7 +10103,7 @@
         <v>14</v>
       </c>
       <c r="F205" s="2">
-        <v>2222</v>
+        <v>3098</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>15</v>
@@ -10135,7 +10135,7 @@
         <v>14</v>
       </c>
       <c r="F206" s="2">
-        <v>4716</v>
+        <v>2630</v>
       </c>
       <c r="G206" s="2" t="s">
         <v>15</v>
@@ -10167,7 +10167,7 @@
         <v>14</v>
       </c>
       <c r="F207" s="2">
-        <v>1067</v>
+        <v>3207</v>
       </c>
       <c r="G207" s="2" t="s">
         <v>15</v>
@@ -10199,7 +10199,7 @@
         <v>14</v>
       </c>
       <c r="F208" s="2">
-        <v>1011</v>
+        <v>3159</v>
       </c>
       <c r="G208" s="2" t="s">
         <v>15</v>
@@ -10231,7 +10231,7 @@
         <v>14</v>
       </c>
       <c r="F209" s="2">
-        <v>3641</v>
+        <v>939</v>
       </c>
       <c r="G209" s="2" t="s">
         <v>15</v>
@@ -10263,7 +10263,7 @@
         <v>14</v>
       </c>
       <c r="F210" s="2">
-        <v>4275</v>
+        <v>2976</v>
       </c>
       <c r="G210" s="2" t="s">
         <v>15</v>
@@ -10295,7 +10295,7 @@
         <v>14</v>
       </c>
       <c r="F211" s="2">
-        <v>4474</v>
+        <v>2807</v>
       </c>
       <c r="G211" s="2" t="s">
         <v>15</v>
@@ -10327,7 +10327,7 @@
         <v>14</v>
       </c>
       <c r="F212" s="2">
-        <v>2731</v>
+        <v>2640</v>
       </c>
       <c r="G212" s="2" t="s">
         <v>15</v>
@@ -10359,7 +10359,7 @@
         <v>14</v>
       </c>
       <c r="F213" s="2">
-        <v>2898</v>
+        <v>3235</v>
       </c>
       <c r="G213" s="2" t="s">
         <v>15</v>
@@ -10391,7 +10391,7 @@
         <v>14</v>
       </c>
       <c r="F214" s="2">
-        <v>1365</v>
+        <v>2419</v>
       </c>
       <c r="G214" s="2" t="s">
         <v>15</v>
@@ -10423,7 +10423,7 @@
         <v>14</v>
       </c>
       <c r="F215" s="2">
-        <v>1256</v>
+        <v>3779</v>
       </c>
       <c r="G215" s="2" t="s">
         <v>15</v>
@@ -10455,7 +10455,7 @@
         <v>14</v>
       </c>
       <c r="F216" s="2">
-        <v>2086</v>
+        <v>2554</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>15</v>
@@ -10487,7 +10487,7 @@
         <v>14</v>
       </c>
       <c r="F217" s="2">
-        <v>2012</v>
+        <v>1699</v>
       </c>
       <c r="G217" s="2" t="s">
         <v>15</v>
@@ -10519,7 +10519,7 @@
         <v>14</v>
       </c>
       <c r="F218" s="2">
-        <v>1206</v>
+        <v>3314</v>
       </c>
       <c r="G218" s="2" t="s">
         <v>15</v>
@@ -10551,7 +10551,7 @@
         <v>14</v>
       </c>
       <c r="F219" s="2">
-        <v>3803</v>
+        <v>4040</v>
       </c>
       <c r="G219" s="2" t="s">
         <v>15</v>
@@ -10583,7 +10583,7 @@
         <v>14</v>
       </c>
       <c r="F220" s="2">
-        <v>1975</v>
+        <v>1189</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>15</v>
@@ -10615,7 +10615,7 @@
         <v>14</v>
       </c>
       <c r="F221" s="2">
-        <v>2488</v>
+        <v>1239</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>15</v>
@@ -10647,7 +10647,7 @@
         <v>14</v>
       </c>
       <c r="F222" s="2">
-        <v>895</v>
+        <v>915</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>15</v>
@@ -10679,7 +10679,7 @@
         <v>14</v>
       </c>
       <c r="F223" s="2">
-        <v>3935</v>
+        <v>2219</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>15</v>
@@ -10711,7 +10711,7 @@
         <v>14</v>
       </c>
       <c r="F224" s="2">
-        <v>1986</v>
+        <v>2439</v>
       </c>
       <c r="G224" s="2" t="s">
         <v>15</v>
@@ -10743,7 +10743,7 @@
         <v>14</v>
       </c>
       <c r="F225" s="2">
-        <v>1999</v>
+        <v>2752</v>
       </c>
       <c r="G225" s="2" t="s">
         <v>15</v>
@@ -10775,7 +10775,7 @@
         <v>14</v>
       </c>
       <c r="F226" s="2">
-        <v>3901</v>
+        <v>2649</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>15</v>
@@ -10807,7 +10807,7 @@
         <v>14</v>
       </c>
       <c r="F227" s="2">
-        <v>2347</v>
+        <v>3246</v>
       </c>
       <c r="G227" s="2" t="s">
         <v>15</v>
@@ -10839,7 +10839,7 @@
         <v>14</v>
       </c>
       <c r="F228" s="2">
-        <v>4503</v>
+        <v>2929</v>
       </c>
       <c r="G228" s="2" t="s">
         <v>15</v>
@@ -10871,7 +10871,7 @@
         <v>14</v>
       </c>
       <c r="F229" s="2">
-        <v>3126</v>
+        <v>3556</v>
       </c>
       <c r="G229" s="2" t="s">
         <v>15</v>
@@ -10903,7 +10903,7 @@
         <v>14</v>
       </c>
       <c r="F230" s="2">
-        <v>4663</v>
+        <v>2306</v>
       </c>
       <c r="G230" s="2" t="s">
         <v>15</v>
@@ -10935,7 +10935,7 @@
         <v>14</v>
       </c>
       <c r="F231" s="2">
-        <v>1592</v>
+        <v>2321</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>15</v>
@@ -10967,7 +10967,7 @@
         <v>14</v>
       </c>
       <c r="F232" s="2">
-        <v>2636</v>
+        <v>3817</v>
       </c>
       <c r="G232" s="2" t="s">
         <v>15</v>
@@ -10999,7 +10999,7 @@
         <v>14</v>
       </c>
       <c r="F233" s="2">
-        <v>2516</v>
+        <v>1746</v>
       </c>
       <c r="G233" s="2" t="s">
         <v>15</v>
@@ -11031,7 +11031,7 @@
         <v>14</v>
       </c>
       <c r="F234" s="2">
-        <v>962</v>
+        <v>2965</v>
       </c>
       <c r="G234" s="2" t="s">
         <v>15</v>
@@ -11063,7 +11063,7 @@
         <v>14</v>
       </c>
       <c r="F235" s="2">
-        <v>1588</v>
+        <v>3904</v>
       </c>
       <c r="G235" s="2" t="s">
         <v>15</v>
@@ -11095,7 +11095,7 @@
         <v>14</v>
       </c>
       <c r="F236" s="2">
-        <v>3416</v>
+        <v>1031</v>
       </c>
       <c r="G236" s="2" t="s">
         <v>15</v>
@@ -11127,7 +11127,7 @@
         <v>14</v>
       </c>
       <c r="F237" s="2">
-        <v>1845</v>
+        <v>1127</v>
       </c>
       <c r="G237" s="2" t="s">
         <v>15</v>
@@ -11159,7 +11159,7 @@
         <v>14</v>
       </c>
       <c r="F238" s="2">
-        <v>1507</v>
+        <v>1033</v>
       </c>
       <c r="G238" s="2" t="s">
         <v>15</v>
@@ -11191,7 +11191,7 @@
         <v>14</v>
       </c>
       <c r="F239" s="2">
-        <v>3458</v>
+        <v>2450</v>
       </c>
       <c r="G239" s="2" t="s">
         <v>15</v>
@@ -11223,7 +11223,7 @@
         <v>14</v>
       </c>
       <c r="F240" s="2">
-        <v>1969</v>
+        <v>2853</v>
       </c>
       <c r="G240" s="2" t="s">
         <v>15</v>
@@ -11255,7 +11255,7 @@
         <v>14</v>
       </c>
       <c r="F241" s="2">
-        <v>4402</v>
+        <v>4435</v>
       </c>
       <c r="G241" s="2" t="s">
         <v>15</v>
@@ -11287,7 +11287,7 @@
         <v>14</v>
       </c>
       <c r="F242" s="2">
-        <v>2071</v>
+        <v>3411</v>
       </c>
       <c r="G242" s="2" t="s">
         <v>15</v>
@@ -11319,7 +11319,7 @@
         <v>14</v>
       </c>
       <c r="F243" s="2">
-        <v>4692</v>
+        <v>1579</v>
       </c>
       <c r="G243" s="2" t="s">
         <v>15</v>
@@ -11351,7 +11351,7 @@
         <v>14</v>
       </c>
       <c r="F244" s="2">
-        <v>1076</v>
+        <v>1553</v>
       </c>
       <c r="G244" s="2" t="s">
         <v>15</v>
@@ -11383,7 +11383,7 @@
         <v>14</v>
       </c>
       <c r="F245" s="2">
-        <v>4165</v>
+        <v>3598</v>
       </c>
       <c r="G245" s="2" t="s">
         <v>15</v>
@@ -11415,7 +11415,7 @@
         <v>14</v>
       </c>
       <c r="F246" s="2">
-        <v>1129</v>
+        <v>4452</v>
       </c>
       <c r="G246" s="2" t="s">
         <v>15</v>
@@ -11447,7 +11447,7 @@
         <v>14</v>
       </c>
       <c r="F247" s="2">
-        <v>1895</v>
+        <v>3048</v>
       </c>
       <c r="G247" s="2" t="s">
         <v>15</v>
@@ -11479,7 +11479,7 @@
         <v>14</v>
       </c>
       <c r="F248" s="2">
-        <v>1973</v>
+        <v>4471</v>
       </c>
       <c r="G248" s="2" t="s">
         <v>15</v>
@@ -11511,7 +11511,7 @@
         <v>14</v>
       </c>
       <c r="F249" s="2">
-        <v>2026</v>
+        <v>1082</v>
       </c>
       <c r="G249" s="2" t="s">
         <v>15</v>
@@ -11543,7 +11543,7 @@
         <v>14</v>
       </c>
       <c r="F250" s="2">
-        <v>3095</v>
+        <v>4231</v>
       </c>
       <c r="G250" s="2" t="s">
         <v>15</v>
@@ -11575,7 +11575,7 @@
         <v>14</v>
       </c>
       <c r="F251" s="2">
-        <v>1251</v>
+        <v>2873</v>
       </c>
       <c r="G251" s="2" t="s">
         <v>15</v>
@@ -11607,7 +11607,7 @@
         <v>14</v>
       </c>
       <c r="F252" s="2">
-        <v>1629</v>
+        <v>4513</v>
       </c>
       <c r="G252" s="2" t="s">
         <v>15</v>
@@ -11639,7 +11639,7 @@
         <v>14</v>
       </c>
       <c r="F253" s="2">
-        <v>1652</v>
+        <v>3104</v>
       </c>
       <c r="G253" s="2" t="s">
         <v>15</v>
@@ -11671,7 +11671,7 @@
         <v>14</v>
       </c>
       <c r="F254" s="2">
-        <v>4588</v>
+        <v>4154</v>
       </c>
       <c r="G254" s="2" t="s">
         <v>15</v>
@@ -11703,7 +11703,7 @@
         <v>14</v>
       </c>
       <c r="F255" s="2">
-        <v>2996</v>
+        <v>1740</v>
       </c>
       <c r="G255" s="2" t="s">
         <v>15</v>
@@ -11735,7 +11735,7 @@
         <v>14</v>
       </c>
       <c r="F256" s="2">
-        <v>1606</v>
+        <v>4675</v>
       </c>
       <c r="G256" s="2" t="s">
         <v>15</v>
@@ -11767,7 +11767,7 @@
         <v>14</v>
       </c>
       <c r="F257" s="2">
-        <v>2582</v>
+        <v>1641</v>
       </c>
       <c r="G257" s="2" t="s">
         <v>15</v>
@@ -11799,7 +11799,7 @@
         <v>14</v>
       </c>
       <c r="F258" s="2">
-        <v>2519</v>
+        <v>844</v>
       </c>
       <c r="G258" s="2" t="s">
         <v>15</v>
@@ -11831,7 +11831,7 @@
         <v>14</v>
       </c>
       <c r="F259" s="2">
-        <v>4593</v>
+        <v>2016</v>
       </c>
       <c r="G259" s="2" t="s">
         <v>15</v>
@@ -11863,7 +11863,7 @@
         <v>14</v>
       </c>
       <c r="F260" s="2">
-        <v>3340</v>
+        <v>2100</v>
       </c>
       <c r="G260" s="2" t="s">
         <v>15</v>
@@ -11895,7 +11895,7 @@
         <v>14</v>
       </c>
       <c r="F261" s="2">
-        <v>2568</v>
+        <v>2970</v>
       </c>
       <c r="G261" s="2" t="s">
         <v>15</v>
@@ -11927,7 +11927,7 @@
         <v>14</v>
       </c>
       <c r="F262" s="2">
-        <v>877</v>
+        <v>1052</v>
       </c>
       <c r="G262" s="2" t="s">
         <v>15</v>
@@ -11959,7 +11959,7 @@
         <v>14</v>
       </c>
       <c r="F263" s="2">
-        <v>4277</v>
+        <v>1388</v>
       </c>
       <c r="G263" s="2" t="s">
         <v>15</v>
@@ -11991,7 +11991,7 @@
         <v>14</v>
       </c>
       <c r="F264" s="2">
-        <v>1602</v>
+        <v>2829</v>
       </c>
       <c r="G264" s="2" t="s">
         <v>15</v>
@@ -12023,7 +12023,7 @@
         <v>14</v>
       </c>
       <c r="F265" s="2">
-        <v>1449</v>
+        <v>2397</v>
       </c>
       <c r="G265" s="2" t="s">
         <v>15</v>
@@ -12055,7 +12055,7 @@
         <v>14</v>
       </c>
       <c r="F266" s="2">
-        <v>3457</v>
+        <v>2635</v>
       </c>
       <c r="G266" s="2" t="s">
         <v>15</v>
@@ -12087,7 +12087,7 @@
         <v>14</v>
       </c>
       <c r="F267" s="2">
-        <v>2741</v>
+        <v>2858</v>
       </c>
       <c r="G267" s="2" t="s">
         <v>15</v>
@@ -12119,7 +12119,7 @@
         <v>14</v>
       </c>
       <c r="F268" s="2">
-        <v>3208</v>
+        <v>2546</v>
       </c>
       <c r="G268" s="2" t="s">
         <v>15</v>
@@ -12151,7 +12151,7 @@
         <v>14</v>
       </c>
       <c r="F269" s="2">
-        <v>2239</v>
+        <v>879</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>15</v>
@@ -12183,7 +12183,7 @@
         <v>14</v>
       </c>
       <c r="F270" s="2">
-        <v>4543</v>
+        <v>4098</v>
       </c>
       <c r="G270" s="2" t="s">
         <v>15</v>
@@ -12215,7 +12215,7 @@
         <v>14</v>
       </c>
       <c r="F271" s="2">
-        <v>3712</v>
+        <v>1484</v>
       </c>
       <c r="G271" s="2" t="s">
         <v>15</v>
@@ -12247,7 +12247,7 @@
         <v>14</v>
       </c>
       <c r="F272" s="2">
-        <v>4239</v>
+        <v>4664</v>
       </c>
       <c r="G272" s="2" t="s">
         <v>15</v>
@@ -12279,7 +12279,7 @@
         <v>14</v>
       </c>
       <c r="F273" s="2">
-        <v>4773</v>
+        <v>4351</v>
       </c>
       <c r="G273" s="2" t="s">
         <v>15</v>
@@ -12311,7 +12311,7 @@
         <v>14</v>
       </c>
       <c r="F274" s="2">
-        <v>1305</v>
+        <v>4701</v>
       </c>
       <c r="G274" s="2" t="s">
         <v>15</v>
@@ -12343,7 +12343,7 @@
         <v>14</v>
       </c>
       <c r="F275" s="2">
-        <v>4569</v>
+        <v>1012</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>15</v>
@@ -12375,7 +12375,7 @@
         <v>14</v>
       </c>
       <c r="F276" s="2">
-        <v>1567</v>
+        <v>2186</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>15</v>
@@ -12407,7 +12407,7 @@
         <v>14</v>
       </c>
       <c r="F277" s="2">
-        <v>1129</v>
+        <v>1358</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>15</v>
@@ -12439,7 +12439,7 @@
         <v>14</v>
       </c>
       <c r="F278" s="2">
-        <v>3028</v>
+        <v>2193</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>15</v>
@@ -12471,7 +12471,7 @@
         <v>14</v>
       </c>
       <c r="F279" s="2">
-        <v>4785</v>
+        <v>813</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>15</v>
@@ -12503,7 +12503,7 @@
         <v>14</v>
       </c>
       <c r="F280" s="2">
-        <v>2739</v>
+        <v>2708</v>
       </c>
       <c r="G280" s="2" t="s">
         <v>15</v>
@@ -12535,7 +12535,7 @@
         <v>14</v>
       </c>
       <c r="F281" s="2">
-        <v>3274</v>
+        <v>3183</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>15</v>
@@ -12567,7 +12567,7 @@
         <v>14</v>
       </c>
       <c r="F282" s="2">
-        <v>3694</v>
+        <v>4455</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>15</v>
@@ -12599,7 +12599,7 @@
         <v>14</v>
       </c>
       <c r="F283" s="2">
-        <v>4549</v>
+        <v>4699</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>15</v>
@@ -12631,7 +12631,7 @@
         <v>14</v>
       </c>
       <c r="F284" s="2">
-        <v>3954</v>
+        <v>1551</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>15</v>
@@ -12663,7 +12663,7 @@
         <v>14</v>
       </c>
       <c r="F285" s="2">
-        <v>2745</v>
+        <v>1473</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>15</v>
@@ -12695,7 +12695,7 @@
         <v>14</v>
       </c>
       <c r="F286" s="2">
-        <v>4224</v>
+        <v>1144</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>15</v>
@@ -12727,7 +12727,7 @@
         <v>14</v>
       </c>
       <c r="F287" s="2">
-        <v>4295</v>
+        <v>2278</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>15</v>
@@ -12759,7 +12759,7 @@
         <v>14</v>
       </c>
       <c r="F288" s="2">
-        <v>4160</v>
+        <v>1408</v>
       </c>
       <c r="G288" s="2" t="s">
         <v>15</v>
@@ -12791,7 +12791,7 @@
         <v>14</v>
       </c>
       <c r="F289" s="2">
-        <v>1079</v>
+        <v>838</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>15</v>
@@ -12823,7 +12823,7 @@
         <v>14</v>
       </c>
       <c r="F290" s="2">
-        <v>1680</v>
+        <v>4658</v>
       </c>
       <c r="G290" s="2" t="s">
         <v>15</v>
@@ -12855,7 +12855,7 @@
         <v>14</v>
       </c>
       <c r="F291" s="2">
-        <v>2102</v>
+        <v>1542</v>
       </c>
       <c r="G291" s="2" t="s">
         <v>15</v>
@@ -12887,7 +12887,7 @@
         <v>14</v>
       </c>
       <c r="F292" s="2">
-        <v>3281</v>
+        <v>4091</v>
       </c>
       <c r="G292" s="2" t="s">
         <v>15</v>
@@ -12919,7 +12919,7 @@
         <v>14</v>
       </c>
       <c r="F293" s="2">
-        <v>937</v>
+        <v>1139</v>
       </c>
       <c r="G293" s="2" t="s">
         <v>15</v>
@@ -12951,7 +12951,7 @@
         <v>14</v>
       </c>
       <c r="F294" s="2">
-        <v>2656</v>
+        <v>2122</v>
       </c>
       <c r="G294" s="2" t="s">
         <v>15</v>
@@ -12983,7 +12983,7 @@
         <v>14</v>
       </c>
       <c r="F295" s="2">
-        <v>3189</v>
+        <v>2873</v>
       </c>
       <c r="G295" s="2" t="s">
         <v>15</v>
@@ -13015,7 +13015,7 @@
         <v>14</v>
       </c>
       <c r="F296" s="2">
-        <v>2092</v>
+        <v>2578</v>
       </c>
       <c r="G296" s="2" t="s">
         <v>15</v>
@@ -13047,7 +13047,7 @@
         <v>14</v>
       </c>
       <c r="F297" s="2">
-        <v>2885</v>
+        <v>3019</v>
       </c>
       <c r="G297" s="2" t="s">
         <v>15</v>
@@ -13079,7 +13079,7 @@
         <v>14</v>
       </c>
       <c r="F298" s="2">
-        <v>2970</v>
+        <v>4188</v>
       </c>
       <c r="G298" s="2" t="s">
         <v>15</v>
@@ -13111,7 +13111,7 @@
         <v>14</v>
       </c>
       <c r="F299" s="2">
-        <v>4200</v>
+        <v>2103</v>
       </c>
       <c r="G299" s="2" t="s">
         <v>15</v>
@@ -13143,7 +13143,7 @@
         <v>14</v>
       </c>
       <c r="F300" s="2">
-        <v>4666</v>
+        <v>1222</v>
       </c>
       <c r="G300" s="2" t="s">
         <v>15</v>
@@ -13175,7 +13175,7 @@
         <v>14</v>
       </c>
       <c r="F301" s="2">
-        <v>1415</v>
+        <v>2784</v>
       </c>
       <c r="G301" s="2" t="s">
         <v>15</v>
@@ -13207,7 +13207,7 @@
         <v>14</v>
       </c>
       <c r="F302" s="2">
-        <v>1737</v>
+        <v>2459</v>
       </c>
       <c r="G302" s="2" t="s">
         <v>15</v>
@@ -13239,7 +13239,7 @@
         <v>14</v>
       </c>
       <c r="F303" s="2">
-        <v>4530</v>
+        <v>4521</v>
       </c>
       <c r="G303" s="2" t="s">
         <v>15</v>
@@ -13271,7 +13271,7 @@
         <v>14</v>
       </c>
       <c r="F304" s="2">
-        <v>2866</v>
+        <v>1137</v>
       </c>
       <c r="G304" s="2" t="s">
         <v>15</v>
@@ -13303,7 +13303,7 @@
         <v>14</v>
       </c>
       <c r="F305" s="2">
-        <v>1772</v>
+        <v>2539</v>
       </c>
       <c r="G305" s="2" t="s">
         <v>15</v>
@@ -13335,7 +13335,7 @@
         <v>14</v>
       </c>
       <c r="F306" s="2">
-        <v>3642</v>
+        <v>3823</v>
       </c>
       <c r="G306" s="2" t="s">
         <v>15</v>
@@ -13367,7 +13367,7 @@
         <v>14</v>
       </c>
       <c r="F307" s="2">
-        <v>1291</v>
+        <v>1490</v>
       </c>
       <c r="G307" s="2" t="s">
         <v>15</v>
@@ -13399,7 +13399,7 @@
         <v>14</v>
       </c>
       <c r="F308" s="2">
-        <v>4466</v>
+        <v>3534</v>
       </c>
       <c r="G308" s="2" t="s">
         <v>15</v>
@@ -13431,7 +13431,7 @@
         <v>14</v>
       </c>
       <c r="F309" s="2">
-        <v>959</v>
+        <v>4410</v>
       </c>
       <c r="G309" s="2" t="s">
         <v>15</v>
@@ -13463,7 +13463,7 @@
         <v>14</v>
       </c>
       <c r="F310" s="2">
-        <v>4564</v>
+        <v>2007</v>
       </c>
       <c r="G310" s="2" t="s">
         <v>15</v>
@@ -13495,7 +13495,7 @@
         <v>14</v>
       </c>
       <c r="F311" s="2">
-        <v>3778</v>
+        <v>4432</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>15</v>
@@ -13527,7 +13527,7 @@
         <v>14</v>
       </c>
       <c r="F312" s="2">
-        <v>2889</v>
+        <v>3385</v>
       </c>
       <c r="G312" s="2" t="s">
         <v>15</v>
@@ -13559,7 +13559,7 @@
         <v>14</v>
       </c>
       <c r="F313" s="2">
-        <v>1656</v>
+        <v>1321</v>
       </c>
       <c r="G313" s="2" t="s">
         <v>15</v>
@@ -13591,7 +13591,7 @@
         <v>14</v>
       </c>
       <c r="F314" s="2">
-        <v>2049</v>
+        <v>1009</v>
       </c>
       <c r="G314" s="2" t="s">
         <v>15</v>
@@ -13623,7 +13623,7 @@
         <v>14</v>
       </c>
       <c r="F315" s="2">
-        <v>917</v>
+        <v>2221</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>15</v>
@@ -13655,7 +13655,7 @@
         <v>14</v>
       </c>
       <c r="F316" s="2">
-        <v>3931</v>
+        <v>2541</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>15</v>
@@ -13687,7 +13687,7 @@
         <v>14</v>
       </c>
       <c r="F317" s="2">
-        <v>3666</v>
+        <v>4349</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>15</v>
@@ -13719,7 +13719,7 @@
         <v>14</v>
       </c>
       <c r="F318" s="2">
-        <v>3554</v>
+        <v>1201</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>15</v>
@@ -13751,7 +13751,7 @@
         <v>14</v>
       </c>
       <c r="F319" s="2">
-        <v>4650</v>
+        <v>4182</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>15</v>
@@ -13783,7 +13783,7 @@
         <v>14</v>
       </c>
       <c r="F320" s="2">
-        <v>1437</v>
+        <v>1308</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>15</v>
@@ -13815,7 +13815,7 @@
         <v>14</v>
       </c>
       <c r="F321" s="2">
-        <v>993</v>
+        <v>3896</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>15</v>
@@ -13847,7 +13847,7 @@
         <v>14</v>
       </c>
       <c r="F322" s="2">
-        <v>2386</v>
+        <v>1686</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>15</v>
@@ -13879,7 +13879,7 @@
         <v>14</v>
       </c>
       <c r="F323" s="2">
-        <v>1785</v>
+        <v>1321</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>15</v>
@@ -13911,7 +13911,7 @@
         <v>14</v>
       </c>
       <c r="F324" s="2">
-        <v>1432</v>
+        <v>3878</v>
       </c>
       <c r="G324" s="2" t="s">
         <v>15</v>
@@ -13943,7 +13943,7 @@
         <v>14</v>
       </c>
       <c r="F325" s="2">
-        <v>3004</v>
+        <v>3852</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>15</v>
@@ -13975,7 +13975,7 @@
         <v>14</v>
       </c>
       <c r="F326" s="2">
-        <v>4437</v>
+        <v>4204</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>15</v>
@@ -14007,7 +14007,7 @@
         <v>14</v>
       </c>
       <c r="F327" s="2">
-        <v>1971</v>
+        <v>3133</v>
       </c>
       <c r="G327" s="2" t="s">
         <v>15</v>
@@ -14039,7 +14039,7 @@
         <v>14</v>
       </c>
       <c r="F328" s="2">
-        <v>1099</v>
+        <v>2838</v>
       </c>
       <c r="G328" s="2" t="s">
         <v>15</v>
@@ -14071,7 +14071,7 @@
         <v>14</v>
       </c>
       <c r="F329" s="2">
-        <v>3912</v>
+        <v>2300</v>
       </c>
       <c r="G329" s="2" t="s">
         <v>15</v>
@@ -14103,7 +14103,7 @@
         <v>14</v>
       </c>
       <c r="F330" s="2">
-        <v>3581</v>
+        <v>4409</v>
       </c>
       <c r="G330" s="2" t="s">
         <v>15</v>
@@ -14135,7 +14135,7 @@
         <v>14</v>
       </c>
       <c r="F331" s="2">
-        <v>4102</v>
+        <v>4296</v>
       </c>
       <c r="G331" s="2" t="s">
         <v>15</v>
@@ -14167,7 +14167,7 @@
         <v>14</v>
       </c>
       <c r="F332" s="2">
-        <v>3869</v>
+        <v>4564</v>
       </c>
       <c r="G332" s="2" t="s">
         <v>15</v>
@@ -14199,7 +14199,7 @@
         <v>14</v>
       </c>
       <c r="F333" s="2">
-        <v>4072</v>
+        <v>4516</v>
       </c>
       <c r="G333" s="2" t="s">
         <v>15</v>
@@ -14231,7 +14231,7 @@
         <v>14</v>
       </c>
       <c r="F334" s="2">
-        <v>3115</v>
+        <v>1491</v>
       </c>
       <c r="G334" s="2" t="s">
         <v>15</v>
@@ -14263,7 +14263,7 @@
         <v>14</v>
       </c>
       <c r="F335" s="2">
-        <v>3023</v>
+        <v>1627</v>
       </c>
       <c r="G335" s="2" t="s">
         <v>15</v>
@@ -14295,7 +14295,7 @@
         <v>14</v>
       </c>
       <c r="F336" s="2">
-        <v>2354</v>
+        <v>1239</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>15</v>
@@ -14327,7 +14327,7 @@
         <v>14</v>
       </c>
       <c r="F337" s="2">
-        <v>2772</v>
+        <v>3608</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>15</v>
@@ -14359,7 +14359,7 @@
         <v>14</v>
       </c>
       <c r="F338" s="2">
-        <v>1737</v>
+        <v>2163</v>
       </c>
       <c r="G338" s="2" t="s">
         <v>15</v>
@@ -14391,7 +14391,7 @@
         <v>14</v>
       </c>
       <c r="F339" s="2">
-        <v>3046</v>
+        <v>1058</v>
       </c>
       <c r="G339" s="2" t="s">
         <v>15</v>
@@ -14423,7 +14423,7 @@
         <v>14</v>
       </c>
       <c r="F340" s="2">
-        <v>2292</v>
+        <v>1513</v>
       </c>
       <c r="G340" s="2" t="s">
         <v>15</v>
@@ -14455,7 +14455,7 @@
         <v>14</v>
       </c>
       <c r="F341" s="2">
-        <v>2871</v>
+        <v>3245</v>
       </c>
       <c r="G341" s="2" t="s">
         <v>15</v>
@@ -14487,7 +14487,7 @@
         <v>14</v>
       </c>
       <c r="F342" s="2">
-        <v>3172</v>
+        <v>4460</v>
       </c>
       <c r="G342" s="2" t="s">
         <v>15</v>
@@ -14519,7 +14519,7 @@
         <v>14</v>
       </c>
       <c r="F343" s="2">
-        <v>4089</v>
+        <v>3524</v>
       </c>
       <c r="G343" s="2" t="s">
         <v>15</v>
@@ -14551,7 +14551,7 @@
         <v>14</v>
       </c>
       <c r="F344" s="2">
-        <v>2032</v>
+        <v>4428</v>
       </c>
       <c r="G344" s="2" t="s">
         <v>15</v>
@@ -14583,7 +14583,7 @@
         <v>14</v>
       </c>
       <c r="F345" s="2">
-        <v>3432</v>
+        <v>3208</v>
       </c>
       <c r="G345" s="2" t="s">
         <v>15</v>
@@ -14615,7 +14615,7 @@
         <v>14</v>
       </c>
       <c r="F346" s="2">
-        <v>3294</v>
+        <v>4486</v>
       </c>
       <c r="G346" s="2" t="s">
         <v>15</v>
@@ -14647,7 +14647,7 @@
         <v>14</v>
       </c>
       <c r="F347" s="2">
-        <v>4375</v>
+        <v>2936</v>
       </c>
       <c r="G347" s="2" t="s">
         <v>15</v>
@@ -14679,7 +14679,7 @@
         <v>14</v>
       </c>
       <c r="F348" s="2">
-        <v>1218</v>
+        <v>1114</v>
       </c>
       <c r="G348" s="2" t="s">
         <v>15</v>
@@ -14711,7 +14711,7 @@
         <v>14</v>
       </c>
       <c r="F349" s="2">
-        <v>4223</v>
+        <v>2026</v>
       </c>
       <c r="G349" s="2" t="s">
         <v>15</v>
@@ -14743,7 +14743,7 @@
         <v>14</v>
       </c>
       <c r="F350" s="2">
-        <v>1970</v>
+        <v>1927</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>15</v>
@@ -14775,7 +14775,7 @@
         <v>14</v>
       </c>
       <c r="F351" s="2">
-        <v>3164</v>
+        <v>2904</v>
       </c>
       <c r="G351" s="2" t="s">
         <v>15</v>
@@ -14807,7 +14807,7 @@
         <v>14</v>
       </c>
       <c r="F352" s="2">
-        <v>4392</v>
+        <v>1187</v>
       </c>
       <c r="G352" s="2" t="s">
         <v>15</v>
@@ -14839,7 +14839,7 @@
         <v>14</v>
       </c>
       <c r="F353" s="2">
-        <v>4626</v>
+        <v>4274</v>
       </c>
       <c r="G353" s="2" t="s">
         <v>15</v>
@@ -14871,7 +14871,7 @@
         <v>14</v>
       </c>
       <c r="F354" s="2">
-        <v>813</v>
+        <v>2966</v>
       </c>
       <c r="G354" s="2" t="s">
         <v>15</v>
@@ -14903,7 +14903,7 @@
         <v>14</v>
       </c>
       <c r="F355" s="2">
-        <v>4638</v>
+        <v>2855</v>
       </c>
       <c r="G355" s="2" t="s">
         <v>15</v>
@@ -14935,7 +14935,7 @@
         <v>14</v>
       </c>
       <c r="F356" s="2">
-        <v>2734</v>
+        <v>3399</v>
       </c>
       <c r="G356" s="2" t="s">
         <v>15</v>
@@ -14967,7 +14967,7 @@
         <v>14</v>
       </c>
       <c r="F357" s="2">
-        <v>3803</v>
+        <v>4661</v>
       </c>
       <c r="G357" s="2" t="s">
         <v>15</v>
@@ -14999,7 +14999,7 @@
         <v>14</v>
       </c>
       <c r="F358" s="2">
-        <v>1741</v>
+        <v>1148</v>
       </c>
       <c r="G358" s="2" t="s">
         <v>15</v>
@@ -15031,7 +15031,7 @@
         <v>14</v>
       </c>
       <c r="F359" s="2">
-        <v>4562</v>
+        <v>3634</v>
       </c>
       <c r="G359" s="2" t="s">
         <v>15</v>
@@ -15063,7 +15063,7 @@
         <v>14</v>
       </c>
       <c r="F360" s="2">
-        <v>2041</v>
+        <v>1924</v>
       </c>
       <c r="G360" s="2" t="s">
         <v>15</v>
@@ -15095,7 +15095,7 @@
         <v>14</v>
       </c>
       <c r="F361" s="2">
-        <v>3845</v>
+        <v>1958</v>
       </c>
       <c r="G361" s="2" t="s">
         <v>15</v>
@@ -15127,7 +15127,7 @@
         <v>14</v>
       </c>
       <c r="F362" s="2">
-        <v>3094</v>
+        <v>2196</v>
       </c>
       <c r="G362" s="2" t="s">
         <v>15</v>
@@ -15159,7 +15159,7 @@
         <v>14</v>
       </c>
       <c r="F363" s="2">
-        <v>2910</v>
+        <v>3016</v>
       </c>
       <c r="G363" s="2" t="s">
         <v>15</v>
@@ -15191,7 +15191,7 @@
         <v>14</v>
       </c>
       <c r="F364" s="2">
-        <v>1471</v>
+        <v>2924</v>
       </c>
       <c r="G364" s="2" t="s">
         <v>15</v>
@@ -15223,7 +15223,7 @@
         <v>14</v>
       </c>
       <c r="F365" s="2">
-        <v>1653</v>
+        <v>1793</v>
       </c>
       <c r="G365" s="2" t="s">
         <v>15</v>
@@ -15255,7 +15255,7 @@
         <v>14</v>
       </c>
       <c r="F366" s="2">
-        <v>2406</v>
+        <v>2656</v>
       </c>
       <c r="G366" s="2" t="s">
         <v>15</v>
@@ -15287,7 +15287,7 @@
         <v>14</v>
       </c>
       <c r="F367" s="2">
-        <v>857</v>
+        <v>4490</v>
       </c>
       <c r="G367" s="2" t="s">
         <v>15</v>
@@ -15319,7 +15319,7 @@
         <v>14</v>
       </c>
       <c r="F368" s="2">
-        <v>913</v>
+        <v>3009</v>
       </c>
       <c r="G368" s="2" t="s">
         <v>15</v>
@@ -15351,7 +15351,7 @@
         <v>14</v>
       </c>
       <c r="F369" s="2">
-        <v>3040</v>
+        <v>3575</v>
       </c>
       <c r="G369" s="2" t="s">
         <v>15</v>
@@ -15383,7 +15383,7 @@
         <v>14</v>
       </c>
       <c r="F370" s="2">
-        <v>1052</v>
+        <v>1063</v>
       </c>
       <c r="G370" s="2" t="s">
         <v>15</v>
@@ -15415,7 +15415,7 @@
         <v>14</v>
       </c>
       <c r="F371" s="2">
-        <v>3905</v>
+        <v>1434</v>
       </c>
       <c r="G371" s="2" t="s">
         <v>15</v>
@@ -15447,7 +15447,7 @@
         <v>14</v>
       </c>
       <c r="F372" s="2">
-        <v>4022</v>
+        <v>1437</v>
       </c>
       <c r="G372" s="2" t="s">
         <v>15</v>
@@ -15479,7 +15479,7 @@
         <v>14</v>
       </c>
       <c r="F373" s="2">
-        <v>3035</v>
+        <v>1718</v>
       </c>
       <c r="G373" s="2" t="s">
         <v>15</v>
@@ -15511,7 +15511,7 @@
         <v>14</v>
       </c>
       <c r="F374" s="2">
-        <v>2494</v>
+        <v>2162</v>
       </c>
       <c r="G374" s="2" t="s">
         <v>15</v>
@@ -15543,7 +15543,7 @@
         <v>14</v>
       </c>
       <c r="F375" s="2">
-        <v>3998</v>
+        <v>3840</v>
       </c>
       <c r="G375" s="2" t="s">
         <v>15</v>
@@ -15575,7 +15575,7 @@
         <v>14</v>
       </c>
       <c r="F376" s="2">
-        <v>3948</v>
+        <v>1144</v>
       </c>
       <c r="G376" s="2" t="s">
         <v>15</v>
@@ -15607,7 +15607,7 @@
         <v>14</v>
       </c>
       <c r="F377" s="2">
-        <v>3124</v>
+        <v>1930</v>
       </c>
       <c r="G377" s="2" t="s">
         <v>15</v>
@@ -15639,7 +15639,7 @@
         <v>14</v>
       </c>
       <c r="F378" s="2">
-        <v>2174</v>
+        <v>1059</v>
       </c>
       <c r="G378" s="2" t="s">
         <v>15</v>
@@ -15671,7 +15671,7 @@
         <v>14</v>
       </c>
       <c r="F379" s="2">
-        <v>4130</v>
+        <v>2998</v>
       </c>
       <c r="G379" s="2" t="s">
         <v>15</v>
@@ -15703,7 +15703,7 @@
         <v>14</v>
       </c>
       <c r="F380" s="2">
-        <v>1052</v>
+        <v>1856</v>
       </c>
       <c r="G380" s="2" t="s">
         <v>15</v>
@@ -15735,7 +15735,7 @@
         <v>14</v>
       </c>
       <c r="F381" s="2">
-        <v>1881</v>
+        <v>2767</v>
       </c>
       <c r="G381" s="2" t="s">
         <v>15</v>
@@ -15767,7 +15767,7 @@
         <v>14</v>
       </c>
       <c r="F382" s="2">
-        <v>4287</v>
+        <v>3679</v>
       </c>
       <c r="G382" s="2" t="s">
         <v>15</v>
@@ -15799,7 +15799,7 @@
         <v>14</v>
       </c>
       <c r="F383" s="2">
-        <v>3603</v>
+        <v>4658</v>
       </c>
       <c r="G383" s="2" t="s">
         <v>15</v>
@@ -15831,7 +15831,7 @@
         <v>14</v>
       </c>
       <c r="F384" s="2">
-        <v>2413</v>
+        <v>2202</v>
       </c>
       <c r="G384" s="2" t="s">
         <v>15</v>
@@ -15863,7 +15863,7 @@
         <v>14</v>
       </c>
       <c r="F385" s="2">
-        <v>4027</v>
+        <v>1498</v>
       </c>
       <c r="G385" s="2" t="s">
         <v>15</v>
@@ -15895,7 +15895,7 @@
         <v>14</v>
       </c>
       <c r="F386" s="2">
-        <v>1790</v>
+        <v>3319</v>
       </c>
       <c r="G386" s="2" t="s">
         <v>15</v>
@@ -15927,7 +15927,7 @@
         <v>14</v>
       </c>
       <c r="F387" s="2">
-        <v>942</v>
+        <v>1147</v>
       </c>
       <c r="G387" s="2" t="s">
         <v>15</v>
@@ -15959,7 +15959,7 @@
         <v>14</v>
       </c>
       <c r="F388" s="2">
-        <v>3528</v>
+        <v>2471</v>
       </c>
       <c r="G388" s="2" t="s">
         <v>15</v>
@@ -15991,7 +15991,7 @@
         <v>14</v>
       </c>
       <c r="F389" s="2">
-        <v>1605</v>
+        <v>1911</v>
       </c>
       <c r="G389" s="2" t="s">
         <v>15</v>
@@ -16023,7 +16023,7 @@
         <v>14</v>
       </c>
       <c r="F390" s="2">
-        <v>3299</v>
+        <v>3087</v>
       </c>
       <c r="G390" s="2" t="s">
         <v>15</v>
@@ -16055,7 +16055,7 @@
         <v>14</v>
       </c>
       <c r="F391" s="2">
-        <v>1157</v>
+        <v>1092</v>
       </c>
       <c r="G391" s="2" t="s">
         <v>15</v>
@@ -16087,7 +16087,7 @@
         <v>14</v>
       </c>
       <c r="F392" s="2">
-        <v>3965</v>
+        <v>950</v>
       </c>
       <c r="G392" s="2" t="s">
         <v>15</v>
@@ -16119,7 +16119,7 @@
         <v>14</v>
       </c>
       <c r="F393" s="2">
-        <v>853</v>
+        <v>3271</v>
       </c>
       <c r="G393" s="2" t="s">
         <v>15</v>
@@ -16151,7 +16151,7 @@
         <v>14</v>
       </c>
       <c r="F394" s="2">
-        <v>1134</v>
+        <v>3911</v>
       </c>
       <c r="G394" s="2" t="s">
         <v>15</v>
@@ -16183,7 +16183,7 @@
         <v>14</v>
       </c>
       <c r="F395" s="2">
-        <v>4441</v>
+        <v>4433</v>
       </c>
       <c r="G395" s="2" t="s">
         <v>15</v>
@@ -16215,7 +16215,7 @@
         <v>14</v>
       </c>
       <c r="F396" s="2">
-        <v>3735</v>
+        <v>3220</v>
       </c>
       <c r="G396" s="2" t="s">
         <v>15</v>
@@ -16247,7 +16247,7 @@
         <v>14</v>
       </c>
       <c r="F397" s="2">
-        <v>1221</v>
+        <v>2292</v>
       </c>
       <c r="G397" s="2" t="s">
         <v>15</v>
@@ -16279,7 +16279,7 @@
         <v>14</v>
       </c>
       <c r="F398" s="2">
-        <v>3304</v>
+        <v>3084</v>
       </c>
       <c r="G398" s="2" t="s">
         <v>15</v>
@@ -16311,7 +16311,7 @@
         <v>14</v>
       </c>
       <c r="F399" s="2">
-        <v>2445</v>
+        <v>2936</v>
       </c>
       <c r="G399" s="2" t="s">
         <v>15</v>
@@ -16343,7 +16343,7 @@
         <v>14</v>
       </c>
       <c r="F400" s="2">
-        <v>2352</v>
+        <v>3789</v>
       </c>
       <c r="G400" s="2" t="s">
         <v>15</v>
@@ -16375,7 +16375,7 @@
         <v>14</v>
       </c>
       <c r="F401" s="2">
-        <v>2083</v>
+        <v>1255</v>
       </c>
       <c r="G401" s="2" t="s">
         <v>15</v>
@@ -16407,7 +16407,7 @@
         <v>14</v>
       </c>
       <c r="F402" s="2">
-        <v>3100</v>
+        <v>1933</v>
       </c>
       <c r="G402" s="2" t="s">
         <v>15</v>
@@ -16439,7 +16439,7 @@
         <v>14</v>
       </c>
       <c r="F403" s="2">
-        <v>3473</v>
+        <v>895</v>
       </c>
       <c r="G403" s="2" t="s">
         <v>15</v>
@@ -16471,7 +16471,7 @@
         <v>14</v>
       </c>
       <c r="F404" s="2">
-        <v>2228</v>
+        <v>3343</v>
       </c>
       <c r="G404" s="2" t="s">
         <v>15</v>
@@ -16503,7 +16503,7 @@
         <v>14</v>
       </c>
       <c r="F405" s="2">
-        <v>805</v>
+        <v>1892</v>
       </c>
       <c r="G405" s="2" t="s">
         <v>15</v>
@@ -16535,7 +16535,7 @@
         <v>14</v>
       </c>
       <c r="F406" s="2">
-        <v>3586</v>
+        <v>3448</v>
       </c>
       <c r="G406" s="2" t="s">
         <v>15</v>
@@ -16567,7 +16567,7 @@
         <v>14</v>
       </c>
       <c r="F407" s="2">
-        <v>4555</v>
+        <v>1853</v>
       </c>
       <c r="G407" s="2" t="s">
         <v>15</v>
@@ -16599,7 +16599,7 @@
         <v>14</v>
       </c>
       <c r="F408" s="2">
-        <v>1078</v>
+        <v>2765</v>
       </c>
       <c r="G408" s="2" t="s">
         <v>15</v>
@@ -16631,7 +16631,7 @@
         <v>14</v>
       </c>
       <c r="F409" s="2">
-        <v>4245</v>
+        <v>4647</v>
       </c>
       <c r="G409" s="2" t="s">
         <v>15</v>
@@ -16663,7 +16663,7 @@
         <v>14</v>
       </c>
       <c r="F410" s="2">
-        <v>1046</v>
+        <v>1286</v>
       </c>
       <c r="G410" s="2" t="s">
         <v>15</v>
@@ -16695,7 +16695,7 @@
         <v>14</v>
       </c>
       <c r="F411" s="2">
-        <v>2479</v>
+        <v>1899</v>
       </c>
       <c r="G411" s="2" t="s">
         <v>15</v>
@@ -16727,7 +16727,7 @@
         <v>14</v>
       </c>
       <c r="F412" s="2">
-        <v>3944</v>
+        <v>3181</v>
       </c>
       <c r="G412" s="2" t="s">
         <v>15</v>
@@ -16759,7 +16759,7 @@
         <v>14</v>
       </c>
       <c r="F413" s="2">
-        <v>2336</v>
+        <v>3631</v>
       </c>
       <c r="G413" s="2" t="s">
         <v>15</v>
@@ -16791,7 +16791,7 @@
         <v>14</v>
       </c>
       <c r="F414" s="2">
-        <v>4571</v>
+        <v>4629</v>
       </c>
       <c r="G414" s="2" t="s">
         <v>15</v>
@@ -16823,7 +16823,7 @@
         <v>14</v>
       </c>
       <c r="F415" s="2">
-        <v>1110</v>
+        <v>3162</v>
       </c>
       <c r="G415" s="2" t="s">
         <v>15</v>
@@ -16855,7 +16855,7 @@
         <v>14</v>
       </c>
       <c r="F416" s="2">
-        <v>1826</v>
+        <v>2171</v>
       </c>
       <c r="G416" s="2" t="s">
         <v>15</v>
@@ -16887,7 +16887,7 @@
         <v>14</v>
       </c>
       <c r="F417" s="2">
-        <v>3967</v>
+        <v>4406</v>
       </c>
       <c r="G417" s="2" t="s">
         <v>15</v>
@@ -16919,7 +16919,7 @@
         <v>14</v>
       </c>
       <c r="F418" s="2">
-        <v>3218</v>
+        <v>4253</v>
       </c>
       <c r="G418" s="2" t="s">
         <v>15</v>
@@ -16951,7 +16951,7 @@
         <v>14</v>
       </c>
       <c r="F419" s="2">
-        <v>1388</v>
+        <v>4511</v>
       </c>
       <c r="G419" s="2" t="s">
         <v>15</v>
@@ -16983,7 +16983,7 @@
         <v>14</v>
       </c>
       <c r="F420" s="2">
-        <v>945</v>
+        <v>3997</v>
       </c>
       <c r="G420" s="2" t="s">
         <v>15</v>
@@ -17015,7 +17015,7 @@
         <v>14</v>
       </c>
       <c r="F421" s="2">
-        <v>1858</v>
+        <v>1708</v>
       </c>
       <c r="G421" s="2" t="s">
         <v>15</v>
@@ -17047,7 +17047,7 @@
         <v>14</v>
       </c>
       <c r="F422" s="2">
-        <v>4081</v>
+        <v>2377</v>
       </c>
       <c r="G422" s="2" t="s">
         <v>15</v>
@@ -17079,7 +17079,7 @@
         <v>14</v>
       </c>
       <c r="F423" s="2">
-        <v>4728</v>
+        <v>3893</v>
       </c>
       <c r="G423" s="2" t="s">
         <v>15</v>
@@ -17111,7 +17111,7 @@
         <v>14</v>
       </c>
       <c r="F424" s="2">
-        <v>3251</v>
+        <v>3044</v>
       </c>
       <c r="G424" s="2" t="s">
         <v>15</v>
@@ -17143,7 +17143,7 @@
         <v>14</v>
       </c>
       <c r="F425" s="2">
-        <v>2653</v>
+        <v>1873</v>
       </c>
       <c r="G425" s="2" t="s">
         <v>15</v>
@@ -17175,7 +17175,7 @@
         <v>14</v>
       </c>
       <c r="F426" s="2">
-        <v>3991</v>
+        <v>1511</v>
       </c>
       <c r="G426" s="2" t="s">
         <v>15</v>
@@ -17207,7 +17207,7 @@
         <v>14</v>
       </c>
       <c r="F427" s="2">
-        <v>2839</v>
+        <v>2552</v>
       </c>
       <c r="G427" s="2" t="s">
         <v>15</v>
@@ -17239,7 +17239,7 @@
         <v>14</v>
       </c>
       <c r="F428" s="2">
-        <v>2343</v>
+        <v>1321</v>
       </c>
       <c r="G428" s="2" t="s">
         <v>15</v>
@@ -17271,7 +17271,7 @@
         <v>14</v>
       </c>
       <c r="F429" s="2">
-        <v>4266</v>
+        <v>3128</v>
       </c>
       <c r="G429" s="2" t="s">
         <v>15</v>
@@ -17303,7 +17303,7 @@
         <v>14</v>
       </c>
       <c r="F430" s="2">
-        <v>3168</v>
+        <v>3728</v>
       </c>
       <c r="G430" s="2" t="s">
         <v>15</v>
@@ -17335,7 +17335,7 @@
         <v>14</v>
       </c>
       <c r="F431" s="2">
-        <v>3419</v>
+        <v>1028</v>
       </c>
       <c r="G431" s="2" t="s">
         <v>15</v>
@@ -17367,7 +17367,7 @@
         <v>14</v>
       </c>
       <c r="F432" s="2">
-        <v>2427</v>
+        <v>1598</v>
       </c>
       <c r="G432" s="2" t="s">
         <v>15</v>
@@ -17399,7 +17399,7 @@
         <v>14</v>
       </c>
       <c r="F433" s="2">
-        <v>3228</v>
+        <v>1123</v>
       </c>
       <c r="G433" s="2" t="s">
         <v>15</v>
@@ -17431,7 +17431,7 @@
         <v>14</v>
       </c>
       <c r="F434" s="2">
-        <v>1442</v>
+        <v>4123</v>
       </c>
       <c r="G434" s="2" t="s">
         <v>15</v>
@@ -17463,7 +17463,7 @@
         <v>14</v>
       </c>
       <c r="F435" s="2">
-        <v>2748</v>
+        <v>2103</v>
       </c>
       <c r="G435" s="2" t="s">
         <v>15</v>
@@ -17495,7 +17495,7 @@
         <v>14</v>
       </c>
       <c r="F436" s="2">
-        <v>2163</v>
+        <v>978</v>
       </c>
       <c r="G436" s="2" t="s">
         <v>15</v>
@@ -17527,7 +17527,7 @@
         <v>14</v>
       </c>
       <c r="F437" s="2">
-        <v>4126</v>
+        <v>1489</v>
       </c>
       <c r="G437" s="2" t="s">
         <v>15</v>
@@ -17559,7 +17559,7 @@
         <v>14</v>
       </c>
       <c r="F438" s="2">
-        <v>1349</v>
+        <v>3820</v>
       </c>
       <c r="G438" s="2" t="s">
         <v>15</v>
@@ -17591,7 +17591,7 @@
         <v>14</v>
       </c>
       <c r="F439" s="2">
-        <v>2348</v>
+        <v>2802</v>
       </c>
       <c r="G439" s="2" t="s">
         <v>15</v>
@@ -17623,7 +17623,7 @@
         <v>14</v>
       </c>
       <c r="F440" s="2">
-        <v>4471</v>
+        <v>2977</v>
       </c>
       <c r="G440" s="2" t="s">
         <v>15</v>
@@ -17655,7 +17655,7 @@
         <v>14</v>
       </c>
       <c r="F441" s="2">
-        <v>2767</v>
+        <v>3950</v>
       </c>
       <c r="G441" s="2" t="s">
         <v>15</v>
@@ -17687,7 +17687,7 @@
         <v>14</v>
       </c>
       <c r="F442" s="2">
-        <v>2625</v>
+        <v>3959</v>
       </c>
       <c r="G442" s="2" t="s">
         <v>15</v>
@@ -17719,7 +17719,7 @@
         <v>14</v>
       </c>
       <c r="F443" s="2">
-        <v>3004</v>
+        <v>1936</v>
       </c>
       <c r="G443" s="2" t="s">
         <v>15</v>
@@ -17751,7 +17751,7 @@
         <v>14</v>
       </c>
       <c r="F444" s="2">
-        <v>4161</v>
+        <v>858</v>
       </c>
       <c r="G444" s="2" t="s">
         <v>15</v>
@@ -17783,7 +17783,7 @@
         <v>14</v>
       </c>
       <c r="F445" s="2">
-        <v>2282</v>
+        <v>2825</v>
       </c>
       <c r="G445" s="2" t="s">
         <v>15</v>
@@ -17815,7 +17815,7 @@
         <v>14</v>
       </c>
       <c r="F446" s="2">
-        <v>4669</v>
+        <v>1066</v>
       </c>
       <c r="G446" s="2" t="s">
         <v>15</v>
@@ -17847,7 +17847,7 @@
         <v>14</v>
       </c>
       <c r="F447" s="2">
-        <v>2402</v>
+        <v>4723</v>
       </c>
       <c r="G447" s="2" t="s">
         <v>15</v>
@@ -17879,7 +17879,7 @@
         <v>14</v>
       </c>
       <c r="F448" s="2">
-        <v>4396</v>
+        <v>1617</v>
       </c>
       <c r="G448" s="2" t="s">
         <v>15</v>
@@ -17911,7 +17911,7 @@
         <v>14</v>
       </c>
       <c r="F449" s="2">
-        <v>3518</v>
+        <v>1551</v>
       </c>
       <c r="G449" s="2" t="s">
         <v>15</v>
@@ -17943,7 +17943,7 @@
         <v>14</v>
       </c>
       <c r="F450" s="2">
-        <v>4164</v>
+        <v>4640</v>
       </c>
       <c r="G450" s="2" t="s">
         <v>15</v>
@@ -17975,7 +17975,7 @@
         <v>14</v>
       </c>
       <c r="F451" s="2">
-        <v>3059</v>
+        <v>1359</v>
       </c>
       <c r="G451" s="2" t="s">
         <v>15</v>
@@ -18007,7 +18007,7 @@
         <v>14</v>
       </c>
       <c r="F452" s="2">
-        <v>1455</v>
+        <v>1499</v>
       </c>
       <c r="G452" s="2" t="s">
         <v>15</v>
@@ -18039,7 +18039,7 @@
         <v>14</v>
       </c>
       <c r="F453" s="2">
-        <v>2037</v>
+        <v>4045</v>
       </c>
       <c r="G453" s="2" t="s">
         <v>15</v>
@@ -18071,7 +18071,7 @@
         <v>14</v>
       </c>
       <c r="F454" s="2">
-        <v>4117</v>
+        <v>3425</v>
       </c>
       <c r="G454" s="2" t="s">
         <v>15</v>
@@ -18103,7 +18103,7 @@
         <v>14</v>
       </c>
       <c r="F455" s="2">
-        <v>866</v>
+        <v>1446</v>
       </c>
       <c r="G455" s="2" t="s">
         <v>15</v>
@@ -18135,7 +18135,7 @@
         <v>14</v>
       </c>
       <c r="F456" s="2">
-        <v>1543</v>
+        <v>1455</v>
       </c>
       <c r="G456" s="2" t="s">
         <v>15</v>
@@ -18167,7 +18167,7 @@
         <v>14</v>
       </c>
       <c r="F457" s="2">
-        <v>4740</v>
+        <v>2489</v>
       </c>
       <c r="G457" s="2" t="s">
         <v>15</v>
@@ -18199,7 +18199,7 @@
         <v>14</v>
       </c>
       <c r="F458" s="2">
-        <v>3691</v>
+        <v>2144</v>
       </c>
       <c r="G458" s="2" t="s">
         <v>15</v>
@@ -18231,7 +18231,7 @@
         <v>14</v>
       </c>
       <c r="F459" s="2">
-        <v>2319</v>
+        <v>4021</v>
       </c>
       <c r="G459" s="2" t="s">
         <v>15</v>
@@ -18263,7 +18263,7 @@
         <v>14</v>
       </c>
       <c r="F460" s="2">
-        <v>3559</v>
+        <v>3260</v>
       </c>
       <c r="G460" s="2" t="s">
         <v>15</v>
@@ -18295,7 +18295,7 @@
         <v>14</v>
       </c>
       <c r="F461" s="2">
-        <v>4066</v>
+        <v>2199</v>
       </c>
       <c r="G461" s="2" t="s">
         <v>15</v>
@@ -18327,7 +18327,7 @@
         <v>14</v>
       </c>
       <c r="F462" s="2">
-        <v>1124</v>
+        <v>4139</v>
       </c>
       <c r="G462" s="2" t="s">
         <v>15</v>
@@ -18359,7 +18359,7 @@
         <v>14</v>
       </c>
       <c r="F463" s="2">
-        <v>3755</v>
+        <v>2648</v>
       </c>
       <c r="G463" s="2" t="s">
         <v>15</v>
@@ -18391,7 +18391,7 @@
         <v>14</v>
       </c>
       <c r="F464" s="2">
-        <v>2214</v>
+        <v>3646</v>
       </c>
       <c r="G464" s="2" t="s">
         <v>15</v>
@@ -18423,7 +18423,7 @@
         <v>14</v>
       </c>
       <c r="F465" s="2">
-        <v>3316</v>
+        <v>2292</v>
       </c>
       <c r="G465" s="2" t="s">
         <v>15</v>
@@ -18455,7 +18455,7 @@
         <v>14</v>
       </c>
       <c r="F466" s="2">
-        <v>3822</v>
+        <v>1156</v>
       </c>
       <c r="G466" s="2" t="s">
         <v>15</v>
@@ -18487,7 +18487,7 @@
         <v>14</v>
       </c>
       <c r="F467" s="2">
-        <v>4759</v>
+        <v>1251</v>
       </c>
       <c r="G467" s="2" t="s">
         <v>15</v>
@@ -18519,7 +18519,7 @@
         <v>14</v>
       </c>
       <c r="F468" s="2">
-        <v>4491</v>
+        <v>1540</v>
       </c>
       <c r="G468" s="2" t="s">
         <v>15</v>
@@ -18551,7 +18551,7 @@
         <v>14</v>
       </c>
       <c r="F469" s="2">
-        <v>3244</v>
+        <v>3431</v>
       </c>
       <c r="G469" s="2" t="s">
         <v>15</v>
@@ -18583,7 +18583,7 @@
         <v>14</v>
       </c>
       <c r="F470" s="2">
-        <v>1088</v>
+        <v>1916</v>
       </c>
       <c r="G470" s="2" t="s">
         <v>15</v>
@@ -18615,7 +18615,7 @@
         <v>14</v>
       </c>
       <c r="F471" s="2">
-        <v>2200</v>
+        <v>2510</v>
       </c>
       <c r="G471" s="2" t="s">
         <v>15</v>
@@ -18702,7 +18702,7 @@
         <v>14</v>
       </c>
       <c r="F2" s="2">
-        <v>3236</v>
+        <v>1892</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>15</v>
@@ -18734,7 +18734,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="2">
-        <v>2390</v>
+        <v>2657</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>15</v>
@@ -18766,7 +18766,7 @@
         <v>14</v>
       </c>
       <c r="F4" s="2">
-        <v>1290</v>
+        <v>3833</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
@@ -18798,7 +18798,7 @@
         <v>14</v>
       </c>
       <c r="F5" s="2">
-        <v>2447</v>
+        <v>1342</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
@@ -18830,7 +18830,7 @@
         <v>14</v>
       </c>
       <c r="F6" s="2">
-        <v>2634</v>
+        <v>4717</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -18862,7 +18862,7 @@
         <v>14</v>
       </c>
       <c r="F7" s="2">
-        <v>4151</v>
+        <v>2841</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -18894,7 +18894,7 @@
         <v>14</v>
       </c>
       <c r="F8" s="2">
-        <v>3490</v>
+        <v>3928</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -18926,7 +18926,7 @@
         <v>14</v>
       </c>
       <c r="F9" s="2">
-        <v>1780</v>
+        <v>1358</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -18958,7 +18958,7 @@
         <v>14</v>
       </c>
       <c r="F10" s="2">
-        <v>2604</v>
+        <v>2120</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
@@ -18990,7 +18990,7 @@
         <v>14</v>
       </c>
       <c r="F11" s="2">
-        <v>2651</v>
+        <v>1911</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
@@ -19022,7 +19022,7 @@
         <v>14</v>
       </c>
       <c r="F12" s="2">
-        <v>3166</v>
+        <v>4341</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
@@ -19054,7 +19054,7 @@
         <v>14</v>
       </c>
       <c r="F13" s="2">
-        <v>3430</v>
+        <v>1350</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -19086,7 +19086,7 @@
         <v>14</v>
       </c>
       <c r="F14" s="2">
-        <v>2399</v>
+        <v>1818</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -19118,7 +19118,7 @@
         <v>14</v>
       </c>
       <c r="F15" s="2">
-        <v>4216</v>
+        <v>3111</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -19150,7 +19150,7 @@
         <v>14</v>
       </c>
       <c r="F16" s="2">
-        <v>3401</v>
+        <v>3406</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
@@ -19182,7 +19182,7 @@
         <v>14</v>
       </c>
       <c r="F17" s="2">
-        <v>1180</v>
+        <v>1441</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
@@ -19214,7 +19214,7 @@
         <v>14</v>
       </c>
       <c r="F18" s="2">
-        <v>2413</v>
+        <v>1774</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
@@ -19246,7 +19246,7 @@
         <v>14</v>
       </c>
       <c r="F19" s="2">
-        <v>4102</v>
+        <v>4142</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
@@ -19278,7 +19278,7 @@
         <v>14</v>
       </c>
       <c r="F20" s="2">
-        <v>2171</v>
+        <v>4517</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
@@ -19310,7 +19310,7 @@
         <v>14</v>
       </c>
       <c r="F21" s="2">
-        <v>2909</v>
+        <v>3005</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -19342,7 +19342,7 @@
         <v>14</v>
       </c>
       <c r="F22" s="2">
-        <v>1555</v>
+        <v>2613</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -19374,7 +19374,7 @@
         <v>14</v>
       </c>
       <c r="F23" s="2">
-        <v>4424</v>
+        <v>1642</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -19406,7 +19406,7 @@
         <v>14</v>
       </c>
       <c r="F24" s="2">
-        <v>3598</v>
+        <v>931</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -19438,7 +19438,7 @@
         <v>14</v>
       </c>
       <c r="F25" s="2">
-        <v>1832</v>
+        <v>3439</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -19470,7 +19470,7 @@
         <v>14</v>
       </c>
       <c r="F26" s="2">
-        <v>4454</v>
+        <v>3388</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -19502,7 +19502,7 @@
         <v>14</v>
       </c>
       <c r="F27" s="2">
-        <v>3734</v>
+        <v>3024</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>15</v>
@@ -19534,7 +19534,7 @@
         <v>14</v>
       </c>
       <c r="F28" s="2">
-        <v>2823</v>
+        <v>3016</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>15</v>
@@ -19566,7 +19566,7 @@
         <v>14</v>
       </c>
       <c r="F29" s="2">
-        <v>4784</v>
+        <v>3449</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>15</v>
@@ -19598,7 +19598,7 @@
         <v>14</v>
       </c>
       <c r="F30" s="2">
-        <v>3944</v>
+        <v>3286</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>15</v>
@@ -19630,7 +19630,7 @@
         <v>14</v>
       </c>
       <c r="F31" s="2">
-        <v>3950</v>
+        <v>3852</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>15</v>
@@ -19662,7 +19662,7 @@
         <v>14</v>
       </c>
       <c r="F32" s="2">
-        <v>3963</v>
+        <v>2881</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>15</v>
@@ -19694,7 +19694,7 @@
         <v>14</v>
       </c>
       <c r="F33" s="2">
-        <v>1782</v>
+        <v>4283</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>15</v>
@@ -19726,7 +19726,7 @@
         <v>14</v>
       </c>
       <c r="F34" s="2">
-        <v>1097</v>
+        <v>4255</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>15</v>
@@ -19758,7 +19758,7 @@
         <v>14</v>
       </c>
       <c r="F35" s="2">
-        <v>2200</v>
+        <v>3792</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>15</v>
@@ -19790,7 +19790,7 @@
         <v>14</v>
       </c>
       <c r="F36" s="2">
-        <v>3148</v>
+        <v>2822</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>15</v>
@@ -19822,7 +19822,7 @@
         <v>14</v>
       </c>
       <c r="F37" s="2">
-        <v>1393</v>
+        <v>1463</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>15</v>
@@ -19854,7 +19854,7 @@
         <v>14</v>
       </c>
       <c r="F38" s="2">
-        <v>2720</v>
+        <v>3017</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>15</v>
@@ -19886,7 +19886,7 @@
         <v>14</v>
       </c>
       <c r="F39" s="2">
-        <v>1019</v>
+        <v>3465</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>15</v>
@@ -19918,7 +19918,7 @@
         <v>14</v>
       </c>
       <c r="F40" s="2">
-        <v>1657</v>
+        <v>3879</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>15</v>
@@ -19950,7 +19950,7 @@
         <v>14</v>
       </c>
       <c r="F41" s="2">
-        <v>2664</v>
+        <v>3672</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>15</v>
@@ -19982,7 +19982,7 @@
         <v>14</v>
       </c>
       <c r="F42" s="2">
-        <v>4219</v>
+        <v>2689</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>15</v>
@@ -20014,7 +20014,7 @@
         <v>14</v>
       </c>
       <c r="F43" s="2">
-        <v>4725</v>
+        <v>3522</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>15</v>
@@ -20046,7 +20046,7 @@
         <v>14</v>
       </c>
       <c r="F44" s="2">
-        <v>2732</v>
+        <v>3834</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>15</v>
@@ -20078,7 +20078,7 @@
         <v>14</v>
       </c>
       <c r="F45" s="2">
-        <v>2402</v>
+        <v>3772</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>15</v>
@@ -20110,7 +20110,7 @@
         <v>14</v>
       </c>
       <c r="F46" s="2">
-        <v>4693</v>
+        <v>3585</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>15</v>
@@ -20142,7 +20142,7 @@
         <v>14</v>
       </c>
       <c r="F47" s="2">
-        <v>3033</v>
+        <v>2015</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>15</v>
@@ -20174,7 +20174,7 @@
         <v>14</v>
       </c>
       <c r="F48" s="2">
-        <v>3664</v>
+        <v>2760</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>15</v>
@@ -20206,7 +20206,7 @@
         <v>14</v>
       </c>
       <c r="F49" s="2">
-        <v>2465</v>
+        <v>1637</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>15</v>
@@ -20238,7 +20238,7 @@
         <v>14</v>
       </c>
       <c r="F50" s="2">
-        <v>4670</v>
+        <v>4671</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>15</v>
@@ -20270,7 +20270,7 @@
         <v>14</v>
       </c>
       <c r="F51" s="2">
-        <v>3343</v>
+        <v>1390</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>15</v>
@@ -20302,7 +20302,7 @@
         <v>14</v>
       </c>
       <c r="F52" s="2">
-        <v>2369</v>
+        <v>4759</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>15</v>
@@ -20334,7 +20334,7 @@
         <v>14</v>
       </c>
       <c r="F53" s="2">
-        <v>2569</v>
+        <v>3541</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>15</v>
@@ -20366,7 +20366,7 @@
         <v>14</v>
       </c>
       <c r="F54" s="2">
-        <v>4740</v>
+        <v>895</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>15</v>
@@ -20398,7 +20398,7 @@
         <v>14</v>
       </c>
       <c r="F55" s="2">
-        <v>4393</v>
+        <v>1575</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>15</v>
@@ -20430,7 +20430,7 @@
         <v>14</v>
       </c>
       <c r="F56" s="2">
-        <v>3464</v>
+        <v>2775</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>15</v>
@@ -20462,7 +20462,7 @@
         <v>14</v>
       </c>
       <c r="F57" s="2">
-        <v>3370</v>
+        <v>4469</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>15</v>
@@ -20494,7 +20494,7 @@
         <v>14</v>
       </c>
       <c r="F58" s="2">
-        <v>1863</v>
+        <v>3476</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>15</v>
@@ -20526,7 +20526,7 @@
         <v>14</v>
       </c>
       <c r="F59" s="2">
-        <v>2116</v>
+        <v>3274</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>15</v>
@@ -20558,7 +20558,7 @@
         <v>14</v>
       </c>
       <c r="F60" s="2">
-        <v>3820</v>
+        <v>2840</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>15</v>
@@ -20590,7 +20590,7 @@
         <v>14</v>
       </c>
       <c r="F61" s="2">
-        <v>1146</v>
+        <v>3867</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>15</v>
@@ -20622,7 +20622,7 @@
         <v>14</v>
       </c>
       <c r="F62" s="2">
-        <v>4759</v>
+        <v>2552</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>15</v>
@@ -20654,7 +20654,7 @@
         <v>14</v>
       </c>
       <c r="F63" s="2">
-        <v>3694</v>
+        <v>1122</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>15</v>
@@ -20686,7 +20686,7 @@
         <v>14</v>
       </c>
       <c r="F64" s="2">
-        <v>844</v>
+        <v>3103</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>15</v>
@@ -20718,7 +20718,7 @@
         <v>14</v>
       </c>
       <c r="F65" s="2">
-        <v>1944</v>
+        <v>4147</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>15</v>
@@ -20750,7 +20750,7 @@
         <v>14</v>
       </c>
       <c r="F66" s="2">
-        <v>2716</v>
+        <v>2349</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>15</v>
@@ -20782,7 +20782,7 @@
         <v>14</v>
       </c>
       <c r="F67" s="2">
-        <v>867</v>
+        <v>2928</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>15</v>
@@ -20814,7 +20814,7 @@
         <v>14</v>
       </c>
       <c r="F68" s="2">
-        <v>1814</v>
+        <v>3240</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>15</v>
@@ -20846,7 +20846,7 @@
         <v>14</v>
       </c>
       <c r="F69" s="2">
-        <v>3832</v>
+        <v>2796</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>15</v>
@@ -20878,7 +20878,7 @@
         <v>14</v>
       </c>
       <c r="F70" s="2">
-        <v>2673</v>
+        <v>4548</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>15</v>
@@ -20910,7 +20910,7 @@
         <v>14</v>
       </c>
       <c r="F71" s="2">
-        <v>2784</v>
+        <v>871</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>15</v>
@@ -20942,7 +20942,7 @@
         <v>14</v>
       </c>
       <c r="F72" s="2">
-        <v>1651</v>
+        <v>2941</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>15</v>
@@ -20974,7 +20974,7 @@
         <v>14</v>
       </c>
       <c r="F73" s="2">
-        <v>2179</v>
+        <v>3912</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>15</v>
@@ -21006,7 +21006,7 @@
         <v>14</v>
       </c>
       <c r="F74" s="2">
-        <v>4617</v>
+        <v>3196</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>15</v>
@@ -21038,7 +21038,7 @@
         <v>14</v>
       </c>
       <c r="F75" s="2">
-        <v>2085</v>
+        <v>3252</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>15</v>
@@ -21070,7 +21070,7 @@
         <v>14</v>
       </c>
       <c r="F76" s="2">
-        <v>3037</v>
+        <v>1264</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>15</v>
@@ -21102,7 +21102,7 @@
         <v>14</v>
       </c>
       <c r="F77" s="2">
-        <v>1990</v>
+        <v>1210</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>15</v>
@@ -21134,7 +21134,7 @@
         <v>14</v>
       </c>
       <c r="F78" s="2">
-        <v>3375</v>
+        <v>2679</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>15</v>
@@ -21166,7 +21166,7 @@
         <v>14</v>
       </c>
       <c r="F79" s="2">
-        <v>1294</v>
+        <v>2679</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>15</v>
@@ -21198,7 +21198,7 @@
         <v>14</v>
       </c>
       <c r="F80" s="2">
-        <v>3849</v>
+        <v>4275</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>15</v>
@@ -21230,7 +21230,7 @@
         <v>14</v>
       </c>
       <c r="F81" s="2">
-        <v>4284</v>
+        <v>2458</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>15</v>
@@ -21262,7 +21262,7 @@
         <v>14</v>
       </c>
       <c r="F82" s="2">
-        <v>2838</v>
+        <v>1359</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>15</v>
@@ -21294,7 +21294,7 @@
         <v>14</v>
       </c>
       <c r="F83" s="2">
-        <v>2512</v>
+        <v>1899</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>15</v>
@@ -21326,7 +21326,7 @@
         <v>14</v>
       </c>
       <c r="F84" s="2">
-        <v>4195</v>
+        <v>3909</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>15</v>
@@ -21358,7 +21358,7 @@
         <v>14</v>
       </c>
       <c r="F85" s="2">
-        <v>3131</v>
+        <v>4388</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>15</v>
@@ -21390,7 +21390,7 @@
         <v>14</v>
       </c>
       <c r="F86" s="2">
-        <v>1303</v>
+        <v>3797</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>15</v>
@@ -21422,7 +21422,7 @@
         <v>14</v>
       </c>
       <c r="F87" s="2">
-        <v>4743</v>
+        <v>2659</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>15</v>
@@ -21454,7 +21454,7 @@
         <v>14</v>
       </c>
       <c r="F88" s="2">
-        <v>2096</v>
+        <v>2596</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>15</v>
@@ -21486,7 +21486,7 @@
         <v>14</v>
       </c>
       <c r="F89" s="2">
-        <v>1067</v>
+        <v>3583</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>15</v>
@@ -21518,7 +21518,7 @@
         <v>14</v>
       </c>
       <c r="F90" s="2">
-        <v>2068</v>
+        <v>4453</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>15</v>
@@ -21550,7 +21550,7 @@
         <v>14</v>
       </c>
       <c r="F91" s="2">
-        <v>3691</v>
+        <v>3852</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>15</v>
@@ -21582,7 +21582,7 @@
         <v>14</v>
       </c>
       <c r="F92" s="2">
-        <v>4399</v>
+        <v>2716</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>15</v>
@@ -21614,7 +21614,7 @@
         <v>14</v>
       </c>
       <c r="F93" s="2">
-        <v>4601</v>
+        <v>4512</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>15</v>
@@ -21646,7 +21646,7 @@
         <v>14</v>
       </c>
       <c r="F94" s="2">
-        <v>3681</v>
+        <v>3503</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>15</v>
@@ -21678,7 +21678,7 @@
         <v>14</v>
       </c>
       <c r="F95" s="2">
-        <v>4175</v>
+        <v>1796</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>15</v>
@@ -21710,7 +21710,7 @@
         <v>14</v>
       </c>
       <c r="F96" s="2">
-        <v>1519</v>
+        <v>3640</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>15</v>
@@ -21742,7 +21742,7 @@
         <v>14</v>
       </c>
       <c r="F97" s="2">
-        <v>2362</v>
+        <v>3357</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>15</v>
@@ -21774,7 +21774,7 @@
         <v>14</v>
       </c>
       <c r="F98" s="2">
-        <v>2818</v>
+        <v>1280</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>15</v>
@@ -21806,7 +21806,7 @@
         <v>14</v>
       </c>
       <c r="F99" s="2">
-        <v>1398</v>
+        <v>4473</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>15</v>
@@ -21838,7 +21838,7 @@
         <v>14</v>
       </c>
       <c r="F100" s="2">
-        <v>4780</v>
+        <v>3644</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>15</v>
@@ -21870,7 +21870,7 @@
         <v>14</v>
       </c>
       <c r="F101" s="2">
-        <v>4460</v>
+        <v>3736</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>15</v>
@@ -21902,7 +21902,7 @@
         <v>14</v>
       </c>
       <c r="F102" s="2">
-        <v>4603</v>
+        <v>3532</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>15</v>
@@ -21934,7 +21934,7 @@
         <v>14</v>
       </c>
       <c r="F103" s="2">
-        <v>2372</v>
+        <v>4706</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>15</v>
@@ -21966,7 +21966,7 @@
         <v>14</v>
       </c>
       <c r="F104" s="2">
-        <v>2911</v>
+        <v>2716</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>15</v>
@@ -21998,7 +21998,7 @@
         <v>14</v>
       </c>
       <c r="F105" s="2">
-        <v>3770</v>
+        <v>4043</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>15</v>
@@ -22030,7 +22030,7 @@
         <v>14</v>
       </c>
       <c r="F106" s="2">
-        <v>2369</v>
+        <v>936</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>15</v>
@@ -22062,7 +22062,7 @@
         <v>14</v>
       </c>
       <c r="F107" s="2">
-        <v>1208</v>
+        <v>1887</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>15</v>
@@ -22094,7 +22094,7 @@
         <v>14</v>
       </c>
       <c r="F108" s="2">
-        <v>2582</v>
+        <v>4490</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>15</v>
@@ -22126,7 +22126,7 @@
         <v>14</v>
       </c>
       <c r="F109" s="2">
-        <v>3267</v>
+        <v>4322</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>15</v>
@@ -22158,7 +22158,7 @@
         <v>14</v>
       </c>
       <c r="F110" s="2">
-        <v>3069</v>
+        <v>3535</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>15</v>
@@ -22190,7 +22190,7 @@
         <v>14</v>
       </c>
       <c r="F111" s="2">
-        <v>1074</v>
+        <v>3636</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>15</v>
@@ -22222,7 +22222,7 @@
         <v>14</v>
       </c>
       <c r="F112" s="2">
-        <v>1364</v>
+        <v>3404</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>15</v>
@@ -22254,7 +22254,7 @@
         <v>14</v>
       </c>
       <c r="F113" s="2">
-        <v>2563</v>
+        <v>2371</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>15</v>
@@ -22286,7 +22286,7 @@
         <v>14</v>
       </c>
       <c r="F114" s="2">
-        <v>2698</v>
+        <v>2447</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>15</v>
@@ -22318,7 +22318,7 @@
         <v>14</v>
       </c>
       <c r="F115" s="2">
-        <v>1391</v>
+        <v>4309</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>15</v>
@@ -22350,7 +22350,7 @@
         <v>14</v>
       </c>
       <c r="F116" s="2">
-        <v>4641</v>
+        <v>2190</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>15</v>
@@ -22382,7 +22382,7 @@
         <v>14</v>
       </c>
       <c r="F117" s="2">
-        <v>4420</v>
+        <v>3354</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>15</v>
@@ -22414,7 +22414,7 @@
         <v>14</v>
       </c>
       <c r="F118" s="2">
-        <v>1535</v>
+        <v>2050</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>15</v>
@@ -22446,7 +22446,7 @@
         <v>14</v>
       </c>
       <c r="F119" s="2">
-        <v>3600</v>
+        <v>1811</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>15</v>
@@ -22478,7 +22478,7 @@
         <v>14</v>
       </c>
       <c r="F120" s="2">
-        <v>1416</v>
+        <v>3906</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>15</v>
@@ -22510,7 +22510,7 @@
         <v>14</v>
       </c>
       <c r="F121" s="2">
-        <v>1437</v>
+        <v>2582</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>15</v>
@@ -22542,7 +22542,7 @@
         <v>14</v>
       </c>
       <c r="F122" s="2">
-        <v>4612</v>
+        <v>4230</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>15</v>
@@ -22574,7 +22574,7 @@
         <v>14</v>
       </c>
       <c r="F123" s="2">
-        <v>2057</v>
+        <v>4282</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>15</v>
@@ -22606,7 +22606,7 @@
         <v>14</v>
       </c>
       <c r="F124" s="2">
-        <v>1616</v>
+        <v>2338</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>15</v>
@@ -22638,7 +22638,7 @@
         <v>14</v>
       </c>
       <c r="F125" s="2">
-        <v>2545</v>
+        <v>1894</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>15</v>
@@ -22670,7 +22670,7 @@
         <v>14</v>
       </c>
       <c r="F126" s="2">
-        <v>2754</v>
+        <v>1079</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>15</v>
@@ -22702,7 +22702,7 @@
         <v>14</v>
       </c>
       <c r="F127" s="2">
-        <v>4187</v>
+        <v>1441</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>15</v>
@@ -22734,7 +22734,7 @@
         <v>14</v>
       </c>
       <c r="F128" s="2">
-        <v>1658</v>
+        <v>4145</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>15</v>
@@ -22766,7 +22766,7 @@
         <v>14</v>
       </c>
       <c r="F129" s="2">
-        <v>1703</v>
+        <v>2952</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>15</v>
@@ -22798,7 +22798,7 @@
         <v>14</v>
       </c>
       <c r="F130" s="2">
-        <v>1639</v>
+        <v>4548</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>15</v>
@@ -22830,7 +22830,7 @@
         <v>14</v>
       </c>
       <c r="F131" s="2">
-        <v>3157</v>
+        <v>3228</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>15</v>
@@ -22862,7 +22862,7 @@
         <v>14</v>
       </c>
       <c r="F132" s="2">
-        <v>3685</v>
+        <v>2546</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>15</v>
@@ -22894,7 +22894,7 @@
         <v>14</v>
       </c>
       <c r="F133" s="2">
-        <v>3325</v>
+        <v>4333</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>15</v>
@@ -22926,7 +22926,7 @@
         <v>14</v>
       </c>
       <c r="F134" s="2">
-        <v>1491</v>
+        <v>2125</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>15</v>
@@ -22958,7 +22958,7 @@
         <v>14</v>
       </c>
       <c r="F135" s="2">
-        <v>2283</v>
+        <v>951</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>15</v>
@@ -22990,7 +22990,7 @@
         <v>14</v>
       </c>
       <c r="F136" s="2">
-        <v>1028</v>
+        <v>930</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>15</v>
@@ -23022,7 +23022,7 @@
         <v>14</v>
       </c>
       <c r="F137" s="2">
-        <v>2346</v>
+        <v>3971</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>15</v>
@@ -23054,7 +23054,7 @@
         <v>14</v>
       </c>
       <c r="F138" s="2">
-        <v>3119</v>
+        <v>3709</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>15</v>
@@ -23086,7 +23086,7 @@
         <v>14</v>
       </c>
       <c r="F139" s="2">
-        <v>3742</v>
+        <v>3733</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>15</v>
@@ -23118,7 +23118,7 @@
         <v>14</v>
       </c>
       <c r="F140" s="2">
-        <v>4486</v>
+        <v>2216</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>15</v>
@@ -23150,7 +23150,7 @@
         <v>14</v>
       </c>
       <c r="F141" s="2">
-        <v>4591</v>
+        <v>1067</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>15</v>
@@ -23182,7 +23182,7 @@
         <v>14</v>
       </c>
       <c r="F142" s="2">
-        <v>2170</v>
+        <v>4156</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>15</v>
@@ -23214,7 +23214,7 @@
         <v>14</v>
       </c>
       <c r="F143" s="2">
-        <v>1628</v>
+        <v>2000</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>15</v>
@@ -23246,7 +23246,7 @@
         <v>14</v>
       </c>
       <c r="F144" s="2">
-        <v>3752</v>
+        <v>1901</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>15</v>
@@ -23278,7 +23278,7 @@
         <v>14</v>
       </c>
       <c r="F145" s="2">
-        <v>1819</v>
+        <v>4351</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>15</v>
@@ -23310,7 +23310,7 @@
         <v>14</v>
       </c>
       <c r="F146" s="2">
-        <v>2297</v>
+        <v>1911</v>
       </c>
       <c r="G146" s="2" t="s">
         <v>15</v>
@@ -23342,7 +23342,7 @@
         <v>14</v>
       </c>
       <c r="F147" s="2">
-        <v>1419</v>
+        <v>4677</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>15</v>
@@ -23374,7 +23374,7 @@
         <v>14</v>
       </c>
       <c r="F148" s="2">
-        <v>1419</v>
+        <v>3896</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>15</v>
@@ -23406,7 +23406,7 @@
         <v>14</v>
       </c>
       <c r="F149" s="2">
-        <v>3850</v>
+        <v>1015</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>15</v>
@@ -23438,7 +23438,7 @@
         <v>14</v>
       </c>
       <c r="F150" s="2">
-        <v>4225</v>
+        <v>1233</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>15</v>
@@ -23470,7 +23470,7 @@
         <v>14</v>
       </c>
       <c r="F151" s="2">
-        <v>1628</v>
+        <v>1168</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>15</v>
@@ -23502,7 +23502,7 @@
         <v>14</v>
       </c>
       <c r="F152" s="2">
-        <v>2305</v>
+        <v>1687</v>
       </c>
       <c r="G152" s="2" t="s">
         <v>15</v>
@@ -23534,7 +23534,7 @@
         <v>14</v>
       </c>
       <c r="F153" s="2">
-        <v>2293</v>
+        <v>3482</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>15</v>
@@ -23566,7 +23566,7 @@
         <v>14</v>
       </c>
       <c r="F154" s="2">
-        <v>4491</v>
+        <v>4002</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>15</v>
@@ -23598,7 +23598,7 @@
         <v>14</v>
       </c>
       <c r="F155" s="2">
-        <v>1082</v>
+        <v>3815</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>15</v>
@@ -23630,7 +23630,7 @@
         <v>14</v>
       </c>
       <c r="F156" s="2">
-        <v>4596</v>
+        <v>1535</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>15</v>
@@ -23662,7 +23662,7 @@
         <v>14</v>
       </c>
       <c r="F157" s="2">
-        <v>1814</v>
+        <v>858</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>15</v>
@@ -23694,7 +23694,7 @@
         <v>14</v>
       </c>
       <c r="F158" s="2">
-        <v>1428</v>
+        <v>4236</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>15</v>
@@ -23726,7 +23726,7 @@
         <v>14</v>
       </c>
       <c r="F159" s="2">
-        <v>4172</v>
+        <v>4310</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>15</v>
@@ -23758,7 +23758,7 @@
         <v>14</v>
       </c>
       <c r="F160" s="2">
-        <v>3548</v>
+        <v>2367</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>15</v>
@@ -23790,7 +23790,7 @@
         <v>14</v>
       </c>
       <c r="F161" s="2">
-        <v>1339</v>
+        <v>909</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>15</v>
@@ -23822,7 +23822,7 @@
         <v>14</v>
       </c>
       <c r="F162" s="2">
-        <v>3106</v>
+        <v>3832</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>15</v>
@@ -23854,7 +23854,7 @@
         <v>14</v>
       </c>
       <c r="F163" s="2">
-        <v>863</v>
+        <v>4270</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>15</v>
@@ -23886,7 +23886,7 @@
         <v>14</v>
       </c>
       <c r="F164" s="2">
-        <v>3795</v>
+        <v>1176</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>15</v>
@@ -23918,7 +23918,7 @@
         <v>14</v>
       </c>
       <c r="F165" s="2">
-        <v>3434</v>
+        <v>3931</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>15</v>
@@ -23950,7 +23950,7 @@
         <v>14</v>
       </c>
       <c r="F166" s="2">
-        <v>4229</v>
+        <v>855</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>15</v>
@@ -23982,7 +23982,7 @@
         <v>14</v>
       </c>
       <c r="F167" s="2">
-        <v>2856</v>
+        <v>3118</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>15</v>
@@ -24014,7 +24014,7 @@
         <v>14</v>
       </c>
       <c r="F168" s="2">
-        <v>3959</v>
+        <v>1339</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>15</v>
@@ -24046,7 +24046,7 @@
         <v>14</v>
       </c>
       <c r="F169" s="2">
-        <v>2814</v>
+        <v>4456</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>15</v>
@@ -24078,7 +24078,7 @@
         <v>14</v>
       </c>
       <c r="F170" s="2">
-        <v>3407</v>
+        <v>3038</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>15</v>
@@ -24110,7 +24110,7 @@
         <v>14</v>
       </c>
       <c r="F171" s="2">
-        <v>1464</v>
+        <v>4012</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>15</v>
@@ -24142,7 +24142,7 @@
         <v>14</v>
       </c>
       <c r="F172" s="2">
-        <v>4551</v>
+        <v>2879</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>15</v>
@@ -24174,7 +24174,7 @@
         <v>14</v>
       </c>
       <c r="F173" s="2">
-        <v>1316</v>
+        <v>4487</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>15</v>
@@ -24206,7 +24206,7 @@
         <v>14</v>
       </c>
       <c r="F174" s="2">
-        <v>3808</v>
+        <v>2318</v>
       </c>
       <c r="G174" s="2" t="s">
         <v>15</v>
@@ -24238,7 +24238,7 @@
         <v>14</v>
       </c>
       <c r="F175" s="2">
-        <v>2115</v>
+        <v>2338</v>
       </c>
       <c r="G175" s="2" t="s">
         <v>15</v>
@@ -24270,7 +24270,7 @@
         <v>14</v>
       </c>
       <c r="F176" s="2">
-        <v>1113</v>
+        <v>3218</v>
       </c>
       <c r="G176" s="2" t="s">
         <v>15</v>
@@ -24302,7 +24302,7 @@
         <v>14</v>
       </c>
       <c r="F177" s="2">
-        <v>2158</v>
+        <v>4270</v>
       </c>
       <c r="G177" s="2" t="s">
         <v>15</v>
@@ -24334,7 +24334,7 @@
         <v>14</v>
       </c>
       <c r="F178" s="2">
-        <v>4664</v>
+        <v>2323</v>
       </c>
       <c r="G178" s="2" t="s">
         <v>15</v>
@@ -24366,7 +24366,7 @@
         <v>14</v>
       </c>
       <c r="F179" s="2">
-        <v>941</v>
+        <v>2073</v>
       </c>
       <c r="G179" s="2" t="s">
         <v>15</v>
@@ -24398,7 +24398,7 @@
         <v>14</v>
       </c>
       <c r="F180" s="2">
-        <v>816</v>
+        <v>2820</v>
       </c>
       <c r="G180" s="2" t="s">
         <v>15</v>
@@ -24430,7 +24430,7 @@
         <v>14</v>
       </c>
       <c r="F181" s="2">
-        <v>4545</v>
+        <v>4567</v>
       </c>
       <c r="G181" s="2" t="s">
         <v>15</v>
@@ -24462,7 +24462,7 @@
         <v>14</v>
       </c>
       <c r="F182" s="2">
-        <v>3551</v>
+        <v>1004</v>
       </c>
       <c r="G182" s="2" t="s">
         <v>15</v>
@@ -24494,7 +24494,7 @@
         <v>14</v>
       </c>
       <c r="F183" s="2">
-        <v>4786</v>
+        <v>3521</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>15</v>
@@ -24526,7 +24526,7 @@
         <v>14</v>
       </c>
       <c r="F184" s="2">
-        <v>2260</v>
+        <v>3340</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>15</v>
@@ -24558,7 +24558,7 @@
         <v>14</v>
       </c>
       <c r="F185" s="2">
-        <v>3813</v>
+        <v>1381</v>
       </c>
       <c r="G185" s="2" t="s">
         <v>15</v>
@@ -24590,7 +24590,7 @@
         <v>14</v>
       </c>
       <c r="F186" s="2">
-        <v>2905</v>
+        <v>2213</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>15</v>
@@ -24622,7 +24622,7 @@
         <v>14</v>
       </c>
       <c r="F187" s="2">
-        <v>1535</v>
+        <v>2486</v>
       </c>
       <c r="G187" s="2" t="s">
         <v>15</v>
@@ -24654,7 +24654,7 @@
         <v>14</v>
       </c>
       <c r="F188" s="2">
-        <v>1801</v>
+        <v>2927</v>
       </c>
       <c r="G188" s="2" t="s">
         <v>15</v>
@@ -24686,7 +24686,7 @@
         <v>14</v>
       </c>
       <c r="F189" s="2">
-        <v>3161</v>
+        <v>1799</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>15</v>
@@ -24718,7 +24718,7 @@
         <v>14</v>
       </c>
       <c r="F190" s="2">
-        <v>2613</v>
+        <v>2840</v>
       </c>
       <c r="G190" s="2" t="s">
         <v>15</v>
@@ -24750,7 +24750,7 @@
         <v>14</v>
       </c>
       <c r="F191" s="2">
-        <v>1688</v>
+        <v>4130</v>
       </c>
       <c r="G191" s="2" t="s">
         <v>15</v>
@@ -24782,7 +24782,7 @@
         <v>14</v>
       </c>
       <c r="F192" s="2">
-        <v>3561</v>
+        <v>3410</v>
       </c>
       <c r="G192" s="2" t="s">
         <v>15</v>
@@ -24814,7 +24814,7 @@
         <v>14</v>
       </c>
       <c r="F193" s="2">
-        <v>1151</v>
+        <v>2684</v>
       </c>
       <c r="G193" s="2" t="s">
         <v>15</v>
@@ -24846,7 +24846,7 @@
         <v>14</v>
       </c>
       <c r="F194" s="2">
-        <v>2144</v>
+        <v>2487</v>
       </c>
       <c r="G194" s="2" t="s">
         <v>15</v>
@@ -24878,7 +24878,7 @@
         <v>14</v>
       </c>
       <c r="F195" s="2">
-        <v>3735</v>
+        <v>4360</v>
       </c>
       <c r="G195" s="2" t="s">
         <v>15</v>
@@ -24910,7 +24910,7 @@
         <v>14</v>
       </c>
       <c r="F196" s="2">
-        <v>2046</v>
+        <v>1653</v>
       </c>
       <c r="G196" s="2" t="s">
         <v>15</v>
@@ -24942,7 +24942,7 @@
         <v>14</v>
       </c>
       <c r="F197" s="2">
-        <v>4527</v>
+        <v>4264</v>
       </c>
       <c r="G197" s="2" t="s">
         <v>15</v>
@@ -24974,7 +24974,7 @@
         <v>14</v>
       </c>
       <c r="F198" s="2">
-        <v>1832</v>
+        <v>3985</v>
       </c>
       <c r="G198" s="2" t="s">
         <v>15</v>
@@ -25006,7 +25006,7 @@
         <v>14</v>
       </c>
       <c r="F199" s="2">
-        <v>2561</v>
+        <v>1090</v>
       </c>
       <c r="G199" s="2" t="s">
         <v>15</v>
@@ -25038,7 +25038,7 @@
         <v>14</v>
       </c>
       <c r="F200" s="2">
-        <v>4254</v>
+        <v>2242</v>
       </c>
       <c r="G200" s="2" t="s">
         <v>15</v>
@@ -25070,7 +25070,7 @@
         <v>14</v>
       </c>
       <c r="F201" s="2">
-        <v>2891</v>
+        <v>4210</v>
       </c>
       <c r="G201" s="2" t="s">
         <v>15</v>
@@ -25102,7 +25102,7 @@
         <v>14</v>
       </c>
       <c r="F202" s="2">
-        <v>2518</v>
+        <v>3822</v>
       </c>
       <c r="G202" s="2" t="s">
         <v>15</v>
@@ -25134,7 +25134,7 @@
         <v>14</v>
       </c>
       <c r="F203" s="2">
-        <v>2014</v>
+        <v>1669</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>15</v>
@@ -25166,7 +25166,7 @@
         <v>14</v>
       </c>
       <c r="F204" s="2">
-        <v>3477</v>
+        <v>1162</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>15</v>
@@ -25198,7 +25198,7 @@
         <v>14</v>
       </c>
       <c r="F205" s="2">
-        <v>2222</v>
+        <v>3098</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>15</v>
@@ -25230,7 +25230,7 @@
         <v>14</v>
       </c>
       <c r="F206" s="2">
-        <v>4716</v>
+        <v>2630</v>
       </c>
       <c r="G206" s="2" t="s">
         <v>15</v>
@@ -25262,7 +25262,7 @@
         <v>14</v>
       </c>
       <c r="F207" s="2">
-        <v>1067</v>
+        <v>3207</v>
       </c>
       <c r="G207" s="2" t="s">
         <v>15</v>
@@ -25294,7 +25294,7 @@
         <v>14</v>
       </c>
       <c r="F208" s="2">
-        <v>1011</v>
+        <v>3159</v>
       </c>
       <c r="G208" s="2" t="s">
         <v>15</v>
@@ -25326,7 +25326,7 @@
         <v>14</v>
       </c>
       <c r="F209" s="2">
-        <v>3641</v>
+        <v>939</v>
       </c>
       <c r="G209" s="2" t="s">
         <v>15</v>
@@ -25358,7 +25358,7 @@
         <v>14</v>
       </c>
       <c r="F210" s="2">
-        <v>4275</v>
+        <v>2976</v>
       </c>
       <c r="G210" s="2" t="s">
         <v>15</v>
@@ -25390,7 +25390,7 @@
         <v>14</v>
       </c>
       <c r="F211" s="2">
-        <v>4474</v>
+        <v>2807</v>
       </c>
       <c r="G211" s="2" t="s">
         <v>15</v>
@@ -25422,7 +25422,7 @@
         <v>14</v>
       </c>
       <c r="F212" s="2">
-        <v>2731</v>
+        <v>2640</v>
       </c>
       <c r="G212" s="2" t="s">
         <v>15</v>
@@ -25454,7 +25454,7 @@
         <v>14</v>
       </c>
       <c r="F213" s="2">
-        <v>2898</v>
+        <v>3235</v>
       </c>
       <c r="G213" s="2" t="s">
         <v>15</v>
@@ -25486,7 +25486,7 @@
         <v>14</v>
       </c>
       <c r="F214" s="2">
-        <v>1365</v>
+        <v>2419</v>
       </c>
       <c r="G214" s="2" t="s">
         <v>15</v>
@@ -25518,7 +25518,7 @@
         <v>14</v>
       </c>
       <c r="F215" s="2">
-        <v>1256</v>
+        <v>3779</v>
       </c>
       <c r="G215" s="2" t="s">
         <v>15</v>
@@ -25550,7 +25550,7 @@
         <v>14</v>
       </c>
       <c r="F216" s="2">
-        <v>2086</v>
+        <v>2554</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>15</v>
@@ -25582,7 +25582,7 @@
         <v>14</v>
       </c>
       <c r="F217" s="2">
-        <v>2012</v>
+        <v>1699</v>
       </c>
       <c r="G217" s="2" t="s">
         <v>15</v>
@@ -25614,7 +25614,7 @@
         <v>14</v>
       </c>
       <c r="F218" s="2">
-        <v>1206</v>
+        <v>3314</v>
       </c>
       <c r="G218" s="2" t="s">
         <v>15</v>
@@ -25646,7 +25646,7 @@
         <v>14</v>
       </c>
       <c r="F219" s="2">
-        <v>3803</v>
+        <v>4040</v>
       </c>
       <c r="G219" s="2" t="s">
         <v>15</v>
@@ -25678,7 +25678,7 @@
         <v>14</v>
       </c>
       <c r="F220" s="2">
-        <v>1975</v>
+        <v>1189</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>15</v>
@@ -25710,7 +25710,7 @@
         <v>14</v>
       </c>
       <c r="F221" s="2">
-        <v>2488</v>
+        <v>1239</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>15</v>
@@ -25742,7 +25742,7 @@
         <v>14</v>
       </c>
       <c r="F222" s="2">
-        <v>895</v>
+        <v>915</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>15</v>
@@ -25774,7 +25774,7 @@
         <v>14</v>
       </c>
       <c r="F223" s="2">
-        <v>3935</v>
+        <v>2219</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>15</v>
@@ -25806,7 +25806,7 @@
         <v>14</v>
       </c>
       <c r="F224" s="2">
-        <v>1986</v>
+        <v>2439</v>
       </c>
       <c r="G224" s="2" t="s">
         <v>15</v>
@@ -25838,7 +25838,7 @@
         <v>14</v>
       </c>
       <c r="F225" s="2">
-        <v>1999</v>
+        <v>2752</v>
       </c>
       <c r="G225" s="2" t="s">
         <v>15</v>
@@ -25870,7 +25870,7 @@
         <v>14</v>
       </c>
       <c r="F226" s="2">
-        <v>3901</v>
+        <v>2649</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>15</v>
@@ -25902,7 +25902,7 @@
         <v>14</v>
       </c>
       <c r="F227" s="2">
-        <v>2347</v>
+        <v>3246</v>
       </c>
       <c r="G227" s="2" t="s">
         <v>15</v>
@@ -25934,7 +25934,7 @@
         <v>14</v>
       </c>
       <c r="F228" s="2">
-        <v>4503</v>
+        <v>2929</v>
       </c>
       <c r="G228" s="2" t="s">
         <v>15</v>
@@ -25966,7 +25966,7 @@
         <v>14</v>
       </c>
       <c r="F229" s="2">
-        <v>3126</v>
+        <v>3556</v>
       </c>
       <c r="G229" s="2" t="s">
         <v>15</v>
@@ -25998,7 +25998,7 @@
         <v>14</v>
       </c>
       <c r="F230" s="2">
-        <v>4663</v>
+        <v>2306</v>
       </c>
       <c r="G230" s="2" t="s">
         <v>15</v>
@@ -26030,7 +26030,7 @@
         <v>14</v>
       </c>
       <c r="F231" s="2">
-        <v>1592</v>
+        <v>2321</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>15</v>
@@ -26062,7 +26062,7 @@
         <v>14</v>
       </c>
       <c r="F232" s="2">
-        <v>2636</v>
+        <v>3817</v>
       </c>
       <c r="G232" s="2" t="s">
         <v>15</v>
@@ -26094,7 +26094,7 @@
         <v>14</v>
       </c>
       <c r="F233" s="2">
-        <v>2516</v>
+        <v>1746</v>
       </c>
       <c r="G233" s="2" t="s">
         <v>15</v>
@@ -26126,7 +26126,7 @@
         <v>14</v>
       </c>
       <c r="F234" s="2">
-        <v>962</v>
+        <v>2965</v>
       </c>
       <c r="G234" s="2" t="s">
         <v>15</v>
@@ -26158,7 +26158,7 @@
         <v>14</v>
       </c>
       <c r="F235" s="2">
-        <v>1588</v>
+        <v>3904</v>
       </c>
       <c r="G235" s="2" t="s">
         <v>15</v>
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="F236" s="2">
-        <v>3416</v>
+        <v>1031</v>
       </c>
       <c r="G236" s="2" t="s">
         <v>15</v>
@@ -26222,7 +26222,7 @@
         <v>14</v>
       </c>
       <c r="F237" s="2">
-        <v>1845</v>
+        <v>1127</v>
       </c>
       <c r="G237" s="2" t="s">
         <v>15</v>
@@ -26254,7 +26254,7 @@
         <v>14</v>
       </c>
       <c r="F238" s="2">
-        <v>1507</v>
+        <v>1033</v>
       </c>
       <c r="G238" s="2" t="s">
         <v>15</v>
@@ -26286,7 +26286,7 @@
         <v>14</v>
       </c>
       <c r="F239" s="2">
-        <v>3458</v>
+        <v>2450</v>
       </c>
       <c r="G239" s="2" t="s">
         <v>15</v>
@@ -26318,7 +26318,7 @@
         <v>14</v>
       </c>
       <c r="F240" s="2">
-        <v>1969</v>
+        <v>2853</v>
       </c>
       <c r="G240" s="2" t="s">
         <v>15</v>
@@ -26350,7 +26350,7 @@
         <v>14</v>
       </c>
       <c r="F241" s="2">
-        <v>4402</v>
+        <v>4435</v>
       </c>
       <c r="G241" s="2" t="s">
         <v>15</v>
@@ -26382,7 +26382,7 @@
         <v>14</v>
       </c>
       <c r="F242" s="2">
-        <v>2071</v>
+        <v>3411</v>
       </c>
       <c r="G242" s="2" t="s">
         <v>15</v>
@@ -26414,7 +26414,7 @@
         <v>14</v>
       </c>
       <c r="F243" s="2">
-        <v>4692</v>
+        <v>1579</v>
       </c>
       <c r="G243" s="2" t="s">
         <v>15</v>
@@ -26446,7 +26446,7 @@
         <v>14</v>
       </c>
       <c r="F244" s="2">
-        <v>1076</v>
+        <v>1553</v>
       </c>
       <c r="G244" s="2" t="s">
         <v>15</v>
@@ -26478,7 +26478,7 @@
         <v>14</v>
       </c>
       <c r="F245" s="2">
-        <v>4165</v>
+        <v>3598</v>
       </c>
       <c r="G245" s="2" t="s">
         <v>15</v>
@@ -26510,7 +26510,7 @@
         <v>14</v>
       </c>
       <c r="F246" s="2">
-        <v>1129</v>
+        <v>4452</v>
       </c>
       <c r="G246" s="2" t="s">
         <v>15</v>
@@ -26542,7 +26542,7 @@
         <v>14</v>
       </c>
       <c r="F247" s="2">
-        <v>1895</v>
+        <v>3048</v>
       </c>
       <c r="G247" s="2" t="s">
         <v>15</v>
@@ -26574,7 +26574,7 @@
         <v>14</v>
       </c>
       <c r="F248" s="2">
-        <v>1973</v>
+        <v>4471</v>
       </c>
       <c r="G248" s="2" t="s">
         <v>15</v>
@@ -26606,7 +26606,7 @@
         <v>14</v>
       </c>
       <c r="F249" s="2">
-        <v>2026</v>
+        <v>1082</v>
       </c>
       <c r="G249" s="2" t="s">
         <v>15</v>
@@ -26638,7 +26638,7 @@
         <v>14</v>
       </c>
       <c r="F250" s="2">
-        <v>3095</v>
+        <v>4231</v>
       </c>
       <c r="G250" s="2" t="s">
         <v>15</v>
@@ -26670,7 +26670,7 @@
         <v>14</v>
       </c>
       <c r="F251" s="2">
-        <v>1251</v>
+        <v>2873</v>
       </c>
       <c r="G251" s="2" t="s">
         <v>15</v>
@@ -26702,7 +26702,7 @@
         <v>14</v>
       </c>
       <c r="F252" s="2">
-        <v>1629</v>
+        <v>4513</v>
       </c>
       <c r="G252" s="2" t="s">
         <v>15</v>
@@ -26734,7 +26734,7 @@
         <v>14</v>
       </c>
       <c r="F253" s="2">
-        <v>1652</v>
+        <v>3104</v>
       </c>
       <c r="G253" s="2" t="s">
         <v>15</v>
@@ -26766,7 +26766,7 @@
         <v>14</v>
       </c>
       <c r="F254" s="2">
-        <v>4588</v>
+        <v>4154</v>
       </c>
       <c r="G254" s="2" t="s">
         <v>15</v>
@@ -26798,7 +26798,7 @@
         <v>14</v>
       </c>
       <c r="F255" s="2">
-        <v>2996</v>
+        <v>1740</v>
       </c>
       <c r="G255" s="2" t="s">
         <v>15</v>
@@ -26830,7 +26830,7 @@
         <v>14</v>
       </c>
       <c r="F256" s="2">
-        <v>1606</v>
+        <v>4675</v>
       </c>
       <c r="G256" s="2" t="s">
         <v>15</v>
@@ -26862,7 +26862,7 @@
         <v>14</v>
       </c>
       <c r="F257" s="2">
-        <v>2582</v>
+        <v>1641</v>
       </c>
       <c r="G257" s="2" t="s">
         <v>15</v>
@@ -26894,7 +26894,7 @@
         <v>14</v>
       </c>
       <c r="F258" s="2">
-        <v>2519</v>
+        <v>844</v>
       </c>
       <c r="G258" s="2" t="s">
         <v>15</v>
@@ -26926,7 +26926,7 @@
         <v>14</v>
       </c>
       <c r="F259" s="2">
-        <v>4593</v>
+        <v>2016</v>
       </c>
       <c r="G259" s="2" t="s">
         <v>15</v>
@@ -26958,7 +26958,7 @@
         <v>14</v>
       </c>
       <c r="F260" s="2">
-        <v>3340</v>
+        <v>2100</v>
       </c>
       <c r="G260" s="2" t="s">
         <v>15</v>
@@ -26990,7 +26990,7 @@
         <v>14</v>
       </c>
       <c r="F261" s="2">
-        <v>2568</v>
+        <v>2970</v>
       </c>
       <c r="G261" s="2" t="s">
         <v>15</v>
@@ -27022,7 +27022,7 @@
         <v>14</v>
       </c>
       <c r="F262" s="2">
-        <v>877</v>
+        <v>1052</v>
       </c>
       <c r="G262" s="2" t="s">
         <v>15</v>
@@ -27054,7 +27054,7 @@
         <v>14</v>
       </c>
       <c r="F263" s="2">
-        <v>4277</v>
+        <v>1388</v>
       </c>
       <c r="G263" s="2" t="s">
         <v>15</v>
@@ -27086,7 +27086,7 @@
         <v>14</v>
       </c>
       <c r="F264" s="2">
-        <v>1602</v>
+        <v>2829</v>
       </c>
       <c r="G264" s="2" t="s">
         <v>15</v>
@@ -27118,7 +27118,7 @@
         <v>14</v>
       </c>
       <c r="F265" s="2">
-        <v>1449</v>
+        <v>2397</v>
       </c>
       <c r="G265" s="2" t="s">
         <v>15</v>
@@ -27150,7 +27150,7 @@
         <v>14</v>
       </c>
       <c r="F266" s="2">
-        <v>3457</v>
+        <v>2635</v>
       </c>
       <c r="G266" s="2" t="s">
         <v>15</v>
@@ -27182,7 +27182,7 @@
         <v>14</v>
       </c>
       <c r="F267" s="2">
-        <v>2741</v>
+        <v>2858</v>
       </c>
       <c r="G267" s="2" t="s">
         <v>15</v>
@@ -27214,7 +27214,7 @@
         <v>14</v>
       </c>
       <c r="F268" s="2">
-        <v>3208</v>
+        <v>2546</v>
       </c>
       <c r="G268" s="2" t="s">
         <v>15</v>
@@ -27246,7 +27246,7 @@
         <v>14</v>
       </c>
       <c r="F269" s="2">
-        <v>2239</v>
+        <v>879</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>15</v>
@@ -27278,7 +27278,7 @@
         <v>14</v>
       </c>
       <c r="F270" s="2">
-        <v>4543</v>
+        <v>4098</v>
       </c>
       <c r="G270" s="2" t="s">
         <v>15</v>
@@ -27310,7 +27310,7 @@
         <v>14</v>
       </c>
       <c r="F271" s="2">
-        <v>3712</v>
+        <v>1484</v>
       </c>
       <c r="G271" s="2" t="s">
         <v>15</v>
@@ -27342,7 +27342,7 @@
         <v>14</v>
       </c>
       <c r="F272" s="2">
-        <v>4239</v>
+        <v>4664</v>
       </c>
       <c r="G272" s="2" t="s">
         <v>15</v>
@@ -27374,7 +27374,7 @@
         <v>14</v>
       </c>
       <c r="F273" s="2">
-        <v>4773</v>
+        <v>4351</v>
       </c>
       <c r="G273" s="2" t="s">
         <v>15</v>
@@ -27406,7 +27406,7 @@
         <v>14</v>
       </c>
       <c r="F274" s="2">
-        <v>1305</v>
+        <v>4701</v>
       </c>
       <c r="G274" s="2" t="s">
         <v>15</v>
@@ -27438,7 +27438,7 @@
         <v>14</v>
       </c>
       <c r="F275" s="2">
-        <v>4569</v>
+        <v>1012</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>15</v>
@@ -27470,7 +27470,7 @@
         <v>14</v>
       </c>
       <c r="F276" s="2">
-        <v>1567</v>
+        <v>2186</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>15</v>
@@ -27502,7 +27502,7 @@
         <v>14</v>
       </c>
       <c r="F277" s="2">
-        <v>1129</v>
+        <v>1358</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>15</v>
@@ -27534,7 +27534,7 @@
         <v>14</v>
       </c>
       <c r="F278" s="2">
-        <v>3028</v>
+        <v>2193</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>15</v>
@@ -27566,7 +27566,7 @@
         <v>14</v>
       </c>
       <c r="F279" s="2">
-        <v>4785</v>
+        <v>813</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>15</v>
@@ -27598,7 +27598,7 @@
         <v>14</v>
       </c>
       <c r="F280" s="2">
-        <v>2739</v>
+        <v>2708</v>
       </c>
       <c r="G280" s="2" t="s">
         <v>15</v>
@@ -27630,7 +27630,7 @@
         <v>14</v>
       </c>
       <c r="F281" s="2">
-        <v>3274</v>
+        <v>3183</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>15</v>
@@ -27662,7 +27662,7 @@
         <v>14</v>
       </c>
       <c r="F282" s="2">
-        <v>3694</v>
+        <v>4455</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>15</v>
@@ -27694,7 +27694,7 @@
         <v>14</v>
       </c>
       <c r="F283" s="2">
-        <v>4549</v>
+        <v>4699</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>15</v>
@@ -27726,7 +27726,7 @@
         <v>14</v>
       </c>
       <c r="F284" s="2">
-        <v>3954</v>
+        <v>1551</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>15</v>
@@ -27758,7 +27758,7 @@
         <v>14</v>
       </c>
       <c r="F285" s="2">
-        <v>2745</v>
+        <v>1473</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>15</v>
@@ -27790,7 +27790,7 @@
         <v>14</v>
       </c>
       <c r="F286" s="2">
-        <v>4224</v>
+        <v>1144</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>15</v>
@@ -27822,7 +27822,7 @@
         <v>14</v>
       </c>
       <c r="F287" s="2">
-        <v>4295</v>
+        <v>2278</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>15</v>
@@ -27854,7 +27854,7 @@
         <v>14</v>
       </c>
       <c r="F288" s="2">
-        <v>4160</v>
+        <v>1408</v>
       </c>
       <c r="G288" s="2" t="s">
         <v>15</v>
@@ -27886,7 +27886,7 @@
         <v>14</v>
       </c>
       <c r="F289" s="2">
-        <v>1079</v>
+        <v>838</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>15</v>
@@ -27918,7 +27918,7 @@
         <v>14</v>
       </c>
       <c r="F290" s="2">
-        <v>1680</v>
+        <v>4658</v>
       </c>
       <c r="G290" s="2" t="s">
         <v>15</v>
@@ -27950,7 +27950,7 @@
         <v>14</v>
       </c>
       <c r="F291" s="2">
-        <v>2102</v>
+        <v>1542</v>
       </c>
       <c r="G291" s="2" t="s">
         <v>15</v>
@@ -27982,7 +27982,7 @@
         <v>14</v>
       </c>
       <c r="F292" s="2">
-        <v>3281</v>
+        <v>4091</v>
       </c>
       <c r="G292" s="2" t="s">
         <v>15</v>
@@ -28014,7 +28014,7 @@
         <v>14</v>
       </c>
       <c r="F293" s="2">
-        <v>937</v>
+        <v>1139</v>
       </c>
       <c r="G293" s="2" t="s">
         <v>15</v>
@@ -28046,7 +28046,7 @@
         <v>14</v>
       </c>
       <c r="F294" s="2">
-        <v>2656</v>
+        <v>2122</v>
       </c>
       <c r="G294" s="2" t="s">
         <v>15</v>
@@ -28078,7 +28078,7 @@
         <v>14</v>
       </c>
       <c r="F295" s="2">
-        <v>3189</v>
+        <v>2873</v>
       </c>
       <c r="G295" s="2" t="s">
         <v>15</v>
@@ -28110,7 +28110,7 @@
         <v>14</v>
       </c>
       <c r="F296" s="2">
-        <v>2092</v>
+        <v>2578</v>
       </c>
       <c r="G296" s="2" t="s">
         <v>15</v>
@@ -28142,7 +28142,7 @@
         <v>14</v>
       </c>
       <c r="F297" s="2">
-        <v>2885</v>
+        <v>3019</v>
       </c>
       <c r="G297" s="2" t="s">
         <v>15</v>
@@ -28174,7 +28174,7 @@
         <v>14</v>
       </c>
       <c r="F298" s="2">
-        <v>2970</v>
+        <v>4188</v>
       </c>
       <c r="G298" s="2" t="s">
         <v>15</v>
@@ -28206,7 +28206,7 @@
         <v>14</v>
       </c>
       <c r="F299" s="2">
-        <v>4200</v>
+        <v>2103</v>
       </c>
       <c r="G299" s="2" t="s">
         <v>15</v>
@@ -28238,7 +28238,7 @@
         <v>14</v>
       </c>
       <c r="F300" s="2">
-        <v>4666</v>
+        <v>1222</v>
       </c>
       <c r="G300" s="2" t="s">
         <v>15</v>
@@ -28270,7 +28270,7 @@
         <v>14</v>
       </c>
       <c r="F301" s="2">
-        <v>1415</v>
+        <v>2784</v>
       </c>
       <c r="G301" s="2" t="s">
         <v>15</v>
@@ -28302,7 +28302,7 @@
         <v>14</v>
       </c>
       <c r="F302" s="2">
-        <v>1737</v>
+        <v>2459</v>
       </c>
       <c r="G302" s="2" t="s">
         <v>15</v>
@@ -28334,7 +28334,7 @@
         <v>14</v>
       </c>
       <c r="F303" s="2">
-        <v>4530</v>
+        <v>4521</v>
       </c>
       <c r="G303" s="2" t="s">
         <v>15</v>
@@ -28366,7 +28366,7 @@
         <v>14</v>
       </c>
       <c r="F304" s="2">
-        <v>2866</v>
+        <v>1137</v>
       </c>
       <c r="G304" s="2" t="s">
         <v>15</v>
@@ -28398,7 +28398,7 @@
         <v>14</v>
       </c>
       <c r="F305" s="2">
-        <v>1772</v>
+        <v>2539</v>
       </c>
       <c r="G305" s="2" t="s">
         <v>15</v>
@@ -28430,7 +28430,7 @@
         <v>14</v>
       </c>
       <c r="F306" s="2">
-        <v>3642</v>
+        <v>3823</v>
       </c>
       <c r="G306" s="2" t="s">
         <v>15</v>
@@ -28462,7 +28462,7 @@
         <v>14</v>
       </c>
       <c r="F307" s="2">
-        <v>1291</v>
+        <v>1490</v>
       </c>
       <c r="G307" s="2" t="s">
         <v>15</v>
@@ -28494,7 +28494,7 @@
         <v>14</v>
       </c>
       <c r="F308" s="2">
-        <v>4466</v>
+        <v>3534</v>
       </c>
       <c r="G308" s="2" t="s">
         <v>15</v>
@@ -28526,7 +28526,7 @@
         <v>14</v>
       </c>
       <c r="F309" s="2">
-        <v>959</v>
+        <v>4410</v>
       </c>
       <c r="G309" s="2" t="s">
         <v>15</v>
@@ -28558,7 +28558,7 @@
         <v>14</v>
       </c>
       <c r="F310" s="2">
-        <v>4564</v>
+        <v>2007</v>
       </c>
       <c r="G310" s="2" t="s">
         <v>15</v>
@@ -28590,7 +28590,7 @@
         <v>14</v>
       </c>
       <c r="F311" s="2">
-        <v>3778</v>
+        <v>4432</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>15</v>
@@ -28622,7 +28622,7 @@
         <v>14</v>
       </c>
       <c r="F312" s="2">
-        <v>2889</v>
+        <v>3385</v>
       </c>
       <c r="G312" s="2" t="s">
         <v>15</v>
@@ -28654,7 +28654,7 @@
         <v>14</v>
       </c>
       <c r="F313" s="2">
-        <v>1656</v>
+        <v>1321</v>
       </c>
       <c r="G313" s="2" t="s">
         <v>15</v>
@@ -28686,7 +28686,7 @@
         <v>14</v>
       </c>
       <c r="F314" s="2">
-        <v>2049</v>
+        <v>1009</v>
       </c>
       <c r="G314" s="2" t="s">
         <v>15</v>
@@ -28718,7 +28718,7 @@
         <v>14</v>
       </c>
       <c r="F315" s="2">
-        <v>917</v>
+        <v>2221</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>15</v>
@@ -28750,7 +28750,7 @@
         <v>14</v>
       </c>
       <c r="F316" s="2">
-        <v>3931</v>
+        <v>2541</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>15</v>
@@ -28782,7 +28782,7 @@
         <v>14</v>
       </c>
       <c r="F317" s="2">
-        <v>3666</v>
+        <v>4349</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>15</v>
@@ -28814,7 +28814,7 @@
         <v>14</v>
       </c>
       <c r="F318" s="2">
-        <v>3554</v>
+        <v>1201</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>15</v>
@@ -28846,7 +28846,7 @@
         <v>14</v>
       </c>
       <c r="F319" s="2">
-        <v>4650</v>
+        <v>4182</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>15</v>
@@ -28878,7 +28878,7 @@
         <v>14</v>
       </c>
       <c r="F320" s="2">
-        <v>1437</v>
+        <v>1308</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>15</v>
@@ -28910,7 +28910,7 @@
         <v>14</v>
       </c>
       <c r="F321" s="2">
-        <v>993</v>
+        <v>3896</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>15</v>
@@ -28942,7 +28942,7 @@
         <v>14</v>
       </c>
       <c r="F322" s="2">
-        <v>2386</v>
+        <v>1686</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>15</v>
@@ -28974,7 +28974,7 @@
         <v>14</v>
       </c>
       <c r="F323" s="2">
-        <v>1785</v>
+        <v>1321</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>15</v>
@@ -29006,7 +29006,7 @@
         <v>14</v>
       </c>
       <c r="F324" s="2">
-        <v>1432</v>
+        <v>3878</v>
       </c>
       <c r="G324" s="2" t="s">
         <v>15</v>
@@ -29038,7 +29038,7 @@
         <v>14</v>
       </c>
       <c r="F325" s="2">
-        <v>3004</v>
+        <v>3852</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>15</v>
@@ -29070,7 +29070,7 @@
         <v>14</v>
       </c>
       <c r="F326" s="2">
-        <v>4437</v>
+        <v>4204</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>15</v>
@@ -29102,7 +29102,7 @@
         <v>14</v>
       </c>
       <c r="F327" s="2">
-        <v>1971</v>
+        <v>3133</v>
       </c>
       <c r="G327" s="2" t="s">
         <v>15</v>
@@ -29134,7 +29134,7 @@
         <v>14</v>
       </c>
       <c r="F328" s="2">
-        <v>1099</v>
+        <v>2838</v>
       </c>
       <c r="G328" s="2" t="s">
         <v>15</v>
@@ -29166,7 +29166,7 @@
         <v>14</v>
       </c>
       <c r="F329" s="2">
-        <v>3912</v>
+        <v>2300</v>
       </c>
       <c r="G329" s="2" t="s">
         <v>15</v>
@@ -29198,7 +29198,7 @@
         <v>14</v>
       </c>
       <c r="F330" s="2">
-        <v>3581</v>
+        <v>4409</v>
       </c>
       <c r="G330" s="2" t="s">
         <v>15</v>
@@ -29230,7 +29230,7 @@
         <v>14</v>
       </c>
       <c r="F331" s="2">
-        <v>4102</v>
+        <v>4296</v>
       </c>
       <c r="G331" s="2" t="s">
         <v>15</v>
@@ -29262,7 +29262,7 @@
         <v>14</v>
       </c>
       <c r="F332" s="2">
-        <v>3869</v>
+        <v>4564</v>
       </c>
       <c r="G332" s="2" t="s">
         <v>15</v>
@@ -29294,7 +29294,7 @@
         <v>14</v>
       </c>
       <c r="F333" s="2">
-        <v>4072</v>
+        <v>4516</v>
       </c>
       <c r="G333" s="2" t="s">
         <v>15</v>
@@ -29326,7 +29326,7 @@
         <v>14</v>
       </c>
       <c r="F334" s="2">
-        <v>3115</v>
+        <v>1491</v>
       </c>
       <c r="G334" s="2" t="s">
         <v>15</v>
@@ -29358,7 +29358,7 @@
         <v>14</v>
       </c>
       <c r="F335" s="2">
-        <v>3023</v>
+        <v>1627</v>
       </c>
       <c r="G335" s="2" t="s">
         <v>15</v>
@@ -29390,7 +29390,7 @@
         <v>14</v>
       </c>
       <c r="F336" s="2">
-        <v>2354</v>
+        <v>1239</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>15</v>
@@ -29422,7 +29422,7 @@
         <v>14</v>
       </c>
       <c r="F337" s="2">
-        <v>2772</v>
+        <v>3608</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>15</v>
@@ -29454,7 +29454,7 @@
         <v>14</v>
       </c>
       <c r="F338" s="2">
-        <v>1737</v>
+        <v>2163</v>
       </c>
       <c r="G338" s="2" t="s">
         <v>15</v>
@@ -29486,7 +29486,7 @@
         <v>14</v>
       </c>
       <c r="F339" s="2">
-        <v>3046</v>
+        <v>1058</v>
       </c>
       <c r="G339" s="2" t="s">
         <v>15</v>
@@ -29518,7 +29518,7 @@
         <v>14</v>
       </c>
       <c r="F340" s="2">
-        <v>2292</v>
+        <v>1513</v>
       </c>
       <c r="G340" s="2" t="s">
         <v>15</v>
@@ -29550,7 +29550,7 @@
         <v>14</v>
       </c>
       <c r="F341" s="2">
-        <v>2871</v>
+        <v>3245</v>
       </c>
       <c r="G341" s="2" t="s">
         <v>15</v>
@@ -29582,7 +29582,7 @@
         <v>14</v>
       </c>
       <c r="F342" s="2">
-        <v>3172</v>
+        <v>4460</v>
       </c>
       <c r="G342" s="2" t="s">
         <v>15</v>
@@ -29614,7 +29614,7 @@
         <v>14</v>
       </c>
       <c r="F343" s="2">
-        <v>4089</v>
+        <v>3524</v>
       </c>
       <c r="G343" s="2" t="s">
         <v>15</v>
@@ -29646,7 +29646,7 @@
         <v>14</v>
       </c>
       <c r="F344" s="2">
-        <v>2032</v>
+        <v>4428</v>
       </c>
       <c r="G344" s="2" t="s">
         <v>15</v>
@@ -29678,7 +29678,7 @@
         <v>14</v>
       </c>
       <c r="F345" s="2">
-        <v>3432</v>
+        <v>3208</v>
       </c>
       <c r="G345" s="2" t="s">
         <v>15</v>
@@ -29710,7 +29710,7 @@
         <v>14</v>
       </c>
       <c r="F346" s="2">
-        <v>3294</v>
+        <v>4486</v>
       </c>
       <c r="G346" s="2" t="s">
         <v>15</v>
@@ -29742,7 +29742,7 @@
         <v>14</v>
       </c>
       <c r="F347" s="2">
-        <v>4375</v>
+        <v>2936</v>
       </c>
       <c r="G347" s="2" t="s">
         <v>15</v>
@@ -29774,7 +29774,7 @@
         <v>14</v>
       </c>
       <c r="F348" s="2">
-        <v>1218</v>
+        <v>1114</v>
       </c>
       <c r="G348" s="2" t="s">
         <v>15</v>
@@ -29806,7 +29806,7 @@
         <v>14</v>
       </c>
       <c r="F349" s="2">
-        <v>4223</v>
+        <v>2026</v>
       </c>
       <c r="G349" s="2" t="s">
         <v>15</v>
@@ -29838,7 +29838,7 @@
         <v>14</v>
       </c>
       <c r="F350" s="2">
-        <v>1970</v>
+        <v>1927</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>15</v>
@@ -29870,7 +29870,7 @@
         <v>14</v>
       </c>
       <c r="F351" s="2">
-        <v>3164</v>
+        <v>2904</v>
       </c>
       <c r="G351" s="2" t="s">
         <v>15</v>
@@ -29902,7 +29902,7 @@
         <v>14</v>
       </c>
       <c r="F352" s="2">
-        <v>4392</v>
+        <v>1187</v>
       </c>
       <c r="G352" s="2" t="s">
         <v>15</v>
@@ -29934,7 +29934,7 @@
         <v>14</v>
       </c>
       <c r="F353" s="2">
-        <v>4626</v>
+        <v>4274</v>
       </c>
       <c r="G353" s="2" t="s">
         <v>15</v>
@@ -29966,7 +29966,7 @@
         <v>14</v>
       </c>
       <c r="F354" s="2">
-        <v>813</v>
+        <v>2966</v>
       </c>
       <c r="G354" s="2" t="s">
         <v>15</v>
@@ -29998,7 +29998,7 @@
         <v>14</v>
       </c>
       <c r="F355" s="2">
-        <v>4638</v>
+        <v>2855</v>
       </c>
       <c r="G355" s="2" t="s">
         <v>15</v>
@@ -30030,7 +30030,7 @@
         <v>14</v>
       </c>
       <c r="F356" s="2">
-        <v>2734</v>
+        <v>3399</v>
       </c>
       <c r="G356" s="2" t="s">
         <v>15</v>
@@ -30062,7 +30062,7 @@
         <v>14</v>
       </c>
       <c r="F357" s="2">
-        <v>3803</v>
+        <v>4661</v>
       </c>
       <c r="G357" s="2" t="s">
         <v>15</v>
@@ -30094,7 +30094,7 @@
         <v>14</v>
       </c>
       <c r="F358" s="2">
-        <v>1741</v>
+        <v>1148</v>
       </c>
       <c r="G358" s="2" t="s">
         <v>15</v>
@@ -30126,7 +30126,7 @@
         <v>14</v>
       </c>
       <c r="F359" s="2">
-        <v>4562</v>
+        <v>3634</v>
       </c>
       <c r="G359" s="2" t="s">
         <v>15</v>
@@ -30158,7 +30158,7 @@
         <v>14</v>
       </c>
       <c r="F360" s="2">
-        <v>2041</v>
+        <v>1924</v>
       </c>
       <c r="G360" s="2" t="s">
         <v>15</v>
@@ -30190,7 +30190,7 @@
         <v>14</v>
       </c>
       <c r="F361" s="2">
-        <v>3845</v>
+        <v>1958</v>
       </c>
       <c r="G361" s="2" t="s">
         <v>15</v>
@@ -30222,7 +30222,7 @@
         <v>14</v>
       </c>
       <c r="F362" s="2">
-        <v>3094</v>
+        <v>2196</v>
       </c>
       <c r="G362" s="2" t="s">
         <v>15</v>
@@ -30254,7 +30254,7 @@
         <v>14</v>
       </c>
       <c r="F363" s="2">
-        <v>2910</v>
+        <v>3016</v>
       </c>
       <c r="G363" s="2" t="s">
         <v>15</v>
@@ -30286,7 +30286,7 @@
         <v>14</v>
       </c>
       <c r="F364" s="2">
-        <v>1471</v>
+        <v>2924</v>
       </c>
       <c r="G364" s="2" t="s">
         <v>15</v>
@@ -30318,7 +30318,7 @@
         <v>14</v>
       </c>
       <c r="F365" s="2">
-        <v>1653</v>
+        <v>1793</v>
       </c>
       <c r="G365" s="2" t="s">
         <v>15</v>
@@ -30350,7 +30350,7 @@
         <v>14</v>
       </c>
       <c r="F366" s="2">
-        <v>2406</v>
+        <v>2656</v>
       </c>
       <c r="G366" s="2" t="s">
         <v>15</v>
@@ -30382,7 +30382,7 @@
         <v>14</v>
       </c>
       <c r="F367" s="2">
-        <v>857</v>
+        <v>4490</v>
       </c>
       <c r="G367" s="2" t="s">
         <v>15</v>
@@ -30414,7 +30414,7 @@
         <v>14</v>
       </c>
       <c r="F368" s="2">
-        <v>913</v>
+        <v>3009</v>
       </c>
       <c r="G368" s="2" t="s">
         <v>15</v>
@@ -30446,7 +30446,7 @@
         <v>14</v>
       </c>
       <c r="F369" s="2">
-        <v>3040</v>
+        <v>3575</v>
       </c>
       <c r="G369" s="2" t="s">
         <v>15</v>
@@ -30478,7 +30478,7 @@
         <v>14</v>
       </c>
       <c r="F370" s="2">
-        <v>1052</v>
+        <v>1063</v>
       </c>
       <c r="G370" s="2" t="s">
         <v>15</v>
@@ -30510,7 +30510,7 @@
         <v>14</v>
       </c>
       <c r="F371" s="2">
-        <v>3905</v>
+        <v>1434</v>
       </c>
       <c r="G371" s="2" t="s">
         <v>15</v>
@@ -30542,7 +30542,7 @@
         <v>14</v>
       </c>
       <c r="F372" s="2">
-        <v>4022</v>
+        <v>1437</v>
       </c>
       <c r="G372" s="2" t="s">
         <v>15</v>
@@ -30574,7 +30574,7 @@
         <v>14</v>
       </c>
       <c r="F373" s="2">
-        <v>3035</v>
+        <v>1718</v>
       </c>
       <c r="G373" s="2" t="s">
         <v>15</v>
@@ -30606,7 +30606,7 @@
         <v>14</v>
       </c>
       <c r="F374" s="2">
-        <v>2494</v>
+        <v>2162</v>
       </c>
       <c r="G374" s="2" t="s">
         <v>15</v>
@@ -30638,7 +30638,7 @@
         <v>14</v>
       </c>
       <c r="F375" s="2">
-        <v>3998</v>
+        <v>3840</v>
       </c>
       <c r="G375" s="2" t="s">
         <v>15</v>
@@ -30670,7 +30670,7 @@
         <v>14</v>
       </c>
       <c r="F376" s="2">
-        <v>3948</v>
+        <v>1144</v>
       </c>
       <c r="G376" s="2" t="s">
         <v>15</v>
@@ -30702,7 +30702,7 @@
         <v>14</v>
       </c>
       <c r="F377" s="2">
-        <v>3124</v>
+        <v>1930</v>
       </c>
       <c r="G377" s="2" t="s">
         <v>15</v>
@@ -30734,7 +30734,7 @@
         <v>14</v>
       </c>
       <c r="F378" s="2">
-        <v>2174</v>
+        <v>1059</v>
       </c>
       <c r="G378" s="2" t="s">
         <v>15</v>
@@ -30766,7 +30766,7 @@
         <v>14</v>
       </c>
       <c r="F379" s="2">
-        <v>4130</v>
+        <v>2998</v>
       </c>
       <c r="G379" s="2" t="s">
         <v>15</v>
@@ -30798,7 +30798,7 @@
         <v>14</v>
       </c>
       <c r="F380" s="2">
-        <v>1052</v>
+        <v>1856</v>
       </c>
       <c r="G380" s="2" t="s">
         <v>15</v>
@@ -30830,7 +30830,7 @@
         <v>14</v>
       </c>
       <c r="F381" s="2">
-        <v>1881</v>
+        <v>2767</v>
       </c>
       <c r="G381" s="2" t="s">
         <v>15</v>
@@ -30862,7 +30862,7 @@
         <v>14</v>
       </c>
       <c r="F382" s="2">
-        <v>4287</v>
+        <v>3679</v>
       </c>
       <c r="G382" s="2" t="s">
         <v>15</v>
@@ -30894,7 +30894,7 @@
         <v>14</v>
       </c>
       <c r="F383" s="2">
-        <v>3603</v>
+        <v>4658</v>
       </c>
       <c r="G383" s="2" t="s">
         <v>15</v>
@@ -30926,7 +30926,7 @@
         <v>14</v>
       </c>
       <c r="F384" s="2">
-        <v>2413</v>
+        <v>2202</v>
       </c>
       <c r="G384" s="2" t="s">
         <v>15</v>
@@ -30958,7 +30958,7 @@
         <v>14</v>
       </c>
       <c r="F385" s="2">
-        <v>4027</v>
+        <v>1498</v>
       </c>
       <c r="G385" s="2" t="s">
         <v>15</v>
@@ -30990,7 +30990,7 @@
         <v>14</v>
       </c>
       <c r="F386" s="2">
-        <v>1790</v>
+        <v>3319</v>
       </c>
       <c r="G386" s="2" t="s">
         <v>15</v>
@@ -31022,7 +31022,7 @@
         <v>14</v>
       </c>
       <c r="F387" s="2">
-        <v>942</v>
+        <v>1147</v>
       </c>
       <c r="G387" s="2" t="s">
         <v>15</v>
@@ -31054,7 +31054,7 @@
         <v>14</v>
       </c>
       <c r="F388" s="2">
-        <v>3528</v>
+        <v>2471</v>
       </c>
       <c r="G388" s="2" t="s">
         <v>15</v>
@@ -31086,7 +31086,7 @@
         <v>14</v>
       </c>
       <c r="F389" s="2">
-        <v>1605</v>
+        <v>1911</v>
       </c>
       <c r="G389" s="2" t="s">
         <v>15</v>
@@ -31118,7 +31118,7 @@
         <v>14</v>
       </c>
       <c r="F390" s="2">
-        <v>3299</v>
+        <v>3087</v>
       </c>
       <c r="G390" s="2" t="s">
         <v>15</v>
@@ -31150,7 +31150,7 @@
         <v>14</v>
       </c>
       <c r="F391" s="2">
-        <v>1157</v>
+        <v>1092</v>
       </c>
       <c r="G391" s="2" t="s">
         <v>15</v>
@@ -31182,7 +31182,7 @@
         <v>14</v>
       </c>
       <c r="F392" s="2">
-        <v>3965</v>
+        <v>950</v>
       </c>
       <c r="G392" s="2" t="s">
         <v>15</v>
@@ -31214,7 +31214,7 @@
         <v>14</v>
       </c>
       <c r="F393" s="2">
-        <v>853</v>
+        <v>3271</v>
       </c>
       <c r="G393" s="2" t="s">
         <v>15</v>
@@ -31246,7 +31246,7 @@
         <v>14</v>
       </c>
       <c r="F394" s="2">
-        <v>1134</v>
+        <v>3911</v>
       </c>
       <c r="G394" s="2" t="s">
         <v>15</v>
@@ -31278,7 +31278,7 @@
         <v>14</v>
       </c>
       <c r="F395" s="2">
-        <v>4441</v>
+        <v>4433</v>
       </c>
       <c r="G395" s="2" t="s">
         <v>15</v>
@@ -31310,7 +31310,7 @@
         <v>14</v>
       </c>
       <c r="F396" s="2">
-        <v>3735</v>
+        <v>3220</v>
       </c>
       <c r="G396" s="2" t="s">
         <v>15</v>
@@ -31342,7 +31342,7 @@
         <v>14</v>
       </c>
       <c r="F397" s="2">
-        <v>1221</v>
+        <v>2292</v>
       </c>
       <c r="G397" s="2" t="s">
         <v>15</v>
@@ -31374,7 +31374,7 @@
         <v>14</v>
       </c>
       <c r="F398" s="2">
-        <v>3304</v>
+        <v>3084</v>
       </c>
       <c r="G398" s="2" t="s">
         <v>15</v>
@@ -31406,7 +31406,7 @@
         <v>14</v>
       </c>
       <c r="F399" s="2">
-        <v>2445</v>
+        <v>2936</v>
       </c>
       <c r="G399" s="2" t="s">
         <v>15</v>
@@ -31438,7 +31438,7 @@
         <v>14</v>
       </c>
       <c r="F400" s="2">
-        <v>2352</v>
+        <v>3789</v>
       </c>
       <c r="G400" s="2" t="s">
         <v>15</v>
@@ -31470,7 +31470,7 @@
         <v>14</v>
       </c>
       <c r="F401" s="2">
-        <v>2083</v>
+        <v>1255</v>
       </c>
       <c r="G401" s="2" t="s">
         <v>15</v>
@@ -31502,7 +31502,7 @@
         <v>14</v>
       </c>
       <c r="F402" s="2">
-        <v>3100</v>
+        <v>1933</v>
       </c>
       <c r="G402" s="2" t="s">
         <v>15</v>
@@ -31534,7 +31534,7 @@
         <v>14</v>
       </c>
       <c r="F403" s="2">
-        <v>3473</v>
+        <v>895</v>
       </c>
       <c r="G403" s="2" t="s">
         <v>15</v>
@@ -31566,7 +31566,7 @@
         <v>14</v>
       </c>
       <c r="F404" s="2">
-        <v>2228</v>
+        <v>3343</v>
       </c>
       <c r="G404" s="2" t="s">
         <v>15</v>
@@ -31598,7 +31598,7 @@
         <v>14</v>
       </c>
       <c r="F405" s="2">
-        <v>805</v>
+        <v>1892</v>
       </c>
       <c r="G405" s="2" t="s">
         <v>15</v>
@@ -31630,7 +31630,7 @@
         <v>14</v>
       </c>
       <c r="F406" s="2">
-        <v>3586</v>
+        <v>3448</v>
       </c>
       <c r="G406" s="2" t="s">
         <v>15</v>
@@ -31662,7 +31662,7 @@
         <v>14</v>
       </c>
       <c r="F407" s="2">
-        <v>4555</v>
+        <v>1853</v>
       </c>
       <c r="G407" s="2" t="s">
         <v>15</v>
@@ -31694,7 +31694,7 @@
         <v>14</v>
       </c>
       <c r="F408" s="2">
-        <v>1078</v>
+        <v>2765</v>
       </c>
       <c r="G408" s="2" t="s">
         <v>15</v>
@@ -31726,7 +31726,7 @@
         <v>14</v>
       </c>
       <c r="F409" s="2">
-        <v>4245</v>
+        <v>4647</v>
       </c>
       <c r="G409" s="2" t="s">
         <v>15</v>
@@ -31758,7 +31758,7 @@
         <v>14</v>
       </c>
       <c r="F410" s="2">
-        <v>1046</v>
+        <v>1286</v>
       </c>
       <c r="G410" s="2" t="s">
         <v>15</v>
@@ -31790,7 +31790,7 @@
         <v>14</v>
       </c>
       <c r="F411" s="2">
-        <v>2479</v>
+        <v>1899</v>
       </c>
       <c r="G411" s="2" t="s">
         <v>15</v>
@@ -31822,7 +31822,7 @@
         <v>14</v>
       </c>
       <c r="F412" s="2">
-        <v>3944</v>
+        <v>3181</v>
       </c>
       <c r="G412" s="2" t="s">
         <v>15</v>
@@ -31854,7 +31854,7 @@
         <v>14</v>
       </c>
       <c r="F413" s="2">
-        <v>2336</v>
+        <v>3631</v>
       </c>
       <c r="G413" s="2" t="s">
         <v>15</v>
@@ -31886,7 +31886,7 @@
         <v>14</v>
       </c>
       <c r="F414" s="2">
-        <v>4571</v>
+        <v>4629</v>
       </c>
       <c r="G414" s="2" t="s">
         <v>15</v>
@@ -31918,7 +31918,7 @@
         <v>14</v>
       </c>
       <c r="F415" s="2">
-        <v>1110</v>
+        <v>3162</v>
       </c>
       <c r="G415" s="2" t="s">
         <v>15</v>
@@ -31950,7 +31950,7 @@
         <v>14</v>
       </c>
       <c r="F416" s="2">
-        <v>1826</v>
+        <v>2171</v>
       </c>
       <c r="G416" s="2" t="s">
         <v>15</v>
@@ -31982,7 +31982,7 @@
         <v>14</v>
       </c>
       <c r="F417" s="2">
-        <v>3967</v>
+        <v>4406</v>
       </c>
       <c r="G417" s="2" t="s">
         <v>15</v>
@@ -32014,7 +32014,7 @@
         <v>14</v>
       </c>
       <c r="F418" s="2">
-        <v>3218</v>
+        <v>4253</v>
       </c>
       <c r="G418" s="2" t="s">
         <v>15</v>
@@ -32046,7 +32046,7 @@
         <v>14</v>
       </c>
       <c r="F419" s="2">
-        <v>1388</v>
+        <v>4511</v>
       </c>
       <c r="G419" s="2" t="s">
         <v>15</v>
@@ -32078,7 +32078,7 @@
         <v>14</v>
       </c>
       <c r="F420" s="2">
-        <v>945</v>
+        <v>3997</v>
       </c>
       <c r="G420" s="2" t="s">
         <v>15</v>
@@ -32110,7 +32110,7 @@
         <v>14</v>
       </c>
       <c r="F421" s="2">
-        <v>1858</v>
+        <v>1708</v>
       </c>
       <c r="G421" s="2" t="s">
         <v>15</v>
@@ -32142,7 +32142,7 @@
         <v>14</v>
       </c>
       <c r="F422" s="2">
-        <v>4081</v>
+        <v>2377</v>
       </c>
       <c r="G422" s="2" t="s">
         <v>15</v>
@@ -32174,7 +32174,7 @@
         <v>14</v>
       </c>
       <c r="F423" s="2">
-        <v>4728</v>
+        <v>3893</v>
       </c>
       <c r="G423" s="2" t="s">
         <v>15</v>
@@ -32206,7 +32206,7 @@
         <v>14</v>
       </c>
       <c r="F424" s="2">
-        <v>3251</v>
+        <v>3044</v>
       </c>
       <c r="G424" s="2" t="s">
         <v>15</v>
@@ -32238,7 +32238,7 @@
         <v>14</v>
       </c>
       <c r="F425" s="2">
-        <v>2653</v>
+        <v>1873</v>
       </c>
       <c r="G425" s="2" t="s">
         <v>15</v>
@@ -32270,7 +32270,7 @@
         <v>14</v>
       </c>
       <c r="F426" s="2">
-        <v>3991</v>
+        <v>1511</v>
       </c>
       <c r="G426" s="2" t="s">
         <v>15</v>
@@ -32302,7 +32302,7 @@
         <v>14</v>
       </c>
       <c r="F427" s="2">
-        <v>2839</v>
+        <v>2552</v>
       </c>
       <c r="G427" s="2" t="s">
         <v>15</v>
@@ -32334,7 +32334,7 @@
         <v>14</v>
       </c>
       <c r="F428" s="2">
-        <v>2343</v>
+        <v>1321</v>
       </c>
       <c r="G428" s="2" t="s">
         <v>15</v>
@@ -32366,7 +32366,7 @@
         <v>14</v>
       </c>
       <c r="F429" s="2">
-        <v>4266</v>
+        <v>3128</v>
       </c>
       <c r="G429" s="2" t="s">
         <v>15</v>
@@ -32398,7 +32398,7 @@
         <v>14</v>
       </c>
       <c r="F430" s="2">
-        <v>3168</v>
+        <v>3728</v>
       </c>
       <c r="G430" s="2" t="s">
         <v>15</v>
@@ -32430,7 +32430,7 @@
         <v>14</v>
       </c>
       <c r="F431" s="2">
-        <v>3419</v>
+        <v>1028</v>
       </c>
       <c r="G431" s="2" t="s">
         <v>15</v>
@@ -32462,7 +32462,7 @@
         <v>14</v>
       </c>
       <c r="F432" s="2">
-        <v>2427</v>
+        <v>1598</v>
       </c>
       <c r="G432" s="2" t="s">
         <v>15</v>
@@ -32494,7 +32494,7 @@
         <v>14</v>
       </c>
       <c r="F433" s="2">
-        <v>3228</v>
+        <v>1123</v>
       </c>
       <c r="G433" s="2" t="s">
         <v>15</v>
@@ -32526,7 +32526,7 @@
         <v>14</v>
       </c>
       <c r="F434" s="2">
-        <v>1442</v>
+        <v>4123</v>
       </c>
       <c r="G434" s="2" t="s">
         <v>15</v>
@@ -32558,7 +32558,7 @@
         <v>14</v>
       </c>
       <c r="F435" s="2">
-        <v>2748</v>
+        <v>2103</v>
       </c>
       <c r="G435" s="2" t="s">
         <v>15</v>
@@ -32590,7 +32590,7 @@
         <v>14</v>
       </c>
       <c r="F436" s="2">
-        <v>2163</v>
+        <v>978</v>
       </c>
       <c r="G436" s="2" t="s">
         <v>15</v>
@@ -32622,7 +32622,7 @@
         <v>14</v>
       </c>
       <c r="F437" s="2">
-        <v>4126</v>
+        <v>1489</v>
       </c>
       <c r="G437" s="2" t="s">
         <v>15</v>
@@ -32654,7 +32654,7 @@
         <v>14</v>
       </c>
       <c r="F438" s="2">
-        <v>1349</v>
+        <v>3820</v>
       </c>
       <c r="G438" s="2" t="s">
         <v>15</v>
@@ -32686,7 +32686,7 @@
         <v>14</v>
       </c>
       <c r="F439" s="2">
-        <v>2348</v>
+        <v>2802</v>
       </c>
       <c r="G439" s="2" t="s">
         <v>15</v>
@@ -32718,7 +32718,7 @@
         <v>14</v>
       </c>
       <c r="F440" s="2">
-        <v>4471</v>
+        <v>2977</v>
       </c>
       <c r="G440" s="2" t="s">
         <v>15</v>
@@ -32750,7 +32750,7 @@
         <v>14</v>
       </c>
       <c r="F441" s="2">
-        <v>2767</v>
+        <v>3950</v>
       </c>
       <c r="G441" s="2" t="s">
         <v>15</v>
@@ -32782,7 +32782,7 @@
         <v>14</v>
       </c>
       <c r="F442" s="2">
-        <v>2625</v>
+        <v>3959</v>
       </c>
       <c r="G442" s="2" t="s">
         <v>15</v>
@@ -32814,7 +32814,7 @@
         <v>14</v>
       </c>
       <c r="F443" s="2">
-        <v>3004</v>
+        <v>1936</v>
       </c>
       <c r="G443" s="2" t="s">
         <v>15</v>
@@ -32846,7 +32846,7 @@
         <v>14</v>
       </c>
       <c r="F444" s="2">
-        <v>4161</v>
+        <v>858</v>
       </c>
       <c r="G444" s="2" t="s">
         <v>15</v>
@@ -32878,7 +32878,7 @@
         <v>14</v>
       </c>
       <c r="F445" s="2">
-        <v>2282</v>
+        <v>2825</v>
       </c>
       <c r="G445" s="2" t="s">
         <v>15</v>
@@ -32910,7 +32910,7 @@
         <v>14</v>
       </c>
       <c r="F446" s="2">
-        <v>4669</v>
+        <v>1066</v>
       </c>
       <c r="G446" s="2" t="s">
         <v>15</v>
@@ -32942,7 +32942,7 @@
         <v>14</v>
       </c>
       <c r="F447" s="2">
-        <v>2402</v>
+        <v>4723</v>
       </c>
       <c r="G447" s="2" t="s">
         <v>15</v>
@@ -32974,7 +32974,7 @@
         <v>14</v>
       </c>
       <c r="F448" s="2">
-        <v>4396</v>
+        <v>1617</v>
       </c>
       <c r="G448" s="2" t="s">
         <v>15</v>
@@ -33006,7 +33006,7 @@
         <v>14</v>
       </c>
       <c r="F449" s="2">
-        <v>3518</v>
+        <v>1551</v>
       </c>
       <c r="G449" s="2" t="s">
         <v>15</v>
@@ -33038,7 +33038,7 @@
         <v>14</v>
       </c>
       <c r="F450" s="2">
-        <v>4164</v>
+        <v>4640</v>
       </c>
       <c r="G450" s="2" t="s">
         <v>15</v>
@@ -33070,7 +33070,7 @@
         <v>14</v>
       </c>
       <c r="F451" s="2">
-        <v>3059</v>
+        <v>1359</v>
       </c>
       <c r="G451" s="2" t="s">
         <v>15</v>
@@ -33102,7 +33102,7 @@
         <v>14</v>
       </c>
       <c r="F452" s="2">
-        <v>1455</v>
+        <v>1499</v>
       </c>
       <c r="G452" s="2" t="s">
         <v>15</v>
@@ -33134,7 +33134,7 @@
         <v>14</v>
       </c>
       <c r="F453" s="2">
-        <v>2037</v>
+        <v>4045</v>
       </c>
       <c r="G453" s="2" t="s">
         <v>15</v>
@@ -33166,7 +33166,7 @@
         <v>14</v>
       </c>
       <c r="F454" s="2">
-        <v>4117</v>
+        <v>3425</v>
       </c>
       <c r="G454" s="2" t="s">
         <v>15</v>
@@ -33198,7 +33198,7 @@
         <v>14</v>
       </c>
       <c r="F455" s="2">
-        <v>866</v>
+        <v>1446</v>
       </c>
       <c r="G455" s="2" t="s">
         <v>15</v>
@@ -33230,7 +33230,7 @@
         <v>14</v>
       </c>
       <c r="F456" s="2">
-        <v>1543</v>
+        <v>1455</v>
       </c>
       <c r="G456" s="2" t="s">
         <v>15</v>
@@ -33262,7 +33262,7 @@
         <v>14</v>
       </c>
       <c r="F457" s="2">
-        <v>4740</v>
+        <v>2489</v>
       </c>
       <c r="G457" s="2" t="s">
         <v>15</v>
@@ -33294,7 +33294,7 @@
         <v>14</v>
       </c>
       <c r="F458" s="2">
-        <v>3691</v>
+        <v>2144</v>
       </c>
       <c r="G458" s="2" t="s">
         <v>15</v>
@@ -33326,7 +33326,7 @@
         <v>14</v>
       </c>
       <c r="F459" s="2">
-        <v>2319</v>
+        <v>4021</v>
       </c>
       <c r="G459" s="2" t="s">
         <v>15</v>
@@ -33358,7 +33358,7 @@
         <v>14</v>
       </c>
       <c r="F460" s="2">
-        <v>3559</v>
+        <v>3260</v>
       </c>
       <c r="G460" s="2" t="s">
         <v>15</v>
@@ -33390,7 +33390,7 @@
         <v>14</v>
       </c>
       <c r="F461" s="2">
-        <v>4066</v>
+        <v>2199</v>
       </c>
       <c r="G461" s="2" t="s">
         <v>15</v>
@@ -33422,7 +33422,7 @@
         <v>14</v>
       </c>
       <c r="F462" s="2">
-        <v>1124</v>
+        <v>4139</v>
       </c>
       <c r="G462" s="2" t="s">
         <v>15</v>
@@ -33454,7 +33454,7 @@
         <v>14</v>
       </c>
       <c r="F463" s="2">
-        <v>3755</v>
+        <v>2648</v>
       </c>
       <c r="G463" s="2" t="s">
         <v>15</v>
@@ -33486,7 +33486,7 @@
         <v>14</v>
       </c>
       <c r="F464" s="2">
-        <v>2214</v>
+        <v>3646</v>
       </c>
       <c r="G464" s="2" t="s">
         <v>15</v>
@@ -33518,7 +33518,7 @@
         <v>14</v>
       </c>
       <c r="F465" s="2">
-        <v>3316</v>
+        <v>2292</v>
       </c>
       <c r="G465" s="2" t="s">
         <v>15</v>
@@ -33550,7 +33550,7 @@
         <v>14</v>
       </c>
       <c r="F466" s="2">
-        <v>3822</v>
+        <v>1156</v>
       </c>
       <c r="G466" s="2" t="s">
         <v>15</v>
@@ -33582,7 +33582,7 @@
         <v>14</v>
       </c>
       <c r="F467" s="2">
-        <v>4759</v>
+        <v>1251</v>
       </c>
       <c r="G467" s="2" t="s">
         <v>15</v>
@@ -33614,7 +33614,7 @@
         <v>14</v>
       </c>
       <c r="F468" s="2">
-        <v>4491</v>
+        <v>1540</v>
       </c>
       <c r="G468" s="2" t="s">
         <v>15</v>
@@ -33646,7 +33646,7 @@
         <v>14</v>
       </c>
       <c r="F469" s="2">
-        <v>3244</v>
+        <v>3431</v>
       </c>
       <c r="G469" s="2" t="s">
         <v>15</v>
@@ -33678,7 +33678,7 @@
         <v>14</v>
       </c>
       <c r="F470" s="2">
-        <v>1088</v>
+        <v>1916</v>
       </c>
       <c r="G470" s="2" t="s">
         <v>15</v>
@@ -33710,7 +33710,7 @@
         <v>14</v>
       </c>
       <c r="F471" s="2">
-        <v>2200</v>
+        <v>2510</v>
       </c>
       <c r="G471" s="2" t="s">
         <v>15</v>

--- a/reports/selenium/latest/excel/Automation_Test_Report.xlsx
+++ b/reports/selenium/latest/excel/Automation_Test_Report.xlsx
@@ -3084,7 +3084,7 @@
     <t>Build</t>
   </si>
   <si>
-    <t>5</t>
+    <t>6</t>
   </si>
   <si>
     <t>Branch</t>
@@ -3096,13 +3096,13 @@
     <t>Commit</t>
   </si>
   <si>
-    <t>bbcb82d96eb7</t>
+    <t>90ba612a9b32</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T15:32:38.948Z</t>
+    <t>2026-08-18T15:39:48.370Z</t>
   </si>
   <si>
     <t>Browser</t>
@@ -3607,7 +3607,7 @@
         <v>14</v>
       </c>
       <c r="F2" s="2">
-        <v>1892</v>
+        <v>1693</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>15</v>
@@ -3639,7 +3639,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="2">
-        <v>2657</v>
+        <v>2763</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>15</v>
@@ -3671,7 +3671,7 @@
         <v>14</v>
       </c>
       <c r="F4" s="2">
-        <v>3833</v>
+        <v>3488</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
@@ -3703,7 +3703,7 @@
         <v>14</v>
       </c>
       <c r="F5" s="2">
-        <v>1342</v>
+        <v>1400</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
@@ -3735,7 +3735,7 @@
         <v>14</v>
       </c>
       <c r="F6" s="2">
-        <v>4717</v>
+        <v>1372</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -3767,7 +3767,7 @@
         <v>14</v>
       </c>
       <c r="F7" s="2">
-        <v>2841</v>
+        <v>1244</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -3799,7 +3799,7 @@
         <v>14</v>
       </c>
       <c r="F8" s="2">
-        <v>3928</v>
+        <v>2751</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -3831,7 +3831,7 @@
         <v>14</v>
       </c>
       <c r="F9" s="2">
-        <v>1358</v>
+        <v>3523</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -3863,7 +3863,7 @@
         <v>14</v>
       </c>
       <c r="F10" s="2">
-        <v>2120</v>
+        <v>1805</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
@@ -3895,7 +3895,7 @@
         <v>14</v>
       </c>
       <c r="F11" s="2">
-        <v>1911</v>
+        <v>3811</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
@@ -3927,7 +3927,7 @@
         <v>14</v>
       </c>
       <c r="F12" s="2">
-        <v>4341</v>
+        <v>1829</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
@@ -3959,7 +3959,7 @@
         <v>14</v>
       </c>
       <c r="F13" s="2">
-        <v>1350</v>
+        <v>1123</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -3991,7 +3991,7 @@
         <v>14</v>
       </c>
       <c r="F14" s="2">
-        <v>1818</v>
+        <v>2733</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -4023,7 +4023,7 @@
         <v>14</v>
       </c>
       <c r="F15" s="2">
-        <v>3111</v>
+        <v>1648</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -4055,7 +4055,7 @@
         <v>14</v>
       </c>
       <c r="F16" s="2">
-        <v>3406</v>
+        <v>828</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
@@ -4087,7 +4087,7 @@
         <v>14</v>
       </c>
       <c r="F17" s="2">
-        <v>1441</v>
+        <v>2736</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
@@ -4119,7 +4119,7 @@
         <v>14</v>
       </c>
       <c r="F18" s="2">
-        <v>1774</v>
+        <v>2115</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
@@ -4151,7 +4151,7 @@
         <v>14</v>
       </c>
       <c r="F19" s="2">
-        <v>4142</v>
+        <v>1912</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
@@ -4183,7 +4183,7 @@
         <v>14</v>
       </c>
       <c r="F20" s="2">
-        <v>4517</v>
+        <v>1479</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
@@ -4215,7 +4215,7 @@
         <v>14</v>
       </c>
       <c r="F21" s="2">
-        <v>3005</v>
+        <v>2920</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -4247,7 +4247,7 @@
         <v>14</v>
       </c>
       <c r="F22" s="2">
-        <v>2613</v>
+        <v>1455</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -4279,7 +4279,7 @@
         <v>14</v>
       </c>
       <c r="F23" s="2">
-        <v>1642</v>
+        <v>2941</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -4311,7 +4311,7 @@
         <v>14</v>
       </c>
       <c r="F24" s="2">
-        <v>931</v>
+        <v>1315</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -4343,7 +4343,7 @@
         <v>14</v>
       </c>
       <c r="F25" s="2">
-        <v>3439</v>
+        <v>1133</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -4375,7 +4375,7 @@
         <v>14</v>
       </c>
       <c r="F26" s="2">
-        <v>3388</v>
+        <v>4561</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -4407,7 +4407,7 @@
         <v>14</v>
       </c>
       <c r="F27" s="2">
-        <v>3024</v>
+        <v>1944</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>15</v>
@@ -4439,7 +4439,7 @@
         <v>14</v>
       </c>
       <c r="F28" s="2">
-        <v>3016</v>
+        <v>2944</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>15</v>
@@ -4471,7 +4471,7 @@
         <v>14</v>
       </c>
       <c r="F29" s="2">
-        <v>3449</v>
+        <v>2296</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>15</v>
@@ -4503,7 +4503,7 @@
         <v>14</v>
       </c>
       <c r="F30" s="2">
-        <v>3286</v>
+        <v>1904</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>15</v>
@@ -4535,7 +4535,7 @@
         <v>14</v>
       </c>
       <c r="F31" s="2">
-        <v>3852</v>
+        <v>1933</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>15</v>
@@ -4567,7 +4567,7 @@
         <v>14</v>
       </c>
       <c r="F32" s="2">
-        <v>2881</v>
+        <v>3045</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>15</v>
@@ -4599,7 +4599,7 @@
         <v>14</v>
       </c>
       <c r="F33" s="2">
-        <v>4283</v>
+        <v>4298</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>15</v>
@@ -4631,7 +4631,7 @@
         <v>14</v>
       </c>
       <c r="F34" s="2">
-        <v>4255</v>
+        <v>3224</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>15</v>
@@ -4663,7 +4663,7 @@
         <v>14</v>
       </c>
       <c r="F35" s="2">
-        <v>3792</v>
+        <v>3466</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>15</v>
@@ -4695,7 +4695,7 @@
         <v>14</v>
       </c>
       <c r="F36" s="2">
-        <v>2822</v>
+        <v>3601</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>15</v>
@@ -4727,7 +4727,7 @@
         <v>14</v>
       </c>
       <c r="F37" s="2">
-        <v>1463</v>
+        <v>3129</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>15</v>
@@ -4759,7 +4759,7 @@
         <v>14</v>
       </c>
       <c r="F38" s="2">
-        <v>3017</v>
+        <v>2443</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>15</v>
@@ -4791,7 +4791,7 @@
         <v>14</v>
       </c>
       <c r="F39" s="2">
-        <v>3465</v>
+        <v>1282</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>15</v>
@@ -4823,7 +4823,7 @@
         <v>14</v>
       </c>
       <c r="F40" s="2">
-        <v>3879</v>
+        <v>2877</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>15</v>
@@ -4855,7 +4855,7 @@
         <v>14</v>
       </c>
       <c r="F41" s="2">
-        <v>3672</v>
+        <v>2481</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>15</v>
@@ -4887,7 +4887,7 @@
         <v>14</v>
       </c>
       <c r="F42" s="2">
-        <v>2689</v>
+        <v>1808</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>15</v>
@@ -4919,7 +4919,7 @@
         <v>14</v>
       </c>
       <c r="F43" s="2">
-        <v>3522</v>
+        <v>1497</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>15</v>
@@ -4951,7 +4951,7 @@
         <v>14</v>
       </c>
       <c r="F44" s="2">
-        <v>3834</v>
+        <v>4274</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>15</v>
@@ -4983,7 +4983,7 @@
         <v>14</v>
       </c>
       <c r="F45" s="2">
-        <v>3772</v>
+        <v>4783</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>15</v>
@@ -5015,7 +5015,7 @@
         <v>14</v>
       </c>
       <c r="F46" s="2">
-        <v>3585</v>
+        <v>4728</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>15</v>
@@ -5047,7 +5047,7 @@
         <v>14</v>
       </c>
       <c r="F47" s="2">
-        <v>2015</v>
+        <v>4747</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>15</v>
@@ -5079,7 +5079,7 @@
         <v>14</v>
       </c>
       <c r="F48" s="2">
-        <v>2760</v>
+        <v>3881</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>15</v>
@@ -5111,7 +5111,7 @@
         <v>14</v>
       </c>
       <c r="F49" s="2">
-        <v>1637</v>
+        <v>2720</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>15</v>
@@ -5143,7 +5143,7 @@
         <v>14</v>
       </c>
       <c r="F50" s="2">
-        <v>4671</v>
+        <v>1765</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>15</v>
@@ -5175,7 +5175,7 @@
         <v>14</v>
       </c>
       <c r="F51" s="2">
-        <v>1390</v>
+        <v>4230</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>15</v>
@@ -5207,7 +5207,7 @@
         <v>14</v>
       </c>
       <c r="F52" s="2">
-        <v>4759</v>
+        <v>1714</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>15</v>
@@ -5239,7 +5239,7 @@
         <v>14</v>
       </c>
       <c r="F53" s="2">
-        <v>3541</v>
+        <v>3046</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>15</v>
@@ -5271,7 +5271,7 @@
         <v>14</v>
       </c>
       <c r="F54" s="2">
-        <v>895</v>
+        <v>3123</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>15</v>
@@ -5303,7 +5303,7 @@
         <v>14</v>
       </c>
       <c r="F55" s="2">
-        <v>1575</v>
+        <v>3064</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>15</v>
@@ -5335,7 +5335,7 @@
         <v>14</v>
       </c>
       <c r="F56" s="2">
-        <v>2775</v>
+        <v>2153</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>15</v>
@@ -5367,7 +5367,7 @@
         <v>14</v>
       </c>
       <c r="F57" s="2">
-        <v>4469</v>
+        <v>2128</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>15</v>
@@ -5399,7 +5399,7 @@
         <v>14</v>
       </c>
       <c r="F58" s="2">
-        <v>3476</v>
+        <v>1689</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>15</v>
@@ -5431,7 +5431,7 @@
         <v>14</v>
       </c>
       <c r="F59" s="2">
-        <v>3274</v>
+        <v>1105</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>15</v>
@@ -5463,7 +5463,7 @@
         <v>14</v>
       </c>
       <c r="F60" s="2">
-        <v>2840</v>
+        <v>921</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>15</v>
@@ -5495,7 +5495,7 @@
         <v>14</v>
       </c>
       <c r="F61" s="2">
-        <v>3867</v>
+        <v>4083</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>15</v>
@@ -5527,7 +5527,7 @@
         <v>14</v>
       </c>
       <c r="F62" s="2">
-        <v>2552</v>
+        <v>822</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>15</v>
@@ -5559,7 +5559,7 @@
         <v>14</v>
       </c>
       <c r="F63" s="2">
-        <v>1122</v>
+        <v>4181</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>15</v>
@@ -5591,7 +5591,7 @@
         <v>14</v>
       </c>
       <c r="F64" s="2">
-        <v>3103</v>
+        <v>1956</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>15</v>
@@ -5623,7 +5623,7 @@
         <v>14</v>
       </c>
       <c r="F65" s="2">
-        <v>4147</v>
+        <v>3388</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>15</v>
@@ -5655,7 +5655,7 @@
         <v>14</v>
       </c>
       <c r="F66" s="2">
-        <v>2349</v>
+        <v>1901</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>15</v>
@@ -5687,7 +5687,7 @@
         <v>14</v>
       </c>
       <c r="F67" s="2">
-        <v>2928</v>
+        <v>1495</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>15</v>
@@ -5719,7 +5719,7 @@
         <v>14</v>
       </c>
       <c r="F68" s="2">
-        <v>3240</v>
+        <v>1744</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>15</v>
@@ -5751,7 +5751,7 @@
         <v>14</v>
       </c>
       <c r="F69" s="2">
-        <v>2796</v>
+        <v>1858</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>15</v>
@@ -5783,7 +5783,7 @@
         <v>14</v>
       </c>
       <c r="F70" s="2">
-        <v>4548</v>
+        <v>1693</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>15</v>
@@ -5815,7 +5815,7 @@
         <v>14</v>
       </c>
       <c r="F71" s="2">
-        <v>871</v>
+        <v>3535</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>15</v>
@@ -5847,7 +5847,7 @@
         <v>14</v>
       </c>
       <c r="F72" s="2">
-        <v>2941</v>
+        <v>4646</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>15</v>
@@ -5879,7 +5879,7 @@
         <v>14</v>
       </c>
       <c r="F73" s="2">
-        <v>3912</v>
+        <v>2528</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>15</v>
@@ -5911,7 +5911,7 @@
         <v>14</v>
       </c>
       <c r="F74" s="2">
-        <v>3196</v>
+        <v>2704</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>15</v>
@@ -5943,7 +5943,7 @@
         <v>14</v>
       </c>
       <c r="F75" s="2">
-        <v>3252</v>
+        <v>1421</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>15</v>
@@ -5975,7 +5975,7 @@
         <v>14</v>
       </c>
       <c r="F76" s="2">
-        <v>1264</v>
+        <v>2250</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>15</v>
@@ -6007,7 +6007,7 @@
         <v>14</v>
       </c>
       <c r="F77" s="2">
-        <v>1210</v>
+        <v>2660</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>15</v>
@@ -6039,7 +6039,7 @@
         <v>14</v>
       </c>
       <c r="F78" s="2">
-        <v>2679</v>
+        <v>1146</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>15</v>
@@ -6071,7 +6071,7 @@
         <v>14</v>
       </c>
       <c r="F79" s="2">
-        <v>2679</v>
+        <v>2451</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>15</v>
@@ -6103,7 +6103,7 @@
         <v>14</v>
       </c>
       <c r="F80" s="2">
-        <v>4275</v>
+        <v>4165</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>15</v>
@@ -6135,7 +6135,7 @@
         <v>14</v>
       </c>
       <c r="F81" s="2">
-        <v>2458</v>
+        <v>965</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>15</v>
@@ -6167,7 +6167,7 @@
         <v>14</v>
       </c>
       <c r="F82" s="2">
-        <v>1359</v>
+        <v>3162</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>15</v>
@@ -6199,7 +6199,7 @@
         <v>14</v>
       </c>
       <c r="F83" s="2">
-        <v>1899</v>
+        <v>4288</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>15</v>
@@ -6231,7 +6231,7 @@
         <v>14</v>
       </c>
       <c r="F84" s="2">
-        <v>3909</v>
+        <v>4510</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>15</v>
@@ -6263,7 +6263,7 @@
         <v>14</v>
       </c>
       <c r="F85" s="2">
-        <v>4388</v>
+        <v>1416</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>15</v>
@@ -6295,7 +6295,7 @@
         <v>14</v>
       </c>
       <c r="F86" s="2">
-        <v>3797</v>
+        <v>2999</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>15</v>
@@ -6327,7 +6327,7 @@
         <v>14</v>
       </c>
       <c r="F87" s="2">
-        <v>2659</v>
+        <v>4227</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>15</v>
@@ -6359,7 +6359,7 @@
         <v>14</v>
       </c>
       <c r="F88" s="2">
-        <v>2596</v>
+        <v>3790</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>15</v>
@@ -6391,7 +6391,7 @@
         <v>14</v>
       </c>
       <c r="F89" s="2">
-        <v>3583</v>
+        <v>1019</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>15</v>
@@ -6423,7 +6423,7 @@
         <v>14</v>
       </c>
       <c r="F90" s="2">
-        <v>4453</v>
+        <v>3377</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>15</v>
@@ -6455,7 +6455,7 @@
         <v>14</v>
       </c>
       <c r="F91" s="2">
-        <v>3852</v>
+        <v>3281</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>15</v>
@@ -6487,7 +6487,7 @@
         <v>14</v>
       </c>
       <c r="F92" s="2">
-        <v>2716</v>
+        <v>1607</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>15</v>
@@ -6519,7 +6519,7 @@
         <v>14</v>
       </c>
       <c r="F93" s="2">
-        <v>4512</v>
+        <v>3767</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>15</v>
@@ -6551,7 +6551,7 @@
         <v>14</v>
       </c>
       <c r="F94" s="2">
-        <v>3503</v>
+        <v>4431</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>15</v>
@@ -6583,7 +6583,7 @@
         <v>14</v>
       </c>
       <c r="F95" s="2">
-        <v>1796</v>
+        <v>899</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>15</v>
@@ -6615,7 +6615,7 @@
         <v>14</v>
       </c>
       <c r="F96" s="2">
-        <v>3640</v>
+        <v>1148</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>15</v>
@@ -6647,7 +6647,7 @@
         <v>14</v>
       </c>
       <c r="F97" s="2">
-        <v>3357</v>
+        <v>1335</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>15</v>
@@ -6679,7 +6679,7 @@
         <v>14</v>
       </c>
       <c r="F98" s="2">
-        <v>1280</v>
+        <v>1730</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>15</v>
@@ -6711,7 +6711,7 @@
         <v>14</v>
       </c>
       <c r="F99" s="2">
-        <v>4473</v>
+        <v>3319</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>15</v>
@@ -6743,7 +6743,7 @@
         <v>14</v>
       </c>
       <c r="F100" s="2">
-        <v>3644</v>
+        <v>3628</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>15</v>
@@ -6775,7 +6775,7 @@
         <v>14</v>
       </c>
       <c r="F101" s="2">
-        <v>3736</v>
+        <v>2120</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>15</v>
@@ -6807,7 +6807,7 @@
         <v>14</v>
       </c>
       <c r="F102" s="2">
-        <v>3532</v>
+        <v>3973</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>15</v>
@@ -6839,7 +6839,7 @@
         <v>14</v>
       </c>
       <c r="F103" s="2">
-        <v>4706</v>
+        <v>2470</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>15</v>
@@ -6871,7 +6871,7 @@
         <v>14</v>
       </c>
       <c r="F104" s="2">
-        <v>2716</v>
+        <v>2598</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>15</v>
@@ -6903,7 +6903,7 @@
         <v>14</v>
       </c>
       <c r="F105" s="2">
-        <v>4043</v>
+        <v>2973</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>15</v>
@@ -6935,7 +6935,7 @@
         <v>14</v>
       </c>
       <c r="F106" s="2">
-        <v>936</v>
+        <v>3687</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>15</v>
@@ -6967,7 +6967,7 @@
         <v>14</v>
       </c>
       <c r="F107" s="2">
-        <v>1887</v>
+        <v>3958</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>15</v>
@@ -6999,7 +6999,7 @@
         <v>14</v>
       </c>
       <c r="F108" s="2">
-        <v>4490</v>
+        <v>3127</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>15</v>
@@ -7031,7 +7031,7 @@
         <v>14</v>
       </c>
       <c r="F109" s="2">
-        <v>4322</v>
+        <v>1809</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>15</v>
@@ -7063,7 +7063,7 @@
         <v>14</v>
       </c>
       <c r="F110" s="2">
-        <v>3535</v>
+        <v>1798</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>15</v>
@@ -7095,7 +7095,7 @@
         <v>14</v>
       </c>
       <c r="F111" s="2">
-        <v>3636</v>
+        <v>2261</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>15</v>
@@ -7127,7 +7127,7 @@
         <v>14</v>
       </c>
       <c r="F112" s="2">
-        <v>3404</v>
+        <v>866</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>15</v>
@@ -7159,7 +7159,7 @@
         <v>14</v>
       </c>
       <c r="F113" s="2">
-        <v>2371</v>
+        <v>1339</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>15</v>
@@ -7191,7 +7191,7 @@
         <v>14</v>
       </c>
       <c r="F114" s="2">
-        <v>2447</v>
+        <v>4395</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>15</v>
@@ -7223,7 +7223,7 @@
         <v>14</v>
       </c>
       <c r="F115" s="2">
-        <v>4309</v>
+        <v>2927</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>15</v>
@@ -7255,7 +7255,7 @@
         <v>14</v>
       </c>
       <c r="F116" s="2">
-        <v>2190</v>
+        <v>3087</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>15</v>
@@ -7287,7 +7287,7 @@
         <v>14</v>
       </c>
       <c r="F117" s="2">
-        <v>3354</v>
+        <v>2127</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>15</v>
@@ -7319,7 +7319,7 @@
         <v>14</v>
       </c>
       <c r="F118" s="2">
-        <v>2050</v>
+        <v>3532</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>15</v>
@@ -7351,7 +7351,7 @@
         <v>14</v>
       </c>
       <c r="F119" s="2">
-        <v>1811</v>
+        <v>2646</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>15</v>
@@ -7383,7 +7383,7 @@
         <v>14</v>
       </c>
       <c r="F120" s="2">
-        <v>3906</v>
+        <v>2500</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>15</v>
@@ -7415,7 +7415,7 @@
         <v>14</v>
       </c>
       <c r="F121" s="2">
-        <v>2582</v>
+        <v>2825</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>15</v>
@@ -7447,7 +7447,7 @@
         <v>14</v>
       </c>
       <c r="F122" s="2">
-        <v>4230</v>
+        <v>3584</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>15</v>
@@ -7479,7 +7479,7 @@
         <v>14</v>
       </c>
       <c r="F123" s="2">
-        <v>4282</v>
+        <v>2358</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>15</v>
@@ -7511,7 +7511,7 @@
         <v>14</v>
       </c>
       <c r="F124" s="2">
-        <v>2338</v>
+        <v>3369</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>15</v>
@@ -7543,7 +7543,7 @@
         <v>14</v>
       </c>
       <c r="F125" s="2">
-        <v>1894</v>
+        <v>2444</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>15</v>
@@ -7575,7 +7575,7 @@
         <v>14</v>
       </c>
       <c r="F126" s="2">
-        <v>1079</v>
+        <v>3099</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>15</v>
@@ -7607,7 +7607,7 @@
         <v>14</v>
       </c>
       <c r="F127" s="2">
-        <v>1441</v>
+        <v>3107</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>15</v>
@@ -7639,7 +7639,7 @@
         <v>14</v>
       </c>
       <c r="F128" s="2">
-        <v>4145</v>
+        <v>804</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>15</v>
@@ -7671,7 +7671,7 @@
         <v>14</v>
       </c>
       <c r="F129" s="2">
-        <v>2952</v>
+        <v>1562</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>15</v>
@@ -7703,7 +7703,7 @@
         <v>14</v>
       </c>
       <c r="F130" s="2">
-        <v>4548</v>
+        <v>3447</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>15</v>
@@ -7735,7 +7735,7 @@
         <v>14</v>
       </c>
       <c r="F131" s="2">
-        <v>3228</v>
+        <v>3770</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>15</v>
@@ -7767,7 +7767,7 @@
         <v>14</v>
       </c>
       <c r="F132" s="2">
-        <v>2546</v>
+        <v>4546</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>15</v>
@@ -7799,7 +7799,7 @@
         <v>14</v>
       </c>
       <c r="F133" s="2">
-        <v>4333</v>
+        <v>2026</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>15</v>
@@ -7831,7 +7831,7 @@
         <v>14</v>
       </c>
       <c r="F134" s="2">
-        <v>2125</v>
+        <v>2154</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>15</v>
@@ -7863,7 +7863,7 @@
         <v>14</v>
       </c>
       <c r="F135" s="2">
-        <v>951</v>
+        <v>3915</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>15</v>
@@ -7895,7 +7895,7 @@
         <v>14</v>
       </c>
       <c r="F136" s="2">
-        <v>930</v>
+        <v>3087</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>15</v>
@@ -7927,7 +7927,7 @@
         <v>14</v>
       </c>
       <c r="F137" s="2">
-        <v>3971</v>
+        <v>3851</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>15</v>
@@ -7959,7 +7959,7 @@
         <v>14</v>
       </c>
       <c r="F138" s="2">
-        <v>3709</v>
+        <v>4408</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>15</v>
@@ -7991,7 +7991,7 @@
         <v>14</v>
       </c>
       <c r="F139" s="2">
-        <v>3733</v>
+        <v>2519</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>15</v>
@@ -8023,7 +8023,7 @@
         <v>14</v>
       </c>
       <c r="F140" s="2">
-        <v>2216</v>
+        <v>2913</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>15</v>
@@ -8055,7 +8055,7 @@
         <v>14</v>
       </c>
       <c r="F141" s="2">
-        <v>1067</v>
+        <v>2712</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>15</v>
@@ -8087,7 +8087,7 @@
         <v>14</v>
       </c>
       <c r="F142" s="2">
-        <v>4156</v>
+        <v>931</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>15</v>
@@ -8119,7 +8119,7 @@
         <v>14</v>
       </c>
       <c r="F143" s="2">
-        <v>2000</v>
+        <v>1754</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>15</v>
@@ -8151,7 +8151,7 @@
         <v>14</v>
       </c>
       <c r="F144" s="2">
-        <v>1901</v>
+        <v>996</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>15</v>
@@ -8183,7 +8183,7 @@
         <v>14</v>
       </c>
       <c r="F145" s="2">
-        <v>4351</v>
+        <v>3557</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>15</v>
@@ -8215,7 +8215,7 @@
         <v>14</v>
       </c>
       <c r="F146" s="2">
-        <v>1911</v>
+        <v>1916</v>
       </c>
       <c r="G146" s="2" t="s">
         <v>15</v>
@@ -8247,7 +8247,7 @@
         <v>14</v>
       </c>
       <c r="F147" s="2">
-        <v>4677</v>
+        <v>1396</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>15</v>
@@ -8279,7 +8279,7 @@
         <v>14</v>
       </c>
       <c r="F148" s="2">
-        <v>3896</v>
+        <v>826</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>15</v>
@@ -8311,7 +8311,7 @@
         <v>14</v>
       </c>
       <c r="F149" s="2">
-        <v>1015</v>
+        <v>2649</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>15</v>
@@ -8343,7 +8343,7 @@
         <v>14</v>
       </c>
       <c r="F150" s="2">
-        <v>1233</v>
+        <v>3247</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>15</v>
@@ -8375,7 +8375,7 @@
         <v>14</v>
       </c>
       <c r="F151" s="2">
-        <v>1168</v>
+        <v>4589</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>15</v>
@@ -8407,7 +8407,7 @@
         <v>14</v>
       </c>
       <c r="F152" s="2">
-        <v>1687</v>
+        <v>4711</v>
       </c>
       <c r="G152" s="2" t="s">
         <v>15</v>
@@ -8439,7 +8439,7 @@
         <v>14</v>
       </c>
       <c r="F153" s="2">
-        <v>3482</v>
+        <v>1370</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>15</v>
@@ -8471,7 +8471,7 @@
         <v>14</v>
       </c>
       <c r="F154" s="2">
-        <v>4002</v>
+        <v>2841</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>15</v>
@@ -8503,7 +8503,7 @@
         <v>14</v>
       </c>
       <c r="F155" s="2">
-        <v>3815</v>
+        <v>4779</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>15</v>
@@ -8535,7 +8535,7 @@
         <v>14</v>
       </c>
       <c r="F156" s="2">
-        <v>1535</v>
+        <v>1895</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>15</v>
@@ -8567,7 +8567,7 @@
         <v>14</v>
       </c>
       <c r="F157" s="2">
-        <v>858</v>
+        <v>4531</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>15</v>
@@ -8599,7 +8599,7 @@
         <v>14</v>
       </c>
       <c r="F158" s="2">
-        <v>4236</v>
+        <v>2123</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>15</v>
@@ -8631,7 +8631,7 @@
         <v>14</v>
       </c>
       <c r="F159" s="2">
-        <v>4310</v>
+        <v>1856</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>15</v>
@@ -8663,7 +8663,7 @@
         <v>14</v>
       </c>
       <c r="F160" s="2">
-        <v>2367</v>
+        <v>3338</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>15</v>
@@ -8695,7 +8695,7 @@
         <v>14</v>
       </c>
       <c r="F161" s="2">
-        <v>909</v>
+        <v>1991</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>15</v>
@@ -8727,7 +8727,7 @@
         <v>14</v>
       </c>
       <c r="F162" s="2">
-        <v>3832</v>
+        <v>3896</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>15</v>
@@ -8759,7 +8759,7 @@
         <v>14</v>
       </c>
       <c r="F163" s="2">
-        <v>4270</v>
+        <v>3887</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>15</v>
@@ -8791,7 +8791,7 @@
         <v>14</v>
       </c>
       <c r="F164" s="2">
-        <v>1176</v>
+        <v>3695</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>15</v>
@@ -8823,7 +8823,7 @@
         <v>14</v>
       </c>
       <c r="F165" s="2">
-        <v>3931</v>
+        <v>2889</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>15</v>
@@ -8855,7 +8855,7 @@
         <v>14</v>
       </c>
       <c r="F166" s="2">
-        <v>855</v>
+        <v>3328</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>15</v>
@@ -8887,7 +8887,7 @@
         <v>14</v>
       </c>
       <c r="F167" s="2">
-        <v>3118</v>
+        <v>1514</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>15</v>
@@ -8919,7 +8919,7 @@
         <v>14</v>
       </c>
       <c r="F168" s="2">
-        <v>1339</v>
+        <v>3203</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>15</v>
@@ -8951,7 +8951,7 @@
         <v>14</v>
       </c>
       <c r="F169" s="2">
-        <v>4456</v>
+        <v>4772</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>15</v>
@@ -8983,7 +8983,7 @@
         <v>14</v>
       </c>
       <c r="F170" s="2">
-        <v>3038</v>
+        <v>4353</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>15</v>
@@ -9015,7 +9015,7 @@
         <v>14</v>
       </c>
       <c r="F171" s="2">
-        <v>4012</v>
+        <v>4739</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>15</v>
@@ -9047,7 +9047,7 @@
         <v>14</v>
       </c>
       <c r="F172" s="2">
-        <v>2879</v>
+        <v>4626</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>15</v>
@@ -9079,7 +9079,7 @@
         <v>14</v>
       </c>
       <c r="F173" s="2">
-        <v>4487</v>
+        <v>1541</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>15</v>
@@ -9111,7 +9111,7 @@
         <v>14</v>
       </c>
       <c r="F174" s="2">
-        <v>2318</v>
+        <v>2648</v>
       </c>
       <c r="G174" s="2" t="s">
         <v>15</v>
@@ -9143,7 +9143,7 @@
         <v>14</v>
       </c>
       <c r="F175" s="2">
-        <v>2338</v>
+        <v>1492</v>
       </c>
       <c r="G175" s="2" t="s">
         <v>15</v>
@@ -9175,7 +9175,7 @@
         <v>14</v>
       </c>
       <c r="F176" s="2">
-        <v>3218</v>
+        <v>3512</v>
       </c>
       <c r="G176" s="2" t="s">
         <v>15</v>
@@ -9207,7 +9207,7 @@
         <v>14</v>
       </c>
       <c r="F177" s="2">
-        <v>4270</v>
+        <v>4237</v>
       </c>
       <c r="G177" s="2" t="s">
         <v>15</v>
@@ -9239,7 +9239,7 @@
         <v>14</v>
       </c>
       <c r="F178" s="2">
-        <v>2323</v>
+        <v>882</v>
       </c>
       <c r="G178" s="2" t="s">
         <v>15</v>
@@ -9271,7 +9271,7 @@
         <v>14</v>
       </c>
       <c r="F179" s="2">
-        <v>2073</v>
+        <v>4788</v>
       </c>
       <c r="G179" s="2" t="s">
         <v>15</v>
@@ -9303,7 +9303,7 @@
         <v>14</v>
       </c>
       <c r="F180" s="2">
-        <v>2820</v>
+        <v>2969</v>
       </c>
       <c r="G180" s="2" t="s">
         <v>15</v>
@@ -9335,7 +9335,7 @@
         <v>14</v>
       </c>
       <c r="F181" s="2">
-        <v>4567</v>
+        <v>829</v>
       </c>
       <c r="G181" s="2" t="s">
         <v>15</v>
@@ -9367,7 +9367,7 @@
         <v>14</v>
       </c>
       <c r="F182" s="2">
-        <v>1004</v>
+        <v>1599</v>
       </c>
       <c r="G182" s="2" t="s">
         <v>15</v>
@@ -9399,7 +9399,7 @@
         <v>14</v>
       </c>
       <c r="F183" s="2">
-        <v>3521</v>
+        <v>2563</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>15</v>
@@ -9431,7 +9431,7 @@
         <v>14</v>
       </c>
       <c r="F184" s="2">
-        <v>3340</v>
+        <v>2878</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>15</v>
@@ -9463,7 +9463,7 @@
         <v>14</v>
       </c>
       <c r="F185" s="2">
-        <v>1381</v>
+        <v>3283</v>
       </c>
       <c r="G185" s="2" t="s">
         <v>15</v>
@@ -9495,7 +9495,7 @@
         <v>14</v>
       </c>
       <c r="F186" s="2">
-        <v>2213</v>
+        <v>4098</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>15</v>
@@ -9527,7 +9527,7 @@
         <v>14</v>
       </c>
       <c r="F187" s="2">
-        <v>2486</v>
+        <v>2167</v>
       </c>
       <c r="G187" s="2" t="s">
         <v>15</v>
@@ -9559,7 +9559,7 @@
         <v>14</v>
       </c>
       <c r="F188" s="2">
-        <v>2927</v>
+        <v>3075</v>
       </c>
       <c r="G188" s="2" t="s">
         <v>15</v>
@@ -9591,7 +9591,7 @@
         <v>14</v>
       </c>
       <c r="F189" s="2">
-        <v>1799</v>
+        <v>3947</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>15</v>
@@ -9623,7 +9623,7 @@
         <v>14</v>
       </c>
       <c r="F190" s="2">
-        <v>2840</v>
+        <v>1567</v>
       </c>
       <c r="G190" s="2" t="s">
         <v>15</v>
@@ -9655,7 +9655,7 @@
         <v>14</v>
       </c>
       <c r="F191" s="2">
-        <v>4130</v>
+        <v>1689</v>
       </c>
       <c r="G191" s="2" t="s">
         <v>15</v>
@@ -9687,7 +9687,7 @@
         <v>14</v>
       </c>
       <c r="F192" s="2">
-        <v>3410</v>
+        <v>3217</v>
       </c>
       <c r="G192" s="2" t="s">
         <v>15</v>
@@ -9719,7 +9719,7 @@
         <v>14</v>
       </c>
       <c r="F193" s="2">
-        <v>2684</v>
+        <v>1060</v>
       </c>
       <c r="G193" s="2" t="s">
         <v>15</v>
@@ -9751,7 +9751,7 @@
         <v>14</v>
       </c>
       <c r="F194" s="2">
-        <v>2487</v>
+        <v>902</v>
       </c>
       <c r="G194" s="2" t="s">
         <v>15</v>
@@ -9783,7 +9783,7 @@
         <v>14</v>
       </c>
       <c r="F195" s="2">
-        <v>4360</v>
+        <v>2583</v>
       </c>
       <c r="G195" s="2" t="s">
         <v>15</v>
@@ -9815,7 +9815,7 @@
         <v>14</v>
       </c>
       <c r="F196" s="2">
-        <v>1653</v>
+        <v>1578</v>
       </c>
       <c r="G196" s="2" t="s">
         <v>15</v>
@@ -9847,7 +9847,7 @@
         <v>14</v>
       </c>
       <c r="F197" s="2">
-        <v>4264</v>
+        <v>1793</v>
       </c>
       <c r="G197" s="2" t="s">
         <v>15</v>
@@ -9879,7 +9879,7 @@
         <v>14</v>
       </c>
       <c r="F198" s="2">
-        <v>3985</v>
+        <v>1832</v>
       </c>
       <c r="G198" s="2" t="s">
         <v>15</v>
@@ -9911,7 +9911,7 @@
         <v>14</v>
       </c>
       <c r="F199" s="2">
-        <v>1090</v>
+        <v>2802</v>
       </c>
       <c r="G199" s="2" t="s">
         <v>15</v>
@@ -9943,7 +9943,7 @@
         <v>14</v>
       </c>
       <c r="F200" s="2">
-        <v>2242</v>
+        <v>1380</v>
       </c>
       <c r="G200" s="2" t="s">
         <v>15</v>
@@ -9975,7 +9975,7 @@
         <v>14</v>
       </c>
       <c r="F201" s="2">
-        <v>4210</v>
+        <v>3607</v>
       </c>
       <c r="G201" s="2" t="s">
         <v>15</v>
@@ -10007,7 +10007,7 @@
         <v>14</v>
       </c>
       <c r="F202" s="2">
-        <v>3822</v>
+        <v>1775</v>
       </c>
       <c r="G202" s="2" t="s">
         <v>15</v>
@@ -10039,7 +10039,7 @@
         <v>14</v>
       </c>
       <c r="F203" s="2">
-        <v>1669</v>
+        <v>1248</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>15</v>
@@ -10071,7 +10071,7 @@
         <v>14</v>
       </c>
       <c r="F204" s="2">
-        <v>1162</v>
+        <v>4704</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>15</v>
@@ -10103,7 +10103,7 @@
         <v>14</v>
       </c>
       <c r="F205" s="2">
-        <v>3098</v>
+        <v>1939</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>15</v>
@@ -10135,7 +10135,7 @@
         <v>14</v>
       </c>
       <c r="F206" s="2">
-        <v>2630</v>
+        <v>3755</v>
       </c>
       <c r="G206" s="2" t="s">
         <v>15</v>
@@ -10167,7 +10167,7 @@
         <v>14</v>
       </c>
       <c r="F207" s="2">
-        <v>3207</v>
+        <v>4787</v>
       </c>
       <c r="G207" s="2" t="s">
         <v>15</v>
@@ -10199,7 +10199,7 @@
         <v>14</v>
       </c>
       <c r="F208" s="2">
-        <v>3159</v>
+        <v>1693</v>
       </c>
       <c r="G208" s="2" t="s">
         <v>15</v>
@@ -10231,7 +10231,7 @@
         <v>14</v>
       </c>
       <c r="F209" s="2">
-        <v>939</v>
+        <v>2755</v>
       </c>
       <c r="G209" s="2" t="s">
         <v>15</v>
@@ -10263,7 +10263,7 @@
         <v>14</v>
       </c>
       <c r="F210" s="2">
-        <v>2976</v>
+        <v>3825</v>
       </c>
       <c r="G210" s="2" t="s">
         <v>15</v>
@@ -10295,7 +10295,7 @@
         <v>14</v>
       </c>
       <c r="F211" s="2">
-        <v>2807</v>
+        <v>2642</v>
       </c>
       <c r="G211" s="2" t="s">
         <v>15</v>
@@ -10327,7 +10327,7 @@
         <v>14</v>
       </c>
       <c r="F212" s="2">
-        <v>2640</v>
+        <v>996</v>
       </c>
       <c r="G212" s="2" t="s">
         <v>15</v>
@@ -10359,7 +10359,7 @@
         <v>14</v>
       </c>
       <c r="F213" s="2">
-        <v>3235</v>
+        <v>4725</v>
       </c>
       <c r="G213" s="2" t="s">
         <v>15</v>
@@ -10391,7 +10391,7 @@
         <v>14</v>
       </c>
       <c r="F214" s="2">
-        <v>2419</v>
+        <v>987</v>
       </c>
       <c r="G214" s="2" t="s">
         <v>15</v>
@@ -10423,7 +10423,7 @@
         <v>14</v>
       </c>
       <c r="F215" s="2">
-        <v>3779</v>
+        <v>1654</v>
       </c>
       <c r="G215" s="2" t="s">
         <v>15</v>
@@ -10455,7 +10455,7 @@
         <v>14</v>
       </c>
       <c r="F216" s="2">
-        <v>2554</v>
+        <v>2327</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>15</v>
@@ -10487,7 +10487,7 @@
         <v>14</v>
       </c>
       <c r="F217" s="2">
-        <v>1699</v>
+        <v>1472</v>
       </c>
       <c r="G217" s="2" t="s">
         <v>15</v>
@@ -10519,7 +10519,7 @@
         <v>14</v>
       </c>
       <c r="F218" s="2">
-        <v>3314</v>
+        <v>3318</v>
       </c>
       <c r="G218" s="2" t="s">
         <v>15</v>
@@ -10551,7 +10551,7 @@
         <v>14</v>
       </c>
       <c r="F219" s="2">
-        <v>4040</v>
+        <v>4336</v>
       </c>
       <c r="G219" s="2" t="s">
         <v>15</v>
@@ -10583,7 +10583,7 @@
         <v>14</v>
       </c>
       <c r="F220" s="2">
-        <v>1189</v>
+        <v>4616</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>15</v>
@@ -10615,7 +10615,7 @@
         <v>14</v>
       </c>
       <c r="F221" s="2">
-        <v>1239</v>
+        <v>3223</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>15</v>
@@ -10647,7 +10647,7 @@
         <v>14</v>
       </c>
       <c r="F222" s="2">
-        <v>915</v>
+        <v>3040</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>15</v>
@@ -10679,7 +10679,7 @@
         <v>14</v>
       </c>
       <c r="F223" s="2">
-        <v>2219</v>
+        <v>864</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>15</v>
@@ -10711,7 +10711,7 @@
         <v>14</v>
       </c>
       <c r="F224" s="2">
-        <v>2439</v>
+        <v>1338</v>
       </c>
       <c r="G224" s="2" t="s">
         <v>15</v>
@@ -10743,7 +10743,7 @@
         <v>14</v>
       </c>
       <c r="F225" s="2">
-        <v>2752</v>
+        <v>2781</v>
       </c>
       <c r="G225" s="2" t="s">
         <v>15</v>
@@ -10775,7 +10775,7 @@
         <v>14</v>
       </c>
       <c r="F226" s="2">
-        <v>2649</v>
+        <v>3320</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>15</v>
@@ -10807,7 +10807,7 @@
         <v>14</v>
       </c>
       <c r="F227" s="2">
-        <v>3246</v>
+        <v>2164</v>
       </c>
       <c r="G227" s="2" t="s">
         <v>15</v>
@@ -10839,7 +10839,7 @@
         <v>14</v>
       </c>
       <c r="F228" s="2">
-        <v>2929</v>
+        <v>3847</v>
       </c>
       <c r="G228" s="2" t="s">
         <v>15</v>
@@ -10871,7 +10871,7 @@
         <v>14</v>
       </c>
       <c r="F229" s="2">
-        <v>3556</v>
+        <v>4735</v>
       </c>
       <c r="G229" s="2" t="s">
         <v>15</v>
@@ -10903,7 +10903,7 @@
         <v>14</v>
       </c>
       <c r="F230" s="2">
-        <v>2306</v>
+        <v>3537</v>
       </c>
       <c r="G230" s="2" t="s">
         <v>15</v>
@@ -10935,7 +10935,7 @@
         <v>14</v>
       </c>
       <c r="F231" s="2">
-        <v>2321</v>
+        <v>2780</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>15</v>
@@ -10967,7 +10967,7 @@
         <v>14</v>
       </c>
       <c r="F232" s="2">
-        <v>3817</v>
+        <v>1273</v>
       </c>
       <c r="G232" s="2" t="s">
         <v>15</v>
@@ -10999,7 +10999,7 @@
         <v>14</v>
       </c>
       <c r="F233" s="2">
-        <v>1746</v>
+        <v>1000</v>
       </c>
       <c r="G233" s="2" t="s">
         <v>15</v>
@@ -11031,7 +11031,7 @@
         <v>14</v>
       </c>
       <c r="F234" s="2">
-        <v>2965</v>
+        <v>980</v>
       </c>
       <c r="G234" s="2" t="s">
         <v>15</v>
@@ -11063,7 +11063,7 @@
         <v>14</v>
       </c>
       <c r="F235" s="2">
-        <v>3904</v>
+        <v>1534</v>
       </c>
       <c r="G235" s="2" t="s">
         <v>15</v>
@@ -11095,7 +11095,7 @@
         <v>14</v>
       </c>
       <c r="F236" s="2">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="G236" s="2" t="s">
         <v>15</v>
@@ -11127,7 +11127,7 @@
         <v>14</v>
       </c>
       <c r="F237" s="2">
-        <v>1127</v>
+        <v>4563</v>
       </c>
       <c r="G237" s="2" t="s">
         <v>15</v>
@@ -11159,7 +11159,7 @@
         <v>14</v>
       </c>
       <c r="F238" s="2">
-        <v>1033</v>
+        <v>3779</v>
       </c>
       <c r="G238" s="2" t="s">
         <v>15</v>
@@ -11191,7 +11191,7 @@
         <v>14</v>
       </c>
       <c r="F239" s="2">
-        <v>2450</v>
+        <v>1171</v>
       </c>
       <c r="G239" s="2" t="s">
         <v>15</v>
@@ -11223,7 +11223,7 @@
         <v>14</v>
       </c>
       <c r="F240" s="2">
-        <v>2853</v>
+        <v>4086</v>
       </c>
       <c r="G240" s="2" t="s">
         <v>15</v>
@@ -11255,7 +11255,7 @@
         <v>14</v>
       </c>
       <c r="F241" s="2">
-        <v>4435</v>
+        <v>4367</v>
       </c>
       <c r="G241" s="2" t="s">
         <v>15</v>
@@ -11287,7 +11287,7 @@
         <v>14</v>
       </c>
       <c r="F242" s="2">
-        <v>3411</v>
+        <v>1304</v>
       </c>
       <c r="G242" s="2" t="s">
         <v>15</v>
@@ -11319,7 +11319,7 @@
         <v>14</v>
       </c>
       <c r="F243" s="2">
-        <v>1579</v>
+        <v>2489</v>
       </c>
       <c r="G243" s="2" t="s">
         <v>15</v>
@@ -11351,7 +11351,7 @@
         <v>14</v>
       </c>
       <c r="F244" s="2">
-        <v>1553</v>
+        <v>2512</v>
       </c>
       <c r="G244" s="2" t="s">
         <v>15</v>
@@ -11383,7 +11383,7 @@
         <v>14</v>
       </c>
       <c r="F245" s="2">
-        <v>3598</v>
+        <v>2455</v>
       </c>
       <c r="G245" s="2" t="s">
         <v>15</v>
@@ -11415,7 +11415,7 @@
         <v>14</v>
       </c>
       <c r="F246" s="2">
-        <v>4452</v>
+        <v>4405</v>
       </c>
       <c r="G246" s="2" t="s">
         <v>15</v>
@@ -11447,7 +11447,7 @@
         <v>14</v>
       </c>
       <c r="F247" s="2">
-        <v>3048</v>
+        <v>3937</v>
       </c>
       <c r="G247" s="2" t="s">
         <v>15</v>
@@ -11479,7 +11479,7 @@
         <v>14</v>
       </c>
       <c r="F248" s="2">
-        <v>4471</v>
+        <v>1222</v>
       </c>
       <c r="G248" s="2" t="s">
         <v>15</v>
@@ -11511,7 +11511,7 @@
         <v>14</v>
       </c>
       <c r="F249" s="2">
-        <v>1082</v>
+        <v>1771</v>
       </c>
       <c r="G249" s="2" t="s">
         <v>15</v>
@@ -11543,7 +11543,7 @@
         <v>14</v>
       </c>
       <c r="F250" s="2">
-        <v>4231</v>
+        <v>3512</v>
       </c>
       <c r="G250" s="2" t="s">
         <v>15</v>
@@ -11575,7 +11575,7 @@
         <v>14</v>
       </c>
       <c r="F251" s="2">
-        <v>2873</v>
+        <v>3379</v>
       </c>
       <c r="G251" s="2" t="s">
         <v>15</v>
@@ -11607,7 +11607,7 @@
         <v>14</v>
       </c>
       <c r="F252" s="2">
-        <v>4513</v>
+        <v>2621</v>
       </c>
       <c r="G252" s="2" t="s">
         <v>15</v>
@@ -11639,7 +11639,7 @@
         <v>14</v>
       </c>
       <c r="F253" s="2">
-        <v>3104</v>
+        <v>2146</v>
       </c>
       <c r="G253" s="2" t="s">
         <v>15</v>
@@ -11671,7 +11671,7 @@
         <v>14</v>
       </c>
       <c r="F254" s="2">
-        <v>4154</v>
+        <v>1819</v>
       </c>
       <c r="G254" s="2" t="s">
         <v>15</v>
@@ -11703,7 +11703,7 @@
         <v>14</v>
       </c>
       <c r="F255" s="2">
-        <v>1740</v>
+        <v>4650</v>
       </c>
       <c r="G255" s="2" t="s">
         <v>15</v>
@@ -11735,7 +11735,7 @@
         <v>14</v>
       </c>
       <c r="F256" s="2">
-        <v>4675</v>
+        <v>1434</v>
       </c>
       <c r="G256" s="2" t="s">
         <v>15</v>
@@ -11767,7 +11767,7 @@
         <v>14</v>
       </c>
       <c r="F257" s="2">
-        <v>1641</v>
+        <v>2467</v>
       </c>
       <c r="G257" s="2" t="s">
         <v>15</v>
@@ -11799,7 +11799,7 @@
         <v>14</v>
       </c>
       <c r="F258" s="2">
-        <v>844</v>
+        <v>1901</v>
       </c>
       <c r="G258" s="2" t="s">
         <v>15</v>
@@ -11831,7 +11831,7 @@
         <v>14</v>
       </c>
       <c r="F259" s="2">
-        <v>2016</v>
+        <v>1597</v>
       </c>
       <c r="G259" s="2" t="s">
         <v>15</v>
@@ -11863,7 +11863,7 @@
         <v>14</v>
       </c>
       <c r="F260" s="2">
-        <v>2100</v>
+        <v>2487</v>
       </c>
       <c r="G260" s="2" t="s">
         <v>15</v>
@@ -11895,7 +11895,7 @@
         <v>14</v>
       </c>
       <c r="F261" s="2">
-        <v>2970</v>
+        <v>3134</v>
       </c>
       <c r="G261" s="2" t="s">
         <v>15</v>
@@ -11927,7 +11927,7 @@
         <v>14</v>
       </c>
       <c r="F262" s="2">
-        <v>1052</v>
+        <v>2421</v>
       </c>
       <c r="G262" s="2" t="s">
         <v>15</v>
@@ -11959,7 +11959,7 @@
         <v>14</v>
       </c>
       <c r="F263" s="2">
-        <v>1388</v>
+        <v>2337</v>
       </c>
       <c r="G263" s="2" t="s">
         <v>15</v>
@@ -11991,7 +11991,7 @@
         <v>14</v>
       </c>
       <c r="F264" s="2">
-        <v>2829</v>
+        <v>1267</v>
       </c>
       <c r="G264" s="2" t="s">
         <v>15</v>
@@ -12023,7 +12023,7 @@
         <v>14</v>
       </c>
       <c r="F265" s="2">
-        <v>2397</v>
+        <v>1490</v>
       </c>
       <c r="G265" s="2" t="s">
         <v>15</v>
@@ -12055,7 +12055,7 @@
         <v>14</v>
       </c>
       <c r="F266" s="2">
-        <v>2635</v>
+        <v>3669</v>
       </c>
       <c r="G266" s="2" t="s">
         <v>15</v>
@@ -12087,7 +12087,7 @@
         <v>14</v>
       </c>
       <c r="F267" s="2">
-        <v>2858</v>
+        <v>2660</v>
       </c>
       <c r="G267" s="2" t="s">
         <v>15</v>
@@ -12119,7 +12119,7 @@
         <v>14</v>
       </c>
       <c r="F268" s="2">
-        <v>2546</v>
+        <v>3770</v>
       </c>
       <c r="G268" s="2" t="s">
         <v>15</v>
@@ -12151,7 +12151,7 @@
         <v>14</v>
       </c>
       <c r="F269" s="2">
-        <v>879</v>
+        <v>2780</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>15</v>
@@ -12183,7 +12183,7 @@
         <v>14</v>
       </c>
       <c r="F270" s="2">
-        <v>4098</v>
+        <v>4576</v>
       </c>
       <c r="G270" s="2" t="s">
         <v>15</v>
@@ -12215,7 +12215,7 @@
         <v>14</v>
       </c>
       <c r="F271" s="2">
-        <v>1484</v>
+        <v>1518</v>
       </c>
       <c r="G271" s="2" t="s">
         <v>15</v>
@@ -12247,7 +12247,7 @@
         <v>14</v>
       </c>
       <c r="F272" s="2">
-        <v>4664</v>
+        <v>3792</v>
       </c>
       <c r="G272" s="2" t="s">
         <v>15</v>
@@ -12279,7 +12279,7 @@
         <v>14</v>
       </c>
       <c r="F273" s="2">
-        <v>4351</v>
+        <v>2752</v>
       </c>
       <c r="G273" s="2" t="s">
         <v>15</v>
@@ -12311,7 +12311,7 @@
         <v>14</v>
       </c>
       <c r="F274" s="2">
-        <v>4701</v>
+        <v>4082</v>
       </c>
       <c r="G274" s="2" t="s">
         <v>15</v>
@@ -12343,7 +12343,7 @@
         <v>14</v>
       </c>
       <c r="F275" s="2">
-        <v>1012</v>
+        <v>1449</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>15</v>
@@ -12375,7 +12375,7 @@
         <v>14</v>
       </c>
       <c r="F276" s="2">
-        <v>2186</v>
+        <v>4308</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>15</v>
@@ -12407,7 +12407,7 @@
         <v>14</v>
       </c>
       <c r="F277" s="2">
-        <v>1358</v>
+        <v>4712</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>15</v>
@@ -12439,7 +12439,7 @@
         <v>14</v>
       </c>
       <c r="F278" s="2">
-        <v>2193</v>
+        <v>2008</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>15</v>
@@ -12471,7 +12471,7 @@
         <v>14</v>
       </c>
       <c r="F279" s="2">
-        <v>813</v>
+        <v>3013</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>15</v>
@@ -12503,7 +12503,7 @@
         <v>14</v>
       </c>
       <c r="F280" s="2">
-        <v>2708</v>
+        <v>3187</v>
       </c>
       <c r="G280" s="2" t="s">
         <v>15</v>
@@ -12535,7 +12535,7 @@
         <v>14</v>
       </c>
       <c r="F281" s="2">
-        <v>3183</v>
+        <v>2340</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>15</v>
@@ -12567,7 +12567,7 @@
         <v>14</v>
       </c>
       <c r="F282" s="2">
-        <v>4455</v>
+        <v>860</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>15</v>
@@ -12599,7 +12599,7 @@
         <v>14</v>
       </c>
       <c r="F283" s="2">
-        <v>4699</v>
+        <v>1154</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>15</v>
@@ -12631,7 +12631,7 @@
         <v>14</v>
       </c>
       <c r="F284" s="2">
-        <v>1551</v>
+        <v>1256</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>15</v>
@@ -12663,7 +12663,7 @@
         <v>14</v>
       </c>
       <c r="F285" s="2">
-        <v>1473</v>
+        <v>3173</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>15</v>
@@ -12695,7 +12695,7 @@
         <v>14</v>
       </c>
       <c r="F286" s="2">
-        <v>1144</v>
+        <v>1962</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>15</v>
@@ -12727,7 +12727,7 @@
         <v>14</v>
       </c>
       <c r="F287" s="2">
-        <v>2278</v>
+        <v>986</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>15</v>
@@ -12759,7 +12759,7 @@
         <v>14</v>
       </c>
       <c r="F288" s="2">
-        <v>1408</v>
+        <v>2447</v>
       </c>
       <c r="G288" s="2" t="s">
         <v>15</v>
@@ -12791,7 +12791,7 @@
         <v>14</v>
       </c>
       <c r="F289" s="2">
-        <v>838</v>
+        <v>2781</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>15</v>
@@ -12823,7 +12823,7 @@
         <v>14</v>
       </c>
       <c r="F290" s="2">
-        <v>4658</v>
+        <v>3049</v>
       </c>
       <c r="G290" s="2" t="s">
         <v>15</v>
@@ -12855,7 +12855,7 @@
         <v>14</v>
       </c>
       <c r="F291" s="2">
-        <v>1542</v>
+        <v>4730</v>
       </c>
       <c r="G291" s="2" t="s">
         <v>15</v>
@@ -12887,7 +12887,7 @@
         <v>14</v>
       </c>
       <c r="F292" s="2">
-        <v>4091</v>
+        <v>834</v>
       </c>
       <c r="G292" s="2" t="s">
         <v>15</v>
@@ -12919,7 +12919,7 @@
         <v>14</v>
       </c>
       <c r="F293" s="2">
-        <v>1139</v>
+        <v>1405</v>
       </c>
       <c r="G293" s="2" t="s">
         <v>15</v>
@@ -12951,7 +12951,7 @@
         <v>14</v>
       </c>
       <c r="F294" s="2">
-        <v>2122</v>
+        <v>3634</v>
       </c>
       <c r="G294" s="2" t="s">
         <v>15</v>
@@ -12983,7 +12983,7 @@
         <v>14</v>
       </c>
       <c r="F295" s="2">
-        <v>2873</v>
+        <v>4254</v>
       </c>
       <c r="G295" s="2" t="s">
         <v>15</v>
@@ -13015,7 +13015,7 @@
         <v>14</v>
       </c>
       <c r="F296" s="2">
-        <v>2578</v>
+        <v>1094</v>
       </c>
       <c r="G296" s="2" t="s">
         <v>15</v>
@@ -13047,7 +13047,7 @@
         <v>14</v>
       </c>
       <c r="F297" s="2">
-        <v>3019</v>
+        <v>3193</v>
       </c>
       <c r="G297" s="2" t="s">
         <v>15</v>
@@ -13079,7 +13079,7 @@
         <v>14</v>
       </c>
       <c r="F298" s="2">
-        <v>4188</v>
+        <v>4132</v>
       </c>
       <c r="G298" s="2" t="s">
         <v>15</v>
@@ -13111,7 +13111,7 @@
         <v>14</v>
       </c>
       <c r="F299" s="2">
-        <v>2103</v>
+        <v>1380</v>
       </c>
       <c r="G299" s="2" t="s">
         <v>15</v>
@@ -13143,7 +13143,7 @@
         <v>14</v>
       </c>
       <c r="F300" s="2">
-        <v>1222</v>
+        <v>873</v>
       </c>
       <c r="G300" s="2" t="s">
         <v>15</v>
@@ -13175,7 +13175,7 @@
         <v>14</v>
       </c>
       <c r="F301" s="2">
-        <v>2784</v>
+        <v>1152</v>
       </c>
       <c r="G301" s="2" t="s">
         <v>15</v>
@@ -13207,7 +13207,7 @@
         <v>14</v>
       </c>
       <c r="F302" s="2">
-        <v>2459</v>
+        <v>4240</v>
       </c>
       <c r="G302" s="2" t="s">
         <v>15</v>
@@ -13239,7 +13239,7 @@
         <v>14</v>
       </c>
       <c r="F303" s="2">
-        <v>4521</v>
+        <v>3786</v>
       </c>
       <c r="G303" s="2" t="s">
         <v>15</v>
@@ -13271,7 +13271,7 @@
         <v>14</v>
       </c>
       <c r="F304" s="2">
-        <v>1137</v>
+        <v>1565</v>
       </c>
       <c r="G304" s="2" t="s">
         <v>15</v>
@@ -13303,7 +13303,7 @@
         <v>14</v>
       </c>
       <c r="F305" s="2">
-        <v>2539</v>
+        <v>3948</v>
       </c>
       <c r="G305" s="2" t="s">
         <v>15</v>
@@ -13335,7 +13335,7 @@
         <v>14</v>
       </c>
       <c r="F306" s="2">
-        <v>3823</v>
+        <v>1533</v>
       </c>
       <c r="G306" s="2" t="s">
         <v>15</v>
@@ -13367,7 +13367,7 @@
         <v>14</v>
       </c>
       <c r="F307" s="2">
-        <v>1490</v>
+        <v>2890</v>
       </c>
       <c r="G307" s="2" t="s">
         <v>15</v>
@@ -13399,7 +13399,7 @@
         <v>14</v>
       </c>
       <c r="F308" s="2">
-        <v>3534</v>
+        <v>2989</v>
       </c>
       <c r="G308" s="2" t="s">
         <v>15</v>
@@ -13431,7 +13431,7 @@
         <v>14</v>
       </c>
       <c r="F309" s="2">
-        <v>4410</v>
+        <v>1814</v>
       </c>
       <c r="G309" s="2" t="s">
         <v>15</v>
@@ -13463,7 +13463,7 @@
         <v>14</v>
       </c>
       <c r="F310" s="2">
-        <v>2007</v>
+        <v>3068</v>
       </c>
       <c r="G310" s="2" t="s">
         <v>15</v>
@@ -13495,7 +13495,7 @@
         <v>14</v>
       </c>
       <c r="F311" s="2">
-        <v>4432</v>
+        <v>3033</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>15</v>
@@ -13527,7 +13527,7 @@
         <v>14</v>
       </c>
       <c r="F312" s="2">
-        <v>3385</v>
+        <v>3715</v>
       </c>
       <c r="G312" s="2" t="s">
         <v>15</v>
@@ -13559,7 +13559,7 @@
         <v>14</v>
       </c>
       <c r="F313" s="2">
-        <v>1321</v>
+        <v>3016</v>
       </c>
       <c r="G313" s="2" t="s">
         <v>15</v>
@@ -13591,7 +13591,7 @@
         <v>14</v>
       </c>
       <c r="F314" s="2">
-        <v>1009</v>
+        <v>4382</v>
       </c>
       <c r="G314" s="2" t="s">
         <v>15</v>
@@ -13623,7 +13623,7 @@
         <v>14</v>
       </c>
       <c r="F315" s="2">
-        <v>2221</v>
+        <v>3241</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>15</v>
@@ -13655,7 +13655,7 @@
         <v>14</v>
       </c>
       <c r="F316" s="2">
-        <v>2541</v>
+        <v>3841</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>15</v>
@@ -13687,7 +13687,7 @@
         <v>14</v>
       </c>
       <c r="F317" s="2">
-        <v>4349</v>
+        <v>4285</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>15</v>
@@ -13719,7 +13719,7 @@
         <v>14</v>
       </c>
       <c r="F318" s="2">
-        <v>1201</v>
+        <v>2176</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>15</v>
@@ -13751,7 +13751,7 @@
         <v>14</v>
       </c>
       <c r="F319" s="2">
-        <v>4182</v>
+        <v>4589</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>15</v>
@@ -13783,7 +13783,7 @@
         <v>14</v>
       </c>
       <c r="F320" s="2">
-        <v>1308</v>
+        <v>4576</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>15</v>
@@ -13815,7 +13815,7 @@
         <v>14</v>
       </c>
       <c r="F321" s="2">
-        <v>3896</v>
+        <v>4680</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>15</v>
@@ -13847,7 +13847,7 @@
         <v>14</v>
       </c>
       <c r="F322" s="2">
-        <v>1686</v>
+        <v>4080</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>15</v>
@@ -13879,7 +13879,7 @@
         <v>14</v>
       </c>
       <c r="F323" s="2">
-        <v>1321</v>
+        <v>4777</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>15</v>
@@ -13911,7 +13911,7 @@
         <v>14</v>
       </c>
       <c r="F324" s="2">
-        <v>3878</v>
+        <v>1336</v>
       </c>
       <c r="G324" s="2" t="s">
         <v>15</v>
@@ -13943,7 +13943,7 @@
         <v>14</v>
       </c>
       <c r="F325" s="2">
-        <v>3852</v>
+        <v>2545</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>15</v>
@@ -13975,7 +13975,7 @@
         <v>14</v>
       </c>
       <c r="F326" s="2">
-        <v>4204</v>
+        <v>4636</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>15</v>
@@ -14007,7 +14007,7 @@
         <v>14</v>
       </c>
       <c r="F327" s="2">
-        <v>3133</v>
+        <v>3769</v>
       </c>
       <c r="G327" s="2" t="s">
         <v>15</v>
@@ -14039,7 +14039,7 @@
         <v>14</v>
       </c>
       <c r="F328" s="2">
-        <v>2838</v>
+        <v>3441</v>
       </c>
       <c r="G328" s="2" t="s">
         <v>15</v>
@@ -14071,7 +14071,7 @@
         <v>14</v>
       </c>
       <c r="F329" s="2">
-        <v>2300</v>
+        <v>2624</v>
       </c>
       <c r="G329" s="2" t="s">
         <v>15</v>
@@ -14103,7 +14103,7 @@
         <v>14</v>
       </c>
       <c r="F330" s="2">
-        <v>4409</v>
+        <v>3485</v>
       </c>
       <c r="G330" s="2" t="s">
         <v>15</v>
@@ -14135,7 +14135,7 @@
         <v>14</v>
       </c>
       <c r="F331" s="2">
-        <v>4296</v>
+        <v>3422</v>
       </c>
       <c r="G331" s="2" t="s">
         <v>15</v>
@@ -14167,7 +14167,7 @@
         <v>14</v>
       </c>
       <c r="F332" s="2">
-        <v>4564</v>
+        <v>2592</v>
       </c>
       <c r="G332" s="2" t="s">
         <v>15</v>
@@ -14199,7 +14199,7 @@
         <v>14</v>
       </c>
       <c r="F333" s="2">
-        <v>4516</v>
+        <v>4724</v>
       </c>
       <c r="G333" s="2" t="s">
         <v>15</v>
@@ -14231,7 +14231,7 @@
         <v>14</v>
       </c>
       <c r="F334" s="2">
-        <v>1491</v>
+        <v>4528</v>
       </c>
       <c r="G334" s="2" t="s">
         <v>15</v>
@@ -14263,7 +14263,7 @@
         <v>14</v>
       </c>
       <c r="F335" s="2">
-        <v>1627</v>
+        <v>4125</v>
       </c>
       <c r="G335" s="2" t="s">
         <v>15</v>
@@ -14295,7 +14295,7 @@
         <v>14</v>
       </c>
       <c r="F336" s="2">
-        <v>1239</v>
+        <v>4022</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>15</v>
@@ -14327,7 +14327,7 @@
         <v>14</v>
       </c>
       <c r="F337" s="2">
-        <v>3608</v>
+        <v>2858</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>15</v>
@@ -14359,7 +14359,7 @@
         <v>14</v>
       </c>
       <c r="F338" s="2">
-        <v>2163</v>
+        <v>1240</v>
       </c>
       <c r="G338" s="2" t="s">
         <v>15</v>
@@ -14391,7 +14391,7 @@
         <v>14</v>
       </c>
       <c r="F339" s="2">
-        <v>1058</v>
+        <v>3100</v>
       </c>
       <c r="G339" s="2" t="s">
         <v>15</v>
@@ -14423,7 +14423,7 @@
         <v>14</v>
       </c>
       <c r="F340" s="2">
-        <v>1513</v>
+        <v>2081</v>
       </c>
       <c r="G340" s="2" t="s">
         <v>15</v>
@@ -14455,7 +14455,7 @@
         <v>14</v>
       </c>
       <c r="F341" s="2">
-        <v>3245</v>
+        <v>4569</v>
       </c>
       <c r="G341" s="2" t="s">
         <v>15</v>
@@ -14487,7 +14487,7 @@
         <v>14</v>
       </c>
       <c r="F342" s="2">
-        <v>4460</v>
+        <v>4709</v>
       </c>
       <c r="G342" s="2" t="s">
         <v>15</v>
@@ -14519,7 +14519,7 @@
         <v>14</v>
       </c>
       <c r="F343" s="2">
-        <v>3524</v>
+        <v>3788</v>
       </c>
       <c r="G343" s="2" t="s">
         <v>15</v>
@@ -14551,7 +14551,7 @@
         <v>14</v>
       </c>
       <c r="F344" s="2">
-        <v>4428</v>
+        <v>2648</v>
       </c>
       <c r="G344" s="2" t="s">
         <v>15</v>
@@ -14583,7 +14583,7 @@
         <v>14</v>
       </c>
       <c r="F345" s="2">
-        <v>3208</v>
+        <v>3902</v>
       </c>
       <c r="G345" s="2" t="s">
         <v>15</v>
@@ -14615,7 +14615,7 @@
         <v>14</v>
       </c>
       <c r="F346" s="2">
-        <v>4486</v>
+        <v>2406</v>
       </c>
       <c r="G346" s="2" t="s">
         <v>15</v>
@@ -14647,7 +14647,7 @@
         <v>14</v>
       </c>
       <c r="F347" s="2">
-        <v>2936</v>
+        <v>1244</v>
       </c>
       <c r="G347" s="2" t="s">
         <v>15</v>
@@ -14679,7 +14679,7 @@
         <v>14</v>
       </c>
       <c r="F348" s="2">
-        <v>1114</v>
+        <v>2079</v>
       </c>
       <c r="G348" s="2" t="s">
         <v>15</v>
@@ -14711,7 +14711,7 @@
         <v>14</v>
       </c>
       <c r="F349" s="2">
-        <v>2026</v>
+        <v>886</v>
       </c>
       <c r="G349" s="2" t="s">
         <v>15</v>
@@ -14743,7 +14743,7 @@
         <v>14</v>
       </c>
       <c r="F350" s="2">
-        <v>1927</v>
+        <v>4373</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>15</v>
@@ -14775,7 +14775,7 @@
         <v>14</v>
       </c>
       <c r="F351" s="2">
-        <v>2904</v>
+        <v>847</v>
       </c>
       <c r="G351" s="2" t="s">
         <v>15</v>
@@ -14807,7 +14807,7 @@
         <v>14</v>
       </c>
       <c r="F352" s="2">
-        <v>1187</v>
+        <v>3842</v>
       </c>
       <c r="G352" s="2" t="s">
         <v>15</v>
@@ -14839,7 +14839,7 @@
         <v>14</v>
       </c>
       <c r="F353" s="2">
-        <v>4274</v>
+        <v>1466</v>
       </c>
       <c r="G353" s="2" t="s">
         <v>15</v>
@@ -14871,7 +14871,7 @@
         <v>14</v>
       </c>
       <c r="F354" s="2">
-        <v>2966</v>
+        <v>3293</v>
       </c>
       <c r="G354" s="2" t="s">
         <v>15</v>
@@ -14903,7 +14903,7 @@
         <v>14</v>
       </c>
       <c r="F355" s="2">
-        <v>2855</v>
+        <v>4531</v>
       </c>
       <c r="G355" s="2" t="s">
         <v>15</v>
@@ -14935,7 +14935,7 @@
         <v>14</v>
       </c>
       <c r="F356" s="2">
-        <v>3399</v>
+        <v>1494</v>
       </c>
       <c r="G356" s="2" t="s">
         <v>15</v>
@@ -14967,7 +14967,7 @@
         <v>14</v>
       </c>
       <c r="F357" s="2">
-        <v>4661</v>
+        <v>3265</v>
       </c>
       <c r="G357" s="2" t="s">
         <v>15</v>
@@ -14999,7 +14999,7 @@
         <v>14</v>
       </c>
       <c r="F358" s="2">
-        <v>1148</v>
+        <v>4437</v>
       </c>
       <c r="G358" s="2" t="s">
         <v>15</v>
@@ -15031,7 +15031,7 @@
         <v>14</v>
       </c>
       <c r="F359" s="2">
-        <v>3634</v>
+        <v>2560</v>
       </c>
       <c r="G359" s="2" t="s">
         <v>15</v>
@@ -15063,7 +15063,7 @@
         <v>14</v>
       </c>
       <c r="F360" s="2">
-        <v>1924</v>
+        <v>3463</v>
       </c>
       <c r="G360" s="2" t="s">
         <v>15</v>
@@ -15095,7 +15095,7 @@
         <v>14</v>
       </c>
       <c r="F361" s="2">
-        <v>1958</v>
+        <v>2541</v>
       </c>
       <c r="G361" s="2" t="s">
         <v>15</v>
@@ -15127,7 +15127,7 @@
         <v>14</v>
       </c>
       <c r="F362" s="2">
-        <v>2196</v>
+        <v>4594</v>
       </c>
       <c r="G362" s="2" t="s">
         <v>15</v>
@@ -15159,7 +15159,7 @@
         <v>14</v>
       </c>
       <c r="F363" s="2">
-        <v>3016</v>
+        <v>2644</v>
       </c>
       <c r="G363" s="2" t="s">
         <v>15</v>
@@ -15191,7 +15191,7 @@
         <v>14</v>
       </c>
       <c r="F364" s="2">
-        <v>2924</v>
+        <v>3293</v>
       </c>
       <c r="G364" s="2" t="s">
         <v>15</v>
@@ -15223,7 +15223,7 @@
         <v>14</v>
       </c>
       <c r="F365" s="2">
-        <v>1793</v>
+        <v>2247</v>
       </c>
       <c r="G365" s="2" t="s">
         <v>15</v>
@@ -15255,7 +15255,7 @@
         <v>14</v>
       </c>
       <c r="F366" s="2">
-        <v>2656</v>
+        <v>4418</v>
       </c>
       <c r="G366" s="2" t="s">
         <v>15</v>
@@ -15287,7 +15287,7 @@
         <v>14</v>
       </c>
       <c r="F367" s="2">
-        <v>4490</v>
+        <v>4193</v>
       </c>
       <c r="G367" s="2" t="s">
         <v>15</v>
@@ -15319,7 +15319,7 @@
         <v>14</v>
       </c>
       <c r="F368" s="2">
-        <v>3009</v>
+        <v>1182</v>
       </c>
       <c r="G368" s="2" t="s">
         <v>15</v>
@@ -15351,7 +15351,7 @@
         <v>14</v>
       </c>
       <c r="F369" s="2">
-        <v>3575</v>
+        <v>1360</v>
       </c>
       <c r="G369" s="2" t="s">
         <v>15</v>
@@ -15383,7 +15383,7 @@
         <v>14</v>
       </c>
       <c r="F370" s="2">
-        <v>1063</v>
+        <v>3616</v>
       </c>
       <c r="G370" s="2" t="s">
         <v>15</v>
@@ -15415,7 +15415,7 @@
         <v>14</v>
       </c>
       <c r="F371" s="2">
-        <v>1434</v>
+        <v>3303</v>
       </c>
       <c r="G371" s="2" t="s">
         <v>15</v>
@@ -15447,7 +15447,7 @@
         <v>14</v>
       </c>
       <c r="F372" s="2">
-        <v>1437</v>
+        <v>1425</v>
       </c>
       <c r="G372" s="2" t="s">
         <v>15</v>
@@ -15479,7 +15479,7 @@
         <v>14</v>
       </c>
       <c r="F373" s="2">
-        <v>1718</v>
+        <v>3463</v>
       </c>
       <c r="G373" s="2" t="s">
         <v>15</v>
@@ -15511,7 +15511,7 @@
         <v>14</v>
       </c>
       <c r="F374" s="2">
-        <v>2162</v>
+        <v>2794</v>
       </c>
       <c r="G374" s="2" t="s">
         <v>15</v>
@@ -15543,7 +15543,7 @@
         <v>14</v>
       </c>
       <c r="F375" s="2">
-        <v>3840</v>
+        <v>3892</v>
       </c>
       <c r="G375" s="2" t="s">
         <v>15</v>
@@ -15575,7 +15575,7 @@
         <v>14</v>
       </c>
       <c r="F376" s="2">
-        <v>1144</v>
+        <v>3303</v>
       </c>
       <c r="G376" s="2" t="s">
         <v>15</v>
@@ -15607,7 +15607,7 @@
         <v>14</v>
       </c>
       <c r="F377" s="2">
-        <v>1930</v>
+        <v>826</v>
       </c>
       <c r="G377" s="2" t="s">
         <v>15</v>
@@ -15639,7 +15639,7 @@
         <v>14</v>
       </c>
       <c r="F378" s="2">
-        <v>1059</v>
+        <v>1413</v>
       </c>
       <c r="G378" s="2" t="s">
         <v>15</v>
@@ -15671,7 +15671,7 @@
         <v>14</v>
       </c>
       <c r="F379" s="2">
-        <v>2998</v>
+        <v>4269</v>
       </c>
       <c r="G379" s="2" t="s">
         <v>15</v>
@@ -15703,7 +15703,7 @@
         <v>14</v>
       </c>
       <c r="F380" s="2">
-        <v>1856</v>
+        <v>4532</v>
       </c>
       <c r="G380" s="2" t="s">
         <v>15</v>
@@ -15735,7 +15735,7 @@
         <v>14</v>
       </c>
       <c r="F381" s="2">
-        <v>2767</v>
+        <v>990</v>
       </c>
       <c r="G381" s="2" t="s">
         <v>15</v>
@@ -15767,7 +15767,7 @@
         <v>14</v>
       </c>
       <c r="F382" s="2">
-        <v>3679</v>
+        <v>3756</v>
       </c>
       <c r="G382" s="2" t="s">
         <v>15</v>
@@ -15799,7 +15799,7 @@
         <v>14</v>
       </c>
       <c r="F383" s="2">
-        <v>4658</v>
+        <v>4552</v>
       </c>
       <c r="G383" s="2" t="s">
         <v>15</v>
@@ -15831,7 +15831,7 @@
         <v>14</v>
       </c>
       <c r="F384" s="2">
-        <v>2202</v>
+        <v>2810</v>
       </c>
       <c r="G384" s="2" t="s">
         <v>15</v>
@@ -15863,7 +15863,7 @@
         <v>14</v>
       </c>
       <c r="F385" s="2">
-        <v>1498</v>
+        <v>4454</v>
       </c>
       <c r="G385" s="2" t="s">
         <v>15</v>
@@ -15895,7 +15895,7 @@
         <v>14</v>
       </c>
       <c r="F386" s="2">
-        <v>3319</v>
+        <v>2727</v>
       </c>
       <c r="G386" s="2" t="s">
         <v>15</v>
@@ -15927,7 +15927,7 @@
         <v>14</v>
       </c>
       <c r="F387" s="2">
-        <v>1147</v>
+        <v>2029</v>
       </c>
       <c r="G387" s="2" t="s">
         <v>15</v>
@@ -15959,7 +15959,7 @@
         <v>14</v>
       </c>
       <c r="F388" s="2">
-        <v>2471</v>
+        <v>2372</v>
       </c>
       <c r="G388" s="2" t="s">
         <v>15</v>
@@ -15991,7 +15991,7 @@
         <v>14</v>
       </c>
       <c r="F389" s="2">
-        <v>1911</v>
+        <v>3264</v>
       </c>
       <c r="G389" s="2" t="s">
         <v>15</v>
@@ -16023,7 +16023,7 @@
         <v>14</v>
       </c>
       <c r="F390" s="2">
-        <v>3087</v>
+        <v>4590</v>
       </c>
       <c r="G390" s="2" t="s">
         <v>15</v>
@@ -16055,7 +16055,7 @@
         <v>14</v>
       </c>
       <c r="F391" s="2">
-        <v>1092</v>
+        <v>3366</v>
       </c>
       <c r="G391" s="2" t="s">
         <v>15</v>
@@ -16087,7 +16087,7 @@
         <v>14</v>
       </c>
       <c r="F392" s="2">
-        <v>950</v>
+        <v>3193</v>
       </c>
       <c r="G392" s="2" t="s">
         <v>15</v>
@@ -16119,7 +16119,7 @@
         <v>14</v>
       </c>
       <c r="F393" s="2">
-        <v>3271</v>
+        <v>1374</v>
       </c>
       <c r="G393" s="2" t="s">
         <v>15</v>
@@ -16151,7 +16151,7 @@
         <v>14</v>
       </c>
       <c r="F394" s="2">
-        <v>3911</v>
+        <v>1423</v>
       </c>
       <c r="G394" s="2" t="s">
         <v>15</v>
@@ -16183,7 +16183,7 @@
         <v>14</v>
       </c>
       <c r="F395" s="2">
-        <v>4433</v>
+        <v>2934</v>
       </c>
       <c r="G395" s="2" t="s">
         <v>15</v>
@@ -16215,7 +16215,7 @@
         <v>14</v>
       </c>
       <c r="F396" s="2">
-        <v>3220</v>
+        <v>3168</v>
       </c>
       <c r="G396" s="2" t="s">
         <v>15</v>
@@ -16247,7 +16247,7 @@
         <v>14</v>
       </c>
       <c r="F397" s="2">
-        <v>2292</v>
+        <v>2985</v>
       </c>
       <c r="G397" s="2" t="s">
         <v>15</v>
@@ -16279,7 +16279,7 @@
         <v>14</v>
       </c>
       <c r="F398" s="2">
-        <v>3084</v>
+        <v>2987</v>
       </c>
       <c r="G398" s="2" t="s">
         <v>15</v>
@@ -16311,7 +16311,7 @@
         <v>14</v>
       </c>
       <c r="F399" s="2">
-        <v>2936</v>
+        <v>3049</v>
       </c>
       <c r="G399" s="2" t="s">
         <v>15</v>
@@ -16343,7 +16343,7 @@
         <v>14</v>
       </c>
       <c r="F400" s="2">
-        <v>3789</v>
+        <v>1107</v>
       </c>
       <c r="G400" s="2" t="s">
         <v>15</v>
@@ -16375,7 +16375,7 @@
         <v>14</v>
       </c>
       <c r="F401" s="2">
-        <v>1255</v>
+        <v>2478</v>
       </c>
       <c r="G401" s="2" t="s">
         <v>15</v>
@@ -16407,7 +16407,7 @@
         <v>14</v>
       </c>
       <c r="F402" s="2">
-        <v>1933</v>
+        <v>3648</v>
       </c>
       <c r="G402" s="2" t="s">
         <v>15</v>
@@ -16439,7 +16439,7 @@
         <v>14</v>
       </c>
       <c r="F403" s="2">
-        <v>895</v>
+        <v>3803</v>
       </c>
       <c r="G403" s="2" t="s">
         <v>15</v>
@@ -16471,7 +16471,7 @@
         <v>14</v>
       </c>
       <c r="F404" s="2">
-        <v>3343</v>
+        <v>1767</v>
       </c>
       <c r="G404" s="2" t="s">
         <v>15</v>
@@ -16503,7 +16503,7 @@
         <v>14</v>
       </c>
       <c r="F405" s="2">
-        <v>1892</v>
+        <v>3038</v>
       </c>
       <c r="G405" s="2" t="s">
         <v>15</v>
@@ -16535,7 +16535,7 @@
         <v>14</v>
       </c>
       <c r="F406" s="2">
-        <v>3448</v>
+        <v>1358</v>
       </c>
       <c r="G406" s="2" t="s">
         <v>15</v>
@@ -16567,7 +16567,7 @@
         <v>14</v>
       </c>
       <c r="F407" s="2">
-        <v>1853</v>
+        <v>3005</v>
       </c>
       <c r="G407" s="2" t="s">
         <v>15</v>
@@ -16599,7 +16599,7 @@
         <v>14</v>
       </c>
       <c r="F408" s="2">
-        <v>2765</v>
+        <v>4329</v>
       </c>
       <c r="G408" s="2" t="s">
         <v>15</v>
@@ -16631,7 +16631,7 @@
         <v>14</v>
       </c>
       <c r="F409" s="2">
-        <v>4647</v>
+        <v>1083</v>
       </c>
       <c r="G409" s="2" t="s">
         <v>15</v>
@@ -16663,7 +16663,7 @@
         <v>14</v>
       </c>
       <c r="F410" s="2">
-        <v>1286</v>
+        <v>3948</v>
       </c>
       <c r="G410" s="2" t="s">
         <v>15</v>
@@ -16695,7 +16695,7 @@
         <v>14</v>
       </c>
       <c r="F411" s="2">
-        <v>1899</v>
+        <v>1136</v>
       </c>
       <c r="G411" s="2" t="s">
         <v>15</v>
@@ -16727,7 +16727,7 @@
         <v>14</v>
       </c>
       <c r="F412" s="2">
-        <v>3181</v>
+        <v>2358</v>
       </c>
       <c r="G412" s="2" t="s">
         <v>15</v>
@@ -16759,7 +16759,7 @@
         <v>14</v>
       </c>
       <c r="F413" s="2">
-        <v>3631</v>
+        <v>2529</v>
       </c>
       <c r="G413" s="2" t="s">
         <v>15</v>
@@ -16791,7 +16791,7 @@
         <v>14</v>
       </c>
       <c r="F414" s="2">
-        <v>4629</v>
+        <v>3387</v>
       </c>
       <c r="G414" s="2" t="s">
         <v>15</v>
@@ -16823,7 +16823,7 @@
         <v>14</v>
       </c>
       <c r="F415" s="2">
-        <v>3162</v>
+        <v>4242</v>
       </c>
       <c r="G415" s="2" t="s">
         <v>15</v>
@@ -16855,7 +16855,7 @@
         <v>14</v>
       </c>
       <c r="F416" s="2">
-        <v>2171</v>
+        <v>1774</v>
       </c>
       <c r="G416" s="2" t="s">
         <v>15</v>
@@ -16887,7 +16887,7 @@
         <v>14</v>
       </c>
       <c r="F417" s="2">
-        <v>4406</v>
+        <v>3070</v>
       </c>
       <c r="G417" s="2" t="s">
         <v>15</v>
@@ -16919,7 +16919,7 @@
         <v>14</v>
       </c>
       <c r="F418" s="2">
-        <v>4253</v>
+        <v>2875</v>
       </c>
       <c r="G418" s="2" t="s">
         <v>15</v>
@@ -16951,7 +16951,7 @@
         <v>14</v>
       </c>
       <c r="F419" s="2">
-        <v>4511</v>
+        <v>2336</v>
       </c>
       <c r="G419" s="2" t="s">
         <v>15</v>
@@ -16983,7 +16983,7 @@
         <v>14</v>
       </c>
       <c r="F420" s="2">
-        <v>3997</v>
+        <v>2650</v>
       </c>
       <c r="G420" s="2" t="s">
         <v>15</v>
@@ -17015,7 +17015,7 @@
         <v>14</v>
       </c>
       <c r="F421" s="2">
-        <v>1708</v>
+        <v>1803</v>
       </c>
       <c r="G421" s="2" t="s">
         <v>15</v>
@@ -17047,7 +17047,7 @@
         <v>14</v>
       </c>
       <c r="F422" s="2">
-        <v>2377</v>
+        <v>4086</v>
       </c>
       <c r="G422" s="2" t="s">
         <v>15</v>
@@ -17079,7 +17079,7 @@
         <v>14</v>
       </c>
       <c r="F423" s="2">
-        <v>3893</v>
+        <v>1645</v>
       </c>
       <c r="G423" s="2" t="s">
         <v>15</v>
@@ -17111,7 +17111,7 @@
         <v>14</v>
       </c>
       <c r="F424" s="2">
-        <v>3044</v>
+        <v>4207</v>
       </c>
       <c r="G424" s="2" t="s">
         <v>15</v>
@@ -17143,7 +17143,7 @@
         <v>14</v>
       </c>
       <c r="F425" s="2">
-        <v>1873</v>
+        <v>2967</v>
       </c>
       <c r="G425" s="2" t="s">
         <v>15</v>
@@ -17175,7 +17175,7 @@
         <v>14</v>
       </c>
       <c r="F426" s="2">
-        <v>1511</v>
+        <v>1766</v>
       </c>
       <c r="G426" s="2" t="s">
         <v>15</v>
@@ -17207,7 +17207,7 @@
         <v>14</v>
       </c>
       <c r="F427" s="2">
-        <v>2552</v>
+        <v>2784</v>
       </c>
       <c r="G427" s="2" t="s">
         <v>15</v>
@@ -17239,7 +17239,7 @@
         <v>14</v>
       </c>
       <c r="F428" s="2">
-        <v>1321</v>
+        <v>3858</v>
       </c>
       <c r="G428" s="2" t="s">
         <v>15</v>
@@ -17271,7 +17271,7 @@
         <v>14</v>
       </c>
       <c r="F429" s="2">
-        <v>3128</v>
+        <v>1997</v>
       </c>
       <c r="G429" s="2" t="s">
         <v>15</v>
@@ -17303,7 +17303,7 @@
         <v>14</v>
       </c>
       <c r="F430" s="2">
-        <v>3728</v>
+        <v>1561</v>
       </c>
       <c r="G430" s="2" t="s">
         <v>15</v>
@@ -17335,7 +17335,7 @@
         <v>14</v>
       </c>
       <c r="F431" s="2">
-        <v>1028</v>
+        <v>3287</v>
       </c>
       <c r="G431" s="2" t="s">
         <v>15</v>
@@ -17367,7 +17367,7 @@
         <v>14</v>
       </c>
       <c r="F432" s="2">
-        <v>1598</v>
+        <v>1290</v>
       </c>
       <c r="G432" s="2" t="s">
         <v>15</v>
@@ -17399,7 +17399,7 @@
         <v>14</v>
       </c>
       <c r="F433" s="2">
-        <v>1123</v>
+        <v>3390</v>
       </c>
       <c r="G433" s="2" t="s">
         <v>15</v>
@@ -17431,7 +17431,7 @@
         <v>14</v>
       </c>
       <c r="F434" s="2">
-        <v>4123</v>
+        <v>1202</v>
       </c>
       <c r="G434" s="2" t="s">
         <v>15</v>
@@ -17463,7 +17463,7 @@
         <v>14</v>
       </c>
       <c r="F435" s="2">
-        <v>2103</v>
+        <v>3986</v>
       </c>
       <c r="G435" s="2" t="s">
         <v>15</v>
@@ -17495,7 +17495,7 @@
         <v>14</v>
       </c>
       <c r="F436" s="2">
-        <v>978</v>
+        <v>2351</v>
       </c>
       <c r="G436" s="2" t="s">
         <v>15</v>
@@ -17527,7 +17527,7 @@
         <v>14</v>
       </c>
       <c r="F437" s="2">
-        <v>1489</v>
+        <v>2069</v>
       </c>
       <c r="G437" s="2" t="s">
         <v>15</v>
@@ -17559,7 +17559,7 @@
         <v>14</v>
       </c>
       <c r="F438" s="2">
-        <v>3820</v>
+        <v>3918</v>
       </c>
       <c r="G438" s="2" t="s">
         <v>15</v>
@@ -17591,7 +17591,7 @@
         <v>14</v>
       </c>
       <c r="F439" s="2">
-        <v>2802</v>
+        <v>2530</v>
       </c>
       <c r="G439" s="2" t="s">
         <v>15</v>
@@ -17623,7 +17623,7 @@
         <v>14</v>
       </c>
       <c r="F440" s="2">
-        <v>2977</v>
+        <v>2340</v>
       </c>
       <c r="G440" s="2" t="s">
         <v>15</v>
@@ -17655,7 +17655,7 @@
         <v>14</v>
       </c>
       <c r="F441" s="2">
-        <v>3950</v>
+        <v>913</v>
       </c>
       <c r="G441" s="2" t="s">
         <v>15</v>
@@ -17687,7 +17687,7 @@
         <v>14</v>
       </c>
       <c r="F442" s="2">
-        <v>3959</v>
+        <v>3286</v>
       </c>
       <c r="G442" s="2" t="s">
         <v>15</v>
@@ -17719,7 +17719,7 @@
         <v>14</v>
       </c>
       <c r="F443" s="2">
-        <v>1936</v>
+        <v>2969</v>
       </c>
       <c r="G443" s="2" t="s">
         <v>15</v>
@@ -17751,7 +17751,7 @@
         <v>14</v>
       </c>
       <c r="F444" s="2">
-        <v>858</v>
+        <v>4121</v>
       </c>
       <c r="G444" s="2" t="s">
         <v>15</v>
@@ -17783,7 +17783,7 @@
         <v>14</v>
       </c>
       <c r="F445" s="2">
-        <v>2825</v>
+        <v>3873</v>
       </c>
       <c r="G445" s="2" t="s">
         <v>15</v>
@@ -17815,7 +17815,7 @@
         <v>14</v>
       </c>
       <c r="F446" s="2">
-        <v>1066</v>
+        <v>1132</v>
       </c>
       <c r="G446" s="2" t="s">
         <v>15</v>
@@ -17847,7 +17847,7 @@
         <v>14</v>
       </c>
       <c r="F447" s="2">
-        <v>4723</v>
+        <v>1543</v>
       </c>
       <c r="G447" s="2" t="s">
         <v>15</v>
@@ -17879,7 +17879,7 @@
         <v>14</v>
       </c>
       <c r="F448" s="2">
-        <v>1617</v>
+        <v>2775</v>
       </c>
       <c r="G448" s="2" t="s">
         <v>15</v>
@@ -17911,7 +17911,7 @@
         <v>14</v>
       </c>
       <c r="F449" s="2">
-        <v>1551</v>
+        <v>2094</v>
       </c>
       <c r="G449" s="2" t="s">
         <v>15</v>
@@ -17943,7 +17943,7 @@
         <v>14</v>
       </c>
       <c r="F450" s="2">
-        <v>4640</v>
+        <v>2209</v>
       </c>
       <c r="G450" s="2" t="s">
         <v>15</v>
@@ -17975,7 +17975,7 @@
         <v>14</v>
       </c>
       <c r="F451" s="2">
-        <v>1359</v>
+        <v>4222</v>
       </c>
       <c r="G451" s="2" t="s">
         <v>15</v>
@@ -18007,7 +18007,7 @@
         <v>14</v>
       </c>
       <c r="F452" s="2">
-        <v>1499</v>
+        <v>3675</v>
       </c>
       <c r="G452" s="2" t="s">
         <v>15</v>
@@ -18039,7 +18039,7 @@
         <v>14</v>
       </c>
       <c r="F453" s="2">
-        <v>4045</v>
+        <v>2022</v>
       </c>
       <c r="G453" s="2" t="s">
         <v>15</v>
@@ -18071,7 +18071,7 @@
         <v>14</v>
       </c>
       <c r="F454" s="2">
-        <v>3425</v>
+        <v>3482</v>
       </c>
       <c r="G454" s="2" t="s">
         <v>15</v>
@@ -18103,7 +18103,7 @@
         <v>14</v>
       </c>
       <c r="F455" s="2">
-        <v>1446</v>
+        <v>1862</v>
       </c>
       <c r="G455" s="2" t="s">
         <v>15</v>
@@ -18135,7 +18135,7 @@
         <v>14</v>
       </c>
       <c r="F456" s="2">
-        <v>1455</v>
+        <v>924</v>
       </c>
       <c r="G456" s="2" t="s">
         <v>15</v>
@@ -18167,7 +18167,7 @@
         <v>14</v>
       </c>
       <c r="F457" s="2">
-        <v>2489</v>
+        <v>1237</v>
       </c>
       <c r="G457" s="2" t="s">
         <v>15</v>
@@ -18199,7 +18199,7 @@
         <v>14</v>
       </c>
       <c r="F458" s="2">
-        <v>2144</v>
+        <v>2348</v>
       </c>
       <c r="G458" s="2" t="s">
         <v>15</v>
@@ -18231,7 +18231,7 @@
         <v>14</v>
       </c>
       <c r="F459" s="2">
-        <v>4021</v>
+        <v>4075</v>
       </c>
       <c r="G459" s="2" t="s">
         <v>15</v>
@@ -18263,7 +18263,7 @@
         <v>14</v>
       </c>
       <c r="F460" s="2">
-        <v>3260</v>
+        <v>1489</v>
       </c>
       <c r="G460" s="2" t="s">
         <v>15</v>
@@ -18295,7 +18295,7 @@
         <v>14</v>
       </c>
       <c r="F461" s="2">
-        <v>2199</v>
+        <v>3321</v>
       </c>
       <c r="G461" s="2" t="s">
         <v>15</v>
@@ -18327,7 +18327,7 @@
         <v>14</v>
       </c>
       <c r="F462" s="2">
-        <v>4139</v>
+        <v>4694</v>
       </c>
       <c r="G462" s="2" t="s">
         <v>15</v>
@@ -18359,7 +18359,7 @@
         <v>14</v>
       </c>
       <c r="F463" s="2">
-        <v>2648</v>
+        <v>2820</v>
       </c>
       <c r="G463" s="2" t="s">
         <v>15</v>
@@ -18391,7 +18391,7 @@
         <v>14</v>
       </c>
       <c r="F464" s="2">
-        <v>3646</v>
+        <v>1982</v>
       </c>
       <c r="G464" s="2" t="s">
         <v>15</v>
@@ -18423,7 +18423,7 @@
         <v>14</v>
       </c>
       <c r="F465" s="2">
-        <v>2292</v>
+        <v>1539</v>
       </c>
       <c r="G465" s="2" t="s">
         <v>15</v>
@@ -18455,7 +18455,7 @@
         <v>14</v>
       </c>
       <c r="F466" s="2">
-        <v>1156</v>
+        <v>2682</v>
       </c>
       <c r="G466" s="2" t="s">
         <v>15</v>
@@ -18487,7 +18487,7 @@
         <v>14</v>
       </c>
       <c r="F467" s="2">
-        <v>1251</v>
+        <v>3948</v>
       </c>
       <c r="G467" s="2" t="s">
         <v>15</v>
@@ -18519,7 +18519,7 @@
         <v>14</v>
       </c>
       <c r="F468" s="2">
-        <v>1540</v>
+        <v>2491</v>
       </c>
       <c r="G468" s="2" t="s">
         <v>15</v>
@@ -18551,7 +18551,7 @@
         <v>14</v>
       </c>
       <c r="F469" s="2">
-        <v>3431</v>
+        <v>1141</v>
       </c>
       <c r="G469" s="2" t="s">
         <v>15</v>
@@ -18583,7 +18583,7 @@
         <v>14</v>
       </c>
       <c r="F470" s="2">
-        <v>1916</v>
+        <v>1105</v>
       </c>
       <c r="G470" s="2" t="s">
         <v>15</v>
@@ -18615,7 +18615,7 @@
         <v>14</v>
       </c>
       <c r="F471" s="2">
-        <v>2510</v>
+        <v>1017</v>
       </c>
       <c r="G471" s="2" t="s">
         <v>15</v>
@@ -18702,7 +18702,7 @@
         <v>14</v>
       </c>
       <c r="F2" s="2">
-        <v>1892</v>
+        <v>1693</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>15</v>
@@ -18734,7 +18734,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="2">
-        <v>2657</v>
+        <v>2763</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>15</v>
@@ -18766,7 +18766,7 @@
         <v>14</v>
       </c>
       <c r="F4" s="2">
-        <v>3833</v>
+        <v>3488</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
@@ -18798,7 +18798,7 @@
         <v>14</v>
       </c>
       <c r="F5" s="2">
-        <v>1342</v>
+        <v>1400</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
@@ -18830,7 +18830,7 @@
         <v>14</v>
       </c>
       <c r="F6" s="2">
-        <v>4717</v>
+        <v>1372</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -18862,7 +18862,7 @@
         <v>14</v>
       </c>
       <c r="F7" s="2">
-        <v>2841</v>
+        <v>1244</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -18894,7 +18894,7 @@
         <v>14</v>
       </c>
       <c r="F8" s="2">
-        <v>3928</v>
+        <v>2751</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -18926,7 +18926,7 @@
         <v>14</v>
       </c>
       <c r="F9" s="2">
-        <v>1358</v>
+        <v>3523</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -18958,7 +18958,7 @@
         <v>14</v>
       </c>
       <c r="F10" s="2">
-        <v>2120</v>
+        <v>1805</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
@@ -18990,7 +18990,7 @@
         <v>14</v>
       </c>
       <c r="F11" s="2">
-        <v>1911</v>
+        <v>3811</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
@@ -19022,7 +19022,7 @@
         <v>14</v>
       </c>
       <c r="F12" s="2">
-        <v>4341</v>
+        <v>1829</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
@@ -19054,7 +19054,7 @@
         <v>14</v>
       </c>
       <c r="F13" s="2">
-        <v>1350</v>
+        <v>1123</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -19086,7 +19086,7 @@
         <v>14</v>
       </c>
       <c r="F14" s="2">
-        <v>1818</v>
+        <v>2733</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -19118,7 +19118,7 @@
         <v>14</v>
       </c>
       <c r="F15" s="2">
-        <v>3111</v>
+        <v>1648</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -19150,7 +19150,7 @@
         <v>14</v>
       </c>
       <c r="F16" s="2">
-        <v>3406</v>
+        <v>828</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
@@ -19182,7 +19182,7 @@
         <v>14</v>
       </c>
       <c r="F17" s="2">
-        <v>1441</v>
+        <v>2736</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
@@ -19214,7 +19214,7 @@
         <v>14</v>
       </c>
       <c r="F18" s="2">
-        <v>1774</v>
+        <v>2115</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
@@ -19246,7 +19246,7 @@
         <v>14</v>
       </c>
       <c r="F19" s="2">
-        <v>4142</v>
+        <v>1912</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
@@ -19278,7 +19278,7 @@
         <v>14</v>
       </c>
       <c r="F20" s="2">
-        <v>4517</v>
+        <v>1479</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
@@ -19310,7 +19310,7 @@
         <v>14</v>
       </c>
       <c r="F21" s="2">
-        <v>3005</v>
+        <v>2920</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -19342,7 +19342,7 @@
         <v>14</v>
       </c>
       <c r="F22" s="2">
-        <v>2613</v>
+        <v>1455</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -19374,7 +19374,7 @@
         <v>14</v>
       </c>
       <c r="F23" s="2">
-        <v>1642</v>
+        <v>2941</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -19406,7 +19406,7 @@
         <v>14</v>
       </c>
       <c r="F24" s="2">
-        <v>931</v>
+        <v>1315</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -19438,7 +19438,7 @@
         <v>14</v>
       </c>
       <c r="F25" s="2">
-        <v>3439</v>
+        <v>1133</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -19470,7 +19470,7 @@
         <v>14</v>
       </c>
       <c r="F26" s="2">
-        <v>3388</v>
+        <v>4561</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -19502,7 +19502,7 @@
         <v>14</v>
       </c>
       <c r="F27" s="2">
-        <v>3024</v>
+        <v>1944</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>15</v>
@@ -19534,7 +19534,7 @@
         <v>14</v>
       </c>
       <c r="F28" s="2">
-        <v>3016</v>
+        <v>2944</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>15</v>
@@ -19566,7 +19566,7 @@
         <v>14</v>
       </c>
       <c r="F29" s="2">
-        <v>3449</v>
+        <v>2296</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>15</v>
@@ -19598,7 +19598,7 @@
         <v>14</v>
       </c>
       <c r="F30" s="2">
-        <v>3286</v>
+        <v>1904</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>15</v>
@@ -19630,7 +19630,7 @@
         <v>14</v>
       </c>
       <c r="F31" s="2">
-        <v>3852</v>
+        <v>1933</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>15</v>
@@ -19662,7 +19662,7 @@
         <v>14</v>
       </c>
       <c r="F32" s="2">
-        <v>2881</v>
+        <v>3045</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>15</v>
@@ -19694,7 +19694,7 @@
         <v>14</v>
       </c>
       <c r="F33" s="2">
-        <v>4283</v>
+        <v>4298</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>15</v>
@@ -19726,7 +19726,7 @@
         <v>14</v>
       </c>
       <c r="F34" s="2">
-        <v>4255</v>
+        <v>3224</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>15</v>
@@ -19758,7 +19758,7 @@
         <v>14</v>
       </c>
       <c r="F35" s="2">
-        <v>3792</v>
+        <v>3466</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>15</v>
@@ -19790,7 +19790,7 @@
         <v>14</v>
       </c>
       <c r="F36" s="2">
-        <v>2822</v>
+        <v>3601</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>15</v>
@@ -19822,7 +19822,7 @@
         <v>14</v>
       </c>
       <c r="F37" s="2">
-        <v>1463</v>
+        <v>3129</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>15</v>
@@ -19854,7 +19854,7 @@
         <v>14</v>
       </c>
       <c r="F38" s="2">
-        <v>3017</v>
+        <v>2443</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>15</v>
@@ -19886,7 +19886,7 @@
         <v>14</v>
       </c>
       <c r="F39" s="2">
-        <v>3465</v>
+        <v>1282</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>15</v>
@@ -19918,7 +19918,7 @@
         <v>14</v>
       </c>
       <c r="F40" s="2">
-        <v>3879</v>
+        <v>2877</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>15</v>
@@ -19950,7 +19950,7 @@
         <v>14</v>
       </c>
       <c r="F41" s="2">
-        <v>3672</v>
+        <v>2481</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>15</v>
@@ -19982,7 +19982,7 @@
         <v>14</v>
       </c>
       <c r="F42" s="2">
-        <v>2689</v>
+        <v>1808</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>15</v>
@@ -20014,7 +20014,7 @@
         <v>14</v>
       </c>
       <c r="F43" s="2">
-        <v>3522</v>
+        <v>1497</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>15</v>
@@ -20046,7 +20046,7 @@
         <v>14</v>
       </c>
       <c r="F44" s="2">
-        <v>3834</v>
+        <v>4274</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>15</v>
@@ -20078,7 +20078,7 @@
         <v>14</v>
       </c>
       <c r="F45" s="2">
-        <v>3772</v>
+        <v>4783</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>15</v>
@@ -20110,7 +20110,7 @@
         <v>14</v>
       </c>
       <c r="F46" s="2">
-        <v>3585</v>
+        <v>4728</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>15</v>
@@ -20142,7 +20142,7 @@
         <v>14</v>
       </c>
       <c r="F47" s="2">
-        <v>2015</v>
+        <v>4747</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>15</v>
@@ -20174,7 +20174,7 @@
         <v>14</v>
       </c>
       <c r="F48" s="2">
-        <v>2760</v>
+        <v>3881</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>15</v>
@@ -20206,7 +20206,7 @@
         <v>14</v>
       </c>
       <c r="F49" s="2">
-        <v>1637</v>
+        <v>2720</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>15</v>
@@ -20238,7 +20238,7 @@
         <v>14</v>
       </c>
       <c r="F50" s="2">
-        <v>4671</v>
+        <v>1765</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>15</v>
@@ -20270,7 +20270,7 @@
         <v>14</v>
       </c>
       <c r="F51" s="2">
-        <v>1390</v>
+        <v>4230</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>15</v>
@@ -20302,7 +20302,7 @@
         <v>14</v>
       </c>
       <c r="F52" s="2">
-        <v>4759</v>
+        <v>1714</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>15</v>
@@ -20334,7 +20334,7 @@
         <v>14</v>
       </c>
       <c r="F53" s="2">
-        <v>3541</v>
+        <v>3046</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>15</v>
@@ -20366,7 +20366,7 @@
         <v>14</v>
       </c>
       <c r="F54" s="2">
-        <v>895</v>
+        <v>3123</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>15</v>
@@ -20398,7 +20398,7 @@
         <v>14</v>
       </c>
       <c r="F55" s="2">
-        <v>1575</v>
+        <v>3064</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>15</v>
@@ -20430,7 +20430,7 @@
         <v>14</v>
       </c>
       <c r="F56" s="2">
-        <v>2775</v>
+        <v>2153</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>15</v>
@@ -20462,7 +20462,7 @@
         <v>14</v>
       </c>
       <c r="F57" s="2">
-        <v>4469</v>
+        <v>2128</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>15</v>
@@ -20494,7 +20494,7 @@
         <v>14</v>
       </c>
       <c r="F58" s="2">
-        <v>3476</v>
+        <v>1689</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>15</v>
@@ -20526,7 +20526,7 @@
         <v>14</v>
       </c>
       <c r="F59" s="2">
-        <v>3274</v>
+        <v>1105</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>15</v>
@@ -20558,7 +20558,7 @@
         <v>14</v>
       </c>
       <c r="F60" s="2">
-        <v>2840</v>
+        <v>921</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>15</v>
@@ -20590,7 +20590,7 @@
         <v>14</v>
       </c>
       <c r="F61" s="2">
-        <v>3867</v>
+        <v>4083</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>15</v>
@@ -20622,7 +20622,7 @@
         <v>14</v>
       </c>
       <c r="F62" s="2">
-        <v>2552</v>
+        <v>822</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>15</v>
@@ -20654,7 +20654,7 @@
         <v>14</v>
       </c>
       <c r="F63" s="2">
-        <v>1122</v>
+        <v>4181</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>15</v>
@@ -20686,7 +20686,7 @@
         <v>14</v>
       </c>
       <c r="F64" s="2">
-        <v>3103</v>
+        <v>1956</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>15</v>
@@ -20718,7 +20718,7 @@
         <v>14</v>
       </c>
       <c r="F65" s="2">
-        <v>4147</v>
+        <v>3388</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>15</v>
@@ -20750,7 +20750,7 @@
         <v>14</v>
       </c>
       <c r="F66" s="2">
-        <v>2349</v>
+        <v>1901</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>15</v>
@@ -20782,7 +20782,7 @@
         <v>14</v>
       </c>
       <c r="F67" s="2">
-        <v>2928</v>
+        <v>1495</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>15</v>
@@ -20814,7 +20814,7 @@
         <v>14</v>
       </c>
       <c r="F68" s="2">
-        <v>3240</v>
+        <v>1744</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>15</v>
@@ -20846,7 +20846,7 @@
         <v>14</v>
       </c>
       <c r="F69" s="2">
-        <v>2796</v>
+        <v>1858</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>15</v>
@@ -20878,7 +20878,7 @@
         <v>14</v>
       </c>
       <c r="F70" s="2">
-        <v>4548</v>
+        <v>1693</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>15</v>
@@ -20910,7 +20910,7 @@
         <v>14</v>
       </c>
       <c r="F71" s="2">
-        <v>871</v>
+        <v>3535</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>15</v>
@@ -20942,7 +20942,7 @@
         <v>14</v>
       </c>
       <c r="F72" s="2">
-        <v>2941</v>
+        <v>4646</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>15</v>
@@ -20974,7 +20974,7 @@
         <v>14</v>
       </c>
       <c r="F73" s="2">
-        <v>3912</v>
+        <v>2528</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>15</v>
@@ -21006,7 +21006,7 @@
         <v>14</v>
       </c>
       <c r="F74" s="2">
-        <v>3196</v>
+        <v>2704</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>15</v>
@@ -21038,7 +21038,7 @@
         <v>14</v>
       </c>
       <c r="F75" s="2">
-        <v>3252</v>
+        <v>1421</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>15</v>
@@ -21070,7 +21070,7 @@
         <v>14</v>
       </c>
       <c r="F76" s="2">
-        <v>1264</v>
+        <v>2250</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>15</v>
@@ -21102,7 +21102,7 @@
         <v>14</v>
       </c>
       <c r="F77" s="2">
-        <v>1210</v>
+        <v>2660</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>15</v>
@@ -21134,7 +21134,7 @@
         <v>14</v>
       </c>
       <c r="F78" s="2">
-        <v>2679</v>
+        <v>1146</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>15</v>
@@ -21166,7 +21166,7 @@
         <v>14</v>
       </c>
       <c r="F79" s="2">
-        <v>2679</v>
+        <v>2451</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>15</v>
@@ -21198,7 +21198,7 @@
         <v>14</v>
       </c>
       <c r="F80" s="2">
-        <v>4275</v>
+        <v>4165</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>15</v>
@@ -21230,7 +21230,7 @@
         <v>14</v>
       </c>
       <c r="F81" s="2">
-        <v>2458</v>
+        <v>965</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>15</v>
@@ -21262,7 +21262,7 @@
         <v>14</v>
       </c>
       <c r="F82" s="2">
-        <v>1359</v>
+        <v>3162</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>15</v>
@@ -21294,7 +21294,7 @@
         <v>14</v>
       </c>
       <c r="F83" s="2">
-        <v>1899</v>
+        <v>4288</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>15</v>
@@ -21326,7 +21326,7 @@
         <v>14</v>
       </c>
       <c r="F84" s="2">
-        <v>3909</v>
+        <v>4510</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>15</v>
@@ -21358,7 +21358,7 @@
         <v>14</v>
       </c>
       <c r="F85" s="2">
-        <v>4388</v>
+        <v>1416</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>15</v>
@@ -21390,7 +21390,7 @@
         <v>14</v>
       </c>
       <c r="F86" s="2">
-        <v>3797</v>
+        <v>2999</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>15</v>
@@ -21422,7 +21422,7 @@
         <v>14</v>
       </c>
       <c r="F87" s="2">
-        <v>2659</v>
+        <v>4227</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>15</v>
@@ -21454,7 +21454,7 @@
         <v>14</v>
       </c>
       <c r="F88" s="2">
-        <v>2596</v>
+        <v>3790</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>15</v>
@@ -21486,7 +21486,7 @@
         <v>14</v>
       </c>
       <c r="F89" s="2">
-        <v>3583</v>
+        <v>1019</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>15</v>
@@ -21518,7 +21518,7 @@
         <v>14</v>
       </c>
       <c r="F90" s="2">
-        <v>4453</v>
+        <v>3377</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>15</v>
@@ -21550,7 +21550,7 @@
         <v>14</v>
       </c>
       <c r="F91" s="2">
-        <v>3852</v>
+        <v>3281</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>15</v>
@@ -21582,7 +21582,7 @@
         <v>14</v>
       </c>
       <c r="F92" s="2">
-        <v>2716</v>
+        <v>1607</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>15</v>
@@ -21614,7 +21614,7 @@
         <v>14</v>
       </c>
       <c r="F93" s="2">
-        <v>4512</v>
+        <v>3767</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>15</v>
@@ -21646,7 +21646,7 @@
         <v>14</v>
       </c>
       <c r="F94" s="2">
-        <v>3503</v>
+        <v>4431</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>15</v>
@@ -21678,7 +21678,7 @@
         <v>14</v>
       </c>
       <c r="F95" s="2">
-        <v>1796</v>
+        <v>899</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>15</v>
@@ -21710,7 +21710,7 @@
         <v>14</v>
       </c>
       <c r="F96" s="2">
-        <v>3640</v>
+        <v>1148</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>15</v>
@@ -21742,7 +21742,7 @@
         <v>14</v>
       </c>
       <c r="F97" s="2">
-        <v>3357</v>
+        <v>1335</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>15</v>
@@ -21774,7 +21774,7 @@
         <v>14</v>
       </c>
       <c r="F98" s="2">
-        <v>1280</v>
+        <v>1730</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>15</v>
@@ -21806,7 +21806,7 @@
         <v>14</v>
       </c>
       <c r="F99" s="2">
-        <v>4473</v>
+        <v>3319</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>15</v>
@@ -21838,7 +21838,7 @@
         <v>14</v>
       </c>
       <c r="F100" s="2">
-        <v>3644</v>
+        <v>3628</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>15</v>
@@ -21870,7 +21870,7 @@
         <v>14</v>
       </c>
       <c r="F101" s="2">
-        <v>3736</v>
+        <v>2120</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>15</v>
@@ -21902,7 +21902,7 @@
         <v>14</v>
       </c>
       <c r="F102" s="2">
-        <v>3532</v>
+        <v>3973</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>15</v>
@@ -21934,7 +21934,7 @@
         <v>14</v>
       </c>
       <c r="F103" s="2">
-        <v>4706</v>
+        <v>2470</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>15</v>
@@ -21966,7 +21966,7 @@
         <v>14</v>
       </c>
       <c r="F104" s="2">
-        <v>2716</v>
+        <v>2598</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>15</v>
@@ -21998,7 +21998,7 @@
         <v>14</v>
       </c>
       <c r="F105" s="2">
-        <v>4043</v>
+        <v>2973</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>15</v>
@@ -22030,7 +22030,7 @@
         <v>14</v>
       </c>
       <c r="F106" s="2">
-        <v>936</v>
+        <v>3687</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>15</v>
@@ -22062,7 +22062,7 @@
         <v>14</v>
       </c>
       <c r="F107" s="2">
-        <v>1887</v>
+        <v>3958</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>15</v>
@@ -22094,7 +22094,7 @@
         <v>14</v>
       </c>
       <c r="F108" s="2">
-        <v>4490</v>
+        <v>3127</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>15</v>
@@ -22126,7 +22126,7 @@
         <v>14</v>
       </c>
       <c r="F109" s="2">
-        <v>4322</v>
+        <v>1809</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>15</v>
@@ -22158,7 +22158,7 @@
         <v>14</v>
       </c>
       <c r="F110" s="2">
-        <v>3535</v>
+        <v>1798</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>15</v>
@@ -22190,7 +22190,7 @@
         <v>14</v>
       </c>
       <c r="F111" s="2">
-        <v>3636</v>
+        <v>2261</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>15</v>
@@ -22222,7 +22222,7 @@
         <v>14</v>
       </c>
       <c r="F112" s="2">
-        <v>3404</v>
+        <v>866</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>15</v>
@@ -22254,7 +22254,7 @@
         <v>14</v>
       </c>
       <c r="F113" s="2">
-        <v>2371</v>
+        <v>1339</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>15</v>
@@ -22286,7 +22286,7 @@
         <v>14</v>
       </c>
       <c r="F114" s="2">
-        <v>2447</v>
+        <v>4395</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>15</v>
@@ -22318,7 +22318,7 @@
         <v>14</v>
       </c>
       <c r="F115" s="2">
-        <v>4309</v>
+        <v>2927</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>15</v>
@@ -22350,7 +22350,7 @@
         <v>14</v>
       </c>
       <c r="F116" s="2">
-        <v>2190</v>
+        <v>3087</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>15</v>
@@ -22382,7 +22382,7 @@
         <v>14</v>
       </c>
       <c r="F117" s="2">
-        <v>3354</v>
+        <v>2127</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>15</v>
@@ -22414,7 +22414,7 @@
         <v>14</v>
       </c>
       <c r="F118" s="2">
-        <v>2050</v>
+        <v>3532</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>15</v>
@@ -22446,7 +22446,7 @@
         <v>14</v>
       </c>
       <c r="F119" s="2">
-        <v>1811</v>
+        <v>2646</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>15</v>
@@ -22478,7 +22478,7 @@
         <v>14</v>
       </c>
       <c r="F120" s="2">
-        <v>3906</v>
+        <v>2500</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>15</v>
@@ -22510,7 +22510,7 @@
         <v>14</v>
       </c>
       <c r="F121" s="2">
-        <v>2582</v>
+        <v>2825</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>15</v>
@@ -22542,7 +22542,7 @@
         <v>14</v>
       </c>
       <c r="F122" s="2">
-        <v>4230</v>
+        <v>3584</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>15</v>
@@ -22574,7 +22574,7 @@
         <v>14</v>
       </c>
       <c r="F123" s="2">
-        <v>4282</v>
+        <v>2358</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>15</v>
@@ -22606,7 +22606,7 @@
         <v>14</v>
       </c>
       <c r="F124" s="2">
-        <v>2338</v>
+        <v>3369</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>15</v>
@@ -22638,7 +22638,7 @@
         <v>14</v>
       </c>
       <c r="F125" s="2">
-        <v>1894</v>
+        <v>2444</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>15</v>
@@ -22670,7 +22670,7 @@
         <v>14</v>
       </c>
       <c r="F126" s="2">
-        <v>1079</v>
+        <v>3099</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>15</v>
@@ -22702,7 +22702,7 @@
         <v>14</v>
       </c>
       <c r="F127" s="2">
-        <v>1441</v>
+        <v>3107</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>15</v>
@@ -22734,7 +22734,7 @@
         <v>14</v>
       </c>
       <c r="F128" s="2">
-        <v>4145</v>
+        <v>804</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>15</v>
@@ -22766,7 +22766,7 @@
         <v>14</v>
       </c>
       <c r="F129" s="2">
-        <v>2952</v>
+        <v>1562</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>15</v>
@@ -22798,7 +22798,7 @@
         <v>14</v>
       </c>
       <c r="F130" s="2">
-        <v>4548</v>
+        <v>3447</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>15</v>
@@ -22830,7 +22830,7 @@
         <v>14</v>
       </c>
       <c r="F131" s="2">
-        <v>3228</v>
+        <v>3770</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>15</v>
@@ -22862,7 +22862,7 @@
         <v>14</v>
       </c>
       <c r="F132" s="2">
-        <v>2546</v>
+        <v>4546</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>15</v>
@@ -22894,7 +22894,7 @@
         <v>14</v>
       </c>
       <c r="F133" s="2">
-        <v>4333</v>
+        <v>2026</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>15</v>
@@ -22926,7 +22926,7 @@
         <v>14</v>
       </c>
       <c r="F134" s="2">
-        <v>2125</v>
+        <v>2154</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>15</v>
@@ -22958,7 +22958,7 @@
         <v>14</v>
       </c>
       <c r="F135" s="2">
-        <v>951</v>
+        <v>3915</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>15</v>
@@ -22990,7 +22990,7 @@
         <v>14</v>
       </c>
       <c r="F136" s="2">
-        <v>930</v>
+        <v>3087</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>15</v>
@@ -23022,7 +23022,7 @@
         <v>14</v>
       </c>
       <c r="F137" s="2">
-        <v>3971</v>
+        <v>3851</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>15</v>
@@ -23054,7 +23054,7 @@
         <v>14</v>
       </c>
       <c r="F138" s="2">
-        <v>3709</v>
+        <v>4408</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>15</v>
@@ -23086,7 +23086,7 @@
         <v>14</v>
       </c>
       <c r="F139" s="2">
-        <v>3733</v>
+        <v>2519</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>15</v>
@@ -23118,7 +23118,7 @@
         <v>14</v>
       </c>
       <c r="F140" s="2">
-        <v>2216</v>
+        <v>2913</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>15</v>
@@ -23150,7 +23150,7 @@
         <v>14</v>
       </c>
       <c r="F141" s="2">
-        <v>1067</v>
+        <v>2712</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>15</v>
@@ -23182,7 +23182,7 @@
         <v>14</v>
       </c>
       <c r="F142" s="2">
-        <v>4156</v>
+        <v>931</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>15</v>
@@ -23214,7 +23214,7 @@
         <v>14</v>
       </c>
       <c r="F143" s="2">
-        <v>2000</v>
+        <v>1754</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>15</v>
@@ -23246,7 +23246,7 @@
         <v>14</v>
       </c>
       <c r="F144" s="2">
-        <v>1901</v>
+        <v>996</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>15</v>
@@ -23278,7 +23278,7 @@
         <v>14</v>
       </c>
       <c r="F145" s="2">
-        <v>4351</v>
+        <v>3557</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>15</v>
@@ -23310,7 +23310,7 @@
         <v>14</v>
       </c>
       <c r="F146" s="2">
-        <v>1911</v>
+        <v>1916</v>
       </c>
       <c r="G146" s="2" t="s">
         <v>15</v>
@@ -23342,7 +23342,7 @@
         <v>14</v>
       </c>
       <c r="F147" s="2">
-        <v>4677</v>
+        <v>1396</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>15</v>
@@ -23374,7 +23374,7 @@
         <v>14</v>
       </c>
       <c r="F148" s="2">
-        <v>3896</v>
+        <v>826</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>15</v>
@@ -23406,7 +23406,7 @@
         <v>14</v>
       </c>
       <c r="F149" s="2">
-        <v>1015</v>
+        <v>2649</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>15</v>
@@ -23438,7 +23438,7 @@
         <v>14</v>
       </c>
       <c r="F150" s="2">
-        <v>1233</v>
+        <v>3247</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>15</v>
@@ -23470,7 +23470,7 @@
         <v>14</v>
       </c>
       <c r="F151" s="2">
-        <v>1168</v>
+        <v>4589</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>15</v>
@@ -23502,7 +23502,7 @@
         <v>14</v>
       </c>
       <c r="F152" s="2">
-        <v>1687</v>
+        <v>4711</v>
       </c>
       <c r="G152" s="2" t="s">
         <v>15</v>
@@ -23534,7 +23534,7 @@
         <v>14</v>
       </c>
       <c r="F153" s="2">
-        <v>3482</v>
+        <v>1370</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>15</v>
@@ -23566,7 +23566,7 @@
         <v>14</v>
       </c>
       <c r="F154" s="2">
-        <v>4002</v>
+        <v>2841</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>15</v>
@@ -23598,7 +23598,7 @@
         <v>14</v>
       </c>
       <c r="F155" s="2">
-        <v>3815</v>
+        <v>4779</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>15</v>
@@ -23630,7 +23630,7 @@
         <v>14</v>
       </c>
       <c r="F156" s="2">
-        <v>1535</v>
+        <v>1895</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>15</v>
@@ -23662,7 +23662,7 @@
         <v>14</v>
       </c>
       <c r="F157" s="2">
-        <v>858</v>
+        <v>4531</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>15</v>
@@ -23694,7 +23694,7 @@
         <v>14</v>
       </c>
       <c r="F158" s="2">
-        <v>4236</v>
+        <v>2123</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>15</v>
@@ -23726,7 +23726,7 @@
         <v>14</v>
       </c>
       <c r="F159" s="2">
-        <v>4310</v>
+        <v>1856</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>15</v>
@@ -23758,7 +23758,7 @@
         <v>14</v>
       </c>
       <c r="F160" s="2">
-        <v>2367</v>
+        <v>3338</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>15</v>
@@ -23790,7 +23790,7 @@
         <v>14</v>
       </c>
       <c r="F161" s="2">
-        <v>909</v>
+        <v>1991</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>15</v>
@@ -23822,7 +23822,7 @@
         <v>14</v>
       </c>
       <c r="F162" s="2">
-        <v>3832</v>
+        <v>3896</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>15</v>
@@ -23854,7 +23854,7 @@
         <v>14</v>
       </c>
       <c r="F163" s="2">
-        <v>4270</v>
+        <v>3887</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>15</v>
@@ -23886,7 +23886,7 @@
         <v>14</v>
       </c>
       <c r="F164" s="2">
-        <v>1176</v>
+        <v>3695</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>15</v>
@@ -23918,7 +23918,7 @@
         <v>14</v>
       </c>
       <c r="F165" s="2">
-        <v>3931</v>
+        <v>2889</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>15</v>
@@ -23950,7 +23950,7 @@
         <v>14</v>
       </c>
       <c r="F166" s="2">
-        <v>855</v>
+        <v>3328</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>15</v>
@@ -23982,7 +23982,7 @@
         <v>14</v>
       </c>
       <c r="F167" s="2">
-        <v>3118</v>
+        <v>1514</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>15</v>
@@ -24014,7 +24014,7 @@
         <v>14</v>
       </c>
       <c r="F168" s="2">
-        <v>1339</v>
+        <v>3203</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>15</v>
@@ -24046,7 +24046,7 @@
         <v>14</v>
       </c>
       <c r="F169" s="2">
-        <v>4456</v>
+        <v>4772</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>15</v>
@@ -24078,7 +24078,7 @@
         <v>14</v>
       </c>
       <c r="F170" s="2">
-        <v>3038</v>
+        <v>4353</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>15</v>
@@ -24110,7 +24110,7 @@
         <v>14</v>
       </c>
       <c r="F171" s="2">
-        <v>4012</v>
+        <v>4739</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>15</v>
@@ -24142,7 +24142,7 @@
         <v>14</v>
       </c>
       <c r="F172" s="2">
-        <v>2879</v>
+        <v>4626</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>15</v>
@@ -24174,7 +24174,7 @@
         <v>14</v>
       </c>
       <c r="F173" s="2">
-        <v>4487</v>
+        <v>1541</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>15</v>
@@ -24206,7 +24206,7 @@
         <v>14</v>
       </c>
       <c r="F174" s="2">
-        <v>2318</v>
+        <v>2648</v>
       </c>
       <c r="G174" s="2" t="s">
         <v>15</v>
@@ -24238,7 +24238,7 @@
         <v>14</v>
       </c>
       <c r="F175" s="2">
-        <v>2338</v>
+        <v>1492</v>
       </c>
       <c r="G175" s="2" t="s">
         <v>15</v>
@@ -24270,7 +24270,7 @@
         <v>14</v>
       </c>
       <c r="F176" s="2">
-        <v>3218</v>
+        <v>3512</v>
       </c>
       <c r="G176" s="2" t="s">
         <v>15</v>
@@ -24302,7 +24302,7 @@
         <v>14</v>
       </c>
       <c r="F177" s="2">
-        <v>4270</v>
+        <v>4237</v>
       </c>
       <c r="G177" s="2" t="s">
         <v>15</v>
@@ -24334,7 +24334,7 @@
         <v>14</v>
       </c>
       <c r="F178" s="2">
-        <v>2323</v>
+        <v>882</v>
       </c>
       <c r="G178" s="2" t="s">
         <v>15</v>
@@ -24366,7 +24366,7 @@
         <v>14</v>
       </c>
       <c r="F179" s="2">
-        <v>2073</v>
+        <v>4788</v>
       </c>
       <c r="G179" s="2" t="s">
         <v>15</v>
@@ -24398,7 +24398,7 @@
         <v>14</v>
       </c>
       <c r="F180" s="2">
-        <v>2820</v>
+        <v>2969</v>
       </c>
       <c r="G180" s="2" t="s">
         <v>15</v>
@@ -24430,7 +24430,7 @@
         <v>14</v>
       </c>
       <c r="F181" s="2">
-        <v>4567</v>
+        <v>829</v>
       </c>
       <c r="G181" s="2" t="s">
         <v>15</v>
@@ -24462,7 +24462,7 @@
         <v>14</v>
       </c>
       <c r="F182" s="2">
-        <v>1004</v>
+        <v>1599</v>
       </c>
       <c r="G182" s="2" t="s">
         <v>15</v>
@@ -24494,7 +24494,7 @@
         <v>14</v>
       </c>
       <c r="F183" s="2">
-        <v>3521</v>
+        <v>2563</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>15</v>
@@ -24526,7 +24526,7 @@
         <v>14</v>
       </c>
       <c r="F184" s="2">
-        <v>3340</v>
+        <v>2878</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>15</v>
@@ -24558,7 +24558,7 @@
         <v>14</v>
       </c>
       <c r="F185" s="2">
-        <v>1381</v>
+        <v>3283</v>
       </c>
       <c r="G185" s="2" t="s">
         <v>15</v>
@@ -24590,7 +24590,7 @@
         <v>14</v>
       </c>
       <c r="F186" s="2">
-        <v>2213</v>
+        <v>4098</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>15</v>
@@ -24622,7 +24622,7 @@
         <v>14</v>
       </c>
       <c r="F187" s="2">
-        <v>2486</v>
+        <v>2167</v>
       </c>
       <c r="G187" s="2" t="s">
         <v>15</v>
@@ -24654,7 +24654,7 @@
         <v>14</v>
       </c>
       <c r="F188" s="2">
-        <v>2927</v>
+        <v>3075</v>
       </c>
       <c r="G188" s="2" t="s">
         <v>15</v>
@@ -24686,7 +24686,7 @@
         <v>14</v>
       </c>
       <c r="F189" s="2">
-        <v>1799</v>
+        <v>3947</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>15</v>
@@ -24718,7 +24718,7 @@
         <v>14</v>
       </c>
       <c r="F190" s="2">
-        <v>2840</v>
+        <v>1567</v>
       </c>
       <c r="G190" s="2" t="s">
         <v>15</v>
@@ -24750,7 +24750,7 @@
         <v>14</v>
       </c>
       <c r="F191" s="2">
-        <v>4130</v>
+        <v>1689</v>
       </c>
       <c r="G191" s="2" t="s">
         <v>15</v>
@@ -24782,7 +24782,7 @@
         <v>14</v>
       </c>
       <c r="F192" s="2">
-        <v>3410</v>
+        <v>3217</v>
       </c>
       <c r="G192" s="2" t="s">
         <v>15</v>
@@ -24814,7 +24814,7 @@
         <v>14</v>
       </c>
       <c r="F193" s="2">
-        <v>2684</v>
+        <v>1060</v>
       </c>
       <c r="G193" s="2" t="s">
         <v>15</v>
@@ -24846,7 +24846,7 @@
         <v>14</v>
       </c>
       <c r="F194" s="2">
-        <v>2487</v>
+        <v>902</v>
       </c>
       <c r="G194" s="2" t="s">
         <v>15</v>
@@ -24878,7 +24878,7 @@
         <v>14</v>
       </c>
       <c r="F195" s="2">
-        <v>4360</v>
+        <v>2583</v>
       </c>
       <c r="G195" s="2" t="s">
         <v>15</v>
@@ -24910,7 +24910,7 @@
         <v>14</v>
       </c>
       <c r="F196" s="2">
-        <v>1653</v>
+        <v>1578</v>
       </c>
       <c r="G196" s="2" t="s">
         <v>15</v>
@@ -24942,7 +24942,7 @@
         <v>14</v>
       </c>
       <c r="F197" s="2">
-        <v>4264</v>
+        <v>1793</v>
       </c>
       <c r="G197" s="2" t="s">
         <v>15</v>
@@ -24974,7 +24974,7 @@
         <v>14</v>
       </c>
       <c r="F198" s="2">
-        <v>3985</v>
+        <v>1832</v>
       </c>
       <c r="G198" s="2" t="s">
         <v>15</v>
@@ -25006,7 +25006,7 @@
         <v>14</v>
       </c>
       <c r="F199" s="2">
-        <v>1090</v>
+        <v>2802</v>
       </c>
       <c r="G199" s="2" t="s">
         <v>15</v>
@@ -25038,7 +25038,7 @@
         <v>14</v>
       </c>
       <c r="F200" s="2">
-        <v>2242</v>
+        <v>1380</v>
       </c>
       <c r="G200" s="2" t="s">
         <v>15</v>
@@ -25070,7 +25070,7 @@
         <v>14</v>
       </c>
       <c r="F201" s="2">
-        <v>4210</v>
+        <v>3607</v>
       </c>
       <c r="G201" s="2" t="s">
         <v>15</v>
@@ -25102,7 +25102,7 @@
         <v>14</v>
       </c>
       <c r="F202" s="2">
-        <v>3822</v>
+        <v>1775</v>
       </c>
       <c r="G202" s="2" t="s">
         <v>15</v>
@@ -25134,7 +25134,7 @@
         <v>14</v>
       </c>
       <c r="F203" s="2">
-        <v>1669</v>
+        <v>1248</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>15</v>
@@ -25166,7 +25166,7 @@
         <v>14</v>
       </c>
       <c r="F204" s="2">
-        <v>1162</v>
+        <v>4704</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>15</v>
@@ -25198,7 +25198,7 @@
         <v>14</v>
       </c>
       <c r="F205" s="2">
-        <v>3098</v>
+        <v>1939</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>15</v>
@@ -25230,7 +25230,7 @@
         <v>14</v>
       </c>
       <c r="F206" s="2">
-        <v>2630</v>
+        <v>3755</v>
       </c>
       <c r="G206" s="2" t="s">
         <v>15</v>
@@ -25262,7 +25262,7 @@
         <v>14</v>
       </c>
       <c r="F207" s="2">
-        <v>3207</v>
+        <v>4787</v>
       </c>
       <c r="G207" s="2" t="s">
         <v>15</v>
@@ -25294,7 +25294,7 @@
         <v>14</v>
       </c>
       <c r="F208" s="2">
-        <v>3159</v>
+        <v>1693</v>
       </c>
       <c r="G208" s="2" t="s">
         <v>15</v>
@@ -25326,7 +25326,7 @@
         <v>14</v>
       </c>
       <c r="F209" s="2">
-        <v>939</v>
+        <v>2755</v>
       </c>
       <c r="G209" s="2" t="s">
         <v>15</v>
@@ -25358,7 +25358,7 @@
         <v>14</v>
       </c>
       <c r="F210" s="2">
-        <v>2976</v>
+        <v>3825</v>
       </c>
       <c r="G210" s="2" t="s">
         <v>15</v>
@@ -25390,7 +25390,7 @@
         <v>14</v>
       </c>
       <c r="F211" s="2">
-        <v>2807</v>
+        <v>2642</v>
       </c>
       <c r="G211" s="2" t="s">
         <v>15</v>
@@ -25422,7 +25422,7 @@
         <v>14</v>
       </c>
       <c r="F212" s="2">
-        <v>2640</v>
+        <v>996</v>
       </c>
       <c r="G212" s="2" t="s">
         <v>15</v>
@@ -25454,7 +25454,7 @@
         <v>14</v>
       </c>
       <c r="F213" s="2">
-        <v>3235</v>
+        <v>4725</v>
       </c>
       <c r="G213" s="2" t="s">
         <v>15</v>
@@ -25486,7 +25486,7 @@
         <v>14</v>
       </c>
       <c r="F214" s="2">
-        <v>2419</v>
+        <v>987</v>
       </c>
       <c r="G214" s="2" t="s">
         <v>15</v>
@@ -25518,7 +25518,7 @@
         <v>14</v>
       </c>
       <c r="F215" s="2">
-        <v>3779</v>
+        <v>1654</v>
       </c>
       <c r="G215" s="2" t="s">
         <v>15</v>
@@ -25550,7 +25550,7 @@
         <v>14</v>
       </c>
       <c r="F216" s="2">
-        <v>2554</v>
+        <v>2327</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>15</v>
@@ -25582,7 +25582,7 @@
         <v>14</v>
       </c>
       <c r="F217" s="2">
-        <v>1699</v>
+        <v>1472</v>
       </c>
       <c r="G217" s="2" t="s">
         <v>15</v>
@@ -25614,7 +25614,7 @@
         <v>14</v>
       </c>
       <c r="F218" s="2">
-        <v>3314</v>
+        <v>3318</v>
       </c>
       <c r="G218" s="2" t="s">
         <v>15</v>
@@ -25646,7 +25646,7 @@
         <v>14</v>
       </c>
       <c r="F219" s="2">
-        <v>4040</v>
+        <v>4336</v>
       </c>
       <c r="G219" s="2" t="s">
         <v>15</v>
@@ -25678,7 +25678,7 @@
         <v>14</v>
       </c>
       <c r="F220" s="2">
-        <v>1189</v>
+        <v>4616</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>15</v>
@@ -25710,7 +25710,7 @@
         <v>14</v>
       </c>
       <c r="F221" s="2">
-        <v>1239</v>
+        <v>3223</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>15</v>
@@ -25742,7 +25742,7 @@
         <v>14</v>
       </c>
       <c r="F222" s="2">
-        <v>915</v>
+        <v>3040</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>15</v>
@@ -25774,7 +25774,7 @@
         <v>14</v>
       </c>
       <c r="F223" s="2">
-        <v>2219</v>
+        <v>864</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>15</v>
@@ -25806,7 +25806,7 @@
         <v>14</v>
       </c>
       <c r="F224" s="2">
-        <v>2439</v>
+        <v>1338</v>
       </c>
       <c r="G224" s="2" t="s">
         <v>15</v>
@@ -25838,7 +25838,7 @@
         <v>14</v>
       </c>
       <c r="F225" s="2">
-        <v>2752</v>
+        <v>2781</v>
       </c>
       <c r="G225" s="2" t="s">
         <v>15</v>
@@ -25870,7 +25870,7 @@
         <v>14</v>
       </c>
       <c r="F226" s="2">
-        <v>2649</v>
+        <v>3320</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>15</v>
@@ -25902,7 +25902,7 @@
         <v>14</v>
       </c>
       <c r="F227" s="2">
-        <v>3246</v>
+        <v>2164</v>
       </c>
       <c r="G227" s="2" t="s">
         <v>15</v>
@@ -25934,7 +25934,7 @@
         <v>14</v>
       </c>
       <c r="F228" s="2">
-        <v>2929</v>
+        <v>3847</v>
       </c>
       <c r="G228" s="2" t="s">
         <v>15</v>
@@ -25966,7 +25966,7 @@
         <v>14</v>
       </c>
       <c r="F229" s="2">
-        <v>3556</v>
+        <v>4735</v>
       </c>
       <c r="G229" s="2" t="s">
         <v>15</v>
@@ -25998,7 +25998,7 @@
         <v>14</v>
       </c>
       <c r="F230" s="2">
-        <v>2306</v>
+        <v>3537</v>
       </c>
       <c r="G230" s="2" t="s">
         <v>15</v>
@@ -26030,7 +26030,7 @@
         <v>14</v>
       </c>
       <c r="F231" s="2">
-        <v>2321</v>
+        <v>2780</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>15</v>
@@ -26062,7 +26062,7 @@
         <v>14</v>
       </c>
       <c r="F232" s="2">
-        <v>3817</v>
+        <v>1273</v>
       </c>
       <c r="G232" s="2" t="s">
         <v>15</v>
@@ -26094,7 +26094,7 @@
         <v>14</v>
       </c>
       <c r="F233" s="2">
-        <v>1746</v>
+        <v>1000</v>
       </c>
       <c r="G233" s="2" t="s">
         <v>15</v>
@@ -26126,7 +26126,7 @@
         <v>14</v>
       </c>
       <c r="F234" s="2">
-        <v>2965</v>
+        <v>980</v>
       </c>
       <c r="G234" s="2" t="s">
         <v>15</v>
@@ -26158,7 +26158,7 @@
         <v>14</v>
       </c>
       <c r="F235" s="2">
-        <v>3904</v>
+        <v>1534</v>
       </c>
       <c r="G235" s="2" t="s">
         <v>15</v>
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="F236" s="2">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="G236" s="2" t="s">
         <v>15</v>
@@ -26222,7 +26222,7 @@
         <v>14</v>
       </c>
       <c r="F237" s="2">
-        <v>1127</v>
+        <v>4563</v>
       </c>
       <c r="G237" s="2" t="s">
         <v>15</v>
@@ -26254,7 +26254,7 @@
         <v>14</v>
       </c>
       <c r="F238" s="2">
-        <v>1033</v>
+        <v>3779</v>
       </c>
       <c r="G238" s="2" t="s">
         <v>15</v>
@@ -26286,7 +26286,7 @@
         <v>14</v>
       </c>
       <c r="F239" s="2">
-        <v>2450</v>
+        <v>1171</v>
       </c>
       <c r="G239" s="2" t="s">
         <v>15</v>
@@ -26318,7 +26318,7 @@
         <v>14</v>
       </c>
       <c r="F240" s="2">
-        <v>2853</v>
+        <v>4086</v>
       </c>
       <c r="G240" s="2" t="s">
         <v>15</v>
@@ -26350,7 +26350,7 @@
         <v>14</v>
       </c>
       <c r="F241" s="2">
-        <v>4435</v>
+        <v>4367</v>
       </c>
       <c r="G241" s="2" t="s">
         <v>15</v>
@@ -26382,7 +26382,7 @@
         <v>14</v>
       </c>
       <c r="F242" s="2">
-        <v>3411</v>
+        <v>1304</v>
       </c>
       <c r="G242" s="2" t="s">
         <v>15</v>
@@ -26414,7 +26414,7 @@
         <v>14</v>
       </c>
       <c r="F243" s="2">
-        <v>1579</v>
+        <v>2489</v>
       </c>
       <c r="G243" s="2" t="s">
         <v>15</v>
@@ -26446,7 +26446,7 @@
         <v>14</v>
       </c>
       <c r="F244" s="2">
-        <v>1553</v>
+        <v>2512</v>
       </c>
       <c r="G244" s="2" t="s">
         <v>15</v>
@@ -26478,7 +26478,7 @@
         <v>14</v>
       </c>
       <c r="F245" s="2">
-        <v>3598</v>
+        <v>2455</v>
       </c>
       <c r="G245" s="2" t="s">
         <v>15</v>
@@ -26510,7 +26510,7 @@
         <v>14</v>
       </c>
       <c r="F246" s="2">
-        <v>4452</v>
+        <v>4405</v>
       </c>
       <c r="G246" s="2" t="s">
         <v>15</v>
@@ -26542,7 +26542,7 @@
         <v>14</v>
       </c>
       <c r="F247" s="2">
-        <v>3048</v>
+        <v>3937</v>
       </c>
       <c r="G247" s="2" t="s">
         <v>15</v>
@@ -26574,7 +26574,7 @@
         <v>14</v>
       </c>
       <c r="F248" s="2">
-        <v>4471</v>
+        <v>1222</v>
       </c>
       <c r="G248" s="2" t="s">
         <v>15</v>
@@ -26606,7 +26606,7 @@
         <v>14</v>
       </c>
       <c r="F249" s="2">
-        <v>1082</v>
+        <v>1771</v>
       </c>
       <c r="G249" s="2" t="s">
         <v>15</v>
@@ -26638,7 +26638,7 @@
         <v>14</v>
       </c>
       <c r="F250" s="2">
-        <v>4231</v>
+        <v>3512</v>
       </c>
       <c r="G250" s="2" t="s">
         <v>15</v>
@@ -26670,7 +26670,7 @@
         <v>14</v>
       </c>
       <c r="F251" s="2">
-        <v>2873</v>
+        <v>3379</v>
       </c>
       <c r="G251" s="2" t="s">
         <v>15</v>
@@ -26702,7 +26702,7 @@
         <v>14</v>
       </c>
       <c r="F252" s="2">
-        <v>4513</v>
+        <v>2621</v>
       </c>
       <c r="G252" s="2" t="s">
         <v>15</v>
@@ -26734,7 +26734,7 @@
         <v>14</v>
       </c>
       <c r="F253" s="2">
-        <v>3104</v>
+        <v>2146</v>
       </c>
       <c r="G253" s="2" t="s">
         <v>15</v>
@@ -26766,7 +26766,7 @@
         <v>14</v>
       </c>
       <c r="F254" s="2">
-        <v>4154</v>
+        <v>1819</v>
       </c>
       <c r="G254" s="2" t="s">
         <v>15</v>
@@ -26798,7 +26798,7 @@
         <v>14</v>
       </c>
       <c r="F255" s="2">
-        <v>1740</v>
+        <v>4650</v>
       </c>
       <c r="G255" s="2" t="s">
         <v>15</v>
@@ -26830,7 +26830,7 @@
         <v>14</v>
       </c>
       <c r="F256" s="2">
-        <v>4675</v>
+        <v>1434</v>
       </c>
       <c r="G256" s="2" t="s">
         <v>15</v>
@@ -26862,7 +26862,7 @@
         <v>14</v>
       </c>
       <c r="F257" s="2">
-        <v>1641</v>
+        <v>2467</v>
       </c>
       <c r="G257" s="2" t="s">
         <v>15</v>
@@ -26894,7 +26894,7 @@
         <v>14</v>
       </c>
       <c r="F258" s="2">
-        <v>844</v>
+        <v>1901</v>
       </c>
       <c r="G258" s="2" t="s">
         <v>15</v>
@@ -26926,7 +26926,7 @@
         <v>14</v>
       </c>
       <c r="F259" s="2">
-        <v>2016</v>
+        <v>1597</v>
       </c>
       <c r="G259" s="2" t="s">
         <v>15</v>
@@ -26958,7 +26958,7 @@
         <v>14</v>
       </c>
       <c r="F260" s="2">
-        <v>2100</v>
+        <v>2487</v>
       </c>
       <c r="G260" s="2" t="s">
         <v>15</v>
@@ -26990,7 +26990,7 @@
         <v>14</v>
       </c>
       <c r="F261" s="2">
-        <v>2970</v>
+        <v>3134</v>
       </c>
       <c r="G261" s="2" t="s">
         <v>15</v>
@@ -27022,7 +27022,7 @@
         <v>14</v>
       </c>
       <c r="F262" s="2">
-        <v>1052</v>
+        <v>2421</v>
       </c>
       <c r="G262" s="2" t="s">
         <v>15</v>
@@ -27054,7 +27054,7 @@
         <v>14</v>
       </c>
       <c r="F263" s="2">
-        <v>1388</v>
+        <v>2337</v>
       </c>
       <c r="G263" s="2" t="s">
         <v>15</v>
@@ -27086,7 +27086,7 @@
         <v>14</v>
       </c>
       <c r="F264" s="2">
-        <v>2829</v>
+        <v>1267</v>
       </c>
       <c r="G264" s="2" t="s">
         <v>15</v>
@@ -27118,7 +27118,7 @@
         <v>14</v>
       </c>
       <c r="F265" s="2">
-        <v>2397</v>
+        <v>1490</v>
       </c>
       <c r="G265" s="2" t="s">
         <v>15</v>
@@ -27150,7 +27150,7 @@
         <v>14</v>
       </c>
       <c r="F266" s="2">
-        <v>2635</v>
+        <v>3669</v>
       </c>
       <c r="G266" s="2" t="s">
         <v>15</v>
@@ -27182,7 +27182,7 @@
         <v>14</v>
       </c>
       <c r="F267" s="2">
-        <v>2858</v>
+        <v>2660</v>
       </c>
       <c r="G267" s="2" t="s">
         <v>15</v>
@@ -27214,7 +27214,7 @@
         <v>14</v>
       </c>
       <c r="F268" s="2">
-        <v>2546</v>
+        <v>3770</v>
       </c>
       <c r="G268" s="2" t="s">
         <v>15</v>
@@ -27246,7 +27246,7 @@
         <v>14</v>
       </c>
       <c r="F269" s="2">
-        <v>879</v>
+        <v>2780</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>15</v>
@@ -27278,7 +27278,7 @@
         <v>14</v>
       </c>
       <c r="F270" s="2">
-        <v>4098</v>
+        <v>4576</v>
       </c>
       <c r="G270" s="2" t="s">
         <v>15</v>
@@ -27310,7 +27310,7 @@
         <v>14</v>
       </c>
       <c r="F271" s="2">
-        <v>1484</v>
+        <v>1518</v>
       </c>
       <c r="G271" s="2" t="s">
         <v>15</v>
@@ -27342,7 +27342,7 @@
         <v>14</v>
       </c>
       <c r="F272" s="2">
-        <v>4664</v>
+        <v>3792</v>
       </c>
       <c r="G272" s="2" t="s">
         <v>15</v>
@@ -27374,7 +27374,7 @@
         <v>14</v>
       </c>
       <c r="F273" s="2">
-        <v>4351</v>
+        <v>2752</v>
       </c>
       <c r="G273" s="2" t="s">
         <v>15</v>
@@ -27406,7 +27406,7 @@
         <v>14</v>
       </c>
       <c r="F274" s="2">
-        <v>4701</v>
+        <v>4082</v>
       </c>
       <c r="G274" s="2" t="s">
         <v>15</v>
@@ -27438,7 +27438,7 @@
         <v>14</v>
       </c>
       <c r="F275" s="2">
-        <v>1012</v>
+        <v>1449</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>15</v>
@@ -27470,7 +27470,7 @@
         <v>14</v>
       </c>
       <c r="F276" s="2">
-        <v>2186</v>
+        <v>4308</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>15</v>
@@ -27502,7 +27502,7 @@
         <v>14</v>
       </c>
       <c r="F277" s="2">
-        <v>1358</v>
+        <v>4712</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>15</v>
@@ -27534,7 +27534,7 @@
         <v>14</v>
       </c>
       <c r="F278" s="2">
-        <v>2193</v>
+        <v>2008</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>15</v>
@@ -27566,7 +27566,7 @@
         <v>14</v>
       </c>
       <c r="F279" s="2">
-        <v>813</v>
+        <v>3013</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>15</v>
@@ -27598,7 +27598,7 @@
         <v>14</v>
       </c>
       <c r="F280" s="2">
-        <v>2708</v>
+        <v>3187</v>
       </c>
       <c r="G280" s="2" t="s">
         <v>15</v>
@@ -27630,7 +27630,7 @@
         <v>14</v>
       </c>
       <c r="F281" s="2">
-        <v>3183</v>
+        <v>2340</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>15</v>
@@ -27662,7 +27662,7 @@
         <v>14</v>
       </c>
       <c r="F282" s="2">
-        <v>4455</v>
+        <v>860</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>15</v>
@@ -27694,7 +27694,7 @@
         <v>14</v>
       </c>
       <c r="F283" s="2">
-        <v>4699</v>
+        <v>1154</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>15</v>
@@ -27726,7 +27726,7 @@
         <v>14</v>
       </c>
       <c r="F284" s="2">
-        <v>1551</v>
+        <v>1256</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>15</v>
@@ -27758,7 +27758,7 @@
         <v>14</v>
       </c>
       <c r="F285" s="2">
-        <v>1473</v>
+        <v>3173</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>15</v>
@@ -27790,7 +27790,7 @@
         <v>14</v>
       </c>
       <c r="F286" s="2">
-        <v>1144</v>
+        <v>1962</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>15</v>
@@ -27822,7 +27822,7 @@
         <v>14</v>
       </c>
       <c r="F287" s="2">
-        <v>2278</v>
+        <v>986</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>15</v>
@@ -27854,7 +27854,7 @@
         <v>14</v>
       </c>
       <c r="F288" s="2">
-        <v>1408</v>
+        <v>2447</v>
       </c>
       <c r="G288" s="2" t="s">
         <v>15</v>
@@ -27886,7 +27886,7 @@
         <v>14</v>
       </c>
       <c r="F289" s="2">
-        <v>838</v>
+        <v>2781</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>15</v>
@@ -27918,7 +27918,7 @@
         <v>14</v>
       </c>
       <c r="F290" s="2">
-        <v>4658</v>
+        <v>3049</v>
       </c>
       <c r="G290" s="2" t="s">
         <v>15</v>
@@ -27950,7 +27950,7 @@
         <v>14</v>
       </c>
       <c r="F291" s="2">
-        <v>1542</v>
+        <v>4730</v>
       </c>
       <c r="G291" s="2" t="s">
         <v>15</v>
@@ -27982,7 +27982,7 @@
         <v>14</v>
       </c>
       <c r="F292" s="2">
-        <v>4091</v>
+        <v>834</v>
       </c>
       <c r="G292" s="2" t="s">
         <v>15</v>
@@ -28014,7 +28014,7 @@
         <v>14</v>
       </c>
       <c r="F293" s="2">
-        <v>1139</v>
+        <v>1405</v>
       </c>
       <c r="G293" s="2" t="s">
         <v>15</v>
@@ -28046,7 +28046,7 @@
         <v>14</v>
       </c>
       <c r="F294" s="2">
-        <v>2122</v>
+        <v>3634</v>
       </c>
       <c r="G294" s="2" t="s">
         <v>15</v>
@@ -28078,7 +28078,7 @@
         <v>14</v>
       </c>
       <c r="F295" s="2">
-        <v>2873</v>
+        <v>4254</v>
       </c>
       <c r="G295" s="2" t="s">
         <v>15</v>
@@ -28110,7 +28110,7 @@
         <v>14</v>
       </c>
       <c r="F296" s="2">
-        <v>2578</v>
+        <v>1094</v>
       </c>
       <c r="G296" s="2" t="s">
         <v>15</v>
@@ -28142,7 +28142,7 @@
         <v>14</v>
       </c>
       <c r="F297" s="2">
-        <v>3019</v>
+        <v>3193</v>
       </c>
       <c r="G297" s="2" t="s">
         <v>15</v>
@@ -28174,7 +28174,7 @@
         <v>14</v>
       </c>
       <c r="F298" s="2">
-        <v>4188</v>
+        <v>4132</v>
       </c>
       <c r="G298" s="2" t="s">
         <v>15</v>
@@ -28206,7 +28206,7 @@
         <v>14</v>
       </c>
       <c r="F299" s="2">
-        <v>2103</v>
+        <v>1380</v>
       </c>
       <c r="G299" s="2" t="s">
         <v>15</v>
@@ -28238,7 +28238,7 @@
         <v>14</v>
       </c>
       <c r="F300" s="2">
-        <v>1222</v>
+        <v>873</v>
       </c>
       <c r="G300" s="2" t="s">
         <v>15</v>
@@ -28270,7 +28270,7 @@
         <v>14</v>
       </c>
       <c r="F301" s="2">
-        <v>2784</v>
+        <v>1152</v>
       </c>
       <c r="G301" s="2" t="s">
         <v>15</v>
@@ -28302,7 +28302,7 @@
         <v>14</v>
       </c>
       <c r="F302" s="2">
-        <v>2459</v>
+        <v>4240</v>
       </c>
       <c r="G302" s="2" t="s">
         <v>15</v>
@@ -28334,7 +28334,7 @@
         <v>14</v>
       </c>
       <c r="F303" s="2">
-        <v>4521</v>
+        <v>3786</v>
       </c>
       <c r="G303" s="2" t="s">
         <v>15</v>
@@ -28366,7 +28366,7 @@
         <v>14</v>
       </c>
       <c r="F304" s="2">
-        <v>1137</v>
+        <v>1565</v>
       </c>
       <c r="G304" s="2" t="s">
         <v>15</v>
@@ -28398,7 +28398,7 @@
         <v>14</v>
       </c>
       <c r="F305" s="2">
-        <v>2539</v>
+        <v>3948</v>
       </c>
       <c r="G305" s="2" t="s">
         <v>15</v>
@@ -28430,7 +28430,7 @@
         <v>14</v>
       </c>
       <c r="F306" s="2">
-        <v>3823</v>
+        <v>1533</v>
       </c>
       <c r="G306" s="2" t="s">
         <v>15</v>
@@ -28462,7 +28462,7 @@
         <v>14</v>
       </c>
       <c r="F307" s="2">
-        <v>1490</v>
+        <v>2890</v>
       </c>
       <c r="G307" s="2" t="s">
         <v>15</v>
@@ -28494,7 +28494,7 @@
         <v>14</v>
       </c>
       <c r="F308" s="2">
-        <v>3534</v>
+        <v>2989</v>
       </c>
       <c r="G308" s="2" t="s">
         <v>15</v>
@@ -28526,7 +28526,7 @@
         <v>14</v>
       </c>
       <c r="F309" s="2">
-        <v>4410</v>
+        <v>1814</v>
       </c>
       <c r="G309" s="2" t="s">
         <v>15</v>
@@ -28558,7 +28558,7 @@
         <v>14</v>
       </c>
       <c r="F310" s="2">
-        <v>2007</v>
+        <v>3068</v>
       </c>
       <c r="G310" s="2" t="s">
         <v>15</v>
@@ -28590,7 +28590,7 @@
         <v>14</v>
       </c>
       <c r="F311" s="2">
-        <v>4432</v>
+        <v>3033</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>15</v>
@@ -28622,7 +28622,7 @@
         <v>14</v>
       </c>
       <c r="F312" s="2">
-        <v>3385</v>
+        <v>3715</v>
       </c>
       <c r="G312" s="2" t="s">
         <v>15</v>
@@ -28654,7 +28654,7 @@
         <v>14</v>
       </c>
       <c r="F313" s="2">
-        <v>1321</v>
+        <v>3016</v>
       </c>
       <c r="G313" s="2" t="s">
         <v>15</v>
@@ -28686,7 +28686,7 @@
         <v>14</v>
       </c>
       <c r="F314" s="2">
-        <v>1009</v>
+        <v>4382</v>
       </c>
       <c r="G314" s="2" t="s">
         <v>15</v>
@@ -28718,7 +28718,7 @@
         <v>14</v>
       </c>
       <c r="F315" s="2">
-        <v>2221</v>
+        <v>3241</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>15</v>
@@ -28750,7 +28750,7 @@
         <v>14</v>
       </c>
       <c r="F316" s="2">
-        <v>2541</v>
+        <v>3841</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>15</v>
@@ -28782,7 +28782,7 @@
         <v>14</v>
       </c>
       <c r="F317" s="2">
-        <v>4349</v>
+        <v>4285</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>15</v>
@@ -28814,7 +28814,7 @@
         <v>14</v>
       </c>
       <c r="F318" s="2">
-        <v>1201</v>
+        <v>2176</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>15</v>
@@ -28846,7 +28846,7 @@
         <v>14</v>
       </c>
       <c r="F319" s="2">
-        <v>4182</v>
+        <v>4589</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>15</v>
@@ -28878,7 +28878,7 @@
         <v>14</v>
       </c>
       <c r="F320" s="2">
-        <v>1308</v>
+        <v>4576</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>15</v>
@@ -28910,7 +28910,7 @@
         <v>14</v>
       </c>
       <c r="F321" s="2">
-        <v>3896</v>
+        <v>4680</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>15</v>
@@ -28942,7 +28942,7 @@
         <v>14</v>
       </c>
       <c r="F322" s="2">
-        <v>1686</v>
+        <v>4080</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>15</v>
@@ -28974,7 +28974,7 @@
         <v>14</v>
       </c>
       <c r="F323" s="2">
-        <v>1321</v>
+        <v>4777</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>15</v>
@@ -29006,7 +29006,7 @@
         <v>14</v>
       </c>
       <c r="F324" s="2">
-        <v>3878</v>
+        <v>1336</v>
       </c>
       <c r="G324" s="2" t="s">
         <v>15</v>
@@ -29038,7 +29038,7 @@
         <v>14</v>
       </c>
       <c r="F325" s="2">
-        <v>3852</v>
+        <v>2545</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>15</v>
@@ -29070,7 +29070,7 @@
         <v>14</v>
       </c>
       <c r="F326" s="2">
-        <v>4204</v>
+        <v>4636</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>15</v>
@@ -29102,7 +29102,7 @@
         <v>14</v>
       </c>
       <c r="F327" s="2">
-        <v>3133</v>
+        <v>3769</v>
       </c>
       <c r="G327" s="2" t="s">
         <v>15</v>
@@ -29134,7 +29134,7 @@
         <v>14</v>
       </c>
       <c r="F328" s="2">
-        <v>2838</v>
+        <v>3441</v>
       </c>
       <c r="G328" s="2" t="s">
         <v>15</v>
@@ -29166,7 +29166,7 @@
         <v>14</v>
       </c>
       <c r="F329" s="2">
-        <v>2300</v>
+        <v>2624</v>
       </c>
       <c r="G329" s="2" t="s">
         <v>15</v>
@@ -29198,7 +29198,7 @@
         <v>14</v>
       </c>
       <c r="F330" s="2">
-        <v>4409</v>
+        <v>3485</v>
       </c>
       <c r="G330" s="2" t="s">
         <v>15</v>
@@ -29230,7 +29230,7 @@
         <v>14</v>
       </c>
       <c r="F331" s="2">
-        <v>4296</v>
+        <v>3422</v>
       </c>
       <c r="G331" s="2" t="s">
         <v>15</v>
@@ -29262,7 +29262,7 @@
         <v>14</v>
       </c>
       <c r="F332" s="2">
-        <v>4564</v>
+        <v>2592</v>
       </c>
       <c r="G332" s="2" t="s">
         <v>15</v>
@@ -29294,7 +29294,7 @@
         <v>14</v>
       </c>
       <c r="F333" s="2">
-        <v>4516</v>
+        <v>4724</v>
       </c>
       <c r="G333" s="2" t="s">
         <v>15</v>
@@ -29326,7 +29326,7 @@
         <v>14</v>
       </c>
       <c r="F334" s="2">
-        <v>1491</v>
+        <v>4528</v>
       </c>
       <c r="G334" s="2" t="s">
         <v>15</v>
@@ -29358,7 +29358,7 @@
         <v>14</v>
       </c>
       <c r="F335" s="2">
-        <v>1627</v>
+        <v>4125</v>
       </c>
       <c r="G335" s="2" t="s">
         <v>15</v>
@@ -29390,7 +29390,7 @@
         <v>14</v>
       </c>
       <c r="F336" s="2">
-        <v>1239</v>
+        <v>4022</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>15</v>
@@ -29422,7 +29422,7 @@
         <v>14</v>
       </c>
       <c r="F337" s="2">
-        <v>3608</v>
+        <v>2858</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>15</v>
@@ -29454,7 +29454,7 @@
         <v>14</v>
       </c>
       <c r="F338" s="2">
-        <v>2163</v>
+        <v>1240</v>
       </c>
       <c r="G338" s="2" t="s">
         <v>15</v>
@@ -29486,7 +29486,7 @@
         <v>14</v>
       </c>
       <c r="F339" s="2">
-        <v>1058</v>
+        <v>3100</v>
       </c>
       <c r="G339" s="2" t="s">
         <v>15</v>
@@ -29518,7 +29518,7 @@
         <v>14</v>
       </c>
       <c r="F340" s="2">
-        <v>1513</v>
+        <v>2081</v>
       </c>
       <c r="G340" s="2" t="s">
         <v>15</v>
@@ -29550,7 +29550,7 @@
         <v>14</v>
       </c>
       <c r="F341" s="2">
-        <v>3245</v>
+        <v>4569</v>
       </c>
       <c r="G341" s="2" t="s">
         <v>15</v>
@@ -29582,7 +29582,7 @@
         <v>14</v>
       </c>
       <c r="F342" s="2">
-        <v>4460</v>
+        <v>4709</v>
       </c>
       <c r="G342" s="2" t="s">
         <v>15</v>
@@ -29614,7 +29614,7 @@
         <v>14</v>
       </c>
       <c r="F343" s="2">
-        <v>3524</v>
+        <v>3788</v>
       </c>
       <c r="G343" s="2" t="s">
         <v>15</v>
@@ -29646,7 +29646,7 @@
         <v>14</v>
       </c>
       <c r="F344" s="2">
-        <v>4428</v>
+        <v>2648</v>
       </c>
       <c r="G344" s="2" t="s">
         <v>15</v>
@@ -29678,7 +29678,7 @@
         <v>14</v>
       </c>
       <c r="F345" s="2">
-        <v>3208</v>
+        <v>3902</v>
       </c>
       <c r="G345" s="2" t="s">
         <v>15</v>
@@ -29710,7 +29710,7 @@
         <v>14</v>
       </c>
       <c r="F346" s="2">
-        <v>4486</v>
+        <v>2406</v>
       </c>
       <c r="G346" s="2" t="s">
         <v>15</v>
@@ -29742,7 +29742,7 @@
         <v>14</v>
       </c>
       <c r="F347" s="2">
-        <v>2936</v>
+        <v>1244</v>
       </c>
       <c r="G347" s="2" t="s">
         <v>15</v>
@@ -29774,7 +29774,7 @@
         <v>14</v>
       </c>
       <c r="F348" s="2">
-        <v>1114</v>
+        <v>2079</v>
       </c>
       <c r="G348" s="2" t="s">
         <v>15</v>
@@ -29806,7 +29806,7 @@
         <v>14</v>
       </c>
       <c r="F349" s="2">
-        <v>2026</v>
+        <v>886</v>
       </c>
       <c r="G349" s="2" t="s">
         <v>15</v>
@@ -29838,7 +29838,7 @@
         <v>14</v>
       </c>
       <c r="F350" s="2">
-        <v>1927</v>
+        <v>4373</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>15</v>
@@ -29870,7 +29870,7 @@
         <v>14</v>
       </c>
       <c r="F351" s="2">
-        <v>2904</v>
+        <v>847</v>
       </c>
       <c r="G351" s="2" t="s">
         <v>15</v>
@@ -29902,7 +29902,7 @@
         <v>14</v>
       </c>
       <c r="F352" s="2">
-        <v>1187</v>
+        <v>3842</v>
       </c>
       <c r="G352" s="2" t="s">
         <v>15</v>
@@ -29934,7 +29934,7 @@
         <v>14</v>
       </c>
       <c r="F353" s="2">
-        <v>4274</v>
+        <v>1466</v>
       </c>
       <c r="G353" s="2" t="s">
         <v>15</v>
@@ -29966,7 +29966,7 @@
         <v>14</v>
       </c>
       <c r="F354" s="2">
-        <v>2966</v>
+        <v>3293</v>
       </c>
       <c r="G354" s="2" t="s">
         <v>15</v>
@@ -29998,7 +29998,7 @@
         <v>14</v>
       </c>
       <c r="F355" s="2">
-        <v>2855</v>
+        <v>4531</v>
       </c>
       <c r="G355" s="2" t="s">
         <v>15</v>
@@ -30030,7 +30030,7 @@
         <v>14</v>
       </c>
       <c r="F356" s="2">
-        <v>3399</v>
+        <v>1494</v>
       </c>
       <c r="G356" s="2" t="s">
         <v>15</v>
@@ -30062,7 +30062,7 @@
         <v>14</v>
       </c>
       <c r="F357" s="2">
-        <v>4661</v>
+        <v>3265</v>
       </c>
       <c r="G357" s="2" t="s">
         <v>15</v>
@@ -30094,7 +30094,7 @@
         <v>14</v>
       </c>
       <c r="F358" s="2">
-        <v>1148</v>
+        <v>4437</v>
       </c>
       <c r="G358" s="2" t="s">
         <v>15</v>
@@ -30126,7 +30126,7 @@
         <v>14</v>
       </c>
       <c r="F359" s="2">
-        <v>3634</v>
+        <v>2560</v>
       </c>
       <c r="G359" s="2" t="s">
         <v>15</v>
@@ -30158,7 +30158,7 @@
         <v>14</v>
       </c>
       <c r="F360" s="2">
-        <v>1924</v>
+        <v>3463</v>
       </c>
       <c r="G360" s="2" t="s">
         <v>15</v>
@@ -30190,7 +30190,7 @@
         <v>14</v>
       </c>
       <c r="F361" s="2">
-        <v>1958</v>
+        <v>2541</v>
       </c>
       <c r="G361" s="2" t="s">
         <v>15</v>
@@ -30222,7 +30222,7 @@
         <v>14</v>
       </c>
       <c r="F362" s="2">
-        <v>2196</v>
+        <v>4594</v>
       </c>
       <c r="G362" s="2" t="s">
         <v>15</v>
@@ -30254,7 +30254,7 @@
         <v>14</v>
       </c>
       <c r="F363" s="2">
-        <v>3016</v>
+        <v>2644</v>
       </c>
       <c r="G363" s="2" t="s">
         <v>15</v>
@@ -30286,7 +30286,7 @@
         <v>14</v>
       </c>
       <c r="F364" s="2">
-        <v>2924</v>
+        <v>3293</v>
       </c>
       <c r="G364" s="2" t="s">
         <v>15</v>
@@ -30318,7 +30318,7 @@
         <v>14</v>
       </c>
       <c r="F365" s="2">
-        <v>1793</v>
+        <v>2247</v>
       </c>
       <c r="G365" s="2" t="s">
         <v>15</v>
@@ -30350,7 +30350,7 @@
         <v>14</v>
       </c>
       <c r="F366" s="2">
-        <v>2656</v>
+        <v>4418</v>
       </c>
       <c r="G366" s="2" t="s">
         <v>15</v>
@@ -30382,7 +30382,7 @@
         <v>14</v>
       </c>
       <c r="F367" s="2">
-        <v>4490</v>
+        <v>4193</v>
       </c>
       <c r="G367" s="2" t="s">
         <v>15</v>
@@ -30414,7 +30414,7 @@
         <v>14</v>
       </c>
       <c r="F368" s="2">
-        <v>3009</v>
+        <v>1182</v>
       </c>
       <c r="G368" s="2" t="s">
         <v>15</v>
@@ -30446,7 +30446,7 @@
         <v>14</v>
       </c>
       <c r="F369" s="2">
-        <v>3575</v>
+        <v>1360</v>
       </c>
       <c r="G369" s="2" t="s">
         <v>15</v>
@@ -30478,7 +30478,7 @@
         <v>14</v>
       </c>
       <c r="F370" s="2">
-        <v>1063</v>
+        <v>3616</v>
       </c>
       <c r="G370" s="2" t="s">
         <v>15</v>
@@ -30510,7 +30510,7 @@
         <v>14</v>
       </c>
       <c r="F371" s="2">
-        <v>1434</v>
+        <v>3303</v>
       </c>
       <c r="G371" s="2" t="s">
         <v>15</v>
@@ -30542,7 +30542,7 @@
         <v>14</v>
       </c>
       <c r="F372" s="2">
-        <v>1437</v>
+        <v>1425</v>
       </c>
       <c r="G372" s="2" t="s">
         <v>15</v>
@@ -30574,7 +30574,7 @@
         <v>14</v>
       </c>
       <c r="F373" s="2">
-        <v>1718</v>
+        <v>3463</v>
       </c>
       <c r="G373" s="2" t="s">
         <v>15</v>
@@ -30606,7 +30606,7 @@
         <v>14</v>
       </c>
       <c r="F374" s="2">
-        <v>2162</v>
+        <v>2794</v>
       </c>
       <c r="G374" s="2" t="s">
         <v>15</v>
@@ -30638,7 +30638,7 @@
         <v>14</v>
       </c>
       <c r="F375" s="2">
-        <v>3840</v>
+        <v>3892</v>
       </c>
       <c r="G375" s="2" t="s">
         <v>15</v>
@@ -30670,7 +30670,7 @@
         <v>14</v>
       </c>
       <c r="F376" s="2">
-        <v>1144</v>
+        <v>3303</v>
       </c>
       <c r="G376" s="2" t="s">
         <v>15</v>
@@ -30702,7 +30702,7 @@
         <v>14</v>
       </c>
       <c r="F377" s="2">
-        <v>1930</v>
+        <v>826</v>
       </c>
       <c r="G377" s="2" t="s">
         <v>15</v>
@@ -30734,7 +30734,7 @@
         <v>14</v>
       </c>
       <c r="F378" s="2">
-        <v>1059</v>
+        <v>1413</v>
       </c>
       <c r="G378" s="2" t="s">
         <v>15</v>
@@ -30766,7 +30766,7 @@
         <v>14</v>
       </c>
       <c r="F379" s="2">
-        <v>2998</v>
+        <v>4269</v>
       </c>
       <c r="G379" s="2" t="s">
         <v>15</v>
@@ -30798,7 +30798,7 @@
         <v>14</v>
       </c>
       <c r="F380" s="2">
-        <v>1856</v>
+        <v>4532</v>
       </c>
       <c r="G380" s="2" t="s">
         <v>15</v>
@@ -30830,7 +30830,7 @@
         <v>14</v>
       </c>
       <c r="F381" s="2">
-        <v>2767</v>
+        <v>990</v>
       </c>
       <c r="G381" s="2" t="s">
         <v>15</v>
@@ -30862,7 +30862,7 @@
         <v>14</v>
       </c>
       <c r="F382" s="2">
-        <v>3679</v>
+        <v>3756</v>
       </c>
       <c r="G382" s="2" t="s">
         <v>15</v>
@@ -30894,7 +30894,7 @@
         <v>14</v>
       </c>
       <c r="F383" s="2">
-        <v>4658</v>
+        <v>4552</v>
       </c>
       <c r="G383" s="2" t="s">
         <v>15</v>
@@ -30926,7 +30926,7 @@
         <v>14</v>
       </c>
       <c r="F384" s="2">
-        <v>2202</v>
+        <v>2810</v>
       </c>
       <c r="G384" s="2" t="s">
         <v>15</v>
@@ -30958,7 +30958,7 @@
         <v>14</v>
       </c>
       <c r="F385" s="2">
-        <v>1498</v>
+        <v>4454</v>
       </c>
       <c r="G385" s="2" t="s">
         <v>15</v>
@@ -30990,7 +30990,7 @@
         <v>14</v>
       </c>
       <c r="F386" s="2">
-        <v>3319</v>
+        <v>2727</v>
       </c>
       <c r="G386" s="2" t="s">
         <v>15</v>
@@ -31022,7 +31022,7 @@
         <v>14</v>
       </c>
       <c r="F387" s="2">
-        <v>1147</v>
+        <v>2029</v>
       </c>
       <c r="G387" s="2" t="s">
         <v>15</v>
@@ -31054,7 +31054,7 @@
         <v>14</v>
       </c>
       <c r="F388" s="2">
-        <v>2471</v>
+        <v>2372</v>
       </c>
       <c r="G388" s="2" t="s">
         <v>15</v>
@@ -31086,7 +31086,7 @@
         <v>14</v>
       </c>
       <c r="F389" s="2">
-        <v>1911</v>
+        <v>3264</v>
       </c>
       <c r="G389" s="2" t="s">
         <v>15</v>
@@ -31118,7 +31118,7 @@
         <v>14</v>
       </c>
       <c r="F390" s="2">
-        <v>3087</v>
+        <v>4590</v>
       </c>
       <c r="G390" s="2" t="s">
         <v>15</v>
@@ -31150,7 +31150,7 @@
         <v>14</v>
       </c>
       <c r="F391" s="2">
-        <v>1092</v>
+        <v>3366</v>
       </c>
       <c r="G391" s="2" t="s">
         <v>15</v>
@@ -31182,7 +31182,7 @@
         <v>14</v>
       </c>
       <c r="F392" s="2">
-        <v>950</v>
+        <v>3193</v>
       </c>
       <c r="G392" s="2" t="s">
         <v>15</v>
@@ -31214,7 +31214,7 @@
         <v>14</v>
       </c>
       <c r="F393" s="2">
-        <v>3271</v>
+        <v>1374</v>
       </c>
       <c r="G393" s="2" t="s">
         <v>15</v>
@@ -31246,7 +31246,7 @@
         <v>14</v>
       </c>
       <c r="F394" s="2">
-        <v>3911</v>
+        <v>1423</v>
       </c>
       <c r="G394" s="2" t="s">
         <v>15</v>
@@ -31278,7 +31278,7 @@
         <v>14</v>
       </c>
       <c r="F395" s="2">
-        <v>4433</v>
+        <v>2934</v>
       </c>
       <c r="G395" s="2" t="s">
         <v>15</v>
@@ -31310,7 +31310,7 @@
         <v>14</v>
       </c>
       <c r="F396" s="2">
-        <v>3220</v>
+        <v>3168</v>
       </c>
       <c r="G396" s="2" t="s">
         <v>15</v>
@@ -31342,7 +31342,7 @@
         <v>14</v>
       </c>
       <c r="F397" s="2">
-        <v>2292</v>
+        <v>2985</v>
       </c>
       <c r="G397" s="2" t="s">
         <v>15</v>
@@ -31374,7 +31374,7 @@
         <v>14</v>
       </c>
       <c r="F398" s="2">
-        <v>3084</v>
+        <v>2987</v>
       </c>
       <c r="G398" s="2" t="s">
         <v>15</v>
@@ -31406,7 +31406,7 @@
         <v>14</v>
       </c>
       <c r="F399" s="2">
-        <v>2936</v>
+        <v>3049</v>
       </c>
       <c r="G399" s="2" t="s">
         <v>15</v>
@@ -31438,7 +31438,7 @@
         <v>14</v>
       </c>
       <c r="F400" s="2">
-        <v>3789</v>
+        <v>1107</v>
       </c>
       <c r="G400" s="2" t="s">
         <v>15</v>
@@ -31470,7 +31470,7 @@
         <v>14</v>
       </c>
       <c r="F401" s="2">
-        <v>1255</v>
+        <v>2478</v>
       </c>
       <c r="G401" s="2" t="s">
         <v>15</v>
@@ -31502,7 +31502,7 @@
         <v>14</v>
       </c>
       <c r="F402" s="2">
-        <v>1933</v>
+        <v>3648</v>
       </c>
       <c r="G402" s="2" t="s">
         <v>15</v>
@@ -31534,7 +31534,7 @@
         <v>14</v>
       </c>
       <c r="F403" s="2">
-        <v>895</v>
+        <v>3803</v>
       </c>
       <c r="G403" s="2" t="s">
         <v>15</v>
@@ -31566,7 +31566,7 @@
         <v>14</v>
       </c>
       <c r="F404" s="2">
-        <v>3343</v>
+        <v>1767</v>
       </c>
       <c r="G404" s="2" t="s">
         <v>15</v>
@@ -31598,7 +31598,7 @@
         <v>14</v>
       </c>
       <c r="F405" s="2">
-        <v>1892</v>
+        <v>3038</v>
       </c>
       <c r="G405" s="2" t="s">
         <v>15</v>
@@ -31630,7 +31630,7 @@
         <v>14</v>
       </c>
       <c r="F406" s="2">
-        <v>3448</v>
+        <v>1358</v>
       </c>
       <c r="G406" s="2" t="s">
         <v>15</v>
@@ -31662,7 +31662,7 @@
         <v>14</v>
       </c>
       <c r="F407" s="2">
-        <v>1853</v>
+        <v>3005</v>
       </c>
       <c r="G407" s="2" t="s">
         <v>15</v>
@@ -31694,7 +31694,7 @@
         <v>14</v>
       </c>
       <c r="F408" s="2">
-        <v>2765</v>
+        <v>4329</v>
       </c>
       <c r="G408" s="2" t="s">
         <v>15</v>
@@ -31726,7 +31726,7 @@
         <v>14</v>
       </c>
       <c r="F409" s="2">
-        <v>4647</v>
+        <v>1083</v>
       </c>
       <c r="G409" s="2" t="s">
         <v>15</v>
@@ -31758,7 +31758,7 @@
         <v>14</v>
       </c>
       <c r="F410" s="2">
-        <v>1286</v>
+        <v>3948</v>
       </c>
       <c r="G410" s="2" t="s">
         <v>15</v>
@@ -31790,7 +31790,7 @@
         <v>14</v>
       </c>
       <c r="F411" s="2">
-        <v>1899</v>
+        <v>1136</v>
       </c>
       <c r="G411" s="2" t="s">
         <v>15</v>
@@ -31822,7 +31822,7 @@
         <v>14</v>
       </c>
       <c r="F412" s="2">
-        <v>3181</v>
+        <v>2358</v>
       </c>
       <c r="G412" s="2" t="s">
         <v>15</v>
@@ -31854,7 +31854,7 @@
         <v>14</v>
       </c>
       <c r="F413" s="2">
-        <v>3631</v>
+        <v>2529</v>
       </c>
       <c r="G413" s="2" t="s">
         <v>15</v>
@@ -31886,7 +31886,7 @@
         <v>14</v>
       </c>
       <c r="F414" s="2">
-        <v>4629</v>
+        <v>3387</v>
       </c>
       <c r="G414" s="2" t="s">
         <v>15</v>
@@ -31918,7 +31918,7 @@
         <v>14</v>
       </c>
       <c r="F415" s="2">
-        <v>3162</v>
+        <v>4242</v>
       </c>
       <c r="G415" s="2" t="s">
         <v>15</v>
@@ -31950,7 +31950,7 @@
         <v>14</v>
       </c>
       <c r="F416" s="2">
-        <v>2171</v>
+        <v>1774</v>
       </c>
       <c r="G416" s="2" t="s">
         <v>15</v>
@@ -31982,7 +31982,7 @@
         <v>14</v>
       </c>
       <c r="F417" s="2">
-        <v>4406</v>
+        <v>3070</v>
       </c>
       <c r="G417" s="2" t="s">
         <v>15</v>
@@ -32014,7 +32014,7 @@
         <v>14</v>
       </c>
       <c r="F418" s="2">
-        <v>4253</v>
+        <v>2875</v>
       </c>
       <c r="G418" s="2" t="s">
         <v>15</v>
@@ -32046,7 +32046,7 @@
         <v>14</v>
       </c>
       <c r="F419" s="2">
-        <v>4511</v>
+        <v>2336</v>
       </c>
       <c r="G419" s="2" t="s">
         <v>15</v>
@@ -32078,7 +32078,7 @@
         <v>14</v>
       </c>
       <c r="F420" s="2">
-        <v>3997</v>
+        <v>2650</v>
       </c>
       <c r="G420" s="2" t="s">
         <v>15</v>
@@ -32110,7 +32110,7 @@
         <v>14</v>
       </c>
       <c r="F421" s="2">
-        <v>1708</v>
+        <v>1803</v>
       </c>
       <c r="G421" s="2" t="s">
         <v>15</v>
@@ -32142,7 +32142,7 @@
         <v>14</v>
       </c>
       <c r="F422" s="2">
-        <v>2377</v>
+        <v>4086</v>
       </c>
       <c r="G422" s="2" t="s">
         <v>15</v>
@@ -32174,7 +32174,7 @@
         <v>14</v>
       </c>
       <c r="F423" s="2">
-        <v>3893</v>
+        <v>1645</v>
       </c>
       <c r="G423" s="2" t="s">
         <v>15</v>
@@ -32206,7 +32206,7 @@
         <v>14</v>
       </c>
       <c r="F424" s="2">
-        <v>3044</v>
+        <v>4207</v>
       </c>
       <c r="G424" s="2" t="s">
         <v>15</v>
@@ -32238,7 +32238,7 @@
         <v>14</v>
       </c>
       <c r="F425" s="2">
-        <v>1873</v>
+        <v>2967</v>
       </c>
       <c r="G425" s="2" t="s">
         <v>15</v>
@@ -32270,7 +32270,7 @@
         <v>14</v>
       </c>
       <c r="F426" s="2">
-        <v>1511</v>
+        <v>1766</v>
       </c>
       <c r="G426" s="2" t="s">
         <v>15</v>
@@ -32302,7 +32302,7 @@
         <v>14</v>
       </c>
       <c r="F427" s="2">
-        <v>2552</v>
+        <v>2784</v>
       </c>
       <c r="G427" s="2" t="s">
         <v>15</v>
@@ -32334,7 +32334,7 @@
         <v>14</v>
       </c>
       <c r="F428" s="2">
-        <v>1321</v>
+        <v>3858</v>
       </c>
       <c r="G428" s="2" t="s">
         <v>15</v>
@@ -32366,7 +32366,7 @@
         <v>14</v>
       </c>
       <c r="F429" s="2">
-        <v>3128</v>
+        <v>1997</v>
       </c>
       <c r="G429" s="2" t="s">
         <v>15</v>
@@ -32398,7 +32398,7 @@
         <v>14</v>
       </c>
       <c r="F430" s="2">
-        <v>3728</v>
+        <v>1561</v>
       </c>
       <c r="G430" s="2" t="s">
         <v>15</v>
@@ -32430,7 +32430,7 @@
         <v>14</v>
       </c>
       <c r="F431" s="2">
-        <v>1028</v>
+        <v>3287</v>
       </c>
       <c r="G431" s="2" t="s">
         <v>15</v>
@@ -32462,7 +32462,7 @@
         <v>14</v>
       </c>
       <c r="F432" s="2">
-        <v>1598</v>
+        <v>1290</v>
       </c>
       <c r="G432" s="2" t="s">
         <v>15</v>
@@ -32494,7 +32494,7 @@
         <v>14</v>
       </c>
       <c r="F433" s="2">
-        <v>1123</v>
+        <v>3390</v>
       </c>
       <c r="G433" s="2" t="s">
         <v>15</v>
@@ -32526,7 +32526,7 @@
         <v>14</v>
       </c>
       <c r="F434" s="2">
-        <v>4123</v>
+        <v>1202</v>
       </c>
       <c r="G434" s="2" t="s">
         <v>15</v>
@@ -32558,7 +32558,7 @@
         <v>14</v>
       </c>
       <c r="F435" s="2">
-        <v>2103</v>
+        <v>3986</v>
       </c>
       <c r="G435" s="2" t="s">
         <v>15</v>
@@ -32590,7 +32590,7 @@
         <v>14</v>
       </c>
       <c r="F436" s="2">
-        <v>978</v>
+        <v>2351</v>
       </c>
       <c r="G436" s="2" t="s">
         <v>15</v>
@@ -32622,7 +32622,7 @@
         <v>14</v>
       </c>
       <c r="F437" s="2">
-        <v>1489</v>
+        <v>2069</v>
       </c>
       <c r="G437" s="2" t="s">
         <v>15</v>
@@ -32654,7 +32654,7 @@
         <v>14</v>
       </c>
       <c r="F438" s="2">
-        <v>3820</v>
+        <v>3918</v>
       </c>
       <c r="G438" s="2" t="s">
         <v>15</v>
@@ -32686,7 +32686,7 @@
         <v>14</v>
       </c>
       <c r="F439" s="2">
-        <v>2802</v>
+        <v>2530</v>
       </c>
       <c r="G439" s="2" t="s">
         <v>15</v>
@@ -32718,7 +32718,7 @@
         <v>14</v>
       </c>
       <c r="F440" s="2">
-        <v>2977</v>
+        <v>2340</v>
       </c>
       <c r="G440" s="2" t="s">
         <v>15</v>
@@ -32750,7 +32750,7 @@
         <v>14</v>
       </c>
       <c r="F441" s="2">
-        <v>3950</v>
+        <v>913</v>
       </c>
       <c r="G441" s="2" t="s">
         <v>15</v>
@@ -32782,7 +32782,7 @@
         <v>14</v>
       </c>
       <c r="F442" s="2">
-        <v>3959</v>
+        <v>3286</v>
       </c>
       <c r="G442" s="2" t="s">
         <v>15</v>
@@ -32814,7 +32814,7 @@
         <v>14</v>
       </c>
       <c r="F443" s="2">
-        <v>1936</v>
+        <v>2969</v>
       </c>
       <c r="G443" s="2" t="s">
         <v>15</v>
@@ -32846,7 +32846,7 @@
         <v>14</v>
       </c>
       <c r="F444" s="2">
-        <v>858</v>
+        <v>4121</v>
       </c>
       <c r="G444" s="2" t="s">
         <v>15</v>
@@ -32878,7 +32878,7 @@
         <v>14</v>
       </c>
       <c r="F445" s="2">
-        <v>2825</v>
+        <v>3873</v>
       </c>
       <c r="G445" s="2" t="s">
         <v>15</v>
@@ -32910,7 +32910,7 @@
         <v>14</v>
       </c>
       <c r="F446" s="2">
-        <v>1066</v>
+        <v>1132</v>
       </c>
       <c r="G446" s="2" t="s">
         <v>15</v>
@@ -32942,7 +32942,7 @@
         <v>14</v>
       </c>
       <c r="F447" s="2">
-        <v>4723</v>
+        <v>1543</v>
       </c>
       <c r="G447" s="2" t="s">
         <v>15</v>
@@ -32974,7 +32974,7 @@
         <v>14</v>
       </c>
       <c r="F448" s="2">
-        <v>1617</v>
+        <v>2775</v>
       </c>
       <c r="G448" s="2" t="s">
         <v>15</v>
@@ -33006,7 +33006,7 @@
         <v>14</v>
       </c>
       <c r="F449" s="2">
-        <v>1551</v>
+        <v>2094</v>
       </c>
       <c r="G449" s="2" t="s">
         <v>15</v>
@@ -33038,7 +33038,7 @@
         <v>14</v>
       </c>
       <c r="F450" s="2">
-        <v>4640</v>
+        <v>2209</v>
       </c>
       <c r="G450" s="2" t="s">
         <v>15</v>
@@ -33070,7 +33070,7 @@
         <v>14</v>
       </c>
       <c r="F451" s="2">
-        <v>1359</v>
+        <v>4222</v>
       </c>
       <c r="G451" s="2" t="s">
         <v>15</v>
@@ -33102,7 +33102,7 @@
         <v>14</v>
       </c>
       <c r="F452" s="2">
-        <v>1499</v>
+        <v>3675</v>
       </c>
       <c r="G452" s="2" t="s">
         <v>15</v>
@@ -33134,7 +33134,7 @@
         <v>14</v>
       </c>
       <c r="F453" s="2">
-        <v>4045</v>
+        <v>2022</v>
       </c>
       <c r="G453" s="2" t="s">
         <v>15</v>
@@ -33166,7 +33166,7 @@
         <v>14</v>
       </c>
       <c r="F454" s="2">
-        <v>3425</v>
+        <v>3482</v>
       </c>
       <c r="G454" s="2" t="s">
         <v>15</v>
@@ -33198,7 +33198,7 @@
         <v>14</v>
       </c>
       <c r="F455" s="2">
-        <v>1446</v>
+        <v>1862</v>
       </c>
       <c r="G455" s="2" t="s">
         <v>15</v>
@@ -33230,7 +33230,7 @@
         <v>14</v>
       </c>
       <c r="F456" s="2">
-        <v>1455</v>
+        <v>924</v>
       </c>
       <c r="G456" s="2" t="s">
         <v>15</v>
@@ -33262,7 +33262,7 @@
         <v>14</v>
       </c>
       <c r="F457" s="2">
-        <v>2489</v>
+        <v>1237</v>
       </c>
       <c r="G457" s="2" t="s">
         <v>15</v>
@@ -33294,7 +33294,7 @@
         <v>14</v>
       </c>
       <c r="F458" s="2">
-        <v>2144</v>
+        <v>2348</v>
       </c>
       <c r="G458" s="2" t="s">
         <v>15</v>
@@ -33326,7 +33326,7 @@
         <v>14</v>
       </c>
       <c r="F459" s="2">
-        <v>4021</v>
+        <v>4075</v>
       </c>
       <c r="G459" s="2" t="s">
         <v>15</v>
@@ -33358,7 +33358,7 @@
         <v>14</v>
       </c>
       <c r="F460" s="2">
-        <v>3260</v>
+        <v>1489</v>
       </c>
       <c r="G460" s="2" t="s">
         <v>15</v>
@@ -33390,7 +33390,7 @@
         <v>14</v>
       </c>
       <c r="F461" s="2">
-        <v>2199</v>
+        <v>3321</v>
       </c>
       <c r="G461" s="2" t="s">
         <v>15</v>
@@ -33422,7 +33422,7 @@
         <v>14</v>
       </c>
       <c r="F462" s="2">
-        <v>4139</v>
+        <v>4694</v>
       </c>
       <c r="G462" s="2" t="s">
         <v>15</v>
@@ -33454,7 +33454,7 @@
         <v>14</v>
       </c>
       <c r="F463" s="2">
-        <v>2648</v>
+        <v>2820</v>
       </c>
       <c r="G463" s="2" t="s">
         <v>15</v>
@@ -33486,7 +33486,7 @@
         <v>14</v>
       </c>
       <c r="F464" s="2">
-        <v>3646</v>
+        <v>1982</v>
       </c>
       <c r="G464" s="2" t="s">
         <v>15</v>
@@ -33518,7 +33518,7 @@
         <v>14</v>
       </c>
       <c r="F465" s="2">
-        <v>2292</v>
+        <v>1539</v>
       </c>
       <c r="G465" s="2" t="s">
         <v>15</v>
@@ -33550,7 +33550,7 @@
         <v>14</v>
       </c>
       <c r="F466" s="2">
-        <v>1156</v>
+        <v>2682</v>
       </c>
       <c r="G466" s="2" t="s">
         <v>15</v>
@@ -33582,7 +33582,7 @@
         <v>14</v>
       </c>
       <c r="F467" s="2">
-        <v>1251</v>
+        <v>3948</v>
       </c>
       <c r="G467" s="2" t="s">
         <v>15</v>
@@ -33614,7 +33614,7 @@
         <v>14</v>
       </c>
       <c r="F468" s="2">
-        <v>1540</v>
+        <v>2491</v>
       </c>
       <c r="G468" s="2" t="s">
         <v>15</v>
@@ -33646,7 +33646,7 @@
         <v>14</v>
       </c>
       <c r="F469" s="2">
-        <v>3431</v>
+        <v>1141</v>
       </c>
       <c r="G469" s="2" t="s">
         <v>15</v>
@@ -33678,7 +33678,7 @@
         <v>14</v>
       </c>
       <c r="F470" s="2">
-        <v>1916</v>
+        <v>1105</v>
       </c>
       <c r="G470" s="2" t="s">
         <v>15</v>
@@ -33710,7 +33710,7 @@
         <v>14</v>
       </c>
       <c r="F471" s="2">
-        <v>2510</v>
+        <v>1017</v>
       </c>
       <c r="G471" s="2" t="s">
         <v>15</v>

--- a/reports/selenium/latest/excel/Automation_Test_Report.xlsx
+++ b/reports/selenium/latest/excel/Automation_Test_Report.xlsx
@@ -3084,7 +3084,7 @@
     <t>Build</t>
   </si>
   <si>
-    <t>6</t>
+    <t>7</t>
   </si>
   <si>
     <t>Branch</t>
@@ -3096,13 +3096,13 @@
     <t>Commit</t>
   </si>
   <si>
-    <t>90ba612a9b32</t>
+    <t>7c78d5ee5289</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T15:39:48.370Z</t>
+    <t>2026-08-18T16:09:54.064Z</t>
   </si>
   <si>
     <t>Browser</t>
@@ -3607,7 +3607,7 @@
         <v>14</v>
       </c>
       <c r="F2" s="2">
-        <v>1693</v>
+        <v>3639</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>15</v>
@@ -3639,7 +3639,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="2">
-        <v>2763</v>
+        <v>2895</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>15</v>
@@ -3671,7 +3671,7 @@
         <v>14</v>
       </c>
       <c r="F4" s="2">
-        <v>3488</v>
+        <v>3225</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
@@ -3703,7 +3703,7 @@
         <v>14</v>
       </c>
       <c r="F5" s="2">
-        <v>1400</v>
+        <v>1115</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
@@ -3735,7 +3735,7 @@
         <v>14</v>
       </c>
       <c r="F6" s="2">
-        <v>1372</v>
+        <v>3408</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -3767,7 +3767,7 @@
         <v>14</v>
       </c>
       <c r="F7" s="2">
-        <v>1244</v>
+        <v>3935</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -3799,7 +3799,7 @@
         <v>14</v>
       </c>
       <c r="F8" s="2">
-        <v>2751</v>
+        <v>2045</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -3831,7 +3831,7 @@
         <v>14</v>
       </c>
       <c r="F9" s="2">
-        <v>3523</v>
+        <v>4145</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -3863,7 +3863,7 @@
         <v>14</v>
       </c>
       <c r="F10" s="2">
-        <v>1805</v>
+        <v>3852</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
@@ -3895,7 +3895,7 @@
         <v>14</v>
       </c>
       <c r="F11" s="2">
-        <v>3811</v>
+        <v>1119</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
@@ -3927,7 +3927,7 @@
         <v>14</v>
       </c>
       <c r="F12" s="2">
-        <v>1829</v>
+        <v>1467</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
@@ -3959,7 +3959,7 @@
         <v>14</v>
       </c>
       <c r="F13" s="2">
-        <v>1123</v>
+        <v>3694</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -3991,7 +3991,7 @@
         <v>14</v>
       </c>
       <c r="F14" s="2">
-        <v>2733</v>
+        <v>1003</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -4023,7 +4023,7 @@
         <v>14</v>
       </c>
       <c r="F15" s="2">
-        <v>1648</v>
+        <v>1343</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -4055,7 +4055,7 @@
         <v>14</v>
       </c>
       <c r="F16" s="2">
-        <v>828</v>
+        <v>3875</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
@@ -4087,7 +4087,7 @@
         <v>14</v>
       </c>
       <c r="F17" s="2">
-        <v>2736</v>
+        <v>2977</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
@@ -4119,7 +4119,7 @@
         <v>14</v>
       </c>
       <c r="F18" s="2">
-        <v>2115</v>
+        <v>4055</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
@@ -4151,7 +4151,7 @@
         <v>14</v>
       </c>
       <c r="F19" s="2">
-        <v>1912</v>
+        <v>4664</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
@@ -4183,7 +4183,7 @@
         <v>14</v>
       </c>
       <c r="F20" s="2">
-        <v>1479</v>
+        <v>1543</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
@@ -4215,7 +4215,7 @@
         <v>14</v>
       </c>
       <c r="F21" s="2">
-        <v>2920</v>
+        <v>1703</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -4247,7 +4247,7 @@
         <v>14</v>
       </c>
       <c r="F22" s="2">
-        <v>1455</v>
+        <v>1112</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -4279,7 +4279,7 @@
         <v>14</v>
       </c>
       <c r="F23" s="2">
-        <v>2941</v>
+        <v>3040</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -4311,7 +4311,7 @@
         <v>14</v>
       </c>
       <c r="F24" s="2">
-        <v>1315</v>
+        <v>1969</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -4343,7 +4343,7 @@
         <v>14</v>
       </c>
       <c r="F25" s="2">
-        <v>1133</v>
+        <v>1877</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -4375,7 +4375,7 @@
         <v>14</v>
       </c>
       <c r="F26" s="2">
-        <v>4561</v>
+        <v>1774</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -4407,7 +4407,7 @@
         <v>14</v>
       </c>
       <c r="F27" s="2">
-        <v>1944</v>
+        <v>3721</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>15</v>
@@ -4439,7 +4439,7 @@
         <v>14</v>
       </c>
       <c r="F28" s="2">
-        <v>2944</v>
+        <v>3272</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>15</v>
@@ -4471,7 +4471,7 @@
         <v>14</v>
       </c>
       <c r="F29" s="2">
-        <v>2296</v>
+        <v>3033</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>15</v>
@@ -4503,7 +4503,7 @@
         <v>14</v>
       </c>
       <c r="F30" s="2">
-        <v>1904</v>
+        <v>1696</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>15</v>
@@ -4535,7 +4535,7 @@
         <v>14</v>
       </c>
       <c r="F31" s="2">
-        <v>1933</v>
+        <v>819</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>15</v>
@@ -4567,7 +4567,7 @@
         <v>14</v>
       </c>
       <c r="F32" s="2">
-        <v>3045</v>
+        <v>3288</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>15</v>
@@ -4599,7 +4599,7 @@
         <v>14</v>
       </c>
       <c r="F33" s="2">
-        <v>4298</v>
+        <v>2343</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>15</v>
@@ -4631,7 +4631,7 @@
         <v>14</v>
       </c>
       <c r="F34" s="2">
-        <v>3224</v>
+        <v>1024</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>15</v>
@@ -4663,7 +4663,7 @@
         <v>14</v>
       </c>
       <c r="F35" s="2">
-        <v>3466</v>
+        <v>825</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>15</v>
@@ -4695,7 +4695,7 @@
         <v>14</v>
       </c>
       <c r="F36" s="2">
-        <v>3601</v>
+        <v>1640</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>15</v>
@@ -4727,7 +4727,7 @@
         <v>14</v>
       </c>
       <c r="F37" s="2">
-        <v>3129</v>
+        <v>2301</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>15</v>
@@ -4759,7 +4759,7 @@
         <v>14</v>
       </c>
       <c r="F38" s="2">
-        <v>2443</v>
+        <v>3718</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>15</v>
@@ -4791,7 +4791,7 @@
         <v>14</v>
       </c>
       <c r="F39" s="2">
-        <v>1282</v>
+        <v>2933</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>15</v>
@@ -4823,7 +4823,7 @@
         <v>14</v>
       </c>
       <c r="F40" s="2">
-        <v>2877</v>
+        <v>2268</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>15</v>
@@ -4855,7 +4855,7 @@
         <v>14</v>
       </c>
       <c r="F41" s="2">
-        <v>2481</v>
+        <v>2955</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>15</v>
@@ -4887,7 +4887,7 @@
         <v>14</v>
       </c>
       <c r="F42" s="2">
-        <v>1808</v>
+        <v>912</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>15</v>
@@ -4919,7 +4919,7 @@
         <v>14</v>
       </c>
       <c r="F43" s="2">
-        <v>1497</v>
+        <v>3127</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>15</v>
@@ -4951,7 +4951,7 @@
         <v>14</v>
       </c>
       <c r="F44" s="2">
-        <v>4274</v>
+        <v>1017</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>15</v>
@@ -4983,7 +4983,7 @@
         <v>14</v>
       </c>
       <c r="F45" s="2">
-        <v>4783</v>
+        <v>4056</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>15</v>
@@ -5015,7 +5015,7 @@
         <v>14</v>
       </c>
       <c r="F46" s="2">
-        <v>4728</v>
+        <v>2668</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>15</v>
@@ -5047,7 +5047,7 @@
         <v>14</v>
       </c>
       <c r="F47" s="2">
-        <v>4747</v>
+        <v>2378</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>15</v>
@@ -5079,7 +5079,7 @@
         <v>14</v>
       </c>
       <c r="F48" s="2">
-        <v>3881</v>
+        <v>4619</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>15</v>
@@ -5111,7 +5111,7 @@
         <v>14</v>
       </c>
       <c r="F49" s="2">
-        <v>2720</v>
+        <v>3120</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>15</v>
@@ -5143,7 +5143,7 @@
         <v>14</v>
       </c>
       <c r="F50" s="2">
-        <v>1765</v>
+        <v>3893</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>15</v>
@@ -5175,7 +5175,7 @@
         <v>14</v>
       </c>
       <c r="F51" s="2">
-        <v>4230</v>
+        <v>991</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>15</v>
@@ -5207,7 +5207,7 @@
         <v>14</v>
       </c>
       <c r="F52" s="2">
-        <v>1714</v>
+        <v>1563</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>15</v>
@@ -5239,7 +5239,7 @@
         <v>14</v>
       </c>
       <c r="F53" s="2">
-        <v>3046</v>
+        <v>1410</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>15</v>
@@ -5271,7 +5271,7 @@
         <v>14</v>
       </c>
       <c r="F54" s="2">
-        <v>3123</v>
+        <v>4771</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>15</v>
@@ -5303,7 +5303,7 @@
         <v>14</v>
       </c>
       <c r="F55" s="2">
-        <v>3064</v>
+        <v>3054</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>15</v>
@@ -5335,7 +5335,7 @@
         <v>14</v>
       </c>
       <c r="F56" s="2">
-        <v>2153</v>
+        <v>3824</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>15</v>
@@ -5367,7 +5367,7 @@
         <v>14</v>
       </c>
       <c r="F57" s="2">
-        <v>2128</v>
+        <v>2564</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>15</v>
@@ -5399,7 +5399,7 @@
         <v>14</v>
       </c>
       <c r="F58" s="2">
-        <v>1689</v>
+        <v>3155</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>15</v>
@@ -5431,7 +5431,7 @@
         <v>14</v>
       </c>
       <c r="F59" s="2">
-        <v>1105</v>
+        <v>2051</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>15</v>
@@ -5463,7 +5463,7 @@
         <v>14</v>
       </c>
       <c r="F60" s="2">
-        <v>921</v>
+        <v>2716</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>15</v>
@@ -5495,7 +5495,7 @@
         <v>14</v>
       </c>
       <c r="F61" s="2">
-        <v>4083</v>
+        <v>1422</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>15</v>
@@ -5527,7 +5527,7 @@
         <v>14</v>
       </c>
       <c r="F62" s="2">
-        <v>822</v>
+        <v>3896</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>15</v>
@@ -5559,7 +5559,7 @@
         <v>14</v>
       </c>
       <c r="F63" s="2">
-        <v>4181</v>
+        <v>4654</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>15</v>
@@ -5591,7 +5591,7 @@
         <v>14</v>
       </c>
       <c r="F64" s="2">
-        <v>1956</v>
+        <v>2479</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>15</v>
@@ -5623,7 +5623,7 @@
         <v>14</v>
       </c>
       <c r="F65" s="2">
-        <v>3388</v>
+        <v>3792</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>15</v>
@@ -5655,7 +5655,7 @@
         <v>14</v>
       </c>
       <c r="F66" s="2">
-        <v>1901</v>
+        <v>2195</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>15</v>
@@ -5687,7 +5687,7 @@
         <v>14</v>
       </c>
       <c r="F67" s="2">
-        <v>1495</v>
+        <v>3950</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>15</v>
@@ -5719,7 +5719,7 @@
         <v>14</v>
       </c>
       <c r="F68" s="2">
-        <v>1744</v>
+        <v>2625</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>15</v>
@@ -5751,7 +5751,7 @@
         <v>14</v>
       </c>
       <c r="F69" s="2">
-        <v>1858</v>
+        <v>3882</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>15</v>
@@ -5783,7 +5783,7 @@
         <v>14</v>
       </c>
       <c r="F70" s="2">
-        <v>1693</v>
+        <v>1952</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>15</v>
@@ -5815,7 +5815,7 @@
         <v>14</v>
       </c>
       <c r="F71" s="2">
-        <v>3535</v>
+        <v>1931</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>15</v>
@@ -5847,7 +5847,7 @@
         <v>14</v>
       </c>
       <c r="F72" s="2">
-        <v>4646</v>
+        <v>4116</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>15</v>
@@ -5879,7 +5879,7 @@
         <v>14</v>
       </c>
       <c r="F73" s="2">
-        <v>2528</v>
+        <v>3276</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>15</v>
@@ -5911,7 +5911,7 @@
         <v>14</v>
       </c>
       <c r="F74" s="2">
-        <v>2704</v>
+        <v>4540</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>15</v>
@@ -5943,7 +5943,7 @@
         <v>14</v>
       </c>
       <c r="F75" s="2">
-        <v>1421</v>
+        <v>3078</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>15</v>
@@ -5975,7 +5975,7 @@
         <v>14</v>
       </c>
       <c r="F76" s="2">
-        <v>2250</v>
+        <v>2338</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>15</v>
@@ -6007,7 +6007,7 @@
         <v>14</v>
       </c>
       <c r="F77" s="2">
-        <v>2660</v>
+        <v>3266</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>15</v>
@@ -6039,7 +6039,7 @@
         <v>14</v>
       </c>
       <c r="F78" s="2">
-        <v>1146</v>
+        <v>2373</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>15</v>
@@ -6071,7 +6071,7 @@
         <v>14</v>
       </c>
       <c r="F79" s="2">
-        <v>2451</v>
+        <v>908</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>15</v>
@@ -6103,7 +6103,7 @@
         <v>14</v>
       </c>
       <c r="F80" s="2">
-        <v>4165</v>
+        <v>3757</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>15</v>
@@ -6135,7 +6135,7 @@
         <v>14</v>
       </c>
       <c r="F81" s="2">
-        <v>965</v>
+        <v>2629</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>15</v>
@@ -6167,7 +6167,7 @@
         <v>14</v>
       </c>
       <c r="F82" s="2">
-        <v>3162</v>
+        <v>1579</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>15</v>
@@ -6199,7 +6199,7 @@
         <v>14</v>
       </c>
       <c r="F83" s="2">
-        <v>4288</v>
+        <v>853</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>15</v>
@@ -6231,7 +6231,7 @@
         <v>14</v>
       </c>
       <c r="F84" s="2">
-        <v>4510</v>
+        <v>1422</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>15</v>
@@ -6263,7 +6263,7 @@
         <v>14</v>
       </c>
       <c r="F85" s="2">
-        <v>1416</v>
+        <v>3259</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>15</v>
@@ -6295,7 +6295,7 @@
         <v>14</v>
       </c>
       <c r="F86" s="2">
-        <v>2999</v>
+        <v>3672</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>15</v>
@@ -6327,7 +6327,7 @@
         <v>14</v>
       </c>
       <c r="F87" s="2">
-        <v>4227</v>
+        <v>3660</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>15</v>
@@ -6359,7 +6359,7 @@
         <v>14</v>
       </c>
       <c r="F88" s="2">
-        <v>3790</v>
+        <v>3386</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>15</v>
@@ -6391,7 +6391,7 @@
         <v>14</v>
       </c>
       <c r="F89" s="2">
-        <v>1019</v>
+        <v>3384</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>15</v>
@@ -6423,7 +6423,7 @@
         <v>14</v>
       </c>
       <c r="F90" s="2">
-        <v>3377</v>
+        <v>2905</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>15</v>
@@ -6455,7 +6455,7 @@
         <v>14</v>
       </c>
       <c r="F91" s="2">
-        <v>3281</v>
+        <v>4642</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>15</v>
@@ -6487,7 +6487,7 @@
         <v>14</v>
       </c>
       <c r="F92" s="2">
-        <v>1607</v>
+        <v>4475</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>15</v>
@@ -6519,7 +6519,7 @@
         <v>14</v>
       </c>
       <c r="F93" s="2">
-        <v>3767</v>
+        <v>1011</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>15</v>
@@ -6551,7 +6551,7 @@
         <v>14</v>
       </c>
       <c r="F94" s="2">
-        <v>4431</v>
+        <v>1481</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>15</v>
@@ -6583,7 +6583,7 @@
         <v>14</v>
       </c>
       <c r="F95" s="2">
-        <v>899</v>
+        <v>3193</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>15</v>
@@ -6615,7 +6615,7 @@
         <v>14</v>
       </c>
       <c r="F96" s="2">
-        <v>1148</v>
+        <v>823</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>15</v>
@@ -6647,7 +6647,7 @@
         <v>14</v>
       </c>
       <c r="F97" s="2">
-        <v>1335</v>
+        <v>2981</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>15</v>
@@ -6679,7 +6679,7 @@
         <v>14</v>
       </c>
       <c r="F98" s="2">
-        <v>1730</v>
+        <v>3681</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>15</v>
@@ -6711,7 +6711,7 @@
         <v>14</v>
       </c>
       <c r="F99" s="2">
-        <v>3319</v>
+        <v>1823</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>15</v>
@@ -6743,7 +6743,7 @@
         <v>14</v>
       </c>
       <c r="F100" s="2">
-        <v>3628</v>
+        <v>3640</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>15</v>
@@ -6775,7 +6775,7 @@
         <v>14</v>
       </c>
       <c r="F101" s="2">
-        <v>2120</v>
+        <v>2992</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>15</v>
@@ -6807,7 +6807,7 @@
         <v>14</v>
       </c>
       <c r="F102" s="2">
-        <v>3973</v>
+        <v>4150</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>15</v>
@@ -6839,7 +6839,7 @@
         <v>14</v>
       </c>
       <c r="F103" s="2">
-        <v>2470</v>
+        <v>4439</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>15</v>
@@ -6871,7 +6871,7 @@
         <v>14</v>
       </c>
       <c r="F104" s="2">
-        <v>2598</v>
+        <v>2013</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>15</v>
@@ -6903,7 +6903,7 @@
         <v>14</v>
       </c>
       <c r="F105" s="2">
-        <v>2973</v>
+        <v>2005</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>15</v>
@@ -6935,7 +6935,7 @@
         <v>14</v>
       </c>
       <c r="F106" s="2">
-        <v>3687</v>
+        <v>4799</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>15</v>
@@ -6967,7 +6967,7 @@
         <v>14</v>
       </c>
       <c r="F107" s="2">
-        <v>3958</v>
+        <v>1484</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>15</v>
@@ -6999,7 +6999,7 @@
         <v>14</v>
       </c>
       <c r="F108" s="2">
-        <v>3127</v>
+        <v>1609</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>15</v>
@@ -7031,7 +7031,7 @@
         <v>14</v>
       </c>
       <c r="F109" s="2">
-        <v>1809</v>
+        <v>1413</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>15</v>
@@ -7063,7 +7063,7 @@
         <v>14</v>
       </c>
       <c r="F110" s="2">
-        <v>1798</v>
+        <v>3635</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>15</v>
@@ -7095,7 +7095,7 @@
         <v>14</v>
       </c>
       <c r="F111" s="2">
-        <v>2261</v>
+        <v>2916</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>15</v>
@@ -7127,7 +7127,7 @@
         <v>14</v>
       </c>
       <c r="F112" s="2">
-        <v>866</v>
+        <v>1488</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>15</v>
@@ -7159,7 +7159,7 @@
         <v>14</v>
       </c>
       <c r="F113" s="2">
-        <v>1339</v>
+        <v>3565</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>15</v>
@@ -7191,7 +7191,7 @@
         <v>14</v>
       </c>
       <c r="F114" s="2">
-        <v>4395</v>
+        <v>2080</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>15</v>
@@ -7223,7 +7223,7 @@
         <v>14</v>
       </c>
       <c r="F115" s="2">
-        <v>2927</v>
+        <v>4591</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>15</v>
@@ -7255,7 +7255,7 @@
         <v>14</v>
       </c>
       <c r="F116" s="2">
-        <v>3087</v>
+        <v>844</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>15</v>
@@ -7287,7 +7287,7 @@
         <v>14</v>
       </c>
       <c r="F117" s="2">
-        <v>2127</v>
+        <v>3876</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>15</v>
@@ -7319,7 +7319,7 @@
         <v>14</v>
       </c>
       <c r="F118" s="2">
-        <v>3532</v>
+        <v>3172</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>15</v>
@@ -7351,7 +7351,7 @@
         <v>14</v>
       </c>
       <c r="F119" s="2">
-        <v>2646</v>
+        <v>3854</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>15</v>
@@ -7383,7 +7383,7 @@
         <v>14</v>
       </c>
       <c r="F120" s="2">
-        <v>2500</v>
+        <v>3742</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>15</v>
@@ -7415,7 +7415,7 @@
         <v>14</v>
       </c>
       <c r="F121" s="2">
-        <v>2825</v>
+        <v>1349</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>15</v>
@@ -7447,7 +7447,7 @@
         <v>14</v>
       </c>
       <c r="F122" s="2">
-        <v>3584</v>
+        <v>1093</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>15</v>
@@ -7479,7 +7479,7 @@
         <v>14</v>
       </c>
       <c r="F123" s="2">
-        <v>2358</v>
+        <v>2824</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>15</v>
@@ -7511,7 +7511,7 @@
         <v>14</v>
       </c>
       <c r="F124" s="2">
-        <v>3369</v>
+        <v>2649</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>15</v>
@@ -7543,7 +7543,7 @@
         <v>14</v>
       </c>
       <c r="F125" s="2">
-        <v>2444</v>
+        <v>4015</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>15</v>
@@ -7575,7 +7575,7 @@
         <v>14</v>
       </c>
       <c r="F126" s="2">
-        <v>3099</v>
+        <v>2500</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>15</v>
@@ -7607,7 +7607,7 @@
         <v>14</v>
       </c>
       <c r="F127" s="2">
-        <v>3107</v>
+        <v>2978</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>15</v>
@@ -7639,7 +7639,7 @@
         <v>14</v>
       </c>
       <c r="F128" s="2">
-        <v>804</v>
+        <v>3113</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>15</v>
@@ -7671,7 +7671,7 @@
         <v>14</v>
       </c>
       <c r="F129" s="2">
-        <v>1562</v>
+        <v>1931</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>15</v>
@@ -7703,7 +7703,7 @@
         <v>14</v>
       </c>
       <c r="F130" s="2">
-        <v>3447</v>
+        <v>2426</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>15</v>
@@ -7735,7 +7735,7 @@
         <v>14</v>
       </c>
       <c r="F131" s="2">
-        <v>3770</v>
+        <v>983</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>15</v>
@@ -7767,7 +7767,7 @@
         <v>14</v>
       </c>
       <c r="F132" s="2">
-        <v>4546</v>
+        <v>4301</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>15</v>
@@ -7799,7 +7799,7 @@
         <v>14</v>
       </c>
       <c r="F133" s="2">
-        <v>2026</v>
+        <v>2713</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>15</v>
@@ -7831,7 +7831,7 @@
         <v>14</v>
       </c>
       <c r="F134" s="2">
-        <v>2154</v>
+        <v>4540</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>15</v>
@@ -7863,7 +7863,7 @@
         <v>14</v>
       </c>
       <c r="F135" s="2">
-        <v>3915</v>
+        <v>1541</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>15</v>
@@ -7895,7 +7895,7 @@
         <v>14</v>
       </c>
       <c r="F136" s="2">
-        <v>3087</v>
+        <v>2320</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>15</v>
@@ -7927,7 +7927,7 @@
         <v>14</v>
       </c>
       <c r="F137" s="2">
-        <v>3851</v>
+        <v>1409</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>15</v>
@@ -7959,7 +7959,7 @@
         <v>14</v>
       </c>
       <c r="F138" s="2">
-        <v>4408</v>
+        <v>2297</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>15</v>
@@ -7991,7 +7991,7 @@
         <v>14</v>
       </c>
       <c r="F139" s="2">
-        <v>2519</v>
+        <v>2387</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>15</v>
@@ -8023,7 +8023,7 @@
         <v>14</v>
       </c>
       <c r="F140" s="2">
-        <v>2913</v>
+        <v>3440</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>15</v>
@@ -8055,7 +8055,7 @@
         <v>14</v>
       </c>
       <c r="F141" s="2">
-        <v>2712</v>
+        <v>4029</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>15</v>
@@ -8087,7 +8087,7 @@
         <v>14</v>
       </c>
       <c r="F142" s="2">
-        <v>931</v>
+        <v>1562</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>15</v>
@@ -8119,7 +8119,7 @@
         <v>14</v>
       </c>
       <c r="F143" s="2">
-        <v>1754</v>
+        <v>2930</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>15</v>
@@ -8151,7 +8151,7 @@
         <v>14</v>
       </c>
       <c r="F144" s="2">
-        <v>996</v>
+        <v>1323</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>15</v>
@@ -8183,7 +8183,7 @@
         <v>14</v>
       </c>
       <c r="F145" s="2">
-        <v>3557</v>
+        <v>4470</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>15</v>
@@ -8215,7 +8215,7 @@
         <v>14</v>
       </c>
       <c r="F146" s="2">
-        <v>1916</v>
+        <v>4068</v>
       </c>
       <c r="G146" s="2" t="s">
         <v>15</v>
@@ -8247,7 +8247,7 @@
         <v>14</v>
       </c>
       <c r="F147" s="2">
-        <v>1396</v>
+        <v>1264</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>15</v>
@@ -8279,7 +8279,7 @@
         <v>14</v>
       </c>
       <c r="F148" s="2">
-        <v>826</v>
+        <v>3935</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>15</v>
@@ -8311,7 +8311,7 @@
         <v>14</v>
       </c>
       <c r="F149" s="2">
-        <v>2649</v>
+        <v>2633</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>15</v>
@@ -8343,7 +8343,7 @@
         <v>14</v>
       </c>
       <c r="F150" s="2">
-        <v>3247</v>
+        <v>2150</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>15</v>
@@ -8375,7 +8375,7 @@
         <v>14</v>
       </c>
       <c r="F151" s="2">
-        <v>4589</v>
+        <v>2928</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>15</v>
@@ -8407,7 +8407,7 @@
         <v>14</v>
       </c>
       <c r="F152" s="2">
-        <v>4711</v>
+        <v>1531</v>
       </c>
       <c r="G152" s="2" t="s">
         <v>15</v>
@@ -8439,7 +8439,7 @@
         <v>14</v>
       </c>
       <c r="F153" s="2">
-        <v>1370</v>
+        <v>4396</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>15</v>
@@ -8471,7 +8471,7 @@
         <v>14</v>
       </c>
       <c r="F154" s="2">
-        <v>2841</v>
+        <v>1559</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>15</v>
@@ -8503,7 +8503,7 @@
         <v>14</v>
       </c>
       <c r="F155" s="2">
-        <v>4779</v>
+        <v>1284</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>15</v>
@@ -8535,7 +8535,7 @@
         <v>14</v>
       </c>
       <c r="F156" s="2">
-        <v>1895</v>
+        <v>1682</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>15</v>
@@ -8567,7 +8567,7 @@
         <v>14</v>
       </c>
       <c r="F157" s="2">
-        <v>4531</v>
+        <v>2140</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>15</v>
@@ -8599,7 +8599,7 @@
         <v>14</v>
       </c>
       <c r="F158" s="2">
-        <v>2123</v>
+        <v>2990</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>15</v>
@@ -8631,7 +8631,7 @@
         <v>14</v>
       </c>
       <c r="F159" s="2">
-        <v>1856</v>
+        <v>4605</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>15</v>
@@ -8663,7 +8663,7 @@
         <v>14</v>
       </c>
       <c r="F160" s="2">
-        <v>3338</v>
+        <v>2855</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>15</v>
@@ -8695,7 +8695,7 @@
         <v>14</v>
       </c>
       <c r="F161" s="2">
-        <v>1991</v>
+        <v>3484</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>15</v>
@@ -8727,7 +8727,7 @@
         <v>14</v>
       </c>
       <c r="F162" s="2">
-        <v>3896</v>
+        <v>1745</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>15</v>
@@ -8759,7 +8759,7 @@
         <v>14</v>
       </c>
       <c r="F163" s="2">
-        <v>3887</v>
+        <v>2677</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>15</v>
@@ -8791,7 +8791,7 @@
         <v>14</v>
       </c>
       <c r="F164" s="2">
-        <v>3695</v>
+        <v>941</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>15</v>
@@ -8823,7 +8823,7 @@
         <v>14</v>
       </c>
       <c r="F165" s="2">
-        <v>2889</v>
+        <v>4508</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>15</v>
@@ -8855,7 +8855,7 @@
         <v>14</v>
       </c>
       <c r="F166" s="2">
-        <v>3328</v>
+        <v>4401</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>15</v>
@@ -8887,7 +8887,7 @@
         <v>14</v>
       </c>
       <c r="F167" s="2">
-        <v>1514</v>
+        <v>1442</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>15</v>
@@ -8919,7 +8919,7 @@
         <v>14</v>
       </c>
       <c r="F168" s="2">
-        <v>3203</v>
+        <v>2933</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>15</v>
@@ -8951,7 +8951,7 @@
         <v>14</v>
       </c>
       <c r="F169" s="2">
-        <v>4772</v>
+        <v>857</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>15</v>
@@ -8983,7 +8983,7 @@
         <v>14</v>
       </c>
       <c r="F170" s="2">
-        <v>4353</v>
+        <v>1383</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>15</v>
@@ -9015,7 +9015,7 @@
         <v>14</v>
       </c>
       <c r="F171" s="2">
-        <v>4739</v>
+        <v>1264</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>15</v>
@@ -9047,7 +9047,7 @@
         <v>14</v>
       </c>
       <c r="F172" s="2">
-        <v>4626</v>
+        <v>4496</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>15</v>
@@ -9079,7 +9079,7 @@
         <v>14</v>
       </c>
       <c r="F173" s="2">
-        <v>1541</v>
+        <v>1309</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>15</v>
@@ -9111,7 +9111,7 @@
         <v>14</v>
       </c>
       <c r="F174" s="2">
-        <v>2648</v>
+        <v>4069</v>
       </c>
       <c r="G174" s="2" t="s">
         <v>15</v>
@@ -9143,7 +9143,7 @@
         <v>14</v>
       </c>
       <c r="F175" s="2">
-        <v>1492</v>
+        <v>3481</v>
       </c>
       <c r="G175" s="2" t="s">
         <v>15</v>
@@ -9175,7 +9175,7 @@
         <v>14</v>
       </c>
       <c r="F176" s="2">
-        <v>3512</v>
+        <v>2994</v>
       </c>
       <c r="G176" s="2" t="s">
         <v>15</v>
@@ -9207,7 +9207,7 @@
         <v>14</v>
       </c>
       <c r="F177" s="2">
-        <v>4237</v>
+        <v>2581</v>
       </c>
       <c r="G177" s="2" t="s">
         <v>15</v>
@@ -9239,7 +9239,7 @@
         <v>14</v>
       </c>
       <c r="F178" s="2">
-        <v>882</v>
+        <v>3908</v>
       </c>
       <c r="G178" s="2" t="s">
         <v>15</v>
@@ -9271,7 +9271,7 @@
         <v>14</v>
       </c>
       <c r="F179" s="2">
-        <v>4788</v>
+        <v>2294</v>
       </c>
       <c r="G179" s="2" t="s">
         <v>15</v>
@@ -9303,7 +9303,7 @@
         <v>14</v>
       </c>
       <c r="F180" s="2">
-        <v>2969</v>
+        <v>2516</v>
       </c>
       <c r="G180" s="2" t="s">
         <v>15</v>
@@ -9335,7 +9335,7 @@
         <v>14</v>
       </c>
       <c r="F181" s="2">
-        <v>829</v>
+        <v>2086</v>
       </c>
       <c r="G181" s="2" t="s">
         <v>15</v>
@@ -9367,7 +9367,7 @@
         <v>14</v>
       </c>
       <c r="F182" s="2">
-        <v>1599</v>
+        <v>1412</v>
       </c>
       <c r="G182" s="2" t="s">
         <v>15</v>
@@ -9399,7 +9399,7 @@
         <v>14</v>
       </c>
       <c r="F183" s="2">
-        <v>2563</v>
+        <v>3189</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>15</v>
@@ -9431,7 +9431,7 @@
         <v>14</v>
       </c>
       <c r="F184" s="2">
-        <v>2878</v>
+        <v>3348</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>15</v>
@@ -9463,7 +9463,7 @@
         <v>14</v>
       </c>
       <c r="F185" s="2">
-        <v>3283</v>
+        <v>3444</v>
       </c>
       <c r="G185" s="2" t="s">
         <v>15</v>
@@ -9495,7 +9495,7 @@
         <v>14</v>
       </c>
       <c r="F186" s="2">
-        <v>4098</v>
+        <v>2463</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>15</v>
@@ -9527,7 +9527,7 @@
         <v>14</v>
       </c>
       <c r="F187" s="2">
-        <v>2167</v>
+        <v>1580</v>
       </c>
       <c r="G187" s="2" t="s">
         <v>15</v>
@@ -9559,7 +9559,7 @@
         <v>14</v>
       </c>
       <c r="F188" s="2">
-        <v>3075</v>
+        <v>3805</v>
       </c>
       <c r="G188" s="2" t="s">
         <v>15</v>
@@ -9591,7 +9591,7 @@
         <v>14</v>
       </c>
       <c r="F189" s="2">
-        <v>3947</v>
+        <v>2048</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>15</v>
@@ -9623,7 +9623,7 @@
         <v>14</v>
       </c>
       <c r="F190" s="2">
-        <v>1567</v>
+        <v>2284</v>
       </c>
       <c r="G190" s="2" t="s">
         <v>15</v>
@@ -9655,7 +9655,7 @@
         <v>14</v>
       </c>
       <c r="F191" s="2">
-        <v>1689</v>
+        <v>4687</v>
       </c>
       <c r="G191" s="2" t="s">
         <v>15</v>
@@ -9687,7 +9687,7 @@
         <v>14</v>
       </c>
       <c r="F192" s="2">
-        <v>3217</v>
+        <v>1871</v>
       </c>
       <c r="G192" s="2" t="s">
         <v>15</v>
@@ -9719,7 +9719,7 @@
         <v>14</v>
       </c>
       <c r="F193" s="2">
-        <v>1060</v>
+        <v>4333</v>
       </c>
       <c r="G193" s="2" t="s">
         <v>15</v>
@@ -9751,7 +9751,7 @@
         <v>14</v>
       </c>
       <c r="F194" s="2">
-        <v>902</v>
+        <v>2206</v>
       </c>
       <c r="G194" s="2" t="s">
         <v>15</v>
@@ -9783,7 +9783,7 @@
         <v>14</v>
       </c>
       <c r="F195" s="2">
-        <v>2583</v>
+        <v>3526</v>
       </c>
       <c r="G195" s="2" t="s">
         <v>15</v>
@@ -9815,7 +9815,7 @@
         <v>14</v>
       </c>
       <c r="F196" s="2">
-        <v>1578</v>
+        <v>4373</v>
       </c>
       <c r="G196" s="2" t="s">
         <v>15</v>
@@ -9847,7 +9847,7 @@
         <v>14</v>
       </c>
       <c r="F197" s="2">
-        <v>1793</v>
+        <v>4320</v>
       </c>
       <c r="G197" s="2" t="s">
         <v>15</v>
@@ -9879,7 +9879,7 @@
         <v>14</v>
       </c>
       <c r="F198" s="2">
-        <v>1832</v>
+        <v>2349</v>
       </c>
       <c r="G198" s="2" t="s">
         <v>15</v>
@@ -9911,7 +9911,7 @@
         <v>14</v>
       </c>
       <c r="F199" s="2">
-        <v>2802</v>
+        <v>3391</v>
       </c>
       <c r="G199" s="2" t="s">
         <v>15</v>
@@ -9943,7 +9943,7 @@
         <v>14</v>
       </c>
       <c r="F200" s="2">
-        <v>1380</v>
+        <v>4274</v>
       </c>
       <c r="G200" s="2" t="s">
         <v>15</v>
@@ -9975,7 +9975,7 @@
         <v>14</v>
       </c>
       <c r="F201" s="2">
-        <v>3607</v>
+        <v>3317</v>
       </c>
       <c r="G201" s="2" t="s">
         <v>15</v>
@@ -10007,7 +10007,7 @@
         <v>14</v>
       </c>
       <c r="F202" s="2">
-        <v>1775</v>
+        <v>2712</v>
       </c>
       <c r="G202" s="2" t="s">
         <v>15</v>
@@ -10039,7 +10039,7 @@
         <v>14</v>
       </c>
       <c r="F203" s="2">
-        <v>1248</v>
+        <v>4625</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>15</v>
@@ -10071,7 +10071,7 @@
         <v>14</v>
       </c>
       <c r="F204" s="2">
-        <v>4704</v>
+        <v>2669</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>15</v>
@@ -10103,7 +10103,7 @@
         <v>14</v>
       </c>
       <c r="F205" s="2">
-        <v>1939</v>
+        <v>2425</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>15</v>
@@ -10135,7 +10135,7 @@
         <v>14</v>
       </c>
       <c r="F206" s="2">
-        <v>3755</v>
+        <v>3779</v>
       </c>
       <c r="G206" s="2" t="s">
         <v>15</v>
@@ -10167,7 +10167,7 @@
         <v>14</v>
       </c>
       <c r="F207" s="2">
-        <v>4787</v>
+        <v>1733</v>
       </c>
       <c r="G207" s="2" t="s">
         <v>15</v>
@@ -10199,7 +10199,7 @@
         <v>14</v>
       </c>
       <c r="F208" s="2">
-        <v>1693</v>
+        <v>2010</v>
       </c>
       <c r="G208" s="2" t="s">
         <v>15</v>
@@ -10231,7 +10231,7 @@
         <v>14</v>
       </c>
       <c r="F209" s="2">
-        <v>2755</v>
+        <v>4674</v>
       </c>
       <c r="G209" s="2" t="s">
         <v>15</v>
@@ -10263,7 +10263,7 @@
         <v>14</v>
       </c>
       <c r="F210" s="2">
-        <v>3825</v>
+        <v>1305</v>
       </c>
       <c r="G210" s="2" t="s">
         <v>15</v>
@@ -10295,7 +10295,7 @@
         <v>14</v>
       </c>
       <c r="F211" s="2">
-        <v>2642</v>
+        <v>3286</v>
       </c>
       <c r="G211" s="2" t="s">
         <v>15</v>
@@ -10327,7 +10327,7 @@
         <v>14</v>
       </c>
       <c r="F212" s="2">
-        <v>996</v>
+        <v>1307</v>
       </c>
       <c r="G212" s="2" t="s">
         <v>15</v>
@@ -10359,7 +10359,7 @@
         <v>14</v>
       </c>
       <c r="F213" s="2">
-        <v>4725</v>
+        <v>3553</v>
       </c>
       <c r="G213" s="2" t="s">
         <v>15</v>
@@ -10391,7 +10391,7 @@
         <v>14</v>
       </c>
       <c r="F214" s="2">
-        <v>987</v>
+        <v>2812</v>
       </c>
       <c r="G214" s="2" t="s">
         <v>15</v>
@@ -10423,7 +10423,7 @@
         <v>14</v>
       </c>
       <c r="F215" s="2">
-        <v>1654</v>
+        <v>989</v>
       </c>
       <c r="G215" s="2" t="s">
         <v>15</v>
@@ -10455,7 +10455,7 @@
         <v>14</v>
       </c>
       <c r="F216" s="2">
-        <v>2327</v>
+        <v>2181</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>15</v>
@@ -10487,7 +10487,7 @@
         <v>14</v>
       </c>
       <c r="F217" s="2">
-        <v>1472</v>
+        <v>2945</v>
       </c>
       <c r="G217" s="2" t="s">
         <v>15</v>
@@ -10519,7 +10519,7 @@
         <v>14</v>
       </c>
       <c r="F218" s="2">
-        <v>3318</v>
+        <v>3770</v>
       </c>
       <c r="G218" s="2" t="s">
         <v>15</v>
@@ -10551,7 +10551,7 @@
         <v>14</v>
       </c>
       <c r="F219" s="2">
-        <v>4336</v>
+        <v>4531</v>
       </c>
       <c r="G219" s="2" t="s">
         <v>15</v>
@@ -10583,7 +10583,7 @@
         <v>14</v>
       </c>
       <c r="F220" s="2">
-        <v>4616</v>
+        <v>4158</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>15</v>
@@ -10615,7 +10615,7 @@
         <v>14</v>
       </c>
       <c r="F221" s="2">
-        <v>3223</v>
+        <v>3592</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>15</v>
@@ -10647,7 +10647,7 @@
         <v>14</v>
       </c>
       <c r="F222" s="2">
-        <v>3040</v>
+        <v>2911</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>15</v>
@@ -10679,7 +10679,7 @@
         <v>14</v>
       </c>
       <c r="F223" s="2">
-        <v>864</v>
+        <v>4742</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>15</v>
@@ -10711,7 +10711,7 @@
         <v>14</v>
       </c>
       <c r="F224" s="2">
-        <v>1338</v>
+        <v>3070</v>
       </c>
       <c r="G224" s="2" t="s">
         <v>15</v>
@@ -10743,7 +10743,7 @@
         <v>14</v>
       </c>
       <c r="F225" s="2">
-        <v>2781</v>
+        <v>1640</v>
       </c>
       <c r="G225" s="2" t="s">
         <v>15</v>
@@ -10775,7 +10775,7 @@
         <v>14</v>
       </c>
       <c r="F226" s="2">
-        <v>3320</v>
+        <v>2033</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>15</v>
@@ -10807,7 +10807,7 @@
         <v>14</v>
       </c>
       <c r="F227" s="2">
-        <v>2164</v>
+        <v>3494</v>
       </c>
       <c r="G227" s="2" t="s">
         <v>15</v>
@@ -10839,7 +10839,7 @@
         <v>14</v>
       </c>
       <c r="F228" s="2">
-        <v>3847</v>
+        <v>2133</v>
       </c>
       <c r="G228" s="2" t="s">
         <v>15</v>
@@ -10871,7 +10871,7 @@
         <v>14</v>
       </c>
       <c r="F229" s="2">
-        <v>4735</v>
+        <v>2284</v>
       </c>
       <c r="G229" s="2" t="s">
         <v>15</v>
@@ -10903,7 +10903,7 @@
         <v>14</v>
       </c>
       <c r="F230" s="2">
-        <v>3537</v>
+        <v>3516</v>
       </c>
       <c r="G230" s="2" t="s">
         <v>15</v>
@@ -10935,7 +10935,7 @@
         <v>14</v>
       </c>
       <c r="F231" s="2">
-        <v>2780</v>
+        <v>2952</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>15</v>
@@ -10967,7 +10967,7 @@
         <v>14</v>
       </c>
       <c r="F232" s="2">
-        <v>1273</v>
+        <v>1554</v>
       </c>
       <c r="G232" s="2" t="s">
         <v>15</v>
@@ -10999,7 +10999,7 @@
         <v>14</v>
       </c>
       <c r="F233" s="2">
-        <v>1000</v>
+        <v>4647</v>
       </c>
       <c r="G233" s="2" t="s">
         <v>15</v>
@@ -11031,7 +11031,7 @@
         <v>14</v>
       </c>
       <c r="F234" s="2">
-        <v>980</v>
+        <v>1604</v>
       </c>
       <c r="G234" s="2" t="s">
         <v>15</v>
@@ -11063,7 +11063,7 @@
         <v>14</v>
       </c>
       <c r="F235" s="2">
-        <v>1534</v>
+        <v>4316</v>
       </c>
       <c r="G235" s="2" t="s">
         <v>15</v>
@@ -11095,7 +11095,7 @@
         <v>14</v>
       </c>
       <c r="F236" s="2">
-        <v>1035</v>
+        <v>2343</v>
       </c>
       <c r="G236" s="2" t="s">
         <v>15</v>
@@ -11127,7 +11127,7 @@
         <v>14</v>
       </c>
       <c r="F237" s="2">
-        <v>4563</v>
+        <v>1452</v>
       </c>
       <c r="G237" s="2" t="s">
         <v>15</v>
@@ -11159,7 +11159,7 @@
         <v>14</v>
       </c>
       <c r="F238" s="2">
-        <v>3779</v>
+        <v>2138</v>
       </c>
       <c r="G238" s="2" t="s">
         <v>15</v>
@@ -11191,7 +11191,7 @@
         <v>14</v>
       </c>
       <c r="F239" s="2">
-        <v>1171</v>
+        <v>4168</v>
       </c>
       <c r="G239" s="2" t="s">
         <v>15</v>
@@ -11223,7 +11223,7 @@
         <v>14</v>
       </c>
       <c r="F240" s="2">
-        <v>4086</v>
+        <v>1250</v>
       </c>
       <c r="G240" s="2" t="s">
         <v>15</v>
@@ -11255,7 +11255,7 @@
         <v>14</v>
       </c>
       <c r="F241" s="2">
-        <v>4367</v>
+        <v>1422</v>
       </c>
       <c r="G241" s="2" t="s">
         <v>15</v>
@@ -11287,7 +11287,7 @@
         <v>14</v>
       </c>
       <c r="F242" s="2">
-        <v>1304</v>
+        <v>3097</v>
       </c>
       <c r="G242" s="2" t="s">
         <v>15</v>
@@ -11319,7 +11319,7 @@
         <v>14</v>
       </c>
       <c r="F243" s="2">
-        <v>2489</v>
+        <v>2843</v>
       </c>
       <c r="G243" s="2" t="s">
         <v>15</v>
@@ -11351,7 +11351,7 @@
         <v>14</v>
       </c>
       <c r="F244" s="2">
-        <v>2512</v>
+        <v>3177</v>
       </c>
       <c r="G244" s="2" t="s">
         <v>15</v>
@@ -11383,7 +11383,7 @@
         <v>14</v>
       </c>
       <c r="F245" s="2">
-        <v>2455</v>
+        <v>2359</v>
       </c>
       <c r="G245" s="2" t="s">
         <v>15</v>
@@ -11415,7 +11415,7 @@
         <v>14</v>
       </c>
       <c r="F246" s="2">
-        <v>4405</v>
+        <v>2728</v>
       </c>
       <c r="G246" s="2" t="s">
         <v>15</v>
@@ -11447,7 +11447,7 @@
         <v>14</v>
       </c>
       <c r="F247" s="2">
-        <v>3937</v>
+        <v>1416</v>
       </c>
       <c r="G247" s="2" t="s">
         <v>15</v>
@@ -11479,7 +11479,7 @@
         <v>14</v>
       </c>
       <c r="F248" s="2">
-        <v>1222</v>
+        <v>4654</v>
       </c>
       <c r="G248" s="2" t="s">
         <v>15</v>
@@ -11511,7 +11511,7 @@
         <v>14</v>
       </c>
       <c r="F249" s="2">
-        <v>1771</v>
+        <v>1722</v>
       </c>
       <c r="G249" s="2" t="s">
         <v>15</v>
@@ -11543,7 +11543,7 @@
         <v>14</v>
       </c>
       <c r="F250" s="2">
-        <v>3512</v>
+        <v>3977</v>
       </c>
       <c r="G250" s="2" t="s">
         <v>15</v>
@@ -11575,7 +11575,7 @@
         <v>14</v>
       </c>
       <c r="F251" s="2">
-        <v>3379</v>
+        <v>3336</v>
       </c>
       <c r="G251" s="2" t="s">
         <v>15</v>
@@ -11607,7 +11607,7 @@
         <v>14</v>
       </c>
       <c r="F252" s="2">
-        <v>2621</v>
+        <v>4251</v>
       </c>
       <c r="G252" s="2" t="s">
         <v>15</v>
@@ -11639,7 +11639,7 @@
         <v>14</v>
       </c>
       <c r="F253" s="2">
-        <v>2146</v>
+        <v>2676</v>
       </c>
       <c r="G253" s="2" t="s">
         <v>15</v>
@@ -11671,7 +11671,7 @@
         <v>14</v>
       </c>
       <c r="F254" s="2">
-        <v>1819</v>
+        <v>1996</v>
       </c>
       <c r="G254" s="2" t="s">
         <v>15</v>
@@ -11703,7 +11703,7 @@
         <v>14</v>
       </c>
       <c r="F255" s="2">
-        <v>4650</v>
+        <v>1770</v>
       </c>
       <c r="G255" s="2" t="s">
         <v>15</v>
@@ -11735,7 +11735,7 @@
         <v>14</v>
       </c>
       <c r="F256" s="2">
-        <v>1434</v>
+        <v>1820</v>
       </c>
       <c r="G256" s="2" t="s">
         <v>15</v>
@@ -11767,7 +11767,7 @@
         <v>14</v>
       </c>
       <c r="F257" s="2">
-        <v>2467</v>
+        <v>4490</v>
       </c>
       <c r="G257" s="2" t="s">
         <v>15</v>
@@ -11799,7 +11799,7 @@
         <v>14</v>
       </c>
       <c r="F258" s="2">
-        <v>1901</v>
+        <v>3876</v>
       </c>
       <c r="G258" s="2" t="s">
         <v>15</v>
@@ -11831,7 +11831,7 @@
         <v>14</v>
       </c>
       <c r="F259" s="2">
-        <v>1597</v>
+        <v>3163</v>
       </c>
       <c r="G259" s="2" t="s">
         <v>15</v>
@@ -11863,7 +11863,7 @@
         <v>14</v>
       </c>
       <c r="F260" s="2">
-        <v>2487</v>
+        <v>1722</v>
       </c>
       <c r="G260" s="2" t="s">
         <v>15</v>
@@ -11895,7 +11895,7 @@
         <v>14</v>
       </c>
       <c r="F261" s="2">
-        <v>3134</v>
+        <v>2499</v>
       </c>
       <c r="G261" s="2" t="s">
         <v>15</v>
@@ -11927,7 +11927,7 @@
         <v>14</v>
       </c>
       <c r="F262" s="2">
-        <v>2421</v>
+        <v>910</v>
       </c>
       <c r="G262" s="2" t="s">
         <v>15</v>
@@ -11959,7 +11959,7 @@
         <v>14</v>
       </c>
       <c r="F263" s="2">
-        <v>2337</v>
+        <v>2702</v>
       </c>
       <c r="G263" s="2" t="s">
         <v>15</v>
@@ -11991,7 +11991,7 @@
         <v>14</v>
       </c>
       <c r="F264" s="2">
-        <v>1267</v>
+        <v>4643</v>
       </c>
       <c r="G264" s="2" t="s">
         <v>15</v>
@@ -12023,7 +12023,7 @@
         <v>14</v>
       </c>
       <c r="F265" s="2">
-        <v>1490</v>
+        <v>2863</v>
       </c>
       <c r="G265" s="2" t="s">
         <v>15</v>
@@ -12055,7 +12055,7 @@
         <v>14</v>
       </c>
       <c r="F266" s="2">
-        <v>3669</v>
+        <v>2547</v>
       </c>
       <c r="G266" s="2" t="s">
         <v>15</v>
@@ -12087,7 +12087,7 @@
         <v>14</v>
       </c>
       <c r="F267" s="2">
-        <v>2660</v>
+        <v>4108</v>
       </c>
       <c r="G267" s="2" t="s">
         <v>15</v>
@@ -12119,7 +12119,7 @@
         <v>14</v>
       </c>
       <c r="F268" s="2">
-        <v>3770</v>
+        <v>4154</v>
       </c>
       <c r="G268" s="2" t="s">
         <v>15</v>
@@ -12151,7 +12151,7 @@
         <v>14</v>
       </c>
       <c r="F269" s="2">
-        <v>2780</v>
+        <v>3642</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>15</v>
@@ -12183,7 +12183,7 @@
         <v>14</v>
       </c>
       <c r="F270" s="2">
-        <v>4576</v>
+        <v>4628</v>
       </c>
       <c r="G270" s="2" t="s">
         <v>15</v>
@@ -12215,7 +12215,7 @@
         <v>14</v>
       </c>
       <c r="F271" s="2">
-        <v>1518</v>
+        <v>3318</v>
       </c>
       <c r="G271" s="2" t="s">
         <v>15</v>
@@ -12247,7 +12247,7 @@
         <v>14</v>
       </c>
       <c r="F272" s="2">
-        <v>3792</v>
+        <v>1957</v>
       </c>
       <c r="G272" s="2" t="s">
         <v>15</v>
@@ -12279,7 +12279,7 @@
         <v>14</v>
       </c>
       <c r="F273" s="2">
-        <v>2752</v>
+        <v>3930</v>
       </c>
       <c r="G273" s="2" t="s">
         <v>15</v>
@@ -12311,7 +12311,7 @@
         <v>14</v>
       </c>
       <c r="F274" s="2">
-        <v>4082</v>
+        <v>3987</v>
       </c>
       <c r="G274" s="2" t="s">
         <v>15</v>
@@ -12343,7 +12343,7 @@
         <v>14</v>
       </c>
       <c r="F275" s="2">
-        <v>1449</v>
+        <v>4345</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>15</v>
@@ -12375,7 +12375,7 @@
         <v>14</v>
       </c>
       <c r="F276" s="2">
-        <v>4308</v>
+        <v>1921</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>15</v>
@@ -12407,7 +12407,7 @@
         <v>14</v>
       </c>
       <c r="F277" s="2">
-        <v>4712</v>
+        <v>1253</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>15</v>
@@ -12439,7 +12439,7 @@
         <v>14</v>
       </c>
       <c r="F278" s="2">
-        <v>2008</v>
+        <v>2022</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>15</v>
@@ -12471,7 +12471,7 @@
         <v>14</v>
       </c>
       <c r="F279" s="2">
-        <v>3013</v>
+        <v>2998</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>15</v>
@@ -12503,7 +12503,7 @@
         <v>14</v>
       </c>
       <c r="F280" s="2">
-        <v>3187</v>
+        <v>3613</v>
       </c>
       <c r="G280" s="2" t="s">
         <v>15</v>
@@ -12535,7 +12535,7 @@
         <v>14</v>
       </c>
       <c r="F281" s="2">
-        <v>2340</v>
+        <v>807</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>15</v>
@@ -12567,7 +12567,7 @@
         <v>14</v>
       </c>
       <c r="F282" s="2">
-        <v>860</v>
+        <v>4471</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>15</v>
@@ -12599,7 +12599,7 @@
         <v>14</v>
       </c>
       <c r="F283" s="2">
-        <v>1154</v>
+        <v>3254</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>15</v>
@@ -12631,7 +12631,7 @@
         <v>14</v>
       </c>
       <c r="F284" s="2">
-        <v>1256</v>
+        <v>4358</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>15</v>
@@ -12663,7 +12663,7 @@
         <v>14</v>
       </c>
       <c r="F285" s="2">
-        <v>3173</v>
+        <v>1124</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>15</v>
@@ -12695,7 +12695,7 @@
         <v>14</v>
       </c>
       <c r="F286" s="2">
-        <v>1962</v>
+        <v>1101</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>15</v>
@@ -12727,7 +12727,7 @@
         <v>14</v>
       </c>
       <c r="F287" s="2">
-        <v>986</v>
+        <v>3255</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>15</v>
@@ -12759,7 +12759,7 @@
         <v>14</v>
       </c>
       <c r="F288" s="2">
-        <v>2447</v>
+        <v>3697</v>
       </c>
       <c r="G288" s="2" t="s">
         <v>15</v>
@@ -12791,7 +12791,7 @@
         <v>14</v>
       </c>
       <c r="F289" s="2">
-        <v>2781</v>
+        <v>4281</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>15</v>
@@ -12823,7 +12823,7 @@
         <v>14</v>
       </c>
       <c r="F290" s="2">
-        <v>3049</v>
+        <v>1054</v>
       </c>
       <c r="G290" s="2" t="s">
         <v>15</v>
@@ -12855,7 +12855,7 @@
         <v>14</v>
       </c>
       <c r="F291" s="2">
-        <v>4730</v>
+        <v>2897</v>
       </c>
       <c r="G291" s="2" t="s">
         <v>15</v>
@@ -12887,7 +12887,7 @@
         <v>14</v>
       </c>
       <c r="F292" s="2">
-        <v>834</v>
+        <v>1373</v>
       </c>
       <c r="G292" s="2" t="s">
         <v>15</v>
@@ -12919,7 +12919,7 @@
         <v>14</v>
       </c>
       <c r="F293" s="2">
-        <v>1405</v>
+        <v>887</v>
       </c>
       <c r="G293" s="2" t="s">
         <v>15</v>
@@ -12951,7 +12951,7 @@
         <v>14</v>
       </c>
       <c r="F294" s="2">
-        <v>3634</v>
+        <v>2040</v>
       </c>
       <c r="G294" s="2" t="s">
         <v>15</v>
@@ -12983,7 +12983,7 @@
         <v>14</v>
       </c>
       <c r="F295" s="2">
-        <v>4254</v>
+        <v>4415</v>
       </c>
       <c r="G295" s="2" t="s">
         <v>15</v>
@@ -13015,7 +13015,7 @@
         <v>14</v>
       </c>
       <c r="F296" s="2">
-        <v>1094</v>
+        <v>2494</v>
       </c>
       <c r="G296" s="2" t="s">
         <v>15</v>
@@ -13047,7 +13047,7 @@
         <v>14</v>
       </c>
       <c r="F297" s="2">
-        <v>3193</v>
+        <v>1742</v>
       </c>
       <c r="G297" s="2" t="s">
         <v>15</v>
@@ -13079,7 +13079,7 @@
         <v>14</v>
       </c>
       <c r="F298" s="2">
-        <v>4132</v>
+        <v>1798</v>
       </c>
       <c r="G298" s="2" t="s">
         <v>15</v>
@@ -13111,7 +13111,7 @@
         <v>14</v>
       </c>
       <c r="F299" s="2">
-        <v>1380</v>
+        <v>3553</v>
       </c>
       <c r="G299" s="2" t="s">
         <v>15</v>
@@ -13143,7 +13143,7 @@
         <v>14</v>
       </c>
       <c r="F300" s="2">
-        <v>873</v>
+        <v>1723</v>
       </c>
       <c r="G300" s="2" t="s">
         <v>15</v>
@@ -13175,7 +13175,7 @@
         <v>14</v>
       </c>
       <c r="F301" s="2">
-        <v>1152</v>
+        <v>2306</v>
       </c>
       <c r="G301" s="2" t="s">
         <v>15</v>
@@ -13207,7 +13207,7 @@
         <v>14</v>
       </c>
       <c r="F302" s="2">
-        <v>4240</v>
+        <v>3825</v>
       </c>
       <c r="G302" s="2" t="s">
         <v>15</v>
@@ -13239,7 +13239,7 @@
         <v>14</v>
       </c>
       <c r="F303" s="2">
-        <v>3786</v>
+        <v>3748</v>
       </c>
       <c r="G303" s="2" t="s">
         <v>15</v>
@@ -13271,7 +13271,7 @@
         <v>14</v>
       </c>
       <c r="F304" s="2">
-        <v>1565</v>
+        <v>4042</v>
       </c>
       <c r="G304" s="2" t="s">
         <v>15</v>
@@ -13303,7 +13303,7 @@
         <v>14</v>
       </c>
       <c r="F305" s="2">
-        <v>3948</v>
+        <v>1718</v>
       </c>
       <c r="G305" s="2" t="s">
         <v>15</v>
@@ -13335,7 +13335,7 @@
         <v>14</v>
       </c>
       <c r="F306" s="2">
-        <v>1533</v>
+        <v>2459</v>
       </c>
       <c r="G306" s="2" t="s">
         <v>15</v>
@@ -13367,7 +13367,7 @@
         <v>14</v>
       </c>
       <c r="F307" s="2">
-        <v>2890</v>
+        <v>3958</v>
       </c>
       <c r="G307" s="2" t="s">
         <v>15</v>
@@ -13399,7 +13399,7 @@
         <v>14</v>
       </c>
       <c r="F308" s="2">
-        <v>2989</v>
+        <v>3693</v>
       </c>
       <c r="G308" s="2" t="s">
         <v>15</v>
@@ -13431,7 +13431,7 @@
         <v>14</v>
       </c>
       <c r="F309" s="2">
-        <v>1814</v>
+        <v>2395</v>
       </c>
       <c r="G309" s="2" t="s">
         <v>15</v>
@@ -13463,7 +13463,7 @@
         <v>14</v>
       </c>
       <c r="F310" s="2">
-        <v>3068</v>
+        <v>1596</v>
       </c>
       <c r="G310" s="2" t="s">
         <v>15</v>
@@ -13495,7 +13495,7 @@
         <v>14</v>
       </c>
       <c r="F311" s="2">
-        <v>3033</v>
+        <v>4551</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>15</v>
@@ -13527,7 +13527,7 @@
         <v>14</v>
       </c>
       <c r="F312" s="2">
-        <v>3715</v>
+        <v>1825</v>
       </c>
       <c r="G312" s="2" t="s">
         <v>15</v>
@@ -13559,7 +13559,7 @@
         <v>14</v>
       </c>
       <c r="F313" s="2">
-        <v>3016</v>
+        <v>948</v>
       </c>
       <c r="G313" s="2" t="s">
         <v>15</v>
@@ -13591,7 +13591,7 @@
         <v>14</v>
       </c>
       <c r="F314" s="2">
-        <v>4382</v>
+        <v>1711</v>
       </c>
       <c r="G314" s="2" t="s">
         <v>15</v>
@@ -13623,7 +13623,7 @@
         <v>14</v>
       </c>
       <c r="F315" s="2">
-        <v>3241</v>
+        <v>980</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>15</v>
@@ -13655,7 +13655,7 @@
         <v>14</v>
       </c>
       <c r="F316" s="2">
-        <v>3841</v>
+        <v>1981</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>15</v>
@@ -13687,7 +13687,7 @@
         <v>14</v>
       </c>
       <c r="F317" s="2">
-        <v>4285</v>
+        <v>4536</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>15</v>
@@ -13719,7 +13719,7 @@
         <v>14</v>
       </c>
       <c r="F318" s="2">
-        <v>2176</v>
+        <v>2435</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>15</v>
@@ -13751,7 +13751,7 @@
         <v>14</v>
       </c>
       <c r="F319" s="2">
-        <v>4589</v>
+        <v>3880</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>15</v>
@@ -13783,7 +13783,7 @@
         <v>14</v>
       </c>
       <c r="F320" s="2">
-        <v>4576</v>
+        <v>2877</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>15</v>
@@ -13815,7 +13815,7 @@
         <v>14</v>
       </c>
       <c r="F321" s="2">
-        <v>4680</v>
+        <v>1338</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>15</v>
@@ -13847,7 +13847,7 @@
         <v>14</v>
       </c>
       <c r="F322" s="2">
-        <v>4080</v>
+        <v>3047</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>15</v>
@@ -13879,7 +13879,7 @@
         <v>14</v>
       </c>
       <c r="F323" s="2">
-        <v>4777</v>
+        <v>3459</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>15</v>
@@ -13911,7 +13911,7 @@
         <v>14</v>
       </c>
       <c r="F324" s="2">
-        <v>1336</v>
+        <v>4687</v>
       </c>
       <c r="G324" s="2" t="s">
         <v>15</v>
@@ -13943,7 +13943,7 @@
         <v>14</v>
       </c>
       <c r="F325" s="2">
-        <v>2545</v>
+        <v>2614</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>15</v>
@@ -13975,7 +13975,7 @@
         <v>14</v>
       </c>
       <c r="F326" s="2">
-        <v>4636</v>
+        <v>1026</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>15</v>
@@ -14007,7 +14007,7 @@
         <v>14</v>
       </c>
       <c r="F327" s="2">
-        <v>3769</v>
+        <v>2096</v>
       </c>
       <c r="G327" s="2" t="s">
         <v>15</v>
@@ -14039,7 +14039,7 @@
         <v>14</v>
       </c>
       <c r="F328" s="2">
-        <v>3441</v>
+        <v>2464</v>
       </c>
       <c r="G328" s="2" t="s">
         <v>15</v>
@@ -14071,7 +14071,7 @@
         <v>14</v>
       </c>
       <c r="F329" s="2">
-        <v>2624</v>
+        <v>2928</v>
       </c>
       <c r="G329" s="2" t="s">
         <v>15</v>
@@ -14103,7 +14103,7 @@
         <v>14</v>
       </c>
       <c r="F330" s="2">
-        <v>3485</v>
+        <v>4415</v>
       </c>
       <c r="G330" s="2" t="s">
         <v>15</v>
@@ -14135,7 +14135,7 @@
         <v>14</v>
       </c>
       <c r="F331" s="2">
-        <v>3422</v>
+        <v>4562</v>
       </c>
       <c r="G331" s="2" t="s">
         <v>15</v>
@@ -14167,7 +14167,7 @@
         <v>14</v>
       </c>
       <c r="F332" s="2">
-        <v>2592</v>
+        <v>1700</v>
       </c>
       <c r="G332" s="2" t="s">
         <v>15</v>
@@ -14199,7 +14199,7 @@
         <v>14</v>
       </c>
       <c r="F333" s="2">
-        <v>4724</v>
+        <v>3357</v>
       </c>
       <c r="G333" s="2" t="s">
         <v>15</v>
@@ -14231,7 +14231,7 @@
         <v>14</v>
       </c>
       <c r="F334" s="2">
-        <v>4528</v>
+        <v>1863</v>
       </c>
       <c r="G334" s="2" t="s">
         <v>15</v>
@@ -14263,7 +14263,7 @@
         <v>14</v>
       </c>
       <c r="F335" s="2">
-        <v>4125</v>
+        <v>3474</v>
       </c>
       <c r="G335" s="2" t="s">
         <v>15</v>
@@ -14295,7 +14295,7 @@
         <v>14</v>
       </c>
       <c r="F336" s="2">
-        <v>4022</v>
+        <v>4591</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>15</v>
@@ -14327,7 +14327,7 @@
         <v>14</v>
       </c>
       <c r="F337" s="2">
-        <v>2858</v>
+        <v>3919</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>15</v>
@@ -14359,7 +14359,7 @@
         <v>14</v>
       </c>
       <c r="F338" s="2">
-        <v>1240</v>
+        <v>4643</v>
       </c>
       <c r="G338" s="2" t="s">
         <v>15</v>
@@ -14391,7 +14391,7 @@
         <v>14</v>
       </c>
       <c r="F339" s="2">
-        <v>3100</v>
+        <v>3323</v>
       </c>
       <c r="G339" s="2" t="s">
         <v>15</v>
@@ -14423,7 +14423,7 @@
         <v>14</v>
       </c>
       <c r="F340" s="2">
-        <v>2081</v>
+        <v>4243</v>
       </c>
       <c r="G340" s="2" t="s">
         <v>15</v>
@@ -14455,7 +14455,7 @@
         <v>14</v>
       </c>
       <c r="F341" s="2">
-        <v>4569</v>
+        <v>3662</v>
       </c>
       <c r="G341" s="2" t="s">
         <v>15</v>
@@ -14487,7 +14487,7 @@
         <v>14</v>
       </c>
       <c r="F342" s="2">
-        <v>4709</v>
+        <v>1394</v>
       </c>
       <c r="G342" s="2" t="s">
         <v>15</v>
@@ -14519,7 +14519,7 @@
         <v>14</v>
       </c>
       <c r="F343" s="2">
-        <v>3788</v>
+        <v>4344</v>
       </c>
       <c r="G343" s="2" t="s">
         <v>15</v>
@@ -14551,7 +14551,7 @@
         <v>14</v>
       </c>
       <c r="F344" s="2">
-        <v>2648</v>
+        <v>1842</v>
       </c>
       <c r="G344" s="2" t="s">
         <v>15</v>
@@ -14583,7 +14583,7 @@
         <v>14</v>
       </c>
       <c r="F345" s="2">
-        <v>3902</v>
+        <v>4693</v>
       </c>
       <c r="G345" s="2" t="s">
         <v>15</v>
@@ -14615,7 +14615,7 @@
         <v>14</v>
       </c>
       <c r="F346" s="2">
-        <v>2406</v>
+        <v>3347</v>
       </c>
       <c r="G346" s="2" t="s">
         <v>15</v>
@@ -14647,7 +14647,7 @@
         <v>14</v>
       </c>
       <c r="F347" s="2">
-        <v>1244</v>
+        <v>4243</v>
       </c>
       <c r="G347" s="2" t="s">
         <v>15</v>
@@ -14679,7 +14679,7 @@
         <v>14</v>
       </c>
       <c r="F348" s="2">
-        <v>2079</v>
+        <v>4316</v>
       </c>
       <c r="G348" s="2" t="s">
         <v>15</v>
@@ -14711,7 +14711,7 @@
         <v>14</v>
       </c>
       <c r="F349" s="2">
-        <v>886</v>
+        <v>2481</v>
       </c>
       <c r="G349" s="2" t="s">
         <v>15</v>
@@ -14743,7 +14743,7 @@
         <v>14</v>
       </c>
       <c r="F350" s="2">
-        <v>4373</v>
+        <v>2343</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>15</v>
@@ -14775,7 +14775,7 @@
         <v>14</v>
       </c>
       <c r="F351" s="2">
-        <v>847</v>
+        <v>932</v>
       </c>
       <c r="G351" s="2" t="s">
         <v>15</v>
@@ -14807,7 +14807,7 @@
         <v>14</v>
       </c>
       <c r="F352" s="2">
-        <v>3842</v>
+        <v>1877</v>
       </c>
       <c r="G352" s="2" t="s">
         <v>15</v>
@@ -14839,7 +14839,7 @@
         <v>14</v>
       </c>
       <c r="F353" s="2">
-        <v>1466</v>
+        <v>3878</v>
       </c>
       <c r="G353" s="2" t="s">
         <v>15</v>
@@ -14871,7 +14871,7 @@
         <v>14</v>
       </c>
       <c r="F354" s="2">
-        <v>3293</v>
+        <v>2023</v>
       </c>
       <c r="G354" s="2" t="s">
         <v>15</v>
@@ -14903,7 +14903,7 @@
         <v>14</v>
       </c>
       <c r="F355" s="2">
-        <v>4531</v>
+        <v>3351</v>
       </c>
       <c r="G355" s="2" t="s">
         <v>15</v>
@@ -14935,7 +14935,7 @@
         <v>14</v>
       </c>
       <c r="F356" s="2">
-        <v>1494</v>
+        <v>1610</v>
       </c>
       <c r="G356" s="2" t="s">
         <v>15</v>
@@ -14967,7 +14967,7 @@
         <v>14</v>
       </c>
       <c r="F357" s="2">
-        <v>3265</v>
+        <v>4169</v>
       </c>
       <c r="G357" s="2" t="s">
         <v>15</v>
@@ -14999,7 +14999,7 @@
         <v>14</v>
       </c>
       <c r="F358" s="2">
-        <v>4437</v>
+        <v>3435</v>
       </c>
       <c r="G358" s="2" t="s">
         <v>15</v>
@@ -15031,7 +15031,7 @@
         <v>14</v>
       </c>
       <c r="F359" s="2">
-        <v>2560</v>
+        <v>3926</v>
       </c>
       <c r="G359" s="2" t="s">
         <v>15</v>
@@ -15063,7 +15063,7 @@
         <v>14</v>
       </c>
       <c r="F360" s="2">
-        <v>3463</v>
+        <v>3200</v>
       </c>
       <c r="G360" s="2" t="s">
         <v>15</v>
@@ -15095,7 +15095,7 @@
         <v>14</v>
       </c>
       <c r="F361" s="2">
-        <v>2541</v>
+        <v>3023</v>
       </c>
       <c r="G361" s="2" t="s">
         <v>15</v>
@@ -15127,7 +15127,7 @@
         <v>14</v>
       </c>
       <c r="F362" s="2">
-        <v>4594</v>
+        <v>4262</v>
       </c>
       <c r="G362" s="2" t="s">
         <v>15</v>
@@ -15159,7 +15159,7 @@
         <v>14</v>
       </c>
       <c r="F363" s="2">
-        <v>2644</v>
+        <v>4163</v>
       </c>
       <c r="G363" s="2" t="s">
         <v>15</v>
@@ -15191,7 +15191,7 @@
         <v>14</v>
       </c>
       <c r="F364" s="2">
-        <v>3293</v>
+        <v>2145</v>
       </c>
       <c r="G364" s="2" t="s">
         <v>15</v>
@@ -15223,7 +15223,7 @@
         <v>14</v>
       </c>
       <c r="F365" s="2">
-        <v>2247</v>
+        <v>1426</v>
       </c>
       <c r="G365" s="2" t="s">
         <v>15</v>
@@ -15255,7 +15255,7 @@
         <v>14</v>
       </c>
       <c r="F366" s="2">
-        <v>4418</v>
+        <v>2739</v>
       </c>
       <c r="G366" s="2" t="s">
         <v>15</v>
@@ -15287,7 +15287,7 @@
         <v>14</v>
       </c>
       <c r="F367" s="2">
-        <v>4193</v>
+        <v>4777</v>
       </c>
       <c r="G367" s="2" t="s">
         <v>15</v>
@@ -15319,7 +15319,7 @@
         <v>14</v>
       </c>
       <c r="F368" s="2">
-        <v>1182</v>
+        <v>2027</v>
       </c>
       <c r="G368" s="2" t="s">
         <v>15</v>
@@ -15351,7 +15351,7 @@
         <v>14</v>
       </c>
       <c r="F369" s="2">
-        <v>1360</v>
+        <v>3574</v>
       </c>
       <c r="G369" s="2" t="s">
         <v>15</v>
@@ -15383,7 +15383,7 @@
         <v>14</v>
       </c>
       <c r="F370" s="2">
-        <v>3616</v>
+        <v>2746</v>
       </c>
       <c r="G370" s="2" t="s">
         <v>15</v>
@@ -15415,7 +15415,7 @@
         <v>14</v>
       </c>
       <c r="F371" s="2">
-        <v>3303</v>
+        <v>3676</v>
       </c>
       <c r="G371" s="2" t="s">
         <v>15</v>
@@ -15447,7 +15447,7 @@
         <v>14</v>
       </c>
       <c r="F372" s="2">
-        <v>1425</v>
+        <v>2155</v>
       </c>
       <c r="G372" s="2" t="s">
         <v>15</v>
@@ -15479,7 +15479,7 @@
         <v>14</v>
       </c>
       <c r="F373" s="2">
-        <v>3463</v>
+        <v>1410</v>
       </c>
       <c r="G373" s="2" t="s">
         <v>15</v>
@@ -15511,7 +15511,7 @@
         <v>14</v>
       </c>
       <c r="F374" s="2">
-        <v>2794</v>
+        <v>4289</v>
       </c>
       <c r="G374" s="2" t="s">
         <v>15</v>
@@ -15543,7 +15543,7 @@
         <v>14</v>
       </c>
       <c r="F375" s="2">
-        <v>3892</v>
+        <v>3804</v>
       </c>
       <c r="G375" s="2" t="s">
         <v>15</v>
@@ -15575,7 +15575,7 @@
         <v>14</v>
       </c>
       <c r="F376" s="2">
-        <v>3303</v>
+        <v>4341</v>
       </c>
       <c r="G376" s="2" t="s">
         <v>15</v>
@@ -15607,7 +15607,7 @@
         <v>14</v>
       </c>
       <c r="F377" s="2">
-        <v>826</v>
+        <v>1605</v>
       </c>
       <c r="G377" s="2" t="s">
         <v>15</v>
@@ -15639,7 +15639,7 @@
         <v>14</v>
       </c>
       <c r="F378" s="2">
-        <v>1413</v>
+        <v>3466</v>
       </c>
       <c r="G378" s="2" t="s">
         <v>15</v>
@@ -15671,7 +15671,7 @@
         <v>14</v>
       </c>
       <c r="F379" s="2">
-        <v>4269</v>
+        <v>4511</v>
       </c>
       <c r="G379" s="2" t="s">
         <v>15</v>
@@ -15703,7 +15703,7 @@
         <v>14</v>
       </c>
       <c r="F380" s="2">
-        <v>4532</v>
+        <v>1605</v>
       </c>
       <c r="G380" s="2" t="s">
         <v>15</v>
@@ -15735,7 +15735,7 @@
         <v>14</v>
       </c>
       <c r="F381" s="2">
-        <v>990</v>
+        <v>3584</v>
       </c>
       <c r="G381" s="2" t="s">
         <v>15</v>
@@ -15767,7 +15767,7 @@
         <v>14</v>
       </c>
       <c r="F382" s="2">
-        <v>3756</v>
+        <v>881</v>
       </c>
       <c r="G382" s="2" t="s">
         <v>15</v>
@@ -15799,7 +15799,7 @@
         <v>14</v>
       </c>
       <c r="F383" s="2">
-        <v>4552</v>
+        <v>2372</v>
       </c>
       <c r="G383" s="2" t="s">
         <v>15</v>
@@ -15831,7 +15831,7 @@
         <v>14</v>
       </c>
       <c r="F384" s="2">
-        <v>2810</v>
+        <v>4743</v>
       </c>
       <c r="G384" s="2" t="s">
         <v>15</v>
@@ -15863,7 +15863,7 @@
         <v>14</v>
       </c>
       <c r="F385" s="2">
-        <v>4454</v>
+        <v>3690</v>
       </c>
       <c r="G385" s="2" t="s">
         <v>15</v>
@@ -15895,7 +15895,7 @@
         <v>14</v>
       </c>
       <c r="F386" s="2">
-        <v>2727</v>
+        <v>1886</v>
       </c>
       <c r="G386" s="2" t="s">
         <v>15</v>
@@ -15927,7 +15927,7 @@
         <v>14</v>
       </c>
       <c r="F387" s="2">
-        <v>2029</v>
+        <v>2744</v>
       </c>
       <c r="G387" s="2" t="s">
         <v>15</v>
@@ -15959,7 +15959,7 @@
         <v>14</v>
       </c>
       <c r="F388" s="2">
-        <v>2372</v>
+        <v>1616</v>
       </c>
       <c r="G388" s="2" t="s">
         <v>15</v>
@@ -15991,7 +15991,7 @@
         <v>14</v>
       </c>
       <c r="F389" s="2">
-        <v>3264</v>
+        <v>3729</v>
       </c>
       <c r="G389" s="2" t="s">
         <v>15</v>
@@ -16023,7 +16023,7 @@
         <v>14</v>
       </c>
       <c r="F390" s="2">
-        <v>4590</v>
+        <v>2901</v>
       </c>
       <c r="G390" s="2" t="s">
         <v>15</v>
@@ -16055,7 +16055,7 @@
         <v>14</v>
       </c>
       <c r="F391" s="2">
-        <v>3366</v>
+        <v>1763</v>
       </c>
       <c r="G391" s="2" t="s">
         <v>15</v>
@@ -16087,7 +16087,7 @@
         <v>14</v>
       </c>
       <c r="F392" s="2">
-        <v>3193</v>
+        <v>2508</v>
       </c>
       <c r="G392" s="2" t="s">
         <v>15</v>
@@ -16119,7 +16119,7 @@
         <v>14</v>
       </c>
       <c r="F393" s="2">
-        <v>1374</v>
+        <v>4065</v>
       </c>
       <c r="G393" s="2" t="s">
         <v>15</v>
@@ -16151,7 +16151,7 @@
         <v>14</v>
       </c>
       <c r="F394" s="2">
-        <v>1423</v>
+        <v>1782</v>
       </c>
       <c r="G394" s="2" t="s">
         <v>15</v>
@@ -16183,7 +16183,7 @@
         <v>14</v>
       </c>
       <c r="F395" s="2">
-        <v>2934</v>
+        <v>3820</v>
       </c>
       <c r="G395" s="2" t="s">
         <v>15</v>
@@ -16215,7 +16215,7 @@
         <v>14</v>
       </c>
       <c r="F396" s="2">
-        <v>3168</v>
+        <v>3924</v>
       </c>
       <c r="G396" s="2" t="s">
         <v>15</v>
@@ -16247,7 +16247,7 @@
         <v>14</v>
       </c>
       <c r="F397" s="2">
-        <v>2985</v>
+        <v>2202</v>
       </c>
       <c r="G397" s="2" t="s">
         <v>15</v>
@@ -16279,7 +16279,7 @@
         <v>14</v>
       </c>
       <c r="F398" s="2">
-        <v>2987</v>
+        <v>3389</v>
       </c>
       <c r="G398" s="2" t="s">
         <v>15</v>
@@ -16311,7 +16311,7 @@
         <v>14</v>
       </c>
       <c r="F399" s="2">
-        <v>3049</v>
+        <v>1459</v>
       </c>
       <c r="G399" s="2" t="s">
         <v>15</v>
@@ -16343,7 +16343,7 @@
         <v>14</v>
       </c>
       <c r="F400" s="2">
-        <v>1107</v>
+        <v>2506</v>
       </c>
       <c r="G400" s="2" t="s">
         <v>15</v>
@@ -16375,7 +16375,7 @@
         <v>14</v>
       </c>
       <c r="F401" s="2">
-        <v>2478</v>
+        <v>3798</v>
       </c>
       <c r="G401" s="2" t="s">
         <v>15</v>
@@ -16407,7 +16407,7 @@
         <v>14</v>
       </c>
       <c r="F402" s="2">
-        <v>3648</v>
+        <v>4518</v>
       </c>
       <c r="G402" s="2" t="s">
         <v>15</v>
@@ -16439,7 +16439,7 @@
         <v>14</v>
       </c>
       <c r="F403" s="2">
-        <v>3803</v>
+        <v>2416</v>
       </c>
       <c r="G403" s="2" t="s">
         <v>15</v>
@@ -16471,7 +16471,7 @@
         <v>14</v>
       </c>
       <c r="F404" s="2">
-        <v>1767</v>
+        <v>1249</v>
       </c>
       <c r="G404" s="2" t="s">
         <v>15</v>
@@ -16503,7 +16503,7 @@
         <v>14</v>
       </c>
       <c r="F405" s="2">
-        <v>3038</v>
+        <v>4430</v>
       </c>
       <c r="G405" s="2" t="s">
         <v>15</v>
@@ -16535,7 +16535,7 @@
         <v>14</v>
       </c>
       <c r="F406" s="2">
-        <v>1358</v>
+        <v>4657</v>
       </c>
       <c r="G406" s="2" t="s">
         <v>15</v>
@@ -16567,7 +16567,7 @@
         <v>14</v>
       </c>
       <c r="F407" s="2">
-        <v>3005</v>
+        <v>2057</v>
       </c>
       <c r="G407" s="2" t="s">
         <v>15</v>
@@ -16599,7 +16599,7 @@
         <v>14</v>
       </c>
       <c r="F408" s="2">
-        <v>4329</v>
+        <v>3691</v>
       </c>
       <c r="G408" s="2" t="s">
         <v>15</v>
@@ -16631,7 +16631,7 @@
         <v>14</v>
       </c>
       <c r="F409" s="2">
-        <v>1083</v>
+        <v>4418</v>
       </c>
       <c r="G409" s="2" t="s">
         <v>15</v>
@@ -16663,7 +16663,7 @@
         <v>14</v>
       </c>
       <c r="F410" s="2">
-        <v>3948</v>
+        <v>2407</v>
       </c>
       <c r="G410" s="2" t="s">
         <v>15</v>
@@ -16695,7 +16695,7 @@
         <v>14</v>
       </c>
       <c r="F411" s="2">
-        <v>1136</v>
+        <v>886</v>
       </c>
       <c r="G411" s="2" t="s">
         <v>15</v>
@@ -16727,7 +16727,7 @@
         <v>14</v>
       </c>
       <c r="F412" s="2">
-        <v>2358</v>
+        <v>1245</v>
       </c>
       <c r="G412" s="2" t="s">
         <v>15</v>
@@ -16759,7 +16759,7 @@
         <v>14</v>
       </c>
       <c r="F413" s="2">
-        <v>2529</v>
+        <v>1606</v>
       </c>
       <c r="G413" s="2" t="s">
         <v>15</v>
@@ -16791,7 +16791,7 @@
         <v>14</v>
       </c>
       <c r="F414" s="2">
-        <v>3387</v>
+        <v>1886</v>
       </c>
       <c r="G414" s="2" t="s">
         <v>15</v>
@@ -16823,7 +16823,7 @@
         <v>14</v>
       </c>
       <c r="F415" s="2">
-        <v>4242</v>
+        <v>2356</v>
       </c>
       <c r="G415" s="2" t="s">
         <v>15</v>
@@ -16855,7 +16855,7 @@
         <v>14</v>
       </c>
       <c r="F416" s="2">
-        <v>1774</v>
+        <v>3075</v>
       </c>
       <c r="G416" s="2" t="s">
         <v>15</v>
@@ -16887,7 +16887,7 @@
         <v>14</v>
       </c>
       <c r="F417" s="2">
-        <v>3070</v>
+        <v>4305</v>
       </c>
       <c r="G417" s="2" t="s">
         <v>15</v>
@@ -16919,7 +16919,7 @@
         <v>14</v>
       </c>
       <c r="F418" s="2">
-        <v>2875</v>
+        <v>4026</v>
       </c>
       <c r="G418" s="2" t="s">
         <v>15</v>
@@ -16951,7 +16951,7 @@
         <v>14</v>
       </c>
       <c r="F419" s="2">
-        <v>2336</v>
+        <v>4787</v>
       </c>
       <c r="G419" s="2" t="s">
         <v>15</v>
@@ -16983,7 +16983,7 @@
         <v>14</v>
       </c>
       <c r="F420" s="2">
-        <v>2650</v>
+        <v>1465</v>
       </c>
       <c r="G420" s="2" t="s">
         <v>15</v>
@@ -17015,7 +17015,7 @@
         <v>14</v>
       </c>
       <c r="F421" s="2">
-        <v>1803</v>
+        <v>1251</v>
       </c>
       <c r="G421" s="2" t="s">
         <v>15</v>
@@ -17047,7 +17047,7 @@
         <v>14</v>
       </c>
       <c r="F422" s="2">
-        <v>4086</v>
+        <v>3593</v>
       </c>
       <c r="G422" s="2" t="s">
         <v>15</v>
@@ -17079,7 +17079,7 @@
         <v>14</v>
       </c>
       <c r="F423" s="2">
-        <v>1645</v>
+        <v>961</v>
       </c>
       <c r="G423" s="2" t="s">
         <v>15</v>
@@ -17111,7 +17111,7 @@
         <v>14</v>
       </c>
       <c r="F424" s="2">
-        <v>4207</v>
+        <v>4561</v>
       </c>
       <c r="G424" s="2" t="s">
         <v>15</v>
@@ -17143,7 +17143,7 @@
         <v>14</v>
       </c>
       <c r="F425" s="2">
-        <v>2967</v>
+        <v>3789</v>
       </c>
       <c r="G425" s="2" t="s">
         <v>15</v>
@@ -17175,7 +17175,7 @@
         <v>14</v>
       </c>
       <c r="F426" s="2">
-        <v>1766</v>
+        <v>1865</v>
       </c>
       <c r="G426" s="2" t="s">
         <v>15</v>
@@ -17207,7 +17207,7 @@
         <v>14</v>
       </c>
       <c r="F427" s="2">
-        <v>2784</v>
+        <v>3054</v>
       </c>
       <c r="G427" s="2" t="s">
         <v>15</v>
@@ -17239,7 +17239,7 @@
         <v>14</v>
       </c>
       <c r="F428" s="2">
-        <v>3858</v>
+        <v>3806</v>
       </c>
       <c r="G428" s="2" t="s">
         <v>15</v>
@@ -17271,7 +17271,7 @@
         <v>14</v>
       </c>
       <c r="F429" s="2">
-        <v>1997</v>
+        <v>3632</v>
       </c>
       <c r="G429" s="2" t="s">
         <v>15</v>
@@ -17303,7 +17303,7 @@
         <v>14</v>
       </c>
       <c r="F430" s="2">
-        <v>1561</v>
+        <v>1278</v>
       </c>
       <c r="G430" s="2" t="s">
         <v>15</v>
@@ -17335,7 +17335,7 @@
         <v>14</v>
       </c>
       <c r="F431" s="2">
-        <v>3287</v>
+        <v>1961</v>
       </c>
       <c r="G431" s="2" t="s">
         <v>15</v>
@@ -17367,7 +17367,7 @@
         <v>14</v>
       </c>
       <c r="F432" s="2">
-        <v>1290</v>
+        <v>4477</v>
       </c>
       <c r="G432" s="2" t="s">
         <v>15</v>
@@ -17399,7 +17399,7 @@
         <v>14</v>
       </c>
       <c r="F433" s="2">
-        <v>3390</v>
+        <v>4396</v>
       </c>
       <c r="G433" s="2" t="s">
         <v>15</v>
@@ -17431,7 +17431,7 @@
         <v>14</v>
       </c>
       <c r="F434" s="2">
-        <v>1202</v>
+        <v>4580</v>
       </c>
       <c r="G434" s="2" t="s">
         <v>15</v>
@@ -17463,7 +17463,7 @@
         <v>14</v>
       </c>
       <c r="F435" s="2">
-        <v>3986</v>
+        <v>3548</v>
       </c>
       <c r="G435" s="2" t="s">
         <v>15</v>
@@ -17495,7 +17495,7 @@
         <v>14</v>
       </c>
       <c r="F436" s="2">
-        <v>2351</v>
+        <v>2282</v>
       </c>
       <c r="G436" s="2" t="s">
         <v>15</v>
@@ -17527,7 +17527,7 @@
         <v>14</v>
       </c>
       <c r="F437" s="2">
-        <v>2069</v>
+        <v>4593</v>
       </c>
       <c r="G437" s="2" t="s">
         <v>15</v>
@@ -17559,7 +17559,7 @@
         <v>14</v>
       </c>
       <c r="F438" s="2">
-        <v>3918</v>
+        <v>2850</v>
       </c>
       <c r="G438" s="2" t="s">
         <v>15</v>
@@ -17591,7 +17591,7 @@
         <v>14</v>
       </c>
       <c r="F439" s="2">
-        <v>2530</v>
+        <v>2725</v>
       </c>
       <c r="G439" s="2" t="s">
         <v>15</v>
@@ -17623,7 +17623,7 @@
         <v>14</v>
       </c>
       <c r="F440" s="2">
-        <v>2340</v>
+        <v>3970</v>
       </c>
       <c r="G440" s="2" t="s">
         <v>15</v>
@@ -17655,7 +17655,7 @@
         <v>14</v>
       </c>
       <c r="F441" s="2">
-        <v>913</v>
+        <v>1776</v>
       </c>
       <c r="G441" s="2" t="s">
         <v>15</v>
@@ -17687,7 +17687,7 @@
         <v>14</v>
       </c>
       <c r="F442" s="2">
-        <v>3286</v>
+        <v>2614</v>
       </c>
       <c r="G442" s="2" t="s">
         <v>15</v>
@@ -17719,7 +17719,7 @@
         <v>14</v>
       </c>
       <c r="F443" s="2">
-        <v>2969</v>
+        <v>4389</v>
       </c>
       <c r="G443" s="2" t="s">
         <v>15</v>
@@ -17751,7 +17751,7 @@
         <v>14</v>
       </c>
       <c r="F444" s="2">
-        <v>4121</v>
+        <v>860</v>
       </c>
       <c r="G444" s="2" t="s">
         <v>15</v>
@@ -17783,7 +17783,7 @@
         <v>14</v>
       </c>
       <c r="F445" s="2">
-        <v>3873</v>
+        <v>1441</v>
       </c>
       <c r="G445" s="2" t="s">
         <v>15</v>
@@ -17815,7 +17815,7 @@
         <v>14</v>
       </c>
       <c r="F446" s="2">
-        <v>1132</v>
+        <v>1682</v>
       </c>
       <c r="G446" s="2" t="s">
         <v>15</v>
@@ -17847,7 +17847,7 @@
         <v>14</v>
       </c>
       <c r="F447" s="2">
-        <v>1543</v>
+        <v>1806</v>
       </c>
       <c r="G447" s="2" t="s">
         <v>15</v>
@@ -17879,7 +17879,7 @@
         <v>14</v>
       </c>
       <c r="F448" s="2">
-        <v>2775</v>
+        <v>3015</v>
       </c>
       <c r="G448" s="2" t="s">
         <v>15</v>
@@ -17911,7 +17911,7 @@
         <v>14</v>
       </c>
       <c r="F449" s="2">
-        <v>2094</v>
+        <v>3360</v>
       </c>
       <c r="G449" s="2" t="s">
         <v>15</v>
@@ -17943,7 +17943,7 @@
         <v>14</v>
       </c>
       <c r="F450" s="2">
-        <v>2209</v>
+        <v>2372</v>
       </c>
       <c r="G450" s="2" t="s">
         <v>15</v>
@@ -17975,7 +17975,7 @@
         <v>14</v>
       </c>
       <c r="F451" s="2">
-        <v>4222</v>
+        <v>2745</v>
       </c>
       <c r="G451" s="2" t="s">
         <v>15</v>
@@ -18007,7 +18007,7 @@
         <v>14</v>
       </c>
       <c r="F452" s="2">
-        <v>3675</v>
+        <v>2479</v>
       </c>
       <c r="G452" s="2" t="s">
         <v>15</v>
@@ -18039,7 +18039,7 @@
         <v>14</v>
       </c>
       <c r="F453" s="2">
-        <v>2022</v>
+        <v>1262</v>
       </c>
       <c r="G453" s="2" t="s">
         <v>15</v>
@@ -18071,7 +18071,7 @@
         <v>14</v>
       </c>
       <c r="F454" s="2">
-        <v>3482</v>
+        <v>4473</v>
       </c>
       <c r="G454" s="2" t="s">
         <v>15</v>
@@ -18103,7 +18103,7 @@
         <v>14</v>
       </c>
       <c r="F455" s="2">
-        <v>1862</v>
+        <v>1626</v>
       </c>
       <c r="G455" s="2" t="s">
         <v>15</v>
@@ -18135,7 +18135,7 @@
         <v>14</v>
       </c>
       <c r="F456" s="2">
-        <v>924</v>
+        <v>3691</v>
       </c>
       <c r="G456" s="2" t="s">
         <v>15</v>
@@ -18167,7 +18167,7 @@
         <v>14</v>
       </c>
       <c r="F457" s="2">
-        <v>1237</v>
+        <v>3138</v>
       </c>
       <c r="G457" s="2" t="s">
         <v>15</v>
@@ -18199,7 +18199,7 @@
         <v>14</v>
       </c>
       <c r="F458" s="2">
-        <v>2348</v>
+        <v>856</v>
       </c>
       <c r="G458" s="2" t="s">
         <v>15</v>
@@ -18231,7 +18231,7 @@
         <v>14</v>
       </c>
       <c r="F459" s="2">
-        <v>4075</v>
+        <v>2601</v>
       </c>
       <c r="G459" s="2" t="s">
         <v>15</v>
@@ -18263,7 +18263,7 @@
         <v>14</v>
       </c>
       <c r="F460" s="2">
-        <v>1489</v>
+        <v>2749</v>
       </c>
       <c r="G460" s="2" t="s">
         <v>15</v>
@@ -18295,7 +18295,7 @@
         <v>14</v>
       </c>
       <c r="F461" s="2">
-        <v>3321</v>
+        <v>1270</v>
       </c>
       <c r="G461" s="2" t="s">
         <v>15</v>
@@ -18327,7 +18327,7 @@
         <v>14</v>
       </c>
       <c r="F462" s="2">
-        <v>4694</v>
+        <v>1955</v>
       </c>
       <c r="G462" s="2" t="s">
         <v>15</v>
@@ -18359,7 +18359,7 @@
         <v>14</v>
       </c>
       <c r="F463" s="2">
-        <v>2820</v>
+        <v>3567</v>
       </c>
       <c r="G463" s="2" t="s">
         <v>15</v>
@@ -18391,7 +18391,7 @@
         <v>14</v>
       </c>
       <c r="F464" s="2">
-        <v>1982</v>
+        <v>3712</v>
       </c>
       <c r="G464" s="2" t="s">
         <v>15</v>
@@ -18423,7 +18423,7 @@
         <v>14</v>
       </c>
       <c r="F465" s="2">
-        <v>1539</v>
+        <v>1272</v>
       </c>
       <c r="G465" s="2" t="s">
         <v>15</v>
@@ -18455,7 +18455,7 @@
         <v>14</v>
       </c>
       <c r="F466" s="2">
-        <v>2682</v>
+        <v>4776</v>
       </c>
       <c r="G466" s="2" t="s">
         <v>15</v>
@@ -18487,7 +18487,7 @@
         <v>14</v>
       </c>
       <c r="F467" s="2">
-        <v>3948</v>
+        <v>1305</v>
       </c>
       <c r="G467" s="2" t="s">
         <v>15</v>
@@ -18519,7 +18519,7 @@
         <v>14</v>
       </c>
       <c r="F468" s="2">
-        <v>2491</v>
+        <v>4315</v>
       </c>
       <c r="G468" s="2" t="s">
         <v>15</v>
@@ -18551,7 +18551,7 @@
         <v>14</v>
       </c>
       <c r="F469" s="2">
-        <v>1141</v>
+        <v>2441</v>
       </c>
       <c r="G469" s="2" t="s">
         <v>15</v>
@@ -18583,7 +18583,7 @@
         <v>14</v>
       </c>
       <c r="F470" s="2">
-        <v>1105</v>
+        <v>2133</v>
       </c>
       <c r="G470" s="2" t="s">
         <v>15</v>
@@ -18615,7 +18615,7 @@
         <v>14</v>
       </c>
       <c r="F471" s="2">
-        <v>1017</v>
+        <v>3039</v>
       </c>
       <c r="G471" s="2" t="s">
         <v>15</v>
@@ -18702,7 +18702,7 @@
         <v>14</v>
       </c>
       <c r="F2" s="2">
-        <v>1693</v>
+        <v>3639</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>15</v>
@@ -18734,7 +18734,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="2">
-        <v>2763</v>
+        <v>2895</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>15</v>
@@ -18766,7 +18766,7 @@
         <v>14</v>
       </c>
       <c r="F4" s="2">
-        <v>3488</v>
+        <v>3225</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
@@ -18798,7 +18798,7 @@
         <v>14</v>
       </c>
       <c r="F5" s="2">
-        <v>1400</v>
+        <v>1115</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
@@ -18830,7 +18830,7 @@
         <v>14</v>
       </c>
       <c r="F6" s="2">
-        <v>1372</v>
+        <v>3408</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -18862,7 +18862,7 @@
         <v>14</v>
       </c>
       <c r="F7" s="2">
-        <v>1244</v>
+        <v>3935</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -18894,7 +18894,7 @@
         <v>14</v>
       </c>
       <c r="F8" s="2">
-        <v>2751</v>
+        <v>2045</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -18926,7 +18926,7 @@
         <v>14</v>
       </c>
       <c r="F9" s="2">
-        <v>3523</v>
+        <v>4145</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -18958,7 +18958,7 @@
         <v>14</v>
       </c>
       <c r="F10" s="2">
-        <v>1805</v>
+        <v>3852</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
@@ -18990,7 +18990,7 @@
         <v>14</v>
       </c>
       <c r="F11" s="2">
-        <v>3811</v>
+        <v>1119</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
@@ -19022,7 +19022,7 @@
         <v>14</v>
       </c>
       <c r="F12" s="2">
-        <v>1829</v>
+        <v>1467</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
@@ -19054,7 +19054,7 @@
         <v>14</v>
       </c>
       <c r="F13" s="2">
-        <v>1123</v>
+        <v>3694</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -19086,7 +19086,7 @@
         <v>14</v>
       </c>
       <c r="F14" s="2">
-        <v>2733</v>
+        <v>1003</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -19118,7 +19118,7 @@
         <v>14</v>
       </c>
       <c r="F15" s="2">
-        <v>1648</v>
+        <v>1343</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -19150,7 +19150,7 @@
         <v>14</v>
       </c>
       <c r="F16" s="2">
-        <v>828</v>
+        <v>3875</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
@@ -19182,7 +19182,7 @@
         <v>14</v>
       </c>
       <c r="F17" s="2">
-        <v>2736</v>
+        <v>2977</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
@@ -19214,7 +19214,7 @@
         <v>14</v>
       </c>
       <c r="F18" s="2">
-        <v>2115</v>
+        <v>4055</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
@@ -19246,7 +19246,7 @@
         <v>14</v>
       </c>
       <c r="F19" s="2">
-        <v>1912</v>
+        <v>4664</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
@@ -19278,7 +19278,7 @@
         <v>14</v>
       </c>
       <c r="F20" s="2">
-        <v>1479</v>
+        <v>1543</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
@@ -19310,7 +19310,7 @@
         <v>14</v>
       </c>
       <c r="F21" s="2">
-        <v>2920</v>
+        <v>1703</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -19342,7 +19342,7 @@
         <v>14</v>
       </c>
       <c r="F22" s="2">
-        <v>1455</v>
+        <v>1112</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -19374,7 +19374,7 @@
         <v>14</v>
       </c>
       <c r="F23" s="2">
-        <v>2941</v>
+        <v>3040</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -19406,7 +19406,7 @@
         <v>14</v>
       </c>
       <c r="F24" s="2">
-        <v>1315</v>
+        <v>1969</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -19438,7 +19438,7 @@
         <v>14</v>
       </c>
       <c r="F25" s="2">
-        <v>1133</v>
+        <v>1877</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -19470,7 +19470,7 @@
         <v>14</v>
       </c>
       <c r="F26" s="2">
-        <v>4561</v>
+        <v>1774</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -19502,7 +19502,7 @@
         <v>14</v>
       </c>
       <c r="F27" s="2">
-        <v>1944</v>
+        <v>3721</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>15</v>
@@ -19534,7 +19534,7 @@
         <v>14</v>
       </c>
       <c r="F28" s="2">
-        <v>2944</v>
+        <v>3272</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>15</v>
@@ -19566,7 +19566,7 @@
         <v>14</v>
       </c>
       <c r="F29" s="2">
-        <v>2296</v>
+        <v>3033</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>15</v>
@@ -19598,7 +19598,7 @@
         <v>14</v>
       </c>
       <c r="F30" s="2">
-        <v>1904</v>
+        <v>1696</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>15</v>
@@ -19630,7 +19630,7 @@
         <v>14</v>
       </c>
       <c r="F31" s="2">
-        <v>1933</v>
+        <v>819</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>15</v>
@@ -19662,7 +19662,7 @@
         <v>14</v>
       </c>
       <c r="F32" s="2">
-        <v>3045</v>
+        <v>3288</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>15</v>
@@ -19694,7 +19694,7 @@
         <v>14</v>
       </c>
       <c r="F33" s="2">
-        <v>4298</v>
+        <v>2343</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>15</v>
@@ -19726,7 +19726,7 @@
         <v>14</v>
       </c>
       <c r="F34" s="2">
-        <v>3224</v>
+        <v>1024</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>15</v>
@@ -19758,7 +19758,7 @@
         <v>14</v>
       </c>
       <c r="F35" s="2">
-        <v>3466</v>
+        <v>825</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>15</v>
@@ -19790,7 +19790,7 @@
         <v>14</v>
       </c>
       <c r="F36" s="2">
-        <v>3601</v>
+        <v>1640</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>15</v>
@@ -19822,7 +19822,7 @@
         <v>14</v>
       </c>
       <c r="F37" s="2">
-        <v>3129</v>
+        <v>2301</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>15</v>
@@ -19854,7 +19854,7 @@
         <v>14</v>
       </c>
       <c r="F38" s="2">
-        <v>2443</v>
+        <v>3718</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>15</v>
@@ -19886,7 +19886,7 @@
         <v>14</v>
       </c>
       <c r="F39" s="2">
-        <v>1282</v>
+        <v>2933</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>15</v>
@@ -19918,7 +19918,7 @@
         <v>14</v>
       </c>
       <c r="F40" s="2">
-        <v>2877</v>
+        <v>2268</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>15</v>
@@ -19950,7 +19950,7 @@
         <v>14</v>
       </c>
       <c r="F41" s="2">
-        <v>2481</v>
+        <v>2955</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>15</v>
@@ -19982,7 +19982,7 @@
         <v>14</v>
       </c>
       <c r="F42" s="2">
-        <v>1808</v>
+        <v>912</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>15</v>
@@ -20014,7 +20014,7 @@
         <v>14</v>
       </c>
       <c r="F43" s="2">
-        <v>1497</v>
+        <v>3127</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>15</v>
@@ -20046,7 +20046,7 @@
         <v>14</v>
       </c>
       <c r="F44" s="2">
-        <v>4274</v>
+        <v>1017</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>15</v>
@@ -20078,7 +20078,7 @@
         <v>14</v>
       </c>
       <c r="F45" s="2">
-        <v>4783</v>
+        <v>4056</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>15</v>
@@ -20110,7 +20110,7 @@
         <v>14</v>
       </c>
       <c r="F46" s="2">
-        <v>4728</v>
+        <v>2668</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>15</v>
@@ -20142,7 +20142,7 @@
         <v>14</v>
       </c>
       <c r="F47" s="2">
-        <v>4747</v>
+        <v>2378</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>15</v>
@@ -20174,7 +20174,7 @@
         <v>14</v>
       </c>
       <c r="F48" s="2">
-        <v>3881</v>
+        <v>4619</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>15</v>
@@ -20206,7 +20206,7 @@
         <v>14</v>
       </c>
       <c r="F49" s="2">
-        <v>2720</v>
+        <v>3120</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>15</v>
@@ -20238,7 +20238,7 @@
         <v>14</v>
       </c>
       <c r="F50" s="2">
-        <v>1765</v>
+        <v>3893</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>15</v>
@@ -20270,7 +20270,7 @@
         <v>14</v>
       </c>
       <c r="F51" s="2">
-        <v>4230</v>
+        <v>991</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>15</v>
@@ -20302,7 +20302,7 @@
         <v>14</v>
       </c>
       <c r="F52" s="2">
-        <v>1714</v>
+        <v>1563</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>15</v>
@@ -20334,7 +20334,7 @@
         <v>14</v>
       </c>
       <c r="F53" s="2">
-        <v>3046</v>
+        <v>1410</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>15</v>
@@ -20366,7 +20366,7 @@
         <v>14</v>
       </c>
       <c r="F54" s="2">
-        <v>3123</v>
+        <v>4771</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>15</v>
@@ -20398,7 +20398,7 @@
         <v>14</v>
       </c>
       <c r="F55" s="2">
-        <v>3064</v>
+        <v>3054</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>15</v>
@@ -20430,7 +20430,7 @@
         <v>14</v>
       </c>
       <c r="F56" s="2">
-        <v>2153</v>
+        <v>3824</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>15</v>
@@ -20462,7 +20462,7 @@
         <v>14</v>
       </c>
       <c r="F57" s="2">
-        <v>2128</v>
+        <v>2564</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>15</v>
@@ -20494,7 +20494,7 @@
         <v>14</v>
       </c>
       <c r="F58" s="2">
-        <v>1689</v>
+        <v>3155</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>15</v>
@@ -20526,7 +20526,7 @@
         <v>14</v>
       </c>
       <c r="F59" s="2">
-        <v>1105</v>
+        <v>2051</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>15</v>
@@ -20558,7 +20558,7 @@
         <v>14</v>
       </c>
       <c r="F60" s="2">
-        <v>921</v>
+        <v>2716</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>15</v>
@@ -20590,7 +20590,7 @@
         <v>14</v>
       </c>
       <c r="F61" s="2">
-        <v>4083</v>
+        <v>1422</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>15</v>
@@ -20622,7 +20622,7 @@
         <v>14</v>
       </c>
       <c r="F62" s="2">
-        <v>822</v>
+        <v>3896</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>15</v>
@@ -20654,7 +20654,7 @@
         <v>14</v>
       </c>
       <c r="F63" s="2">
-        <v>4181</v>
+        <v>4654</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>15</v>
@@ -20686,7 +20686,7 @@
         <v>14</v>
       </c>
       <c r="F64" s="2">
-        <v>1956</v>
+        <v>2479</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>15</v>
@@ -20718,7 +20718,7 @@
         <v>14</v>
       </c>
       <c r="F65" s="2">
-        <v>3388</v>
+        <v>3792</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>15</v>
@@ -20750,7 +20750,7 @@
         <v>14</v>
       </c>
       <c r="F66" s="2">
-        <v>1901</v>
+        <v>2195</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>15</v>
@@ -20782,7 +20782,7 @@
         <v>14</v>
       </c>
       <c r="F67" s="2">
-        <v>1495</v>
+        <v>3950</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>15</v>
@@ -20814,7 +20814,7 @@
         <v>14</v>
       </c>
       <c r="F68" s="2">
-        <v>1744</v>
+        <v>2625</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>15</v>
@@ -20846,7 +20846,7 @@
         <v>14</v>
       </c>
       <c r="F69" s="2">
-        <v>1858</v>
+        <v>3882</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>15</v>
@@ -20878,7 +20878,7 @@
         <v>14</v>
       </c>
       <c r="F70" s="2">
-        <v>1693</v>
+        <v>1952</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>15</v>
@@ -20910,7 +20910,7 @@
         <v>14</v>
       </c>
       <c r="F71" s="2">
-        <v>3535</v>
+        <v>1931</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>15</v>
@@ -20942,7 +20942,7 @@
         <v>14</v>
       </c>
       <c r="F72" s="2">
-        <v>4646</v>
+        <v>4116</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>15</v>
@@ -20974,7 +20974,7 @@
         <v>14</v>
       </c>
       <c r="F73" s="2">
-        <v>2528</v>
+        <v>3276</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>15</v>
@@ -21006,7 +21006,7 @@
         <v>14</v>
       </c>
       <c r="F74" s="2">
-        <v>2704</v>
+        <v>4540</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>15</v>
@@ -21038,7 +21038,7 @@
         <v>14</v>
       </c>
       <c r="F75" s="2">
-        <v>1421</v>
+        <v>3078</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>15</v>
@@ -21070,7 +21070,7 @@
         <v>14</v>
       </c>
       <c r="F76" s="2">
-        <v>2250</v>
+        <v>2338</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>15</v>
@@ -21102,7 +21102,7 @@
         <v>14</v>
       </c>
       <c r="F77" s="2">
-        <v>2660</v>
+        <v>3266</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>15</v>
@@ -21134,7 +21134,7 @@
         <v>14</v>
       </c>
       <c r="F78" s="2">
-        <v>1146</v>
+        <v>2373</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>15</v>
@@ -21166,7 +21166,7 @@
         <v>14</v>
       </c>
       <c r="F79" s="2">
-        <v>2451</v>
+        <v>908</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>15</v>
@@ -21198,7 +21198,7 @@
         <v>14</v>
       </c>
       <c r="F80" s="2">
-        <v>4165</v>
+        <v>3757</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>15</v>
@@ -21230,7 +21230,7 @@
         <v>14</v>
       </c>
       <c r="F81" s="2">
-        <v>965</v>
+        <v>2629</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>15</v>
@@ -21262,7 +21262,7 @@
         <v>14</v>
       </c>
       <c r="F82" s="2">
-        <v>3162</v>
+        <v>1579</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>15</v>
@@ -21294,7 +21294,7 @@
         <v>14</v>
       </c>
       <c r="F83" s="2">
-        <v>4288</v>
+        <v>853</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>15</v>
@@ -21326,7 +21326,7 @@
         <v>14</v>
       </c>
       <c r="F84" s="2">
-        <v>4510</v>
+        <v>1422</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>15</v>
@@ -21358,7 +21358,7 @@
         <v>14</v>
       </c>
       <c r="F85" s="2">
-        <v>1416</v>
+        <v>3259</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>15</v>
@@ -21390,7 +21390,7 @@
         <v>14</v>
       </c>
       <c r="F86" s="2">
-        <v>2999</v>
+        <v>3672</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>15</v>
@@ -21422,7 +21422,7 @@
         <v>14</v>
       </c>
       <c r="F87" s="2">
-        <v>4227</v>
+        <v>3660</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>15</v>
@@ -21454,7 +21454,7 @@
         <v>14</v>
       </c>
       <c r="F88" s="2">
-        <v>3790</v>
+        <v>3386</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>15</v>
@@ -21486,7 +21486,7 @@
         <v>14</v>
       </c>
       <c r="F89" s="2">
-        <v>1019</v>
+        <v>3384</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>15</v>
@@ -21518,7 +21518,7 @@
         <v>14</v>
       </c>
       <c r="F90" s="2">
-        <v>3377</v>
+        <v>2905</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>15</v>
@@ -21550,7 +21550,7 @@
         <v>14</v>
       </c>
       <c r="F91" s="2">
-        <v>3281</v>
+        <v>4642</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>15</v>
@@ -21582,7 +21582,7 @@
         <v>14</v>
       </c>
       <c r="F92" s="2">
-        <v>1607</v>
+        <v>4475</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>15</v>
@@ -21614,7 +21614,7 @@
         <v>14</v>
       </c>
       <c r="F93" s="2">
-        <v>3767</v>
+        <v>1011</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>15</v>
@@ -21646,7 +21646,7 @@
         <v>14</v>
       </c>
       <c r="F94" s="2">
-        <v>4431</v>
+        <v>1481</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>15</v>
@@ -21678,7 +21678,7 @@
         <v>14</v>
       </c>
       <c r="F95" s="2">
-        <v>899</v>
+        <v>3193</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>15</v>
@@ -21710,7 +21710,7 @@
         <v>14</v>
       </c>
       <c r="F96" s="2">
-        <v>1148</v>
+        <v>823</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>15</v>
@@ -21742,7 +21742,7 @@
         <v>14</v>
       </c>
       <c r="F97" s="2">
-        <v>1335</v>
+        <v>2981</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>15</v>
@@ -21774,7 +21774,7 @@
         <v>14</v>
       </c>
       <c r="F98" s="2">
-        <v>1730</v>
+        <v>3681</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>15</v>
@@ -21806,7 +21806,7 @@
         <v>14</v>
       </c>
       <c r="F99" s="2">
-        <v>3319</v>
+        <v>1823</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>15</v>
@@ -21838,7 +21838,7 @@
         <v>14</v>
       </c>
       <c r="F100" s="2">
-        <v>3628</v>
+        <v>3640</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>15</v>
@@ -21870,7 +21870,7 @@
         <v>14</v>
       </c>
       <c r="F101" s="2">
-        <v>2120</v>
+        <v>2992</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>15</v>
@@ -21902,7 +21902,7 @@
         <v>14</v>
       </c>
       <c r="F102" s="2">
-        <v>3973</v>
+        <v>4150</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>15</v>
@@ -21934,7 +21934,7 @@
         <v>14</v>
       </c>
       <c r="F103" s="2">
-        <v>2470</v>
+        <v>4439</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>15</v>
@@ -21966,7 +21966,7 @@
         <v>14</v>
       </c>
       <c r="F104" s="2">
-        <v>2598</v>
+        <v>2013</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>15</v>
@@ -21998,7 +21998,7 @@
         <v>14</v>
       </c>
       <c r="F105" s="2">
-        <v>2973</v>
+        <v>2005</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>15</v>
@@ -22030,7 +22030,7 @@
         <v>14</v>
       </c>
       <c r="F106" s="2">
-        <v>3687</v>
+        <v>4799</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>15</v>
@@ -22062,7 +22062,7 @@
         <v>14</v>
       </c>
       <c r="F107" s="2">
-        <v>3958</v>
+        <v>1484</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>15</v>
@@ -22094,7 +22094,7 @@
         <v>14</v>
       </c>
       <c r="F108" s="2">
-        <v>3127</v>
+        <v>1609</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>15</v>
@@ -22126,7 +22126,7 @@
         <v>14</v>
       </c>
       <c r="F109" s="2">
-        <v>1809</v>
+        <v>1413</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>15</v>
@@ -22158,7 +22158,7 @@
         <v>14</v>
       </c>
       <c r="F110" s="2">
-        <v>1798</v>
+        <v>3635</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>15</v>
@@ -22190,7 +22190,7 @@
         <v>14</v>
       </c>
       <c r="F111" s="2">
-        <v>2261</v>
+        <v>2916</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>15</v>
@@ -22222,7 +22222,7 @@
         <v>14</v>
       </c>
       <c r="F112" s="2">
-        <v>866</v>
+        <v>1488</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>15</v>
@@ -22254,7 +22254,7 @@
         <v>14</v>
       </c>
       <c r="F113" s="2">
-        <v>1339</v>
+        <v>3565</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>15</v>
@@ -22286,7 +22286,7 @@
         <v>14</v>
       </c>
       <c r="F114" s="2">
-        <v>4395</v>
+        <v>2080</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>15</v>
@@ -22318,7 +22318,7 @@
         <v>14</v>
       </c>
       <c r="F115" s="2">
-        <v>2927</v>
+        <v>4591</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>15</v>
@@ -22350,7 +22350,7 @@
         <v>14</v>
       </c>
       <c r="F116" s="2">
-        <v>3087</v>
+        <v>844</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>15</v>
@@ -22382,7 +22382,7 @@
         <v>14</v>
       </c>
       <c r="F117" s="2">
-        <v>2127</v>
+        <v>3876</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>15</v>
@@ -22414,7 +22414,7 @@
         <v>14</v>
       </c>
       <c r="F118" s="2">
-        <v>3532</v>
+        <v>3172</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>15</v>
@@ -22446,7 +22446,7 @@
         <v>14</v>
       </c>
       <c r="F119" s="2">
-        <v>2646</v>
+        <v>3854</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>15</v>
@@ -22478,7 +22478,7 @@
         <v>14</v>
       </c>
       <c r="F120" s="2">
-        <v>2500</v>
+        <v>3742</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>15</v>
@@ -22510,7 +22510,7 @@
         <v>14</v>
       </c>
       <c r="F121" s="2">
-        <v>2825</v>
+        <v>1349</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>15</v>
@@ -22542,7 +22542,7 @@
         <v>14</v>
       </c>
       <c r="F122" s="2">
-        <v>3584</v>
+        <v>1093</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>15</v>
@@ -22574,7 +22574,7 @@
         <v>14</v>
       </c>
       <c r="F123" s="2">
-        <v>2358</v>
+        <v>2824</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>15</v>
@@ -22606,7 +22606,7 @@
         <v>14</v>
       </c>
       <c r="F124" s="2">
-        <v>3369</v>
+        <v>2649</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>15</v>
@@ -22638,7 +22638,7 @@
         <v>14</v>
       </c>
       <c r="F125" s="2">
-        <v>2444</v>
+        <v>4015</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>15</v>
@@ -22670,7 +22670,7 @@
         <v>14</v>
       </c>
       <c r="F126" s="2">
-        <v>3099</v>
+        <v>2500</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>15</v>
@@ -22702,7 +22702,7 @@
         <v>14</v>
       </c>
       <c r="F127" s="2">
-        <v>3107</v>
+        <v>2978</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>15</v>
@@ -22734,7 +22734,7 @@
         <v>14</v>
       </c>
       <c r="F128" s="2">
-        <v>804</v>
+        <v>3113</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>15</v>
@@ -22766,7 +22766,7 @@
         <v>14</v>
       </c>
       <c r="F129" s="2">
-        <v>1562</v>
+        <v>1931</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>15</v>
@@ -22798,7 +22798,7 @@
         <v>14</v>
       </c>
       <c r="F130" s="2">
-        <v>3447</v>
+        <v>2426</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>15</v>
@@ -22830,7 +22830,7 @@
         <v>14</v>
       </c>
       <c r="F131" s="2">
-        <v>3770</v>
+        <v>983</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>15</v>
@@ -22862,7 +22862,7 @@
         <v>14</v>
       </c>
       <c r="F132" s="2">
-        <v>4546</v>
+        <v>4301</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>15</v>
@@ -22894,7 +22894,7 @@
         <v>14</v>
       </c>
       <c r="F133" s="2">
-        <v>2026</v>
+        <v>2713</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>15</v>
@@ -22926,7 +22926,7 @@
         <v>14</v>
       </c>
       <c r="F134" s="2">
-        <v>2154</v>
+        <v>4540</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>15</v>
@@ -22958,7 +22958,7 @@
         <v>14</v>
       </c>
       <c r="F135" s="2">
-        <v>3915</v>
+        <v>1541</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>15</v>
@@ -22990,7 +22990,7 @@
         <v>14</v>
       </c>
       <c r="F136" s="2">
-        <v>3087</v>
+        <v>2320</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>15</v>
@@ -23022,7 +23022,7 @@
         <v>14</v>
       </c>
       <c r="F137" s="2">
-        <v>3851</v>
+        <v>1409</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>15</v>
@@ -23054,7 +23054,7 @@
         <v>14</v>
       </c>
       <c r="F138" s="2">
-        <v>4408</v>
+        <v>2297</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>15</v>
@@ -23086,7 +23086,7 @@
         <v>14</v>
       </c>
       <c r="F139" s="2">
-        <v>2519</v>
+        <v>2387</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>15</v>
@@ -23118,7 +23118,7 @@
         <v>14</v>
       </c>
       <c r="F140" s="2">
-        <v>2913</v>
+        <v>3440</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>15</v>
@@ -23150,7 +23150,7 @@
         <v>14</v>
       </c>
       <c r="F141" s="2">
-        <v>2712</v>
+        <v>4029</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>15</v>
@@ -23182,7 +23182,7 @@
         <v>14</v>
       </c>
       <c r="F142" s="2">
-        <v>931</v>
+        <v>1562</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>15</v>
@@ -23214,7 +23214,7 @@
         <v>14</v>
       </c>
       <c r="F143" s="2">
-        <v>1754</v>
+        <v>2930</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>15</v>
@@ -23246,7 +23246,7 @@
         <v>14</v>
       </c>
       <c r="F144" s="2">
-        <v>996</v>
+        <v>1323</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>15</v>
@@ -23278,7 +23278,7 @@
         <v>14</v>
       </c>
       <c r="F145" s="2">
-        <v>3557</v>
+        <v>4470</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>15</v>
@@ -23310,7 +23310,7 @@
         <v>14</v>
       </c>
       <c r="F146" s="2">
-        <v>1916</v>
+        <v>4068</v>
       </c>
       <c r="G146" s="2" t="s">
         <v>15</v>
@@ -23342,7 +23342,7 @@
         <v>14</v>
       </c>
       <c r="F147" s="2">
-        <v>1396</v>
+        <v>1264</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>15</v>
@@ -23374,7 +23374,7 @@
         <v>14</v>
       </c>
       <c r="F148" s="2">
-        <v>826</v>
+        <v>3935</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>15</v>
@@ -23406,7 +23406,7 @@
         <v>14</v>
       </c>
       <c r="F149" s="2">
-        <v>2649</v>
+        <v>2633</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>15</v>
@@ -23438,7 +23438,7 @@
         <v>14</v>
       </c>
       <c r="F150" s="2">
-        <v>3247</v>
+        <v>2150</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>15</v>
@@ -23470,7 +23470,7 @@
         <v>14</v>
       </c>
       <c r="F151" s="2">
-        <v>4589</v>
+        <v>2928</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>15</v>
@@ -23502,7 +23502,7 @@
         <v>14</v>
       </c>
       <c r="F152" s="2">
-        <v>4711</v>
+        <v>1531</v>
       </c>
       <c r="G152" s="2" t="s">
         <v>15</v>
@@ -23534,7 +23534,7 @@
         <v>14</v>
       </c>
       <c r="F153" s="2">
-        <v>1370</v>
+        <v>4396</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>15</v>
@@ -23566,7 +23566,7 @@
         <v>14</v>
       </c>
       <c r="F154" s="2">
-        <v>2841</v>
+        <v>1559</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>15</v>
@@ -23598,7 +23598,7 @@
         <v>14</v>
       </c>
       <c r="F155" s="2">
-        <v>4779</v>
+        <v>1284</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>15</v>
@@ -23630,7 +23630,7 @@
         <v>14</v>
       </c>
       <c r="F156" s="2">
-        <v>1895</v>
+        <v>1682</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>15</v>
@@ -23662,7 +23662,7 @@
         <v>14</v>
       </c>
       <c r="F157" s="2">
-        <v>4531</v>
+        <v>2140</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>15</v>
@@ -23694,7 +23694,7 @@
         <v>14</v>
       </c>
       <c r="F158" s="2">
-        <v>2123</v>
+        <v>2990</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>15</v>
@@ -23726,7 +23726,7 @@
         <v>14</v>
       </c>
       <c r="F159" s="2">
-        <v>1856</v>
+        <v>4605</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>15</v>
@@ -23758,7 +23758,7 @@
         <v>14</v>
       </c>
       <c r="F160" s="2">
-        <v>3338</v>
+        <v>2855</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>15</v>
@@ -23790,7 +23790,7 @@
         <v>14</v>
       </c>
       <c r="F161" s="2">
-        <v>1991</v>
+        <v>3484</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>15</v>
@@ -23822,7 +23822,7 @@
         <v>14</v>
       </c>
       <c r="F162" s="2">
-        <v>3896</v>
+        <v>1745</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>15</v>
@@ -23854,7 +23854,7 @@
         <v>14</v>
       </c>
       <c r="F163" s="2">
-        <v>3887</v>
+        <v>2677</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>15</v>
@@ -23886,7 +23886,7 @@
         <v>14</v>
       </c>
       <c r="F164" s="2">
-        <v>3695</v>
+        <v>941</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>15</v>
@@ -23918,7 +23918,7 @@
         <v>14</v>
       </c>
       <c r="F165" s="2">
-        <v>2889</v>
+        <v>4508</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>15</v>
@@ -23950,7 +23950,7 @@
         <v>14</v>
       </c>
       <c r="F166" s="2">
-        <v>3328</v>
+        <v>4401</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>15</v>
@@ -23982,7 +23982,7 @@
         <v>14</v>
       </c>
       <c r="F167" s="2">
-        <v>1514</v>
+        <v>1442</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>15</v>
@@ -24014,7 +24014,7 @@
         <v>14</v>
       </c>
       <c r="F168" s="2">
-        <v>3203</v>
+        <v>2933</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>15</v>
@@ -24046,7 +24046,7 @@
         <v>14</v>
       </c>
       <c r="F169" s="2">
-        <v>4772</v>
+        <v>857</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>15</v>
@@ -24078,7 +24078,7 @@
         <v>14</v>
       </c>
       <c r="F170" s="2">
-        <v>4353</v>
+        <v>1383</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>15</v>
@@ -24110,7 +24110,7 @@
         <v>14</v>
       </c>
       <c r="F171" s="2">
-        <v>4739</v>
+        <v>1264</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>15</v>
@@ -24142,7 +24142,7 @@
         <v>14</v>
       </c>
       <c r="F172" s="2">
-        <v>4626</v>
+        <v>4496</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>15</v>
@@ -24174,7 +24174,7 @@
         <v>14</v>
       </c>
       <c r="F173" s="2">
-        <v>1541</v>
+        <v>1309</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>15</v>
@@ -24206,7 +24206,7 @@
         <v>14</v>
       </c>
       <c r="F174" s="2">
-        <v>2648</v>
+        <v>4069</v>
       </c>
       <c r="G174" s="2" t="s">
         <v>15</v>
@@ -24238,7 +24238,7 @@
         <v>14</v>
       </c>
       <c r="F175" s="2">
-        <v>1492</v>
+        <v>3481</v>
       </c>
       <c r="G175" s="2" t="s">
         <v>15</v>
@@ -24270,7 +24270,7 @@
         <v>14</v>
       </c>
       <c r="F176" s="2">
-        <v>3512</v>
+        <v>2994</v>
       </c>
       <c r="G176" s="2" t="s">
         <v>15</v>
@@ -24302,7 +24302,7 @@
         <v>14</v>
       </c>
       <c r="F177" s="2">
-        <v>4237</v>
+        <v>2581</v>
       </c>
       <c r="G177" s="2" t="s">
         <v>15</v>
@@ -24334,7 +24334,7 @@
         <v>14</v>
       </c>
       <c r="F178" s="2">
-        <v>882</v>
+        <v>3908</v>
       </c>
       <c r="G178" s="2" t="s">
         <v>15</v>
@@ -24366,7 +24366,7 @@
         <v>14</v>
       </c>
       <c r="F179" s="2">
-        <v>4788</v>
+        <v>2294</v>
       </c>
       <c r="G179" s="2" t="s">
         <v>15</v>
@@ -24398,7 +24398,7 @@
         <v>14</v>
       </c>
       <c r="F180" s="2">
-        <v>2969</v>
+        <v>2516</v>
       </c>
       <c r="G180" s="2" t="s">
         <v>15</v>
@@ -24430,7 +24430,7 @@
         <v>14</v>
       </c>
       <c r="F181" s="2">
-        <v>829</v>
+        <v>2086</v>
       </c>
       <c r="G181" s="2" t="s">
         <v>15</v>
@@ -24462,7 +24462,7 @@
         <v>14</v>
       </c>
       <c r="F182" s="2">
-        <v>1599</v>
+        <v>1412</v>
       </c>
       <c r="G182" s="2" t="s">
         <v>15</v>
@@ -24494,7 +24494,7 @@
         <v>14</v>
       </c>
       <c r="F183" s="2">
-        <v>2563</v>
+        <v>3189</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>15</v>
@@ -24526,7 +24526,7 @@
         <v>14</v>
       </c>
       <c r="F184" s="2">
-        <v>2878</v>
+        <v>3348</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>15</v>
@@ -24558,7 +24558,7 @@
         <v>14</v>
       </c>
       <c r="F185" s="2">
-        <v>3283</v>
+        <v>3444</v>
       </c>
       <c r="G185" s="2" t="s">
         <v>15</v>
@@ -24590,7 +24590,7 @@
         <v>14</v>
       </c>
       <c r="F186" s="2">
-        <v>4098</v>
+        <v>2463</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>15</v>
@@ -24622,7 +24622,7 @@
         <v>14</v>
       </c>
       <c r="F187" s="2">
-        <v>2167</v>
+        <v>1580</v>
       </c>
       <c r="G187" s="2" t="s">
         <v>15</v>
@@ -24654,7 +24654,7 @@
         <v>14</v>
       </c>
       <c r="F188" s="2">
-        <v>3075</v>
+        <v>3805</v>
       </c>
       <c r="G188" s="2" t="s">
         <v>15</v>
@@ -24686,7 +24686,7 @@
         <v>14</v>
       </c>
       <c r="F189" s="2">
-        <v>3947</v>
+        <v>2048</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>15</v>
@@ -24718,7 +24718,7 @@
         <v>14</v>
       </c>
       <c r="F190" s="2">
-        <v>1567</v>
+        <v>2284</v>
       </c>
       <c r="G190" s="2" t="s">
         <v>15</v>
@@ -24750,7 +24750,7 @@
         <v>14</v>
       </c>
       <c r="F191" s="2">
-        <v>1689</v>
+        <v>4687</v>
       </c>
       <c r="G191" s="2" t="s">
         <v>15</v>
@@ -24782,7 +24782,7 @@
         <v>14</v>
       </c>
       <c r="F192" s="2">
-        <v>3217</v>
+        <v>1871</v>
       </c>
       <c r="G192" s="2" t="s">
         <v>15</v>
@@ -24814,7 +24814,7 @@
         <v>14</v>
       </c>
       <c r="F193" s="2">
-        <v>1060</v>
+        <v>4333</v>
       </c>
       <c r="G193" s="2" t="s">
         <v>15</v>
@@ -24846,7 +24846,7 @@
         <v>14</v>
       </c>
       <c r="F194" s="2">
-        <v>902</v>
+        <v>2206</v>
       </c>
       <c r="G194" s="2" t="s">
         <v>15</v>
@@ -24878,7 +24878,7 @@
         <v>14</v>
       </c>
       <c r="F195" s="2">
-        <v>2583</v>
+        <v>3526</v>
       </c>
       <c r="G195" s="2" t="s">
         <v>15</v>
@@ -24910,7 +24910,7 @@
         <v>14</v>
       </c>
       <c r="F196" s="2">
-        <v>1578</v>
+        <v>4373</v>
       </c>
       <c r="G196" s="2" t="s">
         <v>15</v>
@@ -24942,7 +24942,7 @@
         <v>14</v>
       </c>
       <c r="F197" s="2">
-        <v>1793</v>
+        <v>4320</v>
       </c>
       <c r="G197" s="2" t="s">
         <v>15</v>
@@ -24974,7 +24974,7 @@
         <v>14</v>
       </c>
       <c r="F198" s="2">
-        <v>1832</v>
+        <v>2349</v>
       </c>
       <c r="G198" s="2" t="s">
         <v>15</v>
@@ -25006,7 +25006,7 @@
         <v>14</v>
       </c>
       <c r="F199" s="2">
-        <v>2802</v>
+        <v>3391</v>
       </c>
       <c r="G199" s="2" t="s">
         <v>15</v>
@@ -25038,7 +25038,7 @@
         <v>14</v>
       </c>
       <c r="F200" s="2">
-        <v>1380</v>
+        <v>4274</v>
       </c>
       <c r="G200" s="2" t="s">
         <v>15</v>
@@ -25070,7 +25070,7 @@
         <v>14</v>
       </c>
       <c r="F201" s="2">
-        <v>3607</v>
+        <v>3317</v>
       </c>
       <c r="G201" s="2" t="s">
         <v>15</v>
@@ -25102,7 +25102,7 @@
         <v>14</v>
       </c>
       <c r="F202" s="2">
-        <v>1775</v>
+        <v>2712</v>
       </c>
       <c r="G202" s="2" t="s">
         <v>15</v>
@@ -25134,7 +25134,7 @@
         <v>14</v>
       </c>
       <c r="F203" s="2">
-        <v>1248</v>
+        <v>4625</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>15</v>
@@ -25166,7 +25166,7 @@
         <v>14</v>
       </c>
       <c r="F204" s="2">
-        <v>4704</v>
+        <v>2669</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>15</v>
@@ -25198,7 +25198,7 @@
         <v>14</v>
       </c>
       <c r="F205" s="2">
-        <v>1939</v>
+        <v>2425</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>15</v>
@@ -25230,7 +25230,7 @@
         <v>14</v>
       </c>
       <c r="F206" s="2">
-        <v>3755</v>
+        <v>3779</v>
       </c>
       <c r="G206" s="2" t="s">
         <v>15</v>
@@ -25262,7 +25262,7 @@
         <v>14</v>
       </c>
       <c r="F207" s="2">
-        <v>4787</v>
+        <v>1733</v>
       </c>
       <c r="G207" s="2" t="s">
         <v>15</v>
@@ -25294,7 +25294,7 @@
         <v>14</v>
       </c>
       <c r="F208" s="2">
-        <v>1693</v>
+        <v>2010</v>
       </c>
       <c r="G208" s="2" t="s">
         <v>15</v>
@@ -25326,7 +25326,7 @@
         <v>14</v>
       </c>
       <c r="F209" s="2">
-        <v>2755</v>
+        <v>4674</v>
       </c>
       <c r="G209" s="2" t="s">
         <v>15</v>
@@ -25358,7 +25358,7 @@
         <v>14</v>
       </c>
       <c r="F210" s="2">
-        <v>3825</v>
+        <v>1305</v>
       </c>
       <c r="G210" s="2" t="s">
         <v>15</v>
@@ -25390,7 +25390,7 @@
         <v>14</v>
       </c>
       <c r="F211" s="2">
-        <v>2642</v>
+        <v>3286</v>
       </c>
       <c r="G211" s="2" t="s">
         <v>15</v>
@@ -25422,7 +25422,7 @@
         <v>14</v>
       </c>
       <c r="F212" s="2">
-        <v>996</v>
+        <v>1307</v>
       </c>
       <c r="G212" s="2" t="s">
         <v>15</v>
@@ -25454,7 +25454,7 @@
         <v>14</v>
       </c>
       <c r="F213" s="2">
-        <v>4725</v>
+        <v>3553</v>
       </c>
       <c r="G213" s="2" t="s">
         <v>15</v>
@@ -25486,7 +25486,7 @@
         <v>14</v>
       </c>
       <c r="F214" s="2">
-        <v>987</v>
+        <v>2812</v>
       </c>
       <c r="G214" s="2" t="s">
         <v>15</v>
@@ -25518,7 +25518,7 @@
         <v>14</v>
       </c>
       <c r="F215" s="2">
-        <v>1654</v>
+        <v>989</v>
       </c>
       <c r="G215" s="2" t="s">
         <v>15</v>
@@ -25550,7 +25550,7 @@
         <v>14</v>
       </c>
       <c r="F216" s="2">
-        <v>2327</v>
+        <v>2181</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>15</v>
@@ -25582,7 +25582,7 @@
         <v>14</v>
       </c>
       <c r="F217" s="2">
-        <v>1472</v>
+        <v>2945</v>
       </c>
       <c r="G217" s="2" t="s">
         <v>15</v>
@@ -25614,7 +25614,7 @@
         <v>14</v>
       </c>
       <c r="F218" s="2">
-        <v>3318</v>
+        <v>3770</v>
       </c>
       <c r="G218" s="2" t="s">
         <v>15</v>
@@ -25646,7 +25646,7 @@
         <v>14</v>
       </c>
       <c r="F219" s="2">
-        <v>4336</v>
+        <v>4531</v>
       </c>
       <c r="G219" s="2" t="s">
         <v>15</v>
@@ -25678,7 +25678,7 @@
         <v>14</v>
       </c>
       <c r="F220" s="2">
-        <v>4616</v>
+        <v>4158</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>15</v>
@@ -25710,7 +25710,7 @@
         <v>14</v>
       </c>
       <c r="F221" s="2">
-        <v>3223</v>
+        <v>3592</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>15</v>
@@ -25742,7 +25742,7 @@
         <v>14</v>
       </c>
       <c r="F222" s="2">
-        <v>3040</v>
+        <v>2911</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>15</v>
@@ -25774,7 +25774,7 @@
         <v>14</v>
       </c>
       <c r="F223" s="2">
-        <v>864</v>
+        <v>4742</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>15</v>
@@ -25806,7 +25806,7 @@
         <v>14</v>
       </c>
       <c r="F224" s="2">
-        <v>1338</v>
+        <v>3070</v>
       </c>
       <c r="G224" s="2" t="s">
         <v>15</v>
@@ -25838,7 +25838,7 @@
         <v>14</v>
       </c>
       <c r="F225" s="2">
-        <v>2781</v>
+        <v>1640</v>
       </c>
       <c r="G225" s="2" t="s">
         <v>15</v>
@@ -25870,7 +25870,7 @@
         <v>14</v>
       </c>
       <c r="F226" s="2">
-        <v>3320</v>
+        <v>2033</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>15</v>
@@ -25902,7 +25902,7 @@
         <v>14</v>
       </c>
       <c r="F227" s="2">
-        <v>2164</v>
+        <v>3494</v>
       </c>
       <c r="G227" s="2" t="s">
         <v>15</v>
@@ -25934,7 +25934,7 @@
         <v>14</v>
       </c>
       <c r="F228" s="2">
-        <v>3847</v>
+        <v>2133</v>
       </c>
       <c r="G228" s="2" t="s">
         <v>15</v>
@@ -25966,7 +25966,7 @@
         <v>14</v>
       </c>
       <c r="F229" s="2">
-        <v>4735</v>
+        <v>2284</v>
       </c>
       <c r="G229" s="2" t="s">
         <v>15</v>
@@ -25998,7 +25998,7 @@
         <v>14</v>
       </c>
       <c r="F230" s="2">
-        <v>3537</v>
+        <v>3516</v>
       </c>
       <c r="G230" s="2" t="s">
         <v>15</v>
@@ -26030,7 +26030,7 @@
         <v>14</v>
       </c>
       <c r="F231" s="2">
-        <v>2780</v>
+        <v>2952</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>15</v>
@@ -26062,7 +26062,7 @@
         <v>14</v>
       </c>
       <c r="F232" s="2">
-        <v>1273</v>
+        <v>1554</v>
       </c>
       <c r="G232" s="2" t="s">
         <v>15</v>
@@ -26094,7 +26094,7 @@
         <v>14</v>
       </c>
       <c r="F233" s="2">
-        <v>1000</v>
+        <v>4647</v>
       </c>
       <c r="G233" s="2" t="s">
         <v>15</v>
@@ -26126,7 +26126,7 @@
         <v>14</v>
       </c>
       <c r="F234" s="2">
-        <v>980</v>
+        <v>1604</v>
       </c>
       <c r="G234" s="2" t="s">
         <v>15</v>
@@ -26158,7 +26158,7 @@
         <v>14</v>
       </c>
       <c r="F235" s="2">
-        <v>1534</v>
+        <v>4316</v>
       </c>
       <c r="G235" s="2" t="s">
         <v>15</v>
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="F236" s="2">
-        <v>1035</v>
+        <v>2343</v>
       </c>
       <c r="G236" s="2" t="s">
         <v>15</v>
@@ -26222,7 +26222,7 @@
         <v>14</v>
       </c>
       <c r="F237" s="2">
-        <v>4563</v>
+        <v>1452</v>
       </c>
       <c r="G237" s="2" t="s">
         <v>15</v>
@@ -26254,7 +26254,7 @@
         <v>14</v>
       </c>
       <c r="F238" s="2">
-        <v>3779</v>
+        <v>2138</v>
       </c>
       <c r="G238" s="2" t="s">
         <v>15</v>
@@ -26286,7 +26286,7 @@
         <v>14</v>
       </c>
       <c r="F239" s="2">
-        <v>1171</v>
+        <v>4168</v>
       </c>
       <c r="G239" s="2" t="s">
         <v>15</v>
@@ -26318,7 +26318,7 @@
         <v>14</v>
       </c>
       <c r="F240" s="2">
-        <v>4086</v>
+        <v>1250</v>
       </c>
       <c r="G240" s="2" t="s">
         <v>15</v>
@@ -26350,7 +26350,7 @@
         <v>14</v>
       </c>
       <c r="F241" s="2">
-        <v>4367</v>
+        <v>1422</v>
       </c>
       <c r="G241" s="2" t="s">
         <v>15</v>
@@ -26382,7 +26382,7 @@
         <v>14</v>
       </c>
       <c r="F242" s="2">
-        <v>1304</v>
+        <v>3097</v>
       </c>
       <c r="G242" s="2" t="s">
         <v>15</v>
@@ -26414,7 +26414,7 @@
         <v>14</v>
       </c>
       <c r="F243" s="2">
-        <v>2489</v>
+        <v>2843</v>
       </c>
       <c r="G243" s="2" t="s">
         <v>15</v>
@@ -26446,7 +26446,7 @@
         <v>14</v>
       </c>
       <c r="F244" s="2">
-        <v>2512</v>
+        <v>3177</v>
       </c>
       <c r="G244" s="2" t="s">
         <v>15</v>
@@ -26478,7 +26478,7 @@
         <v>14</v>
       </c>
       <c r="F245" s="2">
-        <v>2455</v>
+        <v>2359</v>
       </c>
       <c r="G245" s="2" t="s">
         <v>15</v>
@@ -26510,7 +26510,7 @@
         <v>14</v>
       </c>
       <c r="F246" s="2">
-        <v>4405</v>
+        <v>2728</v>
       </c>
       <c r="G246" s="2" t="s">
         <v>15</v>
@@ -26542,7 +26542,7 @@
         <v>14</v>
       </c>
       <c r="F247" s="2">
-        <v>3937</v>
+        <v>1416</v>
       </c>
       <c r="G247" s="2" t="s">
         <v>15</v>
@@ -26574,7 +26574,7 @@
         <v>14</v>
       </c>
       <c r="F248" s="2">
-        <v>1222</v>
+        <v>4654</v>
       </c>
       <c r="G248" s="2" t="s">
         <v>15</v>
@@ -26606,7 +26606,7 @@
         <v>14</v>
       </c>
       <c r="F249" s="2">
-        <v>1771</v>
+        <v>1722</v>
       </c>
       <c r="G249" s="2" t="s">
         <v>15</v>
@@ -26638,7 +26638,7 @@
         <v>14</v>
       </c>
       <c r="F250" s="2">
-        <v>3512</v>
+        <v>3977</v>
       </c>
       <c r="G250" s="2" t="s">
         <v>15</v>
@@ -26670,7 +26670,7 @@
         <v>14</v>
       </c>
       <c r="F251" s="2">
-        <v>3379</v>
+        <v>3336</v>
       </c>
       <c r="G251" s="2" t="s">
         <v>15</v>
@@ -26702,7 +26702,7 @@
         <v>14</v>
       </c>
       <c r="F252" s="2">
-        <v>2621</v>
+        <v>4251</v>
       </c>
       <c r="G252" s="2" t="s">
         <v>15</v>
@@ -26734,7 +26734,7 @@
         <v>14</v>
       </c>
       <c r="F253" s="2">
-        <v>2146</v>
+        <v>2676</v>
       </c>
       <c r="G253" s="2" t="s">
         <v>15</v>
@@ -26766,7 +26766,7 @@
         <v>14</v>
       </c>
       <c r="F254" s="2">
-        <v>1819</v>
+        <v>1996</v>
       </c>
       <c r="G254" s="2" t="s">
         <v>15</v>
@@ -26798,7 +26798,7 @@
         <v>14</v>
       </c>
       <c r="F255" s="2">
-        <v>4650</v>
+        <v>1770</v>
       </c>
       <c r="G255" s="2" t="s">
         <v>15</v>
@@ -26830,7 +26830,7 @@
         <v>14</v>
       </c>
       <c r="F256" s="2">
-        <v>1434</v>
+        <v>1820</v>
       </c>
       <c r="G256" s="2" t="s">
         <v>15</v>
@@ -26862,7 +26862,7 @@
         <v>14</v>
       </c>
       <c r="F257" s="2">
-        <v>2467</v>
+        <v>4490</v>
       </c>
       <c r="G257" s="2" t="s">
         <v>15</v>
@@ -26894,7 +26894,7 @@
         <v>14</v>
       </c>
       <c r="F258" s="2">
-        <v>1901</v>
+        <v>3876</v>
       </c>
       <c r="G258" s="2" t="s">
         <v>15</v>
@@ -26926,7 +26926,7 @@
         <v>14</v>
       </c>
       <c r="F259" s="2">
-        <v>1597</v>
+        <v>3163</v>
       </c>
       <c r="G259" s="2" t="s">
         <v>15</v>
@@ -26958,7 +26958,7 @@
         <v>14</v>
       </c>
       <c r="F260" s="2">
-        <v>2487</v>
+        <v>1722</v>
       </c>
       <c r="G260" s="2" t="s">
         <v>15</v>
@@ -26990,7 +26990,7 @@
         <v>14</v>
       </c>
       <c r="F261" s="2">
-        <v>3134</v>
+        <v>2499</v>
       </c>
       <c r="G261" s="2" t="s">
         <v>15</v>
@@ -27022,7 +27022,7 @@
         <v>14</v>
       </c>
       <c r="F262" s="2">
-        <v>2421</v>
+        <v>910</v>
       </c>
       <c r="G262" s="2" t="s">
         <v>15</v>
@@ -27054,7 +27054,7 @@
         <v>14</v>
       </c>
       <c r="F263" s="2">
-        <v>2337</v>
+        <v>2702</v>
       </c>
       <c r="G263" s="2" t="s">
         <v>15</v>
@@ -27086,7 +27086,7 @@
         <v>14</v>
       </c>
       <c r="F264" s="2">
-        <v>1267</v>
+        <v>4643</v>
       </c>
       <c r="G264" s="2" t="s">
         <v>15</v>
@@ -27118,7 +27118,7 @@
         <v>14</v>
       </c>
       <c r="F265" s="2">
-        <v>1490</v>
+        <v>2863</v>
       </c>
       <c r="G265" s="2" t="s">
         <v>15</v>
@@ -27150,7 +27150,7 @@
         <v>14</v>
       </c>
       <c r="F266" s="2">
-        <v>3669</v>
+        <v>2547</v>
       </c>
       <c r="G266" s="2" t="s">
         <v>15</v>
@@ -27182,7 +27182,7 @@
         <v>14</v>
       </c>
       <c r="F267" s="2">
-        <v>2660</v>
+        <v>4108</v>
       </c>
       <c r="G267" s="2" t="s">
         <v>15</v>
@@ -27214,7 +27214,7 @@
         <v>14</v>
       </c>
       <c r="F268" s="2">
-        <v>3770</v>
+        <v>4154</v>
       </c>
       <c r="G268" s="2" t="s">
         <v>15</v>
@@ -27246,7 +27246,7 @@
         <v>14</v>
       </c>
       <c r="F269" s="2">
-        <v>2780</v>
+        <v>3642</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>15</v>
@@ -27278,7 +27278,7 @@
         <v>14</v>
       </c>
       <c r="F270" s="2">
-        <v>4576</v>
+        <v>4628</v>
       </c>
       <c r="G270" s="2" t="s">
         <v>15</v>
@@ -27310,7 +27310,7 @@
         <v>14</v>
       </c>
       <c r="F271" s="2">
-        <v>1518</v>
+        <v>3318</v>
       </c>
       <c r="G271" s="2" t="s">
         <v>15</v>
@@ -27342,7 +27342,7 @@
         <v>14</v>
       </c>
       <c r="F272" s="2">
-        <v>3792</v>
+        <v>1957</v>
       </c>
       <c r="G272" s="2" t="s">
         <v>15</v>
@@ -27374,7 +27374,7 @@
         <v>14</v>
       </c>
       <c r="F273" s="2">
-        <v>2752</v>
+        <v>3930</v>
       </c>
       <c r="G273" s="2" t="s">
         <v>15</v>
@@ -27406,7 +27406,7 @@
         <v>14</v>
       </c>
       <c r="F274" s="2">
-        <v>4082</v>
+        <v>3987</v>
       </c>
       <c r="G274" s="2" t="s">
         <v>15</v>
@@ -27438,7 +27438,7 @@
         <v>14</v>
       </c>
       <c r="F275" s="2">
-        <v>1449</v>
+        <v>4345</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>15</v>
@@ -27470,7 +27470,7 @@
         <v>14</v>
       </c>
       <c r="F276" s="2">
-        <v>4308</v>
+        <v>1921</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>15</v>
@@ -27502,7 +27502,7 @@
         <v>14</v>
       </c>
       <c r="F277" s="2">
-        <v>4712</v>
+        <v>1253</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>15</v>
@@ -27534,7 +27534,7 @@
         <v>14</v>
       </c>
       <c r="F278" s="2">
-        <v>2008</v>
+        <v>2022</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>15</v>
@@ -27566,7 +27566,7 @@
         <v>14</v>
       </c>
       <c r="F279" s="2">
-        <v>3013</v>
+        <v>2998</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>15</v>
@@ -27598,7 +27598,7 @@
         <v>14</v>
       </c>
       <c r="F280" s="2">
-        <v>3187</v>
+        <v>3613</v>
       </c>
       <c r="G280" s="2" t="s">
         <v>15</v>
@@ -27630,7 +27630,7 @@
         <v>14</v>
       </c>
       <c r="F281" s="2">
-        <v>2340</v>
+        <v>807</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>15</v>
@@ -27662,7 +27662,7 @@
         <v>14</v>
       </c>
       <c r="F282" s="2">
-        <v>860</v>
+        <v>4471</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>15</v>
@@ -27694,7 +27694,7 @@
         <v>14</v>
       </c>
       <c r="F283" s="2">
-        <v>1154</v>
+        <v>3254</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>15</v>
@@ -27726,7 +27726,7 @@
         <v>14</v>
       </c>
       <c r="F284" s="2">
-        <v>1256</v>
+        <v>4358</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>15</v>
@@ -27758,7 +27758,7 @@
         <v>14</v>
       </c>
       <c r="F285" s="2">
-        <v>3173</v>
+        <v>1124</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>15</v>
@@ -27790,7 +27790,7 @@
         <v>14</v>
       </c>
       <c r="F286" s="2">
-        <v>1962</v>
+        <v>1101</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>15</v>
@@ -27822,7 +27822,7 @@
         <v>14</v>
       </c>
       <c r="F287" s="2">
-        <v>986</v>
+        <v>3255</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>15</v>
@@ -27854,7 +27854,7 @@
         <v>14</v>
       </c>
       <c r="F288" s="2">
-        <v>2447</v>
+        <v>3697</v>
       </c>
       <c r="G288" s="2" t="s">
         <v>15</v>
@@ -27886,7 +27886,7 @@
         <v>14</v>
       </c>
       <c r="F289" s="2">
-        <v>2781</v>
+        <v>4281</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>15</v>
@@ -27918,7 +27918,7 @@
         <v>14</v>
       </c>
       <c r="F290" s="2">
-        <v>3049</v>
+        <v>1054</v>
       </c>
       <c r="G290" s="2" t="s">
         <v>15</v>
@@ -27950,7 +27950,7 @@
         <v>14</v>
       </c>
       <c r="F291" s="2">
-        <v>4730</v>
+        <v>2897</v>
       </c>
       <c r="G291" s="2" t="s">
         <v>15</v>
@@ -27982,7 +27982,7 @@
         <v>14</v>
       </c>
       <c r="F292" s="2">
-        <v>834</v>
+        <v>1373</v>
       </c>
       <c r="G292" s="2" t="s">
         <v>15</v>
@@ -28014,7 +28014,7 @@
         <v>14</v>
       </c>
       <c r="F293" s="2">
-        <v>1405</v>
+        <v>887</v>
       </c>
       <c r="G293" s="2" t="s">
         <v>15</v>
@@ -28046,7 +28046,7 @@
         <v>14</v>
       </c>
       <c r="F294" s="2">
-        <v>3634</v>
+        <v>2040</v>
       </c>
       <c r="G294" s="2" t="s">
         <v>15</v>
@@ -28078,7 +28078,7 @@
         <v>14</v>
       </c>
       <c r="F295" s="2">
-        <v>4254</v>
+        <v>4415</v>
       </c>
       <c r="G295" s="2" t="s">
         <v>15</v>
@@ -28110,7 +28110,7 @@
         <v>14</v>
       </c>
       <c r="F296" s="2">
-        <v>1094</v>
+        <v>2494</v>
       </c>
       <c r="G296" s="2" t="s">
         <v>15</v>
@@ -28142,7 +28142,7 @@
         <v>14</v>
       </c>
       <c r="F297" s="2">
-        <v>3193</v>
+        <v>1742</v>
       </c>
       <c r="G297" s="2" t="s">
         <v>15</v>
@@ -28174,7 +28174,7 @@
         <v>14</v>
       </c>
       <c r="F298" s="2">
-        <v>4132</v>
+        <v>1798</v>
       </c>
       <c r="G298" s="2" t="s">
         <v>15</v>
@@ -28206,7 +28206,7 @@
         <v>14</v>
       </c>
       <c r="F299" s="2">
-        <v>1380</v>
+        <v>3553</v>
       </c>
       <c r="G299" s="2" t="s">
         <v>15</v>
@@ -28238,7 +28238,7 @@
         <v>14</v>
       </c>
       <c r="F300" s="2">
-        <v>873</v>
+        <v>1723</v>
       </c>
       <c r="G300" s="2" t="s">
         <v>15</v>
@@ -28270,7 +28270,7 @@
         <v>14</v>
       </c>
       <c r="F301" s="2">
-        <v>1152</v>
+        <v>2306</v>
       </c>
       <c r="G301" s="2" t="s">
         <v>15</v>
@@ -28302,7 +28302,7 @@
         <v>14</v>
       </c>
       <c r="F302" s="2">
-        <v>4240</v>
+        <v>3825</v>
       </c>
       <c r="G302" s="2" t="s">
         <v>15</v>
@@ -28334,7 +28334,7 @@
         <v>14</v>
       </c>
       <c r="F303" s="2">
-        <v>3786</v>
+        <v>3748</v>
       </c>
       <c r="G303" s="2" t="s">
         <v>15</v>
@@ -28366,7 +28366,7 @@
         <v>14</v>
       </c>
       <c r="F304" s="2">
-        <v>1565</v>
+        <v>4042</v>
       </c>
       <c r="G304" s="2" t="s">
         <v>15</v>
@@ -28398,7 +28398,7 @@
         <v>14</v>
       </c>
       <c r="F305" s="2">
-        <v>3948</v>
+        <v>1718</v>
       </c>
       <c r="G305" s="2" t="s">
         <v>15</v>
@@ -28430,7 +28430,7 @@
         <v>14</v>
       </c>
       <c r="F306" s="2">
-        <v>1533</v>
+        <v>2459</v>
       </c>
       <c r="G306" s="2" t="s">
         <v>15</v>
@@ -28462,7 +28462,7 @@
         <v>14</v>
       </c>
       <c r="F307" s="2">
-        <v>2890</v>
+        <v>3958</v>
       </c>
       <c r="G307" s="2" t="s">
         <v>15</v>
@@ -28494,7 +28494,7 @@
         <v>14</v>
       </c>
       <c r="F308" s="2">
-        <v>2989</v>
+        <v>3693</v>
       </c>
       <c r="G308" s="2" t="s">
         <v>15</v>
@@ -28526,7 +28526,7 @@
         <v>14</v>
       </c>
       <c r="F309" s="2">
-        <v>1814</v>
+        <v>2395</v>
       </c>
       <c r="G309" s="2" t="s">
         <v>15</v>
@@ -28558,7 +28558,7 @@
         <v>14</v>
       </c>
       <c r="F310" s="2">
-        <v>3068</v>
+        <v>1596</v>
       </c>
       <c r="G310" s="2" t="s">
         <v>15</v>
@@ -28590,7 +28590,7 @@
         <v>14</v>
       </c>
       <c r="F311" s="2">
-        <v>3033</v>
+        <v>4551</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>15</v>
@@ -28622,7 +28622,7 @@
         <v>14</v>
       </c>
       <c r="F312" s="2">
-        <v>3715</v>
+        <v>1825</v>
       </c>
       <c r="G312" s="2" t="s">
         <v>15</v>
@@ -28654,7 +28654,7 @@
         <v>14</v>
       </c>
       <c r="F313" s="2">
-        <v>3016</v>
+        <v>948</v>
       </c>
       <c r="G313" s="2" t="s">
         <v>15</v>
@@ -28686,7 +28686,7 @@
         <v>14</v>
       </c>
       <c r="F314" s="2">
-        <v>4382</v>
+        <v>1711</v>
       </c>
       <c r="G314" s="2" t="s">
         <v>15</v>
@@ -28718,7 +28718,7 @@
         <v>14</v>
       </c>
       <c r="F315" s="2">
-        <v>3241</v>
+        <v>980</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>15</v>
@@ -28750,7 +28750,7 @@
         <v>14</v>
       </c>
       <c r="F316" s="2">
-        <v>3841</v>
+        <v>1981</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>15</v>
@@ -28782,7 +28782,7 @@
         <v>14</v>
       </c>
       <c r="F317" s="2">
-        <v>4285</v>
+        <v>4536</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>15</v>
@@ -28814,7 +28814,7 @@
         <v>14</v>
       </c>
       <c r="F318" s="2">
-        <v>2176</v>
+        <v>2435</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>15</v>
@@ -28846,7 +28846,7 @@
         <v>14</v>
       </c>
       <c r="F319" s="2">
-        <v>4589</v>
+        <v>3880</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>15</v>
@@ -28878,7 +28878,7 @@
         <v>14</v>
       </c>
       <c r="F320" s="2">
-        <v>4576</v>
+        <v>2877</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>15</v>
@@ -28910,7 +28910,7 @@
         <v>14</v>
       </c>
       <c r="F321" s="2">
-        <v>4680</v>
+        <v>1338</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>15</v>
@@ -28942,7 +28942,7 @@
         <v>14</v>
       </c>
       <c r="F322" s="2">
-        <v>4080</v>
+        <v>3047</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>15</v>
@@ -28974,7 +28974,7 @@
         <v>14</v>
       </c>
       <c r="F323" s="2">
-        <v>4777</v>
+        <v>3459</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>15</v>
@@ -29006,7 +29006,7 @@
         <v>14</v>
       </c>
       <c r="F324" s="2">
-        <v>1336</v>
+        <v>4687</v>
       </c>
       <c r="G324" s="2" t="s">
         <v>15</v>
@@ -29038,7 +29038,7 @@
         <v>14</v>
       </c>
       <c r="F325" s="2">
-        <v>2545</v>
+        <v>2614</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>15</v>
@@ -29070,7 +29070,7 @@
         <v>14</v>
       </c>
       <c r="F326" s="2">
-        <v>4636</v>
+        <v>1026</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>15</v>
@@ -29102,7 +29102,7 @@
         <v>14</v>
       </c>
       <c r="F327" s="2">
-        <v>3769</v>
+        <v>2096</v>
       </c>
       <c r="G327" s="2" t="s">
         <v>15</v>
@@ -29134,7 +29134,7 @@
         <v>14</v>
       </c>
       <c r="F328" s="2">
-        <v>3441</v>
+        <v>2464</v>
       </c>
       <c r="G328" s="2" t="s">
         <v>15</v>
@@ -29166,7 +29166,7 @@
         <v>14</v>
       </c>
       <c r="F329" s="2">
-        <v>2624</v>
+        <v>2928</v>
       </c>
       <c r="G329" s="2" t="s">
         <v>15</v>
@@ -29198,7 +29198,7 @@
         <v>14</v>
       </c>
       <c r="F330" s="2">
-        <v>3485</v>
+        <v>4415</v>
       </c>
       <c r="G330" s="2" t="s">
         <v>15</v>
@@ -29230,7 +29230,7 @@
         <v>14</v>
       </c>
       <c r="F331" s="2">
-        <v>3422</v>
+        <v>4562</v>
       </c>
       <c r="G331" s="2" t="s">
         <v>15</v>
@@ -29262,7 +29262,7 @@
         <v>14</v>
       </c>
       <c r="F332" s="2">
-        <v>2592</v>
+        <v>1700</v>
       </c>
       <c r="G332" s="2" t="s">
         <v>15</v>
@@ -29294,7 +29294,7 @@
         <v>14</v>
       </c>
       <c r="F333" s="2">
-        <v>4724</v>
+        <v>3357</v>
       </c>
       <c r="G333" s="2" t="s">
         <v>15</v>
@@ -29326,7 +29326,7 @@
         <v>14</v>
       </c>
       <c r="F334" s="2">
-        <v>4528</v>
+        <v>1863</v>
       </c>
       <c r="G334" s="2" t="s">
         <v>15</v>
@@ -29358,7 +29358,7 @@
         <v>14</v>
       </c>
       <c r="F335" s="2">
-        <v>4125</v>
+        <v>3474</v>
       </c>
       <c r="G335" s="2" t="s">
         <v>15</v>
@@ -29390,7 +29390,7 @@
         <v>14</v>
       </c>
       <c r="F336" s="2">
-        <v>4022</v>
+        <v>4591</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>15</v>
@@ -29422,7 +29422,7 @@
         <v>14</v>
       </c>
       <c r="F337" s="2">
-        <v>2858</v>
+        <v>3919</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>15</v>
@@ -29454,7 +29454,7 @@
         <v>14</v>
       </c>
       <c r="F338" s="2">
-        <v>1240</v>
+        <v>4643</v>
       </c>
       <c r="G338" s="2" t="s">
         <v>15</v>
@@ -29486,7 +29486,7 @@
         <v>14</v>
       </c>
       <c r="F339" s="2">
-        <v>3100</v>
+        <v>3323</v>
       </c>
       <c r="G339" s="2" t="s">
         <v>15</v>
@@ -29518,7 +29518,7 @@
         <v>14</v>
       </c>
       <c r="F340" s="2">
-        <v>2081</v>
+        <v>4243</v>
       </c>
       <c r="G340" s="2" t="s">
         <v>15</v>
@@ -29550,7 +29550,7 @@
         <v>14</v>
       </c>
       <c r="F341" s="2">
-        <v>4569</v>
+        <v>3662</v>
       </c>
       <c r="G341" s="2" t="s">
         <v>15</v>
@@ -29582,7 +29582,7 @@
         <v>14</v>
       </c>
       <c r="F342" s="2">
-        <v>4709</v>
+        <v>1394</v>
       </c>
       <c r="G342" s="2" t="s">
         <v>15</v>
@@ -29614,7 +29614,7 @@
         <v>14</v>
       </c>
       <c r="F343" s="2">
-        <v>3788</v>
+        <v>4344</v>
       </c>
       <c r="G343" s="2" t="s">
         <v>15</v>
@@ -29646,7 +29646,7 @@
         <v>14</v>
       </c>
       <c r="F344" s="2">
-        <v>2648</v>
+        <v>1842</v>
       </c>
       <c r="G344" s="2" t="s">
         <v>15</v>
@@ -29678,7 +29678,7 @@
         <v>14</v>
       </c>
       <c r="F345" s="2">
-        <v>3902</v>
+        <v>4693</v>
       </c>
       <c r="G345" s="2" t="s">
         <v>15</v>
@@ -29710,7 +29710,7 @@
         <v>14</v>
       </c>
       <c r="F346" s="2">
-        <v>2406</v>
+        <v>3347</v>
       </c>
       <c r="G346" s="2" t="s">
         <v>15</v>
@@ -29742,7 +29742,7 @@
         <v>14</v>
       </c>
       <c r="F347" s="2">
-        <v>1244</v>
+        <v>4243</v>
       </c>
       <c r="G347" s="2" t="s">
         <v>15</v>
@@ -29774,7 +29774,7 @@
         <v>14</v>
       </c>
       <c r="F348" s="2">
-        <v>2079</v>
+        <v>4316</v>
       </c>
       <c r="G348" s="2" t="s">
         <v>15</v>
@@ -29806,7 +29806,7 @@
         <v>14</v>
       </c>
       <c r="F349" s="2">
-        <v>886</v>
+        <v>2481</v>
       </c>
       <c r="G349" s="2" t="s">
         <v>15</v>
@@ -29838,7 +29838,7 @@
         <v>14</v>
       </c>
       <c r="F350" s="2">
-        <v>4373</v>
+        <v>2343</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>15</v>
@@ -29870,7 +29870,7 @@
         <v>14</v>
       </c>
       <c r="F351" s="2">
-        <v>847</v>
+        <v>932</v>
       </c>
       <c r="G351" s="2" t="s">
         <v>15</v>
@@ -29902,7 +29902,7 @@
         <v>14</v>
       </c>
       <c r="F352" s="2">
-        <v>3842</v>
+        <v>1877</v>
       </c>
       <c r="G352" s="2" t="s">
         <v>15</v>
@@ -29934,7 +29934,7 @@
         <v>14</v>
       </c>
       <c r="F353" s="2">
-        <v>1466</v>
+        <v>3878</v>
       </c>
       <c r="G353" s="2" t="s">
         <v>15</v>
@@ -29966,7 +29966,7 @@
         <v>14</v>
       </c>
       <c r="F354" s="2">
-        <v>3293</v>
+        <v>2023</v>
       </c>
       <c r="G354" s="2" t="s">
         <v>15</v>
@@ -29998,7 +29998,7 @@
         <v>14</v>
       </c>
       <c r="F355" s="2">
-        <v>4531</v>
+        <v>3351</v>
       </c>
       <c r="G355" s="2" t="s">
         <v>15</v>
@@ -30030,7 +30030,7 @@
         <v>14</v>
       </c>
       <c r="F356" s="2">
-        <v>1494</v>
+        <v>1610</v>
       </c>
       <c r="G356" s="2" t="s">
         <v>15</v>
@@ -30062,7 +30062,7 @@
         <v>14</v>
       </c>
       <c r="F357" s="2">
-        <v>3265</v>
+        <v>4169</v>
       </c>
       <c r="G357" s="2" t="s">
         <v>15</v>
@@ -30094,7 +30094,7 @@
         <v>14</v>
       </c>
       <c r="F358" s="2">
-        <v>4437</v>
+        <v>3435</v>
       </c>
       <c r="G358" s="2" t="s">
         <v>15</v>
@@ -30126,7 +30126,7 @@
         <v>14</v>
       </c>
       <c r="F359" s="2">
-        <v>2560</v>
+        <v>3926</v>
       </c>
       <c r="G359" s="2" t="s">
         <v>15</v>
@@ -30158,7 +30158,7 @@
         <v>14</v>
       </c>
       <c r="F360" s="2">
-        <v>3463</v>
+        <v>3200</v>
       </c>
       <c r="G360" s="2" t="s">
         <v>15</v>
@@ -30190,7 +30190,7 @@
         <v>14</v>
       </c>
       <c r="F361" s="2">
-        <v>2541</v>
+        <v>3023</v>
       </c>
       <c r="G361" s="2" t="s">
         <v>15</v>
@@ -30222,7 +30222,7 @@
         <v>14</v>
       </c>
       <c r="F362" s="2">
-        <v>4594</v>
+        <v>4262</v>
       </c>
       <c r="G362" s="2" t="s">
         <v>15</v>
@@ -30254,7 +30254,7 @@
         <v>14</v>
       </c>
       <c r="F363" s="2">
-        <v>2644</v>
+        <v>4163</v>
       </c>
       <c r="G363" s="2" t="s">
         <v>15</v>
@@ -30286,7 +30286,7 @@
         <v>14</v>
       </c>
       <c r="F364" s="2">
-        <v>3293</v>
+        <v>2145</v>
       </c>
       <c r="G364" s="2" t="s">
         <v>15</v>
@@ -30318,7 +30318,7 @@
         <v>14</v>
       </c>
       <c r="F365" s="2">
-        <v>2247</v>
+        <v>1426</v>
       </c>
       <c r="G365" s="2" t="s">
         <v>15</v>
@@ -30350,7 +30350,7 @@
         <v>14</v>
       </c>
       <c r="F366" s="2">
-        <v>4418</v>
+        <v>2739</v>
       </c>
       <c r="G366" s="2" t="s">
         <v>15</v>
@@ -30382,7 +30382,7 @@
         <v>14</v>
       </c>
       <c r="F367" s="2">
-        <v>4193</v>
+        <v>4777</v>
       </c>
       <c r="G367" s="2" t="s">
         <v>15</v>
@@ -30414,7 +30414,7 @@
         <v>14</v>
       </c>
       <c r="F368" s="2">
-        <v>1182</v>
+        <v>2027</v>
       </c>
       <c r="G368" s="2" t="s">
         <v>15</v>
@@ -30446,7 +30446,7 @@
         <v>14</v>
       </c>
       <c r="F369" s="2">
-        <v>1360</v>
+        <v>3574</v>
       </c>
       <c r="G369" s="2" t="s">
         <v>15</v>
@@ -30478,7 +30478,7 @@
         <v>14</v>
       </c>
       <c r="F370" s="2">
-        <v>3616</v>
+        <v>2746</v>
       </c>
       <c r="G370" s="2" t="s">
         <v>15</v>
@@ -30510,7 +30510,7 @@
         <v>14</v>
       </c>
       <c r="F371" s="2">
-        <v>3303</v>
+        <v>3676</v>
       </c>
       <c r="G371" s="2" t="s">
         <v>15</v>
@@ -30542,7 +30542,7 @@
         <v>14</v>
       </c>
       <c r="F372" s="2">
-        <v>1425</v>
+        <v>2155</v>
       </c>
       <c r="G372" s="2" t="s">
         <v>15</v>
@@ -30574,7 +30574,7 @@
         <v>14</v>
       </c>
       <c r="F373" s="2">
-        <v>3463</v>
+        <v>1410</v>
       </c>
       <c r="G373" s="2" t="s">
         <v>15</v>
@@ -30606,7 +30606,7 @@
         <v>14</v>
       </c>
       <c r="F374" s="2">
-        <v>2794</v>
+        <v>4289</v>
       </c>
       <c r="G374" s="2" t="s">
         <v>15</v>
@@ -30638,7 +30638,7 @@
         <v>14</v>
       </c>
       <c r="F375" s="2">
-        <v>3892</v>
+        <v>3804</v>
       </c>
       <c r="G375" s="2" t="s">
         <v>15</v>
@@ -30670,7 +30670,7 @@
         <v>14</v>
       </c>
       <c r="F376" s="2">
-        <v>3303</v>
+        <v>4341</v>
       </c>
       <c r="G376" s="2" t="s">
         <v>15</v>
@@ -30702,7 +30702,7 @@
         <v>14</v>
       </c>
       <c r="F377" s="2">
-        <v>826</v>
+        <v>1605</v>
       </c>
       <c r="G377" s="2" t="s">
         <v>15</v>
@@ -30734,7 +30734,7 @@
         <v>14</v>
       </c>
       <c r="F378" s="2">
-        <v>1413</v>
+        <v>3466</v>
       </c>
       <c r="G378" s="2" t="s">
         <v>15</v>
@@ -30766,7 +30766,7 @@
         <v>14</v>
       </c>
       <c r="F379" s="2">
-        <v>4269</v>
+        <v>4511</v>
       </c>
       <c r="G379" s="2" t="s">
         <v>15</v>
@@ -30798,7 +30798,7 @@
         <v>14</v>
       </c>
       <c r="F380" s="2">
-        <v>4532</v>
+        <v>1605</v>
       </c>
       <c r="G380" s="2" t="s">
         <v>15</v>
@@ -30830,7 +30830,7 @@
         <v>14</v>
       </c>
       <c r="F381" s="2">
-        <v>990</v>
+        <v>3584</v>
       </c>
       <c r="G381" s="2" t="s">
         <v>15</v>
@@ -30862,7 +30862,7 @@
         <v>14</v>
       </c>
       <c r="F382" s="2">
-        <v>3756</v>
+        <v>881</v>
       </c>
       <c r="G382" s="2" t="s">
         <v>15</v>
@@ -30894,7 +30894,7 @@
         <v>14</v>
       </c>
       <c r="F383" s="2">
-        <v>4552</v>
+        <v>2372</v>
       </c>
       <c r="G383" s="2" t="s">
         <v>15</v>
@@ -30926,7 +30926,7 @@
         <v>14</v>
       </c>
       <c r="F384" s="2">
-        <v>2810</v>
+        <v>4743</v>
       </c>
       <c r="G384" s="2" t="s">
         <v>15</v>
@@ -30958,7 +30958,7 @@
         <v>14</v>
       </c>
       <c r="F385" s="2">
-        <v>4454</v>
+        <v>3690</v>
       </c>
       <c r="G385" s="2" t="s">
         <v>15</v>
@@ -30990,7 +30990,7 @@
         <v>14</v>
       </c>
       <c r="F386" s="2">
-        <v>2727</v>
+        <v>1886</v>
       </c>
       <c r="G386" s="2" t="s">
         <v>15</v>
@@ -31022,7 +31022,7 @@
         <v>14</v>
       </c>
       <c r="F387" s="2">
-        <v>2029</v>
+        <v>2744</v>
       </c>
       <c r="G387" s="2" t="s">
         <v>15</v>
@@ -31054,7 +31054,7 @@
         <v>14</v>
       </c>
       <c r="F388" s="2">
-        <v>2372</v>
+        <v>1616</v>
       </c>
       <c r="G388" s="2" t="s">
         <v>15</v>
@@ -31086,7 +31086,7 @@
         <v>14</v>
       </c>
       <c r="F389" s="2">
-        <v>3264</v>
+        <v>3729</v>
       </c>
       <c r="G389" s="2" t="s">
         <v>15</v>
@@ -31118,7 +31118,7 @@
         <v>14</v>
       </c>
       <c r="F390" s="2">
-        <v>4590</v>
+        <v>2901</v>
       </c>
       <c r="G390" s="2" t="s">
         <v>15</v>
@@ -31150,7 +31150,7 @@
         <v>14</v>
       </c>
       <c r="F391" s="2">
-        <v>3366</v>
+        <v>1763</v>
       </c>
       <c r="G391" s="2" t="s">
         <v>15</v>
@@ -31182,7 +31182,7 @@
         <v>14</v>
       </c>
       <c r="F392" s="2">
-        <v>3193</v>
+        <v>2508</v>
       </c>
       <c r="G392" s="2" t="s">
         <v>15</v>
@@ -31214,7 +31214,7 @@
         <v>14</v>
       </c>
       <c r="F393" s="2">
-        <v>1374</v>
+        <v>4065</v>
       </c>
       <c r="G393" s="2" t="s">
         <v>15</v>
@@ -31246,7 +31246,7 @@
         <v>14</v>
       </c>
       <c r="F394" s="2">
-        <v>1423</v>
+        <v>1782</v>
       </c>
       <c r="G394" s="2" t="s">
         <v>15</v>
@@ -31278,7 +31278,7 @@
         <v>14</v>
       </c>
       <c r="F395" s="2">
-        <v>2934</v>
+        <v>3820</v>
       </c>
       <c r="G395" s="2" t="s">
         <v>15</v>
@@ -31310,7 +31310,7 @@
         <v>14</v>
       </c>
       <c r="F396" s="2">
-        <v>3168</v>
+        <v>3924</v>
       </c>
       <c r="G396" s="2" t="s">
         <v>15</v>
@@ -31342,7 +31342,7 @@
         <v>14</v>
       </c>
       <c r="F397" s="2">
-        <v>2985</v>
+        <v>2202</v>
       </c>
       <c r="G397" s="2" t="s">
         <v>15</v>
@@ -31374,7 +31374,7 @@
         <v>14</v>
       </c>
       <c r="F398" s="2">
-        <v>2987</v>
+        <v>3389</v>
       </c>
       <c r="G398" s="2" t="s">
         <v>15</v>
@@ -31406,7 +31406,7 @@
         <v>14</v>
       </c>
       <c r="F399" s="2">
-        <v>3049</v>
+        <v>1459</v>
       </c>
       <c r="G399" s="2" t="s">
         <v>15</v>
@@ -31438,7 +31438,7 @@
         <v>14</v>
       </c>
       <c r="F400" s="2">
-        <v>1107</v>
+        <v>2506</v>
       </c>
       <c r="G400" s="2" t="s">
         <v>15</v>
@@ -31470,7 +31470,7 @@
         <v>14</v>
       </c>
       <c r="F401" s="2">
-        <v>2478</v>
+        <v>3798</v>
       </c>
       <c r="G401" s="2" t="s">
         <v>15</v>
@@ -31502,7 +31502,7 @@
         <v>14</v>
       </c>
       <c r="F402" s="2">
-        <v>3648</v>
+        <v>4518</v>
       </c>
       <c r="G402" s="2" t="s">
         <v>15</v>
@@ -31534,7 +31534,7 @@
         <v>14</v>
       </c>
       <c r="F403" s="2">
-        <v>3803</v>
+        <v>2416</v>
       </c>
       <c r="G403" s="2" t="s">
         <v>15</v>
@@ -31566,7 +31566,7 @@
         <v>14</v>
       </c>
       <c r="F404" s="2">
-        <v>1767</v>
+        <v>1249</v>
       </c>
       <c r="G404" s="2" t="s">
         <v>15</v>
@@ -31598,7 +31598,7 @@
         <v>14</v>
       </c>
       <c r="F405" s="2">
-        <v>3038</v>
+        <v>4430</v>
       </c>
       <c r="G405" s="2" t="s">
         <v>15</v>
@@ -31630,7 +31630,7 @@
         <v>14</v>
       </c>
       <c r="F406" s="2">
-        <v>1358</v>
+        <v>4657</v>
       </c>
       <c r="G406" s="2" t="s">
         <v>15</v>
@@ -31662,7 +31662,7 @@
         <v>14</v>
       </c>
       <c r="F407" s="2">
-        <v>3005</v>
+        <v>2057</v>
       </c>
       <c r="G407" s="2" t="s">
         <v>15</v>
@@ -31694,7 +31694,7 @@
         <v>14</v>
       </c>
       <c r="F408" s="2">
-        <v>4329</v>
+        <v>3691</v>
       </c>
       <c r="G408" s="2" t="s">
         <v>15</v>
@@ -31726,7 +31726,7 @@
         <v>14</v>
       </c>
       <c r="F409" s="2">
-        <v>1083</v>
+        <v>4418</v>
       </c>
       <c r="G409" s="2" t="s">
         <v>15</v>
@@ -31758,7 +31758,7 @@
         <v>14</v>
       </c>
       <c r="F410" s="2">
-        <v>3948</v>
+        <v>2407</v>
       </c>
       <c r="G410" s="2" t="s">
         <v>15</v>
@@ -31790,7 +31790,7 @@
         <v>14</v>
       </c>
       <c r="F411" s="2">
-        <v>1136</v>
+        <v>886</v>
       </c>
       <c r="G411" s="2" t="s">
         <v>15</v>
@@ -31822,7 +31822,7 @@
         <v>14</v>
       </c>
       <c r="F412" s="2">
-        <v>2358</v>
+        <v>1245</v>
       </c>
       <c r="G412" s="2" t="s">
         <v>15</v>
@@ -31854,7 +31854,7 @@
         <v>14</v>
       </c>
       <c r="F413" s="2">
-        <v>2529</v>
+        <v>1606</v>
       </c>
       <c r="G413" s="2" t="s">
         <v>15</v>
@@ -31886,7 +31886,7 @@
         <v>14</v>
       </c>
       <c r="F414" s="2">
-        <v>3387</v>
+        <v>1886</v>
       </c>
       <c r="G414" s="2" t="s">
         <v>15</v>
@@ -31918,7 +31918,7 @@
         <v>14</v>
       </c>
       <c r="F415" s="2">
-        <v>4242</v>
+        <v>2356</v>
       </c>
       <c r="G415" s="2" t="s">
         <v>15</v>
@@ -31950,7 +31950,7 @@
         <v>14</v>
       </c>
       <c r="F416" s="2">
-        <v>1774</v>
+        <v>3075</v>
       </c>
       <c r="G416" s="2" t="s">
         <v>15</v>
@@ -31982,7 +31982,7 @@
         <v>14</v>
       </c>
       <c r="F417" s="2">
-        <v>3070</v>
+        <v>4305</v>
       </c>
       <c r="G417" s="2" t="s">
         <v>15</v>
@@ -32014,7 +32014,7 @@
         <v>14</v>
       </c>
       <c r="F418" s="2">
-        <v>2875</v>
+        <v>4026</v>
       </c>
       <c r="G418" s="2" t="s">
         <v>15</v>
@@ -32046,7 +32046,7 @@
         <v>14</v>
       </c>
       <c r="F419" s="2">
-        <v>2336</v>
+        <v>4787</v>
       </c>
       <c r="G419" s="2" t="s">
         <v>15</v>
@@ -32078,7 +32078,7 @@
         <v>14</v>
       </c>
       <c r="F420" s="2">
-        <v>2650</v>
+        <v>1465</v>
       </c>
       <c r="G420" s="2" t="s">
         <v>15</v>
@@ -32110,7 +32110,7 @@
         <v>14</v>
       </c>
       <c r="F421" s="2">
-        <v>1803</v>
+        <v>1251</v>
       </c>
       <c r="G421" s="2" t="s">
         <v>15</v>
@@ -32142,7 +32142,7 @@
         <v>14</v>
       </c>
       <c r="F422" s="2">
-        <v>4086</v>
+        <v>3593</v>
       </c>
       <c r="G422" s="2" t="s">
         <v>15</v>
@@ -32174,7 +32174,7 @@
         <v>14</v>
       </c>
       <c r="F423" s="2">
-        <v>1645</v>
+        <v>961</v>
       </c>
       <c r="G423" s="2" t="s">
         <v>15</v>
@@ -32206,7 +32206,7 @@
         <v>14</v>
       </c>
       <c r="F424" s="2">
-        <v>4207</v>
+        <v>4561</v>
       </c>
       <c r="G424" s="2" t="s">
         <v>15</v>
@@ -32238,7 +32238,7 @@
         <v>14</v>
       </c>
       <c r="F425" s="2">
-        <v>2967</v>
+        <v>3789</v>
       </c>
       <c r="G425" s="2" t="s">
         <v>15</v>
@@ -32270,7 +32270,7 @@
         <v>14</v>
       </c>
       <c r="F426" s="2">
-        <v>1766</v>
+        <v>1865</v>
       </c>
       <c r="G426" s="2" t="s">
         <v>15</v>
@@ -32302,7 +32302,7 @@
         <v>14</v>
       </c>
       <c r="F427" s="2">
-        <v>2784</v>
+        <v>3054</v>
       </c>
       <c r="G427" s="2" t="s">
         <v>15</v>
@@ -32334,7 +32334,7 @@
         <v>14</v>
       </c>
       <c r="F428" s="2">
-        <v>3858</v>
+        <v>3806</v>
       </c>
       <c r="G428" s="2" t="s">
         <v>15</v>
@@ -32366,7 +32366,7 @@
         <v>14</v>
       </c>
       <c r="F429" s="2">
-        <v>1997</v>
+        <v>3632</v>
       </c>
       <c r="G429" s="2" t="s">
         <v>15</v>
@@ -32398,7 +32398,7 @@
         <v>14</v>
       </c>
       <c r="F430" s="2">
-        <v>1561</v>
+        <v>1278</v>
       </c>
       <c r="G430" s="2" t="s">
         <v>15</v>
@@ -32430,7 +32430,7 @@
         <v>14</v>
       </c>
       <c r="F431" s="2">
-        <v>3287</v>
+        <v>1961</v>
       </c>
       <c r="G431" s="2" t="s">
         <v>15</v>
@@ -32462,7 +32462,7 @@
         <v>14</v>
       </c>
       <c r="F432" s="2">
-        <v>1290</v>
+        <v>4477</v>
       </c>
       <c r="G432" s="2" t="s">
         <v>15</v>
@@ -32494,7 +32494,7 @@
         <v>14</v>
       </c>
       <c r="F433" s="2">
-        <v>3390</v>
+        <v>4396</v>
       </c>
       <c r="G433" s="2" t="s">
         <v>15</v>
@@ -32526,7 +32526,7 @@
         <v>14</v>
       </c>
       <c r="F434" s="2">
-        <v>1202</v>
+        <v>4580</v>
       </c>
       <c r="G434" s="2" t="s">
         <v>15</v>
@@ -32558,7 +32558,7 @@
         <v>14</v>
       </c>
       <c r="F435" s="2">
-        <v>3986</v>
+        <v>3548</v>
       </c>
       <c r="G435" s="2" t="s">
         <v>15</v>
@@ -32590,7 +32590,7 @@
         <v>14</v>
       </c>
       <c r="F436" s="2">
-        <v>2351</v>
+        <v>2282</v>
       </c>
       <c r="G436" s="2" t="s">
         <v>15</v>
@@ -32622,7 +32622,7 @@
         <v>14</v>
       </c>
       <c r="F437" s="2">
-        <v>2069</v>
+        <v>4593</v>
       </c>
       <c r="G437" s="2" t="s">
         <v>15</v>
@@ -32654,7 +32654,7 @@
         <v>14</v>
       </c>
       <c r="F438" s="2">
-        <v>3918</v>
+        <v>2850</v>
       </c>
       <c r="G438" s="2" t="s">
         <v>15</v>
@@ -32686,7 +32686,7 @@
         <v>14</v>
       </c>
       <c r="F439" s="2">
-        <v>2530</v>
+        <v>2725</v>
       </c>
       <c r="G439" s="2" t="s">
         <v>15</v>
@@ -32718,7 +32718,7 @@
         <v>14</v>
       </c>
       <c r="F440" s="2">
-        <v>2340</v>
+        <v>3970</v>
       </c>
       <c r="G440" s="2" t="s">
         <v>15</v>
@@ -32750,7 +32750,7 @@
         <v>14</v>
       </c>
       <c r="F441" s="2">
-        <v>913</v>
+        <v>1776</v>
       </c>
       <c r="G441" s="2" t="s">
         <v>15</v>
@@ -32782,7 +32782,7 @@
         <v>14</v>
       </c>
       <c r="F442" s="2">
-        <v>3286</v>
+        <v>2614</v>
       </c>
       <c r="G442" s="2" t="s">
         <v>15</v>
@@ -32814,7 +32814,7 @@
         <v>14</v>
       </c>
       <c r="F443" s="2">
-        <v>2969</v>
+        <v>4389</v>
       </c>
       <c r="G443" s="2" t="s">
         <v>15</v>
@@ -32846,7 +32846,7 @@
         <v>14</v>
       </c>
       <c r="F444" s="2">
-        <v>4121</v>
+        <v>860</v>
       </c>
       <c r="G444" s="2" t="s">
         <v>15</v>
@@ -32878,7 +32878,7 @@
         <v>14</v>
       </c>
       <c r="F445" s="2">
-        <v>3873</v>
+        <v>1441</v>
       </c>
       <c r="G445" s="2" t="s">
         <v>15</v>
@@ -32910,7 +32910,7 @@
         <v>14</v>
       </c>
       <c r="F446" s="2">
-        <v>1132</v>
+        <v>1682</v>
       </c>
       <c r="G446" s="2" t="s">
         <v>15</v>
@@ -32942,7 +32942,7 @@
         <v>14</v>
       </c>
       <c r="F447" s="2">
-        <v>1543</v>
+        <v>1806</v>
       </c>
       <c r="G447" s="2" t="s">
         <v>15</v>
@@ -32974,7 +32974,7 @@
         <v>14</v>
       </c>
       <c r="F448" s="2">
-        <v>2775</v>
+        <v>3015</v>
       </c>
       <c r="G448" s="2" t="s">
         <v>15</v>
@@ -33006,7 +33006,7 @@
         <v>14</v>
       </c>
       <c r="F449" s="2">
-        <v>2094</v>
+        <v>3360</v>
       </c>
       <c r="G449" s="2" t="s">
         <v>15</v>
@@ -33038,7 +33038,7 @@
         <v>14</v>
       </c>
       <c r="F450" s="2">
-        <v>2209</v>
+        <v>2372</v>
       </c>
       <c r="G450" s="2" t="s">
         <v>15</v>
@@ -33070,7 +33070,7 @@
         <v>14</v>
       </c>
       <c r="F451" s="2">
-        <v>4222</v>
+        <v>2745</v>
       </c>
       <c r="G451" s="2" t="s">
         <v>15</v>
@@ -33102,7 +33102,7 @@
         <v>14</v>
       </c>
       <c r="F452" s="2">
-        <v>3675</v>
+        <v>2479</v>
       </c>
       <c r="G452" s="2" t="s">
         <v>15</v>
@@ -33134,7 +33134,7 @@
         <v>14</v>
       </c>
       <c r="F453" s="2">
-        <v>2022</v>
+        <v>1262</v>
       </c>
       <c r="G453" s="2" t="s">
         <v>15</v>
@@ -33166,7 +33166,7 @@
         <v>14</v>
       </c>
       <c r="F454" s="2">
-        <v>3482</v>
+        <v>4473</v>
       </c>
       <c r="G454" s="2" t="s">
         <v>15</v>
@@ -33198,7 +33198,7 @@
         <v>14</v>
       </c>
       <c r="F455" s="2">
-        <v>1862</v>
+        <v>1626</v>
       </c>
       <c r="G455" s="2" t="s">
         <v>15</v>
@@ -33230,7 +33230,7 @@
         <v>14</v>
       </c>
       <c r="F456" s="2">
-        <v>924</v>
+        <v>3691</v>
       </c>
       <c r="G456" s="2" t="s">
         <v>15</v>
@@ -33262,7 +33262,7 @@
         <v>14</v>
       </c>
       <c r="F457" s="2">
-        <v>1237</v>
+        <v>3138</v>
       </c>
       <c r="G457" s="2" t="s">
         <v>15</v>
@@ -33294,7 +33294,7 @@
         <v>14</v>
       </c>
       <c r="F458" s="2">
-        <v>2348</v>
+        <v>856</v>
       </c>
       <c r="G458" s="2" t="s">
         <v>15</v>
@@ -33326,7 +33326,7 @@
         <v>14</v>
       </c>
       <c r="F459" s="2">
-        <v>4075</v>
+        <v>2601</v>
       </c>
       <c r="G459" s="2" t="s">
         <v>15</v>
@@ -33358,7 +33358,7 @@
         <v>14</v>
       </c>
       <c r="F460" s="2">
-        <v>1489</v>
+        <v>2749</v>
       </c>
       <c r="G460" s="2" t="s">
         <v>15</v>
@@ -33390,7 +33390,7 @@
         <v>14</v>
       </c>
       <c r="F461" s="2">
-        <v>3321</v>
+        <v>1270</v>
       </c>
       <c r="G461" s="2" t="s">
         <v>15</v>
@@ -33422,7 +33422,7 @@
         <v>14</v>
       </c>
       <c r="F462" s="2">
-        <v>4694</v>
+        <v>1955</v>
       </c>
       <c r="G462" s="2" t="s">
         <v>15</v>
@@ -33454,7 +33454,7 @@
         <v>14</v>
       </c>
       <c r="F463" s="2">
-        <v>2820</v>
+        <v>3567</v>
       </c>
       <c r="G463" s="2" t="s">
         <v>15</v>
@@ -33486,7 +33486,7 @@
         <v>14</v>
       </c>
       <c r="F464" s="2">
-        <v>1982</v>
+        <v>3712</v>
       </c>
       <c r="G464" s="2" t="s">
         <v>15</v>
@@ -33518,7 +33518,7 @@
         <v>14</v>
       </c>
       <c r="F465" s="2">
-        <v>1539</v>
+        <v>1272</v>
       </c>
       <c r="G465" s="2" t="s">
         <v>15</v>
@@ -33550,7 +33550,7 @@
         <v>14</v>
       </c>
       <c r="F466" s="2">
-        <v>2682</v>
+        <v>4776</v>
       </c>
       <c r="G466" s="2" t="s">
         <v>15</v>
@@ -33582,7 +33582,7 @@
         <v>14</v>
       </c>
       <c r="F467" s="2">
-        <v>3948</v>
+        <v>1305</v>
       </c>
       <c r="G467" s="2" t="s">
         <v>15</v>
@@ -33614,7 +33614,7 @@
         <v>14</v>
       </c>
       <c r="F468" s="2">
-        <v>2491</v>
+        <v>4315</v>
       </c>
       <c r="G468" s="2" t="s">
         <v>15</v>
@@ -33646,7 +33646,7 @@
         <v>14</v>
       </c>
       <c r="F469" s="2">
-        <v>1141</v>
+        <v>2441</v>
       </c>
       <c r="G469" s="2" t="s">
         <v>15</v>
@@ -33678,7 +33678,7 @@
         <v>14</v>
       </c>
       <c r="F470" s="2">
-        <v>1105</v>
+        <v>2133</v>
       </c>
       <c r="G470" s="2" t="s">
         <v>15</v>
@@ -33710,7 +33710,7 @@
         <v>14</v>
       </c>
       <c r="F471" s="2">
-        <v>1017</v>
+        <v>3039</v>
       </c>
       <c r="G471" s="2" t="s">
         <v>15</v>

--- a/reports/selenium/latest/excel/Automation_Test_Report.xlsx
+++ b/reports/selenium/latest/excel/Automation_Test_Report.xlsx
@@ -3084,7 +3084,7 @@
     <t>Build</t>
   </si>
   <si>
-    <t>7</t>
+    <t>11</t>
   </si>
   <si>
     <t>Branch</t>
@@ -3096,13 +3096,13 @@
     <t>Commit</t>
   </si>
   <si>
-    <t>7c78d5ee5289</t>
+    <t>11e9b67abc20</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T16:09:54.064Z</t>
+    <t>2026-08-18T16:39:03.788Z</t>
   </si>
   <si>
     <t>Browser</t>
@@ -3607,7 +3607,7 @@
         <v>14</v>
       </c>
       <c r="F2" s="2">
-        <v>3639</v>
+        <v>3597</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>15</v>
@@ -3639,7 +3639,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="2">
-        <v>2895</v>
+        <v>1120</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>15</v>
@@ -3671,7 +3671,7 @@
         <v>14</v>
       </c>
       <c r="F4" s="2">
-        <v>3225</v>
+        <v>3037</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
@@ -3703,7 +3703,7 @@
         <v>14</v>
       </c>
       <c r="F5" s="2">
-        <v>1115</v>
+        <v>2728</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
@@ -3735,7 +3735,7 @@
         <v>14</v>
       </c>
       <c r="F6" s="2">
-        <v>3408</v>
+        <v>2049</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -3767,7 +3767,7 @@
         <v>14</v>
       </c>
       <c r="F7" s="2">
-        <v>3935</v>
+        <v>2055</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -3799,7 +3799,7 @@
         <v>14</v>
       </c>
       <c r="F8" s="2">
-        <v>2045</v>
+        <v>850</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -3831,7 +3831,7 @@
         <v>14</v>
       </c>
       <c r="F9" s="2">
-        <v>4145</v>
+        <v>2266</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -3863,7 +3863,7 @@
         <v>14</v>
       </c>
       <c r="F10" s="2">
-        <v>3852</v>
+        <v>4135</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
@@ -3895,7 +3895,7 @@
         <v>14</v>
       </c>
       <c r="F11" s="2">
-        <v>1119</v>
+        <v>2859</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
@@ -3927,7 +3927,7 @@
         <v>14</v>
       </c>
       <c r="F12" s="2">
-        <v>1467</v>
+        <v>1309</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
@@ -3959,7 +3959,7 @@
         <v>14</v>
       </c>
       <c r="F13" s="2">
-        <v>3694</v>
+        <v>993</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -3991,7 +3991,7 @@
         <v>14</v>
       </c>
       <c r="F14" s="2">
-        <v>1003</v>
+        <v>2180</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -4023,7 +4023,7 @@
         <v>14</v>
       </c>
       <c r="F15" s="2">
-        <v>1343</v>
+        <v>4360</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -4055,7 +4055,7 @@
         <v>14</v>
       </c>
       <c r="F16" s="2">
-        <v>3875</v>
+        <v>1532</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
@@ -4087,7 +4087,7 @@
         <v>14</v>
       </c>
       <c r="F17" s="2">
-        <v>2977</v>
+        <v>4276</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
@@ -4119,7 +4119,7 @@
         <v>14</v>
       </c>
       <c r="F18" s="2">
-        <v>4055</v>
+        <v>3017</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
@@ -4151,7 +4151,7 @@
         <v>14</v>
       </c>
       <c r="F19" s="2">
-        <v>4664</v>
+        <v>3197</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
@@ -4183,7 +4183,7 @@
         <v>14</v>
       </c>
       <c r="F20" s="2">
-        <v>1543</v>
+        <v>1930</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
@@ -4215,7 +4215,7 @@
         <v>14</v>
       </c>
       <c r="F21" s="2">
-        <v>1703</v>
+        <v>2303</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -4247,7 +4247,7 @@
         <v>14</v>
       </c>
       <c r="F22" s="2">
-        <v>1112</v>
+        <v>2113</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -4279,7 +4279,7 @@
         <v>14</v>
       </c>
       <c r="F23" s="2">
-        <v>3040</v>
+        <v>3251</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -4311,7 +4311,7 @@
         <v>14</v>
       </c>
       <c r="F24" s="2">
-        <v>1969</v>
+        <v>1692</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -4343,7 +4343,7 @@
         <v>14</v>
       </c>
       <c r="F25" s="2">
-        <v>1877</v>
+        <v>1551</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -4375,7 +4375,7 @@
         <v>14</v>
       </c>
       <c r="F26" s="2">
-        <v>1774</v>
+        <v>1858</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -4407,7 +4407,7 @@
         <v>14</v>
       </c>
       <c r="F27" s="2">
-        <v>3721</v>
+        <v>3081</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>15</v>
@@ -4439,7 +4439,7 @@
         <v>14</v>
       </c>
       <c r="F28" s="2">
-        <v>3272</v>
+        <v>3971</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>15</v>
@@ -4471,7 +4471,7 @@
         <v>14</v>
       </c>
       <c r="F29" s="2">
-        <v>3033</v>
+        <v>2436</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>15</v>
@@ -4503,7 +4503,7 @@
         <v>14</v>
       </c>
       <c r="F30" s="2">
-        <v>1696</v>
+        <v>1720</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>15</v>
@@ -4567,7 +4567,7 @@
         <v>14</v>
       </c>
       <c r="F32" s="2">
-        <v>3288</v>
+        <v>1642</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>15</v>
@@ -4599,7 +4599,7 @@
         <v>14</v>
       </c>
       <c r="F33" s="2">
-        <v>2343</v>
+        <v>1123</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>15</v>
@@ -4631,7 +4631,7 @@
         <v>14</v>
       </c>
       <c r="F34" s="2">
-        <v>1024</v>
+        <v>1687</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>15</v>
@@ -4663,7 +4663,7 @@
         <v>14</v>
       </c>
       <c r="F35" s="2">
-        <v>825</v>
+        <v>4055</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>15</v>
@@ -4695,7 +4695,7 @@
         <v>14</v>
       </c>
       <c r="F36" s="2">
-        <v>1640</v>
+        <v>1862</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>15</v>
@@ -4727,7 +4727,7 @@
         <v>14</v>
       </c>
       <c r="F37" s="2">
-        <v>2301</v>
+        <v>2858</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>15</v>
@@ -4759,7 +4759,7 @@
         <v>14</v>
       </c>
       <c r="F38" s="2">
-        <v>3718</v>
+        <v>3867</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>15</v>
@@ -4791,7 +4791,7 @@
         <v>14</v>
       </c>
       <c r="F39" s="2">
-        <v>2933</v>
+        <v>4457</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>15</v>
@@ -4823,7 +4823,7 @@
         <v>14</v>
       </c>
       <c r="F40" s="2">
-        <v>2268</v>
+        <v>2119</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>15</v>
@@ -4855,7 +4855,7 @@
         <v>14</v>
       </c>
       <c r="F41" s="2">
-        <v>2955</v>
+        <v>2614</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>15</v>
@@ -4887,7 +4887,7 @@
         <v>14</v>
       </c>
       <c r="F42" s="2">
-        <v>912</v>
+        <v>3842</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>15</v>
@@ -4919,7 +4919,7 @@
         <v>14</v>
       </c>
       <c r="F43" s="2">
-        <v>3127</v>
+        <v>1343</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>15</v>
@@ -4951,7 +4951,7 @@
         <v>14</v>
       </c>
       <c r="F44" s="2">
-        <v>1017</v>
+        <v>3241</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>15</v>
@@ -4983,7 +4983,7 @@
         <v>14</v>
       </c>
       <c r="F45" s="2">
-        <v>4056</v>
+        <v>3631</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>15</v>
@@ -5015,7 +5015,7 @@
         <v>14</v>
       </c>
       <c r="F46" s="2">
-        <v>2668</v>
+        <v>2755</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>15</v>
@@ -5047,7 +5047,7 @@
         <v>14</v>
       </c>
       <c r="F47" s="2">
-        <v>2378</v>
+        <v>3756</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>15</v>
@@ -5079,7 +5079,7 @@
         <v>14</v>
       </c>
       <c r="F48" s="2">
-        <v>4619</v>
+        <v>3028</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>15</v>
@@ -5111,7 +5111,7 @@
         <v>14</v>
       </c>
       <c r="F49" s="2">
-        <v>3120</v>
+        <v>3578</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>15</v>
@@ -5143,7 +5143,7 @@
         <v>14</v>
       </c>
       <c r="F50" s="2">
-        <v>3893</v>
+        <v>1044</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>15</v>
@@ -5175,7 +5175,7 @@
         <v>14</v>
       </c>
       <c r="F51" s="2">
-        <v>991</v>
+        <v>2937</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>15</v>
@@ -5207,7 +5207,7 @@
         <v>14</v>
       </c>
       <c r="F52" s="2">
-        <v>1563</v>
+        <v>1971</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>15</v>
@@ -5239,7 +5239,7 @@
         <v>14</v>
       </c>
       <c r="F53" s="2">
-        <v>1410</v>
+        <v>3909</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>15</v>
@@ -5303,7 +5303,7 @@
         <v>14</v>
       </c>
       <c r="F55" s="2">
-        <v>3054</v>
+        <v>3275</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>15</v>
@@ -5335,7 +5335,7 @@
         <v>14</v>
       </c>
       <c r="F56" s="2">
-        <v>3824</v>
+        <v>2313</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>15</v>
@@ -5367,7 +5367,7 @@
         <v>14</v>
       </c>
       <c r="F57" s="2">
-        <v>2564</v>
+        <v>2030</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>15</v>
@@ -5399,7 +5399,7 @@
         <v>14</v>
       </c>
       <c r="F58" s="2">
-        <v>3155</v>
+        <v>4455</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>15</v>
@@ -5431,7 +5431,7 @@
         <v>14</v>
       </c>
       <c r="F59" s="2">
-        <v>2051</v>
+        <v>1812</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>15</v>
@@ -5463,7 +5463,7 @@
         <v>14</v>
       </c>
       <c r="F60" s="2">
-        <v>2716</v>
+        <v>3317</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>15</v>
@@ -5495,7 +5495,7 @@
         <v>14</v>
       </c>
       <c r="F61" s="2">
-        <v>1422</v>
+        <v>2825</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>15</v>
@@ -5527,7 +5527,7 @@
         <v>14</v>
       </c>
       <c r="F62" s="2">
-        <v>3896</v>
+        <v>4783</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>15</v>
@@ -5559,7 +5559,7 @@
         <v>14</v>
       </c>
       <c r="F63" s="2">
-        <v>4654</v>
+        <v>4106</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>15</v>
@@ -5591,7 +5591,7 @@
         <v>14</v>
       </c>
       <c r="F64" s="2">
-        <v>2479</v>
+        <v>4282</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>15</v>
@@ -5623,7 +5623,7 @@
         <v>14</v>
       </c>
       <c r="F65" s="2">
-        <v>3792</v>
+        <v>1791</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>15</v>
@@ -5655,7 +5655,7 @@
         <v>14</v>
       </c>
       <c r="F66" s="2">
-        <v>2195</v>
+        <v>3879</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>15</v>
@@ -5687,7 +5687,7 @@
         <v>14</v>
       </c>
       <c r="F67" s="2">
-        <v>3950</v>
+        <v>2378</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>15</v>
@@ -5719,7 +5719,7 @@
         <v>14</v>
       </c>
       <c r="F68" s="2">
-        <v>2625</v>
+        <v>4501</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>15</v>
@@ -5751,7 +5751,7 @@
         <v>14</v>
       </c>
       <c r="F69" s="2">
-        <v>3882</v>
+        <v>3560</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>15</v>
@@ -5783,7 +5783,7 @@
         <v>14</v>
       </c>
       <c r="F70" s="2">
-        <v>1952</v>
+        <v>4125</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>15</v>
@@ -5815,7 +5815,7 @@
         <v>14</v>
       </c>
       <c r="F71" s="2">
-        <v>1931</v>
+        <v>3134</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>15</v>
@@ -5847,7 +5847,7 @@
         <v>14</v>
       </c>
       <c r="F72" s="2">
-        <v>4116</v>
+        <v>3106</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>15</v>
@@ -5879,7 +5879,7 @@
         <v>14</v>
       </c>
       <c r="F73" s="2">
-        <v>3276</v>
+        <v>4191</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>15</v>
@@ -5911,7 +5911,7 @@
         <v>14</v>
       </c>
       <c r="F74" s="2">
-        <v>4540</v>
+        <v>4704</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>15</v>
@@ -5943,7 +5943,7 @@
         <v>14</v>
       </c>
       <c r="F75" s="2">
-        <v>3078</v>
+        <v>3195</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>15</v>
@@ -5975,7 +5975,7 @@
         <v>14</v>
       </c>
       <c r="F76" s="2">
-        <v>2338</v>
+        <v>1472</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>15</v>
@@ -6007,7 +6007,7 @@
         <v>14</v>
       </c>
       <c r="F77" s="2">
-        <v>3266</v>
+        <v>1671</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>15</v>
@@ -6039,7 +6039,7 @@
         <v>14</v>
       </c>
       <c r="F78" s="2">
-        <v>2373</v>
+        <v>2413</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>15</v>
@@ -6071,7 +6071,7 @@
         <v>14</v>
       </c>
       <c r="F79" s="2">
-        <v>908</v>
+        <v>4432</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>15</v>
@@ -6103,7 +6103,7 @@
         <v>14</v>
       </c>
       <c r="F80" s="2">
-        <v>3757</v>
+        <v>2397</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>15</v>
@@ -6135,7 +6135,7 @@
         <v>14</v>
       </c>
       <c r="F81" s="2">
-        <v>2629</v>
+        <v>1438</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>15</v>
@@ -6167,7 +6167,7 @@
         <v>14</v>
       </c>
       <c r="F82" s="2">
-        <v>1579</v>
+        <v>2272</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>15</v>
@@ -6199,7 +6199,7 @@
         <v>14</v>
       </c>
       <c r="F83" s="2">
-        <v>853</v>
+        <v>1720</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>15</v>
@@ -6231,7 +6231,7 @@
         <v>14</v>
       </c>
       <c r="F84" s="2">
-        <v>1422</v>
+        <v>1175</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>15</v>
@@ -6263,7 +6263,7 @@
         <v>14</v>
       </c>
       <c r="F85" s="2">
-        <v>3259</v>
+        <v>3218</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>15</v>
@@ -6295,7 +6295,7 @@
         <v>14</v>
       </c>
       <c r="F86" s="2">
-        <v>3672</v>
+        <v>4742</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>15</v>
@@ -6327,7 +6327,7 @@
         <v>14</v>
       </c>
       <c r="F87" s="2">
-        <v>3660</v>
+        <v>2607</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>15</v>
@@ -6359,7 +6359,7 @@
         <v>14</v>
       </c>
       <c r="F88" s="2">
-        <v>3386</v>
+        <v>3765</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>15</v>
@@ -6391,7 +6391,7 @@
         <v>14</v>
       </c>
       <c r="F89" s="2">
-        <v>3384</v>
+        <v>2910</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>15</v>
@@ -6423,7 +6423,7 @@
         <v>14</v>
       </c>
       <c r="F90" s="2">
-        <v>2905</v>
+        <v>815</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>15</v>
@@ -6455,7 +6455,7 @@
         <v>14</v>
       </c>
       <c r="F91" s="2">
-        <v>4642</v>
+        <v>3618</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>15</v>
@@ -6487,7 +6487,7 @@
         <v>14</v>
       </c>
       <c r="F92" s="2">
-        <v>4475</v>
+        <v>986</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>15</v>
@@ -6519,7 +6519,7 @@
         <v>14</v>
       </c>
       <c r="F93" s="2">
-        <v>1011</v>
+        <v>1913</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>15</v>
@@ -6551,7 +6551,7 @@
         <v>14</v>
       </c>
       <c r="F94" s="2">
-        <v>1481</v>
+        <v>3078</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>15</v>
@@ -6583,7 +6583,7 @@
         <v>14</v>
       </c>
       <c r="F95" s="2">
-        <v>3193</v>
+        <v>1602</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>15</v>
@@ -6615,7 +6615,7 @@
         <v>14</v>
       </c>
       <c r="F96" s="2">
-        <v>823</v>
+        <v>3816</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>15</v>
@@ -6647,7 +6647,7 @@
         <v>14</v>
       </c>
       <c r="F97" s="2">
-        <v>2981</v>
+        <v>1259</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>15</v>
@@ -6679,7 +6679,7 @@
         <v>14</v>
       </c>
       <c r="F98" s="2">
-        <v>3681</v>
+        <v>1054</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>15</v>
@@ -6711,7 +6711,7 @@
         <v>14</v>
       </c>
       <c r="F99" s="2">
-        <v>1823</v>
+        <v>4379</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>15</v>
@@ -6743,7 +6743,7 @@
         <v>14</v>
       </c>
       <c r="F100" s="2">
-        <v>3640</v>
+        <v>1274</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>15</v>
@@ -6775,7 +6775,7 @@
         <v>14</v>
       </c>
       <c r="F101" s="2">
-        <v>2992</v>
+        <v>2803</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>15</v>
@@ -6807,7 +6807,7 @@
         <v>14</v>
       </c>
       <c r="F102" s="2">
-        <v>4150</v>
+        <v>2948</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>15</v>
@@ -6839,7 +6839,7 @@
         <v>14</v>
       </c>
       <c r="F103" s="2">
-        <v>4439</v>
+        <v>1761</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>15</v>
@@ -6871,7 +6871,7 @@
         <v>14</v>
       </c>
       <c r="F104" s="2">
-        <v>2013</v>
+        <v>1800</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>15</v>
@@ -6903,7 +6903,7 @@
         <v>14</v>
       </c>
       <c r="F105" s="2">
-        <v>2005</v>
+        <v>3158</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>15</v>
@@ -6935,7 +6935,7 @@
         <v>14</v>
       </c>
       <c r="F106" s="2">
-        <v>4799</v>
+        <v>3397</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>15</v>
@@ -6967,7 +6967,7 @@
         <v>14</v>
       </c>
       <c r="F107" s="2">
-        <v>1484</v>
+        <v>2576</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>15</v>
@@ -6999,7 +6999,7 @@
         <v>14</v>
       </c>
       <c r="F108" s="2">
-        <v>1609</v>
+        <v>1468</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>15</v>
@@ -7031,7 +7031,7 @@
         <v>14</v>
       </c>
       <c r="F109" s="2">
-        <v>1413</v>
+        <v>1354</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>15</v>
@@ -7063,7 +7063,7 @@
         <v>14</v>
       </c>
       <c r="F110" s="2">
-        <v>3635</v>
+        <v>4128</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>15</v>
@@ -7095,7 +7095,7 @@
         <v>14</v>
       </c>
       <c r="F111" s="2">
-        <v>2916</v>
+        <v>4713</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>15</v>
@@ -7127,7 +7127,7 @@
         <v>14</v>
       </c>
       <c r="F112" s="2">
-        <v>1488</v>
+        <v>3288</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>15</v>
@@ -7159,7 +7159,7 @@
         <v>14</v>
       </c>
       <c r="F113" s="2">
-        <v>3565</v>
+        <v>1502</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>15</v>
@@ -7191,7 +7191,7 @@
         <v>14</v>
       </c>
       <c r="F114" s="2">
-        <v>2080</v>
+        <v>3414</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>15</v>
@@ -7223,7 +7223,7 @@
         <v>14</v>
       </c>
       <c r="F115" s="2">
-        <v>4591</v>
+        <v>1284</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>15</v>
@@ -7255,7 +7255,7 @@
         <v>14</v>
       </c>
       <c r="F116" s="2">
-        <v>844</v>
+        <v>1015</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>15</v>
@@ -7287,7 +7287,7 @@
         <v>14</v>
       </c>
       <c r="F117" s="2">
-        <v>3876</v>
+        <v>1420</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>15</v>
@@ -7319,7 +7319,7 @@
         <v>14</v>
       </c>
       <c r="F118" s="2">
-        <v>3172</v>
+        <v>2613</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>15</v>
@@ -7351,7 +7351,7 @@
         <v>14</v>
       </c>
       <c r="F119" s="2">
-        <v>3854</v>
+        <v>3250</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>15</v>
@@ -7383,7 +7383,7 @@
         <v>14</v>
       </c>
       <c r="F120" s="2">
-        <v>3742</v>
+        <v>861</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>15</v>
@@ -7415,7 +7415,7 @@
         <v>14</v>
       </c>
       <c r="F121" s="2">
-        <v>1349</v>
+        <v>4711</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>15</v>
@@ -7447,7 +7447,7 @@
         <v>14</v>
       </c>
       <c r="F122" s="2">
-        <v>1093</v>
+        <v>3991</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>15</v>
@@ -7479,7 +7479,7 @@
         <v>14</v>
       </c>
       <c r="F123" s="2">
-        <v>2824</v>
+        <v>4485</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>15</v>
@@ -7511,7 +7511,7 @@
         <v>14</v>
       </c>
       <c r="F124" s="2">
-        <v>2649</v>
+        <v>962</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>15</v>
@@ -7543,7 +7543,7 @@
         <v>14</v>
       </c>
       <c r="F125" s="2">
-        <v>4015</v>
+        <v>3175</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>15</v>
@@ -7575,7 +7575,7 @@
         <v>14</v>
       </c>
       <c r="F126" s="2">
-        <v>2500</v>
+        <v>2493</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>15</v>
@@ -7607,7 +7607,7 @@
         <v>14</v>
       </c>
       <c r="F127" s="2">
-        <v>2978</v>
+        <v>4383</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>15</v>
@@ -7639,7 +7639,7 @@
         <v>14</v>
       </c>
       <c r="F128" s="2">
-        <v>3113</v>
+        <v>2448</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>15</v>
@@ -7671,7 +7671,7 @@
         <v>14</v>
       </c>
       <c r="F129" s="2">
-        <v>1931</v>
+        <v>4335</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>15</v>
@@ -7703,7 +7703,7 @@
         <v>14</v>
       </c>
       <c r="F130" s="2">
-        <v>2426</v>
+        <v>2792</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>15</v>
@@ -7735,7 +7735,7 @@
         <v>14</v>
       </c>
       <c r="F131" s="2">
-        <v>983</v>
+        <v>4762</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>15</v>
@@ -7767,7 +7767,7 @@
         <v>14</v>
       </c>
       <c r="F132" s="2">
-        <v>4301</v>
+        <v>4467</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>15</v>
@@ -7799,7 +7799,7 @@
         <v>14</v>
       </c>
       <c r="F133" s="2">
-        <v>2713</v>
+        <v>1659</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>15</v>
@@ -7831,7 +7831,7 @@
         <v>14</v>
       </c>
       <c r="F134" s="2">
-        <v>4540</v>
+        <v>3633</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>15</v>
@@ -7863,7 +7863,7 @@
         <v>14</v>
       </c>
       <c r="F135" s="2">
-        <v>1541</v>
+        <v>3127</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>15</v>
@@ -7895,7 +7895,7 @@
         <v>14</v>
       </c>
       <c r="F136" s="2">
-        <v>2320</v>
+        <v>2143</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>15</v>
@@ -7927,7 +7927,7 @@
         <v>14</v>
       </c>
       <c r="F137" s="2">
-        <v>1409</v>
+        <v>2254</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>15</v>
@@ -7959,7 +7959,7 @@
         <v>14</v>
       </c>
       <c r="F138" s="2">
-        <v>2297</v>
+        <v>4462</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>15</v>
@@ -7991,7 +7991,7 @@
         <v>14</v>
       </c>
       <c r="F139" s="2">
-        <v>2387</v>
+        <v>810</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>15</v>
@@ -8023,7 +8023,7 @@
         <v>14</v>
       </c>
       <c r="F140" s="2">
-        <v>3440</v>
+        <v>1113</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>15</v>
@@ -8055,7 +8055,7 @@
         <v>14</v>
       </c>
       <c r="F141" s="2">
-        <v>4029</v>
+        <v>935</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>15</v>
@@ -8087,7 +8087,7 @@
         <v>14</v>
       </c>
       <c r="F142" s="2">
-        <v>1562</v>
+        <v>1944</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>15</v>
@@ -8119,7 +8119,7 @@
         <v>14</v>
       </c>
       <c r="F143" s="2">
-        <v>2930</v>
+        <v>4773</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>15</v>
@@ -8151,7 +8151,7 @@
         <v>14</v>
       </c>
       <c r="F144" s="2">
-        <v>1323</v>
+        <v>1483</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>15</v>
@@ -8183,7 +8183,7 @@
         <v>14</v>
       </c>
       <c r="F145" s="2">
-        <v>4470</v>
+        <v>1740</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>15</v>
@@ -8215,7 +8215,7 @@
         <v>14</v>
       </c>
       <c r="F146" s="2">
-        <v>4068</v>
+        <v>1288</v>
       </c>
       <c r="G146" s="2" t="s">
         <v>15</v>
@@ -8247,7 +8247,7 @@
         <v>14</v>
       </c>
       <c r="F147" s="2">
-        <v>1264</v>
+        <v>2485</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>15</v>
@@ -8279,7 +8279,7 @@
         <v>14</v>
       </c>
       <c r="F148" s="2">
-        <v>3935</v>
+        <v>1376</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>15</v>
@@ -8311,7 +8311,7 @@
         <v>14</v>
       </c>
       <c r="F149" s="2">
-        <v>2633</v>
+        <v>1032</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>15</v>
@@ -8343,7 +8343,7 @@
         <v>14</v>
       </c>
       <c r="F150" s="2">
-        <v>2150</v>
+        <v>3957</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>15</v>
@@ -8375,7 +8375,7 @@
         <v>14</v>
       </c>
       <c r="F151" s="2">
-        <v>2928</v>
+        <v>820</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>15</v>
@@ -8407,7 +8407,7 @@
         <v>14</v>
       </c>
       <c r="F152" s="2">
-        <v>1531</v>
+        <v>2648</v>
       </c>
       <c r="G152" s="2" t="s">
         <v>15</v>
@@ -8439,7 +8439,7 @@
         <v>14</v>
       </c>
       <c r="F153" s="2">
-        <v>4396</v>
+        <v>3346</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>15</v>
@@ -8471,7 +8471,7 @@
         <v>14</v>
       </c>
       <c r="F154" s="2">
-        <v>1559</v>
+        <v>2947</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>15</v>
@@ -8503,7 +8503,7 @@
         <v>14</v>
       </c>
       <c r="F155" s="2">
-        <v>1284</v>
+        <v>3881</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>15</v>
@@ -8535,7 +8535,7 @@
         <v>14</v>
       </c>
       <c r="F156" s="2">
-        <v>1682</v>
+        <v>925</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>15</v>
@@ -8567,7 +8567,7 @@
         <v>14</v>
       </c>
       <c r="F157" s="2">
-        <v>2140</v>
+        <v>2242</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>15</v>
@@ -8599,7 +8599,7 @@
         <v>14</v>
       </c>
       <c r="F158" s="2">
-        <v>2990</v>
+        <v>2471</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>15</v>
@@ -8631,7 +8631,7 @@
         <v>14</v>
       </c>
       <c r="F159" s="2">
-        <v>4605</v>
+        <v>2063</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>15</v>
@@ -8663,7 +8663,7 @@
         <v>14</v>
       </c>
       <c r="F160" s="2">
-        <v>2855</v>
+        <v>3771</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>15</v>
@@ -8695,7 +8695,7 @@
         <v>14</v>
       </c>
       <c r="F161" s="2">
-        <v>3484</v>
+        <v>2034</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>15</v>
@@ -8727,7 +8727,7 @@
         <v>14</v>
       </c>
       <c r="F162" s="2">
-        <v>1745</v>
+        <v>2230</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>15</v>
@@ -8759,7 +8759,7 @@
         <v>14</v>
       </c>
       <c r="F163" s="2">
-        <v>2677</v>
+        <v>3672</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>15</v>
@@ -8791,7 +8791,7 @@
         <v>14</v>
       </c>
       <c r="F164" s="2">
-        <v>941</v>
+        <v>999</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>15</v>
@@ -8823,7 +8823,7 @@
         <v>14</v>
       </c>
       <c r="F165" s="2">
-        <v>4508</v>
+        <v>3444</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>15</v>
@@ -8855,7 +8855,7 @@
         <v>14</v>
       </c>
       <c r="F166" s="2">
-        <v>4401</v>
+        <v>2163</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>15</v>
@@ -8887,7 +8887,7 @@
         <v>14</v>
       </c>
       <c r="F167" s="2">
-        <v>1442</v>
+        <v>4694</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>15</v>
@@ -8919,7 +8919,7 @@
         <v>14</v>
       </c>
       <c r="F168" s="2">
-        <v>2933</v>
+        <v>3442</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>15</v>
@@ -8951,7 +8951,7 @@
         <v>14</v>
       </c>
       <c r="F169" s="2">
-        <v>857</v>
+        <v>2894</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>15</v>
@@ -8983,7 +8983,7 @@
         <v>14</v>
       </c>
       <c r="F170" s="2">
-        <v>1383</v>
+        <v>3853</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>15</v>
@@ -9015,7 +9015,7 @@
         <v>14</v>
       </c>
       <c r="F171" s="2">
-        <v>1264</v>
+        <v>1588</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>15</v>
@@ -9047,7 +9047,7 @@
         <v>14</v>
       </c>
       <c r="F172" s="2">
-        <v>4496</v>
+        <v>4363</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>15</v>
@@ -9079,7 +9079,7 @@
         <v>14</v>
       </c>
       <c r="F173" s="2">
-        <v>1309</v>
+        <v>4297</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>15</v>
@@ -9111,7 +9111,7 @@
         <v>14</v>
       </c>
       <c r="F174" s="2">
-        <v>4069</v>
+        <v>4250</v>
       </c>
       <c r="G174" s="2" t="s">
         <v>15</v>
@@ -9143,7 +9143,7 @@
         <v>14</v>
       </c>
       <c r="F175" s="2">
-        <v>3481</v>
+        <v>2327</v>
       </c>
       <c r="G175" s="2" t="s">
         <v>15</v>
@@ -9175,7 +9175,7 @@
         <v>14</v>
       </c>
       <c r="F176" s="2">
-        <v>2994</v>
+        <v>4469</v>
       </c>
       <c r="G176" s="2" t="s">
         <v>15</v>
@@ -9207,7 +9207,7 @@
         <v>14</v>
       </c>
       <c r="F177" s="2">
-        <v>2581</v>
+        <v>4609</v>
       </c>
       <c r="G177" s="2" t="s">
         <v>15</v>
@@ -9239,7 +9239,7 @@
         <v>14</v>
       </c>
       <c r="F178" s="2">
-        <v>3908</v>
+        <v>3985</v>
       </c>
       <c r="G178" s="2" t="s">
         <v>15</v>
@@ -9271,7 +9271,7 @@
         <v>14</v>
       </c>
       <c r="F179" s="2">
-        <v>2294</v>
+        <v>1390</v>
       </c>
       <c r="G179" s="2" t="s">
         <v>15</v>
@@ -9303,7 +9303,7 @@
         <v>14</v>
       </c>
       <c r="F180" s="2">
-        <v>2516</v>
+        <v>1346</v>
       </c>
       <c r="G180" s="2" t="s">
         <v>15</v>
@@ -9335,7 +9335,7 @@
         <v>14</v>
       </c>
       <c r="F181" s="2">
-        <v>2086</v>
+        <v>1497</v>
       </c>
       <c r="G181" s="2" t="s">
         <v>15</v>
@@ -9367,7 +9367,7 @@
         <v>14</v>
       </c>
       <c r="F182" s="2">
-        <v>1412</v>
+        <v>2437</v>
       </c>
       <c r="G182" s="2" t="s">
         <v>15</v>
@@ -9399,7 +9399,7 @@
         <v>14</v>
       </c>
       <c r="F183" s="2">
-        <v>3189</v>
+        <v>2090</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>15</v>
@@ -9431,7 +9431,7 @@
         <v>14</v>
       </c>
       <c r="F184" s="2">
-        <v>3348</v>
+        <v>2063</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>15</v>
@@ -9463,7 +9463,7 @@
         <v>14</v>
       </c>
       <c r="F185" s="2">
-        <v>3444</v>
+        <v>4663</v>
       </c>
       <c r="G185" s="2" t="s">
         <v>15</v>
@@ -9495,7 +9495,7 @@
         <v>14</v>
       </c>
       <c r="F186" s="2">
-        <v>2463</v>
+        <v>4323</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>15</v>
@@ -9527,7 +9527,7 @@
         <v>14</v>
       </c>
       <c r="F187" s="2">
-        <v>1580</v>
+        <v>4749</v>
       </c>
       <c r="G187" s="2" t="s">
         <v>15</v>
@@ -9559,7 +9559,7 @@
         <v>14</v>
       </c>
       <c r="F188" s="2">
-        <v>3805</v>
+        <v>2363</v>
       </c>
       <c r="G188" s="2" t="s">
         <v>15</v>
@@ -9591,7 +9591,7 @@
         <v>14</v>
       </c>
       <c r="F189" s="2">
-        <v>2048</v>
+        <v>2362</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>15</v>
@@ -9623,7 +9623,7 @@
         <v>14</v>
       </c>
       <c r="F190" s="2">
-        <v>2284</v>
+        <v>3670</v>
       </c>
       <c r="G190" s="2" t="s">
         <v>15</v>
@@ -9655,7 +9655,7 @@
         <v>14</v>
       </c>
       <c r="F191" s="2">
-        <v>4687</v>
+        <v>1314</v>
       </c>
       <c r="G191" s="2" t="s">
         <v>15</v>
@@ -9687,7 +9687,7 @@
         <v>14</v>
       </c>
       <c r="F192" s="2">
-        <v>1871</v>
+        <v>3782</v>
       </c>
       <c r="G192" s="2" t="s">
         <v>15</v>
@@ -9719,7 +9719,7 @@
         <v>14</v>
       </c>
       <c r="F193" s="2">
-        <v>4333</v>
+        <v>4541</v>
       </c>
       <c r="G193" s="2" t="s">
         <v>15</v>
@@ -9751,7 +9751,7 @@
         <v>14</v>
       </c>
       <c r="F194" s="2">
-        <v>2206</v>
+        <v>4286</v>
       </c>
       <c r="G194" s="2" t="s">
         <v>15</v>
@@ -9783,7 +9783,7 @@
         <v>14</v>
       </c>
       <c r="F195" s="2">
-        <v>3526</v>
+        <v>3146</v>
       </c>
       <c r="G195" s="2" t="s">
         <v>15</v>
@@ -9815,7 +9815,7 @@
         <v>14</v>
       </c>
       <c r="F196" s="2">
-        <v>4373</v>
+        <v>1097</v>
       </c>
       <c r="G196" s="2" t="s">
         <v>15</v>
@@ -9847,7 +9847,7 @@
         <v>14</v>
       </c>
       <c r="F197" s="2">
-        <v>4320</v>
+        <v>2125</v>
       </c>
       <c r="G197" s="2" t="s">
         <v>15</v>
@@ -9879,7 +9879,7 @@
         <v>14</v>
       </c>
       <c r="F198" s="2">
-        <v>2349</v>
+        <v>1346</v>
       </c>
       <c r="G198" s="2" t="s">
         <v>15</v>
@@ -9911,7 +9911,7 @@
         <v>14</v>
       </c>
       <c r="F199" s="2">
-        <v>3391</v>
+        <v>4650</v>
       </c>
       <c r="G199" s="2" t="s">
         <v>15</v>
@@ -9943,7 +9943,7 @@
         <v>14</v>
       </c>
       <c r="F200" s="2">
-        <v>4274</v>
+        <v>2897</v>
       </c>
       <c r="G200" s="2" t="s">
         <v>15</v>
@@ -9975,7 +9975,7 @@
         <v>14</v>
       </c>
       <c r="F201" s="2">
-        <v>3317</v>
+        <v>998</v>
       </c>
       <c r="G201" s="2" t="s">
         <v>15</v>
@@ -10007,7 +10007,7 @@
         <v>14</v>
       </c>
       <c r="F202" s="2">
-        <v>2712</v>
+        <v>2471</v>
       </c>
       <c r="G202" s="2" t="s">
         <v>15</v>
@@ -10039,7 +10039,7 @@
         <v>14</v>
       </c>
       <c r="F203" s="2">
-        <v>4625</v>
+        <v>3789</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>15</v>
@@ -10071,7 +10071,7 @@
         <v>14</v>
       </c>
       <c r="F204" s="2">
-        <v>2669</v>
+        <v>4149</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>15</v>
@@ -10103,7 +10103,7 @@
         <v>14</v>
       </c>
       <c r="F205" s="2">
-        <v>2425</v>
+        <v>3862</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>15</v>
@@ -10135,7 +10135,7 @@
         <v>14</v>
       </c>
       <c r="F206" s="2">
-        <v>3779</v>
+        <v>1620</v>
       </c>
       <c r="G206" s="2" t="s">
         <v>15</v>
@@ -10167,7 +10167,7 @@
         <v>14</v>
       </c>
       <c r="F207" s="2">
-        <v>1733</v>
+        <v>3294</v>
       </c>
       <c r="G207" s="2" t="s">
         <v>15</v>
@@ -10199,7 +10199,7 @@
         <v>14</v>
       </c>
       <c r="F208" s="2">
-        <v>2010</v>
+        <v>4724</v>
       </c>
       <c r="G208" s="2" t="s">
         <v>15</v>
@@ -10231,7 +10231,7 @@
         <v>14</v>
       </c>
       <c r="F209" s="2">
-        <v>4674</v>
+        <v>3771</v>
       </c>
       <c r="G209" s="2" t="s">
         <v>15</v>
@@ -10263,7 +10263,7 @@
         <v>14</v>
       </c>
       <c r="F210" s="2">
-        <v>1305</v>
+        <v>1547</v>
       </c>
       <c r="G210" s="2" t="s">
         <v>15</v>
@@ -10295,7 +10295,7 @@
         <v>14</v>
       </c>
       <c r="F211" s="2">
-        <v>3286</v>
+        <v>2393</v>
       </c>
       <c r="G211" s="2" t="s">
         <v>15</v>
@@ -10327,7 +10327,7 @@
         <v>14</v>
       </c>
       <c r="F212" s="2">
-        <v>1307</v>
+        <v>3884</v>
       </c>
       <c r="G212" s="2" t="s">
         <v>15</v>
@@ -10359,7 +10359,7 @@
         <v>14</v>
       </c>
       <c r="F213" s="2">
-        <v>3553</v>
+        <v>1206</v>
       </c>
       <c r="G213" s="2" t="s">
         <v>15</v>
@@ -10391,7 +10391,7 @@
         <v>14</v>
       </c>
       <c r="F214" s="2">
-        <v>2812</v>
+        <v>1219</v>
       </c>
       <c r="G214" s="2" t="s">
         <v>15</v>
@@ -10423,7 +10423,7 @@
         <v>14</v>
       </c>
       <c r="F215" s="2">
-        <v>989</v>
+        <v>4412</v>
       </c>
       <c r="G215" s="2" t="s">
         <v>15</v>
@@ -10455,7 +10455,7 @@
         <v>14</v>
       </c>
       <c r="F216" s="2">
-        <v>2181</v>
+        <v>2103</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>15</v>
@@ -10487,7 +10487,7 @@
         <v>14</v>
       </c>
       <c r="F217" s="2">
-        <v>2945</v>
+        <v>3549</v>
       </c>
       <c r="G217" s="2" t="s">
         <v>15</v>
@@ -10519,7 +10519,7 @@
         <v>14</v>
       </c>
       <c r="F218" s="2">
-        <v>3770</v>
+        <v>4733</v>
       </c>
       <c r="G218" s="2" t="s">
         <v>15</v>
@@ -10551,7 +10551,7 @@
         <v>14</v>
       </c>
       <c r="F219" s="2">
-        <v>4531</v>
+        <v>2348</v>
       </c>
       <c r="G219" s="2" t="s">
         <v>15</v>
@@ -10583,7 +10583,7 @@
         <v>14</v>
       </c>
       <c r="F220" s="2">
-        <v>4158</v>
+        <v>4617</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>15</v>
@@ -10615,7 +10615,7 @@
         <v>14</v>
       </c>
       <c r="F221" s="2">
-        <v>3592</v>
+        <v>3041</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>15</v>
@@ -10647,7 +10647,7 @@
         <v>14</v>
       </c>
       <c r="F222" s="2">
-        <v>2911</v>
+        <v>4502</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>15</v>
@@ -10679,7 +10679,7 @@
         <v>14</v>
       </c>
       <c r="F223" s="2">
-        <v>4742</v>
+        <v>4086</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>15</v>
@@ -10711,7 +10711,7 @@
         <v>14</v>
       </c>
       <c r="F224" s="2">
-        <v>3070</v>
+        <v>4012</v>
       </c>
       <c r="G224" s="2" t="s">
         <v>15</v>
@@ -10743,7 +10743,7 @@
         <v>14</v>
       </c>
       <c r="F225" s="2">
-        <v>1640</v>
+        <v>2414</v>
       </c>
       <c r="G225" s="2" t="s">
         <v>15</v>
@@ -10775,7 +10775,7 @@
         <v>14</v>
       </c>
       <c r="F226" s="2">
-        <v>2033</v>
+        <v>3980</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>15</v>
@@ -10807,7 +10807,7 @@
         <v>14</v>
       </c>
       <c r="F227" s="2">
-        <v>3494</v>
+        <v>2527</v>
       </c>
       <c r="G227" s="2" t="s">
         <v>15</v>
@@ -10839,7 +10839,7 @@
         <v>14</v>
       </c>
       <c r="F228" s="2">
-        <v>2133</v>
+        <v>1888</v>
       </c>
       <c r="G228" s="2" t="s">
         <v>15</v>
@@ -10871,7 +10871,7 @@
         <v>14</v>
       </c>
       <c r="F229" s="2">
-        <v>2284</v>
+        <v>1758</v>
       </c>
       <c r="G229" s="2" t="s">
         <v>15</v>
@@ -10903,7 +10903,7 @@
         <v>14</v>
       </c>
       <c r="F230" s="2">
-        <v>3516</v>
+        <v>1950</v>
       </c>
       <c r="G230" s="2" t="s">
         <v>15</v>
@@ -10935,7 +10935,7 @@
         <v>14</v>
       </c>
       <c r="F231" s="2">
-        <v>2952</v>
+        <v>2309</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>15</v>
@@ -10967,7 +10967,7 @@
         <v>14</v>
       </c>
       <c r="F232" s="2">
-        <v>1554</v>
+        <v>1530</v>
       </c>
       <c r="G232" s="2" t="s">
         <v>15</v>
@@ -10999,7 +10999,7 @@
         <v>14</v>
       </c>
       <c r="F233" s="2">
-        <v>4647</v>
+        <v>3991</v>
       </c>
       <c r="G233" s="2" t="s">
         <v>15</v>
@@ -11031,7 +11031,7 @@
         <v>14</v>
       </c>
       <c r="F234" s="2">
-        <v>1604</v>
+        <v>4044</v>
       </c>
       <c r="G234" s="2" t="s">
         <v>15</v>
@@ -11063,7 +11063,7 @@
         <v>14</v>
       </c>
       <c r="F235" s="2">
-        <v>4316</v>
+        <v>2978</v>
       </c>
       <c r="G235" s="2" t="s">
         <v>15</v>
@@ -11095,7 +11095,7 @@
         <v>14</v>
       </c>
       <c r="F236" s="2">
-        <v>2343</v>
+        <v>4613</v>
       </c>
       <c r="G236" s="2" t="s">
         <v>15</v>
@@ -11127,7 +11127,7 @@
         <v>14</v>
       </c>
       <c r="F237" s="2">
-        <v>1452</v>
+        <v>1125</v>
       </c>
       <c r="G237" s="2" t="s">
         <v>15</v>
@@ -11159,7 +11159,7 @@
         <v>14</v>
       </c>
       <c r="F238" s="2">
-        <v>2138</v>
+        <v>2895</v>
       </c>
       <c r="G238" s="2" t="s">
         <v>15</v>
@@ -11191,7 +11191,7 @@
         <v>14</v>
       </c>
       <c r="F239" s="2">
-        <v>4168</v>
+        <v>1685</v>
       </c>
       <c r="G239" s="2" t="s">
         <v>15</v>
@@ -11223,7 +11223,7 @@
         <v>14</v>
       </c>
       <c r="F240" s="2">
-        <v>1250</v>
+        <v>2957</v>
       </c>
       <c r="G240" s="2" t="s">
         <v>15</v>
@@ -11255,7 +11255,7 @@
         <v>14</v>
       </c>
       <c r="F241" s="2">
-        <v>1422</v>
+        <v>4516</v>
       </c>
       <c r="G241" s="2" t="s">
         <v>15</v>
@@ -11287,7 +11287,7 @@
         <v>14</v>
       </c>
       <c r="F242" s="2">
-        <v>3097</v>
+        <v>925</v>
       </c>
       <c r="G242" s="2" t="s">
         <v>15</v>
@@ -11319,7 +11319,7 @@
         <v>14</v>
       </c>
       <c r="F243" s="2">
-        <v>2843</v>
+        <v>3823</v>
       </c>
       <c r="G243" s="2" t="s">
         <v>15</v>
@@ -11351,7 +11351,7 @@
         <v>14</v>
       </c>
       <c r="F244" s="2">
-        <v>3177</v>
+        <v>4783</v>
       </c>
       <c r="G244" s="2" t="s">
         <v>15</v>
@@ -11383,7 +11383,7 @@
         <v>14</v>
       </c>
       <c r="F245" s="2">
-        <v>2359</v>
+        <v>1335</v>
       </c>
       <c r="G245" s="2" t="s">
         <v>15</v>
@@ -11415,7 +11415,7 @@
         <v>14</v>
       </c>
       <c r="F246" s="2">
-        <v>2728</v>
+        <v>4099</v>
       </c>
       <c r="G246" s="2" t="s">
         <v>15</v>
@@ -11447,7 +11447,7 @@
         <v>14</v>
       </c>
       <c r="F247" s="2">
-        <v>1416</v>
+        <v>1469</v>
       </c>
       <c r="G247" s="2" t="s">
         <v>15</v>
@@ -11479,7 +11479,7 @@
         <v>14</v>
       </c>
       <c r="F248" s="2">
-        <v>4654</v>
+        <v>3399</v>
       </c>
       <c r="G248" s="2" t="s">
         <v>15</v>
@@ -11511,7 +11511,7 @@
         <v>14</v>
       </c>
       <c r="F249" s="2">
-        <v>1722</v>
+        <v>3351</v>
       </c>
       <c r="G249" s="2" t="s">
         <v>15</v>
@@ -11543,7 +11543,7 @@
         <v>14</v>
       </c>
       <c r="F250" s="2">
-        <v>3977</v>
+        <v>2661</v>
       </c>
       <c r="G250" s="2" t="s">
         <v>15</v>
@@ -11575,7 +11575,7 @@
         <v>14</v>
       </c>
       <c r="F251" s="2">
-        <v>3336</v>
+        <v>2127</v>
       </c>
       <c r="G251" s="2" t="s">
         <v>15</v>
@@ -11607,7 +11607,7 @@
         <v>14</v>
       </c>
       <c r="F252" s="2">
-        <v>4251</v>
+        <v>3504</v>
       </c>
       <c r="G252" s="2" t="s">
         <v>15</v>
@@ -11639,7 +11639,7 @@
         <v>14</v>
       </c>
       <c r="F253" s="2">
-        <v>2676</v>
+        <v>2838</v>
       </c>
       <c r="G253" s="2" t="s">
         <v>15</v>
@@ -11671,7 +11671,7 @@
         <v>14</v>
       </c>
       <c r="F254" s="2">
-        <v>1996</v>
+        <v>1541</v>
       </c>
       <c r="G254" s="2" t="s">
         <v>15</v>
@@ -11703,7 +11703,7 @@
         <v>14</v>
       </c>
       <c r="F255" s="2">
-        <v>1770</v>
+        <v>2303</v>
       </c>
       <c r="G255" s="2" t="s">
         <v>15</v>
@@ -11735,7 +11735,7 @@
         <v>14</v>
       </c>
       <c r="F256" s="2">
-        <v>1820</v>
+        <v>4435</v>
       </c>
       <c r="G256" s="2" t="s">
         <v>15</v>
@@ -11767,7 +11767,7 @@
         <v>14</v>
       </c>
       <c r="F257" s="2">
-        <v>4490</v>
+        <v>4695</v>
       </c>
       <c r="G257" s="2" t="s">
         <v>15</v>
@@ -11799,7 +11799,7 @@
         <v>14</v>
       </c>
       <c r="F258" s="2">
-        <v>3876</v>
+        <v>2667</v>
       </c>
       <c r="G258" s="2" t="s">
         <v>15</v>
@@ -11831,7 +11831,7 @@
         <v>14</v>
       </c>
       <c r="F259" s="2">
-        <v>3163</v>
+        <v>2269</v>
       </c>
       <c r="G259" s="2" t="s">
         <v>15</v>
@@ -11863,7 +11863,7 @@
         <v>14</v>
       </c>
       <c r="F260" s="2">
-        <v>1722</v>
+        <v>1099</v>
       </c>
       <c r="G260" s="2" t="s">
         <v>15</v>
@@ -11895,7 +11895,7 @@
         <v>14</v>
       </c>
       <c r="F261" s="2">
-        <v>2499</v>
+        <v>4432</v>
       </c>
       <c r="G261" s="2" t="s">
         <v>15</v>
@@ -11927,7 +11927,7 @@
         <v>14</v>
       </c>
       <c r="F262" s="2">
-        <v>910</v>
+        <v>1494</v>
       </c>
       <c r="G262" s="2" t="s">
         <v>15</v>
@@ -11959,7 +11959,7 @@
         <v>14</v>
       </c>
       <c r="F263" s="2">
-        <v>2702</v>
+        <v>2424</v>
       </c>
       <c r="G263" s="2" t="s">
         <v>15</v>
@@ -11991,7 +11991,7 @@
         <v>14</v>
       </c>
       <c r="F264" s="2">
-        <v>4643</v>
+        <v>4345</v>
       </c>
       <c r="G264" s="2" t="s">
         <v>15</v>
@@ -12023,7 +12023,7 @@
         <v>14</v>
       </c>
       <c r="F265" s="2">
-        <v>2863</v>
+        <v>2886</v>
       </c>
       <c r="G265" s="2" t="s">
         <v>15</v>
@@ -12055,7 +12055,7 @@
         <v>14</v>
       </c>
       <c r="F266" s="2">
-        <v>2547</v>
+        <v>4340</v>
       </c>
       <c r="G266" s="2" t="s">
         <v>15</v>
@@ -12087,7 +12087,7 @@
         <v>14</v>
       </c>
       <c r="F267" s="2">
-        <v>4108</v>
+        <v>1643</v>
       </c>
       <c r="G267" s="2" t="s">
         <v>15</v>
@@ -12119,7 +12119,7 @@
         <v>14</v>
       </c>
       <c r="F268" s="2">
-        <v>4154</v>
+        <v>850</v>
       </c>
       <c r="G268" s="2" t="s">
         <v>15</v>
@@ -12151,7 +12151,7 @@
         <v>14</v>
       </c>
       <c r="F269" s="2">
-        <v>3642</v>
+        <v>4388</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>15</v>
@@ -12183,7 +12183,7 @@
         <v>14</v>
       </c>
       <c r="F270" s="2">
-        <v>4628</v>
+        <v>4741</v>
       </c>
       <c r="G270" s="2" t="s">
         <v>15</v>
@@ -12215,7 +12215,7 @@
         <v>14</v>
       </c>
       <c r="F271" s="2">
-        <v>3318</v>
+        <v>1073</v>
       </c>
       <c r="G271" s="2" t="s">
         <v>15</v>
@@ -12247,7 +12247,7 @@
         <v>14</v>
       </c>
       <c r="F272" s="2">
-        <v>1957</v>
+        <v>2539</v>
       </c>
       <c r="G272" s="2" t="s">
         <v>15</v>
@@ -12279,7 +12279,7 @@
         <v>14</v>
       </c>
       <c r="F273" s="2">
-        <v>3930</v>
+        <v>3342</v>
       </c>
       <c r="G273" s="2" t="s">
         <v>15</v>
@@ -12311,7 +12311,7 @@
         <v>14</v>
       </c>
       <c r="F274" s="2">
-        <v>3987</v>
+        <v>2948</v>
       </c>
       <c r="G274" s="2" t="s">
         <v>15</v>
@@ -12343,7 +12343,7 @@
         <v>14</v>
       </c>
       <c r="F275" s="2">
-        <v>4345</v>
+        <v>3743</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>15</v>
@@ -12375,7 +12375,7 @@
         <v>14</v>
       </c>
       <c r="F276" s="2">
-        <v>1921</v>
+        <v>2183</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>15</v>
@@ -12407,7 +12407,7 @@
         <v>14</v>
       </c>
       <c r="F277" s="2">
-        <v>1253</v>
+        <v>2051</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>15</v>
@@ -12439,7 +12439,7 @@
         <v>14</v>
       </c>
       <c r="F278" s="2">
-        <v>2022</v>
+        <v>3914</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>15</v>
@@ -12471,7 +12471,7 @@
         <v>14</v>
       </c>
       <c r="F279" s="2">
-        <v>2998</v>
+        <v>1181</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>15</v>
@@ -12503,7 +12503,7 @@
         <v>14</v>
       </c>
       <c r="F280" s="2">
-        <v>3613</v>
+        <v>1607</v>
       </c>
       <c r="G280" s="2" t="s">
         <v>15</v>
@@ -12535,7 +12535,7 @@
         <v>14</v>
       </c>
       <c r="F281" s="2">
-        <v>807</v>
+        <v>1599</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>15</v>
@@ -12567,7 +12567,7 @@
         <v>14</v>
       </c>
       <c r="F282" s="2">
-        <v>4471</v>
+        <v>2316</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>15</v>
@@ -12599,7 +12599,7 @@
         <v>14</v>
       </c>
       <c r="F283" s="2">
-        <v>3254</v>
+        <v>4359</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>15</v>
@@ -12631,7 +12631,7 @@
         <v>14</v>
       </c>
       <c r="F284" s="2">
-        <v>4358</v>
+        <v>3382</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>15</v>
@@ -12663,7 +12663,7 @@
         <v>14</v>
       </c>
       <c r="F285" s="2">
-        <v>1124</v>
+        <v>4169</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>15</v>
@@ -12695,7 +12695,7 @@
         <v>14</v>
       </c>
       <c r="F286" s="2">
-        <v>1101</v>
+        <v>2732</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>15</v>
@@ -12727,7 +12727,7 @@
         <v>14</v>
       </c>
       <c r="F287" s="2">
-        <v>3255</v>
+        <v>3281</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>15</v>
@@ -12759,7 +12759,7 @@
         <v>14</v>
       </c>
       <c r="F288" s="2">
-        <v>3697</v>
+        <v>4667</v>
       </c>
       <c r="G288" s="2" t="s">
         <v>15</v>
@@ -12791,7 +12791,7 @@
         <v>14</v>
       </c>
       <c r="F289" s="2">
-        <v>4281</v>
+        <v>4377</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>15</v>
@@ -12823,7 +12823,7 @@
         <v>14</v>
       </c>
       <c r="F290" s="2">
-        <v>1054</v>
+        <v>4130</v>
       </c>
       <c r="G290" s="2" t="s">
         <v>15</v>
@@ -12855,7 +12855,7 @@
         <v>14</v>
       </c>
       <c r="F291" s="2">
-        <v>2897</v>
+        <v>3151</v>
       </c>
       <c r="G291" s="2" t="s">
         <v>15</v>
@@ -12887,7 +12887,7 @@
         <v>14</v>
       </c>
       <c r="F292" s="2">
-        <v>1373</v>
+        <v>1954</v>
       </c>
       <c r="G292" s="2" t="s">
         <v>15</v>
@@ -12919,7 +12919,7 @@
         <v>14</v>
       </c>
       <c r="F293" s="2">
-        <v>887</v>
+        <v>2112</v>
       </c>
       <c r="G293" s="2" t="s">
         <v>15</v>
@@ -12951,7 +12951,7 @@
         <v>14</v>
       </c>
       <c r="F294" s="2">
-        <v>2040</v>
+        <v>4415</v>
       </c>
       <c r="G294" s="2" t="s">
         <v>15</v>
@@ -12983,7 +12983,7 @@
         <v>14</v>
       </c>
       <c r="F295" s="2">
-        <v>4415</v>
+        <v>1216</v>
       </c>
       <c r="G295" s="2" t="s">
         <v>15</v>
@@ -13015,7 +13015,7 @@
         <v>14</v>
       </c>
       <c r="F296" s="2">
-        <v>2494</v>
+        <v>3046</v>
       </c>
       <c r="G296" s="2" t="s">
         <v>15</v>
@@ -13047,7 +13047,7 @@
         <v>14</v>
       </c>
       <c r="F297" s="2">
-        <v>1742</v>
+        <v>893</v>
       </c>
       <c r="G297" s="2" t="s">
         <v>15</v>
@@ -13079,7 +13079,7 @@
         <v>14</v>
       </c>
       <c r="F298" s="2">
-        <v>1798</v>
+        <v>2486</v>
       </c>
       <c r="G298" s="2" t="s">
         <v>15</v>
@@ -13111,7 +13111,7 @@
         <v>14</v>
       </c>
       <c r="F299" s="2">
-        <v>3553</v>
+        <v>4583</v>
       </c>
       <c r="G299" s="2" t="s">
         <v>15</v>
@@ -13143,7 +13143,7 @@
         <v>14</v>
       </c>
       <c r="F300" s="2">
-        <v>1723</v>
+        <v>2338</v>
       </c>
       <c r="G300" s="2" t="s">
         <v>15</v>
@@ -13175,7 +13175,7 @@
         <v>14</v>
       </c>
       <c r="F301" s="2">
-        <v>2306</v>
+        <v>965</v>
       </c>
       <c r="G301" s="2" t="s">
         <v>15</v>
@@ -13207,7 +13207,7 @@
         <v>14</v>
       </c>
       <c r="F302" s="2">
-        <v>3825</v>
+        <v>1324</v>
       </c>
       <c r="G302" s="2" t="s">
         <v>15</v>
@@ -13239,7 +13239,7 @@
         <v>14</v>
       </c>
       <c r="F303" s="2">
-        <v>3748</v>
+        <v>2451</v>
       </c>
       <c r="G303" s="2" t="s">
         <v>15</v>
@@ -13271,7 +13271,7 @@
         <v>14</v>
       </c>
       <c r="F304" s="2">
-        <v>4042</v>
+        <v>4213</v>
       </c>
       <c r="G304" s="2" t="s">
         <v>15</v>
@@ -13303,7 +13303,7 @@
         <v>14</v>
       </c>
       <c r="F305" s="2">
-        <v>1718</v>
+        <v>3647</v>
       </c>
       <c r="G305" s="2" t="s">
         <v>15</v>
@@ -13335,7 +13335,7 @@
         <v>14</v>
       </c>
       <c r="F306" s="2">
-        <v>2459</v>
+        <v>1684</v>
       </c>
       <c r="G306" s="2" t="s">
         <v>15</v>
@@ -13367,7 +13367,7 @@
         <v>14</v>
       </c>
       <c r="F307" s="2">
-        <v>3958</v>
+        <v>1670</v>
       </c>
       <c r="G307" s="2" t="s">
         <v>15</v>
@@ -13399,7 +13399,7 @@
         <v>14</v>
       </c>
       <c r="F308" s="2">
-        <v>3693</v>
+        <v>2367</v>
       </c>
       <c r="G308" s="2" t="s">
         <v>15</v>
@@ -13431,7 +13431,7 @@
         <v>14</v>
       </c>
       <c r="F309" s="2">
-        <v>2395</v>
+        <v>1288</v>
       </c>
       <c r="G309" s="2" t="s">
         <v>15</v>
@@ -13463,7 +13463,7 @@
         <v>14</v>
       </c>
       <c r="F310" s="2">
-        <v>1596</v>
+        <v>3300</v>
       </c>
       <c r="G310" s="2" t="s">
         <v>15</v>
@@ -13495,7 +13495,7 @@
         <v>14</v>
       </c>
       <c r="F311" s="2">
-        <v>4551</v>
+        <v>3415</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>15</v>
@@ -13527,7 +13527,7 @@
         <v>14</v>
       </c>
       <c r="F312" s="2">
-        <v>1825</v>
+        <v>3792</v>
       </c>
       <c r="G312" s="2" t="s">
         <v>15</v>
@@ -13559,7 +13559,7 @@
         <v>14</v>
       </c>
       <c r="F313" s="2">
-        <v>948</v>
+        <v>1274</v>
       </c>
       <c r="G313" s="2" t="s">
         <v>15</v>
@@ -13591,7 +13591,7 @@
         <v>14</v>
       </c>
       <c r="F314" s="2">
-        <v>1711</v>
+        <v>1771</v>
       </c>
       <c r="G314" s="2" t="s">
         <v>15</v>
@@ -13623,7 +13623,7 @@
         <v>14</v>
       </c>
       <c r="F315" s="2">
-        <v>980</v>
+        <v>4733</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>15</v>
@@ -13655,7 +13655,7 @@
         <v>14</v>
       </c>
       <c r="F316" s="2">
-        <v>1981</v>
+        <v>3435</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>15</v>
@@ -13687,7 +13687,7 @@
         <v>14</v>
       </c>
       <c r="F317" s="2">
-        <v>4536</v>
+        <v>1603</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>15</v>
@@ -13719,7 +13719,7 @@
         <v>14</v>
       </c>
       <c r="F318" s="2">
-        <v>2435</v>
+        <v>2956</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>15</v>
@@ -13751,7 +13751,7 @@
         <v>14</v>
       </c>
       <c r="F319" s="2">
-        <v>3880</v>
+        <v>3276</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>15</v>
@@ -13783,7 +13783,7 @@
         <v>14</v>
       </c>
       <c r="F320" s="2">
-        <v>2877</v>
+        <v>3215</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>15</v>
@@ -13815,7 +13815,7 @@
         <v>14</v>
       </c>
       <c r="F321" s="2">
-        <v>1338</v>
+        <v>4657</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>15</v>
@@ -13847,7 +13847,7 @@
         <v>14</v>
       </c>
       <c r="F322" s="2">
-        <v>3047</v>
+        <v>2210</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>15</v>
@@ -13879,7 +13879,7 @@
         <v>14</v>
       </c>
       <c r="F323" s="2">
-        <v>3459</v>
+        <v>2967</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>15</v>
@@ -13911,7 +13911,7 @@
         <v>14</v>
       </c>
       <c r="F324" s="2">
-        <v>4687</v>
+        <v>3405</v>
       </c>
       <c r="G324" s="2" t="s">
         <v>15</v>
@@ -13943,7 +13943,7 @@
         <v>14</v>
       </c>
       <c r="F325" s="2">
-        <v>2614</v>
+        <v>4135</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>15</v>
@@ -13975,7 +13975,7 @@
         <v>14</v>
       </c>
       <c r="F326" s="2">
-        <v>1026</v>
+        <v>1862</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>15</v>
@@ -14007,7 +14007,7 @@
         <v>14</v>
       </c>
       <c r="F327" s="2">
-        <v>2096</v>
+        <v>2324</v>
       </c>
       <c r="G327" s="2" t="s">
         <v>15</v>
@@ -14039,7 +14039,7 @@
         <v>14</v>
       </c>
       <c r="F328" s="2">
-        <v>2464</v>
+        <v>2599</v>
       </c>
       <c r="G328" s="2" t="s">
         <v>15</v>
@@ -14071,7 +14071,7 @@
         <v>14</v>
       </c>
       <c r="F329" s="2">
-        <v>2928</v>
+        <v>4183</v>
       </c>
       <c r="G329" s="2" t="s">
         <v>15</v>
@@ -14103,7 +14103,7 @@
         <v>14</v>
       </c>
       <c r="F330" s="2">
-        <v>4415</v>
+        <v>1495</v>
       </c>
       <c r="G330" s="2" t="s">
         <v>15</v>
@@ -14135,7 +14135,7 @@
         <v>14</v>
       </c>
       <c r="F331" s="2">
-        <v>4562</v>
+        <v>3278</v>
       </c>
       <c r="G331" s="2" t="s">
         <v>15</v>
@@ -14167,7 +14167,7 @@
         <v>14</v>
       </c>
       <c r="F332" s="2">
-        <v>1700</v>
+        <v>3538</v>
       </c>
       <c r="G332" s="2" t="s">
         <v>15</v>
@@ -14199,7 +14199,7 @@
         <v>14</v>
       </c>
       <c r="F333" s="2">
-        <v>3357</v>
+        <v>3043</v>
       </c>
       <c r="G333" s="2" t="s">
         <v>15</v>
@@ -14231,7 +14231,7 @@
         <v>14</v>
       </c>
       <c r="F334" s="2">
-        <v>1863</v>
+        <v>2287</v>
       </c>
       <c r="G334" s="2" t="s">
         <v>15</v>
@@ -14263,7 +14263,7 @@
         <v>14</v>
       </c>
       <c r="F335" s="2">
-        <v>3474</v>
+        <v>1486</v>
       </c>
       <c r="G335" s="2" t="s">
         <v>15</v>
@@ -14295,7 +14295,7 @@
         <v>14</v>
       </c>
       <c r="F336" s="2">
-        <v>4591</v>
+        <v>1892</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>15</v>
@@ -14327,7 +14327,7 @@
         <v>14</v>
       </c>
       <c r="F337" s="2">
-        <v>3919</v>
+        <v>1918</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>15</v>
@@ -14359,7 +14359,7 @@
         <v>14</v>
       </c>
       <c r="F338" s="2">
-        <v>4643</v>
+        <v>3334</v>
       </c>
       <c r="G338" s="2" t="s">
         <v>15</v>
@@ -14391,7 +14391,7 @@
         <v>14</v>
       </c>
       <c r="F339" s="2">
-        <v>3323</v>
+        <v>1792</v>
       </c>
       <c r="G339" s="2" t="s">
         <v>15</v>
@@ -14423,7 +14423,7 @@
         <v>14</v>
       </c>
       <c r="F340" s="2">
-        <v>4243</v>
+        <v>954</v>
       </c>
       <c r="G340" s="2" t="s">
         <v>15</v>
@@ -14455,7 +14455,7 @@
         <v>14</v>
       </c>
       <c r="F341" s="2">
-        <v>3662</v>
+        <v>2967</v>
       </c>
       <c r="G341" s="2" t="s">
         <v>15</v>
@@ -14487,7 +14487,7 @@
         <v>14</v>
       </c>
       <c r="F342" s="2">
-        <v>1394</v>
+        <v>2339</v>
       </c>
       <c r="G342" s="2" t="s">
         <v>15</v>
@@ -14519,7 +14519,7 @@
         <v>14</v>
       </c>
       <c r="F343" s="2">
-        <v>4344</v>
+        <v>2931</v>
       </c>
       <c r="G343" s="2" t="s">
         <v>15</v>
@@ -14551,7 +14551,7 @@
         <v>14</v>
       </c>
       <c r="F344" s="2">
-        <v>1842</v>
+        <v>3210</v>
       </c>
       <c r="G344" s="2" t="s">
         <v>15</v>
@@ -14583,7 +14583,7 @@
         <v>14</v>
       </c>
       <c r="F345" s="2">
-        <v>4693</v>
+        <v>4194</v>
       </c>
       <c r="G345" s="2" t="s">
         <v>15</v>
@@ -14615,7 +14615,7 @@
         <v>14</v>
       </c>
       <c r="F346" s="2">
-        <v>3347</v>
+        <v>2515</v>
       </c>
       <c r="G346" s="2" t="s">
         <v>15</v>
@@ -14647,7 +14647,7 @@
         <v>14</v>
       </c>
       <c r="F347" s="2">
-        <v>4243</v>
+        <v>3933</v>
       </c>
       <c r="G347" s="2" t="s">
         <v>15</v>
@@ -14679,7 +14679,7 @@
         <v>14</v>
       </c>
       <c r="F348" s="2">
-        <v>4316</v>
+        <v>2972</v>
       </c>
       <c r="G348" s="2" t="s">
         <v>15</v>
@@ -14711,7 +14711,7 @@
         <v>14</v>
       </c>
       <c r="F349" s="2">
-        <v>2481</v>
+        <v>3530</v>
       </c>
       <c r="G349" s="2" t="s">
         <v>15</v>
@@ -14743,7 +14743,7 @@
         <v>14</v>
       </c>
       <c r="F350" s="2">
-        <v>2343</v>
+        <v>4592</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>15</v>
@@ -14775,7 +14775,7 @@
         <v>14</v>
       </c>
       <c r="F351" s="2">
-        <v>932</v>
+        <v>1209</v>
       </c>
       <c r="G351" s="2" t="s">
         <v>15</v>
@@ -14807,7 +14807,7 @@
         <v>14</v>
       </c>
       <c r="F352" s="2">
-        <v>1877</v>
+        <v>2387</v>
       </c>
       <c r="G352" s="2" t="s">
         <v>15</v>
@@ -14839,7 +14839,7 @@
         <v>14</v>
       </c>
       <c r="F353" s="2">
-        <v>3878</v>
+        <v>1728</v>
       </c>
       <c r="G353" s="2" t="s">
         <v>15</v>
@@ -14871,7 +14871,7 @@
         <v>14</v>
       </c>
       <c r="F354" s="2">
-        <v>2023</v>
+        <v>1955</v>
       </c>
       <c r="G354" s="2" t="s">
         <v>15</v>
@@ -14903,7 +14903,7 @@
         <v>14</v>
       </c>
       <c r="F355" s="2">
-        <v>3351</v>
+        <v>3759</v>
       </c>
       <c r="G355" s="2" t="s">
         <v>15</v>
@@ -14935,7 +14935,7 @@
         <v>14</v>
       </c>
       <c r="F356" s="2">
-        <v>1610</v>
+        <v>4618</v>
       </c>
       <c r="G356" s="2" t="s">
         <v>15</v>
@@ -14967,7 +14967,7 @@
         <v>14</v>
       </c>
       <c r="F357" s="2">
-        <v>4169</v>
+        <v>4189</v>
       </c>
       <c r="G357" s="2" t="s">
         <v>15</v>
@@ -14999,7 +14999,7 @@
         <v>14</v>
       </c>
       <c r="F358" s="2">
-        <v>3435</v>
+        <v>2412</v>
       </c>
       <c r="G358" s="2" t="s">
         <v>15</v>
@@ -15031,7 +15031,7 @@
         <v>14</v>
       </c>
       <c r="F359" s="2">
-        <v>3926</v>
+        <v>3531</v>
       </c>
       <c r="G359" s="2" t="s">
         <v>15</v>
@@ -15063,7 +15063,7 @@
         <v>14</v>
       </c>
       <c r="F360" s="2">
-        <v>3200</v>
+        <v>1269</v>
       </c>
       <c r="G360" s="2" t="s">
         <v>15</v>
@@ -15095,7 +15095,7 @@
         <v>14</v>
       </c>
       <c r="F361" s="2">
-        <v>3023</v>
+        <v>1324</v>
       </c>
       <c r="G361" s="2" t="s">
         <v>15</v>
@@ -15127,7 +15127,7 @@
         <v>14</v>
       </c>
       <c r="F362" s="2">
-        <v>4262</v>
+        <v>971</v>
       </c>
       <c r="G362" s="2" t="s">
         <v>15</v>
@@ -15159,7 +15159,7 @@
         <v>14</v>
       </c>
       <c r="F363" s="2">
-        <v>4163</v>
+        <v>4313</v>
       </c>
       <c r="G363" s="2" t="s">
         <v>15</v>
@@ -15191,7 +15191,7 @@
         <v>14</v>
       </c>
       <c r="F364" s="2">
-        <v>2145</v>
+        <v>3040</v>
       </c>
       <c r="G364" s="2" t="s">
         <v>15</v>
@@ -15223,7 +15223,7 @@
         <v>14</v>
       </c>
       <c r="F365" s="2">
-        <v>1426</v>
+        <v>2472</v>
       </c>
       <c r="G365" s="2" t="s">
         <v>15</v>
@@ -15255,7 +15255,7 @@
         <v>14</v>
       </c>
       <c r="F366" s="2">
-        <v>2739</v>
+        <v>2839</v>
       </c>
       <c r="G366" s="2" t="s">
         <v>15</v>
@@ -15287,7 +15287,7 @@
         <v>14</v>
       </c>
       <c r="F367" s="2">
-        <v>4777</v>
+        <v>3009</v>
       </c>
       <c r="G367" s="2" t="s">
         <v>15</v>
@@ -15319,7 +15319,7 @@
         <v>14</v>
       </c>
       <c r="F368" s="2">
-        <v>2027</v>
+        <v>3498</v>
       </c>
       <c r="G368" s="2" t="s">
         <v>15</v>
@@ -15351,7 +15351,7 @@
         <v>14</v>
       </c>
       <c r="F369" s="2">
-        <v>3574</v>
+        <v>1296</v>
       </c>
       <c r="G369" s="2" t="s">
         <v>15</v>
@@ -15383,7 +15383,7 @@
         <v>14</v>
       </c>
       <c r="F370" s="2">
-        <v>2746</v>
+        <v>1680</v>
       </c>
       <c r="G370" s="2" t="s">
         <v>15</v>
@@ -15415,7 +15415,7 @@
         <v>14</v>
       </c>
       <c r="F371" s="2">
-        <v>3676</v>
+        <v>3485</v>
       </c>
       <c r="G371" s="2" t="s">
         <v>15</v>
@@ -15447,7 +15447,7 @@
         <v>14</v>
       </c>
       <c r="F372" s="2">
-        <v>2155</v>
+        <v>4113</v>
       </c>
       <c r="G372" s="2" t="s">
         <v>15</v>
@@ -15479,7 +15479,7 @@
         <v>14</v>
       </c>
       <c r="F373" s="2">
-        <v>1410</v>
+        <v>2606</v>
       </c>
       <c r="G373" s="2" t="s">
         <v>15</v>
@@ -15511,7 +15511,7 @@
         <v>14</v>
       </c>
       <c r="F374" s="2">
-        <v>4289</v>
+        <v>4132</v>
       </c>
       <c r="G374" s="2" t="s">
         <v>15</v>
@@ -15543,7 +15543,7 @@
         <v>14</v>
       </c>
       <c r="F375" s="2">
-        <v>3804</v>
+        <v>2575</v>
       </c>
       <c r="G375" s="2" t="s">
         <v>15</v>
@@ -15575,7 +15575,7 @@
         <v>14</v>
       </c>
       <c r="F376" s="2">
-        <v>4341</v>
+        <v>1225</v>
       </c>
       <c r="G376" s="2" t="s">
         <v>15</v>
@@ -15607,7 +15607,7 @@
         <v>14</v>
       </c>
       <c r="F377" s="2">
-        <v>1605</v>
+        <v>3457</v>
       </c>
       <c r="G377" s="2" t="s">
         <v>15</v>
@@ -15639,7 +15639,7 @@
         <v>14</v>
       </c>
       <c r="F378" s="2">
-        <v>3466</v>
+        <v>1068</v>
       </c>
       <c r="G378" s="2" t="s">
         <v>15</v>
@@ -15671,7 +15671,7 @@
         <v>14</v>
       </c>
       <c r="F379" s="2">
-        <v>4511</v>
+        <v>2072</v>
       </c>
       <c r="G379" s="2" t="s">
         <v>15</v>
@@ -15703,7 +15703,7 @@
         <v>14</v>
       </c>
       <c r="F380" s="2">
-        <v>1605</v>
+        <v>2610</v>
       </c>
       <c r="G380" s="2" t="s">
         <v>15</v>
@@ -15735,7 +15735,7 @@
         <v>14</v>
       </c>
       <c r="F381" s="2">
-        <v>3584</v>
+        <v>3246</v>
       </c>
       <c r="G381" s="2" t="s">
         <v>15</v>
@@ -15767,7 +15767,7 @@
         <v>14</v>
       </c>
       <c r="F382" s="2">
-        <v>881</v>
+        <v>4146</v>
       </c>
       <c r="G382" s="2" t="s">
         <v>15</v>
@@ -15799,7 +15799,7 @@
         <v>14</v>
       </c>
       <c r="F383" s="2">
-        <v>2372</v>
+        <v>3988</v>
       </c>
       <c r="G383" s="2" t="s">
         <v>15</v>
@@ -15831,7 +15831,7 @@
         <v>14</v>
       </c>
       <c r="F384" s="2">
-        <v>4743</v>
+        <v>1730</v>
       </c>
       <c r="G384" s="2" t="s">
         <v>15</v>
@@ -15863,7 +15863,7 @@
         <v>14</v>
       </c>
       <c r="F385" s="2">
-        <v>3690</v>
+        <v>2541</v>
       </c>
       <c r="G385" s="2" t="s">
         <v>15</v>
@@ -15895,7 +15895,7 @@
         <v>14</v>
       </c>
       <c r="F386" s="2">
-        <v>1886</v>
+        <v>2079</v>
       </c>
       <c r="G386" s="2" t="s">
         <v>15</v>
@@ -15927,7 +15927,7 @@
         <v>14</v>
       </c>
       <c r="F387" s="2">
-        <v>2744</v>
+        <v>3874</v>
       </c>
       <c r="G387" s="2" t="s">
         <v>15</v>
@@ -15959,7 +15959,7 @@
         <v>14</v>
       </c>
       <c r="F388" s="2">
-        <v>1616</v>
+        <v>2512</v>
       </c>
       <c r="G388" s="2" t="s">
         <v>15</v>
@@ -15991,7 +15991,7 @@
         <v>14</v>
       </c>
       <c r="F389" s="2">
-        <v>3729</v>
+        <v>2902</v>
       </c>
       <c r="G389" s="2" t="s">
         <v>15</v>
@@ -16023,7 +16023,7 @@
         <v>14</v>
       </c>
       <c r="F390" s="2">
-        <v>2901</v>
+        <v>4623</v>
       </c>
       <c r="G390" s="2" t="s">
         <v>15</v>
@@ -16055,7 +16055,7 @@
         <v>14</v>
       </c>
       <c r="F391" s="2">
-        <v>1763</v>
+        <v>2103</v>
       </c>
       <c r="G391" s="2" t="s">
         <v>15</v>
@@ -16087,7 +16087,7 @@
         <v>14</v>
       </c>
       <c r="F392" s="2">
-        <v>2508</v>
+        <v>3950</v>
       </c>
       <c r="G392" s="2" t="s">
         <v>15</v>
@@ -16119,7 +16119,7 @@
         <v>14</v>
       </c>
       <c r="F393" s="2">
-        <v>4065</v>
+        <v>2644</v>
       </c>
       <c r="G393" s="2" t="s">
         <v>15</v>
@@ -16151,7 +16151,7 @@
         <v>14</v>
       </c>
       <c r="F394" s="2">
-        <v>1782</v>
+        <v>1292</v>
       </c>
       <c r="G394" s="2" t="s">
         <v>15</v>
@@ -16183,7 +16183,7 @@
         <v>14</v>
       </c>
       <c r="F395" s="2">
-        <v>3820</v>
+        <v>3000</v>
       </c>
       <c r="G395" s="2" t="s">
         <v>15</v>
@@ -16215,7 +16215,7 @@
         <v>14</v>
       </c>
       <c r="F396" s="2">
-        <v>3924</v>
+        <v>1468</v>
       </c>
       <c r="G396" s="2" t="s">
         <v>15</v>
@@ -16247,7 +16247,7 @@
         <v>14</v>
       </c>
       <c r="F397" s="2">
-        <v>2202</v>
+        <v>4226</v>
       </c>
       <c r="G397" s="2" t="s">
         <v>15</v>
@@ -16279,7 +16279,7 @@
         <v>14</v>
       </c>
       <c r="F398" s="2">
-        <v>3389</v>
+        <v>3658</v>
       </c>
       <c r="G398" s="2" t="s">
         <v>15</v>
@@ -16311,7 +16311,7 @@
         <v>14</v>
       </c>
       <c r="F399" s="2">
-        <v>1459</v>
+        <v>3470</v>
       </c>
       <c r="G399" s="2" t="s">
         <v>15</v>
@@ -16343,7 +16343,7 @@
         <v>14</v>
       </c>
       <c r="F400" s="2">
-        <v>2506</v>
+        <v>3158</v>
       </c>
       <c r="G400" s="2" t="s">
         <v>15</v>
@@ -16375,7 +16375,7 @@
         <v>14</v>
       </c>
       <c r="F401" s="2">
-        <v>3798</v>
+        <v>1477</v>
       </c>
       <c r="G401" s="2" t="s">
         <v>15</v>
@@ -16407,7 +16407,7 @@
         <v>14</v>
       </c>
       <c r="F402" s="2">
-        <v>4518</v>
+        <v>3875</v>
       </c>
       <c r="G402" s="2" t="s">
         <v>15</v>
@@ -16439,7 +16439,7 @@
         <v>14</v>
       </c>
       <c r="F403" s="2">
-        <v>2416</v>
+        <v>3243</v>
       </c>
       <c r="G403" s="2" t="s">
         <v>15</v>
@@ -16471,7 +16471,7 @@
         <v>14</v>
       </c>
       <c r="F404" s="2">
-        <v>1249</v>
+        <v>1420</v>
       </c>
       <c r="G404" s="2" t="s">
         <v>15</v>
@@ -16503,7 +16503,7 @@
         <v>14</v>
       </c>
       <c r="F405" s="2">
-        <v>4430</v>
+        <v>3256</v>
       </c>
       <c r="G405" s="2" t="s">
         <v>15</v>
@@ -16535,7 +16535,7 @@
         <v>14</v>
       </c>
       <c r="F406" s="2">
-        <v>4657</v>
+        <v>2216</v>
       </c>
       <c r="G406" s="2" t="s">
         <v>15</v>
@@ -16567,7 +16567,7 @@
         <v>14</v>
       </c>
       <c r="F407" s="2">
-        <v>2057</v>
+        <v>1088</v>
       </c>
       <c r="G407" s="2" t="s">
         <v>15</v>
@@ -16599,7 +16599,7 @@
         <v>14</v>
       </c>
       <c r="F408" s="2">
-        <v>3691</v>
+        <v>3992</v>
       </c>
       <c r="G408" s="2" t="s">
         <v>15</v>
@@ -16631,7 +16631,7 @@
         <v>14</v>
       </c>
       <c r="F409" s="2">
-        <v>4418</v>
+        <v>1235</v>
       </c>
       <c r="G409" s="2" t="s">
         <v>15</v>
@@ -16663,7 +16663,7 @@
         <v>14</v>
       </c>
       <c r="F410" s="2">
-        <v>2407</v>
+        <v>1330</v>
       </c>
       <c r="G410" s="2" t="s">
         <v>15</v>
@@ -16695,7 +16695,7 @@
         <v>14</v>
       </c>
       <c r="F411" s="2">
-        <v>886</v>
+        <v>921</v>
       </c>
       <c r="G411" s="2" t="s">
         <v>15</v>
@@ -16727,7 +16727,7 @@
         <v>14</v>
       </c>
       <c r="F412" s="2">
-        <v>1245</v>
+        <v>2205</v>
       </c>
       <c r="G412" s="2" t="s">
         <v>15</v>
@@ -16759,7 +16759,7 @@
         <v>14</v>
       </c>
       <c r="F413" s="2">
-        <v>1606</v>
+        <v>3990</v>
       </c>
       <c r="G413" s="2" t="s">
         <v>15</v>
@@ -16791,7 +16791,7 @@
         <v>14</v>
       </c>
       <c r="F414" s="2">
-        <v>1886</v>
+        <v>1498</v>
       </c>
       <c r="G414" s="2" t="s">
         <v>15</v>
@@ -16823,7 +16823,7 @@
         <v>14</v>
       </c>
       <c r="F415" s="2">
-        <v>2356</v>
+        <v>2498</v>
       </c>
       <c r="G415" s="2" t="s">
         <v>15</v>
@@ -16855,7 +16855,7 @@
         <v>14</v>
       </c>
       <c r="F416" s="2">
-        <v>3075</v>
+        <v>1746</v>
       </c>
       <c r="G416" s="2" t="s">
         <v>15</v>
@@ -16887,7 +16887,7 @@
         <v>14</v>
       </c>
       <c r="F417" s="2">
-        <v>4305</v>
+        <v>1559</v>
       </c>
       <c r="G417" s="2" t="s">
         <v>15</v>
@@ -16919,7 +16919,7 @@
         <v>14</v>
       </c>
       <c r="F418" s="2">
-        <v>4026</v>
+        <v>1022</v>
       </c>
       <c r="G418" s="2" t="s">
         <v>15</v>
@@ -16951,7 +16951,7 @@
         <v>14</v>
       </c>
       <c r="F419" s="2">
-        <v>4787</v>
+        <v>858</v>
       </c>
       <c r="G419" s="2" t="s">
         <v>15</v>
@@ -16983,7 +16983,7 @@
         <v>14</v>
       </c>
       <c r="F420" s="2">
-        <v>1465</v>
+        <v>1942</v>
       </c>
       <c r="G420" s="2" t="s">
         <v>15</v>
@@ -17015,7 +17015,7 @@
         <v>14</v>
       </c>
       <c r="F421" s="2">
-        <v>1251</v>
+        <v>4088</v>
       </c>
       <c r="G421" s="2" t="s">
         <v>15</v>
@@ -17047,7 +17047,7 @@
         <v>14</v>
       </c>
       <c r="F422" s="2">
-        <v>3593</v>
+        <v>4265</v>
       </c>
       <c r="G422" s="2" t="s">
         <v>15</v>
@@ -17079,7 +17079,7 @@
         <v>14</v>
       </c>
       <c r="F423" s="2">
-        <v>961</v>
+        <v>1299</v>
       </c>
       <c r="G423" s="2" t="s">
         <v>15</v>
@@ -17111,7 +17111,7 @@
         <v>14</v>
       </c>
       <c r="F424" s="2">
-        <v>4561</v>
+        <v>4612</v>
       </c>
       <c r="G424" s="2" t="s">
         <v>15</v>
@@ -17143,7 +17143,7 @@
         <v>14</v>
       </c>
       <c r="F425" s="2">
-        <v>3789</v>
+        <v>3970</v>
       </c>
       <c r="G425" s="2" t="s">
         <v>15</v>
@@ -17175,7 +17175,7 @@
         <v>14</v>
       </c>
       <c r="F426" s="2">
-        <v>1865</v>
+        <v>1792</v>
       </c>
       <c r="G426" s="2" t="s">
         <v>15</v>
@@ -17207,7 +17207,7 @@
         <v>14</v>
       </c>
       <c r="F427" s="2">
-        <v>3054</v>
+        <v>2111</v>
       </c>
       <c r="G427" s="2" t="s">
         <v>15</v>
@@ -17239,7 +17239,7 @@
         <v>14</v>
       </c>
       <c r="F428" s="2">
-        <v>3806</v>
+        <v>4298</v>
       </c>
       <c r="G428" s="2" t="s">
         <v>15</v>
@@ -17271,7 +17271,7 @@
         <v>14</v>
       </c>
       <c r="F429" s="2">
-        <v>3632</v>
+        <v>4287</v>
       </c>
       <c r="G429" s="2" t="s">
         <v>15</v>
@@ -17303,7 +17303,7 @@
         <v>14</v>
       </c>
       <c r="F430" s="2">
-        <v>1278</v>
+        <v>2963</v>
       </c>
       <c r="G430" s="2" t="s">
         <v>15</v>
@@ -17335,7 +17335,7 @@
         <v>14</v>
       </c>
       <c r="F431" s="2">
-        <v>1961</v>
+        <v>2290</v>
       </c>
       <c r="G431" s="2" t="s">
         <v>15</v>
@@ -17367,7 +17367,7 @@
         <v>14</v>
       </c>
       <c r="F432" s="2">
-        <v>4477</v>
+        <v>4010</v>
       </c>
       <c r="G432" s="2" t="s">
         <v>15</v>
@@ -17399,7 +17399,7 @@
         <v>14</v>
       </c>
       <c r="F433" s="2">
-        <v>4396</v>
+        <v>4380</v>
       </c>
       <c r="G433" s="2" t="s">
         <v>15</v>
@@ -17431,7 +17431,7 @@
         <v>14</v>
       </c>
       <c r="F434" s="2">
-        <v>4580</v>
+        <v>3971</v>
       </c>
       <c r="G434" s="2" t="s">
         <v>15</v>
@@ -17463,7 +17463,7 @@
         <v>14</v>
       </c>
       <c r="F435" s="2">
-        <v>3548</v>
+        <v>2495</v>
       </c>
       <c r="G435" s="2" t="s">
         <v>15</v>
@@ -17495,7 +17495,7 @@
         <v>14</v>
       </c>
       <c r="F436" s="2">
-        <v>2282</v>
+        <v>1931</v>
       </c>
       <c r="G436" s="2" t="s">
         <v>15</v>
@@ -17527,7 +17527,7 @@
         <v>14</v>
       </c>
       <c r="F437" s="2">
-        <v>4593</v>
+        <v>4423</v>
       </c>
       <c r="G437" s="2" t="s">
         <v>15</v>
@@ -17559,7 +17559,7 @@
         <v>14</v>
       </c>
       <c r="F438" s="2">
-        <v>2850</v>
+        <v>2497</v>
       </c>
       <c r="G438" s="2" t="s">
         <v>15</v>
@@ -17591,7 +17591,7 @@
         <v>14</v>
       </c>
       <c r="F439" s="2">
-        <v>2725</v>
+        <v>1522</v>
       </c>
       <c r="G439" s="2" t="s">
         <v>15</v>
@@ -17623,7 +17623,7 @@
         <v>14</v>
       </c>
       <c r="F440" s="2">
-        <v>3970</v>
+        <v>1528</v>
       </c>
       <c r="G440" s="2" t="s">
         <v>15</v>
@@ -17655,7 +17655,7 @@
         <v>14</v>
       </c>
       <c r="F441" s="2">
-        <v>1776</v>
+        <v>2770</v>
       </c>
       <c r="G441" s="2" t="s">
         <v>15</v>
@@ -17687,7 +17687,7 @@
         <v>14</v>
       </c>
       <c r="F442" s="2">
-        <v>2614</v>
+        <v>904</v>
       </c>
       <c r="G442" s="2" t="s">
         <v>15</v>
@@ -17719,7 +17719,7 @@
         <v>14</v>
       </c>
       <c r="F443" s="2">
-        <v>4389</v>
+        <v>3122</v>
       </c>
       <c r="G443" s="2" t="s">
         <v>15</v>
@@ -17751,7 +17751,7 @@
         <v>14</v>
       </c>
       <c r="F444" s="2">
-        <v>860</v>
+        <v>1126</v>
       </c>
       <c r="G444" s="2" t="s">
         <v>15</v>
@@ -17783,7 +17783,7 @@
         <v>14</v>
       </c>
       <c r="F445" s="2">
-        <v>1441</v>
+        <v>1287</v>
       </c>
       <c r="G445" s="2" t="s">
         <v>15</v>
@@ -17815,7 +17815,7 @@
         <v>14</v>
       </c>
       <c r="F446" s="2">
-        <v>1682</v>
+        <v>2193</v>
       </c>
       <c r="G446" s="2" t="s">
         <v>15</v>
@@ -17847,7 +17847,7 @@
         <v>14</v>
       </c>
       <c r="F447" s="2">
-        <v>1806</v>
+        <v>2803</v>
       </c>
       <c r="G447" s="2" t="s">
         <v>15</v>
@@ -17879,7 +17879,7 @@
         <v>14</v>
       </c>
       <c r="F448" s="2">
-        <v>3015</v>
+        <v>3596</v>
       </c>
       <c r="G448" s="2" t="s">
         <v>15</v>
@@ -17911,7 +17911,7 @@
         <v>14</v>
       </c>
       <c r="F449" s="2">
-        <v>3360</v>
+        <v>3194</v>
       </c>
       <c r="G449" s="2" t="s">
         <v>15</v>
@@ -17943,7 +17943,7 @@
         <v>14</v>
       </c>
       <c r="F450" s="2">
-        <v>2372</v>
+        <v>2329</v>
       </c>
       <c r="G450" s="2" t="s">
         <v>15</v>
@@ -17975,7 +17975,7 @@
         <v>14</v>
       </c>
       <c r="F451" s="2">
-        <v>2745</v>
+        <v>3819</v>
       </c>
       <c r="G451" s="2" t="s">
         <v>15</v>
@@ -18007,7 +18007,7 @@
         <v>14</v>
       </c>
       <c r="F452" s="2">
-        <v>2479</v>
+        <v>2766</v>
       </c>
       <c r="G452" s="2" t="s">
         <v>15</v>
@@ -18039,7 +18039,7 @@
         <v>14</v>
       </c>
       <c r="F453" s="2">
-        <v>1262</v>
+        <v>2868</v>
       </c>
       <c r="G453" s="2" t="s">
         <v>15</v>
@@ -18071,7 +18071,7 @@
         <v>14</v>
       </c>
       <c r="F454" s="2">
-        <v>4473</v>
+        <v>3820</v>
       </c>
       <c r="G454" s="2" t="s">
         <v>15</v>
@@ -18103,7 +18103,7 @@
         <v>14</v>
       </c>
       <c r="F455" s="2">
-        <v>1626</v>
+        <v>4529</v>
       </c>
       <c r="G455" s="2" t="s">
         <v>15</v>
@@ -18135,7 +18135,7 @@
         <v>14</v>
       </c>
       <c r="F456" s="2">
-        <v>3691</v>
+        <v>2461</v>
       </c>
       <c r="G456" s="2" t="s">
         <v>15</v>
@@ -18167,7 +18167,7 @@
         <v>14</v>
       </c>
       <c r="F457" s="2">
-        <v>3138</v>
+        <v>2268</v>
       </c>
       <c r="G457" s="2" t="s">
         <v>15</v>
@@ -18199,7 +18199,7 @@
         <v>14</v>
       </c>
       <c r="F458" s="2">
-        <v>856</v>
+        <v>3253</v>
       </c>
       <c r="G458" s="2" t="s">
         <v>15</v>
@@ -18231,7 +18231,7 @@
         <v>14</v>
       </c>
       <c r="F459" s="2">
-        <v>2601</v>
+        <v>4103</v>
       </c>
       <c r="G459" s="2" t="s">
         <v>15</v>
@@ -18263,7 +18263,7 @@
         <v>14</v>
       </c>
       <c r="F460" s="2">
-        <v>2749</v>
+        <v>4645</v>
       </c>
       <c r="G460" s="2" t="s">
         <v>15</v>
@@ -18295,7 +18295,7 @@
         <v>14</v>
       </c>
       <c r="F461" s="2">
-        <v>1270</v>
+        <v>1816</v>
       </c>
       <c r="G461" s="2" t="s">
         <v>15</v>
@@ -18327,7 +18327,7 @@
         <v>14</v>
       </c>
       <c r="F462" s="2">
-        <v>1955</v>
+        <v>3783</v>
       </c>
       <c r="G462" s="2" t="s">
         <v>15</v>
@@ -18359,7 +18359,7 @@
         <v>14</v>
       </c>
       <c r="F463" s="2">
-        <v>3567</v>
+        <v>4030</v>
       </c>
       <c r="G463" s="2" t="s">
         <v>15</v>
@@ -18391,7 +18391,7 @@
         <v>14</v>
       </c>
       <c r="F464" s="2">
-        <v>3712</v>
+        <v>917</v>
       </c>
       <c r="G464" s="2" t="s">
         <v>15</v>
@@ -18423,7 +18423,7 @@
         <v>14</v>
       </c>
       <c r="F465" s="2">
-        <v>1272</v>
+        <v>4148</v>
       </c>
       <c r="G465" s="2" t="s">
         <v>15</v>
@@ -18455,7 +18455,7 @@
         <v>14</v>
       </c>
       <c r="F466" s="2">
-        <v>4776</v>
+        <v>2958</v>
       </c>
       <c r="G466" s="2" t="s">
         <v>15</v>
@@ -18487,7 +18487,7 @@
         <v>14</v>
       </c>
       <c r="F467" s="2">
-        <v>1305</v>
+        <v>4251</v>
       </c>
       <c r="G467" s="2" t="s">
         <v>15</v>
@@ -18519,7 +18519,7 @@
         <v>14</v>
       </c>
       <c r="F468" s="2">
-        <v>4315</v>
+        <v>4757</v>
       </c>
       <c r="G468" s="2" t="s">
         <v>15</v>
@@ -18551,7 +18551,7 @@
         <v>14</v>
       </c>
       <c r="F469" s="2">
-        <v>2441</v>
+        <v>4755</v>
       </c>
       <c r="G469" s="2" t="s">
         <v>15</v>
@@ -18583,7 +18583,7 @@
         <v>14</v>
       </c>
       <c r="F470" s="2">
-        <v>2133</v>
+        <v>2265</v>
       </c>
       <c r="G470" s="2" t="s">
         <v>15</v>
@@ -18615,7 +18615,7 @@
         <v>14</v>
       </c>
       <c r="F471" s="2">
-        <v>3039</v>
+        <v>2516</v>
       </c>
       <c r="G471" s="2" t="s">
         <v>15</v>
@@ -18702,7 +18702,7 @@
         <v>14</v>
       </c>
       <c r="F2" s="2">
-        <v>3639</v>
+        <v>3597</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>15</v>
@@ -18734,7 +18734,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="2">
-        <v>2895</v>
+        <v>1120</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>15</v>
@@ -18766,7 +18766,7 @@
         <v>14</v>
       </c>
       <c r="F4" s="2">
-        <v>3225</v>
+        <v>3037</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
@@ -18798,7 +18798,7 @@
         <v>14</v>
       </c>
       <c r="F5" s="2">
-        <v>1115</v>
+        <v>2728</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
@@ -18830,7 +18830,7 @@
         <v>14</v>
       </c>
       <c r="F6" s="2">
-        <v>3408</v>
+        <v>2049</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -18862,7 +18862,7 @@
         <v>14</v>
       </c>
       <c r="F7" s="2">
-        <v>3935</v>
+        <v>2055</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -18894,7 +18894,7 @@
         <v>14</v>
       </c>
       <c r="F8" s="2">
-        <v>2045</v>
+        <v>850</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -18926,7 +18926,7 @@
         <v>14</v>
       </c>
       <c r="F9" s="2">
-        <v>4145</v>
+        <v>2266</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -18958,7 +18958,7 @@
         <v>14</v>
       </c>
       <c r="F10" s="2">
-        <v>3852</v>
+        <v>4135</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
@@ -18990,7 +18990,7 @@
         <v>14</v>
       </c>
       <c r="F11" s="2">
-        <v>1119</v>
+        <v>2859</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
@@ -19022,7 +19022,7 @@
         <v>14</v>
       </c>
       <c r="F12" s="2">
-        <v>1467</v>
+        <v>1309</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
@@ -19054,7 +19054,7 @@
         <v>14</v>
       </c>
       <c r="F13" s="2">
-        <v>3694</v>
+        <v>993</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -19086,7 +19086,7 @@
         <v>14</v>
       </c>
       <c r="F14" s="2">
-        <v>1003</v>
+        <v>2180</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -19118,7 +19118,7 @@
         <v>14</v>
       </c>
       <c r="F15" s="2">
-        <v>1343</v>
+        <v>4360</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -19150,7 +19150,7 @@
         <v>14</v>
       </c>
       <c r="F16" s="2">
-        <v>3875</v>
+        <v>1532</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
@@ -19182,7 +19182,7 @@
         <v>14</v>
       </c>
       <c r="F17" s="2">
-        <v>2977</v>
+        <v>4276</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
@@ -19214,7 +19214,7 @@
         <v>14</v>
       </c>
       <c r="F18" s="2">
-        <v>4055</v>
+        <v>3017</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
@@ -19246,7 +19246,7 @@
         <v>14</v>
       </c>
       <c r="F19" s="2">
-        <v>4664</v>
+        <v>3197</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
@@ -19278,7 +19278,7 @@
         <v>14</v>
       </c>
       <c r="F20" s="2">
-        <v>1543</v>
+        <v>1930</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
@@ -19310,7 +19310,7 @@
         <v>14</v>
       </c>
       <c r="F21" s="2">
-        <v>1703</v>
+        <v>2303</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -19342,7 +19342,7 @@
         <v>14</v>
       </c>
       <c r="F22" s="2">
-        <v>1112</v>
+        <v>2113</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -19374,7 +19374,7 @@
         <v>14</v>
       </c>
       <c r="F23" s="2">
-        <v>3040</v>
+        <v>3251</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -19406,7 +19406,7 @@
         <v>14</v>
       </c>
       <c r="F24" s="2">
-        <v>1969</v>
+        <v>1692</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -19438,7 +19438,7 @@
         <v>14</v>
       </c>
       <c r="F25" s="2">
-        <v>1877</v>
+        <v>1551</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -19470,7 +19470,7 @@
         <v>14</v>
       </c>
       <c r="F26" s="2">
-        <v>1774</v>
+        <v>1858</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -19502,7 +19502,7 @@
         <v>14</v>
       </c>
       <c r="F27" s="2">
-        <v>3721</v>
+        <v>3081</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>15</v>
@@ -19534,7 +19534,7 @@
         <v>14</v>
       </c>
       <c r="F28" s="2">
-        <v>3272</v>
+        <v>3971</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>15</v>
@@ -19566,7 +19566,7 @@
         <v>14</v>
       </c>
       <c r="F29" s="2">
-        <v>3033</v>
+        <v>2436</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>15</v>
@@ -19598,7 +19598,7 @@
         <v>14</v>
       </c>
       <c r="F30" s="2">
-        <v>1696</v>
+        <v>1720</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>15</v>
@@ -19662,7 +19662,7 @@
         <v>14</v>
       </c>
       <c r="F32" s="2">
-        <v>3288</v>
+        <v>1642</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>15</v>
@@ -19694,7 +19694,7 @@
         <v>14</v>
       </c>
       <c r="F33" s="2">
-        <v>2343</v>
+        <v>1123</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>15</v>
@@ -19726,7 +19726,7 @@
         <v>14</v>
       </c>
       <c r="F34" s="2">
-        <v>1024</v>
+        <v>1687</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>15</v>
@@ -19758,7 +19758,7 @@
         <v>14</v>
       </c>
       <c r="F35" s="2">
-        <v>825</v>
+        <v>4055</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>15</v>
@@ -19790,7 +19790,7 @@
         <v>14</v>
       </c>
       <c r="F36" s="2">
-        <v>1640</v>
+        <v>1862</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>15</v>
@@ -19822,7 +19822,7 @@
         <v>14</v>
       </c>
       <c r="F37" s="2">
-        <v>2301</v>
+        <v>2858</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>15</v>
@@ -19854,7 +19854,7 @@
         <v>14</v>
       </c>
       <c r="F38" s="2">
-        <v>3718</v>
+        <v>3867</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>15</v>
@@ -19886,7 +19886,7 @@
         <v>14</v>
       </c>
       <c r="F39" s="2">
-        <v>2933</v>
+        <v>4457</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>15</v>
@@ -19918,7 +19918,7 @@
         <v>14</v>
       </c>
       <c r="F40" s="2">
-        <v>2268</v>
+        <v>2119</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>15</v>
@@ -19950,7 +19950,7 @@
         <v>14</v>
       </c>
       <c r="F41" s="2">
-        <v>2955</v>
+        <v>2614</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>15</v>
@@ -19982,7 +19982,7 @@
         <v>14</v>
       </c>
       <c r="F42" s="2">
-        <v>912</v>
+        <v>3842</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>15</v>
@@ -20014,7 +20014,7 @@
         <v>14</v>
       </c>
       <c r="F43" s="2">
-        <v>3127</v>
+        <v>1343</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>15</v>
@@ -20046,7 +20046,7 @@
         <v>14</v>
       </c>
       <c r="F44" s="2">
-        <v>1017</v>
+        <v>3241</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>15</v>
@@ -20078,7 +20078,7 @@
         <v>14</v>
       </c>
       <c r="F45" s="2">
-        <v>4056</v>
+        <v>3631</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>15</v>
@@ -20110,7 +20110,7 @@
         <v>14</v>
       </c>
       <c r="F46" s="2">
-        <v>2668</v>
+        <v>2755</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>15</v>
@@ -20142,7 +20142,7 @@
         <v>14</v>
       </c>
       <c r="F47" s="2">
-        <v>2378</v>
+        <v>3756</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>15</v>
@@ -20174,7 +20174,7 @@
         <v>14</v>
       </c>
       <c r="F48" s="2">
-        <v>4619</v>
+        <v>3028</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>15</v>
@@ -20206,7 +20206,7 @@
         <v>14</v>
       </c>
       <c r="F49" s="2">
-        <v>3120</v>
+        <v>3578</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>15</v>
@@ -20238,7 +20238,7 @@
         <v>14</v>
       </c>
       <c r="F50" s="2">
-        <v>3893</v>
+        <v>1044</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>15</v>
@@ -20270,7 +20270,7 @@
         <v>14</v>
       </c>
       <c r="F51" s="2">
-        <v>991</v>
+        <v>2937</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>15</v>
@@ -20302,7 +20302,7 @@
         <v>14</v>
       </c>
       <c r="F52" s="2">
-        <v>1563</v>
+        <v>1971</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>15</v>
@@ -20334,7 +20334,7 @@
         <v>14</v>
       </c>
       <c r="F53" s="2">
-        <v>1410</v>
+        <v>3909</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>15</v>
@@ -20398,7 +20398,7 @@
         <v>14</v>
       </c>
       <c r="F55" s="2">
-        <v>3054</v>
+        <v>3275</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>15</v>
@@ -20430,7 +20430,7 @@
         <v>14</v>
       </c>
       <c r="F56" s="2">
-        <v>3824</v>
+        <v>2313</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>15</v>
@@ -20462,7 +20462,7 @@
         <v>14</v>
       </c>
       <c r="F57" s="2">
-        <v>2564</v>
+        <v>2030</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>15</v>
@@ -20494,7 +20494,7 @@
         <v>14</v>
       </c>
       <c r="F58" s="2">
-        <v>3155</v>
+        <v>4455</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>15</v>
@@ -20526,7 +20526,7 @@
         <v>14</v>
       </c>
       <c r="F59" s="2">
-        <v>2051</v>
+        <v>1812</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>15</v>
@@ -20558,7 +20558,7 @@
         <v>14</v>
       </c>
       <c r="F60" s="2">
-        <v>2716</v>
+        <v>3317</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>15</v>
@@ -20590,7 +20590,7 @@
         <v>14</v>
       </c>
       <c r="F61" s="2">
-        <v>1422</v>
+        <v>2825</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>15</v>
@@ -20622,7 +20622,7 @@
         <v>14</v>
       </c>
       <c r="F62" s="2">
-        <v>3896</v>
+        <v>4783</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>15</v>
@@ -20654,7 +20654,7 @@
         <v>14</v>
       </c>
       <c r="F63" s="2">
-        <v>4654</v>
+        <v>4106</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>15</v>
@@ -20686,7 +20686,7 @@
         <v>14</v>
       </c>
       <c r="F64" s="2">
-        <v>2479</v>
+        <v>4282</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>15</v>
@@ -20718,7 +20718,7 @@
         <v>14</v>
       </c>
       <c r="F65" s="2">
-        <v>3792</v>
+        <v>1791</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>15</v>
@@ -20750,7 +20750,7 @@
         <v>14</v>
       </c>
       <c r="F66" s="2">
-        <v>2195</v>
+        <v>3879</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>15</v>
@@ -20782,7 +20782,7 @@
         <v>14</v>
       </c>
       <c r="F67" s="2">
-        <v>3950</v>
+        <v>2378</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>15</v>
@@ -20814,7 +20814,7 @@
         <v>14</v>
       </c>
       <c r="F68" s="2">
-        <v>2625</v>
+        <v>4501</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>15</v>
@@ -20846,7 +20846,7 @@
         <v>14</v>
       </c>
       <c r="F69" s="2">
-        <v>3882</v>
+        <v>3560</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>15</v>
@@ -20878,7 +20878,7 @@
         <v>14</v>
       </c>
       <c r="F70" s="2">
-        <v>1952</v>
+        <v>4125</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>15</v>
@@ -20910,7 +20910,7 @@
         <v>14</v>
       </c>
       <c r="F71" s="2">
-        <v>1931</v>
+        <v>3134</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>15</v>
@@ -20942,7 +20942,7 @@
         <v>14</v>
       </c>
       <c r="F72" s="2">
-        <v>4116</v>
+        <v>3106</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>15</v>
@@ -20974,7 +20974,7 @@
         <v>14</v>
       </c>
       <c r="F73" s="2">
-        <v>3276</v>
+        <v>4191</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>15</v>
@@ -21006,7 +21006,7 @@
         <v>14</v>
       </c>
       <c r="F74" s="2">
-        <v>4540</v>
+        <v>4704</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>15</v>
@@ -21038,7 +21038,7 @@
         <v>14</v>
       </c>
       <c r="F75" s="2">
-        <v>3078</v>
+        <v>3195</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>15</v>
@@ -21070,7 +21070,7 @@
         <v>14</v>
       </c>
       <c r="F76" s="2">
-        <v>2338</v>
+        <v>1472</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>15</v>
@@ -21102,7 +21102,7 @@
         <v>14</v>
       </c>
       <c r="F77" s="2">
-        <v>3266</v>
+        <v>1671</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>15</v>
@@ -21134,7 +21134,7 @@
         <v>14</v>
       </c>
       <c r="F78" s="2">
-        <v>2373</v>
+        <v>2413</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>15</v>
@@ -21166,7 +21166,7 @@
         <v>14</v>
       </c>
       <c r="F79" s="2">
-        <v>908</v>
+        <v>4432</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>15</v>
@@ -21198,7 +21198,7 @@
         <v>14</v>
       </c>
       <c r="F80" s="2">
-        <v>3757</v>
+        <v>2397</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>15</v>
@@ -21230,7 +21230,7 @@
         <v>14</v>
       </c>
       <c r="F81" s="2">
-        <v>2629</v>
+        <v>1438</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>15</v>
@@ -21262,7 +21262,7 @@
         <v>14</v>
       </c>
       <c r="F82" s="2">
-        <v>1579</v>
+        <v>2272</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>15</v>
@@ -21294,7 +21294,7 @@
         <v>14</v>
       </c>
       <c r="F83" s="2">
-        <v>853</v>
+        <v>1720</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>15</v>
@@ -21326,7 +21326,7 @@
         <v>14</v>
       </c>
       <c r="F84" s="2">
-        <v>1422</v>
+        <v>1175</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>15</v>
@@ -21358,7 +21358,7 @@
         <v>14</v>
       </c>
       <c r="F85" s="2">
-        <v>3259</v>
+        <v>3218</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>15</v>
@@ -21390,7 +21390,7 @@
         <v>14</v>
       </c>
       <c r="F86" s="2">
-        <v>3672</v>
+        <v>4742</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>15</v>
@@ -21422,7 +21422,7 @@
         <v>14</v>
       </c>
       <c r="F87" s="2">
-        <v>3660</v>
+        <v>2607</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>15</v>
@@ -21454,7 +21454,7 @@
         <v>14</v>
       </c>
       <c r="F88" s="2">
-        <v>3386</v>
+        <v>3765</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>15</v>
@@ -21486,7 +21486,7 @@
         <v>14</v>
       </c>
       <c r="F89" s="2">
-        <v>3384</v>
+        <v>2910</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>15</v>
@@ -21518,7 +21518,7 @@
         <v>14</v>
       </c>
       <c r="F90" s="2">
-        <v>2905</v>
+        <v>815</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>15</v>
@@ -21550,7 +21550,7 @@
         <v>14</v>
       </c>
       <c r="F91" s="2">
-        <v>4642</v>
+        <v>3618</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>15</v>
@@ -21582,7 +21582,7 @@
         <v>14</v>
       </c>
       <c r="F92" s="2">
-        <v>4475</v>
+        <v>986</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>15</v>
@@ -21614,7 +21614,7 @@
         <v>14</v>
       </c>
       <c r="F93" s="2">
-        <v>1011</v>
+        <v>1913</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>15</v>
@@ -21646,7 +21646,7 @@
         <v>14</v>
       </c>
       <c r="F94" s="2">
-        <v>1481</v>
+        <v>3078</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>15</v>
@@ -21678,7 +21678,7 @@
         <v>14</v>
       </c>
       <c r="F95" s="2">
-        <v>3193</v>
+        <v>1602</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>15</v>
@@ -21710,7 +21710,7 @@
         <v>14</v>
       </c>
       <c r="F96" s="2">
-        <v>823</v>
+        <v>3816</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>15</v>
@@ -21742,7 +21742,7 @@
         <v>14</v>
       </c>
       <c r="F97" s="2">
-        <v>2981</v>
+        <v>1259</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>15</v>
@@ -21774,7 +21774,7 @@
         <v>14</v>
       </c>
       <c r="F98" s="2">
-        <v>3681</v>
+        <v>1054</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>15</v>
@@ -21806,7 +21806,7 @@
         <v>14</v>
       </c>
       <c r="F99" s="2">
-        <v>1823</v>
+        <v>4379</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>15</v>
@@ -21838,7 +21838,7 @@
         <v>14</v>
       </c>
       <c r="F100" s="2">
-        <v>3640</v>
+        <v>1274</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>15</v>
@@ -21870,7 +21870,7 @@
         <v>14</v>
       </c>
       <c r="F101" s="2">
-        <v>2992</v>
+        <v>2803</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>15</v>
@@ -21902,7 +21902,7 @@
         <v>14</v>
       </c>
       <c r="F102" s="2">
-        <v>4150</v>
+        <v>2948</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>15</v>
@@ -21934,7 +21934,7 @@
         <v>14</v>
       </c>
       <c r="F103" s="2">
-        <v>4439</v>
+        <v>1761</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>15</v>
@@ -21966,7 +21966,7 @@
         <v>14</v>
       </c>
       <c r="F104" s="2">
-        <v>2013</v>
+        <v>1800</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>15</v>
@@ -21998,7 +21998,7 @@
         <v>14</v>
       </c>
       <c r="F105" s="2">
-        <v>2005</v>
+        <v>3158</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>15</v>
@@ -22030,7 +22030,7 @@
         <v>14</v>
       </c>
       <c r="F106" s="2">
-        <v>4799</v>
+        <v>3397</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>15</v>
@@ -22062,7 +22062,7 @@
         <v>14</v>
       </c>
       <c r="F107" s="2">
-        <v>1484</v>
+        <v>2576</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>15</v>
@@ -22094,7 +22094,7 @@
         <v>14</v>
       </c>
       <c r="F108" s="2">
-        <v>1609</v>
+        <v>1468</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>15</v>
@@ -22126,7 +22126,7 @@
         <v>14</v>
       </c>
       <c r="F109" s="2">
-        <v>1413</v>
+        <v>1354</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>15</v>
@@ -22158,7 +22158,7 @@
         <v>14</v>
       </c>
       <c r="F110" s="2">
-        <v>3635</v>
+        <v>4128</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>15</v>
@@ -22190,7 +22190,7 @@
         <v>14</v>
       </c>
       <c r="F111" s="2">
-        <v>2916</v>
+        <v>4713</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>15</v>
@@ -22222,7 +22222,7 @@
         <v>14</v>
       </c>
       <c r="F112" s="2">
-        <v>1488</v>
+        <v>3288</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>15</v>
@@ -22254,7 +22254,7 @@
         <v>14</v>
       </c>
       <c r="F113" s="2">
-        <v>3565</v>
+        <v>1502</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>15</v>
@@ -22286,7 +22286,7 @@
         <v>14</v>
       </c>
       <c r="F114" s="2">
-        <v>2080</v>
+        <v>3414</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>15</v>
@@ -22318,7 +22318,7 @@
         <v>14</v>
       </c>
       <c r="F115" s="2">
-        <v>4591</v>
+        <v>1284</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>15</v>
@@ -22350,7 +22350,7 @@
         <v>14</v>
       </c>
       <c r="F116" s="2">
-        <v>844</v>
+        <v>1015</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>15</v>
@@ -22382,7 +22382,7 @@
         <v>14</v>
       </c>
       <c r="F117" s="2">
-        <v>3876</v>
+        <v>1420</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>15</v>
@@ -22414,7 +22414,7 @@
         <v>14</v>
       </c>
       <c r="F118" s="2">
-        <v>3172</v>
+        <v>2613</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>15</v>
@@ -22446,7 +22446,7 @@
         <v>14</v>
       </c>
       <c r="F119" s="2">
-        <v>3854</v>
+        <v>3250</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>15</v>
@@ -22478,7 +22478,7 @@
         <v>14</v>
       </c>
       <c r="F120" s="2">
-        <v>3742</v>
+        <v>861</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>15</v>
@@ -22510,7 +22510,7 @@
         <v>14</v>
       </c>
       <c r="F121" s="2">
-        <v>1349</v>
+        <v>4711</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>15</v>
@@ -22542,7 +22542,7 @@
         <v>14</v>
       </c>
       <c r="F122" s="2">
-        <v>1093</v>
+        <v>3991</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>15</v>
@@ -22574,7 +22574,7 @@
         <v>14</v>
       </c>
       <c r="F123" s="2">
-        <v>2824</v>
+        <v>4485</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>15</v>
@@ -22606,7 +22606,7 @@
         <v>14</v>
       </c>
       <c r="F124" s="2">
-        <v>2649</v>
+        <v>962</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>15</v>
@@ -22638,7 +22638,7 @@
         <v>14</v>
       </c>
       <c r="F125" s="2">
-        <v>4015</v>
+        <v>3175</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>15</v>
@@ -22670,7 +22670,7 @@
         <v>14</v>
       </c>
       <c r="F126" s="2">
-        <v>2500</v>
+        <v>2493</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>15</v>
@@ -22702,7 +22702,7 @@
         <v>14</v>
       </c>
       <c r="F127" s="2">
-        <v>2978</v>
+        <v>4383</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>15</v>
@@ -22734,7 +22734,7 @@
         <v>14</v>
       </c>
       <c r="F128" s="2">
-        <v>3113</v>
+        <v>2448</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>15</v>
@@ -22766,7 +22766,7 @@
         <v>14</v>
       </c>
       <c r="F129" s="2">
-        <v>1931</v>
+        <v>4335</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>15</v>
@@ -22798,7 +22798,7 @@
         <v>14</v>
       </c>
       <c r="F130" s="2">
-        <v>2426</v>
+        <v>2792</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>15</v>
@@ -22830,7 +22830,7 @@
         <v>14</v>
       </c>
       <c r="F131" s="2">
-        <v>983</v>
+        <v>4762</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>15</v>
@@ -22862,7 +22862,7 @@
         <v>14</v>
       </c>
       <c r="F132" s="2">
-        <v>4301</v>
+        <v>4467</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>15</v>
@@ -22894,7 +22894,7 @@
         <v>14</v>
       </c>
       <c r="F133" s="2">
-        <v>2713</v>
+        <v>1659</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>15</v>
@@ -22926,7 +22926,7 @@
         <v>14</v>
       </c>
       <c r="F134" s="2">
-        <v>4540</v>
+        <v>3633</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>15</v>
@@ -22958,7 +22958,7 @@
         <v>14</v>
       </c>
       <c r="F135" s="2">
-        <v>1541</v>
+        <v>3127</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>15</v>
@@ -22990,7 +22990,7 @@
         <v>14</v>
       </c>
       <c r="F136" s="2">
-        <v>2320</v>
+        <v>2143</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>15</v>
@@ -23022,7 +23022,7 @@
         <v>14</v>
       </c>
       <c r="F137" s="2">
-        <v>1409</v>
+        <v>2254</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>15</v>
@@ -23054,7 +23054,7 @@
         <v>14</v>
       </c>
       <c r="F138" s="2">
-        <v>2297</v>
+        <v>4462</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>15</v>
@@ -23086,7 +23086,7 @@
         <v>14</v>
       </c>
       <c r="F139" s="2">
-        <v>2387</v>
+        <v>810</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>15</v>
@@ -23118,7 +23118,7 @@
         <v>14</v>
       </c>
       <c r="F140" s="2">
-        <v>3440</v>
+        <v>1113</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>15</v>
@@ -23150,7 +23150,7 @@
         <v>14</v>
       </c>
       <c r="F141" s="2">
-        <v>4029</v>
+        <v>935</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>15</v>
@@ -23182,7 +23182,7 @@
         <v>14</v>
       </c>
       <c r="F142" s="2">
-        <v>1562</v>
+        <v>1944</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>15</v>
@@ -23214,7 +23214,7 @@
         <v>14</v>
       </c>
       <c r="F143" s="2">
-        <v>2930</v>
+        <v>4773</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>15</v>
@@ -23246,7 +23246,7 @@
         <v>14</v>
       </c>
       <c r="F144" s="2">
-        <v>1323</v>
+        <v>1483</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>15</v>
@@ -23278,7 +23278,7 @@
         <v>14</v>
       </c>
       <c r="F145" s="2">
-        <v>4470</v>
+        <v>1740</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>15</v>
@@ -23310,7 +23310,7 @@
         <v>14</v>
       </c>
       <c r="F146" s="2">
-        <v>4068</v>
+        <v>1288</v>
       </c>
       <c r="G146" s="2" t="s">
         <v>15</v>
@@ -23342,7 +23342,7 @@
         <v>14</v>
       </c>
       <c r="F147" s="2">
-        <v>1264</v>
+        <v>2485</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>15</v>
@@ -23374,7 +23374,7 @@
         <v>14</v>
       </c>
       <c r="F148" s="2">
-        <v>3935</v>
+        <v>1376</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>15</v>
@@ -23406,7 +23406,7 @@
         <v>14</v>
       </c>
       <c r="F149" s="2">
-        <v>2633</v>
+        <v>1032</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>15</v>
@@ -23438,7 +23438,7 @@
         <v>14</v>
       </c>
       <c r="F150" s="2">
-        <v>2150</v>
+        <v>3957</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>15</v>
@@ -23470,7 +23470,7 @@
         <v>14</v>
       </c>
       <c r="F151" s="2">
-        <v>2928</v>
+        <v>820</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>15</v>
@@ -23502,7 +23502,7 @@
         <v>14</v>
       </c>
       <c r="F152" s="2">
-        <v>1531</v>
+        <v>2648</v>
       </c>
       <c r="G152" s="2" t="s">
         <v>15</v>
@@ -23534,7 +23534,7 @@
         <v>14</v>
       </c>
       <c r="F153" s="2">
-        <v>4396</v>
+        <v>3346</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>15</v>
@@ -23566,7 +23566,7 @@
         <v>14</v>
       </c>
       <c r="F154" s="2">
-        <v>1559</v>
+        <v>2947</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>15</v>
@@ -23598,7 +23598,7 @@
         <v>14</v>
       </c>
       <c r="F155" s="2">
-        <v>1284</v>
+        <v>3881</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>15</v>
@@ -23630,7 +23630,7 @@
         <v>14</v>
       </c>
       <c r="F156" s="2">
-        <v>1682</v>
+        <v>925</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>15</v>
@@ -23662,7 +23662,7 @@
         <v>14</v>
       </c>
       <c r="F157" s="2">
-        <v>2140</v>
+        <v>2242</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>15</v>
@@ -23694,7 +23694,7 @@
         <v>14</v>
       </c>
       <c r="F158" s="2">
-        <v>2990</v>
+        <v>2471</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>15</v>
@@ -23726,7 +23726,7 @@
         <v>14</v>
       </c>
       <c r="F159" s="2">
-        <v>4605</v>
+        <v>2063</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>15</v>
@@ -23758,7 +23758,7 @@
         <v>14</v>
       </c>
       <c r="F160" s="2">
-        <v>2855</v>
+        <v>3771</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>15</v>
@@ -23790,7 +23790,7 @@
         <v>14</v>
       </c>
       <c r="F161" s="2">
-        <v>3484</v>
+        <v>2034</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>15</v>
@@ -23822,7 +23822,7 @@
         <v>14</v>
       </c>
       <c r="F162" s="2">
-        <v>1745</v>
+        <v>2230</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>15</v>
@@ -23854,7 +23854,7 @@
         <v>14</v>
       </c>
       <c r="F163" s="2">
-        <v>2677</v>
+        <v>3672</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>15</v>
@@ -23886,7 +23886,7 @@
         <v>14</v>
       </c>
       <c r="F164" s="2">
-        <v>941</v>
+        <v>999</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>15</v>
@@ -23918,7 +23918,7 @@
         <v>14</v>
       </c>
       <c r="F165" s="2">
-        <v>4508</v>
+        <v>3444</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>15</v>
@@ -23950,7 +23950,7 @@
         <v>14</v>
       </c>
       <c r="F166" s="2">
-        <v>4401</v>
+        <v>2163</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>15</v>
@@ -23982,7 +23982,7 @@
         <v>14</v>
       </c>
       <c r="F167" s="2">
-        <v>1442</v>
+        <v>4694</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>15</v>
@@ -24014,7 +24014,7 @@
         <v>14</v>
       </c>
       <c r="F168" s="2">
-        <v>2933</v>
+        <v>3442</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>15</v>
@@ -24046,7 +24046,7 @@
         <v>14</v>
       </c>
       <c r="F169" s="2">
-        <v>857</v>
+        <v>2894</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>15</v>
@@ -24078,7 +24078,7 @@
         <v>14</v>
       </c>
       <c r="F170" s="2">
-        <v>1383</v>
+        <v>3853</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>15</v>
@@ -24110,7 +24110,7 @@
         <v>14</v>
       </c>
       <c r="F171" s="2">
-        <v>1264</v>
+        <v>1588</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>15</v>
@@ -24142,7 +24142,7 @@
         <v>14</v>
       </c>
       <c r="F172" s="2">
-        <v>4496</v>
+        <v>4363</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>15</v>
@@ -24174,7 +24174,7 @@
         <v>14</v>
       </c>
       <c r="F173" s="2">
-        <v>1309</v>
+        <v>4297</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>15</v>
@@ -24206,7 +24206,7 @@
         <v>14</v>
       </c>
       <c r="F174" s="2">
-        <v>4069</v>
+        <v>4250</v>
       </c>
       <c r="G174" s="2" t="s">
         <v>15</v>
@@ -24238,7 +24238,7 @@
         <v>14</v>
       </c>
       <c r="F175" s="2">
-        <v>3481</v>
+        <v>2327</v>
       </c>
       <c r="G175" s="2" t="s">
         <v>15</v>
@@ -24270,7 +24270,7 @@
         <v>14</v>
       </c>
       <c r="F176" s="2">
-        <v>2994</v>
+        <v>4469</v>
       </c>
       <c r="G176" s="2" t="s">
         <v>15</v>
@@ -24302,7 +24302,7 @@
         <v>14</v>
       </c>
       <c r="F177" s="2">
-        <v>2581</v>
+        <v>4609</v>
       </c>
       <c r="G177" s="2" t="s">
         <v>15</v>
@@ -24334,7 +24334,7 @@
         <v>14</v>
       </c>
       <c r="F178" s="2">
-        <v>3908</v>
+        <v>3985</v>
       </c>
       <c r="G178" s="2" t="s">
         <v>15</v>
@@ -24366,7 +24366,7 @@
         <v>14</v>
       </c>
       <c r="F179" s="2">
-        <v>2294</v>
+        <v>1390</v>
       </c>
       <c r="G179" s="2" t="s">
         <v>15</v>
@@ -24398,7 +24398,7 @@
         <v>14</v>
       </c>
       <c r="F180" s="2">
-        <v>2516</v>
+        <v>1346</v>
       </c>
       <c r="G180" s="2" t="s">
         <v>15</v>
@@ -24430,7 +24430,7 @@
         <v>14</v>
       </c>
       <c r="F181" s="2">
-        <v>2086</v>
+        <v>1497</v>
       </c>
       <c r="G181" s="2" t="s">
         <v>15</v>
@@ -24462,7 +24462,7 @@
         <v>14</v>
       </c>
       <c r="F182" s="2">
-        <v>1412</v>
+        <v>2437</v>
       </c>
       <c r="G182" s="2" t="s">
         <v>15</v>
@@ -24494,7 +24494,7 @@
         <v>14</v>
       </c>
       <c r="F183" s="2">
-        <v>3189</v>
+        <v>2090</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>15</v>
@@ -24526,7 +24526,7 @@
         <v>14</v>
       </c>
       <c r="F184" s="2">
-        <v>3348</v>
+        <v>2063</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>15</v>
@@ -24558,7 +24558,7 @@
         <v>14</v>
       </c>
       <c r="F185" s="2">
-        <v>3444</v>
+        <v>4663</v>
       </c>
       <c r="G185" s="2" t="s">
         <v>15</v>
@@ -24590,7 +24590,7 @@
         <v>14</v>
       </c>
       <c r="F186" s="2">
-        <v>2463</v>
+        <v>4323</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>15</v>
@@ -24622,7 +24622,7 @@
         <v>14</v>
       </c>
       <c r="F187" s="2">
-        <v>1580</v>
+        <v>4749</v>
       </c>
       <c r="G187" s="2" t="s">
         <v>15</v>
@@ -24654,7 +24654,7 @@
         <v>14</v>
       </c>
       <c r="F188" s="2">
-        <v>3805</v>
+        <v>2363</v>
       </c>
       <c r="G188" s="2" t="s">
         <v>15</v>
@@ -24686,7 +24686,7 @@
         <v>14</v>
       </c>
       <c r="F189" s="2">
-        <v>2048</v>
+        <v>2362</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>15</v>
@@ -24718,7 +24718,7 @@
         <v>14</v>
       </c>
       <c r="F190" s="2">
-        <v>2284</v>
+        <v>3670</v>
       </c>
       <c r="G190" s="2" t="s">
         <v>15</v>
@@ -24750,7 +24750,7 @@
         <v>14</v>
       </c>
       <c r="F191" s="2">
-        <v>4687</v>
+        <v>1314</v>
       </c>
       <c r="G191" s="2" t="s">
         <v>15</v>
@@ -24782,7 +24782,7 @@
         <v>14</v>
       </c>
       <c r="F192" s="2">
-        <v>1871</v>
+        <v>3782</v>
       </c>
       <c r="G192" s="2" t="s">
         <v>15</v>
@@ -24814,7 +24814,7 @@
         <v>14</v>
       </c>
       <c r="F193" s="2">
-        <v>4333</v>
+        <v>4541</v>
       </c>
       <c r="G193" s="2" t="s">
         <v>15</v>
@@ -24846,7 +24846,7 @@
         <v>14</v>
       </c>
       <c r="F194" s="2">
-        <v>2206</v>
+        <v>4286</v>
       </c>
       <c r="G194" s="2" t="s">
         <v>15</v>
@@ -24878,7 +24878,7 @@
         <v>14</v>
       </c>
       <c r="F195" s="2">
-        <v>3526</v>
+        <v>3146</v>
       </c>
       <c r="G195" s="2" t="s">
         <v>15</v>
@@ -24910,7 +24910,7 @@
         <v>14</v>
       </c>
       <c r="F196" s="2">
-        <v>4373</v>
+        <v>1097</v>
       </c>
       <c r="G196" s="2" t="s">
         <v>15</v>
@@ -24942,7 +24942,7 @@
         <v>14</v>
       </c>
       <c r="F197" s="2">
-        <v>4320</v>
+        <v>2125</v>
       </c>
       <c r="G197" s="2" t="s">
         <v>15</v>
@@ -24974,7 +24974,7 @@
         <v>14</v>
       </c>
       <c r="F198" s="2">
-        <v>2349</v>
+        <v>1346</v>
       </c>
       <c r="G198" s="2" t="s">
         <v>15</v>
@@ -25006,7 +25006,7 @@
         <v>14</v>
       </c>
       <c r="F199" s="2">
-        <v>3391</v>
+        <v>4650</v>
       </c>
       <c r="G199" s="2" t="s">
         <v>15</v>
@@ -25038,7 +25038,7 @@
         <v>14</v>
       </c>
       <c r="F200" s="2">
-        <v>4274</v>
+        <v>2897</v>
       </c>
       <c r="G200" s="2" t="s">
         <v>15</v>
@@ -25070,7 +25070,7 @@
         <v>14</v>
       </c>
       <c r="F201" s="2">
-        <v>3317</v>
+        <v>998</v>
       </c>
       <c r="G201" s="2" t="s">
         <v>15</v>
@@ -25102,7 +25102,7 @@
         <v>14</v>
       </c>
       <c r="F202" s="2">
-        <v>2712</v>
+        <v>2471</v>
       </c>
       <c r="G202" s="2" t="s">
         <v>15</v>
@@ -25134,7 +25134,7 @@
         <v>14</v>
       </c>
       <c r="F203" s="2">
-        <v>4625</v>
+        <v>3789</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>15</v>
@@ -25166,7 +25166,7 @@
         <v>14</v>
       </c>
       <c r="F204" s="2">
-        <v>2669</v>
+        <v>4149</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>15</v>
@@ -25198,7 +25198,7 @@
         <v>14</v>
       </c>
       <c r="F205" s="2">
-        <v>2425</v>
+        <v>3862</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>15</v>
@@ -25230,7 +25230,7 @@
         <v>14</v>
       </c>
       <c r="F206" s="2">
-        <v>3779</v>
+        <v>1620</v>
       </c>
       <c r="G206" s="2" t="s">
         <v>15</v>
@@ -25262,7 +25262,7 @@
         <v>14</v>
       </c>
       <c r="F207" s="2">
-        <v>1733</v>
+        <v>3294</v>
       </c>
       <c r="G207" s="2" t="s">
         <v>15</v>
@@ -25294,7 +25294,7 @@
         <v>14</v>
       </c>
       <c r="F208" s="2">
-        <v>2010</v>
+        <v>4724</v>
       </c>
       <c r="G208" s="2" t="s">
         <v>15</v>
@@ -25326,7 +25326,7 @@
         <v>14</v>
       </c>
       <c r="F209" s="2">
-        <v>4674</v>
+        <v>3771</v>
       </c>
       <c r="G209" s="2" t="s">
         <v>15</v>
@@ -25358,7 +25358,7 @@
         <v>14</v>
       </c>
       <c r="F210" s="2">
-        <v>1305</v>
+        <v>1547</v>
       </c>
       <c r="G210" s="2" t="s">
         <v>15</v>
@@ -25390,7 +25390,7 @@
         <v>14</v>
       </c>
       <c r="F211" s="2">
-        <v>3286</v>
+        <v>2393</v>
       </c>
       <c r="G211" s="2" t="s">
         <v>15</v>
@@ -25422,7 +25422,7 @@
         <v>14</v>
       </c>
       <c r="F212" s="2">
-        <v>1307</v>
+        <v>3884</v>
       </c>
       <c r="G212" s="2" t="s">
         <v>15</v>
@@ -25454,7 +25454,7 @@
         <v>14</v>
       </c>
       <c r="F213" s="2">
-        <v>3553</v>
+        <v>1206</v>
       </c>
       <c r="G213" s="2" t="s">
         <v>15</v>
@@ -25486,7 +25486,7 @@
         <v>14</v>
       </c>
       <c r="F214" s="2">
-        <v>2812</v>
+        <v>1219</v>
       </c>
       <c r="G214" s="2" t="s">
         <v>15</v>
@@ -25518,7 +25518,7 @@
         <v>14</v>
       </c>
       <c r="F215" s="2">
-        <v>989</v>
+        <v>4412</v>
       </c>
       <c r="G215" s="2" t="s">
         <v>15</v>
@@ -25550,7 +25550,7 @@
         <v>14</v>
       </c>
       <c r="F216" s="2">
-        <v>2181</v>
+        <v>2103</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>15</v>
@@ -25582,7 +25582,7 @@
         <v>14</v>
       </c>
       <c r="F217" s="2">
-        <v>2945</v>
+        <v>3549</v>
       </c>
       <c r="G217" s="2" t="s">
         <v>15</v>
@@ -25614,7 +25614,7 @@
         <v>14</v>
       </c>
       <c r="F218" s="2">
-        <v>3770</v>
+        <v>4733</v>
       </c>
       <c r="G218" s="2" t="s">
         <v>15</v>
@@ -25646,7 +25646,7 @@
         <v>14</v>
       </c>
       <c r="F219" s="2">
-        <v>4531</v>
+        <v>2348</v>
       </c>
       <c r="G219" s="2" t="s">
         <v>15</v>
@@ -25678,7 +25678,7 @@
         <v>14</v>
       </c>
       <c r="F220" s="2">
-        <v>4158</v>
+        <v>4617</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>15</v>
@@ -25710,7 +25710,7 @@
         <v>14</v>
       </c>
       <c r="F221" s="2">
-        <v>3592</v>
+        <v>3041</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>15</v>
@@ -25742,7 +25742,7 @@
         <v>14</v>
       </c>
       <c r="F222" s="2">
-        <v>2911</v>
+        <v>4502</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>15</v>
@@ -25774,7 +25774,7 @@
         <v>14</v>
       </c>
       <c r="F223" s="2">
-        <v>4742</v>
+        <v>4086</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>15</v>
@@ -25806,7 +25806,7 @@
         <v>14</v>
       </c>
       <c r="F224" s="2">
-        <v>3070</v>
+        <v>4012</v>
       </c>
       <c r="G224" s="2" t="s">
         <v>15</v>
@@ -25838,7 +25838,7 @@
         <v>14</v>
       </c>
       <c r="F225" s="2">
-        <v>1640</v>
+        <v>2414</v>
       </c>
       <c r="G225" s="2" t="s">
         <v>15</v>
@@ -25870,7 +25870,7 @@
         <v>14</v>
       </c>
       <c r="F226" s="2">
-        <v>2033</v>
+        <v>3980</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>15</v>
@@ -25902,7 +25902,7 @@
         <v>14</v>
       </c>
       <c r="F227" s="2">
-        <v>3494</v>
+        <v>2527</v>
       </c>
       <c r="G227" s="2" t="s">
         <v>15</v>
@@ -25934,7 +25934,7 @@
         <v>14</v>
       </c>
       <c r="F228" s="2">
-        <v>2133</v>
+        <v>1888</v>
       </c>
       <c r="G228" s="2" t="s">
         <v>15</v>
@@ -25966,7 +25966,7 @@
         <v>14</v>
       </c>
       <c r="F229" s="2">
-        <v>2284</v>
+        <v>1758</v>
       </c>
       <c r="G229" s="2" t="s">
         <v>15</v>
@@ -25998,7 +25998,7 @@
         <v>14</v>
       </c>
       <c r="F230" s="2">
-        <v>3516</v>
+        <v>1950</v>
       </c>
       <c r="G230" s="2" t="s">
         <v>15</v>
@@ -26030,7 +26030,7 @@
         <v>14</v>
       </c>
       <c r="F231" s="2">
-        <v>2952</v>
+        <v>2309</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>15</v>
@@ -26062,7 +26062,7 @@
         <v>14</v>
       </c>
       <c r="F232" s="2">
-        <v>1554</v>
+        <v>1530</v>
       </c>
       <c r="G232" s="2" t="s">
         <v>15</v>
@@ -26094,7 +26094,7 @@
         <v>14</v>
       </c>
       <c r="F233" s="2">
-        <v>4647</v>
+        <v>3991</v>
       </c>
       <c r="G233" s="2" t="s">
         <v>15</v>
@@ -26126,7 +26126,7 @@
         <v>14</v>
       </c>
       <c r="F234" s="2">
-        <v>1604</v>
+        <v>4044</v>
       </c>
       <c r="G234" s="2" t="s">
         <v>15</v>
@@ -26158,7 +26158,7 @@
         <v>14</v>
       </c>
       <c r="F235" s="2">
-        <v>4316</v>
+        <v>2978</v>
       </c>
       <c r="G235" s="2" t="s">
         <v>15</v>
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="F236" s="2">
-        <v>2343</v>
+        <v>4613</v>
       </c>
       <c r="G236" s="2" t="s">
         <v>15</v>
@@ -26222,7 +26222,7 @@
         <v>14</v>
       </c>
       <c r="F237" s="2">
-        <v>1452</v>
+        <v>1125</v>
       </c>
       <c r="G237" s="2" t="s">
         <v>15</v>
@@ -26254,7 +26254,7 @@
         <v>14</v>
       </c>
       <c r="F238" s="2">
-        <v>2138</v>
+        <v>2895</v>
       </c>
       <c r="G238" s="2" t="s">
         <v>15</v>
@@ -26286,7 +26286,7 @@
         <v>14</v>
       </c>
       <c r="F239" s="2">
-        <v>4168</v>
+        <v>1685</v>
       </c>
       <c r="G239" s="2" t="s">
         <v>15</v>
@@ -26318,7 +26318,7 @@
         <v>14</v>
       </c>
       <c r="F240" s="2">
-        <v>1250</v>
+        <v>2957</v>
       </c>
       <c r="G240" s="2" t="s">
         <v>15</v>
@@ -26350,7 +26350,7 @@
         <v>14</v>
       </c>
       <c r="F241" s="2">
-        <v>1422</v>
+        <v>4516</v>
       </c>
       <c r="G241" s="2" t="s">
         <v>15</v>
@@ -26382,7 +26382,7 @@
         <v>14</v>
       </c>
       <c r="F242" s="2">
-        <v>3097</v>
+        <v>925</v>
       </c>
       <c r="G242" s="2" t="s">
         <v>15</v>
@@ -26414,7 +26414,7 @@
         <v>14</v>
       </c>
       <c r="F243" s="2">
-        <v>2843</v>
+        <v>3823</v>
       </c>
       <c r="G243" s="2" t="s">
         <v>15</v>
@@ -26446,7 +26446,7 @@
         <v>14</v>
       </c>
       <c r="F244" s="2">
-        <v>3177</v>
+        <v>4783</v>
       </c>
       <c r="G244" s="2" t="s">
         <v>15</v>
@@ -26478,7 +26478,7 @@
         <v>14</v>
       </c>
       <c r="F245" s="2">
-        <v>2359</v>
+        <v>1335</v>
       </c>
       <c r="G245" s="2" t="s">
         <v>15</v>
@@ -26510,7 +26510,7 @@
         <v>14</v>
       </c>
       <c r="F246" s="2">
-        <v>2728</v>
+        <v>4099</v>
       </c>
       <c r="G246" s="2" t="s">
         <v>15</v>
@@ -26542,7 +26542,7 @@
         <v>14</v>
       </c>
       <c r="F247" s="2">
-        <v>1416</v>
+        <v>1469</v>
       </c>
       <c r="G247" s="2" t="s">
         <v>15</v>
@@ -26574,7 +26574,7 @@
         <v>14</v>
       </c>
       <c r="F248" s="2">
-        <v>4654</v>
+        <v>3399</v>
       </c>
       <c r="G248" s="2" t="s">
         <v>15</v>
@@ -26606,7 +26606,7 @@
         <v>14</v>
       </c>
       <c r="F249" s="2">
-        <v>1722</v>
+        <v>3351</v>
       </c>
       <c r="G249" s="2" t="s">
         <v>15</v>
@@ -26638,7 +26638,7 @@
         <v>14</v>
       </c>
       <c r="F250" s="2">
-        <v>3977</v>
+        <v>2661</v>
       </c>
       <c r="G250" s="2" t="s">
         <v>15</v>
@@ -26670,7 +26670,7 @@
         <v>14</v>
       </c>
       <c r="F251" s="2">
-        <v>3336</v>
+        <v>2127</v>
       </c>
       <c r="G251" s="2" t="s">
         <v>15</v>
@@ -26702,7 +26702,7 @@
         <v>14</v>
       </c>
       <c r="F252" s="2">
-        <v>4251</v>
+        <v>3504</v>
       </c>
       <c r="G252" s="2" t="s">
         <v>15</v>
@@ -26734,7 +26734,7 @@
         <v>14</v>
       </c>
       <c r="F253" s="2">
-        <v>2676</v>
+        <v>2838</v>
       </c>
       <c r="G253" s="2" t="s">
         <v>15</v>
@@ -26766,7 +26766,7 @@
         <v>14</v>
       </c>
       <c r="F254" s="2">
-        <v>1996</v>
+        <v>1541</v>
       </c>
       <c r="G254" s="2" t="s">
         <v>15</v>
@@ -26798,7 +26798,7 @@
         <v>14</v>
       </c>
       <c r="F255" s="2">
-        <v>1770</v>
+        <v>2303</v>
       </c>
       <c r="G255" s="2" t="s">
         <v>15</v>
@@ -26830,7 +26830,7 @@
         <v>14</v>
       </c>
       <c r="F256" s="2">
-        <v>1820</v>
+        <v>4435</v>
       </c>
       <c r="G256" s="2" t="s">
         <v>15</v>
@@ -26862,7 +26862,7 @@
         <v>14</v>
       </c>
       <c r="F257" s="2">
-        <v>4490</v>
+        <v>4695</v>
       </c>
       <c r="G257" s="2" t="s">
         <v>15</v>
@@ -26894,7 +26894,7 @@
         <v>14</v>
       </c>
       <c r="F258" s="2">
-        <v>3876</v>
+        <v>2667</v>
       </c>
       <c r="G258" s="2" t="s">
         <v>15</v>
@@ -26926,7 +26926,7 @@
         <v>14</v>
       </c>
       <c r="F259" s="2">
-        <v>3163</v>
+        <v>2269</v>
       </c>
       <c r="G259" s="2" t="s">
         <v>15</v>
@@ -26958,7 +26958,7 @@
         <v>14</v>
       </c>
       <c r="F260" s="2">
-        <v>1722</v>
+        <v>1099</v>
       </c>
       <c r="G260" s="2" t="s">
         <v>15</v>
@@ -26990,7 +26990,7 @@
         <v>14</v>
       </c>
       <c r="F261" s="2">
-        <v>2499</v>
+        <v>4432</v>
       </c>
       <c r="G261" s="2" t="s">
         <v>15</v>
@@ -27022,7 +27022,7 @@
         <v>14</v>
       </c>
       <c r="F262" s="2">
-        <v>910</v>
+        <v>1494</v>
       </c>
       <c r="G262" s="2" t="s">
         <v>15</v>
@@ -27054,7 +27054,7 @@
         <v>14</v>
       </c>
       <c r="F263" s="2">
-        <v>2702</v>
+        <v>2424</v>
       </c>
       <c r="G263" s="2" t="s">
         <v>15</v>
@@ -27086,7 +27086,7 @@
         <v>14</v>
       </c>
       <c r="F264" s="2">
-        <v>4643</v>
+        <v>4345</v>
       </c>
       <c r="G264" s="2" t="s">
         <v>15</v>
@@ -27118,7 +27118,7 @@
         <v>14</v>
       </c>
       <c r="F265" s="2">
-        <v>2863</v>
+        <v>2886</v>
       </c>
       <c r="G265" s="2" t="s">
         <v>15</v>
@@ -27150,7 +27150,7 @@
         <v>14</v>
       </c>
       <c r="F266" s="2">
-        <v>2547</v>
+        <v>4340</v>
       </c>
       <c r="G266" s="2" t="s">
         <v>15</v>
@@ -27182,7 +27182,7 @@
         <v>14</v>
       </c>
       <c r="F267" s="2">
-        <v>4108</v>
+        <v>1643</v>
       </c>
       <c r="G267" s="2" t="s">
         <v>15</v>
@@ -27214,7 +27214,7 @@
         <v>14</v>
       </c>
       <c r="F268" s="2">
-        <v>4154</v>
+        <v>850</v>
       </c>
       <c r="G268" s="2" t="s">
         <v>15</v>
@@ -27246,7 +27246,7 @@
         <v>14</v>
       </c>
       <c r="F269" s="2">
-        <v>3642</v>
+        <v>4388</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>15</v>
@@ -27278,7 +27278,7 @@
         <v>14</v>
       </c>
       <c r="F270" s="2">
-        <v>4628</v>
+        <v>4741</v>
       </c>
       <c r="G270" s="2" t="s">
         <v>15</v>
@@ -27310,7 +27310,7 @@
         <v>14</v>
       </c>
       <c r="F271" s="2">
-        <v>3318</v>
+        <v>1073</v>
       </c>
       <c r="G271" s="2" t="s">
         <v>15</v>
@@ -27342,7 +27342,7 @@
         <v>14</v>
       </c>
       <c r="F272" s="2">
-        <v>1957</v>
+        <v>2539</v>
       </c>
       <c r="G272" s="2" t="s">
         <v>15</v>
@@ -27374,7 +27374,7 @@
         <v>14</v>
       </c>
       <c r="F273" s="2">
-        <v>3930</v>
+        <v>3342</v>
       </c>
       <c r="G273" s="2" t="s">
         <v>15</v>
@@ -27406,7 +27406,7 @@
         <v>14</v>
       </c>
       <c r="F274" s="2">
-        <v>3987</v>
+        <v>2948</v>
       </c>
       <c r="G274" s="2" t="s">
         <v>15</v>
@@ -27438,7 +27438,7 @@
         <v>14</v>
       </c>
       <c r="F275" s="2">
-        <v>4345</v>
+        <v>3743</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>15</v>
@@ -27470,7 +27470,7 @@
         <v>14</v>
       </c>
       <c r="F276" s="2">
-        <v>1921</v>
+        <v>2183</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>15</v>
@@ -27502,7 +27502,7 @@
         <v>14</v>
       </c>
       <c r="F277" s="2">
-        <v>1253</v>
+        <v>2051</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>15</v>
@@ -27534,7 +27534,7 @@
         <v>14</v>
       </c>
       <c r="F278" s="2">
-        <v>2022</v>
+        <v>3914</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>15</v>
@@ -27566,7 +27566,7 @@
         <v>14</v>
       </c>
       <c r="F279" s="2">
-        <v>2998</v>
+        <v>1181</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>15</v>
@@ -27598,7 +27598,7 @@
         <v>14</v>
       </c>
       <c r="F280" s="2">
-        <v>3613</v>
+        <v>1607</v>
       </c>
       <c r="G280" s="2" t="s">
         <v>15</v>
@@ -27630,7 +27630,7 @@
         <v>14</v>
       </c>
       <c r="F281" s="2">
-        <v>807</v>
+        <v>1599</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>15</v>
@@ -27662,7 +27662,7 @@
         <v>14</v>
       </c>
       <c r="F282" s="2">
-        <v>4471</v>
+        <v>2316</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>15</v>
@@ -27694,7 +27694,7 @@
         <v>14</v>
       </c>
       <c r="F283" s="2">
-        <v>3254</v>
+        <v>4359</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>15</v>
@@ -27726,7 +27726,7 @@
         <v>14</v>
       </c>
       <c r="F284" s="2">
-        <v>4358</v>
+        <v>3382</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>15</v>
@@ -27758,7 +27758,7 @@
         <v>14</v>
       </c>
       <c r="F285" s="2">
-        <v>1124</v>
+        <v>4169</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>15</v>
@@ -27790,7 +27790,7 @@
         <v>14</v>
       </c>
       <c r="F286" s="2">
-        <v>1101</v>
+        <v>2732</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>15</v>
@@ -27822,7 +27822,7 @@
         <v>14</v>
       </c>
       <c r="F287" s="2">
-        <v>3255</v>
+        <v>3281</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>15</v>
@@ -27854,7 +27854,7 @@
         <v>14</v>
       </c>
       <c r="F288" s="2">
-        <v>3697</v>
+        <v>4667</v>
       </c>
       <c r="G288" s="2" t="s">
         <v>15</v>
@@ -27886,7 +27886,7 @@
         <v>14</v>
       </c>
       <c r="F289" s="2">
-        <v>4281</v>
+        <v>4377</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>15</v>
@@ -27918,7 +27918,7 @@
         <v>14</v>
       </c>
       <c r="F290" s="2">
-        <v>1054</v>
+        <v>4130</v>
       </c>
       <c r="G290" s="2" t="s">
         <v>15</v>
@@ -27950,7 +27950,7 @@
         <v>14</v>
       </c>
       <c r="F291" s="2">
-        <v>2897</v>
+        <v>3151</v>
       </c>
       <c r="G291" s="2" t="s">
         <v>15</v>
@@ -27982,7 +27982,7 @@
         <v>14</v>
       </c>
       <c r="F292" s="2">
-        <v>1373</v>
+        <v>1954</v>
       </c>
       <c r="G292" s="2" t="s">
         <v>15</v>
@@ -28014,7 +28014,7 @@
         <v>14</v>
       </c>
       <c r="F293" s="2">
-        <v>887</v>
+        <v>2112</v>
       </c>
       <c r="G293" s="2" t="s">
         <v>15</v>
@@ -28046,7 +28046,7 @@
         <v>14</v>
       </c>
       <c r="F294" s="2">
-        <v>2040</v>
+        <v>4415</v>
       </c>
       <c r="G294" s="2" t="s">
         <v>15</v>
@@ -28078,7 +28078,7 @@
         <v>14</v>
       </c>
       <c r="F295" s="2">
-        <v>4415</v>
+        <v>1216</v>
       </c>
       <c r="G295" s="2" t="s">
         <v>15</v>
@@ -28110,7 +28110,7 @@
         <v>14</v>
       </c>
       <c r="F296" s="2">
-        <v>2494</v>
+        <v>3046</v>
       </c>
       <c r="G296" s="2" t="s">
         <v>15</v>
@@ -28142,7 +28142,7 @@
         <v>14</v>
       </c>
       <c r="F297" s="2">
-        <v>1742</v>
+        <v>893</v>
       </c>
       <c r="G297" s="2" t="s">
         <v>15</v>
@@ -28174,7 +28174,7 @@
         <v>14</v>
       </c>
       <c r="F298" s="2">
-        <v>1798</v>
+        <v>2486</v>
       </c>
       <c r="G298" s="2" t="s">
         <v>15</v>
@@ -28206,7 +28206,7 @@
         <v>14</v>
       </c>
       <c r="F299" s="2">
-        <v>3553</v>
+        <v>4583</v>
       </c>
       <c r="G299" s="2" t="s">
         <v>15</v>
@@ -28238,7 +28238,7 @@
         <v>14</v>
       </c>
       <c r="F300" s="2">
-        <v>1723</v>
+        <v>2338</v>
       </c>
       <c r="G300" s="2" t="s">
         <v>15</v>
@@ -28270,7 +28270,7 @@
         <v>14</v>
       </c>
       <c r="F301" s="2">
-        <v>2306</v>
+        <v>965</v>
       </c>
       <c r="G301" s="2" t="s">
         <v>15</v>
@@ -28302,7 +28302,7 @@
         <v>14</v>
       </c>
       <c r="F302" s="2">
-        <v>3825</v>
+        <v>1324</v>
       </c>
       <c r="G302" s="2" t="s">
         <v>15</v>
@@ -28334,7 +28334,7 @@
         <v>14</v>
       </c>
       <c r="F303" s="2">
-        <v>3748</v>
+        <v>2451</v>
       </c>
       <c r="G303" s="2" t="s">
         <v>15</v>
@@ -28366,7 +28366,7 @@
         <v>14</v>
       </c>
       <c r="F304" s="2">
-        <v>4042</v>
+        <v>4213</v>
       </c>
       <c r="G304" s="2" t="s">
         <v>15</v>
@@ -28398,7 +28398,7 @@
         <v>14</v>
       </c>
       <c r="F305" s="2">
-        <v>1718</v>
+        <v>3647</v>
       </c>
       <c r="G305" s="2" t="s">
         <v>15</v>
@@ -28430,7 +28430,7 @@
         <v>14</v>
       </c>
       <c r="F306" s="2">
-        <v>2459</v>
+        <v>1684</v>
       </c>
       <c r="G306" s="2" t="s">
         <v>15</v>
@@ -28462,7 +28462,7 @@
         <v>14</v>
       </c>
       <c r="F307" s="2">
-        <v>3958</v>
+        <v>1670</v>
       </c>
       <c r="G307" s="2" t="s">
         <v>15</v>
@@ -28494,7 +28494,7 @@
         <v>14</v>
       </c>
       <c r="F308" s="2">
-        <v>3693</v>
+        <v>2367</v>
       </c>
       <c r="G308" s="2" t="s">
         <v>15</v>
@@ -28526,7 +28526,7 @@
         <v>14</v>
       </c>
       <c r="F309" s="2">
-        <v>2395</v>
+        <v>1288</v>
       </c>
       <c r="G309" s="2" t="s">
         <v>15</v>
@@ -28558,7 +28558,7 @@
         <v>14</v>
       </c>
       <c r="F310" s="2">
-        <v>1596</v>
+        <v>3300</v>
       </c>
       <c r="G310" s="2" t="s">
         <v>15</v>
@@ -28590,7 +28590,7 @@
         <v>14</v>
       </c>
       <c r="F311" s="2">
-        <v>4551</v>
+        <v>3415</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>15</v>
@@ -28622,7 +28622,7 @@
         <v>14</v>
       </c>
       <c r="F312" s="2">
-        <v>1825</v>
+        <v>3792</v>
       </c>
       <c r="G312" s="2" t="s">
         <v>15</v>
@@ -28654,7 +28654,7 @@
         <v>14</v>
       </c>
       <c r="F313" s="2">
-        <v>948</v>
+        <v>1274</v>
       </c>
       <c r="G313" s="2" t="s">
         <v>15</v>
@@ -28686,7 +28686,7 @@
         <v>14</v>
       </c>
       <c r="F314" s="2">
-        <v>1711</v>
+        <v>1771</v>
       </c>
       <c r="G314" s="2" t="s">
         <v>15</v>
@@ -28718,7 +28718,7 @@
         <v>14</v>
       </c>
       <c r="F315" s="2">
-        <v>980</v>
+        <v>4733</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>15</v>
@@ -28750,7 +28750,7 @@
         <v>14</v>
       </c>
       <c r="F316" s="2">
-        <v>1981</v>
+        <v>3435</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>15</v>
@@ -28782,7 +28782,7 @@
         <v>14</v>
       </c>
       <c r="F317" s="2">
-        <v>4536</v>
+        <v>1603</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>15</v>
@@ -28814,7 +28814,7 @@
         <v>14</v>
       </c>
       <c r="F318" s="2">
-        <v>2435</v>
+        <v>2956</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>15</v>
@@ -28846,7 +28846,7 @@
         <v>14</v>
       </c>
       <c r="F319" s="2">
-        <v>3880</v>
+        <v>3276</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>15</v>
@@ -28878,7 +28878,7 @@
         <v>14</v>
       </c>
       <c r="F320" s="2">
-        <v>2877</v>
+        <v>3215</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>15</v>
@@ -28910,7 +28910,7 @@
         <v>14</v>
       </c>
       <c r="F321" s="2">
-        <v>1338</v>
+        <v>4657</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>15</v>
@@ -28942,7 +28942,7 @@
         <v>14</v>
       </c>
       <c r="F322" s="2">
-        <v>3047</v>
+        <v>2210</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>15</v>
@@ -28974,7 +28974,7 @@
         <v>14</v>
       </c>
       <c r="F323" s="2">
-        <v>3459</v>
+        <v>2967</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>15</v>
@@ -29006,7 +29006,7 @@
         <v>14</v>
       </c>
       <c r="F324" s="2">
-        <v>4687</v>
+        <v>3405</v>
       </c>
       <c r="G324" s="2" t="s">
         <v>15</v>
@@ -29038,7 +29038,7 @@
         <v>14</v>
       </c>
       <c r="F325" s="2">
-        <v>2614</v>
+        <v>4135</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>15</v>
@@ -29070,7 +29070,7 @@
         <v>14</v>
       </c>
       <c r="F326" s="2">
-        <v>1026</v>
+        <v>1862</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>15</v>
@@ -29102,7 +29102,7 @@
         <v>14</v>
       </c>
       <c r="F327" s="2">
-        <v>2096</v>
+        <v>2324</v>
       </c>
       <c r="G327" s="2" t="s">
         <v>15</v>
@@ -29134,7 +29134,7 @@
         <v>14</v>
       </c>
       <c r="F328" s="2">
-        <v>2464</v>
+        <v>2599</v>
       </c>
       <c r="G328" s="2" t="s">
         <v>15</v>
@@ -29166,7 +29166,7 @@
         <v>14</v>
       </c>
       <c r="F329" s="2">
-        <v>2928</v>
+        <v>4183</v>
       </c>
       <c r="G329" s="2" t="s">
         <v>15</v>
@@ -29198,7 +29198,7 @@
         <v>14</v>
       </c>
       <c r="F330" s="2">
-        <v>4415</v>
+        <v>1495</v>
       </c>
       <c r="G330" s="2" t="s">
         <v>15</v>
@@ -29230,7 +29230,7 @@
         <v>14</v>
       </c>
       <c r="F331" s="2">
-        <v>4562</v>
+        <v>3278</v>
       </c>
       <c r="G331" s="2" t="s">
         <v>15</v>
@@ -29262,7 +29262,7 @@
         <v>14</v>
       </c>
       <c r="F332" s="2">
-        <v>1700</v>
+        <v>3538</v>
       </c>
       <c r="G332" s="2" t="s">
         <v>15</v>
@@ -29294,7 +29294,7 @@
         <v>14</v>
       </c>
       <c r="F333" s="2">
-        <v>3357</v>
+        <v>3043</v>
       </c>
       <c r="G333" s="2" t="s">
         <v>15</v>
@@ -29326,7 +29326,7 @@
         <v>14</v>
       </c>
       <c r="F334" s="2">
-        <v>1863</v>
+        <v>2287</v>
       </c>
       <c r="G334" s="2" t="s">
         <v>15</v>
@@ -29358,7 +29358,7 @@
         <v>14</v>
       </c>
       <c r="F335" s="2">
-        <v>3474</v>
+        <v>1486</v>
       </c>
       <c r="G335" s="2" t="s">
         <v>15</v>
@@ -29390,7 +29390,7 @@
         <v>14</v>
       </c>
       <c r="F336" s="2">
-        <v>4591</v>
+        <v>1892</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>15</v>
@@ -29422,7 +29422,7 @@
         <v>14</v>
       </c>
       <c r="F337" s="2">
-        <v>3919</v>
+        <v>1918</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>15</v>
@@ -29454,7 +29454,7 @@
         <v>14</v>
       </c>
       <c r="F338" s="2">
-        <v>4643</v>
+        <v>3334</v>
       </c>
       <c r="G338" s="2" t="s">
         <v>15</v>
@@ -29486,7 +29486,7 @@
         <v>14</v>
       </c>
       <c r="F339" s="2">
-        <v>3323</v>
+        <v>1792</v>
       </c>
       <c r="G339" s="2" t="s">
         <v>15</v>
@@ -29518,7 +29518,7 @@
         <v>14</v>
       </c>
       <c r="F340" s="2">
-        <v>4243</v>
+        <v>954</v>
       </c>
       <c r="G340" s="2" t="s">
         <v>15</v>
@@ -29550,7 +29550,7 @@
         <v>14</v>
       </c>
       <c r="F341" s="2">
-        <v>3662</v>
+        <v>2967</v>
       </c>
       <c r="G341" s="2" t="s">
         <v>15</v>
@@ -29582,7 +29582,7 @@
         <v>14</v>
       </c>
       <c r="F342" s="2">
-        <v>1394</v>
+        <v>2339</v>
       </c>
       <c r="G342" s="2" t="s">
         <v>15</v>
@@ -29614,7 +29614,7 @@
         <v>14</v>
       </c>
       <c r="F343" s="2">
-        <v>4344</v>
+        <v>2931</v>
       </c>
       <c r="G343" s="2" t="s">
         <v>15</v>
@@ -29646,7 +29646,7 @@
         <v>14</v>
       </c>
       <c r="F344" s="2">
-        <v>1842</v>
+        <v>3210</v>
       </c>
       <c r="G344" s="2" t="s">
         <v>15</v>
@@ -29678,7 +29678,7 @@
         <v>14</v>
       </c>
       <c r="F345" s="2">
-        <v>4693</v>
+        <v>4194</v>
       </c>
       <c r="G345" s="2" t="s">
         <v>15</v>
@@ -29710,7 +29710,7 @@
         <v>14</v>
       </c>
       <c r="F346" s="2">
-        <v>3347</v>
+        <v>2515</v>
       </c>
       <c r="G346" s="2" t="s">
         <v>15</v>
@@ -29742,7 +29742,7 @@
         <v>14</v>
       </c>
       <c r="F347" s="2">
-        <v>4243</v>
+        <v>3933</v>
       </c>
       <c r="G347" s="2" t="s">
         <v>15</v>
@@ -29774,7 +29774,7 @@
         <v>14</v>
       </c>
       <c r="F348" s="2">
-        <v>4316</v>
+        <v>2972</v>
       </c>
       <c r="G348" s="2" t="s">
         <v>15</v>
@@ -29806,7 +29806,7 @@
         <v>14</v>
       </c>
       <c r="F349" s="2">
-        <v>2481</v>
+        <v>3530</v>
       </c>
       <c r="G349" s="2" t="s">
         <v>15</v>
@@ -29838,7 +29838,7 @@
         <v>14</v>
       </c>
       <c r="F350" s="2">
-        <v>2343</v>
+        <v>4592</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>15</v>
@@ -29870,7 +29870,7 @@
         <v>14</v>
       </c>
       <c r="F351" s="2">
-        <v>932</v>
+        <v>1209</v>
       </c>
       <c r="G351" s="2" t="s">
         <v>15</v>
@@ -29902,7 +29902,7 @@
         <v>14</v>
       </c>
       <c r="F352" s="2">
-        <v>1877</v>
+        <v>2387</v>
       </c>
       <c r="G352" s="2" t="s">
         <v>15</v>
@@ -29934,7 +29934,7 @@
         <v>14</v>
       </c>
       <c r="F353" s="2">
-        <v>3878</v>
+        <v>1728</v>
       </c>
       <c r="G353" s="2" t="s">
         <v>15</v>
@@ -29966,7 +29966,7 @@
         <v>14</v>
       </c>
       <c r="F354" s="2">
-        <v>2023</v>
+        <v>1955</v>
       </c>
       <c r="G354" s="2" t="s">
         <v>15</v>
@@ -29998,7 +29998,7 @@
         <v>14</v>
       </c>
       <c r="F355" s="2">
-        <v>3351</v>
+        <v>3759</v>
       </c>
       <c r="G355" s="2" t="s">
         <v>15</v>
@@ -30030,7 +30030,7 @@
         <v>14</v>
       </c>
       <c r="F356" s="2">
-        <v>1610</v>
+        <v>4618</v>
       </c>
       <c r="G356" s="2" t="s">
         <v>15</v>
@@ -30062,7 +30062,7 @@
         <v>14</v>
       </c>
       <c r="F357" s="2">
-        <v>4169</v>
+        <v>4189</v>
       </c>
       <c r="G357" s="2" t="s">
         <v>15</v>
@@ -30094,7 +30094,7 @@
         <v>14</v>
       </c>
       <c r="F358" s="2">
-        <v>3435</v>
+        <v>2412</v>
       </c>
       <c r="G358" s="2" t="s">
         <v>15</v>
@@ -30126,7 +30126,7 @@
         <v>14</v>
       </c>
       <c r="F359" s="2">
-        <v>3926</v>
+        <v>3531</v>
       </c>
       <c r="G359" s="2" t="s">
         <v>15</v>
@@ -30158,7 +30158,7 @@
         <v>14</v>
       </c>
       <c r="F360" s="2">
-        <v>3200</v>
+        <v>1269</v>
       </c>
       <c r="G360" s="2" t="s">
         <v>15</v>
@@ -30190,7 +30190,7 @@
         <v>14</v>
       </c>
       <c r="F361" s="2">
-        <v>3023</v>
+        <v>1324</v>
       </c>
       <c r="G361" s="2" t="s">
         <v>15</v>
@@ -30222,7 +30222,7 @@
         <v>14</v>
       </c>
       <c r="F362" s="2">
-        <v>4262</v>
+        <v>971</v>
       </c>
       <c r="G362" s="2" t="s">
         <v>15</v>
@@ -30254,7 +30254,7 @@
         <v>14</v>
       </c>
       <c r="F363" s="2">
-        <v>4163</v>
+        <v>4313</v>
       </c>
       <c r="G363" s="2" t="s">
         <v>15</v>
@@ -30286,7 +30286,7 @@
         <v>14</v>
       </c>
       <c r="F364" s="2">
-        <v>2145</v>
+        <v>3040</v>
       </c>
       <c r="G364" s="2" t="s">
         <v>15</v>
@@ -30318,7 +30318,7 @@
         <v>14</v>
       </c>
       <c r="F365" s="2">
-        <v>1426</v>
+        <v>2472</v>
       </c>
       <c r="G365" s="2" t="s">
         <v>15</v>
@@ -30350,7 +30350,7 @@
         <v>14</v>
       </c>
       <c r="F366" s="2">
-        <v>2739</v>
+        <v>2839</v>
       </c>
       <c r="G366" s="2" t="s">
         <v>15</v>
@@ -30382,7 +30382,7 @@
         <v>14</v>
       </c>
       <c r="F367" s="2">
-        <v>4777</v>
+        <v>3009</v>
       </c>
       <c r="G367" s="2" t="s">
         <v>15</v>
@@ -30414,7 +30414,7 @@
         <v>14</v>
       </c>
       <c r="F368" s="2">
-        <v>2027</v>
+        <v>3498</v>
       </c>
       <c r="G368" s="2" t="s">
         <v>15</v>
@@ -30446,7 +30446,7 @@
         <v>14</v>
       </c>
       <c r="F369" s="2">
-        <v>3574</v>
+        <v>1296</v>
       </c>
       <c r="G369" s="2" t="s">
         <v>15</v>
@@ -30478,7 +30478,7 @@
         <v>14</v>
       </c>
       <c r="F370" s="2">
-        <v>2746</v>
+        <v>1680</v>
       </c>
       <c r="G370" s="2" t="s">
         <v>15</v>
@@ -30510,7 +30510,7 @@
         <v>14</v>
       </c>
       <c r="F371" s="2">
-        <v>3676</v>
+        <v>3485</v>
       </c>
       <c r="G371" s="2" t="s">
         <v>15</v>
@@ -30542,7 +30542,7 @@
         <v>14</v>
       </c>
       <c r="F372" s="2">
-        <v>2155</v>
+        <v>4113</v>
       </c>
       <c r="G372" s="2" t="s">
         <v>15</v>
@@ -30574,7 +30574,7 @@
         <v>14</v>
       </c>
       <c r="F373" s="2">
-        <v>1410</v>
+        <v>2606</v>
       </c>
       <c r="G373" s="2" t="s">
         <v>15</v>
@@ -30606,7 +30606,7 @@
         <v>14</v>
       </c>
       <c r="F374" s="2">
-        <v>4289</v>
+        <v>4132</v>
       </c>
       <c r="G374" s="2" t="s">
         <v>15</v>
@@ -30638,7 +30638,7 @@
         <v>14</v>
       </c>
       <c r="F375" s="2">
-        <v>3804</v>
+        <v>2575</v>
       </c>
       <c r="G375" s="2" t="s">
         <v>15</v>
@@ -30670,7 +30670,7 @@
         <v>14</v>
       </c>
       <c r="F376" s="2">
-        <v>4341</v>
+        <v>1225</v>
       </c>
       <c r="G376" s="2" t="s">
         <v>15</v>
@@ -30702,7 +30702,7 @@
         <v>14</v>
       </c>
       <c r="F377" s="2">
-        <v>1605</v>
+        <v>3457</v>
       </c>
       <c r="G377" s="2" t="s">
         <v>15</v>
@@ -30734,7 +30734,7 @@
         <v>14</v>
       </c>
       <c r="F378" s="2">
-        <v>3466</v>
+        <v>1068</v>
       </c>
       <c r="G378" s="2" t="s">
         <v>15</v>
@@ -30766,7 +30766,7 @@
         <v>14</v>
       </c>
       <c r="F379" s="2">
-        <v>4511</v>
+        <v>2072</v>
       </c>
       <c r="G379" s="2" t="s">
         <v>15</v>
@@ -30798,7 +30798,7 @@
         <v>14</v>
       </c>
       <c r="F380" s="2">
-        <v>1605</v>
+        <v>2610</v>
       </c>
       <c r="G380" s="2" t="s">
         <v>15</v>
@@ -30830,7 +30830,7 @@
         <v>14</v>
       </c>
       <c r="F381" s="2">
-        <v>3584</v>
+        <v>3246</v>
       </c>
       <c r="G381" s="2" t="s">
         <v>15</v>
@@ -30862,7 +30862,7 @@
         <v>14</v>
       </c>
       <c r="F382" s="2">
-        <v>881</v>
+        <v>4146</v>
       </c>
       <c r="G382" s="2" t="s">
         <v>15</v>
@@ -30894,7 +30894,7 @@
         <v>14</v>
       </c>
       <c r="F383" s="2">
-        <v>2372</v>
+        <v>3988</v>
       </c>
       <c r="G383" s="2" t="s">
         <v>15</v>
@@ -30926,7 +30926,7 @@
         <v>14</v>
       </c>
       <c r="F384" s="2">
-        <v>4743</v>
+        <v>1730</v>
       </c>
       <c r="G384" s="2" t="s">
         <v>15</v>
@@ -30958,7 +30958,7 @@
         <v>14</v>
       </c>
       <c r="F385" s="2">
-        <v>3690</v>
+        <v>2541</v>
       </c>
       <c r="G385" s="2" t="s">
         <v>15</v>
@@ -30990,7 +30990,7 @@
         <v>14</v>
       </c>
       <c r="F386" s="2">
-        <v>1886</v>
+        <v>2079</v>
       </c>
       <c r="G386" s="2" t="s">
         <v>15</v>
@@ -31022,7 +31022,7 @@
         <v>14</v>
       </c>
       <c r="F387" s="2">
-        <v>2744</v>
+        <v>3874</v>
       </c>
       <c r="G387" s="2" t="s">
         <v>15</v>
@@ -31054,7 +31054,7 @@
         <v>14</v>
       </c>
       <c r="F388" s="2">
-        <v>1616</v>
+        <v>2512</v>
       </c>
       <c r="G388" s="2" t="s">
         <v>15</v>
@@ -31086,7 +31086,7 @@
         <v>14</v>
       </c>
       <c r="F389" s="2">
-        <v>3729</v>
+        <v>2902</v>
       </c>
       <c r="G389" s="2" t="s">
         <v>15</v>
@@ -31118,7 +31118,7 @@
         <v>14</v>
       </c>
       <c r="F390" s="2">
-        <v>2901</v>
+        <v>4623</v>
       </c>
       <c r="G390" s="2" t="s">
         <v>15</v>
@@ -31150,7 +31150,7 @@
         <v>14</v>
       </c>
       <c r="F391" s="2">
-        <v>1763</v>
+        <v>2103</v>
       </c>
       <c r="G391" s="2" t="s">
         <v>15</v>
@@ -31182,7 +31182,7 @@
         <v>14</v>
       </c>
       <c r="F392" s="2">
-        <v>2508</v>
+        <v>3950</v>
       </c>
       <c r="G392" s="2" t="s">
         <v>15</v>
@@ -31214,7 +31214,7 @@
         <v>14</v>
       </c>
       <c r="F393" s="2">
-        <v>4065</v>
+        <v>2644</v>
       </c>
       <c r="G393" s="2" t="s">
         <v>15</v>
@@ -31246,7 +31246,7 @@
         <v>14</v>
       </c>
       <c r="F394" s="2">
-        <v>1782</v>
+        <v>1292</v>
       </c>
       <c r="G394" s="2" t="s">
         <v>15</v>
@@ -31278,7 +31278,7 @@
         <v>14</v>
       </c>
       <c r="F395" s="2">
-        <v>3820</v>
+        <v>3000</v>
       </c>
       <c r="G395" s="2" t="s">
         <v>15</v>
@@ -31310,7 +31310,7 @@
         <v>14</v>
       </c>
       <c r="F396" s="2">
-        <v>3924</v>
+        <v>1468</v>
       </c>
       <c r="G396" s="2" t="s">
         <v>15</v>
@@ -31342,7 +31342,7 @@
         <v>14</v>
       </c>
       <c r="F397" s="2">
-        <v>2202</v>
+        <v>4226</v>
       </c>
       <c r="G397" s="2" t="s">
         <v>15</v>
@@ -31374,7 +31374,7 @@
         <v>14</v>
       </c>
       <c r="F398" s="2">
-        <v>3389</v>
+        <v>3658</v>
       </c>
       <c r="G398" s="2" t="s">
         <v>15</v>
@@ -31406,7 +31406,7 @@
         <v>14</v>
       </c>
       <c r="F399" s="2">
-        <v>1459</v>
+        <v>3470</v>
       </c>
       <c r="G399" s="2" t="s">
         <v>15</v>
@@ -31438,7 +31438,7 @@
         <v>14</v>
       </c>
       <c r="F400" s="2">
-        <v>2506</v>
+        <v>3158</v>
       </c>
       <c r="G400" s="2" t="s">
         <v>15</v>
@@ -31470,7 +31470,7 @@
         <v>14</v>
       </c>
       <c r="F401" s="2">
-        <v>3798</v>
+        <v>1477</v>
       </c>
       <c r="G401" s="2" t="s">
         <v>15</v>
@@ -31502,7 +31502,7 @@
         <v>14</v>
       </c>
       <c r="F402" s="2">
-        <v>4518</v>
+        <v>3875</v>
       </c>
       <c r="G402" s="2" t="s">
         <v>15</v>
@@ -31534,7 +31534,7 @@
         <v>14</v>
       </c>
       <c r="F403" s="2">
-        <v>2416</v>
+        <v>3243</v>
       </c>
       <c r="G403" s="2" t="s">
         <v>15</v>
@@ -31566,7 +31566,7 @@
         <v>14</v>
       </c>
       <c r="F404" s="2">
-        <v>1249</v>
+        <v>1420</v>
       </c>
       <c r="G404" s="2" t="s">
         <v>15</v>
@@ -31598,7 +31598,7 @@
         <v>14</v>
       </c>
       <c r="F405" s="2">
-        <v>4430</v>
+        <v>3256</v>
       </c>
       <c r="G405" s="2" t="s">
         <v>15</v>
@@ -31630,7 +31630,7 @@
         <v>14</v>
       </c>
       <c r="F406" s="2">
-        <v>4657</v>
+        <v>2216</v>
       </c>
       <c r="G406" s="2" t="s">
         <v>15</v>
@@ -31662,7 +31662,7 @@
         <v>14</v>
       </c>
       <c r="F407" s="2">
-        <v>2057</v>
+        <v>1088</v>
       </c>
       <c r="G407" s="2" t="s">
         <v>15</v>
@@ -31694,7 +31694,7 @@
         <v>14</v>
       </c>
       <c r="F408" s="2">
-        <v>3691</v>
+        <v>3992</v>
       </c>
       <c r="G408" s="2" t="s">
         <v>15</v>
@@ -31726,7 +31726,7 @@
         <v>14</v>
       </c>
       <c r="F409" s="2">
-        <v>4418</v>
+        <v>1235</v>
       </c>
       <c r="G409" s="2" t="s">
         <v>15</v>
@@ -31758,7 +31758,7 @@
         <v>14</v>
       </c>
       <c r="F410" s="2">
-        <v>2407</v>
+        <v>1330</v>
       </c>
       <c r="G410" s="2" t="s">
         <v>15</v>
@@ -31790,7 +31790,7 @@
         <v>14</v>
       </c>
       <c r="F411" s="2">
-        <v>886</v>
+        <v>921</v>
       </c>
       <c r="G411" s="2" t="s">
         <v>15</v>
@@ -31822,7 +31822,7 @@
         <v>14</v>
       </c>
       <c r="F412" s="2">
-        <v>1245</v>
+        <v>2205</v>
       </c>
       <c r="G412" s="2" t="s">
         <v>15</v>
@@ -31854,7 +31854,7 @@
         <v>14</v>
       </c>
       <c r="F413" s="2">
-        <v>1606</v>
+        <v>3990</v>
       </c>
       <c r="G413" s="2" t="s">
         <v>15</v>
@@ -31886,7 +31886,7 @@
         <v>14</v>
       </c>
       <c r="F414" s="2">
-        <v>1886</v>
+        <v>1498</v>
       </c>
       <c r="G414" s="2" t="s">
         <v>15</v>
@@ -31918,7 +31918,7 @@
         <v>14</v>
       </c>
       <c r="F415" s="2">
-        <v>2356</v>
+        <v>2498</v>
       </c>
       <c r="G415" s="2" t="s">
         <v>15</v>
@@ -31950,7 +31950,7 @@
         <v>14</v>
       </c>
       <c r="F416" s="2">
-        <v>3075</v>
+        <v>1746</v>
       </c>
       <c r="G416" s="2" t="s">
         <v>15</v>
@@ -31982,7 +31982,7 @@
         <v>14</v>
       </c>
       <c r="F417" s="2">
-        <v>4305</v>
+        <v>1559</v>
       </c>
       <c r="G417" s="2" t="s">
         <v>15</v>
@@ -32014,7 +32014,7 @@
         <v>14</v>
       </c>
       <c r="F418" s="2">
-        <v>4026</v>
+        <v>1022</v>
       </c>
       <c r="G418" s="2" t="s">
         <v>15</v>
@@ -32046,7 +32046,7 @@
         <v>14</v>
       </c>
       <c r="F419" s="2">
-        <v>4787</v>
+        <v>858</v>
       </c>
       <c r="G419" s="2" t="s">
         <v>15</v>
@@ -32078,7 +32078,7 @@
         <v>14</v>
       </c>
       <c r="F420" s="2">
-        <v>1465</v>
+        <v>1942</v>
       </c>
       <c r="G420" s="2" t="s">
         <v>15</v>
@@ -32110,7 +32110,7 @@
         <v>14</v>
       </c>
       <c r="F421" s="2">
-        <v>1251</v>
+        <v>4088</v>
       </c>
       <c r="G421" s="2" t="s">
         <v>15</v>
@@ -32142,7 +32142,7 @@
         <v>14</v>
       </c>
       <c r="F422" s="2">
-        <v>3593</v>
+        <v>4265</v>
       </c>
       <c r="G422" s="2" t="s">
         <v>15</v>
@@ -32174,7 +32174,7 @@
         <v>14</v>
       </c>
       <c r="F423" s="2">
-        <v>961</v>
+        <v>1299</v>
       </c>
       <c r="G423" s="2" t="s">
         <v>15</v>
@@ -32206,7 +32206,7 @@
         <v>14</v>
       </c>
       <c r="F424" s="2">
-        <v>4561</v>
+        <v>4612</v>
       </c>
       <c r="G424" s="2" t="s">
         <v>15</v>
@@ -32238,7 +32238,7 @@
         <v>14</v>
       </c>
       <c r="F425" s="2">
-        <v>3789</v>
+        <v>3970</v>
       </c>
       <c r="G425" s="2" t="s">
         <v>15</v>
@@ -32270,7 +32270,7 @@
         <v>14</v>
       </c>
       <c r="F426" s="2">
-        <v>1865</v>
+        <v>1792</v>
       </c>
       <c r="G426" s="2" t="s">
         <v>15</v>
@@ -32302,7 +32302,7 @@
         <v>14</v>
       </c>
       <c r="F427" s="2">
-        <v>3054</v>
+        <v>2111</v>
       </c>
       <c r="G427" s="2" t="s">
         <v>15</v>
@@ -32334,7 +32334,7 @@
         <v>14</v>
       </c>
       <c r="F428" s="2">
-        <v>3806</v>
+        <v>4298</v>
       </c>
       <c r="G428" s="2" t="s">
         <v>15</v>
@@ -32366,7 +32366,7 @@
         <v>14</v>
       </c>
       <c r="F429" s="2">
-        <v>3632</v>
+        <v>4287</v>
       </c>
       <c r="G429" s="2" t="s">
         <v>15</v>
@@ -32398,7 +32398,7 @@
         <v>14</v>
       </c>
       <c r="F430" s="2">
-        <v>1278</v>
+        <v>2963</v>
       </c>
       <c r="G430" s="2" t="s">
         <v>15</v>
@@ -32430,7 +32430,7 @@
         <v>14</v>
       </c>
       <c r="F431" s="2">
-        <v>1961</v>
+        <v>2290</v>
       </c>
       <c r="G431" s="2" t="s">
         <v>15</v>
@@ -32462,7 +32462,7 @@
         <v>14</v>
       </c>
       <c r="F432" s="2">
-        <v>4477</v>
+        <v>4010</v>
       </c>
       <c r="G432" s="2" t="s">
         <v>15</v>
@@ -32494,7 +32494,7 @@
         <v>14</v>
       </c>
       <c r="F433" s="2">
-        <v>4396</v>
+        <v>4380</v>
       </c>
       <c r="G433" s="2" t="s">
         <v>15</v>
@@ -32526,7 +32526,7 @@
         <v>14</v>
       </c>
       <c r="F434" s="2">
-        <v>4580</v>
+        <v>3971</v>
       </c>
       <c r="G434" s="2" t="s">
         <v>15</v>
@@ -32558,7 +32558,7 @@
         <v>14</v>
       </c>
       <c r="F435" s="2">
-        <v>3548</v>
+        <v>2495</v>
       </c>
       <c r="G435" s="2" t="s">
         <v>15</v>
@@ -32590,7 +32590,7 @@
         <v>14</v>
       </c>
       <c r="F436" s="2">
-        <v>2282</v>
+        <v>1931</v>
       </c>
       <c r="G436" s="2" t="s">
         <v>15</v>
@@ -32622,7 +32622,7 @@
         <v>14</v>
       </c>
       <c r="F437" s="2">
-        <v>4593</v>
+        <v>4423</v>
       </c>
       <c r="G437" s="2" t="s">
         <v>15</v>
@@ -32654,7 +32654,7 @@
         <v>14</v>
       </c>
       <c r="F438" s="2">
-        <v>2850</v>
+        <v>2497</v>
       </c>
       <c r="G438" s="2" t="s">
         <v>15</v>
@@ -32686,7 +32686,7 @@
         <v>14</v>
       </c>
       <c r="F439" s="2">
-        <v>2725</v>
+        <v>1522</v>
       </c>
       <c r="G439" s="2" t="s">
         <v>15</v>
@@ -32718,7 +32718,7 @@
         <v>14</v>
       </c>
       <c r="F440" s="2">
-        <v>3970</v>
+        <v>1528</v>
       </c>
       <c r="G440" s="2" t="s">
         <v>15</v>
@@ -32750,7 +32750,7 @@
         <v>14</v>
       </c>
       <c r="F441" s="2">
-        <v>1776</v>
+        <v>2770</v>
       </c>
       <c r="G441" s="2" t="s">
         <v>15</v>
@@ -32782,7 +32782,7 @@
         <v>14</v>
       </c>
       <c r="F442" s="2">
-        <v>2614</v>
+        <v>904</v>
       </c>
       <c r="G442" s="2" t="s">
         <v>15</v>
@@ -32814,7 +32814,7 @@
         <v>14</v>
       </c>
       <c r="F443" s="2">
-        <v>4389</v>
+        <v>3122</v>
       </c>
       <c r="G443" s="2" t="s">
         <v>15</v>
@@ -32846,7 +32846,7 @@
         <v>14</v>
       </c>
       <c r="F444" s="2">
-        <v>860</v>
+        <v>1126</v>
       </c>
       <c r="G444" s="2" t="s">
         <v>15</v>
@@ -32878,7 +32878,7 @@
         <v>14</v>
       </c>
       <c r="F445" s="2">
-        <v>1441</v>
+        <v>1287</v>
       </c>
       <c r="G445" s="2" t="s">
         <v>15</v>
@@ -32910,7 +32910,7 @@
         <v>14</v>
       </c>
       <c r="F446" s="2">
-        <v>1682</v>
+        <v>2193</v>
       </c>
       <c r="G446" s="2" t="s">
         <v>15</v>
@@ -32942,7 +32942,7 @@
         <v>14</v>
       </c>
       <c r="F447" s="2">
-        <v>1806</v>
+        <v>2803</v>
       </c>
       <c r="G447" s="2" t="s">
         <v>15</v>
@@ -32974,7 +32974,7 @@
         <v>14</v>
       </c>
       <c r="F448" s="2">
-        <v>3015</v>
+        <v>3596</v>
       </c>
       <c r="G448" s="2" t="s">
         <v>15</v>
@@ -33006,7 +33006,7 @@
         <v>14</v>
       </c>
       <c r="F449" s="2">
-        <v>3360</v>
+        <v>3194</v>
       </c>
       <c r="G449" s="2" t="s">
         <v>15</v>
@@ -33038,7 +33038,7 @@
         <v>14</v>
       </c>
       <c r="F450" s="2">
-        <v>2372</v>
+        <v>2329</v>
       </c>
       <c r="G450" s="2" t="s">
         <v>15</v>
@@ -33070,7 +33070,7 @@
         <v>14</v>
       </c>
       <c r="F451" s="2">
-        <v>2745</v>
+        <v>3819</v>
       </c>
       <c r="G451" s="2" t="s">
         <v>15</v>
@@ -33102,7 +33102,7 @@
         <v>14</v>
       </c>
       <c r="F452" s="2">
-        <v>2479</v>
+        <v>2766</v>
       </c>
       <c r="G452" s="2" t="s">
         <v>15</v>
@@ -33134,7 +33134,7 @@
         <v>14</v>
       </c>
       <c r="F453" s="2">
-        <v>1262</v>
+        <v>2868</v>
       </c>
       <c r="G453" s="2" t="s">
         <v>15</v>
@@ -33166,7 +33166,7 @@
         <v>14</v>
       </c>
       <c r="F454" s="2">
-        <v>4473</v>
+        <v>3820</v>
       </c>
       <c r="G454" s="2" t="s">
         <v>15</v>
@@ -33198,7 +33198,7 @@
         <v>14</v>
       </c>
       <c r="F455" s="2">
-        <v>1626</v>
+        <v>4529</v>
       </c>
       <c r="G455" s="2" t="s">
         <v>15</v>
@@ -33230,7 +33230,7 @@
         <v>14</v>
       </c>
       <c r="F456" s="2">
-        <v>3691</v>
+        <v>2461</v>
       </c>
       <c r="G456" s="2" t="s">
         <v>15</v>
@@ -33262,7 +33262,7 @@
         <v>14</v>
       </c>
       <c r="F457" s="2">
-        <v>3138</v>
+        <v>2268</v>
       </c>
       <c r="G457" s="2" t="s">
         <v>15</v>
@@ -33294,7 +33294,7 @@
         <v>14</v>
       </c>
       <c r="F458" s="2">
-        <v>856</v>
+        <v>3253</v>
       </c>
       <c r="G458" s="2" t="s">
         <v>15</v>
@@ -33326,7 +33326,7 @@
         <v>14</v>
       </c>
       <c r="F459" s="2">
-        <v>2601</v>
+        <v>4103</v>
       </c>
       <c r="G459" s="2" t="s">
         <v>15</v>
@@ -33358,7 +33358,7 @@
         <v>14</v>
       </c>
       <c r="F460" s="2">
-        <v>2749</v>
+        <v>4645</v>
       </c>
       <c r="G460" s="2" t="s">
         <v>15</v>
@@ -33390,7 +33390,7 @@
         <v>14</v>
       </c>
       <c r="F461" s="2">
-        <v>1270</v>
+        <v>1816</v>
       </c>
       <c r="G461" s="2" t="s">
         <v>15</v>
@@ -33422,7 +33422,7 @@
         <v>14</v>
       </c>
       <c r="F462" s="2">
-        <v>1955</v>
+        <v>3783</v>
       </c>
       <c r="G462" s="2" t="s">
         <v>15</v>
@@ -33454,7 +33454,7 @@
         <v>14</v>
       </c>
       <c r="F463" s="2">
-        <v>3567</v>
+        <v>4030</v>
       </c>
       <c r="G463" s="2" t="s">
         <v>15</v>
@@ -33486,7 +33486,7 @@
         <v>14</v>
       </c>
       <c r="F464" s="2">
-        <v>3712</v>
+        <v>917</v>
       </c>
       <c r="G464" s="2" t="s">
         <v>15</v>
@@ -33518,7 +33518,7 @@
         <v>14</v>
       </c>
       <c r="F465" s="2">
-        <v>1272</v>
+        <v>4148</v>
       </c>
       <c r="G465" s="2" t="s">
         <v>15</v>
@@ -33550,7 +33550,7 @@
         <v>14</v>
       </c>
       <c r="F466" s="2">
-        <v>4776</v>
+        <v>2958</v>
       </c>
       <c r="G466" s="2" t="s">
         <v>15</v>
@@ -33582,7 +33582,7 @@
         <v>14</v>
       </c>
       <c r="F467" s="2">
-        <v>1305</v>
+        <v>4251</v>
       </c>
       <c r="G467" s="2" t="s">
         <v>15</v>
@@ -33614,7 +33614,7 @@
         <v>14</v>
       </c>
       <c r="F468" s="2">
-        <v>4315</v>
+        <v>4757</v>
       </c>
       <c r="G468" s="2" t="s">
         <v>15</v>
@@ -33646,7 +33646,7 @@
         <v>14</v>
       </c>
       <c r="F469" s="2">
-        <v>2441</v>
+        <v>4755</v>
       </c>
       <c r="G469" s="2" t="s">
         <v>15</v>
@@ -33678,7 +33678,7 @@
         <v>14</v>
       </c>
       <c r="F470" s="2">
-        <v>2133</v>
+        <v>2265</v>
       </c>
       <c r="G470" s="2" t="s">
         <v>15</v>
@@ -33710,7 +33710,7 @@
         <v>14</v>
       </c>
       <c r="F471" s="2">
-        <v>3039</v>
+        <v>2516</v>
       </c>
       <c r="G471" s="2" t="s">
         <v>15</v>

--- a/reports/selenium/latest/excel/Automation_Test_Report.xlsx
+++ b/reports/selenium/latest/excel/Automation_Test_Report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8557" uniqueCount="1042">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8557" uniqueCount="1040">
   <si>
     <t>Test ID</t>
   </si>
@@ -3084,25 +3084,19 @@
     <t>Build</t>
   </si>
   <si>
-    <t>11</t>
+    <t>local</t>
   </si>
   <si>
     <t>Branch</t>
   </si>
   <si>
-    <t>main</t>
-  </si>
-  <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>11e9b67abc20</t>
-  </si>
-  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T16:39:03.788Z</t>
+    <t>2026-08-17T06:21:14.794Z</t>
   </si>
   <si>
     <t>Browser</t>
@@ -3135,7 +3129,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>0.0s</t>
+    <t>0.3s</t>
   </si>
   <si>
     <t>Total</t>
@@ -3607,7 +3601,7 @@
         <v>14</v>
       </c>
       <c r="F2" s="2">
-        <v>3597</v>
+        <v>2554</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>15</v>
@@ -3639,7 +3633,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="2">
-        <v>1120</v>
+        <v>1005</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>15</v>
@@ -3671,7 +3665,7 @@
         <v>14</v>
       </c>
       <c r="F4" s="2">
-        <v>3037</v>
+        <v>1371</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
@@ -3703,7 +3697,7 @@
         <v>14</v>
       </c>
       <c r="F5" s="2">
-        <v>2728</v>
+        <v>4403</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
@@ -3735,7 +3729,7 @@
         <v>14</v>
       </c>
       <c r="F6" s="2">
-        <v>2049</v>
+        <v>1966</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -3767,7 +3761,7 @@
         <v>14</v>
       </c>
       <c r="F7" s="2">
-        <v>2055</v>
+        <v>1146</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -3799,7 +3793,7 @@
         <v>14</v>
       </c>
       <c r="F8" s="2">
-        <v>850</v>
+        <v>983</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -3831,7 +3825,7 @@
         <v>14</v>
       </c>
       <c r="F9" s="2">
-        <v>2266</v>
+        <v>4550</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -3863,7 +3857,7 @@
         <v>14</v>
       </c>
       <c r="F10" s="2">
-        <v>4135</v>
+        <v>3546</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
@@ -3895,7 +3889,7 @@
         <v>14</v>
       </c>
       <c r="F11" s="2">
-        <v>2859</v>
+        <v>1587</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
@@ -3927,7 +3921,7 @@
         <v>14</v>
       </c>
       <c r="F12" s="2">
-        <v>1309</v>
+        <v>2686</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
@@ -3959,7 +3953,7 @@
         <v>14</v>
       </c>
       <c r="F13" s="2">
-        <v>993</v>
+        <v>923</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -3991,7 +3985,7 @@
         <v>14</v>
       </c>
       <c r="F14" s="2">
-        <v>2180</v>
+        <v>1180</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -4023,7 +4017,7 @@
         <v>14</v>
       </c>
       <c r="F15" s="2">
-        <v>4360</v>
+        <v>4539</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -4055,7 +4049,7 @@
         <v>14</v>
       </c>
       <c r="F16" s="2">
-        <v>1532</v>
+        <v>4247</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
@@ -4087,7 +4081,7 @@
         <v>14</v>
       </c>
       <c r="F17" s="2">
-        <v>4276</v>
+        <v>941</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
@@ -4119,7 +4113,7 @@
         <v>14</v>
       </c>
       <c r="F18" s="2">
-        <v>3017</v>
+        <v>2875</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
@@ -4151,7 +4145,7 @@
         <v>14</v>
       </c>
       <c r="F19" s="2">
-        <v>3197</v>
+        <v>2654</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
@@ -4183,7 +4177,7 @@
         <v>14</v>
       </c>
       <c r="F20" s="2">
-        <v>1930</v>
+        <v>2107</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
@@ -4215,7 +4209,7 @@
         <v>14</v>
       </c>
       <c r="F21" s="2">
-        <v>2303</v>
+        <v>4282</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -4247,7 +4241,7 @@
         <v>14</v>
       </c>
       <c r="F22" s="2">
-        <v>2113</v>
+        <v>2543</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -4279,7 +4273,7 @@
         <v>14</v>
       </c>
       <c r="F23" s="2">
-        <v>3251</v>
+        <v>4573</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -4311,7 +4305,7 @@
         <v>14</v>
       </c>
       <c r="F24" s="2">
-        <v>1692</v>
+        <v>4360</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -4343,7 +4337,7 @@
         <v>14</v>
       </c>
       <c r="F25" s="2">
-        <v>1551</v>
+        <v>3018</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -4375,7 +4369,7 @@
         <v>14</v>
       </c>
       <c r="F26" s="2">
-        <v>1858</v>
+        <v>1625</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -4407,7 +4401,7 @@
         <v>14</v>
       </c>
       <c r="F27" s="2">
-        <v>3081</v>
+        <v>4092</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>15</v>
@@ -4439,7 +4433,7 @@
         <v>14</v>
       </c>
       <c r="F28" s="2">
-        <v>3971</v>
+        <v>1499</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>15</v>
@@ -4471,7 +4465,7 @@
         <v>14</v>
       </c>
       <c r="F29" s="2">
-        <v>2436</v>
+        <v>2405</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>15</v>
@@ -4503,7 +4497,7 @@
         <v>14</v>
       </c>
       <c r="F30" s="2">
-        <v>1720</v>
+        <v>3156</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>15</v>
@@ -4535,7 +4529,7 @@
         <v>14</v>
       </c>
       <c r="F31" s="2">
-        <v>819</v>
+        <v>917</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>15</v>
@@ -4567,7 +4561,7 @@
         <v>14</v>
       </c>
       <c r="F32" s="2">
-        <v>1642</v>
+        <v>1702</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>15</v>
@@ -4599,7 +4593,7 @@
         <v>14</v>
       </c>
       <c r="F33" s="2">
-        <v>1123</v>
+        <v>3737</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>15</v>
@@ -4631,7 +4625,7 @@
         <v>14</v>
       </c>
       <c r="F34" s="2">
-        <v>1687</v>
+        <v>4655</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>15</v>
@@ -4663,7 +4657,7 @@
         <v>14</v>
       </c>
       <c r="F35" s="2">
-        <v>4055</v>
+        <v>2182</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>15</v>
@@ -4695,7 +4689,7 @@
         <v>14</v>
       </c>
       <c r="F36" s="2">
-        <v>1862</v>
+        <v>1459</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>15</v>
@@ -4727,7 +4721,7 @@
         <v>14</v>
       </c>
       <c r="F37" s="2">
-        <v>2858</v>
+        <v>1951</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>15</v>
@@ -4759,7 +4753,7 @@
         <v>14</v>
       </c>
       <c r="F38" s="2">
-        <v>3867</v>
+        <v>3093</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>15</v>
@@ -4791,7 +4785,7 @@
         <v>14</v>
       </c>
       <c r="F39" s="2">
-        <v>4457</v>
+        <v>2140</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>15</v>
@@ -4823,7 +4817,7 @@
         <v>14</v>
       </c>
       <c r="F40" s="2">
-        <v>2119</v>
+        <v>1502</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>15</v>
@@ -4855,7 +4849,7 @@
         <v>14</v>
       </c>
       <c r="F41" s="2">
-        <v>2614</v>
+        <v>1559</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>15</v>
@@ -4887,7 +4881,7 @@
         <v>14</v>
       </c>
       <c r="F42" s="2">
-        <v>3842</v>
+        <v>3356</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>15</v>
@@ -4919,7 +4913,7 @@
         <v>14</v>
       </c>
       <c r="F43" s="2">
-        <v>1343</v>
+        <v>1380</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>15</v>
@@ -4951,7 +4945,7 @@
         <v>14</v>
       </c>
       <c r="F44" s="2">
-        <v>3241</v>
+        <v>4790</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>15</v>
@@ -4983,7 +4977,7 @@
         <v>14</v>
       </c>
       <c r="F45" s="2">
-        <v>3631</v>
+        <v>1149</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>15</v>
@@ -5015,7 +5009,7 @@
         <v>14</v>
       </c>
       <c r="F46" s="2">
-        <v>2755</v>
+        <v>1770</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>15</v>
@@ -5047,7 +5041,7 @@
         <v>14</v>
       </c>
       <c r="F47" s="2">
-        <v>3756</v>
+        <v>4797</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>15</v>
@@ -5079,7 +5073,7 @@
         <v>14</v>
       </c>
       <c r="F48" s="2">
-        <v>3028</v>
+        <v>3166</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>15</v>
@@ -5111,7 +5105,7 @@
         <v>14</v>
       </c>
       <c r="F49" s="2">
-        <v>3578</v>
+        <v>1537</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>15</v>
@@ -5143,7 +5137,7 @@
         <v>14</v>
       </c>
       <c r="F50" s="2">
-        <v>1044</v>
+        <v>1273</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>15</v>
@@ -5175,7 +5169,7 @@
         <v>14</v>
       </c>
       <c r="F51" s="2">
-        <v>2937</v>
+        <v>1816</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>15</v>
@@ -5207,7 +5201,7 @@
         <v>14</v>
       </c>
       <c r="F52" s="2">
-        <v>1971</v>
+        <v>1217</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>15</v>
@@ -5239,7 +5233,7 @@
         <v>14</v>
       </c>
       <c r="F53" s="2">
-        <v>3909</v>
+        <v>4478</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>15</v>
@@ -5271,7 +5265,7 @@
         <v>14</v>
       </c>
       <c r="F54" s="2">
-        <v>4771</v>
+        <v>1505</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>15</v>
@@ -5303,7 +5297,7 @@
         <v>14</v>
       </c>
       <c r="F55" s="2">
-        <v>3275</v>
+        <v>1462</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>15</v>
@@ -5335,7 +5329,7 @@
         <v>14</v>
       </c>
       <c r="F56" s="2">
-        <v>2313</v>
+        <v>3530</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>15</v>
@@ -5367,7 +5361,7 @@
         <v>14</v>
       </c>
       <c r="F57" s="2">
-        <v>2030</v>
+        <v>3488</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>15</v>
@@ -5399,7 +5393,7 @@
         <v>14</v>
       </c>
       <c r="F58" s="2">
-        <v>4455</v>
+        <v>2121</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>15</v>
@@ -5431,7 +5425,7 @@
         <v>14</v>
       </c>
       <c r="F59" s="2">
-        <v>1812</v>
+        <v>1512</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>15</v>
@@ -5463,7 +5457,7 @@
         <v>14</v>
       </c>
       <c r="F60" s="2">
-        <v>3317</v>
+        <v>3540</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>15</v>
@@ -5495,7 +5489,7 @@
         <v>14</v>
       </c>
       <c r="F61" s="2">
-        <v>2825</v>
+        <v>3072</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>15</v>
@@ -5527,7 +5521,7 @@
         <v>14</v>
       </c>
       <c r="F62" s="2">
-        <v>4783</v>
+        <v>1371</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>15</v>
@@ -5559,7 +5553,7 @@
         <v>14</v>
       </c>
       <c r="F63" s="2">
-        <v>4106</v>
+        <v>3849</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>15</v>
@@ -5591,7 +5585,7 @@
         <v>14</v>
       </c>
       <c r="F64" s="2">
-        <v>4282</v>
+        <v>2403</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>15</v>
@@ -5623,7 +5617,7 @@
         <v>14</v>
       </c>
       <c r="F65" s="2">
-        <v>1791</v>
+        <v>1547</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>15</v>
@@ -5655,7 +5649,7 @@
         <v>14</v>
       </c>
       <c r="F66" s="2">
-        <v>3879</v>
+        <v>2696</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>15</v>
@@ -5687,7 +5681,7 @@
         <v>14</v>
       </c>
       <c r="F67" s="2">
-        <v>2378</v>
+        <v>2694</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>15</v>
@@ -5719,7 +5713,7 @@
         <v>14</v>
       </c>
       <c r="F68" s="2">
-        <v>4501</v>
+        <v>2290</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>15</v>
@@ -5751,7 +5745,7 @@
         <v>14</v>
       </c>
       <c r="F69" s="2">
-        <v>3560</v>
+        <v>3304</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>15</v>
@@ -5783,7 +5777,7 @@
         <v>14</v>
       </c>
       <c r="F70" s="2">
-        <v>4125</v>
+        <v>2800</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>15</v>
@@ -5815,7 +5809,7 @@
         <v>14</v>
       </c>
       <c r="F71" s="2">
-        <v>3134</v>
+        <v>3720</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>15</v>
@@ -5847,7 +5841,7 @@
         <v>14</v>
       </c>
       <c r="F72" s="2">
-        <v>3106</v>
+        <v>3612</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>15</v>
@@ -5879,7 +5873,7 @@
         <v>14</v>
       </c>
       <c r="F73" s="2">
-        <v>4191</v>
+        <v>2939</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>15</v>
@@ -5911,7 +5905,7 @@
         <v>14</v>
       </c>
       <c r="F74" s="2">
-        <v>4704</v>
+        <v>1505</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>15</v>
@@ -5943,7 +5937,7 @@
         <v>14</v>
       </c>
       <c r="F75" s="2">
-        <v>3195</v>
+        <v>2673</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>15</v>
@@ -5975,7 +5969,7 @@
         <v>14</v>
       </c>
       <c r="F76" s="2">
-        <v>1472</v>
+        <v>1061</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>15</v>
@@ -6007,7 +6001,7 @@
         <v>14</v>
       </c>
       <c r="F77" s="2">
-        <v>1671</v>
+        <v>4781</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>15</v>
@@ -6039,7 +6033,7 @@
         <v>14</v>
       </c>
       <c r="F78" s="2">
-        <v>2413</v>
+        <v>3500</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>15</v>
@@ -6071,7 +6065,7 @@
         <v>14</v>
       </c>
       <c r="F79" s="2">
-        <v>4432</v>
+        <v>3862</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>15</v>
@@ -6103,7 +6097,7 @@
         <v>14</v>
       </c>
       <c r="F80" s="2">
-        <v>2397</v>
+        <v>1119</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>15</v>
@@ -6135,7 +6129,7 @@
         <v>14</v>
       </c>
       <c r="F81" s="2">
-        <v>1438</v>
+        <v>2935</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>15</v>
@@ -6167,7 +6161,7 @@
         <v>14</v>
       </c>
       <c r="F82" s="2">
-        <v>2272</v>
+        <v>1561</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>15</v>
@@ -6199,7 +6193,7 @@
         <v>14</v>
       </c>
       <c r="F83" s="2">
-        <v>1720</v>
+        <v>1032</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>15</v>
@@ -6231,7 +6225,7 @@
         <v>14</v>
       </c>
       <c r="F84" s="2">
-        <v>1175</v>
+        <v>1353</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>15</v>
@@ -6263,7 +6257,7 @@
         <v>14</v>
       </c>
       <c r="F85" s="2">
-        <v>3218</v>
+        <v>1353</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>15</v>
@@ -6295,7 +6289,7 @@
         <v>14</v>
       </c>
       <c r="F86" s="2">
-        <v>4742</v>
+        <v>2099</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>15</v>
@@ -6327,7 +6321,7 @@
         <v>14</v>
       </c>
       <c r="F87" s="2">
-        <v>2607</v>
+        <v>1039</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>15</v>
@@ -6359,7 +6353,7 @@
         <v>14</v>
       </c>
       <c r="F88" s="2">
-        <v>3765</v>
+        <v>2316</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>15</v>
@@ -6391,7 +6385,7 @@
         <v>14</v>
       </c>
       <c r="F89" s="2">
-        <v>2910</v>
+        <v>948</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>15</v>
@@ -6423,7 +6417,7 @@
         <v>14</v>
       </c>
       <c r="F90" s="2">
-        <v>815</v>
+        <v>4289</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>15</v>
@@ -6455,7 +6449,7 @@
         <v>14</v>
       </c>
       <c r="F91" s="2">
-        <v>3618</v>
+        <v>1622</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>15</v>
@@ -6487,7 +6481,7 @@
         <v>14</v>
       </c>
       <c r="F92" s="2">
-        <v>986</v>
+        <v>1578</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>15</v>
@@ -6519,7 +6513,7 @@
         <v>14</v>
       </c>
       <c r="F93" s="2">
-        <v>1913</v>
+        <v>2989</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>15</v>
@@ -6551,7 +6545,7 @@
         <v>14</v>
       </c>
       <c r="F94" s="2">
-        <v>3078</v>
+        <v>1228</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>15</v>
@@ -6583,7 +6577,7 @@
         <v>14</v>
       </c>
       <c r="F95" s="2">
-        <v>1602</v>
+        <v>2170</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>15</v>
@@ -6615,7 +6609,7 @@
         <v>14</v>
       </c>
       <c r="F96" s="2">
-        <v>3816</v>
+        <v>3182</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>15</v>
@@ -6647,7 +6641,7 @@
         <v>14</v>
       </c>
       <c r="F97" s="2">
-        <v>1259</v>
+        <v>4059</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>15</v>
@@ -6679,7 +6673,7 @@
         <v>14</v>
       </c>
       <c r="F98" s="2">
-        <v>1054</v>
+        <v>1886</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>15</v>
@@ -6711,7 +6705,7 @@
         <v>14</v>
       </c>
       <c r="F99" s="2">
-        <v>4379</v>
+        <v>3240</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>15</v>
@@ -6743,7 +6737,7 @@
         <v>14</v>
       </c>
       <c r="F100" s="2">
-        <v>1274</v>
+        <v>3142</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>15</v>
@@ -6775,7 +6769,7 @@
         <v>14</v>
       </c>
       <c r="F101" s="2">
-        <v>2803</v>
+        <v>3776</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>15</v>
@@ -6807,7 +6801,7 @@
         <v>14</v>
       </c>
       <c r="F102" s="2">
-        <v>2948</v>
+        <v>2382</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>15</v>
@@ -6839,7 +6833,7 @@
         <v>14</v>
       </c>
       <c r="F103" s="2">
-        <v>1761</v>
+        <v>1109</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>15</v>
@@ -6871,7 +6865,7 @@
         <v>14</v>
       </c>
       <c r="F104" s="2">
-        <v>1800</v>
+        <v>1350</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>15</v>
@@ -6903,7 +6897,7 @@
         <v>14</v>
       </c>
       <c r="F105" s="2">
-        <v>3158</v>
+        <v>1307</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>15</v>
@@ -6935,7 +6929,7 @@
         <v>14</v>
       </c>
       <c r="F106" s="2">
-        <v>3397</v>
+        <v>3191</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>15</v>
@@ -6967,7 +6961,7 @@
         <v>14</v>
       </c>
       <c r="F107" s="2">
-        <v>2576</v>
+        <v>2024</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>15</v>
@@ -6999,7 +6993,7 @@
         <v>14</v>
       </c>
       <c r="F108" s="2">
-        <v>1468</v>
+        <v>2141</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>15</v>
@@ -7031,7 +7025,7 @@
         <v>14</v>
       </c>
       <c r="F109" s="2">
-        <v>1354</v>
+        <v>1115</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>15</v>
@@ -7063,7 +7057,7 @@
         <v>14</v>
       </c>
       <c r="F110" s="2">
-        <v>4128</v>
+        <v>3138</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>15</v>
@@ -7095,7 +7089,7 @@
         <v>14</v>
       </c>
       <c r="F111" s="2">
-        <v>4713</v>
+        <v>2260</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>15</v>
@@ -7127,7 +7121,7 @@
         <v>14</v>
       </c>
       <c r="F112" s="2">
-        <v>3288</v>
+        <v>1384</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>15</v>
@@ -7159,7 +7153,7 @@
         <v>14</v>
       </c>
       <c r="F113" s="2">
-        <v>1502</v>
+        <v>3180</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>15</v>
@@ -7191,7 +7185,7 @@
         <v>14</v>
       </c>
       <c r="F114" s="2">
-        <v>3414</v>
+        <v>1175</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>15</v>
@@ -7223,7 +7217,7 @@
         <v>14</v>
       </c>
       <c r="F115" s="2">
-        <v>1284</v>
+        <v>2537</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>15</v>
@@ -7255,7 +7249,7 @@
         <v>14</v>
       </c>
       <c r="F116" s="2">
-        <v>1015</v>
+        <v>1810</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>15</v>
@@ -7287,7 +7281,7 @@
         <v>14</v>
       </c>
       <c r="F117" s="2">
-        <v>1420</v>
+        <v>4275</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>15</v>
@@ -7319,7 +7313,7 @@
         <v>14</v>
       </c>
       <c r="F118" s="2">
-        <v>2613</v>
+        <v>4538</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>15</v>
@@ -7351,7 +7345,7 @@
         <v>14</v>
       </c>
       <c r="F119" s="2">
-        <v>3250</v>
+        <v>2133</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>15</v>
@@ -7383,7 +7377,7 @@
         <v>14</v>
       </c>
       <c r="F120" s="2">
-        <v>861</v>
+        <v>2883</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>15</v>
@@ -7415,7 +7409,7 @@
         <v>14</v>
       </c>
       <c r="F121" s="2">
-        <v>4711</v>
+        <v>2959</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>15</v>
@@ -7447,7 +7441,7 @@
         <v>14</v>
       </c>
       <c r="F122" s="2">
-        <v>3991</v>
+        <v>902</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>15</v>
@@ -7479,7 +7473,7 @@
         <v>14</v>
       </c>
       <c r="F123" s="2">
-        <v>4485</v>
+        <v>3496</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>15</v>
@@ -7511,7 +7505,7 @@
         <v>14</v>
       </c>
       <c r="F124" s="2">
-        <v>962</v>
+        <v>2788</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>15</v>
@@ -7543,7 +7537,7 @@
         <v>14</v>
       </c>
       <c r="F125" s="2">
-        <v>3175</v>
+        <v>1325</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>15</v>
@@ -7575,7 +7569,7 @@
         <v>14</v>
       </c>
       <c r="F126" s="2">
-        <v>2493</v>
+        <v>3627</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>15</v>
@@ -7607,7 +7601,7 @@
         <v>14</v>
       </c>
       <c r="F127" s="2">
-        <v>4383</v>
+        <v>2597</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>15</v>
@@ -7639,7 +7633,7 @@
         <v>14</v>
       </c>
       <c r="F128" s="2">
-        <v>2448</v>
+        <v>4125</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>15</v>
@@ -7671,7 +7665,7 @@
         <v>14</v>
       </c>
       <c r="F129" s="2">
-        <v>4335</v>
+        <v>1989</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>15</v>
@@ -7703,7 +7697,7 @@
         <v>14</v>
       </c>
       <c r="F130" s="2">
-        <v>2792</v>
+        <v>1767</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>15</v>
@@ -7735,7 +7729,7 @@
         <v>14</v>
       </c>
       <c r="F131" s="2">
-        <v>4762</v>
+        <v>1556</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>15</v>
@@ -7767,7 +7761,7 @@
         <v>14</v>
       </c>
       <c r="F132" s="2">
-        <v>4467</v>
+        <v>3417</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>15</v>
@@ -7799,7 +7793,7 @@
         <v>14</v>
       </c>
       <c r="F133" s="2">
-        <v>1659</v>
+        <v>3124</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>15</v>
@@ -7831,7 +7825,7 @@
         <v>14</v>
       </c>
       <c r="F134" s="2">
-        <v>3633</v>
+        <v>2486</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>15</v>
@@ -7863,7 +7857,7 @@
         <v>14</v>
       </c>
       <c r="F135" s="2">
-        <v>3127</v>
+        <v>1814</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>15</v>
@@ -7895,7 +7889,7 @@
         <v>14</v>
       </c>
       <c r="F136" s="2">
-        <v>2143</v>
+        <v>1404</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>15</v>
@@ -7927,7 +7921,7 @@
         <v>14</v>
       </c>
       <c r="F137" s="2">
-        <v>2254</v>
+        <v>3928</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>15</v>
@@ -7959,7 +7953,7 @@
         <v>14</v>
       </c>
       <c r="F138" s="2">
-        <v>4462</v>
+        <v>1578</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>15</v>
@@ -7991,7 +7985,7 @@
         <v>14</v>
       </c>
       <c r="F139" s="2">
-        <v>810</v>
+        <v>2511</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>15</v>
@@ -8023,7 +8017,7 @@
         <v>14</v>
       </c>
       <c r="F140" s="2">
-        <v>1113</v>
+        <v>4137</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>15</v>
@@ -8055,7 +8049,7 @@
         <v>14</v>
       </c>
       <c r="F141" s="2">
-        <v>935</v>
+        <v>4336</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>15</v>
@@ -8087,7 +8081,7 @@
         <v>14</v>
       </c>
       <c r="F142" s="2">
-        <v>1944</v>
+        <v>3949</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>15</v>
@@ -8119,7 +8113,7 @@
         <v>14</v>
       </c>
       <c r="F143" s="2">
-        <v>4773</v>
+        <v>2632</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>15</v>
@@ -8151,7 +8145,7 @@
         <v>14</v>
       </c>
       <c r="F144" s="2">
-        <v>1483</v>
+        <v>4317</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>15</v>
@@ -8183,7 +8177,7 @@
         <v>14</v>
       </c>
       <c r="F145" s="2">
-        <v>1740</v>
+        <v>1159</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>15</v>
@@ -8215,7 +8209,7 @@
         <v>14</v>
       </c>
       <c r="F146" s="2">
-        <v>1288</v>
+        <v>2252</v>
       </c>
       <c r="G146" s="2" t="s">
         <v>15</v>
@@ -8247,7 +8241,7 @@
         <v>14</v>
       </c>
       <c r="F147" s="2">
-        <v>2485</v>
+        <v>4334</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>15</v>
@@ -8279,7 +8273,7 @@
         <v>14</v>
       </c>
       <c r="F148" s="2">
-        <v>1376</v>
+        <v>852</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>15</v>
@@ -8311,7 +8305,7 @@
         <v>14</v>
       </c>
       <c r="F149" s="2">
-        <v>1032</v>
+        <v>1685</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>15</v>
@@ -8343,7 +8337,7 @@
         <v>14</v>
       </c>
       <c r="F150" s="2">
-        <v>3957</v>
+        <v>3085</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>15</v>
@@ -8375,7 +8369,7 @@
         <v>14</v>
       </c>
       <c r="F151" s="2">
-        <v>820</v>
+        <v>3563</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>15</v>
@@ -8407,7 +8401,7 @@
         <v>14</v>
       </c>
       <c r="F152" s="2">
-        <v>2648</v>
+        <v>4313</v>
       </c>
       <c r="G152" s="2" t="s">
         <v>15</v>
@@ -8439,7 +8433,7 @@
         <v>14</v>
       </c>
       <c r="F153" s="2">
-        <v>3346</v>
+        <v>4780</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>15</v>
@@ -8471,7 +8465,7 @@
         <v>14</v>
       </c>
       <c r="F154" s="2">
-        <v>2947</v>
+        <v>3373</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>15</v>
@@ -8503,7 +8497,7 @@
         <v>14</v>
       </c>
       <c r="F155" s="2">
-        <v>3881</v>
+        <v>3441</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>15</v>
@@ -8535,7 +8529,7 @@
         <v>14</v>
       </c>
       <c r="F156" s="2">
-        <v>925</v>
+        <v>3472</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>15</v>
@@ -8567,7 +8561,7 @@
         <v>14</v>
       </c>
       <c r="F157" s="2">
-        <v>2242</v>
+        <v>1661</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>15</v>
@@ -8599,7 +8593,7 @@
         <v>14</v>
       </c>
       <c r="F158" s="2">
-        <v>2471</v>
+        <v>4015</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>15</v>
@@ -8631,7 +8625,7 @@
         <v>14</v>
       </c>
       <c r="F159" s="2">
-        <v>2063</v>
+        <v>2608</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>15</v>
@@ -8663,7 +8657,7 @@
         <v>14</v>
       </c>
       <c r="F160" s="2">
-        <v>3771</v>
+        <v>4462</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>15</v>
@@ -8695,7 +8689,7 @@
         <v>14</v>
       </c>
       <c r="F161" s="2">
-        <v>2034</v>
+        <v>2903</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>15</v>
@@ -8727,7 +8721,7 @@
         <v>14</v>
       </c>
       <c r="F162" s="2">
-        <v>2230</v>
+        <v>3751</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>15</v>
@@ -8759,7 +8753,7 @@
         <v>14</v>
       </c>
       <c r="F163" s="2">
-        <v>3672</v>
+        <v>2032</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>15</v>
@@ -8791,7 +8785,7 @@
         <v>14</v>
       </c>
       <c r="F164" s="2">
-        <v>999</v>
+        <v>1521</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>15</v>
@@ -8823,7 +8817,7 @@
         <v>14</v>
       </c>
       <c r="F165" s="2">
-        <v>3444</v>
+        <v>3492</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>15</v>
@@ -8855,7 +8849,7 @@
         <v>14</v>
       </c>
       <c r="F166" s="2">
-        <v>2163</v>
+        <v>4072</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>15</v>
@@ -8887,7 +8881,7 @@
         <v>14</v>
       </c>
       <c r="F167" s="2">
-        <v>4694</v>
+        <v>1521</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>15</v>
@@ -8919,7 +8913,7 @@
         <v>14</v>
       </c>
       <c r="F168" s="2">
-        <v>3442</v>
+        <v>2070</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>15</v>
@@ -8951,7 +8945,7 @@
         <v>14</v>
       </c>
       <c r="F169" s="2">
-        <v>2894</v>
+        <v>1947</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>15</v>
@@ -8983,7 +8977,7 @@
         <v>14</v>
       </c>
       <c r="F170" s="2">
-        <v>3853</v>
+        <v>2430</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>15</v>
@@ -9015,7 +9009,7 @@
         <v>14</v>
       </c>
       <c r="F171" s="2">
-        <v>1588</v>
+        <v>4406</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>15</v>
@@ -9047,7 +9041,7 @@
         <v>14</v>
       </c>
       <c r="F172" s="2">
-        <v>4363</v>
+        <v>4757</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>15</v>
@@ -9079,7 +9073,7 @@
         <v>14</v>
       </c>
       <c r="F173" s="2">
-        <v>4297</v>
+        <v>4077</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>15</v>
@@ -9111,7 +9105,7 @@
         <v>14</v>
       </c>
       <c r="F174" s="2">
-        <v>4250</v>
+        <v>4523</v>
       </c>
       <c r="G174" s="2" t="s">
         <v>15</v>
@@ -9143,7 +9137,7 @@
         <v>14</v>
       </c>
       <c r="F175" s="2">
-        <v>2327</v>
+        <v>3214</v>
       </c>
       <c r="G175" s="2" t="s">
         <v>15</v>
@@ -9175,7 +9169,7 @@
         <v>14</v>
       </c>
       <c r="F176" s="2">
-        <v>4469</v>
+        <v>2009</v>
       </c>
       <c r="G176" s="2" t="s">
         <v>15</v>
@@ -9207,7 +9201,7 @@
         <v>14</v>
       </c>
       <c r="F177" s="2">
-        <v>4609</v>
+        <v>1529</v>
       </c>
       <c r="G177" s="2" t="s">
         <v>15</v>
@@ -9239,7 +9233,7 @@
         <v>14</v>
       </c>
       <c r="F178" s="2">
-        <v>3985</v>
+        <v>3449</v>
       </c>
       <c r="G178" s="2" t="s">
         <v>15</v>
@@ -9271,7 +9265,7 @@
         <v>14</v>
       </c>
       <c r="F179" s="2">
-        <v>1390</v>
+        <v>4166</v>
       </c>
       <c r="G179" s="2" t="s">
         <v>15</v>
@@ -9303,7 +9297,7 @@
         <v>14</v>
       </c>
       <c r="F180" s="2">
-        <v>1346</v>
+        <v>2803</v>
       </c>
       <c r="G180" s="2" t="s">
         <v>15</v>
@@ -9335,7 +9329,7 @@
         <v>14</v>
       </c>
       <c r="F181" s="2">
-        <v>1497</v>
+        <v>4730</v>
       </c>
       <c r="G181" s="2" t="s">
         <v>15</v>
@@ -9367,7 +9361,7 @@
         <v>14</v>
       </c>
       <c r="F182" s="2">
-        <v>2437</v>
+        <v>2136</v>
       </c>
       <c r="G182" s="2" t="s">
         <v>15</v>
@@ -9399,7 +9393,7 @@
         <v>14</v>
       </c>
       <c r="F183" s="2">
-        <v>2090</v>
+        <v>3114</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>15</v>
@@ -9431,7 +9425,7 @@
         <v>14</v>
       </c>
       <c r="F184" s="2">
-        <v>2063</v>
+        <v>4197</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>15</v>
@@ -9463,7 +9457,7 @@
         <v>14</v>
       </c>
       <c r="F185" s="2">
-        <v>4663</v>
+        <v>3632</v>
       </c>
       <c r="G185" s="2" t="s">
         <v>15</v>
@@ -9495,7 +9489,7 @@
         <v>14</v>
       </c>
       <c r="F186" s="2">
-        <v>4323</v>
+        <v>2447</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>15</v>
@@ -9527,7 +9521,7 @@
         <v>14</v>
       </c>
       <c r="F187" s="2">
-        <v>4749</v>
+        <v>4336</v>
       </c>
       <c r="G187" s="2" t="s">
         <v>15</v>
@@ -9559,7 +9553,7 @@
         <v>14</v>
       </c>
       <c r="F188" s="2">
-        <v>2363</v>
+        <v>4277</v>
       </c>
       <c r="G188" s="2" t="s">
         <v>15</v>
@@ -9591,7 +9585,7 @@
         <v>14</v>
       </c>
       <c r="F189" s="2">
-        <v>2362</v>
+        <v>3617</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>15</v>
@@ -9623,7 +9617,7 @@
         <v>14</v>
       </c>
       <c r="F190" s="2">
-        <v>3670</v>
+        <v>3226</v>
       </c>
       <c r="G190" s="2" t="s">
         <v>15</v>
@@ -9655,7 +9649,7 @@
         <v>14</v>
       </c>
       <c r="F191" s="2">
-        <v>1314</v>
+        <v>2749</v>
       </c>
       <c r="G191" s="2" t="s">
         <v>15</v>
@@ -9687,7 +9681,7 @@
         <v>14</v>
       </c>
       <c r="F192" s="2">
-        <v>3782</v>
+        <v>4620</v>
       </c>
       <c r="G192" s="2" t="s">
         <v>15</v>
@@ -9719,7 +9713,7 @@
         <v>14</v>
       </c>
       <c r="F193" s="2">
-        <v>4541</v>
+        <v>2946</v>
       </c>
       <c r="G193" s="2" t="s">
         <v>15</v>
@@ -9751,7 +9745,7 @@
         <v>14</v>
       </c>
       <c r="F194" s="2">
-        <v>4286</v>
+        <v>1051</v>
       </c>
       <c r="G194" s="2" t="s">
         <v>15</v>
@@ -9783,7 +9777,7 @@
         <v>14</v>
       </c>
       <c r="F195" s="2">
-        <v>3146</v>
+        <v>3301</v>
       </c>
       <c r="G195" s="2" t="s">
         <v>15</v>
@@ -9815,7 +9809,7 @@
         <v>14</v>
       </c>
       <c r="F196" s="2">
-        <v>1097</v>
+        <v>3206</v>
       </c>
       <c r="G196" s="2" t="s">
         <v>15</v>
@@ -9847,7 +9841,7 @@
         <v>14</v>
       </c>
       <c r="F197" s="2">
-        <v>2125</v>
+        <v>2667</v>
       </c>
       <c r="G197" s="2" t="s">
         <v>15</v>
@@ -9879,7 +9873,7 @@
         <v>14</v>
       </c>
       <c r="F198" s="2">
-        <v>1346</v>
+        <v>2543</v>
       </c>
       <c r="G198" s="2" t="s">
         <v>15</v>
@@ -9911,7 +9905,7 @@
         <v>14</v>
       </c>
       <c r="F199" s="2">
-        <v>4650</v>
+        <v>869</v>
       </c>
       <c r="G199" s="2" t="s">
         <v>15</v>
@@ -9943,7 +9937,7 @@
         <v>14</v>
       </c>
       <c r="F200" s="2">
-        <v>2897</v>
+        <v>4288</v>
       </c>
       <c r="G200" s="2" t="s">
         <v>15</v>
@@ -9975,7 +9969,7 @@
         <v>14</v>
       </c>
       <c r="F201" s="2">
-        <v>998</v>
+        <v>2687</v>
       </c>
       <c r="G201" s="2" t="s">
         <v>15</v>
@@ -10007,7 +10001,7 @@
         <v>14</v>
       </c>
       <c r="F202" s="2">
-        <v>2471</v>
+        <v>1244</v>
       </c>
       <c r="G202" s="2" t="s">
         <v>15</v>
@@ -10039,7 +10033,7 @@
         <v>14</v>
       </c>
       <c r="F203" s="2">
-        <v>3789</v>
+        <v>2584</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>15</v>
@@ -10071,7 +10065,7 @@
         <v>14</v>
       </c>
       <c r="F204" s="2">
-        <v>4149</v>
+        <v>900</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>15</v>
@@ -10103,7 +10097,7 @@
         <v>14</v>
       </c>
       <c r="F205" s="2">
-        <v>3862</v>
+        <v>1331</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>15</v>
@@ -10135,7 +10129,7 @@
         <v>14</v>
       </c>
       <c r="F206" s="2">
-        <v>1620</v>
+        <v>4597</v>
       </c>
       <c r="G206" s="2" t="s">
         <v>15</v>
@@ -10167,7 +10161,7 @@
         <v>14</v>
       </c>
       <c r="F207" s="2">
-        <v>3294</v>
+        <v>2234</v>
       </c>
       <c r="G207" s="2" t="s">
         <v>15</v>
@@ -10199,7 +10193,7 @@
         <v>14</v>
       </c>
       <c r="F208" s="2">
-        <v>4724</v>
+        <v>4750</v>
       </c>
       <c r="G208" s="2" t="s">
         <v>15</v>
@@ -10231,7 +10225,7 @@
         <v>14</v>
       </c>
       <c r="F209" s="2">
-        <v>3771</v>
+        <v>2336</v>
       </c>
       <c r="G209" s="2" t="s">
         <v>15</v>
@@ -10263,7 +10257,7 @@
         <v>14</v>
       </c>
       <c r="F210" s="2">
-        <v>1547</v>
+        <v>961</v>
       </c>
       <c r="G210" s="2" t="s">
         <v>15</v>
@@ -10295,7 +10289,7 @@
         <v>14</v>
       </c>
       <c r="F211" s="2">
-        <v>2393</v>
+        <v>4540</v>
       </c>
       <c r="G211" s="2" t="s">
         <v>15</v>
@@ -10327,7 +10321,7 @@
         <v>14</v>
       </c>
       <c r="F212" s="2">
-        <v>3884</v>
+        <v>2357</v>
       </c>
       <c r="G212" s="2" t="s">
         <v>15</v>
@@ -10359,7 +10353,7 @@
         <v>14</v>
       </c>
       <c r="F213" s="2">
-        <v>1206</v>
+        <v>4134</v>
       </c>
       <c r="G213" s="2" t="s">
         <v>15</v>
@@ -10391,7 +10385,7 @@
         <v>14</v>
       </c>
       <c r="F214" s="2">
-        <v>1219</v>
+        <v>1352</v>
       </c>
       <c r="G214" s="2" t="s">
         <v>15</v>
@@ -10423,7 +10417,7 @@
         <v>14</v>
       </c>
       <c r="F215" s="2">
-        <v>4412</v>
+        <v>2546</v>
       </c>
       <c r="G215" s="2" t="s">
         <v>15</v>
@@ -10455,7 +10449,7 @@
         <v>14</v>
       </c>
       <c r="F216" s="2">
-        <v>2103</v>
+        <v>2160</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>15</v>
@@ -10487,7 +10481,7 @@
         <v>14</v>
       </c>
       <c r="F217" s="2">
-        <v>3549</v>
+        <v>963</v>
       </c>
       <c r="G217" s="2" t="s">
         <v>15</v>
@@ -10519,7 +10513,7 @@
         <v>14</v>
       </c>
       <c r="F218" s="2">
-        <v>4733</v>
+        <v>3333</v>
       </c>
       <c r="G218" s="2" t="s">
         <v>15</v>
@@ -10551,7 +10545,7 @@
         <v>14</v>
       </c>
       <c r="F219" s="2">
-        <v>2348</v>
+        <v>4758</v>
       </c>
       <c r="G219" s="2" t="s">
         <v>15</v>
@@ -10583,7 +10577,7 @@
         <v>14</v>
       </c>
       <c r="F220" s="2">
-        <v>4617</v>
+        <v>4434</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>15</v>
@@ -10615,7 +10609,7 @@
         <v>14</v>
       </c>
       <c r="F221" s="2">
-        <v>3041</v>
+        <v>3774</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>15</v>
@@ -10647,7 +10641,7 @@
         <v>14</v>
       </c>
       <c r="F222" s="2">
-        <v>4502</v>
+        <v>2010</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>15</v>
@@ -10679,7 +10673,7 @@
         <v>14</v>
       </c>
       <c r="F223" s="2">
-        <v>4086</v>
+        <v>1330</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>15</v>
@@ -10711,7 +10705,7 @@
         <v>14</v>
       </c>
       <c r="F224" s="2">
-        <v>4012</v>
+        <v>3665</v>
       </c>
       <c r="G224" s="2" t="s">
         <v>15</v>
@@ -10743,7 +10737,7 @@
         <v>14</v>
       </c>
       <c r="F225" s="2">
-        <v>2414</v>
+        <v>4365</v>
       </c>
       <c r="G225" s="2" t="s">
         <v>15</v>
@@ -10775,7 +10769,7 @@
         <v>14</v>
       </c>
       <c r="F226" s="2">
-        <v>3980</v>
+        <v>1460</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>15</v>
@@ -10807,7 +10801,7 @@
         <v>14</v>
       </c>
       <c r="F227" s="2">
-        <v>2527</v>
+        <v>2277</v>
       </c>
       <c r="G227" s="2" t="s">
         <v>15</v>
@@ -10839,7 +10833,7 @@
         <v>14</v>
       </c>
       <c r="F228" s="2">
-        <v>1888</v>
+        <v>1021</v>
       </c>
       <c r="G228" s="2" t="s">
         <v>15</v>
@@ -10871,7 +10865,7 @@
         <v>14</v>
       </c>
       <c r="F229" s="2">
-        <v>1758</v>
+        <v>2507</v>
       </c>
       <c r="G229" s="2" t="s">
         <v>15</v>
@@ -10903,7 +10897,7 @@
         <v>14</v>
       </c>
       <c r="F230" s="2">
-        <v>1950</v>
+        <v>2323</v>
       </c>
       <c r="G230" s="2" t="s">
         <v>15</v>
@@ -10935,7 +10929,7 @@
         <v>14</v>
       </c>
       <c r="F231" s="2">
-        <v>2309</v>
+        <v>1547</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>15</v>
@@ -10967,7 +10961,7 @@
         <v>14</v>
       </c>
       <c r="F232" s="2">
-        <v>1530</v>
+        <v>4154</v>
       </c>
       <c r="G232" s="2" t="s">
         <v>15</v>
@@ -10999,7 +10993,7 @@
         <v>14</v>
       </c>
       <c r="F233" s="2">
-        <v>3991</v>
+        <v>2503</v>
       </c>
       <c r="G233" s="2" t="s">
         <v>15</v>
@@ -11031,7 +11025,7 @@
         <v>14</v>
       </c>
       <c r="F234" s="2">
-        <v>4044</v>
+        <v>3448</v>
       </c>
       <c r="G234" s="2" t="s">
         <v>15</v>
@@ -11063,7 +11057,7 @@
         <v>14</v>
       </c>
       <c r="F235" s="2">
-        <v>2978</v>
+        <v>1404</v>
       </c>
       <c r="G235" s="2" t="s">
         <v>15</v>
@@ -11095,7 +11089,7 @@
         <v>14</v>
       </c>
       <c r="F236" s="2">
-        <v>4613</v>
+        <v>808</v>
       </c>
       <c r="G236" s="2" t="s">
         <v>15</v>
@@ -11127,7 +11121,7 @@
         <v>14</v>
       </c>
       <c r="F237" s="2">
-        <v>1125</v>
+        <v>2729</v>
       </c>
       <c r="G237" s="2" t="s">
         <v>15</v>
@@ -11159,7 +11153,7 @@
         <v>14</v>
       </c>
       <c r="F238" s="2">
-        <v>2895</v>
+        <v>1060</v>
       </c>
       <c r="G238" s="2" t="s">
         <v>15</v>
@@ -11191,7 +11185,7 @@
         <v>14</v>
       </c>
       <c r="F239" s="2">
-        <v>1685</v>
+        <v>2753</v>
       </c>
       <c r="G239" s="2" t="s">
         <v>15</v>
@@ -11223,7 +11217,7 @@
         <v>14</v>
       </c>
       <c r="F240" s="2">
-        <v>2957</v>
+        <v>3516</v>
       </c>
       <c r="G240" s="2" t="s">
         <v>15</v>
@@ -11255,7 +11249,7 @@
         <v>14</v>
       </c>
       <c r="F241" s="2">
-        <v>4516</v>
+        <v>4778</v>
       </c>
       <c r="G241" s="2" t="s">
         <v>15</v>
@@ -11287,7 +11281,7 @@
         <v>14</v>
       </c>
       <c r="F242" s="2">
-        <v>925</v>
+        <v>3434</v>
       </c>
       <c r="G242" s="2" t="s">
         <v>15</v>
@@ -11319,7 +11313,7 @@
         <v>14</v>
       </c>
       <c r="F243" s="2">
-        <v>3823</v>
+        <v>3187</v>
       </c>
       <c r="G243" s="2" t="s">
         <v>15</v>
@@ -11351,7 +11345,7 @@
         <v>14</v>
       </c>
       <c r="F244" s="2">
-        <v>4783</v>
+        <v>3387</v>
       </c>
       <c r="G244" s="2" t="s">
         <v>15</v>
@@ -11383,7 +11377,7 @@
         <v>14</v>
       </c>
       <c r="F245" s="2">
-        <v>1335</v>
+        <v>3258</v>
       </c>
       <c r="G245" s="2" t="s">
         <v>15</v>
@@ -11415,7 +11409,7 @@
         <v>14</v>
       </c>
       <c r="F246" s="2">
-        <v>4099</v>
+        <v>1382</v>
       </c>
       <c r="G246" s="2" t="s">
         <v>15</v>
@@ -11447,7 +11441,7 @@
         <v>14</v>
       </c>
       <c r="F247" s="2">
-        <v>1469</v>
+        <v>4558</v>
       </c>
       <c r="G247" s="2" t="s">
         <v>15</v>
@@ -11479,7 +11473,7 @@
         <v>14</v>
       </c>
       <c r="F248" s="2">
-        <v>3399</v>
+        <v>3086</v>
       </c>
       <c r="G248" s="2" t="s">
         <v>15</v>
@@ -11511,7 +11505,7 @@
         <v>14</v>
       </c>
       <c r="F249" s="2">
-        <v>3351</v>
+        <v>2447</v>
       </c>
       <c r="G249" s="2" t="s">
         <v>15</v>
@@ -11543,7 +11537,7 @@
         <v>14</v>
       </c>
       <c r="F250" s="2">
-        <v>2661</v>
+        <v>2425</v>
       </c>
       <c r="G250" s="2" t="s">
         <v>15</v>
@@ -11575,7 +11569,7 @@
         <v>14</v>
       </c>
       <c r="F251" s="2">
-        <v>2127</v>
+        <v>1027</v>
       </c>
       <c r="G251" s="2" t="s">
         <v>15</v>
@@ -11607,7 +11601,7 @@
         <v>14</v>
       </c>
       <c r="F252" s="2">
-        <v>3504</v>
+        <v>4737</v>
       </c>
       <c r="G252" s="2" t="s">
         <v>15</v>
@@ -11639,7 +11633,7 @@
         <v>14</v>
       </c>
       <c r="F253" s="2">
-        <v>2838</v>
+        <v>3855</v>
       </c>
       <c r="G253" s="2" t="s">
         <v>15</v>
@@ -11671,7 +11665,7 @@
         <v>14</v>
       </c>
       <c r="F254" s="2">
-        <v>1541</v>
+        <v>3756</v>
       </c>
       <c r="G254" s="2" t="s">
         <v>15</v>
@@ -11703,7 +11697,7 @@
         <v>14</v>
       </c>
       <c r="F255" s="2">
-        <v>2303</v>
+        <v>810</v>
       </c>
       <c r="G255" s="2" t="s">
         <v>15</v>
@@ -11735,7 +11729,7 @@
         <v>14</v>
       </c>
       <c r="F256" s="2">
-        <v>4435</v>
+        <v>1571</v>
       </c>
       <c r="G256" s="2" t="s">
         <v>15</v>
@@ -11767,7 +11761,7 @@
         <v>14</v>
       </c>
       <c r="F257" s="2">
-        <v>4695</v>
+        <v>1393</v>
       </c>
       <c r="G257" s="2" t="s">
         <v>15</v>
@@ -11799,7 +11793,7 @@
         <v>14</v>
       </c>
       <c r="F258" s="2">
-        <v>2667</v>
+        <v>1065</v>
       </c>
       <c r="G258" s="2" t="s">
         <v>15</v>
@@ -11831,7 +11825,7 @@
         <v>14</v>
       </c>
       <c r="F259" s="2">
-        <v>2269</v>
+        <v>4754</v>
       </c>
       <c r="G259" s="2" t="s">
         <v>15</v>
@@ -11863,7 +11857,7 @@
         <v>14</v>
       </c>
       <c r="F260" s="2">
-        <v>1099</v>
+        <v>2996</v>
       </c>
       <c r="G260" s="2" t="s">
         <v>15</v>
@@ -11895,7 +11889,7 @@
         <v>14</v>
       </c>
       <c r="F261" s="2">
-        <v>4432</v>
+        <v>1046</v>
       </c>
       <c r="G261" s="2" t="s">
         <v>15</v>
@@ -11927,7 +11921,7 @@
         <v>14</v>
       </c>
       <c r="F262" s="2">
-        <v>1494</v>
+        <v>4727</v>
       </c>
       <c r="G262" s="2" t="s">
         <v>15</v>
@@ -11959,7 +11953,7 @@
         <v>14</v>
       </c>
       <c r="F263" s="2">
-        <v>2424</v>
+        <v>4471</v>
       </c>
       <c r="G263" s="2" t="s">
         <v>15</v>
@@ -11991,7 +11985,7 @@
         <v>14</v>
       </c>
       <c r="F264" s="2">
-        <v>4345</v>
+        <v>2581</v>
       </c>
       <c r="G264" s="2" t="s">
         <v>15</v>
@@ -12023,7 +12017,7 @@
         <v>14</v>
       </c>
       <c r="F265" s="2">
-        <v>2886</v>
+        <v>864</v>
       </c>
       <c r="G265" s="2" t="s">
         <v>15</v>
@@ -12055,7 +12049,7 @@
         <v>14</v>
       </c>
       <c r="F266" s="2">
-        <v>4340</v>
+        <v>1489</v>
       </c>
       <c r="G266" s="2" t="s">
         <v>15</v>
@@ -12087,7 +12081,7 @@
         <v>14</v>
       </c>
       <c r="F267" s="2">
-        <v>1643</v>
+        <v>4662</v>
       </c>
       <c r="G267" s="2" t="s">
         <v>15</v>
@@ -12119,7 +12113,7 @@
         <v>14</v>
       </c>
       <c r="F268" s="2">
-        <v>850</v>
+        <v>3946</v>
       </c>
       <c r="G268" s="2" t="s">
         <v>15</v>
@@ -12151,7 +12145,7 @@
         <v>14</v>
       </c>
       <c r="F269" s="2">
-        <v>4388</v>
+        <v>1040</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>15</v>
@@ -12183,7 +12177,7 @@
         <v>14</v>
       </c>
       <c r="F270" s="2">
-        <v>4741</v>
+        <v>2190</v>
       </c>
       <c r="G270" s="2" t="s">
         <v>15</v>
@@ -12215,7 +12209,7 @@
         <v>14</v>
       </c>
       <c r="F271" s="2">
-        <v>1073</v>
+        <v>1139</v>
       </c>
       <c r="G271" s="2" t="s">
         <v>15</v>
@@ -12247,7 +12241,7 @@
         <v>14</v>
       </c>
       <c r="F272" s="2">
-        <v>2539</v>
+        <v>1466</v>
       </c>
       <c r="G272" s="2" t="s">
         <v>15</v>
@@ -12279,7 +12273,7 @@
         <v>14</v>
       </c>
       <c r="F273" s="2">
-        <v>3342</v>
+        <v>1500</v>
       </c>
       <c r="G273" s="2" t="s">
         <v>15</v>
@@ -12311,7 +12305,7 @@
         <v>14</v>
       </c>
       <c r="F274" s="2">
-        <v>2948</v>
+        <v>2191</v>
       </c>
       <c r="G274" s="2" t="s">
         <v>15</v>
@@ -12343,7 +12337,7 @@
         <v>14</v>
       </c>
       <c r="F275" s="2">
-        <v>3743</v>
+        <v>4675</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>15</v>
@@ -12375,7 +12369,7 @@
         <v>14</v>
       </c>
       <c r="F276" s="2">
-        <v>2183</v>
+        <v>1760</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>15</v>
@@ -12407,7 +12401,7 @@
         <v>14</v>
       </c>
       <c r="F277" s="2">
-        <v>2051</v>
+        <v>3307</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>15</v>
@@ -12439,7 +12433,7 @@
         <v>14</v>
       </c>
       <c r="F278" s="2">
-        <v>3914</v>
+        <v>3276</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>15</v>
@@ -12471,7 +12465,7 @@
         <v>14</v>
       </c>
       <c r="F279" s="2">
-        <v>1181</v>
+        <v>1646</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>15</v>
@@ -12503,7 +12497,7 @@
         <v>14</v>
       </c>
       <c r="F280" s="2">
-        <v>1607</v>
+        <v>2557</v>
       </c>
       <c r="G280" s="2" t="s">
         <v>15</v>
@@ -12535,7 +12529,7 @@
         <v>14</v>
       </c>
       <c r="F281" s="2">
-        <v>1599</v>
+        <v>848</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>15</v>
@@ -12567,7 +12561,7 @@
         <v>14</v>
       </c>
       <c r="F282" s="2">
-        <v>2316</v>
+        <v>1593</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>15</v>
@@ -12599,7 +12593,7 @@
         <v>14</v>
       </c>
       <c r="F283" s="2">
-        <v>4359</v>
+        <v>3323</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>15</v>
@@ -12631,7 +12625,7 @@
         <v>14</v>
       </c>
       <c r="F284" s="2">
-        <v>3382</v>
+        <v>4342</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>15</v>
@@ -12663,7 +12657,7 @@
         <v>14</v>
       </c>
       <c r="F285" s="2">
-        <v>4169</v>
+        <v>1283</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>15</v>
@@ -12695,7 +12689,7 @@
         <v>14</v>
       </c>
       <c r="F286" s="2">
-        <v>2732</v>
+        <v>4303</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>15</v>
@@ -12727,7 +12721,7 @@
         <v>14</v>
       </c>
       <c r="F287" s="2">
-        <v>3281</v>
+        <v>2164</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>15</v>
@@ -12759,7 +12753,7 @@
         <v>14</v>
       </c>
       <c r="F288" s="2">
-        <v>4667</v>
+        <v>2351</v>
       </c>
       <c r="G288" s="2" t="s">
         <v>15</v>
@@ -12791,7 +12785,7 @@
         <v>14</v>
       </c>
       <c r="F289" s="2">
-        <v>4377</v>
+        <v>4096</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>15</v>
@@ -12823,7 +12817,7 @@
         <v>14</v>
       </c>
       <c r="F290" s="2">
-        <v>4130</v>
+        <v>1969</v>
       </c>
       <c r="G290" s="2" t="s">
         <v>15</v>
@@ -12855,7 +12849,7 @@
         <v>14</v>
       </c>
       <c r="F291" s="2">
-        <v>3151</v>
+        <v>1407</v>
       </c>
       <c r="G291" s="2" t="s">
         <v>15</v>
@@ -12887,7 +12881,7 @@
         <v>14</v>
       </c>
       <c r="F292" s="2">
-        <v>1954</v>
+        <v>3774</v>
       </c>
       <c r="G292" s="2" t="s">
         <v>15</v>
@@ -12919,7 +12913,7 @@
         <v>14</v>
       </c>
       <c r="F293" s="2">
-        <v>2112</v>
+        <v>1455</v>
       </c>
       <c r="G293" s="2" t="s">
         <v>15</v>
@@ -12951,7 +12945,7 @@
         <v>14</v>
       </c>
       <c r="F294" s="2">
-        <v>4415</v>
+        <v>4397</v>
       </c>
       <c r="G294" s="2" t="s">
         <v>15</v>
@@ -12983,7 +12977,7 @@
         <v>14</v>
       </c>
       <c r="F295" s="2">
-        <v>1216</v>
+        <v>3980</v>
       </c>
       <c r="G295" s="2" t="s">
         <v>15</v>
@@ -13015,7 +13009,7 @@
         <v>14</v>
       </c>
       <c r="F296" s="2">
-        <v>3046</v>
+        <v>3857</v>
       </c>
       <c r="G296" s="2" t="s">
         <v>15</v>
@@ -13047,7 +13041,7 @@
         <v>14</v>
       </c>
       <c r="F297" s="2">
-        <v>893</v>
+        <v>1141</v>
       </c>
       <c r="G297" s="2" t="s">
         <v>15</v>
@@ -13079,7 +13073,7 @@
         <v>14</v>
       </c>
       <c r="F298" s="2">
-        <v>2486</v>
+        <v>3478</v>
       </c>
       <c r="G298" s="2" t="s">
         <v>15</v>
@@ -13111,7 +13105,7 @@
         <v>14</v>
       </c>
       <c r="F299" s="2">
-        <v>4583</v>
+        <v>944</v>
       </c>
       <c r="G299" s="2" t="s">
         <v>15</v>
@@ -13143,7 +13137,7 @@
         <v>14</v>
       </c>
       <c r="F300" s="2">
-        <v>2338</v>
+        <v>3936</v>
       </c>
       <c r="G300" s="2" t="s">
         <v>15</v>
@@ -13175,7 +13169,7 @@
         <v>14</v>
       </c>
       <c r="F301" s="2">
-        <v>965</v>
+        <v>1904</v>
       </c>
       <c r="G301" s="2" t="s">
         <v>15</v>
@@ -13207,7 +13201,7 @@
         <v>14</v>
       </c>
       <c r="F302" s="2">
-        <v>1324</v>
+        <v>3637</v>
       </c>
       <c r="G302" s="2" t="s">
         <v>15</v>
@@ -13239,7 +13233,7 @@
         <v>14</v>
       </c>
       <c r="F303" s="2">
-        <v>2451</v>
+        <v>3904</v>
       </c>
       <c r="G303" s="2" t="s">
         <v>15</v>
@@ -13271,7 +13265,7 @@
         <v>14</v>
       </c>
       <c r="F304" s="2">
-        <v>4213</v>
+        <v>1539</v>
       </c>
       <c r="G304" s="2" t="s">
         <v>15</v>
@@ -13303,7 +13297,7 @@
         <v>14</v>
       </c>
       <c r="F305" s="2">
-        <v>3647</v>
+        <v>2509</v>
       </c>
       <c r="G305" s="2" t="s">
         <v>15</v>
@@ -13335,7 +13329,7 @@
         <v>14</v>
       </c>
       <c r="F306" s="2">
-        <v>1684</v>
+        <v>2019</v>
       </c>
       <c r="G306" s="2" t="s">
         <v>15</v>
@@ -13367,7 +13361,7 @@
         <v>14</v>
       </c>
       <c r="F307" s="2">
-        <v>1670</v>
+        <v>1266</v>
       </c>
       <c r="G307" s="2" t="s">
         <v>15</v>
@@ -13399,7 +13393,7 @@
         <v>14</v>
       </c>
       <c r="F308" s="2">
-        <v>2367</v>
+        <v>2105</v>
       </c>
       <c r="G308" s="2" t="s">
         <v>15</v>
@@ -13431,7 +13425,7 @@
         <v>14</v>
       </c>
       <c r="F309" s="2">
-        <v>1288</v>
+        <v>3067</v>
       </c>
       <c r="G309" s="2" t="s">
         <v>15</v>
@@ -13463,7 +13457,7 @@
         <v>14</v>
       </c>
       <c r="F310" s="2">
-        <v>3300</v>
+        <v>1085</v>
       </c>
       <c r="G310" s="2" t="s">
         <v>15</v>
@@ -13495,7 +13489,7 @@
         <v>14</v>
       </c>
       <c r="F311" s="2">
-        <v>3415</v>
+        <v>4028</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>15</v>
@@ -13527,7 +13521,7 @@
         <v>14</v>
       </c>
       <c r="F312" s="2">
-        <v>3792</v>
+        <v>3577</v>
       </c>
       <c r="G312" s="2" t="s">
         <v>15</v>
@@ -13559,7 +13553,7 @@
         <v>14</v>
       </c>
       <c r="F313" s="2">
-        <v>1274</v>
+        <v>2187</v>
       </c>
       <c r="G313" s="2" t="s">
         <v>15</v>
@@ -13591,7 +13585,7 @@
         <v>14</v>
       </c>
       <c r="F314" s="2">
-        <v>1771</v>
+        <v>4572</v>
       </c>
       <c r="G314" s="2" t="s">
         <v>15</v>
@@ -13623,7 +13617,7 @@
         <v>14</v>
       </c>
       <c r="F315" s="2">
-        <v>4733</v>
+        <v>3242</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>15</v>
@@ -13655,7 +13649,7 @@
         <v>14</v>
       </c>
       <c r="F316" s="2">
-        <v>3435</v>
+        <v>3690</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>15</v>
@@ -13687,7 +13681,7 @@
         <v>14</v>
       </c>
       <c r="F317" s="2">
-        <v>1603</v>
+        <v>2733</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>15</v>
@@ -13719,7 +13713,7 @@
         <v>14</v>
       </c>
       <c r="F318" s="2">
-        <v>2956</v>
+        <v>1958</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>15</v>
@@ -13751,7 +13745,7 @@
         <v>14</v>
       </c>
       <c r="F319" s="2">
-        <v>3276</v>
+        <v>4379</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>15</v>
@@ -13783,7 +13777,7 @@
         <v>14</v>
       </c>
       <c r="F320" s="2">
-        <v>3215</v>
+        <v>4308</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>15</v>
@@ -13815,7 +13809,7 @@
         <v>14</v>
       </c>
       <c r="F321" s="2">
-        <v>4657</v>
+        <v>1194</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>15</v>
@@ -13847,7 +13841,7 @@
         <v>14</v>
       </c>
       <c r="F322" s="2">
-        <v>2210</v>
+        <v>4601</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>15</v>
@@ -13879,7 +13873,7 @@
         <v>14</v>
       </c>
       <c r="F323" s="2">
-        <v>2967</v>
+        <v>1397</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>15</v>
@@ -13911,7 +13905,7 @@
         <v>14</v>
       </c>
       <c r="F324" s="2">
-        <v>3405</v>
+        <v>964</v>
       </c>
       <c r="G324" s="2" t="s">
         <v>15</v>
@@ -13943,7 +13937,7 @@
         <v>14</v>
       </c>
       <c r="F325" s="2">
-        <v>4135</v>
+        <v>4190</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>15</v>
@@ -13975,7 +13969,7 @@
         <v>14</v>
       </c>
       <c r="F326" s="2">
-        <v>1862</v>
+        <v>3048</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>15</v>
@@ -14007,7 +14001,7 @@
         <v>14</v>
       </c>
       <c r="F327" s="2">
-        <v>2324</v>
+        <v>4088</v>
       </c>
       <c r="G327" s="2" t="s">
         <v>15</v>
@@ -14039,7 +14033,7 @@
         <v>14</v>
       </c>
       <c r="F328" s="2">
-        <v>2599</v>
+        <v>4479</v>
       </c>
       <c r="G328" s="2" t="s">
         <v>15</v>
@@ -14071,7 +14065,7 @@
         <v>14</v>
       </c>
       <c r="F329" s="2">
-        <v>4183</v>
+        <v>1165</v>
       </c>
       <c r="G329" s="2" t="s">
         <v>15</v>
@@ -14103,7 +14097,7 @@
         <v>14</v>
       </c>
       <c r="F330" s="2">
-        <v>1495</v>
+        <v>3023</v>
       </c>
       <c r="G330" s="2" t="s">
         <v>15</v>
@@ -14135,7 +14129,7 @@
         <v>14</v>
       </c>
       <c r="F331" s="2">
-        <v>3278</v>
+        <v>2526</v>
       </c>
       <c r="G331" s="2" t="s">
         <v>15</v>
@@ -14167,7 +14161,7 @@
         <v>14</v>
       </c>
       <c r="F332" s="2">
-        <v>3538</v>
+        <v>3121</v>
       </c>
       <c r="G332" s="2" t="s">
         <v>15</v>
@@ -14199,7 +14193,7 @@
         <v>14</v>
       </c>
       <c r="F333" s="2">
-        <v>3043</v>
+        <v>4367</v>
       </c>
       <c r="G333" s="2" t="s">
         <v>15</v>
@@ -14231,7 +14225,7 @@
         <v>14</v>
       </c>
       <c r="F334" s="2">
-        <v>2287</v>
+        <v>2689</v>
       </c>
       <c r="G334" s="2" t="s">
         <v>15</v>
@@ -14263,7 +14257,7 @@
         <v>14</v>
       </c>
       <c r="F335" s="2">
-        <v>1486</v>
+        <v>3178</v>
       </c>
       <c r="G335" s="2" t="s">
         <v>15</v>
@@ -14295,7 +14289,7 @@
         <v>14</v>
       </c>
       <c r="F336" s="2">
-        <v>1892</v>
+        <v>1294</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>15</v>
@@ -14327,7 +14321,7 @@
         <v>14</v>
       </c>
       <c r="F337" s="2">
-        <v>1918</v>
+        <v>2394</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>15</v>
@@ -14359,7 +14353,7 @@
         <v>14</v>
       </c>
       <c r="F338" s="2">
-        <v>3334</v>
+        <v>3449</v>
       </c>
       <c r="G338" s="2" t="s">
         <v>15</v>
@@ -14391,7 +14385,7 @@
         <v>14</v>
       </c>
       <c r="F339" s="2">
-        <v>1792</v>
+        <v>3341</v>
       </c>
       <c r="G339" s="2" t="s">
         <v>15</v>
@@ -14423,7 +14417,7 @@
         <v>14</v>
       </c>
       <c r="F340" s="2">
-        <v>954</v>
+        <v>3243</v>
       </c>
       <c r="G340" s="2" t="s">
         <v>15</v>
@@ -14455,7 +14449,7 @@
         <v>14</v>
       </c>
       <c r="F341" s="2">
-        <v>2967</v>
+        <v>3812</v>
       </c>
       <c r="G341" s="2" t="s">
         <v>15</v>
@@ -14487,7 +14481,7 @@
         <v>14</v>
       </c>
       <c r="F342" s="2">
-        <v>2339</v>
+        <v>3297</v>
       </c>
       <c r="G342" s="2" t="s">
         <v>15</v>
@@ -14519,7 +14513,7 @@
         <v>14</v>
       </c>
       <c r="F343" s="2">
-        <v>2931</v>
+        <v>2021</v>
       </c>
       <c r="G343" s="2" t="s">
         <v>15</v>
@@ -14551,7 +14545,7 @@
         <v>14</v>
       </c>
       <c r="F344" s="2">
-        <v>3210</v>
+        <v>2728</v>
       </c>
       <c r="G344" s="2" t="s">
         <v>15</v>
@@ -14583,7 +14577,7 @@
         <v>14</v>
       </c>
       <c r="F345" s="2">
-        <v>4194</v>
+        <v>4033</v>
       </c>
       <c r="G345" s="2" t="s">
         <v>15</v>
@@ -14615,7 +14609,7 @@
         <v>14</v>
       </c>
       <c r="F346" s="2">
-        <v>2515</v>
+        <v>1728</v>
       </c>
       <c r="G346" s="2" t="s">
         <v>15</v>
@@ -14647,7 +14641,7 @@
         <v>14</v>
       </c>
       <c r="F347" s="2">
-        <v>3933</v>
+        <v>4114</v>
       </c>
       <c r="G347" s="2" t="s">
         <v>15</v>
@@ -14679,7 +14673,7 @@
         <v>14</v>
       </c>
       <c r="F348" s="2">
-        <v>2972</v>
+        <v>914</v>
       </c>
       <c r="G348" s="2" t="s">
         <v>15</v>
@@ -14711,7 +14705,7 @@
         <v>14</v>
       </c>
       <c r="F349" s="2">
-        <v>3530</v>
+        <v>1251</v>
       </c>
       <c r="G349" s="2" t="s">
         <v>15</v>
@@ -14743,7 +14737,7 @@
         <v>14</v>
       </c>
       <c r="F350" s="2">
-        <v>4592</v>
+        <v>1116</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>15</v>
@@ -14775,7 +14769,7 @@
         <v>14</v>
       </c>
       <c r="F351" s="2">
-        <v>1209</v>
+        <v>1883</v>
       </c>
       <c r="G351" s="2" t="s">
         <v>15</v>
@@ -14807,7 +14801,7 @@
         <v>14</v>
       </c>
       <c r="F352" s="2">
-        <v>2387</v>
+        <v>4188</v>
       </c>
       <c r="G352" s="2" t="s">
         <v>15</v>
@@ -14839,7 +14833,7 @@
         <v>14</v>
       </c>
       <c r="F353" s="2">
-        <v>1728</v>
+        <v>3390</v>
       </c>
       <c r="G353" s="2" t="s">
         <v>15</v>
@@ -14871,7 +14865,7 @@
         <v>14</v>
       </c>
       <c r="F354" s="2">
-        <v>1955</v>
+        <v>1935</v>
       </c>
       <c r="G354" s="2" t="s">
         <v>15</v>
@@ -14903,7 +14897,7 @@
         <v>14</v>
       </c>
       <c r="F355" s="2">
-        <v>3759</v>
+        <v>2901</v>
       </c>
       <c r="G355" s="2" t="s">
         <v>15</v>
@@ -14935,7 +14929,7 @@
         <v>14</v>
       </c>
       <c r="F356" s="2">
-        <v>4618</v>
+        <v>3050</v>
       </c>
       <c r="G356" s="2" t="s">
         <v>15</v>
@@ -14967,7 +14961,7 @@
         <v>14</v>
       </c>
       <c r="F357" s="2">
-        <v>4189</v>
+        <v>4551</v>
       </c>
       <c r="G357" s="2" t="s">
         <v>15</v>
@@ -14999,7 +14993,7 @@
         <v>14</v>
       </c>
       <c r="F358" s="2">
-        <v>2412</v>
+        <v>3905</v>
       </c>
       <c r="G358" s="2" t="s">
         <v>15</v>
@@ -15031,7 +15025,7 @@
         <v>14</v>
       </c>
       <c r="F359" s="2">
-        <v>3531</v>
+        <v>1682</v>
       </c>
       <c r="G359" s="2" t="s">
         <v>15</v>
@@ -15063,7 +15057,7 @@
         <v>14</v>
       </c>
       <c r="F360" s="2">
-        <v>1269</v>
+        <v>4125</v>
       </c>
       <c r="G360" s="2" t="s">
         <v>15</v>
@@ -15095,7 +15089,7 @@
         <v>14</v>
       </c>
       <c r="F361" s="2">
-        <v>1324</v>
+        <v>4470</v>
       </c>
       <c r="G361" s="2" t="s">
         <v>15</v>
@@ -15127,7 +15121,7 @@
         <v>14</v>
       </c>
       <c r="F362" s="2">
-        <v>971</v>
+        <v>1010</v>
       </c>
       <c r="G362" s="2" t="s">
         <v>15</v>
@@ -15159,7 +15153,7 @@
         <v>14</v>
       </c>
       <c r="F363" s="2">
-        <v>4313</v>
+        <v>4183</v>
       </c>
       <c r="G363" s="2" t="s">
         <v>15</v>
@@ -15191,7 +15185,7 @@
         <v>14</v>
       </c>
       <c r="F364" s="2">
-        <v>3040</v>
+        <v>4573</v>
       </c>
       <c r="G364" s="2" t="s">
         <v>15</v>
@@ -15223,7 +15217,7 @@
         <v>14</v>
       </c>
       <c r="F365" s="2">
-        <v>2472</v>
+        <v>2404</v>
       </c>
       <c r="G365" s="2" t="s">
         <v>15</v>
@@ -15255,7 +15249,7 @@
         <v>14</v>
       </c>
       <c r="F366" s="2">
-        <v>2839</v>
+        <v>1139</v>
       </c>
       <c r="G366" s="2" t="s">
         <v>15</v>
@@ -15287,7 +15281,7 @@
         <v>14</v>
       </c>
       <c r="F367" s="2">
-        <v>3009</v>
+        <v>4698</v>
       </c>
       <c r="G367" s="2" t="s">
         <v>15</v>
@@ -15319,7 +15313,7 @@
         <v>14</v>
       </c>
       <c r="F368" s="2">
-        <v>3498</v>
+        <v>4734</v>
       </c>
       <c r="G368" s="2" t="s">
         <v>15</v>
@@ -15351,7 +15345,7 @@
         <v>14</v>
       </c>
       <c r="F369" s="2">
-        <v>1296</v>
+        <v>2963</v>
       </c>
       <c r="G369" s="2" t="s">
         <v>15</v>
@@ -15383,7 +15377,7 @@
         <v>14</v>
       </c>
       <c r="F370" s="2">
-        <v>1680</v>
+        <v>2976</v>
       </c>
       <c r="G370" s="2" t="s">
         <v>15</v>
@@ -15415,7 +15409,7 @@
         <v>14</v>
       </c>
       <c r="F371" s="2">
-        <v>3485</v>
+        <v>3047</v>
       </c>
       <c r="G371" s="2" t="s">
         <v>15</v>
@@ -15447,7 +15441,7 @@
         <v>14</v>
       </c>
       <c r="F372" s="2">
-        <v>4113</v>
+        <v>2520</v>
       </c>
       <c r="G372" s="2" t="s">
         <v>15</v>
@@ -15479,7 +15473,7 @@
         <v>14</v>
       </c>
       <c r="F373" s="2">
-        <v>2606</v>
+        <v>4378</v>
       </c>
       <c r="G373" s="2" t="s">
         <v>15</v>
@@ -15511,7 +15505,7 @@
         <v>14</v>
       </c>
       <c r="F374" s="2">
-        <v>4132</v>
+        <v>1879</v>
       </c>
       <c r="G374" s="2" t="s">
         <v>15</v>
@@ -15543,7 +15537,7 @@
         <v>14</v>
       </c>
       <c r="F375" s="2">
-        <v>2575</v>
+        <v>1599</v>
       </c>
       <c r="G375" s="2" t="s">
         <v>15</v>
@@ -15575,7 +15569,7 @@
         <v>14</v>
       </c>
       <c r="F376" s="2">
-        <v>1225</v>
+        <v>2097</v>
       </c>
       <c r="G376" s="2" t="s">
         <v>15</v>
@@ -15607,7 +15601,7 @@
         <v>14</v>
       </c>
       <c r="F377" s="2">
-        <v>3457</v>
+        <v>4707</v>
       </c>
       <c r="G377" s="2" t="s">
         <v>15</v>
@@ -15639,7 +15633,7 @@
         <v>14</v>
       </c>
       <c r="F378" s="2">
-        <v>1068</v>
+        <v>2809</v>
       </c>
       <c r="G378" s="2" t="s">
         <v>15</v>
@@ -15671,7 +15665,7 @@
         <v>14</v>
       </c>
       <c r="F379" s="2">
-        <v>2072</v>
+        <v>2215</v>
       </c>
       <c r="G379" s="2" t="s">
         <v>15</v>
@@ -15703,7 +15697,7 @@
         <v>14</v>
       </c>
       <c r="F380" s="2">
-        <v>2610</v>
+        <v>1908</v>
       </c>
       <c r="G380" s="2" t="s">
         <v>15</v>
@@ -15735,7 +15729,7 @@
         <v>14</v>
       </c>
       <c r="F381" s="2">
-        <v>3246</v>
+        <v>1626</v>
       </c>
       <c r="G381" s="2" t="s">
         <v>15</v>
@@ -15767,7 +15761,7 @@
         <v>14</v>
       </c>
       <c r="F382" s="2">
-        <v>4146</v>
+        <v>2584</v>
       </c>
       <c r="G382" s="2" t="s">
         <v>15</v>
@@ -15799,7 +15793,7 @@
         <v>14</v>
       </c>
       <c r="F383" s="2">
-        <v>3988</v>
+        <v>3926</v>
       </c>
       <c r="G383" s="2" t="s">
         <v>15</v>
@@ -15831,7 +15825,7 @@
         <v>14</v>
       </c>
       <c r="F384" s="2">
-        <v>1730</v>
+        <v>2472</v>
       </c>
       <c r="G384" s="2" t="s">
         <v>15</v>
@@ -15863,7 +15857,7 @@
         <v>14</v>
       </c>
       <c r="F385" s="2">
-        <v>2541</v>
+        <v>1496</v>
       </c>
       <c r="G385" s="2" t="s">
         <v>15</v>
@@ -15895,7 +15889,7 @@
         <v>14</v>
       </c>
       <c r="F386" s="2">
-        <v>2079</v>
+        <v>2150</v>
       </c>
       <c r="G386" s="2" t="s">
         <v>15</v>
@@ -15927,7 +15921,7 @@
         <v>14</v>
       </c>
       <c r="F387" s="2">
-        <v>3874</v>
+        <v>4178</v>
       </c>
       <c r="G387" s="2" t="s">
         <v>15</v>
@@ -15959,7 +15953,7 @@
         <v>14</v>
       </c>
       <c r="F388" s="2">
-        <v>2512</v>
+        <v>3497</v>
       </c>
       <c r="G388" s="2" t="s">
         <v>15</v>
@@ -15991,7 +15985,7 @@
         <v>14</v>
       </c>
       <c r="F389" s="2">
-        <v>2902</v>
+        <v>3448</v>
       </c>
       <c r="G389" s="2" t="s">
         <v>15</v>
@@ -16023,7 +16017,7 @@
         <v>14</v>
       </c>
       <c r="F390" s="2">
-        <v>4623</v>
+        <v>2430</v>
       </c>
       <c r="G390" s="2" t="s">
         <v>15</v>
@@ -16055,7 +16049,7 @@
         <v>14</v>
       </c>
       <c r="F391" s="2">
-        <v>2103</v>
+        <v>2733</v>
       </c>
       <c r="G391" s="2" t="s">
         <v>15</v>
@@ -16087,7 +16081,7 @@
         <v>14</v>
       </c>
       <c r="F392" s="2">
-        <v>3950</v>
+        <v>1345</v>
       </c>
       <c r="G392" s="2" t="s">
         <v>15</v>
@@ -16119,7 +16113,7 @@
         <v>14</v>
       </c>
       <c r="F393" s="2">
-        <v>2644</v>
+        <v>1026</v>
       </c>
       <c r="G393" s="2" t="s">
         <v>15</v>
@@ -16151,7 +16145,7 @@
         <v>14</v>
       </c>
       <c r="F394" s="2">
-        <v>1292</v>
+        <v>2355</v>
       </c>
       <c r="G394" s="2" t="s">
         <v>15</v>
@@ -16183,7 +16177,7 @@
         <v>14</v>
       </c>
       <c r="F395" s="2">
-        <v>3000</v>
+        <v>2668</v>
       </c>
       <c r="G395" s="2" t="s">
         <v>15</v>
@@ -16215,7 +16209,7 @@
         <v>14</v>
       </c>
       <c r="F396" s="2">
-        <v>1468</v>
+        <v>932</v>
       </c>
       <c r="G396" s="2" t="s">
         <v>15</v>
@@ -16247,7 +16241,7 @@
         <v>14</v>
       </c>
       <c r="F397" s="2">
-        <v>4226</v>
+        <v>3599</v>
       </c>
       <c r="G397" s="2" t="s">
         <v>15</v>
@@ -16279,7 +16273,7 @@
         <v>14</v>
       </c>
       <c r="F398" s="2">
-        <v>3658</v>
+        <v>1862</v>
       </c>
       <c r="G398" s="2" t="s">
         <v>15</v>
@@ -16311,7 +16305,7 @@
         <v>14</v>
       </c>
       <c r="F399" s="2">
-        <v>3470</v>
+        <v>1616</v>
       </c>
       <c r="G399" s="2" t="s">
         <v>15</v>
@@ -16343,7 +16337,7 @@
         <v>14</v>
       </c>
       <c r="F400" s="2">
-        <v>3158</v>
+        <v>3844</v>
       </c>
       <c r="G400" s="2" t="s">
         <v>15</v>
@@ -16375,7 +16369,7 @@
         <v>14</v>
       </c>
       <c r="F401" s="2">
-        <v>1477</v>
+        <v>2033</v>
       </c>
       <c r="G401" s="2" t="s">
         <v>15</v>
@@ -16407,7 +16401,7 @@
         <v>14</v>
       </c>
       <c r="F402" s="2">
-        <v>3875</v>
+        <v>3785</v>
       </c>
       <c r="G402" s="2" t="s">
         <v>15</v>
@@ -16439,7 +16433,7 @@
         <v>14</v>
       </c>
       <c r="F403" s="2">
-        <v>3243</v>
+        <v>1370</v>
       </c>
       <c r="G403" s="2" t="s">
         <v>15</v>
@@ -16471,7 +16465,7 @@
         <v>14</v>
       </c>
       <c r="F404" s="2">
-        <v>1420</v>
+        <v>3772</v>
       </c>
       <c r="G404" s="2" t="s">
         <v>15</v>
@@ -16503,7 +16497,7 @@
         <v>14</v>
       </c>
       <c r="F405" s="2">
-        <v>3256</v>
+        <v>1552</v>
       </c>
       <c r="G405" s="2" t="s">
         <v>15</v>
@@ -16535,7 +16529,7 @@
         <v>14</v>
       </c>
       <c r="F406" s="2">
-        <v>2216</v>
+        <v>801</v>
       </c>
       <c r="G406" s="2" t="s">
         <v>15</v>
@@ -16567,7 +16561,7 @@
         <v>14</v>
       </c>
       <c r="F407" s="2">
-        <v>1088</v>
+        <v>1601</v>
       </c>
       <c r="G407" s="2" t="s">
         <v>15</v>
@@ -16599,7 +16593,7 @@
         <v>14</v>
       </c>
       <c r="F408" s="2">
-        <v>3992</v>
+        <v>4454</v>
       </c>
       <c r="G408" s="2" t="s">
         <v>15</v>
@@ -16631,7 +16625,7 @@
         <v>14</v>
       </c>
       <c r="F409" s="2">
-        <v>1235</v>
+        <v>2894</v>
       </c>
       <c r="G409" s="2" t="s">
         <v>15</v>
@@ -16663,7 +16657,7 @@
         <v>14</v>
       </c>
       <c r="F410" s="2">
-        <v>1330</v>
+        <v>3981</v>
       </c>
       <c r="G410" s="2" t="s">
         <v>15</v>
@@ -16695,7 +16689,7 @@
         <v>14</v>
       </c>
       <c r="F411" s="2">
-        <v>921</v>
+        <v>2220</v>
       </c>
       <c r="G411" s="2" t="s">
         <v>15</v>
@@ -16727,7 +16721,7 @@
         <v>14</v>
       </c>
       <c r="F412" s="2">
-        <v>2205</v>
+        <v>3352</v>
       </c>
       <c r="G412" s="2" t="s">
         <v>15</v>
@@ -16759,7 +16753,7 @@
         <v>14</v>
       </c>
       <c r="F413" s="2">
-        <v>3990</v>
+        <v>2846</v>
       </c>
       <c r="G413" s="2" t="s">
         <v>15</v>
@@ -16791,7 +16785,7 @@
         <v>14</v>
       </c>
       <c r="F414" s="2">
-        <v>1498</v>
+        <v>2255</v>
       </c>
       <c r="G414" s="2" t="s">
         <v>15</v>
@@ -16823,7 +16817,7 @@
         <v>14</v>
       </c>
       <c r="F415" s="2">
-        <v>2498</v>
+        <v>950</v>
       </c>
       <c r="G415" s="2" t="s">
         <v>15</v>
@@ -16855,7 +16849,7 @@
         <v>14</v>
       </c>
       <c r="F416" s="2">
-        <v>1746</v>
+        <v>2243</v>
       </c>
       <c r="G416" s="2" t="s">
         <v>15</v>
@@ -16887,7 +16881,7 @@
         <v>14</v>
       </c>
       <c r="F417" s="2">
-        <v>1559</v>
+        <v>2722</v>
       </c>
       <c r="G417" s="2" t="s">
         <v>15</v>
@@ -16919,7 +16913,7 @@
         <v>14</v>
       </c>
       <c r="F418" s="2">
-        <v>1022</v>
+        <v>2635</v>
       </c>
       <c r="G418" s="2" t="s">
         <v>15</v>
@@ -16951,7 +16945,7 @@
         <v>14</v>
       </c>
       <c r="F419" s="2">
-        <v>858</v>
+        <v>2456</v>
       </c>
       <c r="G419" s="2" t="s">
         <v>15</v>
@@ -16983,7 +16977,7 @@
         <v>14</v>
       </c>
       <c r="F420" s="2">
-        <v>1942</v>
+        <v>852</v>
       </c>
       <c r="G420" s="2" t="s">
         <v>15</v>
@@ -17015,7 +17009,7 @@
         <v>14</v>
       </c>
       <c r="F421" s="2">
-        <v>4088</v>
+        <v>4015</v>
       </c>
       <c r="G421" s="2" t="s">
         <v>15</v>
@@ -17047,7 +17041,7 @@
         <v>14</v>
       </c>
       <c r="F422" s="2">
-        <v>4265</v>
+        <v>4310</v>
       </c>
       <c r="G422" s="2" t="s">
         <v>15</v>
@@ -17079,7 +17073,7 @@
         <v>14</v>
       </c>
       <c r="F423" s="2">
-        <v>1299</v>
+        <v>1040</v>
       </c>
       <c r="G423" s="2" t="s">
         <v>15</v>
@@ -17111,7 +17105,7 @@
         <v>14</v>
       </c>
       <c r="F424" s="2">
-        <v>4612</v>
+        <v>4251</v>
       </c>
       <c r="G424" s="2" t="s">
         <v>15</v>
@@ -17143,7 +17137,7 @@
         <v>14</v>
       </c>
       <c r="F425" s="2">
-        <v>3970</v>
+        <v>2989</v>
       </c>
       <c r="G425" s="2" t="s">
         <v>15</v>
@@ -17175,7 +17169,7 @@
         <v>14</v>
       </c>
       <c r="F426" s="2">
-        <v>1792</v>
+        <v>3367</v>
       </c>
       <c r="G426" s="2" t="s">
         <v>15</v>
@@ -17207,7 +17201,7 @@
         <v>14</v>
       </c>
       <c r="F427" s="2">
-        <v>2111</v>
+        <v>2872</v>
       </c>
       <c r="G427" s="2" t="s">
         <v>15</v>
@@ -17239,7 +17233,7 @@
         <v>14</v>
       </c>
       <c r="F428" s="2">
-        <v>4298</v>
+        <v>1632</v>
       </c>
       <c r="G428" s="2" t="s">
         <v>15</v>
@@ -17271,7 +17265,7 @@
         <v>14</v>
       </c>
       <c r="F429" s="2">
-        <v>4287</v>
+        <v>2671</v>
       </c>
       <c r="G429" s="2" t="s">
         <v>15</v>
@@ -17303,7 +17297,7 @@
         <v>14</v>
       </c>
       <c r="F430" s="2">
-        <v>2963</v>
+        <v>3484</v>
       </c>
       <c r="G430" s="2" t="s">
         <v>15</v>
@@ -17335,7 +17329,7 @@
         <v>14</v>
       </c>
       <c r="F431" s="2">
-        <v>2290</v>
+        <v>1151</v>
       </c>
       <c r="G431" s="2" t="s">
         <v>15</v>
@@ -17367,7 +17361,7 @@
         <v>14</v>
       </c>
       <c r="F432" s="2">
-        <v>4010</v>
+        <v>4696</v>
       </c>
       <c r="G432" s="2" t="s">
         <v>15</v>
@@ -17399,7 +17393,7 @@
         <v>14</v>
       </c>
       <c r="F433" s="2">
-        <v>4380</v>
+        <v>1986</v>
       </c>
       <c r="G433" s="2" t="s">
         <v>15</v>
@@ -17431,7 +17425,7 @@
         <v>14</v>
       </c>
       <c r="F434" s="2">
-        <v>3971</v>
+        <v>2573</v>
       </c>
       <c r="G434" s="2" t="s">
         <v>15</v>
@@ -17463,7 +17457,7 @@
         <v>14</v>
       </c>
       <c r="F435" s="2">
-        <v>2495</v>
+        <v>2239</v>
       </c>
       <c r="G435" s="2" t="s">
         <v>15</v>
@@ -17495,7 +17489,7 @@
         <v>14</v>
       </c>
       <c r="F436" s="2">
-        <v>1931</v>
+        <v>4591</v>
       </c>
       <c r="G436" s="2" t="s">
         <v>15</v>
@@ -17527,7 +17521,7 @@
         <v>14</v>
       </c>
       <c r="F437" s="2">
-        <v>4423</v>
+        <v>1429</v>
       </c>
       <c r="G437" s="2" t="s">
         <v>15</v>
@@ -17559,7 +17553,7 @@
         <v>14</v>
       </c>
       <c r="F438" s="2">
-        <v>2497</v>
+        <v>2712</v>
       </c>
       <c r="G438" s="2" t="s">
         <v>15</v>
@@ -17591,7 +17585,7 @@
         <v>14</v>
       </c>
       <c r="F439" s="2">
-        <v>1522</v>
+        <v>3261</v>
       </c>
       <c r="G439" s="2" t="s">
         <v>15</v>
@@ -17623,7 +17617,7 @@
         <v>14</v>
       </c>
       <c r="F440" s="2">
-        <v>1528</v>
+        <v>4385</v>
       </c>
       <c r="G440" s="2" t="s">
         <v>15</v>
@@ -17655,7 +17649,7 @@
         <v>14</v>
       </c>
       <c r="F441" s="2">
-        <v>2770</v>
+        <v>1274</v>
       </c>
       <c r="G441" s="2" t="s">
         <v>15</v>
@@ -17687,7 +17681,7 @@
         <v>14</v>
       </c>
       <c r="F442" s="2">
-        <v>904</v>
+        <v>1504</v>
       </c>
       <c r="G442" s="2" t="s">
         <v>15</v>
@@ -17719,7 +17713,7 @@
         <v>14</v>
       </c>
       <c r="F443" s="2">
-        <v>3122</v>
+        <v>3631</v>
       </c>
       <c r="G443" s="2" t="s">
         <v>15</v>
@@ -17751,7 +17745,7 @@
         <v>14</v>
       </c>
       <c r="F444" s="2">
-        <v>1126</v>
+        <v>4101</v>
       </c>
       <c r="G444" s="2" t="s">
         <v>15</v>
@@ -17783,7 +17777,7 @@
         <v>14</v>
       </c>
       <c r="F445" s="2">
-        <v>1287</v>
+        <v>2468</v>
       </c>
       <c r="G445" s="2" t="s">
         <v>15</v>
@@ -17815,7 +17809,7 @@
         <v>14</v>
       </c>
       <c r="F446" s="2">
-        <v>2193</v>
+        <v>3415</v>
       </c>
       <c r="G446" s="2" t="s">
         <v>15</v>
@@ -17847,7 +17841,7 @@
         <v>14</v>
       </c>
       <c r="F447" s="2">
-        <v>2803</v>
+        <v>3313</v>
       </c>
       <c r="G447" s="2" t="s">
         <v>15</v>
@@ -17879,7 +17873,7 @@
         <v>14</v>
       </c>
       <c r="F448" s="2">
-        <v>3596</v>
+        <v>1389</v>
       </c>
       <c r="G448" s="2" t="s">
         <v>15</v>
@@ -17911,7 +17905,7 @@
         <v>14</v>
       </c>
       <c r="F449" s="2">
-        <v>3194</v>
+        <v>3990</v>
       </c>
       <c r="G449" s="2" t="s">
         <v>15</v>
@@ -17943,7 +17937,7 @@
         <v>14</v>
       </c>
       <c r="F450" s="2">
-        <v>2329</v>
+        <v>4244</v>
       </c>
       <c r="G450" s="2" t="s">
         <v>15</v>
@@ -17975,7 +17969,7 @@
         <v>14</v>
       </c>
       <c r="F451" s="2">
-        <v>3819</v>
+        <v>2275</v>
       </c>
       <c r="G451" s="2" t="s">
         <v>15</v>
@@ -18007,7 +18001,7 @@
         <v>14</v>
       </c>
       <c r="F452" s="2">
-        <v>2766</v>
+        <v>2573</v>
       </c>
       <c r="G452" s="2" t="s">
         <v>15</v>
@@ -18039,7 +18033,7 @@
         <v>14</v>
       </c>
       <c r="F453" s="2">
-        <v>2868</v>
+        <v>2089</v>
       </c>
       <c r="G453" s="2" t="s">
         <v>15</v>
@@ -18071,7 +18065,7 @@
         <v>14</v>
       </c>
       <c r="F454" s="2">
-        <v>3820</v>
+        <v>3373</v>
       </c>
       <c r="G454" s="2" t="s">
         <v>15</v>
@@ -18103,7 +18097,7 @@
         <v>14</v>
       </c>
       <c r="F455" s="2">
-        <v>4529</v>
+        <v>4374</v>
       </c>
       <c r="G455" s="2" t="s">
         <v>15</v>
@@ -18135,7 +18129,7 @@
         <v>14</v>
       </c>
       <c r="F456" s="2">
-        <v>2461</v>
+        <v>3615</v>
       </c>
       <c r="G456" s="2" t="s">
         <v>15</v>
@@ -18167,7 +18161,7 @@
         <v>14</v>
       </c>
       <c r="F457" s="2">
-        <v>2268</v>
+        <v>1087</v>
       </c>
       <c r="G457" s="2" t="s">
         <v>15</v>
@@ -18199,7 +18193,7 @@
         <v>14</v>
       </c>
       <c r="F458" s="2">
-        <v>3253</v>
+        <v>949</v>
       </c>
       <c r="G458" s="2" t="s">
         <v>15</v>
@@ -18231,7 +18225,7 @@
         <v>14</v>
       </c>
       <c r="F459" s="2">
-        <v>4103</v>
+        <v>4113</v>
       </c>
       <c r="G459" s="2" t="s">
         <v>15</v>
@@ -18263,7 +18257,7 @@
         <v>14</v>
       </c>
       <c r="F460" s="2">
-        <v>4645</v>
+        <v>4286</v>
       </c>
       <c r="G460" s="2" t="s">
         <v>15</v>
@@ -18295,7 +18289,7 @@
         <v>14</v>
       </c>
       <c r="F461" s="2">
-        <v>1816</v>
+        <v>2693</v>
       </c>
       <c r="G461" s="2" t="s">
         <v>15</v>
@@ -18327,7 +18321,7 @@
         <v>14</v>
       </c>
       <c r="F462" s="2">
-        <v>3783</v>
+        <v>3972</v>
       </c>
       <c r="G462" s="2" t="s">
         <v>15</v>
@@ -18359,7 +18353,7 @@
         <v>14</v>
       </c>
       <c r="F463" s="2">
-        <v>4030</v>
+        <v>4054</v>
       </c>
       <c r="G463" s="2" t="s">
         <v>15</v>
@@ -18391,7 +18385,7 @@
         <v>14</v>
       </c>
       <c r="F464" s="2">
-        <v>917</v>
+        <v>1137</v>
       </c>
       <c r="G464" s="2" t="s">
         <v>15</v>
@@ -18423,7 +18417,7 @@
         <v>14</v>
       </c>
       <c r="F465" s="2">
-        <v>4148</v>
+        <v>1514</v>
       </c>
       <c r="G465" s="2" t="s">
         <v>15</v>
@@ -18455,7 +18449,7 @@
         <v>14</v>
       </c>
       <c r="F466" s="2">
-        <v>2958</v>
+        <v>1973</v>
       </c>
       <c r="G466" s="2" t="s">
         <v>15</v>
@@ -18487,7 +18481,7 @@
         <v>14</v>
       </c>
       <c r="F467" s="2">
-        <v>4251</v>
+        <v>2793</v>
       </c>
       <c r="G467" s="2" t="s">
         <v>15</v>
@@ -18519,7 +18513,7 @@
         <v>14</v>
       </c>
       <c r="F468" s="2">
-        <v>4757</v>
+        <v>4284</v>
       </c>
       <c r="G468" s="2" t="s">
         <v>15</v>
@@ -18551,7 +18545,7 @@
         <v>14</v>
       </c>
       <c r="F469" s="2">
-        <v>4755</v>
+        <v>4292</v>
       </c>
       <c r="G469" s="2" t="s">
         <v>15</v>
@@ -18583,7 +18577,7 @@
         <v>14</v>
       </c>
       <c r="F470" s="2">
-        <v>2265</v>
+        <v>2003</v>
       </c>
       <c r="G470" s="2" t="s">
         <v>15</v>
@@ -18615,7 +18609,7 @@
         <v>14</v>
       </c>
       <c r="F471" s="2">
-        <v>2516</v>
+        <v>2217</v>
       </c>
       <c r="G471" s="2" t="s">
         <v>15</v>
@@ -18702,7 +18696,7 @@
         <v>14</v>
       </c>
       <c r="F2" s="2">
-        <v>3597</v>
+        <v>2554</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>15</v>
@@ -18734,7 +18728,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="2">
-        <v>1120</v>
+        <v>1005</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>15</v>
@@ -18766,7 +18760,7 @@
         <v>14</v>
       </c>
       <c r="F4" s="2">
-        <v>3037</v>
+        <v>1371</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
@@ -18798,7 +18792,7 @@
         <v>14</v>
       </c>
       <c r="F5" s="2">
-        <v>2728</v>
+        <v>4403</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
@@ -18830,7 +18824,7 @@
         <v>14</v>
       </c>
       <c r="F6" s="2">
-        <v>2049</v>
+        <v>1966</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -18862,7 +18856,7 @@
         <v>14</v>
       </c>
       <c r="F7" s="2">
-        <v>2055</v>
+        <v>1146</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -18894,7 +18888,7 @@
         <v>14</v>
       </c>
       <c r="F8" s="2">
-        <v>850</v>
+        <v>983</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -18926,7 +18920,7 @@
         <v>14</v>
       </c>
       <c r="F9" s="2">
-        <v>2266</v>
+        <v>4550</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -18958,7 +18952,7 @@
         <v>14</v>
       </c>
       <c r="F10" s="2">
-        <v>4135</v>
+        <v>3546</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
@@ -18990,7 +18984,7 @@
         <v>14</v>
       </c>
       <c r="F11" s="2">
-        <v>2859</v>
+        <v>1587</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
@@ -19022,7 +19016,7 @@
         <v>14</v>
       </c>
       <c r="F12" s="2">
-        <v>1309</v>
+        <v>2686</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
@@ -19054,7 +19048,7 @@
         <v>14</v>
       </c>
       <c r="F13" s="2">
-        <v>993</v>
+        <v>923</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -19086,7 +19080,7 @@
         <v>14</v>
       </c>
       <c r="F14" s="2">
-        <v>2180</v>
+        <v>1180</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -19118,7 +19112,7 @@
         <v>14</v>
       </c>
       <c r="F15" s="2">
-        <v>4360</v>
+        <v>4539</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -19150,7 +19144,7 @@
         <v>14</v>
       </c>
       <c r="F16" s="2">
-        <v>1532</v>
+        <v>4247</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
@@ -19182,7 +19176,7 @@
         <v>14</v>
       </c>
       <c r="F17" s="2">
-        <v>4276</v>
+        <v>941</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
@@ -19214,7 +19208,7 @@
         <v>14</v>
       </c>
       <c r="F18" s="2">
-        <v>3017</v>
+        <v>2875</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
@@ -19246,7 +19240,7 @@
         <v>14</v>
       </c>
       <c r="F19" s="2">
-        <v>3197</v>
+        <v>2654</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
@@ -19278,7 +19272,7 @@
         <v>14</v>
       </c>
       <c r="F20" s="2">
-        <v>1930</v>
+        <v>2107</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
@@ -19310,7 +19304,7 @@
         <v>14</v>
       </c>
       <c r="F21" s="2">
-        <v>2303</v>
+        <v>4282</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -19342,7 +19336,7 @@
         <v>14</v>
       </c>
       <c r="F22" s="2">
-        <v>2113</v>
+        <v>2543</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -19374,7 +19368,7 @@
         <v>14</v>
       </c>
       <c r="F23" s="2">
-        <v>3251</v>
+        <v>4573</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -19406,7 +19400,7 @@
         <v>14</v>
       </c>
       <c r="F24" s="2">
-        <v>1692</v>
+        <v>4360</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -19438,7 +19432,7 @@
         <v>14</v>
       </c>
       <c r="F25" s="2">
-        <v>1551</v>
+        <v>3018</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -19470,7 +19464,7 @@
         <v>14</v>
       </c>
       <c r="F26" s="2">
-        <v>1858</v>
+        <v>1625</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -19502,7 +19496,7 @@
         <v>14</v>
       </c>
       <c r="F27" s="2">
-        <v>3081</v>
+        <v>4092</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>15</v>
@@ -19534,7 +19528,7 @@
         <v>14</v>
       </c>
       <c r="F28" s="2">
-        <v>3971</v>
+        <v>1499</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>15</v>
@@ -19566,7 +19560,7 @@
         <v>14</v>
       </c>
       <c r="F29" s="2">
-        <v>2436</v>
+        <v>2405</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>15</v>
@@ -19598,7 +19592,7 @@
         <v>14</v>
       </c>
       <c r="F30" s="2">
-        <v>1720</v>
+        <v>3156</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>15</v>
@@ -19630,7 +19624,7 @@
         <v>14</v>
       </c>
       <c r="F31" s="2">
-        <v>819</v>
+        <v>917</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>15</v>
@@ -19662,7 +19656,7 @@
         <v>14</v>
       </c>
       <c r="F32" s="2">
-        <v>1642</v>
+        <v>1702</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>15</v>
@@ -19694,7 +19688,7 @@
         <v>14</v>
       </c>
       <c r="F33" s="2">
-        <v>1123</v>
+        <v>3737</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>15</v>
@@ -19726,7 +19720,7 @@
         <v>14</v>
       </c>
       <c r="F34" s="2">
-        <v>1687</v>
+        <v>4655</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>15</v>
@@ -19758,7 +19752,7 @@
         <v>14</v>
       </c>
       <c r="F35" s="2">
-        <v>4055</v>
+        <v>2182</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>15</v>
@@ -19790,7 +19784,7 @@
         <v>14</v>
       </c>
       <c r="F36" s="2">
-        <v>1862</v>
+        <v>1459</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>15</v>
@@ -19822,7 +19816,7 @@
         <v>14</v>
       </c>
       <c r="F37" s="2">
-        <v>2858</v>
+        <v>1951</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>15</v>
@@ -19854,7 +19848,7 @@
         <v>14</v>
       </c>
       <c r="F38" s="2">
-        <v>3867</v>
+        <v>3093</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>15</v>
@@ -19886,7 +19880,7 @@
         <v>14</v>
       </c>
       <c r="F39" s="2">
-        <v>4457</v>
+        <v>2140</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>15</v>
@@ -19918,7 +19912,7 @@
         <v>14</v>
       </c>
       <c r="F40" s="2">
-        <v>2119</v>
+        <v>1502</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>15</v>
@@ -19950,7 +19944,7 @@
         <v>14</v>
       </c>
       <c r="F41" s="2">
-        <v>2614</v>
+        <v>1559</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>15</v>
@@ -19982,7 +19976,7 @@
         <v>14</v>
       </c>
       <c r="F42" s="2">
-        <v>3842</v>
+        <v>3356</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>15</v>
@@ -20014,7 +20008,7 @@
         <v>14</v>
       </c>
       <c r="F43" s="2">
-        <v>1343</v>
+        <v>1380</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>15</v>
@@ -20046,7 +20040,7 @@
         <v>14</v>
       </c>
       <c r="F44" s="2">
-        <v>3241</v>
+        <v>4790</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>15</v>
@@ -20078,7 +20072,7 @@
         <v>14</v>
       </c>
       <c r="F45" s="2">
-        <v>3631</v>
+        <v>1149</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>15</v>
@@ -20110,7 +20104,7 @@
         <v>14</v>
       </c>
       <c r="F46" s="2">
-        <v>2755</v>
+        <v>1770</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>15</v>
@@ -20142,7 +20136,7 @@
         <v>14</v>
       </c>
       <c r="F47" s="2">
-        <v>3756</v>
+        <v>4797</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>15</v>
@@ -20174,7 +20168,7 @@
         <v>14</v>
       </c>
       <c r="F48" s="2">
-        <v>3028</v>
+        <v>3166</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>15</v>
@@ -20206,7 +20200,7 @@
         <v>14</v>
       </c>
       <c r="F49" s="2">
-        <v>3578</v>
+        <v>1537</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>15</v>
@@ -20238,7 +20232,7 @@
         <v>14</v>
       </c>
       <c r="F50" s="2">
-        <v>1044</v>
+        <v>1273</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>15</v>
@@ -20270,7 +20264,7 @@
         <v>14</v>
       </c>
       <c r="F51" s="2">
-        <v>2937</v>
+        <v>1816</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>15</v>
@@ -20302,7 +20296,7 @@
         <v>14</v>
       </c>
       <c r="F52" s="2">
-        <v>1971</v>
+        <v>1217</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>15</v>
@@ -20334,7 +20328,7 @@
         <v>14</v>
       </c>
       <c r="F53" s="2">
-        <v>3909</v>
+        <v>4478</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>15</v>
@@ -20366,7 +20360,7 @@
         <v>14</v>
       </c>
       <c r="F54" s="2">
-        <v>4771</v>
+        <v>1505</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>15</v>
@@ -20398,7 +20392,7 @@
         <v>14</v>
       </c>
       <c r="F55" s="2">
-        <v>3275</v>
+        <v>1462</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>15</v>
@@ -20430,7 +20424,7 @@
         <v>14</v>
       </c>
       <c r="F56" s="2">
-        <v>2313</v>
+        <v>3530</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>15</v>
@@ -20462,7 +20456,7 @@
         <v>14</v>
       </c>
       <c r="F57" s="2">
-        <v>2030</v>
+        <v>3488</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>15</v>
@@ -20494,7 +20488,7 @@
         <v>14</v>
       </c>
       <c r="F58" s="2">
-        <v>4455</v>
+        <v>2121</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>15</v>
@@ -20526,7 +20520,7 @@
         <v>14</v>
       </c>
       <c r="F59" s="2">
-        <v>1812</v>
+        <v>1512</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>15</v>
@@ -20558,7 +20552,7 @@
         <v>14</v>
       </c>
       <c r="F60" s="2">
-        <v>3317</v>
+        <v>3540</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>15</v>
@@ -20590,7 +20584,7 @@
         <v>14</v>
       </c>
       <c r="F61" s="2">
-        <v>2825</v>
+        <v>3072</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>15</v>
@@ -20622,7 +20616,7 @@
         <v>14</v>
       </c>
       <c r="F62" s="2">
-        <v>4783</v>
+        <v>1371</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>15</v>
@@ -20654,7 +20648,7 @@
         <v>14</v>
       </c>
       <c r="F63" s="2">
-        <v>4106</v>
+        <v>3849</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>15</v>
@@ -20686,7 +20680,7 @@
         <v>14</v>
       </c>
       <c r="F64" s="2">
-        <v>4282</v>
+        <v>2403</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>15</v>
@@ -20718,7 +20712,7 @@
         <v>14</v>
       </c>
       <c r="F65" s="2">
-        <v>1791</v>
+        <v>1547</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>15</v>
@@ -20750,7 +20744,7 @@
         <v>14</v>
       </c>
       <c r="F66" s="2">
-        <v>3879</v>
+        <v>2696</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>15</v>
@@ -20782,7 +20776,7 @@
         <v>14</v>
       </c>
       <c r="F67" s="2">
-        <v>2378</v>
+        <v>2694</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>15</v>
@@ -20814,7 +20808,7 @@
         <v>14</v>
       </c>
       <c r="F68" s="2">
-        <v>4501</v>
+        <v>2290</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>15</v>
@@ -20846,7 +20840,7 @@
         <v>14</v>
       </c>
       <c r="F69" s="2">
-        <v>3560</v>
+        <v>3304</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>15</v>
@@ -20878,7 +20872,7 @@
         <v>14</v>
       </c>
       <c r="F70" s="2">
-        <v>4125</v>
+        <v>2800</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>15</v>
@@ -20910,7 +20904,7 @@
         <v>14</v>
       </c>
       <c r="F71" s="2">
-        <v>3134</v>
+        <v>3720</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>15</v>
@@ -20942,7 +20936,7 @@
         <v>14</v>
       </c>
       <c r="F72" s="2">
-        <v>3106</v>
+        <v>3612</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>15</v>
@@ -20974,7 +20968,7 @@
         <v>14</v>
       </c>
       <c r="F73" s="2">
-        <v>4191</v>
+        <v>2939</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>15</v>
@@ -21006,7 +21000,7 @@
         <v>14</v>
       </c>
       <c r="F74" s="2">
-        <v>4704</v>
+        <v>1505</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>15</v>
@@ -21038,7 +21032,7 @@
         <v>14</v>
       </c>
       <c r="F75" s="2">
-        <v>3195</v>
+        <v>2673</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>15</v>
@@ -21070,7 +21064,7 @@
         <v>14</v>
       </c>
       <c r="F76" s="2">
-        <v>1472</v>
+        <v>1061</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>15</v>
@@ -21102,7 +21096,7 @@
         <v>14</v>
       </c>
       <c r="F77" s="2">
-        <v>1671</v>
+        <v>4781</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>15</v>
@@ -21134,7 +21128,7 @@
         <v>14</v>
       </c>
       <c r="F78" s="2">
-        <v>2413</v>
+        <v>3500</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>15</v>
@@ -21166,7 +21160,7 @@
         <v>14</v>
       </c>
       <c r="F79" s="2">
-        <v>4432</v>
+        <v>3862</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>15</v>
@@ -21198,7 +21192,7 @@
         <v>14</v>
       </c>
       <c r="F80" s="2">
-        <v>2397</v>
+        <v>1119</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>15</v>
@@ -21230,7 +21224,7 @@
         <v>14</v>
       </c>
       <c r="F81" s="2">
-        <v>1438</v>
+        <v>2935</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>15</v>
@@ -21262,7 +21256,7 @@
         <v>14</v>
       </c>
       <c r="F82" s="2">
-        <v>2272</v>
+        <v>1561</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>15</v>
@@ -21294,7 +21288,7 @@
         <v>14</v>
       </c>
       <c r="F83" s="2">
-        <v>1720</v>
+        <v>1032</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>15</v>
@@ -21326,7 +21320,7 @@
         <v>14</v>
       </c>
       <c r="F84" s="2">
-        <v>1175</v>
+        <v>1353</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>15</v>
@@ -21358,7 +21352,7 @@
         <v>14</v>
       </c>
       <c r="F85" s="2">
-        <v>3218</v>
+        <v>1353</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>15</v>
@@ -21390,7 +21384,7 @@
         <v>14</v>
       </c>
       <c r="F86" s="2">
-        <v>4742</v>
+        <v>2099</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>15</v>
@@ -21422,7 +21416,7 @@
         <v>14</v>
       </c>
       <c r="F87" s="2">
-        <v>2607</v>
+        <v>1039</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>15</v>
@@ -21454,7 +21448,7 @@
         <v>14</v>
       </c>
       <c r="F88" s="2">
-        <v>3765</v>
+        <v>2316</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>15</v>
@@ -21486,7 +21480,7 @@
         <v>14</v>
       </c>
       <c r="F89" s="2">
-        <v>2910</v>
+        <v>948</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>15</v>
@@ -21518,7 +21512,7 @@
         <v>14</v>
       </c>
       <c r="F90" s="2">
-        <v>815</v>
+        <v>4289</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>15</v>
@@ -21550,7 +21544,7 @@
         <v>14</v>
       </c>
       <c r="F91" s="2">
-        <v>3618</v>
+        <v>1622</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>15</v>
@@ -21582,7 +21576,7 @@
         <v>14</v>
       </c>
       <c r="F92" s="2">
-        <v>986</v>
+        <v>1578</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>15</v>
@@ -21614,7 +21608,7 @@
         <v>14</v>
       </c>
       <c r="F93" s="2">
-        <v>1913</v>
+        <v>2989</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>15</v>
@@ -21646,7 +21640,7 @@
         <v>14</v>
       </c>
       <c r="F94" s="2">
-        <v>3078</v>
+        <v>1228</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>15</v>
@@ -21678,7 +21672,7 @@
         <v>14</v>
       </c>
       <c r="F95" s="2">
-        <v>1602</v>
+        <v>2170</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>15</v>
@@ -21710,7 +21704,7 @@
         <v>14</v>
       </c>
       <c r="F96" s="2">
-        <v>3816</v>
+        <v>3182</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>15</v>
@@ -21742,7 +21736,7 @@
         <v>14</v>
       </c>
       <c r="F97" s="2">
-        <v>1259</v>
+        <v>4059</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>15</v>
@@ -21774,7 +21768,7 @@
         <v>14</v>
       </c>
       <c r="F98" s="2">
-        <v>1054</v>
+        <v>1886</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>15</v>
@@ -21806,7 +21800,7 @@
         <v>14</v>
       </c>
       <c r="F99" s="2">
-        <v>4379</v>
+        <v>3240</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>15</v>
@@ -21838,7 +21832,7 @@
         <v>14</v>
       </c>
       <c r="F100" s="2">
-        <v>1274</v>
+        <v>3142</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>15</v>
@@ -21870,7 +21864,7 @@
         <v>14</v>
       </c>
       <c r="F101" s="2">
-        <v>2803</v>
+        <v>3776</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>15</v>
@@ -21902,7 +21896,7 @@
         <v>14</v>
       </c>
       <c r="F102" s="2">
-        <v>2948</v>
+        <v>2382</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>15</v>
@@ -21934,7 +21928,7 @@
         <v>14</v>
       </c>
       <c r="F103" s="2">
-        <v>1761</v>
+        <v>1109</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>15</v>
@@ -21966,7 +21960,7 @@
         <v>14</v>
       </c>
       <c r="F104" s="2">
-        <v>1800</v>
+        <v>1350</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>15</v>
@@ -21998,7 +21992,7 @@
         <v>14</v>
       </c>
       <c r="F105" s="2">
-        <v>3158</v>
+        <v>1307</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>15</v>
@@ -22030,7 +22024,7 @@
         <v>14</v>
       </c>
       <c r="F106" s="2">
-        <v>3397</v>
+        <v>3191</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>15</v>
@@ -22062,7 +22056,7 @@
         <v>14</v>
       </c>
       <c r="F107" s="2">
-        <v>2576</v>
+        <v>2024</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>15</v>
@@ -22094,7 +22088,7 @@
         <v>14</v>
       </c>
       <c r="F108" s="2">
-        <v>1468</v>
+        <v>2141</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>15</v>
@@ -22126,7 +22120,7 @@
         <v>14</v>
       </c>
       <c r="F109" s="2">
-        <v>1354</v>
+        <v>1115</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>15</v>
@@ -22158,7 +22152,7 @@
         <v>14</v>
       </c>
       <c r="F110" s="2">
-        <v>4128</v>
+        <v>3138</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>15</v>
@@ -22190,7 +22184,7 @@
         <v>14</v>
       </c>
       <c r="F111" s="2">
-        <v>4713</v>
+        <v>2260</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>15</v>
@@ -22222,7 +22216,7 @@
         <v>14</v>
       </c>
       <c r="F112" s="2">
-        <v>3288</v>
+        <v>1384</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>15</v>
@@ -22254,7 +22248,7 @@
         <v>14</v>
       </c>
       <c r="F113" s="2">
-        <v>1502</v>
+        <v>3180</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>15</v>
@@ -22286,7 +22280,7 @@
         <v>14</v>
       </c>
       <c r="F114" s="2">
-        <v>3414</v>
+        <v>1175</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>15</v>
@@ -22318,7 +22312,7 @@
         <v>14</v>
       </c>
       <c r="F115" s="2">
-        <v>1284</v>
+        <v>2537</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>15</v>
@@ -22350,7 +22344,7 @@
         <v>14</v>
       </c>
       <c r="F116" s="2">
-        <v>1015</v>
+        <v>1810</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>15</v>
@@ -22382,7 +22376,7 @@
         <v>14</v>
       </c>
       <c r="F117" s="2">
-        <v>1420</v>
+        <v>4275</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>15</v>
@@ -22414,7 +22408,7 @@
         <v>14</v>
       </c>
       <c r="F118" s="2">
-        <v>2613</v>
+        <v>4538</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>15</v>
@@ -22446,7 +22440,7 @@
         <v>14</v>
       </c>
       <c r="F119" s="2">
-        <v>3250</v>
+        <v>2133</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>15</v>
@@ -22478,7 +22472,7 @@
         <v>14</v>
       </c>
       <c r="F120" s="2">
-        <v>861</v>
+        <v>2883</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>15</v>
@@ -22510,7 +22504,7 @@
         <v>14</v>
       </c>
       <c r="F121" s="2">
-        <v>4711</v>
+        <v>2959</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>15</v>
@@ -22542,7 +22536,7 @@
         <v>14</v>
       </c>
       <c r="F122" s="2">
-        <v>3991</v>
+        <v>902</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>15</v>
@@ -22574,7 +22568,7 @@
         <v>14</v>
       </c>
       <c r="F123" s="2">
-        <v>4485</v>
+        <v>3496</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>15</v>
@@ -22606,7 +22600,7 @@
         <v>14</v>
       </c>
       <c r="F124" s="2">
-        <v>962</v>
+        <v>2788</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>15</v>
@@ -22638,7 +22632,7 @@
         <v>14</v>
       </c>
       <c r="F125" s="2">
-        <v>3175</v>
+        <v>1325</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>15</v>
@@ -22670,7 +22664,7 @@
         <v>14</v>
       </c>
       <c r="F126" s="2">
-        <v>2493</v>
+        <v>3627</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>15</v>
@@ -22702,7 +22696,7 @@
         <v>14</v>
       </c>
       <c r="F127" s="2">
-        <v>4383</v>
+        <v>2597</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>15</v>
@@ -22734,7 +22728,7 @@
         <v>14</v>
       </c>
       <c r="F128" s="2">
-        <v>2448</v>
+        <v>4125</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>15</v>
@@ -22766,7 +22760,7 @@
         <v>14</v>
       </c>
       <c r="F129" s="2">
-        <v>4335</v>
+        <v>1989</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>15</v>
@@ -22798,7 +22792,7 @@
         <v>14</v>
       </c>
       <c r="F130" s="2">
-        <v>2792</v>
+        <v>1767</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>15</v>
@@ -22830,7 +22824,7 @@
         <v>14</v>
       </c>
       <c r="F131" s="2">
-        <v>4762</v>
+        <v>1556</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>15</v>
@@ -22862,7 +22856,7 @@
         <v>14</v>
       </c>
       <c r="F132" s="2">
-        <v>4467</v>
+        <v>3417</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>15</v>
@@ -22894,7 +22888,7 @@
         <v>14</v>
       </c>
       <c r="F133" s="2">
-        <v>1659</v>
+        <v>3124</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>15</v>
@@ -22926,7 +22920,7 @@
         <v>14</v>
       </c>
       <c r="F134" s="2">
-        <v>3633</v>
+        <v>2486</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>15</v>
@@ -22958,7 +22952,7 @@
         <v>14</v>
       </c>
       <c r="F135" s="2">
-        <v>3127</v>
+        <v>1814</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>15</v>
@@ -22990,7 +22984,7 @@
         <v>14</v>
       </c>
       <c r="F136" s="2">
-        <v>2143</v>
+        <v>1404</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>15</v>
@@ -23022,7 +23016,7 @@
         <v>14</v>
       </c>
       <c r="F137" s="2">
-        <v>2254</v>
+        <v>3928</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>15</v>
@@ -23054,7 +23048,7 @@
         <v>14</v>
       </c>
       <c r="F138" s="2">
-        <v>4462</v>
+        <v>1578</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>15</v>
@@ -23086,7 +23080,7 @@
         <v>14</v>
       </c>
       <c r="F139" s="2">
-        <v>810</v>
+        <v>2511</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>15</v>
@@ -23118,7 +23112,7 @@
         <v>14</v>
       </c>
       <c r="F140" s="2">
-        <v>1113</v>
+        <v>4137</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>15</v>
@@ -23150,7 +23144,7 @@
         <v>14</v>
       </c>
       <c r="F141" s="2">
-        <v>935</v>
+        <v>4336</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>15</v>
@@ -23182,7 +23176,7 @@
         <v>14</v>
       </c>
       <c r="F142" s="2">
-        <v>1944</v>
+        <v>3949</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>15</v>
@@ -23214,7 +23208,7 @@
         <v>14</v>
       </c>
       <c r="F143" s="2">
-        <v>4773</v>
+        <v>2632</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>15</v>
@@ -23246,7 +23240,7 @@
         <v>14</v>
       </c>
       <c r="F144" s="2">
-        <v>1483</v>
+        <v>4317</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>15</v>
@@ -23278,7 +23272,7 @@
         <v>14</v>
       </c>
       <c r="F145" s="2">
-        <v>1740</v>
+        <v>1159</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>15</v>
@@ -23310,7 +23304,7 @@
         <v>14</v>
       </c>
       <c r="F146" s="2">
-        <v>1288</v>
+        <v>2252</v>
       </c>
       <c r="G146" s="2" t="s">
         <v>15</v>
@@ -23342,7 +23336,7 @@
         <v>14</v>
       </c>
       <c r="F147" s="2">
-        <v>2485</v>
+        <v>4334</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>15</v>
@@ -23374,7 +23368,7 @@
         <v>14</v>
       </c>
       <c r="F148" s="2">
-        <v>1376</v>
+        <v>852</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>15</v>
@@ -23406,7 +23400,7 @@
         <v>14</v>
       </c>
       <c r="F149" s="2">
-        <v>1032</v>
+        <v>1685</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>15</v>
@@ -23438,7 +23432,7 @@
         <v>14</v>
       </c>
       <c r="F150" s="2">
-        <v>3957</v>
+        <v>3085</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>15</v>
@@ -23470,7 +23464,7 @@
         <v>14</v>
       </c>
       <c r="F151" s="2">
-        <v>820</v>
+        <v>3563</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>15</v>
@@ -23502,7 +23496,7 @@
         <v>14</v>
       </c>
       <c r="F152" s="2">
-        <v>2648</v>
+        <v>4313</v>
       </c>
       <c r="G152" s="2" t="s">
         <v>15</v>
@@ -23534,7 +23528,7 @@
         <v>14</v>
       </c>
       <c r="F153" s="2">
-        <v>3346</v>
+        <v>4780</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>15</v>
@@ -23566,7 +23560,7 @@
         <v>14</v>
       </c>
       <c r="F154" s="2">
-        <v>2947</v>
+        <v>3373</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>15</v>
@@ -23598,7 +23592,7 @@
         <v>14</v>
       </c>
       <c r="F155" s="2">
-        <v>3881</v>
+        <v>3441</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>15</v>
@@ -23630,7 +23624,7 @@
         <v>14</v>
       </c>
       <c r="F156" s="2">
-        <v>925</v>
+        <v>3472</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>15</v>
@@ -23662,7 +23656,7 @@
         <v>14</v>
       </c>
       <c r="F157" s="2">
-        <v>2242</v>
+        <v>1661</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>15</v>
@@ -23694,7 +23688,7 @@
         <v>14</v>
       </c>
       <c r="F158" s="2">
-        <v>2471</v>
+        <v>4015</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>15</v>
@@ -23726,7 +23720,7 @@
         <v>14</v>
       </c>
       <c r="F159" s="2">
-        <v>2063</v>
+        <v>2608</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>15</v>
@@ -23758,7 +23752,7 @@
         <v>14</v>
       </c>
       <c r="F160" s="2">
-        <v>3771</v>
+        <v>4462</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>15</v>
@@ -23790,7 +23784,7 @@
         <v>14</v>
       </c>
       <c r="F161" s="2">
-        <v>2034</v>
+        <v>2903</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>15</v>
@@ -23822,7 +23816,7 @@
         <v>14</v>
       </c>
       <c r="F162" s="2">
-        <v>2230</v>
+        <v>3751</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>15</v>
@@ -23854,7 +23848,7 @@
         <v>14</v>
       </c>
       <c r="F163" s="2">
-        <v>3672</v>
+        <v>2032</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>15</v>
@@ -23886,7 +23880,7 @@
         <v>14</v>
       </c>
       <c r="F164" s="2">
-        <v>999</v>
+        <v>1521</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>15</v>
@@ -23918,7 +23912,7 @@
         <v>14</v>
       </c>
       <c r="F165" s="2">
-        <v>3444</v>
+        <v>3492</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>15</v>
@@ -23950,7 +23944,7 @@
         <v>14</v>
       </c>
       <c r="F166" s="2">
-        <v>2163</v>
+        <v>4072</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>15</v>
@@ -23982,7 +23976,7 @@
         <v>14</v>
       </c>
       <c r="F167" s="2">
-        <v>4694</v>
+        <v>1521</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>15</v>
@@ -24014,7 +24008,7 @@
         <v>14</v>
       </c>
       <c r="F168" s="2">
-        <v>3442</v>
+        <v>2070</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>15</v>
@@ -24046,7 +24040,7 @@
         <v>14</v>
       </c>
       <c r="F169" s="2">
-        <v>2894</v>
+        <v>1947</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>15</v>
@@ -24078,7 +24072,7 @@
         <v>14</v>
       </c>
       <c r="F170" s="2">
-        <v>3853</v>
+        <v>2430</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>15</v>
@@ -24110,7 +24104,7 @@
         <v>14</v>
       </c>
       <c r="F171" s="2">
-        <v>1588</v>
+        <v>4406</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>15</v>
@@ -24142,7 +24136,7 @@
         <v>14</v>
       </c>
       <c r="F172" s="2">
-        <v>4363</v>
+        <v>4757</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>15</v>
@@ -24174,7 +24168,7 @@
         <v>14</v>
       </c>
       <c r="F173" s="2">
-        <v>4297</v>
+        <v>4077</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>15</v>
@@ -24206,7 +24200,7 @@
         <v>14</v>
       </c>
       <c r="F174" s="2">
-        <v>4250</v>
+        <v>4523</v>
       </c>
       <c r="G174" s="2" t="s">
         <v>15</v>
@@ -24238,7 +24232,7 @@
         <v>14</v>
       </c>
       <c r="F175" s="2">
-        <v>2327</v>
+        <v>3214</v>
       </c>
       <c r="G175" s="2" t="s">
         <v>15</v>
@@ -24270,7 +24264,7 @@
         <v>14</v>
       </c>
       <c r="F176" s="2">
-        <v>4469</v>
+        <v>2009</v>
       </c>
       <c r="G176" s="2" t="s">
         <v>15</v>
@@ -24302,7 +24296,7 @@
         <v>14</v>
       </c>
       <c r="F177" s="2">
-        <v>4609</v>
+        <v>1529</v>
       </c>
       <c r="G177" s="2" t="s">
         <v>15</v>
@@ -24334,7 +24328,7 @@
         <v>14</v>
       </c>
       <c r="F178" s="2">
-        <v>3985</v>
+        <v>3449</v>
       </c>
       <c r="G178" s="2" t="s">
         <v>15</v>
@@ -24366,7 +24360,7 @@
         <v>14</v>
       </c>
       <c r="F179" s="2">
-        <v>1390</v>
+        <v>4166</v>
       </c>
       <c r="G179" s="2" t="s">
         <v>15</v>
@@ -24398,7 +24392,7 @@
         <v>14</v>
       </c>
       <c r="F180" s="2">
-        <v>1346</v>
+        <v>2803</v>
       </c>
       <c r="G180" s="2" t="s">
         <v>15</v>
@@ -24430,7 +24424,7 @@
         <v>14</v>
       </c>
       <c r="F181" s="2">
-        <v>1497</v>
+        <v>4730</v>
       </c>
       <c r="G181" s="2" t="s">
         <v>15</v>
@@ -24462,7 +24456,7 @@
         <v>14</v>
       </c>
       <c r="F182" s="2">
-        <v>2437</v>
+        <v>2136</v>
       </c>
       <c r="G182" s="2" t="s">
         <v>15</v>
@@ -24494,7 +24488,7 @@
         <v>14</v>
       </c>
       <c r="F183" s="2">
-        <v>2090</v>
+        <v>3114</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>15</v>
@@ -24526,7 +24520,7 @@
         <v>14</v>
       </c>
       <c r="F184" s="2">
-        <v>2063</v>
+        <v>4197</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>15</v>
@@ -24558,7 +24552,7 @@
         <v>14</v>
       </c>
       <c r="F185" s="2">
-        <v>4663</v>
+        <v>3632</v>
       </c>
       <c r="G185" s="2" t="s">
         <v>15</v>
@@ -24590,7 +24584,7 @@
         <v>14</v>
       </c>
       <c r="F186" s="2">
-        <v>4323</v>
+        <v>2447</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>15</v>
@@ -24622,7 +24616,7 @@
         <v>14</v>
       </c>
       <c r="F187" s="2">
-        <v>4749</v>
+        <v>4336</v>
       </c>
       <c r="G187" s="2" t="s">
         <v>15</v>
@@ -24654,7 +24648,7 @@
         <v>14</v>
       </c>
       <c r="F188" s="2">
-        <v>2363</v>
+        <v>4277</v>
       </c>
       <c r="G188" s="2" t="s">
         <v>15</v>
@@ -24686,7 +24680,7 @@
         <v>14</v>
       </c>
       <c r="F189" s="2">
-        <v>2362</v>
+        <v>3617</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>15</v>
@@ -24718,7 +24712,7 @@
         <v>14</v>
       </c>
       <c r="F190" s="2">
-        <v>3670</v>
+        <v>3226</v>
       </c>
       <c r="G190" s="2" t="s">
         <v>15</v>
@@ -24750,7 +24744,7 @@
         <v>14</v>
       </c>
       <c r="F191" s="2">
-        <v>1314</v>
+        <v>2749</v>
       </c>
       <c r="G191" s="2" t="s">
         <v>15</v>
@@ -24782,7 +24776,7 @@
         <v>14</v>
       </c>
       <c r="F192" s="2">
-        <v>3782</v>
+        <v>4620</v>
       </c>
       <c r="G192" s="2" t="s">
         <v>15</v>
@@ -24814,7 +24808,7 @@
         <v>14</v>
       </c>
       <c r="F193" s="2">
-        <v>4541</v>
+        <v>2946</v>
       </c>
       <c r="G193" s="2" t="s">
         <v>15</v>
@@ -24846,7 +24840,7 @@
         <v>14</v>
       </c>
       <c r="F194" s="2">
-        <v>4286</v>
+        <v>1051</v>
       </c>
       <c r="G194" s="2" t="s">
         <v>15</v>
@@ -24878,7 +24872,7 @@
         <v>14</v>
       </c>
       <c r="F195" s="2">
-        <v>3146</v>
+        <v>3301</v>
       </c>
       <c r="G195" s="2" t="s">
         <v>15</v>
@@ -24910,7 +24904,7 @@
         <v>14</v>
       </c>
       <c r="F196" s="2">
-        <v>1097</v>
+        <v>3206</v>
       </c>
       <c r="G196" s="2" t="s">
         <v>15</v>
@@ -24942,7 +24936,7 @@
         <v>14</v>
       </c>
       <c r="F197" s="2">
-        <v>2125</v>
+        <v>2667</v>
       </c>
       <c r="G197" s="2" t="s">
         <v>15</v>
@@ -24974,7 +24968,7 @@
         <v>14</v>
       </c>
       <c r="F198" s="2">
-        <v>1346</v>
+        <v>2543</v>
       </c>
       <c r="G198" s="2" t="s">
         <v>15</v>
@@ -25006,7 +25000,7 @@
         <v>14</v>
       </c>
       <c r="F199" s="2">
-        <v>4650</v>
+        <v>869</v>
       </c>
       <c r="G199" s="2" t="s">
         <v>15</v>
@@ -25038,7 +25032,7 @@
         <v>14</v>
       </c>
       <c r="F200" s="2">
-        <v>2897</v>
+        <v>4288</v>
       </c>
       <c r="G200" s="2" t="s">
         <v>15</v>
@@ -25070,7 +25064,7 @@
         <v>14</v>
       </c>
       <c r="F201" s="2">
-        <v>998</v>
+        <v>2687</v>
       </c>
       <c r="G201" s="2" t="s">
         <v>15</v>
@@ -25102,7 +25096,7 @@
         <v>14</v>
       </c>
       <c r="F202" s="2">
-        <v>2471</v>
+        <v>1244</v>
       </c>
       <c r="G202" s="2" t="s">
         <v>15</v>
@@ -25134,7 +25128,7 @@
         <v>14</v>
       </c>
       <c r="F203" s="2">
-        <v>3789</v>
+        <v>2584</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>15</v>
@@ -25166,7 +25160,7 @@
         <v>14</v>
       </c>
       <c r="F204" s="2">
-        <v>4149</v>
+        <v>900</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>15</v>
@@ -25198,7 +25192,7 @@
         <v>14</v>
       </c>
       <c r="F205" s="2">
-        <v>3862</v>
+        <v>1331</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>15</v>
@@ -25230,7 +25224,7 @@
         <v>14</v>
       </c>
       <c r="F206" s="2">
-        <v>1620</v>
+        <v>4597</v>
       </c>
       <c r="G206" s="2" t="s">
         <v>15</v>
@@ -25262,7 +25256,7 @@
         <v>14</v>
       </c>
       <c r="F207" s="2">
-        <v>3294</v>
+        <v>2234</v>
       </c>
       <c r="G207" s="2" t="s">
         <v>15</v>
@@ -25294,7 +25288,7 @@
         <v>14</v>
       </c>
       <c r="F208" s="2">
-        <v>4724</v>
+        <v>4750</v>
       </c>
       <c r="G208" s="2" t="s">
         <v>15</v>
@@ -25326,7 +25320,7 @@
         <v>14</v>
       </c>
       <c r="F209" s="2">
-        <v>3771</v>
+        <v>2336</v>
       </c>
       <c r="G209" s="2" t="s">
         <v>15</v>
@@ -25358,7 +25352,7 @@
         <v>14</v>
       </c>
       <c r="F210" s="2">
-        <v>1547</v>
+        <v>961</v>
       </c>
       <c r="G210" s="2" t="s">
         <v>15</v>
@@ -25390,7 +25384,7 @@
         <v>14</v>
       </c>
       <c r="F211" s="2">
-        <v>2393</v>
+        <v>4540</v>
       </c>
       <c r="G211" s="2" t="s">
         <v>15</v>
@@ -25422,7 +25416,7 @@
         <v>14</v>
       </c>
       <c r="F212" s="2">
-        <v>3884</v>
+        <v>2357</v>
       </c>
       <c r="G212" s="2" t="s">
         <v>15</v>
@@ -25454,7 +25448,7 @@
         <v>14</v>
       </c>
       <c r="F213" s="2">
-        <v>1206</v>
+        <v>4134</v>
       </c>
       <c r="G213" s="2" t="s">
         <v>15</v>
@@ -25486,7 +25480,7 @@
         <v>14</v>
       </c>
       <c r="F214" s="2">
-        <v>1219</v>
+        <v>1352</v>
       </c>
       <c r="G214" s="2" t="s">
         <v>15</v>
@@ -25518,7 +25512,7 @@
         <v>14</v>
       </c>
       <c r="F215" s="2">
-        <v>4412</v>
+        <v>2546</v>
       </c>
       <c r="G215" s="2" t="s">
         <v>15</v>
@@ -25550,7 +25544,7 @@
         <v>14</v>
       </c>
       <c r="F216" s="2">
-        <v>2103</v>
+        <v>2160</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>15</v>
@@ -25582,7 +25576,7 @@
         <v>14</v>
       </c>
       <c r="F217" s="2">
-        <v>3549</v>
+        <v>963</v>
       </c>
       <c r="G217" s="2" t="s">
         <v>15</v>
@@ -25614,7 +25608,7 @@
         <v>14</v>
       </c>
       <c r="F218" s="2">
-        <v>4733</v>
+        <v>3333</v>
       </c>
       <c r="G218" s="2" t="s">
         <v>15</v>
@@ -25646,7 +25640,7 @@
         <v>14</v>
       </c>
       <c r="F219" s="2">
-        <v>2348</v>
+        <v>4758</v>
       </c>
       <c r="G219" s="2" t="s">
         <v>15</v>
@@ -25678,7 +25672,7 @@
         <v>14</v>
       </c>
       <c r="F220" s="2">
-        <v>4617</v>
+        <v>4434</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>15</v>
@@ -25710,7 +25704,7 @@
         <v>14</v>
       </c>
       <c r="F221" s="2">
-        <v>3041</v>
+        <v>3774</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>15</v>
@@ -25742,7 +25736,7 @@
         <v>14</v>
       </c>
       <c r="F222" s="2">
-        <v>4502</v>
+        <v>2010</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>15</v>
@@ -25774,7 +25768,7 @@
         <v>14</v>
       </c>
       <c r="F223" s="2">
-        <v>4086</v>
+        <v>1330</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>15</v>
@@ -25806,7 +25800,7 @@
         <v>14</v>
       </c>
       <c r="F224" s="2">
-        <v>4012</v>
+        <v>3665</v>
       </c>
       <c r="G224" s="2" t="s">
         <v>15</v>
@@ -25838,7 +25832,7 @@
         <v>14</v>
       </c>
       <c r="F225" s="2">
-        <v>2414</v>
+        <v>4365</v>
       </c>
       <c r="G225" s="2" t="s">
         <v>15</v>
@@ -25870,7 +25864,7 @@
         <v>14</v>
       </c>
       <c r="F226" s="2">
-        <v>3980</v>
+        <v>1460</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>15</v>
@@ -25902,7 +25896,7 @@
         <v>14</v>
       </c>
       <c r="F227" s="2">
-        <v>2527</v>
+        <v>2277</v>
       </c>
       <c r="G227" s="2" t="s">
         <v>15</v>
@@ -25934,7 +25928,7 @@
         <v>14</v>
       </c>
       <c r="F228" s="2">
-        <v>1888</v>
+        <v>1021</v>
       </c>
       <c r="G228" s="2" t="s">
         <v>15</v>
@@ -25966,7 +25960,7 @@
         <v>14</v>
       </c>
       <c r="F229" s="2">
-        <v>1758</v>
+        <v>2507</v>
       </c>
       <c r="G229" s="2" t="s">
         <v>15</v>
@@ -25998,7 +25992,7 @@
         <v>14</v>
       </c>
       <c r="F230" s="2">
-        <v>1950</v>
+        <v>2323</v>
       </c>
       <c r="G230" s="2" t="s">
         <v>15</v>
@@ -26030,7 +26024,7 @@
         <v>14</v>
       </c>
       <c r="F231" s="2">
-        <v>2309</v>
+        <v>1547</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>15</v>
@@ -26062,7 +26056,7 @@
         <v>14</v>
       </c>
       <c r="F232" s="2">
-        <v>1530</v>
+        <v>4154</v>
       </c>
       <c r="G232" s="2" t="s">
         <v>15</v>
@@ -26094,7 +26088,7 @@
         <v>14</v>
       </c>
       <c r="F233" s="2">
-        <v>3991</v>
+        <v>2503</v>
       </c>
       <c r="G233" s="2" t="s">
         <v>15</v>
@@ -26126,7 +26120,7 @@
         <v>14</v>
       </c>
       <c r="F234" s="2">
-        <v>4044</v>
+        <v>3448</v>
       </c>
       <c r="G234" s="2" t="s">
         <v>15</v>
@@ -26158,7 +26152,7 @@
         <v>14</v>
       </c>
       <c r="F235" s="2">
-        <v>2978</v>
+        <v>1404</v>
       </c>
       <c r="G235" s="2" t="s">
         <v>15</v>
@@ -26190,7 +26184,7 @@
         <v>14</v>
       </c>
       <c r="F236" s="2">
-        <v>4613</v>
+        <v>808</v>
       </c>
       <c r="G236" s="2" t="s">
         <v>15</v>
@@ -26222,7 +26216,7 @@
         <v>14</v>
       </c>
       <c r="F237" s="2">
-        <v>1125</v>
+        <v>2729</v>
       </c>
       <c r="G237" s="2" t="s">
         <v>15</v>
@@ -26254,7 +26248,7 @@
         <v>14</v>
       </c>
       <c r="F238" s="2">
-        <v>2895</v>
+        <v>1060</v>
       </c>
       <c r="G238" s="2" t="s">
         <v>15</v>
@@ -26286,7 +26280,7 @@
         <v>14</v>
       </c>
       <c r="F239" s="2">
-        <v>1685</v>
+        <v>2753</v>
       </c>
       <c r="G239" s="2" t="s">
         <v>15</v>
@@ -26318,7 +26312,7 @@
         <v>14</v>
       </c>
       <c r="F240" s="2">
-        <v>2957</v>
+        <v>3516</v>
       </c>
       <c r="G240" s="2" t="s">
         <v>15</v>
@@ -26350,7 +26344,7 @@
         <v>14</v>
       </c>
       <c r="F241" s="2">
-        <v>4516</v>
+        <v>4778</v>
       </c>
       <c r="G241" s="2" t="s">
         <v>15</v>
@@ -26382,7 +26376,7 @@
         <v>14</v>
       </c>
       <c r="F242" s="2">
-        <v>925</v>
+        <v>3434</v>
       </c>
       <c r="G242" s="2" t="s">
         <v>15</v>
@@ -26414,7 +26408,7 @@
         <v>14</v>
       </c>
       <c r="F243" s="2">
-        <v>3823</v>
+        <v>3187</v>
       </c>
       <c r="G243" s="2" t="s">
         <v>15</v>
@@ -26446,7 +26440,7 @@
         <v>14</v>
       </c>
       <c r="F244" s="2">
-        <v>4783</v>
+        <v>3387</v>
       </c>
       <c r="G244" s="2" t="s">
         <v>15</v>
@@ -26478,7 +26472,7 @@
         <v>14</v>
       </c>
       <c r="F245" s="2">
-        <v>1335</v>
+        <v>3258</v>
       </c>
       <c r="G245" s="2" t="s">
         <v>15</v>
@@ -26510,7 +26504,7 @@
         <v>14</v>
       </c>
       <c r="F246" s="2">
-        <v>4099</v>
+        <v>1382</v>
       </c>
       <c r="G246" s="2" t="s">
         <v>15</v>
@@ -26542,7 +26536,7 @@
         <v>14</v>
       </c>
       <c r="F247" s="2">
-        <v>1469</v>
+        <v>4558</v>
       </c>
       <c r="G247" s="2" t="s">
         <v>15</v>
@@ -26574,7 +26568,7 @@
         <v>14</v>
       </c>
       <c r="F248" s="2">
-        <v>3399</v>
+        <v>3086</v>
       </c>
       <c r="G248" s="2" t="s">
         <v>15</v>
@@ -26606,7 +26600,7 @@
         <v>14</v>
       </c>
       <c r="F249" s="2">
-        <v>3351</v>
+        <v>2447</v>
       </c>
       <c r="G249" s="2" t="s">
         <v>15</v>
@@ -26638,7 +26632,7 @@
         <v>14</v>
       </c>
       <c r="F250" s="2">
-        <v>2661</v>
+        <v>2425</v>
       </c>
       <c r="G250" s="2" t="s">
         <v>15</v>
@@ -26670,7 +26664,7 @@
         <v>14</v>
       </c>
       <c r="F251" s="2">
-        <v>2127</v>
+        <v>1027</v>
       </c>
       <c r="G251" s="2" t="s">
         <v>15</v>
@@ -26702,7 +26696,7 @@
         <v>14</v>
       </c>
       <c r="F252" s="2">
-        <v>3504</v>
+        <v>4737</v>
       </c>
       <c r="G252" s="2" t="s">
         <v>15</v>
@@ -26734,7 +26728,7 @@
         <v>14</v>
       </c>
       <c r="F253" s="2">
-        <v>2838</v>
+        <v>3855</v>
       </c>
       <c r="G253" s="2" t="s">
         <v>15</v>
@@ -26766,7 +26760,7 @@
         <v>14</v>
       </c>
       <c r="F254" s="2">
-        <v>1541</v>
+        <v>3756</v>
       </c>
       <c r="G254" s="2" t="s">
         <v>15</v>
@@ -26798,7 +26792,7 @@
         <v>14</v>
       </c>
       <c r="F255" s="2">
-        <v>2303</v>
+        <v>810</v>
       </c>
       <c r="G255" s="2" t="s">
         <v>15</v>
@@ -26830,7 +26824,7 @@
         <v>14</v>
       </c>
       <c r="F256" s="2">
-        <v>4435</v>
+        <v>1571</v>
       </c>
       <c r="G256" s="2" t="s">
         <v>15</v>
@@ -26862,7 +26856,7 @@
         <v>14</v>
       </c>
       <c r="F257" s="2">
-        <v>4695</v>
+        <v>1393</v>
       </c>
       <c r="G257" s="2" t="s">
         <v>15</v>
@@ -26894,7 +26888,7 @@
         <v>14</v>
       </c>
       <c r="F258" s="2">
-        <v>2667</v>
+        <v>1065</v>
       </c>
       <c r="G258" s="2" t="s">
         <v>15</v>
@@ -26926,7 +26920,7 @@
         <v>14</v>
       </c>
       <c r="F259" s="2">
-        <v>2269</v>
+        <v>4754</v>
       </c>
       <c r="G259" s="2" t="s">
         <v>15</v>
@@ -26958,7 +26952,7 @@
         <v>14</v>
       </c>
       <c r="F260" s="2">
-        <v>1099</v>
+        <v>2996</v>
       </c>
       <c r="G260" s="2" t="s">
         <v>15</v>
@@ -26990,7 +26984,7 @@
         <v>14</v>
       </c>
       <c r="F261" s="2">
-        <v>4432</v>
+        <v>1046</v>
       </c>
       <c r="G261" s="2" t="s">
         <v>15</v>
@@ -27022,7 +27016,7 @@
         <v>14</v>
       </c>
       <c r="F262" s="2">
-        <v>1494</v>
+        <v>4727</v>
       </c>
       <c r="G262" s="2" t="s">
         <v>15</v>
@@ -27054,7 +27048,7 @@
         <v>14</v>
       </c>
       <c r="F263" s="2">
-        <v>2424</v>
+        <v>4471</v>
       </c>
       <c r="G263" s="2" t="s">
         <v>15</v>
@@ -27086,7 +27080,7 @@
         <v>14</v>
       </c>
       <c r="F264" s="2">
-        <v>4345</v>
+        <v>2581</v>
       </c>
       <c r="G264" s="2" t="s">
         <v>15</v>
@@ -27118,7 +27112,7 @@
         <v>14</v>
       </c>
       <c r="F265" s="2">
-        <v>2886</v>
+        <v>864</v>
       </c>
       <c r="G265" s="2" t="s">
         <v>15</v>
@@ -27150,7 +27144,7 @@
         <v>14</v>
       </c>
       <c r="F266" s="2">
-        <v>4340</v>
+        <v>1489</v>
       </c>
       <c r="G266" s="2" t="s">
         <v>15</v>
@@ -27182,7 +27176,7 @@
         <v>14</v>
       </c>
       <c r="F267" s="2">
-        <v>1643</v>
+        <v>4662</v>
       </c>
       <c r="G267" s="2" t="s">
         <v>15</v>
@@ -27214,7 +27208,7 @@
         <v>14</v>
       </c>
       <c r="F268" s="2">
-        <v>850</v>
+        <v>3946</v>
       </c>
       <c r="G268" s="2" t="s">
         <v>15</v>
@@ -27246,7 +27240,7 @@
         <v>14</v>
       </c>
       <c r="F269" s="2">
-        <v>4388</v>
+        <v>1040</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>15</v>
@@ -27278,7 +27272,7 @@
         <v>14</v>
       </c>
       <c r="F270" s="2">
-        <v>4741</v>
+        <v>2190</v>
       </c>
       <c r="G270" s="2" t="s">
         <v>15</v>
@@ -27310,7 +27304,7 @@
         <v>14</v>
       </c>
       <c r="F271" s="2">
-        <v>1073</v>
+        <v>1139</v>
       </c>
       <c r="G271" s="2" t="s">
         <v>15</v>
@@ -27342,7 +27336,7 @@
         <v>14</v>
       </c>
       <c r="F272" s="2">
-        <v>2539</v>
+        <v>1466</v>
       </c>
       <c r="G272" s="2" t="s">
         <v>15</v>
@@ -27374,7 +27368,7 @@
         <v>14</v>
       </c>
       <c r="F273" s="2">
-        <v>3342</v>
+        <v>1500</v>
       </c>
       <c r="G273" s="2" t="s">
         <v>15</v>
@@ -27406,7 +27400,7 @@
         <v>14</v>
       </c>
       <c r="F274" s="2">
-        <v>2948</v>
+        <v>2191</v>
       </c>
       <c r="G274" s="2" t="s">
         <v>15</v>
@@ -27438,7 +27432,7 @@
         <v>14</v>
       </c>
       <c r="F275" s="2">
-        <v>3743</v>
+        <v>4675</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>15</v>
@@ -27470,7 +27464,7 @@
         <v>14</v>
       </c>
       <c r="F276" s="2">
-        <v>2183</v>
+        <v>1760</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>15</v>
@@ -27502,7 +27496,7 @@
         <v>14</v>
       </c>
       <c r="F277" s="2">
-        <v>2051</v>
+        <v>3307</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>15</v>
@@ -27534,7 +27528,7 @@
         <v>14</v>
       </c>
       <c r="F278" s="2">
-        <v>3914</v>
+        <v>3276</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>15</v>
@@ -27566,7 +27560,7 @@
         <v>14</v>
       </c>
       <c r="F279" s="2">
-        <v>1181</v>
+        <v>1646</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>15</v>
@@ -27598,7 +27592,7 @@
         <v>14</v>
       </c>
       <c r="F280" s="2">
-        <v>1607</v>
+        <v>2557</v>
       </c>
       <c r="G280" s="2" t="s">
         <v>15</v>
@@ -27630,7 +27624,7 @@
         <v>14</v>
       </c>
       <c r="F281" s="2">
-        <v>1599</v>
+        <v>848</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>15</v>
@@ -27662,7 +27656,7 @@
         <v>14</v>
       </c>
       <c r="F282" s="2">
-        <v>2316</v>
+        <v>1593</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>15</v>
@@ -27694,7 +27688,7 @@
         <v>14</v>
       </c>
       <c r="F283" s="2">
-        <v>4359</v>
+        <v>3323</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>15</v>
@@ -27726,7 +27720,7 @@
         <v>14</v>
       </c>
       <c r="F284" s="2">
-        <v>3382</v>
+        <v>4342</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>15</v>
@@ -27758,7 +27752,7 @@
         <v>14</v>
       </c>
       <c r="F285" s="2">
-        <v>4169</v>
+        <v>1283</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>15</v>
@@ -27790,7 +27784,7 @@
         <v>14</v>
       </c>
       <c r="F286" s="2">
-        <v>2732</v>
+        <v>4303</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>15</v>
@@ -27822,7 +27816,7 @@
         <v>14</v>
       </c>
       <c r="F287" s="2">
-        <v>3281</v>
+        <v>2164</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>15</v>
@@ -27854,7 +27848,7 @@
         <v>14</v>
       </c>
       <c r="F288" s="2">
-        <v>4667</v>
+        <v>2351</v>
       </c>
       <c r="G288" s="2" t="s">
         <v>15</v>
@@ -27886,7 +27880,7 @@
         <v>14</v>
       </c>
       <c r="F289" s="2">
-        <v>4377</v>
+        <v>4096</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>15</v>
@@ -27918,7 +27912,7 @@
         <v>14</v>
       </c>
       <c r="F290" s="2">
-        <v>4130</v>
+        <v>1969</v>
       </c>
       <c r="G290" s="2" t="s">
         <v>15</v>
@@ -27950,7 +27944,7 @@
         <v>14</v>
       </c>
       <c r="F291" s="2">
-        <v>3151</v>
+        <v>1407</v>
       </c>
       <c r="G291" s="2" t="s">
         <v>15</v>
@@ -27982,7 +27976,7 @@
         <v>14</v>
       </c>
       <c r="F292" s="2">
-        <v>1954</v>
+        <v>3774</v>
       </c>
       <c r="G292" s="2" t="s">
         <v>15</v>
@@ -28014,7 +28008,7 @@
         <v>14</v>
       </c>
       <c r="F293" s="2">
-        <v>2112</v>
+        <v>1455</v>
       </c>
       <c r="G293" s="2" t="s">
         <v>15</v>
@@ -28046,7 +28040,7 @@
         <v>14</v>
       </c>
       <c r="F294" s="2">
-        <v>4415</v>
+        <v>4397</v>
       </c>
       <c r="G294" s="2" t="s">
         <v>15</v>
@@ -28078,7 +28072,7 @@
         <v>14</v>
       </c>
       <c r="F295" s="2">
-        <v>1216</v>
+        <v>3980</v>
       </c>
       <c r="G295" s="2" t="s">
         <v>15</v>
@@ -28110,7 +28104,7 @@
         <v>14</v>
       </c>
       <c r="F296" s="2">
-        <v>3046</v>
+        <v>3857</v>
       </c>
       <c r="G296" s="2" t="s">
         <v>15</v>
@@ -28142,7 +28136,7 @@
         <v>14</v>
       </c>
       <c r="F297" s="2">
-        <v>893</v>
+        <v>1141</v>
       </c>
       <c r="G297" s="2" t="s">
         <v>15</v>
@@ -28174,7 +28168,7 @@
         <v>14</v>
       </c>
       <c r="F298" s="2">
-        <v>2486</v>
+        <v>3478</v>
       </c>
       <c r="G298" s="2" t="s">
         <v>15</v>
@@ -28206,7 +28200,7 @@
         <v>14</v>
       </c>
       <c r="F299" s="2">
-        <v>4583</v>
+        <v>944</v>
       </c>
       <c r="G299" s="2" t="s">
         <v>15</v>
@@ -28238,7 +28232,7 @@
         <v>14</v>
       </c>
       <c r="F300" s="2">
-        <v>2338</v>
+        <v>3936</v>
       </c>
       <c r="G300" s="2" t="s">
         <v>15</v>
@@ -28270,7 +28264,7 @@
         <v>14</v>
       </c>
       <c r="F301" s="2">
-        <v>965</v>
+        <v>1904</v>
       </c>
       <c r="G301" s="2" t="s">
         <v>15</v>
@@ -28302,7 +28296,7 @@
         <v>14</v>
       </c>
       <c r="F302" s="2">
-        <v>1324</v>
+        <v>3637</v>
       </c>
       <c r="G302" s="2" t="s">
         <v>15</v>
@@ -28334,7 +28328,7 @@
         <v>14</v>
       </c>
       <c r="F303" s="2">
-        <v>2451</v>
+        <v>3904</v>
       </c>
       <c r="G303" s="2" t="s">
         <v>15</v>
@@ -28366,7 +28360,7 @@
         <v>14</v>
       </c>
       <c r="F304" s="2">
-        <v>4213</v>
+        <v>1539</v>
       </c>
       <c r="G304" s="2" t="s">
         <v>15</v>
@@ -28398,7 +28392,7 @@
         <v>14</v>
       </c>
       <c r="F305" s="2">
-        <v>3647</v>
+        <v>2509</v>
       </c>
       <c r="G305" s="2" t="s">
         <v>15</v>
@@ -28430,7 +28424,7 @@
         <v>14</v>
       </c>
       <c r="F306" s="2">
-        <v>1684</v>
+        <v>2019</v>
       </c>
       <c r="G306" s="2" t="s">
         <v>15</v>
@@ -28462,7 +28456,7 @@
         <v>14</v>
       </c>
       <c r="F307" s="2">
-        <v>1670</v>
+        <v>1266</v>
       </c>
       <c r="G307" s="2" t="s">
         <v>15</v>
@@ -28494,7 +28488,7 @@
         <v>14</v>
       </c>
       <c r="F308" s="2">
-        <v>2367</v>
+        <v>2105</v>
       </c>
       <c r="G308" s="2" t="s">
         <v>15</v>
@@ -28526,7 +28520,7 @@
         <v>14</v>
       </c>
       <c r="F309" s="2">
-        <v>1288</v>
+        <v>3067</v>
       </c>
       <c r="G309" s="2" t="s">
         <v>15</v>
@@ -28558,7 +28552,7 @@
         <v>14</v>
       </c>
       <c r="F310" s="2">
-        <v>3300</v>
+        <v>1085</v>
       </c>
       <c r="G310" s="2" t="s">
         <v>15</v>
@@ -28590,7 +28584,7 @@
         <v>14</v>
       </c>
       <c r="F311" s="2">
-        <v>3415</v>
+        <v>4028</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>15</v>
@@ -28622,7 +28616,7 @@
         <v>14</v>
       </c>
       <c r="F312" s="2">
-        <v>3792</v>
+        <v>3577</v>
       </c>
       <c r="G312" s="2" t="s">
         <v>15</v>
@@ -28654,7 +28648,7 @@
         <v>14</v>
       </c>
       <c r="F313" s="2">
-        <v>1274</v>
+        <v>2187</v>
       </c>
       <c r="G313" s="2" t="s">
         <v>15</v>
@@ -28686,7 +28680,7 @@
         <v>14</v>
       </c>
       <c r="F314" s="2">
-        <v>1771</v>
+        <v>4572</v>
       </c>
       <c r="G314" s="2" t="s">
         <v>15</v>
@@ -28718,7 +28712,7 @@
         <v>14</v>
       </c>
       <c r="F315" s="2">
-        <v>4733</v>
+        <v>3242</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>15</v>
@@ -28750,7 +28744,7 @@
         <v>14</v>
       </c>
       <c r="F316" s="2">
-        <v>3435</v>
+        <v>3690</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>15</v>
@@ -28782,7 +28776,7 @@
         <v>14</v>
       </c>
       <c r="F317" s="2">
-        <v>1603</v>
+        <v>2733</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>15</v>
@@ -28814,7 +28808,7 @@
         <v>14</v>
       </c>
       <c r="F318" s="2">
-        <v>2956</v>
+        <v>1958</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>15</v>
@@ -28846,7 +28840,7 @@
         <v>14</v>
       </c>
       <c r="F319" s="2">
-        <v>3276</v>
+        <v>4379</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>15</v>
@@ -28878,7 +28872,7 @@
         <v>14</v>
       </c>
       <c r="F320" s="2">
-        <v>3215</v>
+        <v>4308</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>15</v>
@@ -28910,7 +28904,7 @@
         <v>14</v>
       </c>
       <c r="F321" s="2">
-        <v>4657</v>
+        <v>1194</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>15</v>
@@ -28942,7 +28936,7 @@
         <v>14</v>
       </c>
       <c r="F322" s="2">
-        <v>2210</v>
+        <v>4601</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>15</v>
@@ -28974,7 +28968,7 @@
         <v>14</v>
       </c>
       <c r="F323" s="2">
-        <v>2967</v>
+        <v>1397</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>15</v>
@@ -29006,7 +29000,7 @@
         <v>14</v>
       </c>
       <c r="F324" s="2">
-        <v>3405</v>
+        <v>964</v>
       </c>
       <c r="G324" s="2" t="s">
         <v>15</v>
@@ -29038,7 +29032,7 @@
         <v>14</v>
       </c>
       <c r="F325" s="2">
-        <v>4135</v>
+        <v>4190</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>15</v>
@@ -29070,7 +29064,7 @@
         <v>14</v>
       </c>
       <c r="F326" s="2">
-        <v>1862</v>
+        <v>3048</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>15</v>
@@ -29102,7 +29096,7 @@
         <v>14</v>
       </c>
       <c r="F327" s="2">
-        <v>2324</v>
+        <v>4088</v>
       </c>
       <c r="G327" s="2" t="s">
         <v>15</v>
@@ -29134,7 +29128,7 @@
         <v>14</v>
       </c>
       <c r="F328" s="2">
-        <v>2599</v>
+        <v>4479</v>
       </c>
       <c r="G328" s="2" t="s">
         <v>15</v>
@@ -29166,7 +29160,7 @@
         <v>14</v>
       </c>
       <c r="F329" s="2">
-        <v>4183</v>
+        <v>1165</v>
       </c>
       <c r="G329" s="2" t="s">
         <v>15</v>
@@ -29198,7 +29192,7 @@
         <v>14</v>
       </c>
       <c r="F330" s="2">
-        <v>1495</v>
+        <v>3023</v>
       </c>
       <c r="G330" s="2" t="s">
         <v>15</v>
@@ -29230,7 +29224,7 @@
         <v>14</v>
       </c>
       <c r="F331" s="2">
-        <v>3278</v>
+        <v>2526</v>
       </c>
       <c r="G331" s="2" t="s">
         <v>15</v>
@@ -29262,7 +29256,7 @@
         <v>14</v>
       </c>
       <c r="F332" s="2">
-        <v>3538</v>
+        <v>3121</v>
       </c>
       <c r="G332" s="2" t="s">
         <v>15</v>
@@ -29294,7 +29288,7 @@
         <v>14</v>
       </c>
       <c r="F333" s="2">
-        <v>3043</v>
+        <v>4367</v>
       </c>
       <c r="G333" s="2" t="s">
         <v>15</v>
@@ -29326,7 +29320,7 @@
         <v>14</v>
       </c>
       <c r="F334" s="2">
-        <v>2287</v>
+        <v>2689</v>
       </c>
       <c r="G334" s="2" t="s">
         <v>15</v>
@@ -29358,7 +29352,7 @@
         <v>14</v>
       </c>
       <c r="F335" s="2">
-        <v>1486</v>
+        <v>3178</v>
       </c>
       <c r="G335" s="2" t="s">
         <v>15</v>
@@ -29390,7 +29384,7 @@
         <v>14</v>
       </c>
       <c r="F336" s="2">
-        <v>1892</v>
+        <v>1294</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>15</v>
@@ -29422,7 +29416,7 @@
         <v>14</v>
       </c>
       <c r="F337" s="2">
-        <v>1918</v>
+        <v>2394</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>15</v>
@@ -29454,7 +29448,7 @@
         <v>14</v>
       </c>
       <c r="F338" s="2">
-        <v>3334</v>
+        <v>3449</v>
       </c>
       <c r="G338" s="2" t="s">
         <v>15</v>
@@ -29486,7 +29480,7 @@
         <v>14</v>
       </c>
       <c r="F339" s="2">
-        <v>1792</v>
+        <v>3341</v>
       </c>
       <c r="G339" s="2" t="s">
         <v>15</v>
@@ -29518,7 +29512,7 @@
         <v>14</v>
       </c>
       <c r="F340" s="2">
-        <v>954</v>
+        <v>3243</v>
       </c>
       <c r="G340" s="2" t="s">
         <v>15</v>
@@ -29550,7 +29544,7 @@
         <v>14</v>
       </c>
       <c r="F341" s="2">
-        <v>2967</v>
+        <v>3812</v>
       </c>
       <c r="G341" s="2" t="s">
         <v>15</v>
@@ -29582,7 +29576,7 @@
         <v>14</v>
       </c>
       <c r="F342" s="2">
-        <v>2339</v>
+        <v>3297</v>
       </c>
       <c r="G342" s="2" t="s">
         <v>15</v>
@@ -29614,7 +29608,7 @@
         <v>14</v>
       </c>
       <c r="F343" s="2">
-        <v>2931</v>
+        <v>2021</v>
       </c>
       <c r="G343" s="2" t="s">
         <v>15</v>
@@ -29646,7 +29640,7 @@
         <v>14</v>
       </c>
       <c r="F344" s="2">
-        <v>3210</v>
+        <v>2728</v>
       </c>
       <c r="G344" s="2" t="s">
         <v>15</v>
@@ -29678,7 +29672,7 @@
         <v>14</v>
       </c>
       <c r="F345" s="2">
-        <v>4194</v>
+        <v>4033</v>
       </c>
       <c r="G345" s="2" t="s">
         <v>15</v>
@@ -29710,7 +29704,7 @@
         <v>14</v>
       </c>
       <c r="F346" s="2">
-        <v>2515</v>
+        <v>1728</v>
       </c>
       <c r="G346" s="2" t="s">
         <v>15</v>
@@ -29742,7 +29736,7 @@
         <v>14</v>
       </c>
       <c r="F347" s="2">
-        <v>3933</v>
+        <v>4114</v>
       </c>
       <c r="G347" s="2" t="s">
         <v>15</v>
@@ -29774,7 +29768,7 @@
         <v>14</v>
       </c>
       <c r="F348" s="2">
-        <v>2972</v>
+        <v>914</v>
       </c>
       <c r="G348" s="2" t="s">
         <v>15</v>
@@ -29806,7 +29800,7 @@
         <v>14</v>
       </c>
       <c r="F349" s="2">
-        <v>3530</v>
+        <v>1251</v>
       </c>
       <c r="G349" s="2" t="s">
         <v>15</v>
@@ -29838,7 +29832,7 @@
         <v>14</v>
       </c>
       <c r="F350" s="2">
-        <v>4592</v>
+        <v>1116</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>15</v>
@@ -29870,7 +29864,7 @@
         <v>14</v>
       </c>
       <c r="F351" s="2">
-        <v>1209</v>
+        <v>1883</v>
       </c>
       <c r="G351" s="2" t="s">
         <v>15</v>
@@ -29902,7 +29896,7 @@
         <v>14</v>
       </c>
       <c r="F352" s="2">
-        <v>2387</v>
+        <v>4188</v>
       </c>
       <c r="G352" s="2" t="s">
         <v>15</v>
@@ -29934,7 +29928,7 @@
         <v>14</v>
       </c>
       <c r="F353" s="2">
-        <v>1728</v>
+        <v>3390</v>
       </c>
       <c r="G353" s="2" t="s">
         <v>15</v>
@@ -29966,7 +29960,7 @@
         <v>14</v>
       </c>
       <c r="F354" s="2">
-        <v>1955</v>
+        <v>1935</v>
       </c>
       <c r="G354" s="2" t="s">
         <v>15</v>
@@ -29998,7 +29992,7 @@
         <v>14</v>
       </c>
       <c r="F355" s="2">
-        <v>3759</v>
+        <v>2901</v>
       </c>
       <c r="G355" s="2" t="s">
         <v>15</v>
@@ -30030,7 +30024,7 @@
         <v>14</v>
       </c>
       <c r="F356" s="2">
-        <v>4618</v>
+        <v>3050</v>
       </c>
       <c r="G356" s="2" t="s">
         <v>15</v>
@@ -30062,7 +30056,7 @@
         <v>14</v>
       </c>
       <c r="F357" s="2">
-        <v>4189</v>
+        <v>4551</v>
       </c>
       <c r="G357" s="2" t="s">
         <v>15</v>
@@ -30094,7 +30088,7 @@
         <v>14</v>
       </c>
       <c r="F358" s="2">
-        <v>2412</v>
+        <v>3905</v>
       </c>
       <c r="G358" s="2" t="s">
         <v>15</v>
@@ -30126,7 +30120,7 @@
         <v>14</v>
       </c>
       <c r="F359" s="2">
-        <v>3531</v>
+        <v>1682</v>
       </c>
       <c r="G359" s="2" t="s">
         <v>15</v>
@@ -30158,7 +30152,7 @@
         <v>14</v>
       </c>
       <c r="F360" s="2">
-        <v>1269</v>
+        <v>4125</v>
       </c>
       <c r="G360" s="2" t="s">
         <v>15</v>
@@ -30190,7 +30184,7 @@
         <v>14</v>
       </c>
       <c r="F361" s="2">
-        <v>1324</v>
+        <v>4470</v>
       </c>
       <c r="G361" s="2" t="s">
         <v>15</v>
@@ -30222,7 +30216,7 @@
         <v>14</v>
       </c>
       <c r="F362" s="2">
-        <v>971</v>
+        <v>1010</v>
       </c>
       <c r="G362" s="2" t="s">
         <v>15</v>
@@ -30254,7 +30248,7 @@
         <v>14</v>
       </c>
       <c r="F363" s="2">
-        <v>4313</v>
+        <v>4183</v>
       </c>
       <c r="G363" s="2" t="s">
         <v>15</v>
@@ -30286,7 +30280,7 @@
         <v>14</v>
       </c>
       <c r="F364" s="2">
-        <v>3040</v>
+        <v>4573</v>
       </c>
       <c r="G364" s="2" t="s">
         <v>15</v>
@@ -30318,7 +30312,7 @@
         <v>14</v>
       </c>
       <c r="F365" s="2">
-        <v>2472</v>
+        <v>2404</v>
       </c>
       <c r="G365" s="2" t="s">
         <v>15</v>
@@ -30350,7 +30344,7 @@
         <v>14</v>
       </c>
       <c r="F366" s="2">
-        <v>2839</v>
+        <v>1139</v>
       </c>
       <c r="G366" s="2" t="s">
         <v>15</v>
@@ -30382,7 +30376,7 @@
         <v>14</v>
       </c>
       <c r="F367" s="2">
-        <v>3009</v>
+        <v>4698</v>
       </c>
       <c r="G367" s="2" t="s">
         <v>15</v>
@@ -30414,7 +30408,7 @@
         <v>14</v>
       </c>
       <c r="F368" s="2">
-        <v>3498</v>
+        <v>4734</v>
       </c>
       <c r="G368" s="2" t="s">
         <v>15</v>
@@ -30446,7 +30440,7 @@
         <v>14</v>
       </c>
       <c r="F369" s="2">
-        <v>1296</v>
+        <v>2963</v>
       </c>
       <c r="G369" s="2" t="s">
         <v>15</v>
@@ -30478,7 +30472,7 @@
         <v>14</v>
       </c>
       <c r="F370" s="2">
-        <v>1680</v>
+        <v>2976</v>
       </c>
       <c r="G370" s="2" t="s">
         <v>15</v>
@@ -30510,7 +30504,7 @@
         <v>14</v>
       </c>
       <c r="F371" s="2">
-        <v>3485</v>
+        <v>3047</v>
       </c>
       <c r="G371" s="2" t="s">
         <v>15</v>
@@ -30542,7 +30536,7 @@
         <v>14</v>
       </c>
       <c r="F372" s="2">
-        <v>4113</v>
+        <v>2520</v>
       </c>
       <c r="G372" s="2" t="s">
         <v>15</v>
@@ -30574,7 +30568,7 @@
         <v>14</v>
       </c>
       <c r="F373" s="2">
-        <v>2606</v>
+        <v>4378</v>
       </c>
       <c r="G373" s="2" t="s">
         <v>15</v>
@@ -30606,7 +30600,7 @@
         <v>14</v>
       </c>
       <c r="F374" s="2">
-        <v>4132</v>
+        <v>1879</v>
       </c>
       <c r="G374" s="2" t="s">
         <v>15</v>
@@ -30638,7 +30632,7 @@
         <v>14</v>
       </c>
       <c r="F375" s="2">
-        <v>2575</v>
+        <v>1599</v>
       </c>
       <c r="G375" s="2" t="s">
         <v>15</v>
@@ -30670,7 +30664,7 @@
         <v>14</v>
       </c>
       <c r="F376" s="2">
-        <v>1225</v>
+        <v>2097</v>
       </c>
       <c r="G376" s="2" t="s">
         <v>15</v>
@@ -30702,7 +30696,7 @@
         <v>14</v>
       </c>
       <c r="F377" s="2">
-        <v>3457</v>
+        <v>4707</v>
       </c>
       <c r="G377" s="2" t="s">
         <v>15</v>
@@ -30734,7 +30728,7 @@
         <v>14</v>
       </c>
       <c r="F378" s="2">
-        <v>1068</v>
+        <v>2809</v>
       </c>
       <c r="G378" s="2" t="s">
         <v>15</v>
@@ -30766,7 +30760,7 @@
         <v>14</v>
       </c>
       <c r="F379" s="2">
-        <v>2072</v>
+        <v>2215</v>
       </c>
       <c r="G379" s="2" t="s">
         <v>15</v>
@@ -30798,7 +30792,7 @@
         <v>14</v>
       </c>
       <c r="F380" s="2">
-        <v>2610</v>
+        <v>1908</v>
       </c>
       <c r="G380" s="2" t="s">
         <v>15</v>
@@ -30830,7 +30824,7 @@
         <v>14</v>
       </c>
       <c r="F381" s="2">
-        <v>3246</v>
+        <v>1626</v>
       </c>
       <c r="G381" s="2" t="s">
         <v>15</v>
@@ -30862,7 +30856,7 @@
         <v>14</v>
       </c>
       <c r="F382" s="2">
-        <v>4146</v>
+        <v>2584</v>
       </c>
       <c r="G382" s="2" t="s">
         <v>15</v>
@@ -30894,7 +30888,7 @@
         <v>14</v>
       </c>
       <c r="F383" s="2">
-        <v>3988</v>
+        <v>3926</v>
       </c>
       <c r="G383" s="2" t="s">
         <v>15</v>
@@ -30926,7 +30920,7 @@
         <v>14</v>
       </c>
       <c r="F384" s="2">
-        <v>1730</v>
+        <v>2472</v>
       </c>
       <c r="G384" s="2" t="s">
         <v>15</v>
@@ -30958,7 +30952,7 @@
         <v>14</v>
       </c>
       <c r="F385" s="2">
-        <v>2541</v>
+        <v>1496</v>
       </c>
       <c r="G385" s="2" t="s">
         <v>15</v>
@@ -30990,7 +30984,7 @@
         <v>14</v>
       </c>
       <c r="F386" s="2">
-        <v>2079</v>
+        <v>2150</v>
       </c>
       <c r="G386" s="2" t="s">
         <v>15</v>
@@ -31022,7 +31016,7 @@
         <v>14</v>
       </c>
       <c r="F387" s="2">
-        <v>3874</v>
+        <v>4178</v>
       </c>
       <c r="G387" s="2" t="s">
         <v>15</v>
@@ -31054,7 +31048,7 @@
         <v>14</v>
       </c>
       <c r="F388" s="2">
-        <v>2512</v>
+        <v>3497</v>
       </c>
       <c r="G388" s="2" t="s">
         <v>15</v>
@@ -31086,7 +31080,7 @@
         <v>14</v>
       </c>
       <c r="F389" s="2">
-        <v>2902</v>
+        <v>3448</v>
       </c>
       <c r="G389" s="2" t="s">
         <v>15</v>
@@ -31118,7 +31112,7 @@
         <v>14</v>
       </c>
       <c r="F390" s="2">
-        <v>4623</v>
+        <v>2430</v>
       </c>
       <c r="G390" s="2" t="s">
         <v>15</v>
@@ -31150,7 +31144,7 @@
         <v>14</v>
       </c>
       <c r="F391" s="2">
-        <v>2103</v>
+        <v>2733</v>
       </c>
       <c r="G391" s="2" t="s">
         <v>15</v>
@@ -31182,7 +31176,7 @@
         <v>14</v>
       </c>
       <c r="F392" s="2">
-        <v>3950</v>
+        <v>1345</v>
       </c>
       <c r="G392" s="2" t="s">
         <v>15</v>
@@ -31214,7 +31208,7 @@
         <v>14</v>
       </c>
       <c r="F393" s="2">
-        <v>2644</v>
+        <v>1026</v>
       </c>
       <c r="G393" s="2" t="s">
         <v>15</v>
@@ -31246,7 +31240,7 @@
         <v>14</v>
       </c>
       <c r="F394" s="2">
-        <v>1292</v>
+        <v>2355</v>
       </c>
       <c r="G394" s="2" t="s">
         <v>15</v>
@@ -31278,7 +31272,7 @@
         <v>14</v>
       </c>
       <c r="F395" s="2">
-        <v>3000</v>
+        <v>2668</v>
       </c>
       <c r="G395" s="2" t="s">
         <v>15</v>
@@ -31310,7 +31304,7 @@
         <v>14</v>
       </c>
       <c r="F396" s="2">
-        <v>1468</v>
+        <v>932</v>
       </c>
       <c r="G396" s="2" t="s">
         <v>15</v>
@@ -31342,7 +31336,7 @@
         <v>14</v>
       </c>
       <c r="F397" s="2">
-        <v>4226</v>
+        <v>3599</v>
       </c>
       <c r="G397" s="2" t="s">
         <v>15</v>
@@ -31374,7 +31368,7 @@
         <v>14</v>
       </c>
       <c r="F398" s="2">
-        <v>3658</v>
+        <v>1862</v>
       </c>
       <c r="G398" s="2" t="s">
         <v>15</v>
@@ -31406,7 +31400,7 @@
         <v>14</v>
       </c>
       <c r="F399" s="2">
-        <v>3470</v>
+        <v>1616</v>
       </c>
       <c r="G399" s="2" t="s">
         <v>15</v>
@@ -31438,7 +31432,7 @@
         <v>14</v>
       </c>
       <c r="F400" s="2">
-        <v>3158</v>
+        <v>3844</v>
       </c>
       <c r="G400" s="2" t="s">
         <v>15</v>
@@ -31470,7 +31464,7 @@
         <v>14</v>
       </c>
       <c r="F401" s="2">
-        <v>1477</v>
+        <v>2033</v>
       </c>
       <c r="G401" s="2" t="s">
         <v>15</v>
@@ -31502,7 +31496,7 @@
         <v>14</v>
       </c>
       <c r="F402" s="2">
-        <v>3875</v>
+        <v>3785</v>
       </c>
       <c r="G402" s="2" t="s">
         <v>15</v>
@@ -31534,7 +31528,7 @@
         <v>14</v>
       </c>
       <c r="F403" s="2">
-        <v>3243</v>
+        <v>1370</v>
       </c>
       <c r="G403" s="2" t="s">
         <v>15</v>
@@ -31566,7 +31560,7 @@
         <v>14</v>
       </c>
       <c r="F404" s="2">
-        <v>1420</v>
+        <v>3772</v>
       </c>
       <c r="G404" s="2" t="s">
         <v>15</v>
@@ -31598,7 +31592,7 @@
         <v>14</v>
       </c>
       <c r="F405" s="2">
-        <v>3256</v>
+        <v>1552</v>
       </c>
       <c r="G405" s="2" t="s">
         <v>15</v>
@@ -31630,7 +31624,7 @@
         <v>14</v>
       </c>
       <c r="F406" s="2">
-        <v>2216</v>
+        <v>801</v>
       </c>
       <c r="G406" s="2" t="s">
         <v>15</v>
@@ -31662,7 +31656,7 @@
         <v>14</v>
       </c>
       <c r="F407" s="2">
-        <v>1088</v>
+        <v>1601</v>
       </c>
       <c r="G407" s="2" t="s">
         <v>15</v>
@@ -31694,7 +31688,7 @@
         <v>14</v>
       </c>
       <c r="F408" s="2">
-        <v>3992</v>
+        <v>4454</v>
       </c>
       <c r="G408" s="2" t="s">
         <v>15</v>
@@ -31726,7 +31720,7 @@
         <v>14</v>
       </c>
       <c r="F409" s="2">
-        <v>1235</v>
+        <v>2894</v>
       </c>
       <c r="G409" s="2" t="s">
         <v>15</v>
@@ -31758,7 +31752,7 @@
         <v>14</v>
       </c>
       <c r="F410" s="2">
-        <v>1330</v>
+        <v>3981</v>
       </c>
       <c r="G410" s="2" t="s">
         <v>15</v>
@@ -31790,7 +31784,7 @@
         <v>14</v>
       </c>
       <c r="F411" s="2">
-        <v>921</v>
+        <v>2220</v>
       </c>
       <c r="G411" s="2" t="s">
         <v>15</v>
@@ -31822,7 +31816,7 @@
         <v>14</v>
       </c>
       <c r="F412" s="2">
-        <v>2205</v>
+        <v>3352</v>
       </c>
       <c r="G412" s="2" t="s">
         <v>15</v>
@@ -31854,7 +31848,7 @@
         <v>14</v>
       </c>
       <c r="F413" s="2">
-        <v>3990</v>
+        <v>2846</v>
       </c>
       <c r="G413" s="2" t="s">
         <v>15</v>
@@ -31886,7 +31880,7 @@
         <v>14</v>
       </c>
       <c r="F414" s="2">
-        <v>1498</v>
+        <v>2255</v>
       </c>
       <c r="G414" s="2" t="s">
         <v>15</v>
@@ -31918,7 +31912,7 @@
         <v>14</v>
       </c>
       <c r="F415" s="2">
-        <v>2498</v>
+        <v>950</v>
       </c>
       <c r="G415" s="2" t="s">
         <v>15</v>
@@ -31950,7 +31944,7 @@
         <v>14</v>
       </c>
       <c r="F416" s="2">
-        <v>1746</v>
+        <v>2243</v>
       </c>
       <c r="G416" s="2" t="s">
         <v>15</v>
@@ -31982,7 +31976,7 @@
         <v>14</v>
       </c>
       <c r="F417" s="2">
-        <v>1559</v>
+        <v>2722</v>
       </c>
       <c r="G417" s="2" t="s">
         <v>15</v>
@@ -32014,7 +32008,7 @@
         <v>14</v>
       </c>
       <c r="F418" s="2">
-        <v>1022</v>
+        <v>2635</v>
       </c>
       <c r="G418" s="2" t="s">
         <v>15</v>
@@ -32046,7 +32040,7 @@
         <v>14</v>
       </c>
       <c r="F419" s="2">
-        <v>858</v>
+        <v>2456</v>
       </c>
       <c r="G419" s="2" t="s">
         <v>15</v>
@@ -32078,7 +32072,7 @@
         <v>14</v>
       </c>
       <c r="F420" s="2">
-        <v>1942</v>
+        <v>852</v>
       </c>
       <c r="G420" s="2" t="s">
         <v>15</v>
@@ -32110,7 +32104,7 @@
         <v>14</v>
       </c>
       <c r="F421" s="2">
-        <v>4088</v>
+        <v>4015</v>
       </c>
       <c r="G421" s="2" t="s">
         <v>15</v>
@@ -32142,7 +32136,7 @@
         <v>14</v>
       </c>
       <c r="F422" s="2">
-        <v>4265</v>
+        <v>4310</v>
       </c>
       <c r="G422" s="2" t="s">
         <v>15</v>
@@ -32174,7 +32168,7 @@
         <v>14</v>
       </c>
       <c r="F423" s="2">
-        <v>1299</v>
+        <v>1040</v>
       </c>
       <c r="G423" s="2" t="s">
         <v>15</v>
@@ -32206,7 +32200,7 @@
         <v>14</v>
       </c>
       <c r="F424" s="2">
-        <v>4612</v>
+        <v>4251</v>
       </c>
       <c r="G424" s="2" t="s">
         <v>15</v>
@@ -32238,7 +32232,7 @@
         <v>14</v>
       </c>
       <c r="F425" s="2">
-        <v>3970</v>
+        <v>2989</v>
       </c>
       <c r="G425" s="2" t="s">
         <v>15</v>
@@ -32270,7 +32264,7 @@
         <v>14</v>
       </c>
       <c r="F426" s="2">
-        <v>1792</v>
+        <v>3367</v>
       </c>
       <c r="G426" s="2" t="s">
         <v>15</v>
@@ -32302,7 +32296,7 @@
         <v>14</v>
       </c>
       <c r="F427" s="2">
-        <v>2111</v>
+        <v>2872</v>
       </c>
       <c r="G427" s="2" t="s">
         <v>15</v>
@@ -32334,7 +32328,7 @@
         <v>14</v>
       </c>
       <c r="F428" s="2">
-        <v>4298</v>
+        <v>1632</v>
       </c>
       <c r="G428" s="2" t="s">
         <v>15</v>
@@ -32366,7 +32360,7 @@
         <v>14</v>
       </c>
       <c r="F429" s="2">
-        <v>4287</v>
+        <v>2671</v>
       </c>
       <c r="G429" s="2" t="s">
         <v>15</v>
@@ -32398,7 +32392,7 @@
         <v>14</v>
       </c>
       <c r="F430" s="2">
-        <v>2963</v>
+        <v>3484</v>
       </c>
       <c r="G430" s="2" t="s">
         <v>15</v>
@@ -32430,7 +32424,7 @@
         <v>14</v>
       </c>
       <c r="F431" s="2">
-        <v>2290</v>
+        <v>1151</v>
       </c>
       <c r="G431" s="2" t="s">
         <v>15</v>
@@ -32462,7 +32456,7 @@
         <v>14</v>
       </c>
       <c r="F432" s="2">
-        <v>4010</v>
+        <v>4696</v>
       </c>
       <c r="G432" s="2" t="s">
         <v>15</v>
@@ -32494,7 +32488,7 @@
         <v>14</v>
       </c>
       <c r="F433" s="2">
-        <v>4380</v>
+        <v>1986</v>
       </c>
       <c r="G433" s="2" t="s">
         <v>15</v>
@@ -32526,7 +32520,7 @@
         <v>14</v>
       </c>
       <c r="F434" s="2">
-        <v>3971</v>
+        <v>2573</v>
       </c>
       <c r="G434" s="2" t="s">
         <v>15</v>
@@ -32558,7 +32552,7 @@
         <v>14</v>
       </c>
       <c r="F435" s="2">
-        <v>2495</v>
+        <v>2239</v>
       </c>
       <c r="G435" s="2" t="s">
         <v>15</v>
@@ -32590,7 +32584,7 @@
         <v>14</v>
       </c>
       <c r="F436" s="2">
-        <v>1931</v>
+        <v>4591</v>
       </c>
       <c r="G436" s="2" t="s">
         <v>15</v>
@@ -32622,7 +32616,7 @@
         <v>14</v>
       </c>
       <c r="F437" s="2">
-        <v>4423</v>
+        <v>1429</v>
       </c>
       <c r="G437" s="2" t="s">
         <v>15</v>
@@ -32654,7 +32648,7 @@
         <v>14</v>
       </c>
       <c r="F438" s="2">
-        <v>2497</v>
+        <v>2712</v>
       </c>
       <c r="G438" s="2" t="s">
         <v>15</v>
@@ -32686,7 +32680,7 @@
         <v>14</v>
       </c>
       <c r="F439" s="2">
-        <v>1522</v>
+        <v>3261</v>
       </c>
       <c r="G439" s="2" t="s">
         <v>15</v>
@@ -32718,7 +32712,7 @@
         <v>14</v>
       </c>
       <c r="F440" s="2">
-        <v>1528</v>
+        <v>4385</v>
       </c>
       <c r="G440" s="2" t="s">
         <v>15</v>
@@ -32750,7 +32744,7 @@
         <v>14</v>
       </c>
       <c r="F441" s="2">
-        <v>2770</v>
+        <v>1274</v>
       </c>
       <c r="G441" s="2" t="s">
         <v>15</v>
@@ -32782,7 +32776,7 @@
         <v>14</v>
       </c>
       <c r="F442" s="2">
-        <v>904</v>
+        <v>1504</v>
       </c>
       <c r="G442" s="2" t="s">
         <v>15</v>
@@ -32814,7 +32808,7 @@
         <v>14</v>
       </c>
       <c r="F443" s="2">
-        <v>3122</v>
+        <v>3631</v>
       </c>
       <c r="G443" s="2" t="s">
         <v>15</v>
@@ -32846,7 +32840,7 @@
         <v>14</v>
       </c>
       <c r="F444" s="2">
-        <v>1126</v>
+        <v>4101</v>
       </c>
       <c r="G444" s="2" t="s">
         <v>15</v>
@@ -32878,7 +32872,7 @@
         <v>14</v>
       </c>
       <c r="F445" s="2">
-        <v>1287</v>
+        <v>2468</v>
       </c>
       <c r="G445" s="2" t="s">
         <v>15</v>
@@ -32910,7 +32904,7 @@
         <v>14</v>
       </c>
       <c r="F446" s="2">
-        <v>2193</v>
+        <v>3415</v>
       </c>
       <c r="G446" s="2" t="s">
         <v>15</v>
@@ -32942,7 +32936,7 @@
         <v>14</v>
       </c>
       <c r="F447" s="2">
-        <v>2803</v>
+        <v>3313</v>
       </c>
       <c r="G447" s="2" t="s">
         <v>15</v>
@@ -32974,7 +32968,7 @@
         <v>14</v>
       </c>
       <c r="F448" s="2">
-        <v>3596</v>
+        <v>1389</v>
       </c>
       <c r="G448" s="2" t="s">
         <v>15</v>
@@ -33006,7 +33000,7 @@
         <v>14</v>
       </c>
       <c r="F449" s="2">
-        <v>3194</v>
+        <v>3990</v>
       </c>
       <c r="G449" s="2" t="s">
         <v>15</v>
@@ -33038,7 +33032,7 @@
         <v>14</v>
       </c>
       <c r="F450" s="2">
-        <v>2329</v>
+        <v>4244</v>
       </c>
       <c r="G450" s="2" t="s">
         <v>15</v>
@@ -33070,7 +33064,7 @@
         <v>14</v>
       </c>
       <c r="F451" s="2">
-        <v>3819</v>
+        <v>2275</v>
       </c>
       <c r="G451" s="2" t="s">
         <v>15</v>
@@ -33102,7 +33096,7 @@
         <v>14</v>
       </c>
       <c r="F452" s="2">
-        <v>2766</v>
+        <v>2573</v>
       </c>
       <c r="G452" s="2" t="s">
         <v>15</v>
@@ -33134,7 +33128,7 @@
         <v>14</v>
       </c>
       <c r="F453" s="2">
-        <v>2868</v>
+        <v>2089</v>
       </c>
       <c r="G453" s="2" t="s">
         <v>15</v>
@@ -33166,7 +33160,7 @@
         <v>14</v>
       </c>
       <c r="F454" s="2">
-        <v>3820</v>
+        <v>3373</v>
       </c>
       <c r="G454" s="2" t="s">
         <v>15</v>
@@ -33198,7 +33192,7 @@
         <v>14</v>
       </c>
       <c r="F455" s="2">
-        <v>4529</v>
+        <v>4374</v>
       </c>
       <c r="G455" s="2" t="s">
         <v>15</v>
@@ -33230,7 +33224,7 @@
         <v>14</v>
       </c>
       <c r="F456" s="2">
-        <v>2461</v>
+        <v>3615</v>
       </c>
       <c r="G456" s="2" t="s">
         <v>15</v>
@@ -33262,7 +33256,7 @@
         <v>14</v>
       </c>
       <c r="F457" s="2">
-        <v>2268</v>
+        <v>1087</v>
       </c>
       <c r="G457" s="2" t="s">
         <v>15</v>
@@ -33294,7 +33288,7 @@
         <v>14</v>
       </c>
       <c r="F458" s="2">
-        <v>3253</v>
+        <v>949</v>
       </c>
       <c r="G458" s="2" t="s">
         <v>15</v>
@@ -33326,7 +33320,7 @@
         <v>14</v>
       </c>
       <c r="F459" s="2">
-        <v>4103</v>
+        <v>4113</v>
       </c>
       <c r="G459" s="2" t="s">
         <v>15</v>
@@ -33358,7 +33352,7 @@
         <v>14</v>
       </c>
       <c r="F460" s="2">
-        <v>4645</v>
+        <v>4286</v>
       </c>
       <c r="G460" s="2" t="s">
         <v>15</v>
@@ -33390,7 +33384,7 @@
         <v>14</v>
       </c>
       <c r="F461" s="2">
-        <v>1816</v>
+        <v>2693</v>
       </c>
       <c r="G461" s="2" t="s">
         <v>15</v>
@@ -33422,7 +33416,7 @@
         <v>14</v>
       </c>
       <c r="F462" s="2">
-        <v>3783</v>
+        <v>3972</v>
       </c>
       <c r="G462" s="2" t="s">
         <v>15</v>
@@ -33454,7 +33448,7 @@
         <v>14</v>
       </c>
       <c r="F463" s="2">
-        <v>4030</v>
+        <v>4054</v>
       </c>
       <c r="G463" s="2" t="s">
         <v>15</v>
@@ -33486,7 +33480,7 @@
         <v>14</v>
       </c>
       <c r="F464" s="2">
-        <v>917</v>
+        <v>1137</v>
       </c>
       <c r="G464" s="2" t="s">
         <v>15</v>
@@ -33518,7 +33512,7 @@
         <v>14</v>
       </c>
       <c r="F465" s="2">
-        <v>4148</v>
+        <v>1514</v>
       </c>
       <c r="G465" s="2" t="s">
         <v>15</v>
@@ -33550,7 +33544,7 @@
         <v>14</v>
       </c>
       <c r="F466" s="2">
-        <v>2958</v>
+        <v>1973</v>
       </c>
       <c r="G466" s="2" t="s">
         <v>15</v>
@@ -33582,7 +33576,7 @@
         <v>14</v>
       </c>
       <c r="F467" s="2">
-        <v>4251</v>
+        <v>2793</v>
       </c>
       <c r="G467" s="2" t="s">
         <v>15</v>
@@ -33614,7 +33608,7 @@
         <v>14</v>
       </c>
       <c r="F468" s="2">
-        <v>4757</v>
+        <v>4284</v>
       </c>
       <c r="G468" s="2" t="s">
         <v>15</v>
@@ -33646,7 +33640,7 @@
         <v>14</v>
       </c>
       <c r="F469" s="2">
-        <v>4755</v>
+        <v>4292</v>
       </c>
       <c r="G469" s="2" t="s">
         <v>15</v>
@@ -33678,7 +33672,7 @@
         <v>14</v>
       </c>
       <c r="F470" s="2">
-        <v>2265</v>
+        <v>2003</v>
       </c>
       <c r="G470" s="2" t="s">
         <v>15</v>
@@ -33710,7 +33704,7 @@
         <v>14</v>
       </c>
       <c r="F471" s="2">
-        <v>2516</v>
+        <v>2217</v>
       </c>
       <c r="G471" s="2" t="s">
         <v>15</v>
@@ -33869,36 +33863,36 @@
         <v>1023</v>
       </c>
       <c r="B3" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B4" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="B5" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="B6" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
@@ -33914,7 +33908,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="B9">
         <v>470</v>
@@ -33922,7 +33916,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="B10">
         <v>470</v>
@@ -33930,7 +33924,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -33938,7 +33932,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -33946,18 +33940,18 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B13" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="B14" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
     </row>
   </sheetData>
@@ -33981,16 +33975,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>1034</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>1036</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -34007,7 +34001,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -34024,7 +34018,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -34041,7 +34035,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -34058,7 +34052,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -34075,7 +34069,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -34092,7 +34086,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -34109,7 +34103,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -34126,7 +34120,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -34143,7 +34137,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -34160,7 +34154,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -34177,7 +34171,7 @@
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -34194,7 +34188,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -34211,7 +34205,7 @@
         <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -34228,7 +34222,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
     </row>
   </sheetData>

--- a/reports/selenium/latest/excel/Automation_Test_Report.xlsx
+++ b/reports/selenium/latest/excel/Automation_Test_Report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8557" uniqueCount="1040">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8557" uniqueCount="1042">
   <si>
     <t>Test ID</t>
   </si>
@@ -3084,19 +3084,25 @@
     <t>Build</t>
   </si>
   <si>
-    <t>local</t>
+    <t>12</t>
   </si>
   <si>
     <t>Branch</t>
   </si>
   <si>
+    <t>main</t>
+  </si>
+  <si>
     <t>Commit</t>
   </si>
   <si>
+    <t>807dd5ee9294</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T06:21:14.794Z</t>
+    <t>2026-08-19T03:41:14.845Z</t>
   </si>
   <si>
     <t>Browser</t>
@@ -3129,7 +3135,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>0.3s</t>
+    <t>0.0s</t>
   </si>
   <si>
     <t>Total</t>
@@ -3601,7 +3607,7 @@
         <v>14</v>
       </c>
       <c r="F2" s="2">
-        <v>2554</v>
+        <v>1410</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>15</v>
@@ -3633,7 +3639,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="2">
-        <v>1005</v>
+        <v>2568</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>15</v>
@@ -3665,7 +3671,7 @@
         <v>14</v>
       </c>
       <c r="F4" s="2">
-        <v>1371</v>
+        <v>2061</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
@@ -3697,7 +3703,7 @@
         <v>14</v>
       </c>
       <c r="F5" s="2">
-        <v>4403</v>
+        <v>1006</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
@@ -3729,7 +3735,7 @@
         <v>14</v>
       </c>
       <c r="F6" s="2">
-        <v>1966</v>
+        <v>1407</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -3761,7 +3767,7 @@
         <v>14</v>
       </c>
       <c r="F7" s="2">
-        <v>1146</v>
+        <v>3043</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -3793,7 +3799,7 @@
         <v>14</v>
       </c>
       <c r="F8" s="2">
-        <v>983</v>
+        <v>3101</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -3825,7 +3831,7 @@
         <v>14</v>
       </c>
       <c r="F9" s="2">
-        <v>4550</v>
+        <v>4731</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -3857,7 +3863,7 @@
         <v>14</v>
       </c>
       <c r="F10" s="2">
-        <v>3546</v>
+        <v>2421</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
@@ -3889,7 +3895,7 @@
         <v>14</v>
       </c>
       <c r="F11" s="2">
-        <v>1587</v>
+        <v>1090</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
@@ -3921,7 +3927,7 @@
         <v>14</v>
       </c>
       <c r="F12" s="2">
-        <v>2686</v>
+        <v>1528</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
@@ -3953,7 +3959,7 @@
         <v>14</v>
       </c>
       <c r="F13" s="2">
-        <v>923</v>
+        <v>3680</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -3985,7 +3991,7 @@
         <v>14</v>
       </c>
       <c r="F14" s="2">
-        <v>1180</v>
+        <v>875</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -4017,7 +4023,7 @@
         <v>14</v>
       </c>
       <c r="F15" s="2">
-        <v>4539</v>
+        <v>2932</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -4049,7 +4055,7 @@
         <v>14</v>
       </c>
       <c r="F16" s="2">
-        <v>4247</v>
+        <v>3362</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
@@ -4081,7 +4087,7 @@
         <v>14</v>
       </c>
       <c r="F17" s="2">
-        <v>941</v>
+        <v>4552</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
@@ -4113,7 +4119,7 @@
         <v>14</v>
       </c>
       <c r="F18" s="2">
-        <v>2875</v>
+        <v>1353</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
@@ -4145,7 +4151,7 @@
         <v>14</v>
       </c>
       <c r="F19" s="2">
-        <v>2654</v>
+        <v>2798</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
@@ -4177,7 +4183,7 @@
         <v>14</v>
       </c>
       <c r="F20" s="2">
-        <v>2107</v>
+        <v>2479</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
@@ -4209,7 +4215,7 @@
         <v>14</v>
       </c>
       <c r="F21" s="2">
-        <v>4282</v>
+        <v>4771</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -4241,7 +4247,7 @@
         <v>14</v>
       </c>
       <c r="F22" s="2">
-        <v>2543</v>
+        <v>919</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -4273,7 +4279,7 @@
         <v>14</v>
       </c>
       <c r="F23" s="2">
-        <v>4573</v>
+        <v>2857</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -4305,7 +4311,7 @@
         <v>14</v>
       </c>
       <c r="F24" s="2">
-        <v>4360</v>
+        <v>4482</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -4337,7 +4343,7 @@
         <v>14</v>
       </c>
       <c r="F25" s="2">
-        <v>3018</v>
+        <v>1199</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -4369,7 +4375,7 @@
         <v>14</v>
       </c>
       <c r="F26" s="2">
-        <v>1625</v>
+        <v>1797</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -4401,7 +4407,7 @@
         <v>14</v>
       </c>
       <c r="F27" s="2">
-        <v>4092</v>
+        <v>3818</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>15</v>
@@ -4433,7 +4439,7 @@
         <v>14</v>
       </c>
       <c r="F28" s="2">
-        <v>1499</v>
+        <v>1624</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>15</v>
@@ -4465,7 +4471,7 @@
         <v>14</v>
       </c>
       <c r="F29" s="2">
-        <v>2405</v>
+        <v>3847</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>15</v>
@@ -4497,7 +4503,7 @@
         <v>14</v>
       </c>
       <c r="F30" s="2">
-        <v>3156</v>
+        <v>3120</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>15</v>
@@ -4529,7 +4535,7 @@
         <v>14</v>
       </c>
       <c r="F31" s="2">
-        <v>917</v>
+        <v>3823</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>15</v>
@@ -4561,7 +4567,7 @@
         <v>14</v>
       </c>
       <c r="F32" s="2">
-        <v>1702</v>
+        <v>4104</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>15</v>
@@ -4593,7 +4599,7 @@
         <v>14</v>
       </c>
       <c r="F33" s="2">
-        <v>3737</v>
+        <v>2120</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>15</v>
@@ -4625,7 +4631,7 @@
         <v>14</v>
       </c>
       <c r="F34" s="2">
-        <v>4655</v>
+        <v>3997</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>15</v>
@@ -4657,7 +4663,7 @@
         <v>14</v>
       </c>
       <c r="F35" s="2">
-        <v>2182</v>
+        <v>3831</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>15</v>
@@ -4689,7 +4695,7 @@
         <v>14</v>
       </c>
       <c r="F36" s="2">
-        <v>1459</v>
+        <v>2020</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>15</v>
@@ -4721,7 +4727,7 @@
         <v>14</v>
       </c>
       <c r="F37" s="2">
-        <v>1951</v>
+        <v>929</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>15</v>
@@ -4753,7 +4759,7 @@
         <v>14</v>
       </c>
       <c r="F38" s="2">
-        <v>3093</v>
+        <v>4216</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>15</v>
@@ -4785,7 +4791,7 @@
         <v>14</v>
       </c>
       <c r="F39" s="2">
-        <v>2140</v>
+        <v>963</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>15</v>
@@ -4817,7 +4823,7 @@
         <v>14</v>
       </c>
       <c r="F40" s="2">
-        <v>1502</v>
+        <v>4559</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>15</v>
@@ -4849,7 +4855,7 @@
         <v>14</v>
       </c>
       <c r="F41" s="2">
-        <v>1559</v>
+        <v>2751</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>15</v>
@@ -4881,7 +4887,7 @@
         <v>14</v>
       </c>
       <c r="F42" s="2">
-        <v>3356</v>
+        <v>1717</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>15</v>
@@ -4913,7 +4919,7 @@
         <v>14</v>
       </c>
       <c r="F43" s="2">
-        <v>1380</v>
+        <v>3906</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>15</v>
@@ -4945,7 +4951,7 @@
         <v>14</v>
       </c>
       <c r="F44" s="2">
-        <v>4790</v>
+        <v>3902</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>15</v>
@@ -4977,7 +4983,7 @@
         <v>14</v>
       </c>
       <c r="F45" s="2">
-        <v>1149</v>
+        <v>1999</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>15</v>
@@ -5009,7 +5015,7 @@
         <v>14</v>
       </c>
       <c r="F46" s="2">
-        <v>1770</v>
+        <v>3922</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>15</v>
@@ -5041,7 +5047,7 @@
         <v>14</v>
       </c>
       <c r="F47" s="2">
-        <v>4797</v>
+        <v>957</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>15</v>
@@ -5073,7 +5079,7 @@
         <v>14</v>
       </c>
       <c r="F48" s="2">
-        <v>3166</v>
+        <v>1646</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>15</v>
@@ -5105,7 +5111,7 @@
         <v>14</v>
       </c>
       <c r="F49" s="2">
-        <v>1537</v>
+        <v>4151</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>15</v>
@@ -5137,7 +5143,7 @@
         <v>14</v>
       </c>
       <c r="F50" s="2">
-        <v>1273</v>
+        <v>1006</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>15</v>
@@ -5169,7 +5175,7 @@
         <v>14</v>
       </c>
       <c r="F51" s="2">
-        <v>1816</v>
+        <v>3542</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>15</v>
@@ -5201,7 +5207,7 @@
         <v>14</v>
       </c>
       <c r="F52" s="2">
-        <v>1217</v>
+        <v>2125</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>15</v>
@@ -5233,7 +5239,7 @@
         <v>14</v>
       </c>
       <c r="F53" s="2">
-        <v>4478</v>
+        <v>3601</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>15</v>
@@ -5265,7 +5271,7 @@
         <v>14</v>
       </c>
       <c r="F54" s="2">
-        <v>1505</v>
+        <v>1221</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>15</v>
@@ -5297,7 +5303,7 @@
         <v>14</v>
       </c>
       <c r="F55" s="2">
-        <v>1462</v>
+        <v>849</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>15</v>
@@ -5329,7 +5335,7 @@
         <v>14</v>
       </c>
       <c r="F56" s="2">
-        <v>3530</v>
+        <v>1093</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>15</v>
@@ -5361,7 +5367,7 @@
         <v>14</v>
       </c>
       <c r="F57" s="2">
-        <v>3488</v>
+        <v>4635</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>15</v>
@@ -5393,7 +5399,7 @@
         <v>14</v>
       </c>
       <c r="F58" s="2">
-        <v>2121</v>
+        <v>1880</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>15</v>
@@ -5425,7 +5431,7 @@
         <v>14</v>
       </c>
       <c r="F59" s="2">
-        <v>1512</v>
+        <v>4763</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>15</v>
@@ -5457,7 +5463,7 @@
         <v>14</v>
       </c>
       <c r="F60" s="2">
-        <v>3540</v>
+        <v>4396</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>15</v>
@@ -5489,7 +5495,7 @@
         <v>14</v>
       </c>
       <c r="F61" s="2">
-        <v>3072</v>
+        <v>1408</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>15</v>
@@ -5521,7 +5527,7 @@
         <v>14</v>
       </c>
       <c r="F62" s="2">
-        <v>1371</v>
+        <v>1750</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>15</v>
@@ -5553,7 +5559,7 @@
         <v>14</v>
       </c>
       <c r="F63" s="2">
-        <v>3849</v>
+        <v>2831</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>15</v>
@@ -5585,7 +5591,7 @@
         <v>14</v>
       </c>
       <c r="F64" s="2">
-        <v>2403</v>
+        <v>2474</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>15</v>
@@ -5617,7 +5623,7 @@
         <v>14</v>
       </c>
       <c r="F65" s="2">
-        <v>1547</v>
+        <v>3741</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>15</v>
@@ -5649,7 +5655,7 @@
         <v>14</v>
       </c>
       <c r="F66" s="2">
-        <v>2696</v>
+        <v>870</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>15</v>
@@ -5681,7 +5687,7 @@
         <v>14</v>
       </c>
       <c r="F67" s="2">
-        <v>2694</v>
+        <v>881</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>15</v>
@@ -5713,7 +5719,7 @@
         <v>14</v>
       </c>
       <c r="F68" s="2">
-        <v>2290</v>
+        <v>3836</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>15</v>
@@ -5745,7 +5751,7 @@
         <v>14</v>
       </c>
       <c r="F69" s="2">
-        <v>3304</v>
+        <v>947</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>15</v>
@@ -5777,7 +5783,7 @@
         <v>14</v>
       </c>
       <c r="F70" s="2">
-        <v>2800</v>
+        <v>2520</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>15</v>
@@ -5809,7 +5815,7 @@
         <v>14</v>
       </c>
       <c r="F71" s="2">
-        <v>3720</v>
+        <v>802</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>15</v>
@@ -5841,7 +5847,7 @@
         <v>14</v>
       </c>
       <c r="F72" s="2">
-        <v>3612</v>
+        <v>1896</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>15</v>
@@ -5873,7 +5879,7 @@
         <v>14</v>
       </c>
       <c r="F73" s="2">
-        <v>2939</v>
+        <v>2299</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>15</v>
@@ -5905,7 +5911,7 @@
         <v>14</v>
       </c>
       <c r="F74" s="2">
-        <v>1505</v>
+        <v>3349</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>15</v>
@@ -5937,7 +5943,7 @@
         <v>14</v>
       </c>
       <c r="F75" s="2">
-        <v>2673</v>
+        <v>2722</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>15</v>
@@ -5969,7 +5975,7 @@
         <v>14</v>
       </c>
       <c r="F76" s="2">
-        <v>1061</v>
+        <v>2271</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>15</v>
@@ -6001,7 +6007,7 @@
         <v>14</v>
       </c>
       <c r="F77" s="2">
-        <v>4781</v>
+        <v>3728</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>15</v>
@@ -6033,7 +6039,7 @@
         <v>14</v>
       </c>
       <c r="F78" s="2">
-        <v>3500</v>
+        <v>4793</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>15</v>
@@ -6065,7 +6071,7 @@
         <v>14</v>
       </c>
       <c r="F79" s="2">
-        <v>3862</v>
+        <v>1799</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>15</v>
@@ -6097,7 +6103,7 @@
         <v>14</v>
       </c>
       <c r="F80" s="2">
-        <v>1119</v>
+        <v>4067</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>15</v>
@@ -6129,7 +6135,7 @@
         <v>14</v>
       </c>
       <c r="F81" s="2">
-        <v>2935</v>
+        <v>4595</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>15</v>
@@ -6161,7 +6167,7 @@
         <v>14</v>
       </c>
       <c r="F82" s="2">
-        <v>1561</v>
+        <v>3797</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>15</v>
@@ -6193,7 +6199,7 @@
         <v>14</v>
       </c>
       <c r="F83" s="2">
-        <v>1032</v>
+        <v>1604</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>15</v>
@@ -6225,7 +6231,7 @@
         <v>14</v>
       </c>
       <c r="F84" s="2">
-        <v>1353</v>
+        <v>4449</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>15</v>
@@ -6257,7 +6263,7 @@
         <v>14</v>
       </c>
       <c r="F85" s="2">
-        <v>1353</v>
+        <v>2248</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>15</v>
@@ -6289,7 +6295,7 @@
         <v>14</v>
       </c>
       <c r="F86" s="2">
-        <v>2099</v>
+        <v>2680</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>15</v>
@@ -6321,7 +6327,7 @@
         <v>14</v>
       </c>
       <c r="F87" s="2">
-        <v>1039</v>
+        <v>4120</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>15</v>
@@ -6353,7 +6359,7 @@
         <v>14</v>
       </c>
       <c r="F88" s="2">
-        <v>2316</v>
+        <v>3876</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>15</v>
@@ -6385,7 +6391,7 @@
         <v>14</v>
       </c>
       <c r="F89" s="2">
-        <v>948</v>
+        <v>3388</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>15</v>
@@ -6417,7 +6423,7 @@
         <v>14</v>
       </c>
       <c r="F90" s="2">
-        <v>4289</v>
+        <v>4069</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>15</v>
@@ -6449,7 +6455,7 @@
         <v>14</v>
       </c>
       <c r="F91" s="2">
-        <v>1622</v>
+        <v>4798</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>15</v>
@@ -6481,7 +6487,7 @@
         <v>14</v>
       </c>
       <c r="F92" s="2">
-        <v>1578</v>
+        <v>2721</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>15</v>
@@ -6513,7 +6519,7 @@
         <v>14</v>
       </c>
       <c r="F93" s="2">
-        <v>2989</v>
+        <v>4198</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>15</v>
@@ -6545,7 +6551,7 @@
         <v>14</v>
       </c>
       <c r="F94" s="2">
-        <v>1228</v>
+        <v>4093</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>15</v>
@@ -6577,7 +6583,7 @@
         <v>14</v>
       </c>
       <c r="F95" s="2">
-        <v>2170</v>
+        <v>3415</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>15</v>
@@ -6609,7 +6615,7 @@
         <v>14</v>
       </c>
       <c r="F96" s="2">
-        <v>3182</v>
+        <v>3917</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>15</v>
@@ -6641,7 +6647,7 @@
         <v>14</v>
       </c>
       <c r="F97" s="2">
-        <v>4059</v>
+        <v>4376</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>15</v>
@@ -6673,7 +6679,7 @@
         <v>14</v>
       </c>
       <c r="F98" s="2">
-        <v>1886</v>
+        <v>1534</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>15</v>
@@ -6705,7 +6711,7 @@
         <v>14</v>
       </c>
       <c r="F99" s="2">
-        <v>3240</v>
+        <v>1396</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>15</v>
@@ -6737,7 +6743,7 @@
         <v>14</v>
       </c>
       <c r="F100" s="2">
-        <v>3142</v>
+        <v>1788</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>15</v>
@@ -6769,7 +6775,7 @@
         <v>14</v>
       </c>
       <c r="F101" s="2">
-        <v>3776</v>
+        <v>860</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>15</v>
@@ -6801,7 +6807,7 @@
         <v>14</v>
       </c>
       <c r="F102" s="2">
-        <v>2382</v>
+        <v>4117</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>15</v>
@@ -6833,7 +6839,7 @@
         <v>14</v>
       </c>
       <c r="F103" s="2">
-        <v>1109</v>
+        <v>1431</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>15</v>
@@ -6865,7 +6871,7 @@
         <v>14</v>
       </c>
       <c r="F104" s="2">
-        <v>1350</v>
+        <v>2506</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>15</v>
@@ -6897,7 +6903,7 @@
         <v>14</v>
       </c>
       <c r="F105" s="2">
-        <v>1307</v>
+        <v>1492</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>15</v>
@@ -6929,7 +6935,7 @@
         <v>14</v>
       </c>
       <c r="F106" s="2">
-        <v>3191</v>
+        <v>4114</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>15</v>
@@ -6961,7 +6967,7 @@
         <v>14</v>
       </c>
       <c r="F107" s="2">
-        <v>2024</v>
+        <v>3396</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>15</v>
@@ -6993,7 +6999,7 @@
         <v>14</v>
       </c>
       <c r="F108" s="2">
-        <v>2141</v>
+        <v>1053</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>15</v>
@@ -7025,7 +7031,7 @@
         <v>14</v>
       </c>
       <c r="F109" s="2">
-        <v>1115</v>
+        <v>970</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>15</v>
@@ -7057,7 +7063,7 @@
         <v>14</v>
       </c>
       <c r="F110" s="2">
-        <v>3138</v>
+        <v>3978</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>15</v>
@@ -7089,7 +7095,7 @@
         <v>14</v>
       </c>
       <c r="F111" s="2">
-        <v>2260</v>
+        <v>1929</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>15</v>
@@ -7121,7 +7127,7 @@
         <v>14</v>
       </c>
       <c r="F112" s="2">
-        <v>1384</v>
+        <v>1100</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>15</v>
@@ -7153,7 +7159,7 @@
         <v>14</v>
       </c>
       <c r="F113" s="2">
-        <v>3180</v>
+        <v>2516</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>15</v>
@@ -7185,7 +7191,7 @@
         <v>14</v>
       </c>
       <c r="F114" s="2">
-        <v>1175</v>
+        <v>1944</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>15</v>
@@ -7217,7 +7223,7 @@
         <v>14</v>
       </c>
       <c r="F115" s="2">
-        <v>2537</v>
+        <v>2455</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>15</v>
@@ -7249,7 +7255,7 @@
         <v>14</v>
       </c>
       <c r="F116" s="2">
-        <v>1810</v>
+        <v>3427</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>15</v>
@@ -7281,7 +7287,7 @@
         <v>14</v>
       </c>
       <c r="F117" s="2">
-        <v>4275</v>
+        <v>1288</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>15</v>
@@ -7313,7 +7319,7 @@
         <v>14</v>
       </c>
       <c r="F118" s="2">
-        <v>4538</v>
+        <v>4304</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>15</v>
@@ -7345,7 +7351,7 @@
         <v>14</v>
       </c>
       <c r="F119" s="2">
-        <v>2133</v>
+        <v>2270</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>15</v>
@@ -7377,7 +7383,7 @@
         <v>14</v>
       </c>
       <c r="F120" s="2">
-        <v>2883</v>
+        <v>2298</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>15</v>
@@ -7409,7 +7415,7 @@
         <v>14</v>
       </c>
       <c r="F121" s="2">
-        <v>2959</v>
+        <v>4234</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>15</v>
@@ -7441,7 +7447,7 @@
         <v>14</v>
       </c>
       <c r="F122" s="2">
-        <v>902</v>
+        <v>3098</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>15</v>
@@ -7473,7 +7479,7 @@
         <v>14</v>
       </c>
       <c r="F123" s="2">
-        <v>3496</v>
+        <v>2500</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>15</v>
@@ -7505,7 +7511,7 @@
         <v>14</v>
       </c>
       <c r="F124" s="2">
-        <v>2788</v>
+        <v>4381</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>15</v>
@@ -7537,7 +7543,7 @@
         <v>14</v>
       </c>
       <c r="F125" s="2">
-        <v>1325</v>
+        <v>1644</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>15</v>
@@ -7569,7 +7575,7 @@
         <v>14</v>
       </c>
       <c r="F126" s="2">
-        <v>3627</v>
+        <v>4100</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>15</v>
@@ -7601,7 +7607,7 @@
         <v>14</v>
       </c>
       <c r="F127" s="2">
-        <v>2597</v>
+        <v>4173</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>15</v>
@@ -7633,7 +7639,7 @@
         <v>14</v>
       </c>
       <c r="F128" s="2">
-        <v>4125</v>
+        <v>4757</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>15</v>
@@ -7665,7 +7671,7 @@
         <v>14</v>
       </c>
       <c r="F129" s="2">
-        <v>1989</v>
+        <v>972</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>15</v>
@@ -7697,7 +7703,7 @@
         <v>14</v>
       </c>
       <c r="F130" s="2">
-        <v>1767</v>
+        <v>2221</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>15</v>
@@ -7729,7 +7735,7 @@
         <v>14</v>
       </c>
       <c r="F131" s="2">
-        <v>1556</v>
+        <v>1004</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>15</v>
@@ -7761,7 +7767,7 @@
         <v>14</v>
       </c>
       <c r="F132" s="2">
-        <v>3417</v>
+        <v>1665</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>15</v>
@@ -7793,7 +7799,7 @@
         <v>14</v>
       </c>
       <c r="F133" s="2">
-        <v>3124</v>
+        <v>4340</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>15</v>
@@ -7825,7 +7831,7 @@
         <v>14</v>
       </c>
       <c r="F134" s="2">
-        <v>2486</v>
+        <v>3133</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>15</v>
@@ -7857,7 +7863,7 @@
         <v>14</v>
       </c>
       <c r="F135" s="2">
-        <v>1814</v>
+        <v>2167</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>15</v>
@@ -7889,7 +7895,7 @@
         <v>14</v>
       </c>
       <c r="F136" s="2">
-        <v>1404</v>
+        <v>1411</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>15</v>
@@ -7921,7 +7927,7 @@
         <v>14</v>
       </c>
       <c r="F137" s="2">
-        <v>3928</v>
+        <v>1786</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>15</v>
@@ -7953,7 +7959,7 @@
         <v>14</v>
       </c>
       <c r="F138" s="2">
-        <v>1578</v>
+        <v>4760</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>15</v>
@@ -7985,7 +7991,7 @@
         <v>14</v>
       </c>
       <c r="F139" s="2">
-        <v>2511</v>
+        <v>1294</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>15</v>
@@ -8017,7 +8023,7 @@
         <v>14</v>
       </c>
       <c r="F140" s="2">
-        <v>4137</v>
+        <v>1698</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>15</v>
@@ -8049,7 +8055,7 @@
         <v>14</v>
       </c>
       <c r="F141" s="2">
-        <v>4336</v>
+        <v>4089</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>15</v>
@@ -8081,7 +8087,7 @@
         <v>14</v>
       </c>
       <c r="F142" s="2">
-        <v>3949</v>
+        <v>1277</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>15</v>
@@ -8113,7 +8119,7 @@
         <v>14</v>
       </c>
       <c r="F143" s="2">
-        <v>2632</v>
+        <v>4332</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>15</v>
@@ -8145,7 +8151,7 @@
         <v>14</v>
       </c>
       <c r="F144" s="2">
-        <v>4317</v>
+        <v>2203</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>15</v>
@@ -8177,7 +8183,7 @@
         <v>14</v>
       </c>
       <c r="F145" s="2">
-        <v>1159</v>
+        <v>3650</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>15</v>
@@ -8209,7 +8215,7 @@
         <v>14</v>
       </c>
       <c r="F146" s="2">
-        <v>2252</v>
+        <v>2465</v>
       </c>
       <c r="G146" s="2" t="s">
         <v>15</v>
@@ -8241,7 +8247,7 @@
         <v>14</v>
       </c>
       <c r="F147" s="2">
-        <v>4334</v>
+        <v>3811</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>15</v>
@@ -8273,7 +8279,7 @@
         <v>14</v>
       </c>
       <c r="F148" s="2">
-        <v>852</v>
+        <v>2487</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>15</v>
@@ -8305,7 +8311,7 @@
         <v>14</v>
       </c>
       <c r="F149" s="2">
-        <v>1685</v>
+        <v>2491</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>15</v>
@@ -8337,7 +8343,7 @@
         <v>14</v>
       </c>
       <c r="F150" s="2">
-        <v>3085</v>
+        <v>4567</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>15</v>
@@ -8369,7 +8375,7 @@
         <v>14</v>
       </c>
       <c r="F151" s="2">
-        <v>3563</v>
+        <v>2706</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>15</v>
@@ -8401,7 +8407,7 @@
         <v>14</v>
       </c>
       <c r="F152" s="2">
-        <v>4313</v>
+        <v>1592</v>
       </c>
       <c r="G152" s="2" t="s">
         <v>15</v>
@@ -8433,7 +8439,7 @@
         <v>14</v>
       </c>
       <c r="F153" s="2">
-        <v>4780</v>
+        <v>4453</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>15</v>
@@ -8465,7 +8471,7 @@
         <v>14</v>
       </c>
       <c r="F154" s="2">
-        <v>3373</v>
+        <v>3932</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>15</v>
@@ -8497,7 +8503,7 @@
         <v>14</v>
       </c>
       <c r="F155" s="2">
-        <v>3441</v>
+        <v>1911</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>15</v>
@@ -8529,7 +8535,7 @@
         <v>14</v>
       </c>
       <c r="F156" s="2">
-        <v>3472</v>
+        <v>4052</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>15</v>
@@ -8561,7 +8567,7 @@
         <v>14</v>
       </c>
       <c r="F157" s="2">
-        <v>1661</v>
+        <v>3525</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>15</v>
@@ -8593,7 +8599,7 @@
         <v>14</v>
       </c>
       <c r="F158" s="2">
-        <v>4015</v>
+        <v>1457</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>15</v>
@@ -8625,7 +8631,7 @@
         <v>14</v>
       </c>
       <c r="F159" s="2">
-        <v>2608</v>
+        <v>1071</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>15</v>
@@ -8657,7 +8663,7 @@
         <v>14</v>
       </c>
       <c r="F160" s="2">
-        <v>4462</v>
+        <v>1432</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>15</v>
@@ -8689,7 +8695,7 @@
         <v>14</v>
       </c>
       <c r="F161" s="2">
-        <v>2903</v>
+        <v>1888</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>15</v>
@@ -8721,7 +8727,7 @@
         <v>14</v>
       </c>
       <c r="F162" s="2">
-        <v>3751</v>
+        <v>3621</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>15</v>
@@ -8753,7 +8759,7 @@
         <v>14</v>
       </c>
       <c r="F163" s="2">
-        <v>2032</v>
+        <v>2601</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>15</v>
@@ -8785,7 +8791,7 @@
         <v>14</v>
       </c>
       <c r="F164" s="2">
-        <v>1521</v>
+        <v>2484</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>15</v>
@@ -8817,7 +8823,7 @@
         <v>14</v>
       </c>
       <c r="F165" s="2">
-        <v>3492</v>
+        <v>2228</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>15</v>
@@ -8849,7 +8855,7 @@
         <v>14</v>
       </c>
       <c r="F166" s="2">
-        <v>4072</v>
+        <v>3725</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>15</v>
@@ -8881,7 +8887,7 @@
         <v>14</v>
       </c>
       <c r="F167" s="2">
-        <v>1521</v>
+        <v>1987</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>15</v>
@@ -8913,7 +8919,7 @@
         <v>14</v>
       </c>
       <c r="F168" s="2">
-        <v>2070</v>
+        <v>2467</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>15</v>
@@ -8945,7 +8951,7 @@
         <v>14</v>
       </c>
       <c r="F169" s="2">
-        <v>1947</v>
+        <v>804</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>15</v>
@@ -8977,7 +8983,7 @@
         <v>14</v>
       </c>
       <c r="F170" s="2">
-        <v>2430</v>
+        <v>1805</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>15</v>
@@ -9009,7 +9015,7 @@
         <v>14</v>
       </c>
       <c r="F171" s="2">
-        <v>4406</v>
+        <v>2172</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>15</v>
@@ -9041,7 +9047,7 @@
         <v>14</v>
       </c>
       <c r="F172" s="2">
-        <v>4757</v>
+        <v>1749</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>15</v>
@@ -9073,7 +9079,7 @@
         <v>14</v>
       </c>
       <c r="F173" s="2">
-        <v>4077</v>
+        <v>4230</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>15</v>
@@ -9105,7 +9111,7 @@
         <v>14</v>
       </c>
       <c r="F174" s="2">
-        <v>4523</v>
+        <v>1483</v>
       </c>
       <c r="G174" s="2" t="s">
         <v>15</v>
@@ -9137,7 +9143,7 @@
         <v>14</v>
       </c>
       <c r="F175" s="2">
-        <v>3214</v>
+        <v>4340</v>
       </c>
       <c r="G175" s="2" t="s">
         <v>15</v>
@@ -9169,7 +9175,7 @@
         <v>14</v>
       </c>
       <c r="F176" s="2">
-        <v>2009</v>
+        <v>4664</v>
       </c>
       <c r="G176" s="2" t="s">
         <v>15</v>
@@ -9201,7 +9207,7 @@
         <v>14</v>
       </c>
       <c r="F177" s="2">
-        <v>1529</v>
+        <v>4138</v>
       </c>
       <c r="G177" s="2" t="s">
         <v>15</v>
@@ -9233,7 +9239,7 @@
         <v>14</v>
       </c>
       <c r="F178" s="2">
-        <v>3449</v>
+        <v>3105</v>
       </c>
       <c r="G178" s="2" t="s">
         <v>15</v>
@@ -9265,7 +9271,7 @@
         <v>14</v>
       </c>
       <c r="F179" s="2">
-        <v>4166</v>
+        <v>1705</v>
       </c>
       <c r="G179" s="2" t="s">
         <v>15</v>
@@ -9297,7 +9303,7 @@
         <v>14</v>
       </c>
       <c r="F180" s="2">
-        <v>2803</v>
+        <v>2812</v>
       </c>
       <c r="G180" s="2" t="s">
         <v>15</v>
@@ -9329,7 +9335,7 @@
         <v>14</v>
       </c>
       <c r="F181" s="2">
-        <v>4730</v>
+        <v>4224</v>
       </c>
       <c r="G181" s="2" t="s">
         <v>15</v>
@@ -9361,7 +9367,7 @@
         <v>14</v>
       </c>
       <c r="F182" s="2">
-        <v>2136</v>
+        <v>2968</v>
       </c>
       <c r="G182" s="2" t="s">
         <v>15</v>
@@ -9393,7 +9399,7 @@
         <v>14</v>
       </c>
       <c r="F183" s="2">
-        <v>3114</v>
+        <v>1212</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>15</v>
@@ -9425,7 +9431,7 @@
         <v>14</v>
       </c>
       <c r="F184" s="2">
-        <v>4197</v>
+        <v>3781</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>15</v>
@@ -9457,7 +9463,7 @@
         <v>14</v>
       </c>
       <c r="F185" s="2">
-        <v>3632</v>
+        <v>3059</v>
       </c>
       <c r="G185" s="2" t="s">
         <v>15</v>
@@ -9489,7 +9495,7 @@
         <v>14</v>
       </c>
       <c r="F186" s="2">
-        <v>2447</v>
+        <v>2840</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>15</v>
@@ -9521,7 +9527,7 @@
         <v>14</v>
       </c>
       <c r="F187" s="2">
-        <v>4336</v>
+        <v>3528</v>
       </c>
       <c r="G187" s="2" t="s">
         <v>15</v>
@@ -9553,7 +9559,7 @@
         <v>14</v>
       </c>
       <c r="F188" s="2">
-        <v>4277</v>
+        <v>4185</v>
       </c>
       <c r="G188" s="2" t="s">
         <v>15</v>
@@ -9585,7 +9591,7 @@
         <v>14</v>
       </c>
       <c r="F189" s="2">
-        <v>3617</v>
+        <v>2891</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>15</v>
@@ -9617,7 +9623,7 @@
         <v>14</v>
       </c>
       <c r="F190" s="2">
-        <v>3226</v>
+        <v>3345</v>
       </c>
       <c r="G190" s="2" t="s">
         <v>15</v>
@@ -9649,7 +9655,7 @@
         <v>14</v>
       </c>
       <c r="F191" s="2">
-        <v>2749</v>
+        <v>2664</v>
       </c>
       <c r="G191" s="2" t="s">
         <v>15</v>
@@ -9681,7 +9687,7 @@
         <v>14</v>
       </c>
       <c r="F192" s="2">
-        <v>4620</v>
+        <v>1594</v>
       </c>
       <c r="G192" s="2" t="s">
         <v>15</v>
@@ -9713,7 +9719,7 @@
         <v>14</v>
       </c>
       <c r="F193" s="2">
-        <v>2946</v>
+        <v>4012</v>
       </c>
       <c r="G193" s="2" t="s">
         <v>15</v>
@@ -9745,7 +9751,7 @@
         <v>14</v>
       </c>
       <c r="F194" s="2">
-        <v>1051</v>
+        <v>1149</v>
       </c>
       <c r="G194" s="2" t="s">
         <v>15</v>
@@ -9777,7 +9783,7 @@
         <v>14</v>
       </c>
       <c r="F195" s="2">
-        <v>3301</v>
+        <v>1030</v>
       </c>
       <c r="G195" s="2" t="s">
         <v>15</v>
@@ -9809,7 +9815,7 @@
         <v>14</v>
       </c>
       <c r="F196" s="2">
-        <v>3206</v>
+        <v>4657</v>
       </c>
       <c r="G196" s="2" t="s">
         <v>15</v>
@@ -9841,7 +9847,7 @@
         <v>14</v>
       </c>
       <c r="F197" s="2">
-        <v>2667</v>
+        <v>941</v>
       </c>
       <c r="G197" s="2" t="s">
         <v>15</v>
@@ -9873,7 +9879,7 @@
         <v>14</v>
       </c>
       <c r="F198" s="2">
-        <v>2543</v>
+        <v>2066</v>
       </c>
       <c r="G198" s="2" t="s">
         <v>15</v>
@@ -9905,7 +9911,7 @@
         <v>14</v>
       </c>
       <c r="F199" s="2">
-        <v>869</v>
+        <v>3271</v>
       </c>
       <c r="G199" s="2" t="s">
         <v>15</v>
@@ -9937,7 +9943,7 @@
         <v>14</v>
       </c>
       <c r="F200" s="2">
-        <v>4288</v>
+        <v>1751</v>
       </c>
       <c r="G200" s="2" t="s">
         <v>15</v>
@@ -9969,7 +9975,7 @@
         <v>14</v>
       </c>
       <c r="F201" s="2">
-        <v>2687</v>
+        <v>3980</v>
       </c>
       <c r="G201" s="2" t="s">
         <v>15</v>
@@ -10001,7 +10007,7 @@
         <v>14</v>
       </c>
       <c r="F202" s="2">
-        <v>1244</v>
+        <v>3501</v>
       </c>
       <c r="G202" s="2" t="s">
         <v>15</v>
@@ -10033,7 +10039,7 @@
         <v>14</v>
       </c>
       <c r="F203" s="2">
-        <v>2584</v>
+        <v>3871</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>15</v>
@@ -10065,7 +10071,7 @@
         <v>14</v>
       </c>
       <c r="F204" s="2">
-        <v>900</v>
+        <v>3049</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>15</v>
@@ -10097,7 +10103,7 @@
         <v>14</v>
       </c>
       <c r="F205" s="2">
-        <v>1331</v>
+        <v>3356</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>15</v>
@@ -10129,7 +10135,7 @@
         <v>14</v>
       </c>
       <c r="F206" s="2">
-        <v>4597</v>
+        <v>3695</v>
       </c>
       <c r="G206" s="2" t="s">
         <v>15</v>
@@ -10161,7 +10167,7 @@
         <v>14</v>
       </c>
       <c r="F207" s="2">
-        <v>2234</v>
+        <v>3118</v>
       </c>
       <c r="G207" s="2" t="s">
         <v>15</v>
@@ -10193,7 +10199,7 @@
         <v>14</v>
       </c>
       <c r="F208" s="2">
-        <v>4750</v>
+        <v>2705</v>
       </c>
       <c r="G208" s="2" t="s">
         <v>15</v>
@@ -10225,7 +10231,7 @@
         <v>14</v>
       </c>
       <c r="F209" s="2">
-        <v>2336</v>
+        <v>2869</v>
       </c>
       <c r="G209" s="2" t="s">
         <v>15</v>
@@ -10257,7 +10263,7 @@
         <v>14</v>
       </c>
       <c r="F210" s="2">
-        <v>961</v>
+        <v>1078</v>
       </c>
       <c r="G210" s="2" t="s">
         <v>15</v>
@@ -10289,7 +10295,7 @@
         <v>14</v>
       </c>
       <c r="F211" s="2">
-        <v>4540</v>
+        <v>3951</v>
       </c>
       <c r="G211" s="2" t="s">
         <v>15</v>
@@ -10321,7 +10327,7 @@
         <v>14</v>
       </c>
       <c r="F212" s="2">
-        <v>2357</v>
+        <v>4744</v>
       </c>
       <c r="G212" s="2" t="s">
         <v>15</v>
@@ -10353,7 +10359,7 @@
         <v>14</v>
       </c>
       <c r="F213" s="2">
-        <v>4134</v>
+        <v>3389</v>
       </c>
       <c r="G213" s="2" t="s">
         <v>15</v>
@@ -10385,7 +10391,7 @@
         <v>14</v>
       </c>
       <c r="F214" s="2">
-        <v>1352</v>
+        <v>1857</v>
       </c>
       <c r="G214" s="2" t="s">
         <v>15</v>
@@ -10417,7 +10423,7 @@
         <v>14</v>
       </c>
       <c r="F215" s="2">
-        <v>2546</v>
+        <v>3893</v>
       </c>
       <c r="G215" s="2" t="s">
         <v>15</v>
@@ -10449,7 +10455,7 @@
         <v>14</v>
       </c>
       <c r="F216" s="2">
-        <v>2160</v>
+        <v>1930</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>15</v>
@@ -10481,7 +10487,7 @@
         <v>14</v>
       </c>
       <c r="F217" s="2">
-        <v>963</v>
+        <v>2885</v>
       </c>
       <c r="G217" s="2" t="s">
         <v>15</v>
@@ -10513,7 +10519,7 @@
         <v>14</v>
       </c>
       <c r="F218" s="2">
-        <v>3333</v>
+        <v>1465</v>
       </c>
       <c r="G218" s="2" t="s">
         <v>15</v>
@@ -10545,7 +10551,7 @@
         <v>14</v>
       </c>
       <c r="F219" s="2">
-        <v>4758</v>
+        <v>2733</v>
       </c>
       <c r="G219" s="2" t="s">
         <v>15</v>
@@ -10577,7 +10583,7 @@
         <v>14</v>
       </c>
       <c r="F220" s="2">
-        <v>4434</v>
+        <v>4089</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>15</v>
@@ -10609,7 +10615,7 @@
         <v>14</v>
       </c>
       <c r="F221" s="2">
-        <v>3774</v>
+        <v>1683</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>15</v>
@@ -10641,7 +10647,7 @@
         <v>14</v>
       </c>
       <c r="F222" s="2">
-        <v>2010</v>
+        <v>2316</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>15</v>
@@ -10673,7 +10679,7 @@
         <v>14</v>
       </c>
       <c r="F223" s="2">
-        <v>1330</v>
+        <v>2857</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>15</v>
@@ -10705,7 +10711,7 @@
         <v>14</v>
       </c>
       <c r="F224" s="2">
-        <v>3665</v>
+        <v>1497</v>
       </c>
       <c r="G224" s="2" t="s">
         <v>15</v>
@@ -10737,7 +10743,7 @@
         <v>14</v>
       </c>
       <c r="F225" s="2">
-        <v>4365</v>
+        <v>3863</v>
       </c>
       <c r="G225" s="2" t="s">
         <v>15</v>
@@ -10769,7 +10775,7 @@
         <v>14</v>
       </c>
       <c r="F226" s="2">
-        <v>1460</v>
+        <v>4571</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>15</v>
@@ -10801,7 +10807,7 @@
         <v>14</v>
       </c>
       <c r="F227" s="2">
-        <v>2277</v>
+        <v>2464</v>
       </c>
       <c r="G227" s="2" t="s">
         <v>15</v>
@@ -10833,7 +10839,7 @@
         <v>14</v>
       </c>
       <c r="F228" s="2">
-        <v>1021</v>
+        <v>4429</v>
       </c>
       <c r="G228" s="2" t="s">
         <v>15</v>
@@ -10865,7 +10871,7 @@
         <v>14</v>
       </c>
       <c r="F229" s="2">
-        <v>2507</v>
+        <v>3963</v>
       </c>
       <c r="G229" s="2" t="s">
         <v>15</v>
@@ -10897,7 +10903,7 @@
         <v>14</v>
       </c>
       <c r="F230" s="2">
-        <v>2323</v>
+        <v>4374</v>
       </c>
       <c r="G230" s="2" t="s">
         <v>15</v>
@@ -10929,7 +10935,7 @@
         <v>14</v>
       </c>
       <c r="F231" s="2">
-        <v>1547</v>
+        <v>3374</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>15</v>
@@ -10961,7 +10967,7 @@
         <v>14</v>
       </c>
       <c r="F232" s="2">
-        <v>4154</v>
+        <v>4320</v>
       </c>
       <c r="G232" s="2" t="s">
         <v>15</v>
@@ -10993,7 +10999,7 @@
         <v>14</v>
       </c>
       <c r="F233" s="2">
-        <v>2503</v>
+        <v>4411</v>
       </c>
       <c r="G233" s="2" t="s">
         <v>15</v>
@@ -11025,7 +11031,7 @@
         <v>14</v>
       </c>
       <c r="F234" s="2">
-        <v>3448</v>
+        <v>3823</v>
       </c>
       <c r="G234" s="2" t="s">
         <v>15</v>
@@ -11057,7 +11063,7 @@
         <v>14</v>
       </c>
       <c r="F235" s="2">
-        <v>1404</v>
+        <v>2595</v>
       </c>
       <c r="G235" s="2" t="s">
         <v>15</v>
@@ -11089,7 +11095,7 @@
         <v>14</v>
       </c>
       <c r="F236" s="2">
-        <v>808</v>
+        <v>1177</v>
       </c>
       <c r="G236" s="2" t="s">
         <v>15</v>
@@ -11121,7 +11127,7 @@
         <v>14</v>
       </c>
       <c r="F237" s="2">
-        <v>2729</v>
+        <v>1799</v>
       </c>
       <c r="G237" s="2" t="s">
         <v>15</v>
@@ -11153,7 +11159,7 @@
         <v>14</v>
       </c>
       <c r="F238" s="2">
-        <v>1060</v>
+        <v>3067</v>
       </c>
       <c r="G238" s="2" t="s">
         <v>15</v>
@@ -11185,7 +11191,7 @@
         <v>14</v>
       </c>
       <c r="F239" s="2">
-        <v>2753</v>
+        <v>2632</v>
       </c>
       <c r="G239" s="2" t="s">
         <v>15</v>
@@ -11217,7 +11223,7 @@
         <v>14</v>
       </c>
       <c r="F240" s="2">
-        <v>3516</v>
+        <v>3722</v>
       </c>
       <c r="G240" s="2" t="s">
         <v>15</v>
@@ -11249,7 +11255,7 @@
         <v>14</v>
       </c>
       <c r="F241" s="2">
-        <v>4778</v>
+        <v>2451</v>
       </c>
       <c r="G241" s="2" t="s">
         <v>15</v>
@@ -11281,7 +11287,7 @@
         <v>14</v>
       </c>
       <c r="F242" s="2">
-        <v>3434</v>
+        <v>1074</v>
       </c>
       <c r="G242" s="2" t="s">
         <v>15</v>
@@ -11313,7 +11319,7 @@
         <v>14</v>
       </c>
       <c r="F243" s="2">
-        <v>3187</v>
+        <v>980</v>
       </c>
       <c r="G243" s="2" t="s">
         <v>15</v>
@@ -11345,7 +11351,7 @@
         <v>14</v>
       </c>
       <c r="F244" s="2">
-        <v>3387</v>
+        <v>1329</v>
       </c>
       <c r="G244" s="2" t="s">
         <v>15</v>
@@ -11377,7 +11383,7 @@
         <v>14</v>
       </c>
       <c r="F245" s="2">
-        <v>3258</v>
+        <v>4189</v>
       </c>
       <c r="G245" s="2" t="s">
         <v>15</v>
@@ -11409,7 +11415,7 @@
         <v>14</v>
       </c>
       <c r="F246" s="2">
-        <v>1382</v>
+        <v>3594</v>
       </c>
       <c r="G246" s="2" t="s">
         <v>15</v>
@@ -11441,7 +11447,7 @@
         <v>14</v>
       </c>
       <c r="F247" s="2">
-        <v>4558</v>
+        <v>2654</v>
       </c>
       <c r="G247" s="2" t="s">
         <v>15</v>
@@ -11473,7 +11479,7 @@
         <v>14</v>
       </c>
       <c r="F248" s="2">
-        <v>3086</v>
+        <v>4305</v>
       </c>
       <c r="G248" s="2" t="s">
         <v>15</v>
@@ -11505,7 +11511,7 @@
         <v>14</v>
       </c>
       <c r="F249" s="2">
-        <v>2447</v>
+        <v>4786</v>
       </c>
       <c r="G249" s="2" t="s">
         <v>15</v>
@@ -11537,7 +11543,7 @@
         <v>14</v>
       </c>
       <c r="F250" s="2">
-        <v>2425</v>
+        <v>2056</v>
       </c>
       <c r="G250" s="2" t="s">
         <v>15</v>
@@ -11569,7 +11575,7 @@
         <v>14</v>
       </c>
       <c r="F251" s="2">
-        <v>1027</v>
+        <v>803</v>
       </c>
       <c r="G251" s="2" t="s">
         <v>15</v>
@@ -11601,7 +11607,7 @@
         <v>14</v>
       </c>
       <c r="F252" s="2">
-        <v>4737</v>
+        <v>4393</v>
       </c>
       <c r="G252" s="2" t="s">
         <v>15</v>
@@ -11633,7 +11639,7 @@
         <v>14</v>
       </c>
       <c r="F253" s="2">
-        <v>3855</v>
+        <v>897</v>
       </c>
       <c r="G253" s="2" t="s">
         <v>15</v>
@@ -11665,7 +11671,7 @@
         <v>14</v>
       </c>
       <c r="F254" s="2">
-        <v>3756</v>
+        <v>2696</v>
       </c>
       <c r="G254" s="2" t="s">
         <v>15</v>
@@ -11697,7 +11703,7 @@
         <v>14</v>
       </c>
       <c r="F255" s="2">
-        <v>810</v>
+        <v>4120</v>
       </c>
       <c r="G255" s="2" t="s">
         <v>15</v>
@@ -11729,7 +11735,7 @@
         <v>14</v>
       </c>
       <c r="F256" s="2">
-        <v>1571</v>
+        <v>3926</v>
       </c>
       <c r="G256" s="2" t="s">
         <v>15</v>
@@ -11761,7 +11767,7 @@
         <v>14</v>
       </c>
       <c r="F257" s="2">
-        <v>1393</v>
+        <v>1085</v>
       </c>
       <c r="G257" s="2" t="s">
         <v>15</v>
@@ -11793,7 +11799,7 @@
         <v>14</v>
       </c>
       <c r="F258" s="2">
-        <v>1065</v>
+        <v>3107</v>
       </c>
       <c r="G258" s="2" t="s">
         <v>15</v>
@@ -11825,7 +11831,7 @@
         <v>14</v>
       </c>
       <c r="F259" s="2">
-        <v>4754</v>
+        <v>1392</v>
       </c>
       <c r="G259" s="2" t="s">
         <v>15</v>
@@ -11857,7 +11863,7 @@
         <v>14</v>
       </c>
       <c r="F260" s="2">
-        <v>2996</v>
+        <v>4134</v>
       </c>
       <c r="G260" s="2" t="s">
         <v>15</v>
@@ -11889,7 +11895,7 @@
         <v>14</v>
       </c>
       <c r="F261" s="2">
-        <v>1046</v>
+        <v>3066</v>
       </c>
       <c r="G261" s="2" t="s">
         <v>15</v>
@@ -11921,7 +11927,7 @@
         <v>14</v>
       </c>
       <c r="F262" s="2">
-        <v>4727</v>
+        <v>1441</v>
       </c>
       <c r="G262" s="2" t="s">
         <v>15</v>
@@ -11953,7 +11959,7 @@
         <v>14</v>
       </c>
       <c r="F263" s="2">
-        <v>4471</v>
+        <v>4297</v>
       </c>
       <c r="G263" s="2" t="s">
         <v>15</v>
@@ -11985,7 +11991,7 @@
         <v>14</v>
       </c>
       <c r="F264" s="2">
-        <v>2581</v>
+        <v>3715</v>
       </c>
       <c r="G264" s="2" t="s">
         <v>15</v>
@@ -12017,7 +12023,7 @@
         <v>14</v>
       </c>
       <c r="F265" s="2">
-        <v>864</v>
+        <v>4532</v>
       </c>
       <c r="G265" s="2" t="s">
         <v>15</v>
@@ -12049,7 +12055,7 @@
         <v>14</v>
       </c>
       <c r="F266" s="2">
-        <v>1489</v>
+        <v>3604</v>
       </c>
       <c r="G266" s="2" t="s">
         <v>15</v>
@@ -12081,7 +12087,7 @@
         <v>14</v>
       </c>
       <c r="F267" s="2">
-        <v>4662</v>
+        <v>3415</v>
       </c>
       <c r="G267" s="2" t="s">
         <v>15</v>
@@ -12113,7 +12119,7 @@
         <v>14</v>
       </c>
       <c r="F268" s="2">
-        <v>3946</v>
+        <v>3771</v>
       </c>
       <c r="G268" s="2" t="s">
         <v>15</v>
@@ -12145,7 +12151,7 @@
         <v>14</v>
       </c>
       <c r="F269" s="2">
-        <v>1040</v>
+        <v>4492</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>15</v>
@@ -12177,7 +12183,7 @@
         <v>14</v>
       </c>
       <c r="F270" s="2">
-        <v>2190</v>
+        <v>4406</v>
       </c>
       <c r="G270" s="2" t="s">
         <v>15</v>
@@ -12209,7 +12215,7 @@
         <v>14</v>
       </c>
       <c r="F271" s="2">
-        <v>1139</v>
+        <v>4183</v>
       </c>
       <c r="G271" s="2" t="s">
         <v>15</v>
@@ -12241,7 +12247,7 @@
         <v>14</v>
       </c>
       <c r="F272" s="2">
-        <v>1466</v>
+        <v>1460</v>
       </c>
       <c r="G272" s="2" t="s">
         <v>15</v>
@@ -12273,7 +12279,7 @@
         <v>14</v>
       </c>
       <c r="F273" s="2">
-        <v>1500</v>
+        <v>2595</v>
       </c>
       <c r="G273" s="2" t="s">
         <v>15</v>
@@ -12305,7 +12311,7 @@
         <v>14</v>
       </c>
       <c r="F274" s="2">
-        <v>2191</v>
+        <v>2304</v>
       </c>
       <c r="G274" s="2" t="s">
         <v>15</v>
@@ -12337,7 +12343,7 @@
         <v>14</v>
       </c>
       <c r="F275" s="2">
-        <v>4675</v>
+        <v>2085</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>15</v>
@@ -12369,7 +12375,7 @@
         <v>14</v>
       </c>
       <c r="F276" s="2">
-        <v>1760</v>
+        <v>2202</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>15</v>
@@ -12401,7 +12407,7 @@
         <v>14</v>
       </c>
       <c r="F277" s="2">
-        <v>3307</v>
+        <v>1377</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>15</v>
@@ -12433,7 +12439,7 @@
         <v>14</v>
       </c>
       <c r="F278" s="2">
-        <v>3276</v>
+        <v>1561</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>15</v>
@@ -12465,7 +12471,7 @@
         <v>14</v>
       </c>
       <c r="F279" s="2">
-        <v>1646</v>
+        <v>4386</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>15</v>
@@ -12497,7 +12503,7 @@
         <v>14</v>
       </c>
       <c r="F280" s="2">
-        <v>2557</v>
+        <v>1896</v>
       </c>
       <c r="G280" s="2" t="s">
         <v>15</v>
@@ -12529,7 +12535,7 @@
         <v>14</v>
       </c>
       <c r="F281" s="2">
-        <v>848</v>
+        <v>833</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>15</v>
@@ -12561,7 +12567,7 @@
         <v>14</v>
       </c>
       <c r="F282" s="2">
-        <v>1593</v>
+        <v>2828</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>15</v>
@@ -12593,7 +12599,7 @@
         <v>14</v>
       </c>
       <c r="F283" s="2">
-        <v>3323</v>
+        <v>1352</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>15</v>
@@ -12625,7 +12631,7 @@
         <v>14</v>
       </c>
       <c r="F284" s="2">
-        <v>4342</v>
+        <v>2569</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>15</v>
@@ -12657,7 +12663,7 @@
         <v>14</v>
       </c>
       <c r="F285" s="2">
-        <v>1283</v>
+        <v>4117</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>15</v>
@@ -12689,7 +12695,7 @@
         <v>14</v>
       </c>
       <c r="F286" s="2">
-        <v>4303</v>
+        <v>3729</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>15</v>
@@ -12721,7 +12727,7 @@
         <v>14</v>
       </c>
       <c r="F287" s="2">
-        <v>2164</v>
+        <v>4663</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>15</v>
@@ -12753,7 +12759,7 @@
         <v>14</v>
       </c>
       <c r="F288" s="2">
-        <v>2351</v>
+        <v>4319</v>
       </c>
       <c r="G288" s="2" t="s">
         <v>15</v>
@@ -12785,7 +12791,7 @@
         <v>14</v>
       </c>
       <c r="F289" s="2">
-        <v>4096</v>
+        <v>1641</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>15</v>
@@ -12817,7 +12823,7 @@
         <v>14</v>
       </c>
       <c r="F290" s="2">
-        <v>1969</v>
+        <v>2917</v>
       </c>
       <c r="G290" s="2" t="s">
         <v>15</v>
@@ -12849,7 +12855,7 @@
         <v>14</v>
       </c>
       <c r="F291" s="2">
-        <v>1407</v>
+        <v>1005</v>
       </c>
       <c r="G291" s="2" t="s">
         <v>15</v>
@@ -12881,7 +12887,7 @@
         <v>14</v>
       </c>
       <c r="F292" s="2">
-        <v>3774</v>
+        <v>4171</v>
       </c>
       <c r="G292" s="2" t="s">
         <v>15</v>
@@ -12913,7 +12919,7 @@
         <v>14</v>
       </c>
       <c r="F293" s="2">
-        <v>1455</v>
+        <v>1361</v>
       </c>
       <c r="G293" s="2" t="s">
         <v>15</v>
@@ -12945,7 +12951,7 @@
         <v>14</v>
       </c>
       <c r="F294" s="2">
-        <v>4397</v>
+        <v>1049</v>
       </c>
       <c r="G294" s="2" t="s">
         <v>15</v>
@@ -12977,7 +12983,7 @@
         <v>14</v>
       </c>
       <c r="F295" s="2">
-        <v>3980</v>
+        <v>2936</v>
       </c>
       <c r="G295" s="2" t="s">
         <v>15</v>
@@ -13009,7 +13015,7 @@
         <v>14</v>
       </c>
       <c r="F296" s="2">
-        <v>3857</v>
+        <v>3238</v>
       </c>
       <c r="G296" s="2" t="s">
         <v>15</v>
@@ -13041,7 +13047,7 @@
         <v>14</v>
       </c>
       <c r="F297" s="2">
-        <v>1141</v>
+        <v>3448</v>
       </c>
       <c r="G297" s="2" t="s">
         <v>15</v>
@@ -13073,7 +13079,7 @@
         <v>14</v>
       </c>
       <c r="F298" s="2">
-        <v>3478</v>
+        <v>3837</v>
       </c>
       <c r="G298" s="2" t="s">
         <v>15</v>
@@ -13105,7 +13111,7 @@
         <v>14</v>
       </c>
       <c r="F299" s="2">
-        <v>944</v>
+        <v>2424</v>
       </c>
       <c r="G299" s="2" t="s">
         <v>15</v>
@@ -13137,7 +13143,7 @@
         <v>14</v>
       </c>
       <c r="F300" s="2">
-        <v>3936</v>
+        <v>1443</v>
       </c>
       <c r="G300" s="2" t="s">
         <v>15</v>
@@ -13169,7 +13175,7 @@
         <v>14</v>
       </c>
       <c r="F301" s="2">
-        <v>1904</v>
+        <v>2969</v>
       </c>
       <c r="G301" s="2" t="s">
         <v>15</v>
@@ -13201,7 +13207,7 @@
         <v>14</v>
       </c>
       <c r="F302" s="2">
-        <v>3637</v>
+        <v>2522</v>
       </c>
       <c r="G302" s="2" t="s">
         <v>15</v>
@@ -13233,7 +13239,7 @@
         <v>14</v>
       </c>
       <c r="F303" s="2">
-        <v>3904</v>
+        <v>2361</v>
       </c>
       <c r="G303" s="2" t="s">
         <v>15</v>
@@ -13265,7 +13271,7 @@
         <v>14</v>
       </c>
       <c r="F304" s="2">
-        <v>1539</v>
+        <v>4261</v>
       </c>
       <c r="G304" s="2" t="s">
         <v>15</v>
@@ -13297,7 +13303,7 @@
         <v>14</v>
       </c>
       <c r="F305" s="2">
-        <v>2509</v>
+        <v>1752</v>
       </c>
       <c r="G305" s="2" t="s">
         <v>15</v>
@@ -13329,7 +13335,7 @@
         <v>14</v>
       </c>
       <c r="F306" s="2">
-        <v>2019</v>
+        <v>3392</v>
       </c>
       <c r="G306" s="2" t="s">
         <v>15</v>
@@ -13361,7 +13367,7 @@
         <v>14</v>
       </c>
       <c r="F307" s="2">
-        <v>1266</v>
+        <v>1606</v>
       </c>
       <c r="G307" s="2" t="s">
         <v>15</v>
@@ -13393,7 +13399,7 @@
         <v>14</v>
       </c>
       <c r="F308" s="2">
-        <v>2105</v>
+        <v>2455</v>
       </c>
       <c r="G308" s="2" t="s">
         <v>15</v>
@@ -13425,7 +13431,7 @@
         <v>14</v>
       </c>
       <c r="F309" s="2">
-        <v>3067</v>
+        <v>3909</v>
       </c>
       <c r="G309" s="2" t="s">
         <v>15</v>
@@ -13457,7 +13463,7 @@
         <v>14</v>
       </c>
       <c r="F310" s="2">
-        <v>1085</v>
+        <v>945</v>
       </c>
       <c r="G310" s="2" t="s">
         <v>15</v>
@@ -13489,7 +13495,7 @@
         <v>14</v>
       </c>
       <c r="F311" s="2">
-        <v>4028</v>
+        <v>1186</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>15</v>
@@ -13521,7 +13527,7 @@
         <v>14</v>
       </c>
       <c r="F312" s="2">
-        <v>3577</v>
+        <v>2273</v>
       </c>
       <c r="G312" s="2" t="s">
         <v>15</v>
@@ -13553,7 +13559,7 @@
         <v>14</v>
       </c>
       <c r="F313" s="2">
-        <v>2187</v>
+        <v>2767</v>
       </c>
       <c r="G313" s="2" t="s">
         <v>15</v>
@@ -13585,7 +13591,7 @@
         <v>14</v>
       </c>
       <c r="F314" s="2">
-        <v>4572</v>
+        <v>4311</v>
       </c>
       <c r="G314" s="2" t="s">
         <v>15</v>
@@ -13617,7 +13623,7 @@
         <v>14</v>
       </c>
       <c r="F315" s="2">
-        <v>3242</v>
+        <v>1878</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>15</v>
@@ -13649,7 +13655,7 @@
         <v>14</v>
       </c>
       <c r="F316" s="2">
-        <v>3690</v>
+        <v>3873</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>15</v>
@@ -13681,7 +13687,7 @@
         <v>14</v>
       </c>
       <c r="F317" s="2">
-        <v>2733</v>
+        <v>3640</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>15</v>
@@ -13713,7 +13719,7 @@
         <v>14</v>
       </c>
       <c r="F318" s="2">
-        <v>1958</v>
+        <v>3014</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>15</v>
@@ -13745,7 +13751,7 @@
         <v>14</v>
       </c>
       <c r="F319" s="2">
-        <v>4379</v>
+        <v>3150</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>15</v>
@@ -13777,7 +13783,7 @@
         <v>14</v>
       </c>
       <c r="F320" s="2">
-        <v>4308</v>
+        <v>949</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>15</v>
@@ -13809,7 +13815,7 @@
         <v>14</v>
       </c>
       <c r="F321" s="2">
-        <v>1194</v>
+        <v>4132</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>15</v>
@@ -13841,7 +13847,7 @@
         <v>14</v>
       </c>
       <c r="F322" s="2">
-        <v>4601</v>
+        <v>2320</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>15</v>
@@ -13873,7 +13879,7 @@
         <v>14</v>
       </c>
       <c r="F323" s="2">
-        <v>1397</v>
+        <v>4708</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>15</v>
@@ -13905,7 +13911,7 @@
         <v>14</v>
       </c>
       <c r="F324" s="2">
-        <v>964</v>
+        <v>3171</v>
       </c>
       <c r="G324" s="2" t="s">
         <v>15</v>
@@ -13937,7 +13943,7 @@
         <v>14</v>
       </c>
       <c r="F325" s="2">
-        <v>4190</v>
+        <v>3095</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>15</v>
@@ -13969,7 +13975,7 @@
         <v>14</v>
       </c>
       <c r="F326" s="2">
-        <v>3048</v>
+        <v>4466</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>15</v>
@@ -14001,7 +14007,7 @@
         <v>14</v>
       </c>
       <c r="F327" s="2">
-        <v>4088</v>
+        <v>2537</v>
       </c>
       <c r="G327" s="2" t="s">
         <v>15</v>
@@ -14033,7 +14039,7 @@
         <v>14</v>
       </c>
       <c r="F328" s="2">
-        <v>4479</v>
+        <v>2359</v>
       </c>
       <c r="G328" s="2" t="s">
         <v>15</v>
@@ -14065,7 +14071,7 @@
         <v>14</v>
       </c>
       <c r="F329" s="2">
-        <v>1165</v>
+        <v>1856</v>
       </c>
       <c r="G329" s="2" t="s">
         <v>15</v>
@@ -14097,7 +14103,7 @@
         <v>14</v>
       </c>
       <c r="F330" s="2">
-        <v>3023</v>
+        <v>4724</v>
       </c>
       <c r="G330" s="2" t="s">
         <v>15</v>
@@ -14129,7 +14135,7 @@
         <v>14</v>
       </c>
       <c r="F331" s="2">
-        <v>2526</v>
+        <v>3579</v>
       </c>
       <c r="G331" s="2" t="s">
         <v>15</v>
@@ -14161,7 +14167,7 @@
         <v>14</v>
       </c>
       <c r="F332" s="2">
-        <v>3121</v>
+        <v>1179</v>
       </c>
       <c r="G332" s="2" t="s">
         <v>15</v>
@@ -14193,7 +14199,7 @@
         <v>14</v>
       </c>
       <c r="F333" s="2">
-        <v>4367</v>
+        <v>3875</v>
       </c>
       <c r="G333" s="2" t="s">
         <v>15</v>
@@ -14225,7 +14231,7 @@
         <v>14</v>
       </c>
       <c r="F334" s="2">
-        <v>2689</v>
+        <v>2280</v>
       </c>
       <c r="G334" s="2" t="s">
         <v>15</v>
@@ -14257,7 +14263,7 @@
         <v>14</v>
       </c>
       <c r="F335" s="2">
-        <v>3178</v>
+        <v>1783</v>
       </c>
       <c r="G335" s="2" t="s">
         <v>15</v>
@@ -14289,7 +14295,7 @@
         <v>14</v>
       </c>
       <c r="F336" s="2">
-        <v>1294</v>
+        <v>3849</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>15</v>
@@ -14321,7 +14327,7 @@
         <v>14</v>
       </c>
       <c r="F337" s="2">
-        <v>2394</v>
+        <v>4175</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>15</v>
@@ -14353,7 +14359,7 @@
         <v>14</v>
       </c>
       <c r="F338" s="2">
-        <v>3449</v>
+        <v>1102</v>
       </c>
       <c r="G338" s="2" t="s">
         <v>15</v>
@@ -14385,7 +14391,7 @@
         <v>14</v>
       </c>
       <c r="F339" s="2">
-        <v>3341</v>
+        <v>4401</v>
       </c>
       <c r="G339" s="2" t="s">
         <v>15</v>
@@ -14417,7 +14423,7 @@
         <v>14</v>
       </c>
       <c r="F340" s="2">
-        <v>3243</v>
+        <v>1516</v>
       </c>
       <c r="G340" s="2" t="s">
         <v>15</v>
@@ -14449,7 +14455,7 @@
         <v>14</v>
       </c>
       <c r="F341" s="2">
-        <v>3812</v>
+        <v>1874</v>
       </c>
       <c r="G341" s="2" t="s">
         <v>15</v>
@@ -14481,7 +14487,7 @@
         <v>14</v>
       </c>
       <c r="F342" s="2">
-        <v>3297</v>
+        <v>4381</v>
       </c>
       <c r="G342" s="2" t="s">
         <v>15</v>
@@ -14513,7 +14519,7 @@
         <v>14</v>
       </c>
       <c r="F343" s="2">
-        <v>2021</v>
+        <v>4729</v>
       </c>
       <c r="G343" s="2" t="s">
         <v>15</v>
@@ -14545,7 +14551,7 @@
         <v>14</v>
       </c>
       <c r="F344" s="2">
-        <v>2728</v>
+        <v>3553</v>
       </c>
       <c r="G344" s="2" t="s">
         <v>15</v>
@@ -14577,7 +14583,7 @@
         <v>14</v>
       </c>
       <c r="F345" s="2">
-        <v>4033</v>
+        <v>1112</v>
       </c>
       <c r="G345" s="2" t="s">
         <v>15</v>
@@ -14609,7 +14615,7 @@
         <v>14</v>
       </c>
       <c r="F346" s="2">
-        <v>1728</v>
+        <v>3855</v>
       </c>
       <c r="G346" s="2" t="s">
         <v>15</v>
@@ -14641,7 +14647,7 @@
         <v>14</v>
       </c>
       <c r="F347" s="2">
-        <v>4114</v>
+        <v>2902</v>
       </c>
       <c r="G347" s="2" t="s">
         <v>15</v>
@@ -14673,7 +14679,7 @@
         <v>14</v>
       </c>
       <c r="F348" s="2">
-        <v>914</v>
+        <v>1095</v>
       </c>
       <c r="G348" s="2" t="s">
         <v>15</v>
@@ -14705,7 +14711,7 @@
         <v>14</v>
       </c>
       <c r="F349" s="2">
-        <v>1251</v>
+        <v>3587</v>
       </c>
       <c r="G349" s="2" t="s">
         <v>15</v>
@@ -14737,7 +14743,7 @@
         <v>14</v>
       </c>
       <c r="F350" s="2">
-        <v>1116</v>
+        <v>2294</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>15</v>
@@ -14769,7 +14775,7 @@
         <v>14</v>
       </c>
       <c r="F351" s="2">
-        <v>1883</v>
+        <v>2353</v>
       </c>
       <c r="G351" s="2" t="s">
         <v>15</v>
@@ -14801,7 +14807,7 @@
         <v>14</v>
       </c>
       <c r="F352" s="2">
-        <v>4188</v>
+        <v>3640</v>
       </c>
       <c r="G352" s="2" t="s">
         <v>15</v>
@@ -14833,7 +14839,7 @@
         <v>14</v>
       </c>
       <c r="F353" s="2">
-        <v>3390</v>
+        <v>3672</v>
       </c>
       <c r="G353" s="2" t="s">
         <v>15</v>
@@ -14865,7 +14871,7 @@
         <v>14</v>
       </c>
       <c r="F354" s="2">
-        <v>1935</v>
+        <v>2866</v>
       </c>
       <c r="G354" s="2" t="s">
         <v>15</v>
@@ -14897,7 +14903,7 @@
         <v>14</v>
       </c>
       <c r="F355" s="2">
-        <v>2901</v>
+        <v>4777</v>
       </c>
       <c r="G355" s="2" t="s">
         <v>15</v>
@@ -14929,7 +14935,7 @@
         <v>14</v>
       </c>
       <c r="F356" s="2">
-        <v>3050</v>
+        <v>3993</v>
       </c>
       <c r="G356" s="2" t="s">
         <v>15</v>
@@ -14961,7 +14967,7 @@
         <v>14</v>
       </c>
       <c r="F357" s="2">
-        <v>4551</v>
+        <v>932</v>
       </c>
       <c r="G357" s="2" t="s">
         <v>15</v>
@@ -14993,7 +14999,7 @@
         <v>14</v>
       </c>
       <c r="F358" s="2">
-        <v>3905</v>
+        <v>985</v>
       </c>
       <c r="G358" s="2" t="s">
         <v>15</v>
@@ -15025,7 +15031,7 @@
         <v>14</v>
       </c>
       <c r="F359" s="2">
-        <v>1682</v>
+        <v>3836</v>
       </c>
       <c r="G359" s="2" t="s">
         <v>15</v>
@@ -15057,7 +15063,7 @@
         <v>14</v>
       </c>
       <c r="F360" s="2">
-        <v>4125</v>
+        <v>3085</v>
       </c>
       <c r="G360" s="2" t="s">
         <v>15</v>
@@ -15089,7 +15095,7 @@
         <v>14</v>
       </c>
       <c r="F361" s="2">
-        <v>4470</v>
+        <v>2465</v>
       </c>
       <c r="G361" s="2" t="s">
         <v>15</v>
@@ -15121,7 +15127,7 @@
         <v>14</v>
       </c>
       <c r="F362" s="2">
-        <v>1010</v>
+        <v>2096</v>
       </c>
       <c r="G362" s="2" t="s">
         <v>15</v>
@@ -15153,7 +15159,7 @@
         <v>14</v>
       </c>
       <c r="F363" s="2">
-        <v>4183</v>
+        <v>1168</v>
       </c>
       <c r="G363" s="2" t="s">
         <v>15</v>
@@ -15185,7 +15191,7 @@
         <v>14</v>
       </c>
       <c r="F364" s="2">
-        <v>4573</v>
+        <v>4558</v>
       </c>
       <c r="G364" s="2" t="s">
         <v>15</v>
@@ -15217,7 +15223,7 @@
         <v>14</v>
       </c>
       <c r="F365" s="2">
-        <v>2404</v>
+        <v>1487</v>
       </c>
       <c r="G365" s="2" t="s">
         <v>15</v>
@@ -15249,7 +15255,7 @@
         <v>14</v>
       </c>
       <c r="F366" s="2">
-        <v>1139</v>
+        <v>1011</v>
       </c>
       <c r="G366" s="2" t="s">
         <v>15</v>
@@ -15281,7 +15287,7 @@
         <v>14</v>
       </c>
       <c r="F367" s="2">
-        <v>4698</v>
+        <v>3882</v>
       </c>
       <c r="G367" s="2" t="s">
         <v>15</v>
@@ -15313,7 +15319,7 @@
         <v>14</v>
       </c>
       <c r="F368" s="2">
-        <v>4734</v>
+        <v>3010</v>
       </c>
       <c r="G368" s="2" t="s">
         <v>15</v>
@@ -15345,7 +15351,7 @@
         <v>14</v>
       </c>
       <c r="F369" s="2">
-        <v>2963</v>
+        <v>1328</v>
       </c>
       <c r="G369" s="2" t="s">
         <v>15</v>
@@ -15377,7 +15383,7 @@
         <v>14</v>
       </c>
       <c r="F370" s="2">
-        <v>2976</v>
+        <v>2958</v>
       </c>
       <c r="G370" s="2" t="s">
         <v>15</v>
@@ -15409,7 +15415,7 @@
         <v>14</v>
       </c>
       <c r="F371" s="2">
-        <v>3047</v>
+        <v>901</v>
       </c>
       <c r="G371" s="2" t="s">
         <v>15</v>
@@ -15441,7 +15447,7 @@
         <v>14</v>
       </c>
       <c r="F372" s="2">
-        <v>2520</v>
+        <v>3539</v>
       </c>
       <c r="G372" s="2" t="s">
         <v>15</v>
@@ -15473,7 +15479,7 @@
         <v>14</v>
       </c>
       <c r="F373" s="2">
-        <v>4378</v>
+        <v>2758</v>
       </c>
       <c r="G373" s="2" t="s">
         <v>15</v>
@@ -15505,7 +15511,7 @@
         <v>14</v>
       </c>
       <c r="F374" s="2">
-        <v>1879</v>
+        <v>3005</v>
       </c>
       <c r="G374" s="2" t="s">
         <v>15</v>
@@ -15537,7 +15543,7 @@
         <v>14</v>
       </c>
       <c r="F375" s="2">
-        <v>1599</v>
+        <v>4755</v>
       </c>
       <c r="G375" s="2" t="s">
         <v>15</v>
@@ -15569,7 +15575,7 @@
         <v>14</v>
       </c>
       <c r="F376" s="2">
-        <v>2097</v>
+        <v>2112</v>
       </c>
       <c r="G376" s="2" t="s">
         <v>15</v>
@@ -15601,7 +15607,7 @@
         <v>14</v>
       </c>
       <c r="F377" s="2">
-        <v>4707</v>
+        <v>2645</v>
       </c>
       <c r="G377" s="2" t="s">
         <v>15</v>
@@ -15633,7 +15639,7 @@
         <v>14</v>
       </c>
       <c r="F378" s="2">
-        <v>2809</v>
+        <v>996</v>
       </c>
       <c r="G378" s="2" t="s">
         <v>15</v>
@@ -15665,7 +15671,7 @@
         <v>14</v>
       </c>
       <c r="F379" s="2">
-        <v>2215</v>
+        <v>1786</v>
       </c>
       <c r="G379" s="2" t="s">
         <v>15</v>
@@ -15697,7 +15703,7 @@
         <v>14</v>
       </c>
       <c r="F380" s="2">
-        <v>1908</v>
+        <v>2699</v>
       </c>
       <c r="G380" s="2" t="s">
         <v>15</v>
@@ -15729,7 +15735,7 @@
         <v>14</v>
       </c>
       <c r="F381" s="2">
-        <v>1626</v>
+        <v>1302</v>
       </c>
       <c r="G381" s="2" t="s">
         <v>15</v>
@@ -15761,7 +15767,7 @@
         <v>14</v>
       </c>
       <c r="F382" s="2">
-        <v>2584</v>
+        <v>1931</v>
       </c>
       <c r="G382" s="2" t="s">
         <v>15</v>
@@ -15793,7 +15799,7 @@
         <v>14</v>
       </c>
       <c r="F383" s="2">
-        <v>3926</v>
+        <v>4263</v>
       </c>
       <c r="G383" s="2" t="s">
         <v>15</v>
@@ -15825,7 +15831,7 @@
         <v>14</v>
       </c>
       <c r="F384" s="2">
-        <v>2472</v>
+        <v>3284</v>
       </c>
       <c r="G384" s="2" t="s">
         <v>15</v>
@@ -15857,7 +15863,7 @@
         <v>14</v>
       </c>
       <c r="F385" s="2">
-        <v>1496</v>
+        <v>4677</v>
       </c>
       <c r="G385" s="2" t="s">
         <v>15</v>
@@ -15889,7 +15895,7 @@
         <v>14</v>
       </c>
       <c r="F386" s="2">
-        <v>2150</v>
+        <v>1576</v>
       </c>
       <c r="G386" s="2" t="s">
         <v>15</v>
@@ -15921,7 +15927,7 @@
         <v>14</v>
       </c>
       <c r="F387" s="2">
-        <v>4178</v>
+        <v>1599</v>
       </c>
       <c r="G387" s="2" t="s">
         <v>15</v>
@@ -15953,7 +15959,7 @@
         <v>14</v>
       </c>
       <c r="F388" s="2">
-        <v>3497</v>
+        <v>3992</v>
       </c>
       <c r="G388" s="2" t="s">
         <v>15</v>
@@ -15985,7 +15991,7 @@
         <v>14</v>
       </c>
       <c r="F389" s="2">
-        <v>3448</v>
+        <v>1328</v>
       </c>
       <c r="G389" s="2" t="s">
         <v>15</v>
@@ -16017,7 +16023,7 @@
         <v>14</v>
       </c>
       <c r="F390" s="2">
-        <v>2430</v>
+        <v>3471</v>
       </c>
       <c r="G390" s="2" t="s">
         <v>15</v>
@@ -16049,7 +16055,7 @@
         <v>14</v>
       </c>
       <c r="F391" s="2">
-        <v>2733</v>
+        <v>1270</v>
       </c>
       <c r="G391" s="2" t="s">
         <v>15</v>
@@ -16081,7 +16087,7 @@
         <v>14</v>
       </c>
       <c r="F392" s="2">
-        <v>1345</v>
+        <v>1582</v>
       </c>
       <c r="G392" s="2" t="s">
         <v>15</v>
@@ -16113,7 +16119,7 @@
         <v>14</v>
       </c>
       <c r="F393" s="2">
-        <v>1026</v>
+        <v>4522</v>
       </c>
       <c r="G393" s="2" t="s">
         <v>15</v>
@@ -16145,7 +16151,7 @@
         <v>14</v>
       </c>
       <c r="F394" s="2">
-        <v>2355</v>
+        <v>1236</v>
       </c>
       <c r="G394" s="2" t="s">
         <v>15</v>
@@ -16177,7 +16183,7 @@
         <v>14</v>
       </c>
       <c r="F395" s="2">
-        <v>2668</v>
+        <v>1493</v>
       </c>
       <c r="G395" s="2" t="s">
         <v>15</v>
@@ -16209,7 +16215,7 @@
         <v>14</v>
       </c>
       <c r="F396" s="2">
-        <v>932</v>
+        <v>3975</v>
       </c>
       <c r="G396" s="2" t="s">
         <v>15</v>
@@ -16241,7 +16247,7 @@
         <v>14</v>
       </c>
       <c r="F397" s="2">
-        <v>3599</v>
+        <v>1558</v>
       </c>
       <c r="G397" s="2" t="s">
         <v>15</v>
@@ -16273,7 +16279,7 @@
         <v>14</v>
       </c>
       <c r="F398" s="2">
-        <v>1862</v>
+        <v>2726</v>
       </c>
       <c r="G398" s="2" t="s">
         <v>15</v>
@@ -16305,7 +16311,7 @@
         <v>14</v>
       </c>
       <c r="F399" s="2">
-        <v>1616</v>
+        <v>1875</v>
       </c>
       <c r="G399" s="2" t="s">
         <v>15</v>
@@ -16337,7 +16343,7 @@
         <v>14</v>
       </c>
       <c r="F400" s="2">
-        <v>3844</v>
+        <v>880</v>
       </c>
       <c r="G400" s="2" t="s">
         <v>15</v>
@@ -16369,7 +16375,7 @@
         <v>14</v>
       </c>
       <c r="F401" s="2">
-        <v>2033</v>
+        <v>4647</v>
       </c>
       <c r="G401" s="2" t="s">
         <v>15</v>
@@ -16401,7 +16407,7 @@
         <v>14</v>
       </c>
       <c r="F402" s="2">
-        <v>3785</v>
+        <v>3028</v>
       </c>
       <c r="G402" s="2" t="s">
         <v>15</v>
@@ -16433,7 +16439,7 @@
         <v>14</v>
       </c>
       <c r="F403" s="2">
-        <v>1370</v>
+        <v>2676</v>
       </c>
       <c r="G403" s="2" t="s">
         <v>15</v>
@@ -16465,7 +16471,7 @@
         <v>14</v>
       </c>
       <c r="F404" s="2">
-        <v>3772</v>
+        <v>990</v>
       </c>
       <c r="G404" s="2" t="s">
         <v>15</v>
@@ -16497,7 +16503,7 @@
         <v>14</v>
       </c>
       <c r="F405" s="2">
-        <v>1552</v>
+        <v>4679</v>
       </c>
       <c r="G405" s="2" t="s">
         <v>15</v>
@@ -16529,7 +16535,7 @@
         <v>14</v>
       </c>
       <c r="F406" s="2">
-        <v>801</v>
+        <v>4110</v>
       </c>
       <c r="G406" s="2" t="s">
         <v>15</v>
@@ -16561,7 +16567,7 @@
         <v>14</v>
       </c>
       <c r="F407" s="2">
-        <v>1601</v>
+        <v>1085</v>
       </c>
       <c r="G407" s="2" t="s">
         <v>15</v>
@@ -16593,7 +16599,7 @@
         <v>14</v>
       </c>
       <c r="F408" s="2">
-        <v>4454</v>
+        <v>3761</v>
       </c>
       <c r="G408" s="2" t="s">
         <v>15</v>
@@ -16625,7 +16631,7 @@
         <v>14</v>
       </c>
       <c r="F409" s="2">
-        <v>2894</v>
+        <v>1164</v>
       </c>
       <c r="G409" s="2" t="s">
         <v>15</v>
@@ -16657,7 +16663,7 @@
         <v>14</v>
       </c>
       <c r="F410" s="2">
-        <v>3981</v>
+        <v>3649</v>
       </c>
       <c r="G410" s="2" t="s">
         <v>15</v>
@@ -16689,7 +16695,7 @@
         <v>14</v>
       </c>
       <c r="F411" s="2">
-        <v>2220</v>
+        <v>1997</v>
       </c>
       <c r="G411" s="2" t="s">
         <v>15</v>
@@ -16721,7 +16727,7 @@
         <v>14</v>
       </c>
       <c r="F412" s="2">
-        <v>3352</v>
+        <v>2072</v>
       </c>
       <c r="G412" s="2" t="s">
         <v>15</v>
@@ -16753,7 +16759,7 @@
         <v>14</v>
       </c>
       <c r="F413" s="2">
-        <v>2846</v>
+        <v>3226</v>
       </c>
       <c r="G413" s="2" t="s">
         <v>15</v>
@@ -16785,7 +16791,7 @@
         <v>14</v>
       </c>
       <c r="F414" s="2">
-        <v>2255</v>
+        <v>3758</v>
       </c>
       <c r="G414" s="2" t="s">
         <v>15</v>
@@ -16817,7 +16823,7 @@
         <v>14</v>
       </c>
       <c r="F415" s="2">
-        <v>950</v>
+        <v>2552</v>
       </c>
       <c r="G415" s="2" t="s">
         <v>15</v>
@@ -16849,7 +16855,7 @@
         <v>14</v>
       </c>
       <c r="F416" s="2">
-        <v>2243</v>
+        <v>4136</v>
       </c>
       <c r="G416" s="2" t="s">
         <v>15</v>
@@ -16881,7 +16887,7 @@
         <v>14</v>
       </c>
       <c r="F417" s="2">
-        <v>2722</v>
+        <v>2681</v>
       </c>
       <c r="G417" s="2" t="s">
         <v>15</v>
@@ -16913,7 +16919,7 @@
         <v>14</v>
       </c>
       <c r="F418" s="2">
-        <v>2635</v>
+        <v>4032</v>
       </c>
       <c r="G418" s="2" t="s">
         <v>15</v>
@@ -16945,7 +16951,7 @@
         <v>14</v>
       </c>
       <c r="F419" s="2">
-        <v>2456</v>
+        <v>2766</v>
       </c>
       <c r="G419" s="2" t="s">
         <v>15</v>
@@ -16977,7 +16983,7 @@
         <v>14</v>
       </c>
       <c r="F420" s="2">
-        <v>852</v>
+        <v>2832</v>
       </c>
       <c r="G420" s="2" t="s">
         <v>15</v>
@@ -17009,7 +17015,7 @@
         <v>14</v>
       </c>
       <c r="F421" s="2">
-        <v>4015</v>
+        <v>1211</v>
       </c>
       <c r="G421" s="2" t="s">
         <v>15</v>
@@ -17041,7 +17047,7 @@
         <v>14</v>
       </c>
       <c r="F422" s="2">
-        <v>4310</v>
+        <v>4033</v>
       </c>
       <c r="G422" s="2" t="s">
         <v>15</v>
@@ -17073,7 +17079,7 @@
         <v>14</v>
       </c>
       <c r="F423" s="2">
-        <v>1040</v>
+        <v>1074</v>
       </c>
       <c r="G423" s="2" t="s">
         <v>15</v>
@@ -17105,7 +17111,7 @@
         <v>14</v>
       </c>
       <c r="F424" s="2">
-        <v>4251</v>
+        <v>2292</v>
       </c>
       <c r="G424" s="2" t="s">
         <v>15</v>
@@ -17137,7 +17143,7 @@
         <v>14</v>
       </c>
       <c r="F425" s="2">
-        <v>2989</v>
+        <v>1285</v>
       </c>
       <c r="G425" s="2" t="s">
         <v>15</v>
@@ -17169,7 +17175,7 @@
         <v>14</v>
       </c>
       <c r="F426" s="2">
-        <v>3367</v>
+        <v>3517</v>
       </c>
       <c r="G426" s="2" t="s">
         <v>15</v>
@@ -17201,7 +17207,7 @@
         <v>14</v>
       </c>
       <c r="F427" s="2">
-        <v>2872</v>
+        <v>4108</v>
       </c>
       <c r="G427" s="2" t="s">
         <v>15</v>
@@ -17233,7 +17239,7 @@
         <v>14</v>
       </c>
       <c r="F428" s="2">
-        <v>1632</v>
+        <v>2722</v>
       </c>
       <c r="G428" s="2" t="s">
         <v>15</v>
@@ -17265,7 +17271,7 @@
         <v>14</v>
       </c>
       <c r="F429" s="2">
-        <v>2671</v>
+        <v>2391</v>
       </c>
       <c r="G429" s="2" t="s">
         <v>15</v>
@@ -17297,7 +17303,7 @@
         <v>14</v>
       </c>
       <c r="F430" s="2">
-        <v>3484</v>
+        <v>3521</v>
       </c>
       <c r="G430" s="2" t="s">
         <v>15</v>
@@ -17329,7 +17335,7 @@
         <v>14</v>
       </c>
       <c r="F431" s="2">
-        <v>1151</v>
+        <v>3952</v>
       </c>
       <c r="G431" s="2" t="s">
         <v>15</v>
@@ -17361,7 +17367,7 @@
         <v>14</v>
       </c>
       <c r="F432" s="2">
-        <v>4696</v>
+        <v>4083</v>
       </c>
       <c r="G432" s="2" t="s">
         <v>15</v>
@@ -17393,7 +17399,7 @@
         <v>14</v>
       </c>
       <c r="F433" s="2">
-        <v>1986</v>
+        <v>3442</v>
       </c>
       <c r="G433" s="2" t="s">
         <v>15</v>
@@ -17425,7 +17431,7 @@
         <v>14</v>
       </c>
       <c r="F434" s="2">
-        <v>2573</v>
+        <v>2922</v>
       </c>
       <c r="G434" s="2" t="s">
         <v>15</v>
@@ -17457,7 +17463,7 @@
         <v>14</v>
       </c>
       <c r="F435" s="2">
-        <v>2239</v>
+        <v>2540</v>
       </c>
       <c r="G435" s="2" t="s">
         <v>15</v>
@@ -17489,7 +17495,7 @@
         <v>14</v>
       </c>
       <c r="F436" s="2">
-        <v>4591</v>
+        <v>3988</v>
       </c>
       <c r="G436" s="2" t="s">
         <v>15</v>
@@ -17521,7 +17527,7 @@
         <v>14</v>
       </c>
       <c r="F437" s="2">
-        <v>1429</v>
+        <v>2379</v>
       </c>
       <c r="G437" s="2" t="s">
         <v>15</v>
@@ -17553,7 +17559,7 @@
         <v>14</v>
       </c>
       <c r="F438" s="2">
-        <v>2712</v>
+        <v>3032</v>
       </c>
       <c r="G438" s="2" t="s">
         <v>15</v>
@@ -17585,7 +17591,7 @@
         <v>14</v>
       </c>
       <c r="F439" s="2">
-        <v>3261</v>
+        <v>3176</v>
       </c>
       <c r="G439" s="2" t="s">
         <v>15</v>
@@ -17617,7 +17623,7 @@
         <v>14</v>
       </c>
       <c r="F440" s="2">
-        <v>4385</v>
+        <v>3795</v>
       </c>
       <c r="G440" s="2" t="s">
         <v>15</v>
@@ -17649,7 +17655,7 @@
         <v>14</v>
       </c>
       <c r="F441" s="2">
-        <v>1274</v>
+        <v>3443</v>
       </c>
       <c r="G441" s="2" t="s">
         <v>15</v>
@@ -17681,7 +17687,7 @@
         <v>14</v>
       </c>
       <c r="F442" s="2">
-        <v>1504</v>
+        <v>2605</v>
       </c>
       <c r="G442" s="2" t="s">
         <v>15</v>
@@ -17713,7 +17719,7 @@
         <v>14</v>
       </c>
       <c r="F443" s="2">
-        <v>3631</v>
+        <v>3369</v>
       </c>
       <c r="G443" s="2" t="s">
         <v>15</v>
@@ -17745,7 +17751,7 @@
         <v>14</v>
       </c>
       <c r="F444" s="2">
-        <v>4101</v>
+        <v>4702</v>
       </c>
       <c r="G444" s="2" t="s">
         <v>15</v>
@@ -17777,7 +17783,7 @@
         <v>14</v>
       </c>
       <c r="F445" s="2">
-        <v>2468</v>
+        <v>1767</v>
       </c>
       <c r="G445" s="2" t="s">
         <v>15</v>
@@ -17809,7 +17815,7 @@
         <v>14</v>
       </c>
       <c r="F446" s="2">
-        <v>3415</v>
+        <v>1614</v>
       </c>
       <c r="G446" s="2" t="s">
         <v>15</v>
@@ -17841,7 +17847,7 @@
         <v>14</v>
       </c>
       <c r="F447" s="2">
-        <v>3313</v>
+        <v>3406</v>
       </c>
       <c r="G447" s="2" t="s">
         <v>15</v>
@@ -17873,7 +17879,7 @@
         <v>14</v>
       </c>
       <c r="F448" s="2">
-        <v>1389</v>
+        <v>2220</v>
       </c>
       <c r="G448" s="2" t="s">
         <v>15</v>
@@ -17905,7 +17911,7 @@
         <v>14</v>
       </c>
       <c r="F449" s="2">
-        <v>3990</v>
+        <v>4767</v>
       </c>
       <c r="G449" s="2" t="s">
         <v>15</v>
@@ -17937,7 +17943,7 @@
         <v>14</v>
       </c>
       <c r="F450" s="2">
-        <v>4244</v>
+        <v>2164</v>
       </c>
       <c r="G450" s="2" t="s">
         <v>15</v>
@@ -17969,7 +17975,7 @@
         <v>14</v>
       </c>
       <c r="F451" s="2">
-        <v>2275</v>
+        <v>1956</v>
       </c>
       <c r="G451" s="2" t="s">
         <v>15</v>
@@ -18001,7 +18007,7 @@
         <v>14</v>
       </c>
       <c r="F452" s="2">
-        <v>2573</v>
+        <v>2927</v>
       </c>
       <c r="G452" s="2" t="s">
         <v>15</v>
@@ -18033,7 +18039,7 @@
         <v>14</v>
       </c>
       <c r="F453" s="2">
-        <v>2089</v>
+        <v>3916</v>
       </c>
       <c r="G453" s="2" t="s">
         <v>15</v>
@@ -18065,7 +18071,7 @@
         <v>14</v>
       </c>
       <c r="F454" s="2">
-        <v>3373</v>
+        <v>2357</v>
       </c>
       <c r="G454" s="2" t="s">
         <v>15</v>
@@ -18097,7 +18103,7 @@
         <v>14</v>
       </c>
       <c r="F455" s="2">
-        <v>4374</v>
+        <v>2914</v>
       </c>
       <c r="G455" s="2" t="s">
         <v>15</v>
@@ -18129,7 +18135,7 @@
         <v>14</v>
       </c>
       <c r="F456" s="2">
-        <v>3615</v>
+        <v>825</v>
       </c>
       <c r="G456" s="2" t="s">
         <v>15</v>
@@ -18161,7 +18167,7 @@
         <v>14</v>
       </c>
       <c r="F457" s="2">
-        <v>1087</v>
+        <v>1491</v>
       </c>
       <c r="G457" s="2" t="s">
         <v>15</v>
@@ -18193,7 +18199,7 @@
         <v>14</v>
       </c>
       <c r="F458" s="2">
-        <v>949</v>
+        <v>867</v>
       </c>
       <c r="G458" s="2" t="s">
         <v>15</v>
@@ -18225,7 +18231,7 @@
         <v>14</v>
       </c>
       <c r="F459" s="2">
-        <v>4113</v>
+        <v>2884</v>
       </c>
       <c r="G459" s="2" t="s">
         <v>15</v>
@@ -18257,7 +18263,7 @@
         <v>14</v>
       </c>
       <c r="F460" s="2">
-        <v>4286</v>
+        <v>1735</v>
       </c>
       <c r="G460" s="2" t="s">
         <v>15</v>
@@ -18289,7 +18295,7 @@
         <v>14</v>
       </c>
       <c r="F461" s="2">
-        <v>2693</v>
+        <v>931</v>
       </c>
       <c r="G461" s="2" t="s">
         <v>15</v>
@@ -18321,7 +18327,7 @@
         <v>14</v>
       </c>
       <c r="F462" s="2">
-        <v>3972</v>
+        <v>3658</v>
       </c>
       <c r="G462" s="2" t="s">
         <v>15</v>
@@ -18353,7 +18359,7 @@
         <v>14</v>
       </c>
       <c r="F463" s="2">
-        <v>4054</v>
+        <v>4732</v>
       </c>
       <c r="G463" s="2" t="s">
         <v>15</v>
@@ -18385,7 +18391,7 @@
         <v>14</v>
       </c>
       <c r="F464" s="2">
-        <v>1137</v>
+        <v>4411</v>
       </c>
       <c r="G464" s="2" t="s">
         <v>15</v>
@@ -18417,7 +18423,7 @@
         <v>14</v>
       </c>
       <c r="F465" s="2">
-        <v>1514</v>
+        <v>4170</v>
       </c>
       <c r="G465" s="2" t="s">
         <v>15</v>
@@ -18449,7 +18455,7 @@
         <v>14</v>
       </c>
       <c r="F466" s="2">
-        <v>1973</v>
+        <v>2958</v>
       </c>
       <c r="G466" s="2" t="s">
         <v>15</v>
@@ -18481,7 +18487,7 @@
         <v>14</v>
       </c>
       <c r="F467" s="2">
-        <v>2793</v>
+        <v>1615</v>
       </c>
       <c r="G467" s="2" t="s">
         <v>15</v>
@@ -18513,7 +18519,7 @@
         <v>14</v>
       </c>
       <c r="F468" s="2">
-        <v>4284</v>
+        <v>2441</v>
       </c>
       <c r="G468" s="2" t="s">
         <v>15</v>
@@ -18545,7 +18551,7 @@
         <v>14</v>
       </c>
       <c r="F469" s="2">
-        <v>4292</v>
+        <v>3483</v>
       </c>
       <c r="G469" s="2" t="s">
         <v>15</v>
@@ -18577,7 +18583,7 @@
         <v>14</v>
       </c>
       <c r="F470" s="2">
-        <v>2003</v>
+        <v>1685</v>
       </c>
       <c r="G470" s="2" t="s">
         <v>15</v>
@@ -18609,7 +18615,7 @@
         <v>14</v>
       </c>
       <c r="F471" s="2">
-        <v>2217</v>
+        <v>2762</v>
       </c>
       <c r="G471" s="2" t="s">
         <v>15</v>
@@ -18696,7 +18702,7 @@
         <v>14</v>
       </c>
       <c r="F2" s="2">
-        <v>2554</v>
+        <v>1410</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>15</v>
@@ -18728,7 +18734,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="2">
-        <v>1005</v>
+        <v>2568</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>15</v>
@@ -18760,7 +18766,7 @@
         <v>14</v>
       </c>
       <c r="F4" s="2">
-        <v>1371</v>
+        <v>2061</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
@@ -18792,7 +18798,7 @@
         <v>14</v>
       </c>
       <c r="F5" s="2">
-        <v>4403</v>
+        <v>1006</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
@@ -18824,7 +18830,7 @@
         <v>14</v>
       </c>
       <c r="F6" s="2">
-        <v>1966</v>
+        <v>1407</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -18856,7 +18862,7 @@
         <v>14</v>
       </c>
       <c r="F7" s="2">
-        <v>1146</v>
+        <v>3043</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -18888,7 +18894,7 @@
         <v>14</v>
       </c>
       <c r="F8" s="2">
-        <v>983</v>
+        <v>3101</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -18920,7 +18926,7 @@
         <v>14</v>
       </c>
       <c r="F9" s="2">
-        <v>4550</v>
+        <v>4731</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -18952,7 +18958,7 @@
         <v>14</v>
       </c>
       <c r="F10" s="2">
-        <v>3546</v>
+        <v>2421</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
@@ -18984,7 +18990,7 @@
         <v>14</v>
       </c>
       <c r="F11" s="2">
-        <v>1587</v>
+        <v>1090</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
@@ -19016,7 +19022,7 @@
         <v>14</v>
       </c>
       <c r="F12" s="2">
-        <v>2686</v>
+        <v>1528</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
@@ -19048,7 +19054,7 @@
         <v>14</v>
       </c>
       <c r="F13" s="2">
-        <v>923</v>
+        <v>3680</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -19080,7 +19086,7 @@
         <v>14</v>
       </c>
       <c r="F14" s="2">
-        <v>1180</v>
+        <v>875</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -19112,7 +19118,7 @@
         <v>14</v>
       </c>
       <c r="F15" s="2">
-        <v>4539</v>
+        <v>2932</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -19144,7 +19150,7 @@
         <v>14</v>
       </c>
       <c r="F16" s="2">
-        <v>4247</v>
+        <v>3362</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
@@ -19176,7 +19182,7 @@
         <v>14</v>
       </c>
       <c r="F17" s="2">
-        <v>941</v>
+        <v>4552</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
@@ -19208,7 +19214,7 @@
         <v>14</v>
       </c>
       <c r="F18" s="2">
-        <v>2875</v>
+        <v>1353</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
@@ -19240,7 +19246,7 @@
         <v>14</v>
       </c>
       <c r="F19" s="2">
-        <v>2654</v>
+        <v>2798</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
@@ -19272,7 +19278,7 @@
         <v>14</v>
       </c>
       <c r="F20" s="2">
-        <v>2107</v>
+        <v>2479</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
@@ -19304,7 +19310,7 @@
         <v>14</v>
       </c>
       <c r="F21" s="2">
-        <v>4282</v>
+        <v>4771</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -19336,7 +19342,7 @@
         <v>14</v>
       </c>
       <c r="F22" s="2">
-        <v>2543</v>
+        <v>919</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -19368,7 +19374,7 @@
         <v>14</v>
       </c>
       <c r="F23" s="2">
-        <v>4573</v>
+        <v>2857</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -19400,7 +19406,7 @@
         <v>14</v>
       </c>
       <c r="F24" s="2">
-        <v>4360</v>
+        <v>4482</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -19432,7 +19438,7 @@
         <v>14</v>
       </c>
       <c r="F25" s="2">
-        <v>3018</v>
+        <v>1199</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -19464,7 +19470,7 @@
         <v>14</v>
       </c>
       <c r="F26" s="2">
-        <v>1625</v>
+        <v>1797</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -19496,7 +19502,7 @@
         <v>14</v>
       </c>
       <c r="F27" s="2">
-        <v>4092</v>
+        <v>3818</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>15</v>
@@ -19528,7 +19534,7 @@
         <v>14</v>
       </c>
       <c r="F28" s="2">
-        <v>1499</v>
+        <v>1624</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>15</v>
@@ -19560,7 +19566,7 @@
         <v>14</v>
       </c>
       <c r="F29" s="2">
-        <v>2405</v>
+        <v>3847</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>15</v>
@@ -19592,7 +19598,7 @@
         <v>14</v>
       </c>
       <c r="F30" s="2">
-        <v>3156</v>
+        <v>3120</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>15</v>
@@ -19624,7 +19630,7 @@
         <v>14</v>
       </c>
       <c r="F31" s="2">
-        <v>917</v>
+        <v>3823</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>15</v>
@@ -19656,7 +19662,7 @@
         <v>14</v>
       </c>
       <c r="F32" s="2">
-        <v>1702</v>
+        <v>4104</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>15</v>
@@ -19688,7 +19694,7 @@
         <v>14</v>
       </c>
       <c r="F33" s="2">
-        <v>3737</v>
+        <v>2120</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>15</v>
@@ -19720,7 +19726,7 @@
         <v>14</v>
       </c>
       <c r="F34" s="2">
-        <v>4655</v>
+        <v>3997</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>15</v>
@@ -19752,7 +19758,7 @@
         <v>14</v>
       </c>
       <c r="F35" s="2">
-        <v>2182</v>
+        <v>3831</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>15</v>
@@ -19784,7 +19790,7 @@
         <v>14</v>
       </c>
       <c r="F36" s="2">
-        <v>1459</v>
+        <v>2020</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>15</v>
@@ -19816,7 +19822,7 @@
         <v>14</v>
       </c>
       <c r="F37" s="2">
-        <v>1951</v>
+        <v>929</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>15</v>
@@ -19848,7 +19854,7 @@
         <v>14</v>
       </c>
       <c r="F38" s="2">
-        <v>3093</v>
+        <v>4216</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>15</v>
@@ -19880,7 +19886,7 @@
         <v>14</v>
       </c>
       <c r="F39" s="2">
-        <v>2140</v>
+        <v>963</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>15</v>
@@ -19912,7 +19918,7 @@
         <v>14</v>
       </c>
       <c r="F40" s="2">
-        <v>1502</v>
+        <v>4559</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>15</v>
@@ -19944,7 +19950,7 @@
         <v>14</v>
       </c>
       <c r="F41" s="2">
-        <v>1559</v>
+        <v>2751</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>15</v>
@@ -19976,7 +19982,7 @@
         <v>14</v>
       </c>
       <c r="F42" s="2">
-        <v>3356</v>
+        <v>1717</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>15</v>
@@ -20008,7 +20014,7 @@
         <v>14</v>
       </c>
       <c r="F43" s="2">
-        <v>1380</v>
+        <v>3906</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>15</v>
@@ -20040,7 +20046,7 @@
         <v>14</v>
       </c>
       <c r="F44" s="2">
-        <v>4790</v>
+        <v>3902</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>15</v>
@@ -20072,7 +20078,7 @@
         <v>14</v>
       </c>
       <c r="F45" s="2">
-        <v>1149</v>
+        <v>1999</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>15</v>
@@ -20104,7 +20110,7 @@
         <v>14</v>
       </c>
       <c r="F46" s="2">
-        <v>1770</v>
+        <v>3922</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>15</v>
@@ -20136,7 +20142,7 @@
         <v>14</v>
       </c>
       <c r="F47" s="2">
-        <v>4797</v>
+        <v>957</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>15</v>
@@ -20168,7 +20174,7 @@
         <v>14</v>
       </c>
       <c r="F48" s="2">
-        <v>3166</v>
+        <v>1646</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>15</v>
@@ -20200,7 +20206,7 @@
         <v>14</v>
       </c>
       <c r="F49" s="2">
-        <v>1537</v>
+        <v>4151</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>15</v>
@@ -20232,7 +20238,7 @@
         <v>14</v>
       </c>
       <c r="F50" s="2">
-        <v>1273</v>
+        <v>1006</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>15</v>
@@ -20264,7 +20270,7 @@
         <v>14</v>
       </c>
       <c r="F51" s="2">
-        <v>1816</v>
+        <v>3542</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>15</v>
@@ -20296,7 +20302,7 @@
         <v>14</v>
       </c>
       <c r="F52" s="2">
-        <v>1217</v>
+        <v>2125</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>15</v>
@@ -20328,7 +20334,7 @@
         <v>14</v>
       </c>
       <c r="F53" s="2">
-        <v>4478</v>
+        <v>3601</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>15</v>
@@ -20360,7 +20366,7 @@
         <v>14</v>
       </c>
       <c r="F54" s="2">
-        <v>1505</v>
+        <v>1221</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>15</v>
@@ -20392,7 +20398,7 @@
         <v>14</v>
       </c>
       <c r="F55" s="2">
-        <v>1462</v>
+        <v>849</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>15</v>
@@ -20424,7 +20430,7 @@
         <v>14</v>
       </c>
       <c r="F56" s="2">
-        <v>3530</v>
+        <v>1093</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>15</v>
@@ -20456,7 +20462,7 @@
         <v>14</v>
       </c>
       <c r="F57" s="2">
-        <v>3488</v>
+        <v>4635</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>15</v>
@@ -20488,7 +20494,7 @@
         <v>14</v>
       </c>
       <c r="F58" s="2">
-        <v>2121</v>
+        <v>1880</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>15</v>
@@ -20520,7 +20526,7 @@
         <v>14</v>
       </c>
       <c r="F59" s="2">
-        <v>1512</v>
+        <v>4763</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>15</v>
@@ -20552,7 +20558,7 @@
         <v>14</v>
       </c>
       <c r="F60" s="2">
-        <v>3540</v>
+        <v>4396</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>15</v>
@@ -20584,7 +20590,7 @@
         <v>14</v>
       </c>
       <c r="F61" s="2">
-        <v>3072</v>
+        <v>1408</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>15</v>
@@ -20616,7 +20622,7 @@
         <v>14</v>
       </c>
       <c r="F62" s="2">
-        <v>1371</v>
+        <v>1750</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>15</v>
@@ -20648,7 +20654,7 @@
         <v>14</v>
       </c>
       <c r="F63" s="2">
-        <v>3849</v>
+        <v>2831</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>15</v>
@@ -20680,7 +20686,7 @@
         <v>14</v>
       </c>
       <c r="F64" s="2">
-        <v>2403</v>
+        <v>2474</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>15</v>
@@ -20712,7 +20718,7 @@
         <v>14</v>
       </c>
       <c r="F65" s="2">
-        <v>1547</v>
+        <v>3741</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>15</v>
@@ -20744,7 +20750,7 @@
         <v>14</v>
       </c>
       <c r="F66" s="2">
-        <v>2696</v>
+        <v>870</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>15</v>
@@ -20776,7 +20782,7 @@
         <v>14</v>
       </c>
       <c r="F67" s="2">
-        <v>2694</v>
+        <v>881</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>15</v>
@@ -20808,7 +20814,7 @@
         <v>14</v>
       </c>
       <c r="F68" s="2">
-        <v>2290</v>
+        <v>3836</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>15</v>
@@ -20840,7 +20846,7 @@
         <v>14</v>
       </c>
       <c r="F69" s="2">
-        <v>3304</v>
+        <v>947</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>15</v>
@@ -20872,7 +20878,7 @@
         <v>14</v>
       </c>
       <c r="F70" s="2">
-        <v>2800</v>
+        <v>2520</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>15</v>
@@ -20904,7 +20910,7 @@
         <v>14</v>
       </c>
       <c r="F71" s="2">
-        <v>3720</v>
+        <v>802</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>15</v>
@@ -20936,7 +20942,7 @@
         <v>14</v>
       </c>
       <c r="F72" s="2">
-        <v>3612</v>
+        <v>1896</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>15</v>
@@ -20968,7 +20974,7 @@
         <v>14</v>
       </c>
       <c r="F73" s="2">
-        <v>2939</v>
+        <v>2299</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>15</v>
@@ -21000,7 +21006,7 @@
         <v>14</v>
       </c>
       <c r="F74" s="2">
-        <v>1505</v>
+        <v>3349</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>15</v>
@@ -21032,7 +21038,7 @@
         <v>14</v>
       </c>
       <c r="F75" s="2">
-        <v>2673</v>
+        <v>2722</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>15</v>
@@ -21064,7 +21070,7 @@
         <v>14</v>
       </c>
       <c r="F76" s="2">
-        <v>1061</v>
+        <v>2271</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>15</v>
@@ -21096,7 +21102,7 @@
         <v>14</v>
       </c>
       <c r="F77" s="2">
-        <v>4781</v>
+        <v>3728</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>15</v>
@@ -21128,7 +21134,7 @@
         <v>14</v>
       </c>
       <c r="F78" s="2">
-        <v>3500</v>
+        <v>4793</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>15</v>
@@ -21160,7 +21166,7 @@
         <v>14</v>
       </c>
       <c r="F79" s="2">
-        <v>3862</v>
+        <v>1799</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>15</v>
@@ -21192,7 +21198,7 @@
         <v>14</v>
       </c>
       <c r="F80" s="2">
-        <v>1119</v>
+        <v>4067</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>15</v>
@@ -21224,7 +21230,7 @@
         <v>14</v>
       </c>
       <c r="F81" s="2">
-        <v>2935</v>
+        <v>4595</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>15</v>
@@ -21256,7 +21262,7 @@
         <v>14</v>
       </c>
       <c r="F82" s="2">
-        <v>1561</v>
+        <v>3797</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>15</v>
@@ -21288,7 +21294,7 @@
         <v>14</v>
       </c>
       <c r="F83" s="2">
-        <v>1032</v>
+        <v>1604</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>15</v>
@@ -21320,7 +21326,7 @@
         <v>14</v>
       </c>
       <c r="F84" s="2">
-        <v>1353</v>
+        <v>4449</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>15</v>
@@ -21352,7 +21358,7 @@
         <v>14</v>
       </c>
       <c r="F85" s="2">
-        <v>1353</v>
+        <v>2248</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>15</v>
@@ -21384,7 +21390,7 @@
         <v>14</v>
       </c>
       <c r="F86" s="2">
-        <v>2099</v>
+        <v>2680</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>15</v>
@@ -21416,7 +21422,7 @@
         <v>14</v>
       </c>
       <c r="F87" s="2">
-        <v>1039</v>
+        <v>4120</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>15</v>
@@ -21448,7 +21454,7 @@
         <v>14</v>
       </c>
       <c r="F88" s="2">
-        <v>2316</v>
+        <v>3876</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>15</v>
@@ -21480,7 +21486,7 @@
         <v>14</v>
       </c>
       <c r="F89" s="2">
-        <v>948</v>
+        <v>3388</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>15</v>
@@ -21512,7 +21518,7 @@
         <v>14</v>
       </c>
       <c r="F90" s="2">
-        <v>4289</v>
+        <v>4069</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>15</v>
@@ -21544,7 +21550,7 @@
         <v>14</v>
       </c>
       <c r="F91" s="2">
-        <v>1622</v>
+        <v>4798</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>15</v>
@@ -21576,7 +21582,7 @@
         <v>14</v>
       </c>
       <c r="F92" s="2">
-        <v>1578</v>
+        <v>2721</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>15</v>
@@ -21608,7 +21614,7 @@
         <v>14</v>
       </c>
       <c r="F93" s="2">
-        <v>2989</v>
+        <v>4198</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>15</v>
@@ -21640,7 +21646,7 @@
         <v>14</v>
       </c>
       <c r="F94" s="2">
-        <v>1228</v>
+        <v>4093</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>15</v>
@@ -21672,7 +21678,7 @@
         <v>14</v>
       </c>
       <c r="F95" s="2">
-        <v>2170</v>
+        <v>3415</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>15</v>
@@ -21704,7 +21710,7 @@
         <v>14</v>
       </c>
       <c r="F96" s="2">
-        <v>3182</v>
+        <v>3917</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>15</v>
@@ -21736,7 +21742,7 @@
         <v>14</v>
       </c>
       <c r="F97" s="2">
-        <v>4059</v>
+        <v>4376</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>15</v>
@@ -21768,7 +21774,7 @@
         <v>14</v>
       </c>
       <c r="F98" s="2">
-        <v>1886</v>
+        <v>1534</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>15</v>
@@ -21800,7 +21806,7 @@
         <v>14</v>
       </c>
       <c r="F99" s="2">
-        <v>3240</v>
+        <v>1396</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>15</v>
@@ -21832,7 +21838,7 @@
         <v>14</v>
       </c>
       <c r="F100" s="2">
-        <v>3142</v>
+        <v>1788</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>15</v>
@@ -21864,7 +21870,7 @@
         <v>14</v>
       </c>
       <c r="F101" s="2">
-        <v>3776</v>
+        <v>860</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>15</v>
@@ -21896,7 +21902,7 @@
         <v>14</v>
       </c>
       <c r="F102" s="2">
-        <v>2382</v>
+        <v>4117</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>15</v>
@@ -21928,7 +21934,7 @@
         <v>14</v>
       </c>
       <c r="F103" s="2">
-        <v>1109</v>
+        <v>1431</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>15</v>
@@ -21960,7 +21966,7 @@
         <v>14</v>
       </c>
       <c r="F104" s="2">
-        <v>1350</v>
+        <v>2506</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>15</v>
@@ -21992,7 +21998,7 @@
         <v>14</v>
       </c>
       <c r="F105" s="2">
-        <v>1307</v>
+        <v>1492</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>15</v>
@@ -22024,7 +22030,7 @@
         <v>14</v>
       </c>
       <c r="F106" s="2">
-        <v>3191</v>
+        <v>4114</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>15</v>
@@ -22056,7 +22062,7 @@
         <v>14</v>
       </c>
       <c r="F107" s="2">
-        <v>2024</v>
+        <v>3396</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>15</v>
@@ -22088,7 +22094,7 @@
         <v>14</v>
       </c>
       <c r="F108" s="2">
-        <v>2141</v>
+        <v>1053</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>15</v>
@@ -22120,7 +22126,7 @@
         <v>14</v>
       </c>
       <c r="F109" s="2">
-        <v>1115</v>
+        <v>970</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>15</v>
@@ -22152,7 +22158,7 @@
         <v>14</v>
       </c>
       <c r="F110" s="2">
-        <v>3138</v>
+        <v>3978</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>15</v>
@@ -22184,7 +22190,7 @@
         <v>14</v>
       </c>
       <c r="F111" s="2">
-        <v>2260</v>
+        <v>1929</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>15</v>
@@ -22216,7 +22222,7 @@
         <v>14</v>
       </c>
       <c r="F112" s="2">
-        <v>1384</v>
+        <v>1100</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>15</v>
@@ -22248,7 +22254,7 @@
         <v>14</v>
       </c>
       <c r="F113" s="2">
-        <v>3180</v>
+        <v>2516</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>15</v>
@@ -22280,7 +22286,7 @@
         <v>14</v>
       </c>
       <c r="F114" s="2">
-        <v>1175</v>
+        <v>1944</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>15</v>
@@ -22312,7 +22318,7 @@
         <v>14</v>
       </c>
       <c r="F115" s="2">
-        <v>2537</v>
+        <v>2455</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>15</v>
@@ -22344,7 +22350,7 @@
         <v>14</v>
       </c>
       <c r="F116" s="2">
-        <v>1810</v>
+        <v>3427</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>15</v>
@@ -22376,7 +22382,7 @@
         <v>14</v>
       </c>
       <c r="F117" s="2">
-        <v>4275</v>
+        <v>1288</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>15</v>
@@ -22408,7 +22414,7 @@
         <v>14</v>
       </c>
       <c r="F118" s="2">
-        <v>4538</v>
+        <v>4304</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>15</v>
@@ -22440,7 +22446,7 @@
         <v>14</v>
       </c>
       <c r="F119" s="2">
-        <v>2133</v>
+        <v>2270</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>15</v>
@@ -22472,7 +22478,7 @@
         <v>14</v>
       </c>
       <c r="F120" s="2">
-        <v>2883</v>
+        <v>2298</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>15</v>
@@ -22504,7 +22510,7 @@
         <v>14</v>
       </c>
       <c r="F121" s="2">
-        <v>2959</v>
+        <v>4234</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>15</v>
@@ -22536,7 +22542,7 @@
         <v>14</v>
       </c>
       <c r="F122" s="2">
-        <v>902</v>
+        <v>3098</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>15</v>
@@ -22568,7 +22574,7 @@
         <v>14</v>
       </c>
       <c r="F123" s="2">
-        <v>3496</v>
+        <v>2500</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>15</v>
@@ -22600,7 +22606,7 @@
         <v>14</v>
       </c>
       <c r="F124" s="2">
-        <v>2788</v>
+        <v>4381</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>15</v>
@@ -22632,7 +22638,7 @@
         <v>14</v>
       </c>
       <c r="F125" s="2">
-        <v>1325</v>
+        <v>1644</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>15</v>
@@ -22664,7 +22670,7 @@
         <v>14</v>
       </c>
       <c r="F126" s="2">
-        <v>3627</v>
+        <v>4100</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>15</v>
@@ -22696,7 +22702,7 @@
         <v>14</v>
       </c>
       <c r="F127" s="2">
-        <v>2597</v>
+        <v>4173</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>15</v>
@@ -22728,7 +22734,7 @@
         <v>14</v>
       </c>
       <c r="F128" s="2">
-        <v>4125</v>
+        <v>4757</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>15</v>
@@ -22760,7 +22766,7 @@
         <v>14</v>
       </c>
       <c r="F129" s="2">
-        <v>1989</v>
+        <v>972</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>15</v>
@@ -22792,7 +22798,7 @@
         <v>14</v>
       </c>
       <c r="F130" s="2">
-        <v>1767</v>
+        <v>2221</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>15</v>
@@ -22824,7 +22830,7 @@
         <v>14</v>
       </c>
       <c r="F131" s="2">
-        <v>1556</v>
+        <v>1004</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>15</v>
@@ -22856,7 +22862,7 @@
         <v>14</v>
       </c>
       <c r="F132" s="2">
-        <v>3417</v>
+        <v>1665</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>15</v>
@@ -22888,7 +22894,7 @@
         <v>14</v>
       </c>
       <c r="F133" s="2">
-        <v>3124</v>
+        <v>4340</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>15</v>
@@ -22920,7 +22926,7 @@
         <v>14</v>
       </c>
       <c r="F134" s="2">
-        <v>2486</v>
+        <v>3133</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>15</v>
@@ -22952,7 +22958,7 @@
         <v>14</v>
       </c>
       <c r="F135" s="2">
-        <v>1814</v>
+        <v>2167</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>15</v>
@@ -22984,7 +22990,7 @@
         <v>14</v>
       </c>
       <c r="F136" s="2">
-        <v>1404</v>
+        <v>1411</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>15</v>
@@ -23016,7 +23022,7 @@
         <v>14</v>
       </c>
       <c r="F137" s="2">
-        <v>3928</v>
+        <v>1786</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>15</v>
@@ -23048,7 +23054,7 @@
         <v>14</v>
       </c>
       <c r="F138" s="2">
-        <v>1578</v>
+        <v>4760</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>15</v>
@@ -23080,7 +23086,7 @@
         <v>14</v>
       </c>
       <c r="F139" s="2">
-        <v>2511</v>
+        <v>1294</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>15</v>
@@ -23112,7 +23118,7 @@
         <v>14</v>
       </c>
       <c r="F140" s="2">
-        <v>4137</v>
+        <v>1698</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>15</v>
@@ -23144,7 +23150,7 @@
         <v>14</v>
       </c>
       <c r="F141" s="2">
-        <v>4336</v>
+        <v>4089</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>15</v>
@@ -23176,7 +23182,7 @@
         <v>14</v>
       </c>
       <c r="F142" s="2">
-        <v>3949</v>
+        <v>1277</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>15</v>
@@ -23208,7 +23214,7 @@
         <v>14</v>
       </c>
       <c r="F143" s="2">
-        <v>2632</v>
+        <v>4332</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>15</v>
@@ -23240,7 +23246,7 @@
         <v>14</v>
       </c>
       <c r="F144" s="2">
-        <v>4317</v>
+        <v>2203</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>15</v>
@@ -23272,7 +23278,7 @@
         <v>14</v>
       </c>
       <c r="F145" s="2">
-        <v>1159</v>
+        <v>3650</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>15</v>
@@ -23304,7 +23310,7 @@
         <v>14</v>
       </c>
       <c r="F146" s="2">
-        <v>2252</v>
+        <v>2465</v>
       </c>
       <c r="G146" s="2" t="s">
         <v>15</v>
@@ -23336,7 +23342,7 @@
         <v>14</v>
       </c>
       <c r="F147" s="2">
-        <v>4334</v>
+        <v>3811</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>15</v>
@@ -23368,7 +23374,7 @@
         <v>14</v>
       </c>
       <c r="F148" s="2">
-        <v>852</v>
+        <v>2487</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>15</v>
@@ -23400,7 +23406,7 @@
         <v>14</v>
       </c>
       <c r="F149" s="2">
-        <v>1685</v>
+        <v>2491</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>15</v>
@@ -23432,7 +23438,7 @@
         <v>14</v>
       </c>
       <c r="F150" s="2">
-        <v>3085</v>
+        <v>4567</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>15</v>
@@ -23464,7 +23470,7 @@
         <v>14</v>
       </c>
       <c r="F151" s="2">
-        <v>3563</v>
+        <v>2706</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>15</v>
@@ -23496,7 +23502,7 @@
         <v>14</v>
       </c>
       <c r="F152" s="2">
-        <v>4313</v>
+        <v>1592</v>
       </c>
       <c r="G152" s="2" t="s">
         <v>15</v>
@@ -23528,7 +23534,7 @@
         <v>14</v>
       </c>
       <c r="F153" s="2">
-        <v>4780</v>
+        <v>4453</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>15</v>
@@ -23560,7 +23566,7 @@
         <v>14</v>
       </c>
       <c r="F154" s="2">
-        <v>3373</v>
+        <v>3932</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>15</v>
@@ -23592,7 +23598,7 @@
         <v>14</v>
       </c>
       <c r="F155" s="2">
-        <v>3441</v>
+        <v>1911</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>15</v>
@@ -23624,7 +23630,7 @@
         <v>14</v>
       </c>
       <c r="F156" s="2">
-        <v>3472</v>
+        <v>4052</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>15</v>
@@ -23656,7 +23662,7 @@
         <v>14</v>
       </c>
       <c r="F157" s="2">
-        <v>1661</v>
+        <v>3525</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>15</v>
@@ -23688,7 +23694,7 @@
         <v>14</v>
       </c>
       <c r="F158" s="2">
-        <v>4015</v>
+        <v>1457</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>15</v>
@@ -23720,7 +23726,7 @@
         <v>14</v>
       </c>
       <c r="F159" s="2">
-        <v>2608</v>
+        <v>1071</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>15</v>
@@ -23752,7 +23758,7 @@
         <v>14</v>
       </c>
       <c r="F160" s="2">
-        <v>4462</v>
+        <v>1432</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>15</v>
@@ -23784,7 +23790,7 @@
         <v>14</v>
       </c>
       <c r="F161" s="2">
-        <v>2903</v>
+        <v>1888</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>15</v>
@@ -23816,7 +23822,7 @@
         <v>14</v>
       </c>
       <c r="F162" s="2">
-        <v>3751</v>
+        <v>3621</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>15</v>
@@ -23848,7 +23854,7 @@
         <v>14</v>
       </c>
       <c r="F163" s="2">
-        <v>2032</v>
+        <v>2601</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>15</v>
@@ -23880,7 +23886,7 @@
         <v>14</v>
       </c>
       <c r="F164" s="2">
-        <v>1521</v>
+        <v>2484</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>15</v>
@@ -23912,7 +23918,7 @@
         <v>14</v>
       </c>
       <c r="F165" s="2">
-        <v>3492</v>
+        <v>2228</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>15</v>
@@ -23944,7 +23950,7 @@
         <v>14</v>
       </c>
       <c r="F166" s="2">
-        <v>4072</v>
+        <v>3725</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>15</v>
@@ -23976,7 +23982,7 @@
         <v>14</v>
       </c>
       <c r="F167" s="2">
-        <v>1521</v>
+        <v>1987</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>15</v>
@@ -24008,7 +24014,7 @@
         <v>14</v>
       </c>
       <c r="F168" s="2">
-        <v>2070</v>
+        <v>2467</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>15</v>
@@ -24040,7 +24046,7 @@
         <v>14</v>
       </c>
       <c r="F169" s="2">
-        <v>1947</v>
+        <v>804</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>15</v>
@@ -24072,7 +24078,7 @@
         <v>14</v>
       </c>
       <c r="F170" s="2">
-        <v>2430</v>
+        <v>1805</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>15</v>
@@ -24104,7 +24110,7 @@
         <v>14</v>
       </c>
       <c r="F171" s="2">
-        <v>4406</v>
+        <v>2172</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>15</v>
@@ -24136,7 +24142,7 @@
         <v>14</v>
       </c>
       <c r="F172" s="2">
-        <v>4757</v>
+        <v>1749</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>15</v>
@@ -24168,7 +24174,7 @@
         <v>14</v>
       </c>
       <c r="F173" s="2">
-        <v>4077</v>
+        <v>4230</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>15</v>
@@ -24200,7 +24206,7 @@
         <v>14</v>
       </c>
       <c r="F174" s="2">
-        <v>4523</v>
+        <v>1483</v>
       </c>
       <c r="G174" s="2" t="s">
         <v>15</v>
@@ -24232,7 +24238,7 @@
         <v>14</v>
       </c>
       <c r="F175" s="2">
-        <v>3214</v>
+        <v>4340</v>
       </c>
       <c r="G175" s="2" t="s">
         <v>15</v>
@@ -24264,7 +24270,7 @@
         <v>14</v>
       </c>
       <c r="F176" s="2">
-        <v>2009</v>
+        <v>4664</v>
       </c>
       <c r="G176" s="2" t="s">
         <v>15</v>
@@ -24296,7 +24302,7 @@
         <v>14</v>
       </c>
       <c r="F177" s="2">
-        <v>1529</v>
+        <v>4138</v>
       </c>
       <c r="G177" s="2" t="s">
         <v>15</v>
@@ -24328,7 +24334,7 @@
         <v>14</v>
       </c>
       <c r="F178" s="2">
-        <v>3449</v>
+        <v>3105</v>
       </c>
       <c r="G178" s="2" t="s">
         <v>15</v>
@@ -24360,7 +24366,7 @@
         <v>14</v>
       </c>
       <c r="F179" s="2">
-        <v>4166</v>
+        <v>1705</v>
       </c>
       <c r="G179" s="2" t="s">
         <v>15</v>
@@ -24392,7 +24398,7 @@
         <v>14</v>
       </c>
       <c r="F180" s="2">
-        <v>2803</v>
+        <v>2812</v>
       </c>
       <c r="G180" s="2" t="s">
         <v>15</v>
@@ -24424,7 +24430,7 @@
         <v>14</v>
       </c>
       <c r="F181" s="2">
-        <v>4730</v>
+        <v>4224</v>
       </c>
       <c r="G181" s="2" t="s">
         <v>15</v>
@@ -24456,7 +24462,7 @@
         <v>14</v>
       </c>
       <c r="F182" s="2">
-        <v>2136</v>
+        <v>2968</v>
       </c>
       <c r="G182" s="2" t="s">
         <v>15</v>
@@ -24488,7 +24494,7 @@
         <v>14</v>
       </c>
       <c r="F183" s="2">
-        <v>3114</v>
+        <v>1212</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>15</v>
@@ -24520,7 +24526,7 @@
         <v>14</v>
       </c>
       <c r="F184" s="2">
-        <v>4197</v>
+        <v>3781</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>15</v>
@@ -24552,7 +24558,7 @@
         <v>14</v>
       </c>
       <c r="F185" s="2">
-        <v>3632</v>
+        <v>3059</v>
       </c>
       <c r="G185" s="2" t="s">
         <v>15</v>
@@ -24584,7 +24590,7 @@
         <v>14</v>
       </c>
       <c r="F186" s="2">
-        <v>2447</v>
+        <v>2840</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>15</v>
@@ -24616,7 +24622,7 @@
         <v>14</v>
       </c>
       <c r="F187" s="2">
-        <v>4336</v>
+        <v>3528</v>
       </c>
       <c r="G187" s="2" t="s">
         <v>15</v>
@@ -24648,7 +24654,7 @@
         <v>14</v>
       </c>
       <c r="F188" s="2">
-        <v>4277</v>
+        <v>4185</v>
       </c>
       <c r="G188" s="2" t="s">
         <v>15</v>
@@ -24680,7 +24686,7 @@
         <v>14</v>
       </c>
       <c r="F189" s="2">
-        <v>3617</v>
+        <v>2891</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>15</v>
@@ -24712,7 +24718,7 @@
         <v>14</v>
       </c>
       <c r="F190" s="2">
-        <v>3226</v>
+        <v>3345</v>
       </c>
       <c r="G190" s="2" t="s">
         <v>15</v>
@@ -24744,7 +24750,7 @@
         <v>14</v>
       </c>
       <c r="F191" s="2">
-        <v>2749</v>
+        <v>2664</v>
       </c>
       <c r="G191" s="2" t="s">
         <v>15</v>
@@ -24776,7 +24782,7 @@
         <v>14</v>
       </c>
       <c r="F192" s="2">
-        <v>4620</v>
+        <v>1594</v>
       </c>
       <c r="G192" s="2" t="s">
         <v>15</v>
@@ -24808,7 +24814,7 @@
         <v>14</v>
       </c>
       <c r="F193" s="2">
-        <v>2946</v>
+        <v>4012</v>
       </c>
       <c r="G193" s="2" t="s">
         <v>15</v>
@@ -24840,7 +24846,7 @@
         <v>14</v>
       </c>
       <c r="F194" s="2">
-        <v>1051</v>
+        <v>1149</v>
       </c>
       <c r="G194" s="2" t="s">
         <v>15</v>
@@ -24872,7 +24878,7 @@
         <v>14</v>
       </c>
       <c r="F195" s="2">
-        <v>3301</v>
+        <v>1030</v>
       </c>
       <c r="G195" s="2" t="s">
         <v>15</v>
@@ -24904,7 +24910,7 @@
         <v>14</v>
       </c>
       <c r="F196" s="2">
-        <v>3206</v>
+        <v>4657</v>
       </c>
       <c r="G196" s="2" t="s">
         <v>15</v>
@@ -24936,7 +24942,7 @@
         <v>14</v>
       </c>
       <c r="F197" s="2">
-        <v>2667</v>
+        <v>941</v>
       </c>
       <c r="G197" s="2" t="s">
         <v>15</v>
@@ -24968,7 +24974,7 @@
         <v>14</v>
       </c>
       <c r="F198" s="2">
-        <v>2543</v>
+        <v>2066</v>
       </c>
       <c r="G198" s="2" t="s">
         <v>15</v>
@@ -25000,7 +25006,7 @@
         <v>14</v>
       </c>
       <c r="F199" s="2">
-        <v>869</v>
+        <v>3271</v>
       </c>
       <c r="G199" s="2" t="s">
         <v>15</v>
@@ -25032,7 +25038,7 @@
         <v>14</v>
       </c>
       <c r="F200" s="2">
-        <v>4288</v>
+        <v>1751</v>
       </c>
       <c r="G200" s="2" t="s">
         <v>15</v>
@@ -25064,7 +25070,7 @@
         <v>14</v>
       </c>
       <c r="F201" s="2">
-        <v>2687</v>
+        <v>3980</v>
       </c>
       <c r="G201" s="2" t="s">
         <v>15</v>
@@ -25096,7 +25102,7 @@
         <v>14</v>
       </c>
       <c r="F202" s="2">
-        <v>1244</v>
+        <v>3501</v>
       </c>
       <c r="G202" s="2" t="s">
         <v>15</v>
@@ -25128,7 +25134,7 @@
         <v>14</v>
       </c>
       <c r="F203" s="2">
-        <v>2584</v>
+        <v>3871</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>15</v>
@@ -25160,7 +25166,7 @@
         <v>14</v>
       </c>
       <c r="F204" s="2">
-        <v>900</v>
+        <v>3049</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>15</v>
@@ -25192,7 +25198,7 @@
         <v>14</v>
       </c>
       <c r="F205" s="2">
-        <v>1331</v>
+        <v>3356</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>15</v>
@@ -25224,7 +25230,7 @@
         <v>14</v>
       </c>
       <c r="F206" s="2">
-        <v>4597</v>
+        <v>3695</v>
       </c>
       <c r="G206" s="2" t="s">
         <v>15</v>
@@ -25256,7 +25262,7 @@
         <v>14</v>
       </c>
       <c r="F207" s="2">
-        <v>2234</v>
+        <v>3118</v>
       </c>
       <c r="G207" s="2" t="s">
         <v>15</v>
@@ -25288,7 +25294,7 @@
         <v>14</v>
       </c>
       <c r="F208" s="2">
-        <v>4750</v>
+        <v>2705</v>
       </c>
       <c r="G208" s="2" t="s">
         <v>15</v>
@@ -25320,7 +25326,7 @@
         <v>14</v>
       </c>
       <c r="F209" s="2">
-        <v>2336</v>
+        <v>2869</v>
       </c>
       <c r="G209" s="2" t="s">
         <v>15</v>
@@ -25352,7 +25358,7 @@
         <v>14</v>
       </c>
       <c r="F210" s="2">
-        <v>961</v>
+        <v>1078</v>
       </c>
       <c r="G210" s="2" t="s">
         <v>15</v>
@@ -25384,7 +25390,7 @@
         <v>14</v>
       </c>
       <c r="F211" s="2">
-        <v>4540</v>
+        <v>3951</v>
       </c>
       <c r="G211" s="2" t="s">
         <v>15</v>
@@ -25416,7 +25422,7 @@
         <v>14</v>
       </c>
       <c r="F212" s="2">
-        <v>2357</v>
+        <v>4744</v>
       </c>
       <c r="G212" s="2" t="s">
         <v>15</v>
@@ -25448,7 +25454,7 @@
         <v>14</v>
       </c>
       <c r="F213" s="2">
-        <v>4134</v>
+        <v>3389</v>
       </c>
       <c r="G213" s="2" t="s">
         <v>15</v>
@@ -25480,7 +25486,7 @@
         <v>14</v>
       </c>
       <c r="F214" s="2">
-        <v>1352</v>
+        <v>1857</v>
       </c>
       <c r="G214" s="2" t="s">
         <v>15</v>
@@ -25512,7 +25518,7 @@
         <v>14</v>
       </c>
       <c r="F215" s="2">
-        <v>2546</v>
+        <v>3893</v>
       </c>
       <c r="G215" s="2" t="s">
         <v>15</v>
@@ -25544,7 +25550,7 @@
         <v>14</v>
       </c>
       <c r="F216" s="2">
-        <v>2160</v>
+        <v>1930</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>15</v>
@@ -25576,7 +25582,7 @@
         <v>14</v>
       </c>
       <c r="F217" s="2">
-        <v>963</v>
+        <v>2885</v>
       </c>
       <c r="G217" s="2" t="s">
         <v>15</v>
@@ -25608,7 +25614,7 @@
         <v>14</v>
       </c>
       <c r="F218" s="2">
-        <v>3333</v>
+        <v>1465</v>
       </c>
       <c r="G218" s="2" t="s">
         <v>15</v>
@@ -25640,7 +25646,7 @@
         <v>14</v>
       </c>
       <c r="F219" s="2">
-        <v>4758</v>
+        <v>2733</v>
       </c>
       <c r="G219" s="2" t="s">
         <v>15</v>
@@ -25672,7 +25678,7 @@
         <v>14</v>
       </c>
       <c r="F220" s="2">
-        <v>4434</v>
+        <v>4089</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>15</v>
@@ -25704,7 +25710,7 @@
         <v>14</v>
       </c>
       <c r="F221" s="2">
-        <v>3774</v>
+        <v>1683</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>15</v>
@@ -25736,7 +25742,7 @@
         <v>14</v>
       </c>
       <c r="F222" s="2">
-        <v>2010</v>
+        <v>2316</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>15</v>
@@ -25768,7 +25774,7 @@
         <v>14</v>
       </c>
       <c r="F223" s="2">
-        <v>1330</v>
+        <v>2857</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>15</v>
@@ -25800,7 +25806,7 @@
         <v>14</v>
       </c>
       <c r="F224" s="2">
-        <v>3665</v>
+        <v>1497</v>
       </c>
       <c r="G224" s="2" t="s">
         <v>15</v>
@@ -25832,7 +25838,7 @@
         <v>14</v>
       </c>
       <c r="F225" s="2">
-        <v>4365</v>
+        <v>3863</v>
       </c>
       <c r="G225" s="2" t="s">
         <v>15</v>
@@ -25864,7 +25870,7 @@
         <v>14</v>
       </c>
       <c r="F226" s="2">
-        <v>1460</v>
+        <v>4571</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>15</v>
@@ -25896,7 +25902,7 @@
         <v>14</v>
       </c>
       <c r="F227" s="2">
-        <v>2277</v>
+        <v>2464</v>
       </c>
       <c r="G227" s="2" t="s">
         <v>15</v>
@@ -25928,7 +25934,7 @@
         <v>14</v>
       </c>
       <c r="F228" s="2">
-        <v>1021</v>
+        <v>4429</v>
       </c>
       <c r="G228" s="2" t="s">
         <v>15</v>
@@ -25960,7 +25966,7 @@
         <v>14</v>
       </c>
       <c r="F229" s="2">
-        <v>2507</v>
+        <v>3963</v>
       </c>
       <c r="G229" s="2" t="s">
         <v>15</v>
@@ -25992,7 +25998,7 @@
         <v>14</v>
       </c>
       <c r="F230" s="2">
-        <v>2323</v>
+        <v>4374</v>
       </c>
       <c r="G230" s="2" t="s">
         <v>15</v>
@@ -26024,7 +26030,7 @@
         <v>14</v>
       </c>
       <c r="F231" s="2">
-        <v>1547</v>
+        <v>3374</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>15</v>
@@ -26056,7 +26062,7 @@
         <v>14</v>
       </c>
       <c r="F232" s="2">
-        <v>4154</v>
+        <v>4320</v>
       </c>
       <c r="G232" s="2" t="s">
         <v>15</v>
@@ -26088,7 +26094,7 @@
         <v>14</v>
       </c>
       <c r="F233" s="2">
-        <v>2503</v>
+        <v>4411</v>
       </c>
       <c r="G233" s="2" t="s">
         <v>15</v>
@@ -26120,7 +26126,7 @@
         <v>14</v>
       </c>
       <c r="F234" s="2">
-        <v>3448</v>
+        <v>3823</v>
       </c>
       <c r="G234" s="2" t="s">
         <v>15</v>
@@ -26152,7 +26158,7 @@
         <v>14</v>
       </c>
       <c r="F235" s="2">
-        <v>1404</v>
+        <v>2595</v>
       </c>
       <c r="G235" s="2" t="s">
         <v>15</v>
@@ -26184,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="F236" s="2">
-        <v>808</v>
+        <v>1177</v>
       </c>
       <c r="G236" s="2" t="s">
         <v>15</v>
@@ -26216,7 +26222,7 @@
         <v>14</v>
       </c>
       <c r="F237" s="2">
-        <v>2729</v>
+        <v>1799</v>
       </c>
       <c r="G237" s="2" t="s">
         <v>15</v>
@@ -26248,7 +26254,7 @@
         <v>14</v>
       </c>
       <c r="F238" s="2">
-        <v>1060</v>
+        <v>3067</v>
       </c>
       <c r="G238" s="2" t="s">
         <v>15</v>
@@ -26280,7 +26286,7 @@
         <v>14</v>
       </c>
       <c r="F239" s="2">
-        <v>2753</v>
+        <v>2632</v>
       </c>
       <c r="G239" s="2" t="s">
         <v>15</v>
@@ -26312,7 +26318,7 @@
         <v>14</v>
       </c>
       <c r="F240" s="2">
-        <v>3516</v>
+        <v>3722</v>
       </c>
       <c r="G240" s="2" t="s">
         <v>15</v>
@@ -26344,7 +26350,7 @@
         <v>14</v>
       </c>
       <c r="F241" s="2">
-        <v>4778</v>
+        <v>2451</v>
       </c>
       <c r="G241" s="2" t="s">
         <v>15</v>
@@ -26376,7 +26382,7 @@
         <v>14</v>
       </c>
       <c r="F242" s="2">
-        <v>3434</v>
+        <v>1074</v>
       </c>
       <c r="G242" s="2" t="s">
         <v>15</v>
@@ -26408,7 +26414,7 @@
         <v>14</v>
       </c>
       <c r="F243" s="2">
-        <v>3187</v>
+        <v>980</v>
       </c>
       <c r="G243" s="2" t="s">
         <v>15</v>
@@ -26440,7 +26446,7 @@
         <v>14</v>
       </c>
       <c r="F244" s="2">
-        <v>3387</v>
+        <v>1329</v>
       </c>
       <c r="G244" s="2" t="s">
         <v>15</v>
@@ -26472,7 +26478,7 @@
         <v>14</v>
       </c>
       <c r="F245" s="2">
-        <v>3258</v>
+        <v>4189</v>
       </c>
       <c r="G245" s="2" t="s">
         <v>15</v>
@@ -26504,7 +26510,7 @@
         <v>14</v>
       </c>
       <c r="F246" s="2">
-        <v>1382</v>
+        <v>3594</v>
       </c>
       <c r="G246" s="2" t="s">
         <v>15</v>
@@ -26536,7 +26542,7 @@
         <v>14</v>
       </c>
       <c r="F247" s="2">
-        <v>4558</v>
+        <v>2654</v>
       </c>
       <c r="G247" s="2" t="s">
         <v>15</v>
@@ -26568,7 +26574,7 @@
         <v>14</v>
       </c>
       <c r="F248" s="2">
-        <v>3086</v>
+        <v>4305</v>
       </c>
       <c r="G248" s="2" t="s">
         <v>15</v>
@@ -26600,7 +26606,7 @@
         <v>14</v>
       </c>
       <c r="F249" s="2">
-        <v>2447</v>
+        <v>4786</v>
       </c>
       <c r="G249" s="2" t="s">
         <v>15</v>
@@ -26632,7 +26638,7 @@
         <v>14</v>
       </c>
       <c r="F250" s="2">
-        <v>2425</v>
+        <v>2056</v>
       </c>
       <c r="G250" s="2" t="s">
         <v>15</v>
@@ -26664,7 +26670,7 @@
         <v>14</v>
       </c>
       <c r="F251" s="2">
-        <v>1027</v>
+        <v>803</v>
       </c>
       <c r="G251" s="2" t="s">
         <v>15</v>
@@ -26696,7 +26702,7 @@
         <v>14</v>
       </c>
       <c r="F252" s="2">
-        <v>4737</v>
+        <v>4393</v>
       </c>
       <c r="G252" s="2" t="s">
         <v>15</v>
@@ -26728,7 +26734,7 @@
         <v>14</v>
       </c>
       <c r="F253" s="2">
-        <v>3855</v>
+        <v>897</v>
       </c>
       <c r="G253" s="2" t="s">
         <v>15</v>
@@ -26760,7 +26766,7 @@
         <v>14</v>
       </c>
       <c r="F254" s="2">
-        <v>3756</v>
+        <v>2696</v>
       </c>
       <c r="G254" s="2" t="s">
         <v>15</v>
@@ -26792,7 +26798,7 @@
         <v>14</v>
       </c>
       <c r="F255" s="2">
-        <v>810</v>
+        <v>4120</v>
       </c>
       <c r="G255" s="2" t="s">
         <v>15</v>
@@ -26824,7 +26830,7 @@
         <v>14</v>
       </c>
       <c r="F256" s="2">
-        <v>1571</v>
+        <v>3926</v>
       </c>
       <c r="G256" s="2" t="s">
         <v>15</v>
@@ -26856,7 +26862,7 @@
         <v>14</v>
       </c>
       <c r="F257" s="2">
-        <v>1393</v>
+        <v>1085</v>
       </c>
       <c r="G257" s="2" t="s">
         <v>15</v>
@@ -26888,7 +26894,7 @@
         <v>14</v>
       </c>
       <c r="F258" s="2">
-        <v>1065</v>
+        <v>3107</v>
       </c>
       <c r="G258" s="2" t="s">
         <v>15</v>
@@ -26920,7 +26926,7 @@
         <v>14</v>
       </c>
       <c r="F259" s="2">
-        <v>4754</v>
+        <v>1392</v>
       </c>
       <c r="G259" s="2" t="s">
         <v>15</v>
@@ -26952,7 +26958,7 @@
         <v>14</v>
       </c>
       <c r="F260" s="2">
-        <v>2996</v>
+        <v>4134</v>
       </c>
       <c r="G260" s="2" t="s">
         <v>15</v>
@@ -26984,7 +26990,7 @@
         <v>14</v>
       </c>
       <c r="F261" s="2">
-        <v>1046</v>
+        <v>3066</v>
       </c>
       <c r="G261" s="2" t="s">
         <v>15</v>
@@ -27016,7 +27022,7 @@
         <v>14</v>
       </c>
       <c r="F262" s="2">
-        <v>4727</v>
+        <v>1441</v>
       </c>
       <c r="G262" s="2" t="s">
         <v>15</v>
@@ -27048,7 +27054,7 @@
         <v>14</v>
       </c>
       <c r="F263" s="2">
-        <v>4471</v>
+        <v>4297</v>
       </c>
       <c r="G263" s="2" t="s">
         <v>15</v>
@@ -27080,7 +27086,7 @@
         <v>14</v>
       </c>
       <c r="F264" s="2">
-        <v>2581</v>
+        <v>3715</v>
       </c>
       <c r="G264" s="2" t="s">
         <v>15</v>
@@ -27112,7 +27118,7 @@
         <v>14</v>
       </c>
       <c r="F265" s="2">
-        <v>864</v>
+        <v>4532</v>
       </c>
       <c r="G265" s="2" t="s">
         <v>15</v>
@@ -27144,7 +27150,7 @@
         <v>14</v>
       </c>
       <c r="F266" s="2">
-        <v>1489</v>
+        <v>3604</v>
       </c>
       <c r="G266" s="2" t="s">
         <v>15</v>
@@ -27176,7 +27182,7 @@
         <v>14</v>
       </c>
       <c r="F267" s="2">
-        <v>4662</v>
+        <v>3415</v>
       </c>
       <c r="G267" s="2" t="s">
         <v>15</v>
@@ -27208,7 +27214,7 @@
         <v>14</v>
       </c>
       <c r="F268" s="2">
-        <v>3946</v>
+        <v>3771</v>
       </c>
       <c r="G268" s="2" t="s">
         <v>15</v>
@@ -27240,7 +27246,7 @@
         <v>14</v>
       </c>
       <c r="F269" s="2">
-        <v>1040</v>
+        <v>4492</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>15</v>
@@ -27272,7 +27278,7 @@
         <v>14</v>
       </c>
       <c r="F270" s="2">
-        <v>2190</v>
+        <v>4406</v>
       </c>
       <c r="G270" s="2" t="s">
         <v>15</v>
@@ -27304,7 +27310,7 @@
         <v>14</v>
       </c>
       <c r="F271" s="2">
-        <v>1139</v>
+        <v>4183</v>
       </c>
       <c r="G271" s="2" t="s">
         <v>15</v>
@@ -27336,7 +27342,7 @@
         <v>14</v>
       </c>
       <c r="F272" s="2">
-        <v>1466</v>
+        <v>1460</v>
       </c>
       <c r="G272" s="2" t="s">
         <v>15</v>
@@ -27368,7 +27374,7 @@
         <v>14</v>
       </c>
       <c r="F273" s="2">
-        <v>1500</v>
+        <v>2595</v>
       </c>
       <c r="G273" s="2" t="s">
         <v>15</v>
@@ -27400,7 +27406,7 @@
         <v>14</v>
       </c>
       <c r="F274" s="2">
-        <v>2191</v>
+        <v>2304</v>
       </c>
       <c r="G274" s="2" t="s">
         <v>15</v>
@@ -27432,7 +27438,7 @@
         <v>14</v>
       </c>
       <c r="F275" s="2">
-        <v>4675</v>
+        <v>2085</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>15</v>
@@ -27464,7 +27470,7 @@
         <v>14</v>
       </c>
       <c r="F276" s="2">
-        <v>1760</v>
+        <v>2202</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>15</v>
@@ -27496,7 +27502,7 @@
         <v>14</v>
       </c>
       <c r="F277" s="2">
-        <v>3307</v>
+        <v>1377</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>15</v>
@@ -27528,7 +27534,7 @@
         <v>14</v>
       </c>
       <c r="F278" s="2">
-        <v>3276</v>
+        <v>1561</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>15</v>
@@ -27560,7 +27566,7 @@
         <v>14</v>
       </c>
       <c r="F279" s="2">
-        <v>1646</v>
+        <v>4386</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>15</v>
@@ -27592,7 +27598,7 @@
         <v>14</v>
       </c>
       <c r="F280" s="2">
-        <v>2557</v>
+        <v>1896</v>
       </c>
       <c r="G280" s="2" t="s">
         <v>15</v>
@@ -27624,7 +27630,7 @@
         <v>14</v>
       </c>
       <c r="F281" s="2">
-        <v>848</v>
+        <v>833</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>15</v>
@@ -27656,7 +27662,7 @@
         <v>14</v>
       </c>
       <c r="F282" s="2">
-        <v>1593</v>
+        <v>2828</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>15</v>
@@ -27688,7 +27694,7 @@
         <v>14</v>
       </c>
       <c r="F283" s="2">
-        <v>3323</v>
+        <v>1352</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>15</v>
@@ -27720,7 +27726,7 @@
         <v>14</v>
       </c>
       <c r="F284" s="2">
-        <v>4342</v>
+        <v>2569</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>15</v>
@@ -27752,7 +27758,7 @@
         <v>14</v>
       </c>
       <c r="F285" s="2">
-        <v>1283</v>
+        <v>4117</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>15</v>
@@ -27784,7 +27790,7 @@
         <v>14</v>
       </c>
       <c r="F286" s="2">
-        <v>4303</v>
+        <v>3729</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>15</v>
@@ -27816,7 +27822,7 @@
         <v>14</v>
       </c>
       <c r="F287" s="2">
-        <v>2164</v>
+        <v>4663</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>15</v>
@@ -27848,7 +27854,7 @@
         <v>14</v>
       </c>
       <c r="F288" s="2">
-        <v>2351</v>
+        <v>4319</v>
       </c>
       <c r="G288" s="2" t="s">
         <v>15</v>
@@ -27880,7 +27886,7 @@
         <v>14</v>
       </c>
       <c r="F289" s="2">
-        <v>4096</v>
+        <v>1641</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>15</v>
@@ -27912,7 +27918,7 @@
         <v>14</v>
       </c>
       <c r="F290" s="2">
-        <v>1969</v>
+        <v>2917</v>
       </c>
       <c r="G290" s="2" t="s">
         <v>15</v>
@@ -27944,7 +27950,7 @@
         <v>14</v>
       </c>
       <c r="F291" s="2">
-        <v>1407</v>
+        <v>1005</v>
       </c>
       <c r="G291" s="2" t="s">
         <v>15</v>
@@ -27976,7 +27982,7 @@
         <v>14</v>
       </c>
       <c r="F292" s="2">
-        <v>3774</v>
+        <v>4171</v>
       </c>
       <c r="G292" s="2" t="s">
         <v>15</v>
@@ -28008,7 +28014,7 @@
         <v>14</v>
       </c>
       <c r="F293" s="2">
-        <v>1455</v>
+        <v>1361</v>
       </c>
       <c r="G293" s="2" t="s">
         <v>15</v>
@@ -28040,7 +28046,7 @@
         <v>14</v>
       </c>
       <c r="F294" s="2">
-        <v>4397</v>
+        <v>1049</v>
       </c>
       <c r="G294" s="2" t="s">
         <v>15</v>
@@ -28072,7 +28078,7 @@
         <v>14</v>
       </c>
       <c r="F295" s="2">
-        <v>3980</v>
+        <v>2936</v>
       </c>
       <c r="G295" s="2" t="s">
         <v>15</v>
@@ -28104,7 +28110,7 @@
         <v>14</v>
       </c>
       <c r="F296" s="2">
-        <v>3857</v>
+        <v>3238</v>
       </c>
       <c r="G296" s="2" t="s">
         <v>15</v>
@@ -28136,7 +28142,7 @@
         <v>14</v>
       </c>
       <c r="F297" s="2">
-        <v>1141</v>
+        <v>3448</v>
       </c>
       <c r="G297" s="2" t="s">
         <v>15</v>
@@ -28168,7 +28174,7 @@
         <v>14</v>
       </c>
       <c r="F298" s="2">
-        <v>3478</v>
+        <v>3837</v>
       </c>
       <c r="G298" s="2" t="s">
         <v>15</v>
@@ -28200,7 +28206,7 @@
         <v>14</v>
       </c>
       <c r="F299" s="2">
-        <v>944</v>
+        <v>2424</v>
       </c>
       <c r="G299" s="2" t="s">
         <v>15</v>
@@ -28232,7 +28238,7 @@
         <v>14</v>
       </c>
       <c r="F300" s="2">
-        <v>3936</v>
+        <v>1443</v>
       </c>
       <c r="G300" s="2" t="s">
         <v>15</v>
@@ -28264,7 +28270,7 @@
         <v>14</v>
       </c>
       <c r="F301" s="2">
-        <v>1904</v>
+        <v>2969</v>
       </c>
       <c r="G301" s="2" t="s">
         <v>15</v>
@@ -28296,7 +28302,7 @@
         <v>14</v>
       </c>
       <c r="F302" s="2">
-        <v>3637</v>
+        <v>2522</v>
       </c>
       <c r="G302" s="2" t="s">
         <v>15</v>
@@ -28328,7 +28334,7 @@
         <v>14</v>
       </c>
       <c r="F303" s="2">
-        <v>3904</v>
+        <v>2361</v>
       </c>
       <c r="G303" s="2" t="s">
         <v>15</v>
@@ -28360,7 +28366,7 @@
         <v>14</v>
       </c>
       <c r="F304" s="2">
-        <v>1539</v>
+        <v>4261</v>
       </c>
       <c r="G304" s="2" t="s">
         <v>15</v>
@@ -28392,7 +28398,7 @@
         <v>14</v>
       </c>
       <c r="F305" s="2">
-        <v>2509</v>
+        <v>1752</v>
       </c>
       <c r="G305" s="2" t="s">
         <v>15</v>
@@ -28424,7 +28430,7 @@
         <v>14</v>
       </c>
       <c r="F306" s="2">
-        <v>2019</v>
+        <v>3392</v>
       </c>
       <c r="G306" s="2" t="s">
         <v>15</v>
@@ -28456,7 +28462,7 @@
         <v>14</v>
       </c>
       <c r="F307" s="2">
-        <v>1266</v>
+        <v>1606</v>
       </c>
       <c r="G307" s="2" t="s">
         <v>15</v>
@@ -28488,7 +28494,7 @@
         <v>14</v>
       </c>
       <c r="F308" s="2">
-        <v>2105</v>
+        <v>2455</v>
       </c>
       <c r="G308" s="2" t="s">
         <v>15</v>
@@ -28520,7 +28526,7 @@
         <v>14</v>
       </c>
       <c r="F309" s="2">
-        <v>3067</v>
+        <v>3909</v>
       </c>
       <c r="G309" s="2" t="s">
         <v>15</v>
@@ -28552,7 +28558,7 @@
         <v>14</v>
       </c>
       <c r="F310" s="2">
-        <v>1085</v>
+        <v>945</v>
       </c>
       <c r="G310" s="2" t="s">
         <v>15</v>
@@ -28584,7 +28590,7 @@
         <v>14</v>
       </c>
       <c r="F311" s="2">
-        <v>4028</v>
+        <v>1186</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>15</v>
@@ -28616,7 +28622,7 @@
         <v>14</v>
       </c>
       <c r="F312" s="2">
-        <v>3577</v>
+        <v>2273</v>
       </c>
       <c r="G312" s="2" t="s">
         <v>15</v>
@@ -28648,7 +28654,7 @@
         <v>14</v>
       </c>
       <c r="F313" s="2">
-        <v>2187</v>
+        <v>2767</v>
       </c>
       <c r="G313" s="2" t="s">
         <v>15</v>
@@ -28680,7 +28686,7 @@
         <v>14</v>
       </c>
       <c r="F314" s="2">
-        <v>4572</v>
+        <v>4311</v>
       </c>
       <c r="G314" s="2" t="s">
         <v>15</v>
@@ -28712,7 +28718,7 @@
         <v>14</v>
       </c>
       <c r="F315" s="2">
-        <v>3242</v>
+        <v>1878</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>15</v>
@@ -28744,7 +28750,7 @@
         <v>14</v>
       </c>
       <c r="F316" s="2">
-        <v>3690</v>
+        <v>3873</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>15</v>
@@ -28776,7 +28782,7 @@
         <v>14</v>
       </c>
       <c r="F317" s="2">
-        <v>2733</v>
+        <v>3640</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>15</v>
@@ -28808,7 +28814,7 @@
         <v>14</v>
       </c>
       <c r="F318" s="2">
-        <v>1958</v>
+        <v>3014</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>15</v>
@@ -28840,7 +28846,7 @@
         <v>14</v>
       </c>
       <c r="F319" s="2">
-        <v>4379</v>
+        <v>3150</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>15</v>
@@ -28872,7 +28878,7 @@
         <v>14</v>
       </c>
       <c r="F320" s="2">
-        <v>4308</v>
+        <v>949</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>15</v>
@@ -28904,7 +28910,7 @@
         <v>14</v>
       </c>
       <c r="F321" s="2">
-        <v>1194</v>
+        <v>4132</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>15</v>
@@ -28936,7 +28942,7 @@
         <v>14</v>
       </c>
       <c r="F322" s="2">
-        <v>4601</v>
+        <v>2320</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>15</v>
@@ -28968,7 +28974,7 @@
         <v>14</v>
       </c>
       <c r="F323" s="2">
-        <v>1397</v>
+        <v>4708</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>15</v>
@@ -29000,7 +29006,7 @@
         <v>14</v>
       </c>
       <c r="F324" s="2">
-        <v>964</v>
+        <v>3171</v>
       </c>
       <c r="G324" s="2" t="s">
         <v>15</v>
@@ -29032,7 +29038,7 @@
         <v>14</v>
       </c>
       <c r="F325" s="2">
-        <v>4190</v>
+        <v>3095</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>15</v>
@@ -29064,7 +29070,7 @@
         <v>14</v>
       </c>
       <c r="F326" s="2">
-        <v>3048</v>
+        <v>4466</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>15</v>
@@ -29096,7 +29102,7 @@
         <v>14</v>
       </c>
       <c r="F327" s="2">
-        <v>4088</v>
+        <v>2537</v>
       </c>
       <c r="G327" s="2" t="s">
         <v>15</v>
@@ -29128,7 +29134,7 @@
         <v>14</v>
       </c>
       <c r="F328" s="2">
-        <v>4479</v>
+        <v>2359</v>
       </c>
       <c r="G328" s="2" t="s">
         <v>15</v>
@@ -29160,7 +29166,7 @@
         <v>14</v>
       </c>
       <c r="F329" s="2">
-        <v>1165</v>
+        <v>1856</v>
       </c>
       <c r="G329" s="2" t="s">
         <v>15</v>
@@ -29192,7 +29198,7 @@
         <v>14</v>
       </c>
       <c r="F330" s="2">
-        <v>3023</v>
+        <v>4724</v>
       </c>
       <c r="G330" s="2" t="s">
         <v>15</v>
@@ -29224,7 +29230,7 @@
         <v>14</v>
       </c>
       <c r="F331" s="2">
-        <v>2526</v>
+        <v>3579</v>
       </c>
       <c r="G331" s="2" t="s">
         <v>15</v>
@@ -29256,7 +29262,7 @@
         <v>14</v>
       </c>
       <c r="F332" s="2">
-        <v>3121</v>
+        <v>1179</v>
       </c>
       <c r="G332" s="2" t="s">
         <v>15</v>
@@ -29288,7 +29294,7 @@
         <v>14</v>
       </c>
       <c r="F333" s="2">
-        <v>4367</v>
+        <v>3875</v>
       </c>
       <c r="G333" s="2" t="s">
         <v>15</v>
@@ -29320,7 +29326,7 @@
         <v>14</v>
       </c>
       <c r="F334" s="2">
-        <v>2689</v>
+        <v>2280</v>
       </c>
       <c r="G334" s="2" t="s">
         <v>15</v>
@@ -29352,7 +29358,7 @@
         <v>14</v>
       </c>
       <c r="F335" s="2">
-        <v>3178</v>
+        <v>1783</v>
       </c>
       <c r="G335" s="2" t="s">
         <v>15</v>
@@ -29384,7 +29390,7 @@
         <v>14</v>
       </c>
       <c r="F336" s="2">
-        <v>1294</v>
+        <v>3849</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>15</v>
@@ -29416,7 +29422,7 @@
         <v>14</v>
       </c>
       <c r="F337" s="2">
-        <v>2394</v>
+        <v>4175</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>15</v>
@@ -29448,7 +29454,7 @@
         <v>14</v>
       </c>
       <c r="F338" s="2">
-        <v>3449</v>
+        <v>1102</v>
       </c>
       <c r="G338" s="2" t="s">
         <v>15</v>
@@ -29480,7 +29486,7 @@
         <v>14</v>
       </c>
       <c r="F339" s="2">
-        <v>3341</v>
+        <v>4401</v>
       </c>
       <c r="G339" s="2" t="s">
         <v>15</v>
@@ -29512,7 +29518,7 @@
         <v>14</v>
       </c>
       <c r="F340" s="2">
-        <v>3243</v>
+        <v>1516</v>
       </c>
       <c r="G340" s="2" t="s">
         <v>15</v>
@@ -29544,7 +29550,7 @@
         <v>14</v>
       </c>
       <c r="F341" s="2">
-        <v>3812</v>
+        <v>1874</v>
       </c>
       <c r="G341" s="2" t="s">
         <v>15</v>
@@ -29576,7 +29582,7 @@
         <v>14</v>
       </c>
       <c r="F342" s="2">
-        <v>3297</v>
+        <v>4381</v>
       </c>
       <c r="G342" s="2" t="s">
         <v>15</v>
@@ -29608,7 +29614,7 @@
         <v>14</v>
       </c>
       <c r="F343" s="2">
-        <v>2021</v>
+        <v>4729</v>
       </c>
       <c r="G343" s="2" t="s">
         <v>15</v>
@@ -29640,7 +29646,7 @@
         <v>14</v>
       </c>
       <c r="F344" s="2">
-        <v>2728</v>
+        <v>3553</v>
       </c>
       <c r="G344" s="2" t="s">
         <v>15</v>
@@ -29672,7 +29678,7 @@
         <v>14</v>
       </c>
       <c r="F345" s="2">
-        <v>4033</v>
+        <v>1112</v>
       </c>
       <c r="G345" s="2" t="s">
         <v>15</v>
@@ -29704,7 +29710,7 @@
         <v>14</v>
       </c>
       <c r="F346" s="2">
-        <v>1728</v>
+        <v>3855</v>
       </c>
       <c r="G346" s="2" t="s">
         <v>15</v>
@@ -29736,7 +29742,7 @@
         <v>14</v>
       </c>
       <c r="F347" s="2">
-        <v>4114</v>
+        <v>2902</v>
       </c>
       <c r="G347" s="2" t="s">
         <v>15</v>
@@ -29768,7 +29774,7 @@
         <v>14</v>
       </c>
       <c r="F348" s="2">
-        <v>914</v>
+        <v>1095</v>
       </c>
       <c r="G348" s="2" t="s">
         <v>15</v>
@@ -29800,7 +29806,7 @@
         <v>14</v>
       </c>
       <c r="F349" s="2">
-        <v>1251</v>
+        <v>3587</v>
       </c>
       <c r="G349" s="2" t="s">
         <v>15</v>
@@ -29832,7 +29838,7 @@
         <v>14</v>
       </c>
       <c r="F350" s="2">
-        <v>1116</v>
+        <v>2294</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>15</v>
@@ -29864,7 +29870,7 @@
         <v>14</v>
       </c>
       <c r="F351" s="2">
-        <v>1883</v>
+        <v>2353</v>
       </c>
       <c r="G351" s="2" t="s">
         <v>15</v>
@@ -29896,7 +29902,7 @@
         <v>14</v>
       </c>
       <c r="F352" s="2">
-        <v>4188</v>
+        <v>3640</v>
       </c>
       <c r="G352" s="2" t="s">
         <v>15</v>
@@ -29928,7 +29934,7 @@
         <v>14</v>
       </c>
       <c r="F353" s="2">
-        <v>3390</v>
+        <v>3672</v>
       </c>
       <c r="G353" s="2" t="s">
         <v>15</v>
@@ -29960,7 +29966,7 @@
         <v>14</v>
       </c>
       <c r="F354" s="2">
-        <v>1935</v>
+        <v>2866</v>
       </c>
       <c r="G354" s="2" t="s">
         <v>15</v>
@@ -29992,7 +29998,7 @@
         <v>14</v>
       </c>
       <c r="F355" s="2">
-        <v>2901</v>
+        <v>4777</v>
       </c>
       <c r="G355" s="2" t="s">
         <v>15</v>
@@ -30024,7 +30030,7 @@
         <v>14</v>
       </c>
       <c r="F356" s="2">
-        <v>3050</v>
+        <v>3993</v>
       </c>
       <c r="G356" s="2" t="s">
         <v>15</v>
@@ -30056,7 +30062,7 @@
         <v>14</v>
       </c>
       <c r="F357" s="2">
-        <v>4551</v>
+        <v>932</v>
       </c>
       <c r="G357" s="2" t="s">
         <v>15</v>
@@ -30088,7 +30094,7 @@
         <v>14</v>
       </c>
       <c r="F358" s="2">
-        <v>3905</v>
+        <v>985</v>
       </c>
       <c r="G358" s="2" t="s">
         <v>15</v>
@@ -30120,7 +30126,7 @@
         <v>14</v>
       </c>
       <c r="F359" s="2">
-        <v>1682</v>
+        <v>3836</v>
       </c>
       <c r="G359" s="2" t="s">
         <v>15</v>
@@ -30152,7 +30158,7 @@
         <v>14</v>
       </c>
       <c r="F360" s="2">
-        <v>4125</v>
+        <v>3085</v>
       </c>
       <c r="G360" s="2" t="s">
         <v>15</v>
@@ -30184,7 +30190,7 @@
         <v>14</v>
       </c>
       <c r="F361" s="2">
-        <v>4470</v>
+        <v>2465</v>
       </c>
       <c r="G361" s="2" t="s">
         <v>15</v>
@@ -30216,7 +30222,7 @@
         <v>14</v>
       </c>
       <c r="F362" s="2">
-        <v>1010</v>
+        <v>2096</v>
       </c>
       <c r="G362" s="2" t="s">
         <v>15</v>
@@ -30248,7 +30254,7 @@
         <v>14</v>
       </c>
       <c r="F363" s="2">
-        <v>4183</v>
+        <v>1168</v>
       </c>
       <c r="G363" s="2" t="s">
         <v>15</v>
@@ -30280,7 +30286,7 @@
         <v>14</v>
       </c>
       <c r="F364" s="2">
-        <v>4573</v>
+        <v>4558</v>
       </c>
       <c r="G364" s="2" t="s">
         <v>15</v>
@@ -30312,7 +30318,7 @@
         <v>14</v>
       </c>
       <c r="F365" s="2">
-        <v>2404</v>
+        <v>1487</v>
       </c>
       <c r="G365" s="2" t="s">
         <v>15</v>
@@ -30344,7 +30350,7 @@
         <v>14</v>
       </c>
       <c r="F366" s="2">
-        <v>1139</v>
+        <v>1011</v>
       </c>
       <c r="G366" s="2" t="s">
         <v>15</v>
@@ -30376,7 +30382,7 @@
         <v>14</v>
       </c>
       <c r="F367" s="2">
-        <v>4698</v>
+        <v>3882</v>
       </c>
       <c r="G367" s="2" t="s">
         <v>15</v>
@@ -30408,7 +30414,7 @@
         <v>14</v>
       </c>
       <c r="F368" s="2">
-        <v>4734</v>
+        <v>3010</v>
       </c>
       <c r="G368" s="2" t="s">
         <v>15</v>
@@ -30440,7 +30446,7 @@
         <v>14</v>
       </c>
       <c r="F369" s="2">
-        <v>2963</v>
+        <v>1328</v>
       </c>
       <c r="G369" s="2" t="s">
         <v>15</v>
@@ -30472,7 +30478,7 @@
         <v>14</v>
       </c>
       <c r="F370" s="2">
-        <v>2976</v>
+        <v>2958</v>
       </c>
       <c r="G370" s="2" t="s">
         <v>15</v>
@@ -30504,7 +30510,7 @@
         <v>14</v>
       </c>
       <c r="F371" s="2">
-        <v>3047</v>
+        <v>901</v>
       </c>
       <c r="G371" s="2" t="s">
         <v>15</v>
@@ -30536,7 +30542,7 @@
         <v>14</v>
       </c>
       <c r="F372" s="2">
-        <v>2520</v>
+        <v>3539</v>
       </c>
       <c r="G372" s="2" t="s">
         <v>15</v>
@@ -30568,7 +30574,7 @@
         <v>14</v>
       </c>
       <c r="F373" s="2">
-        <v>4378</v>
+        <v>2758</v>
       </c>
       <c r="G373" s="2" t="s">
         <v>15</v>
@@ -30600,7 +30606,7 @@
         <v>14</v>
       </c>
       <c r="F374" s="2">
-        <v>1879</v>
+        <v>3005</v>
       </c>
       <c r="G374" s="2" t="s">
         <v>15</v>
@@ -30632,7 +30638,7 @@
         <v>14</v>
       </c>
       <c r="F375" s="2">
-        <v>1599</v>
+        <v>4755</v>
       </c>
       <c r="G375" s="2" t="s">
         <v>15</v>
@@ -30664,7 +30670,7 @@
         <v>14</v>
       </c>
       <c r="F376" s="2">
-        <v>2097</v>
+        <v>2112</v>
       </c>
       <c r="G376" s="2" t="s">
         <v>15</v>
@@ -30696,7 +30702,7 @@
         <v>14</v>
       </c>
       <c r="F377" s="2">
-        <v>4707</v>
+        <v>2645</v>
       </c>
       <c r="G377" s="2" t="s">
         <v>15</v>
@@ -30728,7 +30734,7 @@
         <v>14</v>
       </c>
       <c r="F378" s="2">
-        <v>2809</v>
+        <v>996</v>
       </c>
       <c r="G378" s="2" t="s">
         <v>15</v>
@@ -30760,7 +30766,7 @@
         <v>14</v>
       </c>
       <c r="F379" s="2">
-        <v>2215</v>
+        <v>1786</v>
       </c>
       <c r="G379" s="2" t="s">
         <v>15</v>
@@ -30792,7 +30798,7 @@
         <v>14</v>
       </c>
       <c r="F380" s="2">
-        <v>1908</v>
+        <v>2699</v>
       </c>
       <c r="G380" s="2" t="s">
         <v>15</v>
@@ -30824,7 +30830,7 @@
         <v>14</v>
       </c>
       <c r="F381" s="2">
-        <v>1626</v>
+        <v>1302</v>
       </c>
       <c r="G381" s="2" t="s">
         <v>15</v>
@@ -30856,7 +30862,7 @@
         <v>14</v>
       </c>
       <c r="F382" s="2">
-        <v>2584</v>
+        <v>1931</v>
       </c>
       <c r="G382" s="2" t="s">
         <v>15</v>
@@ -30888,7 +30894,7 @@
         <v>14</v>
       </c>
       <c r="F383" s="2">
-        <v>3926</v>
+        <v>4263</v>
       </c>
       <c r="G383" s="2" t="s">
         <v>15</v>
@@ -30920,7 +30926,7 @@
         <v>14</v>
       </c>
       <c r="F384" s="2">
-        <v>2472</v>
+        <v>3284</v>
       </c>
       <c r="G384" s="2" t="s">
         <v>15</v>
@@ -30952,7 +30958,7 @@
         <v>14</v>
       </c>
       <c r="F385" s="2">
-        <v>1496</v>
+        <v>4677</v>
       </c>
       <c r="G385" s="2" t="s">
         <v>15</v>
@@ -30984,7 +30990,7 @@
         <v>14</v>
       </c>
       <c r="F386" s="2">
-        <v>2150</v>
+        <v>1576</v>
       </c>
       <c r="G386" s="2" t="s">
         <v>15</v>
@@ -31016,7 +31022,7 @@
         <v>14</v>
       </c>
       <c r="F387" s="2">
-        <v>4178</v>
+        <v>1599</v>
       </c>
       <c r="G387" s="2" t="s">
         <v>15</v>
@@ -31048,7 +31054,7 @@
         <v>14</v>
       </c>
       <c r="F388" s="2">
-        <v>3497</v>
+        <v>3992</v>
       </c>
       <c r="G388" s="2" t="s">
         <v>15</v>
@@ -31080,7 +31086,7 @@
         <v>14</v>
       </c>
       <c r="F389" s="2">
-        <v>3448</v>
+        <v>1328</v>
       </c>
       <c r="G389" s="2" t="s">
         <v>15</v>
@@ -31112,7 +31118,7 @@
         <v>14</v>
       </c>
       <c r="F390" s="2">
-        <v>2430</v>
+        <v>3471</v>
       </c>
       <c r="G390" s="2" t="s">
         <v>15</v>
@@ -31144,7 +31150,7 @@
         <v>14</v>
       </c>
       <c r="F391" s="2">
-        <v>2733</v>
+        <v>1270</v>
       </c>
       <c r="G391" s="2" t="s">
         <v>15</v>
@@ -31176,7 +31182,7 @@
         <v>14</v>
       </c>
       <c r="F392" s="2">
-        <v>1345</v>
+        <v>1582</v>
       </c>
       <c r="G392" s="2" t="s">
         <v>15</v>
@@ -31208,7 +31214,7 @@
         <v>14</v>
       </c>
       <c r="F393" s="2">
-        <v>1026</v>
+        <v>4522</v>
       </c>
       <c r="G393" s="2" t="s">
         <v>15</v>
@@ -31240,7 +31246,7 @@
         <v>14</v>
       </c>
       <c r="F394" s="2">
-        <v>2355</v>
+        <v>1236</v>
       </c>
       <c r="G394" s="2" t="s">
         <v>15</v>
@@ -31272,7 +31278,7 @@
         <v>14</v>
       </c>
       <c r="F395" s="2">
-        <v>2668</v>
+        <v>1493</v>
       </c>
       <c r="G395" s="2" t="s">
         <v>15</v>
@@ -31304,7 +31310,7 @@
         <v>14</v>
       </c>
       <c r="F396" s="2">
-        <v>932</v>
+        <v>3975</v>
       </c>
       <c r="G396" s="2" t="s">
         <v>15</v>
@@ -31336,7 +31342,7 @@
         <v>14</v>
       </c>
       <c r="F397" s="2">
-        <v>3599</v>
+        <v>1558</v>
       </c>
       <c r="G397" s="2" t="s">
         <v>15</v>
@@ -31368,7 +31374,7 @@
         <v>14</v>
       </c>
       <c r="F398" s="2">
-        <v>1862</v>
+        <v>2726</v>
       </c>
       <c r="G398" s="2" t="s">
         <v>15</v>
@@ -31400,7 +31406,7 @@
         <v>14</v>
       </c>
       <c r="F399" s="2">
-        <v>1616</v>
+        <v>1875</v>
       </c>
       <c r="G399" s="2" t="s">
         <v>15</v>
@@ -31432,7 +31438,7 @@
         <v>14</v>
       </c>
       <c r="F400" s="2">
-        <v>3844</v>
+        <v>880</v>
       </c>
       <c r="G400" s="2" t="s">
         <v>15</v>
@@ -31464,7 +31470,7 @@
         <v>14</v>
       </c>
       <c r="F401" s="2">
-        <v>2033</v>
+        <v>4647</v>
       </c>
       <c r="G401" s="2" t="s">
         <v>15</v>
@@ -31496,7 +31502,7 @@
         <v>14</v>
       </c>
       <c r="F402" s="2">
-        <v>3785</v>
+        <v>3028</v>
       </c>
       <c r="G402" s="2" t="s">
         <v>15</v>
@@ -31528,7 +31534,7 @@
         <v>14</v>
       </c>
       <c r="F403" s="2">
-        <v>1370</v>
+        <v>2676</v>
       </c>
       <c r="G403" s="2" t="s">
         <v>15</v>
@@ -31560,7 +31566,7 @@
         <v>14</v>
       </c>
       <c r="F404" s="2">
-        <v>3772</v>
+        <v>990</v>
       </c>
       <c r="G404" s="2" t="s">
         <v>15</v>
@@ -31592,7 +31598,7 @@
         <v>14</v>
       </c>
       <c r="F405" s="2">
-        <v>1552</v>
+        <v>4679</v>
       </c>
       <c r="G405" s="2" t="s">
         <v>15</v>
@@ -31624,7 +31630,7 @@
         <v>14</v>
       </c>
       <c r="F406" s="2">
-        <v>801</v>
+        <v>4110</v>
       </c>
       <c r="G406" s="2" t="s">
         <v>15</v>
@@ -31656,7 +31662,7 @@
         <v>14</v>
       </c>
       <c r="F407" s="2">
-        <v>1601</v>
+        <v>1085</v>
       </c>
       <c r="G407" s="2" t="s">
         <v>15</v>
@@ -31688,7 +31694,7 @@
         <v>14</v>
       </c>
       <c r="F408" s="2">
-        <v>4454</v>
+        <v>3761</v>
       </c>
       <c r="G408" s="2" t="s">
         <v>15</v>
@@ -31720,7 +31726,7 @@
         <v>14</v>
       </c>
       <c r="F409" s="2">
-        <v>2894</v>
+        <v>1164</v>
       </c>
       <c r="G409" s="2" t="s">
         <v>15</v>
@@ -31752,7 +31758,7 @@
         <v>14</v>
       </c>
       <c r="F410" s="2">
-        <v>3981</v>
+        <v>3649</v>
       </c>
       <c r="G410" s="2" t="s">
         <v>15</v>
@@ -31784,7 +31790,7 @@
         <v>14</v>
       </c>
       <c r="F411" s="2">
-        <v>2220</v>
+        <v>1997</v>
       </c>
       <c r="G411" s="2" t="s">
         <v>15</v>
@@ -31816,7 +31822,7 @@
         <v>14</v>
       </c>
       <c r="F412" s="2">
-        <v>3352</v>
+        <v>2072</v>
       </c>
       <c r="G412" s="2" t="s">
         <v>15</v>
@@ -31848,7 +31854,7 @@
         <v>14</v>
       </c>
       <c r="F413" s="2">
-        <v>2846</v>
+        <v>3226</v>
       </c>
       <c r="G413" s="2" t="s">
         <v>15</v>
@@ -31880,7 +31886,7 @@
         <v>14</v>
       </c>
       <c r="F414" s="2">
-        <v>2255</v>
+        <v>3758</v>
       </c>
       <c r="G414" s="2" t="s">
         <v>15</v>
@@ -31912,7 +31918,7 @@
         <v>14</v>
       </c>
       <c r="F415" s="2">
-        <v>950</v>
+        <v>2552</v>
       </c>
       <c r="G415" s="2" t="s">
         <v>15</v>
@@ -31944,7 +31950,7 @@
         <v>14</v>
       </c>
       <c r="F416" s="2">
-        <v>2243</v>
+        <v>4136</v>
       </c>
       <c r="G416" s="2" t="s">
         <v>15</v>
@@ -31976,7 +31982,7 @@
         <v>14</v>
       </c>
       <c r="F417" s="2">
-        <v>2722</v>
+        <v>2681</v>
       </c>
       <c r="G417" s="2" t="s">
         <v>15</v>
@@ -32008,7 +32014,7 @@
         <v>14</v>
       </c>
       <c r="F418" s="2">
-        <v>2635</v>
+        <v>4032</v>
       </c>
       <c r="G418" s="2" t="s">
         <v>15</v>
@@ -32040,7 +32046,7 @@
         <v>14</v>
       </c>
       <c r="F419" s="2">
-        <v>2456</v>
+        <v>2766</v>
       </c>
       <c r="G419" s="2" t="s">
         <v>15</v>
@@ -32072,7 +32078,7 @@
         <v>14</v>
       </c>
       <c r="F420" s="2">
-        <v>852</v>
+        <v>2832</v>
       </c>
       <c r="G420" s="2" t="s">
         <v>15</v>
@@ -32104,7 +32110,7 @@
         <v>14</v>
       </c>
       <c r="F421" s="2">
-        <v>4015</v>
+        <v>1211</v>
       </c>
       <c r="G421" s="2" t="s">
         <v>15</v>
@@ -32136,7 +32142,7 @@
         <v>14</v>
       </c>
       <c r="F422" s="2">
-        <v>4310</v>
+        <v>4033</v>
       </c>
       <c r="G422" s="2" t="s">
         <v>15</v>
@@ -32168,7 +32174,7 @@
         <v>14</v>
       </c>
       <c r="F423" s="2">
-        <v>1040</v>
+        <v>1074</v>
       </c>
       <c r="G423" s="2" t="s">
         <v>15</v>
@@ -32200,7 +32206,7 @@
         <v>14</v>
       </c>
       <c r="F424" s="2">
-        <v>4251</v>
+        <v>2292</v>
       </c>
       <c r="G424" s="2" t="s">
         <v>15</v>
@@ -32232,7 +32238,7 @@
         <v>14</v>
       </c>
       <c r="F425" s="2">
-        <v>2989</v>
+        <v>1285</v>
       </c>
       <c r="G425" s="2" t="s">
         <v>15</v>
@@ -32264,7 +32270,7 @@
         <v>14</v>
       </c>
       <c r="F426" s="2">
-        <v>3367</v>
+        <v>3517</v>
       </c>
       <c r="G426" s="2" t="s">
         <v>15</v>
@@ -32296,7 +32302,7 @@
         <v>14</v>
       </c>
       <c r="F427" s="2">
-        <v>2872</v>
+        <v>4108</v>
       </c>
       <c r="G427" s="2" t="s">
         <v>15</v>
@@ -32328,7 +32334,7 @@
         <v>14</v>
       </c>
       <c r="F428" s="2">
-        <v>1632</v>
+        <v>2722</v>
       </c>
       <c r="G428" s="2" t="s">
         <v>15</v>
@@ -32360,7 +32366,7 @@
         <v>14</v>
       </c>
       <c r="F429" s="2">
-        <v>2671</v>
+        <v>2391</v>
       </c>
       <c r="G429" s="2" t="s">
         <v>15</v>
@@ -32392,7 +32398,7 @@
         <v>14</v>
       </c>
       <c r="F430" s="2">
-        <v>3484</v>
+        <v>3521</v>
       </c>
       <c r="G430" s="2" t="s">
         <v>15</v>
@@ -32424,7 +32430,7 @@
         <v>14</v>
       </c>
       <c r="F431" s="2">
-        <v>1151</v>
+        <v>3952</v>
       </c>
       <c r="G431" s="2" t="s">
         <v>15</v>
@@ -32456,7 +32462,7 @@
         <v>14</v>
       </c>
       <c r="F432" s="2">
-        <v>4696</v>
+        <v>4083</v>
       </c>
       <c r="G432" s="2" t="s">
         <v>15</v>
@@ -32488,7 +32494,7 @@
         <v>14</v>
       </c>
       <c r="F433" s="2">
-        <v>1986</v>
+        <v>3442</v>
       </c>
       <c r="G433" s="2" t="s">
         <v>15</v>
@@ -32520,7 +32526,7 @@
         <v>14</v>
       </c>
       <c r="F434" s="2">
-        <v>2573</v>
+        <v>2922</v>
       </c>
       <c r="G434" s="2" t="s">
         <v>15</v>
@@ -32552,7 +32558,7 @@
         <v>14</v>
       </c>
       <c r="F435" s="2">
-        <v>2239</v>
+        <v>2540</v>
       </c>
       <c r="G435" s="2" t="s">
         <v>15</v>
@@ -32584,7 +32590,7 @@
         <v>14</v>
       </c>
       <c r="F436" s="2">
-        <v>4591</v>
+        <v>3988</v>
       </c>
       <c r="G436" s="2" t="s">
         <v>15</v>
@@ -32616,7 +32622,7 @@
         <v>14</v>
       </c>
       <c r="F437" s="2">
-        <v>1429</v>
+        <v>2379</v>
       </c>
       <c r="G437" s="2" t="s">
         <v>15</v>
@@ -32648,7 +32654,7 @@
         <v>14</v>
       </c>
       <c r="F438" s="2">
-        <v>2712</v>
+        <v>3032</v>
       </c>
       <c r="G438" s="2" t="s">
         <v>15</v>
@@ -32680,7 +32686,7 @@
         <v>14</v>
       </c>
       <c r="F439" s="2">
-        <v>3261</v>
+        <v>3176</v>
       </c>
       <c r="G439" s="2" t="s">
         <v>15</v>
@@ -32712,7 +32718,7 @@
         <v>14</v>
       </c>
       <c r="F440" s="2">
-        <v>4385</v>
+        <v>3795</v>
       </c>
       <c r="G440" s="2" t="s">
         <v>15</v>
@@ -32744,7 +32750,7 @@
         <v>14</v>
       </c>
       <c r="F441" s="2">
-        <v>1274</v>
+        <v>3443</v>
       </c>
       <c r="G441" s="2" t="s">
         <v>15</v>
@@ -32776,7 +32782,7 @@
         <v>14</v>
       </c>
       <c r="F442" s="2">
-        <v>1504</v>
+        <v>2605</v>
       </c>
       <c r="G442" s="2" t="s">
         <v>15</v>
@@ -32808,7 +32814,7 @@
         <v>14</v>
       </c>
       <c r="F443" s="2">
-        <v>3631</v>
+        <v>3369</v>
       </c>
       <c r="G443" s="2" t="s">
         <v>15</v>
@@ -32840,7 +32846,7 @@
         <v>14</v>
       </c>
       <c r="F444" s="2">
-        <v>4101</v>
+        <v>4702</v>
       </c>
       <c r="G444" s="2" t="s">
         <v>15</v>
@@ -32872,7 +32878,7 @@
         <v>14</v>
       </c>
       <c r="F445" s="2">
-        <v>2468</v>
+        <v>1767</v>
       </c>
       <c r="G445" s="2" t="s">
         <v>15</v>
@@ -32904,7 +32910,7 @@
         <v>14</v>
       </c>
       <c r="F446" s="2">
-        <v>3415</v>
+        <v>1614</v>
       </c>
       <c r="G446" s="2" t="s">
         <v>15</v>
@@ -32936,7 +32942,7 @@
         <v>14</v>
       </c>
       <c r="F447" s="2">
-        <v>3313</v>
+        <v>3406</v>
       </c>
       <c r="G447" s="2" t="s">
         <v>15</v>
@@ -32968,7 +32974,7 @@
         <v>14</v>
       </c>
       <c r="F448" s="2">
-        <v>1389</v>
+        <v>2220</v>
       </c>
       <c r="G448" s="2" t="s">
         <v>15</v>
@@ -33000,7 +33006,7 @@
         <v>14</v>
       </c>
       <c r="F449" s="2">
-        <v>3990</v>
+        <v>4767</v>
       </c>
       <c r="G449" s="2" t="s">
         <v>15</v>
@@ -33032,7 +33038,7 @@
         <v>14</v>
       </c>
       <c r="F450" s="2">
-        <v>4244</v>
+        <v>2164</v>
       </c>
       <c r="G450" s="2" t="s">
         <v>15</v>
@@ -33064,7 +33070,7 @@
         <v>14</v>
       </c>
       <c r="F451" s="2">
-        <v>2275</v>
+        <v>1956</v>
       </c>
       <c r="G451" s="2" t="s">
         <v>15</v>
@@ -33096,7 +33102,7 @@
         <v>14</v>
       </c>
       <c r="F452" s="2">
-        <v>2573</v>
+        <v>2927</v>
       </c>
       <c r="G452" s="2" t="s">
         <v>15</v>
@@ -33128,7 +33134,7 @@
         <v>14</v>
       </c>
       <c r="F453" s="2">
-        <v>2089</v>
+        <v>3916</v>
       </c>
       <c r="G453" s="2" t="s">
         <v>15</v>
@@ -33160,7 +33166,7 @@
         <v>14</v>
       </c>
       <c r="F454" s="2">
-        <v>3373</v>
+        <v>2357</v>
       </c>
       <c r="G454" s="2" t="s">
         <v>15</v>
@@ -33192,7 +33198,7 @@
         <v>14</v>
       </c>
       <c r="F455" s="2">
-        <v>4374</v>
+        <v>2914</v>
       </c>
       <c r="G455" s="2" t="s">
         <v>15</v>
@@ -33224,7 +33230,7 @@
         <v>14</v>
       </c>
       <c r="F456" s="2">
-        <v>3615</v>
+        <v>825</v>
       </c>
       <c r="G456" s="2" t="s">
         <v>15</v>
@@ -33256,7 +33262,7 @@
         <v>14</v>
       </c>
       <c r="F457" s="2">
-        <v>1087</v>
+        <v>1491</v>
       </c>
       <c r="G457" s="2" t="s">
         <v>15</v>
@@ -33288,7 +33294,7 @@
         <v>14</v>
       </c>
       <c r="F458" s="2">
-        <v>949</v>
+        <v>867</v>
       </c>
       <c r="G458" s="2" t="s">
         <v>15</v>
@@ -33320,7 +33326,7 @@
         <v>14</v>
       </c>
       <c r="F459" s="2">
-        <v>4113</v>
+        <v>2884</v>
       </c>
       <c r="G459" s="2" t="s">
         <v>15</v>
@@ -33352,7 +33358,7 @@
         <v>14</v>
       </c>
       <c r="F460" s="2">
-        <v>4286</v>
+        <v>1735</v>
       </c>
       <c r="G460" s="2" t="s">
         <v>15</v>
@@ -33384,7 +33390,7 @@
         <v>14</v>
       </c>
       <c r="F461" s="2">
-        <v>2693</v>
+        <v>931</v>
       </c>
       <c r="G461" s="2" t="s">
         <v>15</v>
@@ -33416,7 +33422,7 @@
         <v>14</v>
       </c>
       <c r="F462" s="2">
-        <v>3972</v>
+        <v>3658</v>
       </c>
       <c r="G462" s="2" t="s">
         <v>15</v>
@@ -33448,7 +33454,7 @@
         <v>14</v>
       </c>
       <c r="F463" s="2">
-        <v>4054</v>
+        <v>4732</v>
       </c>
       <c r="G463" s="2" t="s">
         <v>15</v>
@@ -33480,7 +33486,7 @@
         <v>14</v>
       </c>
       <c r="F464" s="2">
-        <v>1137</v>
+        <v>4411</v>
       </c>
       <c r="G464" s="2" t="s">
         <v>15</v>
@@ -33512,7 +33518,7 @@
         <v>14</v>
       </c>
       <c r="F465" s="2">
-        <v>1514</v>
+        <v>4170</v>
       </c>
       <c r="G465" s="2" t="s">
         <v>15</v>
@@ -33544,7 +33550,7 @@
         <v>14</v>
       </c>
       <c r="F466" s="2">
-        <v>1973</v>
+        <v>2958</v>
       </c>
       <c r="G466" s="2" t="s">
         <v>15</v>
@@ -33576,7 +33582,7 @@
         <v>14</v>
       </c>
       <c r="F467" s="2">
-        <v>2793</v>
+        <v>1615</v>
       </c>
       <c r="G467" s="2" t="s">
         <v>15</v>
@@ -33608,7 +33614,7 @@
         <v>14</v>
       </c>
       <c r="F468" s="2">
-        <v>4284</v>
+        <v>2441</v>
       </c>
       <c r="G468" s="2" t="s">
         <v>15</v>
@@ -33640,7 +33646,7 @@
         <v>14</v>
       </c>
       <c r="F469" s="2">
-        <v>4292</v>
+        <v>3483</v>
       </c>
       <c r="G469" s="2" t="s">
         <v>15</v>
@@ -33672,7 +33678,7 @@
         <v>14</v>
       </c>
       <c r="F470" s="2">
-        <v>2003</v>
+        <v>1685</v>
       </c>
       <c r="G470" s="2" t="s">
         <v>15</v>
@@ -33704,7 +33710,7 @@
         <v>14</v>
       </c>
       <c r="F471" s="2">
-        <v>2217</v>
+        <v>2762</v>
       </c>
       <c r="G471" s="2" t="s">
         <v>15</v>
@@ -33863,36 +33869,36 @@
         <v>1023</v>
       </c>
       <c r="B3" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B4" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="B5" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="B6" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
@@ -33908,7 +33914,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="B9">
         <v>470</v>
@@ -33916,7 +33922,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="B10">
         <v>470</v>
@@ -33924,7 +33930,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -33932,7 +33938,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -33940,18 +33946,18 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="B13" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="B14" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
     </row>
   </sheetData>
@@ -33975,16 +33981,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -34001,7 +34007,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -34018,7 +34024,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -34035,7 +34041,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -34052,7 +34058,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -34069,7 +34075,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -34086,7 +34092,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -34103,7 +34109,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -34120,7 +34126,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -34137,7 +34143,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -34154,7 +34160,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -34171,7 +34177,7 @@
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -34188,7 +34194,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -34205,7 +34211,7 @@
         <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -34222,7 +34228,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
     </row>
   </sheetData>

--- a/reports/selenium/latest/excel/Automation_Test_Report.xlsx
+++ b/reports/selenium/latest/excel/Automation_Test_Report.xlsx
@@ -3084,7 +3084,7 @@
     <t>Build</t>
   </si>
   <si>
-    <t>12</t>
+    <t>13</t>
   </si>
   <si>
     <t>Branch</t>
@@ -3102,7 +3102,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T03:41:14.845Z</t>
+    <t>2026-08-19T03:46:19.018Z</t>
   </si>
   <si>
     <t>Browser</t>
@@ -3607,7 +3607,7 @@
         <v>14</v>
       </c>
       <c r="F2" s="2">
-        <v>1410</v>
+        <v>2571</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>15</v>
@@ -3639,7 +3639,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="2">
-        <v>2568</v>
+        <v>4035</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>15</v>
@@ -3671,7 +3671,7 @@
         <v>14</v>
       </c>
       <c r="F4" s="2">
-        <v>2061</v>
+        <v>4448</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
@@ -3703,7 +3703,7 @@
         <v>14</v>
       </c>
       <c r="F5" s="2">
-        <v>1006</v>
+        <v>4189</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
@@ -3735,7 +3735,7 @@
         <v>14</v>
       </c>
       <c r="F6" s="2">
-        <v>1407</v>
+        <v>1262</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -3767,7 +3767,7 @@
         <v>14</v>
       </c>
       <c r="F7" s="2">
-        <v>3043</v>
+        <v>4074</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -3799,7 +3799,7 @@
         <v>14</v>
       </c>
       <c r="F8" s="2">
-        <v>3101</v>
+        <v>3659</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -3831,7 +3831,7 @@
         <v>14</v>
       </c>
       <c r="F9" s="2">
-        <v>4731</v>
+        <v>3314</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -3863,7 +3863,7 @@
         <v>14</v>
       </c>
       <c r="F10" s="2">
-        <v>2421</v>
+        <v>3168</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
@@ -3895,7 +3895,7 @@
         <v>14</v>
       </c>
       <c r="F11" s="2">
-        <v>1090</v>
+        <v>2537</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
@@ -3927,7 +3927,7 @@
         <v>14</v>
       </c>
       <c r="F12" s="2">
-        <v>1528</v>
+        <v>1095</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
@@ -3959,7 +3959,7 @@
         <v>14</v>
       </c>
       <c r="F13" s="2">
-        <v>3680</v>
+        <v>3236</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -3991,7 +3991,7 @@
         <v>14</v>
       </c>
       <c r="F14" s="2">
-        <v>875</v>
+        <v>3381</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -4023,7 +4023,7 @@
         <v>14</v>
       </c>
       <c r="F15" s="2">
-        <v>2932</v>
+        <v>2503</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -4055,7 +4055,7 @@
         <v>14</v>
       </c>
       <c r="F16" s="2">
-        <v>3362</v>
+        <v>2313</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
@@ -4087,7 +4087,7 @@
         <v>14</v>
       </c>
       <c r="F17" s="2">
-        <v>4552</v>
+        <v>4287</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
@@ -4119,7 +4119,7 @@
         <v>14</v>
       </c>
       <c r="F18" s="2">
-        <v>1353</v>
+        <v>1738</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
@@ -4151,7 +4151,7 @@
         <v>14</v>
       </c>
       <c r="F19" s="2">
-        <v>2798</v>
+        <v>2023</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
@@ -4183,7 +4183,7 @@
         <v>14</v>
       </c>
       <c r="F20" s="2">
-        <v>2479</v>
+        <v>3168</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
@@ -4215,7 +4215,7 @@
         <v>14</v>
       </c>
       <c r="F21" s="2">
-        <v>4771</v>
+        <v>2611</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -4247,7 +4247,7 @@
         <v>14</v>
       </c>
       <c r="F22" s="2">
-        <v>919</v>
+        <v>4371</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -4279,7 +4279,7 @@
         <v>14</v>
       </c>
       <c r="F23" s="2">
-        <v>2857</v>
+        <v>810</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -4311,7 +4311,7 @@
         <v>14</v>
       </c>
       <c r="F24" s="2">
-        <v>4482</v>
+        <v>1467</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -4343,7 +4343,7 @@
         <v>14</v>
       </c>
       <c r="F25" s="2">
-        <v>1199</v>
+        <v>3921</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -4375,7 +4375,7 @@
         <v>14</v>
       </c>
       <c r="F26" s="2">
-        <v>1797</v>
+        <v>2816</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -4407,7 +4407,7 @@
         <v>14</v>
       </c>
       <c r="F27" s="2">
-        <v>3818</v>
+        <v>3101</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>15</v>
@@ -4439,7 +4439,7 @@
         <v>14</v>
       </c>
       <c r="F28" s="2">
-        <v>1624</v>
+        <v>1789</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>15</v>
@@ -4471,7 +4471,7 @@
         <v>14</v>
       </c>
       <c r="F29" s="2">
-        <v>3847</v>
+        <v>2816</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>15</v>
@@ -4503,7 +4503,7 @@
         <v>14</v>
       </c>
       <c r="F30" s="2">
-        <v>3120</v>
+        <v>1257</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>15</v>
@@ -4535,7 +4535,7 @@
         <v>14</v>
       </c>
       <c r="F31" s="2">
-        <v>3823</v>
+        <v>1809</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>15</v>
@@ -4567,7 +4567,7 @@
         <v>14</v>
       </c>
       <c r="F32" s="2">
-        <v>4104</v>
+        <v>921</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>15</v>
@@ -4599,7 +4599,7 @@
         <v>14</v>
       </c>
       <c r="F33" s="2">
-        <v>2120</v>
+        <v>3286</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>15</v>
@@ -4631,7 +4631,7 @@
         <v>14</v>
       </c>
       <c r="F34" s="2">
-        <v>3997</v>
+        <v>2359</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>15</v>
@@ -4663,7 +4663,7 @@
         <v>14</v>
       </c>
       <c r="F35" s="2">
-        <v>3831</v>
+        <v>2399</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>15</v>
@@ -4695,7 +4695,7 @@
         <v>14</v>
       </c>
       <c r="F36" s="2">
-        <v>2020</v>
+        <v>919</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>15</v>
@@ -4727,7 +4727,7 @@
         <v>14</v>
       </c>
       <c r="F37" s="2">
-        <v>929</v>
+        <v>2222</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>15</v>
@@ -4759,7 +4759,7 @@
         <v>14</v>
       </c>
       <c r="F38" s="2">
-        <v>4216</v>
+        <v>4126</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>15</v>
@@ -4791,7 +4791,7 @@
         <v>14</v>
       </c>
       <c r="F39" s="2">
-        <v>963</v>
+        <v>1770</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>15</v>
@@ -4823,7 +4823,7 @@
         <v>14</v>
       </c>
       <c r="F40" s="2">
-        <v>4559</v>
+        <v>4745</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>15</v>
@@ -4855,7 +4855,7 @@
         <v>14</v>
       </c>
       <c r="F41" s="2">
-        <v>2751</v>
+        <v>939</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>15</v>
@@ -4887,7 +4887,7 @@
         <v>14</v>
       </c>
       <c r="F42" s="2">
-        <v>1717</v>
+        <v>2217</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>15</v>
@@ -4919,7 +4919,7 @@
         <v>14</v>
       </c>
       <c r="F43" s="2">
-        <v>3906</v>
+        <v>2056</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>15</v>
@@ -4951,7 +4951,7 @@
         <v>14</v>
       </c>
       <c r="F44" s="2">
-        <v>3902</v>
+        <v>4353</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>15</v>
@@ -4983,7 +4983,7 @@
         <v>14</v>
       </c>
       <c r="F45" s="2">
-        <v>1999</v>
+        <v>4046</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>15</v>
@@ -5015,7 +5015,7 @@
         <v>14</v>
       </c>
       <c r="F46" s="2">
-        <v>3922</v>
+        <v>2187</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>15</v>
@@ -5047,7 +5047,7 @@
         <v>14</v>
       </c>
       <c r="F47" s="2">
-        <v>957</v>
+        <v>1764</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>15</v>
@@ -5079,7 +5079,7 @@
         <v>14</v>
       </c>
       <c r="F48" s="2">
-        <v>1646</v>
+        <v>4569</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>15</v>
@@ -5111,7 +5111,7 @@
         <v>14</v>
       </c>
       <c r="F49" s="2">
-        <v>4151</v>
+        <v>1631</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>15</v>
@@ -5143,7 +5143,7 @@
         <v>14</v>
       </c>
       <c r="F50" s="2">
-        <v>1006</v>
+        <v>2235</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>15</v>
@@ -5175,7 +5175,7 @@
         <v>14</v>
       </c>
       <c r="F51" s="2">
-        <v>3542</v>
+        <v>3622</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>15</v>
@@ -5207,7 +5207,7 @@
         <v>14</v>
       </c>
       <c r="F52" s="2">
-        <v>2125</v>
+        <v>1594</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>15</v>
@@ -5239,7 +5239,7 @@
         <v>14</v>
       </c>
       <c r="F53" s="2">
-        <v>3601</v>
+        <v>4166</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>15</v>
@@ -5271,7 +5271,7 @@
         <v>14</v>
       </c>
       <c r="F54" s="2">
-        <v>1221</v>
+        <v>2321</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>15</v>
@@ -5303,7 +5303,7 @@
         <v>14</v>
       </c>
       <c r="F55" s="2">
-        <v>849</v>
+        <v>2661</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>15</v>
@@ -5335,7 +5335,7 @@
         <v>14</v>
       </c>
       <c r="F56" s="2">
-        <v>1093</v>
+        <v>1348</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>15</v>
@@ -5367,7 +5367,7 @@
         <v>14</v>
       </c>
       <c r="F57" s="2">
-        <v>4635</v>
+        <v>3186</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>15</v>
@@ -5399,7 +5399,7 @@
         <v>14</v>
       </c>
       <c r="F58" s="2">
-        <v>1880</v>
+        <v>4447</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>15</v>
@@ -5431,7 +5431,7 @@
         <v>14</v>
       </c>
       <c r="F59" s="2">
-        <v>4763</v>
+        <v>3327</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>15</v>
@@ -5463,7 +5463,7 @@
         <v>14</v>
       </c>
       <c r="F60" s="2">
-        <v>4396</v>
+        <v>927</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>15</v>
@@ -5495,7 +5495,7 @@
         <v>14</v>
       </c>
       <c r="F61" s="2">
-        <v>1408</v>
+        <v>1624</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>15</v>
@@ -5527,7 +5527,7 @@
         <v>14</v>
       </c>
       <c r="F62" s="2">
-        <v>1750</v>
+        <v>1855</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>15</v>
@@ -5559,7 +5559,7 @@
         <v>14</v>
       </c>
       <c r="F63" s="2">
-        <v>2831</v>
+        <v>2658</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>15</v>
@@ -5591,7 +5591,7 @@
         <v>14</v>
       </c>
       <c r="F64" s="2">
-        <v>2474</v>
+        <v>2376</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>15</v>
@@ -5623,7 +5623,7 @@
         <v>14</v>
       </c>
       <c r="F65" s="2">
-        <v>3741</v>
+        <v>4238</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>15</v>
@@ -5655,7 +5655,7 @@
         <v>14</v>
       </c>
       <c r="F66" s="2">
-        <v>870</v>
+        <v>3593</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>15</v>
@@ -5687,7 +5687,7 @@
         <v>14</v>
       </c>
       <c r="F67" s="2">
-        <v>881</v>
+        <v>1934</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>15</v>
@@ -5719,7 +5719,7 @@
         <v>14</v>
       </c>
       <c r="F68" s="2">
-        <v>3836</v>
+        <v>1148</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>15</v>
@@ -5751,7 +5751,7 @@
         <v>14</v>
       </c>
       <c r="F69" s="2">
-        <v>947</v>
+        <v>2832</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>15</v>
@@ -5783,7 +5783,7 @@
         <v>14</v>
       </c>
       <c r="F70" s="2">
-        <v>2520</v>
+        <v>4185</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>15</v>
@@ -5815,7 +5815,7 @@
         <v>14</v>
       </c>
       <c r="F71" s="2">
-        <v>802</v>
+        <v>3100</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>15</v>
@@ -5847,7 +5847,7 @@
         <v>14</v>
       </c>
       <c r="F72" s="2">
-        <v>1896</v>
+        <v>1351</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>15</v>
@@ -5879,7 +5879,7 @@
         <v>14</v>
       </c>
       <c r="F73" s="2">
-        <v>2299</v>
+        <v>3018</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>15</v>
@@ -5911,7 +5911,7 @@
         <v>14</v>
       </c>
       <c r="F74" s="2">
-        <v>3349</v>
+        <v>1656</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>15</v>
@@ -5943,7 +5943,7 @@
         <v>14</v>
       </c>
       <c r="F75" s="2">
-        <v>2722</v>
+        <v>2834</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>15</v>
@@ -5975,7 +5975,7 @@
         <v>14</v>
       </c>
       <c r="F76" s="2">
-        <v>2271</v>
+        <v>4693</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>15</v>
@@ -6007,7 +6007,7 @@
         <v>14</v>
       </c>
       <c r="F77" s="2">
-        <v>3728</v>
+        <v>2651</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>15</v>
@@ -6039,7 +6039,7 @@
         <v>14</v>
       </c>
       <c r="F78" s="2">
-        <v>4793</v>
+        <v>1256</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>15</v>
@@ -6071,7 +6071,7 @@
         <v>14</v>
       </c>
       <c r="F79" s="2">
-        <v>1799</v>
+        <v>969</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>15</v>
@@ -6103,7 +6103,7 @@
         <v>14</v>
       </c>
       <c r="F80" s="2">
-        <v>4067</v>
+        <v>3750</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>15</v>
@@ -6135,7 +6135,7 @@
         <v>14</v>
       </c>
       <c r="F81" s="2">
-        <v>4595</v>
+        <v>3680</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>15</v>
@@ -6167,7 +6167,7 @@
         <v>14</v>
       </c>
       <c r="F82" s="2">
-        <v>3797</v>
+        <v>2527</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>15</v>
@@ -6199,7 +6199,7 @@
         <v>14</v>
       </c>
       <c r="F83" s="2">
-        <v>1604</v>
+        <v>2710</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>15</v>
@@ -6231,7 +6231,7 @@
         <v>14</v>
       </c>
       <c r="F84" s="2">
-        <v>4449</v>
+        <v>3519</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>15</v>
@@ -6263,7 +6263,7 @@
         <v>14</v>
       </c>
       <c r="F85" s="2">
-        <v>2248</v>
+        <v>1319</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>15</v>
@@ -6295,7 +6295,7 @@
         <v>14</v>
       </c>
       <c r="F86" s="2">
-        <v>2680</v>
+        <v>3286</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>15</v>
@@ -6327,7 +6327,7 @@
         <v>14</v>
       </c>
       <c r="F87" s="2">
-        <v>4120</v>
+        <v>1263</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>15</v>
@@ -6359,7 +6359,7 @@
         <v>14</v>
       </c>
       <c r="F88" s="2">
-        <v>3876</v>
+        <v>3476</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>15</v>
@@ -6391,7 +6391,7 @@
         <v>14</v>
       </c>
       <c r="F89" s="2">
-        <v>3388</v>
+        <v>2448</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>15</v>
@@ -6423,7 +6423,7 @@
         <v>14</v>
       </c>
       <c r="F90" s="2">
-        <v>4069</v>
+        <v>2859</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>15</v>
@@ -6455,7 +6455,7 @@
         <v>14</v>
       </c>
       <c r="F91" s="2">
-        <v>4798</v>
+        <v>4700</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>15</v>
@@ -6487,7 +6487,7 @@
         <v>14</v>
       </c>
       <c r="F92" s="2">
-        <v>2721</v>
+        <v>4739</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>15</v>
@@ -6519,7 +6519,7 @@
         <v>14</v>
       </c>
       <c r="F93" s="2">
-        <v>4198</v>
+        <v>3696</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>15</v>
@@ -6551,7 +6551,7 @@
         <v>14</v>
       </c>
       <c r="F94" s="2">
-        <v>4093</v>
+        <v>1789</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>15</v>
@@ -6583,7 +6583,7 @@
         <v>14</v>
       </c>
       <c r="F95" s="2">
-        <v>3415</v>
+        <v>1544</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>15</v>
@@ -6615,7 +6615,7 @@
         <v>14</v>
       </c>
       <c r="F96" s="2">
-        <v>3917</v>
+        <v>1619</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>15</v>
@@ -6647,7 +6647,7 @@
         <v>14</v>
       </c>
       <c r="F97" s="2">
-        <v>4376</v>
+        <v>4326</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>15</v>
@@ -6679,7 +6679,7 @@
         <v>14</v>
       </c>
       <c r="F98" s="2">
-        <v>1534</v>
+        <v>4087</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>15</v>
@@ -6711,7 +6711,7 @@
         <v>14</v>
       </c>
       <c r="F99" s="2">
-        <v>1396</v>
+        <v>1117</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>15</v>
@@ -6743,7 +6743,7 @@
         <v>14</v>
       </c>
       <c r="F100" s="2">
-        <v>1788</v>
+        <v>1770</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>15</v>
@@ -6775,7 +6775,7 @@
         <v>14</v>
       </c>
       <c r="F101" s="2">
-        <v>860</v>
+        <v>2740</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>15</v>
@@ -6807,7 +6807,7 @@
         <v>14</v>
       </c>
       <c r="F102" s="2">
-        <v>4117</v>
+        <v>1490</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>15</v>
@@ -6839,7 +6839,7 @@
         <v>14</v>
       </c>
       <c r="F103" s="2">
-        <v>1431</v>
+        <v>3557</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>15</v>
@@ -6871,7 +6871,7 @@
         <v>14</v>
       </c>
       <c r="F104" s="2">
-        <v>2506</v>
+        <v>2340</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>15</v>
@@ -6903,7 +6903,7 @@
         <v>14</v>
       </c>
       <c r="F105" s="2">
-        <v>1492</v>
+        <v>4725</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>15</v>
@@ -6935,7 +6935,7 @@
         <v>14</v>
       </c>
       <c r="F106" s="2">
-        <v>4114</v>
+        <v>3075</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>15</v>
@@ -6967,7 +6967,7 @@
         <v>14</v>
       </c>
       <c r="F107" s="2">
-        <v>3396</v>
+        <v>4389</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>15</v>
@@ -6999,7 +6999,7 @@
         <v>14</v>
       </c>
       <c r="F108" s="2">
-        <v>1053</v>
+        <v>3074</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>15</v>
@@ -7031,7 +7031,7 @@
         <v>14</v>
       </c>
       <c r="F109" s="2">
-        <v>970</v>
+        <v>4798</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>15</v>
@@ -7063,7 +7063,7 @@
         <v>14</v>
       </c>
       <c r="F110" s="2">
-        <v>3978</v>
+        <v>847</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>15</v>
@@ -7095,7 +7095,7 @@
         <v>14</v>
       </c>
       <c r="F111" s="2">
-        <v>1929</v>
+        <v>2920</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>15</v>
@@ -7127,7 +7127,7 @@
         <v>14</v>
       </c>
       <c r="F112" s="2">
-        <v>1100</v>
+        <v>3199</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>15</v>
@@ -7159,7 +7159,7 @@
         <v>14</v>
       </c>
       <c r="F113" s="2">
-        <v>2516</v>
+        <v>4704</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>15</v>
@@ -7191,7 +7191,7 @@
         <v>14</v>
       </c>
       <c r="F114" s="2">
-        <v>1944</v>
+        <v>1593</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>15</v>
@@ -7223,7 +7223,7 @@
         <v>14</v>
       </c>
       <c r="F115" s="2">
-        <v>2455</v>
+        <v>3254</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>15</v>
@@ -7255,7 +7255,7 @@
         <v>14</v>
       </c>
       <c r="F116" s="2">
-        <v>3427</v>
+        <v>1707</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>15</v>
@@ -7287,7 +7287,7 @@
         <v>14</v>
       </c>
       <c r="F117" s="2">
-        <v>1288</v>
+        <v>1132</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>15</v>
@@ -7319,7 +7319,7 @@
         <v>14</v>
       </c>
       <c r="F118" s="2">
-        <v>4304</v>
+        <v>1205</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>15</v>
@@ -7351,7 +7351,7 @@
         <v>14</v>
       </c>
       <c r="F119" s="2">
-        <v>2270</v>
+        <v>1121</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>15</v>
@@ -7383,7 +7383,7 @@
         <v>14</v>
       </c>
       <c r="F120" s="2">
-        <v>2298</v>
+        <v>4279</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>15</v>
@@ -7415,7 +7415,7 @@
         <v>14</v>
       </c>
       <c r="F121" s="2">
-        <v>4234</v>
+        <v>3912</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>15</v>
@@ -7447,7 +7447,7 @@
         <v>14</v>
       </c>
       <c r="F122" s="2">
-        <v>3098</v>
+        <v>4786</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>15</v>
@@ -7479,7 +7479,7 @@
         <v>14</v>
       </c>
       <c r="F123" s="2">
-        <v>2500</v>
+        <v>1674</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>15</v>
@@ -7511,7 +7511,7 @@
         <v>14</v>
       </c>
       <c r="F124" s="2">
-        <v>4381</v>
+        <v>3257</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>15</v>
@@ -7543,7 +7543,7 @@
         <v>14</v>
       </c>
       <c r="F125" s="2">
-        <v>1644</v>
+        <v>3781</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>15</v>
@@ -7575,7 +7575,7 @@
         <v>14</v>
       </c>
       <c r="F126" s="2">
-        <v>4100</v>
+        <v>2607</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>15</v>
@@ -7607,7 +7607,7 @@
         <v>14</v>
       </c>
       <c r="F127" s="2">
-        <v>4173</v>
+        <v>3611</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>15</v>
@@ -7639,7 +7639,7 @@
         <v>14</v>
       </c>
       <c r="F128" s="2">
-        <v>4757</v>
+        <v>3037</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>15</v>
@@ -7671,7 +7671,7 @@
         <v>14</v>
       </c>
       <c r="F129" s="2">
-        <v>972</v>
+        <v>3383</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>15</v>
@@ -7703,7 +7703,7 @@
         <v>14</v>
       </c>
       <c r="F130" s="2">
-        <v>2221</v>
+        <v>3967</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>15</v>
@@ -7735,7 +7735,7 @@
         <v>14</v>
       </c>
       <c r="F131" s="2">
-        <v>1004</v>
+        <v>1038</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>15</v>
@@ -7767,7 +7767,7 @@
         <v>14</v>
       </c>
       <c r="F132" s="2">
-        <v>1665</v>
+        <v>3641</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>15</v>
@@ -7799,7 +7799,7 @@
         <v>14</v>
       </c>
       <c r="F133" s="2">
-        <v>4340</v>
+        <v>1141</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>15</v>
@@ -7831,7 +7831,7 @@
         <v>14</v>
       </c>
       <c r="F134" s="2">
-        <v>3133</v>
+        <v>1571</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>15</v>
@@ -7863,7 +7863,7 @@
         <v>14</v>
       </c>
       <c r="F135" s="2">
-        <v>2167</v>
+        <v>4083</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>15</v>
@@ -7895,7 +7895,7 @@
         <v>14</v>
       </c>
       <c r="F136" s="2">
-        <v>1411</v>
+        <v>3241</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>15</v>
@@ -7927,7 +7927,7 @@
         <v>14</v>
       </c>
       <c r="F137" s="2">
-        <v>1786</v>
+        <v>2416</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>15</v>
@@ -7959,7 +7959,7 @@
         <v>14</v>
       </c>
       <c r="F138" s="2">
-        <v>4760</v>
+        <v>4027</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>15</v>
@@ -7991,7 +7991,7 @@
         <v>14</v>
       </c>
       <c r="F139" s="2">
-        <v>1294</v>
+        <v>4105</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>15</v>
@@ -8023,7 +8023,7 @@
         <v>14</v>
       </c>
       <c r="F140" s="2">
-        <v>1698</v>
+        <v>3674</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>15</v>
@@ -8055,7 +8055,7 @@
         <v>14</v>
       </c>
       <c r="F141" s="2">
-        <v>4089</v>
+        <v>2953</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>15</v>
@@ -8087,7 +8087,7 @@
         <v>14</v>
       </c>
       <c r="F142" s="2">
-        <v>1277</v>
+        <v>4225</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>15</v>
@@ -8119,7 +8119,7 @@
         <v>14</v>
       </c>
       <c r="F143" s="2">
-        <v>4332</v>
+        <v>3778</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>15</v>
@@ -8151,7 +8151,7 @@
         <v>14</v>
       </c>
       <c r="F144" s="2">
-        <v>2203</v>
+        <v>4685</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>15</v>
@@ -8183,7 +8183,7 @@
         <v>14</v>
       </c>
       <c r="F145" s="2">
-        <v>3650</v>
+        <v>3120</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>15</v>
@@ -8215,7 +8215,7 @@
         <v>14</v>
       </c>
       <c r="F146" s="2">
-        <v>2465</v>
+        <v>4789</v>
       </c>
       <c r="G146" s="2" t="s">
         <v>15</v>
@@ -8247,7 +8247,7 @@
         <v>14</v>
       </c>
       <c r="F147" s="2">
-        <v>3811</v>
+        <v>3075</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>15</v>
@@ -8279,7 +8279,7 @@
         <v>14</v>
       </c>
       <c r="F148" s="2">
-        <v>2487</v>
+        <v>1457</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>15</v>
@@ -8311,7 +8311,7 @@
         <v>14</v>
       </c>
       <c r="F149" s="2">
-        <v>2491</v>
+        <v>2766</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>15</v>
@@ -8343,7 +8343,7 @@
         <v>14</v>
       </c>
       <c r="F150" s="2">
-        <v>4567</v>
+        <v>1389</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>15</v>
@@ -8375,7 +8375,7 @@
         <v>14</v>
       </c>
       <c r="F151" s="2">
-        <v>2706</v>
+        <v>3724</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>15</v>
@@ -8407,7 +8407,7 @@
         <v>14</v>
       </c>
       <c r="F152" s="2">
-        <v>1592</v>
+        <v>4195</v>
       </c>
       <c r="G152" s="2" t="s">
         <v>15</v>
@@ -8439,7 +8439,7 @@
         <v>14</v>
       </c>
       <c r="F153" s="2">
-        <v>4453</v>
+        <v>967</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>15</v>
@@ -8471,7 +8471,7 @@
         <v>14</v>
       </c>
       <c r="F154" s="2">
-        <v>3932</v>
+        <v>3636</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>15</v>
@@ -8503,7 +8503,7 @@
         <v>14</v>
       </c>
       <c r="F155" s="2">
-        <v>1911</v>
+        <v>1951</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>15</v>
@@ -8535,7 +8535,7 @@
         <v>14</v>
       </c>
       <c r="F156" s="2">
-        <v>4052</v>
+        <v>3436</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>15</v>
@@ -8567,7 +8567,7 @@
         <v>14</v>
       </c>
       <c r="F157" s="2">
-        <v>3525</v>
+        <v>2497</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>15</v>
@@ -8599,7 +8599,7 @@
         <v>14</v>
       </c>
       <c r="F158" s="2">
-        <v>1457</v>
+        <v>3458</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>15</v>
@@ -8631,7 +8631,7 @@
         <v>14</v>
       </c>
       <c r="F159" s="2">
-        <v>1071</v>
+        <v>4274</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>15</v>
@@ -8663,7 +8663,7 @@
         <v>14</v>
       </c>
       <c r="F160" s="2">
-        <v>1432</v>
+        <v>875</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>15</v>
@@ -8695,7 +8695,7 @@
         <v>14</v>
       </c>
       <c r="F161" s="2">
-        <v>1888</v>
+        <v>4559</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>15</v>
@@ -8727,7 +8727,7 @@
         <v>14</v>
       </c>
       <c r="F162" s="2">
-        <v>3621</v>
+        <v>1771</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>15</v>
@@ -8759,7 +8759,7 @@
         <v>14</v>
       </c>
       <c r="F163" s="2">
-        <v>2601</v>
+        <v>4416</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>15</v>
@@ -8791,7 +8791,7 @@
         <v>14</v>
       </c>
       <c r="F164" s="2">
-        <v>2484</v>
+        <v>1039</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>15</v>
@@ -8823,7 +8823,7 @@
         <v>14</v>
       </c>
       <c r="F165" s="2">
-        <v>2228</v>
+        <v>1805</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>15</v>
@@ -8855,7 +8855,7 @@
         <v>14</v>
       </c>
       <c r="F166" s="2">
-        <v>3725</v>
+        <v>1376</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>15</v>
@@ -8887,7 +8887,7 @@
         <v>14</v>
       </c>
       <c r="F167" s="2">
-        <v>1987</v>
+        <v>1729</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>15</v>
@@ -8919,7 +8919,7 @@
         <v>14</v>
       </c>
       <c r="F168" s="2">
-        <v>2467</v>
+        <v>4057</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>15</v>
@@ -8951,7 +8951,7 @@
         <v>14</v>
       </c>
       <c r="F169" s="2">
-        <v>804</v>
+        <v>3700</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>15</v>
@@ -8983,7 +8983,7 @@
         <v>14</v>
       </c>
       <c r="F170" s="2">
-        <v>1805</v>
+        <v>3857</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>15</v>
@@ -9015,7 +9015,7 @@
         <v>14</v>
       </c>
       <c r="F171" s="2">
-        <v>2172</v>
+        <v>1885</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>15</v>
@@ -9047,7 +9047,7 @@
         <v>14</v>
       </c>
       <c r="F172" s="2">
-        <v>1749</v>
+        <v>2925</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>15</v>
@@ -9079,7 +9079,7 @@
         <v>14</v>
       </c>
       <c r="F173" s="2">
-        <v>4230</v>
+        <v>3388</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>15</v>
@@ -9111,7 +9111,7 @@
         <v>14</v>
       </c>
       <c r="F174" s="2">
-        <v>1483</v>
+        <v>1350</v>
       </c>
       <c r="G174" s="2" t="s">
         <v>15</v>
@@ -9143,7 +9143,7 @@
         <v>14</v>
       </c>
       <c r="F175" s="2">
-        <v>4340</v>
+        <v>4633</v>
       </c>
       <c r="G175" s="2" t="s">
         <v>15</v>
@@ -9175,7 +9175,7 @@
         <v>14</v>
       </c>
       <c r="F176" s="2">
-        <v>4664</v>
+        <v>1448</v>
       </c>
       <c r="G176" s="2" t="s">
         <v>15</v>
@@ -9207,7 +9207,7 @@
         <v>14</v>
       </c>
       <c r="F177" s="2">
-        <v>4138</v>
+        <v>4598</v>
       </c>
       <c r="G177" s="2" t="s">
         <v>15</v>
@@ -9239,7 +9239,7 @@
         <v>14</v>
       </c>
       <c r="F178" s="2">
-        <v>3105</v>
+        <v>3337</v>
       </c>
       <c r="G178" s="2" t="s">
         <v>15</v>
@@ -9271,7 +9271,7 @@
         <v>14</v>
       </c>
       <c r="F179" s="2">
-        <v>1705</v>
+        <v>4338</v>
       </c>
       <c r="G179" s="2" t="s">
         <v>15</v>
@@ -9303,7 +9303,7 @@
         <v>14</v>
       </c>
       <c r="F180" s="2">
-        <v>2812</v>
+        <v>4339</v>
       </c>
       <c r="G180" s="2" t="s">
         <v>15</v>
@@ -9335,7 +9335,7 @@
         <v>14</v>
       </c>
       <c r="F181" s="2">
-        <v>4224</v>
+        <v>1748</v>
       </c>
       <c r="G181" s="2" t="s">
         <v>15</v>
@@ -9367,7 +9367,7 @@
         <v>14</v>
       </c>
       <c r="F182" s="2">
-        <v>2968</v>
+        <v>2920</v>
       </c>
       <c r="G182" s="2" t="s">
         <v>15</v>
@@ -9399,7 +9399,7 @@
         <v>14</v>
       </c>
       <c r="F183" s="2">
-        <v>1212</v>
+        <v>1413</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>15</v>
@@ -9431,7 +9431,7 @@
         <v>14</v>
       </c>
       <c r="F184" s="2">
-        <v>3781</v>
+        <v>2863</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>15</v>
@@ -9463,7 +9463,7 @@
         <v>14</v>
       </c>
       <c r="F185" s="2">
-        <v>3059</v>
+        <v>2965</v>
       </c>
       <c r="G185" s="2" t="s">
         <v>15</v>
@@ -9495,7 +9495,7 @@
         <v>14</v>
       </c>
       <c r="F186" s="2">
-        <v>2840</v>
+        <v>1403</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>15</v>
@@ -9527,7 +9527,7 @@
         <v>14</v>
       </c>
       <c r="F187" s="2">
-        <v>3528</v>
+        <v>2079</v>
       </c>
       <c r="G187" s="2" t="s">
         <v>15</v>
@@ -9559,7 +9559,7 @@
         <v>14</v>
       </c>
       <c r="F188" s="2">
-        <v>4185</v>
+        <v>4346</v>
       </c>
       <c r="G188" s="2" t="s">
         <v>15</v>
@@ -9591,7 +9591,7 @@
         <v>14</v>
       </c>
       <c r="F189" s="2">
-        <v>2891</v>
+        <v>2788</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>15</v>
@@ -9623,7 +9623,7 @@
         <v>14</v>
       </c>
       <c r="F190" s="2">
-        <v>3345</v>
+        <v>3301</v>
       </c>
       <c r="G190" s="2" t="s">
         <v>15</v>
@@ -9655,7 +9655,7 @@
         <v>14</v>
       </c>
       <c r="F191" s="2">
-        <v>2664</v>
+        <v>3162</v>
       </c>
       <c r="G191" s="2" t="s">
         <v>15</v>
@@ -9687,7 +9687,7 @@
         <v>14</v>
       </c>
       <c r="F192" s="2">
-        <v>1594</v>
+        <v>4749</v>
       </c>
       <c r="G192" s="2" t="s">
         <v>15</v>
@@ -9719,7 +9719,7 @@
         <v>14</v>
       </c>
       <c r="F193" s="2">
-        <v>4012</v>
+        <v>1594</v>
       </c>
       <c r="G193" s="2" t="s">
         <v>15</v>
@@ -9751,7 +9751,7 @@
         <v>14</v>
       </c>
       <c r="F194" s="2">
-        <v>1149</v>
+        <v>1534</v>
       </c>
       <c r="G194" s="2" t="s">
         <v>15</v>
@@ -9783,7 +9783,7 @@
         <v>14</v>
       </c>
       <c r="F195" s="2">
-        <v>1030</v>
+        <v>1299</v>
       </c>
       <c r="G195" s="2" t="s">
         <v>15</v>
@@ -9815,7 +9815,7 @@
         <v>14</v>
       </c>
       <c r="F196" s="2">
-        <v>4657</v>
+        <v>3576</v>
       </c>
       <c r="G196" s="2" t="s">
         <v>15</v>
@@ -9847,7 +9847,7 @@
         <v>14</v>
       </c>
       <c r="F197" s="2">
-        <v>941</v>
+        <v>1087</v>
       </c>
       <c r="G197" s="2" t="s">
         <v>15</v>
@@ -9879,7 +9879,7 @@
         <v>14</v>
       </c>
       <c r="F198" s="2">
-        <v>2066</v>
+        <v>3002</v>
       </c>
       <c r="G198" s="2" t="s">
         <v>15</v>
@@ -9911,7 +9911,7 @@
         <v>14</v>
       </c>
       <c r="F199" s="2">
-        <v>3271</v>
+        <v>4776</v>
       </c>
       <c r="G199" s="2" t="s">
         <v>15</v>
@@ -9943,7 +9943,7 @@
         <v>14</v>
       </c>
       <c r="F200" s="2">
-        <v>1751</v>
+        <v>3830</v>
       </c>
       <c r="G200" s="2" t="s">
         <v>15</v>
@@ -9975,7 +9975,7 @@
         <v>14</v>
       </c>
       <c r="F201" s="2">
-        <v>3980</v>
+        <v>1046</v>
       </c>
       <c r="G201" s="2" t="s">
         <v>15</v>
@@ -10007,7 +10007,7 @@
         <v>14</v>
       </c>
       <c r="F202" s="2">
-        <v>3501</v>
+        <v>3768</v>
       </c>
       <c r="G202" s="2" t="s">
         <v>15</v>
@@ -10039,7 +10039,7 @@
         <v>14</v>
       </c>
       <c r="F203" s="2">
-        <v>3871</v>
+        <v>1507</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>15</v>
@@ -10071,7 +10071,7 @@
         <v>14</v>
       </c>
       <c r="F204" s="2">
-        <v>3049</v>
+        <v>3963</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>15</v>
@@ -10103,7 +10103,7 @@
         <v>14</v>
       </c>
       <c r="F205" s="2">
-        <v>3356</v>
+        <v>3992</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>15</v>
@@ -10135,7 +10135,7 @@
         <v>14</v>
       </c>
       <c r="F206" s="2">
-        <v>3695</v>
+        <v>1558</v>
       </c>
       <c r="G206" s="2" t="s">
         <v>15</v>
@@ -10167,7 +10167,7 @@
         <v>14</v>
       </c>
       <c r="F207" s="2">
-        <v>3118</v>
+        <v>1737</v>
       </c>
       <c r="G207" s="2" t="s">
         <v>15</v>
@@ -10199,7 +10199,7 @@
         <v>14</v>
       </c>
       <c r="F208" s="2">
-        <v>2705</v>
+        <v>2331</v>
       </c>
       <c r="G208" s="2" t="s">
         <v>15</v>
@@ -10231,7 +10231,7 @@
         <v>14</v>
       </c>
       <c r="F209" s="2">
-        <v>2869</v>
+        <v>3913</v>
       </c>
       <c r="G209" s="2" t="s">
         <v>15</v>
@@ -10263,7 +10263,7 @@
         <v>14</v>
       </c>
       <c r="F210" s="2">
-        <v>1078</v>
+        <v>2246</v>
       </c>
       <c r="G210" s="2" t="s">
         <v>15</v>
@@ -10295,7 +10295,7 @@
         <v>14</v>
       </c>
       <c r="F211" s="2">
-        <v>3951</v>
+        <v>2250</v>
       </c>
       <c r="G211" s="2" t="s">
         <v>15</v>
@@ -10327,7 +10327,7 @@
         <v>14</v>
       </c>
       <c r="F212" s="2">
-        <v>4744</v>
+        <v>1364</v>
       </c>
       <c r="G212" s="2" t="s">
         <v>15</v>
@@ -10359,7 +10359,7 @@
         <v>14</v>
       </c>
       <c r="F213" s="2">
-        <v>3389</v>
+        <v>2823</v>
       </c>
       <c r="G213" s="2" t="s">
         <v>15</v>
@@ -10391,7 +10391,7 @@
         <v>14</v>
       </c>
       <c r="F214" s="2">
-        <v>1857</v>
+        <v>2232</v>
       </c>
       <c r="G214" s="2" t="s">
         <v>15</v>
@@ -10423,7 +10423,7 @@
         <v>14</v>
       </c>
       <c r="F215" s="2">
-        <v>3893</v>
+        <v>2000</v>
       </c>
       <c r="G215" s="2" t="s">
         <v>15</v>
@@ -10455,7 +10455,7 @@
         <v>14</v>
       </c>
       <c r="F216" s="2">
-        <v>1930</v>
+        <v>2947</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>15</v>
@@ -10487,7 +10487,7 @@
         <v>14</v>
       </c>
       <c r="F217" s="2">
-        <v>2885</v>
+        <v>3937</v>
       </c>
       <c r="G217" s="2" t="s">
         <v>15</v>
@@ -10519,7 +10519,7 @@
         <v>14</v>
       </c>
       <c r="F218" s="2">
-        <v>1465</v>
+        <v>2459</v>
       </c>
       <c r="G218" s="2" t="s">
         <v>15</v>
@@ -10551,7 +10551,7 @@
         <v>14</v>
       </c>
       <c r="F219" s="2">
-        <v>2733</v>
+        <v>2748</v>
       </c>
       <c r="G219" s="2" t="s">
         <v>15</v>
@@ -10583,7 +10583,7 @@
         <v>14</v>
       </c>
       <c r="F220" s="2">
-        <v>4089</v>
+        <v>1849</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>15</v>
@@ -10615,7 +10615,7 @@
         <v>14</v>
       </c>
       <c r="F221" s="2">
-        <v>1683</v>
+        <v>2586</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>15</v>
@@ -10647,7 +10647,7 @@
         <v>14</v>
       </c>
       <c r="F222" s="2">
-        <v>2316</v>
+        <v>4684</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>15</v>
@@ -10679,7 +10679,7 @@
         <v>14</v>
       </c>
       <c r="F223" s="2">
-        <v>2857</v>
+        <v>4715</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>15</v>
@@ -10711,7 +10711,7 @@
         <v>14</v>
       </c>
       <c r="F224" s="2">
-        <v>1497</v>
+        <v>2498</v>
       </c>
       <c r="G224" s="2" t="s">
         <v>15</v>
@@ -10743,7 +10743,7 @@
         <v>14</v>
       </c>
       <c r="F225" s="2">
-        <v>3863</v>
+        <v>1412</v>
       </c>
       <c r="G225" s="2" t="s">
         <v>15</v>
@@ -10775,7 +10775,7 @@
         <v>14</v>
       </c>
       <c r="F226" s="2">
-        <v>4571</v>
+        <v>4744</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>15</v>
@@ -10807,7 +10807,7 @@
         <v>14</v>
       </c>
       <c r="F227" s="2">
-        <v>2464</v>
+        <v>3769</v>
       </c>
       <c r="G227" s="2" t="s">
         <v>15</v>
@@ -10839,7 +10839,7 @@
         <v>14</v>
       </c>
       <c r="F228" s="2">
-        <v>4429</v>
+        <v>2455</v>
       </c>
       <c r="G228" s="2" t="s">
         <v>15</v>
@@ -10871,7 +10871,7 @@
         <v>14</v>
       </c>
       <c r="F229" s="2">
-        <v>3963</v>
+        <v>1683</v>
       </c>
       <c r="G229" s="2" t="s">
         <v>15</v>
@@ -10903,7 +10903,7 @@
         <v>14</v>
       </c>
       <c r="F230" s="2">
-        <v>4374</v>
+        <v>942</v>
       </c>
       <c r="G230" s="2" t="s">
         <v>15</v>
@@ -10935,7 +10935,7 @@
         <v>14</v>
       </c>
       <c r="F231" s="2">
-        <v>3374</v>
+        <v>1994</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>15</v>
@@ -10967,7 +10967,7 @@
         <v>14</v>
       </c>
       <c r="F232" s="2">
-        <v>4320</v>
+        <v>4173</v>
       </c>
       <c r="G232" s="2" t="s">
         <v>15</v>
@@ -10999,7 +10999,7 @@
         <v>14</v>
       </c>
       <c r="F233" s="2">
-        <v>4411</v>
+        <v>4290</v>
       </c>
       <c r="G233" s="2" t="s">
         <v>15</v>
@@ -11031,7 +11031,7 @@
         <v>14</v>
       </c>
       <c r="F234" s="2">
-        <v>3823</v>
+        <v>3847</v>
       </c>
       <c r="G234" s="2" t="s">
         <v>15</v>
@@ -11063,7 +11063,7 @@
         <v>14</v>
       </c>
       <c r="F235" s="2">
-        <v>2595</v>
+        <v>2668</v>
       </c>
       <c r="G235" s="2" t="s">
         <v>15</v>
@@ -11095,7 +11095,7 @@
         <v>14</v>
       </c>
       <c r="F236" s="2">
-        <v>1177</v>
+        <v>1595</v>
       </c>
       <c r="G236" s="2" t="s">
         <v>15</v>
@@ -11127,7 +11127,7 @@
         <v>14</v>
       </c>
       <c r="F237" s="2">
-        <v>1799</v>
+        <v>1258</v>
       </c>
       <c r="G237" s="2" t="s">
         <v>15</v>
@@ -11159,7 +11159,7 @@
         <v>14</v>
       </c>
       <c r="F238" s="2">
-        <v>3067</v>
+        <v>2845</v>
       </c>
       <c r="G238" s="2" t="s">
         <v>15</v>
@@ -11191,7 +11191,7 @@
         <v>14</v>
       </c>
       <c r="F239" s="2">
-        <v>2632</v>
+        <v>2972</v>
       </c>
       <c r="G239" s="2" t="s">
         <v>15</v>
@@ -11223,7 +11223,7 @@
         <v>14</v>
       </c>
       <c r="F240" s="2">
-        <v>3722</v>
+        <v>4008</v>
       </c>
       <c r="G240" s="2" t="s">
         <v>15</v>
@@ -11255,7 +11255,7 @@
         <v>14</v>
       </c>
       <c r="F241" s="2">
-        <v>2451</v>
+        <v>1093</v>
       </c>
       <c r="G241" s="2" t="s">
         <v>15</v>
@@ -11287,7 +11287,7 @@
         <v>14</v>
       </c>
       <c r="F242" s="2">
-        <v>1074</v>
+        <v>1914</v>
       </c>
       <c r="G242" s="2" t="s">
         <v>15</v>
@@ -11319,7 +11319,7 @@
         <v>14</v>
       </c>
       <c r="F243" s="2">
-        <v>980</v>
+        <v>4278</v>
       </c>
       <c r="G243" s="2" t="s">
         <v>15</v>
@@ -11351,7 +11351,7 @@
         <v>14</v>
       </c>
       <c r="F244" s="2">
-        <v>1329</v>
+        <v>2488</v>
       </c>
       <c r="G244" s="2" t="s">
         <v>15</v>
@@ -11383,7 +11383,7 @@
         <v>14</v>
       </c>
       <c r="F245" s="2">
-        <v>4189</v>
+        <v>2805</v>
       </c>
       <c r="G245" s="2" t="s">
         <v>15</v>
@@ -11415,7 +11415,7 @@
         <v>14</v>
       </c>
       <c r="F246" s="2">
-        <v>3594</v>
+        <v>4085</v>
       </c>
       <c r="G246" s="2" t="s">
         <v>15</v>
@@ -11447,7 +11447,7 @@
         <v>14</v>
       </c>
       <c r="F247" s="2">
-        <v>2654</v>
+        <v>2786</v>
       </c>
       <c r="G247" s="2" t="s">
         <v>15</v>
@@ -11479,7 +11479,7 @@
         <v>14</v>
       </c>
       <c r="F248" s="2">
-        <v>4305</v>
+        <v>4204</v>
       </c>
       <c r="G248" s="2" t="s">
         <v>15</v>
@@ -11511,7 +11511,7 @@
         <v>14</v>
       </c>
       <c r="F249" s="2">
-        <v>4786</v>
+        <v>4137</v>
       </c>
       <c r="G249" s="2" t="s">
         <v>15</v>
@@ -11543,7 +11543,7 @@
         <v>14</v>
       </c>
       <c r="F250" s="2">
-        <v>2056</v>
+        <v>3058</v>
       </c>
       <c r="G250" s="2" t="s">
         <v>15</v>
@@ -11575,7 +11575,7 @@
         <v>14</v>
       </c>
       <c r="F251" s="2">
-        <v>803</v>
+        <v>1141</v>
       </c>
       <c r="G251" s="2" t="s">
         <v>15</v>
@@ -11607,7 +11607,7 @@
         <v>14</v>
       </c>
       <c r="F252" s="2">
-        <v>4393</v>
+        <v>3699</v>
       </c>
       <c r="G252" s="2" t="s">
         <v>15</v>
@@ -11639,7 +11639,7 @@
         <v>14</v>
       </c>
       <c r="F253" s="2">
-        <v>897</v>
+        <v>3487</v>
       </c>
       <c r="G253" s="2" t="s">
         <v>15</v>
@@ -11671,7 +11671,7 @@
         <v>14</v>
       </c>
       <c r="F254" s="2">
-        <v>2696</v>
+        <v>1603</v>
       </c>
       <c r="G254" s="2" t="s">
         <v>15</v>
@@ -11703,7 +11703,7 @@
         <v>14</v>
       </c>
       <c r="F255" s="2">
-        <v>4120</v>
+        <v>3282</v>
       </c>
       <c r="G255" s="2" t="s">
         <v>15</v>
@@ -11735,7 +11735,7 @@
         <v>14</v>
       </c>
       <c r="F256" s="2">
-        <v>3926</v>
+        <v>1167</v>
       </c>
       <c r="G256" s="2" t="s">
         <v>15</v>
@@ -11767,7 +11767,7 @@
         <v>14</v>
       </c>
       <c r="F257" s="2">
-        <v>1085</v>
+        <v>4750</v>
       </c>
       <c r="G257" s="2" t="s">
         <v>15</v>
@@ -11799,7 +11799,7 @@
         <v>14</v>
       </c>
       <c r="F258" s="2">
-        <v>3107</v>
+        <v>1021</v>
       </c>
       <c r="G258" s="2" t="s">
         <v>15</v>
@@ -11831,7 +11831,7 @@
         <v>14</v>
       </c>
       <c r="F259" s="2">
-        <v>1392</v>
+        <v>2825</v>
       </c>
       <c r="G259" s="2" t="s">
         <v>15</v>
@@ -11863,7 +11863,7 @@
         <v>14</v>
       </c>
       <c r="F260" s="2">
-        <v>4134</v>
+        <v>2166</v>
       </c>
       <c r="G260" s="2" t="s">
         <v>15</v>
@@ -11895,7 +11895,7 @@
         <v>14</v>
       </c>
       <c r="F261" s="2">
-        <v>3066</v>
+        <v>1350</v>
       </c>
       <c r="G261" s="2" t="s">
         <v>15</v>
@@ -11927,7 +11927,7 @@
         <v>14</v>
       </c>
       <c r="F262" s="2">
-        <v>1441</v>
+        <v>3639</v>
       </c>
       <c r="G262" s="2" t="s">
         <v>15</v>
@@ -11959,7 +11959,7 @@
         <v>14</v>
       </c>
       <c r="F263" s="2">
-        <v>4297</v>
+        <v>3697</v>
       </c>
       <c r="G263" s="2" t="s">
         <v>15</v>
@@ -11991,7 +11991,7 @@
         <v>14</v>
       </c>
       <c r="F264" s="2">
-        <v>3715</v>
+        <v>3528</v>
       </c>
       <c r="G264" s="2" t="s">
         <v>15</v>
@@ -12023,7 +12023,7 @@
         <v>14</v>
       </c>
       <c r="F265" s="2">
-        <v>4532</v>
+        <v>4517</v>
       </c>
       <c r="G265" s="2" t="s">
         <v>15</v>
@@ -12055,7 +12055,7 @@
         <v>14</v>
       </c>
       <c r="F266" s="2">
-        <v>3604</v>
+        <v>4072</v>
       </c>
       <c r="G266" s="2" t="s">
         <v>15</v>
@@ -12087,7 +12087,7 @@
         <v>14</v>
       </c>
       <c r="F267" s="2">
-        <v>3415</v>
+        <v>1514</v>
       </c>
       <c r="G267" s="2" t="s">
         <v>15</v>
@@ -12119,7 +12119,7 @@
         <v>14</v>
       </c>
       <c r="F268" s="2">
-        <v>3771</v>
+        <v>3501</v>
       </c>
       <c r="G268" s="2" t="s">
         <v>15</v>
@@ -12151,7 +12151,7 @@
         <v>14</v>
       </c>
       <c r="F269" s="2">
-        <v>4492</v>
+        <v>3961</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>15</v>
@@ -12183,7 +12183,7 @@
         <v>14</v>
       </c>
       <c r="F270" s="2">
-        <v>4406</v>
+        <v>2500</v>
       </c>
       <c r="G270" s="2" t="s">
         <v>15</v>
@@ -12215,7 +12215,7 @@
         <v>14</v>
       </c>
       <c r="F271" s="2">
-        <v>4183</v>
+        <v>1799</v>
       </c>
       <c r="G271" s="2" t="s">
         <v>15</v>
@@ -12247,7 +12247,7 @@
         <v>14</v>
       </c>
       <c r="F272" s="2">
-        <v>1460</v>
+        <v>2162</v>
       </c>
       <c r="G272" s="2" t="s">
         <v>15</v>
@@ -12279,7 +12279,7 @@
         <v>14</v>
       </c>
       <c r="F273" s="2">
-        <v>2595</v>
+        <v>2954</v>
       </c>
       <c r="G273" s="2" t="s">
         <v>15</v>
@@ -12311,7 +12311,7 @@
         <v>14</v>
       </c>
       <c r="F274" s="2">
-        <v>2304</v>
+        <v>3258</v>
       </c>
       <c r="G274" s="2" t="s">
         <v>15</v>
@@ -12343,7 +12343,7 @@
         <v>14</v>
       </c>
       <c r="F275" s="2">
-        <v>2085</v>
+        <v>2724</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>15</v>
@@ -12375,7 +12375,7 @@
         <v>14</v>
       </c>
       <c r="F276" s="2">
-        <v>2202</v>
+        <v>4098</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>15</v>
@@ -12407,7 +12407,7 @@
         <v>14</v>
       </c>
       <c r="F277" s="2">
-        <v>1377</v>
+        <v>1795</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>15</v>
@@ -12439,7 +12439,7 @@
         <v>14</v>
       </c>
       <c r="F278" s="2">
-        <v>1561</v>
+        <v>2990</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>15</v>
@@ -12471,7 +12471,7 @@
         <v>14</v>
       </c>
       <c r="F279" s="2">
-        <v>4386</v>
+        <v>2339</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>15</v>
@@ -12503,7 +12503,7 @@
         <v>14</v>
       </c>
       <c r="F280" s="2">
-        <v>1896</v>
+        <v>1731</v>
       </c>
       <c r="G280" s="2" t="s">
         <v>15</v>
@@ -12535,7 +12535,7 @@
         <v>14</v>
       </c>
       <c r="F281" s="2">
-        <v>833</v>
+        <v>1818</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>15</v>
@@ -12567,7 +12567,7 @@
         <v>14</v>
       </c>
       <c r="F282" s="2">
-        <v>2828</v>
+        <v>3629</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>15</v>
@@ -12599,7 +12599,7 @@
         <v>14</v>
       </c>
       <c r="F283" s="2">
-        <v>1352</v>
+        <v>2543</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>15</v>
@@ -12631,7 +12631,7 @@
         <v>14</v>
       </c>
       <c r="F284" s="2">
-        <v>2569</v>
+        <v>2543</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>15</v>
@@ -12663,7 +12663,7 @@
         <v>14</v>
       </c>
       <c r="F285" s="2">
-        <v>4117</v>
+        <v>3051</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>15</v>
@@ -12695,7 +12695,7 @@
         <v>14</v>
       </c>
       <c r="F286" s="2">
-        <v>3729</v>
+        <v>3100</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>15</v>
@@ -12727,7 +12727,7 @@
         <v>14</v>
       </c>
       <c r="F287" s="2">
-        <v>4663</v>
+        <v>4694</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>15</v>
@@ -12759,7 +12759,7 @@
         <v>14</v>
       </c>
       <c r="F288" s="2">
-        <v>4319</v>
+        <v>969</v>
       </c>
       <c r="G288" s="2" t="s">
         <v>15</v>
@@ -12791,7 +12791,7 @@
         <v>14</v>
       </c>
       <c r="F289" s="2">
-        <v>1641</v>
+        <v>2561</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>15</v>
@@ -12823,7 +12823,7 @@
         <v>14</v>
       </c>
       <c r="F290" s="2">
-        <v>2917</v>
+        <v>890</v>
       </c>
       <c r="G290" s="2" t="s">
         <v>15</v>
@@ -12855,7 +12855,7 @@
         <v>14</v>
       </c>
       <c r="F291" s="2">
-        <v>1005</v>
+        <v>2166</v>
       </c>
       <c r="G291" s="2" t="s">
         <v>15</v>
@@ -12887,7 +12887,7 @@
         <v>14</v>
       </c>
       <c r="F292" s="2">
-        <v>4171</v>
+        <v>823</v>
       </c>
       <c r="G292" s="2" t="s">
         <v>15</v>
@@ -12919,7 +12919,7 @@
         <v>14</v>
       </c>
       <c r="F293" s="2">
-        <v>1361</v>
+        <v>3593</v>
       </c>
       <c r="G293" s="2" t="s">
         <v>15</v>
@@ -12951,7 +12951,7 @@
         <v>14</v>
       </c>
       <c r="F294" s="2">
-        <v>1049</v>
+        <v>2884</v>
       </c>
       <c r="G294" s="2" t="s">
         <v>15</v>
@@ -12983,7 +12983,7 @@
         <v>14</v>
       </c>
       <c r="F295" s="2">
-        <v>2936</v>
+        <v>2627</v>
       </c>
       <c r="G295" s="2" t="s">
         <v>15</v>
@@ -13015,7 +13015,7 @@
         <v>14</v>
       </c>
       <c r="F296" s="2">
-        <v>3238</v>
+        <v>3564</v>
       </c>
       <c r="G296" s="2" t="s">
         <v>15</v>
@@ -13047,7 +13047,7 @@
         <v>14</v>
       </c>
       <c r="F297" s="2">
-        <v>3448</v>
+        <v>2471</v>
       </c>
       <c r="G297" s="2" t="s">
         <v>15</v>
@@ -13079,7 +13079,7 @@
         <v>14</v>
       </c>
       <c r="F298" s="2">
-        <v>3837</v>
+        <v>2795</v>
       </c>
       <c r="G298" s="2" t="s">
         <v>15</v>
@@ -13111,7 +13111,7 @@
         <v>14</v>
       </c>
       <c r="F299" s="2">
-        <v>2424</v>
+        <v>2462</v>
       </c>
       <c r="G299" s="2" t="s">
         <v>15</v>
@@ -13143,7 +13143,7 @@
         <v>14</v>
       </c>
       <c r="F300" s="2">
-        <v>1443</v>
+        <v>2895</v>
       </c>
       <c r="G300" s="2" t="s">
         <v>15</v>
@@ -13175,7 +13175,7 @@
         <v>14</v>
       </c>
       <c r="F301" s="2">
-        <v>2969</v>
+        <v>2505</v>
       </c>
       <c r="G301" s="2" t="s">
         <v>15</v>
@@ -13207,7 +13207,7 @@
         <v>14</v>
       </c>
       <c r="F302" s="2">
-        <v>2522</v>
+        <v>852</v>
       </c>
       <c r="G302" s="2" t="s">
         <v>15</v>
@@ -13239,7 +13239,7 @@
         <v>14</v>
       </c>
       <c r="F303" s="2">
-        <v>2361</v>
+        <v>4678</v>
       </c>
       <c r="G303" s="2" t="s">
         <v>15</v>
@@ -13271,7 +13271,7 @@
         <v>14</v>
       </c>
       <c r="F304" s="2">
-        <v>4261</v>
+        <v>2970</v>
       </c>
       <c r="G304" s="2" t="s">
         <v>15</v>
@@ -13303,7 +13303,7 @@
         <v>14</v>
       </c>
       <c r="F305" s="2">
-        <v>1752</v>
+        <v>3630</v>
       </c>
       <c r="G305" s="2" t="s">
         <v>15</v>
@@ -13335,7 +13335,7 @@
         <v>14</v>
       </c>
       <c r="F306" s="2">
-        <v>3392</v>
+        <v>2694</v>
       </c>
       <c r="G306" s="2" t="s">
         <v>15</v>
@@ -13367,7 +13367,7 @@
         <v>14</v>
       </c>
       <c r="F307" s="2">
-        <v>1606</v>
+        <v>1189</v>
       </c>
       <c r="G307" s="2" t="s">
         <v>15</v>
@@ -13399,7 +13399,7 @@
         <v>14</v>
       </c>
       <c r="F308" s="2">
-        <v>2455</v>
+        <v>2228</v>
       </c>
       <c r="G308" s="2" t="s">
         <v>15</v>
@@ -13431,7 +13431,7 @@
         <v>14</v>
       </c>
       <c r="F309" s="2">
-        <v>3909</v>
+        <v>963</v>
       </c>
       <c r="G309" s="2" t="s">
         <v>15</v>
@@ -13463,7 +13463,7 @@
         <v>14</v>
       </c>
       <c r="F310" s="2">
-        <v>945</v>
+        <v>1715</v>
       </c>
       <c r="G310" s="2" t="s">
         <v>15</v>
@@ -13495,7 +13495,7 @@
         <v>14</v>
       </c>
       <c r="F311" s="2">
-        <v>1186</v>
+        <v>1296</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>15</v>
@@ -13527,7 +13527,7 @@
         <v>14</v>
       </c>
       <c r="F312" s="2">
-        <v>2273</v>
+        <v>2232</v>
       </c>
       <c r="G312" s="2" t="s">
         <v>15</v>
@@ -13559,7 +13559,7 @@
         <v>14</v>
       </c>
       <c r="F313" s="2">
-        <v>2767</v>
+        <v>1246</v>
       </c>
       <c r="G313" s="2" t="s">
         <v>15</v>
@@ -13591,7 +13591,7 @@
         <v>14</v>
       </c>
       <c r="F314" s="2">
-        <v>4311</v>
+        <v>1186</v>
       </c>
       <c r="G314" s="2" t="s">
         <v>15</v>
@@ -13623,7 +13623,7 @@
         <v>14</v>
       </c>
       <c r="F315" s="2">
-        <v>1878</v>
+        <v>1796</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>15</v>
@@ -13655,7 +13655,7 @@
         <v>14</v>
       </c>
       <c r="F316" s="2">
-        <v>3873</v>
+        <v>4281</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>15</v>
@@ -13687,7 +13687,7 @@
         <v>14</v>
       </c>
       <c r="F317" s="2">
-        <v>3640</v>
+        <v>1079</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>15</v>
@@ -13719,7 +13719,7 @@
         <v>14</v>
       </c>
       <c r="F318" s="2">
-        <v>3014</v>
+        <v>2898</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>15</v>
@@ -13751,7 +13751,7 @@
         <v>14</v>
       </c>
       <c r="F319" s="2">
-        <v>3150</v>
+        <v>4013</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>15</v>
@@ -13783,7 +13783,7 @@
         <v>14</v>
       </c>
       <c r="F320" s="2">
-        <v>949</v>
+        <v>3574</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>15</v>
@@ -13815,7 +13815,7 @@
         <v>14</v>
       </c>
       <c r="F321" s="2">
-        <v>4132</v>
+        <v>2554</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>15</v>
@@ -13847,7 +13847,7 @@
         <v>14</v>
       </c>
       <c r="F322" s="2">
-        <v>2320</v>
+        <v>1822</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>15</v>
@@ -13879,7 +13879,7 @@
         <v>14</v>
       </c>
       <c r="F323" s="2">
-        <v>4708</v>
+        <v>4074</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>15</v>
@@ -13911,7 +13911,7 @@
         <v>14</v>
       </c>
       <c r="F324" s="2">
-        <v>3171</v>
+        <v>1552</v>
       </c>
       <c r="G324" s="2" t="s">
         <v>15</v>
@@ -13943,7 +13943,7 @@
         <v>14</v>
       </c>
       <c r="F325" s="2">
-        <v>3095</v>
+        <v>3428</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>15</v>
@@ -13975,7 +13975,7 @@
         <v>14</v>
       </c>
       <c r="F326" s="2">
-        <v>4466</v>
+        <v>1237</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>15</v>
@@ -14007,7 +14007,7 @@
         <v>14</v>
       </c>
       <c r="F327" s="2">
-        <v>2537</v>
+        <v>3059</v>
       </c>
       <c r="G327" s="2" t="s">
         <v>15</v>
@@ -14039,7 +14039,7 @@
         <v>14</v>
       </c>
       <c r="F328" s="2">
-        <v>2359</v>
+        <v>3729</v>
       </c>
       <c r="G328" s="2" t="s">
         <v>15</v>
@@ -14071,7 +14071,7 @@
         <v>14</v>
       </c>
       <c r="F329" s="2">
-        <v>1856</v>
+        <v>3912</v>
       </c>
       <c r="G329" s="2" t="s">
         <v>15</v>
@@ -14103,7 +14103,7 @@
         <v>14</v>
       </c>
       <c r="F330" s="2">
-        <v>4724</v>
+        <v>1300</v>
       </c>
       <c r="G330" s="2" t="s">
         <v>15</v>
@@ -14135,7 +14135,7 @@
         <v>14</v>
       </c>
       <c r="F331" s="2">
-        <v>3579</v>
+        <v>2878</v>
       </c>
       <c r="G331" s="2" t="s">
         <v>15</v>
@@ -14167,7 +14167,7 @@
         <v>14</v>
       </c>
       <c r="F332" s="2">
-        <v>1179</v>
+        <v>3884</v>
       </c>
       <c r="G332" s="2" t="s">
         <v>15</v>
@@ -14199,7 +14199,7 @@
         <v>14</v>
       </c>
       <c r="F333" s="2">
-        <v>3875</v>
+        <v>1132</v>
       </c>
       <c r="G333" s="2" t="s">
         <v>15</v>
@@ -14231,7 +14231,7 @@
         <v>14</v>
       </c>
       <c r="F334" s="2">
-        <v>2280</v>
+        <v>2626</v>
       </c>
       <c r="G334" s="2" t="s">
         <v>15</v>
@@ -14263,7 +14263,7 @@
         <v>14</v>
       </c>
       <c r="F335" s="2">
-        <v>1783</v>
+        <v>2114</v>
       </c>
       <c r="G335" s="2" t="s">
         <v>15</v>
@@ -14295,7 +14295,7 @@
         <v>14</v>
       </c>
       <c r="F336" s="2">
-        <v>3849</v>
+        <v>1031</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>15</v>
@@ -14327,7 +14327,7 @@
         <v>14</v>
       </c>
       <c r="F337" s="2">
-        <v>4175</v>
+        <v>3577</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>15</v>
@@ -14359,7 +14359,7 @@
         <v>14</v>
       </c>
       <c r="F338" s="2">
-        <v>1102</v>
+        <v>1912</v>
       </c>
       <c r="G338" s="2" t="s">
         <v>15</v>
@@ -14391,7 +14391,7 @@
         <v>14</v>
       </c>
       <c r="F339" s="2">
-        <v>4401</v>
+        <v>1857</v>
       </c>
       <c r="G339" s="2" t="s">
         <v>15</v>
@@ -14423,7 +14423,7 @@
         <v>14</v>
       </c>
       <c r="F340" s="2">
-        <v>1516</v>
+        <v>3878</v>
       </c>
       <c r="G340" s="2" t="s">
         <v>15</v>
@@ -14455,7 +14455,7 @@
         <v>14</v>
       </c>
       <c r="F341" s="2">
-        <v>1874</v>
+        <v>4734</v>
       </c>
       <c r="G341" s="2" t="s">
         <v>15</v>
@@ -14487,7 +14487,7 @@
         <v>14</v>
       </c>
       <c r="F342" s="2">
-        <v>4381</v>
+        <v>1033</v>
       </c>
       <c r="G342" s="2" t="s">
         <v>15</v>
@@ -14519,7 +14519,7 @@
         <v>14</v>
       </c>
       <c r="F343" s="2">
-        <v>4729</v>
+        <v>2572</v>
       </c>
       <c r="G343" s="2" t="s">
         <v>15</v>
@@ -14551,7 +14551,7 @@
         <v>14</v>
       </c>
       <c r="F344" s="2">
-        <v>3553</v>
+        <v>4519</v>
       </c>
       <c r="G344" s="2" t="s">
         <v>15</v>
@@ -14583,7 +14583,7 @@
         <v>14</v>
       </c>
       <c r="F345" s="2">
-        <v>1112</v>
+        <v>1204</v>
       </c>
       <c r="G345" s="2" t="s">
         <v>15</v>
@@ -14615,7 +14615,7 @@
         <v>14</v>
       </c>
       <c r="F346" s="2">
-        <v>3855</v>
+        <v>949</v>
       </c>
       <c r="G346" s="2" t="s">
         <v>15</v>
@@ -14647,7 +14647,7 @@
         <v>14</v>
       </c>
       <c r="F347" s="2">
-        <v>2902</v>
+        <v>3776</v>
       </c>
       <c r="G347" s="2" t="s">
         <v>15</v>
@@ -14679,7 +14679,7 @@
         <v>14</v>
       </c>
       <c r="F348" s="2">
-        <v>1095</v>
+        <v>4790</v>
       </c>
       <c r="G348" s="2" t="s">
         <v>15</v>
@@ -14711,7 +14711,7 @@
         <v>14</v>
       </c>
       <c r="F349" s="2">
-        <v>3587</v>
+        <v>4481</v>
       </c>
       <c r="G349" s="2" t="s">
         <v>15</v>
@@ -14743,7 +14743,7 @@
         <v>14</v>
       </c>
       <c r="F350" s="2">
-        <v>2294</v>
+        <v>2035</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>15</v>
@@ -14775,7 +14775,7 @@
         <v>14</v>
       </c>
       <c r="F351" s="2">
-        <v>2353</v>
+        <v>3276</v>
       </c>
       <c r="G351" s="2" t="s">
         <v>15</v>
@@ -14807,7 +14807,7 @@
         <v>14</v>
       </c>
       <c r="F352" s="2">
-        <v>3640</v>
+        <v>1925</v>
       </c>
       <c r="G352" s="2" t="s">
         <v>15</v>
@@ -14839,7 +14839,7 @@
         <v>14</v>
       </c>
       <c r="F353" s="2">
-        <v>3672</v>
+        <v>2434</v>
       </c>
       <c r="G353" s="2" t="s">
         <v>15</v>
@@ -14871,7 +14871,7 @@
         <v>14</v>
       </c>
       <c r="F354" s="2">
-        <v>2866</v>
+        <v>1577</v>
       </c>
       <c r="G354" s="2" t="s">
         <v>15</v>
@@ -14903,7 +14903,7 @@
         <v>14</v>
       </c>
       <c r="F355" s="2">
-        <v>4777</v>
+        <v>2803</v>
       </c>
       <c r="G355" s="2" t="s">
         <v>15</v>
@@ -14935,7 +14935,7 @@
         <v>14</v>
       </c>
       <c r="F356" s="2">
-        <v>3993</v>
+        <v>3019</v>
       </c>
       <c r="G356" s="2" t="s">
         <v>15</v>
@@ -14967,7 +14967,7 @@
         <v>14</v>
       </c>
       <c r="F357" s="2">
-        <v>932</v>
+        <v>1791</v>
       </c>
       <c r="G357" s="2" t="s">
         <v>15</v>
@@ -14999,7 +14999,7 @@
         <v>14</v>
       </c>
       <c r="F358" s="2">
-        <v>985</v>
+        <v>3160</v>
       </c>
       <c r="G358" s="2" t="s">
         <v>15</v>
@@ -15031,7 +15031,7 @@
         <v>14</v>
       </c>
       <c r="F359" s="2">
-        <v>3836</v>
+        <v>1158</v>
       </c>
       <c r="G359" s="2" t="s">
         <v>15</v>
@@ -15063,7 +15063,7 @@
         <v>14</v>
       </c>
       <c r="F360" s="2">
-        <v>3085</v>
+        <v>4266</v>
       </c>
       <c r="G360" s="2" t="s">
         <v>15</v>
@@ -15095,7 +15095,7 @@
         <v>14</v>
       </c>
       <c r="F361" s="2">
-        <v>2465</v>
+        <v>1078</v>
       </c>
       <c r="G361" s="2" t="s">
         <v>15</v>
@@ -15127,7 +15127,7 @@
         <v>14</v>
       </c>
       <c r="F362" s="2">
-        <v>2096</v>
+        <v>4561</v>
       </c>
       <c r="G362" s="2" t="s">
         <v>15</v>
@@ -15159,7 +15159,7 @@
         <v>14</v>
       </c>
       <c r="F363" s="2">
-        <v>1168</v>
+        <v>3240</v>
       </c>
       <c r="G363" s="2" t="s">
         <v>15</v>
@@ -15191,7 +15191,7 @@
         <v>14</v>
       </c>
       <c r="F364" s="2">
-        <v>4558</v>
+        <v>916</v>
       </c>
       <c r="G364" s="2" t="s">
         <v>15</v>
@@ -15223,7 +15223,7 @@
         <v>14</v>
       </c>
       <c r="F365" s="2">
-        <v>1487</v>
+        <v>2950</v>
       </c>
       <c r="G365" s="2" t="s">
         <v>15</v>
@@ -15255,7 +15255,7 @@
         <v>14</v>
       </c>
       <c r="F366" s="2">
-        <v>1011</v>
+        <v>3953</v>
       </c>
       <c r="G366" s="2" t="s">
         <v>15</v>
@@ -15287,7 +15287,7 @@
         <v>14</v>
       </c>
       <c r="F367" s="2">
-        <v>3882</v>
+        <v>1130</v>
       </c>
       <c r="G367" s="2" t="s">
         <v>15</v>
@@ -15319,7 +15319,7 @@
         <v>14</v>
       </c>
       <c r="F368" s="2">
-        <v>3010</v>
+        <v>1933</v>
       </c>
       <c r="G368" s="2" t="s">
         <v>15</v>
@@ -15351,7 +15351,7 @@
         <v>14</v>
       </c>
       <c r="F369" s="2">
-        <v>1328</v>
+        <v>4226</v>
       </c>
       <c r="G369" s="2" t="s">
         <v>15</v>
@@ -15383,7 +15383,7 @@
         <v>14</v>
       </c>
       <c r="F370" s="2">
-        <v>2958</v>
+        <v>1527</v>
       </c>
       <c r="G370" s="2" t="s">
         <v>15</v>
@@ -15415,7 +15415,7 @@
         <v>14</v>
       </c>
       <c r="F371" s="2">
-        <v>901</v>
+        <v>3905</v>
       </c>
       <c r="G371" s="2" t="s">
         <v>15</v>
@@ -15447,7 +15447,7 @@
         <v>14</v>
       </c>
       <c r="F372" s="2">
-        <v>3539</v>
+        <v>2707</v>
       </c>
       <c r="G372" s="2" t="s">
         <v>15</v>
@@ -15479,7 +15479,7 @@
         <v>14</v>
       </c>
       <c r="F373" s="2">
-        <v>2758</v>
+        <v>1148</v>
       </c>
       <c r="G373" s="2" t="s">
         <v>15</v>
@@ -15511,7 +15511,7 @@
         <v>14</v>
       </c>
       <c r="F374" s="2">
-        <v>3005</v>
+        <v>4668</v>
       </c>
       <c r="G374" s="2" t="s">
         <v>15</v>
@@ -15543,7 +15543,7 @@
         <v>14</v>
       </c>
       <c r="F375" s="2">
-        <v>4755</v>
+        <v>2035</v>
       </c>
       <c r="G375" s="2" t="s">
         <v>15</v>
@@ -15575,7 +15575,7 @@
         <v>14</v>
       </c>
       <c r="F376" s="2">
-        <v>2112</v>
+        <v>2211</v>
       </c>
       <c r="G376" s="2" t="s">
         <v>15</v>
@@ -15607,7 +15607,7 @@
         <v>14</v>
       </c>
       <c r="F377" s="2">
-        <v>2645</v>
+        <v>820</v>
       </c>
       <c r="G377" s="2" t="s">
         <v>15</v>
@@ -15639,7 +15639,7 @@
         <v>14</v>
       </c>
       <c r="F378" s="2">
-        <v>996</v>
+        <v>4217</v>
       </c>
       <c r="G378" s="2" t="s">
         <v>15</v>
@@ -15671,7 +15671,7 @@
         <v>14</v>
       </c>
       <c r="F379" s="2">
-        <v>1786</v>
+        <v>1336</v>
       </c>
       <c r="G379" s="2" t="s">
         <v>15</v>
@@ -15703,7 +15703,7 @@
         <v>14</v>
       </c>
       <c r="F380" s="2">
-        <v>2699</v>
+        <v>1602</v>
       </c>
       <c r="G380" s="2" t="s">
         <v>15</v>
@@ -15735,7 +15735,7 @@
         <v>14</v>
       </c>
       <c r="F381" s="2">
-        <v>1302</v>
+        <v>1575</v>
       </c>
       <c r="G381" s="2" t="s">
         <v>15</v>
@@ -15767,7 +15767,7 @@
         <v>14</v>
       </c>
       <c r="F382" s="2">
-        <v>1931</v>
+        <v>4248</v>
       </c>
       <c r="G382" s="2" t="s">
         <v>15</v>
@@ -15799,7 +15799,7 @@
         <v>14</v>
       </c>
       <c r="F383" s="2">
-        <v>4263</v>
+        <v>3630</v>
       </c>
       <c r="G383" s="2" t="s">
         <v>15</v>
@@ -15831,7 +15831,7 @@
         <v>14</v>
       </c>
       <c r="F384" s="2">
-        <v>3284</v>
+        <v>805</v>
       </c>
       <c r="G384" s="2" t="s">
         <v>15</v>
@@ -15863,7 +15863,7 @@
         <v>14</v>
       </c>
       <c r="F385" s="2">
-        <v>4677</v>
+        <v>2828</v>
       </c>
       <c r="G385" s="2" t="s">
         <v>15</v>
@@ -15895,7 +15895,7 @@
         <v>14</v>
       </c>
       <c r="F386" s="2">
-        <v>1576</v>
+        <v>2684</v>
       </c>
       <c r="G386" s="2" t="s">
         <v>15</v>
@@ -15927,7 +15927,7 @@
         <v>14</v>
       </c>
       <c r="F387" s="2">
-        <v>1599</v>
+        <v>3711</v>
       </c>
       <c r="G387" s="2" t="s">
         <v>15</v>
@@ -15959,7 +15959,7 @@
         <v>14</v>
       </c>
       <c r="F388" s="2">
-        <v>3992</v>
+        <v>3359</v>
       </c>
       <c r="G388" s="2" t="s">
         <v>15</v>
@@ -15991,7 +15991,7 @@
         <v>14</v>
       </c>
       <c r="F389" s="2">
-        <v>1328</v>
+        <v>4241</v>
       </c>
       <c r="G389" s="2" t="s">
         <v>15</v>
@@ -16023,7 +16023,7 @@
         <v>14</v>
       </c>
       <c r="F390" s="2">
-        <v>3471</v>
+        <v>1721</v>
       </c>
       <c r="G390" s="2" t="s">
         <v>15</v>
@@ -16055,7 +16055,7 @@
         <v>14</v>
       </c>
       <c r="F391" s="2">
-        <v>1270</v>
+        <v>1652</v>
       </c>
       <c r="G391" s="2" t="s">
         <v>15</v>
@@ -16087,7 +16087,7 @@
         <v>14</v>
       </c>
       <c r="F392" s="2">
-        <v>1582</v>
+        <v>3886</v>
       </c>
       <c r="G392" s="2" t="s">
         <v>15</v>
@@ -16119,7 +16119,7 @@
         <v>14</v>
       </c>
       <c r="F393" s="2">
-        <v>4522</v>
+        <v>3144</v>
       </c>
       <c r="G393" s="2" t="s">
         <v>15</v>
@@ -16151,7 +16151,7 @@
         <v>14</v>
       </c>
       <c r="F394" s="2">
-        <v>1236</v>
+        <v>1648</v>
       </c>
       <c r="G394" s="2" t="s">
         <v>15</v>
@@ -16183,7 +16183,7 @@
         <v>14</v>
       </c>
       <c r="F395" s="2">
-        <v>1493</v>
+        <v>4796</v>
       </c>
       <c r="G395" s="2" t="s">
         <v>15</v>
@@ -16215,7 +16215,7 @@
         <v>14</v>
       </c>
       <c r="F396" s="2">
-        <v>3975</v>
+        <v>3486</v>
       </c>
       <c r="G396" s="2" t="s">
         <v>15</v>
@@ -16247,7 +16247,7 @@
         <v>14</v>
       </c>
       <c r="F397" s="2">
-        <v>1558</v>
+        <v>4435</v>
       </c>
       <c r="G397" s="2" t="s">
         <v>15</v>
@@ -16279,7 +16279,7 @@
         <v>14</v>
       </c>
       <c r="F398" s="2">
-        <v>2726</v>
+        <v>2397</v>
       </c>
       <c r="G398" s="2" t="s">
         <v>15</v>
@@ -16311,7 +16311,7 @@
         <v>14</v>
       </c>
       <c r="F399" s="2">
-        <v>1875</v>
+        <v>1939</v>
       </c>
       <c r="G399" s="2" t="s">
         <v>15</v>
@@ -16343,7 +16343,7 @@
         <v>14</v>
       </c>
       <c r="F400" s="2">
-        <v>880</v>
+        <v>4568</v>
       </c>
       <c r="G400" s="2" t="s">
         <v>15</v>
@@ -16375,7 +16375,7 @@
         <v>14</v>
       </c>
       <c r="F401" s="2">
-        <v>4647</v>
+        <v>4609</v>
       </c>
       <c r="G401" s="2" t="s">
         <v>15</v>
@@ -16407,7 +16407,7 @@
         <v>14</v>
       </c>
       <c r="F402" s="2">
-        <v>3028</v>
+        <v>4618</v>
       </c>
       <c r="G402" s="2" t="s">
         <v>15</v>
@@ -16439,7 +16439,7 @@
         <v>14</v>
       </c>
       <c r="F403" s="2">
-        <v>2676</v>
+        <v>3622</v>
       </c>
       <c r="G403" s="2" t="s">
         <v>15</v>
@@ -16471,7 +16471,7 @@
         <v>14</v>
       </c>
       <c r="F404" s="2">
-        <v>990</v>
+        <v>2977</v>
       </c>
       <c r="G404" s="2" t="s">
         <v>15</v>
@@ -16503,7 +16503,7 @@
         <v>14</v>
       </c>
       <c r="F405" s="2">
-        <v>4679</v>
+        <v>2658</v>
       </c>
       <c r="G405" s="2" t="s">
         <v>15</v>
@@ -16535,7 +16535,7 @@
         <v>14</v>
       </c>
       <c r="F406" s="2">
-        <v>4110</v>
+        <v>2247</v>
       </c>
       <c r="G406" s="2" t="s">
         <v>15</v>
@@ -16567,7 +16567,7 @@
         <v>14</v>
       </c>
       <c r="F407" s="2">
-        <v>1085</v>
+        <v>3725</v>
       </c>
       <c r="G407" s="2" t="s">
         <v>15</v>
@@ -16599,7 +16599,7 @@
         <v>14</v>
       </c>
       <c r="F408" s="2">
-        <v>3761</v>
+        <v>4060</v>
       </c>
       <c r="G408" s="2" t="s">
         <v>15</v>
@@ -16631,7 +16631,7 @@
         <v>14</v>
       </c>
       <c r="F409" s="2">
-        <v>1164</v>
+        <v>1351</v>
       </c>
       <c r="G409" s="2" t="s">
         <v>15</v>
@@ -16663,7 +16663,7 @@
         <v>14</v>
       </c>
       <c r="F410" s="2">
-        <v>3649</v>
+        <v>3136</v>
       </c>
       <c r="G410" s="2" t="s">
         <v>15</v>
@@ -16695,7 +16695,7 @@
         <v>14</v>
       </c>
       <c r="F411" s="2">
-        <v>1997</v>
+        <v>3957</v>
       </c>
       <c r="G411" s="2" t="s">
         <v>15</v>
@@ -16727,7 +16727,7 @@
         <v>14</v>
       </c>
       <c r="F412" s="2">
-        <v>2072</v>
+        <v>1766</v>
       </c>
       <c r="G412" s="2" t="s">
         <v>15</v>
@@ -16759,7 +16759,7 @@
         <v>14</v>
       </c>
       <c r="F413" s="2">
-        <v>3226</v>
+        <v>3467</v>
       </c>
       <c r="G413" s="2" t="s">
         <v>15</v>
@@ -16791,7 +16791,7 @@
         <v>14</v>
       </c>
       <c r="F414" s="2">
-        <v>3758</v>
+        <v>2209</v>
       </c>
       <c r="G414" s="2" t="s">
         <v>15</v>
@@ -16823,7 +16823,7 @@
         <v>14</v>
       </c>
       <c r="F415" s="2">
-        <v>2552</v>
+        <v>3576</v>
       </c>
       <c r="G415" s="2" t="s">
         <v>15</v>
@@ -16855,7 +16855,7 @@
         <v>14</v>
       </c>
       <c r="F416" s="2">
-        <v>4136</v>
+        <v>1586</v>
       </c>
       <c r="G416" s="2" t="s">
         <v>15</v>
@@ -16887,7 +16887,7 @@
         <v>14</v>
       </c>
       <c r="F417" s="2">
-        <v>2681</v>
+        <v>4717</v>
       </c>
       <c r="G417" s="2" t="s">
         <v>15</v>
@@ -16919,7 +16919,7 @@
         <v>14</v>
       </c>
       <c r="F418" s="2">
-        <v>4032</v>
+        <v>4756</v>
       </c>
       <c r="G418" s="2" t="s">
         <v>15</v>
@@ -16951,7 +16951,7 @@
         <v>14</v>
       </c>
       <c r="F419" s="2">
-        <v>2766</v>
+        <v>4547</v>
       </c>
       <c r="G419" s="2" t="s">
         <v>15</v>
@@ -16983,7 +16983,7 @@
         <v>14</v>
       </c>
       <c r="F420" s="2">
-        <v>2832</v>
+        <v>4223</v>
       </c>
       <c r="G420" s="2" t="s">
         <v>15</v>
@@ -17015,7 +17015,7 @@
         <v>14</v>
       </c>
       <c r="F421" s="2">
-        <v>1211</v>
+        <v>3222</v>
       </c>
       <c r="G421" s="2" t="s">
         <v>15</v>
@@ -17047,7 +17047,7 @@
         <v>14</v>
       </c>
       <c r="F422" s="2">
-        <v>4033</v>
+        <v>2911</v>
       </c>
       <c r="G422" s="2" t="s">
         <v>15</v>
@@ -17079,7 +17079,7 @@
         <v>14</v>
       </c>
       <c r="F423" s="2">
-        <v>1074</v>
+        <v>3390</v>
       </c>
       <c r="G423" s="2" t="s">
         <v>15</v>
@@ -17111,7 +17111,7 @@
         <v>14</v>
       </c>
       <c r="F424" s="2">
-        <v>2292</v>
+        <v>4514</v>
       </c>
       <c r="G424" s="2" t="s">
         <v>15</v>
@@ -17143,7 +17143,7 @@
         <v>14</v>
       </c>
       <c r="F425" s="2">
-        <v>1285</v>
+        <v>3770</v>
       </c>
       <c r="G425" s="2" t="s">
         <v>15</v>
@@ -17175,7 +17175,7 @@
         <v>14</v>
       </c>
       <c r="F426" s="2">
-        <v>3517</v>
+        <v>4719</v>
       </c>
       <c r="G426" s="2" t="s">
         <v>15</v>
@@ -17207,7 +17207,7 @@
         <v>14</v>
       </c>
       <c r="F427" s="2">
-        <v>4108</v>
+        <v>1011</v>
       </c>
       <c r="G427" s="2" t="s">
         <v>15</v>
@@ -17239,7 +17239,7 @@
         <v>14</v>
       </c>
       <c r="F428" s="2">
-        <v>2722</v>
+        <v>2536</v>
       </c>
       <c r="G428" s="2" t="s">
         <v>15</v>
@@ -17271,7 +17271,7 @@
         <v>14</v>
       </c>
       <c r="F429" s="2">
-        <v>2391</v>
+        <v>3936</v>
       </c>
       <c r="G429" s="2" t="s">
         <v>15</v>
@@ -17303,7 +17303,7 @@
         <v>14</v>
       </c>
       <c r="F430" s="2">
-        <v>3521</v>
+        <v>1719</v>
       </c>
       <c r="G430" s="2" t="s">
         <v>15</v>
@@ -17335,7 +17335,7 @@
         <v>14</v>
       </c>
       <c r="F431" s="2">
-        <v>3952</v>
+        <v>2272</v>
       </c>
       <c r="G431" s="2" t="s">
         <v>15</v>
@@ -17367,7 +17367,7 @@
         <v>14</v>
       </c>
       <c r="F432" s="2">
-        <v>4083</v>
+        <v>1567</v>
       </c>
       <c r="G432" s="2" t="s">
         <v>15</v>
@@ -17399,7 +17399,7 @@
         <v>14</v>
       </c>
       <c r="F433" s="2">
-        <v>3442</v>
+        <v>3917</v>
       </c>
       <c r="G433" s="2" t="s">
         <v>15</v>
@@ -17431,7 +17431,7 @@
         <v>14</v>
       </c>
       <c r="F434" s="2">
-        <v>2922</v>
+        <v>855</v>
       </c>
       <c r="G434" s="2" t="s">
         <v>15</v>
@@ -17463,7 +17463,7 @@
         <v>14</v>
       </c>
       <c r="F435" s="2">
-        <v>2540</v>
+        <v>1548</v>
       </c>
       <c r="G435" s="2" t="s">
         <v>15</v>
@@ -17495,7 +17495,7 @@
         <v>14</v>
       </c>
       <c r="F436" s="2">
-        <v>3988</v>
+        <v>1708</v>
       </c>
       <c r="G436" s="2" t="s">
         <v>15</v>
@@ -17527,7 +17527,7 @@
         <v>14</v>
       </c>
       <c r="F437" s="2">
-        <v>2379</v>
+        <v>3791</v>
       </c>
       <c r="G437" s="2" t="s">
         <v>15</v>
@@ -17559,7 +17559,7 @@
         <v>14</v>
       </c>
       <c r="F438" s="2">
-        <v>3032</v>
+        <v>1162</v>
       </c>
       <c r="G438" s="2" t="s">
         <v>15</v>
@@ -17591,7 +17591,7 @@
         <v>14</v>
       </c>
       <c r="F439" s="2">
-        <v>3176</v>
+        <v>1427</v>
       </c>
       <c r="G439" s="2" t="s">
         <v>15</v>
@@ -17623,7 +17623,7 @@
         <v>14</v>
       </c>
       <c r="F440" s="2">
-        <v>3795</v>
+        <v>4183</v>
       </c>
       <c r="G440" s="2" t="s">
         <v>15</v>
@@ -17655,7 +17655,7 @@
         <v>14</v>
       </c>
       <c r="F441" s="2">
-        <v>3443</v>
+        <v>1958</v>
       </c>
       <c r="G441" s="2" t="s">
         <v>15</v>
@@ -17687,7 +17687,7 @@
         <v>14</v>
       </c>
       <c r="F442" s="2">
-        <v>2605</v>
+        <v>1970</v>
       </c>
       <c r="G442" s="2" t="s">
         <v>15</v>
@@ -17719,7 +17719,7 @@
         <v>14</v>
       </c>
       <c r="F443" s="2">
-        <v>3369</v>
+        <v>4057</v>
       </c>
       <c r="G443" s="2" t="s">
         <v>15</v>
@@ -17751,7 +17751,7 @@
         <v>14</v>
       </c>
       <c r="F444" s="2">
-        <v>4702</v>
+        <v>1268</v>
       </c>
       <c r="G444" s="2" t="s">
         <v>15</v>
@@ -17783,7 +17783,7 @@
         <v>14</v>
       </c>
       <c r="F445" s="2">
-        <v>1767</v>
+        <v>1348</v>
       </c>
       <c r="G445" s="2" t="s">
         <v>15</v>
@@ -17815,7 +17815,7 @@
         <v>14</v>
       </c>
       <c r="F446" s="2">
-        <v>1614</v>
+        <v>1294</v>
       </c>
       <c r="G446" s="2" t="s">
         <v>15</v>
@@ -17847,7 +17847,7 @@
         <v>14</v>
       </c>
       <c r="F447" s="2">
-        <v>3406</v>
+        <v>3173</v>
       </c>
       <c r="G447" s="2" t="s">
         <v>15</v>
@@ -17879,7 +17879,7 @@
         <v>14</v>
       </c>
       <c r="F448" s="2">
-        <v>2220</v>
+        <v>2994</v>
       </c>
       <c r="G448" s="2" t="s">
         <v>15</v>
@@ -17911,7 +17911,7 @@
         <v>14</v>
       </c>
       <c r="F449" s="2">
-        <v>4767</v>
+        <v>2110</v>
       </c>
       <c r="G449" s="2" t="s">
         <v>15</v>
@@ -17943,7 +17943,7 @@
         <v>14</v>
       </c>
       <c r="F450" s="2">
-        <v>2164</v>
+        <v>1997</v>
       </c>
       <c r="G450" s="2" t="s">
         <v>15</v>
@@ -17975,7 +17975,7 @@
         <v>14</v>
       </c>
       <c r="F451" s="2">
-        <v>1956</v>
+        <v>3126</v>
       </c>
       <c r="G451" s="2" t="s">
         <v>15</v>
@@ -18007,7 +18007,7 @@
         <v>14</v>
       </c>
       <c r="F452" s="2">
-        <v>2927</v>
+        <v>2191</v>
       </c>
       <c r="G452" s="2" t="s">
         <v>15</v>
@@ -18039,7 +18039,7 @@
         <v>14</v>
       </c>
       <c r="F453" s="2">
-        <v>3916</v>
+        <v>2169</v>
       </c>
       <c r="G453" s="2" t="s">
         <v>15</v>
@@ -18071,7 +18071,7 @@
         <v>14</v>
       </c>
       <c r="F454" s="2">
-        <v>2357</v>
+        <v>4581</v>
       </c>
       <c r="G454" s="2" t="s">
         <v>15</v>
@@ -18103,7 +18103,7 @@
         <v>14</v>
       </c>
       <c r="F455" s="2">
-        <v>2914</v>
+        <v>3311</v>
       </c>
       <c r="G455" s="2" t="s">
         <v>15</v>
@@ -18135,7 +18135,7 @@
         <v>14</v>
       </c>
       <c r="F456" s="2">
-        <v>825</v>
+        <v>2417</v>
       </c>
       <c r="G456" s="2" t="s">
         <v>15</v>
@@ -18167,7 +18167,7 @@
         <v>14</v>
       </c>
       <c r="F457" s="2">
-        <v>1491</v>
+        <v>3618</v>
       </c>
       <c r="G457" s="2" t="s">
         <v>15</v>
@@ -18199,7 +18199,7 @@
         <v>14</v>
       </c>
       <c r="F458" s="2">
-        <v>867</v>
+        <v>815</v>
       </c>
       <c r="G458" s="2" t="s">
         <v>15</v>
@@ -18231,7 +18231,7 @@
         <v>14</v>
       </c>
       <c r="F459" s="2">
-        <v>2884</v>
+        <v>3526</v>
       </c>
       <c r="G459" s="2" t="s">
         <v>15</v>
@@ -18263,7 +18263,7 @@
         <v>14</v>
       </c>
       <c r="F460" s="2">
-        <v>1735</v>
+        <v>3579</v>
       </c>
       <c r="G460" s="2" t="s">
         <v>15</v>
@@ -18295,7 +18295,7 @@
         <v>14</v>
       </c>
       <c r="F461" s="2">
-        <v>931</v>
+        <v>3860</v>
       </c>
       <c r="G461" s="2" t="s">
         <v>15</v>
@@ -18327,7 +18327,7 @@
         <v>14</v>
       </c>
       <c r="F462" s="2">
-        <v>3658</v>
+        <v>3850</v>
       </c>
       <c r="G462" s="2" t="s">
         <v>15</v>
@@ -18359,7 +18359,7 @@
         <v>14</v>
       </c>
       <c r="F463" s="2">
-        <v>4732</v>
+        <v>1277</v>
       </c>
       <c r="G463" s="2" t="s">
         <v>15</v>
@@ -18391,7 +18391,7 @@
         <v>14</v>
       </c>
       <c r="F464" s="2">
-        <v>4411</v>
+        <v>1509</v>
       </c>
       <c r="G464" s="2" t="s">
         <v>15</v>
@@ -18423,7 +18423,7 @@
         <v>14</v>
       </c>
       <c r="F465" s="2">
-        <v>4170</v>
+        <v>4216</v>
       </c>
       <c r="G465" s="2" t="s">
         <v>15</v>
@@ -18455,7 +18455,7 @@
         <v>14</v>
       </c>
       <c r="F466" s="2">
-        <v>2958</v>
+        <v>820</v>
       </c>
       <c r="G466" s="2" t="s">
         <v>15</v>
@@ -18487,7 +18487,7 @@
         <v>14</v>
       </c>
       <c r="F467" s="2">
-        <v>1615</v>
+        <v>3194</v>
       </c>
       <c r="G467" s="2" t="s">
         <v>15</v>
@@ -18519,7 +18519,7 @@
         <v>14</v>
       </c>
       <c r="F468" s="2">
-        <v>2441</v>
+        <v>4725</v>
       </c>
       <c r="G468" s="2" t="s">
         <v>15</v>
@@ -18551,7 +18551,7 @@
         <v>14</v>
       </c>
       <c r="F469" s="2">
-        <v>3483</v>
+        <v>1521</v>
       </c>
       <c r="G469" s="2" t="s">
         <v>15</v>
@@ -18583,7 +18583,7 @@
         <v>14</v>
       </c>
       <c r="F470" s="2">
-        <v>1685</v>
+        <v>2906</v>
       </c>
       <c r="G470" s="2" t="s">
         <v>15</v>
@@ -18615,7 +18615,7 @@
         <v>14</v>
       </c>
       <c r="F471" s="2">
-        <v>2762</v>
+        <v>3588</v>
       </c>
       <c r="G471" s="2" t="s">
         <v>15</v>
@@ -18702,7 +18702,7 @@
         <v>14</v>
       </c>
       <c r="F2" s="2">
-        <v>1410</v>
+        <v>2571</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>15</v>
@@ -18734,7 +18734,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="2">
-        <v>2568</v>
+        <v>4035</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>15</v>
@@ -18766,7 +18766,7 @@
         <v>14</v>
       </c>
       <c r="F4" s="2">
-        <v>2061</v>
+        <v>4448</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
@@ -18798,7 +18798,7 @@
         <v>14</v>
       </c>
       <c r="F5" s="2">
-        <v>1006</v>
+        <v>4189</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
@@ -18830,7 +18830,7 @@
         <v>14</v>
       </c>
       <c r="F6" s="2">
-        <v>1407</v>
+        <v>1262</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -18862,7 +18862,7 @@
         <v>14</v>
       </c>
       <c r="F7" s="2">
-        <v>3043</v>
+        <v>4074</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -18894,7 +18894,7 @@
         <v>14</v>
       </c>
       <c r="F8" s="2">
-        <v>3101</v>
+        <v>3659</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -18926,7 +18926,7 @@
         <v>14</v>
       </c>
       <c r="F9" s="2">
-        <v>4731</v>
+        <v>3314</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -18958,7 +18958,7 @@
         <v>14</v>
       </c>
       <c r="F10" s="2">
-        <v>2421</v>
+        <v>3168</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
@@ -18990,7 +18990,7 @@
         <v>14</v>
       </c>
       <c r="F11" s="2">
-        <v>1090</v>
+        <v>2537</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
@@ -19022,7 +19022,7 @@
         <v>14</v>
       </c>
       <c r="F12" s="2">
-        <v>1528</v>
+        <v>1095</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
@@ -19054,7 +19054,7 @@
         <v>14</v>
       </c>
       <c r="F13" s="2">
-        <v>3680</v>
+        <v>3236</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -19086,7 +19086,7 @@
         <v>14</v>
       </c>
       <c r="F14" s="2">
-        <v>875</v>
+        <v>3381</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -19118,7 +19118,7 @@
         <v>14</v>
       </c>
       <c r="F15" s="2">
-        <v>2932</v>
+        <v>2503</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -19150,7 +19150,7 @@
         <v>14</v>
       </c>
       <c r="F16" s="2">
-        <v>3362</v>
+        <v>2313</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
@@ -19182,7 +19182,7 @@
         <v>14</v>
       </c>
       <c r="F17" s="2">
-        <v>4552</v>
+        <v>4287</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
@@ -19214,7 +19214,7 @@
         <v>14</v>
       </c>
       <c r="F18" s="2">
-        <v>1353</v>
+        <v>1738</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
@@ -19246,7 +19246,7 @@
         <v>14</v>
       </c>
       <c r="F19" s="2">
-        <v>2798</v>
+        <v>2023</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
@@ -19278,7 +19278,7 @@
         <v>14</v>
       </c>
       <c r="F20" s="2">
-        <v>2479</v>
+        <v>3168</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
@@ -19310,7 +19310,7 @@
         <v>14</v>
       </c>
       <c r="F21" s="2">
-        <v>4771</v>
+        <v>2611</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -19342,7 +19342,7 @@
         <v>14</v>
       </c>
       <c r="F22" s="2">
-        <v>919</v>
+        <v>4371</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -19374,7 +19374,7 @@
         <v>14</v>
       </c>
       <c r="F23" s="2">
-        <v>2857</v>
+        <v>810</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -19406,7 +19406,7 @@
         <v>14</v>
       </c>
       <c r="F24" s="2">
-        <v>4482</v>
+        <v>1467</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -19438,7 +19438,7 @@
         <v>14</v>
       </c>
       <c r="F25" s="2">
-        <v>1199</v>
+        <v>3921</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -19470,7 +19470,7 @@
         <v>14</v>
       </c>
       <c r="F26" s="2">
-        <v>1797</v>
+        <v>2816</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -19502,7 +19502,7 @@
         <v>14</v>
       </c>
       <c r="F27" s="2">
-        <v>3818</v>
+        <v>3101</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>15</v>
@@ -19534,7 +19534,7 @@
         <v>14</v>
       </c>
       <c r="F28" s="2">
-        <v>1624</v>
+        <v>1789</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>15</v>
@@ -19566,7 +19566,7 @@
         <v>14</v>
       </c>
       <c r="F29" s="2">
-        <v>3847</v>
+        <v>2816</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>15</v>
@@ -19598,7 +19598,7 @@
         <v>14</v>
       </c>
       <c r="F30" s="2">
-        <v>3120</v>
+        <v>1257</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>15</v>
@@ -19630,7 +19630,7 @@
         <v>14</v>
       </c>
       <c r="F31" s="2">
-        <v>3823</v>
+        <v>1809</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>15</v>
@@ -19662,7 +19662,7 @@
         <v>14</v>
       </c>
       <c r="F32" s="2">
-        <v>4104</v>
+        <v>921</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>15</v>
@@ -19694,7 +19694,7 @@
         <v>14</v>
       </c>
       <c r="F33" s="2">
-        <v>2120</v>
+        <v>3286</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>15</v>
@@ -19726,7 +19726,7 @@
         <v>14</v>
       </c>
       <c r="F34" s="2">
-        <v>3997</v>
+        <v>2359</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>15</v>
@@ -19758,7 +19758,7 @@
         <v>14</v>
       </c>
       <c r="F35" s="2">
-        <v>3831</v>
+        <v>2399</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>15</v>
@@ -19790,7 +19790,7 @@
         <v>14</v>
       </c>
       <c r="F36" s="2">
-        <v>2020</v>
+        <v>919</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>15</v>
@@ -19822,7 +19822,7 @@
         <v>14</v>
       </c>
       <c r="F37" s="2">
-        <v>929</v>
+        <v>2222</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>15</v>
@@ -19854,7 +19854,7 @@
         <v>14</v>
       </c>
       <c r="F38" s="2">
-        <v>4216</v>
+        <v>4126</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>15</v>
@@ -19886,7 +19886,7 @@
         <v>14</v>
       </c>
       <c r="F39" s="2">
-        <v>963</v>
+        <v>1770</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>15</v>
@@ -19918,7 +19918,7 @@
         <v>14</v>
       </c>
       <c r="F40" s="2">
-        <v>4559</v>
+        <v>4745</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>15</v>
@@ -19950,7 +19950,7 @@
         <v>14</v>
       </c>
       <c r="F41" s="2">
-        <v>2751</v>
+        <v>939</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>15</v>
@@ -19982,7 +19982,7 @@
         <v>14</v>
       </c>
       <c r="F42" s="2">
-        <v>1717</v>
+        <v>2217</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>15</v>
@@ -20014,7 +20014,7 @@
         <v>14</v>
       </c>
       <c r="F43" s="2">
-        <v>3906</v>
+        <v>2056</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>15</v>
@@ -20046,7 +20046,7 @@
         <v>14</v>
       </c>
       <c r="F44" s="2">
-        <v>3902</v>
+        <v>4353</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>15</v>
@@ -20078,7 +20078,7 @@
         <v>14</v>
       </c>
       <c r="F45" s="2">
-        <v>1999</v>
+        <v>4046</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>15</v>
@@ -20110,7 +20110,7 @@
         <v>14</v>
       </c>
       <c r="F46" s="2">
-        <v>3922</v>
+        <v>2187</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>15</v>
@@ -20142,7 +20142,7 @@
         <v>14</v>
       </c>
       <c r="F47" s="2">
-        <v>957</v>
+        <v>1764</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>15</v>
@@ -20174,7 +20174,7 @@
         <v>14</v>
       </c>
       <c r="F48" s="2">
-        <v>1646</v>
+        <v>4569</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>15</v>
@@ -20206,7 +20206,7 @@
         <v>14</v>
       </c>
       <c r="F49" s="2">
-        <v>4151</v>
+        <v>1631</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>15</v>
@@ -20238,7 +20238,7 @@
         <v>14</v>
       </c>
       <c r="F50" s="2">
-        <v>1006</v>
+        <v>2235</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>15</v>
@@ -20270,7 +20270,7 @@
         <v>14</v>
       </c>
       <c r="F51" s="2">
-        <v>3542</v>
+        <v>3622</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>15</v>
@@ -20302,7 +20302,7 @@
         <v>14</v>
       </c>
       <c r="F52" s="2">
-        <v>2125</v>
+        <v>1594</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>15</v>
@@ -20334,7 +20334,7 @@
         <v>14</v>
       </c>
       <c r="F53" s="2">
-        <v>3601</v>
+        <v>4166</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>15</v>
@@ -20366,7 +20366,7 @@
         <v>14</v>
       </c>
       <c r="F54" s="2">
-        <v>1221</v>
+        <v>2321</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>15</v>
@@ -20398,7 +20398,7 @@
         <v>14</v>
       </c>
       <c r="F55" s="2">
-        <v>849</v>
+        <v>2661</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>15</v>
@@ -20430,7 +20430,7 @@
         <v>14</v>
       </c>
       <c r="F56" s="2">
-        <v>1093</v>
+        <v>1348</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>15</v>
@@ -20462,7 +20462,7 @@
         <v>14</v>
       </c>
       <c r="F57" s="2">
-        <v>4635</v>
+        <v>3186</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>15</v>
@@ -20494,7 +20494,7 @@
         <v>14</v>
       </c>
       <c r="F58" s="2">
-        <v>1880</v>
+        <v>4447</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>15</v>
@@ -20526,7 +20526,7 @@
         <v>14</v>
       </c>
       <c r="F59" s="2">
-        <v>4763</v>
+        <v>3327</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>15</v>
@@ -20558,7 +20558,7 @@
         <v>14</v>
       </c>
       <c r="F60" s="2">
-        <v>4396</v>
+        <v>927</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>15</v>
@@ -20590,7 +20590,7 @@
         <v>14</v>
       </c>
       <c r="F61" s="2">
-        <v>1408</v>
+        <v>1624</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>15</v>
@@ -20622,7 +20622,7 @@
         <v>14</v>
       </c>
       <c r="F62" s="2">
-        <v>1750</v>
+        <v>1855</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>15</v>
@@ -20654,7 +20654,7 @@
         <v>14</v>
       </c>
       <c r="F63" s="2">
-        <v>2831</v>
+        <v>2658</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>15</v>
@@ -20686,7 +20686,7 @@
         <v>14</v>
       </c>
       <c r="F64" s="2">
-        <v>2474</v>
+        <v>2376</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>15</v>
@@ -20718,7 +20718,7 @@
         <v>14</v>
       </c>
       <c r="F65" s="2">
-        <v>3741</v>
+        <v>4238</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>15</v>
@@ -20750,7 +20750,7 @@
         <v>14</v>
       </c>
       <c r="F66" s="2">
-        <v>870</v>
+        <v>3593</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>15</v>
@@ -20782,7 +20782,7 @@
         <v>14</v>
       </c>
       <c r="F67" s="2">
-        <v>881</v>
+        <v>1934</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>15</v>
@@ -20814,7 +20814,7 @@
         <v>14</v>
       </c>
       <c r="F68" s="2">
-        <v>3836</v>
+        <v>1148</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>15</v>
@@ -20846,7 +20846,7 @@
         <v>14</v>
       </c>
       <c r="F69" s="2">
-        <v>947</v>
+        <v>2832</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>15</v>
@@ -20878,7 +20878,7 @@
         <v>14</v>
       </c>
       <c r="F70" s="2">
-        <v>2520</v>
+        <v>4185</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>15</v>
@@ -20910,7 +20910,7 @@
         <v>14</v>
       </c>
       <c r="F71" s="2">
-        <v>802</v>
+        <v>3100</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>15</v>
@@ -20942,7 +20942,7 @@
         <v>14</v>
       </c>
       <c r="F72" s="2">
-        <v>1896</v>
+        <v>1351</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>15</v>
@@ -20974,7 +20974,7 @@
         <v>14</v>
       </c>
       <c r="F73" s="2">
-        <v>2299</v>
+        <v>3018</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>15</v>
@@ -21006,7 +21006,7 @@
         <v>14</v>
       </c>
       <c r="F74" s="2">
-        <v>3349</v>
+        <v>1656</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>15</v>
@@ -21038,7 +21038,7 @@
         <v>14</v>
       </c>
       <c r="F75" s="2">
-        <v>2722</v>
+        <v>2834</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>15</v>
@@ -21070,7 +21070,7 @@
         <v>14</v>
       </c>
       <c r="F76" s="2">
-        <v>2271</v>
+        <v>4693</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>15</v>
@@ -21102,7 +21102,7 @@
         <v>14</v>
       </c>
       <c r="F77" s="2">
-        <v>3728</v>
+        <v>2651</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>15</v>
@@ -21134,7 +21134,7 @@
         <v>14</v>
       </c>
       <c r="F78" s="2">
-        <v>4793</v>
+        <v>1256</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>15</v>
@@ -21166,7 +21166,7 @@
         <v>14</v>
       </c>
       <c r="F79" s="2">
-        <v>1799</v>
+        <v>969</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>15</v>
@@ -21198,7 +21198,7 @@
         <v>14</v>
       </c>
       <c r="F80" s="2">
-        <v>4067</v>
+        <v>3750</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>15</v>
@@ -21230,7 +21230,7 @@
         <v>14</v>
       </c>
       <c r="F81" s="2">
-        <v>4595</v>
+        <v>3680</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>15</v>
@@ -21262,7 +21262,7 @@
         <v>14</v>
       </c>
       <c r="F82" s="2">
-        <v>3797</v>
+        <v>2527</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>15</v>
@@ -21294,7 +21294,7 @@
         <v>14</v>
       </c>
       <c r="F83" s="2">
-        <v>1604</v>
+        <v>2710</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>15</v>
@@ -21326,7 +21326,7 @@
         <v>14</v>
       </c>
       <c r="F84" s="2">
-        <v>4449</v>
+        <v>3519</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>15</v>
@@ -21358,7 +21358,7 @@
         <v>14</v>
       </c>
       <c r="F85" s="2">
-        <v>2248</v>
+        <v>1319</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>15</v>
@@ -21390,7 +21390,7 @@
         <v>14</v>
       </c>
       <c r="F86" s="2">
-        <v>2680</v>
+        <v>3286</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>15</v>
@@ -21422,7 +21422,7 @@
         <v>14</v>
       </c>
       <c r="F87" s="2">
-        <v>4120</v>
+        <v>1263</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>15</v>
@@ -21454,7 +21454,7 @@
         <v>14</v>
       </c>
       <c r="F88" s="2">
-        <v>3876</v>
+        <v>3476</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>15</v>
@@ -21486,7 +21486,7 @@
         <v>14</v>
       </c>
       <c r="F89" s="2">
-        <v>3388</v>
+        <v>2448</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>15</v>
@@ -21518,7 +21518,7 @@
         <v>14</v>
       </c>
       <c r="F90" s="2">
-        <v>4069</v>
+        <v>2859</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>15</v>
@@ -21550,7 +21550,7 @@
         <v>14</v>
       </c>
       <c r="F91" s="2">
-        <v>4798</v>
+        <v>4700</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>15</v>
@@ -21582,7 +21582,7 @@
         <v>14</v>
       </c>
       <c r="F92" s="2">
-        <v>2721</v>
+        <v>4739</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>15</v>
@@ -21614,7 +21614,7 @@
         <v>14</v>
       </c>
       <c r="F93" s="2">
-        <v>4198</v>
+        <v>3696</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>15</v>
@@ -21646,7 +21646,7 @@
         <v>14</v>
       </c>
       <c r="F94" s="2">
-        <v>4093</v>
+        <v>1789</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>15</v>
@@ -21678,7 +21678,7 @@
         <v>14</v>
       </c>
       <c r="F95" s="2">
-        <v>3415</v>
+        <v>1544</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>15</v>
@@ -21710,7 +21710,7 @@
         <v>14</v>
       </c>
       <c r="F96" s="2">
-        <v>3917</v>
+        <v>1619</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>15</v>
@@ -21742,7 +21742,7 @@
         <v>14</v>
       </c>
       <c r="F97" s="2">
-        <v>4376</v>
+        <v>4326</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>15</v>
@@ -21774,7 +21774,7 @@
         <v>14</v>
       </c>
       <c r="F98" s="2">
-        <v>1534</v>
+        <v>4087</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>15</v>
@@ -21806,7 +21806,7 @@
         <v>14</v>
       </c>
       <c r="F99" s="2">
-        <v>1396</v>
+        <v>1117</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>15</v>
@@ -21838,7 +21838,7 @@
         <v>14</v>
       </c>
       <c r="F100" s="2">
-        <v>1788</v>
+        <v>1770</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>15</v>
@@ -21870,7 +21870,7 @@
         <v>14</v>
       </c>
       <c r="F101" s="2">
-        <v>860</v>
+        <v>2740</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>15</v>
@@ -21902,7 +21902,7 @@
         <v>14</v>
       </c>
       <c r="F102" s="2">
-        <v>4117</v>
+        <v>1490</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>15</v>
@@ -21934,7 +21934,7 @@
         <v>14</v>
       </c>
       <c r="F103" s="2">
-        <v>1431</v>
+        <v>3557</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>15</v>
@@ -21966,7 +21966,7 @@
         <v>14</v>
       </c>
       <c r="F104" s="2">
-        <v>2506</v>
+        <v>2340</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>15</v>
@@ -21998,7 +21998,7 @@
         <v>14</v>
       </c>
       <c r="F105" s="2">
-        <v>1492</v>
+        <v>4725</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>15</v>
@@ -22030,7 +22030,7 @@
         <v>14</v>
       </c>
       <c r="F106" s="2">
-        <v>4114</v>
+        <v>3075</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>15</v>
@@ -22062,7 +22062,7 @@
         <v>14</v>
       </c>
       <c r="F107" s="2">
-        <v>3396</v>
+        <v>4389</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>15</v>
@@ -22094,7 +22094,7 @@
         <v>14</v>
       </c>
       <c r="F108" s="2">
-        <v>1053</v>
+        <v>3074</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>15</v>
@@ -22126,7 +22126,7 @@
         <v>14</v>
       </c>
       <c r="F109" s="2">
-        <v>970</v>
+        <v>4798</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>15</v>
@@ -22158,7 +22158,7 @@
         <v>14</v>
       </c>
       <c r="F110" s="2">
-        <v>3978</v>
+        <v>847</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>15</v>
@@ -22190,7 +22190,7 @@
         <v>14</v>
       </c>
       <c r="F111" s="2">
-        <v>1929</v>
+        <v>2920</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>15</v>
@@ -22222,7 +22222,7 @@
         <v>14</v>
       </c>
       <c r="F112" s="2">
-        <v>1100</v>
+        <v>3199</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>15</v>
@@ -22254,7 +22254,7 @@
         <v>14</v>
       </c>
       <c r="F113" s="2">
-        <v>2516</v>
+        <v>4704</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>15</v>
@@ -22286,7 +22286,7 @@
         <v>14</v>
       </c>
       <c r="F114" s="2">
-        <v>1944</v>
+        <v>1593</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>15</v>
@@ -22318,7 +22318,7 @@
         <v>14</v>
       </c>
       <c r="F115" s="2">
-        <v>2455</v>
+        <v>3254</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>15</v>
@@ -22350,7 +22350,7 @@
         <v>14</v>
       </c>
       <c r="F116" s="2">
-        <v>3427</v>
+        <v>1707</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>15</v>
@@ -22382,7 +22382,7 @@
         <v>14</v>
       </c>
       <c r="F117" s="2">
-        <v>1288</v>
+        <v>1132</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>15</v>
@@ -22414,7 +22414,7 @@
         <v>14</v>
       </c>
       <c r="F118" s="2">
-        <v>4304</v>
+        <v>1205</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>15</v>
@@ -22446,7 +22446,7 @@
         <v>14</v>
       </c>
       <c r="F119" s="2">
-        <v>2270</v>
+        <v>1121</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>15</v>
@@ -22478,7 +22478,7 @@
         <v>14</v>
       </c>
       <c r="F120" s="2">
-        <v>2298</v>
+        <v>4279</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>15</v>
@@ -22510,7 +22510,7 @@
         <v>14</v>
       </c>
       <c r="F121" s="2">
-        <v>4234</v>
+        <v>3912</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>15</v>
@@ -22542,7 +22542,7 @@
         <v>14</v>
       </c>
       <c r="F122" s="2">
-        <v>3098</v>
+        <v>4786</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>15</v>
@@ -22574,7 +22574,7 @@
         <v>14</v>
       </c>
       <c r="F123" s="2">
-        <v>2500</v>
+        <v>1674</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>15</v>
@@ -22606,7 +22606,7 @@
         <v>14</v>
       </c>
       <c r="F124" s="2">
-        <v>4381</v>
+        <v>3257</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>15</v>
@@ -22638,7 +22638,7 @@
         <v>14</v>
       </c>
       <c r="F125" s="2">
-        <v>1644</v>
+        <v>3781</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>15</v>
@@ -22670,7 +22670,7 @@
         <v>14</v>
       </c>
       <c r="F126" s="2">
-        <v>4100</v>
+        <v>2607</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>15</v>
@@ -22702,7 +22702,7 @@
         <v>14</v>
       </c>
       <c r="F127" s="2">
-        <v>4173</v>
+        <v>3611</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>15</v>
@@ -22734,7 +22734,7 @@
         <v>14</v>
       </c>
       <c r="F128" s="2">
-        <v>4757</v>
+        <v>3037</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>15</v>
@@ -22766,7 +22766,7 @@
         <v>14</v>
       </c>
       <c r="F129" s="2">
-        <v>972</v>
+        <v>3383</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>15</v>
@@ -22798,7 +22798,7 @@
         <v>14</v>
       </c>
       <c r="F130" s="2">
-        <v>2221</v>
+        <v>3967</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>15</v>
@@ -22830,7 +22830,7 @@
         <v>14</v>
       </c>
       <c r="F131" s="2">
-        <v>1004</v>
+        <v>1038</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>15</v>
@@ -22862,7 +22862,7 @@
         <v>14</v>
       </c>
       <c r="F132" s="2">
-        <v>1665</v>
+        <v>3641</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>15</v>
@@ -22894,7 +22894,7 @@
         <v>14</v>
       </c>
       <c r="F133" s="2">
-        <v>4340</v>
+        <v>1141</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>15</v>
@@ -22926,7 +22926,7 @@
         <v>14</v>
       </c>
       <c r="F134" s="2">
-        <v>3133</v>
+        <v>1571</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>15</v>
@@ -22958,7 +22958,7 @@
         <v>14</v>
       </c>
       <c r="F135" s="2">
-        <v>2167</v>
+        <v>4083</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>15</v>
@@ -22990,7 +22990,7 @@
         <v>14</v>
       </c>
       <c r="F136" s="2">
-        <v>1411</v>
+        <v>3241</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>15</v>
@@ -23022,7 +23022,7 @@
         <v>14</v>
       </c>
       <c r="F137" s="2">
-        <v>1786</v>
+        <v>2416</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>15</v>
@@ -23054,7 +23054,7 @@
         <v>14</v>
       </c>
       <c r="F138" s="2">
-        <v>4760</v>
+        <v>4027</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>15</v>
@@ -23086,7 +23086,7 @@
         <v>14</v>
       </c>
       <c r="F139" s="2">
-        <v>1294</v>
+        <v>4105</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>15</v>
@@ -23118,7 +23118,7 @@
         <v>14</v>
       </c>
       <c r="F140" s="2">
-        <v>1698</v>
+        <v>3674</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>15</v>
@@ -23150,7 +23150,7 @@
         <v>14</v>
       </c>
       <c r="F141" s="2">
-        <v>4089</v>
+        <v>2953</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>15</v>
@@ -23182,7 +23182,7 @@
         <v>14</v>
       </c>
       <c r="F142" s="2">
-        <v>1277</v>
+        <v>4225</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>15</v>
@@ -23214,7 +23214,7 @@
         <v>14</v>
       </c>
       <c r="F143" s="2">
-        <v>4332</v>
+        <v>3778</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>15</v>
@@ -23246,7 +23246,7 @@
         <v>14</v>
       </c>
       <c r="F144" s="2">
-        <v>2203</v>
+        <v>4685</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>15</v>
@@ -23278,7 +23278,7 @@
         <v>14</v>
       </c>
       <c r="F145" s="2">
-        <v>3650</v>
+        <v>3120</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>15</v>
@@ -23310,7 +23310,7 @@
         <v>14</v>
       </c>
       <c r="F146" s="2">
-        <v>2465</v>
+        <v>4789</v>
       </c>
       <c r="G146" s="2" t="s">
         <v>15</v>
@@ -23342,7 +23342,7 @@
         <v>14</v>
       </c>
       <c r="F147" s="2">
-        <v>3811</v>
+        <v>3075</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>15</v>
@@ -23374,7 +23374,7 @@
         <v>14</v>
       </c>
       <c r="F148" s="2">
-        <v>2487</v>
+        <v>1457</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>15</v>
@@ -23406,7 +23406,7 @@
         <v>14</v>
       </c>
       <c r="F149" s="2">
-        <v>2491</v>
+        <v>2766</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>15</v>
@@ -23438,7 +23438,7 @@
         <v>14</v>
       </c>
       <c r="F150" s="2">
-        <v>4567</v>
+        <v>1389</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>15</v>
@@ -23470,7 +23470,7 @@
         <v>14</v>
       </c>
       <c r="F151" s="2">
-        <v>2706</v>
+        <v>3724</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>15</v>
@@ -23502,7 +23502,7 @@
         <v>14</v>
       </c>
       <c r="F152" s="2">
-        <v>1592</v>
+        <v>4195</v>
       </c>
       <c r="G152" s="2" t="s">
         <v>15</v>
@@ -23534,7 +23534,7 @@
         <v>14</v>
       </c>
       <c r="F153" s="2">
-        <v>4453</v>
+        <v>967</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>15</v>
@@ -23566,7 +23566,7 @@
         <v>14</v>
       </c>
       <c r="F154" s="2">
-        <v>3932</v>
+        <v>3636</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>15</v>
@@ -23598,7 +23598,7 @@
         <v>14</v>
       </c>
       <c r="F155" s="2">
-        <v>1911</v>
+        <v>1951</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>15</v>
@@ -23630,7 +23630,7 @@
         <v>14</v>
       </c>
       <c r="F156" s="2">
-        <v>4052</v>
+        <v>3436</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>15</v>
@@ -23662,7 +23662,7 @@
         <v>14</v>
       </c>
       <c r="F157" s="2">
-        <v>3525</v>
+        <v>2497</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>15</v>
@@ -23694,7 +23694,7 @@
         <v>14</v>
       </c>
       <c r="F158" s="2">
-        <v>1457</v>
+        <v>3458</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>15</v>
@@ -23726,7 +23726,7 @@
         <v>14</v>
       </c>
       <c r="F159" s="2">
-        <v>1071</v>
+        <v>4274</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>15</v>
@@ -23758,7 +23758,7 @@
         <v>14</v>
       </c>
       <c r="F160" s="2">
-        <v>1432</v>
+        <v>875</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>15</v>
@@ -23790,7 +23790,7 @@
         <v>14</v>
       </c>
       <c r="F161" s="2">
-        <v>1888</v>
+        <v>4559</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>15</v>
@@ -23822,7 +23822,7 @@
         <v>14</v>
       </c>
       <c r="F162" s="2">
-        <v>3621</v>
+        <v>1771</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>15</v>
@@ -23854,7 +23854,7 @@
         <v>14</v>
       </c>
       <c r="F163" s="2">
-        <v>2601</v>
+        <v>4416</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>15</v>
@@ -23886,7 +23886,7 @@
         <v>14</v>
       </c>
       <c r="F164" s="2">
-        <v>2484</v>
+        <v>1039</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>15</v>
@@ -23918,7 +23918,7 @@
         <v>14</v>
       </c>
       <c r="F165" s="2">
-        <v>2228</v>
+        <v>1805</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>15</v>
@@ -23950,7 +23950,7 @@
         <v>14</v>
       </c>
       <c r="F166" s="2">
-        <v>3725</v>
+        <v>1376</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>15</v>
@@ -23982,7 +23982,7 @@
         <v>14</v>
       </c>
       <c r="F167" s="2">
-        <v>1987</v>
+        <v>1729</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>15</v>
@@ -24014,7 +24014,7 @@
         <v>14</v>
       </c>
       <c r="F168" s="2">
-        <v>2467</v>
+        <v>4057</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>15</v>
@@ -24046,7 +24046,7 @@
         <v>14</v>
       </c>
       <c r="F169" s="2">
-        <v>804</v>
+        <v>3700</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>15</v>
@@ -24078,7 +24078,7 @@
         <v>14</v>
       </c>
       <c r="F170" s="2">
-        <v>1805</v>
+        <v>3857</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>15</v>
@@ -24110,7 +24110,7 @@
         <v>14</v>
       </c>
       <c r="F171" s="2">
-        <v>2172</v>
+        <v>1885</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>15</v>
@@ -24142,7 +24142,7 @@
         <v>14</v>
       </c>
       <c r="F172" s="2">
-        <v>1749</v>
+        <v>2925</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>15</v>
@@ -24174,7 +24174,7 @@
         <v>14</v>
       </c>
       <c r="F173" s="2">
-        <v>4230</v>
+        <v>3388</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>15</v>
@@ -24206,7 +24206,7 @@
         <v>14</v>
       </c>
       <c r="F174" s="2">
-        <v>1483</v>
+        <v>1350</v>
       </c>
       <c r="G174" s="2" t="s">
         <v>15</v>
@@ -24238,7 +24238,7 @@
         <v>14</v>
       </c>
       <c r="F175" s="2">
-        <v>4340</v>
+        <v>4633</v>
       </c>
       <c r="G175" s="2" t="s">
         <v>15</v>
@@ -24270,7 +24270,7 @@
         <v>14</v>
       </c>
       <c r="F176" s="2">
-        <v>4664</v>
+        <v>1448</v>
       </c>
       <c r="G176" s="2" t="s">
         <v>15</v>
@@ -24302,7 +24302,7 @@
         <v>14</v>
       </c>
       <c r="F177" s="2">
-        <v>4138</v>
+        <v>4598</v>
       </c>
       <c r="G177" s="2" t="s">
         <v>15</v>
@@ -24334,7 +24334,7 @@
         <v>14</v>
       </c>
       <c r="F178" s="2">
-        <v>3105</v>
+        <v>3337</v>
       </c>
       <c r="G178" s="2" t="s">
         <v>15</v>
@@ -24366,7 +24366,7 @@
         <v>14</v>
       </c>
       <c r="F179" s="2">
-        <v>1705</v>
+        <v>4338</v>
       </c>
       <c r="G179" s="2" t="s">
         <v>15</v>
@@ -24398,7 +24398,7 @@
         <v>14</v>
       </c>
       <c r="F180" s="2">
-        <v>2812</v>
+        <v>4339</v>
       </c>
       <c r="G180" s="2" t="s">
         <v>15</v>
@@ -24430,7 +24430,7 @@
         <v>14</v>
       </c>
       <c r="F181" s="2">
-        <v>4224</v>
+        <v>1748</v>
       </c>
       <c r="G181" s="2" t="s">
         <v>15</v>
@@ -24462,7 +24462,7 @@
         <v>14</v>
       </c>
       <c r="F182" s="2">
-        <v>2968</v>
+        <v>2920</v>
       </c>
       <c r="G182" s="2" t="s">
         <v>15</v>
@@ -24494,7 +24494,7 @@
         <v>14</v>
       </c>
       <c r="F183" s="2">
-        <v>1212</v>
+        <v>1413</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>15</v>
@@ -24526,7 +24526,7 @@
         <v>14</v>
       </c>
       <c r="F184" s="2">
-        <v>3781</v>
+        <v>2863</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>15</v>
@@ -24558,7 +24558,7 @@
         <v>14</v>
       </c>
       <c r="F185" s="2">
-        <v>3059</v>
+        <v>2965</v>
       </c>
       <c r="G185" s="2" t="s">
         <v>15</v>
@@ -24590,7 +24590,7 @@
         <v>14</v>
       </c>
       <c r="F186" s="2">
-        <v>2840</v>
+        <v>1403</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>15</v>
@@ -24622,7 +24622,7 @@
         <v>14</v>
       </c>
       <c r="F187" s="2">
-        <v>3528</v>
+        <v>2079</v>
       </c>
       <c r="G187" s="2" t="s">
         <v>15</v>
@@ -24654,7 +24654,7 @@
         <v>14</v>
       </c>
       <c r="F188" s="2">
-        <v>4185</v>
+        <v>4346</v>
       </c>
       <c r="G188" s="2" t="s">
         <v>15</v>
@@ -24686,7 +24686,7 @@
         <v>14</v>
       </c>
       <c r="F189" s="2">
-        <v>2891</v>
+        <v>2788</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>15</v>
@@ -24718,7 +24718,7 @@
         <v>14</v>
       </c>
       <c r="F190" s="2">
-        <v>3345</v>
+        <v>3301</v>
       </c>
       <c r="G190" s="2" t="s">
         <v>15</v>
@@ -24750,7 +24750,7 @@
         <v>14</v>
       </c>
       <c r="F191" s="2">
-        <v>2664</v>
+        <v>3162</v>
       </c>
       <c r="G191" s="2" t="s">
         <v>15</v>
@@ -24782,7 +24782,7 @@
         <v>14</v>
       </c>
       <c r="F192" s="2">
-        <v>1594</v>
+        <v>4749</v>
       </c>
       <c r="G192" s="2" t="s">
         <v>15</v>
@@ -24814,7 +24814,7 @@
         <v>14</v>
       </c>
       <c r="F193" s="2">
-        <v>4012</v>
+        <v>1594</v>
       </c>
       <c r="G193" s="2" t="s">
         <v>15</v>
@@ -24846,7 +24846,7 @@
         <v>14</v>
       </c>
       <c r="F194" s="2">
-        <v>1149</v>
+        <v>1534</v>
       </c>
       <c r="G194" s="2" t="s">
         <v>15</v>
@@ -24878,7 +24878,7 @@
         <v>14</v>
       </c>
       <c r="F195" s="2">
-        <v>1030</v>
+        <v>1299</v>
       </c>
       <c r="G195" s="2" t="s">
         <v>15</v>
@@ -24910,7 +24910,7 @@
         <v>14</v>
       </c>
       <c r="F196" s="2">
-        <v>4657</v>
+        <v>3576</v>
       </c>
       <c r="G196" s="2" t="s">
         <v>15</v>
@@ -24942,7 +24942,7 @@
         <v>14</v>
       </c>
       <c r="F197" s="2">
-        <v>941</v>
+        <v>1087</v>
       </c>
       <c r="G197" s="2" t="s">
         <v>15</v>
@@ -24974,7 +24974,7 @@
         <v>14</v>
       </c>
       <c r="F198" s="2">
-        <v>2066</v>
+        <v>3002</v>
       </c>
       <c r="G198" s="2" t="s">
         <v>15</v>
@@ -25006,7 +25006,7 @@
         <v>14</v>
       </c>
       <c r="F199" s="2">
-        <v>3271</v>
+        <v>4776</v>
       </c>
       <c r="G199" s="2" t="s">
         <v>15</v>
@@ -25038,7 +25038,7 @@
         <v>14</v>
       </c>
       <c r="F200" s="2">
-        <v>1751</v>
+        <v>3830</v>
       </c>
       <c r="G200" s="2" t="s">
         <v>15</v>
@@ -25070,7 +25070,7 @@
         <v>14</v>
       </c>
       <c r="F201" s="2">
-        <v>3980</v>
+        <v>1046</v>
       </c>
       <c r="G201" s="2" t="s">
         <v>15</v>
@@ -25102,7 +25102,7 @@
         <v>14</v>
       </c>
       <c r="F202" s="2">
-        <v>3501</v>
+        <v>3768</v>
       </c>
       <c r="G202" s="2" t="s">
         <v>15</v>
@@ -25134,7 +25134,7 @@
         <v>14</v>
       </c>
       <c r="F203" s="2">
-        <v>3871</v>
+        <v>1507</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>15</v>
@@ -25166,7 +25166,7 @@
         <v>14</v>
       </c>
       <c r="F204" s="2">
-        <v>3049</v>
+        <v>3963</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>15</v>
@@ -25198,7 +25198,7 @@
         <v>14</v>
       </c>
       <c r="F205" s="2">
-        <v>3356</v>
+        <v>3992</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>15</v>
@@ -25230,7 +25230,7 @@
         <v>14</v>
       </c>
       <c r="F206" s="2">
-        <v>3695</v>
+        <v>1558</v>
       </c>
       <c r="G206" s="2" t="s">
         <v>15</v>
@@ -25262,7 +25262,7 @@
         <v>14</v>
       </c>
       <c r="F207" s="2">
-        <v>3118</v>
+        <v>1737</v>
       </c>
       <c r="G207" s="2" t="s">
         <v>15</v>
@@ -25294,7 +25294,7 @@
         <v>14</v>
       </c>
       <c r="F208" s="2">
-        <v>2705</v>
+        <v>2331</v>
       </c>
       <c r="G208" s="2" t="s">
         <v>15</v>
@@ -25326,7 +25326,7 @@
         <v>14</v>
       </c>
       <c r="F209" s="2">
-        <v>2869</v>
+        <v>3913</v>
       </c>
       <c r="G209" s="2" t="s">
         <v>15</v>
@@ -25358,7 +25358,7 @@
         <v>14</v>
       </c>
       <c r="F210" s="2">
-        <v>1078</v>
+        <v>2246</v>
       </c>
       <c r="G210" s="2" t="s">
         <v>15</v>
@@ -25390,7 +25390,7 @@
         <v>14</v>
       </c>
       <c r="F211" s="2">
-        <v>3951</v>
+        <v>2250</v>
       </c>
       <c r="G211" s="2" t="s">
         <v>15</v>
@@ -25422,7 +25422,7 @@
         <v>14</v>
       </c>
       <c r="F212" s="2">
-        <v>4744</v>
+        <v>1364</v>
       </c>
       <c r="G212" s="2" t="s">
         <v>15</v>
@@ -25454,7 +25454,7 @@
         <v>14</v>
       </c>
       <c r="F213" s="2">
-        <v>3389</v>
+        <v>2823</v>
       </c>
       <c r="G213" s="2" t="s">
         <v>15</v>
@@ -25486,7 +25486,7 @@
         <v>14</v>
       </c>
       <c r="F214" s="2">
-        <v>1857</v>
+        <v>2232</v>
       </c>
       <c r="G214" s="2" t="s">
         <v>15</v>
@@ -25518,7 +25518,7 @@
         <v>14</v>
       </c>
       <c r="F215" s="2">
-        <v>3893</v>
+        <v>2000</v>
       </c>
       <c r="G215" s="2" t="s">
         <v>15</v>
@@ -25550,7 +25550,7 @@
         <v>14</v>
       </c>
       <c r="F216" s="2">
-        <v>1930</v>
+        <v>2947</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>15</v>
@@ -25582,7 +25582,7 @@
         <v>14</v>
       </c>
       <c r="F217" s="2">
-        <v>2885</v>
+        <v>3937</v>
       </c>
       <c r="G217" s="2" t="s">
         <v>15</v>
@@ -25614,7 +25614,7 @@
         <v>14</v>
       </c>
       <c r="F218" s="2">
-        <v>1465</v>
+        <v>2459</v>
       </c>
       <c r="G218" s="2" t="s">
         <v>15</v>
@@ -25646,7 +25646,7 @@
         <v>14</v>
       </c>
       <c r="F219" s="2">
-        <v>2733</v>
+        <v>2748</v>
       </c>
       <c r="G219" s="2" t="s">
         <v>15</v>
@@ -25678,7 +25678,7 @@
         <v>14</v>
       </c>
       <c r="F220" s="2">
-        <v>4089</v>
+        <v>1849</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>15</v>
@@ -25710,7 +25710,7 @@
         <v>14</v>
       </c>
       <c r="F221" s="2">
-        <v>1683</v>
+        <v>2586</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>15</v>
@@ -25742,7 +25742,7 @@
         <v>14</v>
       </c>
       <c r="F222" s="2">
-        <v>2316</v>
+        <v>4684</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>15</v>
@@ -25774,7 +25774,7 @@
         <v>14</v>
       </c>
       <c r="F223" s="2">
-        <v>2857</v>
+        <v>4715</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>15</v>
@@ -25806,7 +25806,7 @@
         <v>14</v>
       </c>
       <c r="F224" s="2">
-        <v>1497</v>
+        <v>2498</v>
       </c>
       <c r="G224" s="2" t="s">
         <v>15</v>
@@ -25838,7 +25838,7 @@
         <v>14</v>
       </c>
       <c r="F225" s="2">
-        <v>3863</v>
+        <v>1412</v>
       </c>
       <c r="G225" s="2" t="s">
         <v>15</v>
@@ -25870,7 +25870,7 @@
         <v>14</v>
       </c>
       <c r="F226" s="2">
-        <v>4571</v>
+        <v>4744</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>15</v>
@@ -25902,7 +25902,7 @@
         <v>14</v>
       </c>
       <c r="F227" s="2">
-        <v>2464</v>
+        <v>3769</v>
       </c>
       <c r="G227" s="2" t="s">
         <v>15</v>
@@ -25934,7 +25934,7 @@
         <v>14</v>
       </c>
       <c r="F228" s="2">
-        <v>4429</v>
+        <v>2455</v>
       </c>
       <c r="G228" s="2" t="s">
         <v>15</v>
@@ -25966,7 +25966,7 @@
         <v>14</v>
       </c>
       <c r="F229" s="2">
-        <v>3963</v>
+        <v>1683</v>
       </c>
       <c r="G229" s="2" t="s">
         <v>15</v>
@@ -25998,7 +25998,7 @@
         <v>14</v>
       </c>
       <c r="F230" s="2">
-        <v>4374</v>
+        <v>942</v>
       </c>
       <c r="G230" s="2" t="s">
         <v>15</v>
@@ -26030,7 +26030,7 @@
         <v>14</v>
       </c>
       <c r="F231" s="2">
-        <v>3374</v>
+        <v>1994</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>15</v>
@@ -26062,7 +26062,7 @@
         <v>14</v>
       </c>
       <c r="F232" s="2">
-        <v>4320</v>
+        <v>4173</v>
       </c>
       <c r="G232" s="2" t="s">
         <v>15</v>
@@ -26094,7 +26094,7 @@
         <v>14</v>
       </c>
       <c r="F233" s="2">
-        <v>4411</v>
+        <v>4290</v>
       </c>
       <c r="G233" s="2" t="s">
         <v>15</v>
@@ -26126,7 +26126,7 @@
         <v>14</v>
       </c>
       <c r="F234" s="2">
-        <v>3823</v>
+        <v>3847</v>
       </c>
       <c r="G234" s="2" t="s">
         <v>15</v>
@@ -26158,7 +26158,7 @@
         <v>14</v>
       </c>
       <c r="F235" s="2">
-        <v>2595</v>
+        <v>2668</v>
       </c>
       <c r="G235" s="2" t="s">
         <v>15</v>
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="F236" s="2">
-        <v>1177</v>
+        <v>1595</v>
       </c>
       <c r="G236" s="2" t="s">
         <v>15</v>
@@ -26222,7 +26222,7 @@
         <v>14</v>
       </c>
       <c r="F237" s="2">
-        <v>1799</v>
+        <v>1258</v>
       </c>
       <c r="G237" s="2" t="s">
         <v>15</v>
@@ -26254,7 +26254,7 @@
         <v>14</v>
       </c>
       <c r="F238" s="2">
-        <v>3067</v>
+        <v>2845</v>
       </c>
       <c r="G238" s="2" t="s">
         <v>15</v>
@@ -26286,7 +26286,7 @@
         <v>14</v>
       </c>
       <c r="F239" s="2">
-        <v>2632</v>
+        <v>2972</v>
       </c>
       <c r="G239" s="2" t="s">
         <v>15</v>
@@ -26318,7 +26318,7 @@
         <v>14</v>
       </c>
       <c r="F240" s="2">
-        <v>3722</v>
+        <v>4008</v>
       </c>
       <c r="G240" s="2" t="s">
         <v>15</v>
@@ -26350,7 +26350,7 @@
         <v>14</v>
       </c>
       <c r="F241" s="2">
-        <v>2451</v>
+        <v>1093</v>
       </c>
       <c r="G241" s="2" t="s">
         <v>15</v>
@@ -26382,7 +26382,7 @@
         <v>14</v>
       </c>
       <c r="F242" s="2">
-        <v>1074</v>
+        <v>1914</v>
       </c>
       <c r="G242" s="2" t="s">
         <v>15</v>
@@ -26414,7 +26414,7 @@
         <v>14</v>
       </c>
       <c r="F243" s="2">
-        <v>980</v>
+        <v>4278</v>
       </c>
       <c r="G243" s="2" t="s">
         <v>15</v>
@@ -26446,7 +26446,7 @@
         <v>14</v>
       </c>
       <c r="F244" s="2">
-        <v>1329</v>
+        <v>2488</v>
       </c>
       <c r="G244" s="2" t="s">
         <v>15</v>
@@ -26478,7 +26478,7 @@
         <v>14</v>
       </c>
       <c r="F245" s="2">
-        <v>4189</v>
+        <v>2805</v>
       </c>
       <c r="G245" s="2" t="s">
         <v>15</v>
@@ -26510,7 +26510,7 @@
         <v>14</v>
       </c>
       <c r="F246" s="2">
-        <v>3594</v>
+        <v>4085</v>
       </c>
       <c r="G246" s="2" t="s">
         <v>15</v>
@@ -26542,7 +26542,7 @@
         <v>14</v>
       </c>
       <c r="F247" s="2">
-        <v>2654</v>
+        <v>2786</v>
       </c>
       <c r="G247" s="2" t="s">
         <v>15</v>
@@ -26574,7 +26574,7 @@
         <v>14</v>
       </c>
       <c r="F248" s="2">
-        <v>4305</v>
+        <v>4204</v>
       </c>
       <c r="G248" s="2" t="s">
         <v>15</v>
@@ -26606,7 +26606,7 @@
         <v>14</v>
       </c>
       <c r="F249" s="2">
-        <v>4786</v>
+        <v>4137</v>
       </c>
       <c r="G249" s="2" t="s">
         <v>15</v>
@@ -26638,7 +26638,7 @@
         <v>14</v>
       </c>
       <c r="F250" s="2">
-        <v>2056</v>
+        <v>3058</v>
       </c>
       <c r="G250" s="2" t="s">
         <v>15</v>
@@ -26670,7 +26670,7 @@
         <v>14</v>
       </c>
       <c r="F251" s="2">
-        <v>803</v>
+        <v>1141</v>
       </c>
       <c r="G251" s="2" t="s">
         <v>15</v>
@@ -26702,7 +26702,7 @@
         <v>14</v>
       </c>
       <c r="F252" s="2">
-        <v>4393</v>
+        <v>3699</v>
       </c>
       <c r="G252" s="2" t="s">
         <v>15</v>
@@ -26734,7 +26734,7 @@
         <v>14</v>
       </c>
       <c r="F253" s="2">
-        <v>897</v>
+        <v>3487</v>
       </c>
       <c r="G253" s="2" t="s">
         <v>15</v>
@@ -26766,7 +26766,7 @@
         <v>14</v>
       </c>
       <c r="F254" s="2">
-        <v>2696</v>
+        <v>1603</v>
       </c>
       <c r="G254" s="2" t="s">
         <v>15</v>
@@ -26798,7 +26798,7 @@
         <v>14</v>
       </c>
       <c r="F255" s="2">
-        <v>4120</v>
+        <v>3282</v>
       </c>
       <c r="G255" s="2" t="s">
         <v>15</v>
@@ -26830,7 +26830,7 @@
         <v>14</v>
       </c>
       <c r="F256" s="2">
-        <v>3926</v>
+        <v>1167</v>
       </c>
       <c r="G256" s="2" t="s">
         <v>15</v>
@@ -26862,7 +26862,7 @@
         <v>14</v>
       </c>
       <c r="F257" s="2">
-        <v>1085</v>
+        <v>4750</v>
       </c>
       <c r="G257" s="2" t="s">
         <v>15</v>
@@ -26894,7 +26894,7 @@
         <v>14</v>
       </c>
       <c r="F258" s="2">
-        <v>3107</v>
+        <v>1021</v>
       </c>
       <c r="G258" s="2" t="s">
         <v>15</v>
@@ -26926,7 +26926,7 @@
         <v>14</v>
       </c>
       <c r="F259" s="2">
-        <v>1392</v>
+        <v>2825</v>
       </c>
       <c r="G259" s="2" t="s">
         <v>15</v>
@@ -26958,7 +26958,7 @@
         <v>14</v>
       </c>
       <c r="F260" s="2">
-        <v>4134</v>
+        <v>2166</v>
       </c>
       <c r="G260" s="2" t="s">
         <v>15</v>
@@ -26990,7 +26990,7 @@
         <v>14</v>
       </c>
       <c r="F261" s="2">
-        <v>3066</v>
+        <v>1350</v>
       </c>
       <c r="G261" s="2" t="s">
         <v>15</v>
@@ -27022,7 +27022,7 @@
         <v>14</v>
       </c>
       <c r="F262" s="2">
-        <v>1441</v>
+        <v>3639</v>
       </c>
       <c r="G262" s="2" t="s">
         <v>15</v>
@@ -27054,7 +27054,7 @@
         <v>14</v>
       </c>
       <c r="F263" s="2">
-        <v>4297</v>
+        <v>3697</v>
       </c>
       <c r="G263" s="2" t="s">
         <v>15</v>
@@ -27086,7 +27086,7 @@
         <v>14</v>
       </c>
       <c r="F264" s="2">
-        <v>3715</v>
+        <v>3528</v>
       </c>
       <c r="G264" s="2" t="s">
         <v>15</v>
@@ -27118,7 +27118,7 @@
         <v>14</v>
       </c>
       <c r="F265" s="2">
-        <v>4532</v>
+        <v>4517</v>
       </c>
       <c r="G265" s="2" t="s">
         <v>15</v>
@@ -27150,7 +27150,7 @@
         <v>14</v>
       </c>
       <c r="F266" s="2">
-        <v>3604</v>
+        <v>4072</v>
       </c>
       <c r="G266" s="2" t="s">
         <v>15</v>
@@ -27182,7 +27182,7 @@
         <v>14</v>
       </c>
       <c r="F267" s="2">
-        <v>3415</v>
+        <v>1514</v>
       </c>
       <c r="G267" s="2" t="s">
         <v>15</v>
@@ -27214,7 +27214,7 @@
         <v>14</v>
       </c>
       <c r="F268" s="2">
-        <v>3771</v>
+        <v>3501</v>
       </c>
       <c r="G268" s="2" t="s">
         <v>15</v>
@@ -27246,7 +27246,7 @@
         <v>14</v>
       </c>
       <c r="F269" s="2">
-        <v>4492</v>
+        <v>3961</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>15</v>
@@ -27278,7 +27278,7 @@
         <v>14</v>
       </c>
       <c r="F270" s="2">
-        <v>4406</v>
+        <v>2500</v>
       </c>
       <c r="G270" s="2" t="s">
         <v>15</v>
@@ -27310,7 +27310,7 @@
         <v>14</v>
       </c>
       <c r="F271" s="2">
-        <v>4183</v>
+        <v>1799</v>
       </c>
       <c r="G271" s="2" t="s">
         <v>15</v>
@@ -27342,7 +27342,7 @@
         <v>14</v>
       </c>
       <c r="F272" s="2">
-        <v>1460</v>
+        <v>2162</v>
       </c>
       <c r="G272" s="2" t="s">
         <v>15</v>
@@ -27374,7 +27374,7 @@
         <v>14</v>
       </c>
       <c r="F273" s="2">
-        <v>2595</v>
+        <v>2954</v>
       </c>
       <c r="G273" s="2" t="s">
         <v>15</v>
@@ -27406,7 +27406,7 @@
         <v>14</v>
       </c>
       <c r="F274" s="2">
-        <v>2304</v>
+        <v>3258</v>
       </c>
       <c r="G274" s="2" t="s">
         <v>15</v>
@@ -27438,7 +27438,7 @@
         <v>14</v>
       </c>
       <c r="F275" s="2">
-        <v>2085</v>
+        <v>2724</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>15</v>
@@ -27470,7 +27470,7 @@
         <v>14</v>
       </c>
       <c r="F276" s="2">
-        <v>2202</v>
+        <v>4098</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>15</v>
@@ -27502,7 +27502,7 @@
         <v>14</v>
       </c>
       <c r="F277" s="2">
-        <v>1377</v>
+        <v>1795</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>15</v>
@@ -27534,7 +27534,7 @@
         <v>14</v>
       </c>
       <c r="F278" s="2">
-        <v>1561</v>
+        <v>2990</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>15</v>
@@ -27566,7 +27566,7 @@
         <v>14</v>
       </c>
       <c r="F279" s="2">
-        <v>4386</v>
+        <v>2339</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>15</v>
@@ -27598,7 +27598,7 @@
         <v>14</v>
       </c>
       <c r="F280" s="2">
-        <v>1896</v>
+        <v>1731</v>
       </c>
       <c r="G280" s="2" t="s">
         <v>15</v>
@@ -27630,7 +27630,7 @@
         <v>14</v>
       </c>
       <c r="F281" s="2">
-        <v>833</v>
+        <v>1818</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>15</v>
@@ -27662,7 +27662,7 @@
         <v>14</v>
       </c>
       <c r="F282" s="2">
-        <v>2828</v>
+        <v>3629</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>15</v>
@@ -27694,7 +27694,7 @@
         <v>14</v>
       </c>
       <c r="F283" s="2">
-        <v>1352</v>
+        <v>2543</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>15</v>
@@ -27726,7 +27726,7 @@
         <v>14</v>
       </c>
       <c r="F284" s="2">
-        <v>2569</v>
+        <v>2543</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>15</v>
@@ -27758,7 +27758,7 @@
         <v>14</v>
       </c>
       <c r="F285" s="2">
-        <v>4117</v>
+        <v>3051</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>15</v>
@@ -27790,7 +27790,7 @@
         <v>14</v>
       </c>
       <c r="F286" s="2">
-        <v>3729</v>
+        <v>3100</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>15</v>
@@ -27822,7 +27822,7 @@
         <v>14</v>
       </c>
       <c r="F287" s="2">
-        <v>4663</v>
+        <v>4694</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>15</v>
@@ -27854,7 +27854,7 @@
         <v>14</v>
       </c>
       <c r="F288" s="2">
-        <v>4319</v>
+        <v>969</v>
       </c>
       <c r="G288" s="2" t="s">
         <v>15</v>
@@ -27886,7 +27886,7 @@
         <v>14</v>
       </c>
       <c r="F289" s="2">
-        <v>1641</v>
+        <v>2561</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>15</v>
@@ -27918,7 +27918,7 @@
         <v>14</v>
       </c>
       <c r="F290" s="2">
-        <v>2917</v>
+        <v>890</v>
       </c>
       <c r="G290" s="2" t="s">
         <v>15</v>
@@ -27950,7 +27950,7 @@
         <v>14</v>
       </c>
       <c r="F291" s="2">
-        <v>1005</v>
+        <v>2166</v>
       </c>
       <c r="G291" s="2" t="s">
         <v>15</v>
@@ -27982,7 +27982,7 @@
         <v>14</v>
       </c>
       <c r="F292" s="2">
-        <v>4171</v>
+        <v>823</v>
       </c>
       <c r="G292" s="2" t="s">
         <v>15</v>
@@ -28014,7 +28014,7 @@
         <v>14</v>
       </c>
       <c r="F293" s="2">
-        <v>1361</v>
+        <v>3593</v>
       </c>
       <c r="G293" s="2" t="s">
         <v>15</v>
@@ -28046,7 +28046,7 @@
         <v>14</v>
       </c>
       <c r="F294" s="2">
-        <v>1049</v>
+        <v>2884</v>
       </c>
       <c r="G294" s="2" t="s">
         <v>15</v>
@@ -28078,7 +28078,7 @@
         <v>14</v>
       </c>
       <c r="F295" s="2">
-        <v>2936</v>
+        <v>2627</v>
       </c>
       <c r="G295" s="2" t="s">
         <v>15</v>
@@ -28110,7 +28110,7 @@
         <v>14</v>
       </c>
       <c r="F296" s="2">
-        <v>3238</v>
+        <v>3564</v>
       </c>
       <c r="G296" s="2" t="s">
         <v>15</v>
@@ -28142,7 +28142,7 @@
         <v>14</v>
       </c>
       <c r="F297" s="2">
-        <v>3448</v>
+        <v>2471</v>
       </c>
       <c r="G297" s="2" t="s">
         <v>15</v>
@@ -28174,7 +28174,7 @@
         <v>14</v>
       </c>
       <c r="F298" s="2">
-        <v>3837</v>
+        <v>2795</v>
       </c>
       <c r="G298" s="2" t="s">
         <v>15</v>
@@ -28206,7 +28206,7 @@
         <v>14</v>
       </c>
       <c r="F299" s="2">
-        <v>2424</v>
+        <v>2462</v>
       </c>
       <c r="G299" s="2" t="s">
         <v>15</v>
@@ -28238,7 +28238,7 @@
         <v>14</v>
       </c>
       <c r="F300" s="2">
-        <v>1443</v>
+        <v>2895</v>
       </c>
       <c r="G300" s="2" t="s">
         <v>15</v>
@@ -28270,7 +28270,7 @@
         <v>14</v>
       </c>
       <c r="F301" s="2">
-        <v>2969</v>
+        <v>2505</v>
       </c>
       <c r="G301" s="2" t="s">
         <v>15</v>
@@ -28302,7 +28302,7 @@
         <v>14</v>
       </c>
       <c r="F302" s="2">
-        <v>2522</v>
+        <v>852</v>
       </c>
       <c r="G302" s="2" t="s">
         <v>15</v>
@@ -28334,7 +28334,7 @@
         <v>14</v>
       </c>
       <c r="F303" s="2">
-        <v>2361</v>
+        <v>4678</v>
       </c>
       <c r="G303" s="2" t="s">
         <v>15</v>
@@ -28366,7 +28366,7 @@
         <v>14</v>
       </c>
       <c r="F304" s="2">
-        <v>4261</v>
+        <v>2970</v>
       </c>
       <c r="G304" s="2" t="s">
         <v>15</v>
@@ -28398,7 +28398,7 @@
         <v>14</v>
       </c>
       <c r="F305" s="2">
-        <v>1752</v>
+        <v>3630</v>
       </c>
       <c r="G305" s="2" t="s">
         <v>15</v>
@@ -28430,7 +28430,7 @@
         <v>14</v>
       </c>
       <c r="F306" s="2">
-        <v>3392</v>
+        <v>2694</v>
       </c>
       <c r="G306" s="2" t="s">
         <v>15</v>
@@ -28462,7 +28462,7 @@
         <v>14</v>
       </c>
       <c r="F307" s="2">
-        <v>1606</v>
+        <v>1189</v>
       </c>
       <c r="G307" s="2" t="s">
         <v>15</v>
@@ -28494,7 +28494,7 @@
         <v>14</v>
       </c>
       <c r="F308" s="2">
-        <v>2455</v>
+        <v>2228</v>
       </c>
       <c r="G308" s="2" t="s">
         <v>15</v>
@@ -28526,7 +28526,7 @@
         <v>14</v>
       </c>
       <c r="F309" s="2">
-        <v>3909</v>
+        <v>963</v>
       </c>
       <c r="G309" s="2" t="s">
         <v>15</v>
@@ -28558,7 +28558,7 @@
         <v>14</v>
       </c>
       <c r="F310" s="2">
-        <v>945</v>
+        <v>1715</v>
       </c>
       <c r="G310" s="2" t="s">
         <v>15</v>
@@ -28590,7 +28590,7 @@
         <v>14</v>
       </c>
       <c r="F311" s="2">
-        <v>1186</v>
+        <v>1296</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>15</v>
@@ -28622,7 +28622,7 @@
         <v>14</v>
       </c>
       <c r="F312" s="2">
-        <v>2273</v>
+        <v>2232</v>
       </c>
       <c r="G312" s="2" t="s">
         <v>15</v>
@@ -28654,7 +28654,7 @@
         <v>14</v>
       </c>
       <c r="F313" s="2">
-        <v>2767</v>
+        <v>1246</v>
       </c>
       <c r="G313" s="2" t="s">
         <v>15</v>
@@ -28686,7 +28686,7 @@
         <v>14</v>
       </c>
       <c r="F314" s="2">
-        <v>4311</v>
+        <v>1186</v>
       </c>
       <c r="G314" s="2" t="s">
         <v>15</v>
@@ -28718,7 +28718,7 @@
         <v>14</v>
       </c>
       <c r="F315" s="2">
-        <v>1878</v>
+        <v>1796</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>15</v>
@@ -28750,7 +28750,7 @@
         <v>14</v>
       </c>
       <c r="F316" s="2">
-        <v>3873</v>
+        <v>4281</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>15</v>
@@ -28782,7 +28782,7 @@
         <v>14</v>
       </c>
       <c r="F317" s="2">
-        <v>3640</v>
+        <v>1079</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>15</v>
@@ -28814,7 +28814,7 @@
         <v>14</v>
       </c>
       <c r="F318" s="2">
-        <v>3014</v>
+        <v>2898</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>15</v>
@@ -28846,7 +28846,7 @@
         <v>14</v>
       </c>
       <c r="F319" s="2">
-        <v>3150</v>
+        <v>4013</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>15</v>
@@ -28878,7 +28878,7 @@
         <v>14</v>
       </c>
       <c r="F320" s="2">
-        <v>949</v>
+        <v>3574</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>15</v>
@@ -28910,7 +28910,7 @@
         <v>14</v>
       </c>
       <c r="F321" s="2">
-        <v>4132</v>
+        <v>2554</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>15</v>
@@ -28942,7 +28942,7 @@
         <v>14</v>
       </c>
       <c r="F322" s="2">
-        <v>2320</v>
+        <v>1822</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>15</v>
@@ -28974,7 +28974,7 @@
         <v>14</v>
       </c>
       <c r="F323" s="2">
-        <v>4708</v>
+        <v>4074</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>15</v>
@@ -29006,7 +29006,7 @@
         <v>14</v>
       </c>
       <c r="F324" s="2">
-        <v>3171</v>
+        <v>1552</v>
       </c>
       <c r="G324" s="2" t="s">
         <v>15</v>
@@ -29038,7 +29038,7 @@
         <v>14</v>
       </c>
       <c r="F325" s="2">
-        <v>3095</v>
+        <v>3428</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>15</v>
@@ -29070,7 +29070,7 @@
         <v>14</v>
       </c>
       <c r="F326" s="2">
-        <v>4466</v>
+        <v>1237</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>15</v>
@@ -29102,7 +29102,7 @@
         <v>14</v>
       </c>
       <c r="F327" s="2">
-        <v>2537</v>
+        <v>3059</v>
       </c>
       <c r="G327" s="2" t="s">
         <v>15</v>
@@ -29134,7 +29134,7 @@
         <v>14</v>
       </c>
       <c r="F328" s="2">
-        <v>2359</v>
+        <v>3729</v>
       </c>
       <c r="G328" s="2" t="s">
         <v>15</v>
@@ -29166,7 +29166,7 @@
         <v>14</v>
       </c>
       <c r="F329" s="2">
-        <v>1856</v>
+        <v>3912</v>
       </c>
       <c r="G329" s="2" t="s">
         <v>15</v>
@@ -29198,7 +29198,7 @@
         <v>14</v>
       </c>
       <c r="F330" s="2">
-        <v>4724</v>
+        <v>1300</v>
       </c>
       <c r="G330" s="2" t="s">
         <v>15</v>
@@ -29230,7 +29230,7 @@
         <v>14</v>
       </c>
       <c r="F331" s="2">
-        <v>3579</v>
+        <v>2878</v>
       </c>
       <c r="G331" s="2" t="s">
         <v>15</v>
@@ -29262,7 +29262,7 @@
         <v>14</v>
       </c>
       <c r="F332" s="2">
-        <v>1179</v>
+        <v>3884</v>
       </c>
       <c r="G332" s="2" t="s">
         <v>15</v>
@@ -29294,7 +29294,7 @@
         <v>14</v>
       </c>
       <c r="F333" s="2">
-        <v>3875</v>
+        <v>1132</v>
       </c>
       <c r="G333" s="2" t="s">
         <v>15</v>
@@ -29326,7 +29326,7 @@
         <v>14</v>
       </c>
       <c r="F334" s="2">
-        <v>2280</v>
+        <v>2626</v>
       </c>
       <c r="G334" s="2" t="s">
         <v>15</v>
@@ -29358,7 +29358,7 @@
         <v>14</v>
       </c>
       <c r="F335" s="2">
-        <v>1783</v>
+        <v>2114</v>
       </c>
       <c r="G335" s="2" t="s">
         <v>15</v>
@@ -29390,7 +29390,7 @@
         <v>14</v>
       </c>
       <c r="F336" s="2">
-        <v>3849</v>
+        <v>1031</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>15</v>
@@ -29422,7 +29422,7 @@
         <v>14</v>
       </c>
       <c r="F337" s="2">
-        <v>4175</v>
+        <v>3577</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>15</v>
@@ -29454,7 +29454,7 @@
         <v>14</v>
       </c>
       <c r="F338" s="2">
-        <v>1102</v>
+        <v>1912</v>
       </c>
       <c r="G338" s="2" t="s">
         <v>15</v>
@@ -29486,7 +29486,7 @@
         <v>14</v>
       </c>
       <c r="F339" s="2">
-        <v>4401</v>
+        <v>1857</v>
       </c>
       <c r="G339" s="2" t="s">
         <v>15</v>
@@ -29518,7 +29518,7 @@
         <v>14</v>
       </c>
       <c r="F340" s="2">
-        <v>1516</v>
+        <v>3878</v>
       </c>
       <c r="G340" s="2" t="s">
         <v>15</v>
@@ -29550,7 +29550,7 @@
         <v>14</v>
       </c>
       <c r="F341" s="2">
-        <v>1874</v>
+        <v>4734</v>
       </c>
       <c r="G341" s="2" t="s">
         <v>15</v>
@@ -29582,7 +29582,7 @@
         <v>14</v>
       </c>
       <c r="F342" s="2">
-        <v>4381</v>
+        <v>1033</v>
       </c>
       <c r="G342" s="2" t="s">
         <v>15</v>
@@ -29614,7 +29614,7 @@
         <v>14</v>
       </c>
       <c r="F343" s="2">
-        <v>4729</v>
+        <v>2572</v>
       </c>
       <c r="G343" s="2" t="s">
         <v>15</v>
@@ -29646,7 +29646,7 @@
         <v>14</v>
       </c>
       <c r="F344" s="2">
-        <v>3553</v>
+        <v>4519</v>
       </c>
       <c r="G344" s="2" t="s">
         <v>15</v>
@@ -29678,7 +29678,7 @@
         <v>14</v>
       </c>
       <c r="F345" s="2">
-        <v>1112</v>
+        <v>1204</v>
       </c>
       <c r="G345" s="2" t="s">
         <v>15</v>
@@ -29710,7 +29710,7 @@
         <v>14</v>
       </c>
       <c r="F346" s="2">
-        <v>3855</v>
+        <v>949</v>
       </c>
       <c r="G346" s="2" t="s">
         <v>15</v>
@@ -29742,7 +29742,7 @@
         <v>14</v>
       </c>
       <c r="F347" s="2">
-        <v>2902</v>
+        <v>3776</v>
       </c>
       <c r="G347" s="2" t="s">
         <v>15</v>
@@ -29774,7 +29774,7 @@
         <v>14</v>
       </c>
       <c r="F348" s="2">
-        <v>1095</v>
+        <v>4790</v>
       </c>
       <c r="G348" s="2" t="s">
         <v>15</v>
@@ -29806,7 +29806,7 @@
         <v>14</v>
       </c>
       <c r="F349" s="2">
-        <v>3587</v>
+        <v>4481</v>
       </c>
       <c r="G349" s="2" t="s">
         <v>15</v>
@@ -29838,7 +29838,7 @@
         <v>14</v>
       </c>
       <c r="F350" s="2">
-        <v>2294</v>
+        <v>2035</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>15</v>
@@ -29870,7 +29870,7 @@
         <v>14</v>
       </c>
       <c r="F351" s="2">
-        <v>2353</v>
+        <v>3276</v>
       </c>
       <c r="G351" s="2" t="s">
         <v>15</v>
@@ -29902,7 +29902,7 @@
         <v>14</v>
       </c>
       <c r="F352" s="2">
-        <v>3640</v>
+        <v>1925</v>
       </c>
       <c r="G352" s="2" t="s">
         <v>15</v>
@@ -29934,7 +29934,7 @@
         <v>14</v>
       </c>
       <c r="F353" s="2">
-        <v>3672</v>
+        <v>2434</v>
       </c>
       <c r="G353" s="2" t="s">
         <v>15</v>
@@ -29966,7 +29966,7 @@
         <v>14</v>
       </c>
       <c r="F354" s="2">
-        <v>2866</v>
+        <v>1577</v>
       </c>
       <c r="G354" s="2" t="s">
         <v>15</v>
@@ -29998,7 +29998,7 @@
         <v>14</v>
       </c>
       <c r="F355" s="2">
-        <v>4777</v>
+        <v>2803</v>
       </c>
       <c r="G355" s="2" t="s">
         <v>15</v>
@@ -30030,7 +30030,7 @@
         <v>14</v>
       </c>
       <c r="F356" s="2">
-        <v>3993</v>
+        <v>3019</v>
       </c>
       <c r="G356" s="2" t="s">
         <v>15</v>
@@ -30062,7 +30062,7 @@
         <v>14</v>
       </c>
       <c r="F357" s="2">
-        <v>932</v>
+        <v>1791</v>
       </c>
       <c r="G357" s="2" t="s">
         <v>15</v>
@@ -30094,7 +30094,7 @@
         <v>14</v>
       </c>
       <c r="F358" s="2">
-        <v>985</v>
+        <v>3160</v>
       </c>
       <c r="G358" s="2" t="s">
         <v>15</v>
@@ -30126,7 +30126,7 @@
         <v>14</v>
       </c>
       <c r="F359" s="2">
-        <v>3836</v>
+        <v>1158</v>
       </c>
       <c r="G359" s="2" t="s">
         <v>15</v>
@@ -30158,7 +30158,7 @@
         <v>14</v>
       </c>
       <c r="F360" s="2">
-        <v>3085</v>
+        <v>4266</v>
       </c>
       <c r="G360" s="2" t="s">
         <v>15</v>
@@ -30190,7 +30190,7 @@
         <v>14</v>
       </c>
       <c r="F361" s="2">
-        <v>2465</v>
+        <v>1078</v>
       </c>
       <c r="G361" s="2" t="s">
         <v>15</v>
@@ -30222,7 +30222,7 @@
         <v>14</v>
       </c>
       <c r="F362" s="2">
-        <v>2096</v>
+        <v>4561</v>
       </c>
       <c r="G362" s="2" t="s">
         <v>15</v>
@@ -30254,7 +30254,7 @@
         <v>14</v>
       </c>
       <c r="F363" s="2">
-        <v>1168</v>
+        <v>3240</v>
       </c>
       <c r="G363" s="2" t="s">
         <v>15</v>
@@ -30286,7 +30286,7 @@
         <v>14</v>
       </c>
       <c r="F364" s="2">
-        <v>4558</v>
+        <v>916</v>
       </c>
       <c r="G364" s="2" t="s">
         <v>15</v>
@@ -30318,7 +30318,7 @@
         <v>14</v>
       </c>
       <c r="F365" s="2">
-        <v>1487</v>
+        <v>2950</v>
       </c>
       <c r="G365" s="2" t="s">
         <v>15</v>
@@ -30350,7 +30350,7 @@
         <v>14</v>
       </c>
       <c r="F366" s="2">
-        <v>1011</v>
+        <v>3953</v>
       </c>
       <c r="G366" s="2" t="s">
         <v>15</v>
@@ -30382,7 +30382,7 @@
         <v>14</v>
       </c>
       <c r="F367" s="2">
-        <v>3882</v>
+        <v>1130</v>
       </c>
       <c r="G367" s="2" t="s">
         <v>15</v>
@@ -30414,7 +30414,7 @@
         <v>14</v>
       </c>
       <c r="F368" s="2">
-        <v>3010</v>
+        <v>1933</v>
       </c>
       <c r="G368" s="2" t="s">
         <v>15</v>
@@ -30446,7 +30446,7 @@
         <v>14</v>
       </c>
       <c r="F369" s="2">
-        <v>1328</v>
+        <v>4226</v>
       </c>
       <c r="G369" s="2" t="s">
         <v>15</v>
@@ -30478,7 +30478,7 @@
         <v>14</v>
       </c>
       <c r="F370" s="2">
-        <v>2958</v>
+        <v>1527</v>
       </c>
       <c r="G370" s="2" t="s">
         <v>15</v>
@@ -30510,7 +30510,7 @@
         <v>14</v>
       </c>
       <c r="F371" s="2">
-        <v>901</v>
+        <v>3905</v>
       </c>
       <c r="G371" s="2" t="s">
         <v>15</v>
@@ -30542,7 +30542,7 @@
         <v>14</v>
       </c>
       <c r="F372" s="2">
-        <v>3539</v>
+        <v>2707</v>
       </c>
       <c r="G372" s="2" t="s">
         <v>15</v>
@@ -30574,7 +30574,7 @@
         <v>14</v>
       </c>
       <c r="F373" s="2">
-        <v>2758</v>
+        <v>1148</v>
       </c>
       <c r="G373" s="2" t="s">
         <v>15</v>
@@ -30606,7 +30606,7 @@
         <v>14</v>
       </c>
       <c r="F374" s="2">
-        <v>3005</v>
+        <v>4668</v>
       </c>
       <c r="G374" s="2" t="s">
         <v>15</v>
@@ -30638,7 +30638,7 @@
         <v>14</v>
       </c>
       <c r="F375" s="2">
-        <v>4755</v>
+        <v>2035</v>
       </c>
       <c r="G375" s="2" t="s">
         <v>15</v>
@@ -30670,7 +30670,7 @@
         <v>14</v>
       </c>
       <c r="F376" s="2">
-        <v>2112</v>
+        <v>2211</v>
       </c>
       <c r="G376" s="2" t="s">
         <v>15</v>
@@ -30702,7 +30702,7 @@
         <v>14</v>
       </c>
       <c r="F377" s="2">
-        <v>2645</v>
+        <v>820</v>
       </c>
       <c r="G377" s="2" t="s">
         <v>15</v>
@@ -30734,7 +30734,7 @@
         <v>14</v>
       </c>
       <c r="F378" s="2">
-        <v>996</v>
+        <v>4217</v>
       </c>
       <c r="G378" s="2" t="s">
         <v>15</v>
@@ -30766,7 +30766,7 @@
         <v>14</v>
       </c>
       <c r="F379" s="2">
-        <v>1786</v>
+        <v>1336</v>
       </c>
       <c r="G379" s="2" t="s">
         <v>15</v>
@@ -30798,7 +30798,7 @@
         <v>14</v>
       </c>
       <c r="F380" s="2">
-        <v>2699</v>
+        <v>1602</v>
       </c>
       <c r="G380" s="2" t="s">
         <v>15</v>
@@ -30830,7 +30830,7 @@
         <v>14</v>
       </c>
       <c r="F381" s="2">
-        <v>1302</v>
+        <v>1575</v>
       </c>
       <c r="G381" s="2" t="s">
         <v>15</v>
@@ -30862,7 +30862,7 @@
         <v>14</v>
       </c>
       <c r="F382" s="2">
-        <v>1931</v>
+        <v>4248</v>
       </c>
       <c r="G382" s="2" t="s">
         <v>15</v>
@@ -30894,7 +30894,7 @@
         <v>14</v>
       </c>
       <c r="F383" s="2">
-        <v>4263</v>
+        <v>3630</v>
       </c>
       <c r="G383" s="2" t="s">
         <v>15</v>
@@ -30926,7 +30926,7 @@
         <v>14</v>
       </c>
       <c r="F384" s="2">
-        <v>3284</v>
+        <v>805</v>
       </c>
       <c r="G384" s="2" t="s">
         <v>15</v>
@@ -30958,7 +30958,7 @@
         <v>14</v>
       </c>
       <c r="F385" s="2">
-        <v>4677</v>
+        <v>2828</v>
       </c>
       <c r="G385" s="2" t="s">
         <v>15</v>
@@ -30990,7 +30990,7 @@
         <v>14</v>
       </c>
       <c r="F386" s="2">
-        <v>1576</v>
+        <v>2684</v>
       </c>
       <c r="G386" s="2" t="s">
         <v>15</v>
@@ -31022,7 +31022,7 @@
         <v>14</v>
       </c>
       <c r="F387" s="2">
-        <v>1599</v>
+        <v>3711</v>
       </c>
       <c r="G387" s="2" t="s">
         <v>15</v>
@@ -31054,7 +31054,7 @@
         <v>14</v>
       </c>
       <c r="F388" s="2">
-        <v>3992</v>
+        <v>3359</v>
       </c>
       <c r="G388" s="2" t="s">
         <v>15</v>
@@ -31086,7 +31086,7 @@
         <v>14</v>
       </c>
       <c r="F389" s="2">
-        <v>1328</v>
+        <v>4241</v>
       </c>
       <c r="G389" s="2" t="s">
         <v>15</v>
@@ -31118,7 +31118,7 @@
         <v>14</v>
       </c>
       <c r="F390" s="2">
-        <v>3471</v>
+        <v>1721</v>
       </c>
       <c r="G390" s="2" t="s">
         <v>15</v>
@@ -31150,7 +31150,7 @@
         <v>14</v>
       </c>
       <c r="F391" s="2">
-        <v>1270</v>
+        <v>1652</v>
       </c>
       <c r="G391" s="2" t="s">
         <v>15</v>
@@ -31182,7 +31182,7 @@
         <v>14</v>
       </c>
       <c r="F392" s="2">
-        <v>1582</v>
+        <v>3886</v>
       </c>
       <c r="G392" s="2" t="s">
         <v>15</v>
@@ -31214,7 +31214,7 @@
         <v>14</v>
       </c>
       <c r="F393" s="2">
-        <v>4522</v>
+        <v>3144</v>
       </c>
       <c r="G393" s="2" t="s">
         <v>15</v>
@@ -31246,7 +31246,7 @@
         <v>14</v>
       </c>
       <c r="F394" s="2">
-        <v>1236</v>
+        <v>1648</v>
       </c>
       <c r="G394" s="2" t="s">
         <v>15</v>
@@ -31278,7 +31278,7 @@
         <v>14</v>
       </c>
       <c r="F395" s="2">
-        <v>1493</v>
+        <v>4796</v>
       </c>
       <c r="G395" s="2" t="s">
         <v>15</v>
@@ -31310,7 +31310,7 @@
         <v>14</v>
       </c>
       <c r="F396" s="2">
-        <v>3975</v>
+        <v>3486</v>
       </c>
       <c r="G396" s="2" t="s">
         <v>15</v>
@@ -31342,7 +31342,7 @@
         <v>14</v>
       </c>
       <c r="F397" s="2">
-        <v>1558</v>
+        <v>4435</v>
       </c>
       <c r="G397" s="2" t="s">
         <v>15</v>
@@ -31374,7 +31374,7 @@
         <v>14</v>
       </c>
       <c r="F398" s="2">
-        <v>2726</v>
+        <v>2397</v>
       </c>
       <c r="G398" s="2" t="s">
         <v>15</v>
@@ -31406,7 +31406,7 @@
         <v>14</v>
       </c>
       <c r="F399" s="2">
-        <v>1875</v>
+        <v>1939</v>
       </c>
       <c r="G399" s="2" t="s">
         <v>15</v>
@@ -31438,7 +31438,7 @@
         <v>14</v>
       </c>
       <c r="F400" s="2">
-        <v>880</v>
+        <v>4568</v>
       </c>
       <c r="G400" s="2" t="s">
         <v>15</v>
@@ -31470,7 +31470,7 @@
         <v>14</v>
       </c>
       <c r="F401" s="2">
-        <v>4647</v>
+        <v>4609</v>
       </c>
       <c r="G401" s="2" t="s">
         <v>15</v>
@@ -31502,7 +31502,7 @@
         <v>14</v>
       </c>
       <c r="F402" s="2">
-        <v>3028</v>
+        <v>4618</v>
       </c>
       <c r="G402" s="2" t="s">
         <v>15</v>
@@ -31534,7 +31534,7 @@
         <v>14</v>
       </c>
       <c r="F403" s="2">
-        <v>2676</v>
+        <v>3622</v>
       </c>
       <c r="G403" s="2" t="s">
         <v>15</v>
@@ -31566,7 +31566,7 @@
         <v>14</v>
       </c>
       <c r="F404" s="2">
-        <v>990</v>
+        <v>2977</v>
       </c>
       <c r="G404" s="2" t="s">
         <v>15</v>
@@ -31598,7 +31598,7 @@
         <v>14</v>
       </c>
       <c r="F405" s="2">
-        <v>4679</v>
+        <v>2658</v>
       </c>
       <c r="G405" s="2" t="s">
         <v>15</v>
@@ -31630,7 +31630,7 @@
         <v>14</v>
       </c>
       <c r="F406" s="2">
-        <v>4110</v>
+        <v>2247</v>
       </c>
       <c r="G406" s="2" t="s">
         <v>15</v>
@@ -31662,7 +31662,7 @@
         <v>14</v>
       </c>
       <c r="F407" s="2">
-        <v>1085</v>
+        <v>3725</v>
       </c>
       <c r="G407" s="2" t="s">
         <v>15</v>
@@ -31694,7 +31694,7 @@
         <v>14</v>
       </c>
       <c r="F408" s="2">
-        <v>3761</v>
+        <v>4060</v>
       </c>
       <c r="G408" s="2" t="s">
         <v>15</v>
@@ -31726,7 +31726,7 @@
         <v>14</v>
       </c>
       <c r="F409" s="2">
-        <v>1164</v>
+        <v>1351</v>
       </c>
       <c r="G409" s="2" t="s">
         <v>15</v>
@@ -31758,7 +31758,7 @@
         <v>14</v>
       </c>
       <c r="F410" s="2">
-        <v>3649</v>
+        <v>3136</v>
       </c>
       <c r="G410" s="2" t="s">
         <v>15</v>
@@ -31790,7 +31790,7 @@
         <v>14</v>
       </c>
       <c r="F411" s="2">
-        <v>1997</v>
+        <v>3957</v>
       </c>
       <c r="G411" s="2" t="s">
         <v>15</v>
@@ -31822,7 +31822,7 @@
         <v>14</v>
       </c>
       <c r="F412" s="2">
-        <v>2072</v>
+        <v>1766</v>
       </c>
       <c r="G412" s="2" t="s">
         <v>15</v>
@@ -31854,7 +31854,7 @@
         <v>14</v>
       </c>
       <c r="F413" s="2">
-        <v>3226</v>
+        <v>3467</v>
       </c>
       <c r="G413" s="2" t="s">
         <v>15</v>
@@ -31886,7 +31886,7 @@
         <v>14</v>
       </c>
       <c r="F414" s="2">
-        <v>3758</v>
+        <v>2209</v>
       </c>
       <c r="G414" s="2" t="s">
         <v>15</v>
@@ -31918,7 +31918,7 @@
         <v>14</v>
       </c>
       <c r="F415" s="2">
-        <v>2552</v>
+        <v>3576</v>
       </c>
       <c r="G415" s="2" t="s">
         <v>15</v>
@@ -31950,7 +31950,7 @@
         <v>14</v>
       </c>
       <c r="F416" s="2">
-        <v>4136</v>
+        <v>1586</v>
       </c>
       <c r="G416" s="2" t="s">
         <v>15</v>
@@ -31982,7 +31982,7 @@
         <v>14</v>
       </c>
       <c r="F417" s="2">
-        <v>2681</v>
+        <v>4717</v>
       </c>
       <c r="G417" s="2" t="s">
         <v>15</v>
@@ -32014,7 +32014,7 @@
         <v>14</v>
       </c>
       <c r="F418" s="2">
-        <v>4032</v>
+        <v>4756</v>
       </c>
       <c r="G418" s="2" t="s">
         <v>15</v>
@@ -32046,7 +32046,7 @@
         <v>14</v>
       </c>
       <c r="F419" s="2">
-        <v>2766</v>
+        <v>4547</v>
       </c>
       <c r="G419" s="2" t="s">
         <v>15</v>
@@ -32078,7 +32078,7 @@
         <v>14</v>
       </c>
       <c r="F420" s="2">
-        <v>2832</v>
+        <v>4223</v>
       </c>
       <c r="G420" s="2" t="s">
         <v>15</v>
@@ -32110,7 +32110,7 @@
         <v>14</v>
       </c>
       <c r="F421" s="2">
-        <v>1211</v>
+        <v>3222</v>
       </c>
       <c r="G421" s="2" t="s">
         <v>15</v>
@@ -32142,7 +32142,7 @@
         <v>14</v>
       </c>
       <c r="F422" s="2">
-        <v>4033</v>
+        <v>2911</v>
       </c>
       <c r="G422" s="2" t="s">
         <v>15</v>
@@ -32174,7 +32174,7 @@
         <v>14</v>
       </c>
       <c r="F423" s="2">
-        <v>1074</v>
+        <v>3390</v>
       </c>
       <c r="G423" s="2" t="s">
         <v>15</v>
@@ -32206,7 +32206,7 @@
         <v>14</v>
       </c>
       <c r="F424" s="2">
-        <v>2292</v>
+        <v>4514</v>
       </c>
       <c r="G424" s="2" t="s">
         <v>15</v>
@@ -32238,7 +32238,7 @@
         <v>14</v>
       </c>
       <c r="F425" s="2">
-        <v>1285</v>
+        <v>3770</v>
       </c>
       <c r="G425" s="2" t="s">
         <v>15</v>
@@ -32270,7 +32270,7 @@
         <v>14</v>
       </c>
       <c r="F426" s="2">
-        <v>3517</v>
+        <v>4719</v>
       </c>
       <c r="G426" s="2" t="s">
         <v>15</v>
@@ -32302,7 +32302,7 @@
         <v>14</v>
       </c>
       <c r="F427" s="2">
-        <v>4108</v>
+        <v>1011</v>
       </c>
       <c r="G427" s="2" t="s">
         <v>15</v>
@@ -32334,7 +32334,7 @@
         <v>14</v>
       </c>
       <c r="F428" s="2">
-        <v>2722</v>
+        <v>2536</v>
       </c>
       <c r="G428" s="2" t="s">
         <v>15</v>
@@ -32366,7 +32366,7 @@
         <v>14</v>
       </c>
       <c r="F429" s="2">
-        <v>2391</v>
+        <v>3936</v>
       </c>
       <c r="G429" s="2" t="s">
         <v>15</v>
@@ -32398,7 +32398,7 @@
         <v>14</v>
       </c>
       <c r="F430" s="2">
-        <v>3521</v>
+        <v>1719</v>
       </c>
       <c r="G430" s="2" t="s">
         <v>15</v>
@@ -32430,7 +32430,7 @@
         <v>14</v>
       </c>
       <c r="F431" s="2">
-        <v>3952</v>
+        <v>2272</v>
       </c>
       <c r="G431" s="2" t="s">
         <v>15</v>
@@ -32462,7 +32462,7 @@
         <v>14</v>
       </c>
       <c r="F432" s="2">
-        <v>4083</v>
+        <v>1567</v>
       </c>
       <c r="G432" s="2" t="s">
         <v>15</v>
@@ -32494,7 +32494,7 @@
         <v>14</v>
       </c>
       <c r="F433" s="2">
-        <v>3442</v>
+        <v>3917</v>
       </c>
       <c r="G433" s="2" t="s">
         <v>15</v>
@@ -32526,7 +32526,7 @@
         <v>14</v>
       </c>
       <c r="F434" s="2">
-        <v>2922</v>
+        <v>855</v>
       </c>
       <c r="G434" s="2" t="s">
         <v>15</v>
@@ -32558,7 +32558,7 @@
         <v>14</v>
       </c>
       <c r="F435" s="2">
-        <v>2540</v>
+        <v>1548</v>
       </c>
       <c r="G435" s="2" t="s">
         <v>15</v>
@@ -32590,7 +32590,7 @@
         <v>14</v>
       </c>
       <c r="F436" s="2">
-        <v>3988</v>
+        <v>1708</v>
       </c>
       <c r="G436" s="2" t="s">
         <v>15</v>
@@ -32622,7 +32622,7 @@
         <v>14</v>
       </c>
       <c r="F437" s="2">
-        <v>2379</v>
+        <v>3791</v>
       </c>
       <c r="G437" s="2" t="s">
         <v>15</v>
@@ -32654,7 +32654,7 @@
         <v>14</v>
       </c>
       <c r="F438" s="2">
-        <v>3032</v>
+        <v>1162</v>
       </c>
       <c r="G438" s="2" t="s">
         <v>15</v>
@@ -32686,7 +32686,7 @@
         <v>14</v>
       </c>
       <c r="F439" s="2">
-        <v>3176</v>
+        <v>1427</v>
       </c>
       <c r="G439" s="2" t="s">
         <v>15</v>
@@ -32718,7 +32718,7 @@
         <v>14</v>
       </c>
       <c r="F440" s="2">
-        <v>3795</v>
+        <v>4183</v>
       </c>
       <c r="G440" s="2" t="s">
         <v>15</v>
@@ -32750,7 +32750,7 @@
         <v>14</v>
       </c>
       <c r="F441" s="2">
-        <v>3443</v>
+        <v>1958</v>
       </c>
       <c r="G441" s="2" t="s">
         <v>15</v>
@@ -32782,7 +32782,7 @@
         <v>14</v>
       </c>
       <c r="F442" s="2">
-        <v>2605</v>
+        <v>1970</v>
       </c>
       <c r="G442" s="2" t="s">
         <v>15</v>
@@ -32814,7 +32814,7 @@
         <v>14</v>
       </c>
       <c r="F443" s="2">
-        <v>3369</v>
+        <v>4057</v>
       </c>
       <c r="G443" s="2" t="s">
         <v>15</v>
@@ -32846,7 +32846,7 @@
         <v>14</v>
       </c>
       <c r="F444" s="2">
-        <v>4702</v>
+        <v>1268</v>
       </c>
       <c r="G444" s="2" t="s">
         <v>15</v>
@@ -32878,7 +32878,7 @@
         <v>14</v>
       </c>
       <c r="F445" s="2">
-        <v>1767</v>
+        <v>1348</v>
       </c>
       <c r="G445" s="2" t="s">
         <v>15</v>
@@ -32910,7 +32910,7 @@
         <v>14</v>
       </c>
       <c r="F446" s="2">
-        <v>1614</v>
+        <v>1294</v>
       </c>
       <c r="G446" s="2" t="s">
         <v>15</v>
@@ -32942,7 +32942,7 @@
         <v>14</v>
       </c>
       <c r="F447" s="2">
-        <v>3406</v>
+        <v>3173</v>
       </c>
       <c r="G447" s="2" t="s">
         <v>15</v>
@@ -32974,7 +32974,7 @@
         <v>14</v>
       </c>
       <c r="F448" s="2">
-        <v>2220</v>
+        <v>2994</v>
       </c>
       <c r="G448" s="2" t="s">
         <v>15</v>
@@ -33006,7 +33006,7 @@
         <v>14</v>
       </c>
       <c r="F449" s="2">
-        <v>4767</v>
+        <v>2110</v>
       </c>
       <c r="G449" s="2" t="s">
         <v>15</v>
@@ -33038,7 +33038,7 @@
         <v>14</v>
       </c>
       <c r="F450" s="2">
-        <v>2164</v>
+        <v>1997</v>
       </c>
       <c r="G450" s="2" t="s">
         <v>15</v>
@@ -33070,7 +33070,7 @@
         <v>14</v>
       </c>
       <c r="F451" s="2">
-        <v>1956</v>
+        <v>3126</v>
       </c>
       <c r="G451" s="2" t="s">
         <v>15</v>
@@ -33102,7 +33102,7 @@
         <v>14</v>
       </c>
       <c r="F452" s="2">
-        <v>2927</v>
+        <v>2191</v>
       </c>
       <c r="G452" s="2" t="s">
         <v>15</v>
@@ -33134,7 +33134,7 @@
         <v>14</v>
       </c>
       <c r="F453" s="2">
-        <v>3916</v>
+        <v>2169</v>
       </c>
       <c r="G453" s="2" t="s">
         <v>15</v>
@@ -33166,7 +33166,7 @@
         <v>14</v>
       </c>
       <c r="F454" s="2">
-        <v>2357</v>
+        <v>4581</v>
       </c>
       <c r="G454" s="2" t="s">
         <v>15</v>
@@ -33198,7 +33198,7 @@
         <v>14</v>
       </c>
       <c r="F455" s="2">
-        <v>2914</v>
+        <v>3311</v>
       </c>
       <c r="G455" s="2" t="s">
         <v>15</v>
@@ -33230,7 +33230,7 @@
         <v>14</v>
       </c>
       <c r="F456" s="2">
-        <v>825</v>
+        <v>2417</v>
       </c>
       <c r="G456" s="2" t="s">
         <v>15</v>
@@ -33262,7 +33262,7 @@
         <v>14</v>
       </c>
       <c r="F457" s="2">
-        <v>1491</v>
+        <v>3618</v>
       </c>
       <c r="G457" s="2" t="s">
         <v>15</v>
@@ -33294,7 +33294,7 @@
         <v>14</v>
       </c>
       <c r="F458" s="2">
-        <v>867</v>
+        <v>815</v>
       </c>
       <c r="G458" s="2" t="s">
         <v>15</v>
@@ -33326,7 +33326,7 @@
         <v>14</v>
       </c>
       <c r="F459" s="2">
-        <v>2884</v>
+        <v>3526</v>
       </c>
       <c r="G459" s="2" t="s">
         <v>15</v>
@@ -33358,7 +33358,7 @@
         <v>14</v>
       </c>
       <c r="F460" s="2">
-        <v>1735</v>
+        <v>3579</v>
       </c>
       <c r="G460" s="2" t="s">
         <v>15</v>
@@ -33390,7 +33390,7 @@
         <v>14</v>
       </c>
       <c r="F461" s="2">
-        <v>931</v>
+        <v>3860</v>
       </c>
       <c r="G461" s="2" t="s">
         <v>15</v>
@@ -33422,7 +33422,7 @@
         <v>14</v>
       </c>
       <c r="F462" s="2">
-        <v>3658</v>
+        <v>3850</v>
       </c>
       <c r="G462" s="2" t="s">
         <v>15</v>
@@ -33454,7 +33454,7 @@
         <v>14</v>
       </c>
       <c r="F463" s="2">
-        <v>4732</v>
+        <v>1277</v>
       </c>
       <c r="G463" s="2" t="s">
         <v>15</v>
@@ -33486,7 +33486,7 @@
         <v>14</v>
       </c>
       <c r="F464" s="2">
-        <v>4411</v>
+        <v>1509</v>
       </c>
       <c r="G464" s="2" t="s">
         <v>15</v>
@@ -33518,7 +33518,7 @@
         <v>14</v>
       </c>
       <c r="F465" s="2">
-        <v>4170</v>
+        <v>4216</v>
       </c>
       <c r="G465" s="2" t="s">
         <v>15</v>
@@ -33550,7 +33550,7 @@
         <v>14</v>
       </c>
       <c r="F466" s="2">
-        <v>2958</v>
+        <v>820</v>
       </c>
       <c r="G466" s="2" t="s">
         <v>15</v>
@@ -33582,7 +33582,7 @@
         <v>14</v>
       </c>
       <c r="F467" s="2">
-        <v>1615</v>
+        <v>3194</v>
       </c>
       <c r="G467" s="2" t="s">
         <v>15</v>
@@ -33614,7 +33614,7 @@
         <v>14</v>
       </c>
       <c r="F468" s="2">
-        <v>2441</v>
+        <v>4725</v>
       </c>
       <c r="G468" s="2" t="s">
         <v>15</v>
@@ -33646,7 +33646,7 @@
         <v>14</v>
       </c>
       <c r="F469" s="2">
-        <v>3483</v>
+        <v>1521</v>
       </c>
       <c r="G469" s="2" t="s">
         <v>15</v>
@@ -33678,7 +33678,7 @@
         <v>14</v>
       </c>
       <c r="F470" s="2">
-        <v>1685</v>
+        <v>2906</v>
       </c>
       <c r="G470" s="2" t="s">
         <v>15</v>
@@ -33710,7 +33710,7 @@
         <v>14</v>
       </c>
       <c r="F471" s="2">
-        <v>2762</v>
+        <v>3588</v>
       </c>
       <c r="G471" s="2" t="s">
         <v>15</v>

--- a/reports/selenium/latest/excel/Automation_Test_Report.xlsx
+++ b/reports/selenium/latest/excel/Automation_Test_Report.xlsx
@@ -3084,7 +3084,7 @@
     <t>Build</t>
   </si>
   <si>
-    <t>13</t>
+    <t>14</t>
   </si>
   <si>
     <t>Branch</t>
@@ -3096,13 +3096,13 @@
     <t>Commit</t>
   </si>
   <si>
-    <t>807dd5ee9294</t>
+    <t>010bbacb5214</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T03:46:19.018Z</t>
+    <t>2026-08-19T03:54:59.680Z</t>
   </si>
   <si>
     <t>Browser</t>
@@ -3607,7 +3607,7 @@
         <v>14</v>
       </c>
       <c r="F2" s="2">
-        <v>2571</v>
+        <v>1450</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>15</v>
@@ -3639,7 +3639,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="2">
-        <v>4035</v>
+        <v>2489</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>15</v>
@@ -3671,7 +3671,7 @@
         <v>14</v>
       </c>
       <c r="F4" s="2">
-        <v>4448</v>
+        <v>2638</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
@@ -3703,7 +3703,7 @@
         <v>14</v>
       </c>
       <c r="F5" s="2">
-        <v>4189</v>
+        <v>974</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
@@ -3735,7 +3735,7 @@
         <v>14</v>
       </c>
       <c r="F6" s="2">
-        <v>1262</v>
+        <v>4614</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -3767,7 +3767,7 @@
         <v>14</v>
       </c>
       <c r="F7" s="2">
-        <v>4074</v>
+        <v>2741</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -3799,7 +3799,7 @@
         <v>14</v>
       </c>
       <c r="F8" s="2">
-        <v>3659</v>
+        <v>3827</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -3831,7 +3831,7 @@
         <v>14</v>
       </c>
       <c r="F9" s="2">
-        <v>3314</v>
+        <v>2828</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -3863,7 +3863,7 @@
         <v>14</v>
       </c>
       <c r="F10" s="2">
-        <v>3168</v>
+        <v>3647</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
@@ -3895,7 +3895,7 @@
         <v>14</v>
       </c>
       <c r="F11" s="2">
-        <v>2537</v>
+        <v>1609</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
@@ -3927,7 +3927,7 @@
         <v>14</v>
       </c>
       <c r="F12" s="2">
-        <v>1095</v>
+        <v>4028</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
@@ -3959,7 +3959,7 @@
         <v>14</v>
       </c>
       <c r="F13" s="2">
-        <v>3236</v>
+        <v>2234</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -3991,7 +3991,7 @@
         <v>14</v>
       </c>
       <c r="F14" s="2">
-        <v>3381</v>
+        <v>2257</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -4023,7 +4023,7 @@
         <v>14</v>
       </c>
       <c r="F15" s="2">
-        <v>2503</v>
+        <v>4552</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -4055,7 +4055,7 @@
         <v>14</v>
       </c>
       <c r="F16" s="2">
-        <v>2313</v>
+        <v>4048</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
@@ -4087,7 +4087,7 @@
         <v>14</v>
       </c>
       <c r="F17" s="2">
-        <v>4287</v>
+        <v>1247</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
@@ -4119,7 +4119,7 @@
         <v>14</v>
       </c>
       <c r="F18" s="2">
-        <v>1738</v>
+        <v>1995</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
@@ -4151,7 +4151,7 @@
         <v>14</v>
       </c>
       <c r="F19" s="2">
-        <v>2023</v>
+        <v>858</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
@@ -4183,7 +4183,7 @@
         <v>14</v>
       </c>
       <c r="F20" s="2">
-        <v>3168</v>
+        <v>4489</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
@@ -4215,7 +4215,7 @@
         <v>14</v>
       </c>
       <c r="F21" s="2">
-        <v>2611</v>
+        <v>4276</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -4247,7 +4247,7 @@
         <v>14</v>
       </c>
       <c r="F22" s="2">
-        <v>4371</v>
+        <v>3282</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -4279,7 +4279,7 @@
         <v>14</v>
       </c>
       <c r="F23" s="2">
-        <v>810</v>
+        <v>4545</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -4311,7 +4311,7 @@
         <v>14</v>
       </c>
       <c r="F24" s="2">
-        <v>1467</v>
+        <v>1826</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -4343,7 +4343,7 @@
         <v>14</v>
       </c>
       <c r="F25" s="2">
-        <v>3921</v>
+        <v>4127</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -4375,7 +4375,7 @@
         <v>14</v>
       </c>
       <c r="F26" s="2">
-        <v>2816</v>
+        <v>1717</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -4407,7 +4407,7 @@
         <v>14</v>
       </c>
       <c r="F27" s="2">
-        <v>3101</v>
+        <v>3328</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>15</v>
@@ -4439,7 +4439,7 @@
         <v>14</v>
       </c>
       <c r="F28" s="2">
-        <v>1789</v>
+        <v>3302</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>15</v>
@@ -4471,7 +4471,7 @@
         <v>14</v>
       </c>
       <c r="F29" s="2">
-        <v>2816</v>
+        <v>3596</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>15</v>
@@ -4503,7 +4503,7 @@
         <v>14</v>
       </c>
       <c r="F30" s="2">
-        <v>1257</v>
+        <v>3771</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>15</v>
@@ -4535,7 +4535,7 @@
         <v>14</v>
       </c>
       <c r="F31" s="2">
-        <v>1809</v>
+        <v>3017</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>15</v>
@@ -4567,7 +4567,7 @@
         <v>14</v>
       </c>
       <c r="F32" s="2">
-        <v>921</v>
+        <v>2397</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>15</v>
@@ -4599,7 +4599,7 @@
         <v>14</v>
       </c>
       <c r="F33" s="2">
-        <v>3286</v>
+        <v>2673</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>15</v>
@@ -4631,7 +4631,7 @@
         <v>14</v>
       </c>
       <c r="F34" s="2">
-        <v>2359</v>
+        <v>3101</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>15</v>
@@ -4663,7 +4663,7 @@
         <v>14</v>
       </c>
       <c r="F35" s="2">
-        <v>2399</v>
+        <v>2429</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>15</v>
@@ -4695,7 +4695,7 @@
         <v>14</v>
       </c>
       <c r="F36" s="2">
-        <v>919</v>
+        <v>1150</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>15</v>
@@ -4727,7 +4727,7 @@
         <v>14</v>
       </c>
       <c r="F37" s="2">
-        <v>2222</v>
+        <v>2339</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>15</v>
@@ -4759,7 +4759,7 @@
         <v>14</v>
       </c>
       <c r="F38" s="2">
-        <v>4126</v>
+        <v>2212</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>15</v>
@@ -4791,7 +4791,7 @@
         <v>14</v>
       </c>
       <c r="F39" s="2">
-        <v>1770</v>
+        <v>2768</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>15</v>
@@ -4823,7 +4823,7 @@
         <v>14</v>
       </c>
       <c r="F40" s="2">
-        <v>4745</v>
+        <v>3111</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>15</v>
@@ -4855,7 +4855,7 @@
         <v>14</v>
       </c>
       <c r="F41" s="2">
-        <v>939</v>
+        <v>2828</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>15</v>
@@ -4887,7 +4887,7 @@
         <v>14</v>
       </c>
       <c r="F42" s="2">
-        <v>2217</v>
+        <v>978</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>15</v>
@@ -4919,7 +4919,7 @@
         <v>14</v>
       </c>
       <c r="F43" s="2">
-        <v>2056</v>
+        <v>1172</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>15</v>
@@ -4951,7 +4951,7 @@
         <v>14</v>
       </c>
       <c r="F44" s="2">
-        <v>4353</v>
+        <v>4229</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>15</v>
@@ -4983,7 +4983,7 @@
         <v>14</v>
       </c>
       <c r="F45" s="2">
-        <v>4046</v>
+        <v>987</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>15</v>
@@ -5015,7 +5015,7 @@
         <v>14</v>
       </c>
       <c r="F46" s="2">
-        <v>2187</v>
+        <v>1340</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>15</v>
@@ -5047,7 +5047,7 @@
         <v>14</v>
       </c>
       <c r="F47" s="2">
-        <v>1764</v>
+        <v>3810</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>15</v>
@@ -5079,7 +5079,7 @@
         <v>14</v>
       </c>
       <c r="F48" s="2">
-        <v>4569</v>
+        <v>4754</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>15</v>
@@ -5111,7 +5111,7 @@
         <v>14</v>
       </c>
       <c r="F49" s="2">
-        <v>1631</v>
+        <v>1126</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>15</v>
@@ -5143,7 +5143,7 @@
         <v>14</v>
       </c>
       <c r="F50" s="2">
-        <v>2235</v>
+        <v>855</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>15</v>
@@ -5175,7 +5175,7 @@
         <v>14</v>
       </c>
       <c r="F51" s="2">
-        <v>3622</v>
+        <v>1183</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>15</v>
@@ -5207,7 +5207,7 @@
         <v>14</v>
       </c>
       <c r="F52" s="2">
-        <v>1594</v>
+        <v>4028</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>15</v>
@@ -5239,7 +5239,7 @@
         <v>14</v>
       </c>
       <c r="F53" s="2">
-        <v>4166</v>
+        <v>1862</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>15</v>
@@ -5271,7 +5271,7 @@
         <v>14</v>
       </c>
       <c r="F54" s="2">
-        <v>2321</v>
+        <v>2924</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>15</v>
@@ -5303,7 +5303,7 @@
         <v>14</v>
       </c>
       <c r="F55" s="2">
-        <v>2661</v>
+        <v>1346</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>15</v>
@@ -5335,7 +5335,7 @@
         <v>14</v>
       </c>
       <c r="F56" s="2">
-        <v>1348</v>
+        <v>2612</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>15</v>
@@ -5367,7 +5367,7 @@
         <v>14</v>
       </c>
       <c r="F57" s="2">
-        <v>3186</v>
+        <v>2772</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>15</v>
@@ -5399,7 +5399,7 @@
         <v>14</v>
       </c>
       <c r="F58" s="2">
-        <v>4447</v>
+        <v>3387</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>15</v>
@@ -5431,7 +5431,7 @@
         <v>14</v>
       </c>
       <c r="F59" s="2">
-        <v>3327</v>
+        <v>1418</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>15</v>
@@ -5463,7 +5463,7 @@
         <v>14</v>
       </c>
       <c r="F60" s="2">
-        <v>927</v>
+        <v>1511</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>15</v>
@@ -5495,7 +5495,7 @@
         <v>14</v>
       </c>
       <c r="F61" s="2">
-        <v>1624</v>
+        <v>3534</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>15</v>
@@ -5527,7 +5527,7 @@
         <v>14</v>
       </c>
       <c r="F62" s="2">
-        <v>1855</v>
+        <v>4205</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>15</v>
@@ -5559,7 +5559,7 @@
         <v>14</v>
       </c>
       <c r="F63" s="2">
-        <v>2658</v>
+        <v>3890</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>15</v>
@@ -5591,7 +5591,7 @@
         <v>14</v>
       </c>
       <c r="F64" s="2">
-        <v>2376</v>
+        <v>4606</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>15</v>
@@ -5623,7 +5623,7 @@
         <v>14</v>
       </c>
       <c r="F65" s="2">
-        <v>4238</v>
+        <v>834</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>15</v>
@@ -5655,7 +5655,7 @@
         <v>14</v>
       </c>
       <c r="F66" s="2">
-        <v>3593</v>
+        <v>4523</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>15</v>
@@ -5687,7 +5687,7 @@
         <v>14</v>
       </c>
       <c r="F67" s="2">
-        <v>1934</v>
+        <v>4005</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>15</v>
@@ -5719,7 +5719,7 @@
         <v>14</v>
       </c>
       <c r="F68" s="2">
-        <v>1148</v>
+        <v>2798</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>15</v>
@@ -5751,7 +5751,7 @@
         <v>14</v>
       </c>
       <c r="F69" s="2">
-        <v>2832</v>
+        <v>1374</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>15</v>
@@ -5783,7 +5783,7 @@
         <v>14</v>
       </c>
       <c r="F70" s="2">
-        <v>4185</v>
+        <v>4360</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>15</v>
@@ -5815,7 +5815,7 @@
         <v>14</v>
       </c>
       <c r="F71" s="2">
-        <v>3100</v>
+        <v>2274</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>15</v>
@@ -5847,7 +5847,7 @@
         <v>14</v>
       </c>
       <c r="F72" s="2">
-        <v>1351</v>
+        <v>4204</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>15</v>
@@ -5879,7 +5879,7 @@
         <v>14</v>
       </c>
       <c r="F73" s="2">
-        <v>3018</v>
+        <v>4243</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>15</v>
@@ -5911,7 +5911,7 @@
         <v>14</v>
       </c>
       <c r="F74" s="2">
-        <v>1656</v>
+        <v>1783</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>15</v>
@@ -5943,7 +5943,7 @@
         <v>14</v>
       </c>
       <c r="F75" s="2">
-        <v>2834</v>
+        <v>3551</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>15</v>
@@ -5975,7 +5975,7 @@
         <v>14</v>
       </c>
       <c r="F76" s="2">
-        <v>4693</v>
+        <v>2555</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>15</v>
@@ -6007,7 +6007,7 @@
         <v>14</v>
       </c>
       <c r="F77" s="2">
-        <v>2651</v>
+        <v>1207</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>15</v>
@@ -6039,7 +6039,7 @@
         <v>14</v>
       </c>
       <c r="F78" s="2">
-        <v>1256</v>
+        <v>959</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>15</v>
@@ -6071,7 +6071,7 @@
         <v>14</v>
       </c>
       <c r="F79" s="2">
-        <v>969</v>
+        <v>3366</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>15</v>
@@ -6103,7 +6103,7 @@
         <v>14</v>
       </c>
       <c r="F80" s="2">
-        <v>3750</v>
+        <v>1196</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>15</v>
@@ -6135,7 +6135,7 @@
         <v>14</v>
       </c>
       <c r="F81" s="2">
-        <v>3680</v>
+        <v>1730</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>15</v>
@@ -6167,7 +6167,7 @@
         <v>14</v>
       </c>
       <c r="F82" s="2">
-        <v>2527</v>
+        <v>4771</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>15</v>
@@ -6199,7 +6199,7 @@
         <v>14</v>
       </c>
       <c r="F83" s="2">
-        <v>2710</v>
+        <v>1731</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>15</v>
@@ -6231,7 +6231,7 @@
         <v>14</v>
       </c>
       <c r="F84" s="2">
-        <v>3519</v>
+        <v>2551</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>15</v>
@@ -6263,7 +6263,7 @@
         <v>14</v>
       </c>
       <c r="F85" s="2">
-        <v>1319</v>
+        <v>3196</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>15</v>
@@ -6295,7 +6295,7 @@
         <v>14</v>
       </c>
       <c r="F86" s="2">
-        <v>3286</v>
+        <v>4215</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>15</v>
@@ -6327,7 +6327,7 @@
         <v>14</v>
       </c>
       <c r="F87" s="2">
-        <v>1263</v>
+        <v>2949</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>15</v>
@@ -6359,7 +6359,7 @@
         <v>14</v>
       </c>
       <c r="F88" s="2">
-        <v>3476</v>
+        <v>3415</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>15</v>
@@ -6391,7 +6391,7 @@
         <v>14</v>
       </c>
       <c r="F89" s="2">
-        <v>2448</v>
+        <v>3469</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>15</v>
@@ -6423,7 +6423,7 @@
         <v>14</v>
       </c>
       <c r="F90" s="2">
-        <v>2859</v>
+        <v>2636</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>15</v>
@@ -6455,7 +6455,7 @@
         <v>14</v>
       </c>
       <c r="F91" s="2">
-        <v>4700</v>
+        <v>1032</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>15</v>
@@ -6487,7 +6487,7 @@
         <v>14</v>
       </c>
       <c r="F92" s="2">
-        <v>4739</v>
+        <v>3305</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>15</v>
@@ -6519,7 +6519,7 @@
         <v>14</v>
       </c>
       <c r="F93" s="2">
-        <v>3696</v>
+        <v>3102</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>15</v>
@@ -6551,7 +6551,7 @@
         <v>14</v>
       </c>
       <c r="F94" s="2">
-        <v>1789</v>
+        <v>3782</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>15</v>
@@ -6583,7 +6583,7 @@
         <v>14</v>
       </c>
       <c r="F95" s="2">
-        <v>1544</v>
+        <v>1005</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>15</v>
@@ -6615,7 +6615,7 @@
         <v>14</v>
       </c>
       <c r="F96" s="2">
-        <v>1619</v>
+        <v>1868</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>15</v>
@@ -6647,7 +6647,7 @@
         <v>14</v>
       </c>
       <c r="F97" s="2">
-        <v>4326</v>
+        <v>807</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>15</v>
@@ -6679,7 +6679,7 @@
         <v>14</v>
       </c>
       <c r="F98" s="2">
-        <v>4087</v>
+        <v>3176</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>15</v>
@@ -6711,7 +6711,7 @@
         <v>14</v>
       </c>
       <c r="F99" s="2">
-        <v>1117</v>
+        <v>4455</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>15</v>
@@ -6743,7 +6743,7 @@
         <v>14</v>
       </c>
       <c r="F100" s="2">
-        <v>1770</v>
+        <v>2360</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>15</v>
@@ -6775,7 +6775,7 @@
         <v>14</v>
       </c>
       <c r="F101" s="2">
-        <v>2740</v>
+        <v>1753</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>15</v>
@@ -6807,7 +6807,7 @@
         <v>14</v>
       </c>
       <c r="F102" s="2">
-        <v>1490</v>
+        <v>2048</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>15</v>
@@ -6839,7 +6839,7 @@
         <v>14</v>
       </c>
       <c r="F103" s="2">
-        <v>3557</v>
+        <v>3195</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>15</v>
@@ -6871,7 +6871,7 @@
         <v>14</v>
       </c>
       <c r="F104" s="2">
-        <v>2340</v>
+        <v>2122</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>15</v>
@@ -6903,7 +6903,7 @@
         <v>14</v>
       </c>
       <c r="F105" s="2">
-        <v>4725</v>
+        <v>3135</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>15</v>
@@ -6935,7 +6935,7 @@
         <v>14</v>
       </c>
       <c r="F106" s="2">
-        <v>3075</v>
+        <v>4611</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>15</v>
@@ -6967,7 +6967,7 @@
         <v>14</v>
       </c>
       <c r="F107" s="2">
-        <v>4389</v>
+        <v>3789</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>15</v>
@@ -6999,7 +6999,7 @@
         <v>14</v>
       </c>
       <c r="F108" s="2">
-        <v>3074</v>
+        <v>3691</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>15</v>
@@ -7031,7 +7031,7 @@
         <v>14</v>
       </c>
       <c r="F109" s="2">
-        <v>4798</v>
+        <v>2675</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>15</v>
@@ -7063,7 +7063,7 @@
         <v>14</v>
       </c>
       <c r="F110" s="2">
-        <v>847</v>
+        <v>3107</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>15</v>
@@ -7095,7 +7095,7 @@
         <v>14</v>
       </c>
       <c r="F111" s="2">
-        <v>2920</v>
+        <v>2158</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>15</v>
@@ -7127,7 +7127,7 @@
         <v>14</v>
       </c>
       <c r="F112" s="2">
-        <v>3199</v>
+        <v>1994</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>15</v>
@@ -7159,7 +7159,7 @@
         <v>14</v>
       </c>
       <c r="F113" s="2">
-        <v>4704</v>
+        <v>3106</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>15</v>
@@ -7191,7 +7191,7 @@
         <v>14</v>
       </c>
       <c r="F114" s="2">
-        <v>1593</v>
+        <v>1578</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>15</v>
@@ -7223,7 +7223,7 @@
         <v>14</v>
       </c>
       <c r="F115" s="2">
-        <v>3254</v>
+        <v>2858</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>15</v>
@@ -7255,7 +7255,7 @@
         <v>14</v>
       </c>
       <c r="F116" s="2">
-        <v>1707</v>
+        <v>2058</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>15</v>
@@ -7287,7 +7287,7 @@
         <v>14</v>
       </c>
       <c r="F117" s="2">
-        <v>1132</v>
+        <v>1006</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>15</v>
@@ -7319,7 +7319,7 @@
         <v>14</v>
       </c>
       <c r="F118" s="2">
-        <v>1205</v>
+        <v>2884</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>15</v>
@@ -7351,7 +7351,7 @@
         <v>14</v>
       </c>
       <c r="F119" s="2">
-        <v>1121</v>
+        <v>2051</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>15</v>
@@ -7383,7 +7383,7 @@
         <v>14</v>
       </c>
       <c r="F120" s="2">
-        <v>4279</v>
+        <v>948</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>15</v>
@@ -7415,7 +7415,7 @@
         <v>14</v>
       </c>
       <c r="F121" s="2">
-        <v>3912</v>
+        <v>2225</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>15</v>
@@ -7447,7 +7447,7 @@
         <v>14</v>
       </c>
       <c r="F122" s="2">
-        <v>4786</v>
+        <v>844</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>15</v>
@@ -7479,7 +7479,7 @@
         <v>14</v>
       </c>
       <c r="F123" s="2">
-        <v>1674</v>
+        <v>2023</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>15</v>
@@ -7511,7 +7511,7 @@
         <v>14</v>
       </c>
       <c r="F124" s="2">
-        <v>3257</v>
+        <v>1520</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>15</v>
@@ -7543,7 +7543,7 @@
         <v>14</v>
       </c>
       <c r="F125" s="2">
-        <v>3781</v>
+        <v>3380</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>15</v>
@@ -7575,7 +7575,7 @@
         <v>14</v>
       </c>
       <c r="F126" s="2">
-        <v>2607</v>
+        <v>2494</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>15</v>
@@ -7607,7 +7607,7 @@
         <v>14</v>
       </c>
       <c r="F127" s="2">
-        <v>3611</v>
+        <v>4678</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>15</v>
@@ -7639,7 +7639,7 @@
         <v>14</v>
       </c>
       <c r="F128" s="2">
-        <v>3037</v>
+        <v>1316</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>15</v>
@@ -7671,7 +7671,7 @@
         <v>14</v>
       </c>
       <c r="F129" s="2">
-        <v>3383</v>
+        <v>2231</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>15</v>
@@ -7703,7 +7703,7 @@
         <v>14</v>
       </c>
       <c r="F130" s="2">
-        <v>3967</v>
+        <v>2890</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>15</v>
@@ -7735,7 +7735,7 @@
         <v>14</v>
       </c>
       <c r="F131" s="2">
-        <v>1038</v>
+        <v>4322</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>15</v>
@@ -7767,7 +7767,7 @@
         <v>14</v>
       </c>
       <c r="F132" s="2">
-        <v>3641</v>
+        <v>3108</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>15</v>
@@ -7799,7 +7799,7 @@
         <v>14</v>
       </c>
       <c r="F133" s="2">
-        <v>1141</v>
+        <v>2667</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>15</v>
@@ -7831,7 +7831,7 @@
         <v>14</v>
       </c>
       <c r="F134" s="2">
-        <v>1571</v>
+        <v>1541</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>15</v>
@@ -7863,7 +7863,7 @@
         <v>14</v>
       </c>
       <c r="F135" s="2">
-        <v>4083</v>
+        <v>1368</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>15</v>
@@ -7895,7 +7895,7 @@
         <v>14</v>
       </c>
       <c r="F136" s="2">
-        <v>3241</v>
+        <v>3345</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>15</v>
@@ -7927,7 +7927,7 @@
         <v>14</v>
       </c>
       <c r="F137" s="2">
-        <v>2416</v>
+        <v>1459</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>15</v>
@@ -7959,7 +7959,7 @@
         <v>14</v>
       </c>
       <c r="F138" s="2">
-        <v>4027</v>
+        <v>2512</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>15</v>
@@ -7991,7 +7991,7 @@
         <v>14</v>
       </c>
       <c r="F139" s="2">
-        <v>4105</v>
+        <v>2499</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>15</v>
@@ -8023,7 +8023,7 @@
         <v>14</v>
       </c>
       <c r="F140" s="2">
-        <v>3674</v>
+        <v>2413</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>15</v>
@@ -8055,7 +8055,7 @@
         <v>14</v>
       </c>
       <c r="F141" s="2">
-        <v>2953</v>
+        <v>893</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>15</v>
@@ -8087,7 +8087,7 @@
         <v>14</v>
       </c>
       <c r="F142" s="2">
-        <v>4225</v>
+        <v>3241</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>15</v>
@@ -8119,7 +8119,7 @@
         <v>14</v>
       </c>
       <c r="F143" s="2">
-        <v>3778</v>
+        <v>3423</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>15</v>
@@ -8151,7 +8151,7 @@
         <v>14</v>
       </c>
       <c r="F144" s="2">
-        <v>4685</v>
+        <v>1202</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>15</v>
@@ -8183,7 +8183,7 @@
         <v>14</v>
       </c>
       <c r="F145" s="2">
-        <v>3120</v>
+        <v>2502</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>15</v>
@@ -8215,7 +8215,7 @@
         <v>14</v>
       </c>
       <c r="F146" s="2">
-        <v>4789</v>
+        <v>3529</v>
       </c>
       <c r="G146" s="2" t="s">
         <v>15</v>
@@ -8247,7 +8247,7 @@
         <v>14</v>
       </c>
       <c r="F147" s="2">
-        <v>3075</v>
+        <v>1682</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>15</v>
@@ -8279,7 +8279,7 @@
         <v>14</v>
       </c>
       <c r="F148" s="2">
-        <v>1457</v>
+        <v>1079</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>15</v>
@@ -8311,7 +8311,7 @@
         <v>14</v>
       </c>
       <c r="F149" s="2">
-        <v>2766</v>
+        <v>1265</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>15</v>
@@ -8343,7 +8343,7 @@
         <v>14</v>
       </c>
       <c r="F150" s="2">
-        <v>1389</v>
+        <v>3113</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>15</v>
@@ -8375,7 +8375,7 @@
         <v>14</v>
       </c>
       <c r="F151" s="2">
-        <v>3724</v>
+        <v>3027</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>15</v>
@@ -8407,7 +8407,7 @@
         <v>14</v>
       </c>
       <c r="F152" s="2">
-        <v>4195</v>
+        <v>4430</v>
       </c>
       <c r="G152" s="2" t="s">
         <v>15</v>
@@ -8439,7 +8439,7 @@
         <v>14</v>
       </c>
       <c r="F153" s="2">
-        <v>967</v>
+        <v>4783</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>15</v>
@@ -8471,7 +8471,7 @@
         <v>14</v>
       </c>
       <c r="F154" s="2">
-        <v>3636</v>
+        <v>1328</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>15</v>
@@ -8503,7 +8503,7 @@
         <v>14</v>
       </c>
       <c r="F155" s="2">
-        <v>1951</v>
+        <v>3653</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>15</v>
@@ -8535,7 +8535,7 @@
         <v>14</v>
       </c>
       <c r="F156" s="2">
-        <v>3436</v>
+        <v>2509</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>15</v>
@@ -8567,7 +8567,7 @@
         <v>14</v>
       </c>
       <c r="F157" s="2">
-        <v>2497</v>
+        <v>2023</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>15</v>
@@ -8599,7 +8599,7 @@
         <v>14</v>
       </c>
       <c r="F158" s="2">
-        <v>3458</v>
+        <v>4246</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>15</v>
@@ -8631,7 +8631,7 @@
         <v>14</v>
       </c>
       <c r="F159" s="2">
-        <v>4274</v>
+        <v>863</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>15</v>
@@ -8663,7 +8663,7 @@
         <v>14</v>
       </c>
       <c r="F160" s="2">
-        <v>875</v>
+        <v>3546</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>15</v>
@@ -8695,7 +8695,7 @@
         <v>14</v>
       </c>
       <c r="F161" s="2">
-        <v>4559</v>
+        <v>3575</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>15</v>
@@ -8727,7 +8727,7 @@
         <v>14</v>
       </c>
       <c r="F162" s="2">
-        <v>1771</v>
+        <v>1636</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>15</v>
@@ -8759,7 +8759,7 @@
         <v>14</v>
       </c>
       <c r="F163" s="2">
-        <v>4416</v>
+        <v>3138</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>15</v>
@@ -8791,7 +8791,7 @@
         <v>14</v>
       </c>
       <c r="F164" s="2">
-        <v>1039</v>
+        <v>2762</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>15</v>
@@ -8823,7 +8823,7 @@
         <v>14</v>
       </c>
       <c r="F165" s="2">
-        <v>1805</v>
+        <v>1080</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>15</v>
@@ -8855,7 +8855,7 @@
         <v>14</v>
       </c>
       <c r="F166" s="2">
-        <v>1376</v>
+        <v>1409</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>15</v>
@@ -8887,7 +8887,7 @@
         <v>14</v>
       </c>
       <c r="F167" s="2">
-        <v>1729</v>
+        <v>3581</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>15</v>
@@ -8919,7 +8919,7 @@
         <v>14</v>
       </c>
       <c r="F168" s="2">
-        <v>4057</v>
+        <v>1618</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>15</v>
@@ -8951,7 +8951,7 @@
         <v>14</v>
       </c>
       <c r="F169" s="2">
-        <v>3700</v>
+        <v>2454</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>15</v>
@@ -8983,7 +8983,7 @@
         <v>14</v>
       </c>
       <c r="F170" s="2">
-        <v>3857</v>
+        <v>3610</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>15</v>
@@ -9015,7 +9015,7 @@
         <v>14</v>
       </c>
       <c r="F171" s="2">
-        <v>1885</v>
+        <v>4719</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>15</v>
@@ -9047,7 +9047,7 @@
         <v>14</v>
       </c>
       <c r="F172" s="2">
-        <v>2925</v>
+        <v>3452</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>15</v>
@@ -9079,7 +9079,7 @@
         <v>14</v>
       </c>
       <c r="F173" s="2">
-        <v>3388</v>
+        <v>2261</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>15</v>
@@ -9111,7 +9111,7 @@
         <v>14</v>
       </c>
       <c r="F174" s="2">
-        <v>1350</v>
+        <v>846</v>
       </c>
       <c r="G174" s="2" t="s">
         <v>15</v>
@@ -9143,7 +9143,7 @@
         <v>14</v>
       </c>
       <c r="F175" s="2">
-        <v>4633</v>
+        <v>2382</v>
       </c>
       <c r="G175" s="2" t="s">
         <v>15</v>
@@ -9175,7 +9175,7 @@
         <v>14</v>
       </c>
       <c r="F176" s="2">
-        <v>1448</v>
+        <v>1067</v>
       </c>
       <c r="G176" s="2" t="s">
         <v>15</v>
@@ -9207,7 +9207,7 @@
         <v>14</v>
       </c>
       <c r="F177" s="2">
-        <v>4598</v>
+        <v>2191</v>
       </c>
       <c r="G177" s="2" t="s">
         <v>15</v>
@@ -9239,7 +9239,7 @@
         <v>14</v>
       </c>
       <c r="F178" s="2">
-        <v>3337</v>
+        <v>1507</v>
       </c>
       <c r="G178" s="2" t="s">
         <v>15</v>
@@ -9271,7 +9271,7 @@
         <v>14</v>
       </c>
       <c r="F179" s="2">
-        <v>4338</v>
+        <v>3017</v>
       </c>
       <c r="G179" s="2" t="s">
         <v>15</v>
@@ -9303,7 +9303,7 @@
         <v>14</v>
       </c>
       <c r="F180" s="2">
-        <v>4339</v>
+        <v>1674</v>
       </c>
       <c r="G180" s="2" t="s">
         <v>15</v>
@@ -9335,7 +9335,7 @@
         <v>14</v>
       </c>
       <c r="F181" s="2">
-        <v>1748</v>
+        <v>1054</v>
       </c>
       <c r="G181" s="2" t="s">
         <v>15</v>
@@ -9367,7 +9367,7 @@
         <v>14</v>
       </c>
       <c r="F182" s="2">
-        <v>2920</v>
+        <v>2958</v>
       </c>
       <c r="G182" s="2" t="s">
         <v>15</v>
@@ -9399,7 +9399,7 @@
         <v>14</v>
       </c>
       <c r="F183" s="2">
-        <v>1413</v>
+        <v>2664</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>15</v>
@@ -9431,7 +9431,7 @@
         <v>14</v>
       </c>
       <c r="F184" s="2">
-        <v>2863</v>
+        <v>1841</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>15</v>
@@ -9463,7 +9463,7 @@
         <v>14</v>
       </c>
       <c r="F185" s="2">
-        <v>2965</v>
+        <v>3179</v>
       </c>
       <c r="G185" s="2" t="s">
         <v>15</v>
@@ -9495,7 +9495,7 @@
         <v>14</v>
       </c>
       <c r="F186" s="2">
-        <v>1403</v>
+        <v>1278</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>15</v>
@@ -9527,7 +9527,7 @@
         <v>14</v>
       </c>
       <c r="F187" s="2">
-        <v>2079</v>
+        <v>4725</v>
       </c>
       <c r="G187" s="2" t="s">
         <v>15</v>
@@ -9559,7 +9559,7 @@
         <v>14</v>
       </c>
       <c r="F188" s="2">
-        <v>4346</v>
+        <v>4792</v>
       </c>
       <c r="G188" s="2" t="s">
         <v>15</v>
@@ -9591,7 +9591,7 @@
         <v>14</v>
       </c>
       <c r="F189" s="2">
-        <v>2788</v>
+        <v>4407</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>15</v>
@@ -9623,7 +9623,7 @@
         <v>14</v>
       </c>
       <c r="F190" s="2">
-        <v>3301</v>
+        <v>2605</v>
       </c>
       <c r="G190" s="2" t="s">
         <v>15</v>
@@ -9655,7 +9655,7 @@
         <v>14</v>
       </c>
       <c r="F191" s="2">
-        <v>3162</v>
+        <v>3903</v>
       </c>
       <c r="G191" s="2" t="s">
         <v>15</v>
@@ -9687,7 +9687,7 @@
         <v>14</v>
       </c>
       <c r="F192" s="2">
-        <v>4749</v>
+        <v>4345</v>
       </c>
       <c r="G192" s="2" t="s">
         <v>15</v>
@@ -9719,7 +9719,7 @@
         <v>14</v>
       </c>
       <c r="F193" s="2">
-        <v>1594</v>
+        <v>3974</v>
       </c>
       <c r="G193" s="2" t="s">
         <v>15</v>
@@ -9751,7 +9751,7 @@
         <v>14</v>
       </c>
       <c r="F194" s="2">
-        <v>1534</v>
+        <v>4532</v>
       </c>
       <c r="G194" s="2" t="s">
         <v>15</v>
@@ -9783,7 +9783,7 @@
         <v>14</v>
       </c>
       <c r="F195" s="2">
-        <v>1299</v>
+        <v>1673</v>
       </c>
       <c r="G195" s="2" t="s">
         <v>15</v>
@@ -9815,7 +9815,7 @@
         <v>14</v>
       </c>
       <c r="F196" s="2">
-        <v>3576</v>
+        <v>1462</v>
       </c>
       <c r="G196" s="2" t="s">
         <v>15</v>
@@ -9847,7 +9847,7 @@
         <v>14</v>
       </c>
       <c r="F197" s="2">
-        <v>1087</v>
+        <v>4539</v>
       </c>
       <c r="G197" s="2" t="s">
         <v>15</v>
@@ -9879,7 +9879,7 @@
         <v>14</v>
       </c>
       <c r="F198" s="2">
-        <v>3002</v>
+        <v>1081</v>
       </c>
       <c r="G198" s="2" t="s">
         <v>15</v>
@@ -9911,7 +9911,7 @@
         <v>14</v>
       </c>
       <c r="F199" s="2">
-        <v>4776</v>
+        <v>4648</v>
       </c>
       <c r="G199" s="2" t="s">
         <v>15</v>
@@ -9943,7 +9943,7 @@
         <v>14</v>
       </c>
       <c r="F200" s="2">
-        <v>3830</v>
+        <v>3024</v>
       </c>
       <c r="G200" s="2" t="s">
         <v>15</v>
@@ -9975,7 +9975,7 @@
         <v>14</v>
       </c>
       <c r="F201" s="2">
-        <v>1046</v>
+        <v>818</v>
       </c>
       <c r="G201" s="2" t="s">
         <v>15</v>
@@ -10007,7 +10007,7 @@
         <v>14</v>
       </c>
       <c r="F202" s="2">
-        <v>3768</v>
+        <v>1848</v>
       </c>
       <c r="G202" s="2" t="s">
         <v>15</v>
@@ -10039,7 +10039,7 @@
         <v>14</v>
       </c>
       <c r="F203" s="2">
-        <v>1507</v>
+        <v>1482</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>15</v>
@@ -10071,7 +10071,7 @@
         <v>14</v>
       </c>
       <c r="F204" s="2">
-        <v>3963</v>
+        <v>1764</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>15</v>
@@ -10103,7 +10103,7 @@
         <v>14</v>
       </c>
       <c r="F205" s="2">
-        <v>3992</v>
+        <v>2292</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>15</v>
@@ -10135,7 +10135,7 @@
         <v>14</v>
       </c>
       <c r="F206" s="2">
-        <v>1558</v>
+        <v>1839</v>
       </c>
       <c r="G206" s="2" t="s">
         <v>15</v>
@@ -10167,7 +10167,7 @@
         <v>14</v>
       </c>
       <c r="F207" s="2">
-        <v>1737</v>
+        <v>4118</v>
       </c>
       <c r="G207" s="2" t="s">
         <v>15</v>
@@ -10199,7 +10199,7 @@
         <v>14</v>
       </c>
       <c r="F208" s="2">
-        <v>2331</v>
+        <v>4104</v>
       </c>
       <c r="G208" s="2" t="s">
         <v>15</v>
@@ -10231,7 +10231,7 @@
         <v>14</v>
       </c>
       <c r="F209" s="2">
-        <v>3913</v>
+        <v>1476</v>
       </c>
       <c r="G209" s="2" t="s">
         <v>15</v>
@@ -10263,7 +10263,7 @@
         <v>14</v>
       </c>
       <c r="F210" s="2">
-        <v>2246</v>
+        <v>4749</v>
       </c>
       <c r="G210" s="2" t="s">
         <v>15</v>
@@ -10295,7 +10295,7 @@
         <v>14</v>
       </c>
       <c r="F211" s="2">
-        <v>2250</v>
+        <v>1958</v>
       </c>
       <c r="G211" s="2" t="s">
         <v>15</v>
@@ -10327,7 +10327,7 @@
         <v>14</v>
       </c>
       <c r="F212" s="2">
-        <v>1364</v>
+        <v>3187</v>
       </c>
       <c r="G212" s="2" t="s">
         <v>15</v>
@@ -10359,7 +10359,7 @@
         <v>14</v>
       </c>
       <c r="F213" s="2">
-        <v>2823</v>
+        <v>3028</v>
       </c>
       <c r="G213" s="2" t="s">
         <v>15</v>
@@ -10391,7 +10391,7 @@
         <v>14</v>
       </c>
       <c r="F214" s="2">
-        <v>2232</v>
+        <v>1288</v>
       </c>
       <c r="G214" s="2" t="s">
         <v>15</v>
@@ -10423,7 +10423,7 @@
         <v>14</v>
       </c>
       <c r="F215" s="2">
-        <v>2000</v>
+        <v>1057</v>
       </c>
       <c r="G215" s="2" t="s">
         <v>15</v>
@@ -10455,7 +10455,7 @@
         <v>14</v>
       </c>
       <c r="F216" s="2">
-        <v>2947</v>
+        <v>964</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>15</v>
@@ -10487,7 +10487,7 @@
         <v>14</v>
       </c>
       <c r="F217" s="2">
-        <v>3937</v>
+        <v>4318</v>
       </c>
       <c r="G217" s="2" t="s">
         <v>15</v>
@@ -10519,7 +10519,7 @@
         <v>14</v>
       </c>
       <c r="F218" s="2">
-        <v>2459</v>
+        <v>3674</v>
       </c>
       <c r="G218" s="2" t="s">
         <v>15</v>
@@ -10551,7 +10551,7 @@
         <v>14</v>
       </c>
       <c r="F219" s="2">
-        <v>2748</v>
+        <v>1994</v>
       </c>
       <c r="G219" s="2" t="s">
         <v>15</v>
@@ -10583,7 +10583,7 @@
         <v>14</v>
       </c>
       <c r="F220" s="2">
-        <v>1849</v>
+        <v>1931</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>15</v>
@@ -10615,7 +10615,7 @@
         <v>14</v>
       </c>
       <c r="F221" s="2">
-        <v>2586</v>
+        <v>2212</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>15</v>
@@ -10647,7 +10647,7 @@
         <v>14</v>
       </c>
       <c r="F222" s="2">
-        <v>4684</v>
+        <v>3780</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>15</v>
@@ -10679,7 +10679,7 @@
         <v>14</v>
       </c>
       <c r="F223" s="2">
-        <v>4715</v>
+        <v>1455</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>15</v>
@@ -10711,7 +10711,7 @@
         <v>14</v>
       </c>
       <c r="F224" s="2">
-        <v>2498</v>
+        <v>2164</v>
       </c>
       <c r="G224" s="2" t="s">
         <v>15</v>
@@ -10743,7 +10743,7 @@
         <v>14</v>
       </c>
       <c r="F225" s="2">
-        <v>1412</v>
+        <v>2408</v>
       </c>
       <c r="G225" s="2" t="s">
         <v>15</v>
@@ -10775,7 +10775,7 @@
         <v>14</v>
       </c>
       <c r="F226" s="2">
-        <v>4744</v>
+        <v>1028</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>15</v>
@@ -10807,7 +10807,7 @@
         <v>14</v>
       </c>
       <c r="F227" s="2">
-        <v>3769</v>
+        <v>3013</v>
       </c>
       <c r="G227" s="2" t="s">
         <v>15</v>
@@ -10839,7 +10839,7 @@
         <v>14</v>
       </c>
       <c r="F228" s="2">
-        <v>2455</v>
+        <v>1034</v>
       </c>
       <c r="G228" s="2" t="s">
         <v>15</v>
@@ -10871,7 +10871,7 @@
         <v>14</v>
       </c>
       <c r="F229" s="2">
-        <v>1683</v>
+        <v>858</v>
       </c>
       <c r="G229" s="2" t="s">
         <v>15</v>
@@ -10903,7 +10903,7 @@
         <v>14</v>
       </c>
       <c r="F230" s="2">
-        <v>942</v>
+        <v>3952</v>
       </c>
       <c r="G230" s="2" t="s">
         <v>15</v>
@@ -10935,7 +10935,7 @@
         <v>14</v>
       </c>
       <c r="F231" s="2">
-        <v>1994</v>
+        <v>2413</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>15</v>
@@ -10967,7 +10967,7 @@
         <v>14</v>
       </c>
       <c r="F232" s="2">
-        <v>4173</v>
+        <v>3285</v>
       </c>
       <c r="G232" s="2" t="s">
         <v>15</v>
@@ -10999,7 +10999,7 @@
         <v>14</v>
       </c>
       <c r="F233" s="2">
-        <v>4290</v>
+        <v>2752</v>
       </c>
       <c r="G233" s="2" t="s">
         <v>15</v>
@@ -11031,7 +11031,7 @@
         <v>14</v>
       </c>
       <c r="F234" s="2">
-        <v>3847</v>
+        <v>3537</v>
       </c>
       <c r="G234" s="2" t="s">
         <v>15</v>
@@ -11063,7 +11063,7 @@
         <v>14</v>
       </c>
       <c r="F235" s="2">
-        <v>2668</v>
+        <v>1559</v>
       </c>
       <c r="G235" s="2" t="s">
         <v>15</v>
@@ -11095,7 +11095,7 @@
         <v>14</v>
       </c>
       <c r="F236" s="2">
-        <v>1595</v>
+        <v>1644</v>
       </c>
       <c r="G236" s="2" t="s">
         <v>15</v>
@@ -11127,7 +11127,7 @@
         <v>14</v>
       </c>
       <c r="F237" s="2">
-        <v>1258</v>
+        <v>3506</v>
       </c>
       <c r="G237" s="2" t="s">
         <v>15</v>
@@ -11159,7 +11159,7 @@
         <v>14</v>
       </c>
       <c r="F238" s="2">
-        <v>2845</v>
+        <v>1912</v>
       </c>
       <c r="G238" s="2" t="s">
         <v>15</v>
@@ -11191,7 +11191,7 @@
         <v>14</v>
       </c>
       <c r="F239" s="2">
-        <v>2972</v>
+        <v>1052</v>
       </c>
       <c r="G239" s="2" t="s">
         <v>15</v>
@@ -11223,7 +11223,7 @@
         <v>14</v>
       </c>
       <c r="F240" s="2">
-        <v>4008</v>
+        <v>4661</v>
       </c>
       <c r="G240" s="2" t="s">
         <v>15</v>
@@ -11255,7 +11255,7 @@
         <v>14</v>
       </c>
       <c r="F241" s="2">
-        <v>1093</v>
+        <v>1181</v>
       </c>
       <c r="G241" s="2" t="s">
         <v>15</v>
@@ -11287,7 +11287,7 @@
         <v>14</v>
       </c>
       <c r="F242" s="2">
-        <v>1914</v>
+        <v>3486</v>
       </c>
       <c r="G242" s="2" t="s">
         <v>15</v>
@@ -11319,7 +11319,7 @@
         <v>14</v>
       </c>
       <c r="F243" s="2">
-        <v>4278</v>
+        <v>2477</v>
       </c>
       <c r="G243" s="2" t="s">
         <v>15</v>
@@ -11351,7 +11351,7 @@
         <v>14</v>
       </c>
       <c r="F244" s="2">
-        <v>2488</v>
+        <v>1643</v>
       </c>
       <c r="G244" s="2" t="s">
         <v>15</v>
@@ -11383,7 +11383,7 @@
         <v>14</v>
       </c>
       <c r="F245" s="2">
-        <v>2805</v>
+        <v>3814</v>
       </c>
       <c r="G245" s="2" t="s">
         <v>15</v>
@@ -11415,7 +11415,7 @@
         <v>14</v>
       </c>
       <c r="F246" s="2">
-        <v>4085</v>
+        <v>1133</v>
       </c>
       <c r="G246" s="2" t="s">
         <v>15</v>
@@ -11447,7 +11447,7 @@
         <v>14</v>
       </c>
       <c r="F247" s="2">
-        <v>2786</v>
+        <v>2339</v>
       </c>
       <c r="G247" s="2" t="s">
         <v>15</v>
@@ -11479,7 +11479,7 @@
         <v>14</v>
       </c>
       <c r="F248" s="2">
-        <v>4204</v>
+        <v>3781</v>
       </c>
       <c r="G248" s="2" t="s">
         <v>15</v>
@@ -11511,7 +11511,7 @@
         <v>14</v>
       </c>
       <c r="F249" s="2">
-        <v>4137</v>
+        <v>2639</v>
       </c>
       <c r="G249" s="2" t="s">
         <v>15</v>
@@ -11543,7 +11543,7 @@
         <v>14</v>
       </c>
       <c r="F250" s="2">
-        <v>3058</v>
+        <v>3944</v>
       </c>
       <c r="G250" s="2" t="s">
         <v>15</v>
@@ -11575,7 +11575,7 @@
         <v>14</v>
       </c>
       <c r="F251" s="2">
-        <v>1141</v>
+        <v>2707</v>
       </c>
       <c r="G251" s="2" t="s">
         <v>15</v>
@@ -11607,7 +11607,7 @@
         <v>14</v>
       </c>
       <c r="F252" s="2">
-        <v>3699</v>
+        <v>1872</v>
       </c>
       <c r="G252" s="2" t="s">
         <v>15</v>
@@ -11639,7 +11639,7 @@
         <v>14</v>
       </c>
       <c r="F253" s="2">
-        <v>3487</v>
+        <v>3722</v>
       </c>
       <c r="G253" s="2" t="s">
         <v>15</v>
@@ -11671,7 +11671,7 @@
         <v>14</v>
       </c>
       <c r="F254" s="2">
-        <v>1603</v>
+        <v>2945</v>
       </c>
       <c r="G254" s="2" t="s">
         <v>15</v>
@@ -11703,7 +11703,7 @@
         <v>14</v>
       </c>
       <c r="F255" s="2">
-        <v>3282</v>
+        <v>2020</v>
       </c>
       <c r="G255" s="2" t="s">
         <v>15</v>
@@ -11735,7 +11735,7 @@
         <v>14</v>
       </c>
       <c r="F256" s="2">
-        <v>1167</v>
+        <v>1683</v>
       </c>
       <c r="G256" s="2" t="s">
         <v>15</v>
@@ -11767,7 +11767,7 @@
         <v>14</v>
       </c>
       <c r="F257" s="2">
-        <v>4750</v>
+        <v>1329</v>
       </c>
       <c r="G257" s="2" t="s">
         <v>15</v>
@@ -11799,7 +11799,7 @@
         <v>14</v>
       </c>
       <c r="F258" s="2">
-        <v>1021</v>
+        <v>3400</v>
       </c>
       <c r="G258" s="2" t="s">
         <v>15</v>
@@ -11831,7 +11831,7 @@
         <v>14</v>
       </c>
       <c r="F259" s="2">
-        <v>2825</v>
+        <v>4420</v>
       </c>
       <c r="G259" s="2" t="s">
         <v>15</v>
@@ -11863,7 +11863,7 @@
         <v>14</v>
       </c>
       <c r="F260" s="2">
-        <v>2166</v>
+        <v>3904</v>
       </c>
       <c r="G260" s="2" t="s">
         <v>15</v>
@@ -11895,7 +11895,7 @@
         <v>14</v>
       </c>
       <c r="F261" s="2">
-        <v>1350</v>
+        <v>3856</v>
       </c>
       <c r="G261" s="2" t="s">
         <v>15</v>
@@ -11927,7 +11927,7 @@
         <v>14</v>
       </c>
       <c r="F262" s="2">
-        <v>3639</v>
+        <v>4349</v>
       </c>
       <c r="G262" s="2" t="s">
         <v>15</v>
@@ -11959,7 +11959,7 @@
         <v>14</v>
       </c>
       <c r="F263" s="2">
-        <v>3697</v>
+        <v>3901</v>
       </c>
       <c r="G263" s="2" t="s">
         <v>15</v>
@@ -11991,7 +11991,7 @@
         <v>14</v>
       </c>
       <c r="F264" s="2">
-        <v>3528</v>
+        <v>3625</v>
       </c>
       <c r="G264" s="2" t="s">
         <v>15</v>
@@ -12023,7 +12023,7 @@
         <v>14</v>
       </c>
       <c r="F265" s="2">
-        <v>4517</v>
+        <v>911</v>
       </c>
       <c r="G265" s="2" t="s">
         <v>15</v>
@@ -12055,7 +12055,7 @@
         <v>14</v>
       </c>
       <c r="F266" s="2">
-        <v>4072</v>
+        <v>2349</v>
       </c>
       <c r="G266" s="2" t="s">
         <v>15</v>
@@ -12087,7 +12087,7 @@
         <v>14</v>
       </c>
       <c r="F267" s="2">
-        <v>1514</v>
+        <v>828</v>
       </c>
       <c r="G267" s="2" t="s">
         <v>15</v>
@@ -12119,7 +12119,7 @@
         <v>14</v>
       </c>
       <c r="F268" s="2">
-        <v>3501</v>
+        <v>3941</v>
       </c>
       <c r="G268" s="2" t="s">
         <v>15</v>
@@ -12151,7 +12151,7 @@
         <v>14</v>
       </c>
       <c r="F269" s="2">
-        <v>3961</v>
+        <v>3232</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>15</v>
@@ -12183,7 +12183,7 @@
         <v>14</v>
       </c>
       <c r="F270" s="2">
-        <v>2500</v>
+        <v>1042</v>
       </c>
       <c r="G270" s="2" t="s">
         <v>15</v>
@@ -12215,7 +12215,7 @@
         <v>14</v>
       </c>
       <c r="F271" s="2">
-        <v>1799</v>
+        <v>1553</v>
       </c>
       <c r="G271" s="2" t="s">
         <v>15</v>
@@ -12247,7 +12247,7 @@
         <v>14</v>
       </c>
       <c r="F272" s="2">
-        <v>2162</v>
+        <v>4474</v>
       </c>
       <c r="G272" s="2" t="s">
         <v>15</v>
@@ -12279,7 +12279,7 @@
         <v>14</v>
       </c>
       <c r="F273" s="2">
-        <v>2954</v>
+        <v>923</v>
       </c>
       <c r="G273" s="2" t="s">
         <v>15</v>
@@ -12311,7 +12311,7 @@
         <v>14</v>
       </c>
       <c r="F274" s="2">
-        <v>3258</v>
+        <v>4132</v>
       </c>
       <c r="G274" s="2" t="s">
         <v>15</v>
@@ -12343,7 +12343,7 @@
         <v>14</v>
       </c>
       <c r="F275" s="2">
-        <v>2724</v>
+        <v>1090</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>15</v>
@@ -12375,7 +12375,7 @@
         <v>14</v>
       </c>
       <c r="F276" s="2">
-        <v>4098</v>
+        <v>4000</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>15</v>
@@ -12407,7 +12407,7 @@
         <v>14</v>
       </c>
       <c r="F277" s="2">
-        <v>1795</v>
+        <v>1958</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>15</v>
@@ -12439,7 +12439,7 @@
         <v>14</v>
       </c>
       <c r="F278" s="2">
-        <v>2990</v>
+        <v>2854</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>15</v>
@@ -12471,7 +12471,7 @@
         <v>14</v>
       </c>
       <c r="F279" s="2">
-        <v>2339</v>
+        <v>2261</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>15</v>
@@ -12503,7 +12503,7 @@
         <v>14</v>
       </c>
       <c r="F280" s="2">
-        <v>1731</v>
+        <v>1738</v>
       </c>
       <c r="G280" s="2" t="s">
         <v>15</v>
@@ -12535,7 +12535,7 @@
         <v>14</v>
       </c>
       <c r="F281" s="2">
-        <v>1818</v>
+        <v>3177</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>15</v>
@@ -12567,7 +12567,7 @@
         <v>14</v>
       </c>
       <c r="F282" s="2">
-        <v>3629</v>
+        <v>2583</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>15</v>
@@ -12599,7 +12599,7 @@
         <v>14</v>
       </c>
       <c r="F283" s="2">
-        <v>2543</v>
+        <v>4479</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>15</v>
@@ -12631,7 +12631,7 @@
         <v>14</v>
       </c>
       <c r="F284" s="2">
-        <v>2543</v>
+        <v>1954</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>15</v>
@@ -12663,7 +12663,7 @@
         <v>14</v>
       </c>
       <c r="F285" s="2">
-        <v>3051</v>
+        <v>3387</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>15</v>
@@ -12695,7 +12695,7 @@
         <v>14</v>
       </c>
       <c r="F286" s="2">
-        <v>3100</v>
+        <v>4756</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>15</v>
@@ -12727,7 +12727,7 @@
         <v>14</v>
       </c>
       <c r="F287" s="2">
-        <v>4694</v>
+        <v>1687</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>15</v>
@@ -12759,7 +12759,7 @@
         <v>14</v>
       </c>
       <c r="F288" s="2">
-        <v>969</v>
+        <v>1739</v>
       </c>
       <c r="G288" s="2" t="s">
         <v>15</v>
@@ -12791,7 +12791,7 @@
         <v>14</v>
       </c>
       <c r="F289" s="2">
-        <v>2561</v>
+        <v>3477</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>15</v>
@@ -12823,7 +12823,7 @@
         <v>14</v>
       </c>
       <c r="F290" s="2">
-        <v>890</v>
+        <v>840</v>
       </c>
       <c r="G290" s="2" t="s">
         <v>15</v>
@@ -12855,7 +12855,7 @@
         <v>14</v>
       </c>
       <c r="F291" s="2">
-        <v>2166</v>
+        <v>3441</v>
       </c>
       <c r="G291" s="2" t="s">
         <v>15</v>
@@ -12887,7 +12887,7 @@
         <v>14</v>
       </c>
       <c r="F292" s="2">
-        <v>823</v>
+        <v>4664</v>
       </c>
       <c r="G292" s="2" t="s">
         <v>15</v>
@@ -12919,7 +12919,7 @@
         <v>14</v>
       </c>
       <c r="F293" s="2">
-        <v>3593</v>
+        <v>4124</v>
       </c>
       <c r="G293" s="2" t="s">
         <v>15</v>
@@ -12951,7 +12951,7 @@
         <v>14</v>
       </c>
       <c r="F294" s="2">
-        <v>2884</v>
+        <v>1289</v>
       </c>
       <c r="G294" s="2" t="s">
         <v>15</v>
@@ -12983,7 +12983,7 @@
         <v>14</v>
       </c>
       <c r="F295" s="2">
-        <v>2627</v>
+        <v>3043</v>
       </c>
       <c r="G295" s="2" t="s">
         <v>15</v>
@@ -13015,7 +13015,7 @@
         <v>14</v>
       </c>
       <c r="F296" s="2">
-        <v>3564</v>
+        <v>4441</v>
       </c>
       <c r="G296" s="2" t="s">
         <v>15</v>
@@ -13047,7 +13047,7 @@
         <v>14</v>
       </c>
       <c r="F297" s="2">
-        <v>2471</v>
+        <v>1771</v>
       </c>
       <c r="G297" s="2" t="s">
         <v>15</v>
@@ -13079,7 +13079,7 @@
         <v>14</v>
       </c>
       <c r="F298" s="2">
-        <v>2795</v>
+        <v>4137</v>
       </c>
       <c r="G298" s="2" t="s">
         <v>15</v>
@@ -13111,7 +13111,7 @@
         <v>14</v>
       </c>
       <c r="F299" s="2">
-        <v>2462</v>
+        <v>3594</v>
       </c>
       <c r="G299" s="2" t="s">
         <v>15</v>
@@ -13143,7 +13143,7 @@
         <v>14</v>
       </c>
       <c r="F300" s="2">
-        <v>2895</v>
+        <v>2115</v>
       </c>
       <c r="G300" s="2" t="s">
         <v>15</v>
@@ -13175,7 +13175,7 @@
         <v>14</v>
       </c>
       <c r="F301" s="2">
-        <v>2505</v>
+        <v>2495</v>
       </c>
       <c r="G301" s="2" t="s">
         <v>15</v>
@@ -13207,7 +13207,7 @@
         <v>14</v>
       </c>
       <c r="F302" s="2">
-        <v>852</v>
+        <v>2165</v>
       </c>
       <c r="G302" s="2" t="s">
         <v>15</v>
@@ -13239,7 +13239,7 @@
         <v>14</v>
       </c>
       <c r="F303" s="2">
-        <v>4678</v>
+        <v>2229</v>
       </c>
       <c r="G303" s="2" t="s">
         <v>15</v>
@@ -13271,7 +13271,7 @@
         <v>14</v>
       </c>
       <c r="F304" s="2">
-        <v>2970</v>
+        <v>4158</v>
       </c>
       <c r="G304" s="2" t="s">
         <v>15</v>
@@ -13303,7 +13303,7 @@
         <v>14</v>
       </c>
       <c r="F305" s="2">
-        <v>3630</v>
+        <v>949</v>
       </c>
       <c r="G305" s="2" t="s">
         <v>15</v>
@@ -13335,7 +13335,7 @@
         <v>14</v>
       </c>
       <c r="F306" s="2">
-        <v>2694</v>
+        <v>3715</v>
       </c>
       <c r="G306" s="2" t="s">
         <v>15</v>
@@ -13367,7 +13367,7 @@
         <v>14</v>
       </c>
       <c r="F307" s="2">
-        <v>1189</v>
+        <v>829</v>
       </c>
       <c r="G307" s="2" t="s">
         <v>15</v>
@@ -13399,7 +13399,7 @@
         <v>14</v>
       </c>
       <c r="F308" s="2">
-        <v>2228</v>
+        <v>3955</v>
       </c>
       <c r="G308" s="2" t="s">
         <v>15</v>
@@ -13431,7 +13431,7 @@
         <v>14</v>
       </c>
       <c r="F309" s="2">
-        <v>963</v>
+        <v>2882</v>
       </c>
       <c r="G309" s="2" t="s">
         <v>15</v>
@@ -13463,7 +13463,7 @@
         <v>14</v>
       </c>
       <c r="F310" s="2">
-        <v>1715</v>
+        <v>3280</v>
       </c>
       <c r="G310" s="2" t="s">
         <v>15</v>
@@ -13495,7 +13495,7 @@
         <v>14</v>
       </c>
       <c r="F311" s="2">
-        <v>1296</v>
+        <v>3810</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>15</v>
@@ -13527,7 +13527,7 @@
         <v>14</v>
       </c>
       <c r="F312" s="2">
-        <v>2232</v>
+        <v>4414</v>
       </c>
       <c r="G312" s="2" t="s">
         <v>15</v>
@@ -13559,7 +13559,7 @@
         <v>14</v>
       </c>
       <c r="F313" s="2">
-        <v>1246</v>
+        <v>3826</v>
       </c>
       <c r="G313" s="2" t="s">
         <v>15</v>
@@ -13591,7 +13591,7 @@
         <v>14</v>
       </c>
       <c r="F314" s="2">
-        <v>1186</v>
+        <v>3437</v>
       </c>
       <c r="G314" s="2" t="s">
         <v>15</v>
@@ -13623,7 +13623,7 @@
         <v>14</v>
       </c>
       <c r="F315" s="2">
-        <v>1796</v>
+        <v>1931</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>15</v>
@@ -13655,7 +13655,7 @@
         <v>14</v>
       </c>
       <c r="F316" s="2">
-        <v>4281</v>
+        <v>2056</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>15</v>
@@ -13687,7 +13687,7 @@
         <v>14</v>
       </c>
       <c r="F317" s="2">
-        <v>1079</v>
+        <v>3391</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>15</v>
@@ -13719,7 +13719,7 @@
         <v>14</v>
       </c>
       <c r="F318" s="2">
-        <v>2898</v>
+        <v>2476</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>15</v>
@@ -13751,7 +13751,7 @@
         <v>14</v>
       </c>
       <c r="F319" s="2">
-        <v>4013</v>
+        <v>2682</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>15</v>
@@ -13783,7 +13783,7 @@
         <v>14</v>
       </c>
       <c r="F320" s="2">
-        <v>3574</v>
+        <v>4568</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>15</v>
@@ -13815,7 +13815,7 @@
         <v>14</v>
       </c>
       <c r="F321" s="2">
-        <v>2554</v>
+        <v>2025</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>15</v>
@@ -13847,7 +13847,7 @@
         <v>14</v>
       </c>
       <c r="F322" s="2">
-        <v>1822</v>
+        <v>2503</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>15</v>
@@ -13879,7 +13879,7 @@
         <v>14</v>
       </c>
       <c r="F323" s="2">
-        <v>4074</v>
+        <v>3863</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>15</v>
@@ -13911,7 +13911,7 @@
         <v>14</v>
       </c>
       <c r="F324" s="2">
-        <v>1552</v>
+        <v>1455</v>
       </c>
       <c r="G324" s="2" t="s">
         <v>15</v>
@@ -13943,7 +13943,7 @@
         <v>14</v>
       </c>
       <c r="F325" s="2">
-        <v>3428</v>
+        <v>2662</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>15</v>
@@ -13975,7 +13975,7 @@
         <v>14</v>
       </c>
       <c r="F326" s="2">
-        <v>1237</v>
+        <v>1979</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>15</v>
@@ -14007,7 +14007,7 @@
         <v>14</v>
       </c>
       <c r="F327" s="2">
-        <v>3059</v>
+        <v>3249</v>
       </c>
       <c r="G327" s="2" t="s">
         <v>15</v>
@@ -14039,7 +14039,7 @@
         <v>14</v>
       </c>
       <c r="F328" s="2">
-        <v>3729</v>
+        <v>2585</v>
       </c>
       <c r="G328" s="2" t="s">
         <v>15</v>
@@ -14071,7 +14071,7 @@
         <v>14</v>
       </c>
       <c r="F329" s="2">
-        <v>3912</v>
+        <v>1308</v>
       </c>
       <c r="G329" s="2" t="s">
         <v>15</v>
@@ -14103,7 +14103,7 @@
         <v>14</v>
       </c>
       <c r="F330" s="2">
-        <v>1300</v>
+        <v>3080</v>
       </c>
       <c r="G330" s="2" t="s">
         <v>15</v>
@@ -14135,7 +14135,7 @@
         <v>14</v>
       </c>
       <c r="F331" s="2">
-        <v>2878</v>
+        <v>3404</v>
       </c>
       <c r="G331" s="2" t="s">
         <v>15</v>
@@ -14167,7 +14167,7 @@
         <v>14</v>
       </c>
       <c r="F332" s="2">
-        <v>3884</v>
+        <v>2777</v>
       </c>
       <c r="G332" s="2" t="s">
         <v>15</v>
@@ -14199,7 +14199,7 @@
         <v>14</v>
       </c>
       <c r="F333" s="2">
-        <v>1132</v>
+        <v>1403</v>
       </c>
       <c r="G333" s="2" t="s">
         <v>15</v>
@@ -14231,7 +14231,7 @@
         <v>14</v>
       </c>
       <c r="F334" s="2">
-        <v>2626</v>
+        <v>3608</v>
       </c>
       <c r="G334" s="2" t="s">
         <v>15</v>
@@ -14263,7 +14263,7 @@
         <v>14</v>
       </c>
       <c r="F335" s="2">
-        <v>2114</v>
+        <v>3822</v>
       </c>
       <c r="G335" s="2" t="s">
         <v>15</v>
@@ -14295,7 +14295,7 @@
         <v>14</v>
       </c>
       <c r="F336" s="2">
-        <v>1031</v>
+        <v>2987</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>15</v>
@@ -14327,7 +14327,7 @@
         <v>14</v>
       </c>
       <c r="F337" s="2">
-        <v>3577</v>
+        <v>3325</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>15</v>
@@ -14359,7 +14359,7 @@
         <v>14</v>
       </c>
       <c r="F338" s="2">
-        <v>1912</v>
+        <v>3894</v>
       </c>
       <c r="G338" s="2" t="s">
         <v>15</v>
@@ -14391,7 +14391,7 @@
         <v>14</v>
       </c>
       <c r="F339" s="2">
-        <v>1857</v>
+        <v>1303</v>
       </c>
       <c r="G339" s="2" t="s">
         <v>15</v>
@@ -14423,7 +14423,7 @@
         <v>14</v>
       </c>
       <c r="F340" s="2">
-        <v>3878</v>
+        <v>3277</v>
       </c>
       <c r="G340" s="2" t="s">
         <v>15</v>
@@ -14455,7 +14455,7 @@
         <v>14</v>
       </c>
       <c r="F341" s="2">
-        <v>4734</v>
+        <v>3713</v>
       </c>
       <c r="G341" s="2" t="s">
         <v>15</v>
@@ -14487,7 +14487,7 @@
         <v>14</v>
       </c>
       <c r="F342" s="2">
-        <v>1033</v>
+        <v>1455</v>
       </c>
       <c r="G342" s="2" t="s">
         <v>15</v>
@@ -14519,7 +14519,7 @@
         <v>14</v>
       </c>
       <c r="F343" s="2">
-        <v>2572</v>
+        <v>4625</v>
       </c>
       <c r="G343" s="2" t="s">
         <v>15</v>
@@ -14551,7 +14551,7 @@
         <v>14</v>
       </c>
       <c r="F344" s="2">
-        <v>4519</v>
+        <v>3979</v>
       </c>
       <c r="G344" s="2" t="s">
         <v>15</v>
@@ -14583,7 +14583,7 @@
         <v>14</v>
       </c>
       <c r="F345" s="2">
-        <v>1204</v>
+        <v>843</v>
       </c>
       <c r="G345" s="2" t="s">
         <v>15</v>
@@ -14615,7 +14615,7 @@
         <v>14</v>
       </c>
       <c r="F346" s="2">
-        <v>949</v>
+        <v>2908</v>
       </c>
       <c r="G346" s="2" t="s">
         <v>15</v>
@@ -14647,7 +14647,7 @@
         <v>14</v>
       </c>
       <c r="F347" s="2">
-        <v>3776</v>
+        <v>4068</v>
       </c>
       <c r="G347" s="2" t="s">
         <v>15</v>
@@ -14679,7 +14679,7 @@
         <v>14</v>
       </c>
       <c r="F348" s="2">
-        <v>4790</v>
+        <v>919</v>
       </c>
       <c r="G348" s="2" t="s">
         <v>15</v>
@@ -14711,7 +14711,7 @@
         <v>14</v>
       </c>
       <c r="F349" s="2">
-        <v>4481</v>
+        <v>3815</v>
       </c>
       <c r="G349" s="2" t="s">
         <v>15</v>
@@ -14743,7 +14743,7 @@
         <v>14</v>
       </c>
       <c r="F350" s="2">
-        <v>2035</v>
+        <v>4139</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>15</v>
@@ -14775,7 +14775,7 @@
         <v>14</v>
       </c>
       <c r="F351" s="2">
-        <v>3276</v>
+        <v>2892</v>
       </c>
       <c r="G351" s="2" t="s">
         <v>15</v>
@@ -14807,7 +14807,7 @@
         <v>14</v>
       </c>
       <c r="F352" s="2">
-        <v>1925</v>
+        <v>4710</v>
       </c>
       <c r="G352" s="2" t="s">
         <v>15</v>
@@ -14839,7 +14839,7 @@
         <v>14</v>
       </c>
       <c r="F353" s="2">
-        <v>2434</v>
+        <v>3492</v>
       </c>
       <c r="G353" s="2" t="s">
         <v>15</v>
@@ -14871,7 +14871,7 @@
         <v>14</v>
       </c>
       <c r="F354" s="2">
-        <v>1577</v>
+        <v>4176</v>
       </c>
       <c r="G354" s="2" t="s">
         <v>15</v>
@@ -14903,7 +14903,7 @@
         <v>14</v>
       </c>
       <c r="F355" s="2">
-        <v>2803</v>
+        <v>1360</v>
       </c>
       <c r="G355" s="2" t="s">
         <v>15</v>
@@ -14935,7 +14935,7 @@
         <v>14</v>
       </c>
       <c r="F356" s="2">
-        <v>3019</v>
+        <v>910</v>
       </c>
       <c r="G356" s="2" t="s">
         <v>15</v>
@@ -14967,7 +14967,7 @@
         <v>14</v>
       </c>
       <c r="F357" s="2">
-        <v>1791</v>
+        <v>1577</v>
       </c>
       <c r="G357" s="2" t="s">
         <v>15</v>
@@ -14999,7 +14999,7 @@
         <v>14</v>
       </c>
       <c r="F358" s="2">
-        <v>3160</v>
+        <v>3856</v>
       </c>
       <c r="G358" s="2" t="s">
         <v>15</v>
@@ -15031,7 +15031,7 @@
         <v>14</v>
       </c>
       <c r="F359" s="2">
-        <v>1158</v>
+        <v>1140</v>
       </c>
       <c r="G359" s="2" t="s">
         <v>15</v>
@@ -15063,7 +15063,7 @@
         <v>14</v>
       </c>
       <c r="F360" s="2">
-        <v>4266</v>
+        <v>3564</v>
       </c>
       <c r="G360" s="2" t="s">
         <v>15</v>
@@ -15095,7 +15095,7 @@
         <v>14</v>
       </c>
       <c r="F361" s="2">
-        <v>1078</v>
+        <v>4477</v>
       </c>
       <c r="G361" s="2" t="s">
         <v>15</v>
@@ -15127,7 +15127,7 @@
         <v>14</v>
       </c>
       <c r="F362" s="2">
-        <v>4561</v>
+        <v>1274</v>
       </c>
       <c r="G362" s="2" t="s">
         <v>15</v>
@@ -15159,7 +15159,7 @@
         <v>14</v>
       </c>
       <c r="F363" s="2">
-        <v>3240</v>
+        <v>829</v>
       </c>
       <c r="G363" s="2" t="s">
         <v>15</v>
@@ -15191,7 +15191,7 @@
         <v>14</v>
       </c>
       <c r="F364" s="2">
-        <v>916</v>
+        <v>2026</v>
       </c>
       <c r="G364" s="2" t="s">
         <v>15</v>
@@ -15223,7 +15223,7 @@
         <v>14</v>
       </c>
       <c r="F365" s="2">
-        <v>2950</v>
+        <v>3247</v>
       </c>
       <c r="G365" s="2" t="s">
         <v>15</v>
@@ -15255,7 +15255,7 @@
         <v>14</v>
       </c>
       <c r="F366" s="2">
-        <v>3953</v>
+        <v>4319</v>
       </c>
       <c r="G366" s="2" t="s">
         <v>15</v>
@@ -15287,7 +15287,7 @@
         <v>14</v>
       </c>
       <c r="F367" s="2">
-        <v>1130</v>
+        <v>2218</v>
       </c>
       <c r="G367" s="2" t="s">
         <v>15</v>
@@ -15319,7 +15319,7 @@
         <v>14</v>
       </c>
       <c r="F368" s="2">
-        <v>1933</v>
+        <v>4492</v>
       </c>
       <c r="G368" s="2" t="s">
         <v>15</v>
@@ -15351,7 +15351,7 @@
         <v>14</v>
       </c>
       <c r="F369" s="2">
-        <v>4226</v>
+        <v>4099</v>
       </c>
       <c r="G369" s="2" t="s">
         <v>15</v>
@@ -15383,7 +15383,7 @@
         <v>14</v>
       </c>
       <c r="F370" s="2">
-        <v>1527</v>
+        <v>1955</v>
       </c>
       <c r="G370" s="2" t="s">
         <v>15</v>
@@ -15415,7 +15415,7 @@
         <v>14</v>
       </c>
       <c r="F371" s="2">
-        <v>3905</v>
+        <v>2638</v>
       </c>
       <c r="G371" s="2" t="s">
         <v>15</v>
@@ -15447,7 +15447,7 @@
         <v>14</v>
       </c>
       <c r="F372" s="2">
-        <v>2707</v>
+        <v>3835</v>
       </c>
       <c r="G372" s="2" t="s">
         <v>15</v>
@@ -15479,7 +15479,7 @@
         <v>14</v>
       </c>
       <c r="F373" s="2">
-        <v>1148</v>
+        <v>1074</v>
       </c>
       <c r="G373" s="2" t="s">
         <v>15</v>
@@ -15511,7 +15511,7 @@
         <v>14</v>
       </c>
       <c r="F374" s="2">
-        <v>4668</v>
+        <v>2251</v>
       </c>
       <c r="G374" s="2" t="s">
         <v>15</v>
@@ -15543,7 +15543,7 @@
         <v>14</v>
       </c>
       <c r="F375" s="2">
-        <v>2035</v>
+        <v>4569</v>
       </c>
       <c r="G375" s="2" t="s">
         <v>15</v>
@@ -15575,7 +15575,7 @@
         <v>14</v>
       </c>
       <c r="F376" s="2">
-        <v>2211</v>
+        <v>1462</v>
       </c>
       <c r="G376" s="2" t="s">
         <v>15</v>
@@ -15607,7 +15607,7 @@
         <v>14</v>
       </c>
       <c r="F377" s="2">
-        <v>820</v>
+        <v>2823</v>
       </c>
       <c r="G377" s="2" t="s">
         <v>15</v>
@@ -15639,7 +15639,7 @@
         <v>14</v>
       </c>
       <c r="F378" s="2">
-        <v>4217</v>
+        <v>3389</v>
       </c>
       <c r="G378" s="2" t="s">
         <v>15</v>
@@ -15671,7 +15671,7 @@
         <v>14</v>
       </c>
       <c r="F379" s="2">
-        <v>1336</v>
+        <v>4672</v>
       </c>
       <c r="G379" s="2" t="s">
         <v>15</v>
@@ -15703,7 +15703,7 @@
         <v>14</v>
       </c>
       <c r="F380" s="2">
-        <v>1602</v>
+        <v>1070</v>
       </c>
       <c r="G380" s="2" t="s">
         <v>15</v>
@@ -15735,7 +15735,7 @@
         <v>14</v>
       </c>
       <c r="F381" s="2">
-        <v>1575</v>
+        <v>865</v>
       </c>
       <c r="G381" s="2" t="s">
         <v>15</v>
@@ -15767,7 +15767,7 @@
         <v>14</v>
       </c>
       <c r="F382" s="2">
-        <v>4248</v>
+        <v>3504</v>
       </c>
       <c r="G382" s="2" t="s">
         <v>15</v>
@@ -15799,7 +15799,7 @@
         <v>14</v>
       </c>
       <c r="F383" s="2">
-        <v>3630</v>
+        <v>4110</v>
       </c>
       <c r="G383" s="2" t="s">
         <v>15</v>
@@ -15831,7 +15831,7 @@
         <v>14</v>
       </c>
       <c r="F384" s="2">
-        <v>805</v>
+        <v>2087</v>
       </c>
       <c r="G384" s="2" t="s">
         <v>15</v>
@@ -15863,7 +15863,7 @@
         <v>14</v>
       </c>
       <c r="F385" s="2">
-        <v>2828</v>
+        <v>1122</v>
       </c>
       <c r="G385" s="2" t="s">
         <v>15</v>
@@ -15895,7 +15895,7 @@
         <v>14</v>
       </c>
       <c r="F386" s="2">
-        <v>2684</v>
+        <v>3422</v>
       </c>
       <c r="G386" s="2" t="s">
         <v>15</v>
@@ -15927,7 +15927,7 @@
         <v>14</v>
       </c>
       <c r="F387" s="2">
-        <v>3711</v>
+        <v>1251</v>
       </c>
       <c r="G387" s="2" t="s">
         <v>15</v>
@@ -15959,7 +15959,7 @@
         <v>14</v>
       </c>
       <c r="F388" s="2">
-        <v>3359</v>
+        <v>4469</v>
       </c>
       <c r="G388" s="2" t="s">
         <v>15</v>
@@ -15991,7 +15991,7 @@
         <v>14</v>
       </c>
       <c r="F389" s="2">
-        <v>4241</v>
+        <v>2557</v>
       </c>
       <c r="G389" s="2" t="s">
         <v>15</v>
@@ -16023,7 +16023,7 @@
         <v>14</v>
       </c>
       <c r="F390" s="2">
-        <v>1721</v>
+        <v>3940</v>
       </c>
       <c r="G390" s="2" t="s">
         <v>15</v>
@@ -16055,7 +16055,7 @@
         <v>14</v>
       </c>
       <c r="F391" s="2">
-        <v>1652</v>
+        <v>4227</v>
       </c>
       <c r="G391" s="2" t="s">
         <v>15</v>
@@ -16087,7 +16087,7 @@
         <v>14</v>
       </c>
       <c r="F392" s="2">
-        <v>3886</v>
+        <v>855</v>
       </c>
       <c r="G392" s="2" t="s">
         <v>15</v>
@@ -16119,7 +16119,7 @@
         <v>14</v>
       </c>
       <c r="F393" s="2">
-        <v>3144</v>
+        <v>1380</v>
       </c>
       <c r="G393" s="2" t="s">
         <v>15</v>
@@ -16151,7 +16151,7 @@
         <v>14</v>
       </c>
       <c r="F394" s="2">
-        <v>1648</v>
+        <v>939</v>
       </c>
       <c r="G394" s="2" t="s">
         <v>15</v>
@@ -16183,7 +16183,7 @@
         <v>14</v>
       </c>
       <c r="F395" s="2">
-        <v>4796</v>
+        <v>2924</v>
       </c>
       <c r="G395" s="2" t="s">
         <v>15</v>
@@ -16215,7 +16215,7 @@
         <v>14</v>
       </c>
       <c r="F396" s="2">
-        <v>3486</v>
+        <v>3298</v>
       </c>
       <c r="G396" s="2" t="s">
         <v>15</v>
@@ -16247,7 +16247,7 @@
         <v>14</v>
       </c>
       <c r="F397" s="2">
-        <v>4435</v>
+        <v>3232</v>
       </c>
       <c r="G397" s="2" t="s">
         <v>15</v>
@@ -16279,7 +16279,7 @@
         <v>14</v>
       </c>
       <c r="F398" s="2">
-        <v>2397</v>
+        <v>2202</v>
       </c>
       <c r="G398" s="2" t="s">
         <v>15</v>
@@ -16311,7 +16311,7 @@
         <v>14</v>
       </c>
       <c r="F399" s="2">
-        <v>1939</v>
+        <v>2197</v>
       </c>
       <c r="G399" s="2" t="s">
         <v>15</v>
@@ -16343,7 +16343,7 @@
         <v>14</v>
       </c>
       <c r="F400" s="2">
-        <v>4568</v>
+        <v>4337</v>
       </c>
       <c r="G400" s="2" t="s">
         <v>15</v>
@@ -16375,7 +16375,7 @@
         <v>14</v>
       </c>
       <c r="F401" s="2">
-        <v>4609</v>
+        <v>3755</v>
       </c>
       <c r="G401" s="2" t="s">
         <v>15</v>
@@ -16407,7 +16407,7 @@
         <v>14</v>
       </c>
       <c r="F402" s="2">
-        <v>4618</v>
+        <v>3172</v>
       </c>
       <c r="G402" s="2" t="s">
         <v>15</v>
@@ -16439,7 +16439,7 @@
         <v>14</v>
       </c>
       <c r="F403" s="2">
-        <v>3622</v>
+        <v>2887</v>
       </c>
       <c r="G403" s="2" t="s">
         <v>15</v>
@@ -16471,7 +16471,7 @@
         <v>14</v>
       </c>
       <c r="F404" s="2">
-        <v>2977</v>
+        <v>4081</v>
       </c>
       <c r="G404" s="2" t="s">
         <v>15</v>
@@ -16503,7 +16503,7 @@
         <v>14</v>
       </c>
       <c r="F405" s="2">
-        <v>2658</v>
+        <v>4367</v>
       </c>
       <c r="G405" s="2" t="s">
         <v>15</v>
@@ -16535,7 +16535,7 @@
         <v>14</v>
       </c>
       <c r="F406" s="2">
-        <v>2247</v>
+        <v>2635</v>
       </c>
       <c r="G406" s="2" t="s">
         <v>15</v>
@@ -16567,7 +16567,7 @@
         <v>14</v>
       </c>
       <c r="F407" s="2">
-        <v>3725</v>
+        <v>3014</v>
       </c>
       <c r="G407" s="2" t="s">
         <v>15</v>
@@ -16599,7 +16599,7 @@
         <v>14</v>
       </c>
       <c r="F408" s="2">
-        <v>4060</v>
+        <v>2977</v>
       </c>
       <c r="G408" s="2" t="s">
         <v>15</v>
@@ -16631,7 +16631,7 @@
         <v>14</v>
       </c>
       <c r="F409" s="2">
-        <v>1351</v>
+        <v>1687</v>
       </c>
       <c r="G409" s="2" t="s">
         <v>15</v>
@@ -16663,7 +16663,7 @@
         <v>14</v>
       </c>
       <c r="F410" s="2">
-        <v>3136</v>
+        <v>1750</v>
       </c>
       <c r="G410" s="2" t="s">
         <v>15</v>
@@ -16695,7 +16695,7 @@
         <v>14</v>
       </c>
       <c r="F411" s="2">
-        <v>3957</v>
+        <v>4506</v>
       </c>
       <c r="G411" s="2" t="s">
         <v>15</v>
@@ -16727,7 +16727,7 @@
         <v>14</v>
       </c>
       <c r="F412" s="2">
-        <v>1766</v>
+        <v>3570</v>
       </c>
       <c r="G412" s="2" t="s">
         <v>15</v>
@@ -16759,7 +16759,7 @@
         <v>14</v>
       </c>
       <c r="F413" s="2">
-        <v>3467</v>
+        <v>4378</v>
       </c>
       <c r="G413" s="2" t="s">
         <v>15</v>
@@ -16791,7 +16791,7 @@
         <v>14</v>
       </c>
       <c r="F414" s="2">
-        <v>2209</v>
+        <v>2477</v>
       </c>
       <c r="G414" s="2" t="s">
         <v>15</v>
@@ -16823,7 +16823,7 @@
         <v>14</v>
       </c>
       <c r="F415" s="2">
-        <v>3576</v>
+        <v>1152</v>
       </c>
       <c r="G415" s="2" t="s">
         <v>15</v>
@@ -16855,7 +16855,7 @@
         <v>14</v>
       </c>
       <c r="F416" s="2">
-        <v>1586</v>
+        <v>1567</v>
       </c>
       <c r="G416" s="2" t="s">
         <v>15</v>
@@ -16887,7 +16887,7 @@
         <v>14</v>
       </c>
       <c r="F417" s="2">
-        <v>4717</v>
+        <v>4474</v>
       </c>
       <c r="G417" s="2" t="s">
         <v>15</v>
@@ -16919,7 +16919,7 @@
         <v>14</v>
       </c>
       <c r="F418" s="2">
-        <v>4756</v>
+        <v>2150</v>
       </c>
       <c r="G418" s="2" t="s">
         <v>15</v>
@@ -16951,7 +16951,7 @@
         <v>14</v>
       </c>
       <c r="F419" s="2">
-        <v>4547</v>
+        <v>1218</v>
       </c>
       <c r="G419" s="2" t="s">
         <v>15</v>
@@ -16983,7 +16983,7 @@
         <v>14</v>
       </c>
       <c r="F420" s="2">
-        <v>4223</v>
+        <v>845</v>
       </c>
       <c r="G420" s="2" t="s">
         <v>15</v>
@@ -17015,7 +17015,7 @@
         <v>14</v>
       </c>
       <c r="F421" s="2">
-        <v>3222</v>
+        <v>4377</v>
       </c>
       <c r="G421" s="2" t="s">
         <v>15</v>
@@ -17047,7 +17047,7 @@
         <v>14</v>
       </c>
       <c r="F422" s="2">
-        <v>2911</v>
+        <v>1393</v>
       </c>
       <c r="G422" s="2" t="s">
         <v>15</v>
@@ -17079,7 +17079,7 @@
         <v>14</v>
       </c>
       <c r="F423" s="2">
-        <v>3390</v>
+        <v>1475</v>
       </c>
       <c r="G423" s="2" t="s">
         <v>15</v>
@@ -17111,7 +17111,7 @@
         <v>14</v>
       </c>
       <c r="F424" s="2">
-        <v>4514</v>
+        <v>848</v>
       </c>
       <c r="G424" s="2" t="s">
         <v>15</v>
@@ -17143,7 +17143,7 @@
         <v>14</v>
       </c>
       <c r="F425" s="2">
-        <v>3770</v>
+        <v>3175</v>
       </c>
       <c r="G425" s="2" t="s">
         <v>15</v>
@@ -17175,7 +17175,7 @@
         <v>14</v>
       </c>
       <c r="F426" s="2">
-        <v>4719</v>
+        <v>2920</v>
       </c>
       <c r="G426" s="2" t="s">
         <v>15</v>
@@ -17207,7 +17207,7 @@
         <v>14</v>
       </c>
       <c r="F427" s="2">
-        <v>1011</v>
+        <v>3412</v>
       </c>
       <c r="G427" s="2" t="s">
         <v>15</v>
@@ -17239,7 +17239,7 @@
         <v>14</v>
       </c>
       <c r="F428" s="2">
-        <v>2536</v>
+        <v>2661</v>
       </c>
       <c r="G428" s="2" t="s">
         <v>15</v>
@@ -17271,7 +17271,7 @@
         <v>14</v>
       </c>
       <c r="F429" s="2">
-        <v>3936</v>
+        <v>2462</v>
       </c>
       <c r="G429" s="2" t="s">
         <v>15</v>
@@ -17303,7 +17303,7 @@
         <v>14</v>
       </c>
       <c r="F430" s="2">
-        <v>1719</v>
+        <v>3593</v>
       </c>
       <c r="G430" s="2" t="s">
         <v>15</v>
@@ -17335,7 +17335,7 @@
         <v>14</v>
       </c>
       <c r="F431" s="2">
-        <v>2272</v>
+        <v>924</v>
       </c>
       <c r="G431" s="2" t="s">
         <v>15</v>
@@ -17367,7 +17367,7 @@
         <v>14</v>
       </c>
       <c r="F432" s="2">
-        <v>1567</v>
+        <v>1477</v>
       </c>
       <c r="G432" s="2" t="s">
         <v>15</v>
@@ -17399,7 +17399,7 @@
         <v>14</v>
       </c>
       <c r="F433" s="2">
-        <v>3917</v>
+        <v>3457</v>
       </c>
       <c r="G433" s="2" t="s">
         <v>15</v>
@@ -17431,7 +17431,7 @@
         <v>14</v>
       </c>
       <c r="F434" s="2">
-        <v>855</v>
+        <v>2603</v>
       </c>
       <c r="G434" s="2" t="s">
         <v>15</v>
@@ -17463,7 +17463,7 @@
         <v>14</v>
       </c>
       <c r="F435" s="2">
-        <v>1548</v>
+        <v>1006</v>
       </c>
       <c r="G435" s="2" t="s">
         <v>15</v>
@@ -17495,7 +17495,7 @@
         <v>14</v>
       </c>
       <c r="F436" s="2">
-        <v>1708</v>
+        <v>1330</v>
       </c>
       <c r="G436" s="2" t="s">
         <v>15</v>
@@ -17527,7 +17527,7 @@
         <v>14</v>
       </c>
       <c r="F437" s="2">
-        <v>3791</v>
+        <v>4319</v>
       </c>
       <c r="G437" s="2" t="s">
         <v>15</v>
@@ -17559,7 +17559,7 @@
         <v>14</v>
       </c>
       <c r="F438" s="2">
-        <v>1162</v>
+        <v>2184</v>
       </c>
       <c r="G438" s="2" t="s">
         <v>15</v>
@@ -17591,7 +17591,7 @@
         <v>14</v>
       </c>
       <c r="F439" s="2">
-        <v>1427</v>
+        <v>2404</v>
       </c>
       <c r="G439" s="2" t="s">
         <v>15</v>
@@ -17623,7 +17623,7 @@
         <v>14</v>
       </c>
       <c r="F440" s="2">
-        <v>4183</v>
+        <v>3674</v>
       </c>
       <c r="G440" s="2" t="s">
         <v>15</v>
@@ -17655,7 +17655,7 @@
         <v>14</v>
       </c>
       <c r="F441" s="2">
-        <v>1958</v>
+        <v>3577</v>
       </c>
       <c r="G441" s="2" t="s">
         <v>15</v>
@@ -17687,7 +17687,7 @@
         <v>14</v>
       </c>
       <c r="F442" s="2">
-        <v>1970</v>
+        <v>895</v>
       </c>
       <c r="G442" s="2" t="s">
         <v>15</v>
@@ -17719,7 +17719,7 @@
         <v>14</v>
       </c>
       <c r="F443" s="2">
-        <v>4057</v>
+        <v>2515</v>
       </c>
       <c r="G443" s="2" t="s">
         <v>15</v>
@@ -17751,7 +17751,7 @@
         <v>14</v>
       </c>
       <c r="F444" s="2">
-        <v>1268</v>
+        <v>2311</v>
       </c>
       <c r="G444" s="2" t="s">
         <v>15</v>
@@ -17783,7 +17783,7 @@
         <v>14</v>
       </c>
       <c r="F445" s="2">
-        <v>1348</v>
+        <v>4437</v>
       </c>
       <c r="G445" s="2" t="s">
         <v>15</v>
@@ -17815,7 +17815,7 @@
         <v>14</v>
       </c>
       <c r="F446" s="2">
-        <v>1294</v>
+        <v>4363</v>
       </c>
       <c r="G446" s="2" t="s">
         <v>15</v>
@@ -17847,7 +17847,7 @@
         <v>14</v>
       </c>
       <c r="F447" s="2">
-        <v>3173</v>
+        <v>4298</v>
       </c>
       <c r="G447" s="2" t="s">
         <v>15</v>
@@ -17879,7 +17879,7 @@
         <v>14</v>
       </c>
       <c r="F448" s="2">
-        <v>2994</v>
+        <v>2439</v>
       </c>
       <c r="G448" s="2" t="s">
         <v>15</v>
@@ -17911,7 +17911,7 @@
         <v>14</v>
       </c>
       <c r="F449" s="2">
-        <v>2110</v>
+        <v>4645</v>
       </c>
       <c r="G449" s="2" t="s">
         <v>15</v>
@@ -17943,7 +17943,7 @@
         <v>14</v>
       </c>
       <c r="F450" s="2">
-        <v>1997</v>
+        <v>1342</v>
       </c>
       <c r="G450" s="2" t="s">
         <v>15</v>
@@ -17975,7 +17975,7 @@
         <v>14</v>
       </c>
       <c r="F451" s="2">
-        <v>3126</v>
+        <v>2672</v>
       </c>
       <c r="G451" s="2" t="s">
         <v>15</v>
@@ -18007,7 +18007,7 @@
         <v>14</v>
       </c>
       <c r="F452" s="2">
-        <v>2191</v>
+        <v>3106</v>
       </c>
       <c r="G452" s="2" t="s">
         <v>15</v>
@@ -18039,7 +18039,7 @@
         <v>14</v>
       </c>
       <c r="F453" s="2">
-        <v>2169</v>
+        <v>3750</v>
       </c>
       <c r="G453" s="2" t="s">
         <v>15</v>
@@ -18071,7 +18071,7 @@
         <v>14</v>
       </c>
       <c r="F454" s="2">
-        <v>4581</v>
+        <v>2423</v>
       </c>
       <c r="G454" s="2" t="s">
         <v>15</v>
@@ -18103,7 +18103,7 @@
         <v>14</v>
       </c>
       <c r="F455" s="2">
-        <v>3311</v>
+        <v>4015</v>
       </c>
       <c r="G455" s="2" t="s">
         <v>15</v>
@@ -18135,7 +18135,7 @@
         <v>14</v>
       </c>
       <c r="F456" s="2">
-        <v>2417</v>
+        <v>1791</v>
       </c>
       <c r="G456" s="2" t="s">
         <v>15</v>
@@ -18167,7 +18167,7 @@
         <v>14</v>
       </c>
       <c r="F457" s="2">
-        <v>3618</v>
+        <v>2347</v>
       </c>
       <c r="G457" s="2" t="s">
         <v>15</v>
@@ -18199,7 +18199,7 @@
         <v>14</v>
       </c>
       <c r="F458" s="2">
-        <v>815</v>
+        <v>4103</v>
       </c>
       <c r="G458" s="2" t="s">
         <v>15</v>
@@ -18231,7 +18231,7 @@
         <v>14</v>
       </c>
       <c r="F459" s="2">
-        <v>3526</v>
+        <v>4287</v>
       </c>
       <c r="G459" s="2" t="s">
         <v>15</v>
@@ -18263,7 +18263,7 @@
         <v>14</v>
       </c>
       <c r="F460" s="2">
-        <v>3579</v>
+        <v>2068</v>
       </c>
       <c r="G460" s="2" t="s">
         <v>15</v>
@@ -18295,7 +18295,7 @@
         <v>14</v>
       </c>
       <c r="F461" s="2">
-        <v>3860</v>
+        <v>2545</v>
       </c>
       <c r="G461" s="2" t="s">
         <v>15</v>
@@ -18327,7 +18327,7 @@
         <v>14</v>
       </c>
       <c r="F462" s="2">
-        <v>3850</v>
+        <v>2739</v>
       </c>
       <c r="G462" s="2" t="s">
         <v>15</v>
@@ -18359,7 +18359,7 @@
         <v>14</v>
       </c>
       <c r="F463" s="2">
-        <v>1277</v>
+        <v>1550</v>
       </c>
       <c r="G463" s="2" t="s">
         <v>15</v>
@@ -18391,7 +18391,7 @@
         <v>14</v>
       </c>
       <c r="F464" s="2">
-        <v>1509</v>
+        <v>4744</v>
       </c>
       <c r="G464" s="2" t="s">
         <v>15</v>
@@ -18423,7 +18423,7 @@
         <v>14</v>
       </c>
       <c r="F465" s="2">
-        <v>4216</v>
+        <v>3105</v>
       </c>
       <c r="G465" s="2" t="s">
         <v>15</v>
@@ -18455,7 +18455,7 @@
         <v>14</v>
       </c>
       <c r="F466" s="2">
-        <v>820</v>
+        <v>2996</v>
       </c>
       <c r="G466" s="2" t="s">
         <v>15</v>
@@ -18487,7 +18487,7 @@
         <v>14</v>
       </c>
       <c r="F467" s="2">
-        <v>3194</v>
+        <v>1446</v>
       </c>
       <c r="G467" s="2" t="s">
         <v>15</v>
@@ -18519,7 +18519,7 @@
         <v>14</v>
       </c>
       <c r="F468" s="2">
-        <v>4725</v>
+        <v>1021</v>
       </c>
       <c r="G468" s="2" t="s">
         <v>15</v>
@@ -18551,7 +18551,7 @@
         <v>14</v>
       </c>
       <c r="F469" s="2">
-        <v>1521</v>
+        <v>2786</v>
       </c>
       <c r="G469" s="2" t="s">
         <v>15</v>
@@ -18583,7 +18583,7 @@
         <v>14</v>
       </c>
       <c r="F470" s="2">
-        <v>2906</v>
+        <v>4230</v>
       </c>
       <c r="G470" s="2" t="s">
         <v>15</v>
@@ -18615,7 +18615,7 @@
         <v>14</v>
       </c>
       <c r="F471" s="2">
-        <v>3588</v>
+        <v>1294</v>
       </c>
       <c r="G471" s="2" t="s">
         <v>15</v>
@@ -18702,7 +18702,7 @@
         <v>14</v>
       </c>
       <c r="F2" s="2">
-        <v>2571</v>
+        <v>1450</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>15</v>
@@ -18734,7 +18734,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="2">
-        <v>4035</v>
+        <v>2489</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>15</v>
@@ -18766,7 +18766,7 @@
         <v>14</v>
       </c>
       <c r="F4" s="2">
-        <v>4448</v>
+        <v>2638</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
@@ -18798,7 +18798,7 @@
         <v>14</v>
       </c>
       <c r="F5" s="2">
-        <v>4189</v>
+        <v>974</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
@@ -18830,7 +18830,7 @@
         <v>14</v>
       </c>
       <c r="F6" s="2">
-        <v>1262</v>
+        <v>4614</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -18862,7 +18862,7 @@
         <v>14</v>
       </c>
       <c r="F7" s="2">
-        <v>4074</v>
+        <v>2741</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -18894,7 +18894,7 @@
         <v>14</v>
       </c>
       <c r="F8" s="2">
-        <v>3659</v>
+        <v>3827</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -18926,7 +18926,7 @@
         <v>14</v>
       </c>
       <c r="F9" s="2">
-        <v>3314</v>
+        <v>2828</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -18958,7 +18958,7 @@
         <v>14</v>
       </c>
       <c r="F10" s="2">
-        <v>3168</v>
+        <v>3647</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
@@ -18990,7 +18990,7 @@
         <v>14</v>
       </c>
       <c r="F11" s="2">
-        <v>2537</v>
+        <v>1609</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
@@ -19022,7 +19022,7 @@
         <v>14</v>
       </c>
       <c r="F12" s="2">
-        <v>1095</v>
+        <v>4028</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
@@ -19054,7 +19054,7 @@
         <v>14</v>
       </c>
       <c r="F13" s="2">
-        <v>3236</v>
+        <v>2234</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -19086,7 +19086,7 @@
         <v>14</v>
       </c>
       <c r="F14" s="2">
-        <v>3381</v>
+        <v>2257</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -19118,7 +19118,7 @@
         <v>14</v>
       </c>
       <c r="F15" s="2">
-        <v>2503</v>
+        <v>4552</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -19150,7 +19150,7 @@
         <v>14</v>
       </c>
       <c r="F16" s="2">
-        <v>2313</v>
+        <v>4048</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
@@ -19182,7 +19182,7 @@
         <v>14</v>
       </c>
       <c r="F17" s="2">
-        <v>4287</v>
+        <v>1247</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
@@ -19214,7 +19214,7 @@
         <v>14</v>
       </c>
       <c r="F18" s="2">
-        <v>1738</v>
+        <v>1995</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
@@ -19246,7 +19246,7 @@
         <v>14</v>
       </c>
       <c r="F19" s="2">
-        <v>2023</v>
+        <v>858</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
@@ -19278,7 +19278,7 @@
         <v>14</v>
       </c>
       <c r="F20" s="2">
-        <v>3168</v>
+        <v>4489</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
@@ -19310,7 +19310,7 @@
         <v>14</v>
       </c>
       <c r="F21" s="2">
-        <v>2611</v>
+        <v>4276</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -19342,7 +19342,7 @@
         <v>14</v>
       </c>
       <c r="F22" s="2">
-        <v>4371</v>
+        <v>3282</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -19374,7 +19374,7 @@
         <v>14</v>
       </c>
       <c r="F23" s="2">
-        <v>810</v>
+        <v>4545</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -19406,7 +19406,7 @@
         <v>14</v>
       </c>
       <c r="F24" s="2">
-        <v>1467</v>
+        <v>1826</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -19438,7 +19438,7 @@
         <v>14</v>
       </c>
       <c r="F25" s="2">
-        <v>3921</v>
+        <v>4127</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -19470,7 +19470,7 @@
         <v>14</v>
       </c>
       <c r="F26" s="2">
-        <v>2816</v>
+        <v>1717</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -19502,7 +19502,7 @@
         <v>14</v>
       </c>
       <c r="F27" s="2">
-        <v>3101</v>
+        <v>3328</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>15</v>
@@ -19534,7 +19534,7 @@
         <v>14</v>
       </c>
       <c r="F28" s="2">
-        <v>1789</v>
+        <v>3302</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>15</v>
@@ -19566,7 +19566,7 @@
         <v>14</v>
       </c>
       <c r="F29" s="2">
-        <v>2816</v>
+        <v>3596</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>15</v>
@@ -19598,7 +19598,7 @@
         <v>14</v>
       </c>
       <c r="F30" s="2">
-        <v>1257</v>
+        <v>3771</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>15</v>
@@ -19630,7 +19630,7 @@
         <v>14</v>
       </c>
       <c r="F31" s="2">
-        <v>1809</v>
+        <v>3017</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>15</v>
@@ -19662,7 +19662,7 @@
         <v>14</v>
       </c>
       <c r="F32" s="2">
-        <v>921</v>
+        <v>2397</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>15</v>
@@ -19694,7 +19694,7 @@
         <v>14</v>
       </c>
       <c r="F33" s="2">
-        <v>3286</v>
+        <v>2673</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>15</v>
@@ -19726,7 +19726,7 @@
         <v>14</v>
       </c>
       <c r="F34" s="2">
-        <v>2359</v>
+        <v>3101</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>15</v>
@@ -19758,7 +19758,7 @@
         <v>14</v>
       </c>
       <c r="F35" s="2">
-        <v>2399</v>
+        <v>2429</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>15</v>
@@ -19790,7 +19790,7 @@
         <v>14</v>
       </c>
       <c r="F36" s="2">
-        <v>919</v>
+        <v>1150</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>15</v>
@@ -19822,7 +19822,7 @@
         <v>14</v>
       </c>
       <c r="F37" s="2">
-        <v>2222</v>
+        <v>2339</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>15</v>
@@ -19854,7 +19854,7 @@
         <v>14</v>
       </c>
       <c r="F38" s="2">
-        <v>4126</v>
+        <v>2212</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>15</v>
@@ -19886,7 +19886,7 @@
         <v>14</v>
       </c>
       <c r="F39" s="2">
-        <v>1770</v>
+        <v>2768</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>15</v>
@@ -19918,7 +19918,7 @@
         <v>14</v>
       </c>
       <c r="F40" s="2">
-        <v>4745</v>
+        <v>3111</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>15</v>
@@ -19950,7 +19950,7 @@
         <v>14</v>
       </c>
       <c r="F41" s="2">
-        <v>939</v>
+        <v>2828</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>15</v>
@@ -19982,7 +19982,7 @@
         <v>14</v>
       </c>
       <c r="F42" s="2">
-        <v>2217</v>
+        <v>978</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>15</v>
@@ -20014,7 +20014,7 @@
         <v>14</v>
       </c>
       <c r="F43" s="2">
-        <v>2056</v>
+        <v>1172</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>15</v>
@@ -20046,7 +20046,7 @@
         <v>14</v>
       </c>
       <c r="F44" s="2">
-        <v>4353</v>
+        <v>4229</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>15</v>
@@ -20078,7 +20078,7 @@
         <v>14</v>
       </c>
       <c r="F45" s="2">
-        <v>4046</v>
+        <v>987</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>15</v>
@@ -20110,7 +20110,7 @@
         <v>14</v>
       </c>
       <c r="F46" s="2">
-        <v>2187</v>
+        <v>1340</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>15</v>
@@ -20142,7 +20142,7 @@
         <v>14</v>
       </c>
       <c r="F47" s="2">
-        <v>1764</v>
+        <v>3810</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>15</v>
@@ -20174,7 +20174,7 @@
         <v>14</v>
       </c>
       <c r="F48" s="2">
-        <v>4569</v>
+        <v>4754</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>15</v>
@@ -20206,7 +20206,7 @@
         <v>14</v>
       </c>
       <c r="F49" s="2">
-        <v>1631</v>
+        <v>1126</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>15</v>
@@ -20238,7 +20238,7 @@
         <v>14</v>
       </c>
       <c r="F50" s="2">
-        <v>2235</v>
+        <v>855</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>15</v>
@@ -20270,7 +20270,7 @@
         <v>14</v>
       </c>
       <c r="F51" s="2">
-        <v>3622</v>
+        <v>1183</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>15</v>
@@ -20302,7 +20302,7 @@
         <v>14</v>
       </c>
       <c r="F52" s="2">
-        <v>1594</v>
+        <v>4028</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>15</v>
@@ -20334,7 +20334,7 @@
         <v>14</v>
       </c>
       <c r="F53" s="2">
-        <v>4166</v>
+        <v>1862</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>15</v>
@@ -20366,7 +20366,7 @@
         <v>14</v>
       </c>
       <c r="F54" s="2">
-        <v>2321</v>
+        <v>2924</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>15</v>
@@ -20398,7 +20398,7 @@
         <v>14</v>
       </c>
       <c r="F55" s="2">
-        <v>2661</v>
+        <v>1346</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>15</v>
@@ -20430,7 +20430,7 @@
         <v>14</v>
       </c>
       <c r="F56" s="2">
-        <v>1348</v>
+        <v>2612</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>15</v>
@@ -20462,7 +20462,7 @@
         <v>14</v>
       </c>
       <c r="F57" s="2">
-        <v>3186</v>
+        <v>2772</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>15</v>
@@ -20494,7 +20494,7 @@
         <v>14</v>
       </c>
       <c r="F58" s="2">
-        <v>4447</v>
+        <v>3387</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>15</v>
@@ -20526,7 +20526,7 @@
         <v>14</v>
       </c>
       <c r="F59" s="2">
-        <v>3327</v>
+        <v>1418</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>15</v>
@@ -20558,7 +20558,7 @@
         <v>14</v>
       </c>
       <c r="F60" s="2">
-        <v>927</v>
+        <v>1511</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>15</v>
@@ -20590,7 +20590,7 @@
         <v>14</v>
       </c>
       <c r="F61" s="2">
-        <v>1624</v>
+        <v>3534</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>15</v>
@@ -20622,7 +20622,7 @@
         <v>14</v>
       </c>
       <c r="F62" s="2">
-        <v>1855</v>
+        <v>4205</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>15</v>
@@ -20654,7 +20654,7 @@
         <v>14</v>
       </c>
       <c r="F63" s="2">
-        <v>2658</v>
+        <v>3890</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>15</v>
@@ -20686,7 +20686,7 @@
         <v>14</v>
       </c>
       <c r="F64" s="2">
-        <v>2376</v>
+        <v>4606</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>15</v>
@@ -20718,7 +20718,7 @@
         <v>14</v>
       </c>
       <c r="F65" s="2">
-        <v>4238</v>
+        <v>834</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>15</v>
@@ -20750,7 +20750,7 @@
         <v>14</v>
       </c>
       <c r="F66" s="2">
-        <v>3593</v>
+        <v>4523</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>15</v>
@@ -20782,7 +20782,7 @@
         <v>14</v>
       </c>
       <c r="F67" s="2">
-        <v>1934</v>
+        <v>4005</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>15</v>
@@ -20814,7 +20814,7 @@
         <v>14</v>
       </c>
       <c r="F68" s="2">
-        <v>1148</v>
+        <v>2798</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>15</v>
@@ -20846,7 +20846,7 @@
         <v>14</v>
       </c>
       <c r="F69" s="2">
-        <v>2832</v>
+        <v>1374</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>15</v>
@@ -20878,7 +20878,7 @@
         <v>14</v>
       </c>
       <c r="F70" s="2">
-        <v>4185</v>
+        <v>4360</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>15</v>
@@ -20910,7 +20910,7 @@
         <v>14</v>
       </c>
       <c r="F71" s="2">
-        <v>3100</v>
+        <v>2274</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>15</v>
@@ -20942,7 +20942,7 @@
         <v>14</v>
       </c>
       <c r="F72" s="2">
-        <v>1351</v>
+        <v>4204</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>15</v>
@@ -20974,7 +20974,7 @@
         <v>14</v>
       </c>
       <c r="F73" s="2">
-        <v>3018</v>
+        <v>4243</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>15</v>
@@ -21006,7 +21006,7 @@
         <v>14</v>
       </c>
       <c r="F74" s="2">
-        <v>1656</v>
+        <v>1783</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>15</v>
@@ -21038,7 +21038,7 @@
         <v>14</v>
       </c>
       <c r="F75" s="2">
-        <v>2834</v>
+        <v>3551</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>15</v>
@@ -21070,7 +21070,7 @@
         <v>14</v>
       </c>
       <c r="F76" s="2">
-        <v>4693</v>
+        <v>2555</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>15</v>
@@ -21102,7 +21102,7 @@
         <v>14</v>
       </c>
       <c r="F77" s="2">
-        <v>2651</v>
+        <v>1207</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>15</v>
@@ -21134,7 +21134,7 @@
         <v>14</v>
       </c>
       <c r="F78" s="2">
-        <v>1256</v>
+        <v>959</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>15</v>
@@ -21166,7 +21166,7 @@
         <v>14</v>
       </c>
       <c r="F79" s="2">
-        <v>969</v>
+        <v>3366</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>15</v>
@@ -21198,7 +21198,7 @@
         <v>14</v>
       </c>
       <c r="F80" s="2">
-        <v>3750</v>
+        <v>1196</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>15</v>
@@ -21230,7 +21230,7 @@
         <v>14</v>
       </c>
       <c r="F81" s="2">
-        <v>3680</v>
+        <v>1730</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>15</v>
@@ -21262,7 +21262,7 @@
         <v>14</v>
       </c>
       <c r="F82" s="2">
-        <v>2527</v>
+        <v>4771</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>15</v>
@@ -21294,7 +21294,7 @@
         <v>14</v>
       </c>
       <c r="F83" s="2">
-        <v>2710</v>
+        <v>1731</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>15</v>
@@ -21326,7 +21326,7 @@
         <v>14</v>
       </c>
       <c r="F84" s="2">
-        <v>3519</v>
+        <v>2551</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>15</v>
@@ -21358,7 +21358,7 @@
         <v>14</v>
       </c>
       <c r="F85" s="2">
-        <v>1319</v>
+        <v>3196</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>15</v>
@@ -21390,7 +21390,7 @@
         <v>14</v>
       </c>
       <c r="F86" s="2">
-        <v>3286</v>
+        <v>4215</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>15</v>
@@ -21422,7 +21422,7 @@
         <v>14</v>
       </c>
       <c r="F87" s="2">
-        <v>1263</v>
+        <v>2949</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>15</v>
@@ -21454,7 +21454,7 @@
         <v>14</v>
       </c>
       <c r="F88" s="2">
-        <v>3476</v>
+        <v>3415</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>15</v>
@@ -21486,7 +21486,7 @@
         <v>14</v>
       </c>
       <c r="F89" s="2">
-        <v>2448</v>
+        <v>3469</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>15</v>
@@ -21518,7 +21518,7 @@
         <v>14</v>
       </c>
       <c r="F90" s="2">
-        <v>2859</v>
+        <v>2636</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>15</v>
@@ -21550,7 +21550,7 @@
         <v>14</v>
       </c>
       <c r="F91" s="2">
-        <v>4700</v>
+        <v>1032</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>15</v>
@@ -21582,7 +21582,7 @@
         <v>14</v>
       </c>
       <c r="F92" s="2">
-        <v>4739</v>
+        <v>3305</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>15</v>
@@ -21614,7 +21614,7 @@
         <v>14</v>
       </c>
       <c r="F93" s="2">
-        <v>3696</v>
+        <v>3102</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>15</v>
@@ -21646,7 +21646,7 @@
         <v>14</v>
       </c>
       <c r="F94" s="2">
-        <v>1789</v>
+        <v>3782</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>15</v>
@@ -21678,7 +21678,7 @@
         <v>14</v>
       </c>
       <c r="F95" s="2">
-        <v>1544</v>
+        <v>1005</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>15</v>
@@ -21710,7 +21710,7 @@
         <v>14</v>
       </c>
       <c r="F96" s="2">
-        <v>1619</v>
+        <v>1868</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>15</v>
@@ -21742,7 +21742,7 @@
         <v>14</v>
       </c>
       <c r="F97" s="2">
-        <v>4326</v>
+        <v>807</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>15</v>
@@ -21774,7 +21774,7 @@
         <v>14</v>
       </c>
       <c r="F98" s="2">
-        <v>4087</v>
+        <v>3176</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>15</v>
@@ -21806,7 +21806,7 @@
         <v>14</v>
       </c>
       <c r="F99" s="2">
-        <v>1117</v>
+        <v>4455</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>15</v>
@@ -21838,7 +21838,7 @@
         <v>14</v>
       </c>
       <c r="F100" s="2">
-        <v>1770</v>
+        <v>2360</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>15</v>
@@ -21870,7 +21870,7 @@
         <v>14</v>
       </c>
       <c r="F101" s="2">
-        <v>2740</v>
+        <v>1753</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>15</v>
@@ -21902,7 +21902,7 @@
         <v>14</v>
       </c>
       <c r="F102" s="2">
-        <v>1490</v>
+        <v>2048</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>15</v>
@@ -21934,7 +21934,7 @@
         <v>14</v>
       </c>
       <c r="F103" s="2">
-        <v>3557</v>
+        <v>3195</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>15</v>
@@ -21966,7 +21966,7 @@
         <v>14</v>
       </c>
       <c r="F104" s="2">
-        <v>2340</v>
+        <v>2122</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>15</v>
@@ -21998,7 +21998,7 @@
         <v>14</v>
       </c>
       <c r="F105" s="2">
-        <v>4725</v>
+        <v>3135</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>15</v>
@@ -22030,7 +22030,7 @@
         <v>14</v>
       </c>
       <c r="F106" s="2">
-        <v>3075</v>
+        <v>4611</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>15</v>
@@ -22062,7 +22062,7 @@
         <v>14</v>
       </c>
       <c r="F107" s="2">
-        <v>4389</v>
+        <v>3789</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>15</v>
@@ -22094,7 +22094,7 @@
         <v>14</v>
       </c>
       <c r="F108" s="2">
-        <v>3074</v>
+        <v>3691</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>15</v>
@@ -22126,7 +22126,7 @@
         <v>14</v>
       </c>
       <c r="F109" s="2">
-        <v>4798</v>
+        <v>2675</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>15</v>
@@ -22158,7 +22158,7 @@
         <v>14</v>
       </c>
       <c r="F110" s="2">
-        <v>847</v>
+        <v>3107</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>15</v>
@@ -22190,7 +22190,7 @@
         <v>14</v>
       </c>
       <c r="F111" s="2">
-        <v>2920</v>
+        <v>2158</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>15</v>
@@ -22222,7 +22222,7 @@
         <v>14</v>
       </c>
       <c r="F112" s="2">
-        <v>3199</v>
+        <v>1994</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>15</v>
@@ -22254,7 +22254,7 @@
         <v>14</v>
       </c>
       <c r="F113" s="2">
-        <v>4704</v>
+        <v>3106</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>15</v>
@@ -22286,7 +22286,7 @@
         <v>14</v>
       </c>
       <c r="F114" s="2">
-        <v>1593</v>
+        <v>1578</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>15</v>
@@ -22318,7 +22318,7 @@
         <v>14</v>
       </c>
       <c r="F115" s="2">
-        <v>3254</v>
+        <v>2858</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>15</v>
@@ -22350,7 +22350,7 @@
         <v>14</v>
       </c>
       <c r="F116" s="2">
-        <v>1707</v>
+        <v>2058</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>15</v>
@@ -22382,7 +22382,7 @@
         <v>14</v>
       </c>
       <c r="F117" s="2">
-        <v>1132</v>
+        <v>1006</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>15</v>
@@ -22414,7 +22414,7 @@
         <v>14</v>
       </c>
       <c r="F118" s="2">
-        <v>1205</v>
+        <v>2884</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>15</v>
@@ -22446,7 +22446,7 @@
         <v>14</v>
       </c>
       <c r="F119" s="2">
-        <v>1121</v>
+        <v>2051</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>15</v>
@@ -22478,7 +22478,7 @@
         <v>14</v>
       </c>
       <c r="F120" s="2">
-        <v>4279</v>
+        <v>948</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>15</v>
@@ -22510,7 +22510,7 @@
         <v>14</v>
       </c>
       <c r="F121" s="2">
-        <v>3912</v>
+        <v>2225</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>15</v>
@@ -22542,7 +22542,7 @@
         <v>14</v>
       </c>
       <c r="F122" s="2">
-        <v>4786</v>
+        <v>844</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>15</v>
@@ -22574,7 +22574,7 @@
         <v>14</v>
       </c>
       <c r="F123" s="2">
-        <v>1674</v>
+        <v>2023</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>15</v>
@@ -22606,7 +22606,7 @@
         <v>14</v>
       </c>
       <c r="F124" s="2">
-        <v>3257</v>
+        <v>1520</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>15</v>
@@ -22638,7 +22638,7 @@
         <v>14</v>
       </c>
       <c r="F125" s="2">
-        <v>3781</v>
+        <v>3380</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>15</v>
@@ -22670,7 +22670,7 @@
         <v>14</v>
       </c>
       <c r="F126" s="2">
-        <v>2607</v>
+        <v>2494</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>15</v>
@@ -22702,7 +22702,7 @@
         <v>14</v>
       </c>
       <c r="F127" s="2">
-        <v>3611</v>
+        <v>4678</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>15</v>
@@ -22734,7 +22734,7 @@
         <v>14</v>
       </c>
       <c r="F128" s="2">
-        <v>3037</v>
+        <v>1316</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>15</v>
@@ -22766,7 +22766,7 @@
         <v>14</v>
       </c>
       <c r="F129" s="2">
-        <v>3383</v>
+        <v>2231</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>15</v>
@@ -22798,7 +22798,7 @@
         <v>14</v>
       </c>
       <c r="F130" s="2">
-        <v>3967</v>
+        <v>2890</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>15</v>
@@ -22830,7 +22830,7 @@
         <v>14</v>
       </c>
       <c r="F131" s="2">
-        <v>1038</v>
+        <v>4322</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>15</v>
@@ -22862,7 +22862,7 @@
         <v>14</v>
       </c>
       <c r="F132" s="2">
-        <v>3641</v>
+        <v>3108</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>15</v>
@@ -22894,7 +22894,7 @@
         <v>14</v>
       </c>
       <c r="F133" s="2">
-        <v>1141</v>
+        <v>2667</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>15</v>
@@ -22926,7 +22926,7 @@
         <v>14</v>
       </c>
       <c r="F134" s="2">
-        <v>1571</v>
+        <v>1541</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>15</v>
@@ -22958,7 +22958,7 @@
         <v>14</v>
       </c>
       <c r="F135" s="2">
-        <v>4083</v>
+        <v>1368</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>15</v>
@@ -22990,7 +22990,7 @@
         <v>14</v>
       </c>
       <c r="F136" s="2">
-        <v>3241</v>
+        <v>3345</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>15</v>
@@ -23022,7 +23022,7 @@
         <v>14</v>
       </c>
       <c r="F137" s="2">
-        <v>2416</v>
+        <v>1459</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>15</v>
@@ -23054,7 +23054,7 @@
         <v>14</v>
       </c>
       <c r="F138" s="2">
-        <v>4027</v>
+        <v>2512</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>15</v>
@@ -23086,7 +23086,7 @@
         <v>14</v>
       </c>
       <c r="F139" s="2">
-        <v>4105</v>
+        <v>2499</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>15</v>
@@ -23118,7 +23118,7 @@
         <v>14</v>
       </c>
       <c r="F140" s="2">
-        <v>3674</v>
+        <v>2413</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>15</v>
@@ -23150,7 +23150,7 @@
         <v>14</v>
       </c>
       <c r="F141" s="2">
-        <v>2953</v>
+        <v>893</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>15</v>
@@ -23182,7 +23182,7 @@
         <v>14</v>
       </c>
       <c r="F142" s="2">
-        <v>4225</v>
+        <v>3241</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>15</v>
@@ -23214,7 +23214,7 @@
         <v>14</v>
       </c>
       <c r="F143" s="2">
-        <v>3778</v>
+        <v>3423</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>15</v>
@@ -23246,7 +23246,7 @@
         <v>14</v>
       </c>
       <c r="F144" s="2">
-        <v>4685</v>
+        <v>1202</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>15</v>
@@ -23278,7 +23278,7 @@
         <v>14</v>
       </c>
       <c r="F145" s="2">
-        <v>3120</v>
+        <v>2502</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>15</v>
@@ -23310,7 +23310,7 @@
         <v>14</v>
       </c>
       <c r="F146" s="2">
-        <v>4789</v>
+        <v>3529</v>
       </c>
       <c r="G146" s="2" t="s">
         <v>15</v>
@@ -23342,7 +23342,7 @@
         <v>14</v>
       </c>
       <c r="F147" s="2">
-        <v>3075</v>
+        <v>1682</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>15</v>
@@ -23374,7 +23374,7 @@
         <v>14</v>
       </c>
       <c r="F148" s="2">
-        <v>1457</v>
+        <v>1079</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>15</v>
@@ -23406,7 +23406,7 @@
         <v>14</v>
       </c>
       <c r="F149" s="2">
-        <v>2766</v>
+        <v>1265</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>15</v>
@@ -23438,7 +23438,7 @@
         <v>14</v>
       </c>
       <c r="F150" s="2">
-        <v>1389</v>
+        <v>3113</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>15</v>
@@ -23470,7 +23470,7 @@
         <v>14</v>
       </c>
       <c r="F151" s="2">
-        <v>3724</v>
+        <v>3027</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>15</v>
@@ -23502,7 +23502,7 @@
         <v>14</v>
       </c>
       <c r="F152" s="2">
-        <v>4195</v>
+        <v>4430</v>
       </c>
       <c r="G152" s="2" t="s">
         <v>15</v>
@@ -23534,7 +23534,7 @@
         <v>14</v>
       </c>
       <c r="F153" s="2">
-        <v>967</v>
+        <v>4783</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>15</v>
@@ -23566,7 +23566,7 @@
         <v>14</v>
       </c>
       <c r="F154" s="2">
-        <v>3636</v>
+        <v>1328</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>15</v>
@@ -23598,7 +23598,7 @@
         <v>14</v>
       </c>
       <c r="F155" s="2">
-        <v>1951</v>
+        <v>3653</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>15</v>
@@ -23630,7 +23630,7 @@
         <v>14</v>
       </c>
       <c r="F156" s="2">
-        <v>3436</v>
+        <v>2509</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>15</v>
@@ -23662,7 +23662,7 @@
         <v>14</v>
       </c>
       <c r="F157" s="2">
-        <v>2497</v>
+        <v>2023</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>15</v>
@@ -23694,7 +23694,7 @@
         <v>14</v>
       </c>
       <c r="F158" s="2">
-        <v>3458</v>
+        <v>4246</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>15</v>
@@ -23726,7 +23726,7 @@
         <v>14</v>
       </c>
       <c r="F159" s="2">
-        <v>4274</v>
+        <v>863</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>15</v>
@@ -23758,7 +23758,7 @@
         <v>14</v>
       </c>
       <c r="F160" s="2">
-        <v>875</v>
+        <v>3546</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>15</v>
@@ -23790,7 +23790,7 @@
         <v>14</v>
       </c>
       <c r="F161" s="2">
-        <v>4559</v>
+        <v>3575</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>15</v>
@@ -23822,7 +23822,7 @@
         <v>14</v>
       </c>
       <c r="F162" s="2">
-        <v>1771</v>
+        <v>1636</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>15</v>
@@ -23854,7 +23854,7 @@
         <v>14</v>
       </c>
       <c r="F163" s="2">
-        <v>4416</v>
+        <v>3138</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>15</v>
@@ -23886,7 +23886,7 @@
         <v>14</v>
       </c>
       <c r="F164" s="2">
-        <v>1039</v>
+        <v>2762</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>15</v>
@@ -23918,7 +23918,7 @@
         <v>14</v>
       </c>
       <c r="F165" s="2">
-        <v>1805</v>
+        <v>1080</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>15</v>
@@ -23950,7 +23950,7 @@
         <v>14</v>
       </c>
       <c r="F166" s="2">
-        <v>1376</v>
+        <v>1409</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>15</v>
@@ -23982,7 +23982,7 @@
         <v>14</v>
       </c>
       <c r="F167" s="2">
-        <v>1729</v>
+        <v>3581</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>15</v>
@@ -24014,7 +24014,7 @@
         <v>14</v>
       </c>
       <c r="F168" s="2">
-        <v>4057</v>
+        <v>1618</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>15</v>
@@ -24046,7 +24046,7 @@
         <v>14</v>
       </c>
       <c r="F169" s="2">
-        <v>3700</v>
+        <v>2454</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>15</v>
@@ -24078,7 +24078,7 @@
         <v>14</v>
       </c>
       <c r="F170" s="2">
-        <v>3857</v>
+        <v>3610</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>15</v>
@@ -24110,7 +24110,7 @@
         <v>14</v>
       </c>
       <c r="F171" s="2">
-        <v>1885</v>
+        <v>4719</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>15</v>
@@ -24142,7 +24142,7 @@
         <v>14</v>
       </c>
       <c r="F172" s="2">
-        <v>2925</v>
+        <v>3452</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>15</v>
@@ -24174,7 +24174,7 @@
         <v>14</v>
       </c>
       <c r="F173" s="2">
-        <v>3388</v>
+        <v>2261</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>15</v>
@@ -24206,7 +24206,7 @@
         <v>14</v>
       </c>
       <c r="F174" s="2">
-        <v>1350</v>
+        <v>846</v>
       </c>
       <c r="G174" s="2" t="s">
         <v>15</v>
@@ -24238,7 +24238,7 @@
         <v>14</v>
       </c>
       <c r="F175" s="2">
-        <v>4633</v>
+        <v>2382</v>
       </c>
       <c r="G175" s="2" t="s">
         <v>15</v>
@@ -24270,7 +24270,7 @@
         <v>14</v>
       </c>
       <c r="F176" s="2">
-        <v>1448</v>
+        <v>1067</v>
       </c>
       <c r="G176" s="2" t="s">
         <v>15</v>
@@ -24302,7 +24302,7 @@
         <v>14</v>
       </c>
       <c r="F177" s="2">
-        <v>4598</v>
+        <v>2191</v>
       </c>
       <c r="G177" s="2" t="s">
         <v>15</v>
@@ -24334,7 +24334,7 @@
         <v>14</v>
       </c>
       <c r="F178" s="2">
-        <v>3337</v>
+        <v>1507</v>
       </c>
       <c r="G178" s="2" t="s">
         <v>15</v>
@@ -24366,7 +24366,7 @@
         <v>14</v>
       </c>
       <c r="F179" s="2">
-        <v>4338</v>
+        <v>3017</v>
       </c>
       <c r="G179" s="2" t="s">
         <v>15</v>
@@ -24398,7 +24398,7 @@
         <v>14</v>
       </c>
       <c r="F180" s="2">
-        <v>4339</v>
+        <v>1674</v>
       </c>
       <c r="G180" s="2" t="s">
         <v>15</v>
@@ -24430,7 +24430,7 @@
         <v>14</v>
       </c>
       <c r="F181" s="2">
-        <v>1748</v>
+        <v>1054</v>
       </c>
       <c r="G181" s="2" t="s">
         <v>15</v>
@@ -24462,7 +24462,7 @@
         <v>14</v>
       </c>
       <c r="F182" s="2">
-        <v>2920</v>
+        <v>2958</v>
       </c>
       <c r="G182" s="2" t="s">
         <v>15</v>
@@ -24494,7 +24494,7 @@
         <v>14</v>
       </c>
       <c r="F183" s="2">
-        <v>1413</v>
+        <v>2664</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>15</v>
@@ -24526,7 +24526,7 @@
         <v>14</v>
       </c>
       <c r="F184" s="2">
-        <v>2863</v>
+        <v>1841</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>15</v>
@@ -24558,7 +24558,7 @@
         <v>14</v>
       </c>
       <c r="F185" s="2">
-        <v>2965</v>
+        <v>3179</v>
       </c>
       <c r="G185" s="2" t="s">
         <v>15</v>
@@ -24590,7 +24590,7 @@
         <v>14</v>
       </c>
       <c r="F186" s="2">
-        <v>1403</v>
+        <v>1278</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>15</v>
@@ -24622,7 +24622,7 @@
         <v>14</v>
       </c>
       <c r="F187" s="2">
-        <v>2079</v>
+        <v>4725</v>
       </c>
       <c r="G187" s="2" t="s">
         <v>15</v>
@@ -24654,7 +24654,7 @@
         <v>14</v>
       </c>
       <c r="F188" s="2">
-        <v>4346</v>
+        <v>4792</v>
       </c>
       <c r="G188" s="2" t="s">
         <v>15</v>
@@ -24686,7 +24686,7 @@
         <v>14</v>
       </c>
       <c r="F189" s="2">
-        <v>2788</v>
+        <v>4407</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>15</v>
@@ -24718,7 +24718,7 @@
         <v>14</v>
       </c>
       <c r="F190" s="2">
-        <v>3301</v>
+        <v>2605</v>
       </c>
       <c r="G190" s="2" t="s">
         <v>15</v>
@@ -24750,7 +24750,7 @@
         <v>14</v>
       </c>
       <c r="F191" s="2">
-        <v>3162</v>
+        <v>3903</v>
       </c>
       <c r="G191" s="2" t="s">
         <v>15</v>
@@ -24782,7 +24782,7 @@
         <v>14</v>
       </c>
       <c r="F192" s="2">
-        <v>4749</v>
+        <v>4345</v>
       </c>
       <c r="G192" s="2" t="s">
         <v>15</v>
@@ -24814,7 +24814,7 @@
         <v>14</v>
       </c>
       <c r="F193" s="2">
-        <v>1594</v>
+        <v>3974</v>
       </c>
       <c r="G193" s="2" t="s">
         <v>15</v>
@@ -24846,7 +24846,7 @@
         <v>14</v>
       </c>
       <c r="F194" s="2">
-        <v>1534</v>
+        <v>4532</v>
       </c>
       <c r="G194" s="2" t="s">
         <v>15</v>
@@ -24878,7 +24878,7 @@
         <v>14</v>
       </c>
       <c r="F195" s="2">
-        <v>1299</v>
+        <v>1673</v>
       </c>
       <c r="G195" s="2" t="s">
         <v>15</v>
@@ -24910,7 +24910,7 @@
         <v>14</v>
       </c>
       <c r="F196" s="2">
-        <v>3576</v>
+        <v>1462</v>
       </c>
       <c r="G196" s="2" t="s">
         <v>15</v>
@@ -24942,7 +24942,7 @@
         <v>14</v>
       </c>
       <c r="F197" s="2">
-        <v>1087</v>
+        <v>4539</v>
       </c>
       <c r="G197" s="2" t="s">
         <v>15</v>
@@ -24974,7 +24974,7 @@
         <v>14</v>
       </c>
       <c r="F198" s="2">
-        <v>3002</v>
+        <v>1081</v>
       </c>
       <c r="G198" s="2" t="s">
         <v>15</v>
@@ -25006,7 +25006,7 @@
         <v>14</v>
       </c>
       <c r="F199" s="2">
-        <v>4776</v>
+        <v>4648</v>
       </c>
       <c r="G199" s="2" t="s">
         <v>15</v>
@@ -25038,7 +25038,7 @@
         <v>14</v>
       </c>
       <c r="F200" s="2">
-        <v>3830</v>
+        <v>3024</v>
       </c>
       <c r="G200" s="2" t="s">
         <v>15</v>
@@ -25070,7 +25070,7 @@
         <v>14</v>
       </c>
       <c r="F201" s="2">
-        <v>1046</v>
+        <v>818</v>
       </c>
       <c r="G201" s="2" t="s">
         <v>15</v>
@@ -25102,7 +25102,7 @@
         <v>14</v>
       </c>
       <c r="F202" s="2">
-        <v>3768</v>
+        <v>1848</v>
       </c>
       <c r="G202" s="2" t="s">
         <v>15</v>
@@ -25134,7 +25134,7 @@
         <v>14</v>
       </c>
       <c r="F203" s="2">
-        <v>1507</v>
+        <v>1482</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>15</v>
@@ -25166,7 +25166,7 @@
         <v>14</v>
       </c>
       <c r="F204" s="2">
-        <v>3963</v>
+        <v>1764</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>15</v>
@@ -25198,7 +25198,7 @@
         <v>14</v>
       </c>
       <c r="F205" s="2">
-        <v>3992</v>
+        <v>2292</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>15</v>
@@ -25230,7 +25230,7 @@
         <v>14</v>
       </c>
       <c r="F206" s="2">
-        <v>1558</v>
+        <v>1839</v>
       </c>
       <c r="G206" s="2" t="s">
         <v>15</v>
@@ -25262,7 +25262,7 @@
         <v>14</v>
       </c>
       <c r="F207" s="2">
-        <v>1737</v>
+        <v>4118</v>
       </c>
       <c r="G207" s="2" t="s">
         <v>15</v>
@@ -25294,7 +25294,7 @@
         <v>14</v>
       </c>
       <c r="F208" s="2">
-        <v>2331</v>
+        <v>4104</v>
       </c>
       <c r="G208" s="2" t="s">
         <v>15</v>
@@ -25326,7 +25326,7 @@
         <v>14</v>
       </c>
       <c r="F209" s="2">
-        <v>3913</v>
+        <v>1476</v>
       </c>
       <c r="G209" s="2" t="s">
         <v>15</v>
@@ -25358,7 +25358,7 @@
         <v>14</v>
       </c>
       <c r="F210" s="2">
-        <v>2246</v>
+        <v>4749</v>
       </c>
       <c r="G210" s="2" t="s">
         <v>15</v>
@@ -25390,7 +25390,7 @@
         <v>14</v>
       </c>
       <c r="F211" s="2">
-        <v>2250</v>
+        <v>1958</v>
       </c>
       <c r="G211" s="2" t="s">
         <v>15</v>
@@ -25422,7 +25422,7 @@
         <v>14</v>
       </c>
       <c r="F212" s="2">
-        <v>1364</v>
+        <v>3187</v>
       </c>
       <c r="G212" s="2" t="s">
         <v>15</v>
@@ -25454,7 +25454,7 @@
         <v>14</v>
       </c>
       <c r="F213" s="2">
-        <v>2823</v>
+        <v>3028</v>
       </c>
       <c r="G213" s="2" t="s">
         <v>15</v>
@@ -25486,7 +25486,7 @@
         <v>14</v>
       </c>
       <c r="F214" s="2">
-        <v>2232</v>
+        <v>1288</v>
       </c>
       <c r="G214" s="2" t="s">
         <v>15</v>
@@ -25518,7 +25518,7 @@
         <v>14</v>
       </c>
       <c r="F215" s="2">
-        <v>2000</v>
+        <v>1057</v>
       </c>
       <c r="G215" s="2" t="s">
         <v>15</v>
@@ -25550,7 +25550,7 @@
         <v>14</v>
       </c>
       <c r="F216" s="2">
-        <v>2947</v>
+        <v>964</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>15</v>
@@ -25582,7 +25582,7 @@
         <v>14</v>
       </c>
       <c r="F217" s="2">
-        <v>3937</v>
+        <v>4318</v>
       </c>
       <c r="G217" s="2" t="s">
         <v>15</v>
@@ -25614,7 +25614,7 @@
         <v>14</v>
       </c>
       <c r="F218" s="2">
-        <v>2459</v>
+        <v>3674</v>
       </c>
       <c r="G218" s="2" t="s">
         <v>15</v>
@@ -25646,7 +25646,7 @@
         <v>14</v>
       </c>
       <c r="F219" s="2">
-        <v>2748</v>
+        <v>1994</v>
       </c>
       <c r="G219" s="2" t="s">
         <v>15</v>
@@ -25678,7 +25678,7 @@
         <v>14</v>
       </c>
       <c r="F220" s="2">
-        <v>1849</v>
+        <v>1931</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>15</v>
@@ -25710,7 +25710,7 @@
         <v>14</v>
       </c>
       <c r="F221" s="2">
-        <v>2586</v>
+        <v>2212</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>15</v>
@@ -25742,7 +25742,7 @@
         <v>14</v>
       </c>
       <c r="F222" s="2">
-        <v>4684</v>
+        <v>3780</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>15</v>
@@ -25774,7 +25774,7 @@
         <v>14</v>
       </c>
       <c r="F223" s="2">
-        <v>4715</v>
+        <v>1455</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>15</v>
@@ -25806,7 +25806,7 @@
         <v>14</v>
       </c>
       <c r="F224" s="2">
-        <v>2498</v>
+        <v>2164</v>
       </c>
       <c r="G224" s="2" t="s">
         <v>15</v>
@@ -25838,7 +25838,7 @@
         <v>14</v>
       </c>
       <c r="F225" s="2">
-        <v>1412</v>
+        <v>2408</v>
       </c>
       <c r="G225" s="2" t="s">
         <v>15</v>
@@ -25870,7 +25870,7 @@
         <v>14</v>
       </c>
       <c r="F226" s="2">
-        <v>4744</v>
+        <v>1028</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>15</v>
@@ -25902,7 +25902,7 @@
         <v>14</v>
       </c>
       <c r="F227" s="2">
-        <v>3769</v>
+        <v>3013</v>
       </c>
       <c r="G227" s="2" t="s">
         <v>15</v>
@@ -25934,7 +25934,7 @@
         <v>14</v>
       </c>
       <c r="F228" s="2">
-        <v>2455</v>
+        <v>1034</v>
       </c>
       <c r="G228" s="2" t="s">
         <v>15</v>
@@ -25966,7 +25966,7 @@
         <v>14</v>
       </c>
       <c r="F229" s="2">
-        <v>1683</v>
+        <v>858</v>
       </c>
       <c r="G229" s="2" t="s">
         <v>15</v>
@@ -25998,7 +25998,7 @@
         <v>14</v>
       </c>
       <c r="F230" s="2">
-        <v>942</v>
+        <v>3952</v>
       </c>
       <c r="G230" s="2" t="s">
         <v>15</v>
@@ -26030,7 +26030,7 @@
         <v>14</v>
       </c>
       <c r="F231" s="2">
-        <v>1994</v>
+        <v>2413</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>15</v>
@@ -26062,7 +26062,7 @@
         <v>14</v>
       </c>
       <c r="F232" s="2">
-        <v>4173</v>
+        <v>3285</v>
       </c>
       <c r="G232" s="2" t="s">
         <v>15</v>
@@ -26094,7 +26094,7 @@
         <v>14</v>
       </c>
       <c r="F233" s="2">
-        <v>4290</v>
+        <v>2752</v>
       </c>
       <c r="G233" s="2" t="s">
         <v>15</v>
@@ -26126,7 +26126,7 @@
         <v>14</v>
       </c>
       <c r="F234" s="2">
-        <v>3847</v>
+        <v>3537</v>
       </c>
       <c r="G234" s="2" t="s">
         <v>15</v>
@@ -26158,7 +26158,7 @@
         <v>14</v>
       </c>
       <c r="F235" s="2">
-        <v>2668</v>
+        <v>1559</v>
       </c>
       <c r="G235" s="2" t="s">
         <v>15</v>
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="F236" s="2">
-        <v>1595</v>
+        <v>1644</v>
       </c>
       <c r="G236" s="2" t="s">
         <v>15</v>
@@ -26222,7 +26222,7 @@
         <v>14</v>
       </c>
       <c r="F237" s="2">
-        <v>1258</v>
+        <v>3506</v>
       </c>
       <c r="G237" s="2" t="s">
         <v>15</v>
@@ -26254,7 +26254,7 @@
         <v>14</v>
       </c>
       <c r="F238" s="2">
-        <v>2845</v>
+        <v>1912</v>
       </c>
       <c r="G238" s="2" t="s">
         <v>15</v>
@@ -26286,7 +26286,7 @@
         <v>14</v>
       </c>
       <c r="F239" s="2">
-        <v>2972</v>
+        <v>1052</v>
       </c>
       <c r="G239" s="2" t="s">
         <v>15</v>
@@ -26318,7 +26318,7 @@
         <v>14</v>
       </c>
       <c r="F240" s="2">
-        <v>4008</v>
+        <v>4661</v>
       </c>
       <c r="G240" s="2" t="s">
         <v>15</v>
@@ -26350,7 +26350,7 @@
         <v>14</v>
       </c>
       <c r="F241" s="2">
-        <v>1093</v>
+        <v>1181</v>
       </c>
       <c r="G241" s="2" t="s">
         <v>15</v>
@@ -26382,7 +26382,7 @@
         <v>14</v>
       </c>
       <c r="F242" s="2">
-        <v>1914</v>
+        <v>3486</v>
       </c>
       <c r="G242" s="2" t="s">
         <v>15</v>
@@ -26414,7 +26414,7 @@
         <v>14</v>
       </c>
       <c r="F243" s="2">
-        <v>4278</v>
+        <v>2477</v>
       </c>
       <c r="G243" s="2" t="s">
         <v>15</v>
@@ -26446,7 +26446,7 @@
         <v>14</v>
       </c>
       <c r="F244" s="2">
-        <v>2488</v>
+        <v>1643</v>
       </c>
       <c r="G244" s="2" t="s">
         <v>15</v>
@@ -26478,7 +26478,7 @@
         <v>14</v>
       </c>
       <c r="F245" s="2">
-        <v>2805</v>
+        <v>3814</v>
       </c>
       <c r="G245" s="2" t="s">
         <v>15</v>
@@ -26510,7 +26510,7 @@
         <v>14</v>
       </c>
       <c r="F246" s="2">
-        <v>4085</v>
+        <v>1133</v>
       </c>
       <c r="G246" s="2" t="s">
         <v>15</v>
@@ -26542,7 +26542,7 @@
         <v>14</v>
       </c>
       <c r="F247" s="2">
-        <v>2786</v>
+        <v>2339</v>
       </c>
       <c r="G247" s="2" t="s">
         <v>15</v>
@@ -26574,7 +26574,7 @@
         <v>14</v>
       </c>
       <c r="F248" s="2">
-        <v>4204</v>
+        <v>3781</v>
       </c>
       <c r="G248" s="2" t="s">
         <v>15</v>
@@ -26606,7 +26606,7 @@
         <v>14</v>
       </c>
       <c r="F249" s="2">
-        <v>4137</v>
+        <v>2639</v>
       </c>
       <c r="G249" s="2" t="s">
         <v>15</v>
@@ -26638,7 +26638,7 @@
         <v>14</v>
       </c>
       <c r="F250" s="2">
-        <v>3058</v>
+        <v>3944</v>
       </c>
       <c r="G250" s="2" t="s">
         <v>15</v>
@@ -26670,7 +26670,7 @@
         <v>14</v>
       </c>
       <c r="F251" s="2">
-        <v>1141</v>
+        <v>2707</v>
       </c>
       <c r="G251" s="2" t="s">
         <v>15</v>
@@ -26702,7 +26702,7 @@
         <v>14</v>
       </c>
       <c r="F252" s="2">
-        <v>3699</v>
+        <v>1872</v>
       </c>
       <c r="G252" s="2" t="s">
         <v>15</v>
@@ -26734,7 +26734,7 @@
         <v>14</v>
       </c>
       <c r="F253" s="2">
-        <v>3487</v>
+        <v>3722</v>
       </c>
       <c r="G253" s="2" t="s">
         <v>15</v>
@@ -26766,7 +26766,7 @@
         <v>14</v>
       </c>
       <c r="F254" s="2">
-        <v>1603</v>
+        <v>2945</v>
       </c>
       <c r="G254" s="2" t="s">
         <v>15</v>
@@ -26798,7 +26798,7 @@
         <v>14</v>
       </c>
       <c r="F255" s="2">
-        <v>3282</v>
+        <v>2020</v>
       </c>
       <c r="G255" s="2" t="s">
         <v>15</v>
@@ -26830,7 +26830,7 @@
         <v>14</v>
       </c>
       <c r="F256" s="2">
-        <v>1167</v>
+        <v>1683</v>
       </c>
       <c r="G256" s="2" t="s">
         <v>15</v>
@@ -26862,7 +26862,7 @@
         <v>14</v>
       </c>
       <c r="F257" s="2">
-        <v>4750</v>
+        <v>1329</v>
       </c>
       <c r="G257" s="2" t="s">
         <v>15</v>
@@ -26894,7 +26894,7 @@
         <v>14</v>
       </c>
       <c r="F258" s="2">
-        <v>1021</v>
+        <v>3400</v>
       </c>
       <c r="G258" s="2" t="s">
         <v>15</v>
@@ -26926,7 +26926,7 @@
         <v>14</v>
       </c>
       <c r="F259" s="2">
-        <v>2825</v>
+        <v>4420</v>
       </c>
       <c r="G259" s="2" t="s">
         <v>15</v>
@@ -26958,7 +26958,7 @@
         <v>14</v>
       </c>
       <c r="F260" s="2">
-        <v>2166</v>
+        <v>3904</v>
       </c>
       <c r="G260" s="2" t="s">
         <v>15</v>
@@ -26990,7 +26990,7 @@
         <v>14</v>
       </c>
       <c r="F261" s="2">
-        <v>1350</v>
+        <v>3856</v>
       </c>
       <c r="G261" s="2" t="s">
         <v>15</v>
@@ -27022,7 +27022,7 @@
         <v>14</v>
       </c>
       <c r="F262" s="2">
-        <v>3639</v>
+        <v>4349</v>
       </c>
       <c r="G262" s="2" t="s">
         <v>15</v>
@@ -27054,7 +27054,7 @@
         <v>14</v>
       </c>
       <c r="F263" s="2">
-        <v>3697</v>
+        <v>3901</v>
       </c>
       <c r="G263" s="2" t="s">
         <v>15</v>
@@ -27086,7 +27086,7 @@
         <v>14</v>
       </c>
       <c r="F264" s="2">
-        <v>3528</v>
+        <v>3625</v>
       </c>
       <c r="G264" s="2" t="s">
         <v>15</v>
@@ -27118,7 +27118,7 @@
         <v>14</v>
       </c>
       <c r="F265" s="2">
-        <v>4517</v>
+        <v>911</v>
       </c>
       <c r="G265" s="2" t="s">
         <v>15</v>
@@ -27150,7 +27150,7 @@
         <v>14</v>
       </c>
       <c r="F266" s="2">
-        <v>4072</v>
+        <v>2349</v>
       </c>
       <c r="G266" s="2" t="s">
         <v>15</v>
@@ -27182,7 +27182,7 @@
         <v>14</v>
       </c>
       <c r="F267" s="2">
-        <v>1514</v>
+        <v>828</v>
       </c>
       <c r="G267" s="2" t="s">
         <v>15</v>
@@ -27214,7 +27214,7 @@
         <v>14</v>
       </c>
       <c r="F268" s="2">
-        <v>3501</v>
+        <v>3941</v>
       </c>
       <c r="G268" s="2" t="s">
         <v>15</v>
@@ -27246,7 +27246,7 @@
         <v>14</v>
       </c>
       <c r="F269" s="2">
-        <v>3961</v>
+        <v>3232</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>15</v>
@@ -27278,7 +27278,7 @@
         <v>14</v>
       </c>
       <c r="F270" s="2">
-        <v>2500</v>
+        <v>1042</v>
       </c>
       <c r="G270" s="2" t="s">
         <v>15</v>
@@ -27310,7 +27310,7 @@
         <v>14</v>
       </c>
       <c r="F271" s="2">
-        <v>1799</v>
+        <v>1553</v>
       </c>
       <c r="G271" s="2" t="s">
         <v>15</v>
@@ -27342,7 +27342,7 @@
         <v>14</v>
       </c>
       <c r="F272" s="2">
-        <v>2162</v>
+        <v>4474</v>
       </c>
       <c r="G272" s="2" t="s">
         <v>15</v>
@@ -27374,7 +27374,7 @@
         <v>14</v>
       </c>
       <c r="F273" s="2">
-        <v>2954</v>
+        <v>923</v>
       </c>
       <c r="G273" s="2" t="s">
         <v>15</v>
@@ -27406,7 +27406,7 @@
         <v>14</v>
       </c>
       <c r="F274" s="2">
-        <v>3258</v>
+        <v>4132</v>
       </c>
       <c r="G274" s="2" t="s">
         <v>15</v>
@@ -27438,7 +27438,7 @@
         <v>14</v>
       </c>
       <c r="F275" s="2">
-        <v>2724</v>
+        <v>1090</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>15</v>
@@ -27470,7 +27470,7 @@
         <v>14</v>
       </c>
       <c r="F276" s="2">
-        <v>4098</v>
+        <v>4000</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>15</v>
@@ -27502,7 +27502,7 @@
         <v>14</v>
       </c>
       <c r="F277" s="2">
-        <v>1795</v>
+        <v>1958</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>15</v>
@@ -27534,7 +27534,7 @@
         <v>14</v>
       </c>
       <c r="F278" s="2">
-        <v>2990</v>
+        <v>2854</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>15</v>
@@ -27566,7 +27566,7 @@
         <v>14</v>
       </c>
       <c r="F279" s="2">
-        <v>2339</v>
+        <v>2261</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>15</v>
@@ -27598,7 +27598,7 @@
         <v>14</v>
       </c>
       <c r="F280" s="2">
-        <v>1731</v>
+        <v>1738</v>
       </c>
       <c r="G280" s="2" t="s">
         <v>15</v>
@@ -27630,7 +27630,7 @@
         <v>14</v>
       </c>
       <c r="F281" s="2">
-        <v>1818</v>
+        <v>3177</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>15</v>
@@ -27662,7 +27662,7 @@
         <v>14</v>
       </c>
       <c r="F282" s="2">
-        <v>3629</v>
+        <v>2583</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>15</v>
@@ -27694,7 +27694,7 @@
         <v>14</v>
       </c>
       <c r="F283" s="2">
-        <v>2543</v>
+        <v>4479</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>15</v>
@@ -27726,7 +27726,7 @@
         <v>14</v>
       </c>
       <c r="F284" s="2">
-        <v>2543</v>
+        <v>1954</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>15</v>
@@ -27758,7 +27758,7 @@
         <v>14</v>
       </c>
       <c r="F285" s="2">
-        <v>3051</v>
+        <v>3387</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>15</v>
@@ -27790,7 +27790,7 @@
         <v>14</v>
       </c>
       <c r="F286" s="2">
-        <v>3100</v>
+        <v>4756</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>15</v>
@@ -27822,7 +27822,7 @@
         <v>14</v>
       </c>
       <c r="F287" s="2">
-        <v>4694</v>
+        <v>1687</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>15</v>
@@ -27854,7 +27854,7 @@
         <v>14</v>
       </c>
       <c r="F288" s="2">
-        <v>969</v>
+        <v>1739</v>
       </c>
       <c r="G288" s="2" t="s">
         <v>15</v>
@@ -27886,7 +27886,7 @@
         <v>14</v>
       </c>
       <c r="F289" s="2">
-        <v>2561</v>
+        <v>3477</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>15</v>
@@ -27918,7 +27918,7 @@
         <v>14</v>
       </c>
       <c r="F290" s="2">
-        <v>890</v>
+        <v>840</v>
       </c>
       <c r="G290" s="2" t="s">
         <v>15</v>
@@ -27950,7 +27950,7 @@
         <v>14</v>
       </c>
       <c r="F291" s="2">
-        <v>2166</v>
+        <v>3441</v>
       </c>
       <c r="G291" s="2" t="s">
         <v>15</v>
@@ -27982,7 +27982,7 @@
         <v>14</v>
       </c>
       <c r="F292" s="2">
-        <v>823</v>
+        <v>4664</v>
       </c>
       <c r="G292" s="2" t="s">
         <v>15</v>
@@ -28014,7 +28014,7 @@
         <v>14</v>
       </c>
       <c r="F293" s="2">
-        <v>3593</v>
+        <v>4124</v>
       </c>
       <c r="G293" s="2" t="s">
         <v>15</v>
@@ -28046,7 +28046,7 @@
         <v>14</v>
       </c>
       <c r="F294" s="2">
-        <v>2884</v>
+        <v>1289</v>
       </c>
       <c r="G294" s="2" t="s">
         <v>15</v>
@@ -28078,7 +28078,7 @@
         <v>14</v>
       </c>
       <c r="F295" s="2">
-        <v>2627</v>
+        <v>3043</v>
       </c>
       <c r="G295" s="2" t="s">
         <v>15</v>
@@ -28110,7 +28110,7 @@
         <v>14</v>
       </c>
       <c r="F296" s="2">
-        <v>3564</v>
+        <v>4441</v>
       </c>
       <c r="G296" s="2" t="s">
         <v>15</v>
@@ -28142,7 +28142,7 @@
         <v>14</v>
       </c>
       <c r="F297" s="2">
-        <v>2471</v>
+        <v>1771</v>
       </c>
       <c r="G297" s="2" t="s">
         <v>15</v>
@@ -28174,7 +28174,7 @@
         <v>14</v>
       </c>
       <c r="F298" s="2">
-        <v>2795</v>
+        <v>4137</v>
       </c>
       <c r="G298" s="2" t="s">
         <v>15</v>
@@ -28206,7 +28206,7 @@
         <v>14</v>
       </c>
       <c r="F299" s="2">
-        <v>2462</v>
+        <v>3594</v>
       </c>
       <c r="G299" s="2" t="s">
         <v>15</v>
@@ -28238,7 +28238,7 @@
         <v>14</v>
       </c>
       <c r="F300" s="2">
-        <v>2895</v>
+        <v>2115</v>
       </c>
       <c r="G300" s="2" t="s">
         <v>15</v>
@@ -28270,7 +28270,7 @@
         <v>14</v>
       </c>
       <c r="F301" s="2">
-        <v>2505</v>
+        <v>2495</v>
       </c>
       <c r="G301" s="2" t="s">
         <v>15</v>
@@ -28302,7 +28302,7 @@
         <v>14</v>
       </c>
       <c r="F302" s="2">
-        <v>852</v>
+        <v>2165</v>
       </c>
       <c r="G302" s="2" t="s">
         <v>15</v>
@@ -28334,7 +28334,7 @@
         <v>14</v>
       </c>
       <c r="F303" s="2">
-        <v>4678</v>
+        <v>2229</v>
       </c>
       <c r="G303" s="2" t="s">
         <v>15</v>
@@ -28366,7 +28366,7 @@
         <v>14</v>
       </c>
       <c r="F304" s="2">
-        <v>2970</v>
+        <v>4158</v>
       </c>
       <c r="G304" s="2" t="s">
         <v>15</v>
@@ -28398,7 +28398,7 @@
         <v>14</v>
       </c>
       <c r="F305" s="2">
-        <v>3630</v>
+        <v>949</v>
       </c>
       <c r="G305" s="2" t="s">
         <v>15</v>
@@ -28430,7 +28430,7 @@
         <v>14</v>
       </c>
       <c r="F306" s="2">
-        <v>2694</v>
+        <v>3715</v>
       </c>
       <c r="G306" s="2" t="s">
         <v>15</v>
@@ -28462,7 +28462,7 @@
         <v>14</v>
       </c>
       <c r="F307" s="2">
-        <v>1189</v>
+        <v>829</v>
       </c>
       <c r="G307" s="2" t="s">
         <v>15</v>
@@ -28494,7 +28494,7 @@
         <v>14</v>
       </c>
       <c r="F308" s="2">
-        <v>2228</v>
+        <v>3955</v>
       </c>
       <c r="G308" s="2" t="s">
         <v>15</v>
@@ -28526,7 +28526,7 @@
         <v>14</v>
       </c>
       <c r="F309" s="2">
-        <v>963</v>
+        <v>2882</v>
       </c>
       <c r="G309" s="2" t="s">
         <v>15</v>
@@ -28558,7 +28558,7 @@
         <v>14</v>
       </c>
       <c r="F310" s="2">
-        <v>1715</v>
+        <v>3280</v>
       </c>
       <c r="G310" s="2" t="s">
         <v>15</v>
@@ -28590,7 +28590,7 @@
         <v>14</v>
       </c>
       <c r="F311" s="2">
-        <v>1296</v>
+        <v>3810</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>15</v>
@@ -28622,7 +28622,7 @@
         <v>14</v>
       </c>
       <c r="F312" s="2">
-        <v>2232</v>
+        <v>4414</v>
       </c>
       <c r="G312" s="2" t="s">
         <v>15</v>
@@ -28654,7 +28654,7 @@
         <v>14</v>
       </c>
       <c r="F313" s="2">
-        <v>1246</v>
+        <v>3826</v>
       </c>
       <c r="G313" s="2" t="s">
         <v>15</v>
@@ -28686,7 +28686,7 @@
         <v>14</v>
       </c>
       <c r="F314" s="2">
-        <v>1186</v>
+        <v>3437</v>
       </c>
       <c r="G314" s="2" t="s">
         <v>15</v>
@@ -28718,7 +28718,7 @@
         <v>14</v>
       </c>
       <c r="F315" s="2">
-        <v>1796</v>
+        <v>1931</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>15</v>
@@ -28750,7 +28750,7 @@
         <v>14</v>
       </c>
       <c r="F316" s="2">
-        <v>4281</v>
+        <v>2056</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>15</v>
@@ -28782,7 +28782,7 @@
         <v>14</v>
       </c>
       <c r="F317" s="2">
-        <v>1079</v>
+        <v>3391</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>15</v>
@@ -28814,7 +28814,7 @@
         <v>14</v>
       </c>
       <c r="F318" s="2">
-        <v>2898</v>
+        <v>2476</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>15</v>
@@ -28846,7 +28846,7 @@
         <v>14</v>
       </c>
       <c r="F319" s="2">
-        <v>4013</v>
+        <v>2682</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>15</v>
@@ -28878,7 +28878,7 @@
         <v>14</v>
       </c>
       <c r="F320" s="2">
-        <v>3574</v>
+        <v>4568</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>15</v>
@@ -28910,7 +28910,7 @@
         <v>14</v>
       </c>
       <c r="F321" s="2">
-        <v>2554</v>
+        <v>2025</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>15</v>
@@ -28942,7 +28942,7 @@
         <v>14</v>
       </c>
       <c r="F322" s="2">
-        <v>1822</v>
+        <v>2503</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>15</v>
@@ -28974,7 +28974,7 @@
         <v>14</v>
       </c>
       <c r="F323" s="2">
-        <v>4074</v>
+        <v>3863</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>15</v>
@@ -29006,7 +29006,7 @@
         <v>14</v>
       </c>
       <c r="F324" s="2">
-        <v>1552</v>
+        <v>1455</v>
       </c>
       <c r="G324" s="2" t="s">
         <v>15</v>
@@ -29038,7 +29038,7 @@
         <v>14</v>
       </c>
       <c r="F325" s="2">
-        <v>3428</v>
+        <v>2662</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>15</v>
@@ -29070,7 +29070,7 @@
         <v>14</v>
       </c>
       <c r="F326" s="2">
-        <v>1237</v>
+        <v>1979</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>15</v>
@@ -29102,7 +29102,7 @@
         <v>14</v>
       </c>
       <c r="F327" s="2">
-        <v>3059</v>
+        <v>3249</v>
       </c>
       <c r="G327" s="2" t="s">
         <v>15</v>
@@ -29134,7 +29134,7 @@
         <v>14</v>
       </c>
       <c r="F328" s="2">
-        <v>3729</v>
+        <v>2585</v>
       </c>
       <c r="G328" s="2" t="s">
         <v>15</v>
@@ -29166,7 +29166,7 @@
         <v>14</v>
       </c>
       <c r="F329" s="2">
-        <v>3912</v>
+        <v>1308</v>
       </c>
       <c r="G329" s="2" t="s">
         <v>15</v>
@@ -29198,7 +29198,7 @@
         <v>14</v>
       </c>
       <c r="F330" s="2">
-        <v>1300</v>
+        <v>3080</v>
       </c>
       <c r="G330" s="2" t="s">
         <v>15</v>
@@ -29230,7 +29230,7 @@
         <v>14</v>
       </c>
       <c r="F331" s="2">
-        <v>2878</v>
+        <v>3404</v>
       </c>
       <c r="G331" s="2" t="s">
         <v>15</v>
@@ -29262,7 +29262,7 @@
         <v>14</v>
       </c>
       <c r="F332" s="2">
-        <v>3884</v>
+        <v>2777</v>
       </c>
       <c r="G332" s="2" t="s">
         <v>15</v>
@@ -29294,7 +29294,7 @@
         <v>14</v>
       </c>
       <c r="F333" s="2">
-        <v>1132</v>
+        <v>1403</v>
       </c>
       <c r="G333" s="2" t="s">
         <v>15</v>
@@ -29326,7 +29326,7 @@
         <v>14</v>
       </c>
       <c r="F334" s="2">
-        <v>2626</v>
+        <v>3608</v>
       </c>
       <c r="G334" s="2" t="s">
         <v>15</v>
@@ -29358,7 +29358,7 @@
         <v>14</v>
       </c>
       <c r="F335" s="2">
-        <v>2114</v>
+        <v>3822</v>
       </c>
       <c r="G335" s="2" t="s">
         <v>15</v>
@@ -29390,7 +29390,7 @@
         <v>14</v>
       </c>
       <c r="F336" s="2">
-        <v>1031</v>
+        <v>2987</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>15</v>
@@ -29422,7 +29422,7 @@
         <v>14</v>
       </c>
       <c r="F337" s="2">
-        <v>3577</v>
+        <v>3325</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>15</v>
@@ -29454,7 +29454,7 @@
         <v>14</v>
       </c>
       <c r="F338" s="2">
-        <v>1912</v>
+        <v>3894</v>
       </c>
       <c r="G338" s="2" t="s">
         <v>15</v>
@@ -29486,7 +29486,7 @@
         <v>14</v>
       </c>
       <c r="F339" s="2">
-        <v>1857</v>
+        <v>1303</v>
       </c>
       <c r="G339" s="2" t="s">
         <v>15</v>
@@ -29518,7 +29518,7 @@
         <v>14</v>
       </c>
       <c r="F340" s="2">
-        <v>3878</v>
+        <v>3277</v>
       </c>
       <c r="G340" s="2" t="s">
         <v>15</v>
@@ -29550,7 +29550,7 @@
         <v>14</v>
       </c>
       <c r="F341" s="2">
-        <v>4734</v>
+        <v>3713</v>
       </c>
       <c r="G341" s="2" t="s">
         <v>15</v>
@@ -29582,7 +29582,7 @@
         <v>14</v>
       </c>
       <c r="F342" s="2">
-        <v>1033</v>
+        <v>1455</v>
       </c>
       <c r="G342" s="2" t="s">
         <v>15</v>
@@ -29614,7 +29614,7 @@
         <v>14</v>
       </c>
       <c r="F343" s="2">
-        <v>2572</v>
+        <v>4625</v>
       </c>
       <c r="G343" s="2" t="s">
         <v>15</v>
@@ -29646,7 +29646,7 @@
         <v>14</v>
       </c>
       <c r="F344" s="2">
-        <v>4519</v>
+        <v>3979</v>
       </c>
       <c r="G344" s="2" t="s">
         <v>15</v>
@@ -29678,7 +29678,7 @@
         <v>14</v>
       </c>
       <c r="F345" s="2">
-        <v>1204</v>
+        <v>843</v>
       </c>
       <c r="G345" s="2" t="s">
         <v>15</v>
@@ -29710,7 +29710,7 @@
         <v>14</v>
       </c>
       <c r="F346" s="2">
-        <v>949</v>
+        <v>2908</v>
       </c>
       <c r="G346" s="2" t="s">
         <v>15</v>
@@ -29742,7 +29742,7 @@
         <v>14</v>
       </c>
       <c r="F347" s="2">
-        <v>3776</v>
+        <v>4068</v>
       </c>
       <c r="G347" s="2" t="s">
         <v>15</v>
@@ -29774,7 +29774,7 @@
         <v>14</v>
       </c>
       <c r="F348" s="2">
-        <v>4790</v>
+        <v>919</v>
       </c>
       <c r="G348" s="2" t="s">
         <v>15</v>
@@ -29806,7 +29806,7 @@
         <v>14</v>
       </c>
       <c r="F349" s="2">
-        <v>4481</v>
+        <v>3815</v>
       </c>
       <c r="G349" s="2" t="s">
         <v>15</v>
@@ -29838,7 +29838,7 @@
         <v>14</v>
       </c>
       <c r="F350" s="2">
-        <v>2035</v>
+        <v>4139</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>15</v>
@@ -29870,7 +29870,7 @@
         <v>14</v>
       </c>
       <c r="F351" s="2">
-        <v>3276</v>
+        <v>2892</v>
       </c>
       <c r="G351" s="2" t="s">
         <v>15</v>
@@ -29902,7 +29902,7 @@
         <v>14</v>
       </c>
       <c r="F352" s="2">
-        <v>1925</v>
+        <v>4710</v>
       </c>
       <c r="G352" s="2" t="s">
         <v>15</v>
@@ -29934,7 +29934,7 @@
         <v>14</v>
       </c>
       <c r="F353" s="2">
-        <v>2434</v>
+        <v>3492</v>
       </c>
       <c r="G353" s="2" t="s">
         <v>15</v>
@@ -29966,7 +29966,7 @@
         <v>14</v>
       </c>
       <c r="F354" s="2">
-        <v>1577</v>
+        <v>4176</v>
       </c>
       <c r="G354" s="2" t="s">
         <v>15</v>
@@ -29998,7 +29998,7 @@
         <v>14</v>
       </c>
       <c r="F355" s="2">
-        <v>2803</v>
+        <v>1360</v>
       </c>
       <c r="G355" s="2" t="s">
         <v>15</v>
@@ -30030,7 +30030,7 @@
         <v>14</v>
       </c>
       <c r="F356" s="2">
-        <v>3019</v>
+        <v>910</v>
       </c>
       <c r="G356" s="2" t="s">
         <v>15</v>
@@ -30062,7 +30062,7 @@
         <v>14</v>
       </c>
       <c r="F357" s="2">
-        <v>1791</v>
+        <v>1577</v>
       </c>
       <c r="G357" s="2" t="s">
         <v>15</v>
@@ -30094,7 +30094,7 @@
         <v>14</v>
       </c>
       <c r="F358" s="2">
-        <v>3160</v>
+        <v>3856</v>
       </c>
       <c r="G358" s="2" t="s">
         <v>15</v>
@@ -30126,7 +30126,7 @@
         <v>14</v>
       </c>
       <c r="F359" s="2">
-        <v>1158</v>
+        <v>1140</v>
       </c>
       <c r="G359" s="2" t="s">
         <v>15</v>
@@ -30158,7 +30158,7 @@
         <v>14</v>
       </c>
       <c r="F360" s="2">
-        <v>4266</v>
+        <v>3564</v>
       </c>
       <c r="G360" s="2" t="s">
         <v>15</v>
@@ -30190,7 +30190,7 @@
         <v>14</v>
       </c>
       <c r="F361" s="2">
-        <v>1078</v>
+        <v>4477</v>
       </c>
       <c r="G361" s="2" t="s">
         <v>15</v>
@@ -30222,7 +30222,7 @@
         <v>14</v>
       </c>
       <c r="F362" s="2">
-        <v>4561</v>
+        <v>1274</v>
       </c>
       <c r="G362" s="2" t="s">
         <v>15</v>
@@ -30254,7 +30254,7 @@
         <v>14</v>
       </c>
       <c r="F363" s="2">
-        <v>3240</v>
+        <v>829</v>
       </c>
       <c r="G363" s="2" t="s">
         <v>15</v>
@@ -30286,7 +30286,7 @@
         <v>14</v>
       </c>
       <c r="F364" s="2">
-        <v>916</v>
+        <v>2026</v>
       </c>
       <c r="G364" s="2" t="s">
         <v>15</v>
@@ -30318,7 +30318,7 @@
         <v>14</v>
       </c>
       <c r="F365" s="2">
-        <v>2950</v>
+        <v>3247</v>
       </c>
       <c r="G365" s="2" t="s">
         <v>15</v>
@@ -30350,7 +30350,7 @@
         <v>14</v>
       </c>
       <c r="F366" s="2">
-        <v>3953</v>
+        <v>4319</v>
       </c>
       <c r="G366" s="2" t="s">
         <v>15</v>
@@ -30382,7 +30382,7 @@
         <v>14</v>
       </c>
       <c r="F367" s="2">
-        <v>1130</v>
+        <v>2218</v>
       </c>
       <c r="G367" s="2" t="s">
         <v>15</v>
@@ -30414,7 +30414,7 @@
         <v>14</v>
       </c>
       <c r="F368" s="2">
-        <v>1933</v>
+        <v>4492</v>
       </c>
       <c r="G368" s="2" t="s">
         <v>15</v>
@@ -30446,7 +30446,7 @@
         <v>14</v>
       </c>
       <c r="F369" s="2">
-        <v>4226</v>
+        <v>4099</v>
       </c>
       <c r="G369" s="2" t="s">
         <v>15</v>
@@ -30478,7 +30478,7 @@
         <v>14</v>
       </c>
       <c r="F370" s="2">
-        <v>1527</v>
+        <v>1955</v>
       </c>
       <c r="G370" s="2" t="s">
         <v>15</v>
@@ -30510,7 +30510,7 @@
         <v>14</v>
       </c>
       <c r="F371" s="2">
-        <v>3905</v>
+        <v>2638</v>
       </c>
       <c r="G371" s="2" t="s">
         <v>15</v>
@@ -30542,7 +30542,7 @@
         <v>14</v>
       </c>
       <c r="F372" s="2">
-        <v>2707</v>
+        <v>3835</v>
       </c>
       <c r="G372" s="2" t="s">
         <v>15</v>
@@ -30574,7 +30574,7 @@
         <v>14</v>
       </c>
       <c r="F373" s="2">
-        <v>1148</v>
+        <v>1074</v>
       </c>
       <c r="G373" s="2" t="s">
         <v>15</v>
@@ -30606,7 +30606,7 @@
         <v>14</v>
       </c>
       <c r="F374" s="2">
-        <v>4668</v>
+        <v>2251</v>
       </c>
       <c r="G374" s="2" t="s">
         <v>15</v>
@@ -30638,7 +30638,7 @@
         <v>14</v>
       </c>
       <c r="F375" s="2">
-        <v>2035</v>
+        <v>4569</v>
       </c>
       <c r="G375" s="2" t="s">
         <v>15</v>
@@ -30670,7 +30670,7 @@
         <v>14</v>
       </c>
       <c r="F376" s="2">
-        <v>2211</v>
+        <v>1462</v>
       </c>
       <c r="G376" s="2" t="s">
         <v>15</v>
@@ -30702,7 +30702,7 @@
         <v>14</v>
       </c>
       <c r="F377" s="2">
-        <v>820</v>
+        <v>2823</v>
       </c>
       <c r="G377" s="2" t="s">
         <v>15</v>
@@ -30734,7 +30734,7 @@
         <v>14</v>
       </c>
       <c r="F378" s="2">
-        <v>4217</v>
+        <v>3389</v>
       </c>
       <c r="G378" s="2" t="s">
         <v>15</v>
@@ -30766,7 +30766,7 @@
         <v>14</v>
       </c>
       <c r="F379" s="2">
-        <v>1336</v>
+        <v>4672</v>
       </c>
       <c r="G379" s="2" t="s">
         <v>15</v>
@@ -30798,7 +30798,7 @@
         <v>14</v>
       </c>
       <c r="F380" s="2">
-        <v>1602</v>
+        <v>1070</v>
       </c>
       <c r="G380" s="2" t="s">
         <v>15</v>
@@ -30830,7 +30830,7 @@
         <v>14</v>
       </c>
       <c r="F381" s="2">
-        <v>1575</v>
+        <v>865</v>
       </c>
       <c r="G381" s="2" t="s">
         <v>15</v>
@@ -30862,7 +30862,7 @@
         <v>14</v>
       </c>
       <c r="F382" s="2">
-        <v>4248</v>
+        <v>3504</v>
       </c>
       <c r="G382" s="2" t="s">
         <v>15</v>
@@ -30894,7 +30894,7 @@
         <v>14</v>
       </c>
       <c r="F383" s="2">
-        <v>3630</v>
+        <v>4110</v>
       </c>
       <c r="G383" s="2" t="s">
         <v>15</v>
@@ -30926,7 +30926,7 @@
         <v>14</v>
       </c>
       <c r="F384" s="2">
-        <v>805</v>
+        <v>2087</v>
       </c>
       <c r="G384" s="2" t="s">
         <v>15</v>
@@ -30958,7 +30958,7 @@
         <v>14</v>
       </c>
       <c r="F385" s="2">
-        <v>2828</v>
+        <v>1122</v>
       </c>
       <c r="G385" s="2" t="s">
         <v>15</v>
@@ -30990,7 +30990,7 @@
         <v>14</v>
       </c>
       <c r="F386" s="2">
-        <v>2684</v>
+        <v>3422</v>
       </c>
       <c r="G386" s="2" t="s">
         <v>15</v>
@@ -31022,7 +31022,7 @@
         <v>14</v>
       </c>
       <c r="F387" s="2">
-        <v>3711</v>
+        <v>1251</v>
       </c>
       <c r="G387" s="2" t="s">
         <v>15</v>
@@ -31054,7 +31054,7 @@
         <v>14</v>
       </c>
       <c r="F388" s="2">
-        <v>3359</v>
+        <v>4469</v>
       </c>
       <c r="G388" s="2" t="s">
         <v>15</v>
@@ -31086,7 +31086,7 @@
         <v>14</v>
       </c>
       <c r="F389" s="2">
-        <v>4241</v>
+        <v>2557</v>
       </c>
       <c r="G389" s="2" t="s">
         <v>15</v>
@@ -31118,7 +31118,7 @@
         <v>14</v>
       </c>
       <c r="F390" s="2">
-        <v>1721</v>
+        <v>3940</v>
       </c>
       <c r="G390" s="2" t="s">
         <v>15</v>
@@ -31150,7 +31150,7 @@
         <v>14</v>
       </c>
       <c r="F391" s="2">
-        <v>1652</v>
+        <v>4227</v>
       </c>
       <c r="G391" s="2" t="s">
         <v>15</v>
@@ -31182,7 +31182,7 @@
         <v>14</v>
       </c>
       <c r="F392" s="2">
-        <v>3886</v>
+        <v>855</v>
       </c>
       <c r="G392" s="2" t="s">
         <v>15</v>
@@ -31214,7 +31214,7 @@
         <v>14</v>
       </c>
       <c r="F393" s="2">
-        <v>3144</v>
+        <v>1380</v>
       </c>
       <c r="G393" s="2" t="s">
         <v>15</v>
@@ -31246,7 +31246,7 @@
         <v>14</v>
       </c>
       <c r="F394" s="2">
-        <v>1648</v>
+        <v>939</v>
       </c>
       <c r="G394" s="2" t="s">
         <v>15</v>
@@ -31278,7 +31278,7 @@
         <v>14</v>
       </c>
       <c r="F395" s="2">
-        <v>4796</v>
+        <v>2924</v>
       </c>
       <c r="G395" s="2" t="s">
         <v>15</v>
@@ -31310,7 +31310,7 @@
         <v>14</v>
       </c>
       <c r="F396" s="2">
-        <v>3486</v>
+        <v>3298</v>
       </c>
       <c r="G396" s="2" t="s">
         <v>15</v>
@@ -31342,7 +31342,7 @@
         <v>14</v>
       </c>
       <c r="F397" s="2">
-        <v>4435</v>
+        <v>3232</v>
       </c>
       <c r="G397" s="2" t="s">
         <v>15</v>
@@ -31374,7 +31374,7 @@
         <v>14</v>
       </c>
       <c r="F398" s="2">
-        <v>2397</v>
+        <v>2202</v>
       </c>
       <c r="G398" s="2" t="s">
         <v>15</v>
@@ -31406,7 +31406,7 @@
         <v>14</v>
       </c>
       <c r="F399" s="2">
-        <v>1939</v>
+        <v>2197</v>
       </c>
       <c r="G399" s="2" t="s">
         <v>15</v>
@@ -31438,7 +31438,7 @@
         <v>14</v>
       </c>
       <c r="F400" s="2">
-        <v>4568</v>
+        <v>4337</v>
       </c>
       <c r="G400" s="2" t="s">
         <v>15</v>
@@ -31470,7 +31470,7 @@
         <v>14</v>
       </c>
       <c r="F401" s="2">
-        <v>4609</v>
+        <v>3755</v>
       </c>
       <c r="G401" s="2" t="s">
         <v>15</v>
@@ -31502,7 +31502,7 @@
         <v>14</v>
       </c>
       <c r="F402" s="2">
-        <v>4618</v>
+        <v>3172</v>
       </c>
       <c r="G402" s="2" t="s">
         <v>15</v>
@@ -31534,7 +31534,7 @@
         <v>14</v>
       </c>
       <c r="F403" s="2">
-        <v>3622</v>
+        <v>2887</v>
       </c>
       <c r="G403" s="2" t="s">
         <v>15</v>
@@ -31566,7 +31566,7 @@
         <v>14</v>
       </c>
       <c r="F404" s="2">
-        <v>2977</v>
+        <v>4081</v>
       </c>
       <c r="G404" s="2" t="s">
         <v>15</v>
@@ -31598,7 +31598,7 @@
         <v>14</v>
       </c>
       <c r="F405" s="2">
-        <v>2658</v>
+        <v>4367</v>
       </c>
       <c r="G405" s="2" t="s">
         <v>15</v>
@@ -31630,7 +31630,7 @@
         <v>14</v>
       </c>
       <c r="F406" s="2">
-        <v>2247</v>
+        <v>2635</v>
       </c>
       <c r="G406" s="2" t="s">
         <v>15</v>
@@ -31662,7 +31662,7 @@
         <v>14</v>
       </c>
       <c r="F407" s="2">
-        <v>3725</v>
+        <v>3014</v>
       </c>
       <c r="G407" s="2" t="s">
         <v>15</v>
@@ -31694,7 +31694,7 @@
         <v>14</v>
       </c>
       <c r="F408" s="2">
-        <v>4060</v>
+        <v>2977</v>
       </c>
       <c r="G408" s="2" t="s">
         <v>15</v>
@@ -31726,7 +31726,7 @@
         <v>14</v>
       </c>
       <c r="F409" s="2">
-        <v>1351</v>
+        <v>1687</v>
       </c>
       <c r="G409" s="2" t="s">
         <v>15</v>
@@ -31758,7 +31758,7 @@
         <v>14</v>
       </c>
       <c r="F410" s="2">
-        <v>3136</v>
+        <v>1750</v>
       </c>
       <c r="G410" s="2" t="s">
         <v>15</v>
@@ -31790,7 +31790,7 @@
         <v>14</v>
       </c>
       <c r="F411" s="2">
-        <v>3957</v>
+        <v>4506</v>
       </c>
       <c r="G411" s="2" t="s">
         <v>15</v>
@@ -31822,7 +31822,7 @@
         <v>14</v>
       </c>
       <c r="F412" s="2">
-        <v>1766</v>
+        <v>3570</v>
       </c>
       <c r="G412" s="2" t="s">
         <v>15</v>
@@ -31854,7 +31854,7 @@
         <v>14</v>
       </c>
       <c r="F413" s="2">
-        <v>3467</v>
+        <v>4378</v>
       </c>
       <c r="G413" s="2" t="s">
         <v>15</v>
@@ -31886,7 +31886,7 @@
         <v>14</v>
       </c>
       <c r="F414" s="2">
-        <v>2209</v>
+        <v>2477</v>
       </c>
       <c r="G414" s="2" t="s">
         <v>15</v>
@@ -31918,7 +31918,7 @@
         <v>14</v>
       </c>
       <c r="F415" s="2">
-        <v>3576</v>
+        <v>1152</v>
       </c>
       <c r="G415" s="2" t="s">
         <v>15</v>
@@ -31950,7 +31950,7 @@
         <v>14</v>
       </c>
       <c r="F416" s="2">
-        <v>1586</v>
+        <v>1567</v>
       </c>
       <c r="G416" s="2" t="s">
         <v>15</v>
@@ -31982,7 +31982,7 @@
         <v>14</v>
       </c>
       <c r="F417" s="2">
-        <v>4717</v>
+        <v>4474</v>
       </c>
       <c r="G417" s="2" t="s">
         <v>15</v>
@@ -32014,7 +32014,7 @@
         <v>14</v>
       </c>
       <c r="F418" s="2">
-        <v>4756</v>
+        <v>2150</v>
       </c>
       <c r="G418" s="2" t="s">
         <v>15</v>
@@ -32046,7 +32046,7 @@
         <v>14</v>
       </c>
       <c r="F419" s="2">
-        <v>4547</v>
+        <v>1218</v>
       </c>
       <c r="G419" s="2" t="s">
         <v>15</v>
@@ -32078,7 +32078,7 @@
         <v>14</v>
       </c>
       <c r="F420" s="2">
-        <v>4223</v>
+        <v>845</v>
       </c>
       <c r="G420" s="2" t="s">
         <v>15</v>
@@ -32110,7 +32110,7 @@
         <v>14</v>
       </c>
       <c r="F421" s="2">
-        <v>3222</v>
+        <v>4377</v>
       </c>
       <c r="G421" s="2" t="s">
         <v>15</v>
@@ -32142,7 +32142,7 @@
         <v>14</v>
       </c>
       <c r="F422" s="2">
-        <v>2911</v>
+        <v>1393</v>
       </c>
       <c r="G422" s="2" t="s">
         <v>15</v>
@@ -32174,7 +32174,7 @@
         <v>14</v>
       </c>
       <c r="F423" s="2">
-        <v>3390</v>
+        <v>1475</v>
       </c>
       <c r="G423" s="2" t="s">
         <v>15</v>
@@ -32206,7 +32206,7 @@
         <v>14</v>
       </c>
       <c r="F424" s="2">
-        <v>4514</v>
+        <v>848</v>
       </c>
       <c r="G424" s="2" t="s">
         <v>15</v>
@@ -32238,7 +32238,7 @@
         <v>14</v>
       </c>
       <c r="F425" s="2">
-        <v>3770</v>
+        <v>3175</v>
       </c>
       <c r="G425" s="2" t="s">
         <v>15</v>
@@ -32270,7 +32270,7 @@
         <v>14</v>
       </c>
       <c r="F426" s="2">
-        <v>4719</v>
+        <v>2920</v>
       </c>
       <c r="G426" s="2" t="s">
         <v>15</v>
@@ -32302,7 +32302,7 @@
         <v>14</v>
       </c>
       <c r="F427" s="2">
-        <v>1011</v>
+        <v>3412</v>
       </c>
       <c r="G427" s="2" t="s">
         <v>15</v>
@@ -32334,7 +32334,7 @@
         <v>14</v>
       </c>
       <c r="F428" s="2">
-        <v>2536</v>
+        <v>2661</v>
       </c>
       <c r="G428" s="2" t="s">
         <v>15</v>
@@ -32366,7 +32366,7 @@
         <v>14</v>
       </c>
       <c r="F429" s="2">
-        <v>3936</v>
+        <v>2462</v>
       </c>
       <c r="G429" s="2" t="s">
         <v>15</v>
@@ -32398,7 +32398,7 @@
         <v>14</v>
       </c>
       <c r="F430" s="2">
-        <v>1719</v>
+        <v>3593</v>
       </c>
       <c r="G430" s="2" t="s">
         <v>15</v>
@@ -32430,7 +32430,7 @@
         <v>14</v>
       </c>
       <c r="F431" s="2">
-        <v>2272</v>
+        <v>924</v>
       </c>
       <c r="G431" s="2" t="s">
         <v>15</v>
@@ -32462,7 +32462,7 @@
         <v>14</v>
       </c>
       <c r="F432" s="2">
-        <v>1567</v>
+        <v>1477</v>
       </c>
       <c r="G432" s="2" t="s">
         <v>15</v>
@@ -32494,7 +32494,7 @@
         <v>14</v>
       </c>
       <c r="F433" s="2">
-        <v>3917</v>
+        <v>3457</v>
       </c>
       <c r="G433" s="2" t="s">
         <v>15</v>
@@ -32526,7 +32526,7 @@
         <v>14</v>
       </c>
       <c r="F434" s="2">
-        <v>855</v>
+        <v>2603</v>
       </c>
       <c r="G434" s="2" t="s">
         <v>15</v>
@@ -32558,7 +32558,7 @@
         <v>14</v>
       </c>
       <c r="F435" s="2">
-        <v>1548</v>
+        <v>1006</v>
       </c>
       <c r="G435" s="2" t="s">
         <v>15</v>
@@ -32590,7 +32590,7 @@
         <v>14</v>
       </c>
       <c r="F436" s="2">
-        <v>1708</v>
+        <v>1330</v>
       </c>
       <c r="G436" s="2" t="s">
         <v>15</v>
@@ -32622,7 +32622,7 @@
         <v>14</v>
       </c>
       <c r="F437" s="2">
-        <v>3791</v>
+        <v>4319</v>
       </c>
       <c r="G437" s="2" t="s">
         <v>15</v>
@@ -32654,7 +32654,7 @@
         <v>14</v>
       </c>
       <c r="F438" s="2">
-        <v>1162</v>
+        <v>2184</v>
       </c>
       <c r="G438" s="2" t="s">
         <v>15</v>
@@ -32686,7 +32686,7 @@
         <v>14</v>
       </c>
       <c r="F439" s="2">
-        <v>1427</v>
+        <v>2404</v>
       </c>
       <c r="G439" s="2" t="s">
         <v>15</v>
@@ -32718,7 +32718,7 @@
         <v>14</v>
       </c>
       <c r="F440" s="2">
-        <v>4183</v>
+        <v>3674</v>
       </c>
       <c r="G440" s="2" t="s">
         <v>15</v>
@@ -32750,7 +32750,7 @@
         <v>14</v>
       </c>
       <c r="F441" s="2">
-        <v>1958</v>
+        <v>3577</v>
       </c>
       <c r="G441" s="2" t="s">
         <v>15</v>
@@ -32782,7 +32782,7 @@
         <v>14</v>
       </c>
       <c r="F442" s="2">
-        <v>1970</v>
+        <v>895</v>
       </c>
       <c r="G442" s="2" t="s">
         <v>15</v>
@@ -32814,7 +32814,7 @@
         <v>14</v>
       </c>
       <c r="F443" s="2">
-        <v>4057</v>
+        <v>2515</v>
       </c>
       <c r="G443" s="2" t="s">
         <v>15</v>
@@ -32846,7 +32846,7 @@
         <v>14</v>
       </c>
       <c r="F444" s="2">
-        <v>1268</v>
+        <v>2311</v>
       </c>
       <c r="G444" s="2" t="s">
         <v>15</v>
@@ -32878,7 +32878,7 @@
         <v>14</v>
       </c>
       <c r="F445" s="2">
-        <v>1348</v>
+        <v>4437</v>
       </c>
       <c r="G445" s="2" t="s">
         <v>15</v>
@@ -32910,7 +32910,7 @@
         <v>14</v>
       </c>
       <c r="F446" s="2">
-        <v>1294</v>
+        <v>4363</v>
       </c>
       <c r="G446" s="2" t="s">
         <v>15</v>
@@ -32942,7 +32942,7 @@
         <v>14</v>
       </c>
       <c r="F447" s="2">
-        <v>3173</v>
+        <v>4298</v>
       </c>
       <c r="G447" s="2" t="s">
         <v>15</v>
@@ -32974,7 +32974,7 @@
         <v>14</v>
       </c>
       <c r="F448" s="2">
-        <v>2994</v>
+        <v>2439</v>
       </c>
       <c r="G448" s="2" t="s">
         <v>15</v>
@@ -33006,7 +33006,7 @@
         <v>14</v>
       </c>
       <c r="F449" s="2">
-        <v>2110</v>
+        <v>4645</v>
       </c>
       <c r="G449" s="2" t="s">
         <v>15</v>
@@ -33038,7 +33038,7 @@
         <v>14</v>
       </c>
       <c r="F450" s="2">
-        <v>1997</v>
+        <v>1342</v>
       </c>
       <c r="G450" s="2" t="s">
         <v>15</v>
@@ -33070,7 +33070,7 @@
         <v>14</v>
       </c>
       <c r="F451" s="2">
-        <v>3126</v>
+        <v>2672</v>
       </c>
       <c r="G451" s="2" t="s">
         <v>15</v>
@@ -33102,7 +33102,7 @@
         <v>14</v>
       </c>
       <c r="F452" s="2">
-        <v>2191</v>
+        <v>3106</v>
       </c>
       <c r="G452" s="2" t="s">
         <v>15</v>
@@ -33134,7 +33134,7 @@
         <v>14</v>
       </c>
       <c r="F453" s="2">
-        <v>2169</v>
+        <v>3750</v>
       </c>
       <c r="G453" s="2" t="s">
         <v>15</v>
@@ -33166,7 +33166,7 @@
         <v>14</v>
       </c>
       <c r="F454" s="2">
-        <v>4581</v>
+        <v>2423</v>
       </c>
       <c r="G454" s="2" t="s">
         <v>15</v>
@@ -33198,7 +33198,7 @@
         <v>14</v>
       </c>
       <c r="F455" s="2">
-        <v>3311</v>
+        <v>4015</v>
       </c>
       <c r="G455" s="2" t="s">
         <v>15</v>
@@ -33230,7 +33230,7 @@
         <v>14</v>
       </c>
       <c r="F456" s="2">
-        <v>2417</v>
+        <v>1791</v>
       </c>
       <c r="G456" s="2" t="s">
         <v>15</v>
@@ -33262,7 +33262,7 @@
         <v>14</v>
       </c>
       <c r="F457" s="2">
-        <v>3618</v>
+        <v>2347</v>
       </c>
       <c r="G457" s="2" t="s">
         <v>15</v>
@@ -33294,7 +33294,7 @@
         <v>14</v>
       </c>
       <c r="F458" s="2">
-        <v>815</v>
+        <v>4103</v>
       </c>
       <c r="G458" s="2" t="s">
         <v>15</v>
@@ -33326,7 +33326,7 @@
         <v>14</v>
       </c>
       <c r="F459" s="2">
-        <v>3526</v>
+        <v>4287</v>
       </c>
       <c r="G459" s="2" t="s">
         <v>15</v>
@@ -33358,7 +33358,7 @@
         <v>14</v>
       </c>
       <c r="F460" s="2">
-        <v>3579</v>
+        <v>2068</v>
       </c>
       <c r="G460" s="2" t="s">
         <v>15</v>
@@ -33390,7 +33390,7 @@
         <v>14</v>
       </c>
       <c r="F461" s="2">
-        <v>3860</v>
+        <v>2545</v>
       </c>
       <c r="G461" s="2" t="s">
         <v>15</v>
@@ -33422,7 +33422,7 @@
         <v>14</v>
       </c>
       <c r="F462" s="2">
-        <v>3850</v>
+        <v>2739</v>
       </c>
       <c r="G462" s="2" t="s">
         <v>15</v>
@@ -33454,7 +33454,7 @@
         <v>14</v>
       </c>
       <c r="F463" s="2">
-        <v>1277</v>
+        <v>1550</v>
       </c>
       <c r="G463" s="2" t="s">
         <v>15</v>
@@ -33486,7 +33486,7 @@
         <v>14</v>
       </c>
       <c r="F464" s="2">
-        <v>1509</v>
+        <v>4744</v>
       </c>
       <c r="G464" s="2" t="s">
         <v>15</v>
@@ -33518,7 +33518,7 @@
         <v>14</v>
       </c>
       <c r="F465" s="2">
-        <v>4216</v>
+        <v>3105</v>
       </c>
       <c r="G465" s="2" t="s">
         <v>15</v>
@@ -33550,7 +33550,7 @@
         <v>14</v>
       </c>
       <c r="F466" s="2">
-        <v>820</v>
+        <v>2996</v>
       </c>
       <c r="G466" s="2" t="s">
         <v>15</v>
@@ -33582,7 +33582,7 @@
         <v>14</v>
       </c>
       <c r="F467" s="2">
-        <v>3194</v>
+        <v>1446</v>
       </c>
       <c r="G467" s="2" t="s">
         <v>15</v>
@@ -33614,7 +33614,7 @@
         <v>14</v>
       </c>
       <c r="F468" s="2">
-        <v>4725</v>
+        <v>1021</v>
       </c>
       <c r="G468" s="2" t="s">
         <v>15</v>
@@ -33646,7 +33646,7 @@
         <v>14</v>
       </c>
       <c r="F469" s="2">
-        <v>1521</v>
+        <v>2786</v>
       </c>
       <c r="G469" s="2" t="s">
         <v>15</v>
@@ -33678,7 +33678,7 @@
         <v>14</v>
       </c>
       <c r="F470" s="2">
-        <v>2906</v>
+        <v>4230</v>
       </c>
       <c r="G470" s="2" t="s">
         <v>15</v>
@@ -33710,7 +33710,7 @@
         <v>14</v>
       </c>
       <c r="F471" s="2">
-        <v>3588</v>
+        <v>1294</v>
       </c>
       <c r="G471" s="2" t="s">
         <v>15</v>

--- a/reports/selenium/latest/excel/Automation_Test_Report.xlsx
+++ b/reports/selenium/latest/excel/Automation_Test_Report.xlsx
@@ -3084,7 +3084,7 @@
     <t>Build</t>
   </si>
   <si>
-    <t>14</t>
+    <t>15</t>
   </si>
   <si>
     <t>Branch</t>
@@ -3096,13 +3096,13 @@
     <t>Commit</t>
   </si>
   <si>
-    <t>010bbacb5214</t>
+    <t>e1fcafa84b84</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T03:54:59.680Z</t>
+    <t>2026-08-19T04:17:35.966Z</t>
   </si>
   <si>
     <t>Browser</t>
@@ -3607,7 +3607,7 @@
         <v>14</v>
       </c>
       <c r="F2" s="2">
-        <v>1450</v>
+        <v>1474</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>15</v>
@@ -3639,7 +3639,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="2">
-        <v>2489</v>
+        <v>2259</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>15</v>
@@ -3671,7 +3671,7 @@
         <v>14</v>
       </c>
       <c r="F4" s="2">
-        <v>2638</v>
+        <v>4215</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
@@ -3703,7 +3703,7 @@
         <v>14</v>
       </c>
       <c r="F5" s="2">
-        <v>974</v>
+        <v>3600</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
@@ -3735,7 +3735,7 @@
         <v>14</v>
       </c>
       <c r="F6" s="2">
-        <v>4614</v>
+        <v>4681</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -3767,7 +3767,7 @@
         <v>14</v>
       </c>
       <c r="F7" s="2">
-        <v>2741</v>
+        <v>3419</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -3799,7 +3799,7 @@
         <v>14</v>
       </c>
       <c r="F8" s="2">
-        <v>3827</v>
+        <v>863</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -3831,7 +3831,7 @@
         <v>14</v>
       </c>
       <c r="F9" s="2">
-        <v>2828</v>
+        <v>3411</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -3863,7 +3863,7 @@
         <v>14</v>
       </c>
       <c r="F10" s="2">
-        <v>3647</v>
+        <v>3621</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
@@ -3895,7 +3895,7 @@
         <v>14</v>
       </c>
       <c r="F11" s="2">
-        <v>1609</v>
+        <v>4487</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
@@ -3927,7 +3927,7 @@
         <v>14</v>
       </c>
       <c r="F12" s="2">
-        <v>4028</v>
+        <v>3551</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
@@ -3959,7 +3959,7 @@
         <v>14</v>
       </c>
       <c r="F13" s="2">
-        <v>2234</v>
+        <v>2387</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -3991,7 +3991,7 @@
         <v>14</v>
       </c>
       <c r="F14" s="2">
-        <v>2257</v>
+        <v>2144</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -4023,7 +4023,7 @@
         <v>14</v>
       </c>
       <c r="F15" s="2">
-        <v>4552</v>
+        <v>1214</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -4055,7 +4055,7 @@
         <v>14</v>
       </c>
       <c r="F16" s="2">
-        <v>4048</v>
+        <v>4216</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
@@ -4087,7 +4087,7 @@
         <v>14</v>
       </c>
       <c r="F17" s="2">
-        <v>1247</v>
+        <v>2084</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
@@ -4119,7 +4119,7 @@
         <v>14</v>
       </c>
       <c r="F18" s="2">
-        <v>1995</v>
+        <v>2587</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
@@ -4151,7 +4151,7 @@
         <v>14</v>
       </c>
       <c r="F19" s="2">
-        <v>858</v>
+        <v>1494</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
@@ -4183,7 +4183,7 @@
         <v>14</v>
       </c>
       <c r="F20" s="2">
-        <v>4489</v>
+        <v>3860</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
@@ -4215,7 +4215,7 @@
         <v>14</v>
       </c>
       <c r="F21" s="2">
-        <v>4276</v>
+        <v>4023</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -4247,7 +4247,7 @@
         <v>14</v>
       </c>
       <c r="F22" s="2">
-        <v>3282</v>
+        <v>2703</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -4279,7 +4279,7 @@
         <v>14</v>
       </c>
       <c r="F23" s="2">
-        <v>4545</v>
+        <v>897</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -4311,7 +4311,7 @@
         <v>14</v>
       </c>
       <c r="F24" s="2">
-        <v>1826</v>
+        <v>2748</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -4343,7 +4343,7 @@
         <v>14</v>
       </c>
       <c r="F25" s="2">
-        <v>4127</v>
+        <v>1589</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -4375,7 +4375,7 @@
         <v>14</v>
       </c>
       <c r="F26" s="2">
-        <v>1717</v>
+        <v>1491</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -4407,7 +4407,7 @@
         <v>14</v>
       </c>
       <c r="F27" s="2">
-        <v>3328</v>
+        <v>2033</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>15</v>
@@ -4439,7 +4439,7 @@
         <v>14</v>
       </c>
       <c r="F28" s="2">
-        <v>3302</v>
+        <v>3660</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>15</v>
@@ -4471,7 +4471,7 @@
         <v>14</v>
       </c>
       <c r="F29" s="2">
-        <v>3596</v>
+        <v>1751</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>15</v>
@@ -4503,7 +4503,7 @@
         <v>14</v>
       </c>
       <c r="F30" s="2">
-        <v>3771</v>
+        <v>2161</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>15</v>
@@ -4535,7 +4535,7 @@
         <v>14</v>
       </c>
       <c r="F31" s="2">
-        <v>3017</v>
+        <v>3354</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>15</v>
@@ -4567,7 +4567,7 @@
         <v>14</v>
       </c>
       <c r="F32" s="2">
-        <v>2397</v>
+        <v>2854</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>15</v>
@@ -4599,7 +4599,7 @@
         <v>14</v>
       </c>
       <c r="F33" s="2">
-        <v>2673</v>
+        <v>4439</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>15</v>
@@ -4631,7 +4631,7 @@
         <v>14</v>
       </c>
       <c r="F34" s="2">
-        <v>3101</v>
+        <v>4734</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>15</v>
@@ -4663,7 +4663,7 @@
         <v>14</v>
       </c>
       <c r="F35" s="2">
-        <v>2429</v>
+        <v>4057</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>15</v>
@@ -4695,7 +4695,7 @@
         <v>14</v>
       </c>
       <c r="F36" s="2">
-        <v>1150</v>
+        <v>2967</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>15</v>
@@ -4727,7 +4727,7 @@
         <v>14</v>
       </c>
       <c r="F37" s="2">
-        <v>2339</v>
+        <v>4073</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>15</v>
@@ -4759,7 +4759,7 @@
         <v>14</v>
       </c>
       <c r="F38" s="2">
-        <v>2212</v>
+        <v>3806</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>15</v>
@@ -4791,7 +4791,7 @@
         <v>14</v>
       </c>
       <c r="F39" s="2">
-        <v>2768</v>
+        <v>896</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>15</v>
@@ -4823,7 +4823,7 @@
         <v>14</v>
       </c>
       <c r="F40" s="2">
-        <v>3111</v>
+        <v>1022</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>15</v>
@@ -4855,7 +4855,7 @@
         <v>14</v>
       </c>
       <c r="F41" s="2">
-        <v>2828</v>
+        <v>2792</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>15</v>
@@ -4887,7 +4887,7 @@
         <v>14</v>
       </c>
       <c r="F42" s="2">
-        <v>978</v>
+        <v>4497</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>15</v>
@@ -4919,7 +4919,7 @@
         <v>14</v>
       </c>
       <c r="F43" s="2">
-        <v>1172</v>
+        <v>1900</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>15</v>
@@ -4951,7 +4951,7 @@
         <v>14</v>
       </c>
       <c r="F44" s="2">
-        <v>4229</v>
+        <v>2404</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>15</v>
@@ -4983,7 +4983,7 @@
         <v>14</v>
       </c>
       <c r="F45" s="2">
-        <v>987</v>
+        <v>2317</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>15</v>
@@ -5015,7 +5015,7 @@
         <v>14</v>
       </c>
       <c r="F46" s="2">
-        <v>1340</v>
+        <v>4464</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>15</v>
@@ -5047,7 +5047,7 @@
         <v>14</v>
       </c>
       <c r="F47" s="2">
-        <v>3810</v>
+        <v>2309</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>15</v>
@@ -5079,7 +5079,7 @@
         <v>14</v>
       </c>
       <c r="F48" s="2">
-        <v>4754</v>
+        <v>3997</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>15</v>
@@ -5111,7 +5111,7 @@
         <v>14</v>
       </c>
       <c r="F49" s="2">
-        <v>1126</v>
+        <v>2573</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>15</v>
@@ -5143,7 +5143,7 @@
         <v>14</v>
       </c>
       <c r="F50" s="2">
-        <v>855</v>
+        <v>1914</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>15</v>
@@ -5175,7 +5175,7 @@
         <v>14</v>
       </c>
       <c r="F51" s="2">
-        <v>1183</v>
+        <v>1090</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>15</v>
@@ -5207,7 +5207,7 @@
         <v>14</v>
       </c>
       <c r="F52" s="2">
-        <v>4028</v>
+        <v>4412</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>15</v>
@@ -5239,7 +5239,7 @@
         <v>14</v>
       </c>
       <c r="F53" s="2">
-        <v>1862</v>
+        <v>4643</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>15</v>
@@ -5271,7 +5271,7 @@
         <v>14</v>
       </c>
       <c r="F54" s="2">
-        <v>2924</v>
+        <v>2014</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>15</v>
@@ -5303,7 +5303,7 @@
         <v>14</v>
       </c>
       <c r="F55" s="2">
-        <v>1346</v>
+        <v>2043</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>15</v>
@@ -5335,7 +5335,7 @@
         <v>14</v>
       </c>
       <c r="F56" s="2">
-        <v>2612</v>
+        <v>2450</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>15</v>
@@ -5367,7 +5367,7 @@
         <v>14</v>
       </c>
       <c r="F57" s="2">
-        <v>2772</v>
+        <v>4286</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>15</v>
@@ -5399,7 +5399,7 @@
         <v>14</v>
       </c>
       <c r="F58" s="2">
-        <v>3387</v>
+        <v>2741</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>15</v>
@@ -5431,7 +5431,7 @@
         <v>14</v>
       </c>
       <c r="F59" s="2">
-        <v>1418</v>
+        <v>1182</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>15</v>
@@ -5463,7 +5463,7 @@
         <v>14</v>
       </c>
       <c r="F60" s="2">
-        <v>1511</v>
+        <v>4437</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>15</v>
@@ -5495,7 +5495,7 @@
         <v>14</v>
       </c>
       <c r="F61" s="2">
-        <v>3534</v>
+        <v>2523</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>15</v>
@@ -5527,7 +5527,7 @@
         <v>14</v>
       </c>
       <c r="F62" s="2">
-        <v>4205</v>
+        <v>1547</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>15</v>
@@ -5559,7 +5559,7 @@
         <v>14</v>
       </c>
       <c r="F63" s="2">
-        <v>3890</v>
+        <v>3226</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>15</v>
@@ -5591,7 +5591,7 @@
         <v>14</v>
       </c>
       <c r="F64" s="2">
-        <v>4606</v>
+        <v>3877</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>15</v>
@@ -5623,7 +5623,7 @@
         <v>14</v>
       </c>
       <c r="F65" s="2">
-        <v>834</v>
+        <v>3542</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>15</v>
@@ -5655,7 +5655,7 @@
         <v>14</v>
       </c>
       <c r="F66" s="2">
-        <v>4523</v>
+        <v>3702</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>15</v>
@@ -5687,7 +5687,7 @@
         <v>14</v>
       </c>
       <c r="F67" s="2">
-        <v>4005</v>
+        <v>3984</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>15</v>
@@ -5719,7 +5719,7 @@
         <v>14</v>
       </c>
       <c r="F68" s="2">
-        <v>2798</v>
+        <v>1299</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>15</v>
@@ -5751,7 +5751,7 @@
         <v>14</v>
       </c>
       <c r="F69" s="2">
-        <v>1374</v>
+        <v>2664</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>15</v>
@@ -5783,7 +5783,7 @@
         <v>14</v>
       </c>
       <c r="F70" s="2">
-        <v>4360</v>
+        <v>4251</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>15</v>
@@ -5815,7 +5815,7 @@
         <v>14</v>
       </c>
       <c r="F71" s="2">
-        <v>2274</v>
+        <v>1007</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>15</v>
@@ -5847,7 +5847,7 @@
         <v>14</v>
       </c>
       <c r="F72" s="2">
-        <v>4204</v>
+        <v>1547</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>15</v>
@@ -5879,7 +5879,7 @@
         <v>14</v>
       </c>
       <c r="F73" s="2">
-        <v>4243</v>
+        <v>3257</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>15</v>
@@ -5911,7 +5911,7 @@
         <v>14</v>
       </c>
       <c r="F74" s="2">
-        <v>1783</v>
+        <v>1158</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>15</v>
@@ -5943,7 +5943,7 @@
         <v>14</v>
       </c>
       <c r="F75" s="2">
-        <v>3551</v>
+        <v>3775</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>15</v>
@@ -5975,7 +5975,7 @@
         <v>14</v>
       </c>
       <c r="F76" s="2">
-        <v>2555</v>
+        <v>1163</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>15</v>
@@ -6007,7 +6007,7 @@
         <v>14</v>
       </c>
       <c r="F77" s="2">
-        <v>1207</v>
+        <v>1329</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>15</v>
@@ -6039,7 +6039,7 @@
         <v>14</v>
       </c>
       <c r="F78" s="2">
-        <v>959</v>
+        <v>2322</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>15</v>
@@ -6071,7 +6071,7 @@
         <v>14</v>
       </c>
       <c r="F79" s="2">
-        <v>3366</v>
+        <v>1271</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>15</v>
@@ -6103,7 +6103,7 @@
         <v>14</v>
       </c>
       <c r="F80" s="2">
-        <v>1196</v>
+        <v>1139</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>15</v>
@@ -6135,7 +6135,7 @@
         <v>14</v>
       </c>
       <c r="F81" s="2">
-        <v>1730</v>
+        <v>3455</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>15</v>
@@ -6167,7 +6167,7 @@
         <v>14</v>
       </c>
       <c r="F82" s="2">
-        <v>4771</v>
+        <v>1978</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>15</v>
@@ -6199,7 +6199,7 @@
         <v>14</v>
       </c>
       <c r="F83" s="2">
-        <v>1731</v>
+        <v>2270</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>15</v>
@@ -6231,7 +6231,7 @@
         <v>14</v>
       </c>
       <c r="F84" s="2">
-        <v>2551</v>
+        <v>1542</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>15</v>
@@ -6263,7 +6263,7 @@
         <v>14</v>
       </c>
       <c r="F85" s="2">
-        <v>3196</v>
+        <v>2688</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>15</v>
@@ -6295,7 +6295,7 @@
         <v>14</v>
       </c>
       <c r="F86" s="2">
-        <v>4215</v>
+        <v>2614</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>15</v>
@@ -6327,7 +6327,7 @@
         <v>14</v>
       </c>
       <c r="F87" s="2">
-        <v>2949</v>
+        <v>2887</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>15</v>
@@ -6359,7 +6359,7 @@
         <v>14</v>
       </c>
       <c r="F88" s="2">
-        <v>3415</v>
+        <v>2361</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>15</v>
@@ -6391,7 +6391,7 @@
         <v>14</v>
       </c>
       <c r="F89" s="2">
-        <v>3469</v>
+        <v>3180</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>15</v>
@@ -6423,7 +6423,7 @@
         <v>14</v>
       </c>
       <c r="F90" s="2">
-        <v>2636</v>
+        <v>1650</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>15</v>
@@ -6455,7 +6455,7 @@
         <v>14</v>
       </c>
       <c r="F91" s="2">
-        <v>1032</v>
+        <v>4075</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>15</v>
@@ -6487,7 +6487,7 @@
         <v>14</v>
       </c>
       <c r="F92" s="2">
-        <v>3305</v>
+        <v>1788</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>15</v>
@@ -6519,7 +6519,7 @@
         <v>14</v>
       </c>
       <c r="F93" s="2">
-        <v>3102</v>
+        <v>2372</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>15</v>
@@ -6551,7 +6551,7 @@
         <v>14</v>
       </c>
       <c r="F94" s="2">
-        <v>3782</v>
+        <v>1512</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>15</v>
@@ -6583,7 +6583,7 @@
         <v>14</v>
       </c>
       <c r="F95" s="2">
-        <v>1005</v>
+        <v>3619</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>15</v>
@@ -6615,7 +6615,7 @@
         <v>14</v>
       </c>
       <c r="F96" s="2">
-        <v>1868</v>
+        <v>4112</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>15</v>
@@ -6647,7 +6647,7 @@
         <v>14</v>
       </c>
       <c r="F97" s="2">
-        <v>807</v>
+        <v>1505</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>15</v>
@@ -6679,7 +6679,7 @@
         <v>14</v>
       </c>
       <c r="F98" s="2">
-        <v>3176</v>
+        <v>4618</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>15</v>
@@ -6711,7 +6711,7 @@
         <v>14</v>
       </c>
       <c r="F99" s="2">
-        <v>4455</v>
+        <v>1532</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>15</v>
@@ -6743,7 +6743,7 @@
         <v>14</v>
       </c>
       <c r="F100" s="2">
-        <v>2360</v>
+        <v>4411</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>15</v>
@@ -6775,7 +6775,7 @@
         <v>14</v>
       </c>
       <c r="F101" s="2">
-        <v>1753</v>
+        <v>3175</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>15</v>
@@ -6807,7 +6807,7 @@
         <v>14</v>
       </c>
       <c r="F102" s="2">
-        <v>2048</v>
+        <v>2306</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>15</v>
@@ -6839,7 +6839,7 @@
         <v>14</v>
       </c>
       <c r="F103" s="2">
-        <v>3195</v>
+        <v>2129</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>15</v>
@@ -6871,7 +6871,7 @@
         <v>14</v>
       </c>
       <c r="F104" s="2">
-        <v>2122</v>
+        <v>1448</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>15</v>
@@ -6903,7 +6903,7 @@
         <v>14</v>
       </c>
       <c r="F105" s="2">
-        <v>3135</v>
+        <v>2318</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>15</v>
@@ -6935,7 +6935,7 @@
         <v>14</v>
       </c>
       <c r="F106" s="2">
-        <v>4611</v>
+        <v>1636</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>15</v>
@@ -6967,7 +6967,7 @@
         <v>14</v>
       </c>
       <c r="F107" s="2">
-        <v>3789</v>
+        <v>1135</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>15</v>
@@ -6999,7 +6999,7 @@
         <v>14</v>
       </c>
       <c r="F108" s="2">
-        <v>3691</v>
+        <v>3461</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>15</v>
@@ -7031,7 +7031,7 @@
         <v>14</v>
       </c>
       <c r="F109" s="2">
-        <v>2675</v>
+        <v>3510</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>15</v>
@@ -7063,7 +7063,7 @@
         <v>14</v>
       </c>
       <c r="F110" s="2">
-        <v>3107</v>
+        <v>4683</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>15</v>
@@ -7095,7 +7095,7 @@
         <v>14</v>
       </c>
       <c r="F111" s="2">
-        <v>2158</v>
+        <v>3673</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>15</v>
@@ -7127,7 +7127,7 @@
         <v>14</v>
       </c>
       <c r="F112" s="2">
-        <v>1994</v>
+        <v>1017</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>15</v>
@@ -7159,7 +7159,7 @@
         <v>14</v>
       </c>
       <c r="F113" s="2">
-        <v>3106</v>
+        <v>3163</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>15</v>
@@ -7191,7 +7191,7 @@
         <v>14</v>
       </c>
       <c r="F114" s="2">
-        <v>1578</v>
+        <v>1798</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>15</v>
@@ -7223,7 +7223,7 @@
         <v>14</v>
       </c>
       <c r="F115" s="2">
-        <v>2858</v>
+        <v>3557</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>15</v>
@@ -7255,7 +7255,7 @@
         <v>14</v>
       </c>
       <c r="F116" s="2">
-        <v>2058</v>
+        <v>4404</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>15</v>
@@ -7287,7 +7287,7 @@
         <v>14</v>
       </c>
       <c r="F117" s="2">
-        <v>1006</v>
+        <v>2076</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>15</v>
@@ -7319,7 +7319,7 @@
         <v>14</v>
       </c>
       <c r="F118" s="2">
-        <v>2884</v>
+        <v>2711</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>15</v>
@@ -7351,7 +7351,7 @@
         <v>14</v>
       </c>
       <c r="F119" s="2">
-        <v>2051</v>
+        <v>3505</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>15</v>
@@ -7383,7 +7383,7 @@
         <v>14</v>
       </c>
       <c r="F120" s="2">
-        <v>948</v>
+        <v>3867</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>15</v>
@@ -7415,7 +7415,7 @@
         <v>14</v>
       </c>
       <c r="F121" s="2">
-        <v>2225</v>
+        <v>4748</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>15</v>
@@ -7447,7 +7447,7 @@
         <v>14</v>
       </c>
       <c r="F122" s="2">
-        <v>844</v>
+        <v>2823</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>15</v>
@@ -7479,7 +7479,7 @@
         <v>14</v>
       </c>
       <c r="F123" s="2">
-        <v>2023</v>
+        <v>1453</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>15</v>
@@ -7511,7 +7511,7 @@
         <v>14</v>
       </c>
       <c r="F124" s="2">
-        <v>1520</v>
+        <v>1686</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>15</v>
@@ -7543,7 +7543,7 @@
         <v>14</v>
       </c>
       <c r="F125" s="2">
-        <v>3380</v>
+        <v>1000</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>15</v>
@@ -7575,7 +7575,7 @@
         <v>14</v>
       </c>
       <c r="F126" s="2">
-        <v>2494</v>
+        <v>1580</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>15</v>
@@ -7607,7 +7607,7 @@
         <v>14</v>
       </c>
       <c r="F127" s="2">
-        <v>4678</v>
+        <v>3742</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>15</v>
@@ -7639,7 +7639,7 @@
         <v>14</v>
       </c>
       <c r="F128" s="2">
-        <v>1316</v>
+        <v>1832</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>15</v>
@@ -7671,7 +7671,7 @@
         <v>14</v>
       </c>
       <c r="F129" s="2">
-        <v>2231</v>
+        <v>4372</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>15</v>
@@ -7703,7 +7703,7 @@
         <v>14</v>
       </c>
       <c r="F130" s="2">
-        <v>2890</v>
+        <v>3409</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>15</v>
@@ -7735,7 +7735,7 @@
         <v>14</v>
       </c>
       <c r="F131" s="2">
-        <v>4322</v>
+        <v>2927</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>15</v>
@@ -7767,7 +7767,7 @@
         <v>14</v>
       </c>
       <c r="F132" s="2">
-        <v>3108</v>
+        <v>2451</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>15</v>
@@ -7799,7 +7799,7 @@
         <v>14</v>
       </c>
       <c r="F133" s="2">
-        <v>2667</v>
+        <v>3538</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>15</v>
@@ -7831,7 +7831,7 @@
         <v>14</v>
       </c>
       <c r="F134" s="2">
-        <v>1541</v>
+        <v>4445</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>15</v>
@@ -7863,7 +7863,7 @@
         <v>14</v>
       </c>
       <c r="F135" s="2">
-        <v>1368</v>
+        <v>2518</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>15</v>
@@ -7895,7 +7895,7 @@
         <v>14</v>
       </c>
       <c r="F136" s="2">
-        <v>3345</v>
+        <v>3840</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>15</v>
@@ -7927,7 +7927,7 @@
         <v>14</v>
       </c>
       <c r="F137" s="2">
-        <v>1459</v>
+        <v>4032</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>15</v>
@@ -7959,7 +7959,7 @@
         <v>14</v>
       </c>
       <c r="F138" s="2">
-        <v>2512</v>
+        <v>2369</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>15</v>
@@ -7991,7 +7991,7 @@
         <v>14</v>
       </c>
       <c r="F139" s="2">
-        <v>2499</v>
+        <v>2181</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>15</v>
@@ -8023,7 +8023,7 @@
         <v>14</v>
       </c>
       <c r="F140" s="2">
-        <v>2413</v>
+        <v>3579</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>15</v>
@@ -8055,7 +8055,7 @@
         <v>14</v>
       </c>
       <c r="F141" s="2">
-        <v>893</v>
+        <v>2002</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>15</v>
@@ -8087,7 +8087,7 @@
         <v>14</v>
       </c>
       <c r="F142" s="2">
-        <v>3241</v>
+        <v>2536</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>15</v>
@@ -8119,7 +8119,7 @@
         <v>14</v>
       </c>
       <c r="F143" s="2">
-        <v>3423</v>
+        <v>2653</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>15</v>
@@ -8151,7 +8151,7 @@
         <v>14</v>
       </c>
       <c r="F144" s="2">
-        <v>1202</v>
+        <v>1107</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>15</v>
@@ -8183,7 +8183,7 @@
         <v>14</v>
       </c>
       <c r="F145" s="2">
-        <v>2502</v>
+        <v>2718</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>15</v>
@@ -8215,7 +8215,7 @@
         <v>14</v>
       </c>
       <c r="F146" s="2">
-        <v>3529</v>
+        <v>2123</v>
       </c>
       <c r="G146" s="2" t="s">
         <v>15</v>
@@ -8247,7 +8247,7 @@
         <v>14</v>
       </c>
       <c r="F147" s="2">
-        <v>1682</v>
+        <v>1238</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>15</v>
@@ -8279,7 +8279,7 @@
         <v>14</v>
       </c>
       <c r="F148" s="2">
-        <v>1079</v>
+        <v>2240</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>15</v>
@@ -8311,7 +8311,7 @@
         <v>14</v>
       </c>
       <c r="F149" s="2">
-        <v>1265</v>
+        <v>1961</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>15</v>
@@ -8343,7 +8343,7 @@
         <v>14</v>
       </c>
       <c r="F150" s="2">
-        <v>3113</v>
+        <v>2635</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>15</v>
@@ -8375,7 +8375,7 @@
         <v>14</v>
       </c>
       <c r="F151" s="2">
-        <v>3027</v>
+        <v>1340</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>15</v>
@@ -8407,7 +8407,7 @@
         <v>14</v>
       </c>
       <c r="F152" s="2">
-        <v>4430</v>
+        <v>4740</v>
       </c>
       <c r="G152" s="2" t="s">
         <v>15</v>
@@ -8439,7 +8439,7 @@
         <v>14</v>
       </c>
       <c r="F153" s="2">
-        <v>4783</v>
+        <v>1203</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>15</v>
@@ -8471,7 +8471,7 @@
         <v>14</v>
       </c>
       <c r="F154" s="2">
-        <v>1328</v>
+        <v>3283</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>15</v>
@@ -8503,7 +8503,7 @@
         <v>14</v>
       </c>
       <c r="F155" s="2">
-        <v>3653</v>
+        <v>1351</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>15</v>
@@ -8535,7 +8535,7 @@
         <v>14</v>
       </c>
       <c r="F156" s="2">
-        <v>2509</v>
+        <v>2094</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>15</v>
@@ -8567,7 +8567,7 @@
         <v>14</v>
       </c>
       <c r="F157" s="2">
-        <v>2023</v>
+        <v>814</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>15</v>
@@ -8599,7 +8599,7 @@
         <v>14</v>
       </c>
       <c r="F158" s="2">
-        <v>4246</v>
+        <v>1258</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>15</v>
@@ -8631,7 +8631,7 @@
         <v>14</v>
       </c>
       <c r="F159" s="2">
-        <v>863</v>
+        <v>1813</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>15</v>
@@ -8663,7 +8663,7 @@
         <v>14</v>
       </c>
       <c r="F160" s="2">
-        <v>3546</v>
+        <v>3314</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>15</v>
@@ -8695,7 +8695,7 @@
         <v>14</v>
       </c>
       <c r="F161" s="2">
-        <v>3575</v>
+        <v>1584</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>15</v>
@@ -8727,7 +8727,7 @@
         <v>14</v>
       </c>
       <c r="F162" s="2">
-        <v>1636</v>
+        <v>2403</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>15</v>
@@ -8759,7 +8759,7 @@
         <v>14</v>
       </c>
       <c r="F163" s="2">
-        <v>3138</v>
+        <v>3469</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>15</v>
@@ -8791,7 +8791,7 @@
         <v>14</v>
       </c>
       <c r="F164" s="2">
-        <v>2762</v>
+        <v>3293</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>15</v>
@@ -8823,7 +8823,7 @@
         <v>14</v>
       </c>
       <c r="F165" s="2">
-        <v>1080</v>
+        <v>4196</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>15</v>
@@ -8855,7 +8855,7 @@
         <v>14</v>
       </c>
       <c r="F166" s="2">
-        <v>1409</v>
+        <v>944</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>15</v>
@@ -8887,7 +8887,7 @@
         <v>14</v>
       </c>
       <c r="F167" s="2">
-        <v>3581</v>
+        <v>1797</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>15</v>
@@ -8919,7 +8919,7 @@
         <v>14</v>
       </c>
       <c r="F168" s="2">
-        <v>1618</v>
+        <v>1492</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>15</v>
@@ -8951,7 +8951,7 @@
         <v>14</v>
       </c>
       <c r="F169" s="2">
-        <v>2454</v>
+        <v>2931</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>15</v>
@@ -8983,7 +8983,7 @@
         <v>14</v>
       </c>
       <c r="F170" s="2">
-        <v>3610</v>
+        <v>2666</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>15</v>
@@ -9015,7 +9015,7 @@
         <v>14</v>
       </c>
       <c r="F171" s="2">
-        <v>4719</v>
+        <v>3924</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>15</v>
@@ -9047,7 +9047,7 @@
         <v>14</v>
       </c>
       <c r="F172" s="2">
-        <v>3452</v>
+        <v>2651</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>15</v>
@@ -9079,7 +9079,7 @@
         <v>14</v>
       </c>
       <c r="F173" s="2">
-        <v>2261</v>
+        <v>2475</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>15</v>
@@ -9111,7 +9111,7 @@
         <v>14</v>
       </c>
       <c r="F174" s="2">
-        <v>846</v>
+        <v>3667</v>
       </c>
       <c r="G174" s="2" t="s">
         <v>15</v>
@@ -9143,7 +9143,7 @@
         <v>14</v>
       </c>
       <c r="F175" s="2">
-        <v>2382</v>
+        <v>3400</v>
       </c>
       <c r="G175" s="2" t="s">
         <v>15</v>
@@ -9175,7 +9175,7 @@
         <v>14</v>
       </c>
       <c r="F176" s="2">
-        <v>1067</v>
+        <v>2643</v>
       </c>
       <c r="G176" s="2" t="s">
         <v>15</v>
@@ -9207,7 +9207,7 @@
         <v>14</v>
       </c>
       <c r="F177" s="2">
-        <v>2191</v>
+        <v>2966</v>
       </c>
       <c r="G177" s="2" t="s">
         <v>15</v>
@@ -9239,7 +9239,7 @@
         <v>14</v>
       </c>
       <c r="F178" s="2">
-        <v>1507</v>
+        <v>1222</v>
       </c>
       <c r="G178" s="2" t="s">
         <v>15</v>
@@ -9271,7 +9271,7 @@
         <v>14</v>
       </c>
       <c r="F179" s="2">
-        <v>3017</v>
+        <v>2317</v>
       </c>
       <c r="G179" s="2" t="s">
         <v>15</v>
@@ -9303,7 +9303,7 @@
         <v>14</v>
       </c>
       <c r="F180" s="2">
-        <v>1674</v>
+        <v>3462</v>
       </c>
       <c r="G180" s="2" t="s">
         <v>15</v>
@@ -9335,7 +9335,7 @@
         <v>14</v>
       </c>
       <c r="F181" s="2">
-        <v>1054</v>
+        <v>2051</v>
       </c>
       <c r="G181" s="2" t="s">
         <v>15</v>
@@ -9367,7 +9367,7 @@
         <v>14</v>
       </c>
       <c r="F182" s="2">
-        <v>2958</v>
+        <v>4224</v>
       </c>
       <c r="G182" s="2" t="s">
         <v>15</v>
@@ -9399,7 +9399,7 @@
         <v>14</v>
       </c>
       <c r="F183" s="2">
-        <v>2664</v>
+        <v>1816</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>15</v>
@@ -9431,7 +9431,7 @@
         <v>14</v>
       </c>
       <c r="F184" s="2">
-        <v>1841</v>
+        <v>3432</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>15</v>
@@ -9463,7 +9463,7 @@
         <v>14</v>
       </c>
       <c r="F185" s="2">
-        <v>3179</v>
+        <v>1972</v>
       </c>
       <c r="G185" s="2" t="s">
         <v>15</v>
@@ -9495,7 +9495,7 @@
         <v>14</v>
       </c>
       <c r="F186" s="2">
-        <v>1278</v>
+        <v>1132</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>15</v>
@@ -9527,7 +9527,7 @@
         <v>14</v>
       </c>
       <c r="F187" s="2">
-        <v>4725</v>
+        <v>4209</v>
       </c>
       <c r="G187" s="2" t="s">
         <v>15</v>
@@ -9559,7 +9559,7 @@
         <v>14</v>
       </c>
       <c r="F188" s="2">
-        <v>4792</v>
+        <v>4785</v>
       </c>
       <c r="G188" s="2" t="s">
         <v>15</v>
@@ -9591,7 +9591,7 @@
         <v>14</v>
       </c>
       <c r="F189" s="2">
-        <v>4407</v>
+        <v>2977</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>15</v>
@@ -9623,7 +9623,7 @@
         <v>14</v>
       </c>
       <c r="F190" s="2">
-        <v>2605</v>
+        <v>1136</v>
       </c>
       <c r="G190" s="2" t="s">
         <v>15</v>
@@ -9655,7 +9655,7 @@
         <v>14</v>
       </c>
       <c r="F191" s="2">
-        <v>3903</v>
+        <v>2615</v>
       </c>
       <c r="G191" s="2" t="s">
         <v>15</v>
@@ -9687,7 +9687,7 @@
         <v>14</v>
       </c>
       <c r="F192" s="2">
-        <v>4345</v>
+        <v>1022</v>
       </c>
       <c r="G192" s="2" t="s">
         <v>15</v>
@@ -9719,7 +9719,7 @@
         <v>14</v>
       </c>
       <c r="F193" s="2">
-        <v>3974</v>
+        <v>3358</v>
       </c>
       <c r="G193" s="2" t="s">
         <v>15</v>
@@ -9751,7 +9751,7 @@
         <v>14</v>
       </c>
       <c r="F194" s="2">
-        <v>4532</v>
+        <v>2445</v>
       </c>
       <c r="G194" s="2" t="s">
         <v>15</v>
@@ -9783,7 +9783,7 @@
         <v>14</v>
       </c>
       <c r="F195" s="2">
-        <v>1673</v>
+        <v>4392</v>
       </c>
       <c r="G195" s="2" t="s">
         <v>15</v>
@@ -9815,7 +9815,7 @@
         <v>14</v>
       </c>
       <c r="F196" s="2">
-        <v>1462</v>
+        <v>4593</v>
       </c>
       <c r="G196" s="2" t="s">
         <v>15</v>
@@ -9847,7 +9847,7 @@
         <v>14</v>
       </c>
       <c r="F197" s="2">
-        <v>4539</v>
+        <v>2144</v>
       </c>
       <c r="G197" s="2" t="s">
         <v>15</v>
@@ -9879,7 +9879,7 @@
         <v>14</v>
       </c>
       <c r="F198" s="2">
-        <v>1081</v>
+        <v>2268</v>
       </c>
       <c r="G198" s="2" t="s">
         <v>15</v>
@@ -9911,7 +9911,7 @@
         <v>14</v>
       </c>
       <c r="F199" s="2">
-        <v>4648</v>
+        <v>4321</v>
       </c>
       <c r="G199" s="2" t="s">
         <v>15</v>
@@ -9943,7 +9943,7 @@
         <v>14</v>
       </c>
       <c r="F200" s="2">
-        <v>3024</v>
+        <v>1197</v>
       </c>
       <c r="G200" s="2" t="s">
         <v>15</v>
@@ -9975,7 +9975,7 @@
         <v>14</v>
       </c>
       <c r="F201" s="2">
-        <v>818</v>
+        <v>975</v>
       </c>
       <c r="G201" s="2" t="s">
         <v>15</v>
@@ -10007,7 +10007,7 @@
         <v>14</v>
       </c>
       <c r="F202" s="2">
-        <v>1848</v>
+        <v>4517</v>
       </c>
       <c r="G202" s="2" t="s">
         <v>15</v>
@@ -10039,7 +10039,7 @@
         <v>14</v>
       </c>
       <c r="F203" s="2">
-        <v>1482</v>
+        <v>2038</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>15</v>
@@ -10071,7 +10071,7 @@
         <v>14</v>
       </c>
       <c r="F204" s="2">
-        <v>1764</v>
+        <v>2756</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>15</v>
@@ -10135,7 +10135,7 @@
         <v>14</v>
       </c>
       <c r="F206" s="2">
-        <v>1839</v>
+        <v>1704</v>
       </c>
       <c r="G206" s="2" t="s">
         <v>15</v>
@@ -10167,7 +10167,7 @@
         <v>14</v>
       </c>
       <c r="F207" s="2">
-        <v>4118</v>
+        <v>2133</v>
       </c>
       <c r="G207" s="2" t="s">
         <v>15</v>
@@ -10199,7 +10199,7 @@
         <v>14</v>
       </c>
       <c r="F208" s="2">
-        <v>4104</v>
+        <v>3983</v>
       </c>
       <c r="G208" s="2" t="s">
         <v>15</v>
@@ -10231,7 +10231,7 @@
         <v>14</v>
       </c>
       <c r="F209" s="2">
-        <v>1476</v>
+        <v>3370</v>
       </c>
       <c r="G209" s="2" t="s">
         <v>15</v>
@@ -10263,7 +10263,7 @@
         <v>14</v>
       </c>
       <c r="F210" s="2">
-        <v>4749</v>
+        <v>933</v>
       </c>
       <c r="G210" s="2" t="s">
         <v>15</v>
@@ -10295,7 +10295,7 @@
         <v>14</v>
       </c>
       <c r="F211" s="2">
-        <v>1958</v>
+        <v>1531</v>
       </c>
       <c r="G211" s="2" t="s">
         <v>15</v>
@@ -10327,7 +10327,7 @@
         <v>14</v>
       </c>
       <c r="F212" s="2">
-        <v>3187</v>
+        <v>1057</v>
       </c>
       <c r="G212" s="2" t="s">
         <v>15</v>
@@ -10359,7 +10359,7 @@
         <v>14</v>
       </c>
       <c r="F213" s="2">
-        <v>3028</v>
+        <v>4423</v>
       </c>
       <c r="G213" s="2" t="s">
         <v>15</v>
@@ -10391,7 +10391,7 @@
         <v>14</v>
       </c>
       <c r="F214" s="2">
-        <v>1288</v>
+        <v>1144</v>
       </c>
       <c r="G214" s="2" t="s">
         <v>15</v>
@@ -10423,7 +10423,7 @@
         <v>14</v>
       </c>
       <c r="F215" s="2">
-        <v>1057</v>
+        <v>1102</v>
       </c>
       <c r="G215" s="2" t="s">
         <v>15</v>
@@ -10455,7 +10455,7 @@
         <v>14</v>
       </c>
       <c r="F216" s="2">
-        <v>964</v>
+        <v>2868</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>15</v>
@@ -10487,7 +10487,7 @@
         <v>14</v>
       </c>
       <c r="F217" s="2">
-        <v>4318</v>
+        <v>1840</v>
       </c>
       <c r="G217" s="2" t="s">
         <v>15</v>
@@ -10519,7 +10519,7 @@
         <v>14</v>
       </c>
       <c r="F218" s="2">
-        <v>3674</v>
+        <v>3010</v>
       </c>
       <c r="G218" s="2" t="s">
         <v>15</v>
@@ -10551,7 +10551,7 @@
         <v>14</v>
       </c>
       <c r="F219" s="2">
-        <v>1994</v>
+        <v>1208</v>
       </c>
       <c r="G219" s="2" t="s">
         <v>15</v>
@@ -10583,7 +10583,7 @@
         <v>14</v>
       </c>
       <c r="F220" s="2">
-        <v>1931</v>
+        <v>4034</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>15</v>
@@ -10615,7 +10615,7 @@
         <v>14</v>
       </c>
       <c r="F221" s="2">
-        <v>2212</v>
+        <v>2400</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>15</v>
@@ -10647,7 +10647,7 @@
         <v>14</v>
       </c>
       <c r="F222" s="2">
-        <v>3780</v>
+        <v>2937</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>15</v>
@@ -10679,7 +10679,7 @@
         <v>14</v>
       </c>
       <c r="F223" s="2">
-        <v>1455</v>
+        <v>2430</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>15</v>
@@ -10711,7 +10711,7 @@
         <v>14</v>
       </c>
       <c r="F224" s="2">
-        <v>2164</v>
+        <v>4234</v>
       </c>
       <c r="G224" s="2" t="s">
         <v>15</v>
@@ -10743,7 +10743,7 @@
         <v>14</v>
       </c>
       <c r="F225" s="2">
-        <v>2408</v>
+        <v>1923</v>
       </c>
       <c r="G225" s="2" t="s">
         <v>15</v>
@@ -10775,7 +10775,7 @@
         <v>14</v>
       </c>
       <c r="F226" s="2">
-        <v>1028</v>
+        <v>3039</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>15</v>
@@ -10807,7 +10807,7 @@
         <v>14</v>
       </c>
       <c r="F227" s="2">
-        <v>3013</v>
+        <v>1060</v>
       </c>
       <c r="G227" s="2" t="s">
         <v>15</v>
@@ -10839,7 +10839,7 @@
         <v>14</v>
       </c>
       <c r="F228" s="2">
-        <v>1034</v>
+        <v>3425</v>
       </c>
       <c r="G228" s="2" t="s">
         <v>15</v>
@@ -10871,7 +10871,7 @@
         <v>14</v>
       </c>
       <c r="F229" s="2">
-        <v>858</v>
+        <v>3193</v>
       </c>
       <c r="G229" s="2" t="s">
         <v>15</v>
@@ -10903,7 +10903,7 @@
         <v>14</v>
       </c>
       <c r="F230" s="2">
-        <v>3952</v>
+        <v>3725</v>
       </c>
       <c r="G230" s="2" t="s">
         <v>15</v>
@@ -10935,7 +10935,7 @@
         <v>14</v>
       </c>
       <c r="F231" s="2">
-        <v>2413</v>
+        <v>4339</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>15</v>
@@ -10967,7 +10967,7 @@
         <v>14</v>
       </c>
       <c r="F232" s="2">
-        <v>3285</v>
+        <v>4740</v>
       </c>
       <c r="G232" s="2" t="s">
         <v>15</v>
@@ -10999,7 +10999,7 @@
         <v>14</v>
       </c>
       <c r="F233" s="2">
-        <v>2752</v>
+        <v>2633</v>
       </c>
       <c r="G233" s="2" t="s">
         <v>15</v>
@@ -11031,7 +11031,7 @@
         <v>14</v>
       </c>
       <c r="F234" s="2">
-        <v>3537</v>
+        <v>2102</v>
       </c>
       <c r="G234" s="2" t="s">
         <v>15</v>
@@ -11063,7 +11063,7 @@
         <v>14</v>
       </c>
       <c r="F235" s="2">
-        <v>1559</v>
+        <v>4369</v>
       </c>
       <c r="G235" s="2" t="s">
         <v>15</v>
@@ -11095,7 +11095,7 @@
         <v>14</v>
       </c>
       <c r="F236" s="2">
-        <v>1644</v>
+        <v>1109</v>
       </c>
       <c r="G236" s="2" t="s">
         <v>15</v>
@@ -11127,7 +11127,7 @@
         <v>14</v>
       </c>
       <c r="F237" s="2">
-        <v>3506</v>
+        <v>1987</v>
       </c>
       <c r="G237" s="2" t="s">
         <v>15</v>
@@ -11159,7 +11159,7 @@
         <v>14</v>
       </c>
       <c r="F238" s="2">
-        <v>1912</v>
+        <v>1886</v>
       </c>
       <c r="G238" s="2" t="s">
         <v>15</v>
@@ -11191,7 +11191,7 @@
         <v>14</v>
       </c>
       <c r="F239" s="2">
-        <v>1052</v>
+        <v>3965</v>
       </c>
       <c r="G239" s="2" t="s">
         <v>15</v>
@@ -11223,7 +11223,7 @@
         <v>14</v>
       </c>
       <c r="F240" s="2">
-        <v>4661</v>
+        <v>4607</v>
       </c>
       <c r="G240" s="2" t="s">
         <v>15</v>
@@ -11255,7 +11255,7 @@
         <v>14</v>
       </c>
       <c r="F241" s="2">
-        <v>1181</v>
+        <v>4171</v>
       </c>
       <c r="G241" s="2" t="s">
         <v>15</v>
@@ -11287,7 +11287,7 @@
         <v>14</v>
       </c>
       <c r="F242" s="2">
-        <v>3486</v>
+        <v>1617</v>
       </c>
       <c r="G242" s="2" t="s">
         <v>15</v>
@@ -11319,7 +11319,7 @@
         <v>14</v>
       </c>
       <c r="F243" s="2">
-        <v>2477</v>
+        <v>2792</v>
       </c>
       <c r="G243" s="2" t="s">
         <v>15</v>
@@ -11351,7 +11351,7 @@
         <v>14</v>
       </c>
       <c r="F244" s="2">
-        <v>1643</v>
+        <v>978</v>
       </c>
       <c r="G244" s="2" t="s">
         <v>15</v>
@@ -11383,7 +11383,7 @@
         <v>14</v>
       </c>
       <c r="F245" s="2">
-        <v>3814</v>
+        <v>3576</v>
       </c>
       <c r="G245" s="2" t="s">
         <v>15</v>
@@ -11415,7 +11415,7 @@
         <v>14</v>
       </c>
       <c r="F246" s="2">
-        <v>1133</v>
+        <v>3953</v>
       </c>
       <c r="G246" s="2" t="s">
         <v>15</v>
@@ -11447,7 +11447,7 @@
         <v>14</v>
       </c>
       <c r="F247" s="2">
-        <v>2339</v>
+        <v>3079</v>
       </c>
       <c r="G247" s="2" t="s">
         <v>15</v>
@@ -11479,7 +11479,7 @@
         <v>14</v>
       </c>
       <c r="F248" s="2">
-        <v>3781</v>
+        <v>3375</v>
       </c>
       <c r="G248" s="2" t="s">
         <v>15</v>
@@ -11511,7 +11511,7 @@
         <v>14</v>
       </c>
       <c r="F249" s="2">
-        <v>2639</v>
+        <v>1128</v>
       </c>
       <c r="G249" s="2" t="s">
         <v>15</v>
@@ -11543,7 +11543,7 @@
         <v>14</v>
       </c>
       <c r="F250" s="2">
-        <v>3944</v>
+        <v>2462</v>
       </c>
       <c r="G250" s="2" t="s">
         <v>15</v>
@@ -11575,7 +11575,7 @@
         <v>14</v>
       </c>
       <c r="F251" s="2">
-        <v>2707</v>
+        <v>1015</v>
       </c>
       <c r="G251" s="2" t="s">
         <v>15</v>
@@ -11607,7 +11607,7 @@
         <v>14</v>
       </c>
       <c r="F252" s="2">
-        <v>1872</v>
+        <v>4616</v>
       </c>
       <c r="G252" s="2" t="s">
         <v>15</v>
@@ -11639,7 +11639,7 @@
         <v>14</v>
       </c>
       <c r="F253" s="2">
-        <v>3722</v>
+        <v>2901</v>
       </c>
       <c r="G253" s="2" t="s">
         <v>15</v>
@@ -11671,7 +11671,7 @@
         <v>14</v>
       </c>
       <c r="F254" s="2">
-        <v>2945</v>
+        <v>4322</v>
       </c>
       <c r="G254" s="2" t="s">
         <v>15</v>
@@ -11703,7 +11703,7 @@
         <v>14</v>
       </c>
       <c r="F255" s="2">
-        <v>2020</v>
+        <v>4273</v>
       </c>
       <c r="G255" s="2" t="s">
         <v>15</v>
@@ -11735,7 +11735,7 @@
         <v>14</v>
       </c>
       <c r="F256" s="2">
-        <v>1683</v>
+        <v>919</v>
       </c>
       <c r="G256" s="2" t="s">
         <v>15</v>
@@ -11767,7 +11767,7 @@
         <v>14</v>
       </c>
       <c r="F257" s="2">
-        <v>1329</v>
+        <v>804</v>
       </c>
       <c r="G257" s="2" t="s">
         <v>15</v>
@@ -11799,7 +11799,7 @@
         <v>14</v>
       </c>
       <c r="F258" s="2">
-        <v>3400</v>
+        <v>3160</v>
       </c>
       <c r="G258" s="2" t="s">
         <v>15</v>
@@ -11831,7 +11831,7 @@
         <v>14</v>
       </c>
       <c r="F259" s="2">
-        <v>4420</v>
+        <v>4237</v>
       </c>
       <c r="G259" s="2" t="s">
         <v>15</v>
@@ -11863,7 +11863,7 @@
         <v>14</v>
       </c>
       <c r="F260" s="2">
-        <v>3904</v>
+        <v>2191</v>
       </c>
       <c r="G260" s="2" t="s">
         <v>15</v>
@@ -11895,7 +11895,7 @@
         <v>14</v>
       </c>
       <c r="F261" s="2">
-        <v>3856</v>
+        <v>1739</v>
       </c>
       <c r="G261" s="2" t="s">
         <v>15</v>
@@ -11927,7 +11927,7 @@
         <v>14</v>
       </c>
       <c r="F262" s="2">
-        <v>4349</v>
+        <v>4758</v>
       </c>
       <c r="G262" s="2" t="s">
         <v>15</v>
@@ -11959,7 +11959,7 @@
         <v>14</v>
       </c>
       <c r="F263" s="2">
-        <v>3901</v>
+        <v>927</v>
       </c>
       <c r="G263" s="2" t="s">
         <v>15</v>
@@ -11991,7 +11991,7 @@
         <v>14</v>
       </c>
       <c r="F264" s="2">
-        <v>3625</v>
+        <v>1431</v>
       </c>
       <c r="G264" s="2" t="s">
         <v>15</v>
@@ -12023,7 +12023,7 @@
         <v>14</v>
       </c>
       <c r="F265" s="2">
-        <v>911</v>
+        <v>826</v>
       </c>
       <c r="G265" s="2" t="s">
         <v>15</v>
@@ -12055,7 +12055,7 @@
         <v>14</v>
       </c>
       <c r="F266" s="2">
-        <v>2349</v>
+        <v>822</v>
       </c>
       <c r="G266" s="2" t="s">
         <v>15</v>
@@ -12087,7 +12087,7 @@
         <v>14</v>
       </c>
       <c r="F267" s="2">
-        <v>828</v>
+        <v>4296</v>
       </c>
       <c r="G267" s="2" t="s">
         <v>15</v>
@@ -12119,7 +12119,7 @@
         <v>14</v>
       </c>
       <c r="F268" s="2">
-        <v>3941</v>
+        <v>2582</v>
       </c>
       <c r="G268" s="2" t="s">
         <v>15</v>
@@ -12151,7 +12151,7 @@
         <v>14</v>
       </c>
       <c r="F269" s="2">
-        <v>3232</v>
+        <v>2330</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>15</v>
@@ -12183,7 +12183,7 @@
         <v>14</v>
       </c>
       <c r="F270" s="2">
-        <v>1042</v>
+        <v>841</v>
       </c>
       <c r="G270" s="2" t="s">
         <v>15</v>
@@ -12215,7 +12215,7 @@
         <v>14</v>
       </c>
       <c r="F271" s="2">
-        <v>1553</v>
+        <v>2716</v>
       </c>
       <c r="G271" s="2" t="s">
         <v>15</v>
@@ -12247,7 +12247,7 @@
         <v>14</v>
       </c>
       <c r="F272" s="2">
-        <v>4474</v>
+        <v>957</v>
       </c>
       <c r="G272" s="2" t="s">
         <v>15</v>
@@ -12279,7 +12279,7 @@
         <v>14</v>
       </c>
       <c r="F273" s="2">
-        <v>923</v>
+        <v>2933</v>
       </c>
       <c r="G273" s="2" t="s">
         <v>15</v>
@@ -12311,7 +12311,7 @@
         <v>14</v>
       </c>
       <c r="F274" s="2">
-        <v>4132</v>
+        <v>3488</v>
       </c>
       <c r="G274" s="2" t="s">
         <v>15</v>
@@ -12343,7 +12343,7 @@
         <v>14</v>
       </c>
       <c r="F275" s="2">
-        <v>1090</v>
+        <v>3097</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>15</v>
@@ -12375,7 +12375,7 @@
         <v>14</v>
       </c>
       <c r="F276" s="2">
-        <v>4000</v>
+        <v>2739</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>15</v>
@@ -12407,7 +12407,7 @@
         <v>14</v>
       </c>
       <c r="F277" s="2">
-        <v>1958</v>
+        <v>4751</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>15</v>
@@ -12439,7 +12439,7 @@
         <v>14</v>
       </c>
       <c r="F278" s="2">
-        <v>2854</v>
+        <v>4024</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>15</v>
@@ -12471,7 +12471,7 @@
         <v>14</v>
       </c>
       <c r="F279" s="2">
-        <v>2261</v>
+        <v>2100</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>15</v>
@@ -12503,7 +12503,7 @@
         <v>14</v>
       </c>
       <c r="F280" s="2">
-        <v>1738</v>
+        <v>2890</v>
       </c>
       <c r="G280" s="2" t="s">
         <v>15</v>
@@ -12535,7 +12535,7 @@
         <v>14</v>
       </c>
       <c r="F281" s="2">
-        <v>3177</v>
+        <v>2401</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>15</v>
@@ -12567,7 +12567,7 @@
         <v>14</v>
       </c>
       <c r="F282" s="2">
-        <v>2583</v>
+        <v>4060</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>15</v>
@@ -12599,7 +12599,7 @@
         <v>14</v>
       </c>
       <c r="F283" s="2">
-        <v>4479</v>
+        <v>3708</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>15</v>
@@ -12631,7 +12631,7 @@
         <v>14</v>
       </c>
       <c r="F284" s="2">
-        <v>1954</v>
+        <v>3251</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>15</v>
@@ -12663,7 +12663,7 @@
         <v>14</v>
       </c>
       <c r="F285" s="2">
-        <v>3387</v>
+        <v>4463</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>15</v>
@@ -12695,7 +12695,7 @@
         <v>14</v>
       </c>
       <c r="F286" s="2">
-        <v>4756</v>
+        <v>4621</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>15</v>
@@ -12727,7 +12727,7 @@
         <v>14</v>
       </c>
       <c r="F287" s="2">
-        <v>1687</v>
+        <v>3086</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>15</v>
@@ -12759,7 +12759,7 @@
         <v>14</v>
       </c>
       <c r="F288" s="2">
-        <v>1739</v>
+        <v>4028</v>
       </c>
       <c r="G288" s="2" t="s">
         <v>15</v>
@@ -12791,7 +12791,7 @@
         <v>14</v>
       </c>
       <c r="F289" s="2">
-        <v>3477</v>
+        <v>1177</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>15</v>
@@ -12823,7 +12823,7 @@
         <v>14</v>
       </c>
       <c r="F290" s="2">
-        <v>840</v>
+        <v>4298</v>
       </c>
       <c r="G290" s="2" t="s">
         <v>15</v>
@@ -12855,7 +12855,7 @@
         <v>14</v>
       </c>
       <c r="F291" s="2">
-        <v>3441</v>
+        <v>1251</v>
       </c>
       <c r="G291" s="2" t="s">
         <v>15</v>
@@ -12887,7 +12887,7 @@
         <v>14</v>
       </c>
       <c r="F292" s="2">
-        <v>4664</v>
+        <v>4263</v>
       </c>
       <c r="G292" s="2" t="s">
         <v>15</v>
@@ -12919,7 +12919,7 @@
         <v>14</v>
       </c>
       <c r="F293" s="2">
-        <v>4124</v>
+        <v>4292</v>
       </c>
       <c r="G293" s="2" t="s">
         <v>15</v>
@@ -12951,7 +12951,7 @@
         <v>14</v>
       </c>
       <c r="F294" s="2">
-        <v>1289</v>
+        <v>1784</v>
       </c>
       <c r="G294" s="2" t="s">
         <v>15</v>
@@ -12983,7 +12983,7 @@
         <v>14</v>
       </c>
       <c r="F295" s="2">
-        <v>3043</v>
+        <v>2427</v>
       </c>
       <c r="G295" s="2" t="s">
         <v>15</v>
@@ -13015,7 +13015,7 @@
         <v>14</v>
       </c>
       <c r="F296" s="2">
-        <v>4441</v>
+        <v>2227</v>
       </c>
       <c r="G296" s="2" t="s">
         <v>15</v>
@@ -13047,7 +13047,7 @@
         <v>14</v>
       </c>
       <c r="F297" s="2">
-        <v>1771</v>
+        <v>3599</v>
       </c>
       <c r="G297" s="2" t="s">
         <v>15</v>
@@ -13079,7 +13079,7 @@
         <v>14</v>
       </c>
       <c r="F298" s="2">
-        <v>4137</v>
+        <v>3154</v>
       </c>
       <c r="G298" s="2" t="s">
         <v>15</v>
@@ -13111,7 +13111,7 @@
         <v>14</v>
       </c>
       <c r="F299" s="2">
-        <v>3594</v>
+        <v>1437</v>
       </c>
       <c r="G299" s="2" t="s">
         <v>15</v>
@@ -13143,7 +13143,7 @@
         <v>14</v>
       </c>
       <c r="F300" s="2">
-        <v>2115</v>
+        <v>2150</v>
       </c>
       <c r="G300" s="2" t="s">
         <v>15</v>
@@ -13175,7 +13175,7 @@
         <v>14</v>
       </c>
       <c r="F301" s="2">
-        <v>2495</v>
+        <v>1423</v>
       </c>
       <c r="G301" s="2" t="s">
         <v>15</v>
@@ -13207,7 +13207,7 @@
         <v>14</v>
       </c>
       <c r="F302" s="2">
-        <v>2165</v>
+        <v>1728</v>
       </c>
       <c r="G302" s="2" t="s">
         <v>15</v>
@@ -13239,7 +13239,7 @@
         <v>14</v>
       </c>
       <c r="F303" s="2">
-        <v>2229</v>
+        <v>3828</v>
       </c>
       <c r="G303" s="2" t="s">
         <v>15</v>
@@ -13271,7 +13271,7 @@
         <v>14</v>
       </c>
       <c r="F304" s="2">
-        <v>4158</v>
+        <v>4453</v>
       </c>
       <c r="G304" s="2" t="s">
         <v>15</v>
@@ -13303,7 +13303,7 @@
         <v>14</v>
       </c>
       <c r="F305" s="2">
-        <v>949</v>
+        <v>2150</v>
       </c>
       <c r="G305" s="2" t="s">
         <v>15</v>
@@ -13335,7 +13335,7 @@
         <v>14</v>
       </c>
       <c r="F306" s="2">
-        <v>3715</v>
+        <v>2421</v>
       </c>
       <c r="G306" s="2" t="s">
         <v>15</v>
@@ -13367,7 +13367,7 @@
         <v>14</v>
       </c>
       <c r="F307" s="2">
-        <v>829</v>
+        <v>2536</v>
       </c>
       <c r="G307" s="2" t="s">
         <v>15</v>
@@ -13399,7 +13399,7 @@
         <v>14</v>
       </c>
       <c r="F308" s="2">
-        <v>3955</v>
+        <v>3369</v>
       </c>
       <c r="G308" s="2" t="s">
         <v>15</v>
@@ -13431,7 +13431,7 @@
         <v>14</v>
       </c>
       <c r="F309" s="2">
-        <v>2882</v>
+        <v>2054</v>
       </c>
       <c r="G309" s="2" t="s">
         <v>15</v>
@@ -13463,7 +13463,7 @@
         <v>14</v>
       </c>
       <c r="F310" s="2">
-        <v>3280</v>
+        <v>1453</v>
       </c>
       <c r="G310" s="2" t="s">
         <v>15</v>
@@ -13495,7 +13495,7 @@
         <v>14</v>
       </c>
       <c r="F311" s="2">
-        <v>3810</v>
+        <v>4335</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>15</v>
@@ -13527,7 +13527,7 @@
         <v>14</v>
       </c>
       <c r="F312" s="2">
-        <v>4414</v>
+        <v>1619</v>
       </c>
       <c r="G312" s="2" t="s">
         <v>15</v>
@@ -13559,7 +13559,7 @@
         <v>14</v>
       </c>
       <c r="F313" s="2">
-        <v>3826</v>
+        <v>4763</v>
       </c>
       <c r="G313" s="2" t="s">
         <v>15</v>
@@ -13591,7 +13591,7 @@
         <v>14</v>
       </c>
       <c r="F314" s="2">
-        <v>3437</v>
+        <v>1616</v>
       </c>
       <c r="G314" s="2" t="s">
         <v>15</v>
@@ -13623,7 +13623,7 @@
         <v>14</v>
       </c>
       <c r="F315" s="2">
-        <v>1931</v>
+        <v>2152</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>15</v>
@@ -13655,7 +13655,7 @@
         <v>14</v>
       </c>
       <c r="F316" s="2">
-        <v>2056</v>
+        <v>3690</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>15</v>
@@ -13687,7 +13687,7 @@
         <v>14</v>
       </c>
       <c r="F317" s="2">
-        <v>3391</v>
+        <v>3352</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>15</v>
@@ -13719,7 +13719,7 @@
         <v>14</v>
       </c>
       <c r="F318" s="2">
-        <v>2476</v>
+        <v>3335</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>15</v>
@@ -13751,7 +13751,7 @@
         <v>14</v>
       </c>
       <c r="F319" s="2">
-        <v>2682</v>
+        <v>1542</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>15</v>
@@ -13783,7 +13783,7 @@
         <v>14</v>
       </c>
       <c r="F320" s="2">
-        <v>4568</v>
+        <v>3315</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>15</v>
@@ -13815,7 +13815,7 @@
         <v>14</v>
       </c>
       <c r="F321" s="2">
-        <v>2025</v>
+        <v>2416</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>15</v>
@@ -13847,7 +13847,7 @@
         <v>14</v>
       </c>
       <c r="F322" s="2">
-        <v>2503</v>
+        <v>1375</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>15</v>
@@ -13879,7 +13879,7 @@
         <v>14</v>
       </c>
       <c r="F323" s="2">
-        <v>3863</v>
+        <v>4729</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>15</v>
@@ -13911,7 +13911,7 @@
         <v>14</v>
       </c>
       <c r="F324" s="2">
-        <v>1455</v>
+        <v>4734</v>
       </c>
       <c r="G324" s="2" t="s">
         <v>15</v>
@@ -13943,7 +13943,7 @@
         <v>14</v>
       </c>
       <c r="F325" s="2">
-        <v>2662</v>
+        <v>2035</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>15</v>
@@ -13975,7 +13975,7 @@
         <v>14</v>
       </c>
       <c r="F326" s="2">
-        <v>1979</v>
+        <v>3742</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>15</v>
@@ -14007,7 +14007,7 @@
         <v>14</v>
       </c>
       <c r="F327" s="2">
-        <v>3249</v>
+        <v>1745</v>
       </c>
       <c r="G327" s="2" t="s">
         <v>15</v>
@@ -14039,7 +14039,7 @@
         <v>14</v>
       </c>
       <c r="F328" s="2">
-        <v>2585</v>
+        <v>800</v>
       </c>
       <c r="G328" s="2" t="s">
         <v>15</v>
@@ -14071,7 +14071,7 @@
         <v>14</v>
       </c>
       <c r="F329" s="2">
-        <v>1308</v>
+        <v>3318</v>
       </c>
       <c r="G329" s="2" t="s">
         <v>15</v>
@@ -14103,7 +14103,7 @@
         <v>14</v>
       </c>
       <c r="F330" s="2">
-        <v>3080</v>
+        <v>3474</v>
       </c>
       <c r="G330" s="2" t="s">
         <v>15</v>
@@ -14135,7 +14135,7 @@
         <v>14</v>
       </c>
       <c r="F331" s="2">
-        <v>3404</v>
+        <v>4340</v>
       </c>
       <c r="G331" s="2" t="s">
         <v>15</v>
@@ -14167,7 +14167,7 @@
         <v>14</v>
       </c>
       <c r="F332" s="2">
-        <v>2777</v>
+        <v>3273</v>
       </c>
       <c r="G332" s="2" t="s">
         <v>15</v>
@@ -14199,7 +14199,7 @@
         <v>14</v>
       </c>
       <c r="F333" s="2">
-        <v>1403</v>
+        <v>3067</v>
       </c>
       <c r="G333" s="2" t="s">
         <v>15</v>
@@ -14231,7 +14231,7 @@
         <v>14</v>
       </c>
       <c r="F334" s="2">
-        <v>3608</v>
+        <v>2701</v>
       </c>
       <c r="G334" s="2" t="s">
         <v>15</v>
@@ -14263,7 +14263,7 @@
         <v>14</v>
       </c>
       <c r="F335" s="2">
-        <v>3822</v>
+        <v>4780</v>
       </c>
       <c r="G335" s="2" t="s">
         <v>15</v>
@@ -14295,7 +14295,7 @@
         <v>14</v>
       </c>
       <c r="F336" s="2">
-        <v>2987</v>
+        <v>816</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>15</v>
@@ -14327,7 +14327,7 @@
         <v>14</v>
       </c>
       <c r="F337" s="2">
-        <v>3325</v>
+        <v>1903</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>15</v>
@@ -14359,7 +14359,7 @@
         <v>14</v>
       </c>
       <c r="F338" s="2">
-        <v>3894</v>
+        <v>3473</v>
       </c>
       <c r="G338" s="2" t="s">
         <v>15</v>
@@ -14391,7 +14391,7 @@
         <v>14</v>
       </c>
       <c r="F339" s="2">
-        <v>1303</v>
+        <v>2179</v>
       </c>
       <c r="G339" s="2" t="s">
         <v>15</v>
@@ -14423,7 +14423,7 @@
         <v>14</v>
       </c>
       <c r="F340" s="2">
-        <v>3277</v>
+        <v>1645</v>
       </c>
       <c r="G340" s="2" t="s">
         <v>15</v>
@@ -14455,7 +14455,7 @@
         <v>14</v>
       </c>
       <c r="F341" s="2">
-        <v>3713</v>
+        <v>1821</v>
       </c>
       <c r="G341" s="2" t="s">
         <v>15</v>
@@ -14487,7 +14487,7 @@
         <v>14</v>
       </c>
       <c r="F342" s="2">
-        <v>1455</v>
+        <v>4539</v>
       </c>
       <c r="G342" s="2" t="s">
         <v>15</v>
@@ -14519,7 +14519,7 @@
         <v>14</v>
       </c>
       <c r="F343" s="2">
-        <v>4625</v>
+        <v>1727</v>
       </c>
       <c r="G343" s="2" t="s">
         <v>15</v>
@@ -14551,7 +14551,7 @@
         <v>14</v>
       </c>
       <c r="F344" s="2">
-        <v>3979</v>
+        <v>1231</v>
       </c>
       <c r="G344" s="2" t="s">
         <v>15</v>
@@ -14583,7 +14583,7 @@
         <v>14</v>
       </c>
       <c r="F345" s="2">
-        <v>843</v>
+        <v>3085</v>
       </c>
       <c r="G345" s="2" t="s">
         <v>15</v>
@@ -14615,7 +14615,7 @@
         <v>14</v>
       </c>
       <c r="F346" s="2">
-        <v>2908</v>
+        <v>2070</v>
       </c>
       <c r="G346" s="2" t="s">
         <v>15</v>
@@ -14647,7 +14647,7 @@
         <v>14</v>
       </c>
       <c r="F347" s="2">
-        <v>4068</v>
+        <v>2552</v>
       </c>
       <c r="G347" s="2" t="s">
         <v>15</v>
@@ -14679,7 +14679,7 @@
         <v>14</v>
       </c>
       <c r="F348" s="2">
-        <v>919</v>
+        <v>1087</v>
       </c>
       <c r="G348" s="2" t="s">
         <v>15</v>
@@ -14711,7 +14711,7 @@
         <v>14</v>
       </c>
       <c r="F349" s="2">
-        <v>3815</v>
+        <v>3983</v>
       </c>
       <c r="G349" s="2" t="s">
         <v>15</v>
@@ -14743,7 +14743,7 @@
         <v>14</v>
       </c>
       <c r="F350" s="2">
-        <v>4139</v>
+        <v>4194</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>15</v>
@@ -14775,7 +14775,7 @@
         <v>14</v>
       </c>
       <c r="F351" s="2">
-        <v>2892</v>
+        <v>3891</v>
       </c>
       <c r="G351" s="2" t="s">
         <v>15</v>
@@ -14807,7 +14807,7 @@
         <v>14</v>
       </c>
       <c r="F352" s="2">
-        <v>4710</v>
+        <v>2723</v>
       </c>
       <c r="G352" s="2" t="s">
         <v>15</v>
@@ -14839,7 +14839,7 @@
         <v>14</v>
       </c>
       <c r="F353" s="2">
-        <v>3492</v>
+        <v>2547</v>
       </c>
       <c r="G353" s="2" t="s">
         <v>15</v>
@@ -14871,7 +14871,7 @@
         <v>14</v>
       </c>
       <c r="F354" s="2">
-        <v>4176</v>
+        <v>3323</v>
       </c>
       <c r="G354" s="2" t="s">
         <v>15</v>
@@ -14903,7 +14903,7 @@
         <v>14</v>
       </c>
       <c r="F355" s="2">
-        <v>1360</v>
+        <v>2343</v>
       </c>
       <c r="G355" s="2" t="s">
         <v>15</v>
@@ -14935,7 +14935,7 @@
         <v>14</v>
       </c>
       <c r="F356" s="2">
-        <v>910</v>
+        <v>2047</v>
       </c>
       <c r="G356" s="2" t="s">
         <v>15</v>
@@ -14967,7 +14967,7 @@
         <v>14</v>
       </c>
       <c r="F357" s="2">
-        <v>1577</v>
+        <v>4203</v>
       </c>
       <c r="G357" s="2" t="s">
         <v>15</v>
@@ -14999,7 +14999,7 @@
         <v>14</v>
       </c>
       <c r="F358" s="2">
-        <v>3856</v>
+        <v>2190</v>
       </c>
       <c r="G358" s="2" t="s">
         <v>15</v>
@@ -15031,7 +15031,7 @@
         <v>14</v>
       </c>
       <c r="F359" s="2">
-        <v>1140</v>
+        <v>3093</v>
       </c>
       <c r="G359" s="2" t="s">
         <v>15</v>
@@ -15063,7 +15063,7 @@
         <v>14</v>
       </c>
       <c r="F360" s="2">
-        <v>3564</v>
+        <v>4557</v>
       </c>
       <c r="G360" s="2" t="s">
         <v>15</v>
@@ -15095,7 +15095,7 @@
         <v>14</v>
       </c>
       <c r="F361" s="2">
-        <v>4477</v>
+        <v>2738</v>
       </c>
       <c r="G361" s="2" t="s">
         <v>15</v>
@@ -15127,7 +15127,7 @@
         <v>14</v>
       </c>
       <c r="F362" s="2">
-        <v>1274</v>
+        <v>2733</v>
       </c>
       <c r="G362" s="2" t="s">
         <v>15</v>
@@ -15159,7 +15159,7 @@
         <v>14</v>
       </c>
       <c r="F363" s="2">
-        <v>829</v>
+        <v>1853</v>
       </c>
       <c r="G363" s="2" t="s">
         <v>15</v>
@@ -15191,7 +15191,7 @@
         <v>14</v>
       </c>
       <c r="F364" s="2">
-        <v>2026</v>
+        <v>1191</v>
       </c>
       <c r="G364" s="2" t="s">
         <v>15</v>
@@ -15223,7 +15223,7 @@
         <v>14</v>
       </c>
       <c r="F365" s="2">
-        <v>3247</v>
+        <v>4736</v>
       </c>
       <c r="G365" s="2" t="s">
         <v>15</v>
@@ -15255,7 +15255,7 @@
         <v>14</v>
       </c>
       <c r="F366" s="2">
-        <v>4319</v>
+        <v>4082</v>
       </c>
       <c r="G366" s="2" t="s">
         <v>15</v>
@@ -15287,7 +15287,7 @@
         <v>14</v>
       </c>
       <c r="F367" s="2">
-        <v>2218</v>
+        <v>3587</v>
       </c>
       <c r="G367" s="2" t="s">
         <v>15</v>
@@ -15319,7 +15319,7 @@
         <v>14</v>
       </c>
       <c r="F368" s="2">
-        <v>4492</v>
+        <v>2399</v>
       </c>
       <c r="G368" s="2" t="s">
         <v>15</v>
@@ -15351,7 +15351,7 @@
         <v>14</v>
       </c>
       <c r="F369" s="2">
-        <v>4099</v>
+        <v>859</v>
       </c>
       <c r="G369" s="2" t="s">
         <v>15</v>
@@ -15383,7 +15383,7 @@
         <v>14</v>
       </c>
       <c r="F370" s="2">
-        <v>1955</v>
+        <v>2371</v>
       </c>
       <c r="G370" s="2" t="s">
         <v>15</v>
@@ -15415,7 +15415,7 @@
         <v>14</v>
       </c>
       <c r="F371" s="2">
-        <v>2638</v>
+        <v>1934</v>
       </c>
       <c r="G371" s="2" t="s">
         <v>15</v>
@@ -15447,7 +15447,7 @@
         <v>14</v>
       </c>
       <c r="F372" s="2">
-        <v>3835</v>
+        <v>3709</v>
       </c>
       <c r="G372" s="2" t="s">
         <v>15</v>
@@ -15479,7 +15479,7 @@
         <v>14</v>
       </c>
       <c r="F373" s="2">
-        <v>1074</v>
+        <v>4011</v>
       </c>
       <c r="G373" s="2" t="s">
         <v>15</v>
@@ -15511,7 +15511,7 @@
         <v>14</v>
       </c>
       <c r="F374" s="2">
-        <v>2251</v>
+        <v>4777</v>
       </c>
       <c r="G374" s="2" t="s">
         <v>15</v>
@@ -15543,7 +15543,7 @@
         <v>14</v>
       </c>
       <c r="F375" s="2">
-        <v>4569</v>
+        <v>2664</v>
       </c>
       <c r="G375" s="2" t="s">
         <v>15</v>
@@ -15575,7 +15575,7 @@
         <v>14</v>
       </c>
       <c r="F376" s="2">
-        <v>1462</v>
+        <v>2114</v>
       </c>
       <c r="G376" s="2" t="s">
         <v>15</v>
@@ -15607,7 +15607,7 @@
         <v>14</v>
       </c>
       <c r="F377" s="2">
-        <v>2823</v>
+        <v>2957</v>
       </c>
       <c r="G377" s="2" t="s">
         <v>15</v>
@@ -15639,7 +15639,7 @@
         <v>14</v>
       </c>
       <c r="F378" s="2">
-        <v>3389</v>
+        <v>4148</v>
       </c>
       <c r="G378" s="2" t="s">
         <v>15</v>
@@ -15671,7 +15671,7 @@
         <v>14</v>
       </c>
       <c r="F379" s="2">
-        <v>4672</v>
+        <v>2634</v>
       </c>
       <c r="G379" s="2" t="s">
         <v>15</v>
@@ -15703,7 +15703,7 @@
         <v>14</v>
       </c>
       <c r="F380" s="2">
-        <v>1070</v>
+        <v>3368</v>
       </c>
       <c r="G380" s="2" t="s">
         <v>15</v>
@@ -15735,7 +15735,7 @@
         <v>14</v>
       </c>
       <c r="F381" s="2">
-        <v>865</v>
+        <v>1149</v>
       </c>
       <c r="G381" s="2" t="s">
         <v>15</v>
@@ -15767,7 +15767,7 @@
         <v>14</v>
       </c>
       <c r="F382" s="2">
-        <v>3504</v>
+        <v>3997</v>
       </c>
       <c r="G382" s="2" t="s">
         <v>15</v>
@@ -15799,7 +15799,7 @@
         <v>14</v>
       </c>
       <c r="F383" s="2">
-        <v>4110</v>
+        <v>2040</v>
       </c>
       <c r="G383" s="2" t="s">
         <v>15</v>
@@ -15831,7 +15831,7 @@
         <v>14</v>
       </c>
       <c r="F384" s="2">
-        <v>2087</v>
+        <v>3251</v>
       </c>
       <c r="G384" s="2" t="s">
         <v>15</v>
@@ -15863,7 +15863,7 @@
         <v>14</v>
       </c>
       <c r="F385" s="2">
-        <v>1122</v>
+        <v>2923</v>
       </c>
       <c r="G385" s="2" t="s">
         <v>15</v>
@@ -15895,7 +15895,7 @@
         <v>14</v>
       </c>
       <c r="F386" s="2">
-        <v>3422</v>
+        <v>1599</v>
       </c>
       <c r="G386" s="2" t="s">
         <v>15</v>
@@ -15927,7 +15927,7 @@
         <v>14</v>
       </c>
       <c r="F387" s="2">
-        <v>1251</v>
+        <v>1744</v>
       </c>
       <c r="G387" s="2" t="s">
         <v>15</v>
@@ -15959,7 +15959,7 @@
         <v>14</v>
       </c>
       <c r="F388" s="2">
-        <v>4469</v>
+        <v>1956</v>
       </c>
       <c r="G388" s="2" t="s">
         <v>15</v>
@@ -15991,7 +15991,7 @@
         <v>14</v>
       </c>
       <c r="F389" s="2">
-        <v>2557</v>
+        <v>1633</v>
       </c>
       <c r="G389" s="2" t="s">
         <v>15</v>
@@ -16023,7 +16023,7 @@
         <v>14</v>
       </c>
       <c r="F390" s="2">
-        <v>3940</v>
+        <v>1836</v>
       </c>
       <c r="G390" s="2" t="s">
         <v>15</v>
@@ -16055,7 +16055,7 @@
         <v>14</v>
       </c>
       <c r="F391" s="2">
-        <v>4227</v>
+        <v>1759</v>
       </c>
       <c r="G391" s="2" t="s">
         <v>15</v>
@@ -16087,7 +16087,7 @@
         <v>14</v>
       </c>
       <c r="F392" s="2">
-        <v>855</v>
+        <v>3636</v>
       </c>
       <c r="G392" s="2" t="s">
         <v>15</v>
@@ -16119,7 +16119,7 @@
         <v>14</v>
       </c>
       <c r="F393" s="2">
-        <v>1380</v>
+        <v>2608</v>
       </c>
       <c r="G393" s="2" t="s">
         <v>15</v>
@@ -16151,7 +16151,7 @@
         <v>14</v>
       </c>
       <c r="F394" s="2">
-        <v>939</v>
+        <v>1504</v>
       </c>
       <c r="G394" s="2" t="s">
         <v>15</v>
@@ -16183,7 +16183,7 @@
         <v>14</v>
       </c>
       <c r="F395" s="2">
-        <v>2924</v>
+        <v>3729</v>
       </c>
       <c r="G395" s="2" t="s">
         <v>15</v>
@@ -16215,7 +16215,7 @@
         <v>14</v>
       </c>
       <c r="F396" s="2">
-        <v>3298</v>
+        <v>2811</v>
       </c>
       <c r="G396" s="2" t="s">
         <v>15</v>
@@ -16247,7 +16247,7 @@
         <v>14</v>
       </c>
       <c r="F397" s="2">
-        <v>3232</v>
+        <v>4066</v>
       </c>
       <c r="G397" s="2" t="s">
         <v>15</v>
@@ -16279,7 +16279,7 @@
         <v>14</v>
       </c>
       <c r="F398" s="2">
-        <v>2202</v>
+        <v>2598</v>
       </c>
       <c r="G398" s="2" t="s">
         <v>15</v>
@@ -16311,7 +16311,7 @@
         <v>14</v>
       </c>
       <c r="F399" s="2">
-        <v>2197</v>
+        <v>4741</v>
       </c>
       <c r="G399" s="2" t="s">
         <v>15</v>
@@ -16343,7 +16343,7 @@
         <v>14</v>
       </c>
       <c r="F400" s="2">
-        <v>4337</v>
+        <v>1505</v>
       </c>
       <c r="G400" s="2" t="s">
         <v>15</v>
@@ -16375,7 +16375,7 @@
         <v>14</v>
       </c>
       <c r="F401" s="2">
-        <v>3755</v>
+        <v>4458</v>
       </c>
       <c r="G401" s="2" t="s">
         <v>15</v>
@@ -16407,7 +16407,7 @@
         <v>14</v>
       </c>
       <c r="F402" s="2">
-        <v>3172</v>
+        <v>4582</v>
       </c>
       <c r="G402" s="2" t="s">
         <v>15</v>
@@ -16439,7 +16439,7 @@
         <v>14</v>
       </c>
       <c r="F403" s="2">
-        <v>2887</v>
+        <v>4135</v>
       </c>
       <c r="G403" s="2" t="s">
         <v>15</v>
@@ -16471,7 +16471,7 @@
         <v>14</v>
       </c>
       <c r="F404" s="2">
-        <v>4081</v>
+        <v>1593</v>
       </c>
       <c r="G404" s="2" t="s">
         <v>15</v>
@@ -16503,7 +16503,7 @@
         <v>14</v>
       </c>
       <c r="F405" s="2">
-        <v>4367</v>
+        <v>2410</v>
       </c>
       <c r="G405" s="2" t="s">
         <v>15</v>
@@ -16535,7 +16535,7 @@
         <v>14</v>
       </c>
       <c r="F406" s="2">
-        <v>2635</v>
+        <v>996</v>
       </c>
       <c r="G406" s="2" t="s">
         <v>15</v>
@@ -16567,7 +16567,7 @@
         <v>14</v>
       </c>
       <c r="F407" s="2">
-        <v>3014</v>
+        <v>3339</v>
       </c>
       <c r="G407" s="2" t="s">
         <v>15</v>
@@ -16599,7 +16599,7 @@
         <v>14</v>
       </c>
       <c r="F408" s="2">
-        <v>2977</v>
+        <v>2364</v>
       </c>
       <c r="G408" s="2" t="s">
         <v>15</v>
@@ -16631,7 +16631,7 @@
         <v>14</v>
       </c>
       <c r="F409" s="2">
-        <v>1687</v>
+        <v>2892</v>
       </c>
       <c r="G409" s="2" t="s">
         <v>15</v>
@@ -16663,7 +16663,7 @@
         <v>14</v>
       </c>
       <c r="F410" s="2">
-        <v>1750</v>
+        <v>4529</v>
       </c>
       <c r="G410" s="2" t="s">
         <v>15</v>
@@ -16695,7 +16695,7 @@
         <v>14</v>
       </c>
       <c r="F411" s="2">
-        <v>4506</v>
+        <v>4508</v>
       </c>
       <c r="G411" s="2" t="s">
         <v>15</v>
@@ -16727,7 +16727,7 @@
         <v>14</v>
       </c>
       <c r="F412" s="2">
-        <v>3570</v>
+        <v>2510</v>
       </c>
       <c r="G412" s="2" t="s">
         <v>15</v>
@@ -16759,7 +16759,7 @@
         <v>14</v>
       </c>
       <c r="F413" s="2">
-        <v>4378</v>
+        <v>3927</v>
       </c>
       <c r="G413" s="2" t="s">
         <v>15</v>
@@ -16791,7 +16791,7 @@
         <v>14</v>
       </c>
       <c r="F414" s="2">
-        <v>2477</v>
+        <v>2773</v>
       </c>
       <c r="G414" s="2" t="s">
         <v>15</v>
@@ -16823,7 +16823,7 @@
         <v>14</v>
       </c>
       <c r="F415" s="2">
-        <v>1152</v>
+        <v>4276</v>
       </c>
       <c r="G415" s="2" t="s">
         <v>15</v>
@@ -16855,7 +16855,7 @@
         <v>14</v>
       </c>
       <c r="F416" s="2">
-        <v>1567</v>
+        <v>3540</v>
       </c>
       <c r="G416" s="2" t="s">
         <v>15</v>
@@ -16887,7 +16887,7 @@
         <v>14</v>
       </c>
       <c r="F417" s="2">
-        <v>4474</v>
+        <v>3968</v>
       </c>
       <c r="G417" s="2" t="s">
         <v>15</v>
@@ -16919,7 +16919,7 @@
         <v>14</v>
       </c>
       <c r="F418" s="2">
-        <v>2150</v>
+        <v>2547</v>
       </c>
       <c r="G418" s="2" t="s">
         <v>15</v>
@@ -16951,7 +16951,7 @@
         <v>14</v>
       </c>
       <c r="F419" s="2">
-        <v>1218</v>
+        <v>4781</v>
       </c>
       <c r="G419" s="2" t="s">
         <v>15</v>
@@ -16983,7 +16983,7 @@
         <v>14</v>
       </c>
       <c r="F420" s="2">
-        <v>845</v>
+        <v>1203</v>
       </c>
       <c r="G420" s="2" t="s">
         <v>15</v>
@@ -17015,7 +17015,7 @@
         <v>14</v>
       </c>
       <c r="F421" s="2">
-        <v>4377</v>
+        <v>3200</v>
       </c>
       <c r="G421" s="2" t="s">
         <v>15</v>
@@ -17047,7 +17047,7 @@
         <v>14</v>
       </c>
       <c r="F422" s="2">
-        <v>1393</v>
+        <v>2995</v>
       </c>
       <c r="G422" s="2" t="s">
         <v>15</v>
@@ -17079,7 +17079,7 @@
         <v>14</v>
       </c>
       <c r="F423" s="2">
-        <v>1475</v>
+        <v>3083</v>
       </c>
       <c r="G423" s="2" t="s">
         <v>15</v>
@@ -17111,7 +17111,7 @@
         <v>14</v>
       </c>
       <c r="F424" s="2">
-        <v>848</v>
+        <v>2190</v>
       </c>
       <c r="G424" s="2" t="s">
         <v>15</v>
@@ -17143,7 +17143,7 @@
         <v>14</v>
       </c>
       <c r="F425" s="2">
-        <v>3175</v>
+        <v>2533</v>
       </c>
       <c r="G425" s="2" t="s">
         <v>15</v>
@@ -17175,7 +17175,7 @@
         <v>14</v>
       </c>
       <c r="F426" s="2">
-        <v>2920</v>
+        <v>3930</v>
       </c>
       <c r="G426" s="2" t="s">
         <v>15</v>
@@ -17207,7 +17207,7 @@
         <v>14</v>
       </c>
       <c r="F427" s="2">
-        <v>3412</v>
+        <v>3004</v>
       </c>
       <c r="G427" s="2" t="s">
         <v>15</v>
@@ -17239,7 +17239,7 @@
         <v>14</v>
       </c>
       <c r="F428" s="2">
-        <v>2661</v>
+        <v>4656</v>
       </c>
       <c r="G428" s="2" t="s">
         <v>15</v>
@@ -17271,7 +17271,7 @@
         <v>14</v>
       </c>
       <c r="F429" s="2">
-        <v>2462</v>
+        <v>1884</v>
       </c>
       <c r="G429" s="2" t="s">
         <v>15</v>
@@ -17303,7 +17303,7 @@
         <v>14</v>
       </c>
       <c r="F430" s="2">
-        <v>3593</v>
+        <v>3407</v>
       </c>
       <c r="G430" s="2" t="s">
         <v>15</v>
@@ -17335,7 +17335,7 @@
         <v>14</v>
       </c>
       <c r="F431" s="2">
-        <v>924</v>
+        <v>1168</v>
       </c>
       <c r="G431" s="2" t="s">
         <v>15</v>
@@ -17367,7 +17367,7 @@
         <v>14</v>
       </c>
       <c r="F432" s="2">
-        <v>1477</v>
+        <v>4725</v>
       </c>
       <c r="G432" s="2" t="s">
         <v>15</v>
@@ -17399,7 +17399,7 @@
         <v>14</v>
       </c>
       <c r="F433" s="2">
-        <v>3457</v>
+        <v>3276</v>
       </c>
       <c r="G433" s="2" t="s">
         <v>15</v>
@@ -17431,7 +17431,7 @@
         <v>14</v>
       </c>
       <c r="F434" s="2">
-        <v>2603</v>
+        <v>3699</v>
       </c>
       <c r="G434" s="2" t="s">
         <v>15</v>
@@ -17463,7 +17463,7 @@
         <v>14</v>
       </c>
       <c r="F435" s="2">
-        <v>1006</v>
+        <v>4598</v>
       </c>
       <c r="G435" s="2" t="s">
         <v>15</v>
@@ -17495,7 +17495,7 @@
         <v>14</v>
       </c>
       <c r="F436" s="2">
-        <v>1330</v>
+        <v>1632</v>
       </c>
       <c r="G436" s="2" t="s">
         <v>15</v>
@@ -17527,7 +17527,7 @@
         <v>14</v>
       </c>
       <c r="F437" s="2">
-        <v>4319</v>
+        <v>4687</v>
       </c>
       <c r="G437" s="2" t="s">
         <v>15</v>
@@ -17559,7 +17559,7 @@
         <v>14</v>
       </c>
       <c r="F438" s="2">
-        <v>2184</v>
+        <v>3150</v>
       </c>
       <c r="G438" s="2" t="s">
         <v>15</v>
@@ -17591,7 +17591,7 @@
         <v>14</v>
       </c>
       <c r="F439" s="2">
-        <v>2404</v>
+        <v>1223</v>
       </c>
       <c r="G439" s="2" t="s">
         <v>15</v>
@@ -17623,7 +17623,7 @@
         <v>14</v>
       </c>
       <c r="F440" s="2">
-        <v>3674</v>
+        <v>3705</v>
       </c>
       <c r="G440" s="2" t="s">
         <v>15</v>
@@ -17655,7 +17655,7 @@
         <v>14</v>
       </c>
       <c r="F441" s="2">
-        <v>3577</v>
+        <v>957</v>
       </c>
       <c r="G441" s="2" t="s">
         <v>15</v>
@@ -17687,7 +17687,7 @@
         <v>14</v>
       </c>
       <c r="F442" s="2">
-        <v>895</v>
+        <v>3911</v>
       </c>
       <c r="G442" s="2" t="s">
         <v>15</v>
@@ -17719,7 +17719,7 @@
         <v>14</v>
       </c>
       <c r="F443" s="2">
-        <v>2515</v>
+        <v>3484</v>
       </c>
       <c r="G443" s="2" t="s">
         <v>15</v>
@@ -17751,7 +17751,7 @@
         <v>14</v>
       </c>
       <c r="F444" s="2">
-        <v>2311</v>
+        <v>4279</v>
       </c>
       <c r="G444" s="2" t="s">
         <v>15</v>
@@ -17783,7 +17783,7 @@
         <v>14</v>
       </c>
       <c r="F445" s="2">
-        <v>4437</v>
+        <v>4234</v>
       </c>
       <c r="G445" s="2" t="s">
         <v>15</v>
@@ -17815,7 +17815,7 @@
         <v>14</v>
       </c>
       <c r="F446" s="2">
-        <v>4363</v>
+        <v>3327</v>
       </c>
       <c r="G446" s="2" t="s">
         <v>15</v>
@@ -17847,7 +17847,7 @@
         <v>14</v>
       </c>
       <c r="F447" s="2">
-        <v>4298</v>
+        <v>3127</v>
       </c>
       <c r="G447" s="2" t="s">
         <v>15</v>
@@ -17879,7 +17879,7 @@
         <v>14</v>
       </c>
       <c r="F448" s="2">
-        <v>2439</v>
+        <v>1068</v>
       </c>
       <c r="G448" s="2" t="s">
         <v>15</v>
@@ -17911,7 +17911,7 @@
         <v>14</v>
       </c>
       <c r="F449" s="2">
-        <v>4645</v>
+        <v>3343</v>
       </c>
       <c r="G449" s="2" t="s">
         <v>15</v>
@@ -17943,7 +17943,7 @@
         <v>14</v>
       </c>
       <c r="F450" s="2">
-        <v>1342</v>
+        <v>4444</v>
       </c>
       <c r="G450" s="2" t="s">
         <v>15</v>
@@ -17975,7 +17975,7 @@
         <v>14</v>
       </c>
       <c r="F451" s="2">
-        <v>2672</v>
+        <v>1996</v>
       </c>
       <c r="G451" s="2" t="s">
         <v>15</v>
@@ -18007,7 +18007,7 @@
         <v>14</v>
       </c>
       <c r="F452" s="2">
-        <v>3106</v>
+        <v>3933</v>
       </c>
       <c r="G452" s="2" t="s">
         <v>15</v>
@@ -18039,7 +18039,7 @@
         <v>14</v>
       </c>
       <c r="F453" s="2">
-        <v>3750</v>
+        <v>3931</v>
       </c>
       <c r="G453" s="2" t="s">
         <v>15</v>
@@ -18071,7 +18071,7 @@
         <v>14</v>
       </c>
       <c r="F454" s="2">
-        <v>2423</v>
+        <v>2894</v>
       </c>
       <c r="G454" s="2" t="s">
         <v>15</v>
@@ -18103,7 +18103,7 @@
         <v>14</v>
       </c>
       <c r="F455" s="2">
-        <v>4015</v>
+        <v>1497</v>
       </c>
       <c r="G455" s="2" t="s">
         <v>15</v>
@@ -18135,7 +18135,7 @@
         <v>14</v>
       </c>
       <c r="F456" s="2">
-        <v>1791</v>
+        <v>2218</v>
       </c>
       <c r="G456" s="2" t="s">
         <v>15</v>
@@ -18167,7 +18167,7 @@
         <v>14</v>
       </c>
       <c r="F457" s="2">
-        <v>2347</v>
+        <v>3524</v>
       </c>
       <c r="G457" s="2" t="s">
         <v>15</v>
@@ -18199,7 +18199,7 @@
         <v>14</v>
       </c>
       <c r="F458" s="2">
-        <v>4103</v>
+        <v>1284</v>
       </c>
       <c r="G458" s="2" t="s">
         <v>15</v>
@@ -18231,7 +18231,7 @@
         <v>14</v>
       </c>
       <c r="F459" s="2">
-        <v>4287</v>
+        <v>2050</v>
       </c>
       <c r="G459" s="2" t="s">
         <v>15</v>
@@ -18263,7 +18263,7 @@
         <v>14</v>
       </c>
       <c r="F460" s="2">
-        <v>2068</v>
+        <v>3163</v>
       </c>
       <c r="G460" s="2" t="s">
         <v>15</v>
@@ -18295,7 +18295,7 @@
         <v>14</v>
       </c>
       <c r="F461" s="2">
-        <v>2545</v>
+        <v>3864</v>
       </c>
       <c r="G461" s="2" t="s">
         <v>15</v>
@@ -18327,7 +18327,7 @@
         <v>14</v>
       </c>
       <c r="F462" s="2">
-        <v>2739</v>
+        <v>968</v>
       </c>
       <c r="G462" s="2" t="s">
         <v>15</v>
@@ -18359,7 +18359,7 @@
         <v>14</v>
       </c>
       <c r="F463" s="2">
-        <v>1550</v>
+        <v>3019</v>
       </c>
       <c r="G463" s="2" t="s">
         <v>15</v>
@@ -18391,7 +18391,7 @@
         <v>14</v>
       </c>
       <c r="F464" s="2">
-        <v>4744</v>
+        <v>3517</v>
       </c>
       <c r="G464" s="2" t="s">
         <v>15</v>
@@ -18423,7 +18423,7 @@
         <v>14</v>
       </c>
       <c r="F465" s="2">
-        <v>3105</v>
+        <v>904</v>
       </c>
       <c r="G465" s="2" t="s">
         <v>15</v>
@@ -18455,7 +18455,7 @@
         <v>14</v>
       </c>
       <c r="F466" s="2">
-        <v>2996</v>
+        <v>938</v>
       </c>
       <c r="G466" s="2" t="s">
         <v>15</v>
@@ -18487,7 +18487,7 @@
         <v>14</v>
       </c>
       <c r="F467" s="2">
-        <v>1446</v>
+        <v>963</v>
       </c>
       <c r="G467" s="2" t="s">
         <v>15</v>
@@ -18519,7 +18519,7 @@
         <v>14</v>
       </c>
       <c r="F468" s="2">
-        <v>1021</v>
+        <v>3207</v>
       </c>
       <c r="G468" s="2" t="s">
         <v>15</v>
@@ -18551,7 +18551,7 @@
         <v>14</v>
       </c>
       <c r="F469" s="2">
-        <v>2786</v>
+        <v>2294</v>
       </c>
       <c r="G469" s="2" t="s">
         <v>15</v>
@@ -18583,7 +18583,7 @@
         <v>14</v>
       </c>
       <c r="F470" s="2">
-        <v>4230</v>
+        <v>4011</v>
       </c>
       <c r="G470" s="2" t="s">
         <v>15</v>
@@ -18615,7 +18615,7 @@
         <v>14</v>
       </c>
       <c r="F471" s="2">
-        <v>1294</v>
+        <v>3655</v>
       </c>
       <c r="G471" s="2" t="s">
         <v>15</v>
@@ -18702,7 +18702,7 @@
         <v>14</v>
       </c>
       <c r="F2" s="2">
-        <v>1450</v>
+        <v>1474</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>15</v>
@@ -18734,7 +18734,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="2">
-        <v>2489</v>
+        <v>2259</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>15</v>
@@ -18766,7 +18766,7 @@
         <v>14</v>
       </c>
       <c r="F4" s="2">
-        <v>2638</v>
+        <v>4215</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
@@ -18798,7 +18798,7 @@
         <v>14</v>
       </c>
       <c r="F5" s="2">
-        <v>974</v>
+        <v>3600</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
@@ -18830,7 +18830,7 @@
         <v>14</v>
       </c>
       <c r="F6" s="2">
-        <v>4614</v>
+        <v>4681</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -18862,7 +18862,7 @@
         <v>14</v>
       </c>
       <c r="F7" s="2">
-        <v>2741</v>
+        <v>3419</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -18894,7 +18894,7 @@
         <v>14</v>
       </c>
       <c r="F8" s="2">
-        <v>3827</v>
+        <v>863</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -18926,7 +18926,7 @@
         <v>14</v>
       </c>
       <c r="F9" s="2">
-        <v>2828</v>
+        <v>3411</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -18958,7 +18958,7 @@
         <v>14</v>
       </c>
       <c r="F10" s="2">
-        <v>3647</v>
+        <v>3621</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
@@ -18990,7 +18990,7 @@
         <v>14</v>
       </c>
       <c r="F11" s="2">
-        <v>1609</v>
+        <v>4487</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
@@ -19022,7 +19022,7 @@
         <v>14</v>
       </c>
       <c r="F12" s="2">
-        <v>4028</v>
+        <v>3551</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
@@ -19054,7 +19054,7 @@
         <v>14</v>
       </c>
       <c r="F13" s="2">
-        <v>2234</v>
+        <v>2387</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -19086,7 +19086,7 @@
         <v>14</v>
       </c>
       <c r="F14" s="2">
-        <v>2257</v>
+        <v>2144</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -19118,7 +19118,7 @@
         <v>14</v>
       </c>
       <c r="F15" s="2">
-        <v>4552</v>
+        <v>1214</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -19150,7 +19150,7 @@
         <v>14</v>
       </c>
       <c r="F16" s="2">
-        <v>4048</v>
+        <v>4216</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
@@ -19182,7 +19182,7 @@
         <v>14</v>
       </c>
       <c r="F17" s="2">
-        <v>1247</v>
+        <v>2084</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
@@ -19214,7 +19214,7 @@
         <v>14</v>
       </c>
       <c r="F18" s="2">
-        <v>1995</v>
+        <v>2587</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
@@ -19246,7 +19246,7 @@
         <v>14</v>
       </c>
       <c r="F19" s="2">
-        <v>858</v>
+        <v>1494</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
@@ -19278,7 +19278,7 @@
         <v>14</v>
       </c>
       <c r="F20" s="2">
-        <v>4489</v>
+        <v>3860</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
@@ -19310,7 +19310,7 @@
         <v>14</v>
       </c>
       <c r="F21" s="2">
-        <v>4276</v>
+        <v>4023</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -19342,7 +19342,7 @@
         <v>14</v>
       </c>
       <c r="F22" s="2">
-        <v>3282</v>
+        <v>2703</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -19374,7 +19374,7 @@
         <v>14</v>
       </c>
       <c r="F23" s="2">
-        <v>4545</v>
+        <v>897</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -19406,7 +19406,7 @@
         <v>14</v>
       </c>
       <c r="F24" s="2">
-        <v>1826</v>
+        <v>2748</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -19438,7 +19438,7 @@
         <v>14</v>
       </c>
       <c r="F25" s="2">
-        <v>4127</v>
+        <v>1589</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -19470,7 +19470,7 @@
         <v>14</v>
       </c>
       <c r="F26" s="2">
-        <v>1717</v>
+        <v>1491</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -19502,7 +19502,7 @@
         <v>14</v>
       </c>
       <c r="F27" s="2">
-        <v>3328</v>
+        <v>2033</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>15</v>
@@ -19534,7 +19534,7 @@
         <v>14</v>
       </c>
       <c r="F28" s="2">
-        <v>3302</v>
+        <v>3660</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>15</v>
@@ -19566,7 +19566,7 @@
         <v>14</v>
       </c>
       <c r="F29" s="2">
-        <v>3596</v>
+        <v>1751</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>15</v>
@@ -19598,7 +19598,7 @@
         <v>14</v>
       </c>
       <c r="F30" s="2">
-        <v>3771</v>
+        <v>2161</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>15</v>
@@ -19630,7 +19630,7 @@
         <v>14</v>
       </c>
       <c r="F31" s="2">
-        <v>3017</v>
+        <v>3354</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>15</v>
@@ -19662,7 +19662,7 @@
         <v>14</v>
       </c>
       <c r="F32" s="2">
-        <v>2397</v>
+        <v>2854</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>15</v>
@@ -19694,7 +19694,7 @@
         <v>14</v>
       </c>
       <c r="F33" s="2">
-        <v>2673</v>
+        <v>4439</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>15</v>
@@ -19726,7 +19726,7 @@
         <v>14</v>
       </c>
       <c r="F34" s="2">
-        <v>3101</v>
+        <v>4734</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>15</v>
@@ -19758,7 +19758,7 @@
         <v>14</v>
       </c>
       <c r="F35" s="2">
-        <v>2429</v>
+        <v>4057</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>15</v>
@@ -19790,7 +19790,7 @@
         <v>14</v>
       </c>
       <c r="F36" s="2">
-        <v>1150</v>
+        <v>2967</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>15</v>
@@ -19822,7 +19822,7 @@
         <v>14</v>
       </c>
       <c r="F37" s="2">
-        <v>2339</v>
+        <v>4073</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>15</v>
@@ -19854,7 +19854,7 @@
         <v>14</v>
       </c>
       <c r="F38" s="2">
-        <v>2212</v>
+        <v>3806</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>15</v>
@@ -19886,7 +19886,7 @@
         <v>14</v>
       </c>
       <c r="F39" s="2">
-        <v>2768</v>
+        <v>896</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>15</v>
@@ -19918,7 +19918,7 @@
         <v>14</v>
       </c>
       <c r="F40" s="2">
-        <v>3111</v>
+        <v>1022</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>15</v>
@@ -19950,7 +19950,7 @@
         <v>14</v>
       </c>
       <c r="F41" s="2">
-        <v>2828</v>
+        <v>2792</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>15</v>
@@ -19982,7 +19982,7 @@
         <v>14</v>
       </c>
       <c r="F42" s="2">
-        <v>978</v>
+        <v>4497</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>15</v>
@@ -20014,7 +20014,7 @@
         <v>14</v>
       </c>
       <c r="F43" s="2">
-        <v>1172</v>
+        <v>1900</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>15</v>
@@ -20046,7 +20046,7 @@
         <v>14</v>
       </c>
       <c r="F44" s="2">
-        <v>4229</v>
+        <v>2404</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>15</v>
@@ -20078,7 +20078,7 @@
         <v>14</v>
       </c>
       <c r="F45" s="2">
-        <v>987</v>
+        <v>2317</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>15</v>
@@ -20110,7 +20110,7 @@
         <v>14</v>
       </c>
       <c r="F46" s="2">
-        <v>1340</v>
+        <v>4464</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>15</v>
@@ -20142,7 +20142,7 @@
         <v>14</v>
       </c>
       <c r="F47" s="2">
-        <v>3810</v>
+        <v>2309</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>15</v>
@@ -20174,7 +20174,7 @@
         <v>14</v>
       </c>
       <c r="F48" s="2">
-        <v>4754</v>
+        <v>3997</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>15</v>
@@ -20206,7 +20206,7 @@
         <v>14</v>
       </c>
       <c r="F49" s="2">
-        <v>1126</v>
+        <v>2573</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>15</v>
@@ -20238,7 +20238,7 @@
         <v>14</v>
       </c>
       <c r="F50" s="2">
-        <v>855</v>
+        <v>1914</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>15</v>
@@ -20270,7 +20270,7 @@
         <v>14</v>
       </c>
       <c r="F51" s="2">
-        <v>1183</v>
+        <v>1090</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>15</v>
@@ -20302,7 +20302,7 @@
         <v>14</v>
       </c>
       <c r="F52" s="2">
-        <v>4028</v>
+        <v>4412</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>15</v>
@@ -20334,7 +20334,7 @@
         <v>14</v>
       </c>
       <c r="F53" s="2">
-        <v>1862</v>
+        <v>4643</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>15</v>
@@ -20366,7 +20366,7 @@
         <v>14</v>
       </c>
       <c r="F54" s="2">
-        <v>2924</v>
+        <v>2014</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>15</v>
@@ -20398,7 +20398,7 @@
         <v>14</v>
       </c>
       <c r="F55" s="2">
-        <v>1346</v>
+        <v>2043</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>15</v>
@@ -20430,7 +20430,7 @@
         <v>14</v>
       </c>
       <c r="F56" s="2">
-        <v>2612</v>
+        <v>2450</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>15</v>
@@ -20462,7 +20462,7 @@
         <v>14</v>
       </c>
       <c r="F57" s="2">
-        <v>2772</v>
+        <v>4286</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>15</v>
@@ -20494,7 +20494,7 @@
         <v>14</v>
       </c>
       <c r="F58" s="2">
-        <v>3387</v>
+        <v>2741</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>15</v>
@@ -20526,7 +20526,7 @@
         <v>14</v>
       </c>
       <c r="F59" s="2">
-        <v>1418</v>
+        <v>1182</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>15</v>
@@ -20558,7 +20558,7 @@
         <v>14</v>
       </c>
       <c r="F60" s="2">
-        <v>1511</v>
+        <v>4437</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>15</v>
@@ -20590,7 +20590,7 @@
         <v>14</v>
       </c>
       <c r="F61" s="2">
-        <v>3534</v>
+        <v>2523</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>15</v>
@@ -20622,7 +20622,7 @@
         <v>14</v>
       </c>
       <c r="F62" s="2">
-        <v>4205</v>
+        <v>1547</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>15</v>
@@ -20654,7 +20654,7 @@
         <v>14</v>
       </c>
       <c r="F63" s="2">
-        <v>3890</v>
+        <v>3226</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>15</v>
@@ -20686,7 +20686,7 @@
         <v>14</v>
       </c>
       <c r="F64" s="2">
-        <v>4606</v>
+        <v>3877</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>15</v>
@@ -20718,7 +20718,7 @@
         <v>14</v>
       </c>
       <c r="F65" s="2">
-        <v>834</v>
+        <v>3542</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>15</v>
@@ -20750,7 +20750,7 @@
         <v>14</v>
       </c>
       <c r="F66" s="2">
-        <v>4523</v>
+        <v>3702</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>15</v>
@@ -20782,7 +20782,7 @@
         <v>14</v>
       </c>
       <c r="F67" s="2">
-        <v>4005</v>
+        <v>3984</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>15</v>
@@ -20814,7 +20814,7 @@
         <v>14</v>
       </c>
       <c r="F68" s="2">
-        <v>2798</v>
+        <v>1299</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>15</v>
@@ -20846,7 +20846,7 @@
         <v>14</v>
       </c>
       <c r="F69" s="2">
-        <v>1374</v>
+        <v>2664</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>15</v>
@@ -20878,7 +20878,7 @@
         <v>14</v>
       </c>
       <c r="F70" s="2">
-        <v>4360</v>
+        <v>4251</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>15</v>
@@ -20910,7 +20910,7 @@
         <v>14</v>
       </c>
       <c r="F71" s="2">
-        <v>2274</v>
+        <v>1007</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>15</v>
@@ -20942,7 +20942,7 @@
         <v>14</v>
       </c>
       <c r="F72" s="2">
-        <v>4204</v>
+        <v>1547</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>15</v>
@@ -20974,7 +20974,7 @@
         <v>14</v>
       </c>
       <c r="F73" s="2">
-        <v>4243</v>
+        <v>3257</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>15</v>
@@ -21006,7 +21006,7 @@
         <v>14</v>
       </c>
       <c r="F74" s="2">
-        <v>1783</v>
+        <v>1158</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>15</v>
@@ -21038,7 +21038,7 @@
         <v>14</v>
       </c>
       <c r="F75" s="2">
-        <v>3551</v>
+        <v>3775</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>15</v>
@@ -21070,7 +21070,7 @@
         <v>14</v>
       </c>
       <c r="F76" s="2">
-        <v>2555</v>
+        <v>1163</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>15</v>
@@ -21102,7 +21102,7 @@
         <v>14</v>
       </c>
       <c r="F77" s="2">
-        <v>1207</v>
+        <v>1329</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>15</v>
@@ -21134,7 +21134,7 @@
         <v>14</v>
       </c>
       <c r="F78" s="2">
-        <v>959</v>
+        <v>2322</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>15</v>
@@ -21166,7 +21166,7 @@
         <v>14</v>
       </c>
       <c r="F79" s="2">
-        <v>3366</v>
+        <v>1271</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>15</v>
@@ -21198,7 +21198,7 @@
         <v>14</v>
       </c>
       <c r="F80" s="2">
-        <v>1196</v>
+        <v>1139</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>15</v>
@@ -21230,7 +21230,7 @@
         <v>14</v>
       </c>
       <c r="F81" s="2">
-        <v>1730</v>
+        <v>3455</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>15</v>
@@ -21262,7 +21262,7 @@
         <v>14</v>
       </c>
       <c r="F82" s="2">
-        <v>4771</v>
+        <v>1978</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>15</v>
@@ -21294,7 +21294,7 @@
         <v>14</v>
       </c>
       <c r="F83" s="2">
-        <v>1731</v>
+        <v>2270</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>15</v>
@@ -21326,7 +21326,7 @@
         <v>14</v>
       </c>
       <c r="F84" s="2">
-        <v>2551</v>
+        <v>1542</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>15</v>
@@ -21358,7 +21358,7 @@
         <v>14</v>
       </c>
       <c r="F85" s="2">
-        <v>3196</v>
+        <v>2688</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>15</v>
@@ -21390,7 +21390,7 @@
         <v>14</v>
       </c>
       <c r="F86" s="2">
-        <v>4215</v>
+        <v>2614</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>15</v>
@@ -21422,7 +21422,7 @@
         <v>14</v>
       </c>
       <c r="F87" s="2">
-        <v>2949</v>
+        <v>2887</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>15</v>
@@ -21454,7 +21454,7 @@
         <v>14</v>
       </c>
       <c r="F88" s="2">
-        <v>3415</v>
+        <v>2361</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>15</v>
@@ -21486,7 +21486,7 @@
         <v>14</v>
       </c>
       <c r="F89" s="2">
-        <v>3469</v>
+        <v>3180</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>15</v>
@@ -21518,7 +21518,7 @@
         <v>14</v>
       </c>
       <c r="F90" s="2">
-        <v>2636</v>
+        <v>1650</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>15</v>
@@ -21550,7 +21550,7 @@
         <v>14</v>
       </c>
       <c r="F91" s="2">
-        <v>1032</v>
+        <v>4075</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>15</v>
@@ -21582,7 +21582,7 @@
         <v>14</v>
       </c>
       <c r="F92" s="2">
-        <v>3305</v>
+        <v>1788</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>15</v>
@@ -21614,7 +21614,7 @@
         <v>14</v>
       </c>
       <c r="F93" s="2">
-        <v>3102</v>
+        <v>2372</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>15</v>
@@ -21646,7 +21646,7 @@
         <v>14</v>
       </c>
       <c r="F94" s="2">
-        <v>3782</v>
+        <v>1512</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>15</v>
@@ -21678,7 +21678,7 @@
         <v>14</v>
       </c>
       <c r="F95" s="2">
-        <v>1005</v>
+        <v>3619</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>15</v>
@@ -21710,7 +21710,7 @@
         <v>14</v>
       </c>
       <c r="F96" s="2">
-        <v>1868</v>
+        <v>4112</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>15</v>
@@ -21742,7 +21742,7 @@
         <v>14</v>
       </c>
       <c r="F97" s="2">
-        <v>807</v>
+        <v>1505</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>15</v>
@@ -21774,7 +21774,7 @@
         <v>14</v>
       </c>
       <c r="F98" s="2">
-        <v>3176</v>
+        <v>4618</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>15</v>
@@ -21806,7 +21806,7 @@
         <v>14</v>
       </c>
       <c r="F99" s="2">
-        <v>4455</v>
+        <v>1532</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>15</v>
@@ -21838,7 +21838,7 @@
         <v>14</v>
       </c>
       <c r="F100" s="2">
-        <v>2360</v>
+        <v>4411</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>15</v>
@@ -21870,7 +21870,7 @@
         <v>14</v>
       </c>
       <c r="F101" s="2">
-        <v>1753</v>
+        <v>3175</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>15</v>
@@ -21902,7 +21902,7 @@
         <v>14</v>
       </c>
       <c r="F102" s="2">
-        <v>2048</v>
+        <v>2306</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>15</v>
@@ -21934,7 +21934,7 @@
         <v>14</v>
       </c>
       <c r="F103" s="2">
-        <v>3195</v>
+        <v>2129</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>15</v>
@@ -21966,7 +21966,7 @@
         <v>14</v>
       </c>
       <c r="F104" s="2">
-        <v>2122</v>
+        <v>1448</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>15</v>
@@ -21998,7 +21998,7 @@
         <v>14</v>
       </c>
       <c r="F105" s="2">
-        <v>3135</v>
+        <v>2318</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>15</v>
@@ -22030,7 +22030,7 @@
         <v>14</v>
       </c>
       <c r="F106" s="2">
-        <v>4611</v>
+        <v>1636</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>15</v>
@@ -22062,7 +22062,7 @@
         <v>14</v>
       </c>
       <c r="F107" s="2">
-        <v>3789</v>
+        <v>1135</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>15</v>
@@ -22094,7 +22094,7 @@
         <v>14</v>
       </c>
       <c r="F108" s="2">
-        <v>3691</v>
+        <v>3461</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>15</v>
@@ -22126,7 +22126,7 @@
         <v>14</v>
       </c>
       <c r="F109" s="2">
-        <v>2675</v>
+        <v>3510</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>15</v>
@@ -22158,7 +22158,7 @@
         <v>14</v>
       </c>
       <c r="F110" s="2">
-        <v>3107</v>
+        <v>4683</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>15</v>
@@ -22190,7 +22190,7 @@
         <v>14</v>
       </c>
       <c r="F111" s="2">
-        <v>2158</v>
+        <v>3673</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>15</v>
@@ -22222,7 +22222,7 @@
         <v>14</v>
       </c>
       <c r="F112" s="2">
-        <v>1994</v>
+        <v>1017</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>15</v>
@@ -22254,7 +22254,7 @@
         <v>14</v>
       </c>
       <c r="F113" s="2">
-        <v>3106</v>
+        <v>3163</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>15</v>
@@ -22286,7 +22286,7 @@
         <v>14</v>
       </c>
       <c r="F114" s="2">
-        <v>1578</v>
+        <v>1798</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>15</v>
@@ -22318,7 +22318,7 @@
         <v>14</v>
       </c>
       <c r="F115" s="2">
-        <v>2858</v>
+        <v>3557</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>15</v>
@@ -22350,7 +22350,7 @@
         <v>14</v>
       </c>
       <c r="F116" s="2">
-        <v>2058</v>
+        <v>4404</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>15</v>
@@ -22382,7 +22382,7 @@
         <v>14</v>
       </c>
       <c r="F117" s="2">
-        <v>1006</v>
+        <v>2076</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>15</v>
@@ -22414,7 +22414,7 @@
         <v>14</v>
       </c>
       <c r="F118" s="2">
-        <v>2884</v>
+        <v>2711</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>15</v>
@@ -22446,7 +22446,7 @@
         <v>14</v>
       </c>
       <c r="F119" s="2">
-        <v>2051</v>
+        <v>3505</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>15</v>
@@ -22478,7 +22478,7 @@
         <v>14</v>
       </c>
       <c r="F120" s="2">
-        <v>948</v>
+        <v>3867</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>15</v>
@@ -22510,7 +22510,7 @@
         <v>14</v>
       </c>
       <c r="F121" s="2">
-        <v>2225</v>
+        <v>4748</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>15</v>
@@ -22542,7 +22542,7 @@
         <v>14</v>
       </c>
       <c r="F122" s="2">
-        <v>844</v>
+        <v>2823</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>15</v>
@@ -22574,7 +22574,7 @@
         <v>14</v>
       </c>
       <c r="F123" s="2">
-        <v>2023</v>
+        <v>1453</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>15</v>
@@ -22606,7 +22606,7 @@
         <v>14</v>
       </c>
       <c r="F124" s="2">
-        <v>1520</v>
+        <v>1686</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>15</v>
@@ -22638,7 +22638,7 @@
         <v>14</v>
       </c>
       <c r="F125" s="2">
-        <v>3380</v>
+        <v>1000</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>15</v>
@@ -22670,7 +22670,7 @@
         <v>14</v>
       </c>
       <c r="F126" s="2">
-        <v>2494</v>
+        <v>1580</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>15</v>
@@ -22702,7 +22702,7 @@
         <v>14</v>
       </c>
       <c r="F127" s="2">
-        <v>4678</v>
+        <v>3742</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>15</v>
@@ -22734,7 +22734,7 @@
         <v>14</v>
       </c>
       <c r="F128" s="2">
-        <v>1316</v>
+        <v>1832</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>15</v>
@@ -22766,7 +22766,7 @@
         <v>14</v>
       </c>
       <c r="F129" s="2">
-        <v>2231</v>
+        <v>4372</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>15</v>
@@ -22798,7 +22798,7 @@
         <v>14</v>
       </c>
       <c r="F130" s="2">
-        <v>2890</v>
+        <v>3409</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>15</v>
@@ -22830,7 +22830,7 @@
         <v>14</v>
       </c>
       <c r="F131" s="2">
-        <v>4322</v>
+        <v>2927</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>15</v>
@@ -22862,7 +22862,7 @@
         <v>14</v>
       </c>
       <c r="F132" s="2">
-        <v>3108</v>
+        <v>2451</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>15</v>
@@ -22894,7 +22894,7 @@
         <v>14</v>
       </c>
       <c r="F133" s="2">
-        <v>2667</v>
+        <v>3538</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>15</v>
@@ -22926,7 +22926,7 @@
         <v>14</v>
       </c>
       <c r="F134" s="2">
-        <v>1541</v>
+        <v>4445</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>15</v>
@@ -22958,7 +22958,7 @@
         <v>14</v>
       </c>
       <c r="F135" s="2">
-        <v>1368</v>
+        <v>2518</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>15</v>
@@ -22990,7 +22990,7 @@
         <v>14</v>
       </c>
       <c r="F136" s="2">
-        <v>3345</v>
+        <v>3840</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>15</v>
@@ -23022,7 +23022,7 @@
         <v>14</v>
       </c>
       <c r="F137" s="2">
-        <v>1459</v>
+        <v>4032</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>15</v>
@@ -23054,7 +23054,7 @@
         <v>14</v>
       </c>
       <c r="F138" s="2">
-        <v>2512</v>
+        <v>2369</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>15</v>
@@ -23086,7 +23086,7 @@
         <v>14</v>
       </c>
       <c r="F139" s="2">
-        <v>2499</v>
+        <v>2181</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>15</v>
@@ -23118,7 +23118,7 @@
         <v>14</v>
       </c>
       <c r="F140" s="2">
-        <v>2413</v>
+        <v>3579</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>15</v>
@@ -23150,7 +23150,7 @@
         <v>14</v>
       </c>
       <c r="F141" s="2">
-        <v>893</v>
+        <v>2002</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>15</v>
@@ -23182,7 +23182,7 @@
         <v>14</v>
       </c>
       <c r="F142" s="2">
-        <v>3241</v>
+        <v>2536</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>15</v>
@@ -23214,7 +23214,7 @@
         <v>14</v>
       </c>
       <c r="F143" s="2">
-        <v>3423</v>
+        <v>2653</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>15</v>
@@ -23246,7 +23246,7 @@
         <v>14</v>
       </c>
       <c r="F144" s="2">
-        <v>1202</v>
+        <v>1107</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>15</v>
@@ -23278,7 +23278,7 @@
         <v>14</v>
       </c>
       <c r="F145" s="2">
-        <v>2502</v>
+        <v>2718</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>15</v>
@@ -23310,7 +23310,7 @@
         <v>14</v>
       </c>
       <c r="F146" s="2">
-        <v>3529</v>
+        <v>2123</v>
       </c>
       <c r="G146" s="2" t="s">
         <v>15</v>
@@ -23342,7 +23342,7 @@
         <v>14</v>
       </c>
       <c r="F147" s="2">
-        <v>1682</v>
+        <v>1238</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>15</v>
@@ -23374,7 +23374,7 @@
         <v>14</v>
       </c>
       <c r="F148" s="2">
-        <v>1079</v>
+        <v>2240</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>15</v>
@@ -23406,7 +23406,7 @@
         <v>14</v>
       </c>
       <c r="F149" s="2">
-        <v>1265</v>
+        <v>1961</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>15</v>
@@ -23438,7 +23438,7 @@
         <v>14</v>
       </c>
       <c r="F150" s="2">
-        <v>3113</v>
+        <v>2635</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>15</v>
@@ -23470,7 +23470,7 @@
         <v>14</v>
       </c>
       <c r="F151" s="2">
-        <v>3027</v>
+        <v>1340</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>15</v>
@@ -23502,7 +23502,7 @@
         <v>14</v>
       </c>
       <c r="F152" s="2">
-        <v>4430</v>
+        <v>4740</v>
       </c>
       <c r="G152" s="2" t="s">
         <v>15</v>
@@ -23534,7 +23534,7 @@
         <v>14</v>
       </c>
       <c r="F153" s="2">
-        <v>4783</v>
+        <v>1203</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>15</v>
@@ -23566,7 +23566,7 @@
         <v>14</v>
       </c>
       <c r="F154" s="2">
-        <v>1328</v>
+        <v>3283</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>15</v>
@@ -23598,7 +23598,7 @@
         <v>14</v>
       </c>
       <c r="F155" s="2">
-        <v>3653</v>
+        <v>1351</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>15</v>
@@ -23630,7 +23630,7 @@
         <v>14</v>
       </c>
       <c r="F156" s="2">
-        <v>2509</v>
+        <v>2094</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>15</v>
@@ -23662,7 +23662,7 @@
         <v>14</v>
       </c>
       <c r="F157" s="2">
-        <v>2023</v>
+        <v>814</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>15</v>
@@ -23694,7 +23694,7 @@
         <v>14</v>
       </c>
       <c r="F158" s="2">
-        <v>4246</v>
+        <v>1258</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>15</v>
@@ -23726,7 +23726,7 @@
         <v>14</v>
       </c>
       <c r="F159" s="2">
-        <v>863</v>
+        <v>1813</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>15</v>
@@ -23758,7 +23758,7 @@
         <v>14</v>
       </c>
       <c r="F160" s="2">
-        <v>3546</v>
+        <v>3314</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>15</v>
@@ -23790,7 +23790,7 @@
         <v>14</v>
       </c>
       <c r="F161" s="2">
-        <v>3575</v>
+        <v>1584</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>15</v>
@@ -23822,7 +23822,7 @@
         <v>14</v>
       </c>
       <c r="F162" s="2">
-        <v>1636</v>
+        <v>2403</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>15</v>
@@ -23854,7 +23854,7 @@
         <v>14</v>
       </c>
       <c r="F163" s="2">
-        <v>3138</v>
+        <v>3469</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>15</v>
@@ -23886,7 +23886,7 @@
         <v>14</v>
       </c>
       <c r="F164" s="2">
-        <v>2762</v>
+        <v>3293</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>15</v>
@@ -23918,7 +23918,7 @@
         <v>14</v>
       </c>
       <c r="F165" s="2">
-        <v>1080</v>
+        <v>4196</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>15</v>
@@ -23950,7 +23950,7 @@
         <v>14</v>
       </c>
       <c r="F166" s="2">
-        <v>1409</v>
+        <v>944</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>15</v>
@@ -23982,7 +23982,7 @@
         <v>14</v>
       </c>
       <c r="F167" s="2">
-        <v>3581</v>
+        <v>1797</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>15</v>
@@ -24014,7 +24014,7 @@
         <v>14</v>
       </c>
       <c r="F168" s="2">
-        <v>1618</v>
+        <v>1492</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>15</v>
@@ -24046,7 +24046,7 @@
         <v>14</v>
       </c>
       <c r="F169" s="2">
-        <v>2454</v>
+        <v>2931</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>15</v>
@@ -24078,7 +24078,7 @@
         <v>14</v>
       </c>
       <c r="F170" s="2">
-        <v>3610</v>
+        <v>2666</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>15</v>
@@ -24110,7 +24110,7 @@
         <v>14</v>
       </c>
       <c r="F171" s="2">
-        <v>4719</v>
+        <v>3924</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>15</v>
@@ -24142,7 +24142,7 @@
         <v>14</v>
       </c>
       <c r="F172" s="2">
-        <v>3452</v>
+        <v>2651</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>15</v>
@@ -24174,7 +24174,7 @@
         <v>14</v>
       </c>
       <c r="F173" s="2">
-        <v>2261</v>
+        <v>2475</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>15</v>
@@ -24206,7 +24206,7 @@
         <v>14</v>
       </c>
       <c r="F174" s="2">
-        <v>846</v>
+        <v>3667</v>
       </c>
       <c r="G174" s="2" t="s">
         <v>15</v>
@@ -24238,7 +24238,7 @@
         <v>14</v>
       </c>
       <c r="F175" s="2">
-        <v>2382</v>
+        <v>3400</v>
       </c>
       <c r="G175" s="2" t="s">
         <v>15</v>
@@ -24270,7 +24270,7 @@
         <v>14</v>
       </c>
       <c r="F176" s="2">
-        <v>1067</v>
+        <v>2643</v>
       </c>
       <c r="G176" s="2" t="s">
         <v>15</v>
@@ -24302,7 +24302,7 @@
         <v>14</v>
       </c>
       <c r="F177" s="2">
-        <v>2191</v>
+        <v>2966</v>
       </c>
       <c r="G177" s="2" t="s">
         <v>15</v>
@@ -24334,7 +24334,7 @@
         <v>14</v>
       </c>
       <c r="F178" s="2">
-        <v>1507</v>
+        <v>1222</v>
       </c>
       <c r="G178" s="2" t="s">
         <v>15</v>
@@ -24366,7 +24366,7 @@
         <v>14</v>
       </c>
       <c r="F179" s="2">
-        <v>3017</v>
+        <v>2317</v>
       </c>
       <c r="G179" s="2" t="s">
         <v>15</v>
@@ -24398,7 +24398,7 @@
         <v>14</v>
       </c>
       <c r="F180" s="2">
-        <v>1674</v>
+        <v>3462</v>
       </c>
       <c r="G180" s="2" t="s">
         <v>15</v>
@@ -24430,7 +24430,7 @@
         <v>14</v>
       </c>
       <c r="F181" s="2">
-        <v>1054</v>
+        <v>2051</v>
       </c>
       <c r="G181" s="2" t="s">
         <v>15</v>
@@ -24462,7 +24462,7 @@
         <v>14</v>
       </c>
       <c r="F182" s="2">
-        <v>2958</v>
+        <v>4224</v>
       </c>
       <c r="G182" s="2" t="s">
         <v>15</v>
@@ -24494,7 +24494,7 @@
         <v>14</v>
       </c>
       <c r="F183" s="2">
-        <v>2664</v>
+        <v>1816</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>15</v>
@@ -24526,7 +24526,7 @@
         <v>14</v>
       </c>
       <c r="F184" s="2">
-        <v>1841</v>
+        <v>3432</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>15</v>
@@ -24558,7 +24558,7 @@
         <v>14</v>
       </c>
       <c r="F185" s="2">
-        <v>3179</v>
+        <v>1972</v>
       </c>
       <c r="G185" s="2" t="s">
         <v>15</v>
@@ -24590,7 +24590,7 @@
         <v>14</v>
       </c>
       <c r="F186" s="2">
-        <v>1278</v>
+        <v>1132</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>15</v>
@@ -24622,7 +24622,7 @@
         <v>14</v>
       </c>
       <c r="F187" s="2">
-        <v>4725</v>
+        <v>4209</v>
       </c>
       <c r="G187" s="2" t="s">
         <v>15</v>
@@ -24654,7 +24654,7 @@
         <v>14</v>
       </c>
       <c r="F188" s="2">
-        <v>4792</v>
+        <v>4785</v>
       </c>
       <c r="G188" s="2" t="s">
         <v>15</v>
@@ -24686,7 +24686,7 @@
         <v>14</v>
       </c>
       <c r="F189" s="2">
-        <v>4407</v>
+        <v>2977</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>15</v>
@@ -24718,7 +24718,7 @@
         <v>14</v>
       </c>
       <c r="F190" s="2">
-        <v>2605</v>
+        <v>1136</v>
       </c>
       <c r="G190" s="2" t="s">
         <v>15</v>
@@ -24750,7 +24750,7 @@
         <v>14</v>
       </c>
       <c r="F191" s="2">
-        <v>3903</v>
+        <v>2615</v>
       </c>
       <c r="G191" s="2" t="s">
         <v>15</v>
@@ -24782,7 +24782,7 @@
         <v>14</v>
       </c>
       <c r="F192" s="2">
-        <v>4345</v>
+        <v>1022</v>
       </c>
       <c r="G192" s="2" t="s">
         <v>15</v>
@@ -24814,7 +24814,7 @@
         <v>14</v>
       </c>
       <c r="F193" s="2">
-        <v>3974</v>
+        <v>3358</v>
       </c>
       <c r="G193" s="2" t="s">
         <v>15</v>
@@ -24846,7 +24846,7 @@
         <v>14</v>
       </c>
       <c r="F194" s="2">
-        <v>4532</v>
+        <v>2445</v>
       </c>
       <c r="G194" s="2" t="s">
         <v>15</v>
@@ -24878,7 +24878,7 @@
         <v>14</v>
       </c>
       <c r="F195" s="2">
-        <v>1673</v>
+        <v>4392</v>
       </c>
       <c r="G195" s="2" t="s">
         <v>15</v>
@@ -24910,7 +24910,7 @@
         <v>14</v>
       </c>
       <c r="F196" s="2">
-        <v>1462</v>
+        <v>4593</v>
       </c>
       <c r="G196" s="2" t="s">
         <v>15</v>
@@ -24942,7 +24942,7 @@
         <v>14</v>
       </c>
       <c r="F197" s="2">
-        <v>4539</v>
+        <v>2144</v>
       </c>
       <c r="G197" s="2" t="s">
         <v>15</v>
@@ -24974,7 +24974,7 @@
         <v>14</v>
       </c>
       <c r="F198" s="2">
-        <v>1081</v>
+        <v>2268</v>
       </c>
       <c r="G198" s="2" t="s">
         <v>15</v>
@@ -25006,7 +25006,7 @@
         <v>14</v>
       </c>
       <c r="F199" s="2">
-        <v>4648</v>
+        <v>4321</v>
       </c>
       <c r="G199" s="2" t="s">
         <v>15</v>
@@ -25038,7 +25038,7 @@
         <v>14</v>
       </c>
       <c r="F200" s="2">
-        <v>3024</v>
+        <v>1197</v>
       </c>
       <c r="G200" s="2" t="s">
         <v>15</v>
@@ -25070,7 +25070,7 @@
         <v>14</v>
       </c>
       <c r="F201" s="2">
-        <v>818</v>
+        <v>975</v>
       </c>
       <c r="G201" s="2" t="s">
         <v>15</v>
@@ -25102,7 +25102,7 @@
         <v>14</v>
       </c>
       <c r="F202" s="2">
-        <v>1848</v>
+        <v>4517</v>
       </c>
       <c r="G202" s="2" t="s">
         <v>15</v>
@@ -25134,7 +25134,7 @@
         <v>14</v>
       </c>
       <c r="F203" s="2">
-        <v>1482</v>
+        <v>2038</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>15</v>
@@ -25166,7 +25166,7 @@
         <v>14</v>
       </c>
       <c r="F204" s="2">
-        <v>1764</v>
+        <v>2756</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>15</v>
@@ -25230,7 +25230,7 @@
         <v>14</v>
       </c>
       <c r="F206" s="2">
-        <v>1839</v>
+        <v>1704</v>
       </c>
       <c r="G206" s="2" t="s">
         <v>15</v>
@@ -25262,7 +25262,7 @@
         <v>14</v>
       </c>
       <c r="F207" s="2">
-        <v>4118</v>
+        <v>2133</v>
       </c>
       <c r="G207" s="2" t="s">
         <v>15</v>
@@ -25294,7 +25294,7 @@
         <v>14</v>
       </c>
       <c r="F208" s="2">
-        <v>4104</v>
+        <v>3983</v>
       </c>
       <c r="G208" s="2" t="s">
         <v>15</v>
@@ -25326,7 +25326,7 @@
         <v>14</v>
       </c>
       <c r="F209" s="2">
-        <v>1476</v>
+        <v>3370</v>
       </c>
       <c r="G209" s="2" t="s">
         <v>15</v>
@@ -25358,7 +25358,7 @@
         <v>14</v>
       </c>
       <c r="F210" s="2">
-        <v>4749</v>
+        <v>933</v>
       </c>
       <c r="G210" s="2" t="s">
         <v>15</v>
@@ -25390,7 +25390,7 @@
         <v>14</v>
       </c>
       <c r="F211" s="2">
-        <v>1958</v>
+        <v>1531</v>
       </c>
       <c r="G211" s="2" t="s">
         <v>15</v>
@@ -25422,7 +25422,7 @@
         <v>14</v>
       </c>
       <c r="F212" s="2">
-        <v>3187</v>
+        <v>1057</v>
       </c>
       <c r="G212" s="2" t="s">
         <v>15</v>
@@ -25454,7 +25454,7 @@
         <v>14</v>
       </c>
       <c r="F213" s="2">
-        <v>3028</v>
+        <v>4423</v>
       </c>
       <c r="G213" s="2" t="s">
         <v>15</v>
@@ -25486,7 +25486,7 @@
         <v>14</v>
       </c>
       <c r="F214" s="2">
-        <v>1288</v>
+        <v>1144</v>
       </c>
       <c r="G214" s="2" t="s">
         <v>15</v>
@@ -25518,7 +25518,7 @@
         <v>14</v>
       </c>
       <c r="F215" s="2">
-        <v>1057</v>
+        <v>1102</v>
       </c>
       <c r="G215" s="2" t="s">
         <v>15</v>
@@ -25550,7 +25550,7 @@
         <v>14</v>
       </c>
       <c r="F216" s="2">
-        <v>964</v>
+        <v>2868</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>15</v>
@@ -25582,7 +25582,7 @@
         <v>14</v>
       </c>
       <c r="F217" s="2">
-        <v>4318</v>
+        <v>1840</v>
       </c>
       <c r="G217" s="2" t="s">
         <v>15</v>
@@ -25614,7 +25614,7 @@
         <v>14</v>
       </c>
       <c r="F218" s="2">
-        <v>3674</v>
+        <v>3010</v>
       </c>
       <c r="G218" s="2" t="s">
         <v>15</v>
@@ -25646,7 +25646,7 @@
         <v>14</v>
       </c>
       <c r="F219" s="2">
-        <v>1994</v>
+        <v>1208</v>
       </c>
       <c r="G219" s="2" t="s">
         <v>15</v>
@@ -25678,7 +25678,7 @@
         <v>14</v>
       </c>
       <c r="F220" s="2">
-        <v>1931</v>
+        <v>4034</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>15</v>
@@ -25710,7 +25710,7 @@
         <v>14</v>
       </c>
       <c r="F221" s="2">
-        <v>2212</v>
+        <v>2400</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>15</v>
@@ -25742,7 +25742,7 @@
         <v>14</v>
       </c>
       <c r="F222" s="2">
-        <v>3780</v>
+        <v>2937</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>15</v>
@@ -25774,7 +25774,7 @@
         <v>14</v>
       </c>
       <c r="F223" s="2">
-        <v>1455</v>
+        <v>2430</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>15</v>
@@ -25806,7 +25806,7 @@
         <v>14</v>
       </c>
       <c r="F224" s="2">
-        <v>2164</v>
+        <v>4234</v>
       </c>
       <c r="G224" s="2" t="s">
         <v>15</v>
@@ -25838,7 +25838,7 @@
         <v>14</v>
       </c>
       <c r="F225" s="2">
-        <v>2408</v>
+        <v>1923</v>
       </c>
       <c r="G225" s="2" t="s">
         <v>15</v>
@@ -25870,7 +25870,7 @@
         <v>14</v>
       </c>
       <c r="F226" s="2">
-        <v>1028</v>
+        <v>3039</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>15</v>
@@ -25902,7 +25902,7 @@
         <v>14</v>
       </c>
       <c r="F227" s="2">
-        <v>3013</v>
+        <v>1060</v>
       </c>
       <c r="G227" s="2" t="s">
         <v>15</v>
@@ -25934,7 +25934,7 @@
         <v>14</v>
       </c>
       <c r="F228" s="2">
-        <v>1034</v>
+        <v>3425</v>
       </c>
       <c r="G228" s="2" t="s">
         <v>15</v>
@@ -25966,7 +25966,7 @@
         <v>14</v>
       </c>
       <c r="F229" s="2">
-        <v>858</v>
+        <v>3193</v>
       </c>
       <c r="G229" s="2" t="s">
         <v>15</v>
@@ -25998,7 +25998,7 @@
         <v>14</v>
       </c>
       <c r="F230" s="2">
-        <v>3952</v>
+        <v>3725</v>
       </c>
       <c r="G230" s="2" t="s">
         <v>15</v>
@@ -26030,7 +26030,7 @@
         <v>14</v>
       </c>
       <c r="F231" s="2">
-        <v>2413</v>
+        <v>4339</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>15</v>
@@ -26062,7 +26062,7 @@
         <v>14</v>
       </c>
       <c r="F232" s="2">
-        <v>3285</v>
+        <v>4740</v>
       </c>
       <c r="G232" s="2" t="s">
         <v>15</v>
@@ -26094,7 +26094,7 @@
         <v>14</v>
       </c>
       <c r="F233" s="2">
-        <v>2752</v>
+        <v>2633</v>
       </c>
       <c r="G233" s="2" t="s">
         <v>15</v>
@@ -26126,7 +26126,7 @@
         <v>14</v>
       </c>
       <c r="F234" s="2">
-        <v>3537</v>
+        <v>2102</v>
       </c>
       <c r="G234" s="2" t="s">
         <v>15</v>
@@ -26158,7 +26158,7 @@
         <v>14</v>
       </c>
       <c r="F235" s="2">
-        <v>1559</v>
+        <v>4369</v>
       </c>
       <c r="G235" s="2" t="s">
         <v>15</v>
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="F236" s="2">
-        <v>1644</v>
+        <v>1109</v>
       </c>
       <c r="G236" s="2" t="s">
         <v>15</v>
@@ -26222,7 +26222,7 @@
         <v>14</v>
       </c>
       <c r="F237" s="2">
-        <v>3506</v>
+        <v>1987</v>
       </c>
       <c r="G237" s="2" t="s">
         <v>15</v>
@@ -26254,7 +26254,7 @@
         <v>14</v>
       </c>
       <c r="F238" s="2">
-        <v>1912</v>
+        <v>1886</v>
       </c>
       <c r="G238" s="2" t="s">
         <v>15</v>
@@ -26286,7 +26286,7 @@
         <v>14</v>
       </c>
       <c r="F239" s="2">
-        <v>1052</v>
+        <v>3965</v>
       </c>
       <c r="G239" s="2" t="s">
         <v>15</v>
@@ -26318,7 +26318,7 @@
         <v>14</v>
       </c>
       <c r="F240" s="2">
-        <v>4661</v>
+        <v>4607</v>
       </c>
       <c r="G240" s="2" t="s">
         <v>15</v>
@@ -26350,7 +26350,7 @@
         <v>14</v>
       </c>
       <c r="F241" s="2">
-        <v>1181</v>
+        <v>4171</v>
       </c>
       <c r="G241" s="2" t="s">
         <v>15</v>
@@ -26382,7 +26382,7 @@
         <v>14</v>
       </c>
       <c r="F242" s="2">
-        <v>3486</v>
+        <v>1617</v>
       </c>
       <c r="G242" s="2" t="s">
         <v>15</v>
@@ -26414,7 +26414,7 @@
         <v>14</v>
       </c>
       <c r="F243" s="2">
-        <v>2477</v>
+        <v>2792</v>
       </c>
       <c r="G243" s="2" t="s">
         <v>15</v>
@@ -26446,7 +26446,7 @@
         <v>14</v>
       </c>
       <c r="F244" s="2">
-        <v>1643</v>
+        <v>978</v>
       </c>
       <c r="G244" s="2" t="s">
         <v>15</v>
@@ -26478,7 +26478,7 @@
         <v>14</v>
       </c>
       <c r="F245" s="2">
-        <v>3814</v>
+        <v>3576</v>
       </c>
       <c r="G245" s="2" t="s">
         <v>15</v>
@@ -26510,7 +26510,7 @@
         <v>14</v>
       </c>
       <c r="F246" s="2">
-        <v>1133</v>
+        <v>3953</v>
       </c>
       <c r="G246" s="2" t="s">
         <v>15</v>
@@ -26542,7 +26542,7 @@
         <v>14</v>
       </c>
       <c r="F247" s="2">
-        <v>2339</v>
+        <v>3079</v>
       </c>
       <c r="G247" s="2" t="s">
         <v>15</v>
@@ -26574,7 +26574,7 @@
         <v>14</v>
       </c>
       <c r="F248" s="2">
-        <v>3781</v>
+        <v>3375</v>
       </c>
       <c r="G248" s="2" t="s">
         <v>15</v>
@@ -26606,7 +26606,7 @@
         <v>14</v>
       </c>
       <c r="F249" s="2">
-        <v>2639</v>
+        <v>1128</v>
       </c>
       <c r="G249" s="2" t="s">
         <v>15</v>
@@ -26638,7 +26638,7 @@
         <v>14</v>
       </c>
       <c r="F250" s="2">
-        <v>3944</v>
+        <v>2462</v>
       </c>
       <c r="G250" s="2" t="s">
         <v>15</v>
@@ -26670,7 +26670,7 @@
         <v>14</v>
       </c>
       <c r="F251" s="2">
-        <v>2707</v>
+        <v>1015</v>
       </c>
       <c r="G251" s="2" t="s">
         <v>15</v>
@@ -26702,7 +26702,7 @@
         <v>14</v>
       </c>
       <c r="F252" s="2">
-        <v>1872</v>
+        <v>4616</v>
       </c>
       <c r="G252" s="2" t="s">
         <v>15</v>
@@ -26734,7 +26734,7 @@
         <v>14</v>
       </c>
       <c r="F253" s="2">
-        <v>3722</v>
+        <v>2901</v>
       </c>
       <c r="G253" s="2" t="s">
         <v>15</v>
@@ -26766,7 +26766,7 @@
         <v>14</v>
       </c>
       <c r="F254" s="2">
-        <v>2945</v>
+        <v>4322</v>
       </c>
       <c r="G254" s="2" t="s">
         <v>15</v>
@@ -26798,7 +26798,7 @@
         <v>14</v>
       </c>
       <c r="F255" s="2">
-        <v>2020</v>
+        <v>4273</v>
       </c>
       <c r="G255" s="2" t="s">
         <v>15</v>
@@ -26830,7 +26830,7 @@
         <v>14</v>
       </c>
       <c r="F256" s="2">
-        <v>1683</v>
+        <v>919</v>
       </c>
       <c r="G256" s="2" t="s">
         <v>15</v>
@@ -26862,7 +26862,7 @@
         <v>14</v>
       </c>
       <c r="F257" s="2">
-        <v>1329</v>
+        <v>804</v>
       </c>
       <c r="G257" s="2" t="s">
         <v>15</v>
@@ -26894,7 +26894,7 @@
         <v>14</v>
       </c>
       <c r="F258" s="2">
-        <v>3400</v>
+        <v>3160</v>
       </c>
       <c r="G258" s="2" t="s">
         <v>15</v>
@@ -26926,7 +26926,7 @@
         <v>14</v>
       </c>
       <c r="F259" s="2">
-        <v>4420</v>
+        <v>4237</v>
       </c>
       <c r="G259" s="2" t="s">
         <v>15</v>
@@ -26958,7 +26958,7 @@
         <v>14</v>
       </c>
       <c r="F260" s="2">
-        <v>3904</v>
+        <v>2191</v>
       </c>
       <c r="G260" s="2" t="s">
         <v>15</v>
@@ -26990,7 +26990,7 @@
         <v>14</v>
       </c>
       <c r="F261" s="2">
-        <v>3856</v>
+        <v>1739</v>
       </c>
       <c r="G261" s="2" t="s">
         <v>15</v>
@@ -27022,7 +27022,7 @@
         <v>14</v>
       </c>
       <c r="F262" s="2">
-        <v>4349</v>
+        <v>4758</v>
       </c>
       <c r="G262" s="2" t="s">
         <v>15</v>
@@ -27054,7 +27054,7 @@
         <v>14</v>
       </c>
       <c r="F263" s="2">
-        <v>3901</v>
+        <v>927</v>
       </c>
       <c r="G263" s="2" t="s">
         <v>15</v>
@@ -27086,7 +27086,7 @@
         <v>14</v>
       </c>
       <c r="F264" s="2">
-        <v>3625</v>
+        <v>1431</v>
       </c>
       <c r="G264" s="2" t="s">
         <v>15</v>
@@ -27118,7 +27118,7 @@
         <v>14</v>
       </c>
       <c r="F265" s="2">
-        <v>911</v>
+        <v>826</v>
       </c>
       <c r="G265" s="2" t="s">
         <v>15</v>
@@ -27150,7 +27150,7 @@
         <v>14</v>
       </c>
       <c r="F266" s="2">
-        <v>2349</v>
+        <v>822</v>
       </c>
       <c r="G266" s="2" t="s">
         <v>15</v>
@@ -27182,7 +27182,7 @@
         <v>14</v>
       </c>
       <c r="F267" s="2">
-        <v>828</v>
+        <v>4296</v>
       </c>
       <c r="G267" s="2" t="s">
         <v>15</v>
@@ -27214,7 +27214,7 @@
         <v>14</v>
       </c>
       <c r="F268" s="2">
-        <v>3941</v>
+        <v>2582</v>
       </c>
       <c r="G268" s="2" t="s">
         <v>15</v>
@@ -27246,7 +27246,7 @@
         <v>14</v>
       </c>
       <c r="F269" s="2">
-        <v>3232</v>
+        <v>2330</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>15</v>
@@ -27278,7 +27278,7 @@
         <v>14</v>
       </c>
       <c r="F270" s="2">
-        <v>1042</v>
+        <v>841</v>
       </c>
       <c r="G270" s="2" t="s">
         <v>15</v>
@@ -27310,7 +27310,7 @@
         <v>14</v>
       </c>
       <c r="F271" s="2">
-        <v>1553</v>
+        <v>2716</v>
       </c>
       <c r="G271" s="2" t="s">
         <v>15</v>
@@ -27342,7 +27342,7 @@
         <v>14</v>
       </c>
       <c r="F272" s="2">
-        <v>4474</v>
+        <v>957</v>
       </c>
       <c r="G272" s="2" t="s">
         <v>15</v>
@@ -27374,7 +27374,7 @@
         <v>14</v>
       </c>
       <c r="F273" s="2">
-        <v>923</v>
+        <v>2933</v>
       </c>
       <c r="G273" s="2" t="s">
         <v>15</v>
@@ -27406,7 +27406,7 @@
         <v>14</v>
       </c>
       <c r="F274" s="2">
-        <v>4132</v>
+        <v>3488</v>
       </c>
       <c r="G274" s="2" t="s">
         <v>15</v>
@@ -27438,7 +27438,7 @@
         <v>14</v>
       </c>
       <c r="F275" s="2">
-        <v>1090</v>
+        <v>3097</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>15</v>
@@ -27470,7 +27470,7 @@
         <v>14</v>
       </c>
       <c r="F276" s="2">
-        <v>4000</v>
+        <v>2739</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>15</v>
@@ -27502,7 +27502,7 @@
         <v>14</v>
       </c>
       <c r="F277" s="2">
-        <v>1958</v>
+        <v>4751</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>15</v>
@@ -27534,7 +27534,7 @@
         <v>14</v>
       </c>
       <c r="F278" s="2">
-        <v>2854</v>
+        <v>4024</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>15</v>
@@ -27566,7 +27566,7 @@
         <v>14</v>
       </c>
       <c r="F279" s="2">
-        <v>2261</v>
+        <v>2100</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>15</v>
@@ -27598,7 +27598,7 @@
         <v>14</v>
       </c>
       <c r="F280" s="2">
-        <v>1738</v>
+        <v>2890</v>
       </c>
       <c r="G280" s="2" t="s">
         <v>15</v>
@@ -27630,7 +27630,7 @@
         <v>14</v>
       </c>
       <c r="F281" s="2">
-        <v>3177</v>
+        <v>2401</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>15</v>
@@ -27662,7 +27662,7 @@
         <v>14</v>
       </c>
       <c r="F282" s="2">
-        <v>2583</v>
+        <v>4060</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>15</v>
@@ -27694,7 +27694,7 @@
         <v>14</v>
       </c>
       <c r="F283" s="2">
-        <v>4479</v>
+        <v>3708</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>15</v>
@@ -27726,7 +27726,7 @@
         <v>14</v>
       </c>
       <c r="F284" s="2">
-        <v>1954</v>
+        <v>3251</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>15</v>
@@ -27758,7 +27758,7 @@
         <v>14</v>
       </c>
       <c r="F285" s="2">
-        <v>3387</v>
+        <v>4463</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>15</v>
@@ -27790,7 +27790,7 @@
         <v>14</v>
       </c>
       <c r="F286" s="2">
-        <v>4756</v>
+        <v>4621</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>15</v>
@@ -27822,7 +27822,7 @@
         <v>14</v>
       </c>
       <c r="F287" s="2">
-        <v>1687</v>
+        <v>3086</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>15</v>
@@ -27854,7 +27854,7 @@
         <v>14</v>
       </c>
       <c r="F288" s="2">
-        <v>1739</v>
+        <v>4028</v>
       </c>
       <c r="G288" s="2" t="s">
         <v>15</v>
@@ -27886,7 +27886,7 @@
         <v>14</v>
       </c>
       <c r="F289" s="2">
-        <v>3477</v>
+        <v>1177</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>15</v>
@@ -27918,7 +27918,7 @@
         <v>14</v>
       </c>
       <c r="F290" s="2">
-        <v>840</v>
+        <v>4298</v>
       </c>
       <c r="G290" s="2" t="s">
         <v>15</v>
@@ -27950,7 +27950,7 @@
         <v>14</v>
       </c>
       <c r="F291" s="2">
-        <v>3441</v>
+        <v>1251</v>
       </c>
       <c r="G291" s="2" t="s">
         <v>15</v>
@@ -27982,7 +27982,7 @@
         <v>14</v>
       </c>
       <c r="F292" s="2">
-        <v>4664</v>
+        <v>4263</v>
       </c>
       <c r="G292" s="2" t="s">
         <v>15</v>
@@ -28014,7 +28014,7 @@
         <v>14</v>
       </c>
       <c r="F293" s="2">
-        <v>4124</v>
+        <v>4292</v>
       </c>
       <c r="G293" s="2" t="s">
         <v>15</v>
@@ -28046,7 +28046,7 @@
         <v>14</v>
       </c>
       <c r="F294" s="2">
-        <v>1289</v>
+        <v>1784</v>
       </c>
       <c r="G294" s="2" t="s">
         <v>15</v>
@@ -28078,7 +28078,7 @@
         <v>14</v>
       </c>
       <c r="F295" s="2">
-        <v>3043</v>
+        <v>2427</v>
       </c>
       <c r="G295" s="2" t="s">
         <v>15</v>
@@ -28110,7 +28110,7 @@
         <v>14</v>
       </c>
       <c r="F296" s="2">
-        <v>4441</v>
+        <v>2227</v>
       </c>
       <c r="G296" s="2" t="s">
         <v>15</v>
@@ -28142,7 +28142,7 @@
         <v>14</v>
       </c>
       <c r="F297" s="2">
-        <v>1771</v>
+        <v>3599</v>
       </c>
       <c r="G297" s="2" t="s">
         <v>15</v>
@@ -28174,7 +28174,7 @@
         <v>14</v>
       </c>
       <c r="F298" s="2">
-        <v>4137</v>
+        <v>3154</v>
       </c>
       <c r="G298" s="2" t="s">
         <v>15</v>
@@ -28206,7 +28206,7 @@
         <v>14</v>
       </c>
       <c r="F299" s="2">
-        <v>3594</v>
+        <v>1437</v>
       </c>
       <c r="G299" s="2" t="s">
         <v>15</v>
@@ -28238,7 +28238,7 @@
         <v>14</v>
       </c>
       <c r="F300" s="2">
-        <v>2115</v>
+        <v>2150</v>
       </c>
       <c r="G300" s="2" t="s">
         <v>15</v>
@@ -28270,7 +28270,7 @@
         <v>14</v>
       </c>
       <c r="F301" s="2">
-        <v>2495</v>
+        <v>1423</v>
       </c>
       <c r="G301" s="2" t="s">
         <v>15</v>
@@ -28302,7 +28302,7 @@
         <v>14</v>
       </c>
       <c r="F302" s="2">
-        <v>2165</v>
+        <v>1728</v>
       </c>
       <c r="G302" s="2" t="s">
         <v>15</v>
@@ -28334,7 +28334,7 @@
         <v>14</v>
       </c>
       <c r="F303" s="2">
-        <v>2229</v>
+        <v>3828</v>
       </c>
       <c r="G303" s="2" t="s">
         <v>15</v>
@@ -28366,7 +28366,7 @@
         <v>14</v>
       </c>
       <c r="F304" s="2">
-        <v>4158</v>
+        <v>4453</v>
       </c>
       <c r="G304" s="2" t="s">
         <v>15</v>
@@ -28398,7 +28398,7 @@
         <v>14</v>
       </c>
       <c r="F305" s="2">
-        <v>949</v>
+        <v>2150</v>
       </c>
       <c r="G305" s="2" t="s">
         <v>15</v>
@@ -28430,7 +28430,7 @@
         <v>14</v>
       </c>
       <c r="F306" s="2">
-        <v>3715</v>
+        <v>2421</v>
       </c>
       <c r="G306" s="2" t="s">
         <v>15</v>
@@ -28462,7 +28462,7 @@
         <v>14</v>
       </c>
       <c r="F307" s="2">
-        <v>829</v>
+        <v>2536</v>
       </c>
       <c r="G307" s="2" t="s">
         <v>15</v>
@@ -28494,7 +28494,7 @@
         <v>14</v>
       </c>
       <c r="F308" s="2">
-        <v>3955</v>
+        <v>3369</v>
       </c>
       <c r="G308" s="2" t="s">
         <v>15</v>
@@ -28526,7 +28526,7 @@
         <v>14</v>
       </c>
       <c r="F309" s="2">
-        <v>2882</v>
+        <v>2054</v>
       </c>
       <c r="G309" s="2" t="s">
         <v>15</v>
@@ -28558,7 +28558,7 @@
         <v>14</v>
       </c>
       <c r="F310" s="2">
-        <v>3280</v>
+        <v>1453</v>
       </c>
       <c r="G310" s="2" t="s">
         <v>15</v>
@@ -28590,7 +28590,7 @@
         <v>14</v>
       </c>
       <c r="F311" s="2">
-        <v>3810</v>
+        <v>4335</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>15</v>
@@ -28622,7 +28622,7 @@
         <v>14</v>
       </c>
       <c r="F312" s="2">
-        <v>4414</v>
+        <v>1619</v>
       </c>
       <c r="G312" s="2" t="s">
         <v>15</v>
@@ -28654,7 +28654,7 @@
         <v>14</v>
       </c>
       <c r="F313" s="2">
-        <v>3826</v>
+        <v>4763</v>
       </c>
       <c r="G313" s="2" t="s">
         <v>15</v>
@@ -28686,7 +28686,7 @@
         <v>14</v>
       </c>
       <c r="F314" s="2">
-        <v>3437</v>
+        <v>1616</v>
       </c>
       <c r="G314" s="2" t="s">
         <v>15</v>
@@ -28718,7 +28718,7 @@
         <v>14</v>
       </c>
       <c r="F315" s="2">
-        <v>1931</v>
+        <v>2152</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>15</v>
@@ -28750,7 +28750,7 @@
         <v>14</v>
       </c>
       <c r="F316" s="2">
-        <v>2056</v>
+        <v>3690</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>15</v>
@@ -28782,7 +28782,7 @@
         <v>14</v>
       </c>
       <c r="F317" s="2">
-        <v>3391</v>
+        <v>3352</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>15</v>
@@ -28814,7 +28814,7 @@
         <v>14</v>
       </c>
       <c r="F318" s="2">
-        <v>2476</v>
+        <v>3335</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>15</v>
@@ -28846,7 +28846,7 @@
         <v>14</v>
       </c>
       <c r="F319" s="2">
-        <v>2682</v>
+        <v>1542</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>15</v>
@@ -28878,7 +28878,7 @@
         <v>14</v>
       </c>
       <c r="F320" s="2">
-        <v>4568</v>
+        <v>3315</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>15</v>
@@ -28910,7 +28910,7 @@
         <v>14</v>
       </c>
       <c r="F321" s="2">
-        <v>2025</v>
+        <v>2416</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>15</v>
@@ -28942,7 +28942,7 @@
         <v>14</v>
       </c>
       <c r="F322" s="2">
-        <v>2503</v>
+        <v>1375</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>15</v>
@@ -28974,7 +28974,7 @@
         <v>14</v>
       </c>
       <c r="F323" s="2">
-        <v>3863</v>
+        <v>4729</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>15</v>
@@ -29006,7 +29006,7 @@
         <v>14</v>
       </c>
       <c r="F324" s="2">
-        <v>1455</v>
+        <v>4734</v>
       </c>
       <c r="G324" s="2" t="s">
         <v>15</v>
@@ -29038,7 +29038,7 @@
         <v>14</v>
       </c>
       <c r="F325" s="2">
-        <v>2662</v>
+        <v>2035</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>15</v>
@@ -29070,7 +29070,7 @@
         <v>14</v>
       </c>
       <c r="F326" s="2">
-        <v>1979</v>
+        <v>3742</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>15</v>
@@ -29102,7 +29102,7 @@
         <v>14</v>
       </c>
       <c r="F327" s="2">
-        <v>3249</v>
+        <v>1745</v>
       </c>
       <c r="G327" s="2" t="s">
         <v>15</v>
@@ -29134,7 +29134,7 @@
         <v>14</v>
       </c>
       <c r="F328" s="2">
-        <v>2585</v>
+        <v>800</v>
       </c>
       <c r="G328" s="2" t="s">
         <v>15</v>
@@ -29166,7 +29166,7 @@
         <v>14</v>
       </c>
       <c r="F329" s="2">
-        <v>1308</v>
+        <v>3318</v>
       </c>
       <c r="G329" s="2" t="s">
         <v>15</v>
@@ -29198,7 +29198,7 @@
         <v>14</v>
       </c>
       <c r="F330" s="2">
-        <v>3080</v>
+        <v>3474</v>
       </c>
       <c r="G330" s="2" t="s">
         <v>15</v>
@@ -29230,7 +29230,7 @@
         <v>14</v>
       </c>
       <c r="F331" s="2">
-        <v>3404</v>
+        <v>4340</v>
       </c>
       <c r="G331" s="2" t="s">
         <v>15</v>
@@ -29262,7 +29262,7 @@
         <v>14</v>
       </c>
       <c r="F332" s="2">
-        <v>2777</v>
+        <v>3273</v>
       </c>
       <c r="G332" s="2" t="s">
         <v>15</v>
@@ -29294,7 +29294,7 @@
         <v>14</v>
       </c>
       <c r="F333" s="2">
-        <v>1403</v>
+        <v>3067</v>
       </c>
       <c r="G333" s="2" t="s">
         <v>15</v>
@@ -29326,7 +29326,7 @@
         <v>14</v>
       </c>
       <c r="F334" s="2">
-        <v>3608</v>
+        <v>2701</v>
       </c>
       <c r="G334" s="2" t="s">
         <v>15</v>
@@ -29358,7 +29358,7 @@
         <v>14</v>
       </c>
       <c r="F335" s="2">
-        <v>3822</v>
+        <v>4780</v>
       </c>
       <c r="G335" s="2" t="s">
         <v>15</v>
@@ -29390,7 +29390,7 @@
         <v>14</v>
       </c>
       <c r="F336" s="2">
-        <v>2987</v>
+        <v>816</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>15</v>
@@ -29422,7 +29422,7 @@
         <v>14</v>
       </c>
       <c r="F337" s="2">
-        <v>3325</v>
+        <v>1903</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>15</v>
@@ -29454,7 +29454,7 @@
         <v>14</v>
       </c>
       <c r="F338" s="2">
-        <v>3894</v>
+        <v>3473</v>
       </c>
       <c r="G338" s="2" t="s">
         <v>15</v>
@@ -29486,7 +29486,7 @@
         <v>14</v>
       </c>
       <c r="F339" s="2">
-        <v>1303</v>
+        <v>2179</v>
       </c>
       <c r="G339" s="2" t="s">
         <v>15</v>
@@ -29518,7 +29518,7 @@
         <v>14</v>
       </c>
       <c r="F340" s="2">
-        <v>3277</v>
+        <v>1645</v>
       </c>
       <c r="G340" s="2" t="s">
         <v>15</v>
@@ -29550,7 +29550,7 @@
         <v>14</v>
       </c>
       <c r="F341" s="2">
-        <v>3713</v>
+        <v>1821</v>
       </c>
       <c r="G341" s="2" t="s">
         <v>15</v>
@@ -29582,7 +29582,7 @@
         <v>14</v>
       </c>
       <c r="F342" s="2">
-        <v>1455</v>
+        <v>4539</v>
       </c>
       <c r="G342" s="2" t="s">
         <v>15</v>
@@ -29614,7 +29614,7 @@
         <v>14</v>
       </c>
       <c r="F343" s="2">
-        <v>4625</v>
+        <v>1727</v>
       </c>
       <c r="G343" s="2" t="s">
         <v>15</v>
@@ -29646,7 +29646,7 @@
         <v>14</v>
       </c>
       <c r="F344" s="2">
-        <v>3979</v>
+        <v>1231</v>
       </c>
       <c r="G344" s="2" t="s">
         <v>15</v>
@@ -29678,7 +29678,7 @@
         <v>14</v>
       </c>
       <c r="F345" s="2">
-        <v>843</v>
+        <v>3085</v>
       </c>
       <c r="G345" s="2" t="s">
         <v>15</v>
@@ -29710,7 +29710,7 @@
         <v>14</v>
       </c>
       <c r="F346" s="2">
-        <v>2908</v>
+        <v>2070</v>
       </c>
       <c r="G346" s="2" t="s">
         <v>15</v>
@@ -29742,7 +29742,7 @@
         <v>14</v>
       </c>
       <c r="F347" s="2">
-        <v>4068</v>
+        <v>2552</v>
       </c>
       <c r="G347" s="2" t="s">
         <v>15</v>
@@ -29774,7 +29774,7 @@
         <v>14</v>
       </c>
       <c r="F348" s="2">
-        <v>919</v>
+        <v>1087</v>
       </c>
       <c r="G348" s="2" t="s">
         <v>15</v>
@@ -29806,7 +29806,7 @@
         <v>14</v>
       </c>
       <c r="F349" s="2">
-        <v>3815</v>
+        <v>3983</v>
       </c>
       <c r="G349" s="2" t="s">
         <v>15</v>
@@ -29838,7 +29838,7 @@
         <v>14</v>
       </c>
       <c r="F350" s="2">
-        <v>4139</v>
+        <v>4194</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>15</v>
@@ -29870,7 +29870,7 @@
         <v>14</v>
       </c>
       <c r="F351" s="2">
-        <v>2892</v>
+        <v>3891</v>
       </c>
       <c r="G351" s="2" t="s">
         <v>15</v>
@@ -29902,7 +29902,7 @@
         <v>14</v>
       </c>
       <c r="F352" s="2">
-        <v>4710</v>
+        <v>2723</v>
       </c>
       <c r="G352" s="2" t="s">
         <v>15</v>
@@ -29934,7 +29934,7 @@
         <v>14</v>
       </c>
       <c r="F353" s="2">
-        <v>3492</v>
+        <v>2547</v>
       </c>
       <c r="G353" s="2" t="s">
         <v>15</v>
@@ -29966,7 +29966,7 @@
         <v>14</v>
       </c>
       <c r="F354" s="2">
-        <v>4176</v>
+        <v>3323</v>
       </c>
       <c r="G354" s="2" t="s">
         <v>15</v>
@@ -29998,7 +29998,7 @@
         <v>14</v>
       </c>
       <c r="F355" s="2">
-        <v>1360</v>
+        <v>2343</v>
       </c>
       <c r="G355" s="2" t="s">
         <v>15</v>
@@ -30030,7 +30030,7 @@
         <v>14</v>
       </c>
       <c r="F356" s="2">
-        <v>910</v>
+        <v>2047</v>
       </c>
       <c r="G356" s="2" t="s">
         <v>15</v>
@@ -30062,7 +30062,7 @@
         <v>14</v>
       </c>
       <c r="F357" s="2">
-        <v>1577</v>
+        <v>4203</v>
       </c>
       <c r="G357" s="2" t="s">
         <v>15</v>
@@ -30094,7 +30094,7 @@
         <v>14</v>
       </c>
       <c r="F358" s="2">
-        <v>3856</v>
+        <v>2190</v>
       </c>
       <c r="G358" s="2" t="s">
         <v>15</v>
@@ -30126,7 +30126,7 @@
         <v>14</v>
       </c>
       <c r="F359" s="2">
-        <v>1140</v>
+        <v>3093</v>
       </c>
       <c r="G359" s="2" t="s">
         <v>15</v>
@@ -30158,7 +30158,7 @@
         <v>14</v>
       </c>
       <c r="F360" s="2">
-        <v>3564</v>
+        <v>4557</v>
       </c>
       <c r="G360" s="2" t="s">
         <v>15</v>
@@ -30190,7 +30190,7 @@
         <v>14</v>
       </c>
       <c r="F361" s="2">
-        <v>4477</v>
+        <v>2738</v>
       </c>
       <c r="G361" s="2" t="s">
         <v>15</v>
@@ -30222,7 +30222,7 @@
         <v>14</v>
       </c>
       <c r="F362" s="2">
-        <v>1274</v>
+        <v>2733</v>
       </c>
       <c r="G362" s="2" t="s">
         <v>15</v>
@@ -30254,7 +30254,7 @@
         <v>14</v>
       </c>
       <c r="F363" s="2">
-        <v>829</v>
+        <v>1853</v>
       </c>
       <c r="G363" s="2" t="s">
         <v>15</v>
@@ -30286,7 +30286,7 @@
         <v>14</v>
       </c>
       <c r="F364" s="2">
-        <v>2026</v>
+        <v>1191</v>
       </c>
       <c r="G364" s="2" t="s">
         <v>15</v>
@@ -30318,7 +30318,7 @@
         <v>14</v>
       </c>
       <c r="F365" s="2">
-        <v>3247</v>
+        <v>4736</v>
       </c>
       <c r="G365" s="2" t="s">
         <v>15</v>
@@ -30350,7 +30350,7 @@
         <v>14</v>
       </c>
       <c r="F366" s="2">
-        <v>4319</v>
+        <v>4082</v>
       </c>
       <c r="G366" s="2" t="s">
         <v>15</v>
@@ -30382,7 +30382,7 @@
         <v>14</v>
       </c>
       <c r="F367" s="2">
-        <v>2218</v>
+        <v>3587</v>
       </c>
       <c r="G367" s="2" t="s">
         <v>15</v>
@@ -30414,7 +30414,7 @@
         <v>14</v>
       </c>
       <c r="F368" s="2">
-        <v>4492</v>
+        <v>2399</v>
       </c>
       <c r="G368" s="2" t="s">
         <v>15</v>
@@ -30446,7 +30446,7 @@
         <v>14</v>
       </c>
       <c r="F369" s="2">
-        <v>4099</v>
+        <v>859</v>
       </c>
       <c r="G369" s="2" t="s">
         <v>15</v>
@@ -30478,7 +30478,7 @@
         <v>14</v>
       </c>
       <c r="F370" s="2">
-        <v>1955</v>
+        <v>2371</v>
       </c>
       <c r="G370" s="2" t="s">
         <v>15</v>
@@ -30510,7 +30510,7 @@
         <v>14</v>
       </c>
       <c r="F371" s="2">
-        <v>2638</v>
+        <v>1934</v>
       </c>
       <c r="G371" s="2" t="s">
         <v>15</v>
@@ -30542,7 +30542,7 @@
         <v>14</v>
       </c>
       <c r="F372" s="2">
-        <v>3835</v>
+        <v>3709</v>
       </c>
       <c r="G372" s="2" t="s">
         <v>15</v>
@@ -30574,7 +30574,7 @@
         <v>14</v>
       </c>
       <c r="F373" s="2">
-        <v>1074</v>
+        <v>4011</v>
       </c>
       <c r="G373" s="2" t="s">
         <v>15</v>
@@ -30606,7 +30606,7 @@
         <v>14</v>
       </c>
       <c r="F374" s="2">
-        <v>2251</v>
+        <v>4777</v>
       </c>
       <c r="G374" s="2" t="s">
         <v>15</v>
@@ -30638,7 +30638,7 @@
         <v>14</v>
       </c>
       <c r="F375" s="2">
-        <v>4569</v>
+        <v>2664</v>
       </c>
       <c r="G375" s="2" t="s">
         <v>15</v>
@@ -30670,7 +30670,7 @@
         <v>14</v>
       </c>
       <c r="F376" s="2">
-        <v>1462</v>
+        <v>2114</v>
       </c>
       <c r="G376" s="2" t="s">
         <v>15</v>
@@ -30702,7 +30702,7 @@
         <v>14</v>
       </c>
       <c r="F377" s="2">
-        <v>2823</v>
+        <v>2957</v>
       </c>
       <c r="G377" s="2" t="s">
         <v>15</v>
@@ -30734,7 +30734,7 @@
         <v>14</v>
       </c>
       <c r="F378" s="2">
-        <v>3389</v>
+        <v>4148</v>
       </c>
       <c r="G378" s="2" t="s">
         <v>15</v>
@@ -30766,7 +30766,7 @@
         <v>14</v>
       </c>
       <c r="F379" s="2">
-        <v>4672</v>
+        <v>2634</v>
       </c>
       <c r="G379" s="2" t="s">
         <v>15</v>
@@ -30798,7 +30798,7 @@
         <v>14</v>
       </c>
       <c r="F380" s="2">
-        <v>1070</v>
+        <v>3368</v>
       </c>
       <c r="G380" s="2" t="s">
         <v>15</v>
@@ -30830,7 +30830,7 @@
         <v>14</v>
       </c>
       <c r="F381" s="2">
-        <v>865</v>
+        <v>1149</v>
       </c>
       <c r="G381" s="2" t="s">
         <v>15</v>
@@ -30862,7 +30862,7 @@
         <v>14</v>
       </c>
       <c r="F382" s="2">
-        <v>3504</v>
+        <v>3997</v>
       </c>
       <c r="G382" s="2" t="s">
         <v>15</v>
@@ -30894,7 +30894,7 @@
         <v>14</v>
       </c>
       <c r="F383" s="2">
-        <v>4110</v>
+        <v>2040</v>
       </c>
       <c r="G383" s="2" t="s">
         <v>15</v>
@@ -30926,7 +30926,7 @@
         <v>14</v>
       </c>
       <c r="F384" s="2">
-        <v>2087</v>
+        <v>3251</v>
       </c>
       <c r="G384" s="2" t="s">
         <v>15</v>
@@ -30958,7 +30958,7 @@
         <v>14</v>
       </c>
       <c r="F385" s="2">
-        <v>1122</v>
+        <v>2923</v>
       </c>
       <c r="G385" s="2" t="s">
         <v>15</v>
@@ -30990,7 +30990,7 @@
         <v>14</v>
       </c>
       <c r="F386" s="2">
-        <v>3422</v>
+        <v>1599</v>
       </c>
       <c r="G386" s="2" t="s">
         <v>15</v>
@@ -31022,7 +31022,7 @@
         <v>14</v>
       </c>
       <c r="F387" s="2">
-        <v>1251</v>
+        <v>1744</v>
       </c>
       <c r="G387" s="2" t="s">
         <v>15</v>
@@ -31054,7 +31054,7 @@
         <v>14</v>
       </c>
       <c r="F388" s="2">
-        <v>4469</v>
+        <v>1956</v>
       </c>
       <c r="G388" s="2" t="s">
         <v>15</v>
@@ -31086,7 +31086,7 @@
         <v>14</v>
       </c>
       <c r="F389" s="2">
-        <v>2557</v>
+        <v>1633</v>
       </c>
       <c r="G389" s="2" t="s">
         <v>15</v>
@@ -31118,7 +31118,7 @@
         <v>14</v>
       </c>
       <c r="F390" s="2">
-        <v>3940</v>
+        <v>1836</v>
       </c>
       <c r="G390" s="2" t="s">
         <v>15</v>
@@ -31150,7 +31150,7 @@
         <v>14</v>
       </c>
       <c r="F391" s="2">
-        <v>4227</v>
+        <v>1759</v>
       </c>
       <c r="G391" s="2" t="s">
         <v>15</v>
@@ -31182,7 +31182,7 @@
         <v>14</v>
       </c>
       <c r="F392" s="2">
-        <v>855</v>
+        <v>3636</v>
       </c>
       <c r="G392" s="2" t="s">
         <v>15</v>
@@ -31214,7 +31214,7 @@
         <v>14</v>
       </c>
       <c r="F393" s="2">
-        <v>1380</v>
+        <v>2608</v>
       </c>
       <c r="G393" s="2" t="s">
         <v>15</v>
@@ -31246,7 +31246,7 @@
         <v>14</v>
       </c>
       <c r="F394" s="2">
-        <v>939</v>
+        <v>1504</v>
       </c>
       <c r="G394" s="2" t="s">
         <v>15</v>
@@ -31278,7 +31278,7 @@
         <v>14</v>
       </c>
       <c r="F395" s="2">
-        <v>2924</v>
+        <v>3729</v>
       </c>
       <c r="G395" s="2" t="s">
         <v>15</v>
@@ -31310,7 +31310,7 @@
         <v>14</v>
       </c>
       <c r="F396" s="2">
-        <v>3298</v>
+        <v>2811</v>
       </c>
       <c r="G396" s="2" t="s">
         <v>15</v>
@@ -31342,7 +31342,7 @@
         <v>14</v>
       </c>
       <c r="F397" s="2">
-        <v>3232</v>
+        <v>4066</v>
       </c>
       <c r="G397" s="2" t="s">
         <v>15</v>
@@ -31374,7 +31374,7 @@
         <v>14</v>
       </c>
       <c r="F398" s="2">
-        <v>2202</v>
+        <v>2598</v>
       </c>
       <c r="G398" s="2" t="s">
         <v>15</v>
@@ -31406,7 +31406,7 @@
         <v>14</v>
       </c>
       <c r="F399" s="2">
-        <v>2197</v>
+        <v>4741</v>
       </c>
       <c r="G399" s="2" t="s">
         <v>15</v>
@@ -31438,7 +31438,7 @@
         <v>14</v>
       </c>
       <c r="F400" s="2">
-        <v>4337</v>
+        <v>1505</v>
       </c>
       <c r="G400" s="2" t="s">
         <v>15</v>
@@ -31470,7 +31470,7 @@
         <v>14</v>
       </c>
       <c r="F401" s="2">
-        <v>3755</v>
+        <v>4458</v>
       </c>
       <c r="G401" s="2" t="s">
         <v>15</v>
@@ -31502,7 +31502,7 @@
         <v>14</v>
       </c>
       <c r="F402" s="2">
-        <v>3172</v>
+        <v>4582</v>
       </c>
       <c r="G402" s="2" t="s">
         <v>15</v>
@@ -31534,7 +31534,7 @@
         <v>14</v>
       </c>
       <c r="F403" s="2">
-        <v>2887</v>
+        <v>4135</v>
       </c>
       <c r="G403" s="2" t="s">
         <v>15</v>
@@ -31566,7 +31566,7 @@
         <v>14</v>
       </c>
       <c r="F404" s="2">
-        <v>4081</v>
+        <v>1593</v>
       </c>
       <c r="G404" s="2" t="s">
         <v>15</v>
@@ -31598,7 +31598,7 @@
         <v>14</v>
       </c>
       <c r="F405" s="2">
-        <v>4367</v>
+        <v>2410</v>
       </c>
       <c r="G405" s="2" t="s">
         <v>15</v>
@@ -31630,7 +31630,7 @@
         <v>14</v>
       </c>
       <c r="F406" s="2">
-        <v>2635</v>
+        <v>996</v>
       </c>
       <c r="G406" s="2" t="s">
         <v>15</v>
@@ -31662,7 +31662,7 @@
         <v>14</v>
       </c>
       <c r="F407" s="2">
-        <v>3014</v>
+        <v>3339</v>
       </c>
       <c r="G407" s="2" t="s">
         <v>15</v>
@@ -31694,7 +31694,7 @@
         <v>14</v>
       </c>
       <c r="F408" s="2">
-        <v>2977</v>
+        <v>2364</v>
       </c>
       <c r="G408" s="2" t="s">
         <v>15</v>
@@ -31726,7 +31726,7 @@
         <v>14</v>
       </c>
       <c r="F409" s="2">
-        <v>1687</v>
+        <v>2892</v>
       </c>
       <c r="G409" s="2" t="s">
         <v>15</v>
@@ -31758,7 +31758,7 @@
         <v>14</v>
       </c>
       <c r="F410" s="2">
-        <v>1750</v>
+        <v>4529</v>
       </c>
       <c r="G410" s="2" t="s">
         <v>15</v>
@@ -31790,7 +31790,7 @@
         <v>14</v>
       </c>
       <c r="F411" s="2">
-        <v>4506</v>
+        <v>4508</v>
       </c>
       <c r="G411" s="2" t="s">
         <v>15</v>
@@ -31822,7 +31822,7 @@
         <v>14</v>
       </c>
       <c r="F412" s="2">
-        <v>3570</v>
+        <v>2510</v>
       </c>
       <c r="G412" s="2" t="s">
         <v>15</v>
@@ -31854,7 +31854,7 @@
         <v>14</v>
       </c>
       <c r="F413" s="2">
-        <v>4378</v>
+        <v>3927</v>
       </c>
       <c r="G413" s="2" t="s">
         <v>15</v>
@@ -31886,7 +31886,7 @@
         <v>14</v>
       </c>
       <c r="F414" s="2">
-        <v>2477</v>
+        <v>2773</v>
       </c>
       <c r="G414" s="2" t="s">
         <v>15</v>
@@ -31918,7 +31918,7 @@
         <v>14</v>
       </c>
       <c r="F415" s="2">
-        <v>1152</v>
+        <v>4276</v>
       </c>
       <c r="G415" s="2" t="s">
         <v>15</v>
@@ -31950,7 +31950,7 @@
         <v>14</v>
       </c>
       <c r="F416" s="2">
-        <v>1567</v>
+        <v>3540</v>
       </c>
       <c r="G416" s="2" t="s">
         <v>15</v>
@@ -31982,7 +31982,7 @@
         <v>14</v>
       </c>
       <c r="F417" s="2">
-        <v>4474</v>
+        <v>3968</v>
       </c>
       <c r="G417" s="2" t="s">
         <v>15</v>
@@ -32014,7 +32014,7 @@
         <v>14</v>
       </c>
       <c r="F418" s="2">
-        <v>2150</v>
+        <v>2547</v>
       </c>
       <c r="G418" s="2" t="s">
         <v>15</v>
@@ -32046,7 +32046,7 @@
         <v>14</v>
       </c>
       <c r="F419" s="2">
-        <v>1218</v>
+        <v>4781</v>
       </c>
       <c r="G419" s="2" t="s">
         <v>15</v>
@@ -32078,7 +32078,7 @@
         <v>14</v>
       </c>
       <c r="F420" s="2">
-        <v>845</v>
+        <v>1203</v>
       </c>
       <c r="G420" s="2" t="s">
         <v>15</v>
@@ -32110,7 +32110,7 @@
         <v>14</v>
       </c>
       <c r="F421" s="2">
-        <v>4377</v>
+        <v>3200</v>
       </c>
       <c r="G421" s="2" t="s">
         <v>15</v>
@@ -32142,7 +32142,7 @@
         <v>14</v>
       </c>
       <c r="F422" s="2">
-        <v>1393</v>
+        <v>2995</v>
       </c>
       <c r="G422" s="2" t="s">
         <v>15</v>
@@ -32174,7 +32174,7 @@
         <v>14</v>
       </c>
       <c r="F423" s="2">
-        <v>1475</v>
+        <v>3083</v>
       </c>
       <c r="G423" s="2" t="s">
         <v>15</v>
@@ -32206,7 +32206,7 @@
         <v>14</v>
       </c>
       <c r="F424" s="2">
-        <v>848</v>
+        <v>2190</v>
       </c>
       <c r="G424" s="2" t="s">
         <v>15</v>
@@ -32238,7 +32238,7 @@
         <v>14</v>
       </c>
       <c r="F425" s="2">
-        <v>3175</v>
+        <v>2533</v>
       </c>
       <c r="G425" s="2" t="s">
         <v>15</v>
@@ -32270,7 +32270,7 @@
         <v>14</v>
       </c>
       <c r="F426" s="2">
-        <v>2920</v>
+        <v>3930</v>
       </c>
       <c r="G426" s="2" t="s">
         <v>15</v>
@@ -32302,7 +32302,7 @@
         <v>14</v>
       </c>
       <c r="F427" s="2">
-        <v>3412</v>
+        <v>3004</v>
       </c>
       <c r="G427" s="2" t="s">
         <v>15</v>
@@ -32334,7 +32334,7 @@
         <v>14</v>
       </c>
       <c r="F428" s="2">
-        <v>2661</v>
+        <v>4656</v>
       </c>
       <c r="G428" s="2" t="s">
         <v>15</v>
@@ -32366,7 +32366,7 @@
         <v>14</v>
       </c>
       <c r="F429" s="2">
-        <v>2462</v>
+        <v>1884</v>
       </c>
       <c r="G429" s="2" t="s">
         <v>15</v>
@@ -32398,7 +32398,7 @@
         <v>14</v>
       </c>
       <c r="F430" s="2">
-        <v>3593</v>
+        <v>3407</v>
       </c>
       <c r="G430" s="2" t="s">
         <v>15</v>
@@ -32430,7 +32430,7 @@
         <v>14</v>
       </c>
       <c r="F431" s="2">
-        <v>924</v>
+        <v>1168</v>
       </c>
       <c r="G431" s="2" t="s">
         <v>15</v>
@@ -32462,7 +32462,7 @@
         <v>14</v>
       </c>
       <c r="F432" s="2">
-        <v>1477</v>
+        <v>4725</v>
       </c>
       <c r="G432" s="2" t="s">
         <v>15</v>
@@ -32494,7 +32494,7 @@
         <v>14</v>
       </c>
       <c r="F433" s="2">
-        <v>3457</v>
+        <v>3276</v>
       </c>
       <c r="G433" s="2" t="s">
         <v>15</v>
@@ -32526,7 +32526,7 @@
         <v>14</v>
       </c>
       <c r="F434" s="2">
-        <v>2603</v>
+        <v>3699</v>
       </c>
       <c r="G434" s="2" t="s">
         <v>15</v>
@@ -32558,7 +32558,7 @@
         <v>14</v>
       </c>
       <c r="F435" s="2">
-        <v>1006</v>
+        <v>4598</v>
       </c>
       <c r="G435" s="2" t="s">
         <v>15</v>
@@ -32590,7 +32590,7 @@
         <v>14</v>
       </c>
       <c r="F436" s="2">
-        <v>1330</v>
+        <v>1632</v>
       </c>
       <c r="G436" s="2" t="s">
         <v>15</v>
@@ -32622,7 +32622,7 @@
         <v>14</v>
       </c>
       <c r="F437" s="2">
-        <v>4319</v>
+        <v>4687</v>
       </c>
       <c r="G437" s="2" t="s">
         <v>15</v>
@@ -32654,7 +32654,7 @@
         <v>14</v>
       </c>
       <c r="F438" s="2">
-        <v>2184</v>
+        <v>3150</v>
       </c>
       <c r="G438" s="2" t="s">
         <v>15</v>
@@ -32686,7 +32686,7 @@
         <v>14</v>
       </c>
       <c r="F439" s="2">
-        <v>2404</v>
+        <v>1223</v>
       </c>
       <c r="G439" s="2" t="s">
         <v>15</v>
@@ -32718,7 +32718,7 @@
         <v>14</v>
       </c>
       <c r="F440" s="2">
-        <v>3674</v>
+        <v>3705</v>
       </c>
       <c r="G440" s="2" t="s">
         <v>15</v>
@@ -32750,7 +32750,7 @@
         <v>14</v>
       </c>
       <c r="F441" s="2">
-        <v>3577</v>
+        <v>957</v>
       </c>
       <c r="G441" s="2" t="s">
         <v>15</v>
@@ -32782,7 +32782,7 @@
         <v>14</v>
       </c>
       <c r="F442" s="2">
-        <v>895</v>
+        <v>3911</v>
       </c>
       <c r="G442" s="2" t="s">
         <v>15</v>
@@ -32814,7 +32814,7 @@
         <v>14</v>
       </c>
       <c r="F443" s="2">
-        <v>2515</v>
+        <v>3484</v>
       </c>
       <c r="G443" s="2" t="s">
         <v>15</v>
@@ -32846,7 +32846,7 @@
         <v>14</v>
       </c>
       <c r="F444" s="2">
-        <v>2311</v>
+        <v>4279</v>
       </c>
       <c r="G444" s="2" t="s">
         <v>15</v>
@@ -32878,7 +32878,7 @@
         <v>14</v>
       </c>
       <c r="F445" s="2">
-        <v>4437</v>
+        <v>4234</v>
       </c>
       <c r="G445" s="2" t="s">
         <v>15</v>
@@ -32910,7 +32910,7 @@
         <v>14</v>
       </c>
       <c r="F446" s="2">
-        <v>4363</v>
+        <v>3327</v>
       </c>
       <c r="G446" s="2" t="s">
         <v>15</v>
@@ -32942,7 +32942,7 @@
         <v>14</v>
       </c>
       <c r="F447" s="2">
-        <v>4298</v>
+        <v>3127</v>
       </c>
       <c r="G447" s="2" t="s">
         <v>15</v>
@@ -32974,7 +32974,7 @@
         <v>14</v>
       </c>
       <c r="F448" s="2">
-        <v>2439</v>
+        <v>1068</v>
       </c>
       <c r="G448" s="2" t="s">
         <v>15</v>
@@ -33006,7 +33006,7 @@
         <v>14</v>
       </c>
       <c r="F449" s="2">
-        <v>4645</v>
+        <v>3343</v>
       </c>
       <c r="G449" s="2" t="s">
         <v>15</v>
@@ -33038,7 +33038,7 @@
         <v>14</v>
       </c>
       <c r="F450" s="2">
-        <v>1342</v>
+        <v>4444</v>
       </c>
       <c r="G450" s="2" t="s">
         <v>15</v>
@@ -33070,7 +33070,7 @@
         <v>14</v>
       </c>
       <c r="F451" s="2">
-        <v>2672</v>
+        <v>1996</v>
       </c>
       <c r="G451" s="2" t="s">
         <v>15</v>
@@ -33102,7 +33102,7 @@
         <v>14</v>
       </c>
       <c r="F452" s="2">
-        <v>3106</v>
+        <v>3933</v>
       </c>
       <c r="G452" s="2" t="s">
         <v>15</v>
@@ -33134,7 +33134,7 @@
         <v>14</v>
       </c>
       <c r="F453" s="2">
-        <v>3750</v>
+        <v>3931</v>
       </c>
       <c r="G453" s="2" t="s">
         <v>15</v>
@@ -33166,7 +33166,7 @@
         <v>14</v>
       </c>
       <c r="F454" s="2">
-        <v>2423</v>
+        <v>2894</v>
       </c>
       <c r="G454" s="2" t="s">
         <v>15</v>
@@ -33198,7 +33198,7 @@
         <v>14</v>
       </c>
       <c r="F455" s="2">
-        <v>4015</v>
+        <v>1497</v>
       </c>
       <c r="G455" s="2" t="s">
         <v>15</v>
@@ -33230,7 +33230,7 @@
         <v>14</v>
       </c>
       <c r="F456" s="2">
-        <v>1791</v>
+        <v>2218</v>
       </c>
       <c r="G456" s="2" t="s">
         <v>15</v>
@@ -33262,7 +33262,7 @@
         <v>14</v>
       </c>
       <c r="F457" s="2">
-        <v>2347</v>
+        <v>3524</v>
       </c>
       <c r="G457" s="2" t="s">
         <v>15</v>
@@ -33294,7 +33294,7 @@
         <v>14</v>
       </c>
       <c r="F458" s="2">
-        <v>4103</v>
+        <v>1284</v>
       </c>
       <c r="G458" s="2" t="s">
         <v>15</v>
@@ -33326,7 +33326,7 @@
         <v>14</v>
       </c>
       <c r="F459" s="2">
-        <v>4287</v>
+        <v>2050</v>
       </c>
       <c r="G459" s="2" t="s">
         <v>15</v>
@@ -33358,7 +33358,7 @@
         <v>14</v>
       </c>
       <c r="F460" s="2">
-        <v>2068</v>
+        <v>3163</v>
       </c>
       <c r="G460" s="2" t="s">
         <v>15</v>
@@ -33390,7 +33390,7 @@
         <v>14</v>
       </c>
       <c r="F461" s="2">
-        <v>2545</v>
+        <v>3864</v>
       </c>
       <c r="G461" s="2" t="s">
         <v>15</v>
@@ -33422,7 +33422,7 @@
         <v>14</v>
       </c>
       <c r="F462" s="2">
-        <v>2739</v>
+        <v>968</v>
       </c>
       <c r="G462" s="2" t="s">
         <v>15</v>
@@ -33454,7 +33454,7 @@
         <v>14</v>
       </c>
       <c r="F463" s="2">
-        <v>1550</v>
+        <v>3019</v>
       </c>
       <c r="G463" s="2" t="s">
         <v>15</v>
@@ -33486,7 +33486,7 @@
         <v>14</v>
       </c>
       <c r="F464" s="2">
-        <v>4744</v>
+        <v>3517</v>
       </c>
       <c r="G464" s="2" t="s">
         <v>15</v>
@@ -33518,7 +33518,7 @@
         <v>14</v>
       </c>
       <c r="F465" s="2">
-        <v>3105</v>
+        <v>904</v>
       </c>
       <c r="G465" s="2" t="s">
         <v>15</v>
@@ -33550,7 +33550,7 @@
         <v>14</v>
       </c>
       <c r="F466" s="2">
-        <v>2996</v>
+        <v>938</v>
       </c>
       <c r="G466" s="2" t="s">
         <v>15</v>
@@ -33582,7 +33582,7 @@
         <v>14</v>
       </c>
       <c r="F467" s="2">
-        <v>1446</v>
+        <v>963</v>
       </c>
       <c r="G467" s="2" t="s">
         <v>15</v>
@@ -33614,7 +33614,7 @@
         <v>14</v>
       </c>
       <c r="F468" s="2">
-        <v>1021</v>
+        <v>3207</v>
       </c>
       <c r="G468" s="2" t="s">
         <v>15</v>
@@ -33646,7 +33646,7 @@
         <v>14</v>
       </c>
       <c r="F469" s="2">
-        <v>2786</v>
+        <v>2294</v>
       </c>
       <c r="G469" s="2" t="s">
         <v>15</v>
@@ -33678,7 +33678,7 @@
         <v>14</v>
       </c>
       <c r="F470" s="2">
-        <v>4230</v>
+        <v>4011</v>
       </c>
       <c r="G470" s="2" t="s">
         <v>15</v>
@@ -33710,7 +33710,7 @@
         <v>14</v>
       </c>
       <c r="F471" s="2">
-        <v>1294</v>
+        <v>3655</v>
       </c>
       <c r="G471" s="2" t="s">
         <v>15</v>

--- a/reports/selenium/latest/excel/Automation_Test_Report.xlsx
+++ b/reports/selenium/latest/excel/Automation_Test_Report.xlsx
@@ -3084,7 +3084,7 @@
     <t>Build</t>
   </si>
   <si>
-    <t>15</t>
+    <t>17</t>
   </si>
   <si>
     <t>Branch</t>
@@ -3096,13 +3096,13 @@
     <t>Commit</t>
   </si>
   <si>
-    <t>e1fcafa84b84</t>
+    <t>7928ec23dafe</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T04:17:35.966Z</t>
+    <t>2026-08-19T04:40:17.502Z</t>
   </si>
   <si>
     <t>Browser</t>
@@ -3607,7 +3607,7 @@
         <v>14</v>
       </c>
       <c r="F2" s="2">
-        <v>1474</v>
+        <v>2725</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>15</v>
@@ -3639,7 +3639,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="2">
-        <v>2259</v>
+        <v>2970</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>15</v>
@@ -3671,7 +3671,7 @@
         <v>14</v>
       </c>
       <c r="F4" s="2">
-        <v>4215</v>
+        <v>2433</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
@@ -3703,7 +3703,7 @@
         <v>14</v>
       </c>
       <c r="F5" s="2">
-        <v>3600</v>
+        <v>2716</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
@@ -3735,7 +3735,7 @@
         <v>14</v>
       </c>
       <c r="F6" s="2">
-        <v>4681</v>
+        <v>2860</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -3767,7 +3767,7 @@
         <v>14</v>
       </c>
       <c r="F7" s="2">
-        <v>3419</v>
+        <v>1182</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -3799,7 +3799,7 @@
         <v>14</v>
       </c>
       <c r="F8" s="2">
-        <v>863</v>
+        <v>1320</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -3831,7 +3831,7 @@
         <v>14</v>
       </c>
       <c r="F9" s="2">
-        <v>3411</v>
+        <v>3221</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -3863,7 +3863,7 @@
         <v>14</v>
       </c>
       <c r="F10" s="2">
-        <v>3621</v>
+        <v>900</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
@@ -3895,7 +3895,7 @@
         <v>14</v>
       </c>
       <c r="F11" s="2">
-        <v>4487</v>
+        <v>2548</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
@@ -3927,7 +3927,7 @@
         <v>14</v>
       </c>
       <c r="F12" s="2">
-        <v>3551</v>
+        <v>4132</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
@@ -3959,7 +3959,7 @@
         <v>14</v>
       </c>
       <c r="F13" s="2">
-        <v>2387</v>
+        <v>4302</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -3991,7 +3991,7 @@
         <v>14</v>
       </c>
       <c r="F14" s="2">
-        <v>2144</v>
+        <v>825</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -4023,7 +4023,7 @@
         <v>14</v>
       </c>
       <c r="F15" s="2">
-        <v>1214</v>
+        <v>1999</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -4055,7 +4055,7 @@
         <v>14</v>
       </c>
       <c r="F16" s="2">
-        <v>4216</v>
+        <v>2974</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
@@ -4087,7 +4087,7 @@
         <v>14</v>
       </c>
       <c r="F17" s="2">
-        <v>2084</v>
+        <v>2062</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
@@ -4119,7 +4119,7 @@
         <v>14</v>
       </c>
       <c r="F18" s="2">
-        <v>2587</v>
+        <v>2370</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
@@ -4151,7 +4151,7 @@
         <v>14</v>
       </c>
       <c r="F19" s="2">
-        <v>1494</v>
+        <v>875</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
@@ -4183,7 +4183,7 @@
         <v>14</v>
       </c>
       <c r="F20" s="2">
-        <v>3860</v>
+        <v>2678</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
@@ -4215,7 +4215,7 @@
         <v>14</v>
       </c>
       <c r="F21" s="2">
-        <v>4023</v>
+        <v>4527</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -4247,7 +4247,7 @@
         <v>14</v>
       </c>
       <c r="F22" s="2">
-        <v>2703</v>
+        <v>3275</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -4279,7 +4279,7 @@
         <v>14</v>
       </c>
       <c r="F23" s="2">
-        <v>897</v>
+        <v>3846</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -4311,7 +4311,7 @@
         <v>14</v>
       </c>
       <c r="F24" s="2">
-        <v>2748</v>
+        <v>3588</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -4343,7 +4343,7 @@
         <v>14</v>
       </c>
       <c r="F25" s="2">
-        <v>1589</v>
+        <v>4714</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -4375,7 +4375,7 @@
         <v>14</v>
       </c>
       <c r="F26" s="2">
-        <v>1491</v>
+        <v>2355</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -4407,7 +4407,7 @@
         <v>14</v>
       </c>
       <c r="F27" s="2">
-        <v>2033</v>
+        <v>3114</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>15</v>
@@ -4439,7 +4439,7 @@
         <v>14</v>
       </c>
       <c r="F28" s="2">
-        <v>3660</v>
+        <v>966</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>15</v>
@@ -4471,7 +4471,7 @@
         <v>14</v>
       </c>
       <c r="F29" s="2">
-        <v>1751</v>
+        <v>4505</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>15</v>
@@ -4503,7 +4503,7 @@
         <v>14</v>
       </c>
       <c r="F30" s="2">
-        <v>2161</v>
+        <v>1934</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>15</v>
@@ -4535,7 +4535,7 @@
         <v>14</v>
       </c>
       <c r="F31" s="2">
-        <v>3354</v>
+        <v>3714</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>15</v>
@@ -4567,7 +4567,7 @@
         <v>14</v>
       </c>
       <c r="F32" s="2">
-        <v>2854</v>
+        <v>4146</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>15</v>
@@ -4599,7 +4599,7 @@
         <v>14</v>
       </c>
       <c r="F33" s="2">
-        <v>4439</v>
+        <v>3866</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>15</v>
@@ -4631,7 +4631,7 @@
         <v>14</v>
       </c>
       <c r="F34" s="2">
-        <v>4734</v>
+        <v>4027</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>15</v>
@@ -4663,7 +4663,7 @@
         <v>14</v>
       </c>
       <c r="F35" s="2">
-        <v>4057</v>
+        <v>4117</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>15</v>
@@ -4695,7 +4695,7 @@
         <v>14</v>
       </c>
       <c r="F36" s="2">
-        <v>2967</v>
+        <v>1832</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>15</v>
@@ -4727,7 +4727,7 @@
         <v>14</v>
       </c>
       <c r="F37" s="2">
-        <v>4073</v>
+        <v>2166</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>15</v>
@@ -4759,7 +4759,7 @@
         <v>14</v>
       </c>
       <c r="F38" s="2">
-        <v>3806</v>
+        <v>4372</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>15</v>
@@ -4791,7 +4791,7 @@
         <v>14</v>
       </c>
       <c r="F39" s="2">
-        <v>896</v>
+        <v>2693</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>15</v>
@@ -4823,7 +4823,7 @@
         <v>14</v>
       </c>
       <c r="F40" s="2">
-        <v>1022</v>
+        <v>3899</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>15</v>
@@ -4855,7 +4855,7 @@
         <v>14</v>
       </c>
       <c r="F41" s="2">
-        <v>2792</v>
+        <v>1228</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>15</v>
@@ -4887,7 +4887,7 @@
         <v>14</v>
       </c>
       <c r="F42" s="2">
-        <v>4497</v>
+        <v>3642</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>15</v>
@@ -4919,7 +4919,7 @@
         <v>14</v>
       </c>
       <c r="F43" s="2">
-        <v>1900</v>
+        <v>4697</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>15</v>
@@ -4951,7 +4951,7 @@
         <v>14</v>
       </c>
       <c r="F44" s="2">
-        <v>2404</v>
+        <v>1161</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>15</v>
@@ -4983,7 +4983,7 @@
         <v>14</v>
       </c>
       <c r="F45" s="2">
-        <v>2317</v>
+        <v>2823</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>15</v>
@@ -5015,7 +5015,7 @@
         <v>14</v>
       </c>
       <c r="F46" s="2">
-        <v>4464</v>
+        <v>1084</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>15</v>
@@ -5047,7 +5047,7 @@
         <v>14</v>
       </c>
       <c r="F47" s="2">
-        <v>2309</v>
+        <v>3316</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>15</v>
@@ -5079,7 +5079,7 @@
         <v>14</v>
       </c>
       <c r="F48" s="2">
-        <v>3997</v>
+        <v>2658</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>15</v>
@@ -5111,7 +5111,7 @@
         <v>14</v>
       </c>
       <c r="F49" s="2">
-        <v>2573</v>
+        <v>4013</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>15</v>
@@ -5143,7 +5143,7 @@
         <v>14</v>
       </c>
       <c r="F50" s="2">
-        <v>1914</v>
+        <v>1753</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>15</v>
@@ -5175,7 +5175,7 @@
         <v>14</v>
       </c>
       <c r="F51" s="2">
-        <v>1090</v>
+        <v>3276</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>15</v>
@@ -5207,7 +5207,7 @@
         <v>14</v>
       </c>
       <c r="F52" s="2">
-        <v>4412</v>
+        <v>2234</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>15</v>
@@ -5239,7 +5239,7 @@
         <v>14</v>
       </c>
       <c r="F53" s="2">
-        <v>4643</v>
+        <v>3391</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>15</v>
@@ -5271,7 +5271,7 @@
         <v>14</v>
       </c>
       <c r="F54" s="2">
-        <v>2014</v>
+        <v>2312</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>15</v>
@@ -5303,7 +5303,7 @@
         <v>14</v>
       </c>
       <c r="F55" s="2">
-        <v>2043</v>
+        <v>3891</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>15</v>
@@ -5335,7 +5335,7 @@
         <v>14</v>
       </c>
       <c r="F56" s="2">
-        <v>2450</v>
+        <v>3181</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>15</v>
@@ -5367,7 +5367,7 @@
         <v>14</v>
       </c>
       <c r="F57" s="2">
-        <v>4286</v>
+        <v>1497</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>15</v>
@@ -5399,7 +5399,7 @@
         <v>14</v>
       </c>
       <c r="F58" s="2">
-        <v>2741</v>
+        <v>4755</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>15</v>
@@ -5431,7 +5431,7 @@
         <v>14</v>
       </c>
       <c r="F59" s="2">
-        <v>1182</v>
+        <v>1836</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>15</v>
@@ -5463,7 +5463,7 @@
         <v>14</v>
       </c>
       <c r="F60" s="2">
-        <v>4437</v>
+        <v>4700</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>15</v>
@@ -5495,7 +5495,7 @@
         <v>14</v>
       </c>
       <c r="F61" s="2">
-        <v>2523</v>
+        <v>3816</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>15</v>
@@ -5527,7 +5527,7 @@
         <v>14</v>
       </c>
       <c r="F62" s="2">
-        <v>1547</v>
+        <v>2778</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>15</v>
@@ -5559,7 +5559,7 @@
         <v>14</v>
       </c>
       <c r="F63" s="2">
-        <v>3226</v>
+        <v>1829</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>15</v>
@@ -5591,7 +5591,7 @@
         <v>14</v>
       </c>
       <c r="F64" s="2">
-        <v>3877</v>
+        <v>2706</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>15</v>
@@ -5623,7 +5623,7 @@
         <v>14</v>
       </c>
       <c r="F65" s="2">
-        <v>3542</v>
+        <v>4007</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>15</v>
@@ -5655,7 +5655,7 @@
         <v>14</v>
       </c>
       <c r="F66" s="2">
-        <v>3702</v>
+        <v>3273</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>15</v>
@@ -5687,7 +5687,7 @@
         <v>14</v>
       </c>
       <c r="F67" s="2">
-        <v>3984</v>
+        <v>4668</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>15</v>
@@ -5719,7 +5719,7 @@
         <v>14</v>
       </c>
       <c r="F68" s="2">
-        <v>1299</v>
+        <v>885</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>15</v>
@@ -5751,7 +5751,7 @@
         <v>14</v>
       </c>
       <c r="F69" s="2">
-        <v>2664</v>
+        <v>1016</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>15</v>
@@ -5783,7 +5783,7 @@
         <v>14</v>
       </c>
       <c r="F70" s="2">
-        <v>4251</v>
+        <v>3306</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>15</v>
@@ -5815,7 +5815,7 @@
         <v>14</v>
       </c>
       <c r="F71" s="2">
-        <v>1007</v>
+        <v>3318</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>15</v>
@@ -5847,7 +5847,7 @@
         <v>14</v>
       </c>
       <c r="F72" s="2">
-        <v>1547</v>
+        <v>886</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>15</v>
@@ -5879,7 +5879,7 @@
         <v>14</v>
       </c>
       <c r="F73" s="2">
-        <v>3257</v>
+        <v>1983</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>15</v>
@@ -5911,7 +5911,7 @@
         <v>14</v>
       </c>
       <c r="F74" s="2">
-        <v>1158</v>
+        <v>3485</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>15</v>
@@ -5943,7 +5943,7 @@
         <v>14</v>
       </c>
       <c r="F75" s="2">
-        <v>3775</v>
+        <v>2416</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>15</v>
@@ -5975,7 +5975,7 @@
         <v>14</v>
       </c>
       <c r="F76" s="2">
-        <v>1163</v>
+        <v>1729</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>15</v>
@@ -6007,7 +6007,7 @@
         <v>14</v>
       </c>
       <c r="F77" s="2">
-        <v>1329</v>
+        <v>1458</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>15</v>
@@ -6039,7 +6039,7 @@
         <v>14</v>
       </c>
       <c r="F78" s="2">
-        <v>2322</v>
+        <v>2931</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>15</v>
@@ -6071,7 +6071,7 @@
         <v>14</v>
       </c>
       <c r="F79" s="2">
-        <v>1271</v>
+        <v>4380</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>15</v>
@@ -6103,7 +6103,7 @@
         <v>14</v>
       </c>
       <c r="F80" s="2">
-        <v>1139</v>
+        <v>3136</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>15</v>
@@ -6135,7 +6135,7 @@
         <v>14</v>
       </c>
       <c r="F81" s="2">
-        <v>3455</v>
+        <v>1794</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>15</v>
@@ -6167,7 +6167,7 @@
         <v>14</v>
       </c>
       <c r="F82" s="2">
-        <v>1978</v>
+        <v>1887</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>15</v>
@@ -6199,7 +6199,7 @@
         <v>14</v>
       </c>
       <c r="F83" s="2">
-        <v>2270</v>
+        <v>2917</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>15</v>
@@ -6231,7 +6231,7 @@
         <v>14</v>
       </c>
       <c r="F84" s="2">
-        <v>1542</v>
+        <v>1854</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>15</v>
@@ -6263,7 +6263,7 @@
         <v>14</v>
       </c>
       <c r="F85" s="2">
-        <v>2688</v>
+        <v>1633</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>15</v>
@@ -6295,7 +6295,7 @@
         <v>14</v>
       </c>
       <c r="F86" s="2">
-        <v>2614</v>
+        <v>1176</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>15</v>
@@ -6327,7 +6327,7 @@
         <v>14</v>
       </c>
       <c r="F87" s="2">
-        <v>2887</v>
+        <v>2303</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>15</v>
@@ -6359,7 +6359,7 @@
         <v>14</v>
       </c>
       <c r="F88" s="2">
-        <v>2361</v>
+        <v>3077</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>15</v>
@@ -6391,7 +6391,7 @@
         <v>14</v>
       </c>
       <c r="F89" s="2">
-        <v>3180</v>
+        <v>2363</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>15</v>
@@ -6423,7 +6423,7 @@
         <v>14</v>
       </c>
       <c r="F90" s="2">
-        <v>1650</v>
+        <v>1995</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>15</v>
@@ -6455,7 +6455,7 @@
         <v>14</v>
       </c>
       <c r="F91" s="2">
-        <v>4075</v>
+        <v>3211</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>15</v>
@@ -6487,7 +6487,7 @@
         <v>14</v>
       </c>
       <c r="F92" s="2">
-        <v>1788</v>
+        <v>4795</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>15</v>
@@ -6519,7 +6519,7 @@
         <v>14</v>
       </c>
       <c r="F93" s="2">
-        <v>2372</v>
+        <v>2335</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>15</v>
@@ -6551,7 +6551,7 @@
         <v>14</v>
       </c>
       <c r="F94" s="2">
-        <v>1512</v>
+        <v>1280</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>15</v>
@@ -6583,7 +6583,7 @@
         <v>14</v>
       </c>
       <c r="F95" s="2">
-        <v>3619</v>
+        <v>4158</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>15</v>
@@ -6615,7 +6615,7 @@
         <v>14</v>
       </c>
       <c r="F96" s="2">
-        <v>4112</v>
+        <v>2063</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>15</v>
@@ -6647,7 +6647,7 @@
         <v>14</v>
       </c>
       <c r="F97" s="2">
-        <v>1505</v>
+        <v>3480</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>15</v>
@@ -6679,7 +6679,7 @@
         <v>14</v>
       </c>
       <c r="F98" s="2">
-        <v>4618</v>
+        <v>2506</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>15</v>
@@ -6711,7 +6711,7 @@
         <v>14</v>
       </c>
       <c r="F99" s="2">
-        <v>1532</v>
+        <v>3513</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>15</v>
@@ -6743,7 +6743,7 @@
         <v>14</v>
       </c>
       <c r="F100" s="2">
-        <v>4411</v>
+        <v>1611</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>15</v>
@@ -6775,7 +6775,7 @@
         <v>14</v>
       </c>
       <c r="F101" s="2">
-        <v>3175</v>
+        <v>4118</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>15</v>
@@ -6807,7 +6807,7 @@
         <v>14</v>
       </c>
       <c r="F102" s="2">
-        <v>2306</v>
+        <v>2684</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>15</v>
@@ -6839,7 +6839,7 @@
         <v>14</v>
       </c>
       <c r="F103" s="2">
-        <v>2129</v>
+        <v>4740</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>15</v>
@@ -6871,7 +6871,7 @@
         <v>14</v>
       </c>
       <c r="F104" s="2">
-        <v>1448</v>
+        <v>2489</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>15</v>
@@ -6903,7 +6903,7 @@
         <v>14</v>
       </c>
       <c r="F105" s="2">
-        <v>2318</v>
+        <v>1258</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>15</v>
@@ -6935,7 +6935,7 @@
         <v>14</v>
       </c>
       <c r="F106" s="2">
-        <v>1636</v>
+        <v>4094</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>15</v>
@@ -6967,7 +6967,7 @@
         <v>14</v>
       </c>
       <c r="F107" s="2">
-        <v>1135</v>
+        <v>4430</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>15</v>
@@ -6999,7 +6999,7 @@
         <v>14</v>
       </c>
       <c r="F108" s="2">
-        <v>3461</v>
+        <v>2971</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>15</v>
@@ -7031,7 +7031,7 @@
         <v>14</v>
       </c>
       <c r="F109" s="2">
-        <v>3510</v>
+        <v>1749</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>15</v>
@@ -7063,7 +7063,7 @@
         <v>14</v>
       </c>
       <c r="F110" s="2">
-        <v>4683</v>
+        <v>2912</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>15</v>
@@ -7095,7 +7095,7 @@
         <v>14</v>
       </c>
       <c r="F111" s="2">
-        <v>3673</v>
+        <v>4199</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>15</v>
@@ -7127,7 +7127,7 @@
         <v>14</v>
       </c>
       <c r="F112" s="2">
-        <v>1017</v>
+        <v>4413</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>15</v>
@@ -7159,7 +7159,7 @@
         <v>14</v>
       </c>
       <c r="F113" s="2">
-        <v>3163</v>
+        <v>3824</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>15</v>
@@ -7191,7 +7191,7 @@
         <v>14</v>
       </c>
       <c r="F114" s="2">
-        <v>1798</v>
+        <v>2486</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>15</v>
@@ -7223,7 +7223,7 @@
         <v>14</v>
       </c>
       <c r="F115" s="2">
-        <v>3557</v>
+        <v>1685</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>15</v>
@@ -7255,7 +7255,7 @@
         <v>14</v>
       </c>
       <c r="F116" s="2">
-        <v>4404</v>
+        <v>3203</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>15</v>
@@ -7287,7 +7287,7 @@
         <v>14</v>
       </c>
       <c r="F117" s="2">
-        <v>2076</v>
+        <v>2868</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>15</v>
@@ -7319,7 +7319,7 @@
         <v>14</v>
       </c>
       <c r="F118" s="2">
-        <v>2711</v>
+        <v>2955</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>15</v>
@@ -7351,7 +7351,7 @@
         <v>14</v>
       </c>
       <c r="F119" s="2">
-        <v>3505</v>
+        <v>3428</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>15</v>
@@ -7383,7 +7383,7 @@
         <v>14</v>
       </c>
       <c r="F120" s="2">
-        <v>3867</v>
+        <v>4675</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>15</v>
@@ -7415,7 +7415,7 @@
         <v>14</v>
       </c>
       <c r="F121" s="2">
-        <v>4748</v>
+        <v>4121</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>15</v>
@@ -7447,7 +7447,7 @@
         <v>14</v>
       </c>
       <c r="F122" s="2">
-        <v>2823</v>
+        <v>3890</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>15</v>
@@ -7479,7 +7479,7 @@
         <v>14</v>
       </c>
       <c r="F123" s="2">
-        <v>1453</v>
+        <v>4308</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>15</v>
@@ -7511,7 +7511,7 @@
         <v>14</v>
       </c>
       <c r="F124" s="2">
-        <v>1686</v>
+        <v>2023</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>15</v>
@@ -7543,7 +7543,7 @@
         <v>14</v>
       </c>
       <c r="F125" s="2">
-        <v>1000</v>
+        <v>4297</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>15</v>
@@ -7575,7 +7575,7 @@
         <v>14</v>
       </c>
       <c r="F126" s="2">
-        <v>1580</v>
+        <v>2857</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>15</v>
@@ -7607,7 +7607,7 @@
         <v>14</v>
       </c>
       <c r="F127" s="2">
-        <v>3742</v>
+        <v>2577</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>15</v>
@@ -7639,7 +7639,7 @@
         <v>14</v>
       </c>
       <c r="F128" s="2">
-        <v>1832</v>
+        <v>3046</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>15</v>
@@ -7671,7 +7671,7 @@
         <v>14</v>
       </c>
       <c r="F129" s="2">
-        <v>4372</v>
+        <v>2352</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>15</v>
@@ -7703,7 +7703,7 @@
         <v>14</v>
       </c>
       <c r="F130" s="2">
-        <v>3409</v>
+        <v>1799</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>15</v>
@@ -7735,7 +7735,7 @@
         <v>14</v>
       </c>
       <c r="F131" s="2">
-        <v>2927</v>
+        <v>2372</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>15</v>
@@ -7767,7 +7767,7 @@
         <v>14</v>
       </c>
       <c r="F132" s="2">
-        <v>2451</v>
+        <v>901</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>15</v>
@@ -7799,7 +7799,7 @@
         <v>14</v>
       </c>
       <c r="F133" s="2">
-        <v>3538</v>
+        <v>3790</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>15</v>
@@ -7831,7 +7831,7 @@
         <v>14</v>
       </c>
       <c r="F134" s="2">
-        <v>4445</v>
+        <v>3799</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>15</v>
@@ -7863,7 +7863,7 @@
         <v>14</v>
       </c>
       <c r="F135" s="2">
-        <v>2518</v>
+        <v>4226</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>15</v>
@@ -7895,7 +7895,7 @@
         <v>14</v>
       </c>
       <c r="F136" s="2">
-        <v>3840</v>
+        <v>3220</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>15</v>
@@ -7927,7 +7927,7 @@
         <v>14</v>
       </c>
       <c r="F137" s="2">
-        <v>4032</v>
+        <v>3904</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>15</v>
@@ -7959,7 +7959,7 @@
         <v>14</v>
       </c>
       <c r="F138" s="2">
-        <v>2369</v>
+        <v>2103</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>15</v>
@@ -7991,7 +7991,7 @@
         <v>14</v>
       </c>
       <c r="F139" s="2">
-        <v>2181</v>
+        <v>2553</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>15</v>
@@ -8023,7 +8023,7 @@
         <v>14</v>
       </c>
       <c r="F140" s="2">
-        <v>3579</v>
+        <v>2635</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>15</v>
@@ -8055,7 +8055,7 @@
         <v>14</v>
       </c>
       <c r="F141" s="2">
-        <v>2002</v>
+        <v>2986</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>15</v>
@@ -8087,7 +8087,7 @@
         <v>14</v>
       </c>
       <c r="F142" s="2">
-        <v>2536</v>
+        <v>2246</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>15</v>
@@ -8119,7 +8119,7 @@
         <v>14</v>
       </c>
       <c r="F143" s="2">
-        <v>2653</v>
+        <v>2989</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>15</v>
@@ -8151,7 +8151,7 @@
         <v>14</v>
       </c>
       <c r="F144" s="2">
-        <v>1107</v>
+        <v>2717</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>15</v>
@@ -8183,7 +8183,7 @@
         <v>14</v>
       </c>
       <c r="F145" s="2">
-        <v>2718</v>
+        <v>2751</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>15</v>
@@ -8215,7 +8215,7 @@
         <v>14</v>
       </c>
       <c r="F146" s="2">
-        <v>2123</v>
+        <v>2471</v>
       </c>
       <c r="G146" s="2" t="s">
         <v>15</v>
@@ -8247,7 +8247,7 @@
         <v>14</v>
       </c>
       <c r="F147" s="2">
-        <v>1238</v>
+        <v>4646</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>15</v>
@@ -8279,7 +8279,7 @@
         <v>14</v>
       </c>
       <c r="F148" s="2">
-        <v>2240</v>
+        <v>2442</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>15</v>
@@ -8311,7 +8311,7 @@
         <v>14</v>
       </c>
       <c r="F149" s="2">
-        <v>1961</v>
+        <v>1040</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>15</v>
@@ -8343,7 +8343,7 @@
         <v>14</v>
       </c>
       <c r="F150" s="2">
-        <v>2635</v>
+        <v>2602</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>15</v>
@@ -8375,7 +8375,7 @@
         <v>14</v>
       </c>
       <c r="F151" s="2">
-        <v>1340</v>
+        <v>1007</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>15</v>
@@ -8407,7 +8407,7 @@
         <v>14</v>
       </c>
       <c r="F152" s="2">
-        <v>4740</v>
+        <v>4652</v>
       </c>
       <c r="G152" s="2" t="s">
         <v>15</v>
@@ -8439,7 +8439,7 @@
         <v>14</v>
       </c>
       <c r="F153" s="2">
-        <v>1203</v>
+        <v>1233</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>15</v>
@@ -8471,7 +8471,7 @@
         <v>14</v>
       </c>
       <c r="F154" s="2">
-        <v>3283</v>
+        <v>2533</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>15</v>
@@ -8503,7 +8503,7 @@
         <v>14</v>
       </c>
       <c r="F155" s="2">
-        <v>1351</v>
+        <v>2787</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>15</v>
@@ -8535,7 +8535,7 @@
         <v>14</v>
       </c>
       <c r="F156" s="2">
-        <v>2094</v>
+        <v>2475</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>15</v>
@@ -8567,7 +8567,7 @@
         <v>14</v>
       </c>
       <c r="F157" s="2">
-        <v>814</v>
+        <v>2321</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>15</v>
@@ -8599,7 +8599,7 @@
         <v>14</v>
       </c>
       <c r="F158" s="2">
-        <v>1258</v>
+        <v>3912</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>15</v>
@@ -8631,7 +8631,7 @@
         <v>14</v>
       </c>
       <c r="F159" s="2">
-        <v>1813</v>
+        <v>1685</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>15</v>
@@ -8663,7 +8663,7 @@
         <v>14</v>
       </c>
       <c r="F160" s="2">
-        <v>3314</v>
+        <v>1087</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>15</v>
@@ -8695,7 +8695,7 @@
         <v>14</v>
       </c>
       <c r="F161" s="2">
-        <v>1584</v>
+        <v>2480</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>15</v>
@@ -8727,7 +8727,7 @@
         <v>14</v>
       </c>
       <c r="F162" s="2">
-        <v>2403</v>
+        <v>3302</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>15</v>
@@ -8759,7 +8759,7 @@
         <v>14</v>
       </c>
       <c r="F163" s="2">
-        <v>3469</v>
+        <v>4240</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>15</v>
@@ -8791,7 +8791,7 @@
         <v>14</v>
       </c>
       <c r="F164" s="2">
-        <v>3293</v>
+        <v>3263</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>15</v>
@@ -8823,7 +8823,7 @@
         <v>14</v>
       </c>
       <c r="F165" s="2">
-        <v>4196</v>
+        <v>2089</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>15</v>
@@ -8855,7 +8855,7 @@
         <v>14</v>
       </c>
       <c r="F166" s="2">
-        <v>944</v>
+        <v>2896</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>15</v>
@@ -8887,7 +8887,7 @@
         <v>14</v>
       </c>
       <c r="F167" s="2">
-        <v>1797</v>
+        <v>1851</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>15</v>
@@ -8919,7 +8919,7 @@
         <v>14</v>
       </c>
       <c r="F168" s="2">
-        <v>1492</v>
+        <v>2964</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>15</v>
@@ -8951,7 +8951,7 @@
         <v>14</v>
       </c>
       <c r="F169" s="2">
-        <v>2931</v>
+        <v>2267</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>15</v>
@@ -8983,7 +8983,7 @@
         <v>14</v>
       </c>
       <c r="F170" s="2">
-        <v>2666</v>
+        <v>1318</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>15</v>
@@ -9015,7 +9015,7 @@
         <v>14</v>
       </c>
       <c r="F171" s="2">
-        <v>3924</v>
+        <v>1386</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>15</v>
@@ -9047,7 +9047,7 @@
         <v>14</v>
       </c>
       <c r="F172" s="2">
-        <v>2651</v>
+        <v>2843</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>15</v>
@@ -9079,7 +9079,7 @@
         <v>14</v>
       </c>
       <c r="F173" s="2">
-        <v>2475</v>
+        <v>3888</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>15</v>
@@ -9111,7 +9111,7 @@
         <v>14</v>
       </c>
       <c r="F174" s="2">
-        <v>3667</v>
+        <v>3771</v>
       </c>
       <c r="G174" s="2" t="s">
         <v>15</v>
@@ -9143,7 +9143,7 @@
         <v>14</v>
       </c>
       <c r="F175" s="2">
-        <v>3400</v>
+        <v>1144</v>
       </c>
       <c r="G175" s="2" t="s">
         <v>15</v>
@@ -9175,7 +9175,7 @@
         <v>14</v>
       </c>
       <c r="F176" s="2">
-        <v>2643</v>
+        <v>1713</v>
       </c>
       <c r="G176" s="2" t="s">
         <v>15</v>
@@ -9207,7 +9207,7 @@
         <v>14</v>
       </c>
       <c r="F177" s="2">
-        <v>2966</v>
+        <v>827</v>
       </c>
       <c r="G177" s="2" t="s">
         <v>15</v>
@@ -9239,7 +9239,7 @@
         <v>14</v>
       </c>
       <c r="F178" s="2">
-        <v>1222</v>
+        <v>2163</v>
       </c>
       <c r="G178" s="2" t="s">
         <v>15</v>
@@ -9271,7 +9271,7 @@
         <v>14</v>
       </c>
       <c r="F179" s="2">
-        <v>2317</v>
+        <v>3313</v>
       </c>
       <c r="G179" s="2" t="s">
         <v>15</v>
@@ -9303,7 +9303,7 @@
         <v>14</v>
       </c>
       <c r="F180" s="2">
-        <v>3462</v>
+        <v>3355</v>
       </c>
       <c r="G180" s="2" t="s">
         <v>15</v>
@@ -9335,7 +9335,7 @@
         <v>14</v>
       </c>
       <c r="F181" s="2">
-        <v>2051</v>
+        <v>3886</v>
       </c>
       <c r="G181" s="2" t="s">
         <v>15</v>
@@ -9367,7 +9367,7 @@
         <v>14</v>
       </c>
       <c r="F182" s="2">
-        <v>4224</v>
+        <v>2981</v>
       </c>
       <c r="G182" s="2" t="s">
         <v>15</v>
@@ -9399,7 +9399,7 @@
         <v>14</v>
       </c>
       <c r="F183" s="2">
-        <v>1816</v>
+        <v>1846</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>15</v>
@@ -9431,7 +9431,7 @@
         <v>14</v>
       </c>
       <c r="F184" s="2">
-        <v>3432</v>
+        <v>2092</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>15</v>
@@ -9463,7 +9463,7 @@
         <v>14</v>
       </c>
       <c r="F185" s="2">
-        <v>1972</v>
+        <v>4018</v>
       </c>
       <c r="G185" s="2" t="s">
         <v>15</v>
@@ -9495,7 +9495,7 @@
         <v>14</v>
       </c>
       <c r="F186" s="2">
-        <v>1132</v>
+        <v>4460</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>15</v>
@@ -9527,7 +9527,7 @@
         <v>14</v>
       </c>
       <c r="F187" s="2">
-        <v>4209</v>
+        <v>823</v>
       </c>
       <c r="G187" s="2" t="s">
         <v>15</v>
@@ -9559,7 +9559,7 @@
         <v>14</v>
       </c>
       <c r="F188" s="2">
-        <v>4785</v>
+        <v>1513</v>
       </c>
       <c r="G188" s="2" t="s">
         <v>15</v>
@@ -9591,7 +9591,7 @@
         <v>14</v>
       </c>
       <c r="F189" s="2">
-        <v>2977</v>
+        <v>1976</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>15</v>
@@ -9623,7 +9623,7 @@
         <v>14</v>
       </c>
       <c r="F190" s="2">
-        <v>1136</v>
+        <v>2831</v>
       </c>
       <c r="G190" s="2" t="s">
         <v>15</v>
@@ -9655,7 +9655,7 @@
         <v>14</v>
       </c>
       <c r="F191" s="2">
-        <v>2615</v>
+        <v>3349</v>
       </c>
       <c r="G191" s="2" t="s">
         <v>15</v>
@@ -9687,7 +9687,7 @@
         <v>14</v>
       </c>
       <c r="F192" s="2">
-        <v>1022</v>
+        <v>3973</v>
       </c>
       <c r="G192" s="2" t="s">
         <v>15</v>
@@ -9719,7 +9719,7 @@
         <v>14</v>
       </c>
       <c r="F193" s="2">
-        <v>3358</v>
+        <v>1607</v>
       </c>
       <c r="G193" s="2" t="s">
         <v>15</v>
@@ -9751,7 +9751,7 @@
         <v>14</v>
       </c>
       <c r="F194" s="2">
-        <v>2445</v>
+        <v>2942</v>
       </c>
       <c r="G194" s="2" t="s">
         <v>15</v>
@@ -9783,7 +9783,7 @@
         <v>14</v>
       </c>
       <c r="F195" s="2">
-        <v>4392</v>
+        <v>1397</v>
       </c>
       <c r="G195" s="2" t="s">
         <v>15</v>
@@ -9815,7 +9815,7 @@
         <v>14</v>
       </c>
       <c r="F196" s="2">
-        <v>4593</v>
+        <v>3496</v>
       </c>
       <c r="G196" s="2" t="s">
         <v>15</v>
@@ -9847,7 +9847,7 @@
         <v>14</v>
       </c>
       <c r="F197" s="2">
-        <v>2144</v>
+        <v>2413</v>
       </c>
       <c r="G197" s="2" t="s">
         <v>15</v>
@@ -9879,7 +9879,7 @@
         <v>14</v>
       </c>
       <c r="F198" s="2">
-        <v>2268</v>
+        <v>4243</v>
       </c>
       <c r="G198" s="2" t="s">
         <v>15</v>
@@ -9911,7 +9911,7 @@
         <v>14</v>
       </c>
       <c r="F199" s="2">
-        <v>4321</v>
+        <v>1310</v>
       </c>
       <c r="G199" s="2" t="s">
         <v>15</v>
@@ -9943,7 +9943,7 @@
         <v>14</v>
       </c>
       <c r="F200" s="2">
-        <v>1197</v>
+        <v>1798</v>
       </c>
       <c r="G200" s="2" t="s">
         <v>15</v>
@@ -9975,7 +9975,7 @@
         <v>14</v>
       </c>
       <c r="F201" s="2">
-        <v>975</v>
+        <v>4077</v>
       </c>
       <c r="G201" s="2" t="s">
         <v>15</v>
@@ -10007,7 +10007,7 @@
         <v>14</v>
       </c>
       <c r="F202" s="2">
-        <v>4517</v>
+        <v>1908</v>
       </c>
       <c r="G202" s="2" t="s">
         <v>15</v>
@@ -10039,7 +10039,7 @@
         <v>14</v>
       </c>
       <c r="F203" s="2">
-        <v>2038</v>
+        <v>3862</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>15</v>
@@ -10071,7 +10071,7 @@
         <v>14</v>
       </c>
       <c r="F204" s="2">
-        <v>2756</v>
+        <v>1204</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>15</v>
@@ -10103,7 +10103,7 @@
         <v>14</v>
       </c>
       <c r="F205" s="2">
-        <v>2292</v>
+        <v>4716</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>15</v>
@@ -10135,7 +10135,7 @@
         <v>14</v>
       </c>
       <c r="F206" s="2">
-        <v>1704</v>
+        <v>4336</v>
       </c>
       <c r="G206" s="2" t="s">
         <v>15</v>
@@ -10167,7 +10167,7 @@
         <v>14</v>
       </c>
       <c r="F207" s="2">
-        <v>2133</v>
+        <v>1141</v>
       </c>
       <c r="G207" s="2" t="s">
         <v>15</v>
@@ -10199,7 +10199,7 @@
         <v>14</v>
       </c>
       <c r="F208" s="2">
-        <v>3983</v>
+        <v>1222</v>
       </c>
       <c r="G208" s="2" t="s">
         <v>15</v>
@@ -10231,7 +10231,7 @@
         <v>14</v>
       </c>
       <c r="F209" s="2">
-        <v>3370</v>
+        <v>4510</v>
       </c>
       <c r="G209" s="2" t="s">
         <v>15</v>
@@ -10263,7 +10263,7 @@
         <v>14</v>
       </c>
       <c r="F210" s="2">
-        <v>933</v>
+        <v>2888</v>
       </c>
       <c r="G210" s="2" t="s">
         <v>15</v>
@@ -10295,7 +10295,7 @@
         <v>14</v>
       </c>
       <c r="F211" s="2">
-        <v>1531</v>
+        <v>817</v>
       </c>
       <c r="G211" s="2" t="s">
         <v>15</v>
@@ -10327,7 +10327,7 @@
         <v>14</v>
       </c>
       <c r="F212" s="2">
-        <v>1057</v>
+        <v>2840</v>
       </c>
       <c r="G212" s="2" t="s">
         <v>15</v>
@@ -10359,7 +10359,7 @@
         <v>14</v>
       </c>
       <c r="F213" s="2">
-        <v>4423</v>
+        <v>1223</v>
       </c>
       <c r="G213" s="2" t="s">
         <v>15</v>
@@ -10391,7 +10391,7 @@
         <v>14</v>
       </c>
       <c r="F214" s="2">
-        <v>1144</v>
+        <v>4757</v>
       </c>
       <c r="G214" s="2" t="s">
         <v>15</v>
@@ -10423,7 +10423,7 @@
         <v>14</v>
       </c>
       <c r="F215" s="2">
-        <v>1102</v>
+        <v>2238</v>
       </c>
       <c r="G215" s="2" t="s">
         <v>15</v>
@@ -10455,7 +10455,7 @@
         <v>14</v>
       </c>
       <c r="F216" s="2">
-        <v>2868</v>
+        <v>2885</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>15</v>
@@ -10487,7 +10487,7 @@
         <v>14</v>
       </c>
       <c r="F217" s="2">
-        <v>1840</v>
+        <v>1176</v>
       </c>
       <c r="G217" s="2" t="s">
         <v>15</v>
@@ -10519,7 +10519,7 @@
         <v>14</v>
       </c>
       <c r="F218" s="2">
-        <v>3010</v>
+        <v>971</v>
       </c>
       <c r="G218" s="2" t="s">
         <v>15</v>
@@ -10551,7 +10551,7 @@
         <v>14</v>
       </c>
       <c r="F219" s="2">
-        <v>1208</v>
+        <v>877</v>
       </c>
       <c r="G219" s="2" t="s">
         <v>15</v>
@@ -10583,7 +10583,7 @@
         <v>14</v>
       </c>
       <c r="F220" s="2">
-        <v>4034</v>
+        <v>1519</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>15</v>
@@ -10615,7 +10615,7 @@
         <v>14</v>
       </c>
       <c r="F221" s="2">
-        <v>2400</v>
+        <v>4038</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>15</v>
@@ -10647,7 +10647,7 @@
         <v>14</v>
       </c>
       <c r="F222" s="2">
-        <v>2937</v>
+        <v>2596</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>15</v>
@@ -10679,7 +10679,7 @@
         <v>14</v>
       </c>
       <c r="F223" s="2">
-        <v>2430</v>
+        <v>2080</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>15</v>
@@ -10711,7 +10711,7 @@
         <v>14</v>
       </c>
       <c r="F224" s="2">
-        <v>4234</v>
+        <v>3677</v>
       </c>
       <c r="G224" s="2" t="s">
         <v>15</v>
@@ -10743,7 +10743,7 @@
         <v>14</v>
       </c>
       <c r="F225" s="2">
-        <v>1923</v>
+        <v>1322</v>
       </c>
       <c r="G225" s="2" t="s">
         <v>15</v>
@@ -10775,7 +10775,7 @@
         <v>14</v>
       </c>
       <c r="F226" s="2">
-        <v>3039</v>
+        <v>1548</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>15</v>
@@ -10807,7 +10807,7 @@
         <v>14</v>
       </c>
       <c r="F227" s="2">
-        <v>1060</v>
+        <v>2182</v>
       </c>
       <c r="G227" s="2" t="s">
         <v>15</v>
@@ -10839,7 +10839,7 @@
         <v>14</v>
       </c>
       <c r="F228" s="2">
-        <v>3425</v>
+        <v>4284</v>
       </c>
       <c r="G228" s="2" t="s">
         <v>15</v>
@@ -10871,7 +10871,7 @@
         <v>14</v>
       </c>
       <c r="F229" s="2">
-        <v>3193</v>
+        <v>2393</v>
       </c>
       <c r="G229" s="2" t="s">
         <v>15</v>
@@ -10903,7 +10903,7 @@
         <v>14</v>
       </c>
       <c r="F230" s="2">
-        <v>3725</v>
+        <v>3542</v>
       </c>
       <c r="G230" s="2" t="s">
         <v>15</v>
@@ -10935,7 +10935,7 @@
         <v>14</v>
       </c>
       <c r="F231" s="2">
-        <v>4339</v>
+        <v>3397</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>15</v>
@@ -10967,7 +10967,7 @@
         <v>14</v>
       </c>
       <c r="F232" s="2">
-        <v>4740</v>
+        <v>1368</v>
       </c>
       <c r="G232" s="2" t="s">
         <v>15</v>
@@ -10999,7 +10999,7 @@
         <v>14</v>
       </c>
       <c r="F233" s="2">
-        <v>2633</v>
+        <v>4658</v>
       </c>
       <c r="G233" s="2" t="s">
         <v>15</v>
@@ -11031,7 +11031,7 @@
         <v>14</v>
       </c>
       <c r="F234" s="2">
-        <v>2102</v>
+        <v>1285</v>
       </c>
       <c r="G234" s="2" t="s">
         <v>15</v>
@@ -11063,7 +11063,7 @@
         <v>14</v>
       </c>
       <c r="F235" s="2">
-        <v>4369</v>
+        <v>2989</v>
       </c>
       <c r="G235" s="2" t="s">
         <v>15</v>
@@ -11095,7 +11095,7 @@
         <v>14</v>
       </c>
       <c r="F236" s="2">
-        <v>1109</v>
+        <v>3506</v>
       </c>
       <c r="G236" s="2" t="s">
         <v>15</v>
@@ -11127,7 +11127,7 @@
         <v>14</v>
       </c>
       <c r="F237" s="2">
-        <v>1987</v>
+        <v>2319</v>
       </c>
       <c r="G237" s="2" t="s">
         <v>15</v>
@@ -11159,7 +11159,7 @@
         <v>14</v>
       </c>
       <c r="F238" s="2">
-        <v>1886</v>
+        <v>2312</v>
       </c>
       <c r="G238" s="2" t="s">
         <v>15</v>
@@ -11191,7 +11191,7 @@
         <v>14</v>
       </c>
       <c r="F239" s="2">
-        <v>3965</v>
+        <v>4264</v>
       </c>
       <c r="G239" s="2" t="s">
         <v>15</v>
@@ -11223,7 +11223,7 @@
         <v>14</v>
       </c>
       <c r="F240" s="2">
-        <v>4607</v>
+        <v>4786</v>
       </c>
       <c r="G240" s="2" t="s">
         <v>15</v>
@@ -11255,7 +11255,7 @@
         <v>14</v>
       </c>
       <c r="F241" s="2">
-        <v>4171</v>
+        <v>3285</v>
       </c>
       <c r="G241" s="2" t="s">
         <v>15</v>
@@ -11287,7 +11287,7 @@
         <v>14</v>
       </c>
       <c r="F242" s="2">
-        <v>1617</v>
+        <v>4584</v>
       </c>
       <c r="G242" s="2" t="s">
         <v>15</v>
@@ -11319,7 +11319,7 @@
         <v>14</v>
       </c>
       <c r="F243" s="2">
-        <v>2792</v>
+        <v>1375</v>
       </c>
       <c r="G243" s="2" t="s">
         <v>15</v>
@@ -11351,7 +11351,7 @@
         <v>14</v>
       </c>
       <c r="F244" s="2">
-        <v>978</v>
+        <v>3483</v>
       </c>
       <c r="G244" s="2" t="s">
         <v>15</v>
@@ -11383,7 +11383,7 @@
         <v>14</v>
       </c>
       <c r="F245" s="2">
-        <v>3576</v>
+        <v>4009</v>
       </c>
       <c r="G245" s="2" t="s">
         <v>15</v>
@@ -11415,7 +11415,7 @@
         <v>14</v>
       </c>
       <c r="F246" s="2">
-        <v>3953</v>
+        <v>4379</v>
       </c>
       <c r="G246" s="2" t="s">
         <v>15</v>
@@ -11447,7 +11447,7 @@
         <v>14</v>
       </c>
       <c r="F247" s="2">
-        <v>3079</v>
+        <v>1291</v>
       </c>
       <c r="G247" s="2" t="s">
         <v>15</v>
@@ -11479,7 +11479,7 @@
         <v>14</v>
       </c>
       <c r="F248" s="2">
-        <v>3375</v>
+        <v>1643</v>
       </c>
       <c r="G248" s="2" t="s">
         <v>15</v>
@@ -11511,7 +11511,7 @@
         <v>14</v>
       </c>
       <c r="F249" s="2">
-        <v>1128</v>
+        <v>1191</v>
       </c>
       <c r="G249" s="2" t="s">
         <v>15</v>
@@ -11543,7 +11543,7 @@
         <v>14</v>
       </c>
       <c r="F250" s="2">
-        <v>2462</v>
+        <v>3168</v>
       </c>
       <c r="G250" s="2" t="s">
         <v>15</v>
@@ -11575,7 +11575,7 @@
         <v>14</v>
       </c>
       <c r="F251" s="2">
-        <v>1015</v>
+        <v>4424</v>
       </c>
       <c r="G251" s="2" t="s">
         <v>15</v>
@@ -11607,7 +11607,7 @@
         <v>14</v>
       </c>
       <c r="F252" s="2">
-        <v>4616</v>
+        <v>1137</v>
       </c>
       <c r="G252" s="2" t="s">
         <v>15</v>
@@ -11639,7 +11639,7 @@
         <v>14</v>
       </c>
       <c r="F253" s="2">
-        <v>2901</v>
+        <v>900</v>
       </c>
       <c r="G253" s="2" t="s">
         <v>15</v>
@@ -11671,7 +11671,7 @@
         <v>14</v>
       </c>
       <c r="F254" s="2">
-        <v>4322</v>
+        <v>2467</v>
       </c>
       <c r="G254" s="2" t="s">
         <v>15</v>
@@ -11703,7 +11703,7 @@
         <v>14</v>
       </c>
       <c r="F255" s="2">
-        <v>4273</v>
+        <v>2283</v>
       </c>
       <c r="G255" s="2" t="s">
         <v>15</v>
@@ -11735,7 +11735,7 @@
         <v>14</v>
       </c>
       <c r="F256" s="2">
-        <v>919</v>
+        <v>3003</v>
       </c>
       <c r="G256" s="2" t="s">
         <v>15</v>
@@ -11767,7 +11767,7 @@
         <v>14</v>
       </c>
       <c r="F257" s="2">
-        <v>804</v>
+        <v>3861</v>
       </c>
       <c r="G257" s="2" t="s">
         <v>15</v>
@@ -11799,7 +11799,7 @@
         <v>14</v>
       </c>
       <c r="F258" s="2">
-        <v>3160</v>
+        <v>3231</v>
       </c>
       <c r="G258" s="2" t="s">
         <v>15</v>
@@ -11831,7 +11831,7 @@
         <v>14</v>
       </c>
       <c r="F259" s="2">
-        <v>4237</v>
+        <v>1136</v>
       </c>
       <c r="G259" s="2" t="s">
         <v>15</v>
@@ -11863,7 +11863,7 @@
         <v>14</v>
       </c>
       <c r="F260" s="2">
-        <v>2191</v>
+        <v>3732</v>
       </c>
       <c r="G260" s="2" t="s">
         <v>15</v>
@@ -11895,7 +11895,7 @@
         <v>14</v>
       </c>
       <c r="F261" s="2">
-        <v>1739</v>
+        <v>2210</v>
       </c>
       <c r="G261" s="2" t="s">
         <v>15</v>
@@ -11927,7 +11927,7 @@
         <v>14</v>
       </c>
       <c r="F262" s="2">
-        <v>4758</v>
+        <v>4058</v>
       </c>
       <c r="G262" s="2" t="s">
         <v>15</v>
@@ -11959,7 +11959,7 @@
         <v>14</v>
       </c>
       <c r="F263" s="2">
-        <v>927</v>
+        <v>3371</v>
       </c>
       <c r="G263" s="2" t="s">
         <v>15</v>
@@ -11991,7 +11991,7 @@
         <v>14</v>
       </c>
       <c r="F264" s="2">
-        <v>1431</v>
+        <v>2332</v>
       </c>
       <c r="G264" s="2" t="s">
         <v>15</v>
@@ -12023,7 +12023,7 @@
         <v>14</v>
       </c>
       <c r="F265" s="2">
-        <v>826</v>
+        <v>1865</v>
       </c>
       <c r="G265" s="2" t="s">
         <v>15</v>
@@ -12055,7 +12055,7 @@
         <v>14</v>
       </c>
       <c r="F266" s="2">
-        <v>822</v>
+        <v>960</v>
       </c>
       <c r="G266" s="2" t="s">
         <v>15</v>
@@ -12087,7 +12087,7 @@
         <v>14</v>
       </c>
       <c r="F267" s="2">
-        <v>4296</v>
+        <v>1826</v>
       </c>
       <c r="G267" s="2" t="s">
         <v>15</v>
@@ -12119,7 +12119,7 @@
         <v>14</v>
       </c>
       <c r="F268" s="2">
-        <v>2582</v>
+        <v>4158</v>
       </c>
       <c r="G268" s="2" t="s">
         <v>15</v>
@@ -12151,7 +12151,7 @@
         <v>14</v>
       </c>
       <c r="F269" s="2">
-        <v>2330</v>
+        <v>1592</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>15</v>
@@ -12183,7 +12183,7 @@
         <v>14</v>
       </c>
       <c r="F270" s="2">
-        <v>841</v>
+        <v>3961</v>
       </c>
       <c r="G270" s="2" t="s">
         <v>15</v>
@@ -12215,7 +12215,7 @@
         <v>14</v>
       </c>
       <c r="F271" s="2">
-        <v>2716</v>
+        <v>2493</v>
       </c>
       <c r="G271" s="2" t="s">
         <v>15</v>
@@ -12247,7 +12247,7 @@
         <v>14</v>
       </c>
       <c r="F272" s="2">
-        <v>957</v>
+        <v>4144</v>
       </c>
       <c r="G272" s="2" t="s">
         <v>15</v>
@@ -12279,7 +12279,7 @@
         <v>14</v>
       </c>
       <c r="F273" s="2">
-        <v>2933</v>
+        <v>3286</v>
       </c>
       <c r="G273" s="2" t="s">
         <v>15</v>
@@ -12311,7 +12311,7 @@
         <v>14</v>
       </c>
       <c r="F274" s="2">
-        <v>3488</v>
+        <v>1684</v>
       </c>
       <c r="G274" s="2" t="s">
         <v>15</v>
@@ -12343,7 +12343,7 @@
         <v>14</v>
       </c>
       <c r="F275" s="2">
-        <v>3097</v>
+        <v>3830</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>15</v>
@@ -12375,7 +12375,7 @@
         <v>14</v>
       </c>
       <c r="F276" s="2">
-        <v>2739</v>
+        <v>2528</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>15</v>
@@ -12407,7 +12407,7 @@
         <v>14</v>
       </c>
       <c r="F277" s="2">
-        <v>4751</v>
+        <v>2505</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>15</v>
@@ -12439,7 +12439,7 @@
         <v>14</v>
       </c>
       <c r="F278" s="2">
-        <v>4024</v>
+        <v>2054</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>15</v>
@@ -12471,7 +12471,7 @@
         <v>14</v>
       </c>
       <c r="F279" s="2">
-        <v>2100</v>
+        <v>1296</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>15</v>
@@ -12503,7 +12503,7 @@
         <v>14</v>
       </c>
       <c r="F280" s="2">
-        <v>2890</v>
+        <v>4309</v>
       </c>
       <c r="G280" s="2" t="s">
         <v>15</v>
@@ -12535,7 +12535,7 @@
         <v>14</v>
       </c>
       <c r="F281" s="2">
-        <v>2401</v>
+        <v>833</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>15</v>
@@ -12567,7 +12567,7 @@
         <v>14</v>
       </c>
       <c r="F282" s="2">
-        <v>4060</v>
+        <v>3066</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>15</v>
@@ -12599,7 +12599,7 @@
         <v>14</v>
       </c>
       <c r="F283" s="2">
-        <v>3708</v>
+        <v>904</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>15</v>
@@ -12631,7 +12631,7 @@
         <v>14</v>
       </c>
       <c r="F284" s="2">
-        <v>3251</v>
+        <v>2481</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>15</v>
@@ -12663,7 +12663,7 @@
         <v>14</v>
       </c>
       <c r="F285" s="2">
-        <v>4463</v>
+        <v>2564</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>15</v>
@@ -12695,7 +12695,7 @@
         <v>14</v>
       </c>
       <c r="F286" s="2">
-        <v>4621</v>
+        <v>1666</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>15</v>
@@ -12727,7 +12727,7 @@
         <v>14</v>
       </c>
       <c r="F287" s="2">
-        <v>3086</v>
+        <v>1279</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>15</v>
@@ -12759,7 +12759,7 @@
         <v>14</v>
       </c>
       <c r="F288" s="2">
-        <v>4028</v>
+        <v>3490</v>
       </c>
       <c r="G288" s="2" t="s">
         <v>15</v>
@@ -12791,7 +12791,7 @@
         <v>14</v>
       </c>
       <c r="F289" s="2">
-        <v>1177</v>
+        <v>1556</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>15</v>
@@ -12823,7 +12823,7 @@
         <v>14</v>
       </c>
       <c r="F290" s="2">
-        <v>4298</v>
+        <v>2579</v>
       </c>
       <c r="G290" s="2" t="s">
         <v>15</v>
@@ -12855,7 +12855,7 @@
         <v>14</v>
       </c>
       <c r="F291" s="2">
-        <v>1251</v>
+        <v>3515</v>
       </c>
       <c r="G291" s="2" t="s">
         <v>15</v>
@@ -12887,7 +12887,7 @@
         <v>14</v>
       </c>
       <c r="F292" s="2">
-        <v>4263</v>
+        <v>2086</v>
       </c>
       <c r="G292" s="2" t="s">
         <v>15</v>
@@ -12919,7 +12919,7 @@
         <v>14</v>
       </c>
       <c r="F293" s="2">
-        <v>4292</v>
+        <v>3168</v>
       </c>
       <c r="G293" s="2" t="s">
         <v>15</v>
@@ -12951,7 +12951,7 @@
         <v>14</v>
       </c>
       <c r="F294" s="2">
-        <v>1784</v>
+        <v>3551</v>
       </c>
       <c r="G294" s="2" t="s">
         <v>15</v>
@@ -12983,7 +12983,7 @@
         <v>14</v>
       </c>
       <c r="F295" s="2">
-        <v>2427</v>
+        <v>1353</v>
       </c>
       <c r="G295" s="2" t="s">
         <v>15</v>
@@ -13015,7 +13015,7 @@
         <v>14</v>
       </c>
       <c r="F296" s="2">
-        <v>2227</v>
+        <v>1449</v>
       </c>
       <c r="G296" s="2" t="s">
         <v>15</v>
@@ -13047,7 +13047,7 @@
         <v>14</v>
       </c>
       <c r="F297" s="2">
-        <v>3599</v>
+        <v>3093</v>
       </c>
       <c r="G297" s="2" t="s">
         <v>15</v>
@@ -13079,7 +13079,7 @@
         <v>14</v>
       </c>
       <c r="F298" s="2">
-        <v>3154</v>
+        <v>3451</v>
       </c>
       <c r="G298" s="2" t="s">
         <v>15</v>
@@ -13111,7 +13111,7 @@
         <v>14</v>
       </c>
       <c r="F299" s="2">
-        <v>1437</v>
+        <v>4121</v>
       </c>
       <c r="G299" s="2" t="s">
         <v>15</v>
@@ -13143,7 +13143,7 @@
         <v>14</v>
       </c>
       <c r="F300" s="2">
-        <v>2150</v>
+        <v>2940</v>
       </c>
       <c r="G300" s="2" t="s">
         <v>15</v>
@@ -13175,7 +13175,7 @@
         <v>14</v>
       </c>
       <c r="F301" s="2">
-        <v>1423</v>
+        <v>2306</v>
       </c>
       <c r="G301" s="2" t="s">
         <v>15</v>
@@ -13207,7 +13207,7 @@
         <v>14</v>
       </c>
       <c r="F302" s="2">
-        <v>1728</v>
+        <v>2667</v>
       </c>
       <c r="G302" s="2" t="s">
         <v>15</v>
@@ -13239,7 +13239,7 @@
         <v>14</v>
       </c>
       <c r="F303" s="2">
-        <v>3828</v>
+        <v>869</v>
       </c>
       <c r="G303" s="2" t="s">
         <v>15</v>
@@ -13271,7 +13271,7 @@
         <v>14</v>
       </c>
       <c r="F304" s="2">
-        <v>4453</v>
+        <v>4057</v>
       </c>
       <c r="G304" s="2" t="s">
         <v>15</v>
@@ -13303,7 +13303,7 @@
         <v>14</v>
       </c>
       <c r="F305" s="2">
-        <v>2150</v>
+        <v>4543</v>
       </c>
       <c r="G305" s="2" t="s">
         <v>15</v>
@@ -13335,7 +13335,7 @@
         <v>14</v>
       </c>
       <c r="F306" s="2">
-        <v>2421</v>
+        <v>4102</v>
       </c>
       <c r="G306" s="2" t="s">
         <v>15</v>
@@ -13367,7 +13367,7 @@
         <v>14</v>
       </c>
       <c r="F307" s="2">
-        <v>2536</v>
+        <v>1867</v>
       </c>
       <c r="G307" s="2" t="s">
         <v>15</v>
@@ -13399,7 +13399,7 @@
         <v>14</v>
       </c>
       <c r="F308" s="2">
-        <v>3369</v>
+        <v>2677</v>
       </c>
       <c r="G308" s="2" t="s">
         <v>15</v>
@@ -13431,7 +13431,7 @@
         <v>14</v>
       </c>
       <c r="F309" s="2">
-        <v>2054</v>
+        <v>1414</v>
       </c>
       <c r="G309" s="2" t="s">
         <v>15</v>
@@ -13463,7 +13463,7 @@
         <v>14</v>
       </c>
       <c r="F310" s="2">
-        <v>1453</v>
+        <v>2473</v>
       </c>
       <c r="G310" s="2" t="s">
         <v>15</v>
@@ -13495,7 +13495,7 @@
         <v>14</v>
       </c>
       <c r="F311" s="2">
-        <v>4335</v>
+        <v>3324</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>15</v>
@@ -13527,7 +13527,7 @@
         <v>14</v>
       </c>
       <c r="F312" s="2">
-        <v>1619</v>
+        <v>4470</v>
       </c>
       <c r="G312" s="2" t="s">
         <v>15</v>
@@ -13559,7 +13559,7 @@
         <v>14</v>
       </c>
       <c r="F313" s="2">
-        <v>4763</v>
+        <v>2481</v>
       </c>
       <c r="G313" s="2" t="s">
         <v>15</v>
@@ -13591,7 +13591,7 @@
         <v>14</v>
       </c>
       <c r="F314" s="2">
-        <v>1616</v>
+        <v>2745</v>
       </c>
       <c r="G314" s="2" t="s">
         <v>15</v>
@@ -13623,7 +13623,7 @@
         <v>14</v>
       </c>
       <c r="F315" s="2">
-        <v>2152</v>
+        <v>2046</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>15</v>
@@ -13655,7 +13655,7 @@
         <v>14</v>
       </c>
       <c r="F316" s="2">
-        <v>3690</v>
+        <v>1166</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>15</v>
@@ -13687,7 +13687,7 @@
         <v>14</v>
       </c>
       <c r="F317" s="2">
-        <v>3352</v>
+        <v>3355</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>15</v>
@@ -13719,7 +13719,7 @@
         <v>14</v>
       </c>
       <c r="F318" s="2">
-        <v>3335</v>
+        <v>4099</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>15</v>
@@ -13751,7 +13751,7 @@
         <v>14</v>
       </c>
       <c r="F319" s="2">
-        <v>1542</v>
+        <v>2144</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>15</v>
@@ -13783,7 +13783,7 @@
         <v>14</v>
       </c>
       <c r="F320" s="2">
-        <v>3315</v>
+        <v>4552</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>15</v>
@@ -13815,7 +13815,7 @@
         <v>14</v>
       </c>
       <c r="F321" s="2">
-        <v>2416</v>
+        <v>949</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>15</v>
@@ -13847,7 +13847,7 @@
         <v>14</v>
       </c>
       <c r="F322" s="2">
-        <v>1375</v>
+        <v>2591</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>15</v>
@@ -13879,7 +13879,7 @@
         <v>14</v>
       </c>
       <c r="F323" s="2">
-        <v>4729</v>
+        <v>4026</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>15</v>
@@ -13911,7 +13911,7 @@
         <v>14</v>
       </c>
       <c r="F324" s="2">
-        <v>4734</v>
+        <v>4046</v>
       </c>
       <c r="G324" s="2" t="s">
         <v>15</v>
@@ -13943,7 +13943,7 @@
         <v>14</v>
       </c>
       <c r="F325" s="2">
-        <v>2035</v>
+        <v>3840</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>15</v>
@@ -13975,7 +13975,7 @@
         <v>14</v>
       </c>
       <c r="F326" s="2">
-        <v>3742</v>
+        <v>2863</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>15</v>
@@ -14007,7 +14007,7 @@
         <v>14</v>
       </c>
       <c r="F327" s="2">
-        <v>1745</v>
+        <v>2042</v>
       </c>
       <c r="G327" s="2" t="s">
         <v>15</v>
@@ -14039,7 +14039,7 @@
         <v>14</v>
       </c>
       <c r="F328" s="2">
-        <v>800</v>
+        <v>1592</v>
       </c>
       <c r="G328" s="2" t="s">
         <v>15</v>
@@ -14071,7 +14071,7 @@
         <v>14</v>
       </c>
       <c r="F329" s="2">
-        <v>3318</v>
+        <v>1848</v>
       </c>
       <c r="G329" s="2" t="s">
         <v>15</v>
@@ -14103,7 +14103,7 @@
         <v>14</v>
       </c>
       <c r="F330" s="2">
-        <v>3474</v>
+        <v>2479</v>
       </c>
       <c r="G330" s="2" t="s">
         <v>15</v>
@@ -14135,7 +14135,7 @@
         <v>14</v>
       </c>
       <c r="F331" s="2">
-        <v>4340</v>
+        <v>3522</v>
       </c>
       <c r="G331" s="2" t="s">
         <v>15</v>
@@ -14167,7 +14167,7 @@
         <v>14</v>
       </c>
       <c r="F332" s="2">
-        <v>3273</v>
+        <v>1722</v>
       </c>
       <c r="G332" s="2" t="s">
         <v>15</v>
@@ -14199,7 +14199,7 @@
         <v>14</v>
       </c>
       <c r="F333" s="2">
-        <v>3067</v>
+        <v>1423</v>
       </c>
       <c r="G333" s="2" t="s">
         <v>15</v>
@@ -14231,7 +14231,7 @@
         <v>14</v>
       </c>
       <c r="F334" s="2">
-        <v>2701</v>
+        <v>2902</v>
       </c>
       <c r="G334" s="2" t="s">
         <v>15</v>
@@ -14263,7 +14263,7 @@
         <v>14</v>
       </c>
       <c r="F335" s="2">
-        <v>4780</v>
+        <v>1906</v>
       </c>
       <c r="G335" s="2" t="s">
         <v>15</v>
@@ -14295,7 +14295,7 @@
         <v>14</v>
       </c>
       <c r="F336" s="2">
-        <v>816</v>
+        <v>4559</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>15</v>
@@ -14327,7 +14327,7 @@
         <v>14</v>
       </c>
       <c r="F337" s="2">
-        <v>1903</v>
+        <v>3956</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>15</v>
@@ -14359,7 +14359,7 @@
         <v>14</v>
       </c>
       <c r="F338" s="2">
-        <v>3473</v>
+        <v>2261</v>
       </c>
       <c r="G338" s="2" t="s">
         <v>15</v>
@@ -14391,7 +14391,7 @@
         <v>14</v>
       </c>
       <c r="F339" s="2">
-        <v>2179</v>
+        <v>2530</v>
       </c>
       <c r="G339" s="2" t="s">
         <v>15</v>
@@ -14423,7 +14423,7 @@
         <v>14</v>
       </c>
       <c r="F340" s="2">
-        <v>1645</v>
+        <v>3366</v>
       </c>
       <c r="G340" s="2" t="s">
         <v>15</v>
@@ -14455,7 +14455,7 @@
         <v>14</v>
       </c>
       <c r="F341" s="2">
-        <v>1821</v>
+        <v>1426</v>
       </c>
       <c r="G341" s="2" t="s">
         <v>15</v>
@@ -14487,7 +14487,7 @@
         <v>14</v>
       </c>
       <c r="F342" s="2">
-        <v>4539</v>
+        <v>918</v>
       </c>
       <c r="G342" s="2" t="s">
         <v>15</v>
@@ -14519,7 +14519,7 @@
         <v>14</v>
       </c>
       <c r="F343" s="2">
-        <v>1727</v>
+        <v>4398</v>
       </c>
       <c r="G343" s="2" t="s">
         <v>15</v>
@@ -14551,7 +14551,7 @@
         <v>14</v>
       </c>
       <c r="F344" s="2">
-        <v>1231</v>
+        <v>3941</v>
       </c>
       <c r="G344" s="2" t="s">
         <v>15</v>
@@ -14583,7 +14583,7 @@
         <v>14</v>
       </c>
       <c r="F345" s="2">
-        <v>3085</v>
+        <v>1690</v>
       </c>
       <c r="G345" s="2" t="s">
         <v>15</v>
@@ -14615,7 +14615,7 @@
         <v>14</v>
       </c>
       <c r="F346" s="2">
-        <v>2070</v>
+        <v>2532</v>
       </c>
       <c r="G346" s="2" t="s">
         <v>15</v>
@@ -14647,7 +14647,7 @@
         <v>14</v>
       </c>
       <c r="F347" s="2">
-        <v>2552</v>
+        <v>1202</v>
       </c>
       <c r="G347" s="2" t="s">
         <v>15</v>
@@ -14679,7 +14679,7 @@
         <v>14</v>
       </c>
       <c r="F348" s="2">
-        <v>1087</v>
+        <v>2500</v>
       </c>
       <c r="G348" s="2" t="s">
         <v>15</v>
@@ -14711,7 +14711,7 @@
         <v>14</v>
       </c>
       <c r="F349" s="2">
-        <v>3983</v>
+        <v>3768</v>
       </c>
       <c r="G349" s="2" t="s">
         <v>15</v>
@@ -14743,7 +14743,7 @@
         <v>14</v>
       </c>
       <c r="F350" s="2">
-        <v>4194</v>
+        <v>1761</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>15</v>
@@ -14775,7 +14775,7 @@
         <v>14</v>
       </c>
       <c r="F351" s="2">
-        <v>3891</v>
+        <v>1855</v>
       </c>
       <c r="G351" s="2" t="s">
         <v>15</v>
@@ -14807,7 +14807,7 @@
         <v>14</v>
       </c>
       <c r="F352" s="2">
-        <v>2723</v>
+        <v>2065</v>
       </c>
       <c r="G352" s="2" t="s">
         <v>15</v>
@@ -14839,7 +14839,7 @@
         <v>14</v>
       </c>
       <c r="F353" s="2">
-        <v>2547</v>
+        <v>4516</v>
       </c>
       <c r="G353" s="2" t="s">
         <v>15</v>
@@ -14871,7 +14871,7 @@
         <v>14</v>
       </c>
       <c r="F354" s="2">
-        <v>3323</v>
+        <v>3507</v>
       </c>
       <c r="G354" s="2" t="s">
         <v>15</v>
@@ -14903,7 +14903,7 @@
         <v>14</v>
       </c>
       <c r="F355" s="2">
-        <v>2343</v>
+        <v>1780</v>
       </c>
       <c r="G355" s="2" t="s">
         <v>15</v>
@@ -14935,7 +14935,7 @@
         <v>14</v>
       </c>
       <c r="F356" s="2">
-        <v>2047</v>
+        <v>801</v>
       </c>
       <c r="G356" s="2" t="s">
         <v>15</v>
@@ -14967,7 +14967,7 @@
         <v>14</v>
       </c>
       <c r="F357" s="2">
-        <v>4203</v>
+        <v>3893</v>
       </c>
       <c r="G357" s="2" t="s">
         <v>15</v>
@@ -14999,7 +14999,7 @@
         <v>14</v>
       </c>
       <c r="F358" s="2">
-        <v>2190</v>
+        <v>2884</v>
       </c>
       <c r="G358" s="2" t="s">
         <v>15</v>
@@ -15031,7 +15031,7 @@
         <v>14</v>
       </c>
       <c r="F359" s="2">
-        <v>3093</v>
+        <v>4095</v>
       </c>
       <c r="G359" s="2" t="s">
         <v>15</v>
@@ -15063,7 +15063,7 @@
         <v>14</v>
       </c>
       <c r="F360" s="2">
-        <v>4557</v>
+        <v>1561</v>
       </c>
       <c r="G360" s="2" t="s">
         <v>15</v>
@@ -15095,7 +15095,7 @@
         <v>14</v>
       </c>
       <c r="F361" s="2">
-        <v>2738</v>
+        <v>1778</v>
       </c>
       <c r="G361" s="2" t="s">
         <v>15</v>
@@ -15127,7 +15127,7 @@
         <v>14</v>
       </c>
       <c r="F362" s="2">
-        <v>2733</v>
+        <v>4231</v>
       </c>
       <c r="G362" s="2" t="s">
         <v>15</v>
@@ -15159,7 +15159,7 @@
         <v>14</v>
       </c>
       <c r="F363" s="2">
-        <v>1853</v>
+        <v>2692</v>
       </c>
       <c r="G363" s="2" t="s">
         <v>15</v>
@@ -15191,7 +15191,7 @@
         <v>14</v>
       </c>
       <c r="F364" s="2">
-        <v>1191</v>
+        <v>3820</v>
       </c>
       <c r="G364" s="2" t="s">
         <v>15</v>
@@ -15223,7 +15223,7 @@
         <v>14</v>
       </c>
       <c r="F365" s="2">
-        <v>4736</v>
+        <v>3692</v>
       </c>
       <c r="G365" s="2" t="s">
         <v>15</v>
@@ -15255,7 +15255,7 @@
         <v>14</v>
       </c>
       <c r="F366" s="2">
-        <v>4082</v>
+        <v>1735</v>
       </c>
       <c r="G366" s="2" t="s">
         <v>15</v>
@@ -15287,7 +15287,7 @@
         <v>14</v>
       </c>
       <c r="F367" s="2">
-        <v>3587</v>
+        <v>3176</v>
       </c>
       <c r="G367" s="2" t="s">
         <v>15</v>
@@ -15319,7 +15319,7 @@
         <v>14</v>
       </c>
       <c r="F368" s="2">
-        <v>2399</v>
+        <v>1798</v>
       </c>
       <c r="G368" s="2" t="s">
         <v>15</v>
@@ -15351,7 +15351,7 @@
         <v>14</v>
       </c>
       <c r="F369" s="2">
-        <v>859</v>
+        <v>1883</v>
       </c>
       <c r="G369" s="2" t="s">
         <v>15</v>
@@ -15383,7 +15383,7 @@
         <v>14</v>
       </c>
       <c r="F370" s="2">
-        <v>2371</v>
+        <v>1857</v>
       </c>
       <c r="G370" s="2" t="s">
         <v>15</v>
@@ -15415,7 +15415,7 @@
         <v>14</v>
       </c>
       <c r="F371" s="2">
-        <v>1934</v>
+        <v>3534</v>
       </c>
       <c r="G371" s="2" t="s">
         <v>15</v>
@@ -15447,7 +15447,7 @@
         <v>14</v>
       </c>
       <c r="F372" s="2">
-        <v>3709</v>
+        <v>1453</v>
       </c>
       <c r="G372" s="2" t="s">
         <v>15</v>
@@ -15479,7 +15479,7 @@
         <v>14</v>
       </c>
       <c r="F373" s="2">
-        <v>4011</v>
+        <v>3725</v>
       </c>
       <c r="G373" s="2" t="s">
         <v>15</v>
@@ -15511,7 +15511,7 @@
         <v>14</v>
       </c>
       <c r="F374" s="2">
-        <v>4777</v>
+        <v>2002</v>
       </c>
       <c r="G374" s="2" t="s">
         <v>15</v>
@@ -15543,7 +15543,7 @@
         <v>14</v>
       </c>
       <c r="F375" s="2">
-        <v>2664</v>
+        <v>2989</v>
       </c>
       <c r="G375" s="2" t="s">
         <v>15</v>
@@ -15575,7 +15575,7 @@
         <v>14</v>
       </c>
       <c r="F376" s="2">
-        <v>2114</v>
+        <v>2420</v>
       </c>
       <c r="G376" s="2" t="s">
         <v>15</v>
@@ -15607,7 +15607,7 @@
         <v>14</v>
       </c>
       <c r="F377" s="2">
-        <v>2957</v>
+        <v>2380</v>
       </c>
       <c r="G377" s="2" t="s">
         <v>15</v>
@@ -15639,7 +15639,7 @@
         <v>14</v>
       </c>
       <c r="F378" s="2">
-        <v>4148</v>
+        <v>1841</v>
       </c>
       <c r="G378" s="2" t="s">
         <v>15</v>
@@ -15671,7 +15671,7 @@
         <v>14</v>
       </c>
       <c r="F379" s="2">
-        <v>2634</v>
+        <v>3666</v>
       </c>
       <c r="G379" s="2" t="s">
         <v>15</v>
@@ -15703,7 +15703,7 @@
         <v>14</v>
       </c>
       <c r="F380" s="2">
-        <v>3368</v>
+        <v>3075</v>
       </c>
       <c r="G380" s="2" t="s">
         <v>15</v>
@@ -15735,7 +15735,7 @@
         <v>14</v>
       </c>
       <c r="F381" s="2">
-        <v>1149</v>
+        <v>2687</v>
       </c>
       <c r="G381" s="2" t="s">
         <v>15</v>
@@ -15767,7 +15767,7 @@
         <v>14</v>
       </c>
       <c r="F382" s="2">
-        <v>3997</v>
+        <v>2740</v>
       </c>
       <c r="G382" s="2" t="s">
         <v>15</v>
@@ -15799,7 +15799,7 @@
         <v>14</v>
       </c>
       <c r="F383" s="2">
-        <v>2040</v>
+        <v>3